--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="924">
   <si>
     <t>ID</t>
   </si>
@@ -2539,6 +2539,9 @@
     <t>地狱狼王</t>
   </si>
   <si>
+    <t>1000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
     <t>410000000000</t>
   </si>
   <si>
@@ -2551,6 +2554,12 @@
     <t>地狱沙虫王</t>
   </si>
   <si>
+    <t>900000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>20000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
     <t>420000000000</t>
   </si>
   <si>
@@ -2563,6 +2572,12 @@
     <t>地狱鹰王</t>
   </si>
   <si>
+    <t>9000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>400000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
     <t>430000000000</t>
   </si>
   <si>
@@ -2575,6 +2590,12 @@
     <t>地狱角虫王</t>
   </si>
   <si>
+    <t>90000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>8000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
     <t>440000000000</t>
   </si>
   <si>
@@ -2585,6 +2606,12 @@
   </si>
   <si>
     <t>地狱蜈蚣王</t>
+  </si>
+  <si>
+    <t>900000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>160000000000000000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
     <t>450000000000</t>
@@ -3821,7 +3848,7 @@
     <col min="5" max="5" width="6.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
     <col min="7" max="8" width="39.75" style="3" customWidth="1"/>
-    <col min="9" max="9" width="49.625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="50.75" style="3" customWidth="1"/>
     <col min="10" max="10" width="15.875" style="3" customWidth="1"/>
     <col min="11" max="13" width="12.125" style="3" customWidth="1"/>
     <col min="14" max="14" width="9.625" style="3" customWidth="1"/>
@@ -10545,23 +10572,23 @@
         <v>764</v>
       </c>
       <c r="J112" s="1">
-        <f t="shared" ref="J112:J145" si="34">J111+100</f>
+        <f>J111+100</f>
         <v>1600</v>
       </c>
       <c r="K112" s="1">
-        <f t="shared" ref="K112:K145" si="35">K111+100</f>
+        <f>K111+100</f>
         <v>1300</v>
       </c>
       <c r="L112" s="1">
-        <f t="shared" ref="L112:L145" si="36">L111+50</f>
+        <f t="shared" ref="L112:L145" si="34">L111+50</f>
         <v>1050</v>
       </c>
       <c r="M112" s="1">
-        <f t="shared" ref="M112:M145" si="37">M111+50</f>
+        <f t="shared" ref="M112:M145" si="35">M111+50</f>
         <v>1050</v>
       </c>
       <c r="N112" s="3">
-        <f t="shared" ref="N112:N145" si="38">N111+1</f>
+        <f t="shared" ref="N112:N145" si="36">N111+1</f>
         <v>36</v>
       </c>
       <c r="O112" s="6">
@@ -10608,23 +10635,23 @@
         <v>770</v>
       </c>
       <c r="J113" s="1">
+        <f>J112+100</f>
+        <v>1700</v>
+      </c>
+      <c r="K113" s="1">
+        <f>K112+100</f>
+        <v>1400</v>
+      </c>
+      <c r="L113" s="1">
         <f t="shared" si="34"/>
-        <v>1700</v>
-      </c>
-      <c r="K113" s="1">
+        <v>1100</v>
+      </c>
+      <c r="M113" s="1">
         <f t="shared" si="35"/>
-        <v>1400</v>
-      </c>
-      <c r="L113" s="1">
+        <v>1100</v>
+      </c>
+      <c r="N113" s="3">
         <f t="shared" si="36"/>
-        <v>1100</v>
-      </c>
-      <c r="M113" s="1">
-        <f t="shared" si="37"/>
-        <v>1100</v>
-      </c>
-      <c r="N113" s="3">
-        <f t="shared" si="38"/>
         <v>37</v>
       </c>
       <c r="O113" s="6">
@@ -10671,23 +10698,23 @@
         <v>776</v>
       </c>
       <c r="J114" s="1">
+        <f>J113+100</f>
+        <v>1800</v>
+      </c>
+      <c r="K114" s="1">
+        <f>K113+100</f>
+        <v>1500</v>
+      </c>
+      <c r="L114" s="1">
         <f t="shared" si="34"/>
-        <v>1800</v>
-      </c>
-      <c r="K114" s="1">
+        <v>1150</v>
+      </c>
+      <c r="M114" s="1">
         <f t="shared" si="35"/>
-        <v>1500</v>
-      </c>
-      <c r="L114" s="1">
+        <v>1150</v>
+      </c>
+      <c r="N114" s="3">
         <f t="shared" si="36"/>
-        <v>1150</v>
-      </c>
-      <c r="M114" s="1">
-        <f t="shared" si="37"/>
-        <v>1150</v>
-      </c>
-      <c r="N114" s="3">
-        <f t="shared" si="38"/>
         <v>38</v>
       </c>
       <c r="O114" s="6">
@@ -10734,23 +10761,23 @@
         <v>782</v>
       </c>
       <c r="J115" s="1">
+        <f>J114+100</f>
+        <v>1900</v>
+      </c>
+      <c r="K115" s="1">
+        <f>K114+100</f>
+        <v>1600</v>
+      </c>
+      <c r="L115" s="1">
         <f t="shared" si="34"/>
-        <v>1900</v>
-      </c>
-      <c r="K115" s="1">
+        <v>1200</v>
+      </c>
+      <c r="M115" s="1">
         <f t="shared" si="35"/>
-        <v>1600</v>
-      </c>
-      <c r="L115" s="1">
+        <v>1200</v>
+      </c>
+      <c r="N115" s="3">
         <f t="shared" si="36"/>
-        <v>1200</v>
-      </c>
-      <c r="M115" s="1">
-        <f t="shared" si="37"/>
-        <v>1200</v>
-      </c>
-      <c r="N115" s="3">
-        <f t="shared" si="38"/>
         <v>39</v>
       </c>
       <c r="O115" s="6">
@@ -10797,23 +10824,23 @@
         <v>788</v>
       </c>
       <c r="J116" s="1">
+        <f t="shared" ref="J116:J145" si="37">J115+200</f>
+        <v>2100</v>
+      </c>
+      <c r="K116" s="1">
+        <f t="shared" ref="K116:K145" si="38">K115+300</f>
+        <v>1900</v>
+      </c>
+      <c r="L116" s="1">
         <f t="shared" si="34"/>
-        <v>2000</v>
-      </c>
-      <c r="K116" s="1">
+        <v>1250</v>
+      </c>
+      <c r="M116" s="1">
         <f t="shared" si="35"/>
-        <v>1700</v>
-      </c>
-      <c r="L116" s="1">
+        <v>1250</v>
+      </c>
+      <c r="N116" s="3">
         <f t="shared" si="36"/>
-        <v>1250</v>
-      </c>
-      <c r="M116" s="1">
-        <f t="shared" si="37"/>
-        <v>1250</v>
-      </c>
-      <c r="N116" s="3">
-        <f t="shared" si="38"/>
         <v>40</v>
       </c>
       <c r="O116" s="6">
@@ -10862,23 +10889,23 @@
         <v>794</v>
       </c>
       <c r="J117" s="1">
+        <f t="shared" si="37"/>
+        <v>2300</v>
+      </c>
+      <c r="K117" s="1">
+        <f t="shared" si="38"/>
+        <v>2200</v>
+      </c>
+      <c r="L117" s="1">
         <f t="shared" si="34"/>
-        <v>2100</v>
-      </c>
-      <c r="K117" s="1">
+        <v>1300</v>
+      </c>
+      <c r="M117" s="1">
         <f t="shared" si="35"/>
-        <v>1800</v>
-      </c>
-      <c r="L117" s="1">
+        <v>1300</v>
+      </c>
+      <c r="N117" s="3">
         <f t="shared" si="36"/>
-        <v>1300</v>
-      </c>
-      <c r="M117" s="1">
-        <f t="shared" si="37"/>
-        <v>1300</v>
-      </c>
-      <c r="N117" s="3">
-        <f t="shared" si="38"/>
         <v>41</v>
       </c>
       <c r="O117" s="6">
@@ -10927,23 +10954,23 @@
         <v>800</v>
       </c>
       <c r="J118" s="1">
+        <f t="shared" si="37"/>
+        <v>2500</v>
+      </c>
+      <c r="K118" s="1">
+        <f t="shared" si="38"/>
+        <v>2500</v>
+      </c>
+      <c r="L118" s="1">
         <f t="shared" si="34"/>
-        <v>2200</v>
-      </c>
-      <c r="K118" s="1">
+        <v>1350</v>
+      </c>
+      <c r="M118" s="1">
         <f t="shared" si="35"/>
-        <v>1900</v>
-      </c>
-      <c r="L118" s="1">
+        <v>1350</v>
+      </c>
+      <c r="N118" s="3">
         <f t="shared" si="36"/>
-        <v>1350</v>
-      </c>
-      <c r="M118" s="1">
-        <f t="shared" si="37"/>
-        <v>1350</v>
-      </c>
-      <c r="N118" s="3">
-        <f t="shared" si="38"/>
         <v>42</v>
       </c>
       <c r="O118" s="6">
@@ -10992,23 +11019,23 @@
         <v>806</v>
       </c>
       <c r="J119" s="1">
+        <f t="shared" si="37"/>
+        <v>2700</v>
+      </c>
+      <c r="K119" s="1">
+        <f t="shared" si="38"/>
+        <v>2800</v>
+      </c>
+      <c r="L119" s="1">
         <f t="shared" si="34"/>
-        <v>2300</v>
-      </c>
-      <c r="K119" s="1">
+        <v>1400</v>
+      </c>
+      <c r="M119" s="1">
         <f t="shared" si="35"/>
-        <v>2000</v>
-      </c>
-      <c r="L119" s="1">
+        <v>1400</v>
+      </c>
+      <c r="N119" s="3">
         <f t="shared" si="36"/>
-        <v>1400</v>
-      </c>
-      <c r="M119" s="1">
-        <f t="shared" si="37"/>
-        <v>1400</v>
-      </c>
-      <c r="N119" s="3">
-        <f t="shared" si="38"/>
         <v>43</v>
       </c>
       <c r="O119" s="6">
@@ -11057,23 +11084,23 @@
         <v>812</v>
       </c>
       <c r="J120" s="1">
+        <f t="shared" si="37"/>
+        <v>2900</v>
+      </c>
+      <c r="K120" s="1">
+        <f t="shared" si="38"/>
+        <v>3100</v>
+      </c>
+      <c r="L120" s="1">
         <f t="shared" si="34"/>
-        <v>2400</v>
-      </c>
-      <c r="K120" s="1">
+        <v>1450</v>
+      </c>
+      <c r="M120" s="1">
         <f t="shared" si="35"/>
-        <v>2100</v>
-      </c>
-      <c r="L120" s="1">
+        <v>1450</v>
+      </c>
+      <c r="N120" s="3">
         <f t="shared" si="36"/>
-        <v>1450</v>
-      </c>
-      <c r="M120" s="1">
-        <f t="shared" si="37"/>
-        <v>1450</v>
-      </c>
-      <c r="N120" s="3">
-        <f t="shared" si="38"/>
         <v>44</v>
       </c>
       <c r="O120" s="6">
@@ -11098,10 +11125,10 @@
       <c r="W120" s="3"/>
     </row>
     <row r="121" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A121" s="3" t="s">
+      <c r="A121" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="B121" s="1" t="s">
         <v>814</v>
       </c>
       <c r="C121" s="1" t="s">
@@ -11116,33 +11143,33 @@
       <c r="F121" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="G121" s="4">
-        <v>1</v>
-      </c>
-      <c r="H121" s="4">
-        <v>1</v>
-      </c>
-      <c r="I121" s="4">
-        <v>1</v>
+      <c r="G121" s="12" t="s">
+        <v>758</v>
+      </c>
+      <c r="H121" s="11" t="s">
+        <v>758</v>
+      </c>
+      <c r="I121" s="13" t="s">
+        <v>818</v>
       </c>
       <c r="J121" s="1">
+        <f t="shared" si="37"/>
+        <v>3100</v>
+      </c>
+      <c r="K121" s="1">
+        <f t="shared" si="38"/>
+        <v>3400</v>
+      </c>
+      <c r="L121" s="1">
         <f t="shared" si="34"/>
-        <v>2500</v>
-      </c>
-      <c r="K121" s="1">
+        <v>1500</v>
+      </c>
+      <c r="M121" s="1">
         <f t="shared" si="35"/>
-        <v>2200</v>
-      </c>
-      <c r="L121" s="1">
+        <v>1500</v>
+      </c>
+      <c r="N121" s="3">
         <f t="shared" si="36"/>
-        <v>1500</v>
-      </c>
-      <c r="M121" s="1">
-        <f t="shared" si="37"/>
-        <v>1500</v>
-      </c>
-      <c r="N121" s="3">
-        <f t="shared" si="38"/>
         <v>45</v>
       </c>
       <c r="O121" s="6">
@@ -11152,10 +11179,10 @@
         <v>90</v>
       </c>
       <c r="Q121" s="11" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="R121" s="11" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="T121" s="1" t="s">
         <v>151</v>
@@ -11167,51 +11194,51 @@
       <c r="W121" s="3"/>
     </row>
     <row r="122" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A122" s="3" t="s">
+      <c r="A122" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="B122" s="1" t="s">
         <v>814</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E122" s="1">
         <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="G122" s="4">
-        <v>1</v>
-      </c>
-      <c r="H122" s="4">
-        <v>1</v>
-      </c>
-      <c r="I122" s="4">
-        <v>1</v>
+        <v>822</v>
+      </c>
+      <c r="G122" s="12" t="s">
+        <v>823</v>
+      </c>
+      <c r="H122" s="11" t="s">
+        <v>823</v>
+      </c>
+      <c r="I122" s="13" t="s">
+        <v>824</v>
       </c>
       <c r="J122" s="1">
+        <f t="shared" si="37"/>
+        <v>3300</v>
+      </c>
+      <c r="K122" s="1">
+        <f t="shared" si="38"/>
+        <v>3700</v>
+      </c>
+      <c r="L122" s="1">
         <f t="shared" si="34"/>
-        <v>2600</v>
-      </c>
-      <c r="K122" s="1">
+        <v>1550</v>
+      </c>
+      <c r="M122" s="1">
         <f t="shared" si="35"/>
-        <v>2300</v>
-      </c>
-      <c r="L122" s="1">
+        <v>1550</v>
+      </c>
+      <c r="N122" s="3">
         <f t="shared" si="36"/>
-        <v>1550</v>
-      </c>
-      <c r="M122" s="1">
-        <f t="shared" si="37"/>
-        <v>1550</v>
-      </c>
-      <c r="N122" s="3">
-        <f t="shared" si="38"/>
         <v>46</v>
       </c>
       <c r="O122" s="6">
@@ -11221,10 +11248,10 @@
         <v>90</v>
       </c>
       <c r="Q122" s="11" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="R122" s="11" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="T122" s="1" t="s">
         <v>151</v>
@@ -11236,51 +11263,51 @@
       <c r="W122" s="3"/>
     </row>
     <row r="123" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A123" s="3" t="s">
+      <c r="A123" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" s="1" t="s">
         <v>814</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="E123" s="1">
         <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>825</v>
-      </c>
-      <c r="G123" s="4">
-        <v>1</v>
-      </c>
-      <c r="H123" s="4">
-        <v>1</v>
-      </c>
-      <c r="I123" s="4">
-        <v>1</v>
+        <v>828</v>
+      </c>
+      <c r="G123" s="12" t="s">
+        <v>829</v>
+      </c>
+      <c r="H123" s="11" t="s">
+        <v>829</v>
+      </c>
+      <c r="I123" s="13" t="s">
+        <v>830</v>
       </c>
       <c r="J123" s="1">
+        <f t="shared" si="37"/>
+        <v>3500</v>
+      </c>
+      <c r="K123" s="1">
+        <f t="shared" si="38"/>
+        <v>4000</v>
+      </c>
+      <c r="L123" s="1">
         <f t="shared" si="34"/>
-        <v>2700</v>
-      </c>
-      <c r="K123" s="1">
+        <v>1600</v>
+      </c>
+      <c r="M123" s="1">
         <f t="shared" si="35"/>
-        <v>2400</v>
-      </c>
-      <c r="L123" s="1">
+        <v>1600</v>
+      </c>
+      <c r="N123" s="3">
         <f t="shared" si="36"/>
-        <v>1600</v>
-      </c>
-      <c r="M123" s="1">
-        <f t="shared" si="37"/>
-        <v>1600</v>
-      </c>
-      <c r="N123" s="3">
-        <f t="shared" si="38"/>
         <v>47</v>
       </c>
       <c r="O123" s="6">
@@ -11290,10 +11317,10 @@
         <v>90</v>
       </c>
       <c r="Q123" s="11" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="R123" s="11" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="T123" s="1" t="s">
         <v>151</v>
@@ -11305,51 +11332,51 @@
       <c r="W123" s="3"/>
     </row>
     <row r="124" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A124" s="3" t="s">
+      <c r="A124" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="B124" s="1" t="s">
         <v>814</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="E124" s="1">
         <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="G124" s="4">
-        <v>1</v>
-      </c>
-      <c r="H124" s="4">
-        <v>1</v>
-      </c>
-      <c r="I124" s="4">
-        <v>1</v>
+        <v>834</v>
+      </c>
+      <c r="G124" s="12" t="s">
+        <v>835</v>
+      </c>
+      <c r="H124" s="11" t="s">
+        <v>835</v>
+      </c>
+      <c r="I124" s="13" t="s">
+        <v>836</v>
       </c>
       <c r="J124" s="1">
+        <f t="shared" si="37"/>
+        <v>3700</v>
+      </c>
+      <c r="K124" s="1">
+        <f t="shared" si="38"/>
+        <v>4300</v>
+      </c>
+      <c r="L124" s="1">
         <f t="shared" si="34"/>
-        <v>2800</v>
-      </c>
-      <c r="K124" s="1">
+        <v>1650</v>
+      </c>
+      <c r="M124" s="1">
         <f t="shared" si="35"/>
-        <v>2500</v>
-      </c>
-      <c r="L124" s="1">
+        <v>1650</v>
+      </c>
+      <c r="N124" s="3">
         <f t="shared" si="36"/>
-        <v>1650</v>
-      </c>
-      <c r="M124" s="1">
-        <f t="shared" si="37"/>
-        <v>1650</v>
-      </c>
-      <c r="N124" s="3">
-        <f t="shared" si="38"/>
         <v>48</v>
       </c>
       <c r="O124" s="6">
@@ -11359,10 +11386,10 @@
         <v>90</v>
       </c>
       <c r="Q124" s="11" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="R124" s="11" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="T124" s="1" t="s">
         <v>151</v>
@@ -11374,51 +11401,51 @@
       <c r="W124" s="3"/>
     </row>
     <row r="125" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A125" s="3" t="s">
+      <c r="A125" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B125" s="1" t="s">
         <v>814</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="E125" s="1">
         <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>833</v>
-      </c>
-      <c r="G125" s="4">
-        <v>1</v>
-      </c>
-      <c r="H125" s="4">
-        <v>1</v>
-      </c>
-      <c r="I125" s="4">
-        <v>1</v>
+        <v>840</v>
+      </c>
+      <c r="G125" s="12" t="s">
+        <v>841</v>
+      </c>
+      <c r="H125" s="11" t="s">
+        <v>841</v>
+      </c>
+      <c r="I125" s="13" t="s">
+        <v>842</v>
       </c>
       <c r="J125" s="1">
+        <f t="shared" si="37"/>
+        <v>3900</v>
+      </c>
+      <c r="K125" s="1">
+        <f t="shared" si="38"/>
+        <v>4600</v>
+      </c>
+      <c r="L125" s="1">
         <f t="shared" si="34"/>
-        <v>2900</v>
-      </c>
-      <c r="K125" s="1">
+        <v>1700</v>
+      </c>
+      <c r="M125" s="1">
         <f t="shared" si="35"/>
-        <v>2600</v>
-      </c>
-      <c r="L125" s="1">
+        <v>1700</v>
+      </c>
+      <c r="N125" s="3">
         <f t="shared" si="36"/>
-        <v>1700</v>
-      </c>
-      <c r="M125" s="1">
-        <f t="shared" si="37"/>
-        <v>1700</v>
-      </c>
-      <c r="N125" s="3">
-        <f t="shared" si="38"/>
         <v>49</v>
       </c>
       <c r="O125" s="6">
@@ -11428,10 +11455,10 @@
         <v>90</v>
       </c>
       <c r="Q125" s="11" t="s">
-        <v>834</v>
+        <v>843</v>
       </c>
       <c r="R125" s="11" t="s">
-        <v>834</v>
+        <v>843</v>
       </c>
       <c r="T125" s="1" t="s">
         <v>151</v>
@@ -11450,16 +11477,16 @@
         <v>814</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>835</v>
+        <v>844</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>836</v>
+        <v>845</v>
       </c>
       <c r="E126" s="1">
         <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>837</v>
+        <v>846</v>
       </c>
       <c r="G126" s="4">
         <v>1</v>
@@ -11471,23 +11498,23 @@
         <v>1</v>
       </c>
       <c r="J126" s="1">
+        <f t="shared" si="37"/>
+        <v>4100</v>
+      </c>
+      <c r="K126" s="1">
+        <f t="shared" si="38"/>
+        <v>4900</v>
+      </c>
+      <c r="L126" s="1">
         <f t="shared" si="34"/>
-        <v>3000</v>
-      </c>
-      <c r="K126" s="1">
+        <v>1750</v>
+      </c>
+      <c r="M126" s="1">
         <f t="shared" si="35"/>
-        <v>2700</v>
-      </c>
-      <c r="L126" s="1">
+        <v>1750</v>
+      </c>
+      <c r="N126" s="3">
         <f t="shared" si="36"/>
-        <v>1750</v>
-      </c>
-      <c r="M126" s="1">
-        <f t="shared" si="37"/>
-        <v>1750</v>
-      </c>
-      <c r="N126" s="3">
-        <f t="shared" si="38"/>
         <v>50</v>
       </c>
       <c r="O126" s="6">
@@ -11497,10 +11524,10 @@
         <v>90</v>
       </c>
       <c r="Q126" s="11" t="s">
-        <v>838</v>
+        <v>847</v>
       </c>
       <c r="R126" s="11" t="s">
-        <v>838</v>
+        <v>847</v>
       </c>
       <c r="T126" s="1" t="s">
         <v>151</v>
@@ -11519,16 +11546,16 @@
         <v>814</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>839</v>
+        <v>848</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>840</v>
+        <v>849</v>
       </c>
       <c r="E127" s="1">
         <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>841</v>
+        <v>850</v>
       </c>
       <c r="G127" s="4">
         <v>1</v>
@@ -11540,23 +11567,23 @@
         <v>1</v>
       </c>
       <c r="J127" s="1">
+        <f t="shared" si="37"/>
+        <v>4300</v>
+      </c>
+      <c r="K127" s="1">
+        <f t="shared" si="38"/>
+        <v>5200</v>
+      </c>
+      <c r="L127" s="1">
         <f t="shared" si="34"/>
-        <v>3100</v>
-      </c>
-      <c r="K127" s="1">
+        <v>1800</v>
+      </c>
+      <c r="M127" s="1">
         <f t="shared" si="35"/>
-        <v>2800</v>
-      </c>
-      <c r="L127" s="1">
+        <v>1800</v>
+      </c>
+      <c r="N127" s="3">
         <f t="shared" si="36"/>
-        <v>1800</v>
-      </c>
-      <c r="M127" s="1">
-        <f t="shared" si="37"/>
-        <v>1800</v>
-      </c>
-      <c r="N127" s="3">
-        <f t="shared" si="38"/>
         <v>51</v>
       </c>
       <c r="O127" s="6">
@@ -11566,10 +11593,10 @@
         <v>90</v>
       </c>
       <c r="Q127" s="11" t="s">
-        <v>842</v>
+        <v>851</v>
       </c>
       <c r="R127" s="11" t="s">
-        <v>842</v>
+        <v>851</v>
       </c>
       <c r="T127" s="1" t="s">
         <v>151</v>
@@ -11588,16 +11615,16 @@
         <v>814</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>844</v>
+        <v>853</v>
       </c>
       <c r="E128" s="1">
         <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>845</v>
+        <v>854</v>
       </c>
       <c r="G128" s="4">
         <v>1</v>
@@ -11609,23 +11636,23 @@
         <v>1</v>
       </c>
       <c r="J128" s="1">
+        <f t="shared" si="37"/>
+        <v>4500</v>
+      </c>
+      <c r="K128" s="1">
+        <f t="shared" si="38"/>
+        <v>5500</v>
+      </c>
+      <c r="L128" s="1">
         <f t="shared" si="34"/>
-        <v>3200</v>
-      </c>
-      <c r="K128" s="1">
+        <v>1850</v>
+      </c>
+      <c r="M128" s="1">
         <f t="shared" si="35"/>
-        <v>2900</v>
-      </c>
-      <c r="L128" s="1">
+        <v>1850</v>
+      </c>
+      <c r="N128" s="3">
         <f t="shared" si="36"/>
-        <v>1850</v>
-      </c>
-      <c r="M128" s="1">
-        <f t="shared" si="37"/>
-        <v>1850</v>
-      </c>
-      <c r="N128" s="3">
-        <f t="shared" si="38"/>
         <v>52</v>
       </c>
       <c r="O128" s="6">
@@ -11635,10 +11662,10 @@
         <v>90</v>
       </c>
       <c r="Q128" s="11" t="s">
-        <v>846</v>
+        <v>855</v>
       </c>
       <c r="R128" s="11" t="s">
-        <v>846</v>
+        <v>855</v>
       </c>
       <c r="T128" s="1" t="s">
         <v>151</v>
@@ -11657,16 +11684,16 @@
         <v>814</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>847</v>
+        <v>856</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>848</v>
+        <v>857</v>
       </c>
       <c r="E129" s="1">
         <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>849</v>
+        <v>858</v>
       </c>
       <c r="G129" s="4">
         <v>1</v>
@@ -11678,23 +11705,23 @@
         <v>1</v>
       </c>
       <c r="J129" s="1">
+        <f t="shared" si="37"/>
+        <v>4700</v>
+      </c>
+      <c r="K129" s="1">
+        <f t="shared" si="38"/>
+        <v>5800</v>
+      </c>
+      <c r="L129" s="1">
         <f t="shared" si="34"/>
-        <v>3300</v>
-      </c>
-      <c r="K129" s="1">
+        <v>1900</v>
+      </c>
+      <c r="M129" s="1">
         <f t="shared" si="35"/>
-        <v>3000</v>
-      </c>
-      <c r="L129" s="1">
+        <v>1900</v>
+      </c>
+      <c r="N129" s="3">
         <f t="shared" si="36"/>
-        <v>1900</v>
-      </c>
-      <c r="M129" s="1">
-        <f t="shared" si="37"/>
-        <v>1900</v>
-      </c>
-      <c r="N129" s="3">
-        <f t="shared" si="38"/>
         <v>53</v>
       </c>
       <c r="O129" s="6">
@@ -11704,10 +11731,10 @@
         <v>90</v>
       </c>
       <c r="Q129" s="11" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="R129" s="11" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="T129" s="1" t="s">
         <v>151</v>
@@ -11726,16 +11753,16 @@
         <v>814</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>852</v>
+        <v>861</v>
       </c>
       <c r="E130" s="1">
         <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="G130" s="4">
         <v>1</v>
@@ -11747,23 +11774,23 @@
         <v>1</v>
       </c>
       <c r="J130" s="1">
+        <f t="shared" si="37"/>
+        <v>4900</v>
+      </c>
+      <c r="K130" s="1">
+        <f t="shared" si="38"/>
+        <v>6100</v>
+      </c>
+      <c r="L130" s="1">
         <f t="shared" si="34"/>
-        <v>3400</v>
-      </c>
-      <c r="K130" s="1">
+        <v>1950</v>
+      </c>
+      <c r="M130" s="1">
         <f t="shared" si="35"/>
-        <v>3100</v>
-      </c>
-      <c r="L130" s="1">
+        <v>1950</v>
+      </c>
+      <c r="N130" s="3">
         <f t="shared" si="36"/>
-        <v>1950</v>
-      </c>
-      <c r="M130" s="1">
-        <f t="shared" si="37"/>
-        <v>1950</v>
-      </c>
-      <c r="N130" s="3">
-        <f t="shared" si="38"/>
         <v>54</v>
       </c>
       <c r="O130" s="6">
@@ -11773,10 +11800,10 @@
         <v>90</v>
       </c>
       <c r="Q130" s="11" t="s">
-        <v>854</v>
+        <v>863</v>
       </c>
       <c r="R130" s="11" t="s">
-        <v>854</v>
+        <v>863</v>
       </c>
       <c r="T130" s="1" t="s">
         <v>151</v>
@@ -11795,16 +11822,16 @@
         <v>814</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>855</v>
+        <v>864</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>856</v>
+        <v>865</v>
       </c>
       <c r="E131" s="1">
         <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>857</v>
+        <v>866</v>
       </c>
       <c r="G131" s="4">
         <v>1</v>
@@ -11816,23 +11843,23 @@
         <v>1</v>
       </c>
       <c r="J131" s="1">
+        <f t="shared" si="37"/>
+        <v>5100</v>
+      </c>
+      <c r="K131" s="1">
+        <f t="shared" si="38"/>
+        <v>6400</v>
+      </c>
+      <c r="L131" s="1">
         <f t="shared" si="34"/>
-        <v>3500</v>
-      </c>
-      <c r="K131" s="1">
+        <v>2000</v>
+      </c>
+      <c r="M131" s="1">
         <f t="shared" si="35"/>
-        <v>3200</v>
-      </c>
-      <c r="L131" s="1">
+        <v>2000</v>
+      </c>
+      <c r="N131" s="3">
         <f t="shared" si="36"/>
-        <v>2000</v>
-      </c>
-      <c r="M131" s="1">
-        <f t="shared" si="37"/>
-        <v>2000</v>
-      </c>
-      <c r="N131" s="3">
-        <f t="shared" si="38"/>
         <v>55</v>
       </c>
       <c r="O131" s="6">
@@ -11842,10 +11869,10 @@
         <v>90</v>
       </c>
       <c r="Q131" s="11" t="s">
-        <v>858</v>
+        <v>867</v>
       </c>
       <c r="R131" s="11" t="s">
-        <v>858</v>
+        <v>867</v>
       </c>
       <c r="T131" s="1" t="s">
         <v>151</v>
@@ -11862,16 +11889,16 @@
         <v>814</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>859</v>
+        <v>868</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>860</v>
+        <v>869</v>
       </c>
       <c r="E132" s="1">
         <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>861</v>
+        <v>870</v>
       </c>
       <c r="G132" s="4">
         <v>1</v>
@@ -11883,23 +11910,23 @@
         <v>1</v>
       </c>
       <c r="J132" s="1">
+        <f t="shared" si="37"/>
+        <v>5300</v>
+      </c>
+      <c r="K132" s="1">
+        <f t="shared" si="38"/>
+        <v>6700</v>
+      </c>
+      <c r="L132" s="1">
         <f t="shared" si="34"/>
-        <v>3600</v>
-      </c>
-      <c r="K132" s="1">
+        <v>2050</v>
+      </c>
+      <c r="M132" s="1">
         <f t="shared" si="35"/>
-        <v>3300</v>
-      </c>
-      <c r="L132" s="1">
+        <v>2050</v>
+      </c>
+      <c r="N132" s="3">
         <f t="shared" si="36"/>
-        <v>2050</v>
-      </c>
-      <c r="M132" s="1">
-        <f t="shared" si="37"/>
-        <v>2050</v>
-      </c>
-      <c r="N132" s="3">
-        <f t="shared" si="38"/>
         <v>56</v>
       </c>
       <c r="O132" s="6">
@@ -11909,10 +11936,10 @@
         <v>90</v>
       </c>
       <c r="Q132" s="11" t="s">
-        <v>862</v>
+        <v>871</v>
       </c>
       <c r="R132" s="11" t="s">
-        <v>862</v>
+        <v>871</v>
       </c>
       <c r="T132" s="1" t="s">
         <v>151</v>
@@ -11929,16 +11956,16 @@
         <v>814</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>863</v>
+        <v>872</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>864</v>
+        <v>873</v>
       </c>
       <c r="E133" s="1">
         <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>865</v>
+        <v>874</v>
       </c>
       <c r="G133" s="4">
         <v>1</v>
@@ -11950,23 +11977,23 @@
         <v>1</v>
       </c>
       <c r="J133" s="1">
+        <f t="shared" si="37"/>
+        <v>5500</v>
+      </c>
+      <c r="K133" s="1">
+        <f t="shared" si="38"/>
+        <v>7000</v>
+      </c>
+      <c r="L133" s="1">
         <f t="shared" si="34"/>
-        <v>3700</v>
-      </c>
-      <c r="K133" s="1">
+        <v>2100</v>
+      </c>
+      <c r="M133" s="1">
         <f t="shared" si="35"/>
-        <v>3400</v>
-      </c>
-      <c r="L133" s="1">
+        <v>2100</v>
+      </c>
+      <c r="N133" s="3">
         <f t="shared" si="36"/>
-        <v>2100</v>
-      </c>
-      <c r="M133" s="1">
-        <f t="shared" si="37"/>
-        <v>2100</v>
-      </c>
-      <c r="N133" s="3">
-        <f t="shared" si="38"/>
         <v>57</v>
       </c>
       <c r="O133" s="6">
@@ -11976,10 +12003,10 @@
         <v>90</v>
       </c>
       <c r="Q133" s="11" t="s">
-        <v>866</v>
+        <v>875</v>
       </c>
       <c r="R133" s="11" t="s">
-        <v>866</v>
+        <v>875</v>
       </c>
       <c r="T133" s="1" t="s">
         <v>151</v>
@@ -11996,16 +12023,16 @@
         <v>814</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>868</v>
+        <v>877</v>
       </c>
       <c r="E134" s="1">
         <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>869</v>
+        <v>878</v>
       </c>
       <c r="G134" s="4">
         <v>1</v>
@@ -12017,23 +12044,23 @@
         <v>1</v>
       </c>
       <c r="J134" s="1">
+        <f t="shared" si="37"/>
+        <v>5700</v>
+      </c>
+      <c r="K134" s="1">
+        <f t="shared" si="38"/>
+        <v>7300</v>
+      </c>
+      <c r="L134" s="1">
         <f t="shared" si="34"/>
-        <v>3800</v>
-      </c>
-      <c r="K134" s="1">
+        <v>2150</v>
+      </c>
+      <c r="M134" s="1">
         <f t="shared" si="35"/>
-        <v>3500</v>
-      </c>
-      <c r="L134" s="1">
+        <v>2150</v>
+      </c>
+      <c r="N134" s="3">
         <f t="shared" si="36"/>
-        <v>2150</v>
-      </c>
-      <c r="M134" s="1">
-        <f t="shared" si="37"/>
-        <v>2150</v>
-      </c>
-      <c r="N134" s="3">
-        <f t="shared" si="38"/>
         <v>58</v>
       </c>
       <c r="O134" s="6">
@@ -12043,10 +12070,10 @@
         <v>90</v>
       </c>
       <c r="Q134" s="11" t="s">
-        <v>870</v>
+        <v>879</v>
       </c>
       <c r="R134" s="11" t="s">
-        <v>870</v>
+        <v>879</v>
       </c>
       <c r="T134" s="1" t="s">
         <v>151</v>
@@ -12063,16 +12090,16 @@
         <v>814</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>871</v>
+        <v>880</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>872</v>
+        <v>881</v>
       </c>
       <c r="E135" s="1">
         <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>873</v>
+        <v>882</v>
       </c>
       <c r="G135" s="4">
         <v>1</v>
@@ -12084,23 +12111,23 @@
         <v>1</v>
       </c>
       <c r="J135" s="1">
+        <f t="shared" si="37"/>
+        <v>5900</v>
+      </c>
+      <c r="K135" s="1">
+        <f t="shared" si="38"/>
+        <v>7600</v>
+      </c>
+      <c r="L135" s="1">
         <f t="shared" si="34"/>
-        <v>3900</v>
-      </c>
-      <c r="K135" s="1">
+        <v>2200</v>
+      </c>
+      <c r="M135" s="1">
         <f t="shared" si="35"/>
-        <v>3600</v>
-      </c>
-      <c r="L135" s="1">
+        <v>2200</v>
+      </c>
+      <c r="N135" s="3">
         <f t="shared" si="36"/>
-        <v>2200</v>
-      </c>
-      <c r="M135" s="1">
-        <f t="shared" si="37"/>
-        <v>2200</v>
-      </c>
-      <c r="N135" s="3">
-        <f t="shared" si="38"/>
         <v>59</v>
       </c>
       <c r="O135" s="6">
@@ -12110,10 +12137,10 @@
         <v>90</v>
       </c>
       <c r="Q135" s="11" t="s">
-        <v>874</v>
+        <v>883</v>
       </c>
       <c r="R135" s="11" t="s">
-        <v>874</v>
+        <v>883</v>
       </c>
       <c r="T135" s="1" t="s">
         <v>151</v>
@@ -12130,16 +12157,16 @@
         <v>814</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>875</v>
+        <v>884</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>876</v>
+        <v>885</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>877</v>
+        <v>886</v>
       </c>
       <c r="G136" s="4">
         <v>1</v>
@@ -12151,23 +12178,23 @@
         <v>1</v>
       </c>
       <c r="J136" s="1">
+        <f t="shared" si="37"/>
+        <v>6100</v>
+      </c>
+      <c r="K136" s="1">
+        <f t="shared" si="38"/>
+        <v>7900</v>
+      </c>
+      <c r="L136" s="1">
         <f t="shared" si="34"/>
-        <v>4000</v>
-      </c>
-      <c r="K136" s="1">
+        <v>2250</v>
+      </c>
+      <c r="M136" s="1">
         <f t="shared" si="35"/>
-        <v>3700</v>
-      </c>
-      <c r="L136" s="1">
+        <v>2250</v>
+      </c>
+      <c r="N136" s="3">
         <f t="shared" si="36"/>
-        <v>2250</v>
-      </c>
-      <c r="M136" s="1">
-        <f t="shared" si="37"/>
-        <v>2250</v>
-      </c>
-      <c r="N136" s="3">
-        <f t="shared" si="38"/>
         <v>60</v>
       </c>
       <c r="O136" s="6">
@@ -12177,10 +12204,10 @@
         <v>90</v>
       </c>
       <c r="Q136" s="11" t="s">
-        <v>878</v>
+        <v>887</v>
       </c>
       <c r="R136" s="11" t="s">
-        <v>878</v>
+        <v>887</v>
       </c>
       <c r="T136" s="1" t="s">
         <v>151</v>
@@ -12199,16 +12226,16 @@
         <v>814</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>880</v>
+        <v>889</v>
       </c>
       <c r="E137" s="1">
         <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>881</v>
+        <v>890</v>
       </c>
       <c r="G137" s="4">
         <v>1</v>
@@ -12220,23 +12247,23 @@
         <v>1</v>
       </c>
       <c r="J137" s="1">
+        <f t="shared" si="37"/>
+        <v>6300</v>
+      </c>
+      <c r="K137" s="1">
+        <f t="shared" si="38"/>
+        <v>8200</v>
+      </c>
+      <c r="L137" s="1">
         <f t="shared" si="34"/>
-        <v>4100</v>
-      </c>
-      <c r="K137" s="1">
+        <v>2300</v>
+      </c>
+      <c r="M137" s="1">
         <f t="shared" si="35"/>
-        <v>3800</v>
-      </c>
-      <c r="L137" s="1">
+        <v>2300</v>
+      </c>
+      <c r="N137" s="3">
         <f t="shared" si="36"/>
-        <v>2300</v>
-      </c>
-      <c r="M137" s="1">
-        <f t="shared" si="37"/>
-        <v>2300</v>
-      </c>
-      <c r="N137" s="3">
-        <f t="shared" si="38"/>
         <v>61</v>
       </c>
       <c r="O137" s="6">
@@ -12246,10 +12273,10 @@
         <v>90</v>
       </c>
       <c r="Q137" s="11" t="s">
-        <v>882</v>
+        <v>891</v>
       </c>
       <c r="R137" s="11" t="s">
-        <v>882</v>
+        <v>891</v>
       </c>
       <c r="T137" s="1" t="s">
         <v>151</v>
@@ -12268,16 +12295,16 @@
         <v>814</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>883</v>
+        <v>892</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>884</v>
+        <v>893</v>
       </c>
       <c r="E138" s="1">
         <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>885</v>
+        <v>894</v>
       </c>
       <c r="G138" s="4">
         <v>1</v>
@@ -12289,23 +12316,23 @@
         <v>1</v>
       </c>
       <c r="J138" s="1">
+        <f t="shared" si="37"/>
+        <v>6500</v>
+      </c>
+      <c r="K138" s="1">
+        <f t="shared" si="38"/>
+        <v>8500</v>
+      </c>
+      <c r="L138" s="1">
         <f t="shared" si="34"/>
-        <v>4200</v>
-      </c>
-      <c r="K138" s="1">
+        <v>2350</v>
+      </c>
+      <c r="M138" s="1">
         <f t="shared" si="35"/>
-        <v>3900</v>
-      </c>
-      <c r="L138" s="1">
+        <v>2350</v>
+      </c>
+      <c r="N138" s="3">
         <f t="shared" si="36"/>
-        <v>2350</v>
-      </c>
-      <c r="M138" s="1">
-        <f t="shared" si="37"/>
-        <v>2350</v>
-      </c>
-      <c r="N138" s="3">
-        <f t="shared" si="38"/>
         <v>62</v>
       </c>
       <c r="O138" s="6">
@@ -12315,10 +12342,10 @@
         <v>90</v>
       </c>
       <c r="Q138" s="11" t="s">
-        <v>886</v>
+        <v>895</v>
       </c>
       <c r="R138" s="11" t="s">
-        <v>886</v>
+        <v>895</v>
       </c>
       <c r="T138" s="1" t="s">
         <v>151</v>
@@ -12337,16 +12364,16 @@
         <v>814</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>887</v>
+        <v>896</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="E139" s="1">
         <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="G139" s="4">
         <v>1</v>
@@ -12358,23 +12385,23 @@
         <v>1</v>
       </c>
       <c r="J139" s="1">
+        <f t="shared" si="37"/>
+        <v>6700</v>
+      </c>
+      <c r="K139" s="1">
+        <f t="shared" si="38"/>
+        <v>8800</v>
+      </c>
+      <c r="L139" s="1">
         <f t="shared" si="34"/>
-        <v>4300</v>
-      </c>
-      <c r="K139" s="1">
+        <v>2400</v>
+      </c>
+      <c r="M139" s="1">
         <f t="shared" si="35"/>
-        <v>4000</v>
-      </c>
-      <c r="L139" s="1">
+        <v>2400</v>
+      </c>
+      <c r="N139" s="3">
         <f t="shared" si="36"/>
-        <v>2400</v>
-      </c>
-      <c r="M139" s="1">
-        <f t="shared" si="37"/>
-        <v>2400</v>
-      </c>
-      <c r="N139" s="3">
-        <f t="shared" si="38"/>
         <v>63</v>
       </c>
       <c r="O139" s="6">
@@ -12384,10 +12411,10 @@
         <v>90</v>
       </c>
       <c r="Q139" s="11" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="R139" s="11" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="T139" s="1" t="s">
         <v>151</v>
@@ -12406,16 +12433,16 @@
         <v>814</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>891</v>
+        <v>900</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>892</v>
+        <v>901</v>
       </c>
       <c r="E140" s="1">
         <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>893</v>
+        <v>902</v>
       </c>
       <c r="G140" s="4">
         <v>1</v>
@@ -12427,23 +12454,23 @@
         <v>1</v>
       </c>
       <c r="J140" s="1">
+        <f t="shared" si="37"/>
+        <v>6900</v>
+      </c>
+      <c r="K140" s="1">
+        <f t="shared" si="38"/>
+        <v>9100</v>
+      </c>
+      <c r="L140" s="1">
         <f t="shared" si="34"/>
-        <v>4400</v>
-      </c>
-      <c r="K140" s="1">
+        <v>2450</v>
+      </c>
+      <c r="M140" s="1">
         <f t="shared" si="35"/>
-        <v>4100</v>
-      </c>
-      <c r="L140" s="1">
+        <v>2450</v>
+      </c>
+      <c r="N140" s="3">
         <f t="shared" si="36"/>
-        <v>2450</v>
-      </c>
-      <c r="M140" s="1">
-        <f t="shared" si="37"/>
-        <v>2450</v>
-      </c>
-      <c r="N140" s="3">
-        <f t="shared" si="38"/>
         <v>64</v>
       </c>
       <c r="O140" s="6">
@@ -12453,10 +12480,10 @@
         <v>90</v>
       </c>
       <c r="Q140" s="11" t="s">
-        <v>894</v>
+        <v>903</v>
       </c>
       <c r="R140" s="11" t="s">
-        <v>894</v>
+        <v>903</v>
       </c>
       <c r="T140" s="1" t="s">
         <v>151</v>
@@ -12475,16 +12502,16 @@
         <v>814</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>895</v>
+        <v>904</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>896</v>
+        <v>905</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>897</v>
+        <v>906</v>
       </c>
       <c r="G141" s="4">
         <v>1</v>
@@ -12496,23 +12523,23 @@
         <v>1</v>
       </c>
       <c r="J141" s="1">
+        <f t="shared" si="37"/>
+        <v>7100</v>
+      </c>
+      <c r="K141" s="1">
+        <f t="shared" si="38"/>
+        <v>9400</v>
+      </c>
+      <c r="L141" s="1">
         <f t="shared" si="34"/>
-        <v>4500</v>
-      </c>
-      <c r="K141" s="1">
+        <v>2500</v>
+      </c>
+      <c r="M141" s="1">
         <f t="shared" si="35"/>
-        <v>4200</v>
-      </c>
-      <c r="L141" s="1">
+        <v>2500</v>
+      </c>
+      <c r="N141" s="3">
         <f t="shared" si="36"/>
-        <v>2500</v>
-      </c>
-      <c r="M141" s="1">
-        <f t="shared" si="37"/>
-        <v>2500</v>
-      </c>
-      <c r="N141" s="3">
-        <f t="shared" si="38"/>
         <v>65</v>
       </c>
       <c r="O141" s="6">
@@ -12522,10 +12549,10 @@
         <v>90</v>
       </c>
       <c r="Q141" s="11" t="s">
-        <v>898</v>
+        <v>907</v>
       </c>
       <c r="R141" s="11" t="s">
-        <v>898</v>
+        <v>907</v>
       </c>
       <c r="T141" s="1" t="s">
         <v>151</v>
@@ -12544,16 +12571,16 @@
         <v>814</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>899</v>
+        <v>908</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>900</v>
+        <v>909</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>901</v>
+        <v>910</v>
       </c>
       <c r="G142" s="4">
         <v>1</v>
@@ -12565,23 +12592,23 @@
         <v>1</v>
       </c>
       <c r="J142" s="1">
+        <f t="shared" si="37"/>
+        <v>7300</v>
+      </c>
+      <c r="K142" s="1">
+        <f t="shared" si="38"/>
+        <v>9700</v>
+      </c>
+      <c r="L142" s="1">
         <f t="shared" si="34"/>
-        <v>4600</v>
-      </c>
-      <c r="K142" s="1">
+        <v>2550</v>
+      </c>
+      <c r="M142" s="1">
         <f t="shared" si="35"/>
-        <v>4300</v>
-      </c>
-      <c r="L142" s="1">
+        <v>2550</v>
+      </c>
+      <c r="N142" s="3">
         <f t="shared" si="36"/>
-        <v>2550</v>
-      </c>
-      <c r="M142" s="1">
-        <f t="shared" si="37"/>
-        <v>2550</v>
-      </c>
-      <c r="N142" s="3">
-        <f t="shared" si="38"/>
         <v>66</v>
       </c>
       <c r="O142" s="6">
@@ -12591,10 +12618,10 @@
         <v>90</v>
       </c>
       <c r="Q142" s="11" t="s">
-        <v>902</v>
+        <v>911</v>
       </c>
       <c r="R142" s="11" t="s">
-        <v>902</v>
+        <v>911</v>
       </c>
       <c r="T142" s="1" t="s">
         <v>151</v>
@@ -12613,16 +12640,16 @@
         <v>814</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>903</v>
+        <v>912</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>904</v>
+        <v>913</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>905</v>
+        <v>914</v>
       </c>
       <c r="G143" s="4">
         <v>1</v>
@@ -12634,23 +12661,23 @@
         <v>1</v>
       </c>
       <c r="J143" s="1">
+        <f t="shared" si="37"/>
+        <v>7500</v>
+      </c>
+      <c r="K143" s="1">
+        <f t="shared" si="38"/>
+        <v>10000</v>
+      </c>
+      <c r="L143" s="1">
         <f t="shared" si="34"/>
-        <v>4700</v>
-      </c>
-      <c r="K143" s="1">
+        <v>2600</v>
+      </c>
+      <c r="M143" s="1">
         <f t="shared" si="35"/>
-        <v>4400</v>
-      </c>
-      <c r="L143" s="1">
+        <v>2600</v>
+      </c>
+      <c r="N143" s="3">
         <f t="shared" si="36"/>
-        <v>2600</v>
-      </c>
-      <c r="M143" s="1">
-        <f t="shared" si="37"/>
-        <v>2600</v>
-      </c>
-      <c r="N143" s="3">
-        <f t="shared" si="38"/>
         <v>67</v>
       </c>
       <c r="O143" s="6">
@@ -12660,10 +12687,10 @@
         <v>90</v>
       </c>
       <c r="Q143" s="11" t="s">
-        <v>906</v>
+        <v>915</v>
       </c>
       <c r="R143" s="11" t="s">
-        <v>906</v>
+        <v>915</v>
       </c>
       <c r="T143" s="1" t="s">
         <v>151</v>
@@ -12682,16 +12709,16 @@
         <v>814</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>907</v>
+        <v>916</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>908</v>
+        <v>917</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>909</v>
+        <v>918</v>
       </c>
       <c r="G144" s="4">
         <v>1</v>
@@ -12703,23 +12730,23 @@
         <v>1</v>
       </c>
       <c r="J144" s="1">
+        <f t="shared" si="37"/>
+        <v>7700</v>
+      </c>
+      <c r="K144" s="1">
+        <f t="shared" si="38"/>
+        <v>10300</v>
+      </c>
+      <c r="L144" s="1">
         <f t="shared" si="34"/>
-        <v>4800</v>
-      </c>
-      <c r="K144" s="1">
+        <v>2650</v>
+      </c>
+      <c r="M144" s="1">
         <f t="shared" si="35"/>
-        <v>4500</v>
-      </c>
-      <c r="L144" s="1">
+        <v>2650</v>
+      </c>
+      <c r="N144" s="3">
         <f t="shared" si="36"/>
-        <v>2650</v>
-      </c>
-      <c r="M144" s="1">
-        <f t="shared" si="37"/>
-        <v>2650</v>
-      </c>
-      <c r="N144" s="3">
-        <f t="shared" si="38"/>
         <v>68</v>
       </c>
       <c r="O144" s="6">
@@ -12729,10 +12756,10 @@
         <v>90</v>
       </c>
       <c r="Q144" s="11" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="R144" s="11" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="T144" s="1" t="s">
         <v>151</v>
@@ -12751,16 +12778,16 @@
         <v>814</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>912</v>
+        <v>921</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>913</v>
+        <v>922</v>
       </c>
       <c r="G145" s="4">
         <v>1</v>
@@ -12772,23 +12799,23 @@
         <v>1</v>
       </c>
       <c r="J145" s="1">
+        <f t="shared" si="37"/>
+        <v>7900</v>
+      </c>
+      <c r="K145" s="1">
+        <f t="shared" si="38"/>
+        <v>10600</v>
+      </c>
+      <c r="L145" s="1">
         <f t="shared" si="34"/>
-        <v>4900</v>
-      </c>
-      <c r="K145" s="1">
+        <v>2700</v>
+      </c>
+      <c r="M145" s="1">
         <f t="shared" si="35"/>
-        <v>4600</v>
-      </c>
-      <c r="L145" s="1">
+        <v>2700</v>
+      </c>
+      <c r="N145" s="3">
         <f t="shared" si="36"/>
-        <v>2700</v>
-      </c>
-      <c r="M145" s="1">
-        <f t="shared" si="37"/>
-        <v>2700</v>
-      </c>
-      <c r="N145" s="3">
-        <f t="shared" si="38"/>
         <v>69</v>
       </c>
       <c r="O145" s="6">
@@ -12798,10 +12825,10 @@
         <v>90</v>
       </c>
       <c r="Q145" s="11" t="s">
-        <v>914</v>
+        <v>923</v>
       </c>
       <c r="R145" s="11" t="s">
-        <v>914</v>
+        <v>923</v>
       </c>
       <c r="T145" s="1" t="s">
         <v>151</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="920">
   <si>
     <t>ID</t>
   </si>
@@ -2527,96 +2527,96 @@
     <t>400000000000</t>
   </si>
   <si>
+    <t>10115</t>
+  </si>
+  <si>
+    <t>1115</t>
+  </si>
+  <si>
+    <t>地狱狼王</t>
+  </si>
+  <si>
+    <t>1000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>440000000000</t>
+  </si>
+  <si>
+    <t>10116</t>
+  </si>
+  <si>
+    <t>1116</t>
+  </si>
+  <si>
+    <t>地狱沙虫王</t>
+  </si>
+  <si>
+    <t>900000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>20000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>480000000000</t>
+  </si>
+  <si>
+    <t>10117</t>
+  </si>
+  <si>
+    <t>1117</t>
+  </si>
+  <si>
+    <t>地狱鹰王</t>
+  </si>
+  <si>
+    <t>9000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>400000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>520000000000</t>
+  </si>
+  <si>
+    <t>10118</t>
+  </si>
+  <si>
+    <t>1118</t>
+  </si>
+  <si>
+    <t>地狱角虫王</t>
+  </si>
+  <si>
+    <t>90000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>8000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>560000000000</t>
+  </si>
+  <si>
+    <t>10119</t>
+  </si>
+  <si>
+    <t>1119</t>
+  </si>
+  <si>
+    <t>地狱蜈蚣王</t>
+  </si>
+  <si>
+    <t>900000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>160000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>600000000000</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
-    <t>10115</t>
-  </si>
-  <si>
-    <t>1115</t>
-  </si>
-  <si>
-    <t>地狱狼王</t>
-  </si>
-  <si>
-    <t>1000000000000000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>410000000000</t>
-  </si>
-  <si>
-    <t>10116</t>
-  </si>
-  <si>
-    <t>1116</t>
-  </si>
-  <si>
-    <t>地狱沙虫王</t>
-  </si>
-  <si>
-    <t>900000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>20000000000000000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>420000000000</t>
-  </si>
-  <si>
-    <t>10117</t>
-  </si>
-  <si>
-    <t>1117</t>
-  </si>
-  <si>
-    <t>地狱鹰王</t>
-  </si>
-  <si>
-    <t>9000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>400000000000000000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>430000000000</t>
-  </si>
-  <si>
-    <t>10118</t>
-  </si>
-  <si>
-    <t>1118</t>
-  </si>
-  <si>
-    <t>地狱角虫王</t>
-  </si>
-  <si>
-    <t>90000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>8000000000000000000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>440000000000</t>
-  </si>
-  <si>
-    <t>10119</t>
-  </si>
-  <si>
-    <t>1119</t>
-  </si>
-  <si>
-    <t>地狱蜈蚣王</t>
-  </si>
-  <si>
-    <t>900000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>160000000000000000000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>450000000000</t>
-  </si>
-  <si>
     <t>10120</t>
   </si>
   <si>
@@ -2650,9 +2650,6 @@
     <t>地狱白野猪</t>
   </si>
   <si>
-    <t>480000000000</t>
-  </si>
-  <si>
     <t>10123</t>
   </si>
   <si>
@@ -2698,9 +2695,6 @@
     <t>地狱沃玛教皇</t>
   </si>
   <si>
-    <t>520000000000</t>
-  </si>
-  <si>
     <t>10127</t>
   </si>
   <si>
@@ -2746,9 +2740,6 @@
     <t>地狱千年妖王</t>
   </si>
   <si>
-    <t>560000000000</t>
-  </si>
-  <si>
     <t>10131</t>
   </si>
   <si>
@@ -2792,9 +2783,6 @@
   </si>
   <si>
     <t>地狱牛魔王</t>
-  </si>
-  <si>
-    <t>600000000000</t>
   </si>
   <si>
     <t>10135</t>
@@ -11124,24 +11112,18 @@
       <c r="V120" s="3"/>
       <c r="W120" s="3"/>
     </row>
-    <row r="121" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A121" s="1" t="s">
+    <row r="121" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C121" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="C121" s="1" t="s">
+      <c r="D121" s="1" t="s">
         <v>815</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>816</v>
       </c>
       <c r="E121" s="1">
         <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="G121" s="12" t="s">
         <v>758</v>
@@ -11150,7 +11132,7 @@
         <v>758</v>
       </c>
       <c r="I121" s="13" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="J121" s="1">
         <f t="shared" si="37"/>
@@ -11172,17 +11154,18 @@
         <f t="shared" si="36"/>
         <v>45</v>
       </c>
-      <c r="O121" s="6">
-        <v>0</v>
+      <c r="O121" s="3">
+        <f t="shared" ref="O121:O125" si="39">O120+3</f>
+        <v>3</v>
       </c>
       <c r="P121" s="3">
         <v>90</v>
       </c>
       <c r="Q121" s="11" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="R121" s="11" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="T121" s="1" t="s">
         <v>151</v>
@@ -11193,33 +11176,27 @@
       <c r="V121" s="3"/>
       <c r="W121" s="3"/>
     </row>
-    <row r="122" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A122" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>814</v>
-      </c>
+    <row r="122" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C122" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>820</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>821</v>
       </c>
       <c r="E122" s="1">
         <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="G122" s="12" t="s">
         <v>822</v>
       </c>
-      <c r="G122" s="12" t="s">
+      <c r="H122" s="11" t="s">
+        <v>822</v>
+      </c>
+      <c r="I122" s="13" t="s">
         <v>823</v>
-      </c>
-      <c r="H122" s="11" t="s">
-        <v>823</v>
-      </c>
-      <c r="I122" s="13" t="s">
-        <v>824</v>
       </c>
       <c r="J122" s="1">
         <f t="shared" si="37"/>
@@ -11241,17 +11218,18 @@
         <f t="shared" si="36"/>
         <v>46</v>
       </c>
-      <c r="O122" s="6">
-        <v>0</v>
+      <c r="O122" s="3">
+        <f t="shared" si="39"/>
+        <v>6</v>
       </c>
       <c r="P122" s="3">
         <v>90</v>
       </c>
       <c r="Q122" s="11" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="R122" s="11" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="T122" s="1" t="s">
         <v>151</v>
@@ -11262,33 +11240,27 @@
       <c r="V122" s="3"/>
       <c r="W122" s="3"/>
     </row>
-    <row r="123" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A123" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>814</v>
-      </c>
+    <row r="123" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C123" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>826</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>827</v>
       </c>
       <c r="E123" s="1">
         <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="G123" s="12" t="s">
         <v>828</v>
       </c>
-      <c r="G123" s="12" t="s">
+      <c r="H123" s="11" t="s">
+        <v>828</v>
+      </c>
+      <c r="I123" s="13" t="s">
         <v>829</v>
-      </c>
-      <c r="H123" s="11" t="s">
-        <v>829</v>
-      </c>
-      <c r="I123" s="13" t="s">
-        <v>830</v>
       </c>
       <c r="J123" s="1">
         <f t="shared" si="37"/>
@@ -11310,17 +11282,18 @@
         <f t="shared" si="36"/>
         <v>47</v>
       </c>
-      <c r="O123" s="6">
-        <v>0</v>
+      <c r="O123" s="3">
+        <f t="shared" si="39"/>
+        <v>9</v>
       </c>
       <c r="P123" s="3">
         <v>90</v>
       </c>
       <c r="Q123" s="11" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="R123" s="11" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="T123" s="1" t="s">
         <v>151</v>
@@ -11331,33 +11304,27 @@
       <c r="V123" s="3"/>
       <c r="W123" s="3"/>
     </row>
-    <row r="124" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A124" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>814</v>
-      </c>
+    <row r="124" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C124" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>832</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>833</v>
       </c>
       <c r="E124" s="1">
         <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="G124" s="12" t="s">
         <v>834</v>
       </c>
-      <c r="G124" s="12" t="s">
+      <c r="H124" s="11" t="s">
+        <v>834</v>
+      </c>
+      <c r="I124" s="13" t="s">
         <v>835</v>
-      </c>
-      <c r="H124" s="11" t="s">
-        <v>835</v>
-      </c>
-      <c r="I124" s="13" t="s">
-        <v>836</v>
       </c>
       <c r="J124" s="1">
         <f t="shared" si="37"/>
@@ -11379,17 +11346,18 @@
         <f t="shared" si="36"/>
         <v>48</v>
       </c>
-      <c r="O124" s="6">
-        <v>0</v>
+      <c r="O124" s="3">
+        <f t="shared" si="39"/>
+        <v>12</v>
       </c>
       <c r="P124" s="3">
         <v>90</v>
       </c>
       <c r="Q124" s="11" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="R124" s="11" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="T124" s="1" t="s">
         <v>151</v>
@@ -11400,33 +11368,27 @@
       <c r="V124" s="3"/>
       <c r="W124" s="3"/>
     </row>
-    <row r="125" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A125" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>814</v>
-      </c>
+    <row r="125" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C125" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>838</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>839</v>
       </c>
       <c r="E125" s="1">
         <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="G125" s="12" t="s">
         <v>840</v>
       </c>
-      <c r="G125" s="12" t="s">
+      <c r="H125" s="11" t="s">
+        <v>840</v>
+      </c>
+      <c r="I125" s="13" t="s">
         <v>841</v>
-      </c>
-      <c r="H125" s="11" t="s">
-        <v>841</v>
-      </c>
-      <c r="I125" s="13" t="s">
-        <v>842</v>
       </c>
       <c r="J125" s="1">
         <f t="shared" si="37"/>
@@ -11448,17 +11410,18 @@
         <f t="shared" si="36"/>
         <v>49</v>
       </c>
-      <c r="O125" s="6">
-        <v>0</v>
+      <c r="O125" s="3">
+        <f t="shared" si="39"/>
+        <v>15</v>
       </c>
       <c r="P125" s="3">
         <v>90</v>
       </c>
       <c r="Q125" s="11" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="R125" s="11" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="T125" s="1" t="s">
         <v>151</v>
@@ -11471,10 +11434,10 @@
     </row>
     <row r="126" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A126" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>844</v>
@@ -11540,10 +11503,10 @@
     </row>
     <row r="127" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A127" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>848</v>
@@ -11609,10 +11572,10 @@
     </row>
     <row r="128" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A128" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>852</v>
@@ -11662,10 +11625,10 @@
         <v>90</v>
       </c>
       <c r="Q128" s="11" t="s">
-        <v>855</v>
+        <v>824</v>
       </c>
       <c r="R128" s="11" t="s">
-        <v>855</v>
+        <v>824</v>
       </c>
       <c r="T128" s="1" t="s">
         <v>151</v>
@@ -11678,22 +11641,22 @@
     </row>
     <row r="129" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A129" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C129" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>856</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>857</v>
       </c>
       <c r="E129" s="1">
         <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="G129" s="4">
         <v>1</v>
@@ -11731,10 +11694,10 @@
         <v>90</v>
       </c>
       <c r="Q129" s="11" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="R129" s="11" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="T129" s="1" t="s">
         <v>151</v>
@@ -11747,22 +11710,22 @@
     </row>
     <row r="130" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A130" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C130" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>860</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>861</v>
       </c>
       <c r="E130" s="1">
         <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="G130" s="4">
         <v>1</v>
@@ -11800,10 +11763,10 @@
         <v>90</v>
       </c>
       <c r="Q130" s="11" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="R130" s="11" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T130" s="1" t="s">
         <v>151</v>
@@ -11816,22 +11779,22 @@
     </row>
     <row r="131" customHeight="1" spans="1:21">
       <c r="A131" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C131" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>864</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>865</v>
       </c>
       <c r="E131" s="1">
         <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="G131" s="4">
         <v>1</v>
@@ -11869,10 +11832,10 @@
         <v>90</v>
       </c>
       <c r="Q131" s="11" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="R131" s="11" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="T131" s="1" t="s">
         <v>151</v>
@@ -11883,22 +11846,22 @@
     </row>
     <row r="132" customHeight="1" spans="1:21">
       <c r="A132" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C132" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>868</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>869</v>
       </c>
       <c r="E132" s="1">
         <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="G132" s="4">
         <v>1</v>
@@ -11936,10 +11899,10 @@
         <v>90</v>
       </c>
       <c r="Q132" s="11" t="s">
-        <v>871</v>
+        <v>830</v>
       </c>
       <c r="R132" s="11" t="s">
-        <v>871</v>
+        <v>830</v>
       </c>
       <c r="T132" s="1" t="s">
         <v>151</v>
@@ -11950,22 +11913,22 @@
     </row>
     <row r="133" customHeight="1" spans="1:21">
       <c r="A133" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="E133" s="1">
         <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="G133" s="4">
         <v>1</v>
@@ -12003,10 +11966,10 @@
         <v>90</v>
       </c>
       <c r="Q133" s="11" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="R133" s="11" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="T133" s="1" t="s">
         <v>151</v>
@@ -12017,22 +11980,22 @@
     </row>
     <row r="134" customHeight="1" spans="1:21">
       <c r="A134" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="E134" s="1">
         <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="G134" s="4">
         <v>1</v>
@@ -12070,10 +12033,10 @@
         <v>90</v>
       </c>
       <c r="Q134" s="11" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="R134" s="11" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="T134" s="1" t="s">
         <v>151</v>
@@ -12084,22 +12047,22 @@
     </row>
     <row r="135" customHeight="1" spans="1:21">
       <c r="A135" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="E135" s="1">
         <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="G135" s="4">
         <v>1</v>
@@ -12137,10 +12100,10 @@
         <v>90</v>
       </c>
       <c r="Q135" s="11" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="R135" s="11" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="T135" s="1" t="s">
         <v>151</v>
@@ -12151,22 +12114,22 @@
     </row>
     <row r="136" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A136" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="G136" s="4">
         <v>1</v>
@@ -12204,10 +12167,10 @@
         <v>90</v>
       </c>
       <c r="Q136" s="11" t="s">
-        <v>887</v>
+        <v>836</v>
       </c>
       <c r="R136" s="11" t="s">
-        <v>887</v>
+        <v>836</v>
       </c>
       <c r="T136" s="1" t="s">
         <v>151</v>
@@ -12220,22 +12183,22 @@
     </row>
     <row r="137" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A137" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="E137" s="1">
         <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="G137" s="4">
         <v>1</v>
@@ -12273,10 +12236,10 @@
         <v>90</v>
       </c>
       <c r="Q137" s="11" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="R137" s="11" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="T137" s="1" t="s">
         <v>151</v>
@@ -12289,22 +12252,22 @@
     </row>
     <row r="138" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A138" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="E138" s="1">
         <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="G138" s="4">
         <v>1</v>
@@ -12342,10 +12305,10 @@
         <v>90</v>
       </c>
       <c r="Q138" s="11" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="R138" s="11" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="T138" s="1" t="s">
         <v>151</v>
@@ -12358,22 +12321,22 @@
     </row>
     <row r="139" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A139" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="E139" s="1">
         <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="G139" s="4">
         <v>1</v>
@@ -12411,10 +12374,10 @@
         <v>90</v>
       </c>
       <c r="Q139" s="11" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="R139" s="11" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="T139" s="1" t="s">
         <v>151</v>
@@ -12427,22 +12390,22 @@
     </row>
     <row r="140" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A140" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="E140" s="1">
         <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="G140" s="4">
         <v>1</v>
@@ -12480,10 +12443,10 @@
         <v>90</v>
       </c>
       <c r="Q140" s="11" t="s">
-        <v>903</v>
+        <v>842</v>
       </c>
       <c r="R140" s="11" t="s">
-        <v>903</v>
+        <v>842</v>
       </c>
       <c r="T140" s="1" t="s">
         <v>151</v>
@@ -12496,22 +12459,22 @@
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A141" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="G141" s="4">
         <v>1</v>
@@ -12549,10 +12512,10 @@
         <v>90</v>
       </c>
       <c r="Q141" s="11" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="R141" s="11" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="T141" s="1" t="s">
         <v>151</v>
@@ -12565,22 +12528,22 @@
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A142" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="G142" s="4">
         <v>1</v>
@@ -12618,10 +12581,10 @@
         <v>90</v>
       </c>
       <c r="Q142" s="11" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="R142" s="11" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="T142" s="1" t="s">
         <v>151</v>
@@ -12634,22 +12597,22 @@
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A143" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="G143" s="4">
         <v>1</v>
@@ -12687,10 +12650,10 @@
         <v>90</v>
       </c>
       <c r="Q143" s="11" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="R143" s="11" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="T143" s="1" t="s">
         <v>151</v>
@@ -12703,22 +12666,22 @@
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A144" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="G144" s="4">
         <v>1</v>
@@ -12756,10 +12719,10 @@
         <v>90</v>
       </c>
       <c r="Q144" s="11" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="R144" s="11" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="T144" s="1" t="s">
         <v>151</v>
@@ -12772,22 +12735,22 @@
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A145" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="G145" s="4">
         <v>1</v>
@@ -12825,10 +12788,10 @@
         <v>90</v>
       </c>
       <c r="Q145" s="11" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="R145" s="11" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="T145" s="1" t="s">
         <v>151</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="920">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="918">
   <si>
     <t>ID</t>
   </si>
@@ -229,7 +229,7 @@
     <t>1002</t>
   </si>
   <si>
-    <t>稻草人王</t>
+    <t>草人王</t>
   </si>
   <si>
     <t>2000</t>
@@ -250,7 +250,7 @@
     <t>1003</t>
   </si>
   <si>
-    <t>钉耙猫王</t>
+    <t>猫王</t>
   </si>
   <si>
     <t>25000</t>
@@ -274,7 +274,7 @@
     <t>1004</t>
   </si>
   <si>
-    <t>食人花王</t>
+    <t>花王</t>
   </si>
   <si>
     <t>5000000</t>
@@ -313,7 +313,7 @@
     <t>1006</t>
   </si>
   <si>
-    <t>巨型蝙蝠</t>
+    <t>蝙蝠王</t>
   </si>
   <si>
     <t>95000</t>
@@ -433,7 +433,7 @@
     <t>1011</t>
   </si>
   <si>
-    <t>巨型沙虫</t>
+    <t>沙虫王</t>
   </si>
   <si>
     <t>540000</t>
@@ -481,7 +481,7 @@
     <t>1013</t>
   </si>
   <si>
-    <t>巨型多角虫</t>
+    <t>角虫王</t>
   </si>
   <si>
     <t>1075000</t>
@@ -502,7 +502,7 @@
     <t>1014</t>
   </si>
   <si>
-    <t>变异蜈蚣</t>
+    <t>蜈蚣王</t>
   </si>
   <si>
     <t>1515000</t>
@@ -523,7 +523,7 @@
     <t>1015</t>
   </si>
   <si>
-    <t>变异钳虫</t>
+    <t>钳虫王</t>
   </si>
   <si>
     <t>2130000</t>
@@ -547,7 +547,7 @@
     <t>1016</t>
   </si>
   <si>
-    <t>触龙神</t>
+    <t>蠕虫王</t>
   </si>
   <si>
     <t>2995000</t>
@@ -568,7 +568,7 @@
     <t>1017</t>
   </si>
   <si>
-    <t>白野猪</t>
+    <t>猪王</t>
   </si>
   <si>
     <t>4215000</t>
@@ -589,7 +589,7 @@
     <t>1018</t>
   </si>
   <si>
-    <t>猪王</t>
+    <t>猪皇</t>
   </si>
   <si>
     <t>5900000</t>
@@ -610,7 +610,7 @@
     <t>1019</t>
   </si>
   <si>
-    <t>邪恶蝎蛇</t>
+    <t>蝎蛇王</t>
   </si>
   <si>
     <t>8300000</t>
@@ -631,7 +631,7 @@
     <t>1020</t>
   </si>
   <si>
-    <t>沃玛教主</t>
+    <t>恶魔教主</t>
   </si>
   <si>
     <t>11700000</t>
@@ -652,7 +652,7 @@
     <t>1021</t>
   </si>
   <si>
-    <t>沃玛教皇</t>
+    <t>恶魔教皇</t>
   </si>
   <si>
     <t>16500000</t>
@@ -673,7 +673,7 @@
     <t>1022</t>
   </si>
   <si>
-    <t>祖玛教主</t>
+    <t>邪魔教主</t>
   </si>
   <si>
     <t>23200000</t>
@@ -694,7 +694,7 @@
     <t>1023</t>
   </si>
   <si>
-    <t>祖玛教皇</t>
+    <t>邪魔教皇</t>
   </si>
   <si>
     <t>32600000</t>
@@ -715,7 +715,7 @@
     <t>1024</t>
   </si>
   <si>
-    <t>虹魔猪王</t>
+    <t>魔猪王</t>
   </si>
   <si>
     <t>45900000</t>
@@ -736,7 +736,7 @@
     <t>1025</t>
   </si>
   <si>
-    <t>千年妖王</t>
+    <t>烈焰王</t>
   </si>
   <si>
     <t>64550000</t>
@@ -757,7 +757,7 @@
     <t>1026</t>
   </si>
   <si>
-    <t>虹魔教主</t>
+    <t>大邪王</t>
   </si>
   <si>
     <t>90800000</t>
@@ -778,7 +778,7 @@
     <t>1027</t>
   </si>
   <si>
-    <t>恶灵尸王</t>
+    <t>尸魔王</t>
   </si>
   <si>
     <t>127750000</t>
@@ -799,7 +799,7 @@
     <t>1028</t>
   </si>
   <si>
-    <t>黄泉教主</t>
+    <t>骨魔王</t>
   </si>
   <si>
     <t>179650000</t>
@@ -841,7 +841,7 @@
     <t>1030</t>
   </si>
   <si>
-    <t>双头金刚</t>
+    <t>水龙王</t>
   </si>
   <si>
     <t>355450000</t>
@@ -862,7 +862,7 @@
     <t>1031</t>
   </si>
   <si>
-    <t>双头巨人</t>
+    <t>土龙王</t>
   </si>
   <si>
     <t>500000000</t>
@@ -883,7 +883,7 @@
     <t>1032</t>
   </si>
   <si>
-    <t>赤月恶魔</t>
+    <t>毒龙王</t>
   </si>
   <si>
     <t>703250000</t>
@@ -904,7 +904,7 @@
     <t>1033</t>
   </si>
   <si>
-    <t>魔龙教主</t>
+    <t>火龙王</t>
   </si>
   <si>
     <t>989150000</t>
@@ -925,7 +925,7 @@
     <t>1034</t>
   </si>
   <si>
-    <t>火龙神</t>
+    <t>冰龙王</t>
   </si>
   <si>
     <t>1391250000</t>
@@ -1282,7 +1282,7 @@
     <t>1051</t>
   </si>
   <si>
-    <t>幻影触龙神</t>
+    <t>幻影蠕虫王</t>
   </si>
   <si>
     <t>459127100000</t>
@@ -1303,7 +1303,7 @@
     <t>1052</t>
   </si>
   <si>
-    <t>幻影白野猪</t>
+    <t>幻影猪王</t>
   </si>
   <si>
     <t>645774800000</t>
@@ -1324,7 +1324,7 @@
     <t>1053</t>
   </si>
   <si>
-    <t>幻影猪王</t>
+    <t>幻影猪皇</t>
   </si>
   <si>
     <t>908299850000</t>
@@ -1366,7 +1366,7 @@
     <t>1055</t>
   </si>
   <si>
-    <t>幻影沃玛教主</t>
+    <t>幻影恶魔教主</t>
   </si>
   <si>
     <t>1796906800000</t>
@@ -1387,7 +1387,7 @@
     <t>1056</t>
   </si>
   <si>
-    <t>幻影沃玛教皇</t>
+    <t>幻影恶魔教皇</t>
   </si>
   <si>
     <t>2527398400000</t>
@@ -1408,7 +1408,7 @@
     <t>1057</t>
   </si>
   <si>
-    <t>幻影祖玛教主</t>
+    <t>幻影邪魔教主</t>
   </si>
   <si>
     <t>3554854700000</t>
@@ -1429,7 +1429,7 @@
     <t>1058</t>
   </si>
   <si>
-    <t>幻影祖玛教皇</t>
+    <t>幻影邪魔教皇</t>
   </si>
   <si>
     <t>5000000000000</t>
@@ -1471,7 +1471,7 @@
     <t>1060</t>
   </si>
   <si>
-    <t>幻影千年妖王</t>
+    <t>幻影烈焰王</t>
   </si>
   <si>
     <t>9891594400000</t>
@@ -1492,7 +1492,7 @@
     <t>1061</t>
   </si>
   <si>
-    <t>幻影虹魔教主</t>
+    <t>幻影大邪王</t>
   </si>
   <si>
     <t>13912797000000</t>
@@ -1513,7 +1513,7 @@
     <t>1062</t>
   </si>
   <si>
-    <t>幻影恶灵尸王</t>
+    <t>幻影尸魔王</t>
   </si>
   <si>
     <t>19568728000000</t>
@@ -1534,7 +1534,7 @@
     <t>1063</t>
   </si>
   <si>
-    <t>幻影黄泉教主</t>
+    <t>幻影骨魔王</t>
   </si>
   <si>
     <t>27523949000000</t>
@@ -1576,7 +1576,7 @@
     <t>1065</t>
   </si>
   <si>
-    <t>幻影双头金刚</t>
+    <t>幻影水龙王</t>
   </si>
   <si>
     <t>80000000000000</t>
@@ -1597,7 +1597,7 @@
     <t>1066</t>
   </si>
   <si>
-    <t>幻影双头巨人</t>
+    <t>幻影土龙王</t>
   </si>
   <si>
     <t>160000000000000</t>
@@ -1618,7 +1618,7 @@
     <t>1067</t>
   </si>
   <si>
-    <t>幻影赤月恶魔</t>
+    <t>幻影毒龙王</t>
   </si>
   <si>
     <t>320000000000000</t>
@@ -1639,7 +1639,7 @@
     <t>1068</t>
   </si>
   <si>
-    <t>幻影魔龙教主</t>
+    <t>幻影火龙王</t>
   </si>
   <si>
     <t>640000000000000</t>
@@ -1660,7 +1660,7 @@
     <t>1069</t>
   </si>
   <si>
-    <t>幻影火龙神</t>
+    <t>幻影冰龙王</t>
   </si>
   <si>
     <t>1000000000000000</t>
@@ -1963,7 +1963,7 @@
     <t>1086</t>
   </si>
   <si>
-    <t>噩梦触龙神</t>
+    <t>噩梦蠕虫王</t>
   </si>
   <si>
     <t>30000000000000000000</t>
@@ -1984,7 +1984,7 @@
     <t>1087</t>
   </si>
   <si>
-    <t>噩梦白野猪</t>
+    <t>噩梦猪王</t>
   </si>
   <si>
     <t>90000000000000000000</t>
@@ -2005,7 +2005,7 @@
     <t>1088</t>
   </si>
   <si>
-    <t>噩梦猪王</t>
+    <t>噩梦猪皇</t>
   </si>
   <si>
     <t>270000000000000000000</t>
@@ -2047,7 +2047,7 @@
     <t>1090</t>
   </si>
   <si>
-    <t>噩梦沃玛教主</t>
+    <t>噩梦恶魔教主</t>
   </si>
   <si>
     <t>2400000000000000000000</t>
@@ -2068,7 +2068,7 @@
     <t>1091</t>
   </si>
   <si>
-    <t>噩梦沃玛教皇</t>
+    <t>噩梦恶魔教皇</t>
   </si>
   <si>
     <t>7200000000000000000000</t>
@@ -2089,7 +2089,7 @@
     <t>1092</t>
   </si>
   <si>
-    <t>噩梦祖玛教主</t>
+    <t>噩梦邪魔教主</t>
   </si>
   <si>
     <t>21000000000000000000000</t>
@@ -2110,7 +2110,7 @@
     <t>1093</t>
   </si>
   <si>
-    <t>噩梦祖玛教皇</t>
+    <t>噩梦邪魔教皇</t>
   </si>
   <si>
     <t>63000000000000000000000</t>
@@ -2131,9 +2131,6 @@
     <t>1094</t>
   </si>
   <si>
-    <t>噩梦虹魔猪王</t>
-  </si>
-  <si>
     <t>180000000000000000000000</t>
   </si>
   <si>
@@ -2152,7 +2149,7 @@
     <t>1095</t>
   </si>
   <si>
-    <t>噩梦千年妖王</t>
+    <t>噩梦烈焰王</t>
   </si>
   <si>
     <t>540000000000000000000000</t>
@@ -2173,7 +2170,7 @@
     <t>1096</t>
   </si>
   <si>
-    <t>噩梦虹魔教主</t>
+    <t>噩梦大邪王</t>
   </si>
   <si>
     <t>1600000000000000000000000</t>
@@ -2191,7 +2188,7 @@
     <t>1097</t>
   </si>
   <si>
-    <t>噩梦恶灵尸王</t>
+    <t>噩梦尸魔王</t>
   </si>
   <si>
     <t>4800000000000000000000000</t>
@@ -2209,7 +2206,7 @@
     <t>1098</t>
   </si>
   <si>
-    <t>噩梦黄泉教主</t>
+    <t>噩梦骨魔王</t>
   </si>
   <si>
     <t>15000000000000000000000000</t>
@@ -2251,7 +2248,7 @@
     <t>1100</t>
   </si>
   <si>
-    <t>噩梦双头金刚</t>
+    <t>噩梦水龙王</t>
   </si>
   <si>
     <t>135000000000000000000000000</t>
@@ -2272,7 +2269,7 @@
     <t>1101</t>
   </si>
   <si>
-    <t>噩梦双头巨人</t>
+    <t>噩梦土龙王</t>
   </si>
   <si>
     <t>400000000000000000000000000</t>
@@ -2293,7 +2290,7 @@
     <t>1102</t>
   </si>
   <si>
-    <t>噩梦赤月恶魔</t>
+    <t>噩梦毒龙王</t>
   </si>
   <si>
     <t>1200000000000000000000000000</t>
@@ -2314,7 +2311,7 @@
     <t>1103</t>
   </si>
   <si>
-    <t>噩梦魔龙教主</t>
+    <t>噩梦火龙王</t>
   </si>
   <si>
     <t>3600000000000000000000000000</t>
@@ -2335,7 +2332,7 @@
     <t>1104</t>
   </si>
   <si>
-    <t>噩梦火龙神</t>
+    <t>噩梦冰龙王</t>
   </si>
   <si>
     <t>640000000000000000000000000</t>
@@ -2635,7 +2632,7 @@
     <t>1121</t>
   </si>
   <si>
-    <t>地狱触龙神</t>
+    <t>地狱蠕虫王</t>
   </si>
   <si>
     <t>470000000000</t>
@@ -2647,7 +2644,7 @@
     <t>1122</t>
   </si>
   <si>
-    <t>地狱白野猪</t>
+    <t>地狱猪王</t>
   </si>
   <si>
     <t>10123</t>
@@ -2656,7 +2653,7 @@
     <t>1123</t>
   </si>
   <si>
-    <t>地狱猪王</t>
+    <t>地狱猪皇</t>
   </si>
   <si>
     <t>490000000000</t>
@@ -2680,7 +2677,7 @@
     <t>1125</t>
   </si>
   <si>
-    <t>地狱沃玛教主</t>
+    <t>地狱恶魔教主</t>
   </si>
   <si>
     <t>510000000000</t>
@@ -2692,7 +2689,7 @@
     <t>1126</t>
   </si>
   <si>
-    <t>地狱沃玛教皇</t>
+    <t>地狱恶魔教皇</t>
   </si>
   <si>
     <t>10127</t>
@@ -2701,7 +2698,7 @@
     <t>1127</t>
   </si>
   <si>
-    <t>地狱祖玛教主</t>
+    <t>地狱邪魔教主</t>
   </si>
   <si>
     <t>530000000000</t>
@@ -2713,7 +2710,7 @@
     <t>1128</t>
   </si>
   <si>
-    <t>地狱祖玛教皇</t>
+    <t>地狱邪魔教皇</t>
   </si>
   <si>
     <t>540000000000</t>
@@ -2725,9 +2722,6 @@
     <t>1129</t>
   </si>
   <si>
-    <t>地狱虹魔猪王</t>
-  </si>
-  <si>
     <t>550000000000</t>
   </si>
   <si>
@@ -2737,7 +2731,7 @@
     <t>1130</t>
   </si>
   <si>
-    <t>地狱千年妖王</t>
+    <t>地狱烈焰王</t>
   </si>
   <si>
     <t>10131</t>
@@ -2746,7 +2740,7 @@
     <t>1131</t>
   </si>
   <si>
-    <t>地狱虹魔教主</t>
+    <t>地狱大邪王</t>
   </si>
   <si>
     <t>570000000000</t>
@@ -2758,7 +2752,7 @@
     <t>1132</t>
   </si>
   <si>
-    <t>地狱恶灵尸王</t>
+    <t>地狱尸魔王</t>
   </si>
   <si>
     <t>580000000000</t>
@@ -2770,7 +2764,7 @@
     <t>1133</t>
   </si>
   <si>
-    <t>地狱黄泉教主</t>
+    <t>地狱骨魔王</t>
   </si>
   <si>
     <t>590000000000</t>
@@ -2791,7 +2785,7 @@
     <t>1135</t>
   </si>
   <si>
-    <t>地狱双头金刚</t>
+    <t>地狱水龙王</t>
   </si>
   <si>
     <t>610000000000</t>
@@ -2803,7 +2797,7 @@
     <t>1136</t>
   </si>
   <si>
-    <t>地狱双头巨人</t>
+    <t>地狱土龙王</t>
   </si>
   <si>
     <t>620000000000</t>
@@ -2815,7 +2809,7 @@
     <t>1137</t>
   </si>
   <si>
-    <t>地狱赤月恶魔</t>
+    <t>地狱毒龙王</t>
   </si>
   <si>
     <t>630000000000</t>
@@ -2827,7 +2821,7 @@
     <t>1138</t>
   </si>
   <si>
-    <t>地狱魔龙教主</t>
+    <t>地狱火龙王</t>
   </si>
   <si>
     <t>640000000000</t>
@@ -2839,7 +2833,7 @@
     <t>1139</t>
   </si>
   <si>
-    <t>地狱火龙神</t>
+    <t>地狱冰龙王</t>
   </si>
   <si>
     <t>650000000000</t>
@@ -6080,7 +6074,7 @@
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
+      <c r="B41" s="1"/>
       <c r="C41" s="1" t="s">
         <v>285</v>
       </c>
@@ -6139,7 +6133,7 @@
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
+      <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
         <v>292</v>
       </c>
@@ -6198,7 +6192,7 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
+      <c r="B43" s="1"/>
       <c r="C43" s="1" t="s">
         <v>299</v>
       </c>
@@ -6257,7 +6251,7 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
+      <c r="B44" s="1"/>
       <c r="C44" s="1" t="s">
         <v>306</v>
       </c>
@@ -6316,7 +6310,7 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
+      <c r="B45" s="1"/>
       <c r="C45" s="1" t="s">
         <v>313</v>
       </c>
@@ -6375,7 +6369,7 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
+      <c r="B46" s="1"/>
       <c r="C46" s="1" t="s">
         <v>320</v>
       </c>
@@ -6436,7 +6430,7 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
+      <c r="B47" s="1"/>
       <c r="C47" s="1" t="s">
         <v>327</v>
       </c>
@@ -6497,7 +6491,7 @@
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
+      <c r="B48" s="1"/>
       <c r="C48" s="1" t="s">
         <v>334</v>
       </c>
@@ -6558,7 +6552,7 @@
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
+      <c r="B49" s="1"/>
       <c r="C49" s="1" t="s">
         <v>341</v>
       </c>
@@ -6619,7 +6613,7 @@
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
+      <c r="B50" s="1"/>
       <c r="C50" s="1" t="s">
         <v>348</v>
       </c>
@@ -6680,7 +6674,7 @@
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
+      <c r="B51" s="1"/>
       <c r="C51" s="1" t="s">
         <v>355</v>
       </c>
@@ -6742,7 +6736,7 @@
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
+      <c r="B52" s="1"/>
       <c r="C52" s="1" t="s">
         <v>362</v>
       </c>
@@ -6804,7 +6798,7 @@
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
+      <c r="B53" s="1"/>
       <c r="C53" s="1" t="s">
         <v>369</v>
       </c>
@@ -6866,7 +6860,7 @@
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
+      <c r="B54" s="1"/>
       <c r="C54" s="1" t="s">
         <v>376</v>
       </c>
@@ -6928,7 +6922,7 @@
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
+      <c r="B55" s="1"/>
       <c r="C55" s="1" t="s">
         <v>383</v>
       </c>
@@ -6990,7 +6984,7 @@
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
+      <c r="B56" s="1"/>
       <c r="C56" s="1" t="s">
         <v>390</v>
       </c>
@@ -7054,7 +7048,7 @@
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
+      <c r="B57" s="1"/>
       <c r="C57" s="1" t="s">
         <v>397</v>
       </c>
@@ -7118,7 +7112,7 @@
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
+      <c r="B58" s="1"/>
       <c r="C58" s="1" t="s">
         <v>404</v>
       </c>
@@ -7182,7 +7176,7 @@
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
+      <c r="B59" s="1"/>
       <c r="C59" s="1" t="s">
         <v>411</v>
       </c>
@@ -7246,7 +7240,7 @@
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
+      <c r="B60" s="1"/>
       <c r="C60" s="1" t="s">
         <v>418</v>
       </c>
@@ -7310,7 +7304,7 @@
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
+      <c r="B61" s="1"/>
       <c r="C61" s="1" t="s">
         <v>425</v>
       </c>
@@ -7374,7 +7368,7 @@
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
+      <c r="B62" s="1"/>
       <c r="C62" s="1" t="s">
         <v>432</v>
       </c>
@@ -7438,7 +7432,7 @@
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
+      <c r="B63" s="1"/>
       <c r="C63" s="1" t="s">
         <v>439</v>
       </c>
@@ -7502,7 +7496,7 @@
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
+      <c r="B64" s="1"/>
       <c r="C64" s="1" t="s">
         <v>446</v>
       </c>
@@ -7566,7 +7560,7 @@
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
+      <c r="B65" s="1"/>
       <c r="C65" s="1" t="s">
         <v>453</v>
       </c>
@@ -7630,7 +7624,7 @@
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
+      <c r="B66" s="1"/>
       <c r="C66" s="1" t="s">
         <v>460</v>
       </c>
@@ -7694,7 +7688,7 @@
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
+      <c r="B67" s="1"/>
       <c r="C67" s="1" t="s">
         <v>467</v>
       </c>
@@ -7758,7 +7752,7 @@
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
+      <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
         <v>474</v>
       </c>
@@ -7822,7 +7816,7 @@
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
+      <c r="B69" s="1"/>
       <c r="C69" s="1" t="s">
         <v>481</v>
       </c>
@@ -7886,7 +7880,7 @@
     </row>
     <row r="70" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
+      <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
         <v>488</v>
       </c>
@@ -7949,7 +7943,7 @@
     </row>
     <row r="71" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
+      <c r="B71" s="1"/>
       <c r="C71" s="1" t="s">
         <v>495</v>
       </c>
@@ -8013,7 +8007,7 @@
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
+      <c r="B72" s="1"/>
       <c r="C72" s="1" t="s">
         <v>502</v>
       </c>
@@ -8077,7 +8071,7 @@
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
+      <c r="B73" s="1"/>
       <c r="C73" s="1" t="s">
         <v>509</v>
       </c>
@@ -8141,7 +8135,7 @@
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
+      <c r="B74" s="1"/>
       <c r="C74" s="1" t="s">
         <v>516</v>
       </c>
@@ -8205,7 +8199,7 @@
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
+      <c r="B75" s="1"/>
       <c r="C75" s="1" t="s">
         <v>523</v>
       </c>
@@ -9788,16 +9782,16 @@
         <v>3</v>
       </c>
       <c r="F100" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="G100" s="12" t="s">
         <v>682</v>
       </c>
-      <c r="G100" s="12" t="s">
+      <c r="H100" s="11" t="s">
         <v>683</v>
       </c>
-      <c r="H100" s="11" t="s">
+      <c r="I100" s="13" t="s">
         <v>684</v>
-      </c>
-      <c r="I100" s="13" t="s">
-        <v>685</v>
       </c>
       <c r="J100" s="1">
         <f t="shared" si="22"/>
@@ -9825,10 +9819,10 @@
         <v>0</v>
       </c>
       <c r="Q100" s="11" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="R100" s="11" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="T100" s="1" t="s">
         <v>151</v>
@@ -9841,25 +9835,25 @@
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>687</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>688</v>
       </c>
       <c r="E101" s="1">
         <v>3</v>
       </c>
       <c r="F101" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="G101" s="12" t="s">
         <v>689</v>
       </c>
-      <c r="G101" s="12" t="s">
+      <c r="H101" s="11" t="s">
         <v>690</v>
       </c>
-      <c r="H101" s="11" t="s">
+      <c r="I101" s="13" t="s">
         <v>691</v>
-      </c>
-      <c r="I101" s="13" t="s">
-        <v>692</v>
       </c>
       <c r="J101" s="1">
         <f t="shared" ref="J101:M101" si="26">J100+8</f>
@@ -9887,10 +9881,10 @@
         <v>0</v>
       </c>
       <c r="Q101" s="11" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="R101" s="11" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="T101" s="1" t="s">
         <v>151</v>
@@ -9905,25 +9899,25 @@
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>694</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>695</v>
       </c>
       <c r="E102" s="1">
         <v>3</v>
       </c>
       <c r="F102" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="G102" s="12" t="s">
         <v>696</v>
-      </c>
-      <c r="G102" s="12" t="s">
-        <v>697</v>
       </c>
       <c r="H102" s="11" t="s">
         <v>605</v>
       </c>
       <c r="I102" s="13" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="J102" s="1">
         <f t="shared" ref="J102:M102" si="27">J101+8</f>
@@ -9951,10 +9945,10 @@
         <v>0</v>
       </c>
       <c r="Q102" s="11" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="R102" s="11" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="T102" s="1" t="s">
         <v>151</v>
@@ -9969,25 +9963,25 @@
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>700</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>701</v>
       </c>
       <c r="E103" s="1">
         <v>3</v>
       </c>
       <c r="F103" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="G103" s="12" t="s">
         <v>702</v>
-      </c>
-      <c r="G103" s="12" t="s">
-        <v>703</v>
       </c>
       <c r="H103" s="11" t="s">
         <v>610</v>
       </c>
       <c r="I103" s="13" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="J103" s="1">
         <f t="shared" ref="J103:M103" si="28">J102+8</f>
@@ -10015,10 +10009,10 @@
         <v>0</v>
       </c>
       <c r="Q103" s="11" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="R103" s="11" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="T103" s="1" t="s">
         <v>151</v>
@@ -10033,25 +10027,25 @@
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>706</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>707</v>
       </c>
       <c r="E104" s="1">
         <v>3</v>
       </c>
       <c r="F104" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="G104" s="12" t="s">
         <v>708</v>
       </c>
-      <c r="G104" s="12" t="s">
+      <c r="H104" s="11" t="s">
         <v>709</v>
       </c>
-      <c r="H104" s="11" t="s">
+      <c r="I104" s="13" t="s">
         <v>710</v>
-      </c>
-      <c r="I104" s="13" t="s">
-        <v>711</v>
       </c>
       <c r="J104" s="1">
         <f t="shared" ref="J104:M104" si="29">J103+8</f>
@@ -10079,10 +10073,10 @@
         <v>0</v>
       </c>
       <c r="Q104" s="11" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="R104" s="11" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="T104" s="1" t="s">
         <v>151</v>
@@ -10097,25 +10091,25 @@
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>714</v>
       </c>
       <c r="E105" s="1">
         <v>3</v>
       </c>
       <c r="F105" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="G105" s="12" t="s">
         <v>715</v>
       </c>
-      <c r="G105" s="12" t="s">
+      <c r="H105" s="11" t="s">
         <v>716</v>
       </c>
-      <c r="H105" s="11" t="s">
+      <c r="I105" s="13" t="s">
         <v>717</v>
-      </c>
-      <c r="I105" s="13" t="s">
-        <v>718</v>
       </c>
       <c r="J105" s="1">
         <f t="shared" ref="J105:M105" si="30">J104+8</f>
@@ -10143,10 +10137,10 @@
         <v>0</v>
       </c>
       <c r="Q105" s="11" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="R105" s="11" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="T105" s="1" t="s">
         <v>151</v>
@@ -10161,25 +10155,25 @@
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>721</v>
       </c>
       <c r="E106" s="1">
         <v>3</v>
       </c>
       <c r="F106" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="G106" s="12" t="s">
         <v>722</v>
       </c>
-      <c r="G106" s="12" t="s">
+      <c r="H106" s="11" t="s">
         <v>723</v>
       </c>
-      <c r="H106" s="11" t="s">
+      <c r="I106" s="13" t="s">
         <v>724</v>
-      </c>
-      <c r="I106" s="13" t="s">
-        <v>725</v>
       </c>
       <c r="J106" s="1">
         <f t="shared" ref="J106:J115" si="31">J105+15</f>
@@ -10207,10 +10201,10 @@
         <v>0</v>
       </c>
       <c r="Q106" s="11" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="R106" s="11" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T106" s="1" t="s">
         <v>151</v>
@@ -10225,25 +10219,25 @@
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>727</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>728</v>
       </c>
       <c r="E107" s="1">
         <v>3</v>
       </c>
       <c r="F107" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="G107" s="12" t="s">
         <v>729</v>
       </c>
-      <c r="G107" s="12" t="s">
+      <c r="H107" s="11" t="s">
         <v>730</v>
       </c>
-      <c r="H107" s="11" t="s">
+      <c r="I107" s="13" t="s">
         <v>731</v>
-      </c>
-      <c r="I107" s="13" t="s">
-        <v>732</v>
       </c>
       <c r="J107" s="1">
         <f t="shared" si="31"/>
@@ -10271,10 +10265,10 @@
         <v>0</v>
       </c>
       <c r="Q107" s="11" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="R107" s="11" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="T107" s="1" t="s">
         <v>151</v>
@@ -10289,25 +10283,25 @@
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>734</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>735</v>
       </c>
       <c r="E108" s="1">
         <v>3</v>
       </c>
       <c r="F108" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="G108" s="12" t="s">
         <v>736</v>
       </c>
-      <c r="G108" s="12" t="s">
+      <c r="H108" s="11" t="s">
         <v>737</v>
       </c>
-      <c r="H108" s="11" t="s">
+      <c r="I108" s="13" t="s">
         <v>738</v>
-      </c>
-      <c r="I108" s="13" t="s">
-        <v>739</v>
       </c>
       <c r="J108" s="1">
         <f t="shared" si="31"/>
@@ -10335,10 +10329,10 @@
         <v>0</v>
       </c>
       <c r="Q108" s="11" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="R108" s="11" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="T108" s="1" t="s">
         <v>151</v>
@@ -10353,25 +10347,25 @@
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>741</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>742</v>
       </c>
       <c r="E109" s="1">
         <v>3</v>
       </c>
       <c r="F109" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="G109" s="12" t="s">
         <v>743</v>
       </c>
-      <c r="G109" s="12" t="s">
+      <c r="H109" s="11" t="s">
         <v>744</v>
       </c>
-      <c r="H109" s="11" t="s">
+      <c r="I109" s="13" t="s">
         <v>745</v>
-      </c>
-      <c r="I109" s="13" t="s">
-        <v>746</v>
       </c>
       <c r="J109" s="1">
         <f t="shared" si="31"/>
@@ -10399,10 +10393,10 @@
         <v>0</v>
       </c>
       <c r="Q109" s="11" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="R109" s="11" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="T109" s="1" t="s">
         <v>151</v>
@@ -10417,25 +10411,25 @@
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>748</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>749</v>
       </c>
       <c r="E110" s="1">
         <v>3</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G110" s="12" t="s">
         <v>671</v>
       </c>
       <c r="H110" s="11" t="s">
+        <v>750</v>
+      </c>
+      <c r="I110" s="13" t="s">
         <v>751</v>
-      </c>
-      <c r="I110" s="13" t="s">
-        <v>752</v>
       </c>
       <c r="J110" s="1">
         <f t="shared" si="31"/>
@@ -10463,10 +10457,10 @@
         <v>0</v>
       </c>
       <c r="Q110" s="11" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="R110" s="11" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="T110" s="1" t="s">
         <v>151</v>
@@ -10481,25 +10475,25 @@
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="D111" s="2" t="s">
         <v>754</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>755</v>
       </c>
       <c r="E111" s="2">
         <v>4</v>
       </c>
-      <c r="F111" s="2" t="s">
+      <c r="F111" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="G111" s="14" t="s">
         <v>756</v>
       </c>
-      <c r="G111" s="14" t="s">
+      <c r="H111" s="15" t="s">
+        <v>756</v>
+      </c>
+      <c r="I111" s="16" t="s">
         <v>757</v>
-      </c>
-      <c r="H111" s="15" t="s">
-        <v>757</v>
-      </c>
-      <c r="I111" s="16" t="s">
-        <v>758</v>
       </c>
       <c r="J111" s="2">
         <v>1500</v>
@@ -10523,10 +10517,10 @@
         <v>90</v>
       </c>
       <c r="Q111" s="15" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="R111" s="15" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="T111" s="2" t="s">
         <v>151</v>
@@ -10539,25 +10533,25 @@
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>760</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>761</v>
       </c>
       <c r="E112" s="1">
         <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="G112" s="12" t="s">
         <v>762</v>
       </c>
-      <c r="G112" s="12" t="s">
+      <c r="H112" s="11" t="s">
+        <v>762</v>
+      </c>
+      <c r="I112" s="13" t="s">
         <v>763</v>
-      </c>
-      <c r="H112" s="11" t="s">
-        <v>763</v>
-      </c>
-      <c r="I112" s="13" t="s">
-        <v>764</v>
       </c>
       <c r="J112" s="1">
         <f>J111+100</f>
@@ -10586,10 +10580,10 @@
         <v>90</v>
       </c>
       <c r="Q112" s="11" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="R112" s="11" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="T112" s="1" t="s">
         <v>151</v>
@@ -10602,25 +10596,25 @@
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>766</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>767</v>
       </c>
       <c r="E113" s="1">
         <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="G113" s="12" t="s">
         <v>768</v>
       </c>
-      <c r="G113" s="12" t="s">
+      <c r="H113" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="I113" s="13" t="s">
         <v>769</v>
-      </c>
-      <c r="H113" s="11" t="s">
-        <v>769</v>
-      </c>
-      <c r="I113" s="13" t="s">
-        <v>770</v>
       </c>
       <c r="J113" s="1">
         <f>J112+100</f>
@@ -10649,10 +10643,10 @@
         <v>90</v>
       </c>
       <c r="Q113" s="11" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="R113" s="11" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="T113" s="1" t="s">
         <v>151</v>
@@ -10665,25 +10659,25 @@
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>772</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>773</v>
       </c>
       <c r="E114" s="1">
         <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="G114" s="12" t="s">
         <v>774</v>
       </c>
-      <c r="G114" s="12" t="s">
+      <c r="H114" s="11" t="s">
+        <v>774</v>
+      </c>
+      <c r="I114" s="13" t="s">
         <v>775</v>
-      </c>
-      <c r="H114" s="11" t="s">
-        <v>775</v>
-      </c>
-      <c r="I114" s="13" t="s">
-        <v>776</v>
       </c>
       <c r="J114" s="1">
         <f>J113+100</f>
@@ -10712,10 +10706,10 @@
         <v>90</v>
       </c>
       <c r="Q114" s="11" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="R114" s="11" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="T114" s="1" t="s">
         <v>151</v>
@@ -10728,25 +10722,25 @@
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>778</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>779</v>
       </c>
       <c r="E115" s="1">
         <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="G115" s="12" t="s">
         <v>780</v>
       </c>
-      <c r="G115" s="12" t="s">
+      <c r="H115" s="11" t="s">
+        <v>780</v>
+      </c>
+      <c r="I115" s="13" t="s">
         <v>781</v>
-      </c>
-      <c r="H115" s="11" t="s">
-        <v>781</v>
-      </c>
-      <c r="I115" s="13" t="s">
-        <v>782</v>
       </c>
       <c r="J115" s="1">
         <f>J114+100</f>
@@ -10775,10 +10769,10 @@
         <v>90</v>
       </c>
       <c r="Q115" s="11" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="R115" s="11" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="T115" s="1" t="s">
         <v>151</v>
@@ -10791,25 +10785,25 @@
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>784</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>785</v>
       </c>
       <c r="E116" s="1">
         <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="G116" s="12" t="s">
         <v>786</v>
       </c>
-      <c r="G116" s="12" t="s">
+      <c r="H116" s="11" t="s">
+        <v>786</v>
+      </c>
+      <c r="I116" s="13" t="s">
         <v>787</v>
-      </c>
-      <c r="H116" s="11" t="s">
-        <v>787</v>
-      </c>
-      <c r="I116" s="13" t="s">
-        <v>788</v>
       </c>
       <c r="J116" s="1">
         <f t="shared" ref="J116:J145" si="37">J115+200</f>
@@ -10838,10 +10832,10 @@
         <v>90</v>
       </c>
       <c r="Q116" s="11" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="R116" s="11" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="T116" s="1" t="s">
         <v>151</v>
@@ -10856,25 +10850,25 @@
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>790</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>791</v>
       </c>
       <c r="E117" s="1">
         <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="G117" s="12" t="s">
         <v>792</v>
       </c>
-      <c r="G117" s="12" t="s">
+      <c r="H117" s="11" t="s">
+        <v>792</v>
+      </c>
+      <c r="I117" s="13" t="s">
         <v>793</v>
-      </c>
-      <c r="H117" s="11" t="s">
-        <v>793</v>
-      </c>
-      <c r="I117" s="13" t="s">
-        <v>794</v>
       </c>
       <c r="J117" s="1">
         <f t="shared" si="37"/>
@@ -10903,10 +10897,10 @@
         <v>90</v>
       </c>
       <c r="Q117" s="11" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="R117" s="11" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="T117" s="1" t="s">
         <v>151</v>
@@ -10921,25 +10915,25 @@
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>796</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>797</v>
       </c>
       <c r="E118" s="1">
         <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="G118" s="12" t="s">
         <v>798</v>
       </c>
-      <c r="G118" s="12" t="s">
+      <c r="H118" s="11" t="s">
+        <v>798</v>
+      </c>
+      <c r="I118" s="13" t="s">
         <v>799</v>
-      </c>
-      <c r="H118" s="11" t="s">
-        <v>799</v>
-      </c>
-      <c r="I118" s="13" t="s">
-        <v>800</v>
       </c>
       <c r="J118" s="1">
         <f t="shared" si="37"/>
@@ -10968,10 +10962,10 @@
         <v>90</v>
       </c>
       <c r="Q118" s="11" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="R118" s="11" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="T118" s="1" t="s">
         <v>151</v>
@@ -10986,25 +10980,25 @@
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>802</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>803</v>
       </c>
       <c r="E119" s="1">
         <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="G119" s="12" t="s">
         <v>804</v>
       </c>
-      <c r="G119" s="12" t="s">
+      <c r="H119" s="11" t="s">
+        <v>804</v>
+      </c>
+      <c r="I119" s="13" t="s">
         <v>805</v>
-      </c>
-      <c r="H119" s="11" t="s">
-        <v>805</v>
-      </c>
-      <c r="I119" s="13" t="s">
-        <v>806</v>
       </c>
       <c r="J119" s="1">
         <f t="shared" si="37"/>
@@ -11033,10 +11027,10 @@
         <v>90</v>
       </c>
       <c r="Q119" s="11" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="R119" s="11" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="T119" s="1" t="s">
         <v>151</v>
@@ -11051,25 +11045,25 @@
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>808</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>809</v>
       </c>
       <c r="E120" s="1">
         <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="G120" s="12" t="s">
         <v>810</v>
       </c>
-      <c r="G120" s="12" t="s">
+      <c r="H120" s="11" t="s">
+        <v>810</v>
+      </c>
+      <c r="I120" s="13" t="s">
         <v>811</v>
-      </c>
-      <c r="H120" s="11" t="s">
-        <v>811</v>
-      </c>
-      <c r="I120" s="13" t="s">
-        <v>812</v>
       </c>
       <c r="J120" s="1">
         <f t="shared" si="37"/>
@@ -11098,10 +11092,10 @@
         <v>90</v>
       </c>
       <c r="Q120" s="11" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="R120" s="11" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="T120" s="1" t="s">
         <v>151</v>
@@ -11114,25 +11108,25 @@
     </row>
     <row r="121" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C121" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>814</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>815</v>
       </c>
       <c r="E121" s="1">
         <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="G121" s="12" t="s">
+        <v>757</v>
+      </c>
+      <c r="H121" s="11" t="s">
+        <v>757</v>
+      </c>
+      <c r="I121" s="13" t="s">
         <v>816</v>
-      </c>
-      <c r="G121" s="12" t="s">
-        <v>758</v>
-      </c>
-      <c r="H121" s="11" t="s">
-        <v>758</v>
-      </c>
-      <c r="I121" s="13" t="s">
-        <v>817</v>
       </c>
       <c r="J121" s="1">
         <f t="shared" si="37"/>
@@ -11162,10 +11156,10 @@
         <v>90</v>
       </c>
       <c r="Q121" s="11" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="R121" s="11" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="T121" s="1" t="s">
         <v>151</v>
@@ -11178,25 +11172,25 @@
     </row>
     <row r="122" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C122" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>819</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>820</v>
       </c>
       <c r="E122" s="1">
         <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="G122" s="12" t="s">
         <v>821</v>
       </c>
-      <c r="G122" s="12" t="s">
+      <c r="H122" s="11" t="s">
+        <v>821</v>
+      </c>
+      <c r="I122" s="13" t="s">
         <v>822</v>
-      </c>
-      <c r="H122" s="11" t="s">
-        <v>822</v>
-      </c>
-      <c r="I122" s="13" t="s">
-        <v>823</v>
       </c>
       <c r="J122" s="1">
         <f t="shared" si="37"/>
@@ -11226,10 +11220,10 @@
         <v>90</v>
       </c>
       <c r="Q122" s="11" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="R122" s="11" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="T122" s="1" t="s">
         <v>151</v>
@@ -11242,25 +11236,25 @@
     </row>
     <row r="123" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C123" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>825</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>826</v>
       </c>
       <c r="E123" s="1">
         <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="G123" s="12" t="s">
         <v>827</v>
       </c>
-      <c r="G123" s="12" t="s">
+      <c r="H123" s="11" t="s">
+        <v>827</v>
+      </c>
+      <c r="I123" s="13" t="s">
         <v>828</v>
-      </c>
-      <c r="H123" s="11" t="s">
-        <v>828</v>
-      </c>
-      <c r="I123" s="13" t="s">
-        <v>829</v>
       </c>
       <c r="J123" s="1">
         <f t="shared" si="37"/>
@@ -11290,10 +11284,10 @@
         <v>90</v>
       </c>
       <c r="Q123" s="11" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="R123" s="11" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="T123" s="1" t="s">
         <v>151</v>
@@ -11306,25 +11300,25 @@
     </row>
     <row r="124" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C124" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>831</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>832</v>
       </c>
       <c r="E124" s="1">
         <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="G124" s="12" t="s">
         <v>833</v>
       </c>
-      <c r="G124" s="12" t="s">
+      <c r="H124" s="11" t="s">
+        <v>833</v>
+      </c>
+      <c r="I124" s="13" t="s">
         <v>834</v>
-      </c>
-      <c r="H124" s="11" t="s">
-        <v>834</v>
-      </c>
-      <c r="I124" s="13" t="s">
-        <v>835</v>
       </c>
       <c r="J124" s="1">
         <f t="shared" si="37"/>
@@ -11354,10 +11348,10 @@
         <v>90</v>
       </c>
       <c r="Q124" s="11" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="R124" s="11" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="T124" s="1" t="s">
         <v>151</v>
@@ -11370,25 +11364,25 @@
     </row>
     <row r="125" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C125" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>837</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>838</v>
       </c>
       <c r="E125" s="1">
         <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="G125" s="12" t="s">
         <v>839</v>
       </c>
-      <c r="G125" s="12" t="s">
+      <c r="H125" s="11" t="s">
+        <v>839</v>
+      </c>
+      <c r="I125" s="13" t="s">
         <v>840</v>
-      </c>
-      <c r="H125" s="11" t="s">
-        <v>840</v>
-      </c>
-      <c r="I125" s="13" t="s">
-        <v>841</v>
       </c>
       <c r="J125" s="1">
         <f t="shared" si="37"/>
@@ -11418,10 +11412,10 @@
         <v>90</v>
       </c>
       <c r="Q125" s="11" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="R125" s="11" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="T125" s="1" t="s">
         <v>151</v>
@@ -11434,22 +11428,22 @@
     </row>
     <row r="126" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A126" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="B126" s="3" t="s">
-        <v>843</v>
-      </c>
-      <c r="C126" s="1" t="s">
+      <c r="D126" s="1" t="s">
         <v>844</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>845</v>
       </c>
       <c r="E126" s="1">
         <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G126" s="4">
         <v>1</v>
@@ -11487,10 +11481,10 @@
         <v>90</v>
       </c>
       <c r="Q126" s="11" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="R126" s="11" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="T126" s="1" t="s">
         <v>151</v>
@@ -11503,22 +11497,22 @@
     </row>
     <row r="127" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A127" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C127" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>848</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>849</v>
       </c>
       <c r="E127" s="1">
         <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="G127" s="4">
         <v>1</v>
@@ -11556,10 +11550,10 @@
         <v>90</v>
       </c>
       <c r="Q127" s="11" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="R127" s="11" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="T127" s="1" t="s">
         <v>151</v>
@@ -11572,22 +11566,22 @@
     </row>
     <row r="128" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A128" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C128" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>852</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>853</v>
       </c>
       <c r="E128" s="1">
         <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="G128" s="4">
         <v>1</v>
@@ -11625,10 +11619,10 @@
         <v>90</v>
       </c>
       <c r="Q128" s="11" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="R128" s="11" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="T128" s="1" t="s">
         <v>151</v>
@@ -11641,22 +11635,22 @@
     </row>
     <row r="129" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A129" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C129" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>855</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>856</v>
       </c>
       <c r="E129" s="1">
         <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G129" s="4">
         <v>1</v>
@@ -11694,10 +11688,10 @@
         <v>90</v>
       </c>
       <c r="Q129" s="11" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="R129" s="11" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="T129" s="1" t="s">
         <v>151</v>
@@ -11710,22 +11704,22 @@
     </row>
     <row r="130" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A130" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C130" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>859</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>860</v>
       </c>
       <c r="E130" s="1">
         <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="G130" s="4">
         <v>1</v>
@@ -11763,10 +11757,10 @@
         <v>90</v>
       </c>
       <c r="Q130" s="11" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="R130" s="11" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="T130" s="1" t="s">
         <v>151</v>
@@ -11779,22 +11773,22 @@
     </row>
     <row r="131" customHeight="1" spans="1:21">
       <c r="A131" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C131" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>863</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>864</v>
       </c>
       <c r="E131" s="1">
         <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="G131" s="4">
         <v>1</v>
@@ -11832,10 +11826,10 @@
         <v>90</v>
       </c>
       <c r="Q131" s="11" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="R131" s="11" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="T131" s="1" t="s">
         <v>151</v>
@@ -11846,22 +11840,22 @@
     </row>
     <row r="132" customHeight="1" spans="1:21">
       <c r="A132" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C132" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>867</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>868</v>
       </c>
       <c r="E132" s="1">
         <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="G132" s="4">
         <v>1</v>
@@ -11899,10 +11893,10 @@
         <v>90</v>
       </c>
       <c r="Q132" s="11" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="R132" s="11" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="T132" s="1" t="s">
         <v>151</v>
@@ -11913,22 +11907,22 @@
     </row>
     <row r="133" customHeight="1" spans="1:21">
       <c r="A133" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C133" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>870</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>871</v>
       </c>
       <c r="E133" s="1">
         <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G133" s="4">
         <v>1</v>
@@ -11966,10 +11960,10 @@
         <v>90</v>
       </c>
       <c r="Q133" s="11" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="R133" s="11" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="T133" s="1" t="s">
         <v>151</v>
@@ -11980,22 +11974,22 @@
     </row>
     <row r="134" customHeight="1" spans="1:21">
       <c r="A134" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C134" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>874</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>875</v>
       </c>
       <c r="E134" s="1">
         <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="G134" s="4">
         <v>1</v>
@@ -12033,10 +12027,10 @@
         <v>90</v>
       </c>
       <c r="Q134" s="11" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="R134" s="11" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="T134" s="1" t="s">
         <v>151</v>
@@ -12047,22 +12041,22 @@
     </row>
     <row r="135" customHeight="1" spans="1:21">
       <c r="A135" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C135" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>878</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>879</v>
       </c>
       <c r="E135" s="1">
         <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>880</v>
+        <v>455</v>
       </c>
       <c r="G135" s="4">
         <v>1</v>
@@ -12100,10 +12094,10 @@
         <v>90</v>
       </c>
       <c r="Q135" s="11" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="R135" s="11" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="T135" s="1" t="s">
         <v>151</v>
@@ -12114,22 +12108,22 @@
     </row>
     <row r="136" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A136" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="G136" s="4">
         <v>1</v>
@@ -12167,10 +12161,10 @@
         <v>90</v>
       </c>
       <c r="Q136" s="11" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="R136" s="11" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="T136" s="1" t="s">
         <v>151</v>
@@ -12183,22 +12177,22 @@
     </row>
     <row r="137" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A137" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E137" s="1">
         <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="G137" s="4">
         <v>1</v>
@@ -12236,10 +12230,10 @@
         <v>90</v>
       </c>
       <c r="Q137" s="11" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="R137" s="11" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="T137" s="1" t="s">
         <v>151</v>
@@ -12252,22 +12246,22 @@
     </row>
     <row r="138" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A138" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="E138" s="1">
         <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G138" s="4">
         <v>1</v>
@@ -12305,10 +12299,10 @@
         <v>90</v>
       </c>
       <c r="Q138" s="11" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="R138" s="11" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="T138" s="1" t="s">
         <v>151</v>
@@ -12321,22 +12315,22 @@
     </row>
     <row r="139" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A139" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="E139" s="1">
         <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="G139" s="4">
         <v>1</v>
@@ -12374,10 +12368,10 @@
         <v>90</v>
       </c>
       <c r="Q139" s="11" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="R139" s="11" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="T139" s="1" t="s">
         <v>151</v>
@@ -12390,22 +12384,22 @@
     </row>
     <row r="140" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A140" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="E140" s="1">
         <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="G140" s="4">
         <v>1</v>
@@ -12443,10 +12437,10 @@
         <v>90</v>
       </c>
       <c r="Q140" s="11" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="R140" s="11" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="T140" s="1" t="s">
         <v>151</v>
@@ -12459,22 +12453,22 @@
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A141" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="G141" s="4">
         <v>1</v>
@@ -12512,10 +12506,10 @@
         <v>90</v>
       </c>
       <c r="Q141" s="11" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="R141" s="11" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="T141" s="1" t="s">
         <v>151</v>
@@ -12528,22 +12522,22 @@
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A142" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="G142" s="4">
         <v>1</v>
@@ -12581,10 +12575,10 @@
         <v>90</v>
       </c>
       <c r="Q142" s="11" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="R142" s="11" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="T142" s="1" t="s">
         <v>151</v>
@@ -12597,22 +12591,22 @@
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A143" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="G143" s="4">
         <v>1</v>
@@ -12650,10 +12644,10 @@
         <v>90</v>
       </c>
       <c r="Q143" s="11" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="R143" s="11" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="T143" s="1" t="s">
         <v>151</v>
@@ -12666,22 +12660,22 @@
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A144" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="G144" s="4">
         <v>1</v>
@@ -12719,10 +12713,10 @@
         <v>90</v>
       </c>
       <c r="Q144" s="11" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="R144" s="11" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="T144" s="1" t="s">
         <v>151</v>
@@ -12735,22 +12729,22 @@
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A145" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="G145" s="4">
         <v>1</v>
@@ -12788,10 +12782,10 @@
         <v>90</v>
       </c>
       <c r="Q145" s="11" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="R145" s="11" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="T145" s="1" t="s">
         <v>151</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="928">
   <si>
     <t>ID</t>
   </si>
@@ -2611,66 +2611,99 @@
     <t>600000000000</t>
   </si>
   <si>
+    <t>10120</t>
+  </si>
+  <si>
+    <t>1120</t>
+  </si>
+  <si>
+    <t>地狱钳虫王</t>
+  </si>
+  <si>
+    <t>9000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>3200000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>640000000000</t>
+  </si>
+  <si>
+    <t>10121</t>
+  </si>
+  <si>
+    <t>1121</t>
+  </si>
+  <si>
+    <t>地狱蠕虫王</t>
+  </si>
+  <si>
+    <t>90000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>64000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>680000000000</t>
+  </si>
+  <si>
+    <t>10122</t>
+  </si>
+  <si>
+    <t>1122</t>
+  </si>
+  <si>
+    <t>地狱猪王</t>
+  </si>
+  <si>
+    <t>900000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>1280000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>720000000000</t>
+  </si>
+  <si>
+    <t>10123</t>
+  </si>
+  <si>
+    <t>1123</t>
+  </si>
+  <si>
+    <t>地狱猪皇</t>
+  </si>
+  <si>
+    <t>9000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>25600000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>760000000000</t>
+  </si>
+  <si>
+    <t>10124</t>
+  </si>
+  <si>
+    <t>1124</t>
+  </si>
+  <si>
+    <t>地狱蝎王</t>
+  </si>
+  <si>
+    <t>90000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>512000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>800000000000</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
-    <t>10120</t>
-  </si>
-  <si>
-    <t>1120</t>
-  </si>
-  <si>
-    <t>地狱钳虫王</t>
-  </si>
-  <si>
-    <t>460000000000</t>
-  </si>
-  <si>
-    <t>10121</t>
-  </si>
-  <si>
-    <t>1121</t>
-  </si>
-  <si>
-    <t>地狱蠕虫王</t>
-  </si>
-  <si>
-    <t>470000000000</t>
-  </si>
-  <si>
-    <t>10122</t>
-  </si>
-  <si>
-    <t>1122</t>
-  </si>
-  <si>
-    <t>地狱猪王</t>
-  </si>
-  <si>
-    <t>10123</t>
-  </si>
-  <si>
-    <t>1123</t>
-  </si>
-  <si>
-    <t>地狱猪皇</t>
-  </si>
-  <si>
-    <t>490000000000</t>
-  </si>
-  <si>
-    <t>10124</t>
-  </si>
-  <si>
-    <t>1124</t>
-  </si>
-  <si>
-    <t>地狱蝎王</t>
-  </si>
-  <si>
-    <t>500000000000</t>
-  </si>
-  <si>
     <t>10125</t>
   </si>
   <si>
@@ -2822,9 +2855,6 @@
   </si>
   <si>
     <t>地狱火龙王</t>
-  </si>
-  <si>
-    <t>640000000000</t>
   </si>
   <si>
     <t>10139</t>
@@ -3016,12 +3046,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3829,8 +3859,9 @@
     <col min="4" max="4" width="7.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="6.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="8" width="39.75" style="3" customWidth="1"/>
-    <col min="9" max="9" width="50.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="40.75" style="3" customWidth="1"/>
+    <col min="8" max="8" width="41.375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="54.5" style="3" customWidth="1"/>
     <col min="10" max="10" width="15.875" style="3" customWidth="1"/>
     <col min="11" max="13" width="12.125" style="3" customWidth="1"/>
     <col min="14" max="14" width="9.625" style="3" customWidth="1"/>
@@ -11427,32 +11458,28 @@
       <c r="W125" s="3"/>
     </row>
     <row r="126" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A126" s="3" t="s">
+      <c r="A126" s="3"/>
+      <c r="B126" s="3"/>
+      <c r="C126" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="B126" s="3" t="s">
-        <v>842</v>
-      </c>
-      <c r="C126" s="1" t="s">
+      <c r="D126" s="1" t="s">
         <v>843</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>844</v>
       </c>
       <c r="E126" s="1">
         <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="G126" s="12" t="s">
         <v>845</v>
       </c>
-      <c r="G126" s="4">
-        <v>1</v>
-      </c>
-      <c r="H126" s="4">
-        <v>1</v>
-      </c>
-      <c r="I126" s="4">
-        <v>1</v>
+      <c r="H126" s="11" t="s">
+        <v>845</v>
+      </c>
+      <c r="I126" s="13" t="s">
+        <v>846</v>
       </c>
       <c r="J126" s="1">
         <f t="shared" si="37"/>
@@ -11481,10 +11508,10 @@
         <v>90</v>
       </c>
       <c r="Q126" s="11" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="R126" s="11" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="T126" s="1" t="s">
         <v>151</v>
@@ -11496,32 +11523,28 @@
       <c r="W126" s="3"/>
     </row>
     <row r="127" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A127" s="3" t="s">
-        <v>842</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>842</v>
-      </c>
+      <c r="A127" s="3"/>
+      <c r="B127" s="3"/>
       <c r="C127" s="1" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E127" s="1">
         <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>849</v>
-      </c>
-      <c r="G127" s="4">
-        <v>1</v>
-      </c>
-      <c r="H127" s="4">
-        <v>1</v>
-      </c>
-      <c r="I127" s="4">
-        <v>1</v>
+        <v>850</v>
+      </c>
+      <c r="G127" s="12" t="s">
+        <v>851</v>
+      </c>
+      <c r="H127" s="11" t="s">
+        <v>851</v>
+      </c>
+      <c r="I127" s="13" t="s">
+        <v>852</v>
       </c>
       <c r="J127" s="1">
         <f t="shared" si="37"/>
@@ -11550,10 +11573,10 @@
         <v>90</v>
       </c>
       <c r="Q127" s="11" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="R127" s="11" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="T127" s="1" t="s">
         <v>151</v>
@@ -11565,32 +11588,28 @@
       <c r="W127" s="3"/>
     </row>
     <row r="128" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A128" s="3" t="s">
-        <v>842</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>842</v>
-      </c>
+      <c r="A128" s="3"/>
+      <c r="B128" s="3"/>
       <c r="C128" s="1" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="E128" s="1">
         <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="G128" s="4">
-        <v>1</v>
-      </c>
-      <c r="H128" s="4">
-        <v>1</v>
-      </c>
-      <c r="I128" s="4">
-        <v>1</v>
+        <v>856</v>
+      </c>
+      <c r="G128" s="12" t="s">
+        <v>857</v>
+      </c>
+      <c r="H128" s="11" t="s">
+        <v>857</v>
+      </c>
+      <c r="I128" s="13" t="s">
+        <v>858</v>
       </c>
       <c r="J128" s="1">
         <f t="shared" si="37"/>
@@ -11619,10 +11638,10 @@
         <v>90</v>
       </c>
       <c r="Q128" s="11" t="s">
-        <v>823</v>
+        <v>859</v>
       </c>
       <c r="R128" s="11" t="s">
-        <v>823</v>
+        <v>859</v>
       </c>
       <c r="T128" s="1" t="s">
         <v>151</v>
@@ -11634,32 +11653,28 @@
       <c r="W128" s="3"/>
     </row>
     <row r="129" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A129" s="3" t="s">
-        <v>842</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>842</v>
-      </c>
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
       <c r="C129" s="1" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="E129" s="1">
         <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="G129" s="4">
-        <v>1</v>
-      </c>
-      <c r="H129" s="4">
-        <v>1</v>
-      </c>
-      <c r="I129" s="4">
-        <v>1</v>
+        <v>862</v>
+      </c>
+      <c r="G129" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="H129" s="11" t="s">
+        <v>863</v>
+      </c>
+      <c r="I129" s="13" t="s">
+        <v>864</v>
       </c>
       <c r="J129" s="1">
         <f t="shared" si="37"/>
@@ -11688,10 +11703,10 @@
         <v>90</v>
       </c>
       <c r="Q129" s="11" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="R129" s="11" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="T129" s="1" t="s">
         <v>151</v>
@@ -11703,32 +11718,28 @@
       <c r="W129" s="3"/>
     </row>
     <row r="130" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A130" s="3" t="s">
-        <v>842</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>842</v>
-      </c>
+      <c r="A130" s="3"/>
+      <c r="B130" s="3"/>
       <c r="C130" s="1" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="E130" s="1">
         <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>860</v>
-      </c>
-      <c r="G130" s="4">
-        <v>1</v>
-      </c>
-      <c r="H130" s="4">
-        <v>1</v>
-      </c>
-      <c r="I130" s="4">
-        <v>1</v>
+        <v>868</v>
+      </c>
+      <c r="G130" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="H130" s="11" t="s">
+        <v>869</v>
+      </c>
+      <c r="I130" s="13" t="s">
+        <v>870</v>
       </c>
       <c r="J130" s="1">
         <f t="shared" si="37"/>
@@ -11757,10 +11768,10 @@
         <v>90</v>
       </c>
       <c r="Q130" s="11" t="s">
-        <v>861</v>
+        <v>871</v>
       </c>
       <c r="R130" s="11" t="s">
-        <v>861</v>
+        <v>871</v>
       </c>
       <c r="T130" s="1" t="s">
         <v>151</v>
@@ -11773,22 +11784,22 @@
     </row>
     <row r="131" customHeight="1" spans="1:21">
       <c r="A131" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>862</v>
+        <v>873</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>863</v>
+        <v>874</v>
       </c>
       <c r="E131" s="1">
         <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>864</v>
+        <v>875</v>
       </c>
       <c r="G131" s="4">
         <v>1</v>
@@ -11826,10 +11837,10 @@
         <v>90</v>
       </c>
       <c r="Q131" s="11" t="s">
-        <v>865</v>
+        <v>876</v>
       </c>
       <c r="R131" s="11" t="s">
-        <v>865</v>
+        <v>876</v>
       </c>
       <c r="T131" s="1" t="s">
         <v>151</v>
@@ -11840,22 +11851,22 @@
     </row>
     <row r="132" customHeight="1" spans="1:21">
       <c r="A132" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>866</v>
+        <v>877</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>867</v>
+        <v>878</v>
       </c>
       <c r="E132" s="1">
         <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>868</v>
+        <v>879</v>
       </c>
       <c r="G132" s="4">
         <v>1</v>
@@ -11907,22 +11918,22 @@
     </row>
     <row r="133" customHeight="1" spans="1:21">
       <c r="A133" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>870</v>
+        <v>881</v>
       </c>
       <c r="E133" s="1">
         <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>871</v>
+        <v>882</v>
       </c>
       <c r="G133" s="4">
         <v>1</v>
@@ -11960,10 +11971,10 @@
         <v>90</v>
       </c>
       <c r="Q133" s="11" t="s">
-        <v>872</v>
+        <v>883</v>
       </c>
       <c r="R133" s="11" t="s">
-        <v>872</v>
+        <v>883</v>
       </c>
       <c r="T133" s="1" t="s">
         <v>151</v>
@@ -11974,22 +11985,22 @@
     </row>
     <row r="134" customHeight="1" spans="1:21">
       <c r="A134" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>873</v>
+        <v>884</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>874</v>
+        <v>885</v>
       </c>
       <c r="E134" s="1">
         <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>875</v>
+        <v>886</v>
       </c>
       <c r="G134" s="4">
         <v>1</v>
@@ -12027,10 +12038,10 @@
         <v>90</v>
       </c>
       <c r="Q134" s="11" t="s">
-        <v>876</v>
+        <v>887</v>
       </c>
       <c r="R134" s="11" t="s">
-        <v>876</v>
+        <v>887</v>
       </c>
       <c r="T134" s="1" t="s">
         <v>151</v>
@@ -12041,16 +12052,16 @@
     </row>
     <row r="135" customHeight="1" spans="1:21">
       <c r="A135" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>877</v>
+        <v>888</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>878</v>
+        <v>889</v>
       </c>
       <c r="E135" s="1">
         <v>4</v>
@@ -12094,10 +12105,10 @@
         <v>90</v>
       </c>
       <c r="Q135" s="11" t="s">
-        <v>879</v>
+        <v>890</v>
       </c>
       <c r="R135" s="11" t="s">
-        <v>879</v>
+        <v>890</v>
       </c>
       <c r="T135" s="1" t="s">
         <v>151</v>
@@ -12108,22 +12119,22 @@
     </row>
     <row r="136" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A136" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>880</v>
+        <v>891</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>881</v>
+        <v>892</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>882</v>
+        <v>893</v>
       </c>
       <c r="G136" s="4">
         <v>1</v>
@@ -12177,22 +12188,22 @@
     </row>
     <row r="137" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A137" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>883</v>
+        <v>894</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>884</v>
+        <v>895</v>
       </c>
       <c r="E137" s="1">
         <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>885</v>
+        <v>896</v>
       </c>
       <c r="G137" s="4">
         <v>1</v>
@@ -12230,10 +12241,10 @@
         <v>90</v>
       </c>
       <c r="Q137" s="11" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="R137" s="11" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="T137" s="1" t="s">
         <v>151</v>
@@ -12246,22 +12257,22 @@
     </row>
     <row r="138" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A138" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>887</v>
+        <v>898</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>888</v>
+        <v>899</v>
       </c>
       <c r="E138" s="1">
         <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>889</v>
+        <v>900</v>
       </c>
       <c r="G138" s="4">
         <v>1</v>
@@ -12299,10 +12310,10 @@
         <v>90</v>
       </c>
       <c r="Q138" s="11" t="s">
-        <v>890</v>
+        <v>901</v>
       </c>
       <c r="R138" s="11" t="s">
-        <v>890</v>
+        <v>901</v>
       </c>
       <c r="T138" s="1" t="s">
         <v>151</v>
@@ -12315,22 +12326,22 @@
     </row>
     <row r="139" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A139" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>891</v>
+        <v>902</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>892</v>
+        <v>903</v>
       </c>
       <c r="E139" s="1">
         <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>893</v>
+        <v>904</v>
       </c>
       <c r="G139" s="4">
         <v>1</v>
@@ -12368,10 +12379,10 @@
         <v>90</v>
       </c>
       <c r="Q139" s="11" t="s">
-        <v>894</v>
+        <v>905</v>
       </c>
       <c r="R139" s="11" t="s">
-        <v>894</v>
+        <v>905</v>
       </c>
       <c r="T139" s="1" t="s">
         <v>151</v>
@@ -12384,22 +12395,22 @@
     </row>
     <row r="140" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A140" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>895</v>
+        <v>906</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>896</v>
+        <v>907</v>
       </c>
       <c r="E140" s="1">
         <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>897</v>
+        <v>908</v>
       </c>
       <c r="G140" s="4">
         <v>1</v>
@@ -12453,22 +12464,22 @@
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A141" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>899</v>
+        <v>910</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>900</v>
+        <v>911</v>
       </c>
       <c r="G141" s="4">
         <v>1</v>
@@ -12506,10 +12517,10 @@
         <v>90</v>
       </c>
       <c r="Q141" s="11" t="s">
-        <v>901</v>
+        <v>912</v>
       </c>
       <c r="R141" s="11" t="s">
-        <v>901</v>
+        <v>912</v>
       </c>
       <c r="T141" s="1" t="s">
         <v>151</v>
@@ -12522,22 +12533,22 @@
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A142" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>903</v>
+        <v>914</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G142" s="4">
         <v>1</v>
@@ -12575,10 +12586,10 @@
         <v>90</v>
       </c>
       <c r="Q142" s="11" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="R142" s="11" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="T142" s="1" t="s">
         <v>151</v>
@@ -12591,22 +12602,22 @@
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A143" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>906</v>
+        <v>917</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>907</v>
+        <v>918</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>908</v>
+        <v>919</v>
       </c>
       <c r="G143" s="4">
         <v>1</v>
@@ -12644,10 +12655,10 @@
         <v>90</v>
       </c>
       <c r="Q143" s="11" t="s">
-        <v>909</v>
+        <v>920</v>
       </c>
       <c r="R143" s="11" t="s">
-        <v>909</v>
+        <v>920</v>
       </c>
       <c r="T143" s="1" t="s">
         <v>151</v>
@@ -12660,22 +12671,22 @@
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A144" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>910</v>
+        <v>921</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>911</v>
+        <v>922</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>912</v>
+        <v>923</v>
       </c>
       <c r="G144" s="4">
         <v>1</v>
@@ -12713,10 +12724,10 @@
         <v>90</v>
       </c>
       <c r="Q144" s="11" t="s">
-        <v>913</v>
+        <v>847</v>
       </c>
       <c r="R144" s="11" t="s">
-        <v>913</v>
+        <v>847</v>
       </c>
       <c r="T144" s="1" t="s">
         <v>151</v>
@@ -12729,22 +12740,22 @@
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A145" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>914</v>
+        <v>924</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>915</v>
+        <v>925</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>916</v>
+        <v>926</v>
       </c>
       <c r="G145" s="4">
         <v>1</v>
@@ -12782,10 +12793,10 @@
         <v>90</v>
       </c>
       <c r="Q145" s="11" t="s">
-        <v>917</v>
+        <v>927</v>
       </c>
       <c r="R145" s="11" t="s">
-        <v>917</v>
+        <v>927</v>
       </c>
       <c r="T145" s="1" t="s">
         <v>151</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="930">
   <si>
     <t>ID</t>
   </si>
@@ -196,30 +196,39 @@
     <t>鸡王</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>30000</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>10001</t>
+  </si>
+  <si>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>鹿王</t>
+  </si>
+  <si>
+    <t>2500</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>250000</t>
+  </si>
+  <si>
     <t>50000</t>
   </si>
   <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>10001</t>
-  </si>
-  <si>
-    <t>1001</t>
-  </si>
-  <si>
-    <t>鹿王</t>
-  </si>
-  <si>
-    <t>2500</t>
-  </si>
-  <si>
-    <t>500</t>
-  </si>
-  <si>
-    <t>250000</t>
-  </si>
-  <si>
     <t>45</t>
   </si>
   <si>
@@ -374,9 +383,6 @@
   </si>
   <si>
     <t>15000000</t>
-  </si>
-  <si>
-    <t>10</t>
   </si>
   <si>
     <t>10009</t>
@@ -3046,12 +3052,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4102,14 +4108,14 @@
       <c r="F6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="1">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1</v>
+      <c r="G6" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
@@ -4139,7 +4145,7 @@
         <v>34</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U6" s="1">
         <v>-1</v>
@@ -4147,25 +4153,25 @@
     </row>
     <row r="7" customHeight="1" spans="3:22">
       <c r="C7" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
@@ -4189,13 +4195,13 @@
         <v>0</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="U7" s="1">
         <v>-1</v>
@@ -4204,25 +4210,25 @@
     </row>
     <row r="8" customHeight="1" spans="3:22">
       <c r="C8" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>34</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J8" s="1">
         <v>0</v>
@@ -4246,13 +4252,13 @@
         <v>0</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="U8" s="1">
         <v>-1</v>
@@ -4261,25 +4267,25 @@
     </row>
     <row r="9" customHeight="1" spans="3:22">
       <c r="C9" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
@@ -4303,13 +4309,13 @@
         <v>0</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="U9" s="1">
         <v>0</v>
@@ -4318,25 +4324,25 @@
     </row>
     <row r="10" customHeight="1" spans="3:22">
       <c r="C10" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>34</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J10" s="1">
         <v>0</v>
@@ -4360,13 +4366,13 @@
         <v>0</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="U10" s="1">
         <v>0</v>
@@ -4375,25 +4381,25 @@
     </row>
     <row r="11" customHeight="1" spans="3:22">
       <c r="C11" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="J11" s="1">
         <v>0</v>
@@ -4417,13 +4423,13 @@
         <v>0</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="U11" s="1">
         <v>0</v>
@@ -4432,25 +4438,25 @@
     </row>
     <row r="12" customHeight="1" spans="3:22">
       <c r="C12" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J12" s="1">
         <v>0</v>
@@ -4474,13 +4480,13 @@
         <v>0</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="U12" s="1">
         <v>0</v>
@@ -4489,25 +4495,25 @@
     </row>
     <row r="13" customHeight="1" spans="3:22">
       <c r="C13" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J13" s="1">
         <v>0</v>
@@ -4531,13 +4537,13 @@
         <v>0</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U13" s="1">
         <v>0</v>
@@ -4546,25 +4552,25 @@
     </row>
     <row r="14" customHeight="1" spans="3:22">
       <c r="C14" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J14" s="1">
         <v>0</v>
@@ -4588,13 +4594,13 @@
         <v>0</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="U14" s="1">
         <v>0</v>
@@ -4603,25 +4609,25 @@
     </row>
     <row r="15" customHeight="1" spans="3:22">
       <c r="C15" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J15" s="1">
         <v>0</v>
@@ -4645,13 +4651,13 @@
         <v>0</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="U15" s="1">
         <v>0</v>
@@ -4660,25 +4666,25 @@
     </row>
     <row r="16" customHeight="1" spans="3:22">
       <c r="C16" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J16" s="1">
         <v>0</v>
@@ -4702,13 +4708,13 @@
         <v>0</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="U16" s="1">
         <v>0</v>
@@ -4717,25 +4723,25 @@
     </row>
     <row r="17" customHeight="1" spans="3:22">
       <c r="C17" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J17" s="1">
         <v>0</v>
@@ -4759,13 +4765,13 @@
         <v>0</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="U17" s="1">
         <v>0</v>
@@ -4774,25 +4780,25 @@
     </row>
     <row r="18" customHeight="1" spans="3:22">
       <c r="C18" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J18" s="1">
         <v>0</v>
@@ -4816,13 +4822,13 @@
         <v>0</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="U18" s="1">
         <v>0</v>
@@ -4831,25 +4837,25 @@
     </row>
     <row r="19" customHeight="1" spans="3:22">
       <c r="C19" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J19" s="1">
         <v>0</v>
@@ -4873,13 +4879,13 @@
         <v>0</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="U19" s="1">
         <v>0</v>
@@ -4888,25 +4894,25 @@
     </row>
     <row r="20" customHeight="1" spans="3:22">
       <c r="C20" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J20" s="1">
         <v>0</v>
@@ -4930,13 +4936,13 @@
         <v>0</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="U20" s="1">
         <v>0</v>
@@ -4945,25 +4951,25 @@
     </row>
     <row r="21" customHeight="1" spans="3:22">
       <c r="C21" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J21" s="1">
         <f t="shared" ref="J21:J40" si="0">(D21-1014)*1</f>
@@ -4988,13 +4994,13 @@
         <v>0</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U21" s="1">
         <v>0</v>
@@ -5003,25 +5009,25 @@
     </row>
     <row r="22" customHeight="1" spans="3:22">
       <c r="C22" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J22" s="1">
         <f t="shared" si="0"/>
@@ -5046,13 +5052,13 @@
         <v>0</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U22" s="1">
         <v>0</v>
@@ -5061,25 +5067,25 @@
     </row>
     <row r="23" customHeight="1" spans="3:22">
       <c r="C23" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J23" s="1">
         <f t="shared" si="0"/>
@@ -5104,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U23" s="1">
         <v>0</v>
@@ -5119,25 +5125,25 @@
     </row>
     <row r="24" customHeight="1" spans="3:22">
       <c r="C24" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J24" s="1">
         <f t="shared" si="0"/>
@@ -5162,13 +5168,13 @@
         <v>0</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U24" s="1">
         <v>0</v>
@@ -5177,25 +5183,25 @@
     </row>
     <row r="25" customHeight="1" spans="3:22">
       <c r="C25" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J25" s="1">
         <f t="shared" si="0"/>
@@ -5220,13 +5226,13 @@
         <v>0</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U25" s="1">
         <v>0</v>
@@ -5235,25 +5241,25 @@
     </row>
     <row r="26" customHeight="1" spans="3:22">
       <c r="C26" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J26" s="1">
         <f t="shared" si="0"/>
@@ -5278,13 +5284,13 @@
         <v>0</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U26" s="1">
         <v>0</v>
@@ -5293,25 +5299,25 @@
     </row>
     <row r="27" customHeight="1" spans="3:22">
       <c r="C27" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J27" s="1">
         <f t="shared" si="0"/>
@@ -5336,13 +5342,13 @@
         <v>0</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U27" s="1">
         <v>0</v>
@@ -5351,25 +5357,25 @@
     </row>
     <row r="28" customHeight="1" spans="3:22">
       <c r="C28" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J28" s="1">
         <f t="shared" si="0"/>
@@ -5394,13 +5400,13 @@
         <v>0</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U28" s="1">
         <v>0</v>
@@ -5409,25 +5415,25 @@
     </row>
     <row r="29" customHeight="1" spans="3:22">
       <c r="C29" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J29" s="1">
         <f t="shared" si="0"/>
@@ -5452,13 +5458,13 @@
         <v>0</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U29" s="1">
         <v>0</v>
@@ -5467,25 +5473,25 @@
     </row>
     <row r="30" customHeight="1" spans="3:22">
       <c r="C30" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J30" s="1">
         <f t="shared" si="0"/>
@@ -5510,13 +5516,13 @@
         <v>0</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U30" s="1">
         <v>0</v>
@@ -5525,25 +5531,25 @@
     </row>
     <row r="31" customHeight="1" spans="3:22">
       <c r="C31" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J31" s="1">
         <f t="shared" si="0"/>
@@ -5568,13 +5574,13 @@
         <v>0</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U31" s="1">
         <v>0</v>
@@ -5583,25 +5589,25 @@
     </row>
     <row r="32" customHeight="1" spans="3:22">
       <c r="C32" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J32" s="1">
         <f t="shared" si="0"/>
@@ -5626,13 +5632,13 @@
         <v>0</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U32" s="1">
         <v>0</v>
@@ -5641,25 +5647,25 @@
     </row>
     <row r="33" customHeight="1" spans="3:22">
       <c r="C33" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J33" s="1">
         <f t="shared" si="0"/>
@@ -5684,13 +5690,13 @@
         <v>0</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U33" s="1">
         <v>0</v>
@@ -5699,25 +5705,25 @@
     </row>
     <row r="34" customHeight="1" spans="3:22">
       <c r="C34" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J34" s="1">
         <f t="shared" si="0"/>
@@ -5742,13 +5748,13 @@
         <v>0</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U34" s="1">
         <v>0</v>
@@ -5757,25 +5763,25 @@
     </row>
     <row r="35" customHeight="1" spans="3:22">
       <c r="C35" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J35" s="1">
         <f t="shared" si="0"/>
@@ -5800,13 +5806,13 @@
         <v>0</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U35" s="1">
         <v>0</v>
@@ -5815,25 +5821,25 @@
     </row>
     <row r="36" customHeight="1" spans="3:22">
       <c r="C36" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="J36" s="1">
         <f t="shared" si="0"/>
@@ -5858,13 +5864,13 @@
         <v>0</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U36" s="1">
         <v>0</v>
@@ -5873,25 +5879,25 @@
     </row>
     <row r="37" customHeight="1" spans="3:22">
       <c r="C37" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="J37" s="1">
         <f t="shared" si="0"/>
@@ -5916,13 +5922,13 @@
         <v>0</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U37" s="1">
         <v>0</v>
@@ -5931,25 +5937,25 @@
     </row>
     <row r="38" customHeight="1" spans="3:22">
       <c r="C38" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J38" s="1">
         <f t="shared" si="0"/>
@@ -5974,13 +5980,13 @@
         <v>0</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U38" s="1">
         <v>0</v>
@@ -5989,25 +5995,25 @@
     </row>
     <row r="39" customHeight="1" spans="3:22">
       <c r="C39" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J39" s="1">
         <f t="shared" si="0"/>
@@ -6032,13 +6038,13 @@
         <v>0</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U39" s="1">
         <v>0</v>
@@ -6047,25 +6053,25 @@
     </row>
     <row r="40" customHeight="1" spans="3:22">
       <c r="C40" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J40" s="1">
         <f t="shared" si="0"/>
@@ -6090,13 +6096,13 @@
         <v>0</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U40" s="1">
         <v>0</v>
@@ -6105,27 +6111,26 @@
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A41" s="3"/>
-      <c r="B41" s="1"/>
       <c r="C41" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J41" s="1">
         <f>(D41-1034)*5+20</f>
@@ -6150,13 +6155,13 @@
         <v>0</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U41" s="1">
         <v>0</v>
@@ -6164,27 +6169,26 @@
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A42" s="3"/>
-      <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="J42" s="1">
         <f t="shared" ref="J41:J50" si="1">(D42-1034)*4+20</f>
@@ -6209,13 +6213,13 @@
         <v>0</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U42" s="1">
         <v>0</v>
@@ -6223,27 +6227,26 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A43" s="3"/>
-      <c r="B43" s="1"/>
       <c r="C43" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J43" s="1">
         <f t="shared" si="1"/>
@@ -6268,13 +6271,13 @@
         <v>0</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U43" s="1">
         <v>0</v>
@@ -6282,27 +6285,26 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A44" s="3"/>
-      <c r="B44" s="1"/>
       <c r="C44" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E44" s="1">
         <v>2</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J44" s="1">
         <f t="shared" si="1"/>
@@ -6327,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U44" s="1">
         <v>0</v>
@@ -6341,27 +6343,26 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A45" s="3"/>
-      <c r="B45" s="1"/>
       <c r="C45" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E45" s="1">
         <v>2</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J45" s="1">
         <f t="shared" si="1"/>
@@ -6386,13 +6387,13 @@
         <v>0</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U45" s="1">
         <v>0</v>
@@ -6400,27 +6401,26 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A46" s="3"/>
-      <c r="B46" s="1"/>
       <c r="C46" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E46" s="1">
         <v>2</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J46" s="1">
         <f t="shared" si="1"/>
@@ -6445,13 +6445,13 @@
         <v>0</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U46" s="1">
         <v>0</v>
@@ -6461,27 +6461,26 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A47" s="3"/>
-      <c r="B47" s="1"/>
       <c r="C47" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E47" s="1">
         <v>2</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J47" s="1">
         <f t="shared" si="1"/>
@@ -6506,13 +6505,13 @@
         <v>0</v>
       </c>
       <c r="Q47" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U47" s="1">
         <v>0</v>
@@ -6522,27 +6521,26 @@
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A48" s="3"/>
-      <c r="B48" s="1"/>
       <c r="C48" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E48" s="1">
         <v>2</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J48" s="1">
         <f t="shared" si="1"/>
@@ -6567,13 +6565,13 @@
         <v>0</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U48" s="1">
         <v>0</v>
@@ -6583,27 +6581,26 @@
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A49" s="3"/>
-      <c r="B49" s="1"/>
       <c r="C49" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E49" s="1">
         <v>2</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J49" s="1">
         <f t="shared" si="1"/>
@@ -6628,13 +6625,13 @@
         <v>0</v>
       </c>
       <c r="Q49" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U49" s="1">
         <v>0</v>
@@ -6644,27 +6641,26 @@
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A50" s="3"/>
-      <c r="B50" s="1"/>
       <c r="C50" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E50" s="1">
         <v>2</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J50" s="1">
         <f t="shared" si="1"/>
@@ -6689,13 +6685,13 @@
         <v>0</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U50" s="1">
         <v>0</v>
@@ -6705,27 +6701,26 @@
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A51" s="3"/>
-      <c r="B51" s="1"/>
       <c r="C51" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E51" s="1">
         <v>2</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J51" s="1">
         <v>65</v>
@@ -6751,13 +6746,13 @@
         <v>0</v>
       </c>
       <c r="Q51" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U51" s="1">
         <v>0</v>
@@ -6767,27 +6762,26 @@
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A52" s="3"/>
-      <c r="B52" s="1"/>
       <c r="C52" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E52" s="1">
         <v>2</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J52" s="1">
         <v>70</v>
@@ -6813,13 +6807,13 @@
         <v>0</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U52" s="1">
         <v>0</v>
@@ -6829,27 +6823,26 @@
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A53" s="3"/>
-      <c r="B53" s="1"/>
       <c r="C53" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E53" s="1">
         <v>2</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J53" s="1">
         <v>75</v>
@@ -6875,13 +6868,13 @@
         <v>0</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U53" s="1">
         <v>0</v>
@@ -6891,27 +6884,26 @@
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A54" s="3"/>
-      <c r="B54" s="1"/>
       <c r="C54" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E54" s="1">
         <v>2</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J54" s="1">
         <v>80</v>
@@ -6937,13 +6929,13 @@
         <v>0</v>
       </c>
       <c r="Q54" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U54" s="1">
         <v>0</v>
@@ -6953,27 +6945,26 @@
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A55" s="3"/>
-      <c r="B55" s="1"/>
       <c r="C55" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E55" s="1">
         <v>2</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J55" s="1">
         <v>85</v>
@@ -6999,13 +6990,13 @@
         <v>0</v>
       </c>
       <c r="Q55" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U55" s="1">
         <v>0</v>
@@ -7015,27 +7006,26 @@
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A56" s="3"/>
-      <c r="B56" s="1"/>
       <c r="C56" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E56" s="1">
         <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J56" s="1">
         <f t="shared" ref="J56:J65" si="4">(D56-1049)*5+85</f>
@@ -7063,13 +7053,13 @@
         <v>0</v>
       </c>
       <c r="Q56" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U56" s="1">
         <v>0</v>
@@ -7079,27 +7069,26 @@
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A57" s="3"/>
-      <c r="B57" s="1"/>
       <c r="C57" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E57" s="1">
         <v>2</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J57" s="1">
         <f t="shared" si="4"/>
@@ -7127,13 +7116,13 @@
         <v>0</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U57" s="1">
         <v>0</v>
@@ -7143,27 +7132,26 @@
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A58" s="3"/>
-      <c r="B58" s="1"/>
       <c r="C58" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E58" s="1">
         <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J58" s="1">
         <f t="shared" si="4"/>
@@ -7191,13 +7179,13 @@
         <v>0</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U58" s="1">
         <v>0</v>
@@ -7207,27 +7195,26 @@
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A59" s="3"/>
-      <c r="B59" s="1"/>
       <c r="C59" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E59" s="1">
         <v>2</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="J59" s="1">
         <f t="shared" si="4"/>
@@ -7255,13 +7242,13 @@
         <v>0</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U59" s="1">
         <v>0</v>
@@ -7271,27 +7258,26 @@
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A60" s="3"/>
-      <c r="B60" s="1"/>
       <c r="C60" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E60" s="1">
         <v>2</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J60" s="1">
         <f t="shared" si="4"/>
@@ -7319,13 +7305,13 @@
         <v>0</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U60" s="1">
         <v>0</v>
@@ -7335,27 +7321,26 @@
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A61" s="3"/>
-      <c r="B61" s="1"/>
       <c r="C61" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E61" s="1">
         <v>2</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J61" s="1">
         <f t="shared" si="4"/>
@@ -7383,13 +7368,13 @@
         <v>0</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U61" s="1">
         <v>0</v>
@@ -7399,27 +7384,26 @@
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A62" s="3"/>
-      <c r="B62" s="1"/>
       <c r="C62" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E62" s="1">
         <v>2</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="J62" s="1">
         <f t="shared" si="4"/>
@@ -7447,13 +7431,13 @@
         <v>0</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="R62" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U62" s="1">
         <v>0</v>
@@ -7463,27 +7447,26 @@
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A63" s="3"/>
-      <c r="B63" s="1"/>
       <c r="C63" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E63" s="1">
         <v>2</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="J63" s="1">
         <f t="shared" si="4"/>
@@ -7511,13 +7494,13 @@
         <v>0</v>
       </c>
       <c r="Q63" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="R63" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U63" s="1">
         <v>0</v>
@@ -7527,27 +7510,26 @@
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A64" s="3"/>
-      <c r="B64" s="1"/>
       <c r="C64" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E64" s="1">
         <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="J64" s="1">
         <f t="shared" si="4"/>
@@ -7575,13 +7557,13 @@
         <v>0</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U64" s="1">
         <v>0</v>
@@ -7591,27 +7573,26 @@
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A65" s="3"/>
-      <c r="B65" s="1"/>
       <c r="C65" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E65" s="1">
         <v>2</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="J65" s="1">
         <f t="shared" si="4"/>
@@ -7639,13 +7620,13 @@
         <v>0</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="R65" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U65" s="1">
         <v>0</v>
@@ -7655,27 +7636,26 @@
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A66" s="3"/>
-      <c r="B66" s="1"/>
       <c r="C66" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E66" s="1">
         <v>2</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="J66" s="1">
         <f t="shared" ref="J66:M66" si="6">J65+8</f>
@@ -7703,13 +7683,13 @@
         <v>0</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U66" s="1">
         <v>0</v>
@@ -7719,27 +7699,26 @@
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A67" s="3"/>
-      <c r="B67" s="1"/>
       <c r="C67" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E67" s="1">
         <v>2</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J67" s="1">
         <f t="shared" ref="J66:J71" si="7">J66+8</f>
@@ -7767,13 +7746,13 @@
         <v>0</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="R67" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U67" s="1">
         <v>0</v>
@@ -7783,27 +7762,26 @@
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A68" s="3"/>
-      <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E68" s="1">
         <v>2</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="J68" s="1">
         <f t="shared" si="7"/>
@@ -7831,13 +7809,13 @@
         <v>0</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="R68" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U68" s="1">
         <v>0</v>
@@ -7847,27 +7825,26 @@
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A69" s="3"/>
-      <c r="B69" s="1"/>
       <c r="C69" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="J69" s="1">
         <f t="shared" si="7"/>
@@ -7895,13 +7872,13 @@
         <v>0</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U69" s="1">
         <v>0</v>
@@ -7911,27 +7888,26 @@
     </row>
     <row r="70" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A70" s="3"/>
-      <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="J70" s="1">
         <f t="shared" si="7"/>
@@ -7958,13 +7934,13 @@
         <v>0</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="R70" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U70" s="1">
         <v>0</v>
@@ -7974,27 +7950,26 @@
     </row>
     <row r="71" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A71" s="3"/>
-      <c r="B71" s="1"/>
       <c r="C71" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G71" s="12" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="I71" s="12" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="J71" s="1">
         <f t="shared" ref="J71:M71" si="11">J70+15</f>
@@ -8022,13 +7997,13 @@
         <v>0</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="R71" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U71" s="1">
         <v>0</v>
@@ -8038,27 +8013,26 @@
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A72" s="3"/>
-      <c r="B72" s="1"/>
       <c r="C72" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="G72" s="12" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J72" s="1">
         <f t="shared" ref="J72:J81" si="14">J71+15</f>
@@ -8086,13 +8060,13 @@
         <v>0</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U72" s="1">
         <v>0</v>
@@ -8102,27 +8076,26 @@
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A73" s="3"/>
-      <c r="B73" s="1"/>
       <c r="C73" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G73" s="12" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I73" s="13" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="J73" s="1">
         <f t="shared" si="14"/>
@@ -8150,13 +8123,13 @@
         <v>0</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="R73" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U73" s="1">
         <v>0</v>
@@ -8166,27 +8139,26 @@
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A74" s="3"/>
-      <c r="B74" s="1"/>
       <c r="C74" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G74" s="12" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="J74" s="1">
         <f t="shared" si="14"/>
@@ -8214,13 +8186,13 @@
         <v>0</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="R74" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U74" s="1">
         <v>0</v>
@@ -8230,27 +8202,26 @@
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A75" s="3"/>
-      <c r="B75" s="1"/>
       <c r="C75" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="G75" s="12" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="I75" s="13" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="J75" s="1">
         <f t="shared" si="14"/>
@@ -8278,13 +8249,13 @@
         <v>0</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="R75" s="11" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U75" s="1">
         <v>0</v>
@@ -8296,25 +8267,25 @@
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E76" s="1">
         <v>3</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="G76" s="12" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="I76" s="13" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="J76" s="1">
         <f t="shared" si="14"/>
@@ -8348,7 +8319,7 @@
         <v>22938500000</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U76" s="1">
         <v>0</v>
@@ -8358,25 +8329,25 @@
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E77" s="1">
         <v>3</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G77" s="12" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="I77" s="13" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="J77" s="1">
         <f t="shared" si="14"/>
@@ -8410,7 +8381,7 @@
         <v>23938500000</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U77" s="1">
         <v>0</v>
@@ -8420,25 +8391,25 @@
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E78" s="1">
         <v>3</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="G78" s="12" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="J78" s="1">
         <f t="shared" si="14"/>
@@ -8472,7 +8443,7 @@
         <v>24938500000</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U78" s="1">
         <v>0</v>
@@ -8482,25 +8453,25 @@
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E79" s="1">
         <v>3</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="I79" s="13" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="J79" s="1">
         <f t="shared" si="14"/>
@@ -8534,7 +8505,7 @@
         <v>25938500000</v>
       </c>
       <c r="T79" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U79" s="1">
         <v>0</v>
@@ -8544,25 +8515,25 @@
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E80" s="1">
         <v>3</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="G80" s="12" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="J80" s="1">
         <f t="shared" si="14"/>
@@ -8596,7 +8567,7 @@
         <v>26938500000</v>
       </c>
       <c r="T80" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U80" s="1">
         <v>0</v>
@@ -8606,25 +8577,25 @@
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E81" s="1">
         <v>3</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="G81" s="12" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="H81" s="11" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="I81" s="13" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="J81" s="1">
         <f t="shared" ref="J81:J91" si="16">J80+20</f>
@@ -8658,7 +8629,7 @@
         <v>30000000000</v>
       </c>
       <c r="T81" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U81" s="1">
         <v>0</v>
@@ -8670,25 +8641,25 @@
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E82" s="1">
         <v>3</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="G82" s="12" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="J82" s="1">
         <f t="shared" si="16"/>
@@ -8722,7 +8693,7 @@
         <v>32000000000</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U82" s="1">
         <v>0</v>
@@ -8734,25 +8705,25 @@
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E83" s="1">
         <v>3</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="G83" s="12" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="H83" s="11" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="J83" s="1">
         <f t="shared" si="16"/>
@@ -8786,7 +8757,7 @@
         <v>34000000000</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U83" s="1">
         <v>0</v>
@@ -8798,25 +8769,25 @@
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E84" s="1">
         <v>3</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="G84" s="12" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="I84" s="13" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="J84" s="1">
         <f t="shared" si="16"/>
@@ -8850,7 +8821,7 @@
         <v>37000000000</v>
       </c>
       <c r="T84" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U84" s="1">
         <v>0</v>
@@ -8862,25 +8833,25 @@
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E85" s="1">
         <v>3</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="G85" s="12" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H85" s="11" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="J85" s="1">
         <f t="shared" si="16"/>
@@ -8914,7 +8885,7 @@
         <v>40000000000</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U85" s="1">
         <v>0</v>
@@ -8926,25 +8897,25 @@
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E86" s="1">
         <v>3</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G86" s="12" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="H86" s="11" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="I86" s="13" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="J86" s="1">
         <f t="shared" si="16"/>
@@ -8978,7 +8949,7 @@
         <v>50000000000</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U86" s="1">
         <v>0</v>
@@ -8990,25 +8961,25 @@
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E87" s="1">
         <v>3</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G87" s="12" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H87" s="11" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="I87" s="13" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="J87" s="1">
         <f t="shared" si="16"/>
@@ -9042,7 +9013,7 @@
         <v>60000000000</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U87" s="1">
         <v>0</v>
@@ -9054,25 +9025,25 @@
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E88" s="1">
         <v>3</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G88" s="12" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="H88" s="11" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="I88" s="13" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="J88" s="1">
         <f t="shared" si="16"/>
@@ -9106,7 +9077,7 @@
         <v>70000000000</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U88" s="1">
         <v>0</v>
@@ -9118,25 +9089,25 @@
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E89" s="1">
         <v>3</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G89" s="12" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H89" s="11" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I89" s="13" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="J89" s="1">
         <f t="shared" si="16"/>
@@ -9170,7 +9141,7 @@
         <v>80000000000</v>
       </c>
       <c r="T89" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U89" s="1">
         <v>0</v>
@@ -9182,25 +9153,25 @@
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="E90" s="1">
         <v>3</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="G90" s="12" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="I90" s="13" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="J90" s="1">
         <f t="shared" si="16"/>
@@ -9228,13 +9199,13 @@
         <v>0</v>
       </c>
       <c r="Q90" s="11" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="R90" s="11" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="T90" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U90" s="1">
         <v>0</v>
@@ -9246,25 +9217,25 @@
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E91" s="1">
         <v>3</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="G91" s="12" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="H91" s="11" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="J91" s="1">
         <f t="shared" ref="J91:J96" si="18">J90+25</f>
@@ -9292,13 +9263,13 @@
         <v>0</v>
       </c>
       <c r="Q91" s="11" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="R91" s="11" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="T91" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U91" s="1">
         <v>0</v>
@@ -9310,25 +9281,25 @@
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E92" s="1">
         <v>3</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="G92" s="12" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="I92" s="13" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="J92" s="1">
         <f t="shared" si="18"/>
@@ -9356,13 +9327,13 @@
         <v>0</v>
       </c>
       <c r="Q92" s="11" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="R92" s="11" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="T92" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U92" s="1">
         <v>0</v>
@@ -9374,25 +9345,25 @@
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E93" s="1">
         <v>3</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G93" s="12" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="I93" s="13" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="J93" s="1">
         <f t="shared" si="18"/>
@@ -9420,13 +9391,13 @@
         <v>0</v>
       </c>
       <c r="Q93" s="11" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="R93" s="11" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="T93" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U93" s="1">
         <v>0</v>
@@ -9438,25 +9409,25 @@
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E94" s="1">
         <v>3</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="G94" s="12" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="I94" s="13" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="J94" s="1">
         <f t="shared" si="18"/>
@@ -9484,13 +9455,13 @@
         <v>0</v>
       </c>
       <c r="Q94" s="11" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="R94" s="11" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="T94" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U94" s="1">
         <v>0</v>
@@ -9502,25 +9473,25 @@
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="1" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E95" s="1">
         <v>3</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="G95" s="12" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="I95" s="13" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="J95" s="1">
         <f t="shared" si="18"/>
@@ -9548,13 +9519,13 @@
         <v>0</v>
       </c>
       <c r="Q95" s="11" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="R95" s="11" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="T95" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U95" s="1">
         <v>0</v>
@@ -9564,25 +9535,25 @@
     </row>
     <row r="96" customHeight="1" spans="3:21">
       <c r="C96" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E96" s="1">
         <v>3</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="G96" s="12" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="H96" s="11" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="I96" s="13" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="J96" s="1">
         <f t="shared" ref="J96:J100" si="22">J95+30</f>
@@ -9610,13 +9581,13 @@
         <v>0</v>
       </c>
       <c r="Q96" s="11" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="R96" s="11" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="T96" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U96" s="1">
         <v>0</v>
@@ -9624,25 +9595,25 @@
     </row>
     <row r="97" customHeight="1" spans="3:21">
       <c r="C97" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E97" s="1">
         <v>3</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="G97" s="12" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="H97" s="11" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="I97" s="13" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="J97" s="1">
         <f t="shared" si="22"/>
@@ -9670,13 +9641,13 @@
         <v>0</v>
       </c>
       <c r="Q97" s="11" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="R97" s="11" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="T97" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U97" s="1">
         <v>0</v>
@@ -9684,25 +9655,25 @@
     </row>
     <row r="98" customHeight="1" spans="3:21">
       <c r="C98" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E98" s="1">
         <v>3</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="G98" s="12" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="H98" s="11" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="I98" s="13" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="J98" s="1">
         <f t="shared" si="22"/>
@@ -9730,13 +9701,13 @@
         <v>0</v>
       </c>
       <c r="Q98" s="11" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="R98" s="11" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="T98" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U98" s="1">
         <v>0</v>
@@ -9744,25 +9715,25 @@
     </row>
     <row r="99" customHeight="1" spans="3:21">
       <c r="C99" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="E99" s="1">
         <v>3</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="G99" s="12" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="H99" s="11" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="I99" s="13" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="J99" s="1">
         <f t="shared" si="22"/>
@@ -9790,13 +9761,13 @@
         <v>0</v>
       </c>
       <c r="Q99" s="11" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="R99" s="11" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="T99" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U99" s="1">
         <v>0</v>
@@ -9804,25 +9775,25 @@
     </row>
     <row r="100" customHeight="1" spans="3:21">
       <c r="C100" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E100" s="1">
         <v>3</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="G100" s="12" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="I100" s="13" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="J100" s="1">
         <f t="shared" si="22"/>
@@ -9850,13 +9821,13 @@
         <v>0</v>
       </c>
       <c r="Q100" s="11" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="R100" s="11" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="T100" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U100" s="1">
         <v>0</v>
@@ -9866,25 +9837,25 @@
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E101" s="1">
         <v>3</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="G101" s="12" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="H101" s="11" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="I101" s="13" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="J101" s="1">
         <f t="shared" ref="J101:M101" si="26">J100+8</f>
@@ -9912,13 +9883,13 @@
         <v>0</v>
       </c>
       <c r="Q101" s="11" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="R101" s="11" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="T101" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U101" s="1">
         <v>0</v>
@@ -9930,25 +9901,25 @@
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E102" s="1">
         <v>3</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="G102" s="12" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="I102" s="13" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="J102" s="1">
         <f t="shared" ref="J102:M102" si="27">J101+8</f>
@@ -9976,13 +9947,13 @@
         <v>0</v>
       </c>
       <c r="Q102" s="11" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="R102" s="11" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="T102" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U102" s="1">
         <v>0</v>
@@ -9994,25 +9965,25 @@
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E103" s="1">
         <v>3</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="G103" s="12" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="H103" s="11" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="I103" s="13" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="J103" s="1">
         <f t="shared" ref="J103:M103" si="28">J102+8</f>
@@ -10040,13 +10011,13 @@
         <v>0</v>
       </c>
       <c r="Q103" s="11" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="R103" s="11" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="T103" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U103" s="1">
         <v>0</v>
@@ -10058,25 +10029,25 @@
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="E104" s="1">
         <v>3</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="G104" s="12" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="I104" s="13" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="J104" s="1">
         <f t="shared" ref="J104:M104" si="29">J103+8</f>
@@ -10104,13 +10075,13 @@
         <v>0</v>
       </c>
       <c r="Q104" s="11" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="R104" s="11" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="T104" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U104" s="1">
         <v>0</v>
@@ -10122,25 +10093,25 @@
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E105" s="1">
         <v>3</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="G105" s="12" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="H105" s="11" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="I105" s="13" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="J105" s="1">
         <f t="shared" ref="J105:M105" si="30">J104+8</f>
@@ -10168,13 +10139,13 @@
         <v>0</v>
       </c>
       <c r="Q105" s="11" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="R105" s="11" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="T105" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U105" s="1">
         <v>0</v>
@@ -10186,25 +10157,25 @@
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E106" s="1">
         <v>3</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="G106" s="12" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="H106" s="11" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="I106" s="13" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="J106" s="1">
         <f t="shared" ref="J106:J115" si="31">J105+15</f>
@@ -10232,13 +10203,13 @@
         <v>0</v>
       </c>
       <c r="Q106" s="11" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="R106" s="11" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="T106" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U106" s="1">
         <v>0</v>
@@ -10250,25 +10221,25 @@
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="E107" s="1">
         <v>3</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="G107" s="12" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="H107" s="11" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="I107" s="13" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="J107" s="1">
         <f t="shared" si="31"/>
@@ -10296,13 +10267,13 @@
         <v>0</v>
       </c>
       <c r="Q107" s="11" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="R107" s="11" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="T107" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U107" s="1">
         <v>0</v>
@@ -10314,25 +10285,25 @@
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="1" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="E108" s="1">
         <v>3</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="G108" s="12" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="H108" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="I108" s="13" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="J108" s="1">
         <f t="shared" si="31"/>
@@ -10360,13 +10331,13 @@
         <v>0</v>
       </c>
       <c r="Q108" s="11" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="R108" s="11" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="T108" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U108" s="1">
         <v>0</v>
@@ -10378,25 +10349,25 @@
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="E109" s="1">
         <v>3</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="G109" s="12" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="H109" s="11" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="I109" s="13" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="J109" s="1">
         <f t="shared" si="31"/>
@@ -10424,13 +10395,13 @@
         <v>0</v>
       </c>
       <c r="Q109" s="11" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="R109" s="11" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="T109" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U109" s="1">
         <v>0</v>
@@ -10442,25 +10413,25 @@
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="1" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="E110" s="1">
         <v>3</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="G110" s="12" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="H110" s="11" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="I110" s="13" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="J110" s="1">
         <f t="shared" si="31"/>
@@ -10488,13 +10459,13 @@
         <v>0</v>
       </c>
       <c r="Q110" s="11" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="R110" s="11" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="T110" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U110" s="1">
         <v>0</v>
@@ -10506,25 +10477,25 @@
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="2" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E111" s="2">
         <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="G111" s="14" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="H111" s="15" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="I111" s="16" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="J111" s="2">
         <v>1500</v>
@@ -10548,13 +10519,13 @@
         <v>90</v>
       </c>
       <c r="Q111" s="15" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="R111" s="15" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="T111" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U111" s="2">
         <v>0</v>
@@ -10564,25 +10535,25 @@
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="1" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="E112" s="1">
         <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="G112" s="12" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="H112" s="11" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="I112" s="13" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="J112" s="1">
         <f>J111+100</f>
@@ -10611,13 +10582,13 @@
         <v>90</v>
       </c>
       <c r="Q112" s="11" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="R112" s="11" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="T112" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U112" s="1">
         <v>0</v>
@@ -10627,25 +10598,25 @@
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="1" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="E113" s="1">
         <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G113" s="12" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="H113" s="11" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="I113" s="13" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="J113" s="1">
         <f>J112+100</f>
@@ -10674,13 +10645,13 @@
         <v>90</v>
       </c>
       <c r="Q113" s="11" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="R113" s="11" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="T113" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U113" s="1">
         <v>0</v>
@@ -10690,25 +10661,25 @@
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="1" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="E114" s="1">
         <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="G114" s="12" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="H114" s="11" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="I114" s="13" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="J114" s="1">
         <f>J113+100</f>
@@ -10737,13 +10708,13 @@
         <v>90</v>
       </c>
       <c r="Q114" s="11" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="R114" s="11" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="T114" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U114" s="1">
         <v>0</v>
@@ -10753,25 +10724,25 @@
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="1" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="E115" s="1">
         <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="G115" s="12" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="H115" s="11" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="I115" s="13" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="J115" s="1">
         <f>J114+100</f>
@@ -10800,13 +10771,13 @@
         <v>90</v>
       </c>
       <c r="Q115" s="11" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="R115" s="11" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="T115" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U115" s="1">
         <v>0</v>
@@ -10816,25 +10787,25 @@
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="E116" s="1">
         <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="G116" s="12" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="H116" s="11" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="I116" s="13" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="J116" s="1">
         <f t="shared" ref="J116:J145" si="37">J115+200</f>
@@ -10863,13 +10834,13 @@
         <v>90</v>
       </c>
       <c r="Q116" s="11" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="R116" s="11" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="T116" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U116" s="1">
         <v>0</v>
@@ -10881,25 +10852,25 @@
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="1" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="E117" s="1">
         <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="G117" s="12" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="H117" s="11" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="I117" s="13" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="J117" s="1">
         <f t="shared" si="37"/>
@@ -10928,13 +10899,13 @@
         <v>90</v>
       </c>
       <c r="Q117" s="11" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="R117" s="11" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="T117" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U117" s="1">
         <v>0</v>
@@ -10946,25 +10917,25 @@
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="1" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="E118" s="1">
         <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="G118" s="12" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="H118" s="11" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="I118" s="13" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="J118" s="1">
         <f t="shared" si="37"/>
@@ -10993,13 +10964,13 @@
         <v>90</v>
       </c>
       <c r="Q118" s="11" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="R118" s="11" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="T118" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U118" s="1">
         <v>0</v>
@@ -11011,25 +10982,25 @@
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="1" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="E119" s="1">
         <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="G119" s="12" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H119" s="11" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="I119" s="13" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="J119" s="1">
         <f t="shared" si="37"/>
@@ -11058,13 +11029,13 @@
         <v>90</v>
       </c>
       <c r="Q119" s="11" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="R119" s="11" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="T119" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U119" s="1">
         <v>0</v>
@@ -11076,25 +11047,25 @@
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="1" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="E120" s="1">
         <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="G120" s="12" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="H120" s="11" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="I120" s="13" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="J120" s="1">
         <f t="shared" si="37"/>
@@ -11123,13 +11094,13 @@
         <v>90</v>
       </c>
       <c r="Q120" s="11" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="R120" s="11" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="T120" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U120" s="1">
         <v>0</v>
@@ -11139,25 +11110,25 @@
     </row>
     <row r="121" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C121" s="1" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="E121" s="1">
         <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="G121" s="12" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="H121" s="11" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="I121" s="13" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="J121" s="1">
         <f t="shared" si="37"/>
@@ -11187,13 +11158,13 @@
         <v>90</v>
       </c>
       <c r="Q121" s="11" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="R121" s="11" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="T121" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U121" s="1">
         <v>0</v>
@@ -11203,25 +11174,25 @@
     </row>
     <row r="122" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C122" s="1" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="E122" s="1">
         <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="G122" s="12" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="H122" s="11" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="I122" s="13" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="J122" s="1">
         <f t="shared" si="37"/>
@@ -11251,13 +11222,13 @@
         <v>90</v>
       </c>
       <c r="Q122" s="11" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="R122" s="11" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="T122" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U122" s="1">
         <v>0</v>
@@ -11267,25 +11238,25 @@
     </row>
     <row r="123" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C123" s="1" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="E123" s="1">
         <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="G123" s="12" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="H123" s="11" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="I123" s="13" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="J123" s="1">
         <f t="shared" si="37"/>
@@ -11315,13 +11286,13 @@
         <v>90</v>
       </c>
       <c r="Q123" s="11" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="R123" s="11" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="T123" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U123" s="1">
         <v>0</v>
@@ -11331,25 +11302,25 @@
     </row>
     <row r="124" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C124" s="1" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="E124" s="1">
         <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="G124" s="12" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="H124" s="11" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="I124" s="13" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J124" s="1">
         <f t="shared" si="37"/>
@@ -11379,13 +11350,13 @@
         <v>90</v>
       </c>
       <c r="Q124" s="11" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="R124" s="11" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="T124" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U124" s="1">
         <v>0</v>
@@ -11395,25 +11366,25 @@
     </row>
     <row r="125" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C125" s="1" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="E125" s="1">
         <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="G125" s="12" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="H125" s="11" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="I125" s="13" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="J125" s="1">
         <f t="shared" si="37"/>
@@ -11443,13 +11414,13 @@
         <v>90</v>
       </c>
       <c r="Q125" s="11" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="R125" s="11" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="T125" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U125" s="1">
         <v>0</v>
@@ -11461,25 +11432,25 @@
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="1" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="E126" s="1">
         <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="G126" s="12" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="H126" s="11" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="I126" s="13" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="J126" s="1">
         <f t="shared" si="37"/>
@@ -11508,13 +11479,13 @@
         <v>90</v>
       </c>
       <c r="Q126" s="11" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="R126" s="11" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="T126" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U126" s="1">
         <v>0</v>
@@ -11526,25 +11497,25 @@
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="1" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="E127" s="1">
         <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="G127" s="12" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="H127" s="11" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="I127" s="13" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="J127" s="1">
         <f t="shared" si="37"/>
@@ -11573,13 +11544,13 @@
         <v>90</v>
       </c>
       <c r="Q127" s="11" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="R127" s="11" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="T127" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U127" s="1">
         <v>0</v>
@@ -11591,25 +11562,25 @@
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="1" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="E128" s="1">
         <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="G128" s="12" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="H128" s="11" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="I128" s="13" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="J128" s="1">
         <f t="shared" si="37"/>
@@ -11638,13 +11609,13 @@
         <v>90</v>
       </c>
       <c r="Q128" s="11" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="R128" s="11" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="T128" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U128" s="1">
         <v>0</v>
@@ -11656,25 +11627,25 @@
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="1" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="E129" s="1">
         <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="G129" s="12" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="H129" s="11" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="I129" s="13" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="J129" s="1">
         <f t="shared" si="37"/>
@@ -11703,13 +11674,13 @@
         <v>90</v>
       </c>
       <c r="Q129" s="11" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="R129" s="11" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="T129" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U129" s="1">
         <v>0</v>
@@ -11721,25 +11692,25 @@
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="1" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="E130" s="1">
         <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="G130" s="12" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="H130" s="11" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="I130" s="13" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="J130" s="1">
         <f t="shared" si="37"/>
@@ -11768,13 +11739,13 @@
         <v>90</v>
       </c>
       <c r="Q130" s="11" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="R130" s="11" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="T130" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U130" s="1">
         <v>0</v>
@@ -11784,22 +11755,22 @@
     </row>
     <row r="131" customHeight="1" spans="1:21">
       <c r="A131" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="E131" s="1">
         <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="G131" s="4">
         <v>1</v>
@@ -11837,13 +11808,13 @@
         <v>90</v>
       </c>
       <c r="Q131" s="11" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="R131" s="11" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="T131" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U131" s="1">
         <v>0</v>
@@ -11851,22 +11822,22 @@
     </row>
     <row r="132" customHeight="1" spans="1:21">
       <c r="A132" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="E132" s="1">
         <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="G132" s="4">
         <v>1</v>
@@ -11904,13 +11875,13 @@
         <v>90</v>
       </c>
       <c r="Q132" s="11" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="R132" s="11" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="T132" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U132" s="1">
         <v>0</v>
@@ -11918,22 +11889,22 @@
     </row>
     <row r="133" customHeight="1" spans="1:21">
       <c r="A133" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="E133" s="1">
         <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="G133" s="4">
         <v>1</v>
@@ -11971,13 +11942,13 @@
         <v>90</v>
       </c>
       <c r="Q133" s="11" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="R133" s="11" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="T133" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U133" s="1">
         <v>0</v>
@@ -11985,22 +11956,22 @@
     </row>
     <row r="134" customHeight="1" spans="1:21">
       <c r="A134" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="E134" s="1">
         <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="G134" s="4">
         <v>1</v>
@@ -12038,13 +12009,13 @@
         <v>90</v>
       </c>
       <c r="Q134" s="11" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="R134" s="11" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="T134" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U134" s="1">
         <v>0</v>
@@ -12052,22 +12023,22 @@
     </row>
     <row r="135" customHeight="1" spans="1:21">
       <c r="A135" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="E135" s="1">
         <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="G135" s="4">
         <v>1</v>
@@ -12105,13 +12076,13 @@
         <v>90</v>
       </c>
       <c r="Q135" s="11" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="R135" s="11" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="T135" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U135" s="1">
         <v>0</v>
@@ -12119,22 +12090,22 @@
     </row>
     <row r="136" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A136" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="G136" s="4">
         <v>1</v>
@@ -12172,13 +12143,13 @@
         <v>90</v>
       </c>
       <c r="Q136" s="11" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="R136" s="11" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="T136" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U136" s="1">
         <v>0</v>
@@ -12188,22 +12159,22 @@
     </row>
     <row r="137" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A137" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E137" s="1">
         <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="G137" s="4">
         <v>1</v>
@@ -12241,13 +12212,13 @@
         <v>90</v>
       </c>
       <c r="Q137" s="11" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="R137" s="11" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="T137" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U137" s="1">
         <v>0</v>
@@ -12257,22 +12228,22 @@
     </row>
     <row r="138" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A138" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="E138" s="1">
         <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="G138" s="4">
         <v>1</v>
@@ -12310,13 +12281,13 @@
         <v>90</v>
       </c>
       <c r="Q138" s="11" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="R138" s="11" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="T138" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U138" s="1">
         <v>0</v>
@@ -12326,22 +12297,22 @@
     </row>
     <row r="139" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A139" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="E139" s="1">
         <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="G139" s="4">
         <v>1</v>
@@ -12379,13 +12350,13 @@
         <v>90</v>
       </c>
       <c r="Q139" s="11" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="R139" s="11" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="T139" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U139" s="1">
         <v>0</v>
@@ -12395,22 +12366,22 @@
     </row>
     <row r="140" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A140" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="E140" s="1">
         <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="G140" s="4">
         <v>1</v>
@@ -12448,13 +12419,13 @@
         <v>90</v>
       </c>
       <c r="Q140" s="11" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="R140" s="11" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="T140" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U140" s="1">
         <v>0</v>
@@ -12464,22 +12435,22 @@
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A141" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="G141" s="4">
         <v>1</v>
@@ -12517,13 +12488,13 @@
         <v>90</v>
       </c>
       <c r="Q141" s="11" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="R141" s="11" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="T141" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U141" s="1">
         <v>0</v>
@@ -12533,22 +12504,22 @@
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A142" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="G142" s="4">
         <v>1</v>
@@ -12586,13 +12557,13 @@
         <v>90</v>
       </c>
       <c r="Q142" s="11" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="R142" s="11" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="T142" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U142" s="1">
         <v>0</v>
@@ -12602,22 +12573,22 @@
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A143" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="G143" s="4">
         <v>1</v>
@@ -12655,13 +12626,13 @@
         <v>90</v>
       </c>
       <c r="Q143" s="11" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="R143" s="11" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="T143" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U143" s="1">
         <v>0</v>
@@ -12671,22 +12642,22 @@
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A144" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="G144" s="4">
         <v>1</v>
@@ -12724,13 +12695,13 @@
         <v>90</v>
       </c>
       <c r="Q144" s="11" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="R144" s="11" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="T144" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U144" s="1">
         <v>0</v>
@@ -12740,22 +12711,22 @@
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A145" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="G145" s="4">
         <v>1</v>
@@ -12793,13 +12764,13 @@
         <v>90</v>
       </c>
       <c r="Q145" s="11" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="R145" s="11" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="T145" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U145" s="1">
         <v>0</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="941">
   <si>
     <t>ID</t>
   </si>
@@ -181,6 +181,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>double</t>
+  </si>
+  <si>
     <t>long</t>
   </si>
   <si>
@@ -2707,61 +2710,91 @@
     <t>800000000000</t>
   </si>
   <si>
+    <t>10125</t>
+  </si>
+  <si>
+    <t>1125</t>
+  </si>
+  <si>
+    <t>地狱恶魔教主</t>
+  </si>
+  <si>
+    <t>900000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>10000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>840000000000</t>
+  </si>
+  <si>
+    <t>10126</t>
+  </si>
+  <si>
+    <t>1126</t>
+  </si>
+  <si>
+    <t>地狱恶魔教皇</t>
+  </si>
+  <si>
+    <t>9000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>200000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>880000000000</t>
+  </si>
+  <si>
+    <t>10127</t>
+  </si>
+  <si>
+    <t>1127</t>
+  </si>
+  <si>
+    <t>地狱邪魔教主</t>
+  </si>
+  <si>
+    <t>90000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>4000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>920000000000</t>
+  </si>
+  <si>
+    <t>10128</t>
+  </si>
+  <si>
+    <t>1128</t>
+  </si>
+  <si>
+    <t>地狱邪魔教皇</t>
+  </si>
+  <si>
+    <t>900000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>80000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>960000000000</t>
+  </si>
+  <si>
+    <t>10129</t>
+  </si>
+  <si>
+    <t>1129</t>
+  </si>
+  <si>
+    <t>9000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>1600000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>10125</t>
-  </si>
-  <si>
-    <t>1125</t>
-  </si>
-  <si>
-    <t>地狱恶魔教主</t>
-  </si>
-  <si>
-    <t>510000000000</t>
-  </si>
-  <si>
-    <t>10126</t>
-  </si>
-  <si>
-    <t>1126</t>
-  </si>
-  <si>
-    <t>地狱恶魔教皇</t>
-  </si>
-  <si>
-    <t>10127</t>
-  </si>
-  <si>
-    <t>1127</t>
-  </si>
-  <si>
-    <t>地狱邪魔教主</t>
-  </si>
-  <si>
-    <t>530000000000</t>
-  </si>
-  <si>
-    <t>10128</t>
-  </si>
-  <si>
-    <t>1128</t>
-  </si>
-  <si>
-    <t>地狱邪魔教皇</t>
-  </si>
-  <si>
-    <t>540000000000</t>
-  </si>
-  <si>
-    <t>10129</t>
-  </si>
-  <si>
-    <t>1129</t>
-  </si>
-  <si>
-    <t>550000000000</t>
   </si>
   <si>
     <t>10130</t>
@@ -3865,9 +3898,9 @@
     <col min="4" max="4" width="7.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="6.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="40.75" style="3" customWidth="1"/>
-    <col min="8" max="8" width="41.375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="54.5" style="3" customWidth="1"/>
+    <col min="7" max="7" width="48.5" style="3" customWidth="1"/>
+    <col min="8" max="8" width="52.1666666666667" style="3" customWidth="1"/>
+    <col min="9" max="9" width="61.8333333333333" style="3" customWidth="1"/>
     <col min="10" max="10" width="15.875" style="3" customWidth="1"/>
     <col min="11" max="13" width="12.125" style="3" customWidth="1"/>
     <col min="14" max="14" width="9.625" style="3" customWidth="1"/>
@@ -4077,45 +4110,45 @@
         <v>30</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S5" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T5" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U5" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="12" spans="3:21">
+    <row r="6" s="1" customFormat="1" ht="11.5" spans="3:21">
       <c r="C6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
@@ -4139,13 +4172,13 @@
         <v>0</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U6" s="1">
         <v>-1</v>
@@ -4153,25 +4186,25 @@
     </row>
     <row r="7" customHeight="1" spans="3:22">
       <c r="C7" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
@@ -4195,13 +4228,13 @@
         <v>0</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U7" s="1">
         <v>-1</v>
@@ -4210,25 +4243,25 @@
     </row>
     <row r="8" customHeight="1" spans="3:22">
       <c r="C8" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J8" s="1">
         <v>0</v>
@@ -4252,13 +4285,13 @@
         <v>0</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U8" s="1">
         <v>-1</v>
@@ -4267,25 +4300,25 @@
     </row>
     <row r="9" customHeight="1" spans="3:22">
       <c r="C9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
@@ -4309,13 +4342,13 @@
         <v>0</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U9" s="1">
         <v>0</v>
@@ -4324,25 +4357,25 @@
     </row>
     <row r="10" customHeight="1" spans="3:22">
       <c r="C10" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J10" s="1">
         <v>0</v>
@@ -4366,13 +4399,13 @@
         <v>0</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="U10" s="1">
         <v>0</v>
@@ -4381,25 +4414,25 @@
     </row>
     <row r="11" customHeight="1" spans="3:22">
       <c r="C11" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J11" s="1">
         <v>0</v>
@@ -4423,13 +4456,13 @@
         <v>0</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U11" s="1">
         <v>0</v>
@@ -4438,25 +4471,25 @@
     </row>
     <row r="12" customHeight="1" spans="3:22">
       <c r="C12" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J12" s="1">
         <v>0</v>
@@ -4480,13 +4513,13 @@
         <v>0</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U12" s="1">
         <v>0</v>
@@ -4495,25 +4528,25 @@
     </row>
     <row r="13" customHeight="1" spans="3:22">
       <c r="C13" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J13" s="1">
         <v>0</v>
@@ -4537,13 +4570,13 @@
         <v>0</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="U13" s="1">
         <v>0</v>
@@ -4552,25 +4585,25 @@
     </row>
     <row r="14" customHeight="1" spans="3:22">
       <c r="C14" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J14" s="1">
         <v>0</v>
@@ -4594,13 +4627,13 @@
         <v>0</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="U14" s="1">
         <v>0</v>
@@ -4609,25 +4642,25 @@
     </row>
     <row r="15" customHeight="1" spans="3:22">
       <c r="C15" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J15" s="1">
         <v>0</v>
@@ -4651,13 +4684,13 @@
         <v>0</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U15" s="1">
         <v>0</v>
@@ -4666,25 +4699,25 @@
     </row>
     <row r="16" customHeight="1" spans="3:22">
       <c r="C16" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J16" s="1">
         <v>0</v>
@@ -4708,13 +4741,13 @@
         <v>0</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="U16" s="1">
         <v>0</v>
@@ -4723,25 +4756,25 @@
     </row>
     <row r="17" customHeight="1" spans="3:22">
       <c r="C17" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J17" s="1">
         <v>0</v>
@@ -4765,13 +4798,13 @@
         <v>0</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="U17" s="1">
         <v>0</v>
@@ -4780,25 +4813,25 @@
     </row>
     <row r="18" customHeight="1" spans="3:22">
       <c r="C18" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J18" s="1">
         <v>0</v>
@@ -4822,13 +4855,13 @@
         <v>0</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="U18" s="1">
         <v>0</v>
@@ -4837,25 +4870,25 @@
     </row>
     <row r="19" customHeight="1" spans="3:22">
       <c r="C19" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J19" s="1">
         <v>0</v>
@@ -4879,13 +4912,13 @@
         <v>0</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="U19" s="1">
         <v>0</v>
@@ -4894,25 +4927,25 @@
     </row>
     <row r="20" customHeight="1" spans="3:22">
       <c r="C20" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J20" s="1">
         <v>0</v>
@@ -4936,13 +4969,13 @@
         <v>0</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="U20" s="1">
         <v>0</v>
@@ -4951,25 +4984,25 @@
     </row>
     <row r="21" customHeight="1" spans="3:22">
       <c r="C21" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J21" s="1">
         <f t="shared" ref="J21:J40" si="0">(D21-1014)*1</f>
@@ -4994,13 +5027,13 @@
         <v>0</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U21" s="1">
         <v>0</v>
@@ -5009,25 +5042,25 @@
     </row>
     <row r="22" customHeight="1" spans="3:22">
       <c r="C22" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J22" s="1">
         <f t="shared" si="0"/>
@@ -5052,13 +5085,13 @@
         <v>0</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U22" s="1">
         <v>0</v>
@@ -5067,25 +5100,25 @@
     </row>
     <row r="23" customHeight="1" spans="3:22">
       <c r="C23" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J23" s="1">
         <f t="shared" si="0"/>
@@ -5110,13 +5143,13 @@
         <v>0</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U23" s="1">
         <v>0</v>
@@ -5125,25 +5158,25 @@
     </row>
     <row r="24" customHeight="1" spans="3:22">
       <c r="C24" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J24" s="1">
         <f t="shared" si="0"/>
@@ -5168,13 +5201,13 @@
         <v>0</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U24" s="1">
         <v>0</v>
@@ -5183,25 +5216,25 @@
     </row>
     <row r="25" customHeight="1" spans="3:22">
       <c r="C25" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J25" s="1">
         <f t="shared" si="0"/>
@@ -5226,13 +5259,13 @@
         <v>0</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U25" s="1">
         <v>0</v>
@@ -5241,25 +5274,25 @@
     </row>
     <row r="26" customHeight="1" spans="3:22">
       <c r="C26" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J26" s="1">
         <f t="shared" si="0"/>
@@ -5284,13 +5317,13 @@
         <v>0</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U26" s="1">
         <v>0</v>
@@ -5299,25 +5332,25 @@
     </row>
     <row r="27" customHeight="1" spans="3:22">
       <c r="C27" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J27" s="1">
         <f t="shared" si="0"/>
@@ -5342,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U27" s="1">
         <v>0</v>
@@ -5357,25 +5390,25 @@
     </row>
     <row r="28" customHeight="1" spans="3:22">
       <c r="C28" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J28" s="1">
         <f t="shared" si="0"/>
@@ -5400,13 +5433,13 @@
         <v>0</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U28" s="1">
         <v>0</v>
@@ -5415,25 +5448,25 @@
     </row>
     <row r="29" customHeight="1" spans="3:22">
       <c r="C29" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J29" s="1">
         <f t="shared" si="0"/>
@@ -5458,13 +5491,13 @@
         <v>0</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U29" s="1">
         <v>0</v>
@@ -5473,25 +5506,25 @@
     </row>
     <row r="30" customHeight="1" spans="3:22">
       <c r="C30" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J30" s="1">
         <f t="shared" si="0"/>
@@ -5516,13 +5549,13 @@
         <v>0</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U30" s="1">
         <v>0</v>
@@ -5531,25 +5564,25 @@
     </row>
     <row r="31" customHeight="1" spans="3:22">
       <c r="C31" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J31" s="1">
         <f t="shared" si="0"/>
@@ -5574,13 +5607,13 @@
         <v>0</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U31" s="1">
         <v>0</v>
@@ -5589,25 +5622,25 @@
     </row>
     <row r="32" customHeight="1" spans="3:22">
       <c r="C32" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J32" s="1">
         <f t="shared" si="0"/>
@@ -5632,13 +5665,13 @@
         <v>0</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U32" s="1">
         <v>0</v>
@@ -5647,25 +5680,25 @@
     </row>
     <row r="33" customHeight="1" spans="3:22">
       <c r="C33" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J33" s="1">
         <f t="shared" si="0"/>
@@ -5690,13 +5723,13 @@
         <v>0</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U33" s="1">
         <v>0</v>
@@ -5705,25 +5738,25 @@
     </row>
     <row r="34" customHeight="1" spans="3:22">
       <c r="C34" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J34" s="1">
         <f t="shared" si="0"/>
@@ -5748,13 +5781,13 @@
         <v>0</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U34" s="1">
         <v>0</v>
@@ -5763,25 +5796,25 @@
     </row>
     <row r="35" customHeight="1" spans="3:22">
       <c r="C35" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J35" s="1">
         <f t="shared" si="0"/>
@@ -5806,13 +5839,13 @@
         <v>0</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U35" s="1">
         <v>0</v>
@@ -5821,25 +5854,25 @@
     </row>
     <row r="36" customHeight="1" spans="3:22">
       <c r="C36" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J36" s="1">
         <f t="shared" si="0"/>
@@ -5864,13 +5897,13 @@
         <v>0</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U36" s="1">
         <v>0</v>
@@ -5879,25 +5912,25 @@
     </row>
     <row r="37" customHeight="1" spans="3:22">
       <c r="C37" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J37" s="1">
         <f t="shared" si="0"/>
@@ -5922,13 +5955,13 @@
         <v>0</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U37" s="1">
         <v>0</v>
@@ -5937,25 +5970,25 @@
     </row>
     <row r="38" customHeight="1" spans="3:22">
       <c r="C38" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J38" s="1">
         <f t="shared" si="0"/>
@@ -5980,13 +6013,13 @@
         <v>0</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U38" s="1">
         <v>0</v>
@@ -5995,25 +6028,25 @@
     </row>
     <row r="39" customHeight="1" spans="3:22">
       <c r="C39" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J39" s="1">
         <f t="shared" si="0"/>
@@ -6038,13 +6071,13 @@
         <v>0</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U39" s="1">
         <v>0</v>
@@ -6053,25 +6086,25 @@
     </row>
     <row r="40" customHeight="1" spans="3:22">
       <c r="C40" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J40" s="1">
         <f t="shared" si="0"/>
@@ -6096,13 +6129,13 @@
         <v>0</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U40" s="1">
         <v>0</v>
@@ -6112,25 +6145,25 @@
     <row r="41" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A41" s="3"/>
       <c r="C41" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J41" s="1">
         <f>(D41-1034)*5+20</f>
@@ -6155,13 +6188,13 @@
         <v>0</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U41" s="1">
         <v>0</v>
@@ -6170,25 +6203,25 @@
     <row r="42" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A42" s="3"/>
       <c r="C42" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J42" s="1">
         <f t="shared" ref="J41:J50" si="1">(D42-1034)*4+20</f>
@@ -6213,13 +6246,13 @@
         <v>0</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U42" s="1">
         <v>0</v>
@@ -6228,25 +6261,25 @@
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A43" s="3"/>
       <c r="C43" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J43" s="1">
         <f t="shared" si="1"/>
@@ -6271,13 +6304,13 @@
         <v>0</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U43" s="1">
         <v>0</v>
@@ -6286,25 +6319,25 @@
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A44" s="3"/>
       <c r="C44" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E44" s="1">
         <v>2</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J44" s="1">
         <f t="shared" si="1"/>
@@ -6329,13 +6362,13 @@
         <v>0</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U44" s="1">
         <v>0</v>
@@ -6344,25 +6377,25 @@
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A45" s="3"/>
       <c r="C45" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E45" s="1">
         <v>2</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J45" s="1">
         <f t="shared" si="1"/>
@@ -6387,13 +6420,13 @@
         <v>0</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U45" s="1">
         <v>0</v>
@@ -6402,25 +6435,25 @@
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A46" s="3"/>
       <c r="C46" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E46" s="1">
         <v>2</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J46" s="1">
         <f t="shared" si="1"/>
@@ -6445,13 +6478,13 @@
         <v>0</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U46" s="1">
         <v>0</v>
@@ -6462,25 +6495,25 @@
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A47" s="3"/>
       <c r="C47" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E47" s="1">
         <v>2</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J47" s="1">
         <f t="shared" si="1"/>
@@ -6505,13 +6538,13 @@
         <v>0</v>
       </c>
       <c r="Q47" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U47" s="1">
         <v>0</v>
@@ -6522,25 +6555,25 @@
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A48" s="3"/>
       <c r="C48" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E48" s="1">
         <v>2</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J48" s="1">
         <f t="shared" si="1"/>
@@ -6565,13 +6598,13 @@
         <v>0</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U48" s="1">
         <v>0</v>
@@ -6582,25 +6615,25 @@
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A49" s="3"/>
       <c r="C49" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E49" s="1">
         <v>2</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J49" s="1">
         <f t="shared" si="1"/>
@@ -6625,13 +6658,13 @@
         <v>0</v>
       </c>
       <c r="Q49" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U49" s="1">
         <v>0</v>
@@ -6642,25 +6675,25 @@
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A50" s="3"/>
       <c r="C50" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E50" s="1">
         <v>2</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J50" s="1">
         <f t="shared" si="1"/>
@@ -6685,13 +6718,13 @@
         <v>0</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U50" s="1">
         <v>0</v>
@@ -6702,25 +6735,25 @@
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A51" s="3"/>
       <c r="C51" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E51" s="1">
         <v>2</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J51" s="1">
         <v>65</v>
@@ -6746,13 +6779,13 @@
         <v>0</v>
       </c>
       <c r="Q51" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U51" s="1">
         <v>0</v>
@@ -6763,25 +6796,25 @@
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A52" s="3"/>
       <c r="C52" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E52" s="1">
         <v>2</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J52" s="1">
         <v>70</v>
@@ -6807,13 +6840,13 @@
         <v>0</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U52" s="1">
         <v>0</v>
@@ -6824,25 +6857,25 @@
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A53" s="3"/>
       <c r="C53" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E53" s="1">
         <v>2</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J53" s="1">
         <v>75</v>
@@ -6868,13 +6901,13 @@
         <v>0</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U53" s="1">
         <v>0</v>
@@ -6885,25 +6918,25 @@
     <row r="54" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A54" s="3"/>
       <c r="C54" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E54" s="1">
         <v>2</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J54" s="1">
         <v>80</v>
@@ -6929,13 +6962,13 @@
         <v>0</v>
       </c>
       <c r="Q54" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U54" s="1">
         <v>0</v>
@@ -6946,25 +6979,25 @@
     <row r="55" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A55" s="3"/>
       <c r="C55" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E55" s="1">
         <v>2</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J55" s="1">
         <v>85</v>
@@ -6990,13 +7023,13 @@
         <v>0</v>
       </c>
       <c r="Q55" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U55" s="1">
         <v>0</v>
@@ -7007,25 +7040,25 @@
     <row r="56" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A56" s="3"/>
       <c r="C56" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E56" s="1">
         <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J56" s="1">
         <f t="shared" ref="J56:J65" si="4">(D56-1049)*5+85</f>
@@ -7053,13 +7086,13 @@
         <v>0</v>
       </c>
       <c r="Q56" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U56" s="1">
         <v>0</v>
@@ -7070,25 +7103,25 @@
     <row r="57" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A57" s="3"/>
       <c r="C57" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E57" s="1">
         <v>2</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J57" s="1">
         <f t="shared" si="4"/>
@@ -7116,13 +7149,13 @@
         <v>0</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U57" s="1">
         <v>0</v>
@@ -7133,25 +7166,25 @@
     <row r="58" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A58" s="3"/>
       <c r="C58" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E58" s="1">
         <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J58" s="1">
         <f t="shared" si="4"/>
@@ -7179,13 +7212,13 @@
         <v>0</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U58" s="1">
         <v>0</v>
@@ -7196,25 +7229,25 @@
     <row r="59" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A59" s="3"/>
       <c r="C59" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E59" s="1">
         <v>2</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J59" s="1">
         <f t="shared" si="4"/>
@@ -7242,13 +7275,13 @@
         <v>0</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U59" s="1">
         <v>0</v>
@@ -7259,25 +7292,25 @@
     <row r="60" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A60" s="3"/>
       <c r="C60" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E60" s="1">
         <v>2</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J60" s="1">
         <f t="shared" si="4"/>
@@ -7305,13 +7338,13 @@
         <v>0</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U60" s="1">
         <v>0</v>
@@ -7322,25 +7355,25 @@
     <row r="61" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A61" s="3"/>
       <c r="C61" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E61" s="1">
         <v>2</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J61" s="1">
         <f t="shared" si="4"/>
@@ -7368,13 +7401,13 @@
         <v>0</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U61" s="1">
         <v>0</v>
@@ -7385,25 +7418,25 @@
     <row r="62" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A62" s="3"/>
       <c r="C62" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E62" s="1">
         <v>2</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J62" s="1">
         <f t="shared" si="4"/>
@@ -7431,13 +7464,13 @@
         <v>0</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="R62" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U62" s="1">
         <v>0</v>
@@ -7448,25 +7481,25 @@
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A63" s="3"/>
       <c r="C63" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E63" s="1">
         <v>2</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J63" s="1">
         <f t="shared" si="4"/>
@@ -7494,13 +7527,13 @@
         <v>0</v>
       </c>
       <c r="Q63" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="R63" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U63" s="1">
         <v>0</v>
@@ -7511,25 +7544,25 @@
     <row r="64" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A64" s="3"/>
       <c r="C64" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E64" s="1">
         <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J64" s="1">
         <f t="shared" si="4"/>
@@ -7557,13 +7590,13 @@
         <v>0</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U64" s="1">
         <v>0</v>
@@ -7574,25 +7607,25 @@
     <row r="65" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A65" s="3"/>
       <c r="C65" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E65" s="1">
         <v>2</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J65" s="1">
         <f t="shared" si="4"/>
@@ -7620,13 +7653,13 @@
         <v>0</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="R65" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U65" s="1">
         <v>0</v>
@@ -7637,25 +7670,25 @@
     <row r="66" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A66" s="3"/>
       <c r="C66" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E66" s="1">
         <v>2</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J66" s="1">
         <f t="shared" ref="J66:M66" si="6">J65+8</f>
@@ -7683,13 +7716,13 @@
         <v>0</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U66" s="1">
         <v>0</v>
@@ -7700,25 +7733,25 @@
     <row r="67" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A67" s="3"/>
       <c r="C67" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E67" s="1">
         <v>2</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J67" s="1">
         <f t="shared" ref="J66:J71" si="7">J66+8</f>
@@ -7746,13 +7779,13 @@
         <v>0</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="R67" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U67" s="1">
         <v>0</v>
@@ -7763,25 +7796,25 @@
     <row r="68" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A68" s="3"/>
       <c r="C68" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E68" s="1">
         <v>2</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J68" s="1">
         <f t="shared" si="7"/>
@@ -7809,13 +7842,13 @@
         <v>0</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="R68" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U68" s="1">
         <v>0</v>
@@ -7826,25 +7859,25 @@
     <row r="69" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A69" s="3"/>
       <c r="C69" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J69" s="1">
         <f t="shared" si="7"/>
@@ -7872,13 +7905,13 @@
         <v>0</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U69" s="1">
         <v>0</v>
@@ -7889,25 +7922,25 @@
     <row r="70" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A70" s="3"/>
       <c r="C70" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J70" s="1">
         <f t="shared" si="7"/>
@@ -7934,13 +7967,13 @@
         <v>0</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="R70" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U70" s="1">
         <v>0</v>
@@ -7951,25 +7984,25 @@
     <row r="71" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A71" s="3"/>
       <c r="C71" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G71" s="12" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="I71" s="12" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J71" s="1">
         <f t="shared" ref="J71:M71" si="11">J70+15</f>
@@ -7997,13 +8030,13 @@
         <v>0</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="R71" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U71" s="1">
         <v>0</v>
@@ -8014,25 +8047,25 @@
     <row r="72" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A72" s="3"/>
       <c r="C72" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G72" s="12" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J72" s="1">
         <f t="shared" ref="J72:J81" si="14">J71+15</f>
@@ -8060,13 +8093,13 @@
         <v>0</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U72" s="1">
         <v>0</v>
@@ -8077,25 +8110,25 @@
     <row r="73" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A73" s="3"/>
       <c r="C73" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G73" s="12" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="I73" s="13" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J73" s="1">
         <f t="shared" si="14"/>
@@ -8123,13 +8156,13 @@
         <v>0</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="R73" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U73" s="1">
         <v>0</v>
@@ -8140,25 +8173,25 @@
     <row r="74" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A74" s="3"/>
       <c r="C74" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G74" s="12" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J74" s="1">
         <f t="shared" si="14"/>
@@ -8186,13 +8219,13 @@
         <v>0</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="R74" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U74" s="1">
         <v>0</v>
@@ -8203,25 +8236,25 @@
     <row r="75" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A75" s="3"/>
       <c r="C75" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G75" s="12" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I75" s="13" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J75" s="1">
         <f t="shared" si="14"/>
@@ -8249,13 +8282,13 @@
         <v>0</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="R75" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U75" s="1">
         <v>0</v>
@@ -8267,25 +8300,25 @@
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E76" s="1">
         <v>3</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="G76" s="12" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="I76" s="13" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="J76" s="1">
         <f t="shared" si="14"/>
@@ -8319,7 +8352,7 @@
         <v>22938500000</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U76" s="1">
         <v>0</v>
@@ -8329,25 +8362,25 @@
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E77" s="1">
         <v>3</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="G77" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I77" s="13" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J77" s="1">
         <f t="shared" si="14"/>
@@ -8381,7 +8414,7 @@
         <v>23938500000</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U77" s="1">
         <v>0</v>
@@ -8391,25 +8424,25 @@
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E78" s="1">
         <v>3</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="G78" s="12" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J78" s="1">
         <f t="shared" si="14"/>
@@ -8443,7 +8476,7 @@
         <v>24938500000</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U78" s="1">
         <v>0</v>
@@ -8453,25 +8486,25 @@
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E79" s="1">
         <v>3</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I79" s="13" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="J79" s="1">
         <f t="shared" si="14"/>
@@ -8505,7 +8538,7 @@
         <v>25938500000</v>
       </c>
       <c r="T79" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U79" s="1">
         <v>0</v>
@@ -8515,25 +8548,25 @@
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E80" s="1">
         <v>3</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="G80" s="12" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="J80" s="1">
         <f t="shared" si="14"/>
@@ -8567,7 +8600,7 @@
         <v>26938500000</v>
       </c>
       <c r="T80" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U80" s="1">
         <v>0</v>
@@ -8577,25 +8610,25 @@
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E81" s="1">
         <v>3</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G81" s="12" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H81" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I81" s="13" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J81" s="1">
         <f t="shared" ref="J81:J91" si="16">J80+20</f>
@@ -8629,7 +8662,7 @@
         <v>30000000000</v>
       </c>
       <c r="T81" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U81" s="1">
         <v>0</v>
@@ -8641,25 +8674,25 @@
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E82" s="1">
         <v>3</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G82" s="12" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J82" s="1">
         <f t="shared" si="16"/>
@@ -8693,7 +8726,7 @@
         <v>32000000000</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U82" s="1">
         <v>0</v>
@@ -8705,25 +8738,25 @@
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E83" s="1">
         <v>3</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G83" s="12" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H83" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="J83" s="1">
         <f t="shared" si="16"/>
@@ -8757,7 +8790,7 @@
         <v>34000000000</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U83" s="1">
         <v>0</v>
@@ -8769,25 +8802,25 @@
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E84" s="1">
         <v>3</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G84" s="12" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="I84" s="13" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="J84" s="1">
         <f t="shared" si="16"/>
@@ -8821,7 +8854,7 @@
         <v>37000000000</v>
       </c>
       <c r="T84" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U84" s="1">
         <v>0</v>
@@ -8833,25 +8866,25 @@
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E85" s="1">
         <v>3</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="G85" s="12" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H85" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="J85" s="1">
         <f t="shared" si="16"/>
@@ -8885,7 +8918,7 @@
         <v>40000000000</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U85" s="1">
         <v>0</v>
@@ -8897,25 +8930,25 @@
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E86" s="1">
         <v>3</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="G86" s="12" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H86" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="I86" s="13" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="J86" s="1">
         <f t="shared" si="16"/>
@@ -8949,7 +8982,7 @@
         <v>50000000000</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U86" s="1">
         <v>0</v>
@@ -8961,25 +8994,25 @@
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E87" s="1">
         <v>3</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G87" s="12" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H87" s="11" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="I87" s="13" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="J87" s="1">
         <f t="shared" si="16"/>
@@ -9013,7 +9046,7 @@
         <v>60000000000</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U87" s="1">
         <v>0</v>
@@ -9025,25 +9058,25 @@
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E88" s="1">
         <v>3</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G88" s="12" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H88" s="11" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="I88" s="13" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="J88" s="1">
         <f t="shared" si="16"/>
@@ -9077,7 +9110,7 @@
         <v>70000000000</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U88" s="1">
         <v>0</v>
@@ -9089,25 +9122,25 @@
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E89" s="1">
         <v>3</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G89" s="12" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H89" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I89" s="13" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="J89" s="1">
         <f t="shared" si="16"/>
@@ -9141,7 +9174,7 @@
         <v>80000000000</v>
       </c>
       <c r="T89" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U89" s="1">
         <v>0</v>
@@ -9153,25 +9186,25 @@
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E90" s="1">
         <v>3</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G90" s="12" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="I90" s="13" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="J90" s="1">
         <f t="shared" si="16"/>
@@ -9199,13 +9232,13 @@
         <v>0</v>
       </c>
       <c r="Q90" s="11" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="R90" s="11" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="T90" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U90" s="1">
         <v>0</v>
@@ -9217,25 +9250,25 @@
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E91" s="1">
         <v>3</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="G91" s="12" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H91" s="11" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="J91" s="1">
         <f t="shared" ref="J91:J96" si="18">J90+25</f>
@@ -9263,13 +9296,13 @@
         <v>0</v>
       </c>
       <c r="Q91" s="11" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="R91" s="11" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="T91" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U91" s="1">
         <v>0</v>
@@ -9281,25 +9314,25 @@
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E92" s="1">
         <v>3</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G92" s="12" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="I92" s="13" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="J92" s="1">
         <f t="shared" si="18"/>
@@ -9327,13 +9360,13 @@
         <v>0</v>
       </c>
       <c r="Q92" s="11" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="R92" s="11" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="T92" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U92" s="1">
         <v>0</v>
@@ -9345,25 +9378,25 @@
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E93" s="1">
         <v>3</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="G93" s="12" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="I93" s="13" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="J93" s="1">
         <f t="shared" si="18"/>
@@ -9391,13 +9424,13 @@
         <v>0</v>
       </c>
       <c r="Q93" s="11" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="R93" s="11" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="T93" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U93" s="1">
         <v>0</v>
@@ -9409,25 +9442,25 @@
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E94" s="1">
         <v>3</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="G94" s="12" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="I94" s="13" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="J94" s="1">
         <f t="shared" si="18"/>
@@ -9455,13 +9488,13 @@
         <v>0</v>
       </c>
       <c r="Q94" s="11" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="R94" s="11" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="T94" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U94" s="1">
         <v>0</v>
@@ -9473,25 +9506,25 @@
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E95" s="1">
         <v>3</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="G95" s="12" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="I95" s="13" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="J95" s="1">
         <f t="shared" si="18"/>
@@ -9519,13 +9552,13 @@
         <v>0</v>
       </c>
       <c r="Q95" s="11" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="R95" s="11" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="T95" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U95" s="1">
         <v>0</v>
@@ -9535,25 +9568,25 @@
     </row>
     <row r="96" customHeight="1" spans="3:21">
       <c r="C96" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E96" s="1">
         <v>3</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="G96" s="12" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H96" s="11" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="I96" s="13" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="J96" s="1">
         <f t="shared" ref="J96:J100" si="22">J95+30</f>
@@ -9581,13 +9614,13 @@
         <v>0</v>
       </c>
       <c r="Q96" s="11" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="R96" s="11" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="T96" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U96" s="1">
         <v>0</v>
@@ -9595,25 +9628,25 @@
     </row>
     <row r="97" customHeight="1" spans="3:21">
       <c r="C97" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E97" s="1">
         <v>3</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G97" s="12" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H97" s="11" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="I97" s="13" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="J97" s="1">
         <f t="shared" si="22"/>
@@ -9641,13 +9674,13 @@
         <v>0</v>
       </c>
       <c r="Q97" s="11" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="R97" s="11" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="T97" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U97" s="1">
         <v>0</v>
@@ -9655,25 +9688,25 @@
     </row>
     <row r="98" customHeight="1" spans="3:21">
       <c r="C98" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E98" s="1">
         <v>3</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G98" s="12" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H98" s="11" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="I98" s="13" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="J98" s="1">
         <f t="shared" si="22"/>
@@ -9701,13 +9734,13 @@
         <v>0</v>
       </c>
       <c r="Q98" s="11" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="R98" s="11" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="T98" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U98" s="1">
         <v>0</v>
@@ -9715,25 +9748,25 @@
     </row>
     <row r="99" customHeight="1" spans="3:21">
       <c r="C99" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E99" s="1">
         <v>3</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G99" s="12" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H99" s="11" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="I99" s="13" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="J99" s="1">
         <f t="shared" si="22"/>
@@ -9761,13 +9794,13 @@
         <v>0</v>
       </c>
       <c r="Q99" s="11" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="R99" s="11" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="T99" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U99" s="1">
         <v>0</v>
@@ -9775,25 +9808,25 @@
     </row>
     <row r="100" customHeight="1" spans="3:21">
       <c r="C100" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E100" s="1">
         <v>3</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G100" s="12" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="I100" s="13" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="J100" s="1">
         <f t="shared" si="22"/>
@@ -9821,13 +9854,13 @@
         <v>0</v>
       </c>
       <c r="Q100" s="11" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="R100" s="11" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="T100" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U100" s="1">
         <v>0</v>
@@ -9837,25 +9870,25 @@
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E101" s="1">
         <v>3</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G101" s="12" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H101" s="11" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="I101" s="13" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="J101" s="1">
         <f t="shared" ref="J101:M101" si="26">J100+8</f>
@@ -9883,13 +9916,13 @@
         <v>0</v>
       </c>
       <c r="Q101" s="11" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="R101" s="11" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="T101" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U101" s="1">
         <v>0</v>
@@ -9901,25 +9934,25 @@
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E102" s="1">
         <v>3</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="G102" s="12" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I102" s="13" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="J102" s="1">
         <f t="shared" ref="J102:M102" si="27">J101+8</f>
@@ -9947,13 +9980,13 @@
         <v>0</v>
       </c>
       <c r="Q102" s="11" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="R102" s="11" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="T102" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U102" s="1">
         <v>0</v>
@@ -9965,25 +9998,25 @@
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E103" s="1">
         <v>3</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="G103" s="12" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H103" s="11" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="I103" s="13" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="J103" s="1">
         <f t="shared" ref="J103:M103" si="28">J102+8</f>
@@ -10011,13 +10044,13 @@
         <v>0</v>
       </c>
       <c r="Q103" s="11" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="R103" s="11" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="T103" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U103" s="1">
         <v>0</v>
@@ -10029,25 +10062,25 @@
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E104" s="1">
         <v>3</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="G104" s="12" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="I104" s="13" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="J104" s="1">
         <f t="shared" ref="J104:M104" si="29">J103+8</f>
@@ -10075,13 +10108,13 @@
         <v>0</v>
       </c>
       <c r="Q104" s="11" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="R104" s="11" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="T104" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U104" s="1">
         <v>0</v>
@@ -10093,25 +10126,25 @@
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E105" s="1">
         <v>3</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="G105" s="12" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H105" s="11" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="I105" s="13" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="J105" s="1">
         <f t="shared" ref="J105:M105" si="30">J104+8</f>
@@ -10139,13 +10172,13 @@
         <v>0</v>
       </c>
       <c r="Q105" s="11" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="R105" s="11" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="T105" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U105" s="1">
         <v>0</v>
@@ -10157,25 +10190,25 @@
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E106" s="1">
         <v>3</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="G106" s="12" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H106" s="11" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="I106" s="13" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="J106" s="1">
         <f t="shared" ref="J106:J115" si="31">J105+15</f>
@@ -10203,13 +10236,13 @@
         <v>0</v>
       </c>
       <c r="Q106" s="11" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="R106" s="11" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="T106" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U106" s="1">
         <v>0</v>
@@ -10221,25 +10254,25 @@
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E107" s="1">
         <v>3</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="G107" s="12" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H107" s="11" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="I107" s="13" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="J107" s="1">
         <f t="shared" si="31"/>
@@ -10267,13 +10300,13 @@
         <v>0</v>
       </c>
       <c r="Q107" s="11" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="R107" s="11" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="T107" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U107" s="1">
         <v>0</v>
@@ -10285,25 +10318,25 @@
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E108" s="1">
         <v>3</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="G108" s="12" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H108" s="11" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="I108" s="13" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="J108" s="1">
         <f t="shared" si="31"/>
@@ -10331,13 +10364,13 @@
         <v>0</v>
       </c>
       <c r="Q108" s="11" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="R108" s="11" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="T108" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U108" s="1">
         <v>0</v>
@@ -10349,25 +10382,25 @@
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E109" s="1">
         <v>3</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="G109" s="12" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H109" s="11" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="I109" s="13" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="J109" s="1">
         <f t="shared" si="31"/>
@@ -10395,13 +10428,13 @@
         <v>0</v>
       </c>
       <c r="Q109" s="11" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="R109" s="11" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="T109" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U109" s="1">
         <v>0</v>
@@ -10413,25 +10446,25 @@
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E110" s="1">
         <v>3</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="G110" s="12" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H110" s="11" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="I110" s="13" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="J110" s="1">
         <f t="shared" si="31"/>
@@ -10459,13 +10492,13 @@
         <v>0</v>
       </c>
       <c r="Q110" s="11" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="R110" s="11" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="T110" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U110" s="1">
         <v>0</v>
@@ -10477,25 +10510,25 @@
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E111" s="2">
         <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="G111" s="14" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H111" s="15" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="I111" s="16" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="J111" s="2">
         <v>1500</v>
@@ -10519,13 +10552,13 @@
         <v>90</v>
       </c>
       <c r="Q111" s="15" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="R111" s="15" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="T111" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U111" s="2">
         <v>0</v>
@@ -10535,25 +10568,25 @@
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E112" s="1">
         <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="G112" s="12" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H112" s="11" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="I112" s="13" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="J112" s="1">
         <f>J111+100</f>
@@ -10582,13 +10615,13 @@
         <v>90</v>
       </c>
       <c r="Q112" s="11" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="R112" s="11" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="T112" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U112" s="1">
         <v>0</v>
@@ -10598,25 +10631,25 @@
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E113" s="1">
         <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="G113" s="12" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H113" s="11" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="I113" s="13" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="J113" s="1">
         <f>J112+100</f>
@@ -10645,13 +10678,13 @@
         <v>90</v>
       </c>
       <c r="Q113" s="11" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="R113" s="11" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="T113" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U113" s="1">
         <v>0</v>
@@ -10661,25 +10694,25 @@
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="1" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E114" s="1">
         <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="G114" s="12" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H114" s="11" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="I114" s="13" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="J114" s="1">
         <f>J113+100</f>
@@ -10708,13 +10741,13 @@
         <v>90</v>
       </c>
       <c r="Q114" s="11" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="R114" s="11" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="T114" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U114" s="1">
         <v>0</v>
@@ -10724,25 +10757,25 @@
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E115" s="1">
         <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G115" s="12" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H115" s="11" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="I115" s="13" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="J115" s="1">
         <f>J114+100</f>
@@ -10771,13 +10804,13 @@
         <v>90</v>
       </c>
       <c r="Q115" s="11" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="R115" s="11" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="T115" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U115" s="1">
         <v>0</v>
@@ -10787,32 +10820,32 @@
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="1" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E116" s="1">
         <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G116" s="12" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H116" s="11" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="I116" s="13" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="J116" s="1">
-        <f t="shared" ref="J116:J145" si="37">J115+200</f>
+        <f>J115+200</f>
         <v>2100</v>
       </c>
       <c r="K116" s="1">
-        <f t="shared" ref="K116:K145" si="38">K115+300</f>
+        <f>K115+300</f>
         <v>1900</v>
       </c>
       <c r="L116" s="1">
@@ -10834,13 +10867,13 @@
         <v>90</v>
       </c>
       <c r="Q116" s="11" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="R116" s="11" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="T116" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U116" s="1">
         <v>0</v>
@@ -10852,32 +10885,32 @@
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="1" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="E117" s="1">
         <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="G117" s="12" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H117" s="11" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="I117" s="13" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="J117" s="1">
-        <f t="shared" si="37"/>
+        <f>J116+200</f>
         <v>2300</v>
       </c>
       <c r="K117" s="1">
-        <f t="shared" si="38"/>
+        <f>K116+300</f>
         <v>2200</v>
       </c>
       <c r="L117" s="1">
@@ -10899,13 +10932,13 @@
         <v>90</v>
       </c>
       <c r="Q117" s="11" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="R117" s="11" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="T117" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U117" s="1">
         <v>0</v>
@@ -10917,32 +10950,32 @@
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="1" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E118" s="1">
         <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="G118" s="12" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H118" s="11" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="I118" s="13" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="J118" s="1">
-        <f t="shared" si="37"/>
+        <f>J117+200</f>
         <v>2500</v>
       </c>
       <c r="K118" s="1">
-        <f t="shared" si="38"/>
+        <f>K117+300</f>
         <v>2500</v>
       </c>
       <c r="L118" s="1">
@@ -10964,13 +10997,13 @@
         <v>90</v>
       </c>
       <c r="Q118" s="11" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="R118" s="11" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="T118" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U118" s="1">
         <v>0</v>
@@ -10982,32 +11015,32 @@
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="1" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E119" s="1">
         <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="G119" s="12" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H119" s="11" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="I119" s="13" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="J119" s="1">
-        <f t="shared" si="37"/>
+        <f>J118+200</f>
         <v>2700</v>
       </c>
       <c r="K119" s="1">
-        <f t="shared" si="38"/>
+        <f>K118+300</f>
         <v>2800</v>
       </c>
       <c r="L119" s="1">
@@ -11029,13 +11062,13 @@
         <v>90</v>
       </c>
       <c r="Q119" s="11" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="R119" s="11" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="T119" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U119" s="1">
         <v>0</v>
@@ -11047,32 +11080,32 @@
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E120" s="1">
         <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="G120" s="12" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H120" s="11" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="I120" s="13" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="J120" s="1">
-        <f t="shared" si="37"/>
+        <f>J119+200</f>
         <v>2900</v>
       </c>
       <c r="K120" s="1">
-        <f t="shared" si="38"/>
+        <f>K119+300</f>
         <v>3100</v>
       </c>
       <c r="L120" s="1">
@@ -11094,13 +11127,13 @@
         <v>90</v>
       </c>
       <c r="Q120" s="11" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="R120" s="11" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="T120" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U120" s="1">
         <v>0</v>
@@ -11110,32 +11143,32 @@
     </row>
     <row r="121" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C121" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="E121" s="1">
         <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G121" s="12" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H121" s="11" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="I121" s="13" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="J121" s="1">
-        <f t="shared" si="37"/>
+        <f>J120+200</f>
         <v>3100</v>
       </c>
       <c r="K121" s="1">
-        <f t="shared" si="38"/>
+        <f>K120+300</f>
         <v>3400</v>
       </c>
       <c r="L121" s="1">
@@ -11151,20 +11184,20 @@
         <v>45</v>
       </c>
       <c r="O121" s="3">
-        <f t="shared" ref="O121:O125" si="39">O120+3</f>
+        <f>O120+3</f>
         <v>3</v>
       </c>
       <c r="P121" s="3">
         <v>90</v>
       </c>
       <c r="Q121" s="11" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="R121" s="11" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="T121" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U121" s="1">
         <v>0</v>
@@ -11174,32 +11207,32 @@
     </row>
     <row r="122" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C122" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="E122" s="1">
         <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G122" s="12" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H122" s="11" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="I122" s="13" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="J122" s="1">
-        <f t="shared" si="37"/>
+        <f>J121+200</f>
         <v>3300</v>
       </c>
       <c r="K122" s="1">
-        <f t="shared" si="38"/>
+        <f>K121+300</f>
         <v>3700</v>
       </c>
       <c r="L122" s="1">
@@ -11215,20 +11248,20 @@
         <v>46</v>
       </c>
       <c r="O122" s="3">
-        <f t="shared" si="39"/>
+        <f>O121+3</f>
         <v>6</v>
       </c>
       <c r="P122" s="3">
         <v>90</v>
       </c>
       <c r="Q122" s="11" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="R122" s="11" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="T122" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U122" s="1">
         <v>0</v>
@@ -11238,32 +11271,32 @@
     </row>
     <row r="123" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C123" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E123" s="1">
         <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G123" s="12" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H123" s="11" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="I123" s="13" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="J123" s="1">
-        <f t="shared" si="37"/>
+        <f>J122+200</f>
         <v>3500</v>
       </c>
       <c r="K123" s="1">
-        <f t="shared" si="38"/>
+        <f>K122+300</f>
         <v>4000</v>
       </c>
       <c r="L123" s="1">
@@ -11279,20 +11312,20 @@
         <v>47</v>
       </c>
       <c r="O123" s="3">
-        <f t="shared" si="39"/>
+        <f>O122+3</f>
         <v>9</v>
       </c>
       <c r="P123" s="3">
         <v>90</v>
       </c>
       <c r="Q123" s="11" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="R123" s="11" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="T123" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U123" s="1">
         <v>0</v>
@@ -11302,32 +11335,32 @@
     </row>
     <row r="124" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C124" s="1" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E124" s="1">
         <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="G124" s="12" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H124" s="11" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="I124" s="13" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="J124" s="1">
-        <f t="shared" si="37"/>
+        <f>J123+200</f>
         <v>3700</v>
       </c>
       <c r="K124" s="1">
-        <f t="shared" si="38"/>
+        <f>K123+300</f>
         <v>4300</v>
       </c>
       <c r="L124" s="1">
@@ -11343,20 +11376,20 @@
         <v>48</v>
       </c>
       <c r="O124" s="3">
-        <f t="shared" si="39"/>
+        <f>O123+3</f>
         <v>12</v>
       </c>
       <c r="P124" s="3">
         <v>90</v>
       </c>
       <c r="Q124" s="11" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="R124" s="11" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="T124" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U124" s="1">
         <v>0</v>
@@ -11366,32 +11399,32 @@
     </row>
     <row r="125" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C125" s="1" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="E125" s="1">
         <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G125" s="12" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H125" s="11" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="I125" s="13" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="J125" s="1">
-        <f t="shared" si="37"/>
+        <f>J124+200</f>
         <v>3900</v>
       </c>
       <c r="K125" s="1">
-        <f t="shared" si="38"/>
+        <f>K124+300</f>
         <v>4600</v>
       </c>
       <c r="L125" s="1">
@@ -11407,20 +11440,20 @@
         <v>49</v>
       </c>
       <c r="O125" s="3">
-        <f t="shared" si="39"/>
+        <f>O124+3</f>
         <v>15</v>
       </c>
       <c r="P125" s="3">
         <v>90</v>
       </c>
       <c r="Q125" s="11" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="R125" s="11" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="T125" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U125" s="1">
         <v>0</v>
@@ -11432,32 +11465,32 @@
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="1" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E126" s="1">
         <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="G126" s="12" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H126" s="11" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="I126" s="13" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="J126" s="1">
-        <f t="shared" si="37"/>
+        <f>J125+200</f>
         <v>4100</v>
       </c>
       <c r="K126" s="1">
-        <f t="shared" si="38"/>
+        <f>K125+300</f>
         <v>4900</v>
       </c>
       <c r="L126" s="1">
@@ -11472,20 +11505,21 @@
         <f t="shared" si="36"/>
         <v>50</v>
       </c>
-      <c r="O126" s="6">
-        <v>0</v>
+      <c r="O126" s="3">
+        <f>O125+3</f>
+        <v>18</v>
       </c>
       <c r="P126" s="3">
         <v>90</v>
       </c>
       <c r="Q126" s="11" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="R126" s="11" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="T126" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U126" s="1">
         <v>0</v>
@@ -11497,32 +11531,32 @@
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="1" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="E127" s="1">
         <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G127" s="12" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H127" s="11" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="I127" s="13" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="J127" s="1">
-        <f t="shared" si="37"/>
+        <f>J126+200</f>
         <v>4300</v>
       </c>
       <c r="K127" s="1">
-        <f t="shared" si="38"/>
+        <f>K126+300</f>
         <v>5200</v>
       </c>
       <c r="L127" s="1">
@@ -11537,20 +11571,21 @@
         <f t="shared" si="36"/>
         <v>51</v>
       </c>
-      <c r="O127" s="6">
-        <v>0</v>
+      <c r="O127" s="3">
+        <f>O126+3</f>
+        <v>21</v>
       </c>
       <c r="P127" s="3">
         <v>90</v>
       </c>
       <c r="Q127" s="11" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="R127" s="11" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="T127" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U127" s="1">
         <v>0</v>
@@ -11562,32 +11597,32 @@
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="1" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="E128" s="1">
         <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="G128" s="12" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H128" s="11" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="I128" s="13" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="J128" s="1">
-        <f t="shared" si="37"/>
+        <f>J127+200</f>
         <v>4500</v>
       </c>
       <c r="K128" s="1">
-        <f t="shared" si="38"/>
+        <f>K127+300</f>
         <v>5500</v>
       </c>
       <c r="L128" s="1">
@@ -11602,20 +11637,21 @@
         <f t="shared" si="36"/>
         <v>52</v>
       </c>
-      <c r="O128" s="6">
-        <v>0</v>
+      <c r="O128" s="3">
+        <f>O127+3</f>
+        <v>24</v>
       </c>
       <c r="P128" s="3">
         <v>90</v>
       </c>
       <c r="Q128" s="11" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="R128" s="11" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="T128" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U128" s="1">
         <v>0</v>
@@ -11627,32 +11663,32 @@
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="1" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="E129" s="1">
         <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G129" s="12" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H129" s="11" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="I129" s="13" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="J129" s="1">
-        <f t="shared" si="37"/>
+        <f>J128+200</f>
         <v>4700</v>
       </c>
       <c r="K129" s="1">
-        <f t="shared" si="38"/>
+        <f>K128+300</f>
         <v>5800</v>
       </c>
       <c r="L129" s="1">
@@ -11667,20 +11703,21 @@
         <f t="shared" si="36"/>
         <v>53</v>
       </c>
-      <c r="O129" s="6">
-        <v>0</v>
+      <c r="O129" s="3">
+        <f>O128+3</f>
+        <v>27</v>
       </c>
       <c r="P129" s="3">
         <v>90</v>
       </c>
       <c r="Q129" s="11" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="R129" s="11" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="T129" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U129" s="1">
         <v>0</v>
@@ -11692,33 +11729,33 @@
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="1" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="E130" s="1">
         <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="G130" s="12" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H130" s="11" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="I130" s="13" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="J130" s="1">
-        <f t="shared" si="37"/>
-        <v>4900</v>
+        <f t="shared" ref="J130:J135" si="37">J129+300</f>
+        <v>5000</v>
       </c>
       <c r="K130" s="1">
-        <f t="shared" si="38"/>
-        <v>6100</v>
+        <f t="shared" ref="K130:K140" si="38">K129+400</f>
+        <v>6200</v>
       </c>
       <c r="L130" s="1">
         <f t="shared" si="34"/>
@@ -11732,20 +11769,21 @@
         <f t="shared" si="36"/>
         <v>54</v>
       </c>
-      <c r="O130" s="6">
-        <v>0</v>
+      <c r="O130" s="3">
+        <f>O129+3</f>
+        <v>30</v>
       </c>
       <c r="P130" s="3">
         <v>90</v>
       </c>
       <c r="Q130" s="11" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="R130" s="11" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="T130" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U130" s="1">
         <v>0</v>
@@ -11753,13 +11791,7 @@
       <c r="V130" s="3"/>
       <c r="W130" s="3"/>
     </row>
-    <row r="131" customHeight="1" spans="1:21">
-      <c r="A131" s="3" t="s">
-        <v>874</v>
-      </c>
-      <c r="B131" s="3" t="s">
-        <v>874</v>
-      </c>
+    <row r="131" customHeight="1" spans="3:21">
       <c r="C131" s="1" t="s">
         <v>875</v>
       </c>
@@ -11772,317 +11804,298 @@
       <c r="F131" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="G131" s="4">
-        <v>1</v>
-      </c>
-      <c r="H131" s="4">
-        <v>1</v>
-      </c>
-      <c r="I131" s="4">
-        <v>1</v>
+      <c r="G131" s="12" t="s">
+        <v>878</v>
+      </c>
+      <c r="H131" s="11" t="s">
+        <v>878</v>
+      </c>
+      <c r="I131" s="13" t="s">
+        <v>879</v>
       </c>
       <c r="J131" s="1">
-        <f t="shared" si="37"/>
-        <v>5100</v>
+        <f>J130+400</f>
+        <v>5400</v>
       </c>
       <c r="K131" s="1">
         <f t="shared" si="38"/>
-        <v>6400</v>
+        <v>6600</v>
       </c>
       <c r="L131" s="1">
-        <f t="shared" si="34"/>
-        <v>2000</v>
+        <f t="shared" ref="L131:L135" si="39">L130+100</f>
+        <v>2050</v>
       </c>
       <c r="M131" s="1">
-        <f t="shared" si="35"/>
-        <v>2000</v>
+        <f t="shared" ref="M131:M135" si="40">M130+100</f>
+        <v>2050</v>
       </c>
       <c r="N131" s="3">
-        <f t="shared" si="36"/>
-        <v>55</v>
-      </c>
-      <c r="O131" s="6">
-        <v>0</v>
+        <f t="shared" ref="N131:N145" si="41">N130+2</f>
+        <v>56</v>
+      </c>
+      <c r="O131" s="3">
+        <f t="shared" ref="O131:O145" si="42">O130+4</f>
+        <v>34</v>
       </c>
       <c r="P131" s="3">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Q131" s="11" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="R131" s="11" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="T131" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U131" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="132" customHeight="1" spans="1:21">
-      <c r="A132" s="3" t="s">
-        <v>874</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>874</v>
-      </c>
+    <row r="132" customHeight="1" spans="3:21">
       <c r="C132" s="1" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="E132" s="1">
         <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>881</v>
-      </c>
-      <c r="G132" s="4">
-        <v>1</v>
-      </c>
-      <c r="H132" s="4">
-        <v>1</v>
-      </c>
-      <c r="I132" s="4">
-        <v>1</v>
+        <v>883</v>
+      </c>
+      <c r="G132" s="12" t="s">
+        <v>884</v>
+      </c>
+      <c r="H132" s="11" t="s">
+        <v>884</v>
+      </c>
+      <c r="I132" s="13" t="s">
+        <v>885</v>
       </c>
       <c r="J132" s="1">
         <f t="shared" si="37"/>
-        <v>5300</v>
+        <v>5700</v>
       </c>
       <c r="K132" s="1">
         <f t="shared" si="38"/>
-        <v>6700</v>
+        <v>7000</v>
       </c>
       <c r="L132" s="1">
-        <f t="shared" si="34"/>
-        <v>2050</v>
+        <f t="shared" si="39"/>
+        <v>2150</v>
       </c>
       <c r="M132" s="1">
-        <f t="shared" si="35"/>
-        <v>2050</v>
+        <f t="shared" si="40"/>
+        <v>2150</v>
       </c>
       <c r="N132" s="3">
-        <f t="shared" si="36"/>
-        <v>56</v>
-      </c>
-      <c r="O132" s="6">
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>58</v>
+      </c>
+      <c r="O132" s="3">
+        <f t="shared" si="42"/>
+        <v>38</v>
       </c>
       <c r="P132" s="3">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="Q132" s="11" t="s">
-        <v>831</v>
+        <v>886</v>
       </c>
       <c r="R132" s="11" t="s">
-        <v>831</v>
+        <v>886</v>
       </c>
       <c r="T132" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U132" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="133" customHeight="1" spans="1:21">
-      <c r="A133" s="3" t="s">
-        <v>874</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>874</v>
-      </c>
+    <row r="133" customHeight="1" spans="3:21">
       <c r="C133" s="1" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="E133" s="1">
         <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>884</v>
-      </c>
-      <c r="G133" s="4">
-        <v>1</v>
-      </c>
-      <c r="H133" s="4">
-        <v>1</v>
-      </c>
-      <c r="I133" s="4">
-        <v>1</v>
+        <v>889</v>
+      </c>
+      <c r="G133" s="12" t="s">
+        <v>890</v>
+      </c>
+      <c r="H133" s="11" t="s">
+        <v>890</v>
+      </c>
+      <c r="I133" s="13" t="s">
+        <v>891</v>
       </c>
       <c r="J133" s="1">
         <f t="shared" si="37"/>
-        <v>5500</v>
+        <v>6000</v>
       </c>
       <c r="K133" s="1">
         <f t="shared" si="38"/>
-        <v>7000</v>
+        <v>7400</v>
       </c>
       <c r="L133" s="1">
-        <f t="shared" si="34"/>
-        <v>2100</v>
+        <f t="shared" si="39"/>
+        <v>2250</v>
       </c>
       <c r="M133" s="1">
-        <f t="shared" si="35"/>
-        <v>2100</v>
+        <f t="shared" si="40"/>
+        <v>2250</v>
       </c>
       <c r="N133" s="3">
-        <f t="shared" si="36"/>
-        <v>57</v>
-      </c>
-      <c r="O133" s="6">
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>60</v>
+      </c>
+      <c r="O133" s="3">
+        <f t="shared" si="42"/>
+        <v>42</v>
       </c>
       <c r="P133" s="3">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="Q133" s="11" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="R133" s="11" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="T133" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U133" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="134" customHeight="1" spans="1:21">
-      <c r="A134" s="3" t="s">
-        <v>874</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>874</v>
-      </c>
+    <row r="134" customHeight="1" spans="3:21">
       <c r="C134" s="1" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
       <c r="E134" s="1">
         <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>888</v>
-      </c>
-      <c r="G134" s="4">
-        <v>1</v>
-      </c>
-      <c r="H134" s="4">
-        <v>1</v>
-      </c>
-      <c r="I134" s="4">
-        <v>1</v>
+        <v>895</v>
+      </c>
+      <c r="G134" s="12" t="s">
+        <v>896</v>
+      </c>
+      <c r="H134" s="11" t="s">
+        <v>896</v>
+      </c>
+      <c r="I134" s="13" t="s">
+        <v>897</v>
       </c>
       <c r="J134" s="1">
         <f t="shared" si="37"/>
-        <v>5700</v>
+        <v>6300</v>
       </c>
       <c r="K134" s="1">
         <f t="shared" si="38"/>
-        <v>7300</v>
+        <v>7800</v>
       </c>
       <c r="L134" s="1">
-        <f t="shared" si="34"/>
-        <v>2150</v>
+        <f t="shared" si="39"/>
+        <v>2350</v>
       </c>
       <c r="M134" s="1">
-        <f t="shared" si="35"/>
-        <v>2150</v>
+        <f t="shared" si="40"/>
+        <v>2350</v>
       </c>
       <c r="N134" s="3">
-        <f t="shared" si="36"/>
-        <v>58</v>
-      </c>
-      <c r="O134" s="6">
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>62</v>
+      </c>
+      <c r="O134" s="3">
+        <f t="shared" si="42"/>
+        <v>46</v>
       </c>
       <c r="P134" s="3">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="Q134" s="11" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="R134" s="11" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="T134" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U134" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="135" customHeight="1" spans="1:21">
-      <c r="A135" s="3" t="s">
-        <v>874</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>874</v>
-      </c>
+    <row r="135" customHeight="1" spans="3:21">
       <c r="C135" s="1" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>891</v>
+        <v>900</v>
       </c>
       <c r="E135" s="1">
         <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="G135" s="4">
-        <v>1</v>
-      </c>
-      <c r="H135" s="4">
-        <v>1</v>
-      </c>
-      <c r="I135" s="4">
-        <v>1</v>
+        <v>458</v>
+      </c>
+      <c r="G135" s="12" t="s">
+        <v>901</v>
+      </c>
+      <c r="H135" s="11" t="s">
+        <v>901</v>
+      </c>
+      <c r="I135" s="13" t="s">
+        <v>902</v>
       </c>
       <c r="J135" s="1">
         <f t="shared" si="37"/>
-        <v>5900</v>
+        <v>6600</v>
       </c>
       <c r="K135" s="1">
         <f t="shared" si="38"/>
-        <v>7600</v>
+        <v>8200</v>
       </c>
       <c r="L135" s="1">
-        <f t="shared" si="34"/>
-        <v>2200</v>
+        <f t="shared" si="39"/>
+        <v>2450</v>
       </c>
       <c r="M135" s="1">
-        <f t="shared" si="35"/>
-        <v>2200</v>
+        <f t="shared" si="40"/>
+        <v>2450</v>
       </c>
       <c r="N135" s="3">
-        <f t="shared" si="36"/>
-        <v>59</v>
-      </c>
-      <c r="O135" s="6">
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>64</v>
+      </c>
+      <c r="O135" s="3">
+        <f t="shared" si="42"/>
+        <v>50</v>
       </c>
       <c r="P135" s="3">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="Q135" s="11" t="s">
-        <v>892</v>
+        <v>453</v>
       </c>
       <c r="R135" s="11" t="s">
-        <v>892</v>
+        <v>453</v>
       </c>
       <c r="T135" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U135" s="1">
         <v>0</v>
@@ -12090,22 +12103,22 @@
     </row>
     <row r="136" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A136" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>893</v>
+        <v>904</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>894</v>
+        <v>905</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>895</v>
+        <v>906</v>
       </c>
       <c r="G136" s="4">
         <v>1</v>
@@ -12117,39 +12130,40 @@
         <v>1</v>
       </c>
       <c r="J136" s="1">
-        <f t="shared" si="37"/>
-        <v>6100</v>
+        <f t="shared" ref="J136:J140" si="43">J135+400</f>
+        <v>7000</v>
       </c>
       <c r="K136" s="1">
         <f t="shared" si="38"/>
-        <v>7900</v>
+        <v>8600</v>
       </c>
       <c r="L136" s="1">
-        <f t="shared" si="34"/>
-        <v>2250</v>
+        <f t="shared" ref="L136:L140" si="44">L135+150</f>
+        <v>2600</v>
       </c>
       <c r="M136" s="1">
-        <f t="shared" si="35"/>
-        <v>2250</v>
+        <f t="shared" ref="M136:M140" si="45">M135+150</f>
+        <v>2600</v>
       </c>
       <c r="N136" s="3">
-        <f t="shared" si="36"/>
-        <v>60</v>
-      </c>
-      <c r="O136" s="6">
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>66</v>
+      </c>
+      <c r="O136" s="3">
+        <f t="shared" si="42"/>
+        <v>54</v>
       </c>
       <c r="P136" s="3">
-        <v>90</v>
+        <v>99.2</v>
       </c>
       <c r="Q136" s="11" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="R136" s="11" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="T136" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U136" s="1">
         <v>0</v>
@@ -12159,22 +12173,22 @@
     </row>
     <row r="137" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A137" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>896</v>
+        <v>907</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>897</v>
+        <v>908</v>
       </c>
       <c r="E137" s="1">
         <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="G137" s="4">
         <v>1</v>
@@ -12186,39 +12200,40 @@
         <v>1</v>
       </c>
       <c r="J137" s="1">
-        <f t="shared" si="37"/>
-        <v>6300</v>
+        <f t="shared" si="43"/>
+        <v>7400</v>
       </c>
       <c r="K137" s="1">
         <f t="shared" si="38"/>
-        <v>8200</v>
+        <v>9000</v>
       </c>
       <c r="L137" s="1">
-        <f t="shared" si="34"/>
-        <v>2300</v>
+        <f t="shared" si="44"/>
+        <v>2750</v>
       </c>
       <c r="M137" s="1">
-        <f t="shared" si="35"/>
-        <v>2300</v>
+        <f t="shared" si="45"/>
+        <v>2750</v>
       </c>
       <c r="N137" s="3">
-        <f t="shared" si="36"/>
-        <v>61</v>
-      </c>
-      <c r="O137" s="6">
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>68</v>
+      </c>
+      <c r="O137" s="3">
+        <f t="shared" si="42"/>
+        <v>58</v>
       </c>
       <c r="P137" s="3">
-        <v>90</v>
+        <v>99.4</v>
       </c>
       <c r="Q137" s="11" t="s">
-        <v>899</v>
+        <v>910</v>
       </c>
       <c r="R137" s="11" t="s">
-        <v>899</v>
+        <v>910</v>
       </c>
       <c r="T137" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U137" s="1">
         <v>0</v>
@@ -12228,22 +12243,22 @@
     </row>
     <row r="138" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A138" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>900</v>
+        <v>911</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>901</v>
+        <v>912</v>
       </c>
       <c r="E138" s="1">
         <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="G138" s="4">
         <v>1</v>
@@ -12255,39 +12270,40 @@
         <v>1</v>
       </c>
       <c r="J138" s="1">
-        <f t="shared" si="37"/>
-        <v>6500</v>
+        <f t="shared" si="43"/>
+        <v>7800</v>
       </c>
       <c r="K138" s="1">
         <f t="shared" si="38"/>
-        <v>8500</v>
+        <v>9400</v>
       </c>
       <c r="L138" s="1">
-        <f t="shared" si="34"/>
-        <v>2350</v>
+        <f t="shared" si="44"/>
+        <v>2900</v>
       </c>
       <c r="M138" s="1">
-        <f t="shared" si="35"/>
-        <v>2350</v>
+        <f t="shared" si="45"/>
+        <v>2900</v>
       </c>
       <c r="N138" s="3">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
+        <v>70</v>
+      </c>
+      <c r="O138" s="3">
+        <f t="shared" si="42"/>
         <v>62</v>
       </c>
-      <c r="O138" s="6">
-        <v>0</v>
-      </c>
       <c r="P138" s="3">
-        <v>90</v>
+        <v>99.6</v>
       </c>
       <c r="Q138" s="11" t="s">
-        <v>903</v>
+        <v>914</v>
       </c>
       <c r="R138" s="11" t="s">
-        <v>903</v>
+        <v>914</v>
       </c>
       <c r="T138" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U138" s="1">
         <v>0</v>
@@ -12297,22 +12313,22 @@
     </row>
     <row r="139" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A139" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="E139" s="1">
         <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>906</v>
+        <v>917</v>
       </c>
       <c r="G139" s="4">
         <v>1</v>
@@ -12324,39 +12340,40 @@
         <v>1</v>
       </c>
       <c r="J139" s="1">
-        <f t="shared" si="37"/>
-        <v>6700</v>
+        <f t="shared" si="43"/>
+        <v>8200</v>
       </c>
       <c r="K139" s="1">
         <f t="shared" si="38"/>
-        <v>8800</v>
+        <v>9800</v>
       </c>
       <c r="L139" s="1">
-        <f t="shared" si="34"/>
-        <v>2400</v>
+        <f t="shared" si="44"/>
+        <v>3050</v>
       </c>
       <c r="M139" s="1">
-        <f t="shared" si="35"/>
-        <v>2400</v>
+        <f t="shared" si="45"/>
+        <v>3050</v>
       </c>
       <c r="N139" s="3">
-        <f t="shared" si="36"/>
-        <v>63</v>
-      </c>
-      <c r="O139" s="6">
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>72</v>
+      </c>
+      <c r="O139" s="3">
+        <f t="shared" si="42"/>
+        <v>66</v>
       </c>
       <c r="P139" s="3">
-        <v>90</v>
+        <v>99.8</v>
       </c>
       <c r="Q139" s="11" t="s">
-        <v>907</v>
+        <v>918</v>
       </c>
       <c r="R139" s="11" t="s">
-        <v>907</v>
+        <v>918</v>
       </c>
       <c r="T139" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U139" s="1">
         <v>0</v>
@@ -12366,22 +12383,22 @@
     </row>
     <row r="140" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A140" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>908</v>
+        <v>919</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>909</v>
+        <v>920</v>
       </c>
       <c r="E140" s="1">
         <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>910</v>
+        <v>921</v>
       </c>
       <c r="G140" s="4">
         <v>1</v>
@@ -12393,39 +12410,40 @@
         <v>1</v>
       </c>
       <c r="J140" s="1">
-        <f t="shared" si="37"/>
-        <v>6900</v>
+        <f t="shared" si="43"/>
+        <v>8600</v>
       </c>
       <c r="K140" s="1">
         <f t="shared" si="38"/>
-        <v>9100</v>
+        <v>10200</v>
       </c>
       <c r="L140" s="1">
-        <f t="shared" si="34"/>
-        <v>2450</v>
+        <f t="shared" si="44"/>
+        <v>3200</v>
       </c>
       <c r="M140" s="1">
-        <f t="shared" si="35"/>
-        <v>2450</v>
+        <f t="shared" si="45"/>
+        <v>3200</v>
       </c>
       <c r="N140" s="3">
-        <f t="shared" si="36"/>
-        <v>64</v>
-      </c>
-      <c r="O140" s="6">
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>74</v>
+      </c>
+      <c r="O140" s="3">
+        <f t="shared" si="42"/>
+        <v>70</v>
       </c>
       <c r="P140" s="3">
-        <v>90</v>
+        <v>99.9</v>
       </c>
       <c r="Q140" s="11" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="R140" s="11" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="T140" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U140" s="1">
         <v>0</v>
@@ -12435,22 +12453,22 @@
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A141" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>911</v>
+        <v>922</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>912</v>
+        <v>923</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>913</v>
+        <v>924</v>
       </c>
       <c r="G141" s="4">
         <v>1</v>
@@ -12462,39 +12480,40 @@
         <v>1</v>
       </c>
       <c r="J141" s="1">
-        <f t="shared" si="37"/>
-        <v>7100</v>
+        <f t="shared" ref="J141:J145" si="46">J140+500</f>
+        <v>9100</v>
       </c>
       <c r="K141" s="1">
-        <f t="shared" si="38"/>
-        <v>9400</v>
+        <f t="shared" ref="K141:K145" si="47">K140+500</f>
+        <v>10700</v>
       </c>
       <c r="L141" s="1">
-        <f t="shared" si="34"/>
-        <v>2500</v>
+        <f t="shared" ref="L141:L145" si="48">L140+200</f>
+        <v>3400</v>
       </c>
       <c r="M141" s="1">
-        <f t="shared" si="35"/>
-        <v>2500</v>
+        <f t="shared" ref="M141:M145" si="49">M140+200</f>
+        <v>3400</v>
       </c>
       <c r="N141" s="3">
-        <f t="shared" si="36"/>
-        <v>65</v>
-      </c>
-      <c r="O141" s="6">
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>76</v>
+      </c>
+      <c r="O141" s="3">
+        <f t="shared" si="42"/>
+        <v>74</v>
       </c>
       <c r="P141" s="3">
-        <v>90</v>
+        <v>99.92</v>
       </c>
       <c r="Q141" s="11" t="s">
-        <v>914</v>
+        <v>925</v>
       </c>
       <c r="R141" s="11" t="s">
-        <v>914</v>
+        <v>925</v>
       </c>
       <c r="T141" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U141" s="1">
         <v>0</v>
@@ -12504,22 +12523,22 @@
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A142" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>915</v>
+        <v>926</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>916</v>
+        <v>927</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>917</v>
+        <v>928</v>
       </c>
       <c r="G142" s="4">
         <v>1</v>
@@ -12531,39 +12550,40 @@
         <v>1</v>
       </c>
       <c r="J142" s="1">
-        <f t="shared" si="37"/>
-        <v>7300</v>
+        <f t="shared" si="46"/>
+        <v>9600</v>
       </c>
       <c r="K142" s="1">
-        <f t="shared" si="38"/>
-        <v>9700</v>
+        <f t="shared" si="47"/>
+        <v>11200</v>
       </c>
       <c r="L142" s="1">
-        <f t="shared" si="34"/>
-        <v>2550</v>
+        <f t="shared" si="48"/>
+        <v>3600</v>
       </c>
       <c r="M142" s="1">
-        <f t="shared" si="35"/>
-        <v>2550</v>
+        <f t="shared" si="49"/>
+        <v>3600</v>
       </c>
       <c r="N142" s="3">
-        <f t="shared" si="36"/>
-        <v>66</v>
-      </c>
-      <c r="O142" s="6">
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>78</v>
+      </c>
+      <c r="O142" s="3">
+        <f t="shared" si="42"/>
+        <v>78</v>
       </c>
       <c r="P142" s="3">
-        <v>90</v>
+        <v>99.94</v>
       </c>
       <c r="Q142" s="11" t="s">
-        <v>918</v>
+        <v>929</v>
       </c>
       <c r="R142" s="11" t="s">
-        <v>918</v>
+        <v>929</v>
       </c>
       <c r="T142" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U142" s="1">
         <v>0</v>
@@ -12573,22 +12593,22 @@
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A143" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>919</v>
+        <v>930</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>920</v>
+        <v>931</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>921</v>
+        <v>932</v>
       </c>
       <c r="G143" s="4">
         <v>1</v>
@@ -12600,39 +12620,40 @@
         <v>1</v>
       </c>
       <c r="J143" s="1">
-        <f t="shared" si="37"/>
-        <v>7500</v>
+        <f t="shared" si="46"/>
+        <v>10100</v>
       </c>
       <c r="K143" s="1">
-        <f t="shared" si="38"/>
-        <v>10000</v>
+        <f t="shared" si="47"/>
+        <v>11700</v>
       </c>
       <c r="L143" s="1">
-        <f t="shared" si="34"/>
-        <v>2600</v>
+        <f t="shared" si="48"/>
+        <v>3800</v>
       </c>
       <c r="M143" s="1">
-        <f t="shared" si="35"/>
-        <v>2600</v>
+        <f t="shared" si="49"/>
+        <v>3800</v>
       </c>
       <c r="N143" s="3">
-        <f t="shared" si="36"/>
-        <v>67</v>
-      </c>
-      <c r="O143" s="6">
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>80</v>
+      </c>
+      <c r="O143" s="3">
+        <f t="shared" si="42"/>
+        <v>82</v>
       </c>
       <c r="P143" s="3">
-        <v>90</v>
+        <v>99.96</v>
       </c>
       <c r="Q143" s="11" t="s">
-        <v>922</v>
+        <v>933</v>
       </c>
       <c r="R143" s="11" t="s">
-        <v>922</v>
+        <v>933</v>
       </c>
       <c r="T143" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U143" s="1">
         <v>0</v>
@@ -12642,22 +12663,22 @@
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A144" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>923</v>
+        <v>934</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>924</v>
+        <v>935</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>925</v>
+        <v>936</v>
       </c>
       <c r="G144" s="4">
         <v>1</v>
@@ -12669,39 +12690,40 @@
         <v>1</v>
       </c>
       <c r="J144" s="1">
-        <f t="shared" si="37"/>
-        <v>7700</v>
+        <f t="shared" si="46"/>
+        <v>10600</v>
       </c>
       <c r="K144" s="1">
-        <f t="shared" si="38"/>
-        <v>10300</v>
+        <f t="shared" si="47"/>
+        <v>12200</v>
       </c>
       <c r="L144" s="1">
-        <f t="shared" si="34"/>
-        <v>2650</v>
+        <f t="shared" si="48"/>
+        <v>4000</v>
       </c>
       <c r="M144" s="1">
-        <f t="shared" si="35"/>
-        <v>2650</v>
+        <f t="shared" si="49"/>
+        <v>4000</v>
       </c>
       <c r="N144" s="3">
-        <f t="shared" si="36"/>
-        <v>68</v>
-      </c>
-      <c r="O144" s="6">
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>82</v>
+      </c>
+      <c r="O144" s="3">
+        <f t="shared" si="42"/>
+        <v>86</v>
       </c>
       <c r="P144" s="3">
-        <v>90</v>
+        <v>99.98</v>
       </c>
       <c r="Q144" s="11" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="R144" s="11" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="T144" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U144" s="1">
         <v>0</v>
@@ -12711,22 +12733,22 @@
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A145" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>926</v>
+        <v>937</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>927</v>
+        <v>938</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>928</v>
+        <v>939</v>
       </c>
       <c r="G145" s="4">
         <v>1</v>
@@ -12738,39 +12760,40 @@
         <v>1</v>
       </c>
       <c r="J145" s="1">
-        <f t="shared" si="37"/>
-        <v>7900</v>
+        <f t="shared" si="46"/>
+        <v>11100</v>
       </c>
       <c r="K145" s="1">
-        <f t="shared" si="38"/>
-        <v>10600</v>
+        <f t="shared" si="47"/>
+        <v>12700</v>
       </c>
       <c r="L145" s="1">
-        <f t="shared" si="34"/>
-        <v>2700</v>
+        <f t="shared" si="48"/>
+        <v>4200</v>
       </c>
       <c r="M145" s="1">
-        <f t="shared" si="35"/>
-        <v>2700</v>
+        <f t="shared" si="49"/>
+        <v>4200</v>
       </c>
       <c r="N145" s="3">
-        <f t="shared" si="36"/>
-        <v>69</v>
-      </c>
-      <c r="O145" s="6">
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>84</v>
+      </c>
+      <c r="O145" s="3">
+        <f t="shared" si="42"/>
+        <v>90</v>
       </c>
       <c r="P145" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="Q145" s="11" t="s">
-        <v>929</v>
+        <v>940</v>
       </c>
       <c r="R145" s="11" t="s">
-        <v>929</v>
+        <v>940</v>
       </c>
       <c r="T145" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U145" s="1">
         <v>0</v>
@@ -12780,7 +12803,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:P5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:O5 P5 C3:P4" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="941">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="953">
   <si>
     <t>ID</t>
   </si>
@@ -2794,61 +2794,97 @@
     <t>1600000000000000000000000000000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
+    <t>10130</t>
+  </si>
+  <si>
+    <t>1130</t>
+  </si>
+  <si>
+    <t>地狱烈焰王</t>
+  </si>
+  <si>
+    <t>90000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>32000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>1100000000000</t>
+  </si>
+  <si>
+    <t>10131</t>
+  </si>
+  <si>
+    <t>1131</t>
+  </si>
+  <si>
+    <t>地狱大邪王</t>
+  </si>
+  <si>
+    <t>900000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>640000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>1200000000000</t>
+  </si>
+  <si>
+    <t>10132</t>
+  </si>
+  <si>
+    <t>1132</t>
+  </si>
+  <si>
+    <t>地狱尸魔王</t>
+  </si>
+  <si>
+    <t>9000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>12800000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>1300000000000</t>
+  </si>
+  <si>
+    <t>10133</t>
+  </si>
+  <si>
+    <t>1133</t>
+  </si>
+  <si>
+    <t>地狱骨魔王</t>
+  </si>
+  <si>
+    <t>90000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>512000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>1400000000000</t>
+  </si>
+  <si>
+    <t>10134</t>
+  </si>
+  <si>
+    <t>1134</t>
+  </si>
+  <si>
+    <t>地狱牛魔王</t>
+  </si>
+  <si>
+    <t>900000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>10000000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>1500000000000</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>10130</t>
-  </si>
-  <si>
-    <t>1130</t>
-  </si>
-  <si>
-    <t>地狱烈焰王</t>
-  </si>
-  <si>
-    <t>10131</t>
-  </si>
-  <si>
-    <t>1131</t>
-  </si>
-  <si>
-    <t>地狱大邪王</t>
-  </si>
-  <si>
-    <t>570000000000</t>
-  </si>
-  <si>
-    <t>10132</t>
-  </si>
-  <si>
-    <t>1132</t>
-  </si>
-  <si>
-    <t>地狱尸魔王</t>
-  </si>
-  <si>
-    <t>580000000000</t>
-  </si>
-  <si>
-    <t>10133</t>
-  </si>
-  <si>
-    <t>1133</t>
-  </si>
-  <si>
-    <t>地狱骨魔王</t>
-  </si>
-  <si>
-    <t>590000000000</t>
-  </si>
-  <si>
-    <t>10134</t>
-  </si>
-  <si>
-    <t>1134</t>
-  </si>
-  <si>
-    <t>地狱牛魔王</t>
   </si>
   <si>
     <t>10135</t>
@@ -3898,9 +3934,9 @@
     <col min="4" max="4" width="7.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="6.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="48.5" style="3" customWidth="1"/>
+    <col min="7" max="7" width="50.25" style="3" customWidth="1"/>
     <col min="8" max="8" width="52.1666666666667" style="3" customWidth="1"/>
-    <col min="9" max="9" width="61.8333333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="67.75" style="3" customWidth="1"/>
     <col min="10" max="10" width="15.875" style="3" customWidth="1"/>
     <col min="11" max="13" width="12.125" style="3" customWidth="1"/>
     <col min="14" max="14" width="9.625" style="3" customWidth="1"/>
@@ -4128,7 +4164,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="11.5" spans="3:21">
+    <row r="6" s="1" customFormat="1" ht="12" spans="3:21">
       <c r="C6" s="1" t="s">
         <v>35</v>
       </c>
@@ -10841,11 +10877,11 @@
         <v>790</v>
       </c>
       <c r="J116" s="1">
-        <f>J115+200</f>
+        <f t="shared" ref="J116:J129" si="37">J115+200</f>
         <v>2100</v>
       </c>
       <c r="K116" s="1">
-        <f>K115+300</f>
+        <f t="shared" ref="K116:K129" si="38">K115+300</f>
         <v>1900</v>
       </c>
       <c r="L116" s="1">
@@ -10906,11 +10942,11 @@
         <v>796</v>
       </c>
       <c r="J117" s="1">
-        <f>J116+200</f>
+        <f t="shared" si="37"/>
         <v>2300</v>
       </c>
       <c r="K117" s="1">
-        <f>K116+300</f>
+        <f t="shared" si="38"/>
         <v>2200</v>
       </c>
       <c r="L117" s="1">
@@ -10971,11 +11007,11 @@
         <v>802</v>
       </c>
       <c r="J118" s="1">
-        <f>J117+200</f>
+        <f t="shared" si="37"/>
         <v>2500</v>
       </c>
       <c r="K118" s="1">
-        <f>K117+300</f>
+        <f t="shared" si="38"/>
         <v>2500</v>
       </c>
       <c r="L118" s="1">
@@ -11036,11 +11072,11 @@
         <v>808</v>
       </c>
       <c r="J119" s="1">
-        <f>J118+200</f>
+        <f t="shared" si="37"/>
         <v>2700</v>
       </c>
       <c r="K119" s="1">
-        <f>K118+300</f>
+        <f t="shared" si="38"/>
         <v>2800</v>
       </c>
       <c r="L119" s="1">
@@ -11101,11 +11137,11 @@
         <v>814</v>
       </c>
       <c r="J120" s="1">
-        <f>J119+200</f>
+        <f t="shared" si="37"/>
         <v>2900</v>
       </c>
       <c r="K120" s="1">
-        <f>K119+300</f>
+        <f t="shared" si="38"/>
         <v>3100</v>
       </c>
       <c r="L120" s="1">
@@ -11164,11 +11200,11 @@
         <v>819</v>
       </c>
       <c r="J121" s="1">
-        <f>J120+200</f>
+        <f t="shared" si="37"/>
         <v>3100</v>
       </c>
       <c r="K121" s="1">
-        <f>K120+300</f>
+        <f t="shared" si="38"/>
         <v>3400</v>
       </c>
       <c r="L121" s="1">
@@ -11184,7 +11220,7 @@
         <v>45</v>
       </c>
       <c r="O121" s="3">
-        <f>O120+3</f>
+        <f t="shared" ref="O121:O130" si="39">O120+3</f>
         <v>3</v>
       </c>
       <c r="P121" s="3">
@@ -11228,11 +11264,11 @@
         <v>825</v>
       </c>
       <c r="J122" s="1">
-        <f>J121+200</f>
+        <f t="shared" si="37"/>
         <v>3300</v>
       </c>
       <c r="K122" s="1">
-        <f>K121+300</f>
+        <f t="shared" si="38"/>
         <v>3700</v>
       </c>
       <c r="L122" s="1">
@@ -11248,7 +11284,7 @@
         <v>46</v>
       </c>
       <c r="O122" s="3">
-        <f>O121+3</f>
+        <f t="shared" si="39"/>
         <v>6</v>
       </c>
       <c r="P122" s="3">
@@ -11292,11 +11328,11 @@
         <v>831</v>
       </c>
       <c r="J123" s="1">
-        <f>J122+200</f>
+        <f t="shared" si="37"/>
         <v>3500</v>
       </c>
       <c r="K123" s="1">
-        <f>K122+300</f>
+        <f t="shared" si="38"/>
         <v>4000</v>
       </c>
       <c r="L123" s="1">
@@ -11312,7 +11348,7 @@
         <v>47</v>
       </c>
       <c r="O123" s="3">
-        <f>O122+3</f>
+        <f t="shared" si="39"/>
         <v>9</v>
       </c>
       <c r="P123" s="3">
@@ -11356,11 +11392,11 @@
         <v>837</v>
       </c>
       <c r="J124" s="1">
-        <f>J123+200</f>
+        <f t="shared" si="37"/>
         <v>3700</v>
       </c>
       <c r="K124" s="1">
-        <f>K123+300</f>
+        <f t="shared" si="38"/>
         <v>4300</v>
       </c>
       <c r="L124" s="1">
@@ -11376,7 +11412,7 @@
         <v>48</v>
       </c>
       <c r="O124" s="3">
-        <f>O123+3</f>
+        <f t="shared" si="39"/>
         <v>12</v>
       </c>
       <c r="P124" s="3">
@@ -11420,11 +11456,11 @@
         <v>843</v>
       </c>
       <c r="J125" s="1">
-        <f>J124+200</f>
+        <f t="shared" si="37"/>
         <v>3900</v>
       </c>
       <c r="K125" s="1">
-        <f>K124+300</f>
+        <f t="shared" si="38"/>
         <v>4600</v>
       </c>
       <c r="L125" s="1">
@@ -11440,7 +11476,7 @@
         <v>49</v>
       </c>
       <c r="O125" s="3">
-        <f>O124+3</f>
+        <f t="shared" si="39"/>
         <v>15</v>
       </c>
       <c r="P125" s="3">
@@ -11486,11 +11522,11 @@
         <v>849</v>
       </c>
       <c r="J126" s="1">
-        <f>J125+200</f>
+        <f t="shared" si="37"/>
         <v>4100</v>
       </c>
       <c r="K126" s="1">
-        <f>K125+300</f>
+        <f t="shared" si="38"/>
         <v>4900</v>
       </c>
       <c r="L126" s="1">
@@ -11506,7 +11542,7 @@
         <v>50</v>
       </c>
       <c r="O126" s="3">
-        <f>O125+3</f>
+        <f t="shared" si="39"/>
         <v>18</v>
       </c>
       <c r="P126" s="3">
@@ -11552,11 +11588,11 @@
         <v>855</v>
       </c>
       <c r="J127" s="1">
-        <f>J126+200</f>
+        <f t="shared" si="37"/>
         <v>4300</v>
       </c>
       <c r="K127" s="1">
-        <f>K126+300</f>
+        <f t="shared" si="38"/>
         <v>5200</v>
       </c>
       <c r="L127" s="1">
@@ -11572,7 +11608,7 @@
         <v>51</v>
       </c>
       <c r="O127" s="3">
-        <f>O126+3</f>
+        <f t="shared" si="39"/>
         <v>21</v>
       </c>
       <c r="P127" s="3">
@@ -11618,11 +11654,11 @@
         <v>861</v>
       </c>
       <c r="J128" s="1">
-        <f>J127+200</f>
+        <f t="shared" si="37"/>
         <v>4500</v>
       </c>
       <c r="K128" s="1">
-        <f>K127+300</f>
+        <f t="shared" si="38"/>
         <v>5500</v>
       </c>
       <c r="L128" s="1">
@@ -11638,7 +11674,7 @@
         <v>52</v>
       </c>
       <c r="O128" s="3">
-        <f>O127+3</f>
+        <f t="shared" si="39"/>
         <v>24</v>
       </c>
       <c r="P128" s="3">
@@ -11684,11 +11720,11 @@
         <v>867</v>
       </c>
       <c r="J129" s="1">
-        <f>J128+200</f>
+        <f t="shared" si="37"/>
         <v>4700</v>
       </c>
       <c r="K129" s="1">
-        <f>K128+300</f>
+        <f t="shared" si="38"/>
         <v>5800</v>
       </c>
       <c r="L129" s="1">
@@ -11704,7 +11740,7 @@
         <v>53</v>
       </c>
       <c r="O129" s="3">
-        <f>O128+3</f>
+        <f t="shared" si="39"/>
         <v>27</v>
       </c>
       <c r="P129" s="3">
@@ -11750,11 +11786,11 @@
         <v>873</v>
       </c>
       <c r="J130" s="1">
-        <f t="shared" ref="J130:J135" si="37">J129+300</f>
+        <f t="shared" ref="J130:J135" si="40">J129+300</f>
         <v>5000</v>
       </c>
       <c r="K130" s="1">
-        <f t="shared" ref="K130:K140" si="38">K129+400</f>
+        <f t="shared" ref="K130:K140" si="41">K129+400</f>
         <v>6200</v>
       </c>
       <c r="L130" s="1">
@@ -11770,7 +11806,7 @@
         <v>54</v>
       </c>
       <c r="O130" s="3">
-        <f>O129+3</f>
+        <f t="shared" si="39"/>
         <v>30</v>
       </c>
       <c r="P130" s="3">
@@ -11818,23 +11854,23 @@
         <v>5400</v>
       </c>
       <c r="K131" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>6600</v>
       </c>
       <c r="L131" s="1">
-        <f t="shared" ref="L131:L135" si="39">L130+100</f>
+        <f t="shared" ref="L131:L135" si="42">L130+100</f>
         <v>2050</v>
       </c>
       <c r="M131" s="1">
-        <f t="shared" ref="M131:M135" si="40">M130+100</f>
+        <f t="shared" ref="M131:M135" si="43">M130+100</f>
         <v>2050</v>
       </c>
       <c r="N131" s="3">
-        <f t="shared" ref="N131:N145" si="41">N130+2</f>
+        <f t="shared" ref="N131:N145" si="44">N130+2</f>
         <v>56</v>
       </c>
       <c r="O131" s="3">
-        <f t="shared" ref="O131:O145" si="42">O130+4</f>
+        <f t="shared" ref="O131:O145" si="45">O130+4</f>
         <v>34</v>
       </c>
       <c r="P131" s="3">
@@ -11876,27 +11912,27 @@
         <v>885</v>
       </c>
       <c r="J132" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>5700</v>
       </c>
       <c r="K132" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>7000</v>
       </c>
       <c r="L132" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>2150</v>
       </c>
       <c r="M132" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>2150</v>
       </c>
       <c r="N132" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>58</v>
       </c>
       <c r="O132" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>38</v>
       </c>
       <c r="P132" s="3">
@@ -11938,27 +11974,27 @@
         <v>891</v>
       </c>
       <c r="J133" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>6000</v>
       </c>
       <c r="K133" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>7400</v>
       </c>
       <c r="L133" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>2250</v>
       </c>
       <c r="M133" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>2250</v>
       </c>
       <c r="N133" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>60</v>
       </c>
       <c r="O133" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>42</v>
       </c>
       <c r="P133" s="3">
@@ -12000,27 +12036,27 @@
         <v>897</v>
       </c>
       <c r="J134" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>6300</v>
       </c>
       <c r="K134" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>7800</v>
       </c>
       <c r="L134" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>2350</v>
       </c>
       <c r="M134" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>2350</v>
       </c>
       <c r="N134" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>62</v>
       </c>
       <c r="O134" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>46</v>
       </c>
       <c r="P134" s="3">
@@ -12062,27 +12098,27 @@
         <v>902</v>
       </c>
       <c r="J135" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>6600</v>
       </c>
       <c r="K135" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>8200</v>
       </c>
       <c r="L135" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>2450</v>
       </c>
       <c r="M135" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>2450</v>
       </c>
       <c r="N135" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>64</v>
       </c>
       <c r="O135" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>50</v>
       </c>
       <c r="P135" s="3">
@@ -12102,65 +12138,61 @@
       </c>
     </row>
     <row r="136" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A136" s="3" t="s">
+      <c r="A136" s="3"/>
+      <c r="B136" s="3"/>
+      <c r="C136" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="B136" s="3" t="s">
-        <v>903</v>
-      </c>
-      <c r="C136" s="1" t="s">
+      <c r="D136" s="1" t="s">
         <v>904</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>905</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="G136" s="12" t="s">
         <v>906</v>
       </c>
-      <c r="G136" s="4">
-        <v>1</v>
-      </c>
-      <c r="H136" s="4">
-        <v>1</v>
-      </c>
-      <c r="I136" s="4">
-        <v>1</v>
+      <c r="H136" s="11" t="s">
+        <v>906</v>
+      </c>
+      <c r="I136" s="13" t="s">
+        <v>907</v>
       </c>
       <c r="J136" s="1">
-        <f t="shared" ref="J136:J140" si="43">J135+400</f>
-        <v>7000</v>
+        <f t="shared" ref="J136:J145" si="46">J135+500</f>
+        <v>7100</v>
       </c>
       <c r="K136" s="1">
-        <f t="shared" si="38"/>
-        <v>8600</v>
+        <f t="shared" ref="K136:K145" si="47">K135+500</f>
+        <v>8700</v>
       </c>
       <c r="L136" s="1">
-        <f t="shared" ref="L136:L140" si="44">L135+150</f>
-        <v>2600</v>
+        <f t="shared" ref="L136:L145" si="48">L135+200</f>
+        <v>2650</v>
       </c>
       <c r="M136" s="1">
-        <f t="shared" ref="M136:M140" si="45">M135+150</f>
-        <v>2600</v>
+        <f t="shared" ref="M136:M145" si="49">M135+200</f>
+        <v>2650</v>
       </c>
       <c r="N136" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>66</v>
       </c>
       <c r="O136" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>54</v>
       </c>
       <c r="P136" s="3">
         <v>99.2</v>
       </c>
       <c r="Q136" s="11" t="s">
-        <v>838</v>
+        <v>908</v>
       </c>
       <c r="R136" s="11" t="s">
-        <v>838</v>
+        <v>908</v>
       </c>
       <c r="T136" s="1" t="s">
         <v>154</v>
@@ -12172,65 +12204,61 @@
       <c r="W136" s="3"/>
     </row>
     <row r="137" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A137" s="3" t="s">
-        <v>903</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>903</v>
-      </c>
+      <c r="A137" s="3"/>
+      <c r="B137" s="3"/>
       <c r="C137" s="1" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="E137" s="1">
         <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="G137" s="4">
-        <v>1</v>
-      </c>
-      <c r="H137" s="4">
-        <v>1</v>
-      </c>
-      <c r="I137" s="4">
-        <v>1</v>
+        <v>911</v>
+      </c>
+      <c r="G137" s="12" t="s">
+        <v>912</v>
+      </c>
+      <c r="H137" s="11" t="s">
+        <v>912</v>
+      </c>
+      <c r="I137" s="13" t="s">
+        <v>913</v>
       </c>
       <c r="J137" s="1">
-        <f t="shared" si="43"/>
-        <v>7400</v>
+        <f t="shared" si="46"/>
+        <v>7600</v>
       </c>
       <c r="K137" s="1">
-        <f t="shared" si="38"/>
-        <v>9000</v>
+        <f t="shared" si="47"/>
+        <v>9200</v>
       </c>
       <c r="L137" s="1">
+        <f t="shared" si="48"/>
+        <v>2850</v>
+      </c>
+      <c r="M137" s="1">
+        <f t="shared" si="49"/>
+        <v>2850</v>
+      </c>
+      <c r="N137" s="3">
         <f t="shared" si="44"/>
-        <v>2750</v>
-      </c>
-      <c r="M137" s="1">
+        <v>68</v>
+      </c>
+      <c r="O137" s="3">
         <f t="shared" si="45"/>
-        <v>2750</v>
-      </c>
-      <c r="N137" s="3">
-        <f t="shared" si="41"/>
-        <v>68</v>
-      </c>
-      <c r="O137" s="3">
-        <f t="shared" si="42"/>
         <v>58</v>
       </c>
       <c r="P137" s="3">
         <v>99.4</v>
       </c>
       <c r="Q137" s="11" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="R137" s="11" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="T137" s="1" t="s">
         <v>154</v>
@@ -12242,65 +12270,61 @@
       <c r="W137" s="3"/>
     </row>
     <row r="138" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A138" s="3" t="s">
-        <v>903</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>903</v>
-      </c>
+      <c r="A138" s="3"/>
+      <c r="B138" s="3"/>
       <c r="C138" s="1" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="E138" s="1">
         <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="G138" s="4">
-        <v>1</v>
-      </c>
-      <c r="H138" s="4">
-        <v>1</v>
-      </c>
-      <c r="I138" s="4">
-        <v>1</v>
+        <v>917</v>
+      </c>
+      <c r="G138" s="12" t="s">
+        <v>918</v>
+      </c>
+      <c r="H138" s="11" t="s">
+        <v>918</v>
+      </c>
+      <c r="I138" s="13" t="s">
+        <v>919</v>
       </c>
       <c r="J138" s="1">
-        <f t="shared" si="43"/>
-        <v>7800</v>
+        <f t="shared" si="46"/>
+        <v>8100</v>
       </c>
       <c r="K138" s="1">
-        <f t="shared" si="38"/>
-        <v>9400</v>
+        <f t="shared" si="47"/>
+        <v>9700</v>
       </c>
       <c r="L138" s="1">
+        <f t="shared" si="48"/>
+        <v>3050</v>
+      </c>
+      <c r="M138" s="1">
+        <f t="shared" si="49"/>
+        <v>3050</v>
+      </c>
+      <c r="N138" s="3">
         <f t="shared" si="44"/>
-        <v>2900</v>
-      </c>
-      <c r="M138" s="1">
+        <v>70</v>
+      </c>
+      <c r="O138" s="3">
         <f t="shared" si="45"/>
-        <v>2900</v>
-      </c>
-      <c r="N138" s="3">
-        <f t="shared" si="41"/>
-        <v>70</v>
-      </c>
-      <c r="O138" s="3">
-        <f t="shared" si="42"/>
         <v>62</v>
       </c>
       <c r="P138" s="3">
         <v>99.6</v>
       </c>
       <c r="Q138" s="11" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="R138" s="11" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="T138" s="1" t="s">
         <v>154</v>
@@ -12312,65 +12336,61 @@
       <c r="W138" s="3"/>
     </row>
     <row r="139" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A139" s="3" t="s">
-        <v>903</v>
-      </c>
-      <c r="B139" s="3" t="s">
-        <v>903</v>
-      </c>
+      <c r="A139" s="3"/>
+      <c r="B139" s="3"/>
       <c r="C139" s="1" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="E139" s="1">
         <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>917</v>
-      </c>
-      <c r="G139" s="4">
-        <v>1</v>
-      </c>
-      <c r="H139" s="4">
-        <v>1</v>
-      </c>
-      <c r="I139" s="4">
-        <v>1</v>
+        <v>923</v>
+      </c>
+      <c r="G139" s="12" t="s">
+        <v>924</v>
+      </c>
+      <c r="H139" s="11" t="s">
+        <v>924</v>
+      </c>
+      <c r="I139" s="13" t="s">
+        <v>925</v>
       </c>
       <c r="J139" s="1">
-        <f t="shared" si="43"/>
-        <v>8200</v>
+        <f t="shared" si="46"/>
+        <v>8600</v>
       </c>
       <c r="K139" s="1">
-        <f t="shared" si="38"/>
-        <v>9800</v>
+        <f t="shared" si="47"/>
+        <v>10200</v>
       </c>
       <c r="L139" s="1">
+        <f t="shared" si="48"/>
+        <v>3250</v>
+      </c>
+      <c r="M139" s="1">
+        <f t="shared" si="49"/>
+        <v>3250</v>
+      </c>
+      <c r="N139" s="3">
         <f t="shared" si="44"/>
-        <v>3050</v>
-      </c>
-      <c r="M139" s="1">
+        <v>72</v>
+      </c>
+      <c r="O139" s="3">
         <f t="shared" si="45"/>
-        <v>3050</v>
-      </c>
-      <c r="N139" s="3">
-        <f t="shared" si="41"/>
-        <v>72</v>
-      </c>
-      <c r="O139" s="3">
-        <f t="shared" si="42"/>
         <v>66</v>
       </c>
       <c r="P139" s="3">
         <v>99.8</v>
       </c>
       <c r="Q139" s="11" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="R139" s="11" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="T139" s="1" t="s">
         <v>154</v>
@@ -12382,65 +12402,61 @@
       <c r="W139" s="3"/>
     </row>
     <row r="140" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A140" s="3" t="s">
-        <v>903</v>
-      </c>
-      <c r="B140" s="3" t="s">
-        <v>903</v>
-      </c>
+      <c r="A140" s="3"/>
+      <c r="B140" s="3"/>
       <c r="C140" s="1" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
       <c r="E140" s="1">
         <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>921</v>
-      </c>
-      <c r="G140" s="4">
-        <v>1</v>
-      </c>
-      <c r="H140" s="4">
-        <v>1</v>
-      </c>
-      <c r="I140" s="4">
-        <v>1</v>
+        <v>929</v>
+      </c>
+      <c r="G140" s="12" t="s">
+        <v>930</v>
+      </c>
+      <c r="H140" s="11" t="s">
+        <v>930</v>
+      </c>
+      <c r="I140" s="13" t="s">
+        <v>931</v>
       </c>
       <c r="J140" s="1">
-        <f t="shared" si="43"/>
-        <v>8600</v>
+        <f t="shared" si="46"/>
+        <v>9100</v>
       </c>
       <c r="K140" s="1">
-        <f t="shared" si="38"/>
-        <v>10200</v>
+        <f t="shared" si="47"/>
+        <v>10700</v>
       </c>
       <c r="L140" s="1">
+        <f t="shared" si="48"/>
+        <v>3450</v>
+      </c>
+      <c r="M140" s="1">
+        <f t="shared" si="49"/>
+        <v>3450</v>
+      </c>
+      <c r="N140" s="3">
         <f t="shared" si="44"/>
-        <v>3200</v>
-      </c>
-      <c r="M140" s="1">
+        <v>74</v>
+      </c>
+      <c r="O140" s="3">
         <f t="shared" si="45"/>
-        <v>3200</v>
-      </c>
-      <c r="N140" s="3">
-        <f t="shared" si="41"/>
-        <v>74</v>
-      </c>
-      <c r="O140" s="3">
-        <f t="shared" si="42"/>
         <v>70</v>
       </c>
       <c r="P140" s="3">
         <v>99.9</v>
       </c>
       <c r="Q140" s="11" t="s">
-        <v>844</v>
+        <v>932</v>
       </c>
       <c r="R140" s="11" t="s">
-        <v>844</v>
+        <v>932</v>
       </c>
       <c r="T140" s="1" t="s">
         <v>154</v>
@@ -12453,22 +12469,22 @@
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A141" s="3" t="s">
-        <v>903</v>
+        <v>933</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>903</v>
+        <v>933</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>922</v>
+        <v>934</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>923</v>
+        <v>935</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>924</v>
+        <v>936</v>
       </c>
       <c r="G141" s="4">
         <v>1</v>
@@ -12480,37 +12496,37 @@
         <v>1</v>
       </c>
       <c r="J141" s="1">
-        <f t="shared" ref="J141:J145" si="46">J140+500</f>
-        <v>9100</v>
+        <f t="shared" ref="J141:J145" si="50">J140+600</f>
+        <v>9700</v>
       </c>
       <c r="K141" s="1">
-        <f t="shared" ref="K141:K145" si="47">K140+500</f>
-        <v>10700</v>
+        <f t="shared" ref="K141:K145" si="51">K140+600</f>
+        <v>11300</v>
       </c>
       <c r="L141" s="1">
-        <f t="shared" ref="L141:L145" si="48">L140+200</f>
-        <v>3400</v>
+        <f t="shared" ref="L141:L145" si="52">L140+250</f>
+        <v>3700</v>
       </c>
       <c r="M141" s="1">
-        <f t="shared" ref="M141:M145" si="49">M140+200</f>
-        <v>3400</v>
+        <f t="shared" ref="M141:M145" si="53">M140+250</f>
+        <v>3700</v>
       </c>
       <c r="N141" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>76</v>
       </c>
       <c r="O141" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>74</v>
       </c>
       <c r="P141" s="3">
         <v>99.92</v>
       </c>
       <c r="Q141" s="11" t="s">
-        <v>925</v>
+        <v>937</v>
       </c>
       <c r="R141" s="11" t="s">
-        <v>925</v>
+        <v>937</v>
       </c>
       <c r="T141" s="1" t="s">
         <v>154</v>
@@ -12523,22 +12539,22 @@
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A142" s="3" t="s">
-        <v>903</v>
+        <v>933</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>903</v>
+        <v>933</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>927</v>
+        <v>939</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>928</v>
+        <v>940</v>
       </c>
       <c r="G142" s="4">
         <v>1</v>
@@ -12550,37 +12566,37 @@
         <v>1</v>
       </c>
       <c r="J142" s="1">
-        <f t="shared" si="46"/>
-        <v>9600</v>
+        <f t="shared" si="50"/>
+        <v>10300</v>
       </c>
       <c r="K142" s="1">
-        <f t="shared" si="47"/>
-        <v>11200</v>
+        <f t="shared" si="51"/>
+        <v>11900</v>
       </c>
       <c r="L142" s="1">
-        <f t="shared" si="48"/>
-        <v>3600</v>
+        <f t="shared" si="52"/>
+        <v>3950</v>
       </c>
       <c r="M142" s="1">
-        <f t="shared" si="49"/>
-        <v>3600</v>
+        <f t="shared" si="53"/>
+        <v>3950</v>
       </c>
       <c r="N142" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>78</v>
       </c>
       <c r="O142" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>78</v>
       </c>
       <c r="P142" s="3">
         <v>99.94</v>
       </c>
       <c r="Q142" s="11" t="s">
-        <v>929</v>
+        <v>941</v>
       </c>
       <c r="R142" s="11" t="s">
-        <v>929</v>
+        <v>941</v>
       </c>
       <c r="T142" s="1" t="s">
         <v>154</v>
@@ -12593,22 +12609,22 @@
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A143" s="3" t="s">
-        <v>903</v>
+        <v>933</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>903</v>
+        <v>933</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>931</v>
+        <v>943</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>932</v>
+        <v>944</v>
       </c>
       <c r="G143" s="4">
         <v>1</v>
@@ -12620,37 +12636,37 @@
         <v>1</v>
       </c>
       <c r="J143" s="1">
-        <f t="shared" si="46"/>
-        <v>10100</v>
+        <f t="shared" si="50"/>
+        <v>10900</v>
       </c>
       <c r="K143" s="1">
-        <f t="shared" si="47"/>
-        <v>11700</v>
+        <f t="shared" si="51"/>
+        <v>12500</v>
       </c>
       <c r="L143" s="1">
-        <f t="shared" si="48"/>
-        <v>3800</v>
+        <f t="shared" si="52"/>
+        <v>4200</v>
       </c>
       <c r="M143" s="1">
-        <f t="shared" si="49"/>
-        <v>3800</v>
+        <f t="shared" si="53"/>
+        <v>4200</v>
       </c>
       <c r="N143" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>80</v>
       </c>
       <c r="O143" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>82</v>
       </c>
       <c r="P143" s="3">
         <v>99.96</v>
       </c>
       <c r="Q143" s="11" t="s">
-        <v>933</v>
+        <v>945</v>
       </c>
       <c r="R143" s="11" t="s">
-        <v>933</v>
+        <v>945</v>
       </c>
       <c r="T143" s="1" t="s">
         <v>154</v>
@@ -12663,22 +12679,22 @@
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A144" s="3" t="s">
-        <v>903</v>
+        <v>933</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>903</v>
+        <v>933</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>934</v>
+        <v>946</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>935</v>
+        <v>947</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="G144" s="4">
         <v>1</v>
@@ -12690,27 +12706,27 @@
         <v>1</v>
       </c>
       <c r="J144" s="1">
-        <f t="shared" si="46"/>
-        <v>10600</v>
+        <f t="shared" si="50"/>
+        <v>11500</v>
       </c>
       <c r="K144" s="1">
-        <f t="shared" si="47"/>
-        <v>12200</v>
+        <f t="shared" si="51"/>
+        <v>13100</v>
       </c>
       <c r="L144" s="1">
-        <f t="shared" si="48"/>
-        <v>4000</v>
+        <f t="shared" si="52"/>
+        <v>4450</v>
       </c>
       <c r="M144" s="1">
-        <f t="shared" si="49"/>
-        <v>4000</v>
+        <f t="shared" si="53"/>
+        <v>4450</v>
       </c>
       <c r="N144" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>82</v>
       </c>
       <c r="O144" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>86</v>
       </c>
       <c r="P144" s="3">
@@ -12733,22 +12749,22 @@
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A145" s="3" t="s">
-        <v>903</v>
+        <v>933</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>903</v>
+        <v>933</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>937</v>
+        <v>949</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>938</v>
+        <v>950</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>939</v>
+        <v>951</v>
       </c>
       <c r="G145" s="4">
         <v>1</v>
@@ -12760,37 +12776,37 @@
         <v>1</v>
       </c>
       <c r="J145" s="1">
-        <f t="shared" si="46"/>
-        <v>11100</v>
+        <f t="shared" si="50"/>
+        <v>12100</v>
       </c>
       <c r="K145" s="1">
-        <f t="shared" si="47"/>
-        <v>12700</v>
+        <f t="shared" si="51"/>
+        <v>13700</v>
       </c>
       <c r="L145" s="1">
-        <f t="shared" si="48"/>
-        <v>4200</v>
+        <f t="shared" si="52"/>
+        <v>4700</v>
       </c>
       <c r="M145" s="1">
-        <f t="shared" si="49"/>
-        <v>4200</v>
+        <f t="shared" si="53"/>
+        <v>4700</v>
       </c>
       <c r="N145" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>84</v>
       </c>
       <c r="O145" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>90</v>
       </c>
       <c r="P145" s="3">
         <v>99.99</v>
       </c>
       <c r="Q145" s="11" t="s">
-        <v>940</v>
+        <v>952</v>
       </c>
       <c r="R145" s="11" t="s">
-        <v>940</v>
+        <v>952</v>
       </c>
       <c r="T145" s="1" t="s">
         <v>154</v>
@@ -12803,7 +12819,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:O5 P5 C3:P4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:P5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="953">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="962">
   <si>
     <t>ID</t>
   </si>
@@ -2884,9 +2884,6 @@
     <t>1500000000000</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
     <t>10135</t>
   </si>
   <si>
@@ -2896,6 +2893,12 @@
     <t>地狱水龙王</t>
   </si>
   <si>
+    <t>9000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>200000000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
     <t>610000000000</t>
   </si>
   <si>
@@ -2908,6 +2911,12 @@
     <t>地狱土龙王</t>
   </si>
   <si>
+    <t>90000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>4000000000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
     <t>620000000000</t>
   </si>
   <si>
@@ -2920,6 +2929,12 @@
     <t>地狱毒龙王</t>
   </si>
   <si>
+    <t>900000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>80000000000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
     <t>630000000000</t>
   </si>
   <si>
@@ -2932,6 +2947,12 @@
     <t>地狱火龙王</t>
   </si>
   <si>
+    <t>9000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>1600000000000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
     <t>10139</t>
   </si>
   <si>
@@ -2939,6 +2960,12 @@
   </si>
   <si>
     <t>地狱冰龙王</t>
+  </si>
+  <si>
+    <t>90000000000000000000000000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>32000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
     <t>650000000000</t>
@@ -3934,7 +3961,7 @@
     <col min="4" max="4" width="7.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="6.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="50.25" style="3" customWidth="1"/>
+    <col min="7" max="7" width="52.5" style="3" customWidth="1"/>
     <col min="8" max="8" width="52.1666666666667" style="3" customWidth="1"/>
     <col min="9" max="9" width="67.75" style="3" customWidth="1"/>
     <col min="10" max="10" width="15.875" style="3" customWidth="1"/>
@@ -4164,7 +4191,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="12" spans="3:21">
+    <row r="6" s="1" customFormat="1" ht="11.5" spans="3:21">
       <c r="C6" s="1" t="s">
         <v>35</v>
       </c>
@@ -12468,32 +12495,28 @@
       <c r="W140" s="3"/>
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A141" s="3" t="s">
+      <c r="A141" s="3"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="1" t="s">
         <v>933</v>
       </c>
-      <c r="B141" s="3" t="s">
-        <v>933</v>
-      </c>
-      <c r="C141" s="1" t="s">
+      <c r="D141" s="1" t="s">
         <v>934</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>935</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="G141" s="12" t="s">
         <v>936</v>
       </c>
-      <c r="G141" s="4">
-        <v>1</v>
-      </c>
-      <c r="H141" s="4">
-        <v>1</v>
-      </c>
-      <c r="I141" s="4">
-        <v>1</v>
+      <c r="H141" s="11" t="s">
+        <v>936</v>
+      </c>
+      <c r="I141" s="13" t="s">
+        <v>937</v>
       </c>
       <c r="J141" s="1">
         <f t="shared" ref="J141:J145" si="50">J140+600</f>
@@ -12523,10 +12546,10 @@
         <v>99.92</v>
       </c>
       <c r="Q141" s="11" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="R141" s="11" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="T141" s="1" t="s">
         <v>154</v>
@@ -12538,32 +12561,28 @@
       <c r="W141" s="3"/>
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A142" s="3" t="s">
-        <v>933</v>
-      </c>
-      <c r="B142" s="3" t="s">
-        <v>933</v>
-      </c>
+      <c r="A142" s="3"/>
+      <c r="B142" s="3"/>
       <c r="C142" s="1" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>940</v>
-      </c>
-      <c r="G142" s="4">
-        <v>1</v>
-      </c>
-      <c r="H142" s="4">
-        <v>1</v>
-      </c>
-      <c r="I142" s="4">
-        <v>1</v>
+        <v>941</v>
+      </c>
+      <c r="G142" s="12" t="s">
+        <v>942</v>
+      </c>
+      <c r="H142" s="11" t="s">
+        <v>942</v>
+      </c>
+      <c r="I142" s="13" t="s">
+        <v>943</v>
       </c>
       <c r="J142" s="1">
         <f t="shared" si="50"/>
@@ -12593,10 +12612,10 @@
         <v>99.94</v>
       </c>
       <c r="Q142" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="R142" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="T142" s="1" t="s">
         <v>154</v>
@@ -12608,32 +12627,28 @@
       <c r="W142" s="3"/>
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A143" s="3" t="s">
-        <v>933</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>933</v>
-      </c>
+      <c r="A143" s="3"/>
+      <c r="B143" s="3"/>
       <c r="C143" s="1" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>944</v>
-      </c>
-      <c r="G143" s="4">
-        <v>1</v>
-      </c>
-      <c r="H143" s="4">
-        <v>1</v>
-      </c>
-      <c r="I143" s="4">
-        <v>1</v>
+        <v>947</v>
+      </c>
+      <c r="G143" s="12" t="s">
+        <v>948</v>
+      </c>
+      <c r="H143" s="11" t="s">
+        <v>948</v>
+      </c>
+      <c r="I143" s="13" t="s">
+        <v>949</v>
       </c>
       <c r="J143" s="1">
         <f t="shared" si="50"/>
@@ -12663,10 +12678,10 @@
         <v>99.96</v>
       </c>
       <c r="Q143" s="11" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="R143" s="11" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="T143" s="1" t="s">
         <v>154</v>
@@ -12678,32 +12693,28 @@
       <c r="W143" s="3"/>
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A144" s="3" t="s">
-        <v>933</v>
-      </c>
-      <c r="B144" s="3" t="s">
-        <v>933</v>
-      </c>
+      <c r="A144" s="3"/>
+      <c r="B144" s="3"/>
       <c r="C144" s="1" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>948</v>
-      </c>
-      <c r="G144" s="4">
-        <v>1</v>
-      </c>
-      <c r="H144" s="4">
-        <v>1</v>
-      </c>
-      <c r="I144" s="4">
-        <v>1</v>
+        <v>953</v>
+      </c>
+      <c r="G144" s="12" t="s">
+        <v>954</v>
+      </c>
+      <c r="H144" s="11" t="s">
+        <v>954</v>
+      </c>
+      <c r="I144" s="13" t="s">
+        <v>955</v>
       </c>
       <c r="J144" s="1">
         <f t="shared" si="50"/>
@@ -12748,32 +12759,28 @@
       <c r="W144" s="3"/>
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A145" s="3" t="s">
-        <v>933</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>933</v>
-      </c>
+      <c r="A145" s="3"/>
+      <c r="B145" s="3"/>
       <c r="C145" s="1" t="s">
-        <v>949</v>
+        <v>956</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>950</v>
+        <v>957</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>951</v>
-      </c>
-      <c r="G145" s="4">
-        <v>1</v>
-      </c>
-      <c r="H145" s="4">
-        <v>1</v>
-      </c>
-      <c r="I145" s="4">
-        <v>1</v>
+        <v>958</v>
+      </c>
+      <c r="G145" s="12" t="s">
+        <v>959</v>
+      </c>
+      <c r="H145" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="I145" s="13" t="s">
+        <v>960</v>
       </c>
       <c r="J145" s="1">
         <f t="shared" si="50"/>
@@ -12803,10 +12810,10 @@
         <v>99.99</v>
       </c>
       <c r="Q145" s="11" t="s">
-        <v>952</v>
+        <v>961</v>
       </c>
       <c r="R145" s="11" t="s">
-        <v>952</v>
+        <v>961</v>
       </c>
       <c r="T145" s="1" t="s">
         <v>154</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="962">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="963">
   <si>
     <t>ID</t>
   </si>
@@ -2899,7 +2899,7 @@
     <t>200000000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>610000000000</t>
+    <t>1800000000000</t>
   </si>
   <si>
     <t>10136</t>
@@ -2917,7 +2917,7 @@
     <t>4000000000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>620000000000</t>
+    <t>2100000000000</t>
   </si>
   <si>
     <t>10137</t>
@@ -2935,7 +2935,7 @@
     <t>80000000000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>630000000000</t>
+    <t>2400000000000</t>
   </si>
   <si>
     <t>10138</t>
@@ -2953,6 +2953,9 @@
     <t>1600000000000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
+    <t>2700000000000</t>
+  </si>
+  <si>
     <t>10139</t>
   </si>
   <si>
@@ -2968,7 +2971,7 @@
     <t>32000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
   </si>
   <si>
-    <t>650000000000</t>
+    <t>3000000000000</t>
   </si>
 </sst>
 </file>
@@ -4191,7 +4194,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="11.5" spans="3:21">
+    <row r="6" s="1" customFormat="1" ht="12" spans="3:21">
       <c r="C6" s="1" t="s">
         <v>35</v>
       </c>
@@ -12744,10 +12747,10 @@
         <v>99.98</v>
       </c>
       <c r="Q144" s="11" t="s">
-        <v>850</v>
+        <v>956</v>
       </c>
       <c r="R144" s="11" t="s">
-        <v>850</v>
+        <v>956</v>
       </c>
       <c r="T144" s="1" t="s">
         <v>154</v>
@@ -12762,25 +12765,25 @@
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="G145" s="12" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H145" s="11" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="I145" s="13" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="J145" s="1">
         <f t="shared" si="50"/>
@@ -12810,10 +12813,10 @@
         <v>99.99</v>
       </c>
       <c r="Q145" s="11" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="R145" s="11" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="T145" s="1" t="s">
         <v>154</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="1070">
   <si>
     <t>ID</t>
   </si>
@@ -2984,6 +2984,12 @@
   </si>
   <si>
     <t>深渊鸡王</t>
+  </si>
+  <si>
+    <t>9000僧</t>
+  </si>
+  <si>
+    <t>64000不</t>
   </si>
   <si>
     <t>10141</t>
@@ -3466,12 +3472,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4521,7 +4527,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="12" spans="3:22">
+    <row r="6" s="1" customFormat="1" ht="11.5" spans="3:22">
       <c r="C6" s="1" t="s">
         <v>36</v>
       </c>
@@ -13589,14 +13595,14 @@
       <c r="F146" s="1" t="s">
         <v>966</v>
       </c>
-      <c r="G146" s="14" t="s">
-        <v>760</v>
-      </c>
-      <c r="H146" s="15" t="s">
-        <v>760</v>
-      </c>
-      <c r="I146" s="16" t="s">
-        <v>761</v>
+      <c r="G146" s="8" t="s">
+        <v>967</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="I146" s="10" t="s">
+        <v>968</v>
       </c>
       <c r="J146" s="1">
         <v>0</v>
@@ -13639,16 +13645,16 @@
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="11" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="D147" s="11" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="E147" s="1">
         <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="G147" s="12" t="s">
         <v>766</v>
@@ -13705,16 +13711,16 @@
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="11" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="D148" s="11" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="E148" s="1">
         <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="G148" s="12" t="s">
         <v>772</v>
@@ -13771,16 +13777,16 @@
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="11" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="D149" s="11" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="E149" s="1">
         <v>4</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="G149" s="12" t="s">
         <v>778</v>
@@ -13837,16 +13843,16 @@
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="11" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="E150" s="1">
         <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="G150" s="12" t="s">
         <v>784</v>
@@ -13903,16 +13909,16 @@
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="11" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="E151" s="1">
         <v>4</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="G151" s="12" t="s">
         <v>790</v>
@@ -13971,16 +13977,16 @@
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="11" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="E152" s="1">
         <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="G152" s="12" t="s">
         <v>796</v>
@@ -14039,16 +14045,16 @@
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="11" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="E153" s="1">
         <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="G153" s="12" t="s">
         <v>802</v>
@@ -14107,16 +14113,16 @@
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="11" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="E154" s="1">
         <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="G154" s="12" t="s">
         <v>808</v>
@@ -14175,16 +14181,16 @@
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="11" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="E155" s="1">
         <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="G155" s="12" t="s">
         <v>814</v>
@@ -14241,16 +14247,16 @@
     </row>
     <row r="156" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C156" s="11" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="E156" s="1">
         <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="G156" s="12" t="s">
         <v>761</v>
@@ -14308,16 +14314,16 @@
     </row>
     <row r="157" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C157" s="11" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="D157" s="11" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="E157" s="1">
         <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="G157" s="12" t="s">
         <v>825</v>
@@ -14375,16 +14381,16 @@
     </row>
     <row r="158" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C158" s="11" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="D158" s="11" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="E158" s="1">
         <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="G158" s="12" t="s">
         <v>831</v>
@@ -14442,16 +14448,16 @@
     </row>
     <row r="159" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C159" s="11" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="D159" s="11" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="E159" s="1">
         <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="G159" s="12" t="s">
         <v>837</v>
@@ -14509,16 +14515,16 @@
     </row>
     <row r="160" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C160" s="11" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="D160" s="11" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="E160" s="1">
         <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="G160" s="12" t="s">
         <v>843</v>
@@ -14578,16 +14584,16 @@
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="11" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="E161" s="1">
         <v>4</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="G161" s="12" t="s">
         <v>849</v>
@@ -14647,16 +14653,16 @@
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="11" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="D162" s="11" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="E162" s="1">
         <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="G162" s="12" t="s">
         <v>855</v>
@@ -14716,16 +14722,16 @@
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="11" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="D163" s="11" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="E163" s="1">
         <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="G163" s="12" t="s">
         <v>861</v>
@@ -14785,16 +14791,16 @@
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="11" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="E164" s="1">
         <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="G164" s="12" t="s">
         <v>867</v>
@@ -14854,16 +14860,16 @@
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="11" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="D165" s="11" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="E165" s="1">
         <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="G165" s="12" t="s">
         <v>873</v>
@@ -14921,16 +14927,16 @@
     </row>
     <row r="166" customHeight="1" spans="3:22">
       <c r="C166" s="11" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="D166" s="11" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="E166" s="1">
         <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="G166" s="12" t="s">
         <v>879</v>
@@ -14986,16 +14992,16 @@
     </row>
     <row r="167" customHeight="1" spans="3:22">
       <c r="C167" s="11" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="D167" s="11" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="E167" s="1">
         <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="G167" s="12" t="s">
         <v>885</v>
@@ -15051,16 +15057,16 @@
     </row>
     <row r="168" customHeight="1" spans="3:22">
       <c r="C168" s="11" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="D168" s="11" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="E168" s="1">
         <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="G168" s="12" t="s">
         <v>891</v>
@@ -15116,16 +15122,16 @@
     </row>
     <row r="169" customHeight="1" spans="3:22">
       <c r="C169" s="11" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="D169" s="11" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="E169" s="1">
         <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="G169" s="12" t="s">
         <v>897</v>
@@ -15181,10 +15187,10 @@
     </row>
     <row r="170" customHeight="1" spans="3:22">
       <c r="C170" s="11" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="D170" s="11" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="E170" s="1">
         <v>4</v>
@@ -15248,16 +15254,16 @@
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="11" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="D171" s="11" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="E171" s="1">
         <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="G171" s="12" t="s">
         <v>907</v>
@@ -15317,16 +15323,16 @@
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="11" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="D172" s="11" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="E172" s="1">
         <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="G172" s="12" t="s">
         <v>913</v>
@@ -15386,16 +15392,16 @@
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="11" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D173" s="11" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="E173" s="1">
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="G173" s="12" t="s">
         <v>919</v>
@@ -15455,16 +15461,16 @@
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="11" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="D174" s="11" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="E174" s="1">
         <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="G174" s="12" t="s">
         <v>925</v>
@@ -15524,16 +15530,16 @@
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="11" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="D175" s="11" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="E175" s="1">
         <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="G175" s="12" t="s">
         <v>931</v>
@@ -15593,16 +15599,16 @@
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="11" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D176" s="11" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E176" s="1">
         <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="G176" s="12" t="s">
         <v>937</v>
@@ -15662,16 +15668,16 @@
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="11" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="D177" s="11" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="E177" s="1">
         <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="G177" s="12" t="s">
         <v>943</v>
@@ -15731,16 +15737,16 @@
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="11" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="D178" s="11" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="E178" s="1">
         <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="G178" s="12" t="s">
         <v>949</v>
@@ -15800,16 +15806,16 @@
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="11" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="D179" s="11" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E179" s="1">
         <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="G179" s="12" t="s">
         <v>955</v>
@@ -15869,16 +15875,16 @@
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="11" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="D180" s="11" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="E180" s="1">
         <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="G180" s="12" t="s">
         <v>961</v>
@@ -15936,7 +15942,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="J3 J4 J5 C3:I5 K3:Q5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:Q5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="1070">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="1161">
   <si>
     <t>ID</t>
   </si>
@@ -2992,6 +2992,9 @@
     <t>64000不</t>
   </si>
   <si>
+    <t>3300000000000</t>
+  </si>
+  <si>
     <t>10141</t>
   </si>
   <si>
@@ -3001,6 +3004,15 @@
     <t>深渊鹿王</t>
   </si>
   <si>
+    <t>9祇</t>
+  </si>
+  <si>
+    <t>128可</t>
+  </si>
+  <si>
+    <t>3600000000000</t>
+  </si>
+  <si>
     <t>10142</t>
   </si>
   <si>
@@ -3010,6 +3022,15 @@
     <t>深渊草王</t>
   </si>
   <si>
+    <t>90祇</t>
+  </si>
+  <si>
+    <t>2560可</t>
+  </si>
+  <si>
+    <t>3900000000000</t>
+  </si>
+  <si>
     <t>10143</t>
   </si>
   <si>
@@ -3019,6 +3040,15 @@
     <t>深渊猫王</t>
   </si>
   <si>
+    <t>900祇</t>
+  </si>
+  <si>
+    <t>5思</t>
+  </si>
+  <si>
+    <t>4200000000000</t>
+  </si>
+  <si>
     <t>10144</t>
   </si>
   <si>
@@ -3028,6 +3058,15 @@
     <t>深渊花王</t>
   </si>
   <si>
+    <t>9000祇</t>
+  </si>
+  <si>
+    <t>100思</t>
+  </si>
+  <si>
+    <t>4500000000000</t>
+  </si>
+  <si>
     <t>10145</t>
   </si>
   <si>
@@ -3037,6 +3076,15 @@
     <t>深渊雪王</t>
   </si>
   <si>
+    <t>9那</t>
+  </si>
+  <si>
+    <t>2000思</t>
+  </si>
+  <si>
+    <t>4800000000000</t>
+  </si>
+  <si>
     <t>10146</t>
   </si>
   <si>
@@ -3046,6 +3094,15 @@
     <t>深渊蝠王</t>
   </si>
   <si>
+    <t>90那</t>
+  </si>
+  <si>
+    <t>4议</t>
+  </si>
+  <si>
+    <t>5100000000000</t>
+  </si>
+  <si>
     <t>10147</t>
   </si>
   <si>
@@ -3055,6 +3112,15 @@
     <t>深渊骷髅王</t>
   </si>
   <si>
+    <t>900那</t>
+  </si>
+  <si>
+    <t>80议</t>
+  </si>
+  <si>
+    <t>5400000000000</t>
+  </si>
+  <si>
     <t>10148</t>
   </si>
   <si>
@@ -3064,6 +3130,15 @@
     <t>深渊尸王</t>
   </si>
   <si>
+    <t>9000那</t>
+  </si>
+  <si>
+    <t>1600议</t>
+  </si>
+  <si>
+    <t>5700000000000</t>
+  </si>
+  <si>
     <t>10149</t>
   </si>
   <si>
@@ -3073,6 +3148,15 @@
     <t>深渊蛇王</t>
   </si>
   <si>
+    <t>9由</t>
+  </si>
+  <si>
+    <t>32000无</t>
+  </si>
+  <si>
+    <t>6000000000000</t>
+  </si>
+  <si>
     <t>10150</t>
   </si>
   <si>
@@ -3082,6 +3166,15 @@
     <t>深渊狼王</t>
   </si>
   <si>
+    <t>90由</t>
+  </si>
+  <si>
+    <t>64无</t>
+  </si>
+  <si>
+    <t>1亿</t>
+  </si>
+  <si>
     <t>10151</t>
   </si>
   <si>
@@ -3091,6 +3184,15 @@
     <t>深渊沙虫王</t>
   </si>
   <si>
+    <t>900由</t>
+  </si>
+  <si>
+    <t>1280无</t>
+  </si>
+  <si>
+    <t>5亿</t>
+  </si>
+  <si>
     <t>10152</t>
   </si>
   <si>
@@ -3100,6 +3202,15 @@
     <t>深渊鹰王</t>
   </si>
   <si>
+    <t>9000由</t>
+  </si>
+  <si>
+    <t>51200无</t>
+  </si>
+  <si>
+    <t>20亿</t>
+  </si>
+  <si>
     <t>10153</t>
   </si>
   <si>
@@ -3109,6 +3220,15 @@
     <t>深渊角虫王</t>
   </si>
   <si>
+    <t>9他</t>
+  </si>
+  <si>
+    <t>10量</t>
+  </si>
+  <si>
+    <t>100亿</t>
+  </si>
+  <si>
     <t>10154</t>
   </si>
   <si>
@@ -3118,6 +3238,15 @@
     <t>深渊蜈蚣王</t>
   </si>
   <si>
+    <t>90他</t>
+  </si>
+  <si>
+    <t>200量</t>
+  </si>
+  <si>
+    <t>500亿</t>
+  </si>
+  <si>
     <t>10155</t>
   </si>
   <si>
@@ -3127,6 +3256,15 @@
     <t>深渊钳虫王</t>
   </si>
   <si>
+    <t>900他</t>
+  </si>
+  <si>
+    <t>4000量</t>
+  </si>
+  <si>
+    <t>2500亿</t>
+  </si>
+  <si>
     <t>10156</t>
   </si>
   <si>
@@ -3136,6 +3274,15 @@
     <t>深渊蠕虫王</t>
   </si>
   <si>
+    <t>9000他</t>
+  </si>
+  <si>
+    <t>8大</t>
+  </si>
+  <si>
+    <t>12500亿</t>
+  </si>
+  <si>
     <t>10157</t>
   </si>
   <si>
@@ -3145,6 +3292,15 @@
     <t>深渊猪王</t>
   </si>
   <si>
+    <t>9不</t>
+  </si>
+  <si>
+    <t>160大</t>
+  </si>
+  <si>
+    <t>62500亿</t>
+  </si>
+  <si>
     <t>10158</t>
   </si>
   <si>
@@ -3154,6 +3310,15 @@
     <t>深渊猪皇</t>
   </si>
   <si>
+    <t>90不</t>
+  </si>
+  <si>
+    <t>3200大</t>
+  </si>
+  <si>
+    <t>32兆</t>
+  </si>
+  <si>
     <t>10159</t>
   </si>
   <si>
@@ -3163,6 +3328,15 @@
     <t>深渊蝎王</t>
   </si>
   <si>
+    <t>900不</t>
+  </si>
+  <si>
+    <t>64000大</t>
+  </si>
+  <si>
+    <t>160兆</t>
+  </si>
+  <si>
     <t>10160</t>
   </si>
   <si>
@@ -3172,6 +3346,15 @@
     <t>深渊恶魔教主</t>
   </si>
   <si>
+    <t>9000不</t>
+  </si>
+  <si>
+    <t>128数</t>
+  </si>
+  <si>
+    <t>800兆</t>
+  </si>
+  <si>
     <t>10161</t>
   </si>
   <si>
@@ -3181,6 +3364,15 @@
     <t>深渊恶魔教皇</t>
   </si>
   <si>
+    <t>9可</t>
+  </si>
+  <si>
+    <t>2560数</t>
+  </si>
+  <si>
+    <t>4000兆</t>
+  </si>
+  <si>
     <t>10162</t>
   </si>
   <si>
@@ -3190,6 +3382,15 @@
     <t>深渊邪魔教主</t>
   </si>
   <si>
+    <t>90可</t>
+  </si>
+  <si>
+    <t>5120数</t>
+  </si>
+  <si>
+    <t>2京</t>
+  </si>
+  <si>
     <t>10163</t>
   </si>
   <si>
@@ -3199,12 +3400,24 @@
     <t>深渊邪魔教皇</t>
   </si>
   <si>
+    <t>900可</t>
+  </si>
+  <si>
+    <t>10京</t>
+  </si>
+  <si>
     <t>10164</t>
   </si>
   <si>
     <t>1164</t>
   </si>
   <si>
+    <t>9000可</t>
+  </si>
+  <si>
+    <t>50京</t>
+  </si>
+  <si>
     <t>10165</t>
   </si>
   <si>
@@ -3214,6 +3427,12 @@
     <t>深渊烈焰王</t>
   </si>
   <si>
+    <t>9思</t>
+  </si>
+  <si>
+    <t>250京</t>
+  </si>
+  <si>
     <t>10166</t>
   </si>
   <si>
@@ -3223,6 +3442,12 @@
     <t>深渊大邪王</t>
   </si>
   <si>
+    <t>90思</t>
+  </si>
+  <si>
+    <t>1250京</t>
+  </si>
+  <si>
     <t>10167</t>
   </si>
   <si>
@@ -3232,6 +3457,12 @@
     <t>深渊尸魔王</t>
   </si>
   <si>
+    <t>900思</t>
+  </si>
+  <si>
+    <t>6250京</t>
+  </si>
+  <si>
     <t>10168</t>
   </si>
   <si>
@@ -3241,6 +3472,12 @@
     <t>深渊骨魔王</t>
   </si>
   <si>
+    <t>9000思</t>
+  </si>
+  <si>
+    <t>3垓</t>
+  </si>
+  <si>
     <t>10169</t>
   </si>
   <si>
@@ -3250,6 +3487,12 @@
     <t>深渊牛魔王</t>
   </si>
   <si>
+    <t>9议</t>
+  </si>
+  <si>
+    <t>15垓</t>
+  </si>
+  <si>
     <t>10170</t>
   </si>
   <si>
@@ -3259,6 +3502,12 @@
     <t>深渊水龙王</t>
   </si>
   <si>
+    <t>90议</t>
+  </si>
+  <si>
+    <t>75垓</t>
+  </si>
+  <si>
     <t>10171</t>
   </si>
   <si>
@@ -3268,6 +3517,12 @@
     <t>深渊土龙王</t>
   </si>
   <si>
+    <t>900议</t>
+  </si>
+  <si>
+    <t>375垓</t>
+  </si>
+  <si>
     <t>10172</t>
   </si>
   <si>
@@ -3277,6 +3532,12 @@
     <t>深渊毒龙王</t>
   </si>
   <si>
+    <t>9000议</t>
+  </si>
+  <si>
+    <t>2000垓</t>
+  </si>
+  <si>
     <t>10173</t>
   </si>
   <si>
@@ -3286,6 +3547,12 @@
     <t>深渊火龙王</t>
   </si>
   <si>
+    <t>9无</t>
+  </si>
+  <si>
+    <t>1秭</t>
+  </si>
+  <si>
     <t>10174</t>
   </si>
   <si>
@@ -3293,6 +3560,12 @@
   </si>
   <si>
     <t>深渊冰龙王</t>
+  </si>
+  <si>
+    <t>90无</t>
+  </si>
+  <si>
+    <t>5秭</t>
   </si>
 </sst>
 </file>
@@ -12607,11 +12880,11 @@
         <v>2050</v>
       </c>
       <c r="O131" s="3">
-        <f t="shared" ref="O131:O145" si="44">O130+2</f>
+        <f>O130+2</f>
         <v>56</v>
       </c>
       <c r="P131" s="3">
-        <f t="shared" ref="P131:P145" si="45">P130+4</f>
+        <f t="shared" ref="P131:P180" si="44">P130+4</f>
         <v>34</v>
       </c>
       <c r="Q131" s="3">
@@ -12672,11 +12945,11 @@
         <v>2150</v>
       </c>
       <c r="O132" s="3">
+        <f>O131+2</f>
+        <v>58</v>
+      </c>
+      <c r="P132" s="3">
         <f t="shared" si="44"/>
-        <v>58</v>
-      </c>
-      <c r="P132" s="3">
-        <f t="shared" si="45"/>
         <v>38</v>
       </c>
       <c r="Q132" s="3">
@@ -12737,11 +13010,11 @@
         <v>2250</v>
       </c>
       <c r="O133" s="3">
+        <f>O132+2</f>
+        <v>60</v>
+      </c>
+      <c r="P133" s="3">
         <f t="shared" si="44"/>
-        <v>60</v>
-      </c>
-      <c r="P133" s="3">
-        <f t="shared" si="45"/>
         <v>42</v>
       </c>
       <c r="Q133" s="3">
@@ -12802,11 +13075,11 @@
         <v>2350</v>
       </c>
       <c r="O134" s="3">
+        <f>O133+2</f>
+        <v>62</v>
+      </c>
+      <c r="P134" s="3">
         <f t="shared" si="44"/>
-        <v>62</v>
-      </c>
-      <c r="P134" s="3">
-        <f t="shared" si="45"/>
         <v>46</v>
       </c>
       <c r="Q134" s="3">
@@ -12867,11 +13140,11 @@
         <v>2450</v>
       </c>
       <c r="O135" s="3">
+        <f>O134+2</f>
+        <v>64</v>
+      </c>
+      <c r="P135" s="3">
         <f t="shared" si="44"/>
-        <v>64</v>
-      </c>
-      <c r="P135" s="3">
-        <f t="shared" si="45"/>
         <v>50</v>
       </c>
       <c r="Q135" s="3">
@@ -12918,27 +13191,27 @@
         <v>0</v>
       </c>
       <c r="K136" s="1">
-        <f t="shared" ref="K136:K145" si="46">K135+500</f>
+        <f t="shared" ref="K136:K145" si="45">K135+500</f>
         <v>7100</v>
       </c>
       <c r="L136" s="1">
-        <f t="shared" ref="L136:L145" si="47">L135+500</f>
+        <f t="shared" ref="L136:L145" si="46">L135+500</f>
         <v>8700</v>
       </c>
       <c r="M136" s="1">
-        <f t="shared" ref="M136:M145" si="48">M135+200</f>
+        <f t="shared" ref="M136:M145" si="47">M135+200</f>
         <v>2650</v>
       </c>
       <c r="N136" s="1">
-        <f t="shared" ref="N136:N145" si="49">N135+200</f>
+        <f t="shared" ref="N136:N145" si="48">N135+200</f>
         <v>2650</v>
       </c>
       <c r="O136" s="3">
+        <f>O135+2</f>
+        <v>66</v>
+      </c>
+      <c r="P136" s="3">
         <f t="shared" si="44"/>
-        <v>66</v>
-      </c>
-      <c r="P136" s="3">
-        <f t="shared" si="45"/>
         <v>54</v>
       </c>
       <c r="Q136" s="3">
@@ -12987,27 +13260,27 @@
         <v>0</v>
       </c>
       <c r="K137" s="1">
+        <f t="shared" si="45"/>
+        <v>7600</v>
+      </c>
+      <c r="L137" s="1">
         <f t="shared" si="46"/>
-        <v>7600</v>
-      </c>
-      <c r="L137" s="1">
+        <v>9200</v>
+      </c>
+      <c r="M137" s="1">
         <f t="shared" si="47"/>
-        <v>9200</v>
-      </c>
-      <c r="M137" s="1">
+        <v>2850</v>
+      </c>
+      <c r="N137" s="1">
         <f t="shared" si="48"/>
         <v>2850</v>
       </c>
-      <c r="N137" s="1">
-        <f t="shared" si="49"/>
-        <v>2850</v>
-      </c>
       <c r="O137" s="3">
+        <f>O136+2</f>
+        <v>68</v>
+      </c>
+      <c r="P137" s="3">
         <f t="shared" si="44"/>
-        <v>68</v>
-      </c>
-      <c r="P137" s="3">
-        <f t="shared" si="45"/>
         <v>58</v>
       </c>
       <c r="Q137" s="3">
@@ -13056,27 +13329,27 @@
         <v>0</v>
       </c>
       <c r="K138" s="1">
+        <f t="shared" si="45"/>
+        <v>8100</v>
+      </c>
+      <c r="L138" s="1">
         <f t="shared" si="46"/>
-        <v>8100</v>
-      </c>
-      <c r="L138" s="1">
+        <v>9700</v>
+      </c>
+      <c r="M138" s="1">
         <f t="shared" si="47"/>
-        <v>9700</v>
-      </c>
-      <c r="M138" s="1">
+        <v>3050</v>
+      </c>
+      <c r="N138" s="1">
         <f t="shared" si="48"/>
         <v>3050</v>
       </c>
-      <c r="N138" s="1">
-        <f t="shared" si="49"/>
-        <v>3050</v>
-      </c>
       <c r="O138" s="3">
+        <f>O137+2</f>
+        <v>70</v>
+      </c>
+      <c r="P138" s="3">
         <f t="shared" si="44"/>
-        <v>70</v>
-      </c>
-      <c r="P138" s="3">
-        <f t="shared" si="45"/>
         <v>62</v>
       </c>
       <c r="Q138" s="3">
@@ -13125,27 +13398,27 @@
         <v>0</v>
       </c>
       <c r="K139" s="1">
+        <f t="shared" si="45"/>
+        <v>8600</v>
+      </c>
+      <c r="L139" s="1">
         <f t="shared" si="46"/>
-        <v>8600</v>
-      </c>
-      <c r="L139" s="1">
+        <v>10200</v>
+      </c>
+      <c r="M139" s="1">
         <f t="shared" si="47"/>
-        <v>10200</v>
-      </c>
-      <c r="M139" s="1">
+        <v>3250</v>
+      </c>
+      <c r="N139" s="1">
         <f t="shared" si="48"/>
         <v>3250</v>
       </c>
-      <c r="N139" s="1">
-        <f t="shared" si="49"/>
-        <v>3250</v>
-      </c>
       <c r="O139" s="3">
+        <f>O138+2</f>
+        <v>72</v>
+      </c>
+      <c r="P139" s="3">
         <f t="shared" si="44"/>
-        <v>72</v>
-      </c>
-      <c r="P139" s="3">
-        <f t="shared" si="45"/>
         <v>66</v>
       </c>
       <c r="Q139" s="3">
@@ -13194,27 +13467,27 @@
         <v>0</v>
       </c>
       <c r="K140" s="1">
+        <f t="shared" si="45"/>
+        <v>9100</v>
+      </c>
+      <c r="L140" s="1">
         <f t="shared" si="46"/>
-        <v>9100</v>
-      </c>
-      <c r="L140" s="1">
+        <v>10700</v>
+      </c>
+      <c r="M140" s="1">
         <f t="shared" si="47"/>
-        <v>10700</v>
-      </c>
-      <c r="M140" s="1">
+        <v>3450</v>
+      </c>
+      <c r="N140" s="1">
         <f t="shared" si="48"/>
         <v>3450</v>
       </c>
-      <c r="N140" s="1">
-        <f t="shared" si="49"/>
-        <v>3450</v>
-      </c>
       <c r="O140" s="3">
+        <f>O139+2</f>
+        <v>74</v>
+      </c>
+      <c r="P140" s="3">
         <f t="shared" si="44"/>
-        <v>74</v>
-      </c>
-      <c r="P140" s="3">
-        <f t="shared" si="45"/>
         <v>70</v>
       </c>
       <c r="Q140" s="3">
@@ -13263,27 +13536,27 @@
         <v>0</v>
       </c>
       <c r="K141" s="1">
-        <f t="shared" ref="K141:K145" si="50">K140+600</f>
+        <f t="shared" ref="K141:K180" si="49">K140+600</f>
         <v>9700</v>
       </c>
       <c r="L141" s="1">
-        <f t="shared" ref="L141:L145" si="51">L140+600</f>
+        <f t="shared" ref="L141:L180" si="50">L140+600</f>
         <v>11300</v>
       </c>
       <c r="M141" s="1">
-        <f t="shared" ref="M141:M145" si="52">M140+250</f>
+        <f t="shared" ref="M141:M180" si="51">M140+250</f>
         <v>3700</v>
       </c>
       <c r="N141" s="1">
-        <f t="shared" ref="N141:N145" si="53">N140+250</f>
+        <f t="shared" ref="N141:N180" si="52">N140+250</f>
         <v>3700</v>
       </c>
       <c r="O141" s="3">
+        <f>O140+2</f>
+        <v>76</v>
+      </c>
+      <c r="P141" s="3">
         <f t="shared" si="44"/>
-        <v>76</v>
-      </c>
-      <c r="P141" s="3">
-        <f t="shared" si="45"/>
         <v>74</v>
       </c>
       <c r="Q141" s="3">
@@ -13332,27 +13605,27 @@
         <v>0</v>
       </c>
       <c r="K142" s="1">
+        <f t="shared" si="49"/>
+        <v>10300</v>
+      </c>
+      <c r="L142" s="1">
         <f t="shared" si="50"/>
-        <v>10300</v>
-      </c>
-      <c r="L142" s="1">
+        <v>11900</v>
+      </c>
+      <c r="M142" s="1">
         <f t="shared" si="51"/>
-        <v>11900</v>
-      </c>
-      <c r="M142" s="1">
+        <v>3950</v>
+      </c>
+      <c r="N142" s="1">
         <f t="shared" si="52"/>
         <v>3950</v>
       </c>
-      <c r="N142" s="1">
-        <f t="shared" si="53"/>
-        <v>3950</v>
-      </c>
       <c r="O142" s="3">
+        <f>O141+2</f>
+        <v>78</v>
+      </c>
+      <c r="P142" s="3">
         <f t="shared" si="44"/>
-        <v>78</v>
-      </c>
-      <c r="P142" s="3">
-        <f t="shared" si="45"/>
         <v>78</v>
       </c>
       <c r="Q142" s="3">
@@ -13401,27 +13674,27 @@
         <v>0</v>
       </c>
       <c r="K143" s="1">
+        <f t="shared" si="49"/>
+        <v>10900</v>
+      </c>
+      <c r="L143" s="1">
         <f t="shared" si="50"/>
-        <v>10900</v>
-      </c>
-      <c r="L143" s="1">
+        <v>12500</v>
+      </c>
+      <c r="M143" s="1">
         <f t="shared" si="51"/>
-        <v>12500</v>
-      </c>
-      <c r="M143" s="1">
+        <v>4200</v>
+      </c>
+      <c r="N143" s="1">
         <f t="shared" si="52"/>
         <v>4200</v>
       </c>
-      <c r="N143" s="1">
-        <f t="shared" si="53"/>
-        <v>4200</v>
-      </c>
       <c r="O143" s="3">
+        <f>O142+2</f>
+        <v>80</v>
+      </c>
+      <c r="P143" s="3">
         <f t="shared" si="44"/>
-        <v>80</v>
-      </c>
-      <c r="P143" s="3">
-        <f t="shared" si="45"/>
         <v>82</v>
       </c>
       <c r="Q143" s="3">
@@ -13470,27 +13743,27 @@
         <v>0</v>
       </c>
       <c r="K144" s="1">
+        <f t="shared" si="49"/>
+        <v>11500</v>
+      </c>
+      <c r="L144" s="1">
         <f t="shared" si="50"/>
-        <v>11500</v>
-      </c>
-      <c r="L144" s="1">
+        <v>13100</v>
+      </c>
+      <c r="M144" s="1">
         <f t="shared" si="51"/>
-        <v>13100</v>
-      </c>
-      <c r="M144" s="1">
+        <v>4450</v>
+      </c>
+      <c r="N144" s="1">
         <f t="shared" si="52"/>
         <v>4450</v>
       </c>
-      <c r="N144" s="1">
-        <f t="shared" si="53"/>
-        <v>4450</v>
-      </c>
       <c r="O144" s="3">
+        <f>O143+2</f>
+        <v>82</v>
+      </c>
+      <c r="P144" s="3">
         <f t="shared" si="44"/>
-        <v>82</v>
-      </c>
-      <c r="P144" s="3">
-        <f t="shared" si="45"/>
         <v>86</v>
       </c>
       <c r="Q144" s="3">
@@ -13539,27 +13812,27 @@
         <v>0</v>
       </c>
       <c r="K145" s="1">
+        <f t="shared" si="49"/>
+        <v>12100</v>
+      </c>
+      <c r="L145" s="1">
         <f t="shared" si="50"/>
-        <v>12100</v>
-      </c>
-      <c r="L145" s="1">
+        <v>13700</v>
+      </c>
+      <c r="M145" s="1">
         <f t="shared" si="51"/>
-        <v>13700</v>
-      </c>
-      <c r="M145" s="1">
+        <v>4700</v>
+      </c>
+      <c r="N145" s="1">
         <f t="shared" si="52"/>
         <v>4700</v>
       </c>
-      <c r="N145" s="1">
-        <f t="shared" si="53"/>
-        <v>4700</v>
-      </c>
       <c r="O145" s="3">
+        <f>O144+2</f>
+        <v>84</v>
+      </c>
+      <c r="P145" s="3">
         <f t="shared" si="44"/>
-        <v>84</v>
-      </c>
-      <c r="P145" s="3">
-        <f t="shared" si="45"/>
         <v>90</v>
       </c>
       <c r="Q145" s="3">
@@ -13605,34 +13878,40 @@
         <v>968</v>
       </c>
       <c r="J146" s="1">
-        <v>0</v>
-      </c>
-      <c r="K146" s="2">
-        <v>1500</v>
-      </c>
-      <c r="L146" s="2">
-        <v>1200</v>
-      </c>
-      <c r="M146" s="2">
-        <v>1000</v>
-      </c>
-      <c r="N146" s="2">
-        <v>1000</v>
+        <v>10</v>
+      </c>
+      <c r="K146" s="1">
+        <f t="shared" si="49"/>
+        <v>12700</v>
+      </c>
+      <c r="L146" s="1">
+        <f t="shared" si="50"/>
+        <v>14300</v>
+      </c>
+      <c r="M146" s="1">
+        <f t="shared" si="51"/>
+        <v>4950</v>
+      </c>
+      <c r="N146" s="1">
+        <f t="shared" si="52"/>
+        <v>4950</v>
       </c>
       <c r="O146" s="3">
-        <v>35</v>
-      </c>
-      <c r="P146" s="6">
-        <v>0</v>
+        <f t="shared" ref="O146:O180" si="53">O145+3</f>
+        <v>87</v>
+      </c>
+      <c r="P146" s="3">
+        <f t="shared" si="44"/>
+        <v>94</v>
       </c>
       <c r="Q146" s="3">
-        <v>90</v>
-      </c>
-      <c r="R146" s="15" t="s">
-        <v>762</v>
-      </c>
-      <c r="S146" s="15" t="s">
-        <v>762</v>
+        <v>99.99</v>
+      </c>
+      <c r="R146" s="11" t="s">
+        <v>969</v>
+      </c>
+      <c r="S146" s="11" t="s">
+        <v>969</v>
       </c>
       <c r="U146" s="2" t="s">
         <v>155</v>
@@ -13645,60 +13924,62 @@
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="11" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D147" s="11" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="E147" s="1">
         <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>971</v>
-      </c>
-      <c r="G147" s="12" t="s">
-        <v>766</v>
-      </c>
-      <c r="H147" s="11" t="s">
-        <v>766</v>
-      </c>
-      <c r="I147" s="13" t="s">
-        <v>767</v>
+        <v>972</v>
+      </c>
+      <c r="G147" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="H147" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="I147" s="9" t="s">
+        <v>974</v>
       </c>
       <c r="J147" s="1">
-        <v>0</v>
+        <f t="shared" ref="J147:J155" si="54">J146*5</f>
+        <v>50</v>
       </c>
       <c r="K147" s="1">
-        <f t="shared" ref="K147:K150" si="54">K146+100</f>
-        <v>1600</v>
+        <f t="shared" si="49"/>
+        <v>13300</v>
       </c>
       <c r="L147" s="1">
-        <f t="shared" ref="L147:L150" si="55">L146+100</f>
-        <v>1300</v>
+        <f t="shared" si="50"/>
+        <v>14900</v>
       </c>
       <c r="M147" s="1">
-        <f t="shared" ref="M147:M165" si="56">M146+50</f>
-        <v>1050</v>
+        <f t="shared" si="51"/>
+        <v>5200</v>
       </c>
       <c r="N147" s="1">
-        <f t="shared" ref="N147:N165" si="57">N146+50</f>
-        <v>1050</v>
+        <f t="shared" si="52"/>
+        <v>5200</v>
       </c>
       <c r="O147" s="3">
-        <f t="shared" ref="O147:O165" si="58">O146+1</f>
-        <v>36</v>
-      </c>
-      <c r="P147" s="6">
-        <v>0</v>
+        <f t="shared" si="53"/>
+        <v>90</v>
+      </c>
+      <c r="P147" s="3">
+        <f t="shared" si="44"/>
+        <v>98</v>
       </c>
       <c r="Q147" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="R147" s="11" t="s">
-        <v>768</v>
+        <v>975</v>
       </c>
       <c r="S147" s="11" t="s">
-        <v>768</v>
+        <v>975</v>
       </c>
       <c r="U147" s="1" t="s">
         <v>155</v>
@@ -13711,60 +13992,62 @@
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="11" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="D148" s="11" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="E148" s="1">
         <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>974</v>
-      </c>
-      <c r="G148" s="12" t="s">
-        <v>772</v>
-      </c>
-      <c r="H148" s="11" t="s">
-        <v>772</v>
-      </c>
-      <c r="I148" s="13" t="s">
-        <v>773</v>
+        <v>978</v>
+      </c>
+      <c r="G148" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="H148" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="I148" s="9" t="s">
+        <v>980</v>
       </c>
       <c r="J148" s="1">
-        <v>0</v>
+        <f t="shared" si="54"/>
+        <v>250</v>
       </c>
       <c r="K148" s="1">
-        <f t="shared" si="54"/>
-        <v>1700</v>
+        <f t="shared" si="49"/>
+        <v>13900</v>
       </c>
       <c r="L148" s="1">
-        <f t="shared" si="55"/>
-        <v>1400</v>
+        <f t="shared" si="50"/>
+        <v>15500</v>
       </c>
       <c r="M148" s="1">
-        <f t="shared" si="56"/>
-        <v>1100</v>
+        <f t="shared" si="51"/>
+        <v>5450</v>
       </c>
       <c r="N148" s="1">
-        <f t="shared" si="57"/>
-        <v>1100</v>
+        <f t="shared" si="52"/>
+        <v>5450</v>
       </c>
       <c r="O148" s="3">
-        <f t="shared" si="58"/>
-        <v>37</v>
-      </c>
-      <c r="P148" s="6">
-        <v>0</v>
+        <f t="shared" si="53"/>
+        <v>93</v>
+      </c>
+      <c r="P148" s="3">
+        <f t="shared" si="44"/>
+        <v>102</v>
       </c>
       <c r="Q148" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="R148" s="11" t="s">
-        <v>774</v>
+        <v>981</v>
       </c>
       <c r="S148" s="11" t="s">
-        <v>774</v>
+        <v>981</v>
       </c>
       <c r="U148" s="1" t="s">
         <v>155</v>
@@ -13777,60 +14060,62 @@
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="11" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="D149" s="11" t="s">
-        <v>976</v>
+        <v>983</v>
       </c>
       <c r="E149" s="1">
         <v>4</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>977</v>
-      </c>
-      <c r="G149" s="12" t="s">
-        <v>778</v>
-      </c>
-      <c r="H149" s="11" t="s">
-        <v>778</v>
-      </c>
-      <c r="I149" s="13" t="s">
-        <v>779</v>
+        <v>984</v>
+      </c>
+      <c r="G149" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="H149" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="I149" s="9" t="s">
+        <v>986</v>
       </c>
       <c r="J149" s="1">
-        <v>0</v>
+        <f t="shared" si="54"/>
+        <v>1250</v>
       </c>
       <c r="K149" s="1">
-        <f t="shared" si="54"/>
-        <v>1800</v>
+        <f t="shared" si="49"/>
+        <v>14500</v>
       </c>
       <c r="L149" s="1">
-        <f t="shared" si="55"/>
-        <v>1500</v>
+        <f t="shared" si="50"/>
+        <v>16100</v>
       </c>
       <c r="M149" s="1">
-        <f t="shared" si="56"/>
-        <v>1150</v>
+        <f t="shared" si="51"/>
+        <v>5700</v>
       </c>
       <c r="N149" s="1">
-        <f t="shared" si="57"/>
-        <v>1150</v>
+        <f t="shared" si="52"/>
+        <v>5700</v>
       </c>
       <c r="O149" s="3">
-        <f t="shared" si="58"/>
-        <v>38</v>
-      </c>
-      <c r="P149" s="6">
-        <v>0</v>
+        <f t="shared" si="53"/>
+        <v>96</v>
+      </c>
+      <c r="P149" s="3">
+        <f t="shared" si="44"/>
+        <v>106</v>
       </c>
       <c r="Q149" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="R149" s="11" t="s">
-        <v>780</v>
+        <v>987</v>
       </c>
       <c r="S149" s="11" t="s">
-        <v>780</v>
+        <v>987</v>
       </c>
       <c r="U149" s="1" t="s">
         <v>155</v>
@@ -13843,60 +14128,62 @@
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="11" t="s">
-        <v>978</v>
+        <v>988</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>979</v>
+        <v>989</v>
       </c>
       <c r="E150" s="1">
         <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>980</v>
-      </c>
-      <c r="G150" s="12" t="s">
-        <v>784</v>
-      </c>
-      <c r="H150" s="11" t="s">
-        <v>784</v>
-      </c>
-      <c r="I150" s="13" t="s">
-        <v>785</v>
+        <v>990</v>
+      </c>
+      <c r="G150" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="H150" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="I150" s="9" t="s">
+        <v>992</v>
       </c>
       <c r="J150" s="1">
-        <v>0</v>
+        <f t="shared" si="54"/>
+        <v>6250</v>
       </c>
       <c r="K150" s="1">
-        <f t="shared" si="54"/>
-        <v>1900</v>
+        <f t="shared" si="49"/>
+        <v>15100</v>
       </c>
       <c r="L150" s="1">
-        <f t="shared" si="55"/>
-        <v>1600</v>
+        <f t="shared" si="50"/>
+        <v>16700</v>
       </c>
       <c r="M150" s="1">
-        <f t="shared" si="56"/>
-        <v>1200</v>
+        <f t="shared" si="51"/>
+        <v>5950</v>
       </c>
       <c r="N150" s="1">
-        <f t="shared" si="57"/>
-        <v>1200</v>
+        <f t="shared" si="52"/>
+        <v>5950</v>
       </c>
       <c r="O150" s="3">
-        <f t="shared" si="58"/>
-        <v>39</v>
-      </c>
-      <c r="P150" s="6">
-        <v>0</v>
+        <f t="shared" si="53"/>
+        <v>99</v>
+      </c>
+      <c r="P150" s="3">
+        <f t="shared" si="44"/>
+        <v>110</v>
       </c>
       <c r="Q150" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="R150" s="11" t="s">
-        <v>786</v>
+        <v>993</v>
       </c>
       <c r="S150" s="11" t="s">
-        <v>786</v>
+        <v>993</v>
       </c>
       <c r="U150" s="1" t="s">
         <v>155</v>
@@ -13909,60 +14196,62 @@
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="11" t="s">
-        <v>981</v>
+        <v>994</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>982</v>
+        <v>995</v>
       </c>
       <c r="E151" s="1">
         <v>4</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>983</v>
-      </c>
-      <c r="G151" s="12" t="s">
-        <v>790</v>
-      </c>
-      <c r="H151" s="11" t="s">
-        <v>790</v>
-      </c>
-      <c r="I151" s="13" t="s">
-        <v>791</v>
+        <v>996</v>
+      </c>
+      <c r="G151" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="H151" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="I151" s="9" t="s">
+        <v>998</v>
       </c>
       <c r="J151" s="1">
-        <v>0</v>
+        <f t="shared" si="54"/>
+        <v>31250</v>
       </c>
       <c r="K151" s="1">
-        <f t="shared" ref="K151:K164" si="59">K150+200</f>
-        <v>2100</v>
+        <f t="shared" si="49"/>
+        <v>15700</v>
       </c>
       <c r="L151" s="1">
-        <f t="shared" ref="L151:L164" si="60">L150+300</f>
-        <v>1900</v>
+        <f t="shared" si="50"/>
+        <v>17300</v>
       </c>
       <c r="M151" s="1">
-        <f t="shared" si="56"/>
-        <v>1250</v>
+        <f t="shared" si="51"/>
+        <v>6200</v>
       </c>
       <c r="N151" s="1">
-        <f t="shared" si="57"/>
-        <v>1250</v>
+        <f t="shared" si="52"/>
+        <v>6200</v>
       </c>
       <c r="O151" s="3">
-        <f t="shared" si="58"/>
-        <v>40</v>
-      </c>
-      <c r="P151" s="6">
-        <v>0</v>
+        <f t="shared" si="53"/>
+        <v>102</v>
+      </c>
+      <c r="P151" s="3">
+        <f t="shared" si="44"/>
+        <v>114</v>
       </c>
       <c r="Q151" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="R151" s="11" t="s">
-        <v>792</v>
+        <v>999</v>
       </c>
       <c r="S151" s="11" t="s">
-        <v>792</v>
+        <v>999</v>
       </c>
       <c r="U151" s="1" t="s">
         <v>155</v>
@@ -13977,60 +14266,62 @@
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="11" t="s">
-        <v>984</v>
+        <v>1000</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>985</v>
+        <v>1001</v>
       </c>
       <c r="E152" s="1">
         <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>986</v>
-      </c>
-      <c r="G152" s="12" t="s">
-        <v>796</v>
-      </c>
-      <c r="H152" s="11" t="s">
-        <v>796</v>
-      </c>
-      <c r="I152" s="13" t="s">
-        <v>797</v>
+        <v>1002</v>
+      </c>
+      <c r="G152" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H152" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I152" s="9" t="s">
+        <v>1004</v>
       </c>
       <c r="J152" s="1">
-        <v>0</v>
+        <f t="shared" si="54"/>
+        <v>156250</v>
       </c>
       <c r="K152" s="1">
-        <f t="shared" si="59"/>
-        <v>2300</v>
+        <f t="shared" si="49"/>
+        <v>16300</v>
       </c>
       <c r="L152" s="1">
-        <f t="shared" si="60"/>
-        <v>2200</v>
+        <f t="shared" si="50"/>
+        <v>17900</v>
       </c>
       <c r="M152" s="1">
-        <f t="shared" si="56"/>
-        <v>1300</v>
+        <f t="shared" si="51"/>
+        <v>6450</v>
       </c>
       <c r="N152" s="1">
-        <f t="shared" si="57"/>
-        <v>1300</v>
+        <f t="shared" si="52"/>
+        <v>6450</v>
       </c>
       <c r="O152" s="3">
-        <f t="shared" si="58"/>
-        <v>41</v>
-      </c>
-      <c r="P152" s="6">
-        <v>0</v>
+        <f t="shared" si="53"/>
+        <v>105</v>
+      </c>
+      <c r="P152" s="3">
+        <f t="shared" si="44"/>
+        <v>118</v>
       </c>
       <c r="Q152" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="R152" s="11" t="s">
-        <v>798</v>
+        <v>1005</v>
       </c>
       <c r="S152" s="11" t="s">
-        <v>798</v>
+        <v>1005</v>
       </c>
       <c r="U152" s="1" t="s">
         <v>155</v>
@@ -14045,60 +14336,62 @@
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="11" t="s">
-        <v>987</v>
+        <v>1006</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>988</v>
+        <v>1007</v>
       </c>
       <c r="E153" s="1">
         <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>989</v>
-      </c>
-      <c r="G153" s="12" t="s">
-        <v>802</v>
-      </c>
-      <c r="H153" s="11" t="s">
-        <v>802</v>
-      </c>
-      <c r="I153" s="13" t="s">
-        <v>803</v>
+        <v>1008</v>
+      </c>
+      <c r="G153" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="H153" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I153" s="9" t="s">
+        <v>1010</v>
       </c>
       <c r="J153" s="1">
-        <v>0</v>
+        <f t="shared" si="54"/>
+        <v>781250</v>
       </c>
       <c r="K153" s="1">
-        <f t="shared" si="59"/>
-        <v>2500</v>
+        <f t="shared" si="49"/>
+        <v>16900</v>
       </c>
       <c r="L153" s="1">
-        <f t="shared" si="60"/>
-        <v>2500</v>
+        <f t="shared" si="50"/>
+        <v>18500</v>
       </c>
       <c r="M153" s="1">
-        <f t="shared" si="56"/>
-        <v>1350</v>
+        <f t="shared" si="51"/>
+        <v>6700</v>
       </c>
       <c r="N153" s="1">
-        <f t="shared" si="57"/>
-        <v>1350</v>
+        <f t="shared" si="52"/>
+        <v>6700</v>
       </c>
       <c r="O153" s="3">
-        <f t="shared" si="58"/>
-        <v>42</v>
-      </c>
-      <c r="P153" s="6">
-        <v>0</v>
+        <f t="shared" si="53"/>
+        <v>108</v>
+      </c>
+      <c r="P153" s="3">
+        <f t="shared" si="44"/>
+        <v>122</v>
       </c>
       <c r="Q153" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="R153" s="11" t="s">
-        <v>804</v>
+        <v>1011</v>
       </c>
       <c r="S153" s="11" t="s">
-        <v>804</v>
+        <v>1011</v>
       </c>
       <c r="U153" s="1" t="s">
         <v>155</v>
@@ -14113,60 +14406,62 @@
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="11" t="s">
-        <v>990</v>
+        <v>1012</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>991</v>
+        <v>1013</v>
       </c>
       <c r="E154" s="1">
         <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>992</v>
-      </c>
-      <c r="G154" s="12" t="s">
-        <v>808</v>
-      </c>
-      <c r="H154" s="11" t="s">
-        <v>808</v>
-      </c>
-      <c r="I154" s="13" t="s">
-        <v>809</v>
+        <v>1014</v>
+      </c>
+      <c r="G154" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H154" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="I154" s="9" t="s">
+        <v>1016</v>
       </c>
       <c r="J154" s="1">
-        <v>0</v>
+        <f t="shared" si="54"/>
+        <v>3906250</v>
       </c>
       <c r="K154" s="1">
-        <f t="shared" si="59"/>
-        <v>2700</v>
+        <f t="shared" si="49"/>
+        <v>17500</v>
       </c>
       <c r="L154" s="1">
-        <f t="shared" si="60"/>
-        <v>2800</v>
+        <f t="shared" si="50"/>
+        <v>19100</v>
       </c>
       <c r="M154" s="1">
-        <f t="shared" si="56"/>
-        <v>1400</v>
+        <f t="shared" si="51"/>
+        <v>6950</v>
       </c>
       <c r="N154" s="1">
-        <f t="shared" si="57"/>
-        <v>1400</v>
+        <f t="shared" si="52"/>
+        <v>6950</v>
       </c>
       <c r="O154" s="3">
-        <f t="shared" si="58"/>
-        <v>43</v>
-      </c>
-      <c r="P154" s="6">
-        <v>0</v>
+        <f t="shared" si="53"/>
+        <v>111</v>
+      </c>
+      <c r="P154" s="3">
+        <f t="shared" si="44"/>
+        <v>126</v>
       </c>
       <c r="Q154" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="R154" s="11" t="s">
-        <v>810</v>
+        <v>1017</v>
       </c>
       <c r="S154" s="11" t="s">
-        <v>810</v>
+        <v>1017</v>
       </c>
       <c r="U154" s="1" t="s">
         <v>155</v>
@@ -14181,60 +14476,62 @@
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="11" t="s">
-        <v>993</v>
+        <v>1018</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>994</v>
+        <v>1019</v>
       </c>
       <c r="E155" s="1">
         <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>995</v>
-      </c>
-      <c r="G155" s="12" t="s">
-        <v>814</v>
-      </c>
-      <c r="H155" s="11" t="s">
-        <v>814</v>
-      </c>
-      <c r="I155" s="13" t="s">
-        <v>815</v>
+        <v>1020</v>
+      </c>
+      <c r="G155" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H155" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I155" s="9" t="s">
+        <v>1022</v>
       </c>
       <c r="J155" s="1">
-        <v>0</v>
+        <f t="shared" si="54"/>
+        <v>19531250</v>
       </c>
       <c r="K155" s="1">
-        <f t="shared" si="59"/>
-        <v>2900</v>
+        <f t="shared" si="49"/>
+        <v>18100</v>
       </c>
       <c r="L155" s="1">
-        <f t="shared" si="60"/>
-        <v>3100</v>
+        <f t="shared" si="50"/>
+        <v>19700</v>
       </c>
       <c r="M155" s="1">
-        <f t="shared" si="56"/>
-        <v>1450</v>
+        <f t="shared" si="51"/>
+        <v>7200</v>
       </c>
       <c r="N155" s="1">
-        <f t="shared" si="57"/>
-        <v>1450</v>
+        <f t="shared" si="52"/>
+        <v>7200</v>
       </c>
       <c r="O155" s="3">
-        <f t="shared" si="58"/>
-        <v>44</v>
-      </c>
-      <c r="P155" s="6">
-        <v>0</v>
+        <f t="shared" si="53"/>
+        <v>114</v>
+      </c>
+      <c r="P155" s="3">
+        <f t="shared" si="44"/>
+        <v>130</v>
       </c>
       <c r="Q155" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="R155" s="11" t="s">
-        <v>816</v>
+        <v>1023</v>
       </c>
       <c r="S155" s="11" t="s">
-        <v>816</v>
+        <v>1023</v>
       </c>
       <c r="U155" s="1" t="s">
         <v>155</v>
@@ -14247,55 +14544,55 @@
     </row>
     <row r="156" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C156" s="11" t="s">
-        <v>996</v>
+        <v>1024</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>997</v>
+        <v>1025</v>
       </c>
       <c r="E156" s="1">
         <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>998</v>
-      </c>
-      <c r="G156" s="12" t="s">
-        <v>761</v>
-      </c>
-      <c r="H156" s="11" t="s">
-        <v>761</v>
-      </c>
-      <c r="I156" s="13" t="s">
-        <v>820</v>
-      </c>
-      <c r="J156" s="1">
-        <v>0</v>
+        <v>1026</v>
+      </c>
+      <c r="G156" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H156" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="I156" s="9" t="s">
+        <v>1028</v>
+      </c>
+      <c r="J156" s="1" t="s">
+        <v>1029</v>
       </c>
       <c r="K156" s="1">
-        <f t="shared" si="59"/>
-        <v>3100</v>
+        <f t="shared" si="49"/>
+        <v>18700</v>
       </c>
       <c r="L156" s="1">
-        <f t="shared" si="60"/>
-        <v>3400</v>
+        <f t="shared" si="50"/>
+        <v>20300</v>
       </c>
       <c r="M156" s="1">
-        <f t="shared" si="56"/>
-        <v>1500</v>
+        <f t="shared" si="51"/>
+        <v>7450</v>
       </c>
       <c r="N156" s="1">
-        <f t="shared" si="57"/>
-        <v>1500</v>
+        <f t="shared" si="52"/>
+        <v>7450</v>
       </c>
       <c r="O156" s="3">
-        <f t="shared" si="58"/>
-        <v>45</v>
+        <f t="shared" si="53"/>
+        <v>117</v>
       </c>
       <c r="P156" s="3">
-        <f t="shared" ref="P156:P165" si="61">P155+3</f>
-        <v>3</v>
+        <f t="shared" si="44"/>
+        <v>134</v>
       </c>
       <c r="Q156" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="R156" s="11" t="s">
         <v>821</v>
@@ -14314,55 +14611,55 @@
     </row>
     <row r="157" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C157" s="11" t="s">
-        <v>999</v>
+        <v>1030</v>
       </c>
       <c r="D157" s="11" t="s">
-        <v>1000</v>
+        <v>1031</v>
       </c>
       <c r="E157" s="1">
         <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>1001</v>
-      </c>
-      <c r="G157" s="12" t="s">
-        <v>825</v>
-      </c>
-      <c r="H157" s="11" t="s">
-        <v>825</v>
-      </c>
-      <c r="I157" s="13" t="s">
-        <v>826</v>
-      </c>
-      <c r="J157" s="1">
-        <v>0</v>
+        <v>1032</v>
+      </c>
+      <c r="G157" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H157" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="I157" s="9" t="s">
+        <v>1034</v>
+      </c>
+      <c r="J157" s="1" t="s">
+        <v>1035</v>
       </c>
       <c r="K157" s="1">
-        <f t="shared" si="59"/>
-        <v>3300</v>
+        <f t="shared" si="49"/>
+        <v>19300</v>
       </c>
       <c r="L157" s="1">
-        <f t="shared" si="60"/>
-        <v>3700</v>
+        <f t="shared" si="50"/>
+        <v>20900</v>
       </c>
       <c r="M157" s="1">
-        <f t="shared" si="56"/>
-        <v>1550</v>
+        <f t="shared" si="51"/>
+        <v>7700</v>
       </c>
       <c r="N157" s="1">
-        <f t="shared" si="57"/>
-        <v>1550</v>
+        <f t="shared" si="52"/>
+        <v>7700</v>
       </c>
       <c r="O157" s="3">
-        <f t="shared" si="58"/>
-        <v>46</v>
+        <f t="shared" si="53"/>
+        <v>120</v>
       </c>
       <c r="P157" s="3">
-        <f t="shared" si="61"/>
-        <v>6</v>
+        <f t="shared" si="44"/>
+        <v>138</v>
       </c>
       <c r="Q157" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="R157" s="11" t="s">
         <v>827</v>
@@ -14381,55 +14678,55 @@
     </row>
     <row r="158" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C158" s="11" t="s">
-        <v>1002</v>
+        <v>1036</v>
       </c>
       <c r="D158" s="11" t="s">
-        <v>1003</v>
+        <v>1037</v>
       </c>
       <c r="E158" s="1">
         <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G158" s="12" t="s">
-        <v>831</v>
-      </c>
-      <c r="H158" s="11" t="s">
-        <v>831</v>
-      </c>
-      <c r="I158" s="13" t="s">
-        <v>832</v>
-      </c>
-      <c r="J158" s="1">
-        <v>0</v>
+        <v>1038</v>
+      </c>
+      <c r="G158" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H158" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I158" s="9" t="s">
+        <v>1040</v>
+      </c>
+      <c r="J158" s="1" t="s">
+        <v>1041</v>
       </c>
       <c r="K158" s="1">
-        <f t="shared" si="59"/>
-        <v>3500</v>
+        <f t="shared" si="49"/>
+        <v>19900</v>
       </c>
       <c r="L158" s="1">
-        <f t="shared" si="60"/>
-        <v>4000</v>
+        <f t="shared" si="50"/>
+        <v>21500</v>
       </c>
       <c r="M158" s="1">
-        <f t="shared" si="56"/>
-        <v>1600</v>
+        <f t="shared" si="51"/>
+        <v>7950</v>
       </c>
       <c r="N158" s="1">
-        <f t="shared" si="57"/>
-        <v>1600</v>
+        <f t="shared" si="52"/>
+        <v>7950</v>
       </c>
       <c r="O158" s="3">
-        <f t="shared" si="58"/>
-        <v>47</v>
+        <f t="shared" si="53"/>
+        <v>123</v>
       </c>
       <c r="P158" s="3">
-        <f t="shared" si="61"/>
-        <v>9</v>
+        <f t="shared" si="44"/>
+        <v>142</v>
       </c>
       <c r="Q158" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="R158" s="11" t="s">
         <v>833</v>
@@ -14448,55 +14745,55 @@
     </row>
     <row r="159" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C159" s="11" t="s">
-        <v>1005</v>
+        <v>1042</v>
       </c>
       <c r="D159" s="11" t="s">
-        <v>1006</v>
+        <v>1043</v>
       </c>
       <c r="E159" s="1">
         <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1007</v>
-      </c>
-      <c r="G159" s="12" t="s">
-        <v>837</v>
-      </c>
-      <c r="H159" s="11" t="s">
-        <v>837</v>
-      </c>
-      <c r="I159" s="13" t="s">
-        <v>838</v>
-      </c>
-      <c r="J159" s="1">
-        <v>0</v>
+        <v>1044</v>
+      </c>
+      <c r="G159" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="H159" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I159" s="9" t="s">
+        <v>1046</v>
+      </c>
+      <c r="J159" s="1" t="s">
+        <v>1047</v>
       </c>
       <c r="K159" s="1">
-        <f t="shared" si="59"/>
-        <v>3700</v>
+        <f t="shared" si="49"/>
+        <v>20500</v>
       </c>
       <c r="L159" s="1">
-        <f t="shared" si="60"/>
-        <v>4300</v>
+        <f t="shared" si="50"/>
+        <v>22100</v>
       </c>
       <c r="M159" s="1">
-        <f t="shared" si="56"/>
-        <v>1650</v>
+        <f t="shared" si="51"/>
+        <v>8200</v>
       </c>
       <c r="N159" s="1">
-        <f t="shared" si="57"/>
-        <v>1650</v>
+        <f t="shared" si="52"/>
+        <v>8200</v>
       </c>
       <c r="O159" s="3">
-        <f t="shared" si="58"/>
-        <v>48</v>
+        <f t="shared" si="53"/>
+        <v>126</v>
       </c>
       <c r="P159" s="3">
-        <f t="shared" si="61"/>
-        <v>12</v>
+        <f t="shared" si="44"/>
+        <v>146</v>
       </c>
       <c r="Q159" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="R159" s="11" t="s">
         <v>839</v>
@@ -14515,55 +14812,55 @@
     </row>
     <row r="160" s="1" customFormat="1" customHeight="1" spans="3:24">
       <c r="C160" s="11" t="s">
-        <v>1008</v>
+        <v>1048</v>
       </c>
       <c r="D160" s="11" t="s">
-        <v>1009</v>
+        <v>1049</v>
       </c>
       <c r="E160" s="1">
         <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G160" s="12" t="s">
-        <v>843</v>
-      </c>
-      <c r="H160" s="11" t="s">
-        <v>843</v>
-      </c>
-      <c r="I160" s="13" t="s">
-        <v>844</v>
-      </c>
-      <c r="J160" s="1">
-        <v>0</v>
+        <v>1050</v>
+      </c>
+      <c r="G160" s="4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H160" s="4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="I160" s="9" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J160" s="1" t="s">
+        <v>1053</v>
       </c>
       <c r="K160" s="1">
-        <f t="shared" si="59"/>
-        <v>3900</v>
+        <f t="shared" si="49"/>
+        <v>21100</v>
       </c>
       <c r="L160" s="1">
-        <f t="shared" si="60"/>
-        <v>4600</v>
+        <f t="shared" si="50"/>
+        <v>22700</v>
       </c>
       <c r="M160" s="1">
-        <f t="shared" si="56"/>
-        <v>1700</v>
+        <f t="shared" si="51"/>
+        <v>8450</v>
       </c>
       <c r="N160" s="1">
-        <f t="shared" si="57"/>
-        <v>1700</v>
+        <f t="shared" si="52"/>
+        <v>8450</v>
       </c>
       <c r="O160" s="3">
-        <f t="shared" si="58"/>
-        <v>49</v>
+        <f t="shared" si="53"/>
+        <v>129</v>
       </c>
       <c r="P160" s="3">
-        <f t="shared" si="61"/>
-        <v>15</v>
+        <f t="shared" si="44"/>
+        <v>150</v>
       </c>
       <c r="Q160" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="R160" s="11" t="s">
         <v>845</v>
@@ -14584,55 +14881,55 @@
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="11" t="s">
-        <v>1011</v>
+        <v>1054</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>1012</v>
+        <v>1055</v>
       </c>
       <c r="E161" s="1">
         <v>4</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>1013</v>
-      </c>
-      <c r="G161" s="12" t="s">
-        <v>849</v>
-      </c>
-      <c r="H161" s="11" t="s">
-        <v>849</v>
-      </c>
-      <c r="I161" s="13" t="s">
-        <v>850</v>
-      </c>
-      <c r="J161" s="1">
-        <v>0</v>
+        <v>1056</v>
+      </c>
+      <c r="G161" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H161" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="I161" s="9" t="s">
+        <v>1058</v>
+      </c>
+      <c r="J161" s="1" t="s">
+        <v>1059</v>
       </c>
       <c r="K161" s="1">
-        <f t="shared" si="59"/>
-        <v>4100</v>
+        <f t="shared" si="49"/>
+        <v>21700</v>
       </c>
       <c r="L161" s="1">
-        <f t="shared" si="60"/>
-        <v>4900</v>
+        <f t="shared" si="50"/>
+        <v>23300</v>
       </c>
       <c r="M161" s="1">
-        <f t="shared" si="56"/>
-        <v>1750</v>
+        <f t="shared" si="51"/>
+        <v>8700</v>
       </c>
       <c r="N161" s="1">
-        <f t="shared" si="57"/>
-        <v>1750</v>
+        <f t="shared" si="52"/>
+        <v>8700</v>
       </c>
       <c r="O161" s="3">
-        <f t="shared" si="58"/>
-        <v>50</v>
+        <f t="shared" si="53"/>
+        <v>132</v>
       </c>
       <c r="P161" s="3">
-        <f t="shared" si="61"/>
-        <v>18</v>
+        <f t="shared" si="44"/>
+        <v>154</v>
       </c>
       <c r="Q161" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="R161" s="11" t="s">
         <v>851</v>
@@ -14653,55 +14950,55 @@
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="11" t="s">
-        <v>1014</v>
+        <v>1060</v>
       </c>
       <c r="D162" s="11" t="s">
-        <v>1015</v>
+        <v>1061</v>
       </c>
       <c r="E162" s="1">
         <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1016</v>
-      </c>
-      <c r="G162" s="12" t="s">
-        <v>855</v>
-      </c>
-      <c r="H162" s="11" t="s">
-        <v>855</v>
-      </c>
-      <c r="I162" s="13" t="s">
-        <v>856</v>
-      </c>
-      <c r="J162" s="1">
-        <v>0</v>
+        <v>1062</v>
+      </c>
+      <c r="G162" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="H162" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="I162" s="9" t="s">
+        <v>1064</v>
+      </c>
+      <c r="J162" s="1" t="s">
+        <v>1065</v>
       </c>
       <c r="K162" s="1">
-        <f t="shared" si="59"/>
-        <v>4300</v>
+        <f t="shared" si="49"/>
+        <v>22300</v>
       </c>
       <c r="L162" s="1">
-        <f t="shared" si="60"/>
-        <v>5200</v>
+        <f t="shared" si="50"/>
+        <v>23900</v>
       </c>
       <c r="M162" s="1">
-        <f t="shared" si="56"/>
-        <v>1800</v>
+        <f t="shared" si="51"/>
+        <v>8950</v>
       </c>
       <c r="N162" s="1">
-        <f t="shared" si="57"/>
-        <v>1800</v>
+        <f t="shared" si="52"/>
+        <v>8950</v>
       </c>
       <c r="O162" s="3">
-        <f t="shared" si="58"/>
-        <v>51</v>
+        <f t="shared" si="53"/>
+        <v>135</v>
       </c>
       <c r="P162" s="3">
-        <f t="shared" si="61"/>
-        <v>21</v>
+        <f t="shared" si="44"/>
+        <v>158</v>
       </c>
       <c r="Q162" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="R162" s="11" t="s">
         <v>857</v>
@@ -14722,55 +15019,55 @@
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="11" t="s">
-        <v>1017</v>
+        <v>1066</v>
       </c>
       <c r="D163" s="11" t="s">
-        <v>1018</v>
+        <v>1067</v>
       </c>
       <c r="E163" s="1">
         <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1019</v>
-      </c>
-      <c r="G163" s="12" t="s">
-        <v>861</v>
-      </c>
-      <c r="H163" s="11" t="s">
-        <v>861</v>
-      </c>
-      <c r="I163" s="13" t="s">
-        <v>862</v>
-      </c>
-      <c r="J163" s="1">
-        <v>0</v>
+        <v>1068</v>
+      </c>
+      <c r="G163" s="4" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H163" s="4" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I163" s="9" t="s">
+        <v>1070</v>
+      </c>
+      <c r="J163" s="1" t="s">
+        <v>1071</v>
       </c>
       <c r="K163" s="1">
-        <f t="shared" si="59"/>
-        <v>4500</v>
+        <f t="shared" si="49"/>
+        <v>22900</v>
       </c>
       <c r="L163" s="1">
-        <f t="shared" si="60"/>
-        <v>5500</v>
+        <f t="shared" si="50"/>
+        <v>24500</v>
       </c>
       <c r="M163" s="1">
-        <f t="shared" si="56"/>
-        <v>1850</v>
+        <f t="shared" si="51"/>
+        <v>9200</v>
       </c>
       <c r="N163" s="1">
-        <f t="shared" si="57"/>
-        <v>1850</v>
+        <f t="shared" si="52"/>
+        <v>9200</v>
       </c>
       <c r="O163" s="3">
-        <f t="shared" si="58"/>
-        <v>52</v>
+        <f t="shared" si="53"/>
+        <v>138</v>
       </c>
       <c r="P163" s="3">
-        <f t="shared" si="61"/>
-        <v>24</v>
+        <f t="shared" si="44"/>
+        <v>162</v>
       </c>
       <c r="Q163" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="R163" s="11" t="s">
         <v>863</v>
@@ -14791,55 +15088,55 @@
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="11" t="s">
-        <v>1020</v>
+        <v>1072</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>1021</v>
+        <v>1073</v>
       </c>
       <c r="E164" s="1">
         <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1022</v>
-      </c>
-      <c r="G164" s="12" t="s">
-        <v>867</v>
-      </c>
-      <c r="H164" s="11" t="s">
-        <v>867</v>
-      </c>
-      <c r="I164" s="13" t="s">
-        <v>868</v>
-      </c>
-      <c r="J164" s="1">
-        <v>0</v>
+        <v>1074</v>
+      </c>
+      <c r="G164" s="4" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H164" s="4" t="s">
+        <v>1075</v>
+      </c>
+      <c r="I164" s="9" t="s">
+        <v>1076</v>
+      </c>
+      <c r="J164" s="1" t="s">
+        <v>1077</v>
       </c>
       <c r="K164" s="1">
-        <f t="shared" si="59"/>
-        <v>4700</v>
+        <f t="shared" si="49"/>
+        <v>23500</v>
       </c>
       <c r="L164" s="1">
-        <f t="shared" si="60"/>
-        <v>5800</v>
+        <f t="shared" si="50"/>
+        <v>25100</v>
       </c>
       <c r="M164" s="1">
-        <f t="shared" si="56"/>
-        <v>1900</v>
+        <f t="shared" si="51"/>
+        <v>9450</v>
       </c>
       <c r="N164" s="1">
-        <f t="shared" si="57"/>
-        <v>1900</v>
+        <f t="shared" si="52"/>
+        <v>9450</v>
       </c>
       <c r="O164" s="3">
-        <f t="shared" si="58"/>
-        <v>53</v>
+        <f t="shared" si="53"/>
+        <v>141</v>
       </c>
       <c r="P164" s="3">
-        <f t="shared" si="61"/>
-        <v>27</v>
+        <f t="shared" si="44"/>
+        <v>166</v>
       </c>
       <c r="Q164" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="R164" s="11" t="s">
         <v>869</v>
@@ -14860,55 +15157,55 @@
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="11" t="s">
-        <v>1023</v>
+        <v>1078</v>
       </c>
       <c r="D165" s="11" t="s">
-        <v>1024</v>
+        <v>1079</v>
       </c>
       <c r="E165" s="1">
         <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G165" s="12" t="s">
-        <v>873</v>
-      </c>
-      <c r="H165" s="11" t="s">
-        <v>873</v>
-      </c>
-      <c r="I165" s="13" t="s">
-        <v>874</v>
-      </c>
-      <c r="J165" s="1">
-        <v>0</v>
+        <v>1080</v>
+      </c>
+      <c r="G165" s="4" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H165" s="4" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I165" s="9" t="s">
+        <v>1082</v>
+      </c>
+      <c r="J165" s="1" t="s">
+        <v>1083</v>
       </c>
       <c r="K165" s="1">
-        <f t="shared" ref="K165:K170" si="62">K164+300</f>
-        <v>5000</v>
+        <f t="shared" si="49"/>
+        <v>24100</v>
       </c>
       <c r="L165" s="1">
-        <f t="shared" ref="L165:L170" si="63">L164+400</f>
-        <v>6200</v>
+        <f t="shared" si="50"/>
+        <v>25700</v>
       </c>
       <c r="M165" s="1">
-        <f t="shared" si="56"/>
-        <v>1950</v>
+        <f t="shared" si="51"/>
+        <v>9700</v>
       </c>
       <c r="N165" s="1">
-        <f t="shared" si="57"/>
-        <v>1950</v>
+        <f t="shared" si="52"/>
+        <v>9700</v>
       </c>
       <c r="O165" s="3">
-        <f t="shared" si="58"/>
-        <v>54</v>
+        <f t="shared" si="53"/>
+        <v>144</v>
       </c>
       <c r="P165" s="3">
-        <f t="shared" si="61"/>
-        <v>30</v>
+        <f t="shared" si="44"/>
+        <v>170</v>
       </c>
       <c r="Q165" s="3">
-        <v>90</v>
+        <v>99.99</v>
       </c>
       <c r="R165" s="11" t="s">
         <v>875</v>
@@ -14927,55 +15224,55 @@
     </row>
     <row r="166" customHeight="1" spans="3:22">
       <c r="C166" s="11" t="s">
-        <v>1026</v>
+        <v>1084</v>
       </c>
       <c r="D166" s="11" t="s">
-        <v>1027</v>
+        <v>1085</v>
       </c>
       <c r="E166" s="1">
         <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1028</v>
-      </c>
-      <c r="G166" s="12" t="s">
-        <v>879</v>
-      </c>
-      <c r="H166" s="11" t="s">
-        <v>879</v>
-      </c>
-      <c r="I166" s="13" t="s">
-        <v>880</v>
-      </c>
-      <c r="J166" s="1">
-        <v>0</v>
+        <v>1086</v>
+      </c>
+      <c r="G166" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H166" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I166" s="9" t="s">
+        <v>1088</v>
+      </c>
+      <c r="J166" s="1" t="s">
+        <v>1089</v>
       </c>
       <c r="K166" s="1">
-        <f>K165+400</f>
-        <v>5400</v>
+        <f t="shared" si="49"/>
+        <v>24700</v>
       </c>
       <c r="L166" s="1">
-        <f t="shared" si="63"/>
-        <v>6600</v>
+        <f t="shared" si="50"/>
+        <v>26300</v>
       </c>
       <c r="M166" s="1">
-        <f t="shared" ref="M166:M170" si="64">M165+100</f>
-        <v>2050</v>
+        <f t="shared" si="51"/>
+        <v>9950</v>
       </c>
       <c r="N166" s="1">
-        <f t="shared" ref="N166:N170" si="65">N165+100</f>
-        <v>2050</v>
+        <f t="shared" si="52"/>
+        <v>9950</v>
       </c>
       <c r="O166" s="3">
-        <f t="shared" ref="O166:O180" si="66">O165+2</f>
-        <v>56</v>
+        <f t="shared" si="53"/>
+        <v>147</v>
       </c>
       <c r="P166" s="3">
-        <f t="shared" ref="P166:P180" si="67">P165+4</f>
-        <v>34</v>
+        <f t="shared" si="44"/>
+        <v>174</v>
       </c>
       <c r="Q166" s="3">
-        <v>92</v>
+        <v>99.99</v>
       </c>
       <c r="R166" s="11" t="s">
         <v>881</v>
@@ -14992,55 +15289,55 @@
     </row>
     <row r="167" customHeight="1" spans="3:22">
       <c r="C167" s="11" t="s">
-        <v>1029</v>
+        <v>1090</v>
       </c>
       <c r="D167" s="11" t="s">
-        <v>1030</v>
+        <v>1091</v>
       </c>
       <c r="E167" s="1">
         <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1031</v>
-      </c>
-      <c r="G167" s="12" t="s">
-        <v>885</v>
-      </c>
-      <c r="H167" s="11" t="s">
-        <v>885</v>
-      </c>
-      <c r="I167" s="13" t="s">
-        <v>886</v>
-      </c>
-      <c r="J167" s="1">
-        <v>0</v>
+        <v>1092</v>
+      </c>
+      <c r="G167" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="H167" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="I167" s="9" t="s">
+        <v>1094</v>
+      </c>
+      <c r="J167" s="1" t="s">
+        <v>1095</v>
       </c>
       <c r="K167" s="1">
-        <f t="shared" si="62"/>
-        <v>5700</v>
+        <f t="shared" si="49"/>
+        <v>25300</v>
       </c>
       <c r="L167" s="1">
-        <f t="shared" si="63"/>
-        <v>7000</v>
+        <f t="shared" si="50"/>
+        <v>26900</v>
       </c>
       <c r="M167" s="1">
-        <f t="shared" si="64"/>
-        <v>2150</v>
+        <f t="shared" si="51"/>
+        <v>10200</v>
       </c>
       <c r="N167" s="1">
-        <f t="shared" si="65"/>
-        <v>2150</v>
+        <f t="shared" si="52"/>
+        <v>10200</v>
       </c>
       <c r="O167" s="3">
-        <f t="shared" si="66"/>
-        <v>58</v>
+        <f t="shared" si="53"/>
+        <v>150</v>
       </c>
       <c r="P167" s="3">
-        <f t="shared" si="67"/>
-        <v>38</v>
+        <f t="shared" si="44"/>
+        <v>178</v>
       </c>
       <c r="Q167" s="3">
-        <v>94</v>
+        <v>99.99</v>
       </c>
       <c r="R167" s="11" t="s">
         <v>887</v>
@@ -15057,55 +15354,55 @@
     </row>
     <row r="168" customHeight="1" spans="3:22">
       <c r="C168" s="11" t="s">
-        <v>1032</v>
+        <v>1096</v>
       </c>
       <c r="D168" s="11" t="s">
-        <v>1033</v>
+        <v>1097</v>
       </c>
       <c r="E168" s="1">
         <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1034</v>
-      </c>
-      <c r="G168" s="12" t="s">
-        <v>891</v>
-      </c>
-      <c r="H168" s="11" t="s">
-        <v>891</v>
-      </c>
-      <c r="I168" s="13" t="s">
-        <v>892</v>
-      </c>
-      <c r="J168" s="1">
-        <v>0</v>
+        <v>1098</v>
+      </c>
+      <c r="G168" s="4" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H168" s="4" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I168" s="9" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J168" s="1" t="s">
+        <v>1101</v>
       </c>
       <c r="K168" s="1">
-        <f t="shared" si="62"/>
-        <v>6000</v>
+        <f t="shared" si="49"/>
+        <v>25900</v>
       </c>
       <c r="L168" s="1">
-        <f t="shared" si="63"/>
-        <v>7400</v>
+        <f t="shared" si="50"/>
+        <v>27500</v>
       </c>
       <c r="M168" s="1">
-        <f t="shared" si="64"/>
-        <v>2250</v>
+        <f t="shared" si="51"/>
+        <v>10450</v>
       </c>
       <c r="N168" s="1">
-        <f t="shared" si="65"/>
-        <v>2250</v>
+        <f t="shared" si="52"/>
+        <v>10450</v>
       </c>
       <c r="O168" s="3">
-        <f t="shared" si="66"/>
-        <v>60</v>
+        <f t="shared" si="53"/>
+        <v>153</v>
       </c>
       <c r="P168" s="3">
-        <f t="shared" si="67"/>
-        <v>42</v>
+        <f t="shared" si="44"/>
+        <v>182</v>
       </c>
       <c r="Q168" s="3">
-        <v>96</v>
+        <v>99.99</v>
       </c>
       <c r="R168" s="11" t="s">
         <v>893</v>
@@ -15122,55 +15419,55 @@
     </row>
     <row r="169" customHeight="1" spans="3:22">
       <c r="C169" s="11" t="s">
-        <v>1035</v>
+        <v>1102</v>
       </c>
       <c r="D169" s="11" t="s">
-        <v>1036</v>
+        <v>1103</v>
       </c>
       <c r="E169" s="1">
         <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1037</v>
-      </c>
-      <c r="G169" s="12" t="s">
-        <v>897</v>
-      </c>
-      <c r="H169" s="11" t="s">
-        <v>897</v>
-      </c>
-      <c r="I169" s="13" t="s">
-        <v>898</v>
-      </c>
-      <c r="J169" s="1">
-        <v>0</v>
+        <v>1104</v>
+      </c>
+      <c r="G169" s="4" t="s">
+        <v>1105</v>
+      </c>
+      <c r="H169" s="4" t="s">
+        <v>1105</v>
+      </c>
+      <c r="I169" s="9" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J169" s="1" t="s">
+        <v>1106</v>
       </c>
       <c r="K169" s="1">
-        <f t="shared" si="62"/>
-        <v>6300</v>
+        <f t="shared" si="49"/>
+        <v>26500</v>
       </c>
       <c r="L169" s="1">
-        <f t="shared" si="63"/>
-        <v>7800</v>
+        <f t="shared" si="50"/>
+        <v>28100</v>
       </c>
       <c r="M169" s="1">
-        <f t="shared" si="64"/>
-        <v>2350</v>
+        <f t="shared" si="51"/>
+        <v>10700</v>
       </c>
       <c r="N169" s="1">
-        <f t="shared" si="65"/>
-        <v>2350</v>
+        <f t="shared" si="52"/>
+        <v>10700</v>
       </c>
       <c r="O169" s="3">
-        <f t="shared" si="66"/>
-        <v>62</v>
+        <f t="shared" si="53"/>
+        <v>156</v>
       </c>
       <c r="P169" s="3">
-        <f t="shared" si="67"/>
-        <v>46</v>
+        <f t="shared" si="44"/>
+        <v>186</v>
       </c>
       <c r="Q169" s="3">
-        <v>98</v>
+        <v>99.99</v>
       </c>
       <c r="R169" s="11" t="s">
         <v>899</v>
@@ -15187,10 +15484,10 @@
     </row>
     <row r="170" customHeight="1" spans="3:22">
       <c r="C170" s="11" t="s">
-        <v>1038</v>
+        <v>1107</v>
       </c>
       <c r="D170" s="11" t="s">
-        <v>1039</v>
+        <v>1108</v>
       </c>
       <c r="E170" s="1">
         <v>4</v>
@@ -15198,44 +15495,44 @@
       <c r="F170" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="G170" s="12" t="s">
-        <v>902</v>
-      </c>
-      <c r="H170" s="11" t="s">
-        <v>902</v>
-      </c>
-      <c r="I170" s="13" t="s">
-        <v>903</v>
-      </c>
-      <c r="J170" s="1">
-        <v>0</v>
+      <c r="G170" s="4" t="s">
+        <v>1109</v>
+      </c>
+      <c r="H170" s="4" t="s">
+        <v>1109</v>
+      </c>
+      <c r="I170" s="9" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J170" s="1" t="s">
+        <v>1110</v>
       </c>
       <c r="K170" s="1">
-        <f t="shared" si="62"/>
-        <v>6600</v>
+        <f t="shared" si="49"/>
+        <v>27100</v>
       </c>
       <c r="L170" s="1">
-        <f t="shared" si="63"/>
-        <v>8200</v>
+        <f t="shared" si="50"/>
+        <v>28700</v>
       </c>
       <c r="M170" s="1">
-        <f t="shared" si="64"/>
-        <v>2450</v>
+        <f t="shared" si="51"/>
+        <v>10950</v>
       </c>
       <c r="N170" s="1">
-        <f t="shared" si="65"/>
-        <v>2450</v>
+        <f t="shared" si="52"/>
+        <v>10950</v>
       </c>
       <c r="O170" s="3">
-        <f t="shared" si="66"/>
-        <v>64</v>
+        <f t="shared" si="53"/>
+        <v>159</v>
       </c>
       <c r="P170" s="3">
-        <f t="shared" si="67"/>
-        <v>50</v>
+        <f t="shared" si="44"/>
+        <v>190</v>
       </c>
       <c r="Q170" s="3">
-        <v>99</v>
+        <v>99.99</v>
       </c>
       <c r="R170" s="11" t="s">
         <v>454</v>
@@ -15254,55 +15551,55 @@
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="11" t="s">
-        <v>1040</v>
+        <v>1111</v>
       </c>
       <c r="D171" s="11" t="s">
-        <v>1041</v>
+        <v>1112</v>
       </c>
       <c r="E171" s="1">
         <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1042</v>
-      </c>
-      <c r="G171" s="12" t="s">
-        <v>907</v>
-      </c>
-      <c r="H171" s="11" t="s">
-        <v>907</v>
-      </c>
-      <c r="I171" s="13" t="s">
-        <v>908</v>
-      </c>
-      <c r="J171" s="1">
-        <v>0</v>
+        <v>1113</v>
+      </c>
+      <c r="G171" s="4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H171" s="4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I171" s="9" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J171" s="1" t="s">
+        <v>1115</v>
       </c>
       <c r="K171" s="1">
-        <f t="shared" ref="K171:K175" si="68">K170+500</f>
-        <v>7100</v>
+        <f t="shared" si="49"/>
+        <v>27700</v>
       </c>
       <c r="L171" s="1">
-        <f t="shared" ref="L171:L175" si="69">L170+500</f>
-        <v>8700</v>
+        <f t="shared" si="50"/>
+        <v>29300</v>
       </c>
       <c r="M171" s="1">
-        <f t="shared" ref="M171:M175" si="70">M170+200</f>
-        <v>2650</v>
+        <f t="shared" si="51"/>
+        <v>11200</v>
       </c>
       <c r="N171" s="1">
-        <f t="shared" ref="N171:N175" si="71">N170+200</f>
-        <v>2650</v>
+        <f t="shared" si="52"/>
+        <v>11200</v>
       </c>
       <c r="O171" s="3">
-        <f t="shared" si="66"/>
-        <v>66</v>
+        <f t="shared" si="53"/>
+        <v>162</v>
       </c>
       <c r="P171" s="3">
-        <f t="shared" si="67"/>
-        <v>54</v>
+        <f t="shared" si="44"/>
+        <v>194</v>
       </c>
       <c r="Q171" s="3">
-        <v>99.2</v>
+        <v>99.99</v>
       </c>
       <c r="R171" s="11" t="s">
         <v>909</v>
@@ -15323,55 +15620,55 @@
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="11" t="s">
-        <v>1043</v>
+        <v>1116</v>
       </c>
       <c r="D172" s="11" t="s">
-        <v>1044</v>
+        <v>1117</v>
       </c>
       <c r="E172" s="1">
         <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="G172" s="12" t="s">
-        <v>913</v>
-      </c>
-      <c r="H172" s="11" t="s">
-        <v>913</v>
-      </c>
-      <c r="I172" s="13" t="s">
-        <v>914</v>
-      </c>
-      <c r="J172" s="1">
-        <v>0</v>
+        <v>1118</v>
+      </c>
+      <c r="G172" s="4" t="s">
+        <v>1119</v>
+      </c>
+      <c r="H172" s="4" t="s">
+        <v>1119</v>
+      </c>
+      <c r="I172" s="9" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J172" s="1" t="s">
+        <v>1120</v>
       </c>
       <c r="K172" s="1">
-        <f t="shared" si="68"/>
-        <v>7600</v>
+        <f t="shared" si="49"/>
+        <v>28300</v>
       </c>
       <c r="L172" s="1">
-        <f t="shared" si="69"/>
-        <v>9200</v>
+        <f t="shared" si="50"/>
+        <v>29900</v>
       </c>
       <c r="M172" s="1">
-        <f t="shared" si="70"/>
-        <v>2850</v>
+        <f t="shared" si="51"/>
+        <v>11450</v>
       </c>
       <c r="N172" s="1">
-        <f t="shared" si="71"/>
-        <v>2850</v>
+        <f t="shared" si="52"/>
+        <v>11450</v>
       </c>
       <c r="O172" s="3">
-        <f t="shared" si="66"/>
-        <v>68</v>
+        <f t="shared" si="53"/>
+        <v>165</v>
       </c>
       <c r="P172" s="3">
-        <f t="shared" si="67"/>
-        <v>58</v>
+        <f t="shared" si="44"/>
+        <v>198</v>
       </c>
       <c r="Q172" s="3">
-        <v>99.4</v>
+        <v>99.99</v>
       </c>
       <c r="R172" s="11" t="s">
         <v>915</v>
@@ -15392,55 +15689,55 @@
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="11" t="s">
-        <v>1046</v>
+        <v>1121</v>
       </c>
       <c r="D173" s="11" t="s">
-        <v>1047</v>
+        <v>1122</v>
       </c>
       <c r="E173" s="1">
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1048</v>
-      </c>
-      <c r="G173" s="12" t="s">
-        <v>919</v>
-      </c>
-      <c r="H173" s="11" t="s">
-        <v>919</v>
-      </c>
-      <c r="I173" s="13" t="s">
-        <v>920</v>
-      </c>
-      <c r="J173" s="1">
-        <v>0</v>
+        <v>1123</v>
+      </c>
+      <c r="G173" s="4" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H173" s="4" t="s">
+        <v>1124</v>
+      </c>
+      <c r="I173" s="9" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J173" s="1" t="s">
+        <v>1125</v>
       </c>
       <c r="K173" s="1">
-        <f t="shared" si="68"/>
-        <v>8100</v>
+        <f t="shared" si="49"/>
+        <v>28900</v>
       </c>
       <c r="L173" s="1">
-        <f t="shared" si="69"/>
-        <v>9700</v>
+        <f t="shared" si="50"/>
+        <v>30500</v>
       </c>
       <c r="M173" s="1">
-        <f t="shared" si="70"/>
-        <v>3050</v>
+        <f t="shared" si="51"/>
+        <v>11700</v>
       </c>
       <c r="N173" s="1">
-        <f t="shared" si="71"/>
-        <v>3050</v>
+        <f t="shared" si="52"/>
+        <v>11700</v>
       </c>
       <c r="O173" s="3">
-        <f t="shared" si="66"/>
-        <v>70</v>
+        <f t="shared" si="53"/>
+        <v>168</v>
       </c>
       <c r="P173" s="3">
-        <f t="shared" si="67"/>
-        <v>62</v>
+        <f t="shared" si="44"/>
+        <v>202</v>
       </c>
       <c r="Q173" s="3">
-        <v>99.6</v>
+        <v>99.99</v>
       </c>
       <c r="R173" s="11" t="s">
         <v>921</v>
@@ -15461,55 +15758,55 @@
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="11" t="s">
-        <v>1049</v>
+        <v>1126</v>
       </c>
       <c r="D174" s="11" t="s">
-        <v>1050</v>
+        <v>1127</v>
       </c>
       <c r="E174" s="1">
         <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1051</v>
-      </c>
-      <c r="G174" s="12" t="s">
-        <v>925</v>
-      </c>
-      <c r="H174" s="11" t="s">
-        <v>925</v>
-      </c>
-      <c r="I174" s="13" t="s">
-        <v>926</v>
-      </c>
-      <c r="J174" s="1">
-        <v>0</v>
+        <v>1128</v>
+      </c>
+      <c r="G174" s="4" t="s">
+        <v>1129</v>
+      </c>
+      <c r="H174" s="4" t="s">
+        <v>1129</v>
+      </c>
+      <c r="I174" s="9" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J174" s="1" t="s">
+        <v>1130</v>
       </c>
       <c r="K174" s="1">
-        <f t="shared" si="68"/>
-        <v>8600</v>
+        <f t="shared" si="49"/>
+        <v>29500</v>
       </c>
       <c r="L174" s="1">
-        <f t="shared" si="69"/>
-        <v>10200</v>
+        <f t="shared" si="50"/>
+        <v>31100</v>
       </c>
       <c r="M174" s="1">
-        <f t="shared" si="70"/>
-        <v>3250</v>
+        <f t="shared" si="51"/>
+        <v>11950</v>
       </c>
       <c r="N174" s="1">
-        <f t="shared" si="71"/>
-        <v>3250</v>
+        <f t="shared" si="52"/>
+        <v>11950</v>
       </c>
       <c r="O174" s="3">
-        <f t="shared" si="66"/>
-        <v>72</v>
+        <f t="shared" si="53"/>
+        <v>171</v>
       </c>
       <c r="P174" s="3">
-        <f t="shared" si="67"/>
-        <v>66</v>
+        <f t="shared" si="44"/>
+        <v>206</v>
       </c>
       <c r="Q174" s="3">
-        <v>99.8</v>
+        <v>99.99</v>
       </c>
       <c r="R174" s="11" t="s">
         <v>927</v>
@@ -15530,55 +15827,55 @@
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="11" t="s">
-        <v>1052</v>
+        <v>1131</v>
       </c>
       <c r="D175" s="11" t="s">
-        <v>1053</v>
+        <v>1132</v>
       </c>
       <c r="E175" s="1">
         <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1054</v>
-      </c>
-      <c r="G175" s="12" t="s">
-        <v>931</v>
-      </c>
-      <c r="H175" s="11" t="s">
-        <v>931</v>
-      </c>
-      <c r="I175" s="13" t="s">
-        <v>932</v>
-      </c>
-      <c r="J175" s="1">
-        <v>0</v>
+        <v>1133</v>
+      </c>
+      <c r="G175" s="4" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H175" s="4" t="s">
+        <v>1134</v>
+      </c>
+      <c r="I175" s="9" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J175" s="1" t="s">
+        <v>1135</v>
       </c>
       <c r="K175" s="1">
-        <f t="shared" si="68"/>
-        <v>9100</v>
+        <f t="shared" si="49"/>
+        <v>30100</v>
       </c>
       <c r="L175" s="1">
-        <f t="shared" si="69"/>
-        <v>10700</v>
+        <f t="shared" si="50"/>
+        <v>31700</v>
       </c>
       <c r="M175" s="1">
-        <f t="shared" si="70"/>
-        <v>3450</v>
+        <f t="shared" si="51"/>
+        <v>12200</v>
       </c>
       <c r="N175" s="1">
-        <f t="shared" si="71"/>
-        <v>3450</v>
+        <f t="shared" si="52"/>
+        <v>12200</v>
       </c>
       <c r="O175" s="3">
-        <f t="shared" si="66"/>
-        <v>74</v>
+        <f t="shared" si="53"/>
+        <v>174</v>
       </c>
       <c r="P175" s="3">
-        <f t="shared" si="67"/>
-        <v>70</v>
+        <f t="shared" si="44"/>
+        <v>210</v>
       </c>
       <c r="Q175" s="3">
-        <v>99.9</v>
+        <v>99.99</v>
       </c>
       <c r="R175" s="11" t="s">
         <v>933</v>
@@ -15599,55 +15896,55 @@
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="11" t="s">
-        <v>1055</v>
+        <v>1136</v>
       </c>
       <c r="D176" s="11" t="s">
-        <v>1056</v>
+        <v>1137</v>
       </c>
       <c r="E176" s="1">
         <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="G176" s="12" t="s">
-        <v>937</v>
-      </c>
-      <c r="H176" s="11" t="s">
-        <v>937</v>
-      </c>
-      <c r="I176" s="13" t="s">
-        <v>938</v>
-      </c>
-      <c r="J176" s="1">
-        <v>0</v>
+        <v>1138</v>
+      </c>
+      <c r="G176" s="4" t="s">
+        <v>1139</v>
+      </c>
+      <c r="H176" s="4" t="s">
+        <v>1139</v>
+      </c>
+      <c r="I176" s="9" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J176" s="1" t="s">
+        <v>1140</v>
       </c>
       <c r="K176" s="1">
-        <f t="shared" ref="K176:K180" si="72">K175+600</f>
-        <v>9700</v>
+        <f t="shared" si="49"/>
+        <v>30700</v>
       </c>
       <c r="L176" s="1">
-        <f t="shared" ref="L176:L180" si="73">L175+600</f>
-        <v>11300</v>
+        <f t="shared" si="50"/>
+        <v>32300</v>
       </c>
       <c r="M176" s="1">
-        <f t="shared" ref="M176:M180" si="74">M175+250</f>
-        <v>3700</v>
+        <f t="shared" si="51"/>
+        <v>12450</v>
       </c>
       <c r="N176" s="1">
-        <f t="shared" ref="N176:N180" si="75">N175+250</f>
-        <v>3700</v>
+        <f t="shared" si="52"/>
+        <v>12450</v>
       </c>
       <c r="O176" s="3">
-        <f t="shared" si="66"/>
-        <v>76</v>
+        <f t="shared" si="53"/>
+        <v>177</v>
       </c>
       <c r="P176" s="3">
-        <f t="shared" si="67"/>
-        <v>74</v>
+        <f t="shared" si="44"/>
+        <v>214</v>
       </c>
       <c r="Q176" s="3">
-        <v>99.92</v>
+        <v>99.99</v>
       </c>
       <c r="R176" s="11" t="s">
         <v>939</v>
@@ -15668,55 +15965,55 @@
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="11" t="s">
-        <v>1058</v>
+        <v>1141</v>
       </c>
       <c r="D177" s="11" t="s">
-        <v>1059</v>
+        <v>1142</v>
       </c>
       <c r="E177" s="1">
         <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1060</v>
-      </c>
-      <c r="G177" s="12" t="s">
-        <v>943</v>
-      </c>
-      <c r="H177" s="11" t="s">
-        <v>943</v>
-      </c>
-      <c r="I177" s="13" t="s">
-        <v>944</v>
-      </c>
-      <c r="J177" s="1">
-        <v>0</v>
+        <v>1143</v>
+      </c>
+      <c r="G177" s="4" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H177" s="4" t="s">
+        <v>1144</v>
+      </c>
+      <c r="I177" s="9" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J177" s="1" t="s">
+        <v>1145</v>
       </c>
       <c r="K177" s="1">
-        <f t="shared" si="72"/>
-        <v>10300</v>
+        <f t="shared" si="49"/>
+        <v>31300</v>
       </c>
       <c r="L177" s="1">
-        <f t="shared" si="73"/>
-        <v>11900</v>
+        <f t="shared" si="50"/>
+        <v>32900</v>
       </c>
       <c r="M177" s="1">
-        <f t="shared" si="74"/>
-        <v>3950</v>
+        <f t="shared" si="51"/>
+        <v>12700</v>
       </c>
       <c r="N177" s="1">
-        <f t="shared" si="75"/>
-        <v>3950</v>
+        <f t="shared" si="52"/>
+        <v>12700</v>
       </c>
       <c r="O177" s="3">
-        <f t="shared" si="66"/>
-        <v>78</v>
+        <f t="shared" si="53"/>
+        <v>180</v>
       </c>
       <c r="P177" s="3">
-        <f t="shared" si="67"/>
-        <v>78</v>
+        <f t="shared" si="44"/>
+        <v>218</v>
       </c>
       <c r="Q177" s="3">
-        <v>99.94</v>
+        <v>99.99</v>
       </c>
       <c r="R177" s="11" t="s">
         <v>945</v>
@@ -15737,55 +16034,55 @@
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="11" t="s">
-        <v>1061</v>
+        <v>1146</v>
       </c>
       <c r="D178" s="11" t="s">
-        <v>1062</v>
+        <v>1147</v>
       </c>
       <c r="E178" s="1">
         <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1063</v>
-      </c>
-      <c r="G178" s="12" t="s">
-        <v>949</v>
-      </c>
-      <c r="H178" s="11" t="s">
-        <v>949</v>
-      </c>
-      <c r="I178" s="13" t="s">
-        <v>950</v>
-      </c>
-      <c r="J178" s="1">
-        <v>0</v>
+        <v>1148</v>
+      </c>
+      <c r="G178" s="4" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H178" s="4" t="s">
+        <v>1149</v>
+      </c>
+      <c r="I178" s="9" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J178" s="1" t="s">
+        <v>1150</v>
       </c>
       <c r="K178" s="1">
-        <f t="shared" si="72"/>
-        <v>10900</v>
+        <f t="shared" si="49"/>
+        <v>31900</v>
       </c>
       <c r="L178" s="1">
-        <f t="shared" si="73"/>
-        <v>12500</v>
+        <f t="shared" si="50"/>
+        <v>33500</v>
       </c>
       <c r="M178" s="1">
-        <f t="shared" si="74"/>
-        <v>4200</v>
+        <f t="shared" si="51"/>
+        <v>12950</v>
       </c>
       <c r="N178" s="1">
-        <f t="shared" si="75"/>
-        <v>4200</v>
+        <f t="shared" si="52"/>
+        <v>12950</v>
       </c>
       <c r="O178" s="3">
-        <f t="shared" si="66"/>
-        <v>80</v>
+        <f t="shared" si="53"/>
+        <v>183</v>
       </c>
       <c r="P178" s="3">
-        <f t="shared" si="67"/>
-        <v>82</v>
+        <f t="shared" si="44"/>
+        <v>222</v>
       </c>
       <c r="Q178" s="3">
-        <v>99.96</v>
+        <v>99.99</v>
       </c>
       <c r="R178" s="11" t="s">
         <v>951</v>
@@ -15806,55 +16103,55 @@
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="11" t="s">
-        <v>1064</v>
+        <v>1151</v>
       </c>
       <c r="D179" s="11" t="s">
-        <v>1065</v>
+        <v>1152</v>
       </c>
       <c r="E179" s="1">
         <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1066</v>
-      </c>
-      <c r="G179" s="12" t="s">
-        <v>955</v>
-      </c>
-      <c r="H179" s="11" t="s">
-        <v>955</v>
-      </c>
-      <c r="I179" s="13" t="s">
-        <v>956</v>
-      </c>
-      <c r="J179" s="1">
-        <v>0</v>
+        <v>1153</v>
+      </c>
+      <c r="G179" s="4" t="s">
+        <v>1154</v>
+      </c>
+      <c r="H179" s="4" t="s">
+        <v>1154</v>
+      </c>
+      <c r="I179" s="9" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J179" s="1" t="s">
+        <v>1155</v>
       </c>
       <c r="K179" s="1">
-        <f t="shared" si="72"/>
-        <v>11500</v>
+        <f t="shared" si="49"/>
+        <v>32500</v>
       </c>
       <c r="L179" s="1">
-        <f t="shared" si="73"/>
-        <v>13100</v>
+        <f t="shared" si="50"/>
+        <v>34100</v>
       </c>
       <c r="M179" s="1">
-        <f t="shared" si="74"/>
-        <v>4450</v>
+        <f t="shared" si="51"/>
+        <v>13200</v>
       </c>
       <c r="N179" s="1">
-        <f t="shared" si="75"/>
-        <v>4450</v>
+        <f t="shared" si="52"/>
+        <v>13200</v>
       </c>
       <c r="O179" s="3">
-        <f t="shared" si="66"/>
-        <v>82</v>
+        <f t="shared" si="53"/>
+        <v>186</v>
       </c>
       <c r="P179" s="3">
-        <f t="shared" si="67"/>
-        <v>86</v>
+        <f t="shared" si="44"/>
+        <v>226</v>
       </c>
       <c r="Q179" s="3">
-        <v>99.98</v>
+        <v>99.99</v>
       </c>
       <c r="R179" s="11" t="s">
         <v>957</v>
@@ -15875,52 +16172,52 @@
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="11" t="s">
-        <v>1067</v>
+        <v>1156</v>
       </c>
       <c r="D180" s="11" t="s">
-        <v>1068</v>
+        <v>1157</v>
       </c>
       <c r="E180" s="1">
         <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1069</v>
-      </c>
-      <c r="G180" s="12" t="s">
-        <v>961</v>
-      </c>
-      <c r="H180" s="11" t="s">
-        <v>961</v>
-      </c>
-      <c r="I180" s="13" t="s">
-        <v>962</v>
-      </c>
-      <c r="J180" s="1">
-        <v>0</v>
+        <v>1158</v>
+      </c>
+      <c r="G180" s="4" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H180" s="4" t="s">
+        <v>1159</v>
+      </c>
+      <c r="I180" s="9" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J180" s="1" t="s">
+        <v>1160</v>
       </c>
       <c r="K180" s="1">
-        <f t="shared" si="72"/>
-        <v>12100</v>
+        <f t="shared" si="49"/>
+        <v>33100</v>
       </c>
       <c r="L180" s="1">
-        <f t="shared" si="73"/>
-        <v>13700</v>
+        <f t="shared" si="50"/>
+        <v>34700</v>
       </c>
       <c r="M180" s="1">
-        <f t="shared" si="74"/>
-        <v>4700</v>
+        <f t="shared" si="51"/>
+        <v>13450</v>
       </c>
       <c r="N180" s="1">
-        <f t="shared" si="75"/>
-        <v>4700</v>
+        <f t="shared" si="52"/>
+        <v>13450</v>
       </c>
       <c r="O180" s="3">
-        <f t="shared" si="66"/>
-        <v>84</v>
+        <f t="shared" si="53"/>
+        <v>189</v>
       </c>
       <c r="P180" s="3">
-        <f t="shared" si="67"/>
-        <v>90</v>
+        <f t="shared" si="44"/>
+        <v>230</v>
       </c>
       <c r="Q180" s="3">
         <v>99.99</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -4761,7 +4761,7 @@
         <v>32</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>31</v>
@@ -4800,7 +4800,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="11.5" spans="3:22">
+    <row r="6" s="1" customFormat="1" ht="12" spans="3:22">
       <c r="C6" s="1" t="s">
         <v>36</v>
       </c>
@@ -12880,11 +12880,11 @@
         <v>2050</v>
       </c>
       <c r="O131" s="3">
-        <f>O130+2</f>
+        <f t="shared" ref="O131:O145" si="44">O130+2</f>
         <v>56</v>
       </c>
       <c r="P131" s="3">
-        <f t="shared" ref="P131:P180" si="44">P130+4</f>
+        <f t="shared" ref="P131:P180" si="45">P130+4</f>
         <v>34</v>
       </c>
       <c r="Q131" s="3">
@@ -12945,11 +12945,11 @@
         <v>2150</v>
       </c>
       <c r="O132" s="3">
-        <f>O131+2</f>
+        <f t="shared" si="44"/>
         <v>58</v>
       </c>
       <c r="P132" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>38</v>
       </c>
       <c r="Q132" s="3">
@@ -13010,11 +13010,11 @@
         <v>2250</v>
       </c>
       <c r="O133" s="3">
-        <f>O132+2</f>
+        <f t="shared" si="44"/>
         <v>60</v>
       </c>
       <c r="P133" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>42</v>
       </c>
       <c r="Q133" s="3">
@@ -13075,11 +13075,11 @@
         <v>2350</v>
       </c>
       <c r="O134" s="3">
-        <f>O133+2</f>
+        <f t="shared" si="44"/>
         <v>62</v>
       </c>
       <c r="P134" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>46</v>
       </c>
       <c r="Q134" s="3">
@@ -13140,11 +13140,11 @@
         <v>2450</v>
       </c>
       <c r="O135" s="3">
-        <f>O134+2</f>
+        <f t="shared" si="44"/>
         <v>64</v>
       </c>
       <c r="P135" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>50</v>
       </c>
       <c r="Q135" s="3">
@@ -13191,27 +13191,27 @@
         <v>0</v>
       </c>
       <c r="K136" s="1">
-        <f t="shared" ref="K136:K145" si="45">K135+500</f>
+        <f t="shared" ref="K136:K145" si="46">K135+500</f>
         <v>7100</v>
       </c>
       <c r="L136" s="1">
-        <f t="shared" ref="L136:L145" si="46">L135+500</f>
+        <f t="shared" ref="L136:L145" si="47">L135+500</f>
         <v>8700</v>
       </c>
       <c r="M136" s="1">
-        <f t="shared" ref="M136:M145" si="47">M135+200</f>
+        <f t="shared" ref="M136:M145" si="48">M135+200</f>
         <v>2650</v>
       </c>
       <c r="N136" s="1">
-        <f t="shared" ref="N136:N145" si="48">N135+200</f>
+        <f t="shared" ref="N136:N145" si="49">N135+200</f>
         <v>2650</v>
       </c>
       <c r="O136" s="3">
-        <f>O135+2</f>
+        <f t="shared" si="44"/>
         <v>66</v>
       </c>
       <c r="P136" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>54</v>
       </c>
       <c r="Q136" s="3">
@@ -13260,27 +13260,27 @@
         <v>0</v>
       </c>
       <c r="K137" s="1">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>7600</v>
       </c>
       <c r="L137" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>9200</v>
       </c>
       <c r="M137" s="1">
-        <f t="shared" si="47"/>
-        <v>2850</v>
-      </c>
-      <c r="N137" s="1">
         <f t="shared" si="48"/>
         <v>2850</v>
       </c>
+      <c r="N137" s="1">
+        <f t="shared" si="49"/>
+        <v>2850</v>
+      </c>
       <c r="O137" s="3">
-        <f>O136+2</f>
+        <f t="shared" si="44"/>
         <v>68</v>
       </c>
       <c r="P137" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>58</v>
       </c>
       <c r="Q137" s="3">
@@ -13329,27 +13329,27 @@
         <v>0</v>
       </c>
       <c r="K138" s="1">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>8100</v>
       </c>
       <c r="L138" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>9700</v>
       </c>
       <c r="M138" s="1">
-        <f t="shared" si="47"/>
-        <v>3050</v>
-      </c>
-      <c r="N138" s="1">
         <f t="shared" si="48"/>
         <v>3050</v>
       </c>
+      <c r="N138" s="1">
+        <f t="shared" si="49"/>
+        <v>3050</v>
+      </c>
       <c r="O138" s="3">
-        <f>O137+2</f>
+        <f t="shared" si="44"/>
         <v>70</v>
       </c>
       <c r="P138" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>62</v>
       </c>
       <c r="Q138" s="3">
@@ -13398,27 +13398,27 @@
         <v>0</v>
       </c>
       <c r="K139" s="1">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>8600</v>
       </c>
       <c r="L139" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>10200</v>
       </c>
       <c r="M139" s="1">
-        <f t="shared" si="47"/>
-        <v>3250</v>
-      </c>
-      <c r="N139" s="1">
         <f t="shared" si="48"/>
         <v>3250</v>
       </c>
+      <c r="N139" s="1">
+        <f t="shared" si="49"/>
+        <v>3250</v>
+      </c>
       <c r="O139" s="3">
-        <f>O138+2</f>
+        <f t="shared" si="44"/>
         <v>72</v>
       </c>
       <c r="P139" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>66</v>
       </c>
       <c r="Q139" s="3">
@@ -13467,27 +13467,27 @@
         <v>0</v>
       </c>
       <c r="K140" s="1">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>9100</v>
       </c>
       <c r="L140" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>10700</v>
       </c>
       <c r="M140" s="1">
-        <f t="shared" si="47"/>
-        <v>3450</v>
-      </c>
-      <c r="N140" s="1">
         <f t="shared" si="48"/>
         <v>3450</v>
       </c>
+      <c r="N140" s="1">
+        <f t="shared" si="49"/>
+        <v>3450</v>
+      </c>
       <c r="O140" s="3">
-        <f>O139+2</f>
+        <f t="shared" si="44"/>
         <v>74</v>
       </c>
       <c r="P140" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>70</v>
       </c>
       <c r="Q140" s="3">
@@ -13536,27 +13536,27 @@
         <v>0</v>
       </c>
       <c r="K141" s="1">
-        <f t="shared" ref="K141:K180" si="49">K140+600</f>
+        <f t="shared" ref="K141:K180" si="50">K140+600</f>
         <v>9700</v>
       </c>
       <c r="L141" s="1">
-        <f t="shared" ref="L141:L180" si="50">L140+600</f>
+        <f t="shared" ref="L141:L180" si="51">L140+600</f>
         <v>11300</v>
       </c>
       <c r="M141" s="1">
-        <f t="shared" ref="M141:M180" si="51">M140+250</f>
+        <f t="shared" ref="M141:M180" si="52">M140+250</f>
         <v>3700</v>
       </c>
       <c r="N141" s="1">
-        <f t="shared" ref="N141:N180" si="52">N140+250</f>
+        <f t="shared" ref="N141:N180" si="53">N140+250</f>
         <v>3700</v>
       </c>
       <c r="O141" s="3">
-        <f>O140+2</f>
+        <f t="shared" si="44"/>
         <v>76</v>
       </c>
       <c r="P141" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>74</v>
       </c>
       <c r="Q141" s="3">
@@ -13605,27 +13605,27 @@
         <v>0</v>
       </c>
       <c r="K142" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>10300</v>
       </c>
       <c r="L142" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>11900</v>
       </c>
       <c r="M142" s="1">
-        <f t="shared" si="51"/>
-        <v>3950</v>
-      </c>
-      <c r="N142" s="1">
         <f t="shared" si="52"/>
         <v>3950</v>
       </c>
+      <c r="N142" s="1">
+        <f t="shared" si="53"/>
+        <v>3950</v>
+      </c>
       <c r="O142" s="3">
-        <f>O141+2</f>
+        <f t="shared" si="44"/>
         <v>78</v>
       </c>
       <c r="P142" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>78</v>
       </c>
       <c r="Q142" s="3">
@@ -13674,27 +13674,27 @@
         <v>0</v>
       </c>
       <c r="K143" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>10900</v>
       </c>
       <c r="L143" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>12500</v>
       </c>
       <c r="M143" s="1">
-        <f t="shared" si="51"/>
-        <v>4200</v>
-      </c>
-      <c r="N143" s="1">
         <f t="shared" si="52"/>
         <v>4200</v>
       </c>
+      <c r="N143" s="1">
+        <f t="shared" si="53"/>
+        <v>4200</v>
+      </c>
       <c r="O143" s="3">
-        <f>O142+2</f>
+        <f t="shared" si="44"/>
         <v>80</v>
       </c>
       <c r="P143" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>82</v>
       </c>
       <c r="Q143" s="3">
@@ -13743,27 +13743,27 @@
         <v>0</v>
       </c>
       <c r="K144" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>11500</v>
       </c>
       <c r="L144" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>13100</v>
       </c>
       <c r="M144" s="1">
-        <f t="shared" si="51"/>
-        <v>4450</v>
-      </c>
-      <c r="N144" s="1">
         <f t="shared" si="52"/>
         <v>4450</v>
       </c>
+      <c r="N144" s="1">
+        <f t="shared" si="53"/>
+        <v>4450</v>
+      </c>
       <c r="O144" s="3">
-        <f>O143+2</f>
+        <f t="shared" si="44"/>
         <v>82</v>
       </c>
       <c r="P144" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>86</v>
       </c>
       <c r="Q144" s="3">
@@ -13812,27 +13812,27 @@
         <v>0</v>
       </c>
       <c r="K145" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>12100</v>
       </c>
       <c r="L145" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>13700</v>
       </c>
       <c r="M145" s="1">
-        <f t="shared" si="51"/>
-        <v>4700</v>
-      </c>
-      <c r="N145" s="1">
         <f t="shared" si="52"/>
         <v>4700</v>
       </c>
+      <c r="N145" s="1">
+        <f t="shared" si="53"/>
+        <v>4700</v>
+      </c>
       <c r="O145" s="3">
-        <f>O144+2</f>
+        <f t="shared" si="44"/>
         <v>84</v>
       </c>
       <c r="P145" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>90</v>
       </c>
       <c r="Q145" s="3">
@@ -13881,27 +13881,27 @@
         <v>10</v>
       </c>
       <c r="K146" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>12700</v>
       </c>
       <c r="L146" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>14300</v>
       </c>
       <c r="M146" s="1">
-        <f t="shared" si="51"/>
-        <v>4950</v>
-      </c>
-      <c r="N146" s="1">
         <f t="shared" si="52"/>
         <v>4950</v>
       </c>
+      <c r="N146" s="1">
+        <f t="shared" si="53"/>
+        <v>4950</v>
+      </c>
       <c r="O146" s="3">
-        <f t="shared" ref="O146:O180" si="53">O145+3</f>
+        <f t="shared" ref="O146:O180" si="54">O145+3</f>
         <v>87</v>
       </c>
       <c r="P146" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>94</v>
       </c>
       <c r="Q146" s="3">
@@ -13945,31 +13945,31 @@
         <v>974</v>
       </c>
       <c r="J147" s="1">
-        <f t="shared" ref="J147:J155" si="54">J146*5</f>
+        <f t="shared" ref="J147:J155" si="55">J146*5</f>
         <v>50</v>
       </c>
       <c r="K147" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>13300</v>
       </c>
       <c r="L147" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>14900</v>
       </c>
       <c r="M147" s="1">
-        <f t="shared" si="51"/>
-        <v>5200</v>
-      </c>
-      <c r="N147" s="1">
         <f t="shared" si="52"/>
         <v>5200</v>
       </c>
+      <c r="N147" s="1">
+        <f t="shared" si="53"/>
+        <v>5200</v>
+      </c>
       <c r="O147" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>90</v>
       </c>
       <c r="P147" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>98</v>
       </c>
       <c r="Q147" s="3">
@@ -14013,31 +14013,31 @@
         <v>980</v>
       </c>
       <c r="J148" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>250</v>
       </c>
       <c r="K148" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>13900</v>
       </c>
       <c r="L148" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>15500</v>
       </c>
       <c r="M148" s="1">
-        <f t="shared" si="51"/>
-        <v>5450</v>
-      </c>
-      <c r="N148" s="1">
         <f t="shared" si="52"/>
         <v>5450</v>
       </c>
+      <c r="N148" s="1">
+        <f t="shared" si="53"/>
+        <v>5450</v>
+      </c>
       <c r="O148" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>93</v>
       </c>
       <c r="P148" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>102</v>
       </c>
       <c r="Q148" s="3">
@@ -14081,31 +14081,31 @@
         <v>986</v>
       </c>
       <c r="J149" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>1250</v>
       </c>
       <c r="K149" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>14500</v>
       </c>
       <c r="L149" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>16100</v>
       </c>
       <c r="M149" s="1">
-        <f t="shared" si="51"/>
-        <v>5700</v>
-      </c>
-      <c r="N149" s="1">
         <f t="shared" si="52"/>
         <v>5700</v>
       </c>
+      <c r="N149" s="1">
+        <f t="shared" si="53"/>
+        <v>5700</v>
+      </c>
       <c r="O149" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>96</v>
       </c>
       <c r="P149" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>106</v>
       </c>
       <c r="Q149" s="3">
@@ -14149,31 +14149,31 @@
         <v>992</v>
       </c>
       <c r="J150" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>6250</v>
       </c>
       <c r="K150" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>15100</v>
       </c>
       <c r="L150" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>16700</v>
       </c>
       <c r="M150" s="1">
-        <f t="shared" si="51"/>
-        <v>5950</v>
-      </c>
-      <c r="N150" s="1">
         <f t="shared" si="52"/>
         <v>5950</v>
       </c>
+      <c r="N150" s="1">
+        <f t="shared" si="53"/>
+        <v>5950</v>
+      </c>
       <c r="O150" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>99</v>
       </c>
       <c r="P150" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>110</v>
       </c>
       <c r="Q150" s="3">
@@ -14217,31 +14217,31 @@
         <v>998</v>
       </c>
       <c r="J151" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>31250</v>
       </c>
       <c r="K151" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>15700</v>
       </c>
       <c r="L151" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>17300</v>
       </c>
       <c r="M151" s="1">
-        <f t="shared" si="51"/>
-        <v>6200</v>
-      </c>
-      <c r="N151" s="1">
         <f t="shared" si="52"/>
         <v>6200</v>
       </c>
+      <c r="N151" s="1">
+        <f t="shared" si="53"/>
+        <v>6200</v>
+      </c>
       <c r="O151" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>102</v>
       </c>
       <c r="P151" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>114</v>
       </c>
       <c r="Q151" s="3">
@@ -14287,31 +14287,31 @@
         <v>1004</v>
       </c>
       <c r="J152" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>156250</v>
       </c>
       <c r="K152" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>16300</v>
       </c>
       <c r="L152" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>17900</v>
       </c>
       <c r="M152" s="1">
-        <f t="shared" si="51"/>
-        <v>6450</v>
-      </c>
-      <c r="N152" s="1">
         <f t="shared" si="52"/>
         <v>6450</v>
       </c>
+      <c r="N152" s="1">
+        <f t="shared" si="53"/>
+        <v>6450</v>
+      </c>
       <c r="O152" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>105</v>
       </c>
       <c r="P152" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>118</v>
       </c>
       <c r="Q152" s="3">
@@ -14357,31 +14357,31 @@
         <v>1010</v>
       </c>
       <c r="J153" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>781250</v>
       </c>
       <c r="K153" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>16900</v>
       </c>
       <c r="L153" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>18500</v>
       </c>
       <c r="M153" s="1">
-        <f t="shared" si="51"/>
-        <v>6700</v>
-      </c>
-      <c r="N153" s="1">
         <f t="shared" si="52"/>
         <v>6700</v>
       </c>
+      <c r="N153" s="1">
+        <f t="shared" si="53"/>
+        <v>6700</v>
+      </c>
       <c r="O153" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>108</v>
       </c>
       <c r="P153" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>122</v>
       </c>
       <c r="Q153" s="3">
@@ -14427,31 +14427,31 @@
         <v>1016</v>
       </c>
       <c r="J154" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>3906250</v>
       </c>
       <c r="K154" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>17500</v>
       </c>
       <c r="L154" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>19100</v>
       </c>
       <c r="M154" s="1">
-        <f t="shared" si="51"/>
-        <v>6950</v>
-      </c>
-      <c r="N154" s="1">
         <f t="shared" si="52"/>
         <v>6950</v>
       </c>
+      <c r="N154" s="1">
+        <f t="shared" si="53"/>
+        <v>6950</v>
+      </c>
       <c r="O154" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>111</v>
       </c>
       <c r="P154" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>126</v>
       </c>
       <c r="Q154" s="3">
@@ -14497,31 +14497,31 @@
         <v>1022</v>
       </c>
       <c r="J155" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>19531250</v>
       </c>
       <c r="K155" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>18100</v>
       </c>
       <c r="L155" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>19700</v>
       </c>
       <c r="M155" s="1">
-        <f t="shared" si="51"/>
-        <v>7200</v>
-      </c>
-      <c r="N155" s="1">
         <f t="shared" si="52"/>
         <v>7200</v>
       </c>
+      <c r="N155" s="1">
+        <f t="shared" si="53"/>
+        <v>7200</v>
+      </c>
       <c r="O155" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>114</v>
       </c>
       <c r="P155" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>130</v>
       </c>
       <c r="Q155" s="3">
@@ -14568,27 +14568,27 @@
         <v>1029</v>
       </c>
       <c r="K156" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>18700</v>
       </c>
       <c r="L156" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>20300</v>
       </c>
       <c r="M156" s="1">
-        <f t="shared" si="51"/>
-        <v>7450</v>
-      </c>
-      <c r="N156" s="1">
         <f t="shared" si="52"/>
         <v>7450</v>
       </c>
+      <c r="N156" s="1">
+        <f t="shared" si="53"/>
+        <v>7450</v>
+      </c>
       <c r="O156" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>117</v>
       </c>
       <c r="P156" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>134</v>
       </c>
       <c r="Q156" s="3">
@@ -14635,27 +14635,27 @@
         <v>1035</v>
       </c>
       <c r="K157" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>19300</v>
       </c>
       <c r="L157" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>20900</v>
       </c>
       <c r="M157" s="1">
-        <f t="shared" si="51"/>
-        <v>7700</v>
-      </c>
-      <c r="N157" s="1">
         <f t="shared" si="52"/>
         <v>7700</v>
       </c>
+      <c r="N157" s="1">
+        <f t="shared" si="53"/>
+        <v>7700</v>
+      </c>
       <c r="O157" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>120</v>
       </c>
       <c r="P157" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>138</v>
       </c>
       <c r="Q157" s="3">
@@ -14702,27 +14702,27 @@
         <v>1041</v>
       </c>
       <c r="K158" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>19900</v>
       </c>
       <c r="L158" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>21500</v>
       </c>
       <c r="M158" s="1">
-        <f t="shared" si="51"/>
-        <v>7950</v>
-      </c>
-      <c r="N158" s="1">
         <f t="shared" si="52"/>
         <v>7950</v>
       </c>
+      <c r="N158" s="1">
+        <f t="shared" si="53"/>
+        <v>7950</v>
+      </c>
       <c r="O158" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>123</v>
       </c>
       <c r="P158" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>142</v>
       </c>
       <c r="Q158" s="3">
@@ -14769,27 +14769,27 @@
         <v>1047</v>
       </c>
       <c r="K159" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>20500</v>
       </c>
       <c r="L159" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>22100</v>
       </c>
       <c r="M159" s="1">
-        <f t="shared" si="51"/>
-        <v>8200</v>
-      </c>
-      <c r="N159" s="1">
         <f t="shared" si="52"/>
         <v>8200</v>
       </c>
+      <c r="N159" s="1">
+        <f t="shared" si="53"/>
+        <v>8200</v>
+      </c>
       <c r="O159" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>126</v>
       </c>
       <c r="P159" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>146</v>
       </c>
       <c r="Q159" s="3">
@@ -14836,27 +14836,27 @@
         <v>1053</v>
       </c>
       <c r="K160" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>21100</v>
       </c>
       <c r="L160" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>22700</v>
       </c>
       <c r="M160" s="1">
-        <f t="shared" si="51"/>
-        <v>8450</v>
-      </c>
-      <c r="N160" s="1">
         <f t="shared" si="52"/>
         <v>8450</v>
       </c>
+      <c r="N160" s="1">
+        <f t="shared" si="53"/>
+        <v>8450</v>
+      </c>
       <c r="O160" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>129</v>
       </c>
       <c r="P160" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>150</v>
       </c>
       <c r="Q160" s="3">
@@ -14905,27 +14905,27 @@
         <v>1059</v>
       </c>
       <c r="K161" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>21700</v>
       </c>
       <c r="L161" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>23300</v>
       </c>
       <c r="M161" s="1">
-        <f t="shared" si="51"/>
-        <v>8700</v>
-      </c>
-      <c r="N161" s="1">
         <f t="shared" si="52"/>
         <v>8700</v>
       </c>
+      <c r="N161" s="1">
+        <f t="shared" si="53"/>
+        <v>8700</v>
+      </c>
       <c r="O161" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>132</v>
       </c>
       <c r="P161" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>154</v>
       </c>
       <c r="Q161" s="3">
@@ -14974,27 +14974,27 @@
         <v>1065</v>
       </c>
       <c r="K162" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>22300</v>
       </c>
       <c r="L162" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>23900</v>
       </c>
       <c r="M162" s="1">
-        <f t="shared" si="51"/>
-        <v>8950</v>
-      </c>
-      <c r="N162" s="1">
         <f t="shared" si="52"/>
         <v>8950</v>
       </c>
+      <c r="N162" s="1">
+        <f t="shared" si="53"/>
+        <v>8950</v>
+      </c>
       <c r="O162" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>135</v>
       </c>
       <c r="P162" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>158</v>
       </c>
       <c r="Q162" s="3">
@@ -15043,27 +15043,27 @@
         <v>1071</v>
       </c>
       <c r="K163" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>22900</v>
       </c>
       <c r="L163" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>24500</v>
       </c>
       <c r="M163" s="1">
-        <f t="shared" si="51"/>
-        <v>9200</v>
-      </c>
-      <c r="N163" s="1">
         <f t="shared" si="52"/>
         <v>9200</v>
       </c>
+      <c r="N163" s="1">
+        <f t="shared" si="53"/>
+        <v>9200</v>
+      </c>
       <c r="O163" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>138</v>
       </c>
       <c r="P163" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>162</v>
       </c>
       <c r="Q163" s="3">
@@ -15112,27 +15112,27 @@
         <v>1077</v>
       </c>
       <c r="K164" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>23500</v>
       </c>
       <c r="L164" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>25100</v>
       </c>
       <c r="M164" s="1">
-        <f t="shared" si="51"/>
-        <v>9450</v>
-      </c>
-      <c r="N164" s="1">
         <f t="shared" si="52"/>
         <v>9450</v>
       </c>
+      <c r="N164" s="1">
+        <f t="shared" si="53"/>
+        <v>9450</v>
+      </c>
       <c r="O164" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>141</v>
       </c>
       <c r="P164" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>166</v>
       </c>
       <c r="Q164" s="3">
@@ -15181,27 +15181,27 @@
         <v>1083</v>
       </c>
       <c r="K165" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>24100</v>
       </c>
       <c r="L165" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>25700</v>
       </c>
       <c r="M165" s="1">
-        <f t="shared" si="51"/>
-        <v>9700</v>
-      </c>
-      <c r="N165" s="1">
         <f t="shared" si="52"/>
         <v>9700</v>
       </c>
+      <c r="N165" s="1">
+        <f t="shared" si="53"/>
+        <v>9700</v>
+      </c>
       <c r="O165" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>144</v>
       </c>
       <c r="P165" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>170</v>
       </c>
       <c r="Q165" s="3">
@@ -15248,27 +15248,27 @@
         <v>1089</v>
       </c>
       <c r="K166" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>24700</v>
       </c>
       <c r="L166" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>26300</v>
       </c>
       <c r="M166" s="1">
-        <f t="shared" si="51"/>
-        <v>9950</v>
-      </c>
-      <c r="N166" s="1">
         <f t="shared" si="52"/>
         <v>9950</v>
       </c>
+      <c r="N166" s="1">
+        <f t="shared" si="53"/>
+        <v>9950</v>
+      </c>
       <c r="O166" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>147</v>
       </c>
       <c r="P166" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>174</v>
       </c>
       <c r="Q166" s="3">
@@ -15313,27 +15313,27 @@
         <v>1095</v>
       </c>
       <c r="K167" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>25300</v>
       </c>
       <c r="L167" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>26900</v>
       </c>
       <c r="M167" s="1">
-        <f t="shared" si="51"/>
-        <v>10200</v>
-      </c>
-      <c r="N167" s="1">
         <f t="shared" si="52"/>
         <v>10200</v>
       </c>
+      <c r="N167" s="1">
+        <f t="shared" si="53"/>
+        <v>10200</v>
+      </c>
       <c r="O167" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>150</v>
       </c>
       <c r="P167" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>178</v>
       </c>
       <c r="Q167" s="3">
@@ -15378,27 +15378,27 @@
         <v>1101</v>
       </c>
       <c r="K168" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>25900</v>
       </c>
       <c r="L168" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>27500</v>
       </c>
       <c r="M168" s="1">
-        <f t="shared" si="51"/>
-        <v>10450</v>
-      </c>
-      <c r="N168" s="1">
         <f t="shared" si="52"/>
         <v>10450</v>
       </c>
+      <c r="N168" s="1">
+        <f t="shared" si="53"/>
+        <v>10450</v>
+      </c>
       <c r="O168" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>153</v>
       </c>
       <c r="P168" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>182</v>
       </c>
       <c r="Q168" s="3">
@@ -15443,27 +15443,27 @@
         <v>1106</v>
       </c>
       <c r="K169" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>26500</v>
       </c>
       <c r="L169" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>28100</v>
       </c>
       <c r="M169" s="1">
-        <f t="shared" si="51"/>
-        <v>10700</v>
-      </c>
-      <c r="N169" s="1">
         <f t="shared" si="52"/>
         <v>10700</v>
       </c>
+      <c r="N169" s="1">
+        <f t="shared" si="53"/>
+        <v>10700</v>
+      </c>
       <c r="O169" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>156</v>
       </c>
       <c r="P169" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>186</v>
       </c>
       <c r="Q169" s="3">
@@ -15508,27 +15508,27 @@
         <v>1110</v>
       </c>
       <c r="K170" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>27100</v>
       </c>
       <c r="L170" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>28700</v>
       </c>
       <c r="M170" s="1">
-        <f t="shared" si="51"/>
-        <v>10950</v>
-      </c>
-      <c r="N170" s="1">
         <f t="shared" si="52"/>
         <v>10950</v>
       </c>
+      <c r="N170" s="1">
+        <f t="shared" si="53"/>
+        <v>10950</v>
+      </c>
       <c r="O170" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>159</v>
       </c>
       <c r="P170" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>190</v>
       </c>
       <c r="Q170" s="3">
@@ -15575,27 +15575,27 @@
         <v>1115</v>
       </c>
       <c r="K171" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>27700</v>
       </c>
       <c r="L171" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>29300</v>
       </c>
       <c r="M171" s="1">
-        <f t="shared" si="51"/>
-        <v>11200</v>
-      </c>
-      <c r="N171" s="1">
         <f t="shared" si="52"/>
         <v>11200</v>
       </c>
+      <c r="N171" s="1">
+        <f t="shared" si="53"/>
+        <v>11200</v>
+      </c>
       <c r="O171" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>162</v>
       </c>
       <c r="P171" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>194</v>
       </c>
       <c r="Q171" s="3">
@@ -15644,27 +15644,27 @@
         <v>1120</v>
       </c>
       <c r="K172" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>28300</v>
       </c>
       <c r="L172" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>29900</v>
       </c>
       <c r="M172" s="1">
-        <f t="shared" si="51"/>
-        <v>11450</v>
-      </c>
-      <c r="N172" s="1">
         <f t="shared" si="52"/>
         <v>11450</v>
       </c>
+      <c r="N172" s="1">
+        <f t="shared" si="53"/>
+        <v>11450</v>
+      </c>
       <c r="O172" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>165</v>
       </c>
       <c r="P172" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>198</v>
       </c>
       <c r="Q172" s="3">
@@ -15713,27 +15713,27 @@
         <v>1125</v>
       </c>
       <c r="K173" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>28900</v>
       </c>
       <c r="L173" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>30500</v>
       </c>
       <c r="M173" s="1">
-        <f t="shared" si="51"/>
-        <v>11700</v>
-      </c>
-      <c r="N173" s="1">
         <f t="shared" si="52"/>
         <v>11700</v>
       </c>
+      <c r="N173" s="1">
+        <f t="shared" si="53"/>
+        <v>11700</v>
+      </c>
       <c r="O173" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>168</v>
       </c>
       <c r="P173" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>202</v>
       </c>
       <c r="Q173" s="3">
@@ -15782,27 +15782,27 @@
         <v>1130</v>
       </c>
       <c r="K174" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>29500</v>
       </c>
       <c r="L174" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>31100</v>
       </c>
       <c r="M174" s="1">
-        <f t="shared" si="51"/>
-        <v>11950</v>
-      </c>
-      <c r="N174" s="1">
         <f t="shared" si="52"/>
         <v>11950</v>
       </c>
+      <c r="N174" s="1">
+        <f t="shared" si="53"/>
+        <v>11950</v>
+      </c>
       <c r="O174" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>171</v>
       </c>
       <c r="P174" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>206</v>
       </c>
       <c r="Q174" s="3">
@@ -15851,27 +15851,27 @@
         <v>1135</v>
       </c>
       <c r="K175" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>30100</v>
       </c>
       <c r="L175" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>31700</v>
       </c>
       <c r="M175" s="1">
-        <f t="shared" si="51"/>
-        <v>12200</v>
-      </c>
-      <c r="N175" s="1">
         <f t="shared" si="52"/>
         <v>12200</v>
       </c>
+      <c r="N175" s="1">
+        <f t="shared" si="53"/>
+        <v>12200</v>
+      </c>
       <c r="O175" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>174</v>
       </c>
       <c r="P175" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>210</v>
       </c>
       <c r="Q175" s="3">
@@ -15920,27 +15920,27 @@
         <v>1140</v>
       </c>
       <c r="K176" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>30700</v>
       </c>
       <c r="L176" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>32300</v>
       </c>
       <c r="M176" s="1">
-        <f t="shared" si="51"/>
-        <v>12450</v>
-      </c>
-      <c r="N176" s="1">
         <f t="shared" si="52"/>
         <v>12450</v>
       </c>
+      <c r="N176" s="1">
+        <f t="shared" si="53"/>
+        <v>12450</v>
+      </c>
       <c r="O176" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>177</v>
       </c>
       <c r="P176" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>214</v>
       </c>
       <c r="Q176" s="3">
@@ -15989,27 +15989,27 @@
         <v>1145</v>
       </c>
       <c r="K177" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>31300</v>
       </c>
       <c r="L177" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>32900</v>
       </c>
       <c r="M177" s="1">
-        <f t="shared" si="51"/>
-        <v>12700</v>
-      </c>
-      <c r="N177" s="1">
         <f t="shared" si="52"/>
         <v>12700</v>
       </c>
+      <c r="N177" s="1">
+        <f t="shared" si="53"/>
+        <v>12700</v>
+      </c>
       <c r="O177" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>180</v>
       </c>
       <c r="P177" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>218</v>
       </c>
       <c r="Q177" s="3">
@@ -16058,27 +16058,27 @@
         <v>1150</v>
       </c>
       <c r="K178" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>31900</v>
       </c>
       <c r="L178" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>33500</v>
       </c>
       <c r="M178" s="1">
-        <f t="shared" si="51"/>
-        <v>12950</v>
-      </c>
-      <c r="N178" s="1">
         <f t="shared" si="52"/>
         <v>12950</v>
       </c>
+      <c r="N178" s="1">
+        <f t="shared" si="53"/>
+        <v>12950</v>
+      </c>
       <c r="O178" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>183</v>
       </c>
       <c r="P178" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>222</v>
       </c>
       <c r="Q178" s="3">
@@ -16127,27 +16127,27 @@
         <v>1155</v>
       </c>
       <c r="K179" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>32500</v>
       </c>
       <c r="L179" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>34100</v>
       </c>
       <c r="M179" s="1">
-        <f t="shared" si="51"/>
-        <v>13200</v>
-      </c>
-      <c r="N179" s="1">
         <f t="shared" si="52"/>
         <v>13200</v>
       </c>
+      <c r="N179" s="1">
+        <f t="shared" si="53"/>
+        <v>13200</v>
+      </c>
       <c r="O179" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>186</v>
       </c>
       <c r="P179" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>226</v>
       </c>
       <c r="Q179" s="3">
@@ -16196,27 +16196,27 @@
         <v>1160</v>
       </c>
       <c r="K180" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>33100</v>
       </c>
       <c r="L180" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>34700</v>
       </c>
       <c r="M180" s="1">
-        <f t="shared" si="51"/>
-        <v>13450</v>
-      </c>
-      <c r="N180" s="1">
         <f t="shared" si="52"/>
         <v>13450</v>
       </c>
+      <c r="N180" s="1">
+        <f t="shared" si="53"/>
+        <v>13450</v>
+      </c>
       <c r="O180" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>189</v>
       </c>
       <c r="P180" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>230</v>
       </c>
       <c r="Q180" s="3">
@@ -16239,7 +16239,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:Q5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:I5 J5 K5:Q5 C3:Q4" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -4800,7 +4800,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="12" spans="3:22">
+    <row r="6" s="1" customFormat="1" ht="11.5" spans="3:22">
       <c r="C6" s="1" t="s">
         <v>36</v>
       </c>
@@ -13863,7 +13863,7 @@
         <v>965</v>
       </c>
       <c r="E146" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>966</v>
@@ -13930,7 +13930,7 @@
         <v>971</v>
       </c>
       <c r="E147" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>972</v>
@@ -13998,7 +13998,7 @@
         <v>977</v>
       </c>
       <c r="E148" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>978</v>
@@ -14066,7 +14066,7 @@
         <v>983</v>
       </c>
       <c r="E149" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>984</v>
@@ -14134,7 +14134,7 @@
         <v>989</v>
       </c>
       <c r="E150" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>990</v>
@@ -14202,7 +14202,7 @@
         <v>995</v>
       </c>
       <c r="E151" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>996</v>
@@ -14272,7 +14272,7 @@
         <v>1001</v>
       </c>
       <c r="E152" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>1002</v>
@@ -14342,7 +14342,7 @@
         <v>1007</v>
       </c>
       <c r="E153" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>1008</v>
@@ -14412,7 +14412,7 @@
         <v>1013</v>
       </c>
       <c r="E154" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>1014</v>
@@ -14482,7 +14482,7 @@
         <v>1019</v>
       </c>
       <c r="E155" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>1020</v>
@@ -14542,7 +14542,9 @@
       <c r="W155" s="3"/>
       <c r="X155" s="3"/>
     </row>
-    <row r="156" s="1" customFormat="1" customHeight="1" spans="3:24">
+    <row r="156" s="1" customFormat="1" customHeight="1" spans="1:24">
+      <c r="A156" s="3"/>
+      <c r="B156" s="3"/>
       <c r="C156" s="11" t="s">
         <v>1024</v>
       </c>
@@ -14550,7 +14552,7 @@
         <v>1025</v>
       </c>
       <c r="E156" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>1026</v>
@@ -14609,7 +14611,9 @@
       <c r="W156" s="3"/>
       <c r="X156" s="3"/>
     </row>
-    <row r="157" s="1" customFormat="1" customHeight="1" spans="3:24">
+    <row r="157" s="1" customFormat="1" customHeight="1" spans="1:24">
+      <c r="A157" s="3"/>
+      <c r="B157" s="3"/>
       <c r="C157" s="11" t="s">
         <v>1030</v>
       </c>
@@ -14617,7 +14621,7 @@
         <v>1031</v>
       </c>
       <c r="E157" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>1032</v>
@@ -14676,7 +14680,9 @@
       <c r="W157" s="3"/>
       <c r="X157" s="3"/>
     </row>
-    <row r="158" s="1" customFormat="1" customHeight="1" spans="3:24">
+    <row r="158" s="1" customFormat="1" customHeight="1" spans="1:24">
+      <c r="A158" s="3"/>
+      <c r="B158" s="3"/>
       <c r="C158" s="11" t="s">
         <v>1036</v>
       </c>
@@ -14684,7 +14690,7 @@
         <v>1037</v>
       </c>
       <c r="E158" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>1038</v>
@@ -14743,7 +14749,9 @@
       <c r="W158" s="3"/>
       <c r="X158" s="3"/>
     </row>
-    <row r="159" s="1" customFormat="1" customHeight="1" spans="3:24">
+    <row r="159" s="1" customFormat="1" customHeight="1" spans="1:24">
+      <c r="A159" s="3"/>
+      <c r="B159" s="3"/>
       <c r="C159" s="11" t="s">
         <v>1042</v>
       </c>
@@ -14751,7 +14759,7 @@
         <v>1043</v>
       </c>
       <c r="E159" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>1044</v>
@@ -14810,7 +14818,9 @@
       <c r="W159" s="3"/>
       <c r="X159" s="3"/>
     </row>
-    <row r="160" s="1" customFormat="1" customHeight="1" spans="3:24">
+    <row r="160" s="1" customFormat="1" customHeight="1" spans="1:24">
+      <c r="A160" s="3"/>
+      <c r="B160" s="3"/>
       <c r="C160" s="11" t="s">
         <v>1048</v>
       </c>
@@ -14818,7 +14828,7 @@
         <v>1049</v>
       </c>
       <c r="E160" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>1050</v>
@@ -14887,7 +14897,7 @@
         <v>1055</v>
       </c>
       <c r="E161" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>1056</v>
@@ -14956,7 +14966,7 @@
         <v>1061</v>
       </c>
       <c r="E162" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>1062</v>
@@ -15025,7 +15035,7 @@
         <v>1067</v>
       </c>
       <c r="E163" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>1068</v>
@@ -15094,7 +15104,7 @@
         <v>1073</v>
       </c>
       <c r="E164" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>1074</v>
@@ -15163,7 +15173,7 @@
         <v>1079</v>
       </c>
       <c r="E165" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>1080</v>
@@ -15230,7 +15240,7 @@
         <v>1085</v>
       </c>
       <c r="E166" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>1086</v>
@@ -15295,7 +15305,7 @@
         <v>1091</v>
       </c>
       <c r="E167" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>1092</v>
@@ -15360,7 +15370,7 @@
         <v>1097</v>
       </c>
       <c r="E168" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>1098</v>
@@ -15425,7 +15435,7 @@
         <v>1103</v>
       </c>
       <c r="E169" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>1104</v>
@@ -15490,7 +15500,7 @@
         <v>1108</v>
       </c>
       <c r="E170" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>459</v>
@@ -15557,7 +15567,7 @@
         <v>1112</v>
       </c>
       <c r="E171" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>1113</v>
@@ -15626,7 +15636,7 @@
         <v>1117</v>
       </c>
       <c r="E172" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>1118</v>
@@ -15695,7 +15705,7 @@
         <v>1122</v>
       </c>
       <c r="E173" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>1123</v>
@@ -15764,7 +15774,7 @@
         <v>1127</v>
       </c>
       <c r="E174" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>1128</v>
@@ -15833,7 +15843,7 @@
         <v>1132</v>
       </c>
       <c r="E175" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>1133</v>
@@ -15902,7 +15912,7 @@
         <v>1137</v>
       </c>
       <c r="E176" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>1138</v>
@@ -15971,7 +15981,7 @@
         <v>1142</v>
       </c>
       <c r="E177" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>1143</v>
@@ -16040,7 +16050,7 @@
         <v>1147</v>
       </c>
       <c r="E178" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>1148</v>
@@ -16109,7 +16119,7 @@
         <v>1152</v>
       </c>
       <c r="E179" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>1153</v>
@@ -16178,7 +16188,7 @@
         <v>1157</v>
       </c>
       <c r="E180" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>1158</v>
@@ -16239,7 +16249,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:I5 J5 K5:Q5 C3:Q4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:Q5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="1163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="1174">
   <si>
     <t>ID</t>
   </si>
@@ -2989,12 +2989,18 @@
     <t>深渊鸡王</t>
   </si>
   <si>
+    <t>1000恒</t>
+  </si>
+  <si>
     <t>9000僧</t>
   </si>
   <si>
     <t>64000不</t>
   </si>
   <si>
+    <t>10垓</t>
+  </si>
+  <si>
     <t>3300000000000</t>
   </si>
   <si>
@@ -3007,12 +3013,18 @@
     <t>深渊鹿王</t>
   </si>
   <si>
+    <t>4000恒</t>
+  </si>
+  <si>
     <t>9祇</t>
   </si>
   <si>
     <t>128可</t>
   </si>
   <si>
+    <t>50垓</t>
+  </si>
+  <si>
     <t>3600000000000</t>
   </si>
   <si>
@@ -3025,12 +3037,18 @@
     <t>深渊草王</t>
   </si>
   <si>
+    <t>16000恒</t>
+  </si>
+  <si>
     <t>90祇</t>
   </si>
   <si>
     <t>2560可</t>
   </si>
   <si>
+    <t>250垓</t>
+  </si>
+  <si>
     <t>3900000000000</t>
   </si>
   <si>
@@ -3043,12 +3061,18 @@
     <t>深渊猫王</t>
   </si>
   <si>
+    <t>64000恒</t>
+  </si>
+  <si>
     <t>900祇</t>
   </si>
   <si>
     <t>5思</t>
   </si>
   <si>
+    <t>1250垓</t>
+  </si>
+  <si>
     <t>4200000000000</t>
   </si>
   <si>
@@ -3061,12 +3085,18 @@
     <t>深渊花王</t>
   </si>
   <si>
+    <t>24河</t>
+  </si>
+  <si>
     <t>9000祇</t>
   </si>
   <si>
     <t>100思</t>
   </si>
   <si>
+    <t>6250垓</t>
+  </si>
+  <si>
     <t>4500000000000</t>
   </si>
   <si>
@@ -3086,6 +3116,9 @@
   </si>
   <si>
     <t>2000思</t>
+  </si>
+  <si>
+    <t>25000垓</t>
   </si>
   <si>
     <t>4800000000000</t>
@@ -4818,7 +4851,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="12" spans="3:23">
+    <row r="6" s="1" customFormat="1" ht="11.5" spans="3:23">
       <c r="C6" s="1" t="s">
         <v>37</v>
       </c>
@@ -13276,7 +13309,7 @@
         <v>2050</v>
       </c>
       <c r="P131" s="3">
-        <f t="shared" ref="P131:P145" si="44">P130+2</f>
+        <f t="shared" ref="P131:P146" si="44">P130+2</f>
         <v>56</v>
       </c>
       <c r="Q131" s="3">
@@ -14310,16 +14343,16 @@
         <v>968</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="I146" s="10" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="J146" s="1">
         <v>10</v>
       </c>
-      <c r="K146" s="1">
-        <v>0</v>
+      <c r="K146" s="1" t="s">
+        <v>971</v>
       </c>
       <c r="L146" s="1">
         <f t="shared" si="50"/>
@@ -14338,21 +14371,20 @@
         <v>4950</v>
       </c>
       <c r="P146" s="3">
-        <f t="shared" ref="P146:P180" si="54">P145+3</f>
+        <f>P145+3</f>
         <v>87</v>
       </c>
       <c r="Q146" s="3">
-        <f t="shared" si="45"/>
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="R146" s="3">
         <v>99.99</v>
       </c>
       <c r="S146" s="11" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="T146" s="11" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="V146" s="2" t="s">
         <v>156</v>
@@ -14365,32 +14397,32 @@
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="11" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D147" s="11" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="E147" s="1">
         <v>5</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="H147" s="4" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="I147" s="9" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="J147" s="1">
-        <f t="shared" ref="J147:J155" si="55">J146*5</f>
+        <f t="shared" ref="J147:J155" si="54">J146*5</f>
         <v>50</v>
       </c>
-      <c r="K147" s="1">
-        <v>0</v>
+      <c r="K147" s="1" t="s">
+        <v>979</v>
       </c>
       <c r="L147" s="1">
         <f t="shared" si="50"/>
@@ -14409,21 +14441,21 @@
         <v>5200</v>
       </c>
       <c r="P147" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" ref="P146:P180" si="55">P146+3</f>
         <v>90</v>
       </c>
       <c r="Q147" s="3">
         <f t="shared" si="45"/>
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="R147" s="3">
         <v>99.99</v>
       </c>
       <c r="S147" s="11" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="T147" s="11" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="V147" s="1" t="s">
         <v>156</v>
@@ -14436,32 +14468,32 @@
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="11" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="D148" s="11" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="E148" s="1">
         <v>5</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="H148" s="4" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="I148" s="9" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="J148" s="1">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>250</v>
       </c>
-      <c r="K148" s="1">
-        <v>0</v>
+      <c r="K148" s="1" t="s">
+        <v>987</v>
       </c>
       <c r="L148" s="1">
         <f t="shared" si="50"/>
@@ -14480,21 +14512,21 @@
         <v>5450</v>
       </c>
       <c r="P148" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>93</v>
       </c>
       <c r="Q148" s="3">
         <f t="shared" si="45"/>
-        <v>102</v>
+        <v>158</v>
       </c>
       <c r="R148" s="3">
         <v>99.99</v>
       </c>
       <c r="S148" s="11" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="T148" s="11" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="V148" s="1" t="s">
         <v>156</v>
@@ -14507,32 +14539,32 @@
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="11" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="D149" s="11" t="s">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="E149" s="1">
         <v>5</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="H149" s="4" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="I149" s="9" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="J149" s="1">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>1250</v>
       </c>
-      <c r="K149" s="1">
-        <v>0</v>
+      <c r="K149" s="1" t="s">
+        <v>995</v>
       </c>
       <c r="L149" s="1">
         <f t="shared" si="50"/>
@@ -14551,21 +14583,21 @@
         <v>5700</v>
       </c>
       <c r="P149" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>96</v>
       </c>
       <c r="Q149" s="3">
         <f t="shared" si="45"/>
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="R149" s="3">
         <v>99.99</v>
       </c>
       <c r="S149" s="11" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="T149" s="11" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="V149" s="1" t="s">
         <v>156</v>
@@ -14578,32 +14610,32 @@
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="11" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="E150" s="1">
         <v>5</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>992</v>
+        <v>1001</v>
       </c>
       <c r="I150" s="9" t="s">
-        <v>993</v>
+        <v>1002</v>
       </c>
       <c r="J150" s="1">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>6250</v>
       </c>
-      <c r="K150" s="1">
-        <v>0</v>
+      <c r="K150" s="1" t="s">
+        <v>1003</v>
       </c>
       <c r="L150" s="1">
         <f t="shared" si="50"/>
@@ -14622,21 +14654,21 @@
         <v>5950</v>
       </c>
       <c r="P150" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>99</v>
       </c>
       <c r="Q150" s="3">
         <f t="shared" si="45"/>
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="R150" s="3">
         <v>99.99</v>
       </c>
       <c r="S150" s="11" t="s">
-        <v>994</v>
+        <v>1004</v>
       </c>
       <c r="T150" s="11" t="s">
-        <v>994</v>
+        <v>1004</v>
       </c>
       <c r="V150" s="1" t="s">
         <v>156</v>
@@ -14647,38 +14679,38 @@
     </row>
     <row r="151" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A151" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>996</v>
+        <v>1006</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>997</v>
+        <v>1007</v>
       </c>
       <c r="E151" s="1">
         <v>5</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>998</v>
+        <v>1008</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>999</v>
+        <v>1009</v>
       </c>
       <c r="H151" s="4" t="s">
-        <v>999</v>
+        <v>1009</v>
       </c>
       <c r="I151" s="9" t="s">
-        <v>1000</v>
+        <v>1010</v>
       </c>
       <c r="J151" s="1">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>31250</v>
       </c>
-      <c r="K151" s="1">
-        <v>0</v>
+      <c r="K151" s="1" t="s">
+        <v>1011</v>
       </c>
       <c r="L151" s="1">
         <f t="shared" si="50"/>
@@ -14697,21 +14729,21 @@
         <v>6200</v>
       </c>
       <c r="P151" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>102</v>
       </c>
       <c r="Q151" s="3">
         <f t="shared" si="45"/>
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="R151" s="3">
         <v>99.99</v>
       </c>
       <c r="S151" s="11" t="s">
-        <v>1001</v>
+        <v>1012</v>
       </c>
       <c r="T151" s="11" t="s">
-        <v>1001</v>
+        <v>1012</v>
       </c>
       <c r="V151" s="1" t="s">
         <v>156</v>
@@ -14724,34 +14756,34 @@
     </row>
     <row r="152" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A152" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>1002</v>
+        <v>1013</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>1003</v>
+        <v>1014</v>
       </c>
       <c r="E152" s="1">
         <v>5</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1004</v>
+        <v>1015</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>1005</v>
+        <v>1016</v>
       </c>
       <c r="H152" s="4" t="s">
-        <v>1005</v>
+        <v>1016</v>
       </c>
       <c r="I152" s="9" t="s">
-        <v>1006</v>
+        <v>1017</v>
       </c>
       <c r="J152" s="1">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>156250</v>
       </c>
       <c r="K152" s="1">
@@ -14774,21 +14806,21 @@
         <v>6450</v>
       </c>
       <c r="P152" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>105</v>
       </c>
       <c r="Q152" s="3">
         <f t="shared" si="45"/>
-        <v>118</v>
+        <v>174</v>
       </c>
       <c r="R152" s="3">
         <v>99.99</v>
       </c>
       <c r="S152" s="11" t="s">
-        <v>1007</v>
+        <v>1018</v>
       </c>
       <c r="T152" s="11" t="s">
-        <v>1007</v>
+        <v>1018</v>
       </c>
       <c r="V152" s="1" t="s">
         <v>156</v>
@@ -14801,34 +14833,34 @@
     </row>
     <row r="153" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A153" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>1008</v>
+        <v>1019</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>1009</v>
+        <v>1020</v>
       </c>
       <c r="E153" s="1">
         <v>5</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>1010</v>
+        <v>1021</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>1011</v>
+        <v>1022</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>1011</v>
+        <v>1022</v>
       </c>
       <c r="I153" s="9" t="s">
-        <v>1012</v>
+        <v>1023</v>
       </c>
       <c r="J153" s="1">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>781250</v>
       </c>
       <c r="K153" s="1">
@@ -14851,21 +14883,21 @@
         <v>6700</v>
       </c>
       <c r="P153" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>108</v>
       </c>
       <c r="Q153" s="3">
         <f t="shared" si="45"/>
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="R153" s="3">
         <v>99.99</v>
       </c>
       <c r="S153" s="11" t="s">
-        <v>1013</v>
+        <v>1024</v>
       </c>
       <c r="T153" s="11" t="s">
-        <v>1013</v>
+        <v>1024</v>
       </c>
       <c r="V153" s="1" t="s">
         <v>156</v>
@@ -14878,34 +14910,34 @@
     </row>
     <row r="154" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A154" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>1014</v>
+        <v>1025</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>1015</v>
+        <v>1026</v>
       </c>
       <c r="E154" s="1">
         <v>5</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>1016</v>
+        <v>1027</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>1017</v>
+        <v>1028</v>
       </c>
       <c r="H154" s="4" t="s">
-        <v>1017</v>
+        <v>1028</v>
       </c>
       <c r="I154" s="9" t="s">
-        <v>1018</v>
+        <v>1029</v>
       </c>
       <c r="J154" s="1">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>3906250</v>
       </c>
       <c r="K154" s="1">
@@ -14928,21 +14960,21 @@
         <v>6950</v>
       </c>
       <c r="P154" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>111</v>
       </c>
       <c r="Q154" s="3">
         <f t="shared" si="45"/>
-        <v>126</v>
+        <v>182</v>
       </c>
       <c r="R154" s="3">
         <v>99.99</v>
       </c>
       <c r="S154" s="11" t="s">
-        <v>1019</v>
+        <v>1030</v>
       </c>
       <c r="T154" s="11" t="s">
-        <v>1019</v>
+        <v>1030</v>
       </c>
       <c r="V154" s="1" t="s">
         <v>156</v>
@@ -14955,34 +14987,34 @@
     </row>
     <row r="155" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A155" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>1020</v>
+        <v>1031</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>1021</v>
+        <v>1032</v>
       </c>
       <c r="E155" s="1">
         <v>5</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>1022</v>
+        <v>1033</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>1023</v>
+        <v>1034</v>
       </c>
       <c r="H155" s="4" t="s">
-        <v>1023</v>
+        <v>1034</v>
       </c>
       <c r="I155" s="9" t="s">
-        <v>1024</v>
+        <v>1035</v>
       </c>
       <c r="J155" s="1">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>19531250</v>
       </c>
       <c r="K155" s="1">
@@ -15005,21 +15037,21 @@
         <v>7200</v>
       </c>
       <c r="P155" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>114</v>
       </c>
       <c r="Q155" s="3">
         <f t="shared" si="45"/>
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="R155" s="3">
         <v>99.99</v>
       </c>
       <c r="S155" s="11" t="s">
-        <v>1025</v>
+        <v>1036</v>
       </c>
       <c r="T155" s="11" t="s">
-        <v>1025</v>
+        <v>1036</v>
       </c>
       <c r="V155" s="1" t="s">
         <v>156</v>
@@ -15032,34 +15064,34 @@
     </row>
     <row r="156" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A156" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>1026</v>
+        <v>1037</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>1027</v>
+        <v>1038</v>
       </c>
       <c r="E156" s="1">
         <v>5</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>1028</v>
+        <v>1039</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>1029</v>
+        <v>1040</v>
       </c>
       <c r="H156" s="4" t="s">
-        <v>1029</v>
+        <v>1040</v>
       </c>
       <c r="I156" s="9" t="s">
-        <v>1030</v>
+        <v>1041</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>1031</v>
+        <v>1042</v>
       </c>
       <c r="K156" s="1">
         <v>0</v>
@@ -15081,12 +15113,12 @@
         <v>7450</v>
       </c>
       <c r="P156" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>117</v>
       </c>
       <c r="Q156" s="3">
         <f t="shared" si="45"/>
-        <v>134</v>
+        <v>190</v>
       </c>
       <c r="R156" s="3">
         <v>99.99</v>
@@ -15108,34 +15140,34 @@
     </row>
     <row r="157" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A157" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>1032</v>
+        <v>1043</v>
       </c>
       <c r="D157" s="11" t="s">
-        <v>1033</v>
+        <v>1044</v>
       </c>
       <c r="E157" s="1">
         <v>5</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>1034</v>
+        <v>1045</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>1035</v>
+        <v>1046</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>1035</v>
+        <v>1046</v>
       </c>
       <c r="I157" s="9" t="s">
-        <v>1036</v>
+        <v>1047</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>1037</v>
+        <v>1048</v>
       </c>
       <c r="K157" s="1">
         <v>0</v>
@@ -15157,12 +15189,12 @@
         <v>7700</v>
       </c>
       <c r="P157" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>120</v>
       </c>
       <c r="Q157" s="3">
         <f t="shared" si="45"/>
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="R157" s="3">
         <v>99.99</v>
@@ -15184,34 +15216,34 @@
     </row>
     <row r="158" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A158" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>1038</v>
+        <v>1049</v>
       </c>
       <c r="D158" s="11" t="s">
-        <v>1039</v>
+        <v>1050</v>
       </c>
       <c r="E158" s="1">
         <v>5</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1040</v>
+        <v>1051</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>1041</v>
+        <v>1052</v>
       </c>
       <c r="H158" s="4" t="s">
-        <v>1041</v>
+        <v>1052</v>
       </c>
       <c r="I158" s="9" t="s">
-        <v>1042</v>
+        <v>1053</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>1043</v>
+        <v>1054</v>
       </c>
       <c r="K158" s="1">
         <v>0</v>
@@ -15233,12 +15265,12 @@
         <v>7950</v>
       </c>
       <c r="P158" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>123</v>
       </c>
       <c r="Q158" s="3">
         <f t="shared" si="45"/>
-        <v>142</v>
+        <v>198</v>
       </c>
       <c r="R158" s="3">
         <v>99.99</v>
@@ -15260,34 +15292,34 @@
     </row>
     <row r="159" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A159" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>1044</v>
+        <v>1055</v>
       </c>
       <c r="D159" s="11" t="s">
-        <v>1045</v>
+        <v>1056</v>
       </c>
       <c r="E159" s="1">
         <v>5</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1046</v>
+        <v>1057</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>1047</v>
+        <v>1058</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>1047</v>
+        <v>1058</v>
       </c>
       <c r="I159" s="9" t="s">
-        <v>1048</v>
+        <v>1059</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>1049</v>
+        <v>1060</v>
       </c>
       <c r="K159" s="1">
         <v>0</v>
@@ -15309,12 +15341,12 @@
         <v>8200</v>
       </c>
       <c r="P159" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>126</v>
       </c>
       <c r="Q159" s="3">
         <f t="shared" si="45"/>
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="R159" s="3">
         <v>99.99</v>
@@ -15336,34 +15368,34 @@
     </row>
     <row r="160" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A160" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>1050</v>
+        <v>1061</v>
       </c>
       <c r="D160" s="11" t="s">
-        <v>1051</v>
+        <v>1062</v>
       </c>
       <c r="E160" s="1">
         <v>5</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>1052</v>
+        <v>1063</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>1053</v>
+        <v>1064</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>1053</v>
+        <v>1064</v>
       </c>
       <c r="I160" s="9" t="s">
-        <v>1054</v>
+        <v>1065</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>1055</v>
+        <v>1066</v>
       </c>
       <c r="K160" s="1">
         <v>0</v>
@@ -15385,12 +15417,12 @@
         <v>8450</v>
       </c>
       <c r="P160" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>129</v>
       </c>
       <c r="Q160" s="3">
         <f t="shared" si="45"/>
-        <v>150</v>
+        <v>206</v>
       </c>
       <c r="R160" s="3">
         <v>99.99</v>
@@ -15412,34 +15444,34 @@
     </row>
     <row r="161" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A161" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>1056</v>
+        <v>1067</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>1057</v>
+        <v>1068</v>
       </c>
       <c r="E161" s="1">
         <v>5</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>1058</v>
+        <v>1069</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>1059</v>
+        <v>1070</v>
       </c>
       <c r="H161" s="4" t="s">
-        <v>1059</v>
+        <v>1070</v>
       </c>
       <c r="I161" s="9" t="s">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>1061</v>
+        <v>1072</v>
       </c>
       <c r="K161" s="1">
         <v>0</v>
@@ -15461,12 +15493,12 @@
         <v>8700</v>
       </c>
       <c r="P161" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>132</v>
       </c>
       <c r="Q161" s="3">
         <f t="shared" si="45"/>
-        <v>154</v>
+        <v>210</v>
       </c>
       <c r="R161" s="3">
         <v>99.99</v>
@@ -15488,34 +15520,34 @@
     </row>
     <row r="162" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A162" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>1062</v>
+        <v>1073</v>
       </c>
       <c r="D162" s="11" t="s">
-        <v>1063</v>
+        <v>1074</v>
       </c>
       <c r="E162" s="1">
         <v>5</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>1065</v>
+        <v>1076</v>
       </c>
       <c r="H162" s="4" t="s">
-        <v>1065</v>
+        <v>1076</v>
       </c>
       <c r="I162" s="9" t="s">
-        <v>1066</v>
+        <v>1077</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
       <c r="K162" s="1">
         <v>0</v>
@@ -15537,12 +15569,12 @@
         <v>8950</v>
       </c>
       <c r="P162" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>135</v>
       </c>
       <c r="Q162" s="3">
         <f t="shared" si="45"/>
-        <v>158</v>
+        <v>214</v>
       </c>
       <c r="R162" s="3">
         <v>99.99</v>
@@ -15564,34 +15596,34 @@
     </row>
     <row r="163" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A163" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>1068</v>
+        <v>1079</v>
       </c>
       <c r="D163" s="11" t="s">
-        <v>1069</v>
+        <v>1080</v>
       </c>
       <c r="E163" s="1">
         <v>5</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1070</v>
+        <v>1081</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="H163" s="4" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="I163" s="9" t="s">
-        <v>1072</v>
+        <v>1083</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>1073</v>
+        <v>1084</v>
       </c>
       <c r="K163" s="1">
         <v>0</v>
@@ -15613,12 +15645,12 @@
         <v>9200</v>
       </c>
       <c r="P163" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>138</v>
       </c>
       <c r="Q163" s="3">
         <f t="shared" si="45"/>
-        <v>162</v>
+        <v>218</v>
       </c>
       <c r="R163" s="3">
         <v>99.99</v>
@@ -15640,34 +15672,34 @@
     </row>
     <row r="164" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A164" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>1074</v>
+        <v>1085</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>1075</v>
+        <v>1086</v>
       </c>
       <c r="E164" s="1">
         <v>5</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1076</v>
+        <v>1087</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>1077</v>
+        <v>1088</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>1077</v>
+        <v>1088</v>
       </c>
       <c r="I164" s="9" t="s">
-        <v>1078</v>
+        <v>1089</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>1079</v>
+        <v>1090</v>
       </c>
       <c r="K164" s="1">
         <v>0</v>
@@ -15689,12 +15721,12 @@
         <v>9450</v>
       </c>
       <c r="P164" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>141</v>
       </c>
       <c r="Q164" s="3">
         <f t="shared" si="45"/>
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="R164" s="3">
         <v>99.99</v>
@@ -15716,34 +15748,34 @@
     </row>
     <row r="165" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A165" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>1080</v>
+        <v>1091</v>
       </c>
       <c r="D165" s="11" t="s">
-        <v>1081</v>
+        <v>1092</v>
       </c>
       <c r="E165" s="1">
         <v>5</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1082</v>
+        <v>1093</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>1083</v>
+        <v>1094</v>
       </c>
       <c r="H165" s="4" t="s">
-        <v>1083</v>
+        <v>1094</v>
       </c>
       <c r="I165" s="9" t="s">
-        <v>1084</v>
+        <v>1095</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>1085</v>
+        <v>1096</v>
       </c>
       <c r="K165" s="1">
         <v>0</v>
@@ -15765,12 +15797,12 @@
         <v>9700</v>
       </c>
       <c r="P165" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>144</v>
       </c>
       <c r="Q165" s="3">
         <f t="shared" si="45"/>
-        <v>170</v>
+        <v>226</v>
       </c>
       <c r="R165" s="3">
         <v>99.99</v>
@@ -15792,34 +15824,34 @@
     </row>
     <row r="166" customHeight="1" spans="1:23">
       <c r="A166" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>1086</v>
+        <v>1097</v>
       </c>
       <c r="D166" s="11" t="s">
-        <v>1087</v>
+        <v>1098</v>
       </c>
       <c r="E166" s="1">
         <v>5</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1088</v>
+        <v>1099</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>1089</v>
+        <v>1100</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>1089</v>
+        <v>1100</v>
       </c>
       <c r="I166" s="9" t="s">
-        <v>1090</v>
+        <v>1101</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>1091</v>
+        <v>1102</v>
       </c>
       <c r="K166" s="1">
         <v>0</v>
@@ -15841,12 +15873,12 @@
         <v>9950</v>
       </c>
       <c r="P166" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>147</v>
       </c>
       <c r="Q166" s="3">
         <f t="shared" si="45"/>
-        <v>174</v>
+        <v>230</v>
       </c>
       <c r="R166" s="3">
         <v>99.99</v>
@@ -15866,34 +15898,34 @@
     </row>
     <row r="167" customHeight="1" spans="1:23">
       <c r="A167" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>1092</v>
+        <v>1103</v>
       </c>
       <c r="D167" s="11" t="s">
-        <v>1093</v>
+        <v>1104</v>
       </c>
       <c r="E167" s="1">
         <v>5</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1094</v>
+        <v>1105</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>1095</v>
+        <v>1106</v>
       </c>
       <c r="H167" s="4" t="s">
-        <v>1095</v>
+        <v>1106</v>
       </c>
       <c r="I167" s="9" t="s">
-        <v>1096</v>
+        <v>1107</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>1097</v>
+        <v>1108</v>
       </c>
       <c r="K167" s="1">
         <v>0</v>
@@ -15915,12 +15947,12 @@
         <v>10200</v>
       </c>
       <c r="P167" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>150</v>
       </c>
       <c r="Q167" s="3">
         <f t="shared" si="45"/>
-        <v>178</v>
+        <v>234</v>
       </c>
       <c r="R167" s="3">
         <v>99.99</v>
@@ -15940,34 +15972,34 @@
     </row>
     <row r="168" customHeight="1" spans="1:23">
       <c r="A168" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>1098</v>
+        <v>1109</v>
       </c>
       <c r="D168" s="11" t="s">
-        <v>1099</v>
+        <v>1110</v>
       </c>
       <c r="E168" s="1">
         <v>5</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1100</v>
+        <v>1111</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>1101</v>
+        <v>1112</v>
       </c>
       <c r="H168" s="4" t="s">
-        <v>1101</v>
+        <v>1112</v>
       </c>
       <c r="I168" s="9" t="s">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>1103</v>
+        <v>1114</v>
       </c>
       <c r="K168" s="1">
         <v>0</v>
@@ -15989,12 +16021,12 @@
         <v>10450</v>
       </c>
       <c r="P168" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>153</v>
       </c>
       <c r="Q168" s="3">
         <f t="shared" si="45"/>
-        <v>182</v>
+        <v>238</v>
       </c>
       <c r="R168" s="3">
         <v>99.99</v>
@@ -16014,34 +16046,34 @@
     </row>
     <row r="169" customHeight="1" spans="1:23">
       <c r="A169" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>1104</v>
+        <v>1115</v>
       </c>
       <c r="D169" s="11" t="s">
-        <v>1105</v>
+        <v>1116</v>
       </c>
       <c r="E169" s="1">
         <v>5</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1106</v>
+        <v>1117</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>1107</v>
+        <v>1118</v>
       </c>
       <c r="H169" s="4" t="s">
-        <v>1107</v>
+        <v>1118</v>
       </c>
       <c r="I169" s="9" t="s">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>1108</v>
+        <v>1119</v>
       </c>
       <c r="K169" s="1">
         <v>0</v>
@@ -16063,12 +16095,12 @@
         <v>10700</v>
       </c>
       <c r="P169" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>156</v>
       </c>
       <c r="Q169" s="3">
         <f t="shared" si="45"/>
-        <v>186</v>
+        <v>242</v>
       </c>
       <c r="R169" s="3">
         <v>99.99</v>
@@ -16088,16 +16120,16 @@
     </row>
     <row r="170" customHeight="1" spans="1:23">
       <c r="A170" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>1109</v>
+        <v>1120</v>
       </c>
       <c r="D170" s="11" t="s">
-        <v>1110</v>
+        <v>1121</v>
       </c>
       <c r="E170" s="1">
         <v>5</v>
@@ -16106,16 +16138,16 @@
         <v>460</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>1111</v>
+        <v>1122</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>1111</v>
+        <v>1122</v>
       </c>
       <c r="I170" s="9" t="s">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>1112</v>
+        <v>1123</v>
       </c>
       <c r="K170" s="1">
         <v>0</v>
@@ -16137,12 +16169,12 @@
         <v>10950</v>
       </c>
       <c r="P170" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>159</v>
       </c>
       <c r="Q170" s="3">
         <f t="shared" si="45"/>
-        <v>190</v>
+        <v>246</v>
       </c>
       <c r="R170" s="3">
         <v>99.99</v>
@@ -16162,34 +16194,34 @@
     </row>
     <row r="171" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A171" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>1113</v>
+        <v>1124</v>
       </c>
       <c r="D171" s="11" t="s">
-        <v>1114</v>
+        <v>1125</v>
       </c>
       <c r="E171" s="1">
         <v>5</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1115</v>
+        <v>1126</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>1116</v>
+        <v>1127</v>
       </c>
       <c r="H171" s="4" t="s">
-        <v>1116</v>
+        <v>1127</v>
       </c>
       <c r="I171" s="9" t="s">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>1117</v>
+        <v>1128</v>
       </c>
       <c r="K171" s="1">
         <v>0</v>
@@ -16211,12 +16243,12 @@
         <v>11200</v>
       </c>
       <c r="P171" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>162</v>
       </c>
       <c r="Q171" s="3">
         <f t="shared" si="45"/>
-        <v>194</v>
+        <v>250</v>
       </c>
       <c r="R171" s="3">
         <v>99.99</v>
@@ -16238,34 +16270,34 @@
     </row>
     <row r="172" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A172" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C172" s="11" t="s">
-        <v>1118</v>
+        <v>1129</v>
       </c>
       <c r="D172" s="11" t="s">
-        <v>1119</v>
+        <v>1130</v>
       </c>
       <c r="E172" s="1">
         <v>5</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1120</v>
+        <v>1131</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>1121</v>
+        <v>1132</v>
       </c>
       <c r="H172" s="4" t="s">
-        <v>1121</v>
+        <v>1132</v>
       </c>
       <c r="I172" s="9" t="s">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>1122</v>
+        <v>1133</v>
       </c>
       <c r="K172" s="1">
         <v>0</v>
@@ -16287,12 +16319,12 @@
         <v>11450</v>
       </c>
       <c r="P172" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>165</v>
       </c>
       <c r="Q172" s="3">
         <f t="shared" si="45"/>
-        <v>198</v>
+        <v>254</v>
       </c>
       <c r="R172" s="3">
         <v>99.99</v>
@@ -16314,34 +16346,34 @@
     </row>
     <row r="173" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A173" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C173" s="11" t="s">
-        <v>1123</v>
+        <v>1134</v>
       </c>
       <c r="D173" s="11" t="s">
-        <v>1124</v>
+        <v>1135</v>
       </c>
       <c r="E173" s="1">
         <v>5</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1125</v>
+        <v>1136</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>1126</v>
+        <v>1137</v>
       </c>
       <c r="H173" s="4" t="s">
-        <v>1126</v>
+        <v>1137</v>
       </c>
       <c r="I173" s="9" t="s">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>1127</v>
+        <v>1138</v>
       </c>
       <c r="K173" s="1">
         <v>0</v>
@@ -16363,12 +16395,12 @@
         <v>11700</v>
       </c>
       <c r="P173" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>168</v>
       </c>
       <c r="Q173" s="3">
         <f t="shared" si="45"/>
-        <v>202</v>
+        <v>258</v>
       </c>
       <c r="R173" s="3">
         <v>99.99</v>
@@ -16390,34 +16422,34 @@
     </row>
     <row r="174" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A174" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C174" s="11" t="s">
-        <v>1128</v>
+        <v>1139</v>
       </c>
       <c r="D174" s="11" t="s">
-        <v>1129</v>
+        <v>1140</v>
       </c>
       <c r="E174" s="1">
         <v>5</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1130</v>
+        <v>1141</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>1131</v>
+        <v>1142</v>
       </c>
       <c r="H174" s="4" t="s">
-        <v>1131</v>
+        <v>1142</v>
       </c>
       <c r="I174" s="9" t="s">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>1132</v>
+        <v>1143</v>
       </c>
       <c r="K174" s="1">
         <v>0</v>
@@ -16439,12 +16471,12 @@
         <v>11950</v>
       </c>
       <c r="P174" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>171</v>
       </c>
       <c r="Q174" s="3">
         <f t="shared" si="45"/>
-        <v>206</v>
+        <v>262</v>
       </c>
       <c r="R174" s="3">
         <v>99.99</v>
@@ -16466,34 +16498,34 @@
     </row>
     <row r="175" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A175" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C175" s="11" t="s">
-        <v>1133</v>
+        <v>1144</v>
       </c>
       <c r="D175" s="11" t="s">
-        <v>1134</v>
+        <v>1145</v>
       </c>
       <c r="E175" s="1">
         <v>5</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1135</v>
+        <v>1146</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>1136</v>
+        <v>1147</v>
       </c>
       <c r="H175" s="4" t="s">
-        <v>1136</v>
+        <v>1147</v>
       </c>
       <c r="I175" s="9" t="s">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>1137</v>
+        <v>1148</v>
       </c>
       <c r="K175" s="1">
         <v>0</v>
@@ -16515,12 +16547,12 @@
         <v>12200</v>
       </c>
       <c r="P175" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>174</v>
       </c>
       <c r="Q175" s="3">
         <f t="shared" si="45"/>
-        <v>210</v>
+        <v>266</v>
       </c>
       <c r="R175" s="3">
         <v>99.99</v>
@@ -16542,34 +16574,34 @@
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A176" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C176" s="11" t="s">
-        <v>1138</v>
+        <v>1149</v>
       </c>
       <c r="D176" s="11" t="s">
-        <v>1139</v>
+        <v>1150</v>
       </c>
       <c r="E176" s="1">
         <v>5</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1140</v>
+        <v>1151</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>1141</v>
+        <v>1152</v>
       </c>
       <c r="H176" s="4" t="s">
-        <v>1141</v>
+        <v>1152</v>
       </c>
       <c r="I176" s="9" t="s">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>1142</v>
+        <v>1153</v>
       </c>
       <c r="K176" s="1">
         <v>0</v>
@@ -16591,12 +16623,12 @@
         <v>12450</v>
       </c>
       <c r="P176" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>177</v>
       </c>
       <c r="Q176" s="3">
         <f t="shared" si="45"/>
-        <v>214</v>
+        <v>270</v>
       </c>
       <c r="R176" s="3">
         <v>99.99</v>
@@ -16618,34 +16650,34 @@
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A177" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>1143</v>
+        <v>1154</v>
       </c>
       <c r="D177" s="11" t="s">
-        <v>1144</v>
+        <v>1155</v>
       </c>
       <c r="E177" s="1">
         <v>5</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1145</v>
+        <v>1156</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>1146</v>
+        <v>1157</v>
       </c>
       <c r="H177" s="4" t="s">
-        <v>1146</v>
+        <v>1157</v>
       </c>
       <c r="I177" s="9" t="s">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>1147</v>
+        <v>1158</v>
       </c>
       <c r="K177" s="1">
         <v>0</v>
@@ -16667,12 +16699,12 @@
         <v>12700</v>
       </c>
       <c r="P177" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>180</v>
       </c>
       <c r="Q177" s="3">
         <f t="shared" si="45"/>
-        <v>218</v>
+        <v>274</v>
       </c>
       <c r="R177" s="3">
         <v>99.99</v>
@@ -16694,34 +16726,34 @@
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A178" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C178" s="11" t="s">
-        <v>1148</v>
+        <v>1159</v>
       </c>
       <c r="D178" s="11" t="s">
-        <v>1149</v>
+        <v>1160</v>
       </c>
       <c r="E178" s="1">
         <v>5</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1150</v>
+        <v>1161</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>1151</v>
+        <v>1162</v>
       </c>
       <c r="H178" s="4" t="s">
-        <v>1151</v>
+        <v>1162</v>
       </c>
       <c r="I178" s="9" t="s">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>1152</v>
+        <v>1163</v>
       </c>
       <c r="K178" s="1">
         <v>0</v>
@@ -16743,12 +16775,12 @@
         <v>12950</v>
       </c>
       <c r="P178" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>183</v>
       </c>
       <c r="Q178" s="3">
         <f t="shared" si="45"/>
-        <v>222</v>
+        <v>278</v>
       </c>
       <c r="R178" s="3">
         <v>99.99</v>
@@ -16770,34 +16802,34 @@
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A179" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C179" s="11" t="s">
-        <v>1153</v>
+        <v>1164</v>
       </c>
       <c r="D179" s="11" t="s">
-        <v>1154</v>
+        <v>1165</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1155</v>
+        <v>1166</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>1156</v>
+        <v>1167</v>
       </c>
       <c r="H179" s="4" t="s">
-        <v>1156</v>
+        <v>1167</v>
       </c>
       <c r="I179" s="9" t="s">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>1157</v>
+        <v>1168</v>
       </c>
       <c r="K179" s="1">
         <v>0</v>
@@ -16819,12 +16851,12 @@
         <v>13200</v>
       </c>
       <c r="P179" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>186</v>
       </c>
       <c r="Q179" s="3">
         <f t="shared" si="45"/>
-        <v>226</v>
+        <v>282</v>
       </c>
       <c r="R179" s="3">
         <v>99.99</v>
@@ -16846,34 +16878,34 @@
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A180" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C180" s="11" t="s">
-        <v>1158</v>
+        <v>1169</v>
       </c>
       <c r="D180" s="11" t="s">
-        <v>1159</v>
+        <v>1170</v>
       </c>
       <c r="E180" s="1">
         <v>5</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1160</v>
+        <v>1171</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>1161</v>
+        <v>1172</v>
       </c>
       <c r="H180" s="4" t="s">
-        <v>1161</v>
+        <v>1172</v>
       </c>
       <c r="I180" s="9" t="s">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>1162</v>
+        <v>1173</v>
       </c>
       <c r="K180" s="1">
         <v>0</v>
@@ -16895,12 +16927,12 @@
         <v>13450</v>
       </c>
       <c r="P180" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>189</v>
       </c>
       <c r="Q180" s="3">
         <f t="shared" si="45"/>
-        <v>230</v>
+        <v>286</v>
       </c>
       <c r="R180" s="3">
         <v>99.99</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -14697,7 +14697,7 @@
         <v>1008</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>1009</v>
+        <v>1000</v>
       </c>
       <c r="H151" s="4" t="s">
         <v>1009</v>
@@ -14774,7 +14774,7 @@
         <v>1015</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>1016</v>
+        <v>1000</v>
       </c>
       <c r="H152" s="4" t="s">
         <v>1016</v>
@@ -14851,7 +14851,7 @@
         <v>1021</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>1022</v>
+        <v>1000</v>
       </c>
       <c r="H153" s="4" t="s">
         <v>1022</v>
@@ -14928,7 +14928,7 @@
         <v>1027</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>1028</v>
+        <v>1000</v>
       </c>
       <c r="H154" s="4" t="s">
         <v>1028</v>
@@ -15005,7 +15005,7 @@
         <v>1033</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>1034</v>
+        <v>1000</v>
       </c>
       <c r="H155" s="4" t="s">
         <v>1034</v>
@@ -15082,7 +15082,7 @@
         <v>1039</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>1040</v>
+        <v>1000</v>
       </c>
       <c r="H156" s="4" t="s">
         <v>1040</v>
@@ -15158,7 +15158,7 @@
         <v>1045</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>1046</v>
+        <v>1000</v>
       </c>
       <c r="H157" s="4" t="s">
         <v>1046</v>
@@ -15234,7 +15234,7 @@
         <v>1051</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>1052</v>
+        <v>1000</v>
       </c>
       <c r="H158" s="4" t="s">
         <v>1052</v>
@@ -15310,7 +15310,7 @@
         <v>1057</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>1058</v>
+        <v>1000</v>
       </c>
       <c r="H159" s="4" t="s">
         <v>1058</v>
@@ -15386,7 +15386,7 @@
         <v>1063</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>1064</v>
+        <v>1000</v>
       </c>
       <c r="H160" s="4" t="s">
         <v>1064</v>
@@ -15462,7 +15462,7 @@
         <v>1069</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>1070</v>
+        <v>1000</v>
       </c>
       <c r="H161" s="4" t="s">
         <v>1070</v>
@@ -15538,7 +15538,7 @@
         <v>1075</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>1076</v>
+        <v>1000</v>
       </c>
       <c r="H162" s="4" t="s">
         <v>1076</v>
@@ -15614,7 +15614,7 @@
         <v>1081</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>1082</v>
+        <v>1000</v>
       </c>
       <c r="H163" s="4" t="s">
         <v>1082</v>
@@ -15690,7 +15690,7 @@
         <v>1087</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>1088</v>
+        <v>1000</v>
       </c>
       <c r="H164" s="4" t="s">
         <v>1088</v>
@@ -15766,7 +15766,7 @@
         <v>1093</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>1094</v>
+        <v>1000</v>
       </c>
       <c r="H165" s="4" t="s">
         <v>1094</v>
@@ -15842,7 +15842,7 @@
         <v>1099</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="H166" s="4" t="s">
         <v>1100</v>
@@ -15916,7 +15916,7 @@
         <v>1105</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>1106</v>
+        <v>1000</v>
       </c>
       <c r="H167" s="4" t="s">
         <v>1106</v>
@@ -15990,7 +15990,7 @@
         <v>1111</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>1112</v>
+        <v>1000</v>
       </c>
       <c r="H168" s="4" t="s">
         <v>1112</v>
@@ -16064,7 +16064,7 @@
         <v>1117</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>1118</v>
+        <v>1000</v>
       </c>
       <c r="H169" s="4" t="s">
         <v>1118</v>
@@ -16138,7 +16138,7 @@
         <v>460</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>1122</v>
+        <v>1000</v>
       </c>
       <c r="H170" s="4" t="s">
         <v>1122</v>
@@ -16212,7 +16212,7 @@
         <v>1126</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>1127</v>
+        <v>1000</v>
       </c>
       <c r="H171" s="4" t="s">
         <v>1127</v>
@@ -16288,7 +16288,7 @@
         <v>1131</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>1132</v>
+        <v>1000</v>
       </c>
       <c r="H172" s="4" t="s">
         <v>1132</v>
@@ -16364,7 +16364,7 @@
         <v>1136</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>1137</v>
+        <v>1000</v>
       </c>
       <c r="H173" s="4" t="s">
         <v>1137</v>
@@ -16440,7 +16440,7 @@
         <v>1141</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>1142</v>
+        <v>1000</v>
       </c>
       <c r="H174" s="4" t="s">
         <v>1142</v>
@@ -16516,7 +16516,7 @@
         <v>1146</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>1147</v>
+        <v>1000</v>
       </c>
       <c r="H175" s="4" t="s">
         <v>1147</v>
@@ -16592,7 +16592,7 @@
         <v>1151</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>1152</v>
+        <v>1000</v>
       </c>
       <c r="H176" s="4" t="s">
         <v>1152</v>
@@ -16668,7 +16668,7 @@
         <v>1156</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>1157</v>
+        <v>1000</v>
       </c>
       <c r="H177" s="4" t="s">
         <v>1157</v>
@@ -16744,7 +16744,7 @@
         <v>1161</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>1162</v>
+        <v>1000</v>
       </c>
       <c r="H178" s="4" t="s">
         <v>1162</v>
@@ -16820,7 +16820,7 @@
         <v>1166</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>1167</v>
+        <v>1000</v>
       </c>
       <c r="H179" s="4" t="s">
         <v>1167</v>
@@ -16896,7 +16896,7 @@
         <v>1171</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>1172</v>
+        <v>1000</v>
       </c>
       <c r="H180" s="4" t="s">
         <v>1172</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -2971,10 +2971,10 @@
     <t>地狱冰龙王</t>
   </si>
   <si>
-    <t>90000000000000000000000000000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>32000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000</t>
+    <t>900僧</t>
+  </si>
+  <si>
+    <t>3200不</t>
   </si>
   <si>
     <t>3000000000000</t>
@@ -2989,7 +2989,7 @@
     <t>深渊鸡王</t>
   </si>
   <si>
-    <t>1000恒</t>
+    <t>1000极</t>
   </si>
   <si>
     <t>9000僧</t>
@@ -2998,7 +2998,7 @@
     <t>64000不</t>
   </si>
   <si>
-    <t>10垓</t>
+    <t>10秭</t>
   </si>
   <si>
     <t>3300000000000</t>
@@ -3013,7 +3013,7 @@
     <t>深渊鹿王</t>
   </si>
   <si>
-    <t>4000恒</t>
+    <t>4000极</t>
   </si>
   <si>
     <t>9祇</t>
@@ -3022,7 +3022,7 @@
     <t>128可</t>
   </si>
   <si>
-    <t>50垓</t>
+    <t>100秭</t>
   </si>
   <si>
     <t>3600000000000</t>
@@ -3037,7 +3037,7 @@
     <t>深渊草王</t>
   </si>
   <si>
-    <t>16000恒</t>
+    <t>16000极</t>
   </si>
   <si>
     <t>90祇</t>
@@ -3046,7 +3046,7 @@
     <t>2560可</t>
   </si>
   <si>
-    <t>250垓</t>
+    <t>1000秭</t>
   </si>
   <si>
     <t>3900000000000</t>
@@ -3061,7 +3061,7 @@
     <t>深渊猫王</t>
   </si>
   <si>
-    <t>64000恒</t>
+    <t>64000极</t>
   </si>
   <si>
     <t>900祇</t>
@@ -3070,7 +3070,7 @@
     <t>5思</t>
   </si>
   <si>
-    <t>1250垓</t>
+    <t>1穰</t>
   </si>
   <si>
     <t>4200000000000</t>
@@ -3094,7 +3094,7 @@
     <t>100思</t>
   </si>
   <si>
-    <t>6250垓</t>
+    <t>10穰</t>
   </si>
   <si>
     <t>4500000000000</t>
@@ -3118,7 +3118,7 @@
     <t>2000思</t>
   </si>
   <si>
-    <t>25000垓</t>
+    <t>100穰</t>
   </si>
   <si>
     <t>4800000000000</t>
@@ -4851,7 +4851,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="11.5" spans="3:23">
+    <row r="6" s="1" customFormat="1" ht="12" spans="3:23">
       <c r="C6" s="1" t="s">
         <v>37</v>
       </c>
@@ -14267,13 +14267,13 @@
       <c r="F145" s="1" t="s">
         <v>961</v>
       </c>
-      <c r="G145" s="12" t="s">
+      <c r="G145" s="4" t="s">
         <v>962</v>
       </c>
-      <c r="H145" s="11" t="s">
+      <c r="H145" s="1" t="s">
         <v>962</v>
       </c>
-      <c r="I145" s="13" t="s">
+      <c r="I145" s="9" t="s">
         <v>963</v>
       </c>
       <c r="J145" s="1">

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="1100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="1125">
   <si>
     <t>ID</t>
   </si>
@@ -3100,67 +3100,142 @@
     <t>4500000000000</t>
   </si>
   <si>
+    <t>10145</t>
+  </si>
+  <si>
+    <t>1145</t>
+  </si>
+  <si>
+    <t>深渊雪王</t>
+  </si>
+  <si>
+    <t>96恒</t>
+  </si>
+  <si>
+    <t>9那</t>
+  </si>
+  <si>
+    <t>2议</t>
+  </si>
+  <si>
+    <t>3万</t>
+  </si>
+  <si>
+    <t>1000穰</t>
+  </si>
+  <si>
+    <t>4800000000000</t>
+  </si>
+  <si>
+    <t>10146</t>
+  </si>
+  <si>
+    <t>1146</t>
+  </si>
+  <si>
+    <t>深渊蝠王</t>
+  </si>
+  <si>
+    <t>400恒</t>
+  </si>
+  <si>
+    <t>90那</t>
+  </si>
+  <si>
+    <t>40议</t>
+  </si>
+  <si>
+    <t>15万</t>
+  </si>
+  <si>
+    <t>10000穰</t>
+  </si>
+  <si>
+    <t>5100000000000</t>
+  </si>
+  <si>
+    <t>10147</t>
+  </si>
+  <si>
+    <t>1147</t>
+  </si>
+  <si>
+    <t>深渊骷髅王</t>
+  </si>
+  <si>
+    <t>1600恒</t>
+  </si>
+  <si>
+    <t>900那</t>
+  </si>
+  <si>
+    <t>800议</t>
+  </si>
+  <si>
+    <t>75万</t>
+  </si>
+  <si>
+    <t>10沟</t>
+  </si>
+  <si>
+    <t>5400000000000</t>
+  </si>
+  <si>
+    <t>10148</t>
+  </si>
+  <si>
+    <t>1148</t>
+  </si>
+  <si>
+    <t>深渊尸王</t>
+  </si>
+  <si>
+    <t>6400恒</t>
+  </si>
+  <si>
+    <t>9000那</t>
+  </si>
+  <si>
+    <t>16000议</t>
+  </si>
+  <si>
+    <t>375万</t>
+  </si>
+  <si>
+    <t>100沟</t>
+  </si>
+  <si>
+    <t>5700000000000</t>
+  </si>
+  <si>
+    <t>10149</t>
+  </si>
+  <si>
+    <t>1149</t>
+  </si>
+  <si>
+    <t>深渊蛇王</t>
+  </si>
+  <si>
+    <t>3河</t>
+  </si>
+  <si>
+    <t>9由</t>
+  </si>
+  <si>
+    <t>32无</t>
+  </si>
+  <si>
+    <t>2000万</t>
+  </si>
+  <si>
+    <t>1000沟</t>
+  </si>
+  <si>
+    <t>6000000000000</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>10145</t>
-  </si>
-  <si>
-    <t>1145</t>
-  </si>
-  <si>
-    <t>深渊雪王</t>
-  </si>
-  <si>
-    <t>4800000000000</t>
-  </si>
-  <si>
-    <t>10146</t>
-  </si>
-  <si>
-    <t>1146</t>
-  </si>
-  <si>
-    <t>深渊蝠王</t>
-  </si>
-  <si>
-    <t>5100000000000</t>
-  </si>
-  <si>
-    <t>10147</t>
-  </si>
-  <si>
-    <t>1147</t>
-  </si>
-  <si>
-    <t>深渊骷髅王</t>
-  </si>
-  <si>
-    <t>5400000000000</t>
-  </si>
-  <si>
-    <t>10148</t>
-  </si>
-  <si>
-    <t>1148</t>
-  </si>
-  <si>
-    <t>深渊尸王</t>
-  </si>
-  <si>
-    <t>5700000000000</t>
-  </si>
-  <si>
-    <t>10149</t>
-  </si>
-  <si>
-    <t>1149</t>
-  </si>
-  <si>
-    <t>深渊蛇王</t>
-  </si>
-  <si>
-    <t>6000000000000</t>
   </si>
   <si>
     <t>10150</t>
@@ -4634,7 +4709,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="11.5" spans="3:23">
+    <row r="6" s="1" customFormat="1" ht="12" spans="3:23">
       <c r="C6" s="1" t="s">
         <v>37</v>
       </c>
@@ -14461,38 +14536,34 @@
       </c>
     </row>
     <row r="151" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A151" s="4" t="s">
+      <c r="A151" s="4"/>
+      <c r="B151" s="4"/>
+      <c r="C151" s="15" t="s">
         <v>1005</v>
       </c>
-      <c r="B151" s="4" t="s">
-        <v>1005</v>
-      </c>
-      <c r="C151" s="15" t="s">
+      <c r="D151" s="15" t="s">
         <v>1006</v>
-      </c>
-      <c r="D151" s="15" t="s">
-        <v>1007</v>
       </c>
       <c r="E151" s="1">
         <v>5</v>
       </c>
       <c r="F151" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G151" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="G151" s="1">
-        <v>0</v>
-      </c>
-      <c r="H151" s="1">
-        <v>0</v>
-      </c>
-      <c r="I151" s="1">
-        <v>0</v>
-      </c>
-      <c r="J151" s="1">
-        <v>0</v>
-      </c>
-      <c r="K151" s="1">
-        <v>0</v>
+      <c r="H151" s="5" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J151" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K151" s="1" t="s">
+        <v>1012</v>
       </c>
       <c r="L151" s="1">
         <f t="shared" si="50"/>
@@ -14522,10 +14593,10 @@
         <v>99.99</v>
       </c>
       <c r="S151" s="15" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="T151" s="15" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="V151" s="1" t="s">
         <v>156</v>
@@ -14537,38 +14608,34 @@
       <c r="Y151" s="4"/>
     </row>
     <row r="152" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A152" s="4" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>1005</v>
-      </c>
+      <c r="A152" s="4"/>
+      <c r="B152" s="4"/>
       <c r="C152" s="15" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="D152" s="15" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="E152" s="1">
         <v>5</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1012</v>
-      </c>
-      <c r="G152" s="1">
-        <v>0</v>
-      </c>
-      <c r="H152" s="1">
-        <v>0</v>
-      </c>
-      <c r="I152" s="1">
-        <v>0</v>
-      </c>
-      <c r="J152" s="1">
-        <v>0</v>
-      </c>
-      <c r="K152" s="1">
-        <v>0</v>
+        <v>1016</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="H152" s="5" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="J152" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="K152" s="1" t="s">
+        <v>1021</v>
       </c>
       <c r="L152" s="1">
         <f t="shared" si="50"/>
@@ -14598,10 +14665,10 @@
         <v>99.99</v>
       </c>
       <c r="S152" s="15" t="s">
-        <v>1013</v>
+        <v>1022</v>
       </c>
       <c r="T152" s="15" t="s">
-        <v>1013</v>
+        <v>1022</v>
       </c>
       <c r="V152" s="1" t="s">
         <v>156</v>
@@ -14613,38 +14680,34 @@
       <c r="Y152" s="4"/>
     </row>
     <row r="153" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A153" s="4" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B153" s="4" t="s">
-        <v>1005</v>
-      </c>
+      <c r="A153" s="4"/>
+      <c r="B153" s="4"/>
       <c r="C153" s="15" t="s">
-        <v>1014</v>
+        <v>1023</v>
       </c>
       <c r="D153" s="15" t="s">
-        <v>1015</v>
+        <v>1024</v>
       </c>
       <c r="E153" s="1">
         <v>5</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>1016</v>
-      </c>
-      <c r="G153" s="1">
-        <v>0</v>
-      </c>
-      <c r="H153" s="1">
-        <v>0</v>
-      </c>
-      <c r="I153" s="1">
-        <v>0</v>
-      </c>
-      <c r="J153" s="1">
-        <v>0</v>
-      </c>
-      <c r="K153" s="1">
-        <v>0</v>
+        <v>1025</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H153" s="5" t="s">
+        <v>1027</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="J153" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="K153" s="1" t="s">
+        <v>1030</v>
       </c>
       <c r="L153" s="1">
         <f t="shared" si="50"/>
@@ -14674,10 +14737,10 @@
         <v>99.99</v>
       </c>
       <c r="S153" s="15" t="s">
-        <v>1017</v>
+        <v>1031</v>
       </c>
       <c r="T153" s="15" t="s">
-        <v>1017</v>
+        <v>1031</v>
       </c>
       <c r="V153" s="1" t="s">
         <v>156</v>
@@ -14689,38 +14752,34 @@
       <c r="Y153" s="4"/>
     </row>
     <row r="154" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A154" s="4" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B154" s="4" t="s">
-        <v>1005</v>
-      </c>
+      <c r="A154" s="4"/>
+      <c r="B154" s="4"/>
       <c r="C154" s="15" t="s">
-        <v>1018</v>
+        <v>1032</v>
       </c>
       <c r="D154" s="15" t="s">
-        <v>1019</v>
+        <v>1033</v>
       </c>
       <c r="E154" s="1">
         <v>5</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>1020</v>
-      </c>
-      <c r="G154" s="1">
-        <v>0</v>
-      </c>
-      <c r="H154" s="1">
-        <v>0</v>
-      </c>
-      <c r="I154" s="1">
-        <v>0</v>
-      </c>
-      <c r="J154" s="1">
-        <v>0</v>
-      </c>
-      <c r="K154" s="1">
-        <v>0</v>
+        <v>1034</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H154" s="5" t="s">
+        <v>1036</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="J154" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="K154" s="1" t="s">
+        <v>1039</v>
       </c>
       <c r="L154" s="1">
         <f t="shared" si="50"/>
@@ -14750,10 +14809,10 @@
         <v>99.99</v>
       </c>
       <c r="S154" s="15" t="s">
-        <v>1021</v>
+        <v>1040</v>
       </c>
       <c r="T154" s="15" t="s">
-        <v>1021</v>
+        <v>1040</v>
       </c>
       <c r="V154" s="1" t="s">
         <v>156</v>
@@ -14765,38 +14824,34 @@
       <c r="Y154" s="4"/>
     </row>
     <row r="155" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A155" s="4" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B155" s="4" t="s">
-        <v>1005</v>
-      </c>
+      <c r="A155" s="4"/>
+      <c r="B155" s="4"/>
       <c r="C155" s="15" t="s">
-        <v>1022</v>
+        <v>1041</v>
       </c>
       <c r="D155" s="15" t="s">
-        <v>1023</v>
+        <v>1042</v>
       </c>
       <c r="E155" s="1">
         <v>5</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>1024</v>
-      </c>
-      <c r="G155" s="1">
-        <v>0</v>
-      </c>
-      <c r="H155" s="1">
-        <v>0</v>
-      </c>
-      <c r="I155" s="1">
-        <v>0</v>
-      </c>
-      <c r="J155" s="1">
-        <v>0</v>
-      </c>
-      <c r="K155" s="1">
-        <v>0</v>
+        <v>1043</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H155" s="5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="J155" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="K155" s="1" t="s">
+        <v>1048</v>
       </c>
       <c r="L155" s="1">
         <f t="shared" si="50"/>
@@ -14826,10 +14881,10 @@
         <v>99.99</v>
       </c>
       <c r="S155" s="15" t="s">
-        <v>1025</v>
+        <v>1049</v>
       </c>
       <c r="T155" s="15" t="s">
-        <v>1025</v>
+        <v>1049</v>
       </c>
       <c r="V155" s="1" t="s">
         <v>156</v>
@@ -14842,22 +14897,22 @@
     </row>
     <row r="156" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A156" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>1026</v>
+        <v>1051</v>
       </c>
       <c r="D156" s="15" t="s">
-        <v>1027</v>
+        <v>1052</v>
       </c>
       <c r="E156" s="1">
         <v>5</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>1028</v>
+        <v>1053</v>
       </c>
       <c r="G156" s="1">
         <v>0</v>
@@ -14918,22 +14973,22 @@
     </row>
     <row r="157" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A157" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>1029</v>
+        <v>1054</v>
       </c>
       <c r="D157" s="15" t="s">
-        <v>1030</v>
+        <v>1055</v>
       </c>
       <c r="E157" s="1">
         <v>5</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>1031</v>
+        <v>1056</v>
       </c>
       <c r="G157" s="1">
         <v>0</v>
@@ -14994,22 +15049,22 @@
     </row>
     <row r="158" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A158" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>1032</v>
+        <v>1057</v>
       </c>
       <c r="D158" s="15" t="s">
-        <v>1033</v>
+        <v>1058</v>
       </c>
       <c r="E158" s="1">
         <v>5</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1034</v>
+        <v>1059</v>
       </c>
       <c r="G158" s="1">
         <v>0</v>
@@ -15070,22 +15125,22 @@
     </row>
     <row r="159" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A159" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>1035</v>
+        <v>1060</v>
       </c>
       <c r="D159" s="15" t="s">
-        <v>1036</v>
+        <v>1061</v>
       </c>
       <c r="E159" s="1">
         <v>5</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1037</v>
+        <v>1062</v>
       </c>
       <c r="G159" s="1">
         <v>0</v>
@@ -15146,22 +15201,22 @@
     </row>
     <row r="160" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A160" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>1038</v>
+        <v>1063</v>
       </c>
       <c r="D160" s="15" t="s">
-        <v>1039</v>
+        <v>1064</v>
       </c>
       <c r="E160" s="1">
         <v>5</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>1040</v>
+        <v>1065</v>
       </c>
       <c r="G160" s="1">
         <v>0</v>
@@ -15222,22 +15277,22 @@
     </row>
     <row r="161" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A161" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>1041</v>
+        <v>1066</v>
       </c>
       <c r="D161" s="15" t="s">
-        <v>1042</v>
+        <v>1067</v>
       </c>
       <c r="E161" s="1">
         <v>5</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>1043</v>
+        <v>1068</v>
       </c>
       <c r="G161" s="1">
         <v>0</v>
@@ -15298,22 +15353,22 @@
     </row>
     <row r="162" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A162" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>1044</v>
+        <v>1069</v>
       </c>
       <c r="D162" s="15" t="s">
-        <v>1045</v>
+        <v>1070</v>
       </c>
       <c r="E162" s="1">
         <v>5</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1046</v>
+        <v>1071</v>
       </c>
       <c r="G162" s="1">
         <v>0</v>
@@ -15374,22 +15429,22 @@
     </row>
     <row r="163" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A163" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>1047</v>
+        <v>1072</v>
       </c>
       <c r="D163" s="15" t="s">
-        <v>1048</v>
+        <v>1073</v>
       </c>
       <c r="E163" s="1">
         <v>5</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1049</v>
+        <v>1074</v>
       </c>
       <c r="G163" s="1">
         <v>0</v>
@@ -15450,22 +15505,22 @@
     </row>
     <row r="164" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A164" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>1050</v>
+        <v>1075</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>1051</v>
+        <v>1076</v>
       </c>
       <c r="E164" s="1">
         <v>5</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1052</v>
+        <v>1077</v>
       </c>
       <c r="G164" s="1">
         <v>0</v>
@@ -15526,22 +15581,22 @@
     </row>
     <row r="165" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A165" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>1053</v>
+        <v>1078</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>1054</v>
+        <v>1079</v>
       </c>
       <c r="E165" s="1">
         <v>5</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1055</v>
+        <v>1080</v>
       </c>
       <c r="G165" s="1">
         <v>0</v>
@@ -15602,22 +15657,22 @@
     </row>
     <row r="166" customHeight="1" spans="1:23">
       <c r="A166" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>1056</v>
+        <v>1081</v>
       </c>
       <c r="D166" s="15" t="s">
-        <v>1057</v>
+        <v>1082</v>
       </c>
       <c r="E166" s="1">
         <v>5</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1058</v>
+        <v>1083</v>
       </c>
       <c r="G166" s="1">
         <v>0</v>
@@ -15676,22 +15731,22 @@
     </row>
     <row r="167" customHeight="1" spans="1:23">
       <c r="A167" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>1059</v>
+        <v>1084</v>
       </c>
       <c r="D167" s="15" t="s">
-        <v>1060</v>
+        <v>1085</v>
       </c>
       <c r="E167" s="1">
         <v>5</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1061</v>
+        <v>1086</v>
       </c>
       <c r="G167" s="1">
         <v>0</v>
@@ -15750,22 +15805,22 @@
     </row>
     <row r="168" customHeight="1" spans="1:23">
       <c r="A168" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>1062</v>
+        <v>1087</v>
       </c>
       <c r="D168" s="15" t="s">
-        <v>1063</v>
+        <v>1088</v>
       </c>
       <c r="E168" s="1">
         <v>5</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1064</v>
+        <v>1089</v>
       </c>
       <c r="G168" s="1">
         <v>0</v>
@@ -15824,22 +15879,22 @@
     </row>
     <row r="169" customHeight="1" spans="1:23">
       <c r="A169" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>1065</v>
+        <v>1090</v>
       </c>
       <c r="D169" s="15" t="s">
-        <v>1066</v>
+        <v>1091</v>
       </c>
       <c r="E169" s="1">
         <v>5</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1067</v>
+        <v>1092</v>
       </c>
       <c r="G169" s="1">
         <v>0</v>
@@ -15898,16 +15953,16 @@
     </row>
     <row r="170" customHeight="1" spans="1:23">
       <c r="A170" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C170" s="15" t="s">
-        <v>1068</v>
+        <v>1093</v>
       </c>
       <c r="D170" s="15" t="s">
-        <v>1069</v>
+        <v>1094</v>
       </c>
       <c r="E170" s="1">
         <v>5</v>
@@ -15972,22 +16027,22 @@
     </row>
     <row r="171" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A171" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C171" s="15" t="s">
-        <v>1070</v>
+        <v>1095</v>
       </c>
       <c r="D171" s="15" t="s">
-        <v>1071</v>
+        <v>1096</v>
       </c>
       <c r="E171" s="1">
         <v>5</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1072</v>
+        <v>1097</v>
       </c>
       <c r="G171" s="1">
         <v>0</v>
@@ -16048,22 +16103,22 @@
     </row>
     <row r="172" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A172" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>1073</v>
+        <v>1098</v>
       </c>
       <c r="D172" s="15" t="s">
-        <v>1074</v>
+        <v>1099</v>
       </c>
       <c r="E172" s="1">
         <v>5</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="G172" s="1">
         <v>0</v>
@@ -16124,22 +16179,22 @@
     </row>
     <row r="173" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A173" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C173" s="15" t="s">
-        <v>1076</v>
+        <v>1101</v>
       </c>
       <c r="D173" s="15" t="s">
-        <v>1077</v>
+        <v>1102</v>
       </c>
       <c r="E173" s="1">
         <v>5</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1078</v>
+        <v>1103</v>
       </c>
       <c r="G173" s="1">
         <v>0</v>
@@ -16200,22 +16255,22 @@
     </row>
     <row r="174" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A174" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C174" s="15" t="s">
-        <v>1079</v>
+        <v>1104</v>
       </c>
       <c r="D174" s="15" t="s">
-        <v>1080</v>
+        <v>1105</v>
       </c>
       <c r="E174" s="1">
         <v>5</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1081</v>
+        <v>1106</v>
       </c>
       <c r="G174" s="1">
         <v>0</v>
@@ -16276,22 +16331,22 @@
     </row>
     <row r="175" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A175" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C175" s="15" t="s">
-        <v>1082</v>
+        <v>1107</v>
       </c>
       <c r="D175" s="15" t="s">
-        <v>1083</v>
+        <v>1108</v>
       </c>
       <c r="E175" s="1">
         <v>5</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1084</v>
+        <v>1109</v>
       </c>
       <c r="G175" s="1">
         <v>0</v>
@@ -16352,22 +16407,22 @@
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A176" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C176" s="15" t="s">
-        <v>1085</v>
+        <v>1110</v>
       </c>
       <c r="D176" s="15" t="s">
-        <v>1086</v>
+        <v>1111</v>
       </c>
       <c r="E176" s="1">
         <v>5</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1087</v>
+        <v>1112</v>
       </c>
       <c r="G176" s="1">
         <v>0</v>
@@ -16428,22 +16483,22 @@
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A177" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C177" s="15" t="s">
-        <v>1088</v>
+        <v>1113</v>
       </c>
       <c r="D177" s="15" t="s">
-        <v>1089</v>
+        <v>1114</v>
       </c>
       <c r="E177" s="1">
         <v>5</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1090</v>
+        <v>1115</v>
       </c>
       <c r="G177" s="1">
         <v>0</v>
@@ -16504,22 +16559,22 @@
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A178" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C178" s="15" t="s">
-        <v>1091</v>
+        <v>1116</v>
       </c>
       <c r="D178" s="15" t="s">
-        <v>1092</v>
+        <v>1117</v>
       </c>
       <c r="E178" s="1">
         <v>5</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1093</v>
+        <v>1118</v>
       </c>
       <c r="G178" s="1">
         <v>0</v>
@@ -16580,22 +16635,22 @@
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A179" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C179" s="15" t="s">
-        <v>1094</v>
+        <v>1119</v>
       </c>
       <c r="D179" s="15" t="s">
-        <v>1095</v>
+        <v>1120</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1096</v>
+        <v>1121</v>
       </c>
       <c r="G179" s="1">
         <v>0</v>
@@ -16656,22 +16711,22 @@
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A180" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="C180" s="15" t="s">
-        <v>1097</v>
+        <v>1122</v>
       </c>
       <c r="D180" s="15" t="s">
-        <v>1098</v>
+        <v>1123</v>
       </c>
       <c r="E180" s="1">
         <v>5</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1099</v>
+        <v>1124</v>
       </c>
       <c r="G180" s="1">
         <v>0</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="1125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="1155">
   <si>
     <t>ID</t>
   </si>
@@ -3235,52 +3235,142 @@
     <t>6000000000000</t>
   </si>
   <si>
+    <t>10150</t>
+  </si>
+  <si>
+    <t>1150</t>
+  </si>
+  <si>
+    <t>深渊狼王</t>
+  </si>
+  <si>
+    <t>15河</t>
+  </si>
+  <si>
+    <t>90由</t>
+  </si>
+  <si>
+    <t>640无</t>
+  </si>
+  <si>
+    <t>2亿</t>
+  </si>
+  <si>
+    <t>1涧</t>
+  </si>
+  <si>
+    <t>6300000000000</t>
+  </si>
+  <si>
+    <t>10151</t>
+  </si>
+  <si>
+    <t>1151</t>
+  </si>
+  <si>
+    <t>深渊沙虫王</t>
+  </si>
+  <si>
+    <t>75河</t>
+  </si>
+  <si>
+    <t>900由</t>
+  </si>
+  <si>
+    <t>12800无</t>
+  </si>
+  <si>
+    <t>20亿</t>
+  </si>
+  <si>
+    <t>10涧</t>
+  </si>
+  <si>
+    <t>6600000000000</t>
+  </si>
+  <si>
+    <t>10152</t>
+  </si>
+  <si>
+    <t>1152</t>
+  </si>
+  <si>
+    <t>深渊鹰王</t>
+  </si>
+  <si>
+    <t>375河</t>
+  </si>
+  <si>
+    <t>9000由</t>
+  </si>
+  <si>
+    <t>25量</t>
+  </si>
+  <si>
+    <t>200亿</t>
+  </si>
+  <si>
+    <t>100涧</t>
+  </si>
+  <si>
+    <t>6900000000000</t>
+  </si>
+  <si>
+    <t>10153</t>
+  </si>
+  <si>
+    <t>1153</t>
+  </si>
+  <si>
+    <t>深渊角虫王</t>
+  </si>
+  <si>
+    <t>2000河</t>
+  </si>
+  <si>
+    <t>9他</t>
+  </si>
+  <si>
+    <t>250量</t>
+  </si>
+  <si>
+    <t>2000亿</t>
+  </si>
+  <si>
+    <t>1000涧</t>
+  </si>
+  <si>
+    <t>7200000000000</t>
+  </si>
+  <si>
+    <t>10154</t>
+  </si>
+  <si>
+    <t>1154</t>
+  </si>
+  <si>
+    <t>深渊蜈蚣王</t>
+  </si>
+  <si>
+    <t>1沙</t>
+  </si>
+  <si>
+    <t>90他</t>
+  </si>
+  <si>
+    <t>5000量</t>
+  </si>
+  <si>
+    <t>2兆</t>
+  </si>
+  <si>
+    <t>1正</t>
+  </si>
+  <si>
+    <t>7500000000000</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>10150</t>
-  </si>
-  <si>
-    <t>1150</t>
-  </si>
-  <si>
-    <t>深渊狼王</t>
-  </si>
-  <si>
-    <t>10151</t>
-  </si>
-  <si>
-    <t>1151</t>
-  </si>
-  <si>
-    <t>深渊沙虫王</t>
-  </si>
-  <si>
-    <t>10152</t>
-  </si>
-  <si>
-    <t>1152</t>
-  </si>
-  <si>
-    <t>深渊鹰王</t>
-  </si>
-  <si>
-    <t>10153</t>
-  </si>
-  <si>
-    <t>1153</t>
-  </si>
-  <si>
-    <t>深渊角虫王</t>
-  </si>
-  <si>
-    <t>10154</t>
-  </si>
-  <si>
-    <t>1154</t>
-  </si>
-  <si>
-    <t>深渊蜈蚣王</t>
   </si>
   <si>
     <t>10155</t>
@@ -14896,38 +14986,34 @@
       <c r="Y155" s="4"/>
     </row>
     <row r="156" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A156" s="4" t="s">
+      <c r="A156" s="4"/>
+      <c r="B156" s="4"/>
+      <c r="C156" s="15" t="s">
         <v>1050</v>
       </c>
-      <c r="B156" s="4" t="s">
-        <v>1050</v>
-      </c>
-      <c r="C156" s="15" t="s">
+      <c r="D156" s="15" t="s">
         <v>1051</v>
-      </c>
-      <c r="D156" s="15" t="s">
-        <v>1052</v>
       </c>
       <c r="E156" s="1">
         <v>5</v>
       </c>
       <c r="F156" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G156" s="1" t="s">
         <v>1053</v>
       </c>
-      <c r="G156" s="1">
-        <v>0</v>
-      </c>
-      <c r="H156" s="1">
-        <v>0</v>
-      </c>
-      <c r="I156" s="1">
-        <v>0</v>
-      </c>
-      <c r="J156" s="1">
-        <v>0</v>
-      </c>
-      <c r="K156" s="1">
-        <v>0</v>
+      <c r="H156" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="J156" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="K156" s="1" t="s">
+        <v>1057</v>
       </c>
       <c r="L156" s="1">
         <f t="shared" si="50"/>
@@ -14957,10 +15043,10 @@
         <v>99.99</v>
       </c>
       <c r="S156" s="15" t="s">
-        <v>822</v>
+        <v>1058</v>
       </c>
       <c r="T156" s="15" t="s">
-        <v>822</v>
+        <v>1058</v>
       </c>
       <c r="V156" s="1" t="s">
         <v>156</v>
@@ -14972,38 +15058,34 @@
       <c r="Y156" s="4"/>
     </row>
     <row r="157" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A157" s="4" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B157" s="4" t="s">
-        <v>1050</v>
-      </c>
+      <c r="A157" s="4"/>
+      <c r="B157" s="4"/>
       <c r="C157" s="15" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="D157" s="15" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="E157" s="1">
         <v>5</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>1056</v>
-      </c>
-      <c r="G157" s="1">
-        <v>0</v>
-      </c>
-      <c r="H157" s="1">
-        <v>0</v>
-      </c>
-      <c r="I157" s="1">
-        <v>0</v>
-      </c>
-      <c r="J157" s="1">
-        <v>0</v>
-      </c>
-      <c r="K157" s="1">
-        <v>0</v>
+        <v>1061</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H157" s="5" t="s">
+        <v>1063</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="J157" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="K157" s="1" t="s">
+        <v>1066</v>
       </c>
       <c r="L157" s="1">
         <f t="shared" si="50"/>
@@ -15033,10 +15115,10 @@
         <v>99.99</v>
       </c>
       <c r="S157" s="15" t="s">
-        <v>828</v>
+        <v>1067</v>
       </c>
       <c r="T157" s="15" t="s">
-        <v>828</v>
+        <v>1067</v>
       </c>
       <c r="V157" s="1" t="s">
         <v>156</v>
@@ -15048,38 +15130,34 @@
       <c r="Y157" s="4"/>
     </row>
     <row r="158" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A158" s="4" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B158" s="4" t="s">
-        <v>1050</v>
-      </c>
+      <c r="A158" s="4"/>
+      <c r="B158" s="4"/>
       <c r="C158" s="15" t="s">
-        <v>1057</v>
+        <v>1068</v>
       </c>
       <c r="D158" s="15" t="s">
-        <v>1058</v>
+        <v>1069</v>
       </c>
       <c r="E158" s="1">
         <v>5</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="G158" s="1">
-        <v>0</v>
-      </c>
-      <c r="H158" s="1">
-        <v>0</v>
-      </c>
-      <c r="I158" s="1">
-        <v>0</v>
-      </c>
-      <c r="J158" s="1">
-        <v>0</v>
-      </c>
-      <c r="K158" s="1">
-        <v>0</v>
+        <v>1070</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="H158" s="5" t="s">
+        <v>1072</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="J158" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="K158" s="1" t="s">
+        <v>1075</v>
       </c>
       <c r="L158" s="1">
         <f t="shared" si="50"/>
@@ -15109,10 +15187,10 @@
         <v>99.99</v>
       </c>
       <c r="S158" s="15" t="s">
-        <v>834</v>
+        <v>1076</v>
       </c>
       <c r="T158" s="15" t="s">
-        <v>834</v>
+        <v>1076</v>
       </c>
       <c r="V158" s="1" t="s">
         <v>156</v>
@@ -15124,38 +15202,34 @@
       <c r="Y158" s="4"/>
     </row>
     <row r="159" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A159" s="4" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B159" s="4" t="s">
-        <v>1050</v>
-      </c>
+      <c r="A159" s="4"/>
+      <c r="B159" s="4"/>
       <c r="C159" s="15" t="s">
-        <v>1060</v>
+        <v>1077</v>
       </c>
       <c r="D159" s="15" t="s">
-        <v>1061</v>
+        <v>1078</v>
       </c>
       <c r="E159" s="1">
         <v>5</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1062</v>
-      </c>
-      <c r="G159" s="1">
-        <v>0</v>
-      </c>
-      <c r="H159" s="1">
-        <v>0</v>
-      </c>
-      <c r="I159" s="1">
-        <v>0</v>
-      </c>
-      <c r="J159" s="1">
-        <v>0</v>
-      </c>
-      <c r="K159" s="1">
-        <v>0</v>
+        <v>1079</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H159" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="J159" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="K159" s="1" t="s">
+        <v>1084</v>
       </c>
       <c r="L159" s="1">
         <f t="shared" si="50"/>
@@ -15185,10 +15259,10 @@
         <v>99.99</v>
       </c>
       <c r="S159" s="15" t="s">
-        <v>840</v>
+        <v>1085</v>
       </c>
       <c r="T159" s="15" t="s">
-        <v>840</v>
+        <v>1085</v>
       </c>
       <c r="V159" s="1" t="s">
         <v>156</v>
@@ -15200,38 +15274,34 @@
       <c r="Y159" s="4"/>
     </row>
     <row r="160" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A160" s="4" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B160" s="4" t="s">
-        <v>1050</v>
-      </c>
+      <c r="A160" s="4"/>
+      <c r="B160" s="4"/>
       <c r="C160" s="15" t="s">
-        <v>1063</v>
+        <v>1086</v>
       </c>
       <c r="D160" s="15" t="s">
-        <v>1064</v>
+        <v>1087</v>
       </c>
       <c r="E160" s="1">
         <v>5</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>1065</v>
-      </c>
-      <c r="G160" s="1">
-        <v>0</v>
-      </c>
-      <c r="H160" s="1">
-        <v>0</v>
-      </c>
-      <c r="I160" s="1">
-        <v>0</v>
-      </c>
-      <c r="J160" s="1">
-        <v>0</v>
-      </c>
-      <c r="K160" s="1">
-        <v>0</v>
+        <v>1088</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="H160" s="5" t="s">
+        <v>1090</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="J160" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="K160" s="1" t="s">
+        <v>1093</v>
       </c>
       <c r="L160" s="1">
         <f t="shared" si="50"/>
@@ -15261,10 +15331,10 @@
         <v>99.99</v>
       </c>
       <c r="S160" s="15" t="s">
-        <v>846</v>
+        <v>1094</v>
       </c>
       <c r="T160" s="15" t="s">
-        <v>846</v>
+        <v>1094</v>
       </c>
       <c r="V160" s="1" t="s">
         <v>156</v>
@@ -15277,22 +15347,22 @@
     </row>
     <row r="161" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A161" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>1066</v>
+        <v>1096</v>
       </c>
       <c r="D161" s="15" t="s">
-        <v>1067</v>
+        <v>1097</v>
       </c>
       <c r="E161" s="1">
         <v>5</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>1068</v>
+        <v>1098</v>
       </c>
       <c r="G161" s="1">
         <v>0</v>
@@ -15353,22 +15423,22 @@
     </row>
     <row r="162" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A162" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>1069</v>
+        <v>1099</v>
       </c>
       <c r="D162" s="15" t="s">
-        <v>1070</v>
+        <v>1100</v>
       </c>
       <c r="E162" s="1">
         <v>5</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1071</v>
+        <v>1101</v>
       </c>
       <c r="G162" s="1">
         <v>0</v>
@@ -15429,22 +15499,22 @@
     </row>
     <row r="163" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A163" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>1072</v>
+        <v>1102</v>
       </c>
       <c r="D163" s="15" t="s">
-        <v>1073</v>
+        <v>1103</v>
       </c>
       <c r="E163" s="1">
         <v>5</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1074</v>
+        <v>1104</v>
       </c>
       <c r="G163" s="1">
         <v>0</v>
@@ -15505,22 +15575,22 @@
     </row>
     <row r="164" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A164" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>1075</v>
+        <v>1105</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>1076</v>
+        <v>1106</v>
       </c>
       <c r="E164" s="1">
         <v>5</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1077</v>
+        <v>1107</v>
       </c>
       <c r="G164" s="1">
         <v>0</v>
@@ -15581,22 +15651,22 @@
     </row>
     <row r="165" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A165" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>1078</v>
+        <v>1108</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>1079</v>
+        <v>1109</v>
       </c>
       <c r="E165" s="1">
         <v>5</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1080</v>
+        <v>1110</v>
       </c>
       <c r="G165" s="1">
         <v>0</v>
@@ -15657,22 +15727,22 @@
     </row>
     <row r="166" customHeight="1" spans="1:23">
       <c r="A166" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>1081</v>
+        <v>1111</v>
       </c>
       <c r="D166" s="15" t="s">
-        <v>1082</v>
+        <v>1112</v>
       </c>
       <c r="E166" s="1">
         <v>5</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1083</v>
+        <v>1113</v>
       </c>
       <c r="G166" s="1">
         <v>0</v>
@@ -15731,22 +15801,22 @@
     </row>
     <row r="167" customHeight="1" spans="1:23">
       <c r="A167" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>1084</v>
+        <v>1114</v>
       </c>
       <c r="D167" s="15" t="s">
-        <v>1085</v>
+        <v>1115</v>
       </c>
       <c r="E167" s="1">
         <v>5</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1086</v>
+        <v>1116</v>
       </c>
       <c r="G167" s="1">
         <v>0</v>
@@ -15805,22 +15875,22 @@
     </row>
     <row r="168" customHeight="1" spans="1:23">
       <c r="A168" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>1087</v>
+        <v>1117</v>
       </c>
       <c r="D168" s="15" t="s">
-        <v>1088</v>
+        <v>1118</v>
       </c>
       <c r="E168" s="1">
         <v>5</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1089</v>
+        <v>1119</v>
       </c>
       <c r="G168" s="1">
         <v>0</v>
@@ -15879,22 +15949,22 @@
     </row>
     <row r="169" customHeight="1" spans="1:23">
       <c r="A169" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>1090</v>
+        <v>1120</v>
       </c>
       <c r="D169" s="15" t="s">
-        <v>1091</v>
+        <v>1121</v>
       </c>
       <c r="E169" s="1">
         <v>5</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1092</v>
+        <v>1122</v>
       </c>
       <c r="G169" s="1">
         <v>0</v>
@@ -15953,16 +16023,16 @@
     </row>
     <row r="170" customHeight="1" spans="1:23">
       <c r="A170" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C170" s="15" t="s">
-        <v>1093</v>
+        <v>1123</v>
       </c>
       <c r="D170" s="15" t="s">
-        <v>1094</v>
+        <v>1124</v>
       </c>
       <c r="E170" s="1">
         <v>5</v>
@@ -16027,22 +16097,22 @@
     </row>
     <row r="171" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A171" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C171" s="15" t="s">
-        <v>1095</v>
+        <v>1125</v>
       </c>
       <c r="D171" s="15" t="s">
-        <v>1096</v>
+        <v>1126</v>
       </c>
       <c r="E171" s="1">
         <v>5</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1097</v>
+        <v>1127</v>
       </c>
       <c r="G171" s="1">
         <v>0</v>
@@ -16103,22 +16173,22 @@
     </row>
     <row r="172" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A172" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>1098</v>
+        <v>1128</v>
       </c>
       <c r="D172" s="15" t="s">
-        <v>1099</v>
+        <v>1129</v>
       </c>
       <c r="E172" s="1">
         <v>5</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1100</v>
+        <v>1130</v>
       </c>
       <c r="G172" s="1">
         <v>0</v>
@@ -16179,22 +16249,22 @@
     </row>
     <row r="173" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A173" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C173" s="15" t="s">
-        <v>1101</v>
+        <v>1131</v>
       </c>
       <c r="D173" s="15" t="s">
-        <v>1102</v>
+        <v>1132</v>
       </c>
       <c r="E173" s="1">
         <v>5</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1103</v>
+        <v>1133</v>
       </c>
       <c r="G173" s="1">
         <v>0</v>
@@ -16255,22 +16325,22 @@
     </row>
     <row r="174" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A174" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C174" s="15" t="s">
-        <v>1104</v>
+        <v>1134</v>
       </c>
       <c r="D174" s="15" t="s">
-        <v>1105</v>
+        <v>1135</v>
       </c>
       <c r="E174" s="1">
         <v>5</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1106</v>
+        <v>1136</v>
       </c>
       <c r="G174" s="1">
         <v>0</v>
@@ -16331,22 +16401,22 @@
     </row>
     <row r="175" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A175" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C175" s="15" t="s">
-        <v>1107</v>
+        <v>1137</v>
       </c>
       <c r="D175" s="15" t="s">
-        <v>1108</v>
+        <v>1138</v>
       </c>
       <c r="E175" s="1">
         <v>5</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1109</v>
+        <v>1139</v>
       </c>
       <c r="G175" s="1">
         <v>0</v>
@@ -16407,22 +16477,22 @@
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A176" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C176" s="15" t="s">
-        <v>1110</v>
+        <v>1140</v>
       </c>
       <c r="D176" s="15" t="s">
-        <v>1111</v>
+        <v>1141</v>
       </c>
       <c r="E176" s="1">
         <v>5</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1112</v>
+        <v>1142</v>
       </c>
       <c r="G176" s="1">
         <v>0</v>
@@ -16483,22 +16553,22 @@
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A177" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C177" s="15" t="s">
-        <v>1113</v>
+        <v>1143</v>
       </c>
       <c r="D177" s="15" t="s">
-        <v>1114</v>
+        <v>1144</v>
       </c>
       <c r="E177" s="1">
         <v>5</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1115</v>
+        <v>1145</v>
       </c>
       <c r="G177" s="1">
         <v>0</v>
@@ -16559,22 +16629,22 @@
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A178" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C178" s="15" t="s">
-        <v>1116</v>
+        <v>1146</v>
       </c>
       <c r="D178" s="15" t="s">
-        <v>1117</v>
+        <v>1147</v>
       </c>
       <c r="E178" s="1">
         <v>5</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1118</v>
+        <v>1148</v>
       </c>
       <c r="G178" s="1">
         <v>0</v>
@@ -16635,22 +16705,22 @@
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A179" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C179" s="15" t="s">
-        <v>1119</v>
+        <v>1149</v>
       </c>
       <c r="D179" s="15" t="s">
-        <v>1120</v>
+        <v>1150</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1121</v>
+        <v>1151</v>
       </c>
       <c r="G179" s="1">
         <v>0</v>
@@ -16711,22 +16781,22 @@
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A180" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C180" s="15" t="s">
-        <v>1122</v>
+        <v>1152</v>
       </c>
       <c r="D180" s="15" t="s">
-        <v>1123</v>
+        <v>1153</v>
       </c>
       <c r="E180" s="1">
         <v>5</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1124</v>
+        <v>1154</v>
       </c>
       <c r="G180" s="1">
         <v>0</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="1155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="1170">
   <si>
     <t>ID</t>
   </si>
@@ -3217,7 +3217,7 @@
     <t>深渊蛇王</t>
   </si>
   <si>
-    <t>3河</t>
+    <t>6河</t>
   </si>
   <si>
     <t>9由</t>
@@ -3244,7 +3244,7 @@
     <t>深渊狼王</t>
   </si>
   <si>
-    <t>15河</t>
+    <t>90河</t>
   </si>
   <si>
     <t>90由</t>
@@ -3253,10 +3253,10 @@
     <t>640无</t>
   </si>
   <si>
-    <t>2亿</t>
-  </si>
-  <si>
-    <t>1涧</t>
+    <t>4亿</t>
+  </si>
+  <si>
+    <t>4涧</t>
   </si>
   <si>
     <t>6300000000000</t>
@@ -3271,7 +3271,7 @@
     <t>深渊沙虫王</t>
   </si>
   <si>
-    <t>75河</t>
+    <t>900河</t>
   </si>
   <si>
     <t>900由</t>
@@ -3280,10 +3280,10 @@
     <t>12800无</t>
   </si>
   <si>
-    <t>20亿</t>
-  </si>
-  <si>
-    <t>10涧</t>
+    <t>80亿</t>
+  </si>
+  <si>
+    <t>80涧</t>
   </si>
   <si>
     <t>6600000000000</t>
@@ -3298,7 +3298,7 @@
     <t>深渊鹰王</t>
   </si>
   <si>
-    <t>375河</t>
+    <t>9000河</t>
   </si>
   <si>
     <t>9000由</t>
@@ -3307,10 +3307,10 @@
     <t>25量</t>
   </si>
   <si>
-    <t>200亿</t>
-  </si>
-  <si>
-    <t>100涧</t>
+    <t>1600亿</t>
+  </si>
+  <si>
+    <t>1600涧</t>
   </si>
   <si>
     <t>6900000000000</t>
@@ -3325,7 +3325,7 @@
     <t>深渊角虫王</t>
   </si>
   <si>
-    <t>2000河</t>
+    <t>9沙</t>
   </si>
   <si>
     <t>9他</t>
@@ -3334,10 +3334,10 @@
     <t>250量</t>
   </si>
   <si>
-    <t>2000亿</t>
-  </si>
-  <si>
-    <t>1000涧</t>
+    <t>32兆</t>
+  </si>
+  <si>
+    <t>32正</t>
   </si>
   <si>
     <t>7200000000000</t>
@@ -3352,7 +3352,7 @@
     <t>深渊蜈蚣王</t>
   </si>
   <si>
-    <t>1沙</t>
+    <t>90沙</t>
   </si>
   <si>
     <t>90他</t>
@@ -3361,10 +3361,10 @@
     <t>5000量</t>
   </si>
   <si>
-    <t>2兆</t>
-  </si>
-  <si>
-    <t>1正</t>
+    <t>640兆</t>
+  </si>
+  <si>
+    <t>640正</t>
   </si>
   <si>
     <t>7500000000000</t>
@@ -3382,6 +3382,15 @@
     <t>深渊钳虫王</t>
   </si>
   <si>
+    <t>900沙</t>
+  </si>
+  <si>
+    <t>900他</t>
+  </si>
+  <si>
+    <t>10大</t>
+  </si>
+  <si>
     <t>10156</t>
   </si>
   <si>
@@ -3391,6 +3400,15 @@
     <t>深渊蠕虫王</t>
   </si>
   <si>
+    <t>9000沙</t>
+  </si>
+  <si>
+    <t>9000他</t>
+  </si>
+  <si>
+    <t>200大</t>
+  </si>
+  <si>
     <t>10157</t>
   </si>
   <si>
@@ -3400,6 +3418,15 @@
     <t>深渊猪王</t>
   </si>
   <si>
+    <t>9阿</t>
+  </si>
+  <si>
+    <t>9不</t>
+  </si>
+  <si>
+    <t>4000大</t>
+  </si>
+  <si>
     <t>10158</t>
   </si>
   <si>
@@ -3409,6 +3436,32 @@
     <t>深渊猪皇</t>
   </si>
   <si>
+    <t>90阿</t>
+  </si>
+  <si>
+    <t>90不</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+  </si>
+  <si>
     <t>10159</t>
   </si>
   <si>
@@ -3416,6 +3469,32 @@
   </si>
   <si>
     <t>深渊蝎王</t>
+  </si>
+  <si>
+    <t>900阿</t>
+  </si>
+  <si>
+    <t>900不</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>160数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
   </si>
   <si>
     <t>10160</t>
@@ -3561,7 +3640,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3725,6 +3804,12 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -15364,21 +15449,17 @@
       <c r="F161" s="1" t="s">
         <v>1098</v>
       </c>
-      <c r="G161" s="1">
-        <v>0</v>
-      </c>
-      <c r="H161" s="1">
-        <v>0</v>
-      </c>
-      <c r="I161" s="1">
-        <v>0</v>
-      </c>
-      <c r="J161" s="1">
-        <v>0</v>
-      </c>
-      <c r="K161" s="1">
-        <v>0</v>
-      </c>
+      <c r="G161" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H161" s="5" t="s">
+        <v>1100</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J161" s="1"/>
+      <c r="K161" s="1"/>
       <c r="L161" s="1">
         <f t="shared" si="50"/>
         <v>21700</v>
@@ -15429,32 +15510,28 @@
         <v>1095</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="D162" s="15" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="E162" s="1">
         <v>5</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="G162" s="1">
-        <v>0</v>
-      </c>
-      <c r="H162" s="1">
-        <v>0</v>
-      </c>
-      <c r="I162" s="1">
-        <v>0</v>
-      </c>
-      <c r="J162" s="1">
-        <v>0</v>
-      </c>
-      <c r="K162" s="1">
-        <v>0</v>
-      </c>
+        <v>1104</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="H162" s="5" t="s">
+        <v>1106</v>
+      </c>
+      <c r="I162" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="J162" s="1"/>
+      <c r="K162" s="1"/>
       <c r="L162" s="1">
         <f t="shared" si="50"/>
         <v>22300</v>
@@ -15505,32 +15582,28 @@
         <v>1095</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>1102</v>
+        <v>1108</v>
       </c>
       <c r="D163" s="15" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="E163" s="1">
         <v>5</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1104</v>
-      </c>
-      <c r="G163" s="1">
-        <v>0</v>
-      </c>
-      <c r="H163" s="1">
-        <v>0</v>
-      </c>
-      <c r="I163" s="1">
-        <v>0</v>
-      </c>
-      <c r="J163" s="1">
-        <v>0</v>
-      </c>
-      <c r="K163" s="1">
-        <v>0</v>
-      </c>
+        <v>1110</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H163" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="J163" s="1"/>
+      <c r="K163" s="1"/>
       <c r="L163" s="1">
         <f t="shared" si="50"/>
         <v>22900</v>
@@ -15581,31 +15654,25 @@
         <v>1095</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>1105</v>
+        <v>1114</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>1106</v>
+        <v>1115</v>
       </c>
       <c r="E164" s="1">
         <v>5</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G164" s="1">
-        <v>0</v>
-      </c>
-      <c r="H164" s="1">
-        <v>0</v>
-      </c>
-      <c r="I164" s="1">
-        <v>0</v>
-      </c>
-      <c r="J164" s="1">
-        <v>0</v>
-      </c>
-      <c r="K164" s="1">
-        <v>0</v>
+        <v>1116</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>1119</v>
       </c>
       <c r="L164" s="1">
         <f t="shared" si="50"/>
@@ -15657,31 +15724,25 @@
         <v>1095</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>1108</v>
+        <v>1120</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="E165" s="1">
         <v>5</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1110</v>
-      </c>
-      <c r="G165" s="1">
-        <v>0</v>
-      </c>
-      <c r="H165" s="1">
-        <v>0</v>
-      </c>
-      <c r="I165" s="1">
-        <v>0</v>
-      </c>
-      <c r="J165" s="1">
-        <v>0</v>
-      </c>
-      <c r="K165" s="1">
-        <v>0</v>
+        <v>1122</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H165" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>1125</v>
       </c>
       <c r="L165" s="1">
         <f t="shared" si="50"/>
@@ -15733,16 +15794,16 @@
         <v>1095</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>1111</v>
+        <v>1126</v>
       </c>
       <c r="D166" s="15" t="s">
-        <v>1112</v>
+        <v>1127</v>
       </c>
       <c r="E166" s="1">
         <v>5</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1113</v>
+        <v>1128</v>
       </c>
       <c r="G166" s="1">
         <v>0</v>
@@ -15807,16 +15868,16 @@
         <v>1095</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>1114</v>
+        <v>1129</v>
       </c>
       <c r="D167" s="15" t="s">
-        <v>1115</v>
+        <v>1130</v>
       </c>
       <c r="E167" s="1">
         <v>5</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1116</v>
+        <v>1131</v>
       </c>
       <c r="G167" s="1">
         <v>0</v>
@@ -15881,16 +15942,16 @@
         <v>1095</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>1117</v>
+        <v>1132</v>
       </c>
       <c r="D168" s="15" t="s">
-        <v>1118</v>
+        <v>1133</v>
       </c>
       <c r="E168" s="1">
         <v>5</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1119</v>
+        <v>1134</v>
       </c>
       <c r="G168" s="1">
         <v>0</v>
@@ -15955,16 +16016,16 @@
         <v>1095</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D169" s="15" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="E169" s="1">
         <v>5</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="G169" s="1">
         <v>0</v>
@@ -16029,10 +16090,10 @@
         <v>1095</v>
       </c>
       <c r="C170" s="15" t="s">
-        <v>1123</v>
+        <v>1138</v>
       </c>
       <c r="D170" s="15" t="s">
-        <v>1124</v>
+        <v>1139</v>
       </c>
       <c r="E170" s="1">
         <v>5</v>
@@ -16103,16 +16164,16 @@
         <v>1095</v>
       </c>
       <c r="C171" s="15" t="s">
-        <v>1125</v>
+        <v>1140</v>
       </c>
       <c r="D171" s="15" t="s">
-        <v>1126</v>
+        <v>1141</v>
       </c>
       <c r="E171" s="1">
         <v>5</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1127</v>
+        <v>1142</v>
       </c>
       <c r="G171" s="1">
         <v>0</v>
@@ -16179,16 +16240,16 @@
         <v>1095</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>1128</v>
+        <v>1143</v>
       </c>
       <c r="D172" s="15" t="s">
-        <v>1129</v>
+        <v>1144</v>
       </c>
       <c r="E172" s="1">
         <v>5</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1130</v>
+        <v>1145</v>
       </c>
       <c r="G172" s="1">
         <v>0</v>
@@ -16255,16 +16316,16 @@
         <v>1095</v>
       </c>
       <c r="C173" s="15" t="s">
-        <v>1131</v>
+        <v>1146</v>
       </c>
       <c r="D173" s="15" t="s">
-        <v>1132</v>
+        <v>1147</v>
       </c>
       <c r="E173" s="1">
         <v>5</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1133</v>
+        <v>1148</v>
       </c>
       <c r="G173" s="1">
         <v>0</v>
@@ -16331,16 +16392,16 @@
         <v>1095</v>
       </c>
       <c r="C174" s="15" t="s">
-        <v>1134</v>
+        <v>1149</v>
       </c>
       <c r="D174" s="15" t="s">
-        <v>1135</v>
+        <v>1150</v>
       </c>
       <c r="E174" s="1">
         <v>5</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1136</v>
+        <v>1151</v>
       </c>
       <c r="G174" s="1">
         <v>0</v>
@@ -16407,16 +16468,16 @@
         <v>1095</v>
       </c>
       <c r="C175" s="15" t="s">
-        <v>1137</v>
+        <v>1152</v>
       </c>
       <c r="D175" s="15" t="s">
-        <v>1138</v>
+        <v>1153</v>
       </c>
       <c r="E175" s="1">
         <v>5</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1139</v>
+        <v>1154</v>
       </c>
       <c r="G175" s="1">
         <v>0</v>
@@ -16483,16 +16544,16 @@
         <v>1095</v>
       </c>
       <c r="C176" s="15" t="s">
-        <v>1140</v>
+        <v>1155</v>
       </c>
       <c r="D176" s="15" t="s">
-        <v>1141</v>
+        <v>1156</v>
       </c>
       <c r="E176" s="1">
         <v>5</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1142</v>
+        <v>1157</v>
       </c>
       <c r="G176" s="1">
         <v>0</v>
@@ -16559,16 +16620,16 @@
         <v>1095</v>
       </c>
       <c r="C177" s="15" t="s">
-        <v>1143</v>
+        <v>1158</v>
       </c>
       <c r="D177" s="15" t="s">
-        <v>1144</v>
+        <v>1159</v>
       </c>
       <c r="E177" s="1">
         <v>5</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1145</v>
+        <v>1160</v>
       </c>
       <c r="G177" s="1">
         <v>0</v>
@@ -16635,16 +16696,16 @@
         <v>1095</v>
       </c>
       <c r="C178" s="15" t="s">
-        <v>1146</v>
+        <v>1161</v>
       </c>
       <c r="D178" s="15" t="s">
-        <v>1147</v>
+        <v>1162</v>
       </c>
       <c r="E178" s="1">
         <v>5</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1148</v>
+        <v>1163</v>
       </c>
       <c r="G178" s="1">
         <v>0</v>
@@ -16711,16 +16772,16 @@
         <v>1095</v>
       </c>
       <c r="C179" s="15" t="s">
-        <v>1149</v>
+        <v>1164</v>
       </c>
       <c r="D179" s="15" t="s">
-        <v>1150</v>
+        <v>1165</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1151</v>
+        <v>1166</v>
       </c>
       <c r="G179" s="1">
         <v>0</v>
@@ -16787,16 +16848,16 @@
         <v>1095</v>
       </c>
       <c r="C180" s="15" t="s">
-        <v>1152</v>
+        <v>1167</v>
       </c>
       <c r="D180" s="15" t="s">
-        <v>1153</v>
+        <v>1168</v>
       </c>
       <c r="E180" s="1">
         <v>5</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1154</v>
+        <v>1169</v>
       </c>
       <c r="G180" s="1">
         <v>0</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="1170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="1185">
   <si>
     <t>ID</t>
   </si>
@@ -3370,9 +3370,6 @@
     <t>7500000000000</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
     <t>10155</t>
   </si>
   <si>
@@ -3391,6 +3388,15 @@
     <t>10大</t>
   </si>
   <si>
+    <t>12800兆</t>
+  </si>
+  <si>
+    <t>12800正</t>
+  </si>
+  <si>
+    <t>7800000000000</t>
+  </si>
+  <si>
     <t>10156</t>
   </si>
   <si>
@@ -3409,6 +3415,15 @@
     <t>200大</t>
   </si>
   <si>
+    <t>25京</t>
+  </si>
+  <si>
+    <t>25载</t>
+  </si>
+  <si>
+    <t>8100000000000</t>
+  </si>
+  <si>
     <t>10157</t>
   </si>
   <si>
@@ -3425,6 +3440,15 @@
   </si>
   <si>
     <t>4000大</t>
+  </si>
+  <si>
+    <t>500京</t>
+  </si>
+  <si>
+    <t>500载</t>
+  </si>
+  <si>
+    <t>8400000000000</t>
   </si>
   <si>
     <t>10158</t>
@@ -3462,6 +3486,15 @@
     </r>
   </si>
   <si>
+    <t>1垓</t>
+  </si>
+  <si>
+    <t>1极</t>
+  </si>
+  <si>
+    <t>8700000000000</t>
+  </si>
+  <si>
     <t>10159</t>
   </si>
   <si>
@@ -3495,6 +3528,18 @@
       </rPr>
       <t>‌</t>
     </r>
+  </si>
+  <si>
+    <t>20垓</t>
+  </si>
+  <si>
+    <t>20极</t>
+  </si>
+  <si>
+    <t>9000000000000</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>10160</t>
@@ -4624,27 +4669,27 @@
   <dimension ref="A1:Y180"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="6.87610619469027" style="4" customWidth="1"/>
     <col min="2" max="2" width="9" style="4"/>
-    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="7.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.25" style="4" customWidth="1"/>
+    <col min="3" max="3" width="9.87610619469027" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6283185840708" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.87610619469027" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1238938053097" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.2477876106195" style="4" customWidth="1"/>
     <col min="8" max="8" width="23" style="4" customWidth="1"/>
-    <col min="9" max="9" width="22.625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="22.6283185840708" style="4" customWidth="1"/>
     <col min="10" max="10" width="16" style="4" customWidth="1"/>
-    <col min="11" max="11" width="11.75" style="4" customWidth="1"/>
-    <col min="12" max="12" width="15.875" style="4" customWidth="1"/>
-    <col min="13" max="15" width="12.125" style="4" customWidth="1"/>
-    <col min="16" max="16" width="9.625" style="4" customWidth="1"/>
-    <col min="17" max="17" width="7.5" style="4" customWidth="1"/>
-    <col min="18" max="18" width="7.125" style="4" customWidth="1"/>
-    <col min="19" max="19" width="16.375" style="4" customWidth="1"/>
+    <col min="11" max="11" width="11.7522123893805" style="4" customWidth="1"/>
+    <col min="12" max="12" width="15.8761061946903" style="4" customWidth="1"/>
+    <col min="13" max="15" width="12.1238938053097" style="4" customWidth="1"/>
+    <col min="16" max="16" width="9.6283185840708" style="4" customWidth="1"/>
+    <col min="17" max="17" width="7.50442477876106" style="4" customWidth="1"/>
+    <col min="18" max="18" width="7.12389380530973" style="4" customWidth="1"/>
+    <col min="19" max="19" width="16.3716814159292" style="4" customWidth="1"/>
     <col min="20" max="20" width="13" style="4" customWidth="1"/>
-    <col min="21" max="21" width="13.75" style="1" customWidth="1"/>
-    <col min="22" max="22" width="15.5" style="1" customWidth="1"/>
-    <col min="23" max="23" width="13.375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="13.7522123893805" style="1" customWidth="1"/>
+    <col min="22" max="22" width="15.5044247787611" style="1" customWidth="1"/>
+    <col min="23" max="23" width="13.3716814159292" style="1" customWidth="1"/>
     <col min="24" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -4884,7 +4929,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="12" spans="3:23">
+    <row r="6" s="1" customFormat="1" ht="11.6" spans="3:23">
       <c r="C6" s="1" t="s">
         <v>37</v>
       </c>
@@ -14474,7 +14519,7 @@
         <v>5200</v>
       </c>
       <c r="P147" s="4">
-        <f t="shared" ref="P146:P180" si="55">P146+3</f>
+        <f>P146+3</f>
         <v>90</v>
       </c>
       <c r="Q147" s="4">
@@ -14545,7 +14590,7 @@
         <v>5450</v>
       </c>
       <c r="P148" s="4">
-        <f t="shared" si="55"/>
+        <f>P147+3</f>
         <v>93</v>
       </c>
       <c r="Q148" s="4">
@@ -14616,7 +14661,7 @@
         <v>5700</v>
       </c>
       <c r="P149" s="4">
-        <f t="shared" si="55"/>
+        <f>P148+3</f>
         <v>96</v>
       </c>
       <c r="Q149" s="4">
@@ -14687,7 +14732,7 @@
         <v>5950</v>
       </c>
       <c r="P150" s="4">
-        <f t="shared" si="55"/>
+        <f>P149+3</f>
         <v>99</v>
       </c>
       <c r="Q150" s="4">
@@ -14757,7 +14802,7 @@
         <v>6200</v>
       </c>
       <c r="P151" s="4">
-        <f t="shared" si="55"/>
+        <f>P150+3</f>
         <v>102</v>
       </c>
       <c r="Q151" s="4">
@@ -14829,7 +14874,7 @@
         <v>6450</v>
       </c>
       <c r="P152" s="4">
-        <f t="shared" si="55"/>
+        <f>P151+3</f>
         <v>105</v>
       </c>
       <c r="Q152" s="4">
@@ -14901,7 +14946,7 @@
         <v>6700</v>
       </c>
       <c r="P153" s="4">
-        <f t="shared" si="55"/>
+        <f>P152+3</f>
         <v>108</v>
       </c>
       <c r="Q153" s="4">
@@ -14973,7 +15018,7 @@
         <v>6950</v>
       </c>
       <c r="P154" s="4">
-        <f t="shared" si="55"/>
+        <f>P153+3</f>
         <v>111</v>
       </c>
       <c r="Q154" s="4">
@@ -15045,7 +15090,7 @@
         <v>7200</v>
       </c>
       <c r="P155" s="4">
-        <f t="shared" si="55"/>
+        <f>P154+3</f>
         <v>114</v>
       </c>
       <c r="Q155" s="4">
@@ -15117,7 +15162,7 @@
         <v>7450</v>
       </c>
       <c r="P156" s="4">
-        <f t="shared" si="55"/>
+        <f>P155+3</f>
         <v>117</v>
       </c>
       <c r="Q156" s="4">
@@ -15189,7 +15234,7 @@
         <v>7700</v>
       </c>
       <c r="P157" s="4">
-        <f t="shared" si="55"/>
+        <f>P156+3</f>
         <v>120</v>
       </c>
       <c r="Q157" s="4">
@@ -15261,7 +15306,7 @@
         <v>7950</v>
       </c>
       <c r="P158" s="4">
-        <f t="shared" si="55"/>
+        <f>P157+3</f>
         <v>123</v>
       </c>
       <c r="Q158" s="4">
@@ -15333,7 +15378,7 @@
         <v>8200</v>
       </c>
       <c r="P159" s="4">
-        <f t="shared" si="55"/>
+        <f>P158+3</f>
         <v>126</v>
       </c>
       <c r="Q159" s="4">
@@ -15405,7 +15450,7 @@
         <v>8450</v>
       </c>
       <c r="P160" s="4">
-        <f t="shared" si="55"/>
+        <f>P159+3</f>
         <v>129</v>
       </c>
       <c r="Q160" s="4">
@@ -15431,35 +15476,35 @@
       <c r="Y160" s="4"/>
     </row>
     <row r="161" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A161" s="4" t="s">
+      <c r="A161" s="4"/>
+      <c r="B161" s="4"/>
+      <c r="C161" s="15" t="s">
         <v>1095</v>
       </c>
-      <c r="B161" s="4" t="s">
-        <v>1095</v>
-      </c>
-      <c r="C161" s="15" t="s">
+      <c r="D161" s="15" t="s">
         <v>1096</v>
-      </c>
-      <c r="D161" s="15" t="s">
-        <v>1097</v>
       </c>
       <c r="E161" s="1">
         <v>5</v>
       </c>
       <c r="F161" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="G161" s="1" t="s">
         <v>1098</v>
       </c>
-      <c r="G161" s="1" t="s">
+      <c r="H161" s="5" t="s">
         <v>1099</v>
       </c>
-      <c r="H161" s="5" t="s">
+      <c r="I161" s="1" t="s">
         <v>1100</v>
       </c>
-      <c r="I161" s="1" t="s">
+      <c r="J161" s="1" t="s">
         <v>1101</v>
       </c>
-      <c r="J161" s="1"/>
-      <c r="K161" s="1"/>
+      <c r="K161" s="1" t="s">
+        <v>1102</v>
+      </c>
       <c r="L161" s="1">
         <f t="shared" si="50"/>
         <v>21700</v>
@@ -15477,21 +15522,21 @@
         <v>8700</v>
       </c>
       <c r="P161" s="4">
-        <f t="shared" si="55"/>
-        <v>132</v>
+        <f>P160+4</f>
+        <v>133</v>
       </c>
       <c r="Q161" s="4">
-        <f t="shared" si="45"/>
-        <v>210</v>
+        <f>Q160+5</f>
+        <v>211</v>
       </c>
       <c r="R161" s="4">
         <v>99.99</v>
       </c>
       <c r="S161" s="15" t="s">
-        <v>852</v>
+        <v>1103</v>
       </c>
       <c r="T161" s="15" t="s">
-        <v>852</v>
+        <v>1103</v>
       </c>
       <c r="V161" s="1" t="s">
         <v>156</v>
@@ -15503,35 +15548,35 @@
       <c r="Y161" s="4"/>
     </row>
     <row r="162" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A162" s="4" t="s">
-        <v>1095</v>
-      </c>
-      <c r="B162" s="4" t="s">
-        <v>1095</v>
-      </c>
+      <c r="A162" s="4"/>
+      <c r="B162" s="4"/>
       <c r="C162" s="15" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="D162" s="15" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="E162" s="1">
         <v>5</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="H162" s="5" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>1107</v>
-      </c>
-      <c r="J162" s="1"/>
-      <c r="K162" s="1"/>
+        <v>1109</v>
+      </c>
+      <c r="J162" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="K162" s="1" t="s">
+        <v>1111</v>
+      </c>
       <c r="L162" s="1">
         <f t="shared" si="50"/>
         <v>22300</v>
@@ -15549,21 +15594,21 @@
         <v>8950</v>
       </c>
       <c r="P162" s="4">
-        <f t="shared" si="55"/>
-        <v>135</v>
+        <f>P161+4</f>
+        <v>137</v>
       </c>
       <c r="Q162" s="4">
-        <f t="shared" si="45"/>
-        <v>214</v>
+        <f>Q161+5</f>
+        <v>216</v>
       </c>
       <c r="R162" s="4">
         <v>99.99</v>
       </c>
       <c r="S162" s="15" t="s">
-        <v>858</v>
+        <v>1112</v>
       </c>
       <c r="T162" s="15" t="s">
-        <v>858</v>
+        <v>1112</v>
       </c>
       <c r="V162" s="1" t="s">
         <v>156</v>
@@ -15575,35 +15620,35 @@
       <c r="Y162" s="4"/>
     </row>
     <row r="163" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A163" s="4" t="s">
-        <v>1095</v>
-      </c>
-      <c r="B163" s="4" t="s">
-        <v>1095</v>
-      </c>
+      <c r="A163" s="4"/>
+      <c r="B163" s="4"/>
       <c r="C163" s="15" t="s">
-        <v>1108</v>
+        <v>1113</v>
       </c>
       <c r="D163" s="15" t="s">
-        <v>1109</v>
+        <v>1114</v>
       </c>
       <c r="E163" s="1">
         <v>5</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>1113</v>
-      </c>
-      <c r="J163" s="1"/>
-      <c r="K163" s="1"/>
+        <v>1118</v>
+      </c>
+      <c r="J163" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="K163" s="1" t="s">
+        <v>1120</v>
+      </c>
       <c r="L163" s="1">
         <f t="shared" si="50"/>
         <v>22900</v>
@@ -15621,21 +15666,21 @@
         <v>9200</v>
       </c>
       <c r="P163" s="4">
-        <f t="shared" si="55"/>
-        <v>138</v>
+        <f>P162+4</f>
+        <v>141</v>
       </c>
       <c r="Q163" s="4">
-        <f t="shared" si="45"/>
-        <v>218</v>
+        <f>Q162+5</f>
+        <v>221</v>
       </c>
       <c r="R163" s="4">
         <v>99.99</v>
       </c>
       <c r="S163" s="15" t="s">
-        <v>864</v>
+        <v>1121</v>
       </c>
       <c r="T163" s="15" t="s">
-        <v>864</v>
+        <v>1121</v>
       </c>
       <c r="V163" s="1" t="s">
         <v>156</v>
@@ -15647,32 +15692,34 @@
       <c r="Y163" s="4"/>
     </row>
     <row r="164" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A164" s="4" t="s">
-        <v>1095</v>
-      </c>
-      <c r="B164" s="4" t="s">
-        <v>1095</v>
-      </c>
+      <c r="A164" s="4"/>
+      <c r="B164" s="4"/>
       <c r="C164" s="15" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
       <c r="E164" s="1">
         <v>5</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>1117</v>
+        <v>1125</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>1118</v>
+        <v>1126</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>1119</v>
+        <v>1127</v>
+      </c>
+      <c r="J164" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K164" s="1" t="s">
+        <v>1129</v>
       </c>
       <c r="L164" s="1">
         <f t="shared" si="50"/>
@@ -15691,21 +15738,21 @@
         <v>9450</v>
       </c>
       <c r="P164" s="4">
-        <f t="shared" si="55"/>
-        <v>141</v>
+        <f>P163+4</f>
+        <v>145</v>
       </c>
       <c r="Q164" s="4">
-        <f t="shared" si="45"/>
-        <v>222</v>
+        <f>Q163+5</f>
+        <v>226</v>
       </c>
       <c r="R164" s="4">
         <v>99.99</v>
       </c>
       <c r="S164" s="15" t="s">
-        <v>870</v>
+        <v>1130</v>
       </c>
       <c r="T164" s="15" t="s">
-        <v>870</v>
+        <v>1130</v>
       </c>
       <c r="V164" s="1" t="s">
         <v>156</v>
@@ -15717,32 +15764,34 @@
       <c r="Y164" s="4"/>
     </row>
     <row r="165" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A165" s="4" t="s">
-        <v>1095</v>
-      </c>
-      <c r="B165" s="4" t="s">
-        <v>1095</v>
-      </c>
+      <c r="A165" s="4"/>
+      <c r="B165" s="4"/>
       <c r="C165" s="15" t="s">
-        <v>1120</v>
+        <v>1131</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>1121</v>
+        <v>1132</v>
       </c>
       <c r="E165" s="1">
         <v>5</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1122</v>
+        <v>1133</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>1123</v>
+        <v>1134</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>1124</v>
+        <v>1135</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>1125</v>
+        <v>1136</v>
+      </c>
+      <c r="J165" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="K165" s="1" t="s">
+        <v>1138</v>
       </c>
       <c r="L165" s="1">
         <f t="shared" si="50"/>
@@ -15761,21 +15810,21 @@
         <v>9700</v>
       </c>
       <c r="P165" s="4">
-        <f t="shared" si="55"/>
-        <v>144</v>
+        <f>P164+4</f>
+        <v>149</v>
       </c>
       <c r="Q165" s="4">
-        <f t="shared" si="45"/>
-        <v>226</v>
+        <f>Q164+5</f>
+        <v>231</v>
       </c>
       <c r="R165" s="4">
         <v>99.99</v>
       </c>
       <c r="S165" s="15" t="s">
-        <v>876</v>
+        <v>1139</v>
       </c>
       <c r="T165" s="15" t="s">
-        <v>876</v>
+        <v>1139</v>
       </c>
       <c r="V165" s="1" t="s">
         <v>156</v>
@@ -15788,22 +15837,22 @@
     </row>
     <row r="166" customHeight="1" spans="1:23">
       <c r="A166" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>1126</v>
+        <v>1141</v>
       </c>
       <c r="D166" s="15" t="s">
-        <v>1127</v>
+        <v>1142</v>
       </c>
       <c r="E166" s="1">
         <v>5</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1128</v>
+        <v>1143</v>
       </c>
       <c r="G166" s="1">
         <v>0</v>
@@ -15837,12 +15886,12 @@
         <v>9950</v>
       </c>
       <c r="P166" s="4">
-        <f t="shared" si="55"/>
-        <v>147</v>
+        <f t="shared" ref="P166:P180" si="55">P165+5</f>
+        <v>154</v>
       </c>
       <c r="Q166" s="4">
-        <f t="shared" si="45"/>
-        <v>230</v>
+        <f t="shared" ref="Q166:Q180" si="56">Q165+6</f>
+        <v>237</v>
       </c>
       <c r="R166" s="4">
         <v>99.99</v>
@@ -15862,22 +15911,22 @@
     </row>
     <row r="167" customHeight="1" spans="1:23">
       <c r="A167" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>1129</v>
+        <v>1144</v>
       </c>
       <c r="D167" s="15" t="s">
-        <v>1130</v>
+        <v>1145</v>
       </c>
       <c r="E167" s="1">
         <v>5</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1131</v>
+        <v>1146</v>
       </c>
       <c r="G167" s="1">
         <v>0</v>
@@ -15912,11 +15961,11 @@
       </c>
       <c r="P167" s="4">
         <f t="shared" si="55"/>
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="Q167" s="4">
-        <f t="shared" si="45"/>
-        <v>234</v>
+        <f t="shared" si="56"/>
+        <v>243</v>
       </c>
       <c r="R167" s="4">
         <v>99.99</v>
@@ -15936,22 +15985,22 @@
     </row>
     <row r="168" customHeight="1" spans="1:23">
       <c r="A168" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>1132</v>
+        <v>1147</v>
       </c>
       <c r="D168" s="15" t="s">
-        <v>1133</v>
+        <v>1148</v>
       </c>
       <c r="E168" s="1">
         <v>5</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1134</v>
+        <v>1149</v>
       </c>
       <c r="G168" s="1">
         <v>0</v>
@@ -15986,11 +16035,11 @@
       </c>
       <c r="P168" s="4">
         <f t="shared" si="55"/>
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="Q168" s="4">
-        <f t="shared" si="45"/>
-        <v>238</v>
+        <f t="shared" si="56"/>
+        <v>249</v>
       </c>
       <c r="R168" s="4">
         <v>99.99</v>
@@ -16010,22 +16059,22 @@
     </row>
     <row r="169" customHeight="1" spans="1:23">
       <c r="A169" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>1135</v>
+        <v>1150</v>
       </c>
       <c r="D169" s="15" t="s">
-        <v>1136</v>
+        <v>1151</v>
       </c>
       <c r="E169" s="1">
         <v>5</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1137</v>
+        <v>1152</v>
       </c>
       <c r="G169" s="1">
         <v>0</v>
@@ -16060,11 +16109,11 @@
       </c>
       <c r="P169" s="4">
         <f t="shared" si="55"/>
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="Q169" s="4">
-        <f t="shared" si="45"/>
-        <v>242</v>
+        <f t="shared" si="56"/>
+        <v>255</v>
       </c>
       <c r="R169" s="4">
         <v>99.99</v>
@@ -16084,16 +16133,16 @@
     </row>
     <row r="170" customHeight="1" spans="1:23">
       <c r="A170" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="C170" s="15" t="s">
-        <v>1138</v>
+        <v>1153</v>
       </c>
       <c r="D170" s="15" t="s">
-        <v>1139</v>
+        <v>1154</v>
       </c>
       <c r="E170" s="1">
         <v>5</v>
@@ -16134,11 +16183,11 @@
       </c>
       <c r="P170" s="4">
         <f t="shared" si="55"/>
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="Q170" s="4">
-        <f t="shared" si="45"/>
-        <v>246</v>
+        <f t="shared" si="56"/>
+        <v>261</v>
       </c>
       <c r="R170" s="4">
         <v>99.99</v>
@@ -16158,22 +16207,22 @@
     </row>
     <row r="171" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A171" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="C171" s="15" t="s">
-        <v>1140</v>
+        <v>1155</v>
       </c>
       <c r="D171" s="15" t="s">
-        <v>1141</v>
+        <v>1156</v>
       </c>
       <c r="E171" s="1">
         <v>5</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1142</v>
+        <v>1157</v>
       </c>
       <c r="G171" s="1">
         <v>0</v>
@@ -16208,11 +16257,11 @@
       </c>
       <c r="P171" s="4">
         <f t="shared" si="55"/>
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="Q171" s="4">
-        <f t="shared" si="45"/>
-        <v>250</v>
+        <f t="shared" si="56"/>
+        <v>267</v>
       </c>
       <c r="R171" s="4">
         <v>99.99</v>
@@ -16234,22 +16283,22 @@
     </row>
     <row r="172" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A172" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>1143</v>
+        <v>1158</v>
       </c>
       <c r="D172" s="15" t="s">
-        <v>1144</v>
+        <v>1159</v>
       </c>
       <c r="E172" s="1">
         <v>5</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1145</v>
+        <v>1160</v>
       </c>
       <c r="G172" s="1">
         <v>0</v>
@@ -16284,11 +16333,11 @@
       </c>
       <c r="P172" s="4">
         <f t="shared" si="55"/>
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="Q172" s="4">
-        <f t="shared" si="45"/>
-        <v>254</v>
+        <f t="shared" si="56"/>
+        <v>273</v>
       </c>
       <c r="R172" s="4">
         <v>99.99</v>
@@ -16310,22 +16359,22 @@
     </row>
     <row r="173" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A173" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="C173" s="15" t="s">
-        <v>1146</v>
+        <v>1161</v>
       </c>
       <c r="D173" s="15" t="s">
-        <v>1147</v>
+        <v>1162</v>
       </c>
       <c r="E173" s="1">
         <v>5</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1148</v>
+        <v>1163</v>
       </c>
       <c r="G173" s="1">
         <v>0</v>
@@ -16360,11 +16409,11 @@
       </c>
       <c r="P173" s="4">
         <f t="shared" si="55"/>
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="Q173" s="4">
-        <f t="shared" si="45"/>
-        <v>258</v>
+        <f t="shared" si="56"/>
+        <v>279</v>
       </c>
       <c r="R173" s="4">
         <v>99.99</v>
@@ -16386,22 +16435,22 @@
     </row>
     <row r="174" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A174" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="C174" s="15" t="s">
-        <v>1149</v>
+        <v>1164</v>
       </c>
       <c r="D174" s="15" t="s">
-        <v>1150</v>
+        <v>1165</v>
       </c>
       <c r="E174" s="1">
         <v>5</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1151</v>
+        <v>1166</v>
       </c>
       <c r="G174" s="1">
         <v>0</v>
@@ -16436,11 +16485,11 @@
       </c>
       <c r="P174" s="4">
         <f t="shared" si="55"/>
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="Q174" s="4">
-        <f t="shared" si="45"/>
-        <v>262</v>
+        <f t="shared" si="56"/>
+        <v>285</v>
       </c>
       <c r="R174" s="4">
         <v>99.99</v>
@@ -16462,22 +16511,22 @@
     </row>
     <row r="175" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A175" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="C175" s="15" t="s">
-        <v>1152</v>
+        <v>1167</v>
       </c>
       <c r="D175" s="15" t="s">
-        <v>1153</v>
+        <v>1168</v>
       </c>
       <c r="E175" s="1">
         <v>5</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1154</v>
+        <v>1169</v>
       </c>
       <c r="G175" s="1">
         <v>0</v>
@@ -16512,11 +16561,11 @@
       </c>
       <c r="P175" s="4">
         <f t="shared" si="55"/>
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="Q175" s="4">
-        <f t="shared" si="45"/>
-        <v>266</v>
+        <f t="shared" si="56"/>
+        <v>291</v>
       </c>
       <c r="R175" s="4">
         <v>99.99</v>
@@ -16538,22 +16587,22 @@
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A176" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="C176" s="15" t="s">
-        <v>1155</v>
+        <v>1170</v>
       </c>
       <c r="D176" s="15" t="s">
-        <v>1156</v>
+        <v>1171</v>
       </c>
       <c r="E176" s="1">
         <v>5</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1157</v>
+        <v>1172</v>
       </c>
       <c r="G176" s="1">
         <v>0</v>
@@ -16588,11 +16637,11 @@
       </c>
       <c r="P176" s="4">
         <f t="shared" si="55"/>
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="Q176" s="4">
-        <f t="shared" si="45"/>
-        <v>270</v>
+        <f t="shared" si="56"/>
+        <v>297</v>
       </c>
       <c r="R176" s="4">
         <v>99.99</v>
@@ -16614,22 +16663,22 @@
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A177" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="C177" s="15" t="s">
-        <v>1158</v>
+        <v>1173</v>
       </c>
       <c r="D177" s="15" t="s">
-        <v>1159</v>
+        <v>1174</v>
       </c>
       <c r="E177" s="1">
         <v>5</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1160</v>
+        <v>1175</v>
       </c>
       <c r="G177" s="1">
         <v>0</v>
@@ -16664,11 +16713,11 @@
       </c>
       <c r="P177" s="4">
         <f t="shared" si="55"/>
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="Q177" s="4">
-        <f t="shared" si="45"/>
-        <v>274</v>
+        <f t="shared" si="56"/>
+        <v>303</v>
       </c>
       <c r="R177" s="4">
         <v>99.99</v>
@@ -16690,22 +16739,22 @@
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A178" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="C178" s="15" t="s">
-        <v>1161</v>
+        <v>1176</v>
       </c>
       <c r="D178" s="15" t="s">
-        <v>1162</v>
+        <v>1177</v>
       </c>
       <c r="E178" s="1">
         <v>5</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1163</v>
+        <v>1178</v>
       </c>
       <c r="G178" s="1">
         <v>0</v>
@@ -16740,11 +16789,11 @@
       </c>
       <c r="P178" s="4">
         <f t="shared" si="55"/>
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="Q178" s="4">
-        <f t="shared" si="45"/>
-        <v>278</v>
+        <f t="shared" si="56"/>
+        <v>309</v>
       </c>
       <c r="R178" s="4">
         <v>99.99</v>
@@ -16766,22 +16815,22 @@
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A179" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="C179" s="15" t="s">
-        <v>1164</v>
+        <v>1179</v>
       </c>
       <c r="D179" s="15" t="s">
-        <v>1165</v>
+        <v>1180</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1166</v>
+        <v>1181</v>
       </c>
       <c r="G179" s="1">
         <v>0</v>
@@ -16816,11 +16865,11 @@
       </c>
       <c r="P179" s="4">
         <f t="shared" si="55"/>
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="Q179" s="4">
-        <f t="shared" si="45"/>
-        <v>282</v>
+        <f t="shared" si="56"/>
+        <v>315</v>
       </c>
       <c r="R179" s="4">
         <v>99.99</v>
@@ -16842,22 +16891,22 @@
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A180" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="C180" s="15" t="s">
-        <v>1167</v>
+        <v>1182</v>
       </c>
       <c r="D180" s="15" t="s">
-        <v>1168</v>
+        <v>1183</v>
       </c>
       <c r="E180" s="1">
         <v>5</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1169</v>
+        <v>1184</v>
       </c>
       <c r="G180" s="1">
         <v>0</v>
@@ -16892,11 +16941,11 @@
       </c>
       <c r="P180" s="4">
         <f t="shared" si="55"/>
-        <v>189</v>
+        <v>224</v>
       </c>
       <c r="Q180" s="4">
-        <f t="shared" si="45"/>
-        <v>286</v>
+        <f t="shared" si="56"/>
+        <v>321</v>
       </c>
       <c r="R180" s="4">
         <v>99.99</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -3466,24 +3466,7 @@
     <t>90不</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>8数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>‌</t>
-    </r>
+    <t>8数</t>
   </si>
   <si>
     <t>1垓</t>
@@ -3510,24 +3493,7 @@
     <t>900不</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>160数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>‌</t>
-    </r>
+    <t>160数</t>
   </si>
   <si>
     <t>20垓</t>
@@ -3685,7 +3651,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3849,12 +3815,6 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -14449,7 +14409,7 @@
         <v>4950</v>
       </c>
       <c r="P146" s="12">
-        <f>P145+3</f>
+        <f t="shared" ref="P146:P160" si="54">P145+3</f>
         <v>87</v>
       </c>
       <c r="Q146" s="12">
@@ -14496,7 +14456,7 @@
         <v>978</v>
       </c>
       <c r="J147" s="1">
-        <f t="shared" ref="J147:J155" si="54">J146*5</f>
+        <f t="shared" ref="J147:J155" si="55">J146*5</f>
         <v>50</v>
       </c>
       <c r="K147" s="1" t="s">
@@ -14519,7 +14479,7 @@
         <v>5200</v>
       </c>
       <c r="P147" s="4">
-        <f>P146+3</f>
+        <f t="shared" si="54"/>
         <v>90</v>
       </c>
       <c r="Q147" s="4">
@@ -14567,7 +14527,7 @@
         <v>986</v>
       </c>
       <c r="J148" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>250</v>
       </c>
       <c r="K148" s="1" t="s">
@@ -14590,7 +14550,7 @@
         <v>5450</v>
       </c>
       <c r="P148" s="4">
-        <f>P147+3</f>
+        <f t="shared" si="54"/>
         <v>93</v>
       </c>
       <c r="Q148" s="4">
@@ -14638,7 +14598,7 @@
         <v>994</v>
       </c>
       <c r="J149" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>1250</v>
       </c>
       <c r="K149" s="1" t="s">
@@ -14661,7 +14621,7 @@
         <v>5700</v>
       </c>
       <c r="P149" s="4">
-        <f>P148+3</f>
+        <f t="shared" si="54"/>
         <v>96</v>
       </c>
       <c r="Q149" s="4">
@@ -14709,7 +14669,7 @@
         <v>1002</v>
       </c>
       <c r="J150" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>6250</v>
       </c>
       <c r="K150" s="1" t="s">
@@ -14732,7 +14692,7 @@
         <v>5950</v>
       </c>
       <c r="P150" s="4">
-        <f>P149+3</f>
+        <f t="shared" si="54"/>
         <v>99</v>
       </c>
       <c r="Q150" s="4">
@@ -14802,7 +14762,7 @@
         <v>6200</v>
       </c>
       <c r="P151" s="4">
-        <f>P150+3</f>
+        <f t="shared" si="54"/>
         <v>102</v>
       </c>
       <c r="Q151" s="4">
@@ -14874,7 +14834,7 @@
         <v>6450</v>
       </c>
       <c r="P152" s="4">
-        <f>P151+3</f>
+        <f t="shared" si="54"/>
         <v>105</v>
       </c>
       <c r="Q152" s="4">
@@ -14946,7 +14906,7 @@
         <v>6700</v>
       </c>
       <c r="P153" s="4">
-        <f>P152+3</f>
+        <f t="shared" si="54"/>
         <v>108</v>
       </c>
       <c r="Q153" s="4">
@@ -15018,7 +14978,7 @@
         <v>6950</v>
       </c>
       <c r="P154" s="4">
-        <f>P153+3</f>
+        <f t="shared" si="54"/>
         <v>111</v>
       </c>
       <c r="Q154" s="4">
@@ -15090,7 +15050,7 @@
         <v>7200</v>
       </c>
       <c r="P155" s="4">
-        <f>P154+3</f>
+        <f t="shared" si="54"/>
         <v>114</v>
       </c>
       <c r="Q155" s="4">
@@ -15162,7 +15122,7 @@
         <v>7450</v>
       </c>
       <c r="P156" s="4">
-        <f>P155+3</f>
+        <f t="shared" si="54"/>
         <v>117</v>
       </c>
       <c r="Q156" s="4">
@@ -15234,7 +15194,7 @@
         <v>7700</v>
       </c>
       <c r="P157" s="4">
-        <f>P156+3</f>
+        <f t="shared" si="54"/>
         <v>120</v>
       </c>
       <c r="Q157" s="4">
@@ -15306,7 +15266,7 @@
         <v>7950</v>
       </c>
       <c r="P158" s="4">
-        <f>P157+3</f>
+        <f t="shared" si="54"/>
         <v>123</v>
       </c>
       <c r="Q158" s="4">
@@ -15378,7 +15338,7 @@
         <v>8200</v>
       </c>
       <c r="P159" s="4">
-        <f>P158+3</f>
+        <f t="shared" si="54"/>
         <v>126</v>
       </c>
       <c r="Q159" s="4">
@@ -15450,7 +15410,7 @@
         <v>8450</v>
       </c>
       <c r="P160" s="4">
-        <f>P159+3</f>
+        <f t="shared" si="54"/>
         <v>129</v>
       </c>
       <c r="Q160" s="4">
@@ -15886,11 +15846,11 @@
         <v>9950</v>
       </c>
       <c r="P166" s="4">
-        <f t="shared" ref="P166:P180" si="55">P165+5</f>
+        <f t="shared" ref="P166:P180" si="56">P165+5</f>
         <v>154</v>
       </c>
       <c r="Q166" s="4">
-        <f t="shared" ref="Q166:Q180" si="56">Q165+6</f>
+        <f t="shared" ref="Q166:Q180" si="57">Q165+6</f>
         <v>237</v>
       </c>
       <c r="R166" s="4">
@@ -15960,11 +15920,11 @@
         <v>10200</v>
       </c>
       <c r="P167" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>159</v>
       </c>
       <c r="Q167" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>243</v>
       </c>
       <c r="R167" s="4">
@@ -16034,11 +15994,11 @@
         <v>10450</v>
       </c>
       <c r="P168" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>164</v>
       </c>
       <c r="Q168" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>249</v>
       </c>
       <c r="R168" s="4">
@@ -16108,11 +16068,11 @@
         <v>10700</v>
       </c>
       <c r="P169" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>169</v>
       </c>
       <c r="Q169" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>255</v>
       </c>
       <c r="R169" s="4">
@@ -16182,11 +16142,11 @@
         <v>10950</v>
       </c>
       <c r="P170" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>174</v>
       </c>
       <c r="Q170" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>261</v>
       </c>
       <c r="R170" s="4">
@@ -16256,11 +16216,11 @@
         <v>11200</v>
       </c>
       <c r="P171" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>179</v>
       </c>
       <c r="Q171" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>267</v>
       </c>
       <c r="R171" s="4">
@@ -16332,11 +16292,11 @@
         <v>11450</v>
       </c>
       <c r="P172" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>184</v>
       </c>
       <c r="Q172" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>273</v>
       </c>
       <c r="R172" s="4">
@@ -16408,11 +16368,11 @@
         <v>11700</v>
       </c>
       <c r="P173" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>189</v>
       </c>
       <c r="Q173" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>279</v>
       </c>
       <c r="R173" s="4">
@@ -16484,11 +16444,11 @@
         <v>11950</v>
       </c>
       <c r="P174" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>194</v>
       </c>
       <c r="Q174" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>285</v>
       </c>
       <c r="R174" s="4">
@@ -16560,11 +16520,11 @@
         <v>12200</v>
       </c>
       <c r="P175" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>199</v>
       </c>
       <c r="Q175" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>291</v>
       </c>
       <c r="R175" s="4">
@@ -16636,11 +16596,11 @@
         <v>12450</v>
       </c>
       <c r="P176" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>204</v>
       </c>
       <c r="Q176" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>297</v>
       </c>
       <c r="R176" s="4">
@@ -16712,11 +16672,11 @@
         <v>12700</v>
       </c>
       <c r="P177" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>209</v>
       </c>
       <c r="Q177" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>303</v>
       </c>
       <c r="R177" s="4">
@@ -16788,11 +16748,11 @@
         <v>12950</v>
       </c>
       <c r="P178" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>214</v>
       </c>
       <c r="Q178" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>309</v>
       </c>
       <c r="R178" s="4">
@@ -16864,11 +16824,11 @@
         <v>13200</v>
       </c>
       <c r="P179" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>219</v>
       </c>
       <c r="Q179" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>315</v>
       </c>
       <c r="R179" s="4">
@@ -16940,11 +16900,11 @@
         <v>13450</v>
       </c>
       <c r="P180" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>224</v>
       </c>
       <c r="Q180" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>321</v>
       </c>
       <c r="R180" s="4">

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="1185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="1225">
   <si>
     <t>ID</t>
   </si>
@@ -3439,7 +3439,7 @@
     <t>9不</t>
   </si>
   <si>
-    <t>4000大</t>
+    <t>4E+115</t>
   </si>
   <si>
     <t>500京</t>
@@ -3466,7 +3466,7 @@
     <t>90不</t>
   </si>
   <si>
-    <t>8数</t>
+    <t>8E+116</t>
   </si>
   <si>
     <t>1垓</t>
@@ -3487,69 +3487,159 @@
     <t>深渊蝎王</t>
   </si>
   <si>
-    <t>900阿</t>
-  </si>
-  <si>
-    <t>900不</t>
-  </si>
-  <si>
-    <t>160数</t>
-  </si>
-  <si>
-    <t>20垓</t>
-  </si>
-  <si>
-    <t>20极</t>
+    <t>9E+66</t>
+  </si>
+  <si>
+    <t>9E+90</t>
+  </si>
+  <si>
+    <t>16E+117</t>
+  </si>
+  <si>
+    <t>2E+21</t>
+  </si>
+  <si>
+    <t>2E+49</t>
   </si>
   <si>
     <t>9000000000000</t>
   </si>
   <si>
+    <t>10160</t>
+  </si>
+  <si>
+    <t>1160</t>
+  </si>
+  <si>
+    <t>深渊恶魔教主</t>
+  </si>
+  <si>
+    <t>9E+67</t>
+  </si>
+  <si>
+    <t>9E+91</t>
+  </si>
+  <si>
+    <t>32E+118</t>
+  </si>
+  <si>
+    <t>4E+22</t>
+  </si>
+  <si>
+    <t>4E+50</t>
+  </si>
+  <si>
+    <t>9300000000000</t>
+  </si>
+  <si>
+    <t>10161</t>
+  </si>
+  <si>
+    <t>1161</t>
+  </si>
+  <si>
+    <t>深渊恶魔教皇</t>
+  </si>
+  <si>
+    <t>9E+68</t>
+  </si>
+  <si>
+    <t>9E+92</t>
+  </si>
+  <si>
+    <t>64E+119</t>
+  </si>
+  <si>
+    <t>8E+23</t>
+  </si>
+  <si>
+    <t>8E+51</t>
+  </si>
+  <si>
+    <t>9600000000000</t>
+  </si>
+  <si>
+    <t>10162</t>
+  </si>
+  <si>
+    <t>1162</t>
+  </si>
+  <si>
+    <t>深渊邪魔教主</t>
+  </si>
+  <si>
+    <t>9E+69</t>
+  </si>
+  <si>
+    <t>9E+93</t>
+  </si>
+  <si>
+    <t>128E+120</t>
+  </si>
+  <si>
+    <t>16E+24</t>
+  </si>
+  <si>
+    <t>16E+52</t>
+  </si>
+  <si>
+    <t>9900000000000</t>
+  </si>
+  <si>
+    <t>10163</t>
+  </si>
+  <si>
+    <t>1163</t>
+  </si>
+  <si>
+    <t>深渊邪魔教皇</t>
+  </si>
+  <si>
+    <t>9E+70</t>
+  </si>
+  <si>
+    <t>9E+94</t>
+  </si>
+  <si>
+    <t>256E+121</t>
+  </si>
+  <si>
+    <t>32E+25</t>
+  </si>
+  <si>
+    <t>32E+53</t>
+  </si>
+  <si>
+    <t>10200000000000</t>
+  </si>
+  <si>
+    <t>10164</t>
+  </si>
+  <si>
+    <t>1164</t>
+  </si>
+  <si>
+    <t>9E+71</t>
+  </si>
+  <si>
+    <t>9E+95</t>
+  </si>
+  <si>
+    <t>512E+122</t>
+  </si>
+  <si>
+    <t>64E+26</t>
+  </si>
+  <si>
+    <t>64E+54</t>
+  </si>
+  <si>
+    <t>10500000000000</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
-    <t>10160</t>
-  </si>
-  <si>
-    <t>1160</t>
-  </si>
-  <si>
-    <t>深渊恶魔教主</t>
-  </si>
-  <si>
-    <t>10161</t>
-  </si>
-  <si>
-    <t>1161</t>
-  </si>
-  <si>
-    <t>深渊恶魔教皇</t>
-  </si>
-  <si>
-    <t>10162</t>
-  </si>
-  <si>
-    <t>1162</t>
-  </si>
-  <si>
-    <t>深渊邪魔教主</t>
-  </si>
-  <si>
-    <t>10163</t>
-  </si>
-  <si>
-    <t>1163</t>
-  </si>
-  <si>
-    <t>深渊邪魔教皇</t>
-  </si>
-  <si>
-    <t>10164</t>
-  </si>
-  <si>
-    <t>1164</t>
-  </si>
-  <si>
     <t>10165</t>
   </si>
   <si>
@@ -3559,6 +3649,9 @@
     <t>深渊烈焰王</t>
   </si>
   <si>
+    <t>10800000000000</t>
+  </si>
+  <si>
     <t>10166</t>
   </si>
   <si>
@@ -3568,6 +3661,9 @@
     <t>深渊大邪王</t>
   </si>
   <si>
+    <t>11100000000000</t>
+  </si>
+  <si>
     <t>10167</t>
   </si>
   <si>
@@ -3577,6 +3673,9 @@
     <t>深渊尸魔王</t>
   </si>
   <si>
+    <t>11400000000000</t>
+  </si>
+  <si>
     <t>10168</t>
   </si>
   <si>
@@ -3586,6 +3685,9 @@
     <t>深渊骨魔王</t>
   </si>
   <si>
+    <t>11700000000000</t>
+  </si>
+  <si>
     <t>10169</t>
   </si>
   <si>
@@ -3595,6 +3697,9 @@
     <t>深渊牛魔王</t>
   </si>
   <si>
+    <t>12000000000000</t>
+  </si>
+  <si>
     <t>10170</t>
   </si>
   <si>
@@ -3604,6 +3709,9 @@
     <t>深渊水龙王</t>
   </si>
   <si>
+    <t>12300000000000</t>
+  </si>
+  <si>
     <t>10171</t>
   </si>
   <si>
@@ -3613,6 +3721,9 @@
     <t>深渊土龙王</t>
   </si>
   <si>
+    <t>12600000000000</t>
+  </si>
+  <si>
     <t>10172</t>
   </si>
   <si>
@@ -3622,6 +3733,9 @@
     <t>深渊毒龙王</t>
   </si>
   <si>
+    <t>12900000000000</t>
+  </si>
+  <si>
     <t>10173</t>
   </si>
   <si>
@@ -3631,6 +3745,9 @@
     <t>深渊火龙王</t>
   </si>
   <si>
+    <t>13200000000000</t>
+  </si>
+  <si>
     <t>10174</t>
   </si>
   <si>
@@ -3638,6 +3755,9 @@
   </si>
   <si>
     <t>深渊冰龙王</t>
+  </si>
+  <si>
+    <t>13500000000000</t>
   </si>
 </sst>
 </file>
@@ -3651,7 +3771,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3662,6 +3782,12 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -4152,16 +4278,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4170,136 +4293,147 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
@@ -4307,6 +4441,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4629,263 +4770,263 @@
   <dimension ref="A1:Y180"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.87610619469027" style="4" customWidth="1"/>
-    <col min="2" max="2" width="9" style="4"/>
+    <col min="1" max="1" width="6.87610619469027" style="5" customWidth="1"/>
+    <col min="2" max="2" width="9" style="5"/>
     <col min="3" max="3" width="9.87610619469027" style="1" customWidth="1"/>
     <col min="4" max="4" width="7.6283185840708" style="1" customWidth="1"/>
     <col min="5" max="5" width="6.87610619469027" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.1238938053097" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.2477876106195" style="4" customWidth="1"/>
-    <col min="8" max="8" width="23" style="4" customWidth="1"/>
-    <col min="9" max="9" width="22.6283185840708" style="4" customWidth="1"/>
-    <col min="10" max="10" width="16" style="4" customWidth="1"/>
-    <col min="11" max="11" width="11.7522123893805" style="4" customWidth="1"/>
-    <col min="12" max="12" width="15.8761061946903" style="4" customWidth="1"/>
-    <col min="13" max="15" width="12.1238938053097" style="4" customWidth="1"/>
-    <col min="16" max="16" width="9.6283185840708" style="4" customWidth="1"/>
-    <col min="17" max="17" width="7.50442477876106" style="4" customWidth="1"/>
-    <col min="18" max="18" width="7.12389380530973" style="4" customWidth="1"/>
-    <col min="19" max="19" width="16.3716814159292" style="4" customWidth="1"/>
-    <col min="20" max="20" width="13" style="4" customWidth="1"/>
+    <col min="7" max="7" width="23.2477876106195" style="5" customWidth="1"/>
+    <col min="8" max="8" width="23" style="5" customWidth="1"/>
+    <col min="9" max="9" width="22.6283185840708" style="5" customWidth="1"/>
+    <col min="10" max="10" width="16" style="5" customWidth="1"/>
+    <col min="11" max="11" width="11.7522123893805" style="5" customWidth="1"/>
+    <col min="12" max="12" width="15.8761061946903" style="5" customWidth="1"/>
+    <col min="13" max="15" width="12.1238938053097" style="5" customWidth="1"/>
+    <col min="16" max="16" width="9.6283185840708" style="5" customWidth="1"/>
+    <col min="17" max="17" width="7.50442477876106" style="5" customWidth="1"/>
+    <col min="18" max="18" width="7.12389380530973" style="5" customWidth="1"/>
+    <col min="19" max="19" width="16.3716814159292" style="5" customWidth="1"/>
+    <col min="20" max="20" width="13" style="5" customWidth="1"/>
     <col min="21" max="21" width="13.7522123893805" style="1" customWidth="1"/>
     <col min="22" max="22" width="15.5044247787611" style="1" customWidth="1"/>
     <col min="23" max="23" width="13.3716814159292" style="1" customWidth="1"/>
-    <col min="24" max="16384" width="9" style="4"/>
+    <col min="24" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
+      <c r="A1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="8" t="s">
+      <c r="U3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="8" t="s">
+      <c r="V3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="8" t="s">
+      <c r="W3" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="6" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="Q4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="R4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="S4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="T4" s="6" t="s">
+      <c r="T4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="U4" s="8" t="s">
+      <c r="U4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="V4" s="8" t="s">
+      <c r="V4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="W4" s="8" t="s">
+      <c r="W4" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="6" t="s">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="Q5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="R5" s="6" t="s">
+      <c r="R5" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="S5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="T5" s="6" t="s">
+      <c r="T5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="U5" s="8" t="s">
+      <c r="U5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="V5" s="8" t="s">
+      <c r="V5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="W5" s="8" t="s">
+      <c r="W5" s="9" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4902,13 +5043,13 @@
       <c r="F6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="19" t="s">
         <v>42</v>
       </c>
       <c r="J6" s="1">
@@ -4929,13 +5070,13 @@
       <c r="O6" s="1">
         <v>0</v>
       </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7">
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
         <v>0</v>
       </c>
       <c r="S6" s="1" t="s">
@@ -4991,13 +5132,13 @@
       <c r="O7" s="1">
         <v>0</v>
       </c>
-      <c r="P7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="7">
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
         <v>0</v>
       </c>
       <c r="S7" s="1" t="s">
@@ -5054,13 +5195,13 @@
       <c r="O8" s="1">
         <v>0</v>
       </c>
-      <c r="P8" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="7">
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8">
         <v>0</v>
       </c>
       <c r="S8" s="1" t="s">
@@ -5117,13 +5258,13 @@
       <c r="O9" s="1">
         <v>0</v>
       </c>
-      <c r="P9" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>0</v>
-      </c>
-      <c r="R9" s="7">
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
         <v>0</v>
       </c>
       <c r="S9" s="1" t="s">
@@ -5180,13 +5321,13 @@
       <c r="O10" s="1">
         <v>0</v>
       </c>
-      <c r="P10" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>0</v>
-      </c>
-      <c r="R10" s="7">
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8">
         <v>0</v>
       </c>
       <c r="S10" s="1" t="s">
@@ -5243,13 +5384,13 @@
       <c r="O11" s="1">
         <v>0</v>
       </c>
-      <c r="P11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>0</v>
-      </c>
-      <c r="R11" s="7">
+      <c r="P11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8">
         <v>0</v>
       </c>
       <c r="S11" s="1" t="s">
@@ -5306,13 +5447,13 @@
       <c r="O12" s="1">
         <v>0</v>
       </c>
-      <c r="P12" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>0</v>
-      </c>
-      <c r="R12" s="7">
+      <c r="P12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
         <v>0</v>
       </c>
       <c r="S12" s="1" t="s">
@@ -5369,13 +5510,13 @@
       <c r="O13" s="1">
         <v>0</v>
       </c>
-      <c r="P13" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="7">
-        <v>0</v>
-      </c>
-      <c r="R13" s="7">
+      <c r="P13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+      <c r="R13" s="8">
         <v>0</v>
       </c>
       <c r="S13" s="1" t="s">
@@ -5432,13 +5573,13 @@
       <c r="O14" s="1">
         <v>0</v>
       </c>
-      <c r="P14" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="7">
-        <v>0</v>
-      </c>
-      <c r="R14" s="7">
+      <c r="P14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8">
         <v>0</v>
       </c>
       <c r="S14" s="1" t="s">
@@ -5495,13 +5636,13 @@
       <c r="O15" s="1">
         <v>0</v>
       </c>
-      <c r="P15" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="7">
-        <v>0</v>
-      </c>
-      <c r="R15" s="7">
+      <c r="P15" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8">
         <v>0</v>
       </c>
       <c r="S15" s="1" t="s">
@@ -5558,13 +5699,13 @@
       <c r="O16" s="1">
         <v>0</v>
       </c>
-      <c r="P16" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="7">
-        <v>0</v>
-      </c>
-      <c r="R16" s="7">
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0</v>
+      </c>
+      <c r="R16" s="8">
         <v>0</v>
       </c>
       <c r="S16" s="1" t="s">
@@ -5621,13 +5762,13 @@
       <c r="O17" s="1">
         <v>0</v>
       </c>
-      <c r="P17" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="7">
-        <v>0</v>
-      </c>
-      <c r="R17" s="7">
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+      <c r="R17" s="8">
         <v>0</v>
       </c>
       <c r="S17" s="1" t="s">
@@ -5684,13 +5825,13 @@
       <c r="O18" s="1">
         <v>0</v>
       </c>
-      <c r="P18" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="7">
-        <v>0</v>
-      </c>
-      <c r="R18" s="7">
+      <c r="P18" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0</v>
+      </c>
+      <c r="R18" s="8">
         <v>0</v>
       </c>
       <c r="S18" s="1" t="s">
@@ -5747,13 +5888,13 @@
       <c r="O19" s="1">
         <v>0</v>
       </c>
-      <c r="P19" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="7">
-        <v>0</v>
-      </c>
-      <c r="R19" s="7">
+      <c r="P19" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>0</v>
+      </c>
+      <c r="R19" s="8">
         <v>0</v>
       </c>
       <c r="S19" s="1" t="s">
@@ -5810,13 +5951,13 @@
       <c r="O20" s="1">
         <v>0</v>
       </c>
-      <c r="P20" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="7">
-        <v>0</v>
-      </c>
-      <c r="R20" s="7">
+      <c r="P20" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>0</v>
+      </c>
+      <c r="R20" s="8">
         <v>0</v>
       </c>
       <c r="S20" s="1" t="s">
@@ -5874,13 +6015,13 @@
       <c r="O21" s="1">
         <v>0</v>
       </c>
-      <c r="P21" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="7">
-        <v>0</v>
-      </c>
-      <c r="R21" s="7">
+      <c r="P21" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>0</v>
+      </c>
+      <c r="R21" s="8">
         <v>0</v>
       </c>
       <c r="S21" s="1" t="s">
@@ -5938,13 +6079,13 @@
       <c r="O22" s="1">
         <v>0</v>
       </c>
-      <c r="P22" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="7">
-        <v>0</v>
-      </c>
-      <c r="R22" s="7">
+      <c r="P22" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>0</v>
+      </c>
+      <c r="R22" s="8">
         <v>0</v>
       </c>
       <c r="S22" s="1" t="s">
@@ -6002,13 +6143,13 @@
       <c r="O23" s="1">
         <v>0</v>
       </c>
-      <c r="P23" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="7">
-        <v>0</v>
-      </c>
-      <c r="R23" s="7">
+      <c r="P23" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>0</v>
+      </c>
+      <c r="R23" s="8">
         <v>0</v>
       </c>
       <c r="S23" s="1" t="s">
@@ -6066,13 +6207,13 @@
       <c r="O24" s="1">
         <v>0</v>
       </c>
-      <c r="P24" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="7">
-        <v>0</v>
-      </c>
-      <c r="R24" s="7">
+      <c r="P24" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>0</v>
+      </c>
+      <c r="R24" s="8">
         <v>0</v>
       </c>
       <c r="S24" s="1" t="s">
@@ -6130,13 +6271,13 @@
       <c r="O25" s="1">
         <v>0</v>
       </c>
-      <c r="P25" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="7">
-        <v>0</v>
-      </c>
-      <c r="R25" s="7">
+      <c r="P25" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="8">
+        <v>0</v>
+      </c>
+      <c r="R25" s="8">
         <v>0</v>
       </c>
       <c r="S25" s="1" t="s">
@@ -6194,13 +6335,13 @@
       <c r="O26" s="1">
         <v>0</v>
       </c>
-      <c r="P26" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="7">
-        <v>0</v>
-      </c>
-      <c r="R26" s="7">
+      <c r="P26" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="8">
+        <v>0</v>
+      </c>
+      <c r="R26" s="8">
         <v>0</v>
       </c>
       <c r="S26" s="1" t="s">
@@ -6258,13 +6399,13 @@
       <c r="O27" s="1">
         <v>0</v>
       </c>
-      <c r="P27" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="7">
-        <v>0</v>
-      </c>
-      <c r="R27" s="7">
+      <c r="P27" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="8">
+        <v>0</v>
+      </c>
+      <c r="R27" s="8">
         <v>0</v>
       </c>
       <c r="S27" s="1" t="s">
@@ -6322,13 +6463,13 @@
       <c r="O28" s="1">
         <v>0</v>
       </c>
-      <c r="P28" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="7">
-        <v>0</v>
-      </c>
-      <c r="R28" s="7">
+      <c r="P28" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>0</v>
+      </c>
+      <c r="R28" s="8">
         <v>0</v>
       </c>
       <c r="S28" s="1" t="s">
@@ -6386,13 +6527,13 @@
       <c r="O29" s="1">
         <v>0</v>
       </c>
-      <c r="P29" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="7">
-        <v>0</v>
-      </c>
-      <c r="R29" s="7">
+      <c r="P29" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="8">
+        <v>0</v>
+      </c>
+      <c r="R29" s="8">
         <v>0</v>
       </c>
       <c r="S29" s="1" t="s">
@@ -6450,13 +6591,13 @@
       <c r="O30" s="1">
         <v>0</v>
       </c>
-      <c r="P30" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="7">
-        <v>0</v>
-      </c>
-      <c r="R30" s="7">
+      <c r="P30" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="8">
+        <v>0</v>
+      </c>
+      <c r="R30" s="8">
         <v>0</v>
       </c>
       <c r="S30" s="1" t="s">
@@ -6514,13 +6655,13 @@
       <c r="O31" s="1">
         <v>0</v>
       </c>
-      <c r="P31" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="7">
-        <v>0</v>
-      </c>
-      <c r="R31" s="7">
+      <c r="P31" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="8">
+        <v>0</v>
+      </c>
+      <c r="R31" s="8">
         <v>0</v>
       </c>
       <c r="S31" s="1" t="s">
@@ -6578,13 +6719,13 @@
       <c r="O32" s="1">
         <v>0</v>
       </c>
-      <c r="P32" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="7">
-        <v>0</v>
-      </c>
-      <c r="R32" s="7">
+      <c r="P32" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="8">
+        <v>0</v>
+      </c>
+      <c r="R32" s="8">
         <v>0</v>
       </c>
       <c r="S32" s="1" t="s">
@@ -6642,13 +6783,13 @@
       <c r="O33" s="1">
         <v>0</v>
       </c>
-      <c r="P33" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="7">
-        <v>0</v>
-      </c>
-      <c r="R33" s="7">
+      <c r="P33" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="8">
+        <v>0</v>
+      </c>
+      <c r="R33" s="8">
         <v>0</v>
       </c>
       <c r="S33" s="1" t="s">
@@ -6706,13 +6847,13 @@
       <c r="O34" s="1">
         <v>0</v>
       </c>
-      <c r="P34" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="7">
-        <v>0</v>
-      </c>
-      <c r="R34" s="7">
+      <c r="P34" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>0</v>
+      </c>
+      <c r="R34" s="8">
         <v>0</v>
       </c>
       <c r="S34" s="1" t="s">
@@ -6770,13 +6911,13 @@
       <c r="O35" s="1">
         <v>0</v>
       </c>
-      <c r="P35" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="7">
-        <v>0</v>
-      </c>
-      <c r="R35" s="7">
+      <c r="P35" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="8">
+        <v>0</v>
+      </c>
+      <c r="R35" s="8">
         <v>0</v>
       </c>
       <c r="S35" s="1" t="s">
@@ -6834,13 +6975,13 @@
       <c r="O36" s="1">
         <v>0</v>
       </c>
-      <c r="P36" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="7">
-        <v>0</v>
-      </c>
-      <c r="R36" s="7">
+      <c r="P36" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>0</v>
+      </c>
+      <c r="R36" s="8">
         <v>0</v>
       </c>
       <c r="S36" s="1" t="s">
@@ -6898,13 +7039,13 @@
       <c r="O37" s="1">
         <v>0</v>
       </c>
-      <c r="P37" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="7">
-        <v>0</v>
-      </c>
-      <c r="R37" s="7">
+      <c r="P37" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="8">
+        <v>0</v>
+      </c>
+      <c r="R37" s="8">
         <v>0</v>
       </c>
       <c r="S37" s="1" t="s">
@@ -6962,13 +7103,13 @@
       <c r="O38" s="1">
         <v>0</v>
       </c>
-      <c r="P38" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="7">
-        <v>0</v>
-      </c>
-      <c r="R38" s="7">
+      <c r="P38" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="8">
+        <v>0</v>
+      </c>
+      <c r="R38" s="8">
         <v>0</v>
       </c>
       <c r="S38" s="1" t="s">
@@ -7026,13 +7167,13 @@
       <c r="O39" s="1">
         <v>0</v>
       </c>
-      <c r="P39" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="7">
-        <v>0</v>
-      </c>
-      <c r="R39" s="7">
+      <c r="P39" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="8">
+        <v>0</v>
+      </c>
+      <c r="R39" s="8">
         <v>0</v>
       </c>
       <c r="S39" s="1" t="s">
@@ -7062,7 +7203,7 @@
       <c r="F40" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="G40" s="15" t="s">
+      <c r="G40" s="19" t="s">
         <v>286</v>
       </c>
       <c r="H40" s="1" t="s">
@@ -7090,13 +7231,13 @@
       <c r="O40" s="1">
         <v>0</v>
       </c>
-      <c r="P40" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="7">
-        <v>0</v>
-      </c>
-      <c r="R40" s="7">
+      <c r="P40" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="8">
+        <v>0</v>
+      </c>
+      <c r="R40" s="8">
         <v>0</v>
       </c>
       <c r="S40" s="1" t="s">
@@ -7114,7 +7255,7 @@
       <c r="X40" s="1"/>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A41" s="4"/>
+      <c r="A41" s="5"/>
       <c r="C41" s="1" t="s">
         <v>290</v>
       </c>
@@ -7155,13 +7296,13 @@
       <c r="O41" s="1">
         <v>0</v>
       </c>
-      <c r="P41" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="7">
-        <v>0</v>
-      </c>
-      <c r="R41" s="7">
+      <c r="P41" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="8">
+        <v>0</v>
+      </c>
+      <c r="R41" s="8">
         <v>0</v>
       </c>
       <c r="S41" s="1" t="s">
@@ -7178,7 +7319,7 @@
       </c>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A42" s="4"/>
+      <c r="A42" s="5"/>
       <c r="C42" s="1" t="s">
         <v>297</v>
       </c>
@@ -7219,13 +7360,13 @@
       <c r="O42" s="1">
         <v>0</v>
       </c>
-      <c r="P42" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="7">
-        <v>0</v>
-      </c>
-      <c r="R42" s="7">
+      <c r="P42" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>0</v>
+      </c>
+      <c r="R42" s="8">
         <v>0</v>
       </c>
       <c r="S42" s="1" t="s">
@@ -7242,7 +7383,7 @@
       </c>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A43" s="4"/>
+      <c r="A43" s="5"/>
       <c r="C43" s="1" t="s">
         <v>304</v>
       </c>
@@ -7283,13 +7424,13 @@
       <c r="O43" s="1">
         <v>0</v>
       </c>
-      <c r="P43" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="7">
-        <v>0</v>
-      </c>
-      <c r="R43" s="7">
+      <c r="P43" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="8">
+        <v>0</v>
+      </c>
+      <c r="R43" s="8">
         <v>0</v>
       </c>
       <c r="S43" s="1" t="s">
@@ -7306,7 +7447,7 @@
       </c>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A44" s="4"/>
+      <c r="A44" s="5"/>
       <c r="C44" s="1" t="s">
         <v>311</v>
       </c>
@@ -7347,13 +7488,13 @@
       <c r="O44" s="1">
         <v>0</v>
       </c>
-      <c r="P44" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="7">
-        <v>0</v>
-      </c>
-      <c r="R44" s="7">
+      <c r="P44" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="8">
+        <v>0</v>
+      </c>
+      <c r="R44" s="8">
         <v>0</v>
       </c>
       <c r="S44" s="1" t="s">
@@ -7370,7 +7511,7 @@
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A45" s="4"/>
+      <c r="A45" s="5"/>
       <c r="C45" s="1" t="s">
         <v>318</v>
       </c>
@@ -7411,13 +7552,13 @@
       <c r="O45" s="1">
         <v>0</v>
       </c>
-      <c r="P45" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="7">
-        <v>0</v>
-      </c>
-      <c r="R45" s="7">
+      <c r="P45" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="8">
+        <v>0</v>
+      </c>
+      <c r="R45" s="8">
         <v>0</v>
       </c>
       <c r="S45" s="1" t="s">
@@ -7434,7 +7575,7 @@
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A46" s="4"/>
+      <c r="A46" s="5"/>
       <c r="C46" s="1" t="s">
         <v>325</v>
       </c>
@@ -7475,13 +7616,13 @@
       <c r="O46" s="1">
         <v>0</v>
       </c>
-      <c r="P46" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="7">
-        <v>0</v>
-      </c>
-      <c r="R46" s="7">
+      <c r="P46" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="8">
+        <v>0</v>
+      </c>
+      <c r="R46" s="8">
         <v>0</v>
       </c>
       <c r="S46" s="1" t="s">
@@ -7496,11 +7637,11 @@
       <c r="W46" s="1">
         <v>0</v>
       </c>
-      <c r="X46" s="4"/>
-      <c r="Y46" s="4"/>
+      <c r="X46" s="5"/>
+      <c r="Y46" s="5"/>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A47" s="4"/>
+      <c r="A47" s="5"/>
       <c r="C47" s="1" t="s">
         <v>332</v>
       </c>
@@ -7541,13 +7682,13 @@
       <c r="O47" s="1">
         <v>0</v>
       </c>
-      <c r="P47" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="7">
-        <v>0</v>
-      </c>
-      <c r="R47" s="7">
+      <c r="P47" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="8">
+        <v>0</v>
+      </c>
+      <c r="R47" s="8">
         <v>0</v>
       </c>
       <c r="S47" s="1" t="s">
@@ -7562,11 +7703,11 @@
       <c r="W47" s="1">
         <v>0</v>
       </c>
-      <c r="X47" s="4"/>
-      <c r="Y47" s="4"/>
+      <c r="X47" s="5"/>
+      <c r="Y47" s="5"/>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A48" s="4"/>
+      <c r="A48" s="5"/>
       <c r="C48" s="1" t="s">
         <v>339</v>
       </c>
@@ -7607,13 +7748,13 @@
       <c r="O48" s="1">
         <v>0</v>
       </c>
-      <c r="P48" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="7">
-        <v>0</v>
-      </c>
-      <c r="R48" s="7">
+      <c r="P48" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="8">
+        <v>0</v>
+      </c>
+      <c r="R48" s="8">
         <v>0</v>
       </c>
       <c r="S48" s="1" t="s">
@@ -7628,11 +7769,11 @@
       <c r="W48" s="1">
         <v>0</v>
       </c>
-      <c r="X48" s="4"/>
-      <c r="Y48" s="4"/>
+      <c r="X48" s="5"/>
+      <c r="Y48" s="5"/>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A49" s="4"/>
+      <c r="A49" s="5"/>
       <c r="C49" s="1" t="s">
         <v>346</v>
       </c>
@@ -7673,13 +7814,13 @@
       <c r="O49" s="1">
         <v>0</v>
       </c>
-      <c r="P49" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="7">
-        <v>0</v>
-      </c>
-      <c r="R49" s="7">
+      <c r="P49" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="8">
+        <v>0</v>
+      </c>
+      <c r="R49" s="8">
         <v>0</v>
       </c>
       <c r="S49" s="1" t="s">
@@ -7694,11 +7835,11 @@
       <c r="W49" s="1">
         <v>0</v>
       </c>
-      <c r="X49" s="4"/>
-      <c r="Y49" s="4"/>
+      <c r="X49" s="5"/>
+      <c r="Y49" s="5"/>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A50" s="4"/>
+      <c r="A50" s="5"/>
       <c r="C50" s="1" t="s">
         <v>353</v>
       </c>
@@ -7739,13 +7880,13 @@
       <c r="O50" s="1">
         <v>0</v>
       </c>
-      <c r="P50" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="7">
-        <v>0</v>
-      </c>
-      <c r="R50" s="7">
+      <c r="P50" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="8">
+        <v>0</v>
+      </c>
+      <c r="R50" s="8">
         <v>0</v>
       </c>
       <c r="S50" s="1" t="s">
@@ -7760,11 +7901,11 @@
       <c r="W50" s="1">
         <v>0</v>
       </c>
-      <c r="X50" s="4"/>
-      <c r="Y50" s="4"/>
+      <c r="X50" s="5"/>
+      <c r="Y50" s="5"/>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A51" s="4"/>
+      <c r="A51" s="5"/>
       <c r="C51" s="1" t="s">
         <v>360</v>
       </c>
@@ -7806,13 +7947,13 @@
         <f t="shared" ref="O51:O65" si="3">(D51-1044)*5</f>
         <v>5</v>
       </c>
-      <c r="P51" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="7">
-        <v>0</v>
-      </c>
-      <c r="R51" s="7">
+      <c r="P51" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>0</v>
+      </c>
+      <c r="R51" s="8">
         <v>0</v>
       </c>
       <c r="S51" s="1" t="s">
@@ -7827,11 +7968,11 @@
       <c r="W51" s="1">
         <v>0</v>
       </c>
-      <c r="X51" s="4"/>
-      <c r="Y51" s="4"/>
+      <c r="X51" s="5"/>
+      <c r="Y51" s="5"/>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A52" s="4"/>
+      <c r="A52" s="5"/>
       <c r="C52" s="1" t="s">
         <v>367</v>
       </c>
@@ -7873,13 +8014,13 @@
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="P52" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="7">
-        <v>0</v>
-      </c>
-      <c r="R52" s="7">
+      <c r="P52" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="8">
+        <v>0</v>
+      </c>
+      <c r="R52" s="8">
         <v>0</v>
       </c>
       <c r="S52" s="1" t="s">
@@ -7894,11 +8035,11 @@
       <c r="W52" s="1">
         <v>0</v>
       </c>
-      <c r="X52" s="4"/>
-      <c r="Y52" s="4"/>
+      <c r="X52" s="5"/>
+      <c r="Y52" s="5"/>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A53" s="4"/>
+      <c r="A53" s="5"/>
       <c r="C53" s="1" t="s">
         <v>374</v>
       </c>
@@ -7940,13 +8081,13 @@
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="P53" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="7">
-        <v>0</v>
-      </c>
-      <c r="R53" s="7">
+      <c r="P53" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="8">
+        <v>0</v>
+      </c>
+      <c r="R53" s="8">
         <v>0</v>
       </c>
       <c r="S53" s="1" t="s">
@@ -7961,11 +8102,11 @@
       <c r="W53" s="1">
         <v>0</v>
       </c>
-      <c r="X53" s="4"/>
-      <c r="Y53" s="4"/>
+      <c r="X53" s="5"/>
+      <c r="Y53" s="5"/>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A54" s="4"/>
+      <c r="A54" s="5"/>
       <c r="C54" s="1" t="s">
         <v>381</v>
       </c>
@@ -8007,13 +8148,13 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="P54" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="7">
-        <v>0</v>
-      </c>
-      <c r="R54" s="7">
+      <c r="P54" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="8">
+        <v>0</v>
+      </c>
+      <c r="R54" s="8">
         <v>0</v>
       </c>
       <c r="S54" s="1" t="s">
@@ -8028,11 +8169,11 @@
       <c r="W54" s="1">
         <v>0</v>
       </c>
-      <c r="X54" s="4"/>
-      <c r="Y54" s="4"/>
+      <c r="X54" s="5"/>
+      <c r="Y54" s="5"/>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A55" s="4"/>
+      <c r="A55" s="5"/>
       <c r="C55" s="1" t="s">
         <v>388</v>
       </c>
@@ -8074,13 +8215,13 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="P55" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="7">
-        <v>0</v>
-      </c>
-      <c r="R55" s="7">
+      <c r="P55" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="8">
+        <v>0</v>
+      </c>
+      <c r="R55" s="8">
         <v>0</v>
       </c>
       <c r="S55" s="1" t="s">
@@ -8095,11 +8236,11 @@
       <c r="W55" s="1">
         <v>0</v>
       </c>
-      <c r="X55" s="4"/>
-      <c r="Y55" s="4"/>
+      <c r="X55" s="5"/>
+      <c r="Y55" s="5"/>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A56" s="4"/>
+      <c r="A56" s="5"/>
       <c r="C56" s="1" t="s">
         <v>395</v>
       </c>
@@ -8143,13 +8284,13 @@
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="P56" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="7">
-        <v>0</v>
-      </c>
-      <c r="R56" s="7">
+      <c r="P56" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="8">
+        <v>0</v>
+      </c>
+      <c r="R56" s="8">
         <v>0</v>
       </c>
       <c r="S56" s="1" t="s">
@@ -8164,11 +8305,11 @@
       <c r="W56" s="1">
         <v>0</v>
       </c>
-      <c r="X56" s="4"/>
-      <c r="Y56" s="4"/>
+      <c r="X56" s="5"/>
+      <c r="Y56" s="5"/>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A57" s="4"/>
+      <c r="A57" s="5"/>
       <c r="C57" s="1" t="s">
         <v>402</v>
       </c>
@@ -8212,13 +8353,13 @@
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="P57" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="7">
-        <v>0</v>
-      </c>
-      <c r="R57" s="7">
+      <c r="P57" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="8">
+        <v>0</v>
+      </c>
+      <c r="R57" s="8">
         <v>0</v>
       </c>
       <c r="S57" s="1" t="s">
@@ -8233,11 +8374,11 @@
       <c r="W57" s="1">
         <v>0</v>
       </c>
-      <c r="X57" s="4"/>
-      <c r="Y57" s="4"/>
+      <c r="X57" s="5"/>
+      <c r="Y57" s="5"/>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A58" s="4"/>
+      <c r="A58" s="5"/>
       <c r="C58" s="1" t="s">
         <v>409</v>
       </c>
@@ -8281,13 +8422,13 @@
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="P58" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="7">
-        <v>0</v>
-      </c>
-      <c r="R58" s="7">
+      <c r="P58" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>0</v>
+      </c>
+      <c r="R58" s="8">
         <v>0</v>
       </c>
       <c r="S58" s="1" t="s">
@@ -8302,11 +8443,11 @@
       <c r="W58" s="1">
         <v>0</v>
       </c>
-      <c r="X58" s="4"/>
-      <c r="Y58" s="4"/>
+      <c r="X58" s="5"/>
+      <c r="Y58" s="5"/>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A59" s="4"/>
+      <c r="A59" s="5"/>
       <c r="C59" s="1" t="s">
         <v>416</v>
       </c>
@@ -8350,13 +8491,13 @@
         <f t="shared" si="3"/>
         <v>45</v>
       </c>
-      <c r="P59" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="7">
-        <v>0</v>
-      </c>
-      <c r="R59" s="7">
+      <c r="P59" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="8">
+        <v>0</v>
+      </c>
+      <c r="R59" s="8">
         <v>0</v>
       </c>
       <c r="S59" s="1" t="s">
@@ -8371,11 +8512,11 @@
       <c r="W59" s="1">
         <v>0</v>
       </c>
-      <c r="X59" s="4"/>
-      <c r="Y59" s="4"/>
+      <c r="X59" s="5"/>
+      <c r="Y59" s="5"/>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A60" s="4"/>
+      <c r="A60" s="5"/>
       <c r="C60" s="1" t="s">
         <v>423</v>
       </c>
@@ -8419,13 +8560,13 @@
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="P60" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="7">
-        <v>0</v>
-      </c>
-      <c r="R60" s="7">
+      <c r="P60" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="8">
+        <v>0</v>
+      </c>
+      <c r="R60" s="8">
         <v>0</v>
       </c>
       <c r="S60" s="1" t="s">
@@ -8440,11 +8581,11 @@
       <c r="W60" s="1">
         <v>0</v>
       </c>
-      <c r="X60" s="4"/>
-      <c r="Y60" s="4"/>
+      <c r="X60" s="5"/>
+      <c r="Y60" s="5"/>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A61" s="4"/>
+      <c r="A61" s="5"/>
       <c r="C61" s="1" t="s">
         <v>430</v>
       </c>
@@ -8488,13 +8629,13 @@
         <f t="shared" si="3"/>
         <v>55</v>
       </c>
-      <c r="P61" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="7">
-        <v>0</v>
-      </c>
-      <c r="R61" s="7">
+      <c r="P61" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="8">
+        <v>0</v>
+      </c>
+      <c r="R61" s="8">
         <v>0</v>
       </c>
       <c r="S61" s="1" t="s">
@@ -8509,11 +8650,11 @@
       <c r="W61" s="1">
         <v>0</v>
       </c>
-      <c r="X61" s="4"/>
-      <c r="Y61" s="4"/>
+      <c r="X61" s="5"/>
+      <c r="Y61" s="5"/>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A62" s="4"/>
+      <c r="A62" s="5"/>
       <c r="C62" s="1" t="s">
         <v>437</v>
       </c>
@@ -8557,13 +8698,13 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-      <c r="P62" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="7">
-        <v>0</v>
-      </c>
-      <c r="R62" s="7">
+      <c r="P62" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="8">
+        <v>0</v>
+      </c>
+      <c r="R62" s="8">
         <v>0</v>
       </c>
       <c r="S62" s="1" t="s">
@@ -8578,11 +8719,11 @@
       <c r="W62" s="1">
         <v>0</v>
       </c>
-      <c r="X62" s="4"/>
-      <c r="Y62" s="4"/>
+      <c r="X62" s="5"/>
+      <c r="Y62" s="5"/>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A63" s="4"/>
+      <c r="A63" s="5"/>
       <c r="C63" s="1" t="s">
         <v>444</v>
       </c>
@@ -8626,13 +8767,13 @@
         <f t="shared" si="3"/>
         <v>65</v>
       </c>
-      <c r="P63" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="7">
-        <v>0</v>
-      </c>
-      <c r="R63" s="7">
+      <c r="P63" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="8">
+        <v>0</v>
+      </c>
+      <c r="R63" s="8">
         <v>0</v>
       </c>
       <c r="S63" s="1" t="s">
@@ -8647,11 +8788,11 @@
       <c r="W63" s="1">
         <v>0</v>
       </c>
-      <c r="X63" s="4"/>
-      <c r="Y63" s="4"/>
+      <c r="X63" s="5"/>
+      <c r="Y63" s="5"/>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A64" s="4"/>
+      <c r="A64" s="5"/>
       <c r="C64" s="1" t="s">
         <v>451</v>
       </c>
@@ -8695,13 +8836,13 @@
         <f t="shared" si="3"/>
         <v>70</v>
       </c>
-      <c r="P64" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="7">
-        <v>0</v>
-      </c>
-      <c r="R64" s="7">
+      <c r="P64" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="8">
+        <v>0</v>
+      </c>
+      <c r="R64" s="8">
         <v>0</v>
       </c>
       <c r="S64" s="1" t="s">
@@ -8716,11 +8857,11 @@
       <c r="W64" s="1">
         <v>0</v>
       </c>
-      <c r="X64" s="4"/>
-      <c r="Y64" s="4"/>
+      <c r="X64" s="5"/>
+      <c r="Y64" s="5"/>
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A65" s="4"/>
+      <c r="A65" s="5"/>
       <c r="C65" s="1" t="s">
         <v>458</v>
       </c>
@@ -8739,7 +8880,7 @@
       <c r="H65" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="I65" s="15" t="s">
+      <c r="I65" s="19" t="s">
         <v>463</v>
       </c>
       <c r="J65" s="1">
@@ -8764,13 +8905,13 @@
         <f t="shared" si="3"/>
         <v>75</v>
       </c>
-      <c r="P65" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="7">
-        <v>0</v>
-      </c>
-      <c r="R65" s="7">
+      <c r="P65" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="8">
+        <v>0</v>
+      </c>
+      <c r="R65" s="8">
         <v>0</v>
       </c>
       <c r="S65" s="1" t="s">
@@ -8785,11 +8926,11 @@
       <c r="W65" s="1">
         <v>0</v>
       </c>
-      <c r="X65" s="4"/>
-      <c r="Y65" s="4"/>
+      <c r="X65" s="5"/>
+      <c r="Y65" s="5"/>
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A66" s="4"/>
+      <c r="A66" s="5"/>
       <c r="C66" s="1" t="s">
         <v>465</v>
       </c>
@@ -8808,7 +8949,7 @@
       <c r="H66" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="I66" s="15" t="s">
+      <c r="I66" s="19" t="s">
         <v>470</v>
       </c>
       <c r="J66" s="1">
@@ -8833,13 +8974,13 @@
         <f t="shared" si="6"/>
         <v>83</v>
       </c>
-      <c r="P66" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="7">
-        <v>0</v>
-      </c>
-      <c r="R66" s="7">
+      <c r="P66" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="8">
+        <v>0</v>
+      </c>
+      <c r="R66" s="8">
         <v>0</v>
       </c>
       <c r="S66" s="1" t="s">
@@ -8854,11 +8995,11 @@
       <c r="W66" s="1">
         <v>0</v>
       </c>
-      <c r="X66" s="4"/>
-      <c r="Y66" s="4"/>
+      <c r="X66" s="5"/>
+      <c r="Y66" s="5"/>
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A67" s="4"/>
+      <c r="A67" s="5"/>
       <c r="C67" s="1" t="s">
         <v>472</v>
       </c>
@@ -8877,7 +9018,7 @@
       <c r="H67" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="I67" s="15" t="s">
+      <c r="I67" s="19" t="s">
         <v>477</v>
       </c>
       <c r="J67" s="1">
@@ -8902,13 +9043,13 @@
         <f t="shared" ref="O67:O71" si="10">O66+8</f>
         <v>91</v>
       </c>
-      <c r="P67" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="7">
-        <v>0</v>
-      </c>
-      <c r="R67" s="7">
+      <c r="P67" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="8">
+        <v>0</v>
+      </c>
+      <c r="R67" s="8">
         <v>0</v>
       </c>
       <c r="S67" s="1" t="s">
@@ -8923,11 +9064,11 @@
       <c r="W67" s="1">
         <v>0</v>
       </c>
-      <c r="X67" s="4"/>
-      <c r="Y67" s="4"/>
+      <c r="X67" s="5"/>
+      <c r="Y67" s="5"/>
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A68" s="4"/>
+      <c r="A68" s="5"/>
       <c r="C68" s="1" t="s">
         <v>479</v>
       </c>
@@ -8946,7 +9087,7 @@
       <c r="H68" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="I68" s="15" t="s">
+      <c r="I68" s="19" t="s">
         <v>484</v>
       </c>
       <c r="J68" s="1">
@@ -8971,13 +9112,13 @@
         <f t="shared" si="10"/>
         <v>99</v>
       </c>
-      <c r="P68" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="7">
-        <v>0</v>
-      </c>
-      <c r="R68" s="7">
+      <c r="P68" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="8">
+        <v>0</v>
+      </c>
+      <c r="R68" s="8">
         <v>0</v>
       </c>
       <c r="S68" s="1" t="s">
@@ -8992,11 +9133,11 @@
       <c r="W68" s="1">
         <v>0</v>
       </c>
-      <c r="X68" s="4"/>
-      <c r="Y68" s="4"/>
+      <c r="X68" s="5"/>
+      <c r="Y68" s="5"/>
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A69" s="4"/>
+      <c r="A69" s="5"/>
       <c r="C69" s="1" t="s">
         <v>486</v>
       </c>
@@ -9015,7 +9156,7 @@
       <c r="H69" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="I69" s="15" t="s">
+      <c r="I69" s="19" t="s">
         <v>491</v>
       </c>
       <c r="J69" s="1">
@@ -9040,13 +9181,13 @@
         <f t="shared" si="10"/>
         <v>107</v>
       </c>
-      <c r="P69" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="7">
-        <v>0</v>
-      </c>
-      <c r="R69" s="7">
+      <c r="P69" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="8">
+        <v>0</v>
+      </c>
+      <c r="R69" s="8">
         <v>0</v>
       </c>
       <c r="S69" s="1" t="s">
@@ -9061,11 +9202,11 @@
       <c r="W69" s="1">
         <v>0</v>
       </c>
-      <c r="X69" s="4"/>
-      <c r="Y69" s="4"/>
+      <c r="X69" s="5"/>
+      <c r="Y69" s="5"/>
     </row>
     <row r="70" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A70" s="4"/>
+      <c r="A70" s="5"/>
       <c r="C70" s="1" t="s">
         <v>493</v>
       </c>
@@ -9084,7 +9225,7 @@
       <c r="H70" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="I70" s="15" t="s">
+      <c r="I70" s="19" t="s">
         <v>498</v>
       </c>
       <c r="J70" s="1">
@@ -9108,13 +9249,13 @@
         <f t="shared" si="10"/>
         <v>115</v>
       </c>
-      <c r="P70" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="7">
-        <v>0</v>
-      </c>
-      <c r="R70" s="7">
+      <c r="P70" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="8">
+        <v>0</v>
+      </c>
+      <c r="R70" s="8">
         <v>0</v>
       </c>
       <c r="S70" s="1" t="s">
@@ -9129,11 +9270,11 @@
       <c r="W70" s="1">
         <v>0</v>
       </c>
-      <c r="X70" s="4"/>
-      <c r="Y70" s="4"/>
+      <c r="X70" s="5"/>
+      <c r="Y70" s="5"/>
     </row>
     <row r="71" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A71" s="4"/>
+      <c r="A71" s="5"/>
       <c r="C71" s="1" t="s">
         <v>500</v>
       </c>
@@ -9146,13 +9287,13 @@
       <c r="F71" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="G71" s="16" t="s">
+      <c r="G71" s="20" t="s">
         <v>503</v>
       </c>
-      <c r="H71" s="15" t="s">
+      <c r="H71" s="19" t="s">
         <v>504</v>
       </c>
-      <c r="I71" s="16" t="s">
+      <c r="I71" s="20" t="s">
         <v>505</v>
       </c>
       <c r="J71" s="1">
@@ -9177,13 +9318,13 @@
         <f t="shared" si="11"/>
         <v>130</v>
       </c>
-      <c r="P71" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q71" s="7">
-        <v>0</v>
-      </c>
-      <c r="R71" s="7">
+      <c r="P71" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="8">
+        <v>0</v>
+      </c>
+      <c r="R71" s="8">
         <v>0</v>
       </c>
       <c r="S71" s="1" t="s">
@@ -9198,11 +9339,11 @@
       <c r="W71" s="1">
         <v>0</v>
       </c>
-      <c r="X71" s="4"/>
-      <c r="Y71" s="4"/>
+      <c r="X71" s="5"/>
+      <c r="Y71" s="5"/>
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A72" s="4"/>
+      <c r="A72" s="5"/>
       <c r="C72" s="1" t="s">
         <v>507</v>
       </c>
@@ -9215,13 +9356,13 @@
       <c r="F72" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="G72" s="16" t="s">
+      <c r="G72" s="20" t="s">
         <v>510</v>
       </c>
-      <c r="H72" s="15" t="s">
+      <c r="H72" s="19" t="s">
         <v>511</v>
       </c>
-      <c r="I72" s="17" t="s">
+      <c r="I72" s="21" t="s">
         <v>512</v>
       </c>
       <c r="J72" s="1">
@@ -9246,13 +9387,13 @@
         <f t="shared" ref="O71:O95" si="15">O71+15</f>
         <v>145</v>
       </c>
-      <c r="P72" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="7">
-        <v>0</v>
-      </c>
-      <c r="R72" s="7">
+      <c r="P72" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="8">
+        <v>0</v>
+      </c>
+      <c r="R72" s="8">
         <v>0</v>
       </c>
       <c r="S72" s="1" t="s">
@@ -9267,11 +9408,11 @@
       <c r="W72" s="1">
         <v>0</v>
       </c>
-      <c r="X72" s="4"/>
-      <c r="Y72" s="4"/>
+      <c r="X72" s="5"/>
+      <c r="Y72" s="5"/>
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A73" s="4"/>
+      <c r="A73" s="5"/>
       <c r="C73" s="1" t="s">
         <v>514</v>
       </c>
@@ -9284,13 +9425,13 @@
       <c r="F73" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="G73" s="16" t="s">
+      <c r="G73" s="20" t="s">
         <v>517</v>
       </c>
-      <c r="H73" s="15" t="s">
+      <c r="H73" s="19" t="s">
         <v>518</v>
       </c>
-      <c r="I73" s="17" t="s">
+      <c r="I73" s="21" t="s">
         <v>519</v>
       </c>
       <c r="J73" s="1">
@@ -9315,13 +9456,13 @@
         <f t="shared" si="15"/>
         <v>160</v>
       </c>
-      <c r="P73" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="7">
-        <v>0</v>
-      </c>
-      <c r="R73" s="7">
+      <c r="P73" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="8">
+        <v>0</v>
+      </c>
+      <c r="R73" s="8">
         <v>0</v>
       </c>
       <c r="S73" s="1" t="s">
@@ -9336,11 +9477,11 @@
       <c r="W73" s="1">
         <v>0</v>
       </c>
-      <c r="X73" s="4"/>
-      <c r="Y73" s="4"/>
+      <c r="X73" s="5"/>
+      <c r="Y73" s="5"/>
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A74" s="4"/>
+      <c r="A74" s="5"/>
       <c r="C74" s="1" t="s">
         <v>521</v>
       </c>
@@ -9353,13 +9494,13 @@
       <c r="F74" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="G74" s="16" t="s">
+      <c r="G74" s="20" t="s">
         <v>524</v>
       </c>
-      <c r="H74" s="15" t="s">
+      <c r="H74" s="19" t="s">
         <v>525</v>
       </c>
-      <c r="I74" s="17" t="s">
+      <c r="I74" s="21" t="s">
         <v>526</v>
       </c>
       <c r="J74" s="1">
@@ -9384,13 +9525,13 @@
         <f t="shared" si="15"/>
         <v>175</v>
       </c>
-      <c r="P74" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="7">
-        <v>0</v>
-      </c>
-      <c r="R74" s="7">
+      <c r="P74" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="8">
+        <v>0</v>
+      </c>
+      <c r="R74" s="8">
         <v>0</v>
       </c>
       <c r="S74" s="1" t="s">
@@ -9405,11 +9546,11 @@
       <c r="W74" s="1">
         <v>0</v>
       </c>
-      <c r="X74" s="4"/>
-      <c r="Y74" s="4"/>
+      <c r="X74" s="5"/>
+      <c r="Y74" s="5"/>
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A75" s="4"/>
+      <c r="A75" s="5"/>
       <c r="C75" s="1" t="s">
         <v>528</v>
       </c>
@@ -9422,13 +9563,13 @@
       <c r="F75" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="G75" s="16" t="s">
+      <c r="G75" s="20" t="s">
         <v>531</v>
       </c>
-      <c r="H75" s="15" t="s">
+      <c r="H75" s="19" t="s">
         <v>532</v>
       </c>
-      <c r="I75" s="17" t="s">
+      <c r="I75" s="21" t="s">
         <v>533</v>
       </c>
       <c r="J75" s="1">
@@ -9453,19 +9594,19 @@
         <f t="shared" si="15"/>
         <v>190</v>
       </c>
-      <c r="P75" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="7">
-        <v>0</v>
-      </c>
-      <c r="R75" s="7">
+      <c r="P75" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="8">
+        <v>0</v>
+      </c>
+      <c r="R75" s="8">
         <v>0</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="T75" s="15" t="s">
+      <c r="T75" s="19" t="s">
         <v>534</v>
       </c>
       <c r="V75" s="1" t="s">
@@ -9474,12 +9615,12 @@
       <c r="W75" s="1">
         <v>0</v>
       </c>
-      <c r="X75" s="4"/>
-      <c r="Y75" s="4"/>
+      <c r="X75" s="5"/>
+      <c r="Y75" s="5"/>
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A76" s="4"/>
-      <c r="B76" s="4"/>
+      <c r="A76" s="5"/>
+      <c r="B76" s="5"/>
       <c r="C76" s="1" t="s">
         <v>535</v>
       </c>
@@ -9492,13 +9633,13 @@
       <c r="F76" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="G76" s="16" t="s">
+      <c r="G76" s="20" t="s">
         <v>538</v>
       </c>
-      <c r="H76" s="15" t="s">
+      <c r="H76" s="19" t="s">
         <v>539</v>
       </c>
-      <c r="I76" s="17" t="s">
+      <c r="I76" s="21" t="s">
         <v>540</v>
       </c>
       <c r="J76" s="1">
@@ -9523,13 +9664,13 @@
         <f t="shared" si="15"/>
         <v>205</v>
       </c>
-      <c r="P76" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="7">
-        <v>0</v>
-      </c>
-      <c r="R76" s="7">
+      <c r="P76" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>0</v>
+      </c>
+      <c r="R76" s="8">
         <v>0</v>
       </c>
       <c r="S76" s="1">
@@ -9546,8 +9687,8 @@
       </c>
     </row>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
       <c r="C77" s="1" t="s">
         <v>541</v>
       </c>
@@ -9560,13 +9701,13 @@
       <c r="F77" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="G77" s="16" t="s">
+      <c r="G77" s="20" t="s">
         <v>544</v>
       </c>
-      <c r="H77" s="15" t="s">
+      <c r="H77" s="19" t="s">
         <v>545</v>
       </c>
-      <c r="I77" s="17" t="s">
+      <c r="I77" s="21" t="s">
         <v>546</v>
       </c>
       <c r="J77" s="1">
@@ -9591,13 +9732,13 @@
         <f t="shared" si="15"/>
         <v>220</v>
       </c>
-      <c r="P77" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="7">
-        <v>0</v>
-      </c>
-      <c r="R77" s="7">
+      <c r="P77" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="8">
+        <v>0</v>
+      </c>
+      <c r="R77" s="8">
         <v>0</v>
       </c>
       <c r="S77" s="1">
@@ -9614,8 +9755,8 @@
       </c>
     </row>
     <row r="78" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A78" s="4"/>
-      <c r="B78" s="4"/>
+      <c r="A78" s="5"/>
+      <c r="B78" s="5"/>
       <c r="C78" s="1" t="s">
         <v>547</v>
       </c>
@@ -9628,13 +9769,13 @@
       <c r="F78" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="G78" s="16" t="s">
+      <c r="G78" s="20" t="s">
         <v>550</v>
       </c>
-      <c r="H78" s="15" t="s">
+      <c r="H78" s="19" t="s">
         <v>551</v>
       </c>
-      <c r="I78" s="17" t="s">
+      <c r="I78" s="21" t="s">
         <v>552</v>
       </c>
       <c r="J78" s="1">
@@ -9659,13 +9800,13 @@
         <f t="shared" si="15"/>
         <v>235</v>
       </c>
-      <c r="P78" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="7">
-        <v>0</v>
-      </c>
-      <c r="R78" s="7">
+      <c r="P78" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="8">
+        <v>0</v>
+      </c>
+      <c r="R78" s="8">
         <v>0</v>
       </c>
       <c r="S78" s="1">
@@ -9682,8 +9823,8 @@
       </c>
     </row>
     <row r="79" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A79" s="4"/>
-      <c r="B79" s="4"/>
+      <c r="A79" s="5"/>
+      <c r="B79" s="5"/>
       <c r="C79" s="1" t="s">
         <v>553</v>
       </c>
@@ -9696,13 +9837,13 @@
       <c r="F79" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="G79" s="16" t="s">
+      <c r="G79" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="H79" s="15" t="s">
+      <c r="H79" s="19" t="s">
         <v>557</v>
       </c>
-      <c r="I79" s="17" t="s">
+      <c r="I79" s="21" t="s">
         <v>558</v>
       </c>
       <c r="J79" s="1">
@@ -9727,13 +9868,13 @@
         <f t="shared" si="15"/>
         <v>250</v>
       </c>
-      <c r="P79" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="7">
-        <v>0</v>
-      </c>
-      <c r="R79" s="7">
+      <c r="P79" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="8">
+        <v>0</v>
+      </c>
+      <c r="R79" s="8">
         <v>0</v>
       </c>
       <c r="S79" s="1">
@@ -9750,8 +9891,8 @@
       </c>
     </row>
     <row r="80" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
+      <c r="A80" s="5"/>
+      <c r="B80" s="5"/>
       <c r="C80" s="1" t="s">
         <v>559</v>
       </c>
@@ -9764,13 +9905,13 @@
       <c r="F80" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="G80" s="16" t="s">
+      <c r="G80" s="20" t="s">
         <v>562</v>
       </c>
-      <c r="H80" s="15" t="s">
+      <c r="H80" s="19" t="s">
         <v>563</v>
       </c>
-      <c r="I80" s="17" t="s">
+      <c r="I80" s="21" t="s">
         <v>564</v>
       </c>
       <c r="J80" s="1">
@@ -9795,13 +9936,13 @@
         <f t="shared" si="15"/>
         <v>265</v>
       </c>
-      <c r="P80" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="7">
-        <v>0</v>
-      </c>
-      <c r="R80" s="7">
+      <c r="P80" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="8">
+        <v>0</v>
+      </c>
+      <c r="R80" s="8">
         <v>0</v>
       </c>
       <c r="S80" s="1">
@@ -9818,8 +9959,8 @@
       </c>
     </row>
     <row r="81" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A81" s="4"/>
-      <c r="B81" s="4"/>
+      <c r="A81" s="5"/>
+      <c r="B81" s="5"/>
       <c r="C81" s="1" t="s">
         <v>565</v>
       </c>
@@ -9832,13 +9973,13 @@
       <c r="F81" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="G81" s="16" t="s">
+      <c r="G81" s="20" t="s">
         <v>568</v>
       </c>
-      <c r="H81" s="15" t="s">
+      <c r="H81" s="19" t="s">
         <v>569</v>
       </c>
-      <c r="I81" s="17" t="s">
+      <c r="I81" s="21" t="s">
         <v>570</v>
       </c>
       <c r="J81" s="1">
@@ -9863,13 +10004,13 @@
         <f t="shared" si="15"/>
         <v>280</v>
       </c>
-      <c r="P81" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="7">
-        <v>0</v>
-      </c>
-      <c r="R81" s="7">
+      <c r="P81" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="8">
+        <v>0</v>
+      </c>
+      <c r="R81" s="8">
         <v>0</v>
       </c>
       <c r="S81" s="1">
@@ -9884,12 +10025,12 @@
       <c r="W81" s="1">
         <v>0</v>
       </c>
-      <c r="X81" s="4"/>
-      <c r="Y81" s="4"/>
+      <c r="X81" s="5"/>
+      <c r="Y81" s="5"/>
     </row>
     <row r="82" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A82" s="4"/>
-      <c r="B82" s="4"/>
+      <c r="A82" s="5"/>
+      <c r="B82" s="5"/>
       <c r="C82" s="1" t="s">
         <v>571</v>
       </c>
@@ -9902,13 +10043,13 @@
       <c r="F82" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="G82" s="16" t="s">
+      <c r="G82" s="20" t="s">
         <v>574</v>
       </c>
-      <c r="H82" s="15" t="s">
+      <c r="H82" s="19" t="s">
         <v>575</v>
       </c>
-      <c r="I82" s="17" t="s">
+      <c r="I82" s="21" t="s">
         <v>576</v>
       </c>
       <c r="J82" s="1">
@@ -9933,13 +10074,13 @@
         <f t="shared" si="15"/>
         <v>295</v>
       </c>
-      <c r="P82" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="7">
-        <v>0</v>
-      </c>
-      <c r="R82" s="7">
+      <c r="P82" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="8">
+        <v>0</v>
+      </c>
+      <c r="R82" s="8">
         <v>0</v>
       </c>
       <c r="S82" s="1">
@@ -9954,12 +10095,12 @@
       <c r="W82" s="1">
         <v>0</v>
       </c>
-      <c r="X82" s="4"/>
-      <c r="Y82" s="4"/>
+      <c r="X82" s="5"/>
+      <c r="Y82" s="5"/>
     </row>
     <row r="83" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
+      <c r="A83" s="5"/>
+      <c r="B83" s="5"/>
       <c r="C83" s="1" t="s">
         <v>577</v>
       </c>
@@ -9972,13 +10113,13 @@
       <c r="F83" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="G83" s="16" t="s">
+      <c r="G83" s="20" t="s">
         <v>580</v>
       </c>
-      <c r="H83" s="15" t="s">
+      <c r="H83" s="19" t="s">
         <v>531</v>
       </c>
-      <c r="I83" s="17" t="s">
+      <c r="I83" s="21" t="s">
         <v>581</v>
       </c>
       <c r="J83" s="1">
@@ -10003,13 +10144,13 @@
         <f t="shared" si="15"/>
         <v>310</v>
       </c>
-      <c r="P83" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="7">
-        <v>0</v>
-      </c>
-      <c r="R83" s="7">
+      <c r="P83" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="8">
+        <v>0</v>
+      </c>
+      <c r="R83" s="8">
         <v>0</v>
       </c>
       <c r="S83" s="1">
@@ -10024,12 +10165,12 @@
       <c r="W83" s="1">
         <v>0</v>
       </c>
-      <c r="X83" s="4"/>
-      <c r="Y83" s="4"/>
+      <c r="X83" s="5"/>
+      <c r="Y83" s="5"/>
     </row>
     <row r="84" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A84" s="4"/>
-      <c r="B84" s="4"/>
+      <c r="A84" s="5"/>
+      <c r="B84" s="5"/>
       <c r="C84" s="1" t="s">
         <v>582</v>
       </c>
@@ -10042,13 +10183,13 @@
       <c r="F84" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="G84" s="16" t="s">
+      <c r="G84" s="20" t="s">
         <v>585</v>
       </c>
-      <c r="H84" s="15" t="s">
+      <c r="H84" s="19" t="s">
         <v>586</v>
       </c>
-      <c r="I84" s="17" t="s">
+      <c r="I84" s="21" t="s">
         <v>587</v>
       </c>
       <c r="J84" s="1">
@@ -10073,13 +10214,13 @@
         <f t="shared" si="15"/>
         <v>325</v>
       </c>
-      <c r="P84" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="7">
-        <v>0</v>
-      </c>
-      <c r="R84" s="7">
+      <c r="P84" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="8">
+        <v>0</v>
+      </c>
+      <c r="R84" s="8">
         <v>0</v>
       </c>
       <c r="S84" s="1">
@@ -10094,12 +10235,12 @@
       <c r="W84" s="1">
         <v>0</v>
       </c>
-      <c r="X84" s="4"/>
-      <c r="Y84" s="4"/>
+      <c r="X84" s="5"/>
+      <c r="Y84" s="5"/>
     </row>
     <row r="85" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A85" s="4"/>
-      <c r="B85" s="4"/>
+      <c r="A85" s="5"/>
+      <c r="B85" s="5"/>
       <c r="C85" s="1" t="s">
         <v>588</v>
       </c>
@@ -10112,13 +10253,13 @@
       <c r="F85" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="G85" s="16" t="s">
+      <c r="G85" s="20" t="s">
         <v>463</v>
       </c>
-      <c r="H85" s="15" t="s">
+      <c r="H85" s="19" t="s">
         <v>591</v>
       </c>
-      <c r="I85" s="17" t="s">
+      <c r="I85" s="21" t="s">
         <v>592</v>
       </c>
       <c r="J85" s="1">
@@ -10143,13 +10284,13 @@
         <f t="shared" si="15"/>
         <v>340</v>
       </c>
-      <c r="P85" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q85" s="7">
-        <v>0</v>
-      </c>
-      <c r="R85" s="7">
+      <c r="P85" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="8">
+        <v>0</v>
+      </c>
+      <c r="R85" s="8">
         <v>0</v>
       </c>
       <c r="S85" s="1">
@@ -10164,12 +10305,12 @@
       <c r="W85" s="1">
         <v>0</v>
       </c>
-      <c r="X85" s="4"/>
-      <c r="Y85" s="4"/>
+      <c r="X85" s="5"/>
+      <c r="Y85" s="5"/>
     </row>
     <row r="86" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A86" s="4"/>
-      <c r="B86" s="4"/>
+      <c r="A86" s="5"/>
+      <c r="B86" s="5"/>
       <c r="C86" s="1" t="s">
         <v>593</v>
       </c>
@@ -10182,13 +10323,13 @@
       <c r="F86" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="G86" s="16" t="s">
+      <c r="G86" s="20" t="s">
         <v>596</v>
       </c>
-      <c r="H86" s="15" t="s">
+      <c r="H86" s="19" t="s">
         <v>597</v>
       </c>
-      <c r="I86" s="17" t="s">
+      <c r="I86" s="21" t="s">
         <v>598</v>
       </c>
       <c r="J86" s="1">
@@ -10213,13 +10354,13 @@
         <f t="shared" si="15"/>
         <v>355</v>
       </c>
-      <c r="P86" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q86" s="7">
-        <v>0</v>
-      </c>
-      <c r="R86" s="7">
+      <c r="P86" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="8">
+        <v>0</v>
+      </c>
+      <c r="R86" s="8">
         <v>0</v>
       </c>
       <c r="S86" s="1">
@@ -10234,12 +10375,12 @@
       <c r="W86" s="1">
         <v>0</v>
       </c>
-      <c r="X86" s="4"/>
-      <c r="Y86" s="4"/>
+      <c r="X86" s="5"/>
+      <c r="Y86" s="5"/>
     </row>
     <row r="87" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A87" s="4"/>
-      <c r="B87" s="4"/>
+      <c r="A87" s="5"/>
+      <c r="B87" s="5"/>
       <c r="C87" s="1" t="s">
         <v>599</v>
       </c>
@@ -10252,13 +10393,13 @@
       <c r="F87" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="G87" s="16" t="s">
+      <c r="G87" s="20" t="s">
         <v>602</v>
       </c>
-      <c r="H87" s="15" t="s">
+      <c r="H87" s="19" t="s">
         <v>603</v>
       </c>
-      <c r="I87" s="17" t="s">
+      <c r="I87" s="21" t="s">
         <v>604</v>
       </c>
       <c r="J87" s="1">
@@ -10283,13 +10424,13 @@
         <f t="shared" si="15"/>
         <v>370</v>
       </c>
-      <c r="P87" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q87" s="7">
-        <v>0</v>
-      </c>
-      <c r="R87" s="7">
+      <c r="P87" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="8">
+        <v>0</v>
+      </c>
+      <c r="R87" s="8">
         <v>0</v>
       </c>
       <c r="S87" s="1">
@@ -10304,12 +10445,12 @@
       <c r="W87" s="1">
         <v>0</v>
       </c>
-      <c r="X87" s="4"/>
-      <c r="Y87" s="4"/>
+      <c r="X87" s="5"/>
+      <c r="Y87" s="5"/>
     </row>
     <row r="88" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A88" s="4"/>
-      <c r="B88" s="4"/>
+      <c r="A88" s="5"/>
+      <c r="B88" s="5"/>
       <c r="C88" s="1" t="s">
         <v>605</v>
       </c>
@@ -10322,13 +10463,13 @@
       <c r="F88" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="G88" s="16" t="s">
+      <c r="G88" s="20" t="s">
         <v>608</v>
       </c>
-      <c r="H88" s="15" t="s">
+      <c r="H88" s="19" t="s">
         <v>609</v>
       </c>
-      <c r="I88" s="17" t="s">
+      <c r="I88" s="21" t="s">
         <v>610</v>
       </c>
       <c r="J88" s="1">
@@ -10353,13 +10494,13 @@
         <f t="shared" si="15"/>
         <v>385</v>
       </c>
-      <c r="P88" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q88" s="7">
-        <v>0</v>
-      </c>
-      <c r="R88" s="7">
+      <c r="P88" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="8">
+        <v>0</v>
+      </c>
+      <c r="R88" s="8">
         <v>0</v>
       </c>
       <c r="S88" s="1">
@@ -10374,12 +10515,12 @@
       <c r="W88" s="1">
         <v>0</v>
       </c>
-      <c r="X88" s="4"/>
-      <c r="Y88" s="4"/>
+      <c r="X88" s="5"/>
+      <c r="Y88" s="5"/>
     </row>
     <row r="89" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A89" s="4"/>
-      <c r="B89" s="4"/>
+      <c r="A89" s="5"/>
+      <c r="B89" s="5"/>
       <c r="C89" s="1" t="s">
         <v>611</v>
       </c>
@@ -10392,13 +10533,13 @@
       <c r="F89" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="G89" s="16" t="s">
+      <c r="G89" s="20" t="s">
         <v>614</v>
       </c>
-      <c r="H89" s="15" t="s">
+      <c r="H89" s="19" t="s">
         <v>463</v>
       </c>
-      <c r="I89" s="17" t="s">
+      <c r="I89" s="21" t="s">
         <v>615</v>
       </c>
       <c r="J89" s="1">
@@ -10423,13 +10564,13 @@
         <f t="shared" si="15"/>
         <v>400</v>
       </c>
-      <c r="P89" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="7">
-        <v>0</v>
-      </c>
-      <c r="R89" s="7">
+      <c r="P89" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>0</v>
+      </c>
+      <c r="R89" s="8">
         <v>0</v>
       </c>
       <c r="S89" s="1">
@@ -10444,12 +10585,12 @@
       <c r="W89" s="1">
         <v>0</v>
       </c>
-      <c r="X89" s="4"/>
-      <c r="Y89" s="4"/>
+      <c r="X89" s="5"/>
+      <c r="Y89" s="5"/>
     </row>
     <row r="90" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A90" s="4"/>
-      <c r="B90" s="4"/>
+      <c r="A90" s="5"/>
+      <c r="B90" s="5"/>
       <c r="C90" s="1" t="s">
         <v>616</v>
       </c>
@@ -10462,13 +10603,13 @@
       <c r="F90" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="G90" s="16" t="s">
+      <c r="G90" s="20" t="s">
         <v>619</v>
       </c>
-      <c r="H90" s="15" t="s">
+      <c r="H90" s="19" t="s">
         <v>620</v>
       </c>
-      <c r="I90" s="17" t="s">
+      <c r="I90" s="21" t="s">
         <v>621</v>
       </c>
       <c r="J90" s="1">
@@ -10493,19 +10634,19 @@
         <f t="shared" si="15"/>
         <v>415</v>
       </c>
-      <c r="P90" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q90" s="7">
-        <v>0</v>
-      </c>
-      <c r="R90" s="7">
-        <v>0</v>
-      </c>
-      <c r="S90" s="15" t="s">
+      <c r="P90" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="8">
+        <v>0</v>
+      </c>
+      <c r="R90" s="8">
+        <v>0</v>
+      </c>
+      <c r="S90" s="19" t="s">
         <v>622</v>
       </c>
-      <c r="T90" s="15" t="s">
+      <c r="T90" s="19" t="s">
         <v>622</v>
       </c>
       <c r="V90" s="1" t="s">
@@ -10514,12 +10655,12 @@
       <c r="W90" s="1">
         <v>0</v>
       </c>
-      <c r="X90" s="4"/>
-      <c r="Y90" s="4"/>
+      <c r="X90" s="5"/>
+      <c r="Y90" s="5"/>
     </row>
     <row r="91" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A91" s="4"/>
-      <c r="B91" s="4"/>
+      <c r="A91" s="5"/>
+      <c r="B91" s="5"/>
       <c r="C91" s="1" t="s">
         <v>623</v>
       </c>
@@ -10532,13 +10673,13 @@
       <c r="F91" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G91" s="16" t="s">
+      <c r="G91" s="20" t="s">
         <v>512</v>
       </c>
-      <c r="H91" s="15" t="s">
+      <c r="H91" s="19" t="s">
         <v>626</v>
       </c>
-      <c r="I91" s="17" t="s">
+      <c r="I91" s="21" t="s">
         <v>627</v>
       </c>
       <c r="J91" s="1">
@@ -10563,19 +10704,19 @@
         <f t="shared" ref="O91:O96" si="21">O90+20</f>
         <v>435</v>
       </c>
-      <c r="P91" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="7">
-        <v>0</v>
-      </c>
-      <c r="R91" s="7">
-        <v>0</v>
-      </c>
-      <c r="S91" s="15" t="s">
+      <c r="P91" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="8">
+        <v>0</v>
+      </c>
+      <c r="R91" s="8">
+        <v>0</v>
+      </c>
+      <c r="S91" s="19" t="s">
         <v>628</v>
       </c>
-      <c r="T91" s="15" t="s">
+      <c r="T91" s="19" t="s">
         <v>628</v>
       </c>
       <c r="V91" s="1" t="s">
@@ -10584,12 +10725,12 @@
       <c r="W91" s="1">
         <v>0</v>
       </c>
-      <c r="X91" s="4"/>
-      <c r="Y91" s="4"/>
+      <c r="X91" s="5"/>
+      <c r="Y91" s="5"/>
     </row>
     <row r="92" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4"/>
+      <c r="A92" s="5"/>
+      <c r="B92" s="5"/>
       <c r="C92" s="1" t="s">
         <v>629</v>
       </c>
@@ -10602,13 +10743,13 @@
       <c r="F92" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="G92" s="16" t="s">
+      <c r="G92" s="20" t="s">
         <v>632</v>
       </c>
-      <c r="H92" s="15" t="s">
+      <c r="H92" s="19" t="s">
         <v>633</v>
       </c>
-      <c r="I92" s="17" t="s">
+      <c r="I92" s="21" t="s">
         <v>634</v>
       </c>
       <c r="J92" s="1">
@@ -10633,19 +10774,19 @@
         <f t="shared" si="21"/>
         <v>455</v>
       </c>
-      <c r="P92" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q92" s="7">
-        <v>0</v>
-      </c>
-      <c r="R92" s="7">
-        <v>0</v>
-      </c>
-      <c r="S92" s="15" t="s">
+      <c r="P92" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="8">
+        <v>0</v>
+      </c>
+      <c r="R92" s="8">
+        <v>0</v>
+      </c>
+      <c r="S92" s="19" t="s">
         <v>635</v>
       </c>
-      <c r="T92" s="15" t="s">
+      <c r="T92" s="19" t="s">
         <v>635</v>
       </c>
       <c r="V92" s="1" t="s">
@@ -10654,12 +10795,12 @@
       <c r="W92" s="1">
         <v>0</v>
       </c>
-      <c r="X92" s="4"/>
-      <c r="Y92" s="4"/>
+      <c r="X92" s="5"/>
+      <c r="Y92" s="5"/>
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A93" s="4"/>
-      <c r="B93" s="4"/>
+      <c r="A93" s="5"/>
+      <c r="B93" s="5"/>
       <c r="C93" s="1" t="s">
         <v>636</v>
       </c>
@@ -10672,13 +10813,13 @@
       <c r="F93" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="G93" s="16" t="s">
+      <c r="G93" s="20" t="s">
         <v>639</v>
       </c>
-      <c r="H93" s="15" t="s">
+      <c r="H93" s="19" t="s">
         <v>640</v>
       </c>
-      <c r="I93" s="17" t="s">
+      <c r="I93" s="21" t="s">
         <v>641</v>
       </c>
       <c r="J93" s="1">
@@ -10703,19 +10844,19 @@
         <f t="shared" si="21"/>
         <v>475</v>
       </c>
-      <c r="P93" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q93" s="7">
-        <v>0</v>
-      </c>
-      <c r="R93" s="7">
-        <v>0</v>
-      </c>
-      <c r="S93" s="15" t="s">
+      <c r="P93" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="8">
+        <v>0</v>
+      </c>
+      <c r="R93" s="8">
+        <v>0</v>
+      </c>
+      <c r="S93" s="19" t="s">
         <v>642</v>
       </c>
-      <c r="T93" s="15" t="s">
+      <c r="T93" s="19" t="s">
         <v>642</v>
       </c>
       <c r="V93" s="1" t="s">
@@ -10724,12 +10865,12 @@
       <c r="W93" s="1">
         <v>0</v>
       </c>
-      <c r="X93" s="4"/>
-      <c r="Y93" s="4"/>
+      <c r="X93" s="5"/>
+      <c r="Y93" s="5"/>
     </row>
     <row r="94" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A94" s="4"/>
-      <c r="B94" s="4"/>
+      <c r="A94" s="5"/>
+      <c r="B94" s="5"/>
       <c r="C94" s="1" t="s">
         <v>643</v>
       </c>
@@ -10742,13 +10883,13 @@
       <c r="F94" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="G94" s="16" t="s">
+      <c r="G94" s="20" t="s">
         <v>646</v>
       </c>
-      <c r="H94" s="15" t="s">
+      <c r="H94" s="19" t="s">
         <v>647</v>
       </c>
-      <c r="I94" s="17" t="s">
+      <c r="I94" s="21" t="s">
         <v>648</v>
       </c>
       <c r="J94" s="1">
@@ -10773,19 +10914,19 @@
         <f t="shared" si="21"/>
         <v>495</v>
       </c>
-      <c r="P94" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="7">
-        <v>0</v>
-      </c>
-      <c r="R94" s="7">
-        <v>0</v>
-      </c>
-      <c r="S94" s="15" t="s">
+      <c r="P94" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="8">
+        <v>0</v>
+      </c>
+      <c r="R94" s="8">
+        <v>0</v>
+      </c>
+      <c r="S94" s="19" t="s">
         <v>649</v>
       </c>
-      <c r="T94" s="15" t="s">
+      <c r="T94" s="19" t="s">
         <v>649</v>
       </c>
       <c r="V94" s="1" t="s">
@@ -10794,12 +10935,12 @@
       <c r="W94" s="1">
         <v>0</v>
       </c>
-      <c r="X94" s="4"/>
-      <c r="Y94" s="4"/>
+      <c r="X94" s="5"/>
+      <c r="Y94" s="5"/>
     </row>
     <row r="95" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A95" s="4"/>
-      <c r="B95" s="4"/>
+      <c r="A95" s="5"/>
+      <c r="B95" s="5"/>
       <c r="C95" s="1" t="s">
         <v>650</v>
       </c>
@@ -10812,13 +10953,13 @@
       <c r="F95" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="G95" s="16" t="s">
+      <c r="G95" s="20" t="s">
         <v>653</v>
       </c>
-      <c r="H95" s="15" t="s">
+      <c r="H95" s="19" t="s">
         <v>654</v>
       </c>
-      <c r="I95" s="17" t="s">
+      <c r="I95" s="21" t="s">
         <v>655</v>
       </c>
       <c r="J95" s="1">
@@ -10843,19 +10984,19 @@
         <f t="shared" si="21"/>
         <v>515</v>
       </c>
-      <c r="P95" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q95" s="7">
-        <v>0</v>
-      </c>
-      <c r="R95" s="7">
-        <v>0</v>
-      </c>
-      <c r="S95" s="15" t="s">
+      <c r="P95" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="8">
+        <v>0</v>
+      </c>
+      <c r="R95" s="8">
+        <v>0</v>
+      </c>
+      <c r="S95" s="19" t="s">
         <v>656</v>
       </c>
-      <c r="T95" s="15" t="s">
+      <c r="T95" s="19" t="s">
         <v>656</v>
       </c>
       <c r="V95" s="1" t="s">
@@ -10864,8 +11005,8 @@
       <c r="W95" s="1">
         <v>0</v>
       </c>
-      <c r="X95" s="4"/>
-      <c r="Y95" s="4"/>
+      <c r="X95" s="5"/>
+      <c r="Y95" s="5"/>
     </row>
     <row r="96" customHeight="1" spans="3:23">
       <c r="C96" s="1" t="s">
@@ -10880,13 +11021,13 @@
       <c r="F96" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="G96" s="16" t="s">
+      <c r="G96" s="20" t="s">
         <v>660</v>
       </c>
-      <c r="H96" s="15" t="s">
+      <c r="H96" s="19" t="s">
         <v>661</v>
       </c>
-      <c r="I96" s="17" t="s">
+      <c r="I96" s="21" t="s">
         <v>662</v>
       </c>
       <c r="J96" s="1">
@@ -10911,19 +11052,19 @@
         <f t="shared" ref="O96:O100" si="25">O95+25</f>
         <v>540</v>
       </c>
-      <c r="P96" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="7">
-        <v>0</v>
-      </c>
-      <c r="R96" s="7">
-        <v>0</v>
-      </c>
-      <c r="S96" s="15" t="s">
+      <c r="P96" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="8">
+        <v>0</v>
+      </c>
+      <c r="R96" s="8">
+        <v>0</v>
+      </c>
+      <c r="S96" s="19" t="s">
         <v>663</v>
       </c>
-      <c r="T96" s="15" t="s">
+      <c r="T96" s="19" t="s">
         <v>663</v>
       </c>
       <c r="V96" s="1" t="s">
@@ -10946,13 +11087,13 @@
       <c r="F97" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="G97" s="16" t="s">
+      <c r="G97" s="20" t="s">
         <v>667</v>
       </c>
-      <c r="H97" s="15" t="s">
+      <c r="H97" s="19" t="s">
         <v>668</v>
       </c>
-      <c r="I97" s="17" t="s">
+      <c r="I97" s="21" t="s">
         <v>669</v>
       </c>
       <c r="J97" s="1">
@@ -10977,19 +11118,19 @@
         <f t="shared" si="25"/>
         <v>565</v>
       </c>
-      <c r="P97" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="7">
-        <v>0</v>
-      </c>
-      <c r="R97" s="7">
-        <v>0</v>
-      </c>
-      <c r="S97" s="15" t="s">
+      <c r="P97" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="8">
+        <v>0</v>
+      </c>
+      <c r="R97" s="8">
+        <v>0</v>
+      </c>
+      <c r="S97" s="19" t="s">
         <v>670</v>
       </c>
-      <c r="T97" s="15" t="s">
+      <c r="T97" s="19" t="s">
         <v>670</v>
       </c>
       <c r="V97" s="1" t="s">
@@ -11012,13 +11153,13 @@
       <c r="F98" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="G98" s="16" t="s">
+      <c r="G98" s="20" t="s">
         <v>674</v>
       </c>
-      <c r="H98" s="15" t="s">
+      <c r="H98" s="19" t="s">
         <v>675</v>
       </c>
-      <c r="I98" s="17" t="s">
+      <c r="I98" s="21" t="s">
         <v>676</v>
       </c>
       <c r="J98" s="1">
@@ -11043,19 +11184,19 @@
         <f t="shared" si="25"/>
         <v>590</v>
       </c>
-      <c r="P98" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q98" s="7">
-        <v>0</v>
-      </c>
-      <c r="R98" s="7">
-        <v>0</v>
-      </c>
-      <c r="S98" s="15" t="s">
+      <c r="P98" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="8">
+        <v>0</v>
+      </c>
+      <c r="R98" s="8">
+        <v>0</v>
+      </c>
+      <c r="S98" s="19" t="s">
         <v>677</v>
       </c>
-      <c r="T98" s="15" t="s">
+      <c r="T98" s="19" t="s">
         <v>677</v>
       </c>
       <c r="V98" s="1" t="s">
@@ -11078,13 +11219,13 @@
       <c r="F99" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="G99" s="16" t="s">
+      <c r="G99" s="20" t="s">
         <v>681</v>
       </c>
-      <c r="H99" s="15" t="s">
+      <c r="H99" s="19" t="s">
         <v>682</v>
       </c>
-      <c r="I99" s="17" t="s">
+      <c r="I99" s="21" t="s">
         <v>683</v>
       </c>
       <c r="J99" s="1">
@@ -11109,19 +11250,19 @@
         <f t="shared" si="25"/>
         <v>615</v>
       </c>
-      <c r="P99" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q99" s="4">
-        <v>0</v>
-      </c>
-      <c r="R99" s="7">
-        <v>0</v>
-      </c>
-      <c r="S99" s="15" t="s">
+      <c r="P99" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="5">
+        <v>0</v>
+      </c>
+      <c r="R99" s="8">
+        <v>0</v>
+      </c>
+      <c r="S99" s="19" t="s">
         <v>684</v>
       </c>
-      <c r="T99" s="15" t="s">
+      <c r="T99" s="19" t="s">
         <v>684</v>
       </c>
       <c r="V99" s="1" t="s">
@@ -11144,13 +11285,13 @@
       <c r="F100" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="G100" s="16" t="s">
+      <c r="G100" s="20" t="s">
         <v>687</v>
       </c>
-      <c r="H100" s="15" t="s">
+      <c r="H100" s="19" t="s">
         <v>688</v>
       </c>
-      <c r="I100" s="17" t="s">
+      <c r="I100" s="21" t="s">
         <v>689</v>
       </c>
       <c r="J100" s="1">
@@ -11175,19 +11316,19 @@
         <f t="shared" si="25"/>
         <v>640</v>
       </c>
-      <c r="P100" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="4">
-        <v>0</v>
-      </c>
-      <c r="R100" s="7">
-        <v>0</v>
-      </c>
-      <c r="S100" s="15" t="s">
+      <c r="P100" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="5">
+        <v>0</v>
+      </c>
+      <c r="R100" s="8">
+        <v>0</v>
+      </c>
+      <c r="S100" s="19" t="s">
         <v>690</v>
       </c>
-      <c r="T100" s="15" t="s">
+      <c r="T100" s="19" t="s">
         <v>690</v>
       </c>
       <c r="V100" s="1" t="s">
@@ -11198,8 +11339,8 @@
       </c>
     </row>
     <row r="101" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A101" s="4"/>
-      <c r="B101" s="4"/>
+      <c r="A101" s="5"/>
+      <c r="B101" s="5"/>
       <c r="C101" s="1" t="s">
         <v>691</v>
       </c>
@@ -11212,13 +11353,13 @@
       <c r="F101" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="G101" s="16" t="s">
+      <c r="G101" s="20" t="s">
         <v>694</v>
       </c>
-      <c r="H101" s="15" t="s">
+      <c r="H101" s="19" t="s">
         <v>695</v>
       </c>
-      <c r="I101" s="17" t="s">
+      <c r="I101" s="21" t="s">
         <v>696</v>
       </c>
       <c r="J101" s="1">
@@ -11243,19 +11384,19 @@
         <f t="shared" si="26"/>
         <v>648</v>
       </c>
-      <c r="P101" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="4">
-        <v>0</v>
-      </c>
-      <c r="R101" s="7">
-        <v>0</v>
-      </c>
-      <c r="S101" s="15" t="s">
+      <c r="P101" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="5">
+        <v>0</v>
+      </c>
+      <c r="R101" s="8">
+        <v>0</v>
+      </c>
+      <c r="S101" s="19" t="s">
         <v>697</v>
       </c>
-      <c r="T101" s="15" t="s">
+      <c r="T101" s="19" t="s">
         <v>697</v>
       </c>
       <c r="V101" s="1" t="s">
@@ -11264,12 +11405,12 @@
       <c r="W101" s="1">
         <v>0</v>
       </c>
-      <c r="X101" s="4"/>
-      <c r="Y101" s="4"/>
+      <c r="X101" s="5"/>
+      <c r="Y101" s="5"/>
     </row>
     <row r="102" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A102" s="4"/>
-      <c r="B102" s="4"/>
+      <c r="A102" s="5"/>
+      <c r="B102" s="5"/>
       <c r="C102" s="1" t="s">
         <v>698</v>
       </c>
@@ -11282,13 +11423,13 @@
       <c r="F102" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="G102" s="16" t="s">
+      <c r="G102" s="20" t="s">
         <v>701</v>
       </c>
-      <c r="H102" s="15" t="s">
+      <c r="H102" s="19" t="s">
         <v>610</v>
       </c>
-      <c r="I102" s="17" t="s">
+      <c r="I102" s="21" t="s">
         <v>702</v>
       </c>
       <c r="J102" s="1">
@@ -11313,19 +11454,19 @@
         <f t="shared" si="27"/>
         <v>656</v>
       </c>
-      <c r="P102" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="4">
-        <v>0</v>
-      </c>
-      <c r="R102" s="7">
-        <v>0</v>
-      </c>
-      <c r="S102" s="15" t="s">
+      <c r="P102" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="5">
+        <v>0</v>
+      </c>
+      <c r="R102" s="8">
+        <v>0</v>
+      </c>
+      <c r="S102" s="19" t="s">
         <v>703</v>
       </c>
-      <c r="T102" s="15" t="s">
+      <c r="T102" s="19" t="s">
         <v>703</v>
       </c>
       <c r="V102" s="1" t="s">
@@ -11334,12 +11475,12 @@
       <c r="W102" s="1">
         <v>0</v>
       </c>
-      <c r="X102" s="4"/>
-      <c r="Y102" s="4"/>
+      <c r="X102" s="5"/>
+      <c r="Y102" s="5"/>
     </row>
     <row r="103" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A103" s="4"/>
-      <c r="B103" s="4"/>
+      <c r="A103" s="5"/>
+      <c r="B103" s="5"/>
       <c r="C103" s="1" t="s">
         <v>704</v>
       </c>
@@ -11352,13 +11493,13 @@
       <c r="F103" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="G103" s="16" t="s">
+      <c r="G103" s="20" t="s">
         <v>707</v>
       </c>
-      <c r="H103" s="15" t="s">
+      <c r="H103" s="19" t="s">
         <v>615</v>
       </c>
-      <c r="I103" s="17" t="s">
+      <c r="I103" s="21" t="s">
         <v>708</v>
       </c>
       <c r="J103" s="1">
@@ -11383,19 +11524,19 @@
         <f t="shared" si="28"/>
         <v>664</v>
       </c>
-      <c r="P103" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q103" s="4">
-        <v>0</v>
-      </c>
-      <c r="R103" s="7">
-        <v>0</v>
-      </c>
-      <c r="S103" s="15" t="s">
+      <c r="P103" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="5">
+        <v>0</v>
+      </c>
+      <c r="R103" s="8">
+        <v>0</v>
+      </c>
+      <c r="S103" s="19" t="s">
         <v>709</v>
       </c>
-      <c r="T103" s="15" t="s">
+      <c r="T103" s="19" t="s">
         <v>709</v>
       </c>
       <c r="V103" s="1" t="s">
@@ -11404,12 +11545,12 @@
       <c r="W103" s="1">
         <v>0</v>
       </c>
-      <c r="X103" s="4"/>
-      <c r="Y103" s="4"/>
+      <c r="X103" s="5"/>
+      <c r="Y103" s="5"/>
     </row>
     <row r="104" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A104" s="4"/>
-      <c r="B104" s="4"/>
+      <c r="A104" s="5"/>
+      <c r="B104" s="5"/>
       <c r="C104" s="1" t="s">
         <v>710</v>
       </c>
@@ -11422,13 +11563,13 @@
       <c r="F104" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="G104" s="16" t="s">
+      <c r="G104" s="20" t="s">
         <v>713</v>
       </c>
-      <c r="H104" s="15" t="s">
+      <c r="H104" s="19" t="s">
         <v>714</v>
       </c>
-      <c r="I104" s="17" t="s">
+      <c r="I104" s="21" t="s">
         <v>715</v>
       </c>
       <c r="J104" s="1">
@@ -11453,19 +11594,19 @@
         <f t="shared" si="29"/>
         <v>672</v>
       </c>
-      <c r="P104" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q104" s="4">
-        <v>0</v>
-      </c>
-      <c r="R104" s="7">
-        <v>0</v>
-      </c>
-      <c r="S104" s="15" t="s">
+      <c r="P104" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="5">
+        <v>0</v>
+      </c>
+      <c r="R104" s="8">
+        <v>0</v>
+      </c>
+      <c r="S104" s="19" t="s">
         <v>716</v>
       </c>
-      <c r="T104" s="15" t="s">
+      <c r="T104" s="19" t="s">
         <v>716</v>
       </c>
       <c r="V104" s="1" t="s">
@@ -11474,12 +11615,12 @@
       <c r="W104" s="1">
         <v>0</v>
       </c>
-      <c r="X104" s="4"/>
-      <c r="Y104" s="4"/>
+      <c r="X104" s="5"/>
+      <c r="Y104" s="5"/>
     </row>
     <row r="105" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A105" s="4"/>
-      <c r="B105" s="4"/>
+      <c r="A105" s="5"/>
+      <c r="B105" s="5"/>
       <c r="C105" s="1" t="s">
         <v>717</v>
       </c>
@@ -11492,13 +11633,13 @@
       <c r="F105" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="G105" s="16" t="s">
+      <c r="G105" s="20" t="s">
         <v>720</v>
       </c>
-      <c r="H105" s="15" t="s">
+      <c r="H105" s="19" t="s">
         <v>721</v>
       </c>
-      <c r="I105" s="17" t="s">
+      <c r="I105" s="21" t="s">
         <v>722</v>
       </c>
       <c r="J105" s="1">
@@ -11523,19 +11664,19 @@
         <f t="shared" si="30"/>
         <v>680</v>
       </c>
-      <c r="P105" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q105" s="4">
-        <v>0</v>
-      </c>
-      <c r="R105" s="7">
-        <v>0</v>
-      </c>
-      <c r="S105" s="15" t="s">
+      <c r="P105" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="5">
+        <v>0</v>
+      </c>
+      <c r="R105" s="8">
+        <v>0</v>
+      </c>
+      <c r="S105" s="19" t="s">
         <v>723</v>
       </c>
-      <c r="T105" s="15" t="s">
+      <c r="T105" s="19" t="s">
         <v>723</v>
       </c>
       <c r="V105" s="1" t="s">
@@ -11544,12 +11685,12 @@
       <c r="W105" s="1">
         <v>0</v>
       </c>
-      <c r="X105" s="4"/>
-      <c r="Y105" s="4"/>
+      <c r="X105" s="5"/>
+      <c r="Y105" s="5"/>
     </row>
     <row r="106" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A106" s="4"/>
-      <c r="B106" s="4"/>
+      <c r="A106" s="5"/>
+      <c r="B106" s="5"/>
       <c r="C106" s="1" t="s">
         <v>724</v>
       </c>
@@ -11562,13 +11703,13 @@
       <c r="F106" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="G106" s="16" t="s">
+      <c r="G106" s="20" t="s">
         <v>727</v>
       </c>
-      <c r="H106" s="15" t="s">
+      <c r="H106" s="19" t="s">
         <v>728</v>
       </c>
-      <c r="I106" s="17" t="s">
+      <c r="I106" s="21" t="s">
         <v>729</v>
       </c>
       <c r="J106" s="1">
@@ -11593,19 +11734,19 @@
         <f>O105+15</f>
         <v>695</v>
       </c>
-      <c r="P106" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q106" s="4">
-        <v>0</v>
-      </c>
-      <c r="R106" s="7">
-        <v>0</v>
-      </c>
-      <c r="S106" s="15" t="s">
+      <c r="P106" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="5">
+        <v>0</v>
+      </c>
+      <c r="R106" s="8">
+        <v>0</v>
+      </c>
+      <c r="S106" s="19" t="s">
         <v>730</v>
       </c>
-      <c r="T106" s="15" t="s">
+      <c r="T106" s="19" t="s">
         <v>730</v>
       </c>
       <c r="V106" s="1" t="s">
@@ -11614,12 +11755,12 @@
       <c r="W106" s="1">
         <v>0</v>
       </c>
-      <c r="X106" s="4"/>
-      <c r="Y106" s="4"/>
+      <c r="X106" s="5"/>
+      <c r="Y106" s="5"/>
     </row>
     <row r="107" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A107" s="4"/>
-      <c r="B107" s="4"/>
+      <c r="A107" s="5"/>
+      <c r="B107" s="5"/>
       <c r="C107" s="1" t="s">
         <v>731</v>
       </c>
@@ -11632,13 +11773,13 @@
       <c r="F107" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="G107" s="16" t="s">
+      <c r="G107" s="20" t="s">
         <v>734</v>
       </c>
-      <c r="H107" s="15" t="s">
+      <c r="H107" s="19" t="s">
         <v>735</v>
       </c>
-      <c r="I107" s="17" t="s">
+      <c r="I107" s="21" t="s">
         <v>736</v>
       </c>
       <c r="J107" s="1">
@@ -11663,19 +11804,19 @@
         <f>O106+15</f>
         <v>710</v>
       </c>
-      <c r="P107" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q107" s="4">
-        <v>0</v>
-      </c>
-      <c r="R107" s="7">
-        <v>0</v>
-      </c>
-      <c r="S107" s="15" t="s">
+      <c r="P107" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="5">
+        <v>0</v>
+      </c>
+      <c r="R107" s="8">
+        <v>0</v>
+      </c>
+      <c r="S107" s="19" t="s">
         <v>737</v>
       </c>
-      <c r="T107" s="15" t="s">
+      <c r="T107" s="19" t="s">
         <v>737</v>
       </c>
       <c r="V107" s="1" t="s">
@@ -11684,12 +11825,12 @@
       <c r="W107" s="1">
         <v>0</v>
       </c>
-      <c r="X107" s="4"/>
-      <c r="Y107" s="4"/>
+      <c r="X107" s="5"/>
+      <c r="Y107" s="5"/>
     </row>
     <row r="108" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A108" s="4"/>
-      <c r="B108" s="4"/>
+      <c r="A108" s="5"/>
+      <c r="B108" s="5"/>
       <c r="C108" s="1" t="s">
         <v>738</v>
       </c>
@@ -11702,13 +11843,13 @@
       <c r="F108" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="G108" s="16" t="s">
+      <c r="G108" s="20" t="s">
         <v>741</v>
       </c>
-      <c r="H108" s="15" t="s">
+      <c r="H108" s="19" t="s">
         <v>742</v>
       </c>
-      <c r="I108" s="17" t="s">
+      <c r="I108" s="21" t="s">
         <v>743</v>
       </c>
       <c r="J108" s="1">
@@ -11733,19 +11874,19 @@
         <f>O107+15</f>
         <v>725</v>
       </c>
-      <c r="P108" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q108" s="4">
-        <v>0</v>
-      </c>
-      <c r="R108" s="7">
-        <v>0</v>
-      </c>
-      <c r="S108" s="15" t="s">
+      <c r="P108" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="5">
+        <v>0</v>
+      </c>
+      <c r="R108" s="8">
+        <v>0</v>
+      </c>
+      <c r="S108" s="19" t="s">
         <v>744</v>
       </c>
-      <c r="T108" s="15" t="s">
+      <c r="T108" s="19" t="s">
         <v>744</v>
       </c>
       <c r="V108" s="1" t="s">
@@ -11754,12 +11895,12 @@
       <c r="W108" s="1">
         <v>0</v>
       </c>
-      <c r="X108" s="4"/>
-      <c r="Y108" s="4"/>
+      <c r="X108" s="5"/>
+      <c r="Y108" s="5"/>
     </row>
     <row r="109" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A109" s="4"/>
-      <c r="B109" s="4"/>
+      <c r="A109" s="5"/>
+      <c r="B109" s="5"/>
       <c r="C109" s="1" t="s">
         <v>745</v>
       </c>
@@ -11772,13 +11913,13 @@
       <c r="F109" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="G109" s="16" t="s">
+      <c r="G109" s="20" t="s">
         <v>748</v>
       </c>
-      <c r="H109" s="15" t="s">
+      <c r="H109" s="19" t="s">
         <v>749</v>
       </c>
-      <c r="I109" s="17" t="s">
+      <c r="I109" s="21" t="s">
         <v>750</v>
       </c>
       <c r="J109" s="1">
@@ -11803,19 +11944,19 @@
         <f>O108+15</f>
         <v>740</v>
       </c>
-      <c r="P109" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q109" s="4">
-        <v>0</v>
-      </c>
-      <c r="R109" s="7">
-        <v>0</v>
-      </c>
-      <c r="S109" s="15" t="s">
+      <c r="P109" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="5">
+        <v>0</v>
+      </c>
+      <c r="R109" s="8">
+        <v>0</v>
+      </c>
+      <c r="S109" s="19" t="s">
         <v>751</v>
       </c>
-      <c r="T109" s="15" t="s">
+      <c r="T109" s="19" t="s">
         <v>751</v>
       </c>
       <c r="V109" s="1" t="s">
@@ -11824,12 +11965,12 @@
       <c r="W109" s="1">
         <v>0</v>
       </c>
-      <c r="X109" s="4"/>
-      <c r="Y109" s="4"/>
+      <c r="X109" s="5"/>
+      <c r="Y109" s="5"/>
     </row>
     <row r="110" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A110" s="4"/>
-      <c r="B110" s="4"/>
+      <c r="A110" s="5"/>
+      <c r="B110" s="5"/>
       <c r="C110" s="1" t="s">
         <v>752</v>
       </c>
@@ -11842,13 +11983,13 @@
       <c r="F110" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="G110" s="16" t="s">
+      <c r="G110" s="20" t="s">
         <v>676</v>
       </c>
-      <c r="H110" s="15" t="s">
+      <c r="H110" s="19" t="s">
         <v>755</v>
       </c>
-      <c r="I110" s="17" t="s">
+      <c r="I110" s="21" t="s">
         <v>756</v>
       </c>
       <c r="J110" s="1">
@@ -11873,19 +12014,19 @@
         <f>O109+15</f>
         <v>755</v>
       </c>
-      <c r="P110" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q110" s="4">
-        <v>0</v>
-      </c>
-      <c r="R110" s="7">
-        <v>0</v>
-      </c>
-      <c r="S110" s="15" t="s">
+      <c r="P110" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="5">
+        <v>0</v>
+      </c>
+      <c r="R110" s="8">
+        <v>0</v>
+      </c>
+      <c r="S110" s="19" t="s">
         <v>757</v>
       </c>
-      <c r="T110" s="15" t="s">
+      <c r="T110" s="19" t="s">
         <v>757</v>
       </c>
       <c r="V110" s="1" t="s">
@@ -11894,12 +12035,12 @@
       <c r="W110" s="1">
         <v>0</v>
       </c>
-      <c r="X110" s="4"/>
-      <c r="Y110" s="4"/>
+      <c r="X110" s="5"/>
+      <c r="Y110" s="5"/>
     </row>
     <row r="111" s="2" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A111" s="4"/>
-      <c r="B111" s="4"/>
+      <c r="A111" s="5"/>
+      <c r="B111" s="5"/>
       <c r="C111" s="2" t="s">
         <v>758</v>
       </c>
@@ -11912,13 +12053,13 @@
       <c r="F111" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="G111" s="18" t="s">
+      <c r="G111" s="22" t="s">
         <v>761</v>
       </c>
-      <c r="H111" s="19" t="s">
+      <c r="H111" s="23" t="s">
         <v>761</v>
       </c>
-      <c r="I111" s="20" t="s">
+      <c r="I111" s="24" t="s">
         <v>762</v>
       </c>
       <c r="J111" s="1">
@@ -11939,19 +12080,19 @@
       <c r="O111" s="2">
         <v>1000</v>
       </c>
-      <c r="P111" s="4">
+      <c r="P111" s="5">
         <v>35</v>
       </c>
-      <c r="Q111" s="7">
-        <v>0</v>
-      </c>
-      <c r="R111" s="4">
+      <c r="Q111" s="8">
+        <v>0</v>
+      </c>
+      <c r="R111" s="5">
         <v>90</v>
       </c>
-      <c r="S111" s="19" t="s">
+      <c r="S111" s="23" t="s">
         <v>763</v>
       </c>
-      <c r="T111" s="19" t="s">
+      <c r="T111" s="23" t="s">
         <v>763</v>
       </c>
       <c r="V111" s="2" t="s">
@@ -11962,8 +12103,8 @@
       </c>
     </row>
     <row r="112" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A112" s="4"/>
-      <c r="B112" s="4"/>
+      <c r="A112" s="5"/>
+      <c r="B112" s="5"/>
       <c r="C112" s="1" t="s">
         <v>764</v>
       </c>
@@ -11976,13 +12117,13 @@
       <c r="F112" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="G112" s="16" t="s">
+      <c r="G112" s="20" t="s">
         <v>767</v>
       </c>
-      <c r="H112" s="15" t="s">
+      <c r="H112" s="19" t="s">
         <v>767</v>
       </c>
-      <c r="I112" s="17" t="s">
+      <c r="I112" s="21" t="s">
         <v>768</v>
       </c>
       <c r="J112" s="1">
@@ -12007,20 +12148,20 @@
         <f t="shared" ref="O112:O145" si="35">O111+50</f>
         <v>1050</v>
       </c>
-      <c r="P112" s="4">
+      <c r="P112" s="5">
         <f t="shared" ref="P112:P145" si="36">P111+1</f>
         <v>36</v>
       </c>
-      <c r="Q112" s="7">
-        <v>0</v>
-      </c>
-      <c r="R112" s="4">
+      <c r="Q112" s="8">
+        <v>0</v>
+      </c>
+      <c r="R112" s="5">
         <v>90</v>
       </c>
-      <c r="S112" s="15" t="s">
+      <c r="S112" s="19" t="s">
         <v>769</v>
       </c>
-      <c r="T112" s="15" t="s">
+      <c r="T112" s="19" t="s">
         <v>769</v>
       </c>
       <c r="V112" s="1" t="s">
@@ -12031,8 +12172,8 @@
       </c>
     </row>
     <row r="113" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A113" s="4"/>
-      <c r="B113" s="4"/>
+      <c r="A113" s="5"/>
+      <c r="B113" s="5"/>
       <c r="C113" s="1" t="s">
         <v>770</v>
       </c>
@@ -12045,13 +12186,13 @@
       <c r="F113" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="G113" s="16" t="s">
+      <c r="G113" s="20" t="s">
         <v>773</v>
       </c>
-      <c r="H113" s="15" t="s">
+      <c r="H113" s="19" t="s">
         <v>773</v>
       </c>
-      <c r="I113" s="17" t="s">
+      <c r="I113" s="21" t="s">
         <v>774</v>
       </c>
       <c r="J113" s="1">
@@ -12076,20 +12217,20 @@
         <f t="shared" si="35"/>
         <v>1100</v>
       </c>
-      <c r="P113" s="4">
+      <c r="P113" s="5">
         <f t="shared" si="36"/>
         <v>37</v>
       </c>
-      <c r="Q113" s="7">
-        <v>0</v>
-      </c>
-      <c r="R113" s="4">
+      <c r="Q113" s="8">
+        <v>0</v>
+      </c>
+      <c r="R113" s="5">
         <v>90</v>
       </c>
-      <c r="S113" s="15" t="s">
+      <c r="S113" s="19" t="s">
         <v>775</v>
       </c>
-      <c r="T113" s="15" t="s">
+      <c r="T113" s="19" t="s">
         <v>775</v>
       </c>
       <c r="V113" s="1" t="s">
@@ -12100,8 +12241,8 @@
       </c>
     </row>
     <row r="114" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A114" s="4"/>
-      <c r="B114" s="4"/>
+      <c r="A114" s="5"/>
+      <c r="B114" s="5"/>
       <c r="C114" s="1" t="s">
         <v>776</v>
       </c>
@@ -12114,13 +12255,13 @@
       <c r="F114" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="G114" s="16" t="s">
+      <c r="G114" s="20" t="s">
         <v>779</v>
       </c>
-      <c r="H114" s="15" t="s">
+      <c r="H114" s="19" t="s">
         <v>779</v>
       </c>
-      <c r="I114" s="17" t="s">
+      <c r="I114" s="21" t="s">
         <v>780</v>
       </c>
       <c r="J114" s="1">
@@ -12145,20 +12286,20 @@
         <f t="shared" si="35"/>
         <v>1150</v>
       </c>
-      <c r="P114" s="4">
+      <c r="P114" s="5">
         <f t="shared" si="36"/>
         <v>38</v>
       </c>
-      <c r="Q114" s="7">
-        <v>0</v>
-      </c>
-      <c r="R114" s="4">
+      <c r="Q114" s="8">
+        <v>0</v>
+      </c>
+      <c r="R114" s="5">
         <v>90</v>
       </c>
-      <c r="S114" s="15" t="s">
+      <c r="S114" s="19" t="s">
         <v>781</v>
       </c>
-      <c r="T114" s="15" t="s">
+      <c r="T114" s="19" t="s">
         <v>781</v>
       </c>
       <c r="V114" s="1" t="s">
@@ -12169,8 +12310,8 @@
       </c>
     </row>
     <row r="115" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A115" s="4"/>
-      <c r="B115" s="4"/>
+      <c r="A115" s="5"/>
+      <c r="B115" s="5"/>
       <c r="C115" s="1" t="s">
         <v>782</v>
       </c>
@@ -12183,13 +12324,13 @@
       <c r="F115" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="G115" s="16" t="s">
+      <c r="G115" s="20" t="s">
         <v>785</v>
       </c>
-      <c r="H115" s="15" t="s">
+      <c r="H115" s="19" t="s">
         <v>785</v>
       </c>
-      <c r="I115" s="17" t="s">
+      <c r="I115" s="21" t="s">
         <v>786</v>
       </c>
       <c r="J115" s="1">
@@ -12214,20 +12355,20 @@
         <f t="shared" si="35"/>
         <v>1200</v>
       </c>
-      <c r="P115" s="4">
+      <c r="P115" s="5">
         <f t="shared" si="36"/>
         <v>39</v>
       </c>
-      <c r="Q115" s="7">
-        <v>0</v>
-      </c>
-      <c r="R115" s="4">
+      <c r="Q115" s="8">
+        <v>0</v>
+      </c>
+      <c r="R115" s="5">
         <v>90</v>
       </c>
-      <c r="S115" s="15" t="s">
+      <c r="S115" s="19" t="s">
         <v>787</v>
       </c>
-      <c r="T115" s="15" t="s">
+      <c r="T115" s="19" t="s">
         <v>787</v>
       </c>
       <c r="V115" s="1" t="s">
@@ -12238,8 +12379,8 @@
       </c>
     </row>
     <row r="116" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A116" s="4"/>
-      <c r="B116" s="4"/>
+      <c r="A116" s="5"/>
+      <c r="B116" s="5"/>
       <c r="C116" s="1" t="s">
         <v>788</v>
       </c>
@@ -12252,13 +12393,13 @@
       <c r="F116" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="G116" s="16" t="s">
+      <c r="G116" s="20" t="s">
         <v>791</v>
       </c>
-      <c r="H116" s="15" t="s">
+      <c r="H116" s="19" t="s">
         <v>791</v>
       </c>
-      <c r="I116" s="17" t="s">
+      <c r="I116" s="21" t="s">
         <v>792</v>
       </c>
       <c r="J116" s="1">
@@ -12283,20 +12424,20 @@
         <f t="shared" si="35"/>
         <v>1250</v>
       </c>
-      <c r="P116" s="4">
+      <c r="P116" s="5">
         <f t="shared" si="36"/>
         <v>40</v>
       </c>
-      <c r="Q116" s="7">
-        <v>0</v>
-      </c>
-      <c r="R116" s="4">
+      <c r="Q116" s="8">
+        <v>0</v>
+      </c>
+      <c r="R116" s="5">
         <v>90</v>
       </c>
-      <c r="S116" s="15" t="s">
+      <c r="S116" s="19" t="s">
         <v>793</v>
       </c>
-      <c r="T116" s="15" t="s">
+      <c r="T116" s="19" t="s">
         <v>793</v>
       </c>
       <c r="V116" s="1" t="s">
@@ -12305,12 +12446,12 @@
       <c r="W116" s="1">
         <v>0</v>
       </c>
-      <c r="X116" s="4"/>
-      <c r="Y116" s="4"/>
+      <c r="X116" s="5"/>
+      <c r="Y116" s="5"/>
     </row>
     <row r="117" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A117" s="4"/>
-      <c r="B117" s="4"/>
+      <c r="A117" s="5"/>
+      <c r="B117" s="5"/>
       <c r="C117" s="1" t="s">
         <v>794</v>
       </c>
@@ -12323,13 +12464,13 @@
       <c r="F117" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="G117" s="16" t="s">
+      <c r="G117" s="20" t="s">
         <v>797</v>
       </c>
-      <c r="H117" s="15" t="s">
+      <c r="H117" s="19" t="s">
         <v>797</v>
       </c>
-      <c r="I117" s="17" t="s">
+      <c r="I117" s="21" t="s">
         <v>798</v>
       </c>
       <c r="J117" s="1">
@@ -12354,20 +12495,20 @@
         <f t="shared" si="35"/>
         <v>1300</v>
       </c>
-      <c r="P117" s="4">
+      <c r="P117" s="5">
         <f t="shared" si="36"/>
         <v>41</v>
       </c>
-      <c r="Q117" s="7">
-        <v>0</v>
-      </c>
-      <c r="R117" s="4">
+      <c r="Q117" s="8">
+        <v>0</v>
+      </c>
+      <c r="R117" s="5">
         <v>90</v>
       </c>
-      <c r="S117" s="15" t="s">
+      <c r="S117" s="19" t="s">
         <v>799</v>
       </c>
-      <c r="T117" s="15" t="s">
+      <c r="T117" s="19" t="s">
         <v>799</v>
       </c>
       <c r="V117" s="1" t="s">
@@ -12376,12 +12517,12 @@
       <c r="W117" s="1">
         <v>0</v>
       </c>
-      <c r="X117" s="4"/>
-      <c r="Y117" s="4"/>
+      <c r="X117" s="5"/>
+      <c r="Y117" s="5"/>
     </row>
     <row r="118" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A118" s="4"/>
-      <c r="B118" s="4"/>
+      <c r="A118" s="5"/>
+      <c r="B118" s="5"/>
       <c r="C118" s="1" t="s">
         <v>800</v>
       </c>
@@ -12394,13 +12535,13 @@
       <c r="F118" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="G118" s="16" t="s">
+      <c r="G118" s="20" t="s">
         <v>803</v>
       </c>
-      <c r="H118" s="15" t="s">
+      <c r="H118" s="19" t="s">
         <v>803</v>
       </c>
-      <c r="I118" s="17" t="s">
+      <c r="I118" s="21" t="s">
         <v>804</v>
       </c>
       <c r="J118" s="1">
@@ -12425,20 +12566,20 @@
         <f t="shared" si="35"/>
         <v>1350</v>
       </c>
-      <c r="P118" s="4">
+      <c r="P118" s="5">
         <f t="shared" si="36"/>
         <v>42</v>
       </c>
-      <c r="Q118" s="7">
-        <v>0</v>
-      </c>
-      <c r="R118" s="4">
+      <c r="Q118" s="8">
+        <v>0</v>
+      </c>
+      <c r="R118" s="5">
         <v>90</v>
       </c>
-      <c r="S118" s="15" t="s">
+      <c r="S118" s="19" t="s">
         <v>805</v>
       </c>
-      <c r="T118" s="15" t="s">
+      <c r="T118" s="19" t="s">
         <v>805</v>
       </c>
       <c r="V118" s="1" t="s">
@@ -12447,12 +12588,12 @@
       <c r="W118" s="1">
         <v>0</v>
       </c>
-      <c r="X118" s="4"/>
-      <c r="Y118" s="4"/>
+      <c r="X118" s="5"/>
+      <c r="Y118" s="5"/>
     </row>
     <row r="119" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A119" s="4"/>
-      <c r="B119" s="4"/>
+      <c r="A119" s="5"/>
+      <c r="B119" s="5"/>
       <c r="C119" s="1" t="s">
         <v>806</v>
       </c>
@@ -12465,13 +12606,13 @@
       <c r="F119" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="G119" s="16" t="s">
+      <c r="G119" s="20" t="s">
         <v>809</v>
       </c>
-      <c r="H119" s="15" t="s">
+      <c r="H119" s="19" t="s">
         <v>809</v>
       </c>
-      <c r="I119" s="17" t="s">
+      <c r="I119" s="21" t="s">
         <v>810</v>
       </c>
       <c r="J119" s="1">
@@ -12496,20 +12637,20 @@
         <f t="shared" si="35"/>
         <v>1400</v>
       </c>
-      <c r="P119" s="4">
+      <c r="P119" s="5">
         <f t="shared" si="36"/>
         <v>43</v>
       </c>
-      <c r="Q119" s="7">
-        <v>0</v>
-      </c>
-      <c r="R119" s="4">
+      <c r="Q119" s="8">
+        <v>0</v>
+      </c>
+      <c r="R119" s="5">
         <v>90</v>
       </c>
-      <c r="S119" s="15" t="s">
+      <c r="S119" s="19" t="s">
         <v>811</v>
       </c>
-      <c r="T119" s="15" t="s">
+      <c r="T119" s="19" t="s">
         <v>811</v>
       </c>
       <c r="V119" s="1" t="s">
@@ -12518,12 +12659,12 @@
       <c r="W119" s="1">
         <v>0</v>
       </c>
-      <c r="X119" s="4"/>
-      <c r="Y119" s="4"/>
+      <c r="X119" s="5"/>
+      <c r="Y119" s="5"/>
     </row>
     <row r="120" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A120" s="4"/>
-      <c r="B120" s="4"/>
+      <c r="A120" s="5"/>
+      <c r="B120" s="5"/>
       <c r="C120" s="1" t="s">
         <v>812</v>
       </c>
@@ -12536,13 +12677,13 @@
       <c r="F120" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="G120" s="16" t="s">
+      <c r="G120" s="20" t="s">
         <v>815</v>
       </c>
-      <c r="H120" s="15" t="s">
+      <c r="H120" s="19" t="s">
         <v>815</v>
       </c>
-      <c r="I120" s="17" t="s">
+      <c r="I120" s="21" t="s">
         <v>816</v>
       </c>
       <c r="J120" s="1">
@@ -12567,20 +12708,20 @@
         <f t="shared" si="35"/>
         <v>1450</v>
       </c>
-      <c r="P120" s="4">
+      <c r="P120" s="5">
         <f t="shared" si="36"/>
         <v>44</v>
       </c>
-      <c r="Q120" s="7">
-        <v>0</v>
-      </c>
-      <c r="R120" s="4">
+      <c r="Q120" s="8">
+        <v>0</v>
+      </c>
+      <c r="R120" s="5">
         <v>90</v>
       </c>
-      <c r="S120" s="15" t="s">
+      <c r="S120" s="19" t="s">
         <v>817</v>
       </c>
-      <c r="T120" s="15" t="s">
+      <c r="T120" s="19" t="s">
         <v>817</v>
       </c>
       <c r="V120" s="1" t="s">
@@ -12589,8 +12730,8 @@
       <c r="W120" s="1">
         <v>0</v>
       </c>
-      <c r="X120" s="4"/>
-      <c r="Y120" s="4"/>
+      <c r="X120" s="5"/>
+      <c r="Y120" s="5"/>
     </row>
     <row r="121" s="1" customFormat="1" customHeight="1" spans="3:25">
       <c r="C121" s="1" t="s">
@@ -12605,13 +12746,13 @@
       <c r="F121" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="G121" s="16" t="s">
+      <c r="G121" s="20" t="s">
         <v>762</v>
       </c>
-      <c r="H121" s="15" t="s">
+      <c r="H121" s="19" t="s">
         <v>762</v>
       </c>
-      <c r="I121" s="17" t="s">
+      <c r="I121" s="21" t="s">
         <v>821</v>
       </c>
       <c r="J121" s="1">
@@ -12636,21 +12777,21 @@
         <f t="shared" si="35"/>
         <v>1500</v>
       </c>
-      <c r="P121" s="4">
+      <c r="P121" s="5">
         <f t="shared" si="36"/>
         <v>45</v>
       </c>
-      <c r="Q121" s="4">
+      <c r="Q121" s="5">
         <f t="shared" ref="Q121:Q130" si="39">Q120+3</f>
         <v>3</v>
       </c>
-      <c r="R121" s="4">
+      <c r="R121" s="5">
         <v>90</v>
       </c>
-      <c r="S121" s="15" t="s">
+      <c r="S121" s="19" t="s">
         <v>822</v>
       </c>
-      <c r="T121" s="15" t="s">
+      <c r="T121" s="19" t="s">
         <v>822</v>
       </c>
       <c r="V121" s="1" t="s">
@@ -12659,8 +12800,8 @@
       <c r="W121" s="1">
         <v>0</v>
       </c>
-      <c r="X121" s="4"/>
-      <c r="Y121" s="4"/>
+      <c r="X121" s="5"/>
+      <c r="Y121" s="5"/>
     </row>
     <row r="122" s="1" customFormat="1" customHeight="1" spans="3:25">
       <c r="C122" s="1" t="s">
@@ -12675,13 +12816,13 @@
       <c r="F122" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="G122" s="16" t="s">
+      <c r="G122" s="20" t="s">
         <v>826</v>
       </c>
-      <c r="H122" s="15" t="s">
+      <c r="H122" s="19" t="s">
         <v>826</v>
       </c>
-      <c r="I122" s="17" t="s">
+      <c r="I122" s="21" t="s">
         <v>827</v>
       </c>
       <c r="J122" s="1">
@@ -12706,21 +12847,21 @@
         <f t="shared" si="35"/>
         <v>1550</v>
       </c>
-      <c r="P122" s="4">
+      <c r="P122" s="5">
         <f t="shared" si="36"/>
         <v>46</v>
       </c>
-      <c r="Q122" s="4">
+      <c r="Q122" s="5">
         <f t="shared" si="39"/>
         <v>6</v>
       </c>
-      <c r="R122" s="4">
+      <c r="R122" s="5">
         <v>90</v>
       </c>
-      <c r="S122" s="15" t="s">
+      <c r="S122" s="19" t="s">
         <v>828</v>
       </c>
-      <c r="T122" s="15" t="s">
+      <c r="T122" s="19" t="s">
         <v>828</v>
       </c>
       <c r="V122" s="1" t="s">
@@ -12729,8 +12870,8 @@
       <c r="W122" s="1">
         <v>0</v>
       </c>
-      <c r="X122" s="4"/>
-      <c r="Y122" s="4"/>
+      <c r="X122" s="5"/>
+      <c r="Y122" s="5"/>
     </row>
     <row r="123" s="1" customFormat="1" customHeight="1" spans="3:25">
       <c r="C123" s="1" t="s">
@@ -12745,13 +12886,13 @@
       <c r="F123" s="1" t="s">
         <v>831</v>
       </c>
-      <c r="G123" s="16" t="s">
+      <c r="G123" s="20" t="s">
         <v>832</v>
       </c>
-      <c r="H123" s="15" t="s">
+      <c r="H123" s="19" t="s">
         <v>832</v>
       </c>
-      <c r="I123" s="17" t="s">
+      <c r="I123" s="21" t="s">
         <v>833</v>
       </c>
       <c r="J123" s="1">
@@ -12776,21 +12917,21 @@
         <f t="shared" si="35"/>
         <v>1600</v>
       </c>
-      <c r="P123" s="4">
+      <c r="P123" s="5">
         <f t="shared" si="36"/>
         <v>47</v>
       </c>
-      <c r="Q123" s="4">
+      <c r="Q123" s="5">
         <f t="shared" si="39"/>
         <v>9</v>
       </c>
-      <c r="R123" s="4">
+      <c r="R123" s="5">
         <v>90</v>
       </c>
-      <c r="S123" s="15" t="s">
+      <c r="S123" s="19" t="s">
         <v>834</v>
       </c>
-      <c r="T123" s="15" t="s">
+      <c r="T123" s="19" t="s">
         <v>834</v>
       </c>
       <c r="V123" s="1" t="s">
@@ -12799,8 +12940,8 @@
       <c r="W123" s="1">
         <v>0</v>
       </c>
-      <c r="X123" s="4"/>
-      <c r="Y123" s="4"/>
+      <c r="X123" s="5"/>
+      <c r="Y123" s="5"/>
     </row>
     <row r="124" s="1" customFormat="1" customHeight="1" spans="3:25">
       <c r="C124" s="1" t="s">
@@ -12815,13 +12956,13 @@
       <c r="F124" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="G124" s="16" t="s">
+      <c r="G124" s="20" t="s">
         <v>838</v>
       </c>
-      <c r="H124" s="15" t="s">
+      <c r="H124" s="19" t="s">
         <v>838</v>
       </c>
-      <c r="I124" s="17" t="s">
+      <c r="I124" s="21" t="s">
         <v>839</v>
       </c>
       <c r="J124" s="1">
@@ -12846,21 +12987,21 @@
         <f t="shared" si="35"/>
         <v>1650</v>
       </c>
-      <c r="P124" s="4">
+      <c r="P124" s="5">
         <f t="shared" si="36"/>
         <v>48</v>
       </c>
-      <c r="Q124" s="4">
+      <c r="Q124" s="5">
         <f t="shared" si="39"/>
         <v>12</v>
       </c>
-      <c r="R124" s="4">
+      <c r="R124" s="5">
         <v>90</v>
       </c>
-      <c r="S124" s="15" t="s">
+      <c r="S124" s="19" t="s">
         <v>840</v>
       </c>
-      <c r="T124" s="15" t="s">
+      <c r="T124" s="19" t="s">
         <v>840</v>
       </c>
       <c r="V124" s="1" t="s">
@@ -12869,8 +13010,8 @@
       <c r="W124" s="1">
         <v>0</v>
       </c>
-      <c r="X124" s="4"/>
-      <c r="Y124" s="4"/>
+      <c r="X124" s="5"/>
+      <c r="Y124" s="5"/>
     </row>
     <row r="125" s="1" customFormat="1" customHeight="1" spans="3:25">
       <c r="C125" s="1" t="s">
@@ -12885,13 +13026,13 @@
       <c r="F125" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="G125" s="16" t="s">
+      <c r="G125" s="20" t="s">
         <v>844</v>
       </c>
-      <c r="H125" s="15" t="s">
+      <c r="H125" s="19" t="s">
         <v>844</v>
       </c>
-      <c r="I125" s="17" t="s">
+      <c r="I125" s="21" t="s">
         <v>845</v>
       </c>
       <c r="J125" s="1">
@@ -12916,21 +13057,21 @@
         <f t="shared" si="35"/>
         <v>1700</v>
       </c>
-      <c r="P125" s="4">
+      <c r="P125" s="5">
         <f t="shared" si="36"/>
         <v>49</v>
       </c>
-      <c r="Q125" s="4">
+      <c r="Q125" s="5">
         <f t="shared" si="39"/>
         <v>15</v>
       </c>
-      <c r="R125" s="4">
+      <c r="R125" s="5">
         <v>90</v>
       </c>
-      <c r="S125" s="15" t="s">
+      <c r="S125" s="19" t="s">
         <v>846</v>
       </c>
-      <c r="T125" s="15" t="s">
+      <c r="T125" s="19" t="s">
         <v>846</v>
       </c>
       <c r="V125" s="1" t="s">
@@ -12939,12 +13080,12 @@
       <c r="W125" s="1">
         <v>0</v>
       </c>
-      <c r="X125" s="4"/>
-      <c r="Y125" s="4"/>
+      <c r="X125" s="5"/>
+      <c r="Y125" s="5"/>
     </row>
     <row r="126" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A126" s="4"/>
-      <c r="B126" s="4"/>
+      <c r="A126" s="5"/>
+      <c r="B126" s="5"/>
       <c r="C126" s="1" t="s">
         <v>847</v>
       </c>
@@ -12957,13 +13098,13 @@
       <c r="F126" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="G126" s="16" t="s">
+      <c r="G126" s="20" t="s">
         <v>850</v>
       </c>
-      <c r="H126" s="15" t="s">
+      <c r="H126" s="19" t="s">
         <v>850</v>
       </c>
-      <c r="I126" s="17" t="s">
+      <c r="I126" s="21" t="s">
         <v>851</v>
       </c>
       <c r="J126" s="1">
@@ -12988,21 +13129,21 @@
         <f t="shared" si="35"/>
         <v>1750</v>
       </c>
-      <c r="P126" s="4">
+      <c r="P126" s="5">
         <f t="shared" si="36"/>
         <v>50</v>
       </c>
-      <c r="Q126" s="4">
+      <c r="Q126" s="5">
         <f t="shared" si="39"/>
         <v>18</v>
       </c>
-      <c r="R126" s="4">
+      <c r="R126" s="5">
         <v>90</v>
       </c>
-      <c r="S126" s="15" t="s">
+      <c r="S126" s="19" t="s">
         <v>852</v>
       </c>
-      <c r="T126" s="15" t="s">
+      <c r="T126" s="19" t="s">
         <v>852</v>
       </c>
       <c r="V126" s="1" t="s">
@@ -13011,12 +13152,12 @@
       <c r="W126" s="1">
         <v>0</v>
       </c>
-      <c r="X126" s="4"/>
-      <c r="Y126" s="4"/>
+      <c r="X126" s="5"/>
+      <c r="Y126" s="5"/>
     </row>
     <row r="127" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A127" s="4"/>
-      <c r="B127" s="4"/>
+      <c r="A127" s="5"/>
+      <c r="B127" s="5"/>
       <c r="C127" s="1" t="s">
         <v>853</v>
       </c>
@@ -13029,13 +13170,13 @@
       <c r="F127" s="1" t="s">
         <v>855</v>
       </c>
-      <c r="G127" s="16" t="s">
+      <c r="G127" s="20" t="s">
         <v>856</v>
       </c>
-      <c r="H127" s="15" t="s">
+      <c r="H127" s="19" t="s">
         <v>856</v>
       </c>
-      <c r="I127" s="17" t="s">
+      <c r="I127" s="21" t="s">
         <v>857</v>
       </c>
       <c r="J127" s="1">
@@ -13060,21 +13201,21 @@
         <f t="shared" si="35"/>
         <v>1800</v>
       </c>
-      <c r="P127" s="4">
+      <c r="P127" s="5">
         <f t="shared" si="36"/>
         <v>51</v>
       </c>
-      <c r="Q127" s="4">
+      <c r="Q127" s="5">
         <f t="shared" si="39"/>
         <v>21</v>
       </c>
-      <c r="R127" s="4">
+      <c r="R127" s="5">
         <v>90</v>
       </c>
-      <c r="S127" s="15" t="s">
+      <c r="S127" s="19" t="s">
         <v>858</v>
       </c>
-      <c r="T127" s="15" t="s">
+      <c r="T127" s="19" t="s">
         <v>858</v>
       </c>
       <c r="V127" s="1" t="s">
@@ -13083,12 +13224,12 @@
       <c r="W127" s="1">
         <v>0</v>
       </c>
-      <c r="X127" s="4"/>
-      <c r="Y127" s="4"/>
+      <c r="X127" s="5"/>
+      <c r="Y127" s="5"/>
     </row>
     <row r="128" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A128" s="4"/>
-      <c r="B128" s="4"/>
+      <c r="A128" s="5"/>
+      <c r="B128" s="5"/>
       <c r="C128" s="1" t="s">
         <v>859</v>
       </c>
@@ -13101,13 +13242,13 @@
       <c r="F128" s="1" t="s">
         <v>861</v>
       </c>
-      <c r="G128" s="16" t="s">
+      <c r="G128" s="20" t="s">
         <v>862</v>
       </c>
-      <c r="H128" s="15" t="s">
+      <c r="H128" s="19" t="s">
         <v>862</v>
       </c>
-      <c r="I128" s="17" t="s">
+      <c r="I128" s="21" t="s">
         <v>863</v>
       </c>
       <c r="J128" s="1">
@@ -13132,21 +13273,21 @@
         <f t="shared" si="35"/>
         <v>1850</v>
       </c>
-      <c r="P128" s="4">
+      <c r="P128" s="5">
         <f t="shared" si="36"/>
         <v>52</v>
       </c>
-      <c r="Q128" s="4">
+      <c r="Q128" s="5">
         <f t="shared" si="39"/>
         <v>24</v>
       </c>
-      <c r="R128" s="4">
+      <c r="R128" s="5">
         <v>90</v>
       </c>
-      <c r="S128" s="15" t="s">
+      <c r="S128" s="19" t="s">
         <v>864</v>
       </c>
-      <c r="T128" s="15" t="s">
+      <c r="T128" s="19" t="s">
         <v>864</v>
       </c>
       <c r="V128" s="1" t="s">
@@ -13155,12 +13296,12 @@
       <c r="W128" s="1">
         <v>0</v>
       </c>
-      <c r="X128" s="4"/>
-      <c r="Y128" s="4"/>
+      <c r="X128" s="5"/>
+      <c r="Y128" s="5"/>
     </row>
     <row r="129" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A129" s="4"/>
-      <c r="B129" s="4"/>
+      <c r="A129" s="5"/>
+      <c r="B129" s="5"/>
       <c r="C129" s="1" t="s">
         <v>865</v>
       </c>
@@ -13173,13 +13314,13 @@
       <c r="F129" s="1" t="s">
         <v>867</v>
       </c>
-      <c r="G129" s="16" t="s">
+      <c r="G129" s="20" t="s">
         <v>868</v>
       </c>
-      <c r="H129" s="15" t="s">
+      <c r="H129" s="19" t="s">
         <v>868</v>
       </c>
-      <c r="I129" s="17" t="s">
+      <c r="I129" s="21" t="s">
         <v>869</v>
       </c>
       <c r="J129" s="1">
@@ -13204,21 +13345,21 @@
         <f t="shared" si="35"/>
         <v>1900</v>
       </c>
-      <c r="P129" s="4">
+      <c r="P129" s="5">
         <f t="shared" si="36"/>
         <v>53</v>
       </c>
-      <c r="Q129" s="4">
+      <c r="Q129" s="5">
         <f t="shared" si="39"/>
         <v>27</v>
       </c>
-      <c r="R129" s="4">
+      <c r="R129" s="5">
         <v>90</v>
       </c>
-      <c r="S129" s="15" t="s">
+      <c r="S129" s="19" t="s">
         <v>870</v>
       </c>
-      <c r="T129" s="15" t="s">
+      <c r="T129" s="19" t="s">
         <v>870</v>
       </c>
       <c r="V129" s="1" t="s">
@@ -13227,12 +13368,12 @@
       <c r="W129" s="1">
         <v>0</v>
       </c>
-      <c r="X129" s="4"/>
-      <c r="Y129" s="4"/>
+      <c r="X129" s="5"/>
+      <c r="Y129" s="5"/>
     </row>
     <row r="130" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A130" s="4"/>
-      <c r="B130" s="4"/>
+      <c r="A130" s="5"/>
+      <c r="B130" s="5"/>
       <c r="C130" s="1" t="s">
         <v>871</v>
       </c>
@@ -13245,13 +13386,13 @@
       <c r="F130" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="G130" s="16" t="s">
+      <c r="G130" s="20" t="s">
         <v>874</v>
       </c>
-      <c r="H130" s="15" t="s">
+      <c r="H130" s="19" t="s">
         <v>874</v>
       </c>
-      <c r="I130" s="17" t="s">
+      <c r="I130" s="21" t="s">
         <v>875</v>
       </c>
       <c r="J130" s="1">
@@ -13276,21 +13417,21 @@
         <f t="shared" si="35"/>
         <v>1950</v>
       </c>
-      <c r="P130" s="4">
+      <c r="P130" s="5">
         <f t="shared" si="36"/>
         <v>54</v>
       </c>
-      <c r="Q130" s="4">
+      <c r="Q130" s="5">
         <f t="shared" si="39"/>
         <v>30</v>
       </c>
-      <c r="R130" s="4">
+      <c r="R130" s="5">
         <v>90</v>
       </c>
-      <c r="S130" s="15" t="s">
+      <c r="S130" s="19" t="s">
         <v>876</v>
       </c>
-      <c r="T130" s="15" t="s">
+      <c r="T130" s="19" t="s">
         <v>876</v>
       </c>
       <c r="V130" s="1" t="s">
@@ -13299,8 +13440,8 @@
       <c r="W130" s="1">
         <v>0</v>
       </c>
-      <c r="X130" s="4"/>
-      <c r="Y130" s="4"/>
+      <c r="X130" s="5"/>
+      <c r="Y130" s="5"/>
     </row>
     <row r="131" customHeight="1" spans="3:23">
       <c r="C131" s="1" t="s">
@@ -13315,13 +13456,13 @@
       <c r="F131" s="1" t="s">
         <v>879</v>
       </c>
-      <c r="G131" s="16" t="s">
+      <c r="G131" s="20" t="s">
         <v>880</v>
       </c>
-      <c r="H131" s="15" t="s">
+      <c r="H131" s="19" t="s">
         <v>880</v>
       </c>
-      <c r="I131" s="17" t="s">
+      <c r="I131" s="21" t="s">
         <v>881</v>
       </c>
       <c r="J131" s="1">
@@ -13346,21 +13487,21 @@
         <f t="shared" ref="O131:O135" si="43">O130+100</f>
         <v>2050</v>
       </c>
-      <c r="P131" s="4">
+      <c r="P131" s="5">
         <f t="shared" ref="P131:P146" si="44">P130+2</f>
         <v>56</v>
       </c>
-      <c r="Q131" s="4">
+      <c r="Q131" s="5">
         <f t="shared" ref="Q131:Q180" si="45">Q130+4</f>
         <v>34</v>
       </c>
-      <c r="R131" s="4">
+      <c r="R131" s="5">
         <v>92</v>
       </c>
-      <c r="S131" s="15" t="s">
+      <c r="S131" s="19" t="s">
         <v>882</v>
       </c>
-      <c r="T131" s="15" t="s">
+      <c r="T131" s="19" t="s">
         <v>882</v>
       </c>
       <c r="V131" s="1" t="s">
@@ -13383,13 +13524,13 @@
       <c r="F132" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="G132" s="16" t="s">
+      <c r="G132" s="20" t="s">
         <v>886</v>
       </c>
-      <c r="H132" s="15" t="s">
+      <c r="H132" s="19" t="s">
         <v>886</v>
       </c>
-      <c r="I132" s="17" t="s">
+      <c r="I132" s="21" t="s">
         <v>887</v>
       </c>
       <c r="J132" s="1">
@@ -13414,21 +13555,21 @@
         <f t="shared" si="43"/>
         <v>2150</v>
       </c>
-      <c r="P132" s="4">
+      <c r="P132" s="5">
         <f t="shared" si="44"/>
         <v>58</v>
       </c>
-      <c r="Q132" s="4">
+      <c r="Q132" s="5">
         <f t="shared" si="45"/>
         <v>38</v>
       </c>
-      <c r="R132" s="4">
+      <c r="R132" s="5">
         <v>94</v>
       </c>
-      <c r="S132" s="15" t="s">
+      <c r="S132" s="19" t="s">
         <v>888</v>
       </c>
-      <c r="T132" s="15" t="s">
+      <c r="T132" s="19" t="s">
         <v>888</v>
       </c>
       <c r="V132" s="1" t="s">
@@ -13451,13 +13592,13 @@
       <c r="F133" s="1" t="s">
         <v>891</v>
       </c>
-      <c r="G133" s="16" t="s">
+      <c r="G133" s="20" t="s">
         <v>892</v>
       </c>
-      <c r="H133" s="15" t="s">
+      <c r="H133" s="19" t="s">
         <v>892</v>
       </c>
-      <c r="I133" s="17" t="s">
+      <c r="I133" s="21" t="s">
         <v>893</v>
       </c>
       <c r="J133" s="1">
@@ -13482,21 +13623,21 @@
         <f t="shared" si="43"/>
         <v>2250</v>
       </c>
-      <c r="P133" s="4">
+      <c r="P133" s="5">
         <f t="shared" si="44"/>
         <v>60</v>
       </c>
-      <c r="Q133" s="4">
+      <c r="Q133" s="5">
         <f t="shared" si="45"/>
         <v>42</v>
       </c>
-      <c r="R133" s="4">
+      <c r="R133" s="5">
         <v>96</v>
       </c>
-      <c r="S133" s="15" t="s">
+      <c r="S133" s="19" t="s">
         <v>894</v>
       </c>
-      <c r="T133" s="15" t="s">
+      <c r="T133" s="19" t="s">
         <v>894</v>
       </c>
       <c r="V133" s="1" t="s">
@@ -13519,13 +13660,13 @@
       <c r="F134" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="G134" s="16" t="s">
+      <c r="G134" s="20" t="s">
         <v>898</v>
       </c>
-      <c r="H134" s="15" t="s">
+      <c r="H134" s="19" t="s">
         <v>898</v>
       </c>
-      <c r="I134" s="17" t="s">
+      <c r="I134" s="21" t="s">
         <v>899</v>
       </c>
       <c r="J134" s="1">
@@ -13550,21 +13691,21 @@
         <f t="shared" si="43"/>
         <v>2350</v>
       </c>
-      <c r="P134" s="4">
+      <c r="P134" s="5">
         <f t="shared" si="44"/>
         <v>62</v>
       </c>
-      <c r="Q134" s="4">
+      <c r="Q134" s="5">
         <f t="shared" si="45"/>
         <v>46</v>
       </c>
-      <c r="R134" s="4">
+      <c r="R134" s="5">
         <v>98</v>
       </c>
-      <c r="S134" s="15" t="s">
+      <c r="S134" s="19" t="s">
         <v>900</v>
       </c>
-      <c r="T134" s="15" t="s">
+      <c r="T134" s="19" t="s">
         <v>900</v>
       </c>
       <c r="V134" s="1" t="s">
@@ -13587,13 +13728,13 @@
       <c r="F135" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="G135" s="16" t="s">
+      <c r="G135" s="20" t="s">
         <v>903</v>
       </c>
-      <c r="H135" s="15" t="s">
+      <c r="H135" s="19" t="s">
         <v>903</v>
       </c>
-      <c r="I135" s="17" t="s">
+      <c r="I135" s="21" t="s">
         <v>904</v>
       </c>
       <c r="J135" s="1">
@@ -13618,21 +13759,21 @@
         <f t="shared" si="43"/>
         <v>2450</v>
       </c>
-      <c r="P135" s="4">
+      <c r="P135" s="5">
         <f t="shared" si="44"/>
         <v>64</v>
       </c>
-      <c r="Q135" s="4">
+      <c r="Q135" s="5">
         <f t="shared" si="45"/>
         <v>50</v>
       </c>
-      <c r="R135" s="4">
+      <c r="R135" s="5">
         <v>99</v>
       </c>
-      <c r="S135" s="15" t="s">
+      <c r="S135" s="19" t="s">
         <v>455</v>
       </c>
-      <c r="T135" s="15" t="s">
+      <c r="T135" s="19" t="s">
         <v>455</v>
       </c>
       <c r="V135" s="1" t="s">
@@ -13643,8 +13784,8 @@
       </c>
     </row>
     <row r="136" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A136" s="4"/>
-      <c r="B136" s="4"/>
+      <c r="A136" s="5"/>
+      <c r="B136" s="5"/>
       <c r="C136" s="1" t="s">
         <v>905</v>
       </c>
@@ -13657,13 +13798,13 @@
       <c r="F136" s="1" t="s">
         <v>907</v>
       </c>
-      <c r="G136" s="16" t="s">
+      <c r="G136" s="20" t="s">
         <v>908</v>
       </c>
-      <c r="H136" s="15" t="s">
+      <c r="H136" s="19" t="s">
         <v>908</v>
       </c>
-      <c r="I136" s="17" t="s">
+      <c r="I136" s="21" t="s">
         <v>909</v>
       </c>
       <c r="J136" s="1">
@@ -13688,21 +13829,21 @@
         <f t="shared" ref="O136:O145" si="49">O135+200</f>
         <v>2650</v>
       </c>
-      <c r="P136" s="4">
+      <c r="P136" s="5">
         <f t="shared" si="44"/>
         <v>66</v>
       </c>
-      <c r="Q136" s="4">
+      <c r="Q136" s="5">
         <f t="shared" si="45"/>
         <v>54</v>
       </c>
-      <c r="R136" s="4">
+      <c r="R136" s="5">
         <v>99.2</v>
       </c>
-      <c r="S136" s="15" t="s">
+      <c r="S136" s="19" t="s">
         <v>910</v>
       </c>
-      <c r="T136" s="15" t="s">
+      <c r="T136" s="19" t="s">
         <v>910</v>
       </c>
       <c r="V136" s="1" t="s">
@@ -13711,12 +13852,12 @@
       <c r="W136" s="1">
         <v>0</v>
       </c>
-      <c r="X136" s="4"/>
-      <c r="Y136" s="4"/>
+      <c r="X136" s="5"/>
+      <c r="Y136" s="5"/>
     </row>
     <row r="137" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A137" s="4"/>
-      <c r="B137" s="4"/>
+      <c r="A137" s="5"/>
+      <c r="B137" s="5"/>
       <c r="C137" s="1" t="s">
         <v>911</v>
       </c>
@@ -13729,13 +13870,13 @@
       <c r="F137" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="G137" s="16" t="s">
+      <c r="G137" s="20" t="s">
         <v>914</v>
       </c>
-      <c r="H137" s="15" t="s">
+      <c r="H137" s="19" t="s">
         <v>914</v>
       </c>
-      <c r="I137" s="17" t="s">
+      <c r="I137" s="21" t="s">
         <v>915</v>
       </c>
       <c r="J137" s="1">
@@ -13760,21 +13901,21 @@
         <f t="shared" si="49"/>
         <v>2850</v>
       </c>
-      <c r="P137" s="4">
+      <c r="P137" s="5">
         <f t="shared" si="44"/>
         <v>68</v>
       </c>
-      <c r="Q137" s="4">
+      <c r="Q137" s="5">
         <f t="shared" si="45"/>
         <v>58</v>
       </c>
-      <c r="R137" s="4">
+      <c r="R137" s="5">
         <v>99.4</v>
       </c>
-      <c r="S137" s="15" t="s">
+      <c r="S137" s="19" t="s">
         <v>916</v>
       </c>
-      <c r="T137" s="15" t="s">
+      <c r="T137" s="19" t="s">
         <v>916</v>
       </c>
       <c r="V137" s="1" t="s">
@@ -13783,12 +13924,12 @@
       <c r="W137" s="1">
         <v>0</v>
       </c>
-      <c r="X137" s="4"/>
-      <c r="Y137" s="4"/>
+      <c r="X137" s="5"/>
+      <c r="Y137" s="5"/>
     </row>
     <row r="138" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A138" s="4"/>
-      <c r="B138" s="4"/>
+      <c r="A138" s="5"/>
+      <c r="B138" s="5"/>
       <c r="C138" s="1" t="s">
         <v>917</v>
       </c>
@@ -13801,13 +13942,13 @@
       <c r="F138" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="G138" s="16" t="s">
+      <c r="G138" s="20" t="s">
         <v>920</v>
       </c>
-      <c r="H138" s="15" t="s">
+      <c r="H138" s="19" t="s">
         <v>920</v>
       </c>
-      <c r="I138" s="17" t="s">
+      <c r="I138" s="21" t="s">
         <v>921</v>
       </c>
       <c r="J138" s="1">
@@ -13832,21 +13973,21 @@
         <f t="shared" si="49"/>
         <v>3050</v>
       </c>
-      <c r="P138" s="4">
+      <c r="P138" s="5">
         <f t="shared" si="44"/>
         <v>70</v>
       </c>
-      <c r="Q138" s="4">
+      <c r="Q138" s="5">
         <f t="shared" si="45"/>
         <v>62</v>
       </c>
-      <c r="R138" s="4">
+      <c r="R138" s="5">
         <v>99.6</v>
       </c>
-      <c r="S138" s="15" t="s">
+      <c r="S138" s="19" t="s">
         <v>922</v>
       </c>
-      <c r="T138" s="15" t="s">
+      <c r="T138" s="19" t="s">
         <v>922</v>
       </c>
       <c r="V138" s="1" t="s">
@@ -13855,12 +13996,12 @@
       <c r="W138" s="1">
         <v>0</v>
       </c>
-      <c r="X138" s="4"/>
-      <c r="Y138" s="4"/>
+      <c r="X138" s="5"/>
+      <c r="Y138" s="5"/>
     </row>
     <row r="139" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A139" s="4"/>
-      <c r="B139" s="4"/>
+      <c r="A139" s="5"/>
+      <c r="B139" s="5"/>
       <c r="C139" s="1" t="s">
         <v>923</v>
       </c>
@@ -13873,13 +14014,13 @@
       <c r="F139" s="1" t="s">
         <v>925</v>
       </c>
-      <c r="G139" s="16" t="s">
+      <c r="G139" s="20" t="s">
         <v>926</v>
       </c>
-      <c r="H139" s="15" t="s">
+      <c r="H139" s="19" t="s">
         <v>926</v>
       </c>
-      <c r="I139" s="17" t="s">
+      <c r="I139" s="21" t="s">
         <v>927</v>
       </c>
       <c r="J139" s="1">
@@ -13904,21 +14045,21 @@
         <f t="shared" si="49"/>
         <v>3250</v>
       </c>
-      <c r="P139" s="4">
+      <c r="P139" s="5">
         <f t="shared" si="44"/>
         <v>72</v>
       </c>
-      <c r="Q139" s="4">
+      <c r="Q139" s="5">
         <f t="shared" si="45"/>
         <v>66</v>
       </c>
-      <c r="R139" s="4">
+      <c r="R139" s="5">
         <v>99.8</v>
       </c>
-      <c r="S139" s="15" t="s">
+      <c r="S139" s="19" t="s">
         <v>928</v>
       </c>
-      <c r="T139" s="15" t="s">
+      <c r="T139" s="19" t="s">
         <v>928</v>
       </c>
       <c r="V139" s="1" t="s">
@@ -13927,12 +14068,12 @@
       <c r="W139" s="1">
         <v>0</v>
       </c>
-      <c r="X139" s="4"/>
-      <c r="Y139" s="4"/>
+      <c r="X139" s="5"/>
+      <c r="Y139" s="5"/>
     </row>
     <row r="140" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A140" s="4"/>
-      <c r="B140" s="4"/>
+      <c r="A140" s="5"/>
+      <c r="B140" s="5"/>
       <c r="C140" s="1" t="s">
         <v>929</v>
       </c>
@@ -13945,13 +14086,13 @@
       <c r="F140" s="1" t="s">
         <v>931</v>
       </c>
-      <c r="G140" s="16" t="s">
+      <c r="G140" s="20" t="s">
         <v>932</v>
       </c>
-      <c r="H140" s="15" t="s">
+      <c r="H140" s="19" t="s">
         <v>932</v>
       </c>
-      <c r="I140" s="17" t="s">
+      <c r="I140" s="21" t="s">
         <v>933</v>
       </c>
       <c r="J140" s="1">
@@ -13976,21 +14117,21 @@
         <f t="shared" si="49"/>
         <v>3450</v>
       </c>
-      <c r="P140" s="4">
+      <c r="P140" s="5">
         <f t="shared" si="44"/>
         <v>74</v>
       </c>
-      <c r="Q140" s="4">
+      <c r="Q140" s="5">
         <f t="shared" si="45"/>
         <v>70</v>
       </c>
-      <c r="R140" s="4">
+      <c r="R140" s="5">
         <v>99.9</v>
       </c>
-      <c r="S140" s="15" t="s">
+      <c r="S140" s="19" t="s">
         <v>934</v>
       </c>
-      <c r="T140" s="15" t="s">
+      <c r="T140" s="19" t="s">
         <v>934</v>
       </c>
       <c r="V140" s="1" t="s">
@@ -13999,12 +14140,12 @@
       <c r="W140" s="1">
         <v>0</v>
       </c>
-      <c r="X140" s="4"/>
-      <c r="Y140" s="4"/>
+      <c r="X140" s="5"/>
+      <c r="Y140" s="5"/>
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A141" s="4"/>
-      <c r="B141" s="4"/>
+      <c r="A141" s="5"/>
+      <c r="B141" s="5"/>
       <c r="C141" s="1" t="s">
         <v>935</v>
       </c>
@@ -14017,13 +14158,13 @@
       <c r="F141" s="1" t="s">
         <v>937</v>
       </c>
-      <c r="G141" s="16" t="s">
+      <c r="G141" s="20" t="s">
         <v>938</v>
       </c>
-      <c r="H141" s="15" t="s">
+      <c r="H141" s="19" t="s">
         <v>938</v>
       </c>
-      <c r="I141" s="17" t="s">
+      <c r="I141" s="21" t="s">
         <v>939</v>
       </c>
       <c r="J141" s="1">
@@ -14048,21 +14189,21 @@
         <f t="shared" ref="O141:O180" si="53">O140+250</f>
         <v>3700</v>
       </c>
-      <c r="P141" s="4">
+      <c r="P141" s="5">
         <f t="shared" si="44"/>
         <v>76</v>
       </c>
-      <c r="Q141" s="4">
+      <c r="Q141" s="5">
         <f t="shared" si="45"/>
         <v>74</v>
       </c>
-      <c r="R141" s="4">
+      <c r="R141" s="5">
         <v>99.92</v>
       </c>
-      <c r="S141" s="15" t="s">
+      <c r="S141" s="19" t="s">
         <v>940</v>
       </c>
-      <c r="T141" s="15" t="s">
+      <c r="T141" s="19" t="s">
         <v>940</v>
       </c>
       <c r="V141" s="1" t="s">
@@ -14071,12 +14212,12 @@
       <c r="W141" s="1">
         <v>0</v>
       </c>
-      <c r="X141" s="4"/>
-      <c r="Y141" s="4"/>
+      <c r="X141" s="5"/>
+      <c r="Y141" s="5"/>
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A142" s="4"/>
-      <c r="B142" s="4"/>
+      <c r="A142" s="5"/>
+      <c r="B142" s="5"/>
       <c r="C142" s="1" t="s">
         <v>941</v>
       </c>
@@ -14089,13 +14230,13 @@
       <c r="F142" s="1" t="s">
         <v>943</v>
       </c>
-      <c r="G142" s="16" t="s">
+      <c r="G142" s="20" t="s">
         <v>944</v>
       </c>
-      <c r="H142" s="15" t="s">
+      <c r="H142" s="19" t="s">
         <v>944</v>
       </c>
-      <c r="I142" s="17" t="s">
+      <c r="I142" s="21" t="s">
         <v>945</v>
       </c>
       <c r="J142" s="1">
@@ -14120,21 +14261,21 @@
         <f t="shared" si="53"/>
         <v>3950</v>
       </c>
-      <c r="P142" s="4">
+      <c r="P142" s="5">
         <f t="shared" si="44"/>
         <v>78</v>
       </c>
-      <c r="Q142" s="4">
+      <c r="Q142" s="5">
         <f t="shared" si="45"/>
         <v>78</v>
       </c>
-      <c r="R142" s="4">
+      <c r="R142" s="5">
         <v>99.94</v>
       </c>
-      <c r="S142" s="15" t="s">
+      <c r="S142" s="19" t="s">
         <v>946</v>
       </c>
-      <c r="T142" s="15" t="s">
+      <c r="T142" s="19" t="s">
         <v>946</v>
       </c>
       <c r="V142" s="1" t="s">
@@ -14143,12 +14284,12 @@
       <c r="W142" s="1">
         <v>0</v>
       </c>
-      <c r="X142" s="4"/>
-      <c r="Y142" s="4"/>
+      <c r="X142" s="5"/>
+      <c r="Y142" s="5"/>
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A143" s="4"/>
-      <c r="B143" s="4"/>
+      <c r="A143" s="5"/>
+      <c r="B143" s="5"/>
       <c r="C143" s="1" t="s">
         <v>947</v>
       </c>
@@ -14161,13 +14302,13 @@
       <c r="F143" s="1" t="s">
         <v>949</v>
       </c>
-      <c r="G143" s="16" t="s">
+      <c r="G143" s="20" t="s">
         <v>950</v>
       </c>
-      <c r="H143" s="15" t="s">
+      <c r="H143" s="19" t="s">
         <v>950</v>
       </c>
-      <c r="I143" s="17" t="s">
+      <c r="I143" s="21" t="s">
         <v>951</v>
       </c>
       <c r="J143" s="1">
@@ -14192,21 +14333,21 @@
         <f t="shared" si="53"/>
         <v>4200</v>
       </c>
-      <c r="P143" s="4">
+      <c r="P143" s="5">
         <f t="shared" si="44"/>
         <v>80</v>
       </c>
-      <c r="Q143" s="4">
+      <c r="Q143" s="5">
         <f t="shared" si="45"/>
         <v>82</v>
       </c>
-      <c r="R143" s="4">
+      <c r="R143" s="5">
         <v>99.96</v>
       </c>
-      <c r="S143" s="15" t="s">
+      <c r="S143" s="19" t="s">
         <v>952</v>
       </c>
-      <c r="T143" s="15" t="s">
+      <c r="T143" s="19" t="s">
         <v>952</v>
       </c>
       <c r="V143" s="1" t="s">
@@ -14215,12 +14356,12 @@
       <c r="W143" s="1">
         <v>0</v>
       </c>
-      <c r="X143" s="4"/>
-      <c r="Y143" s="4"/>
+      <c r="X143" s="5"/>
+      <c r="Y143" s="5"/>
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A144" s="4"/>
-      <c r="B144" s="4"/>
+      <c r="A144" s="5"/>
+      <c r="B144" s="5"/>
       <c r="C144" s="1" t="s">
         <v>953</v>
       </c>
@@ -14233,13 +14374,13 @@
       <c r="F144" s="1" t="s">
         <v>955</v>
       </c>
-      <c r="G144" s="16" t="s">
+      <c r="G144" s="20" t="s">
         <v>956</v>
       </c>
-      <c r="H144" s="15" t="s">
+      <c r="H144" s="19" t="s">
         <v>956</v>
       </c>
-      <c r="I144" s="17" t="s">
+      <c r="I144" s="21" t="s">
         <v>957</v>
       </c>
       <c r="J144" s="1">
@@ -14264,21 +14405,21 @@
         <f t="shared" si="53"/>
         <v>4450</v>
       </c>
-      <c r="P144" s="4">
+      <c r="P144" s="5">
         <f t="shared" si="44"/>
         <v>82</v>
       </c>
-      <c r="Q144" s="4">
+      <c r="Q144" s="5">
         <f t="shared" si="45"/>
         <v>86</v>
       </c>
-      <c r="R144" s="4">
+      <c r="R144" s="5">
         <v>99.98</v>
       </c>
-      <c r="S144" s="15" t="s">
+      <c r="S144" s="19" t="s">
         <v>958</v>
       </c>
-      <c r="T144" s="15" t="s">
+      <c r="T144" s="19" t="s">
         <v>958</v>
       </c>
       <c r="V144" s="1" t="s">
@@ -14287,12 +14428,12 @@
       <c r="W144" s="1">
         <v>0</v>
       </c>
-      <c r="X144" s="4"/>
-      <c r="Y144" s="4"/>
+      <c r="X144" s="5"/>
+      <c r="Y144" s="5"/>
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A145" s="4"/>
-      <c r="B145" s="4"/>
+      <c r="A145" s="5"/>
+      <c r="B145" s="5"/>
       <c r="C145" s="1" t="s">
         <v>959</v>
       </c>
@@ -14305,13 +14446,13 @@
       <c r="F145" s="1" t="s">
         <v>961</v>
       </c>
-      <c r="G145" s="5" t="s">
+      <c r="G145" s="6" t="s">
         <v>962</v>
       </c>
       <c r="H145" s="1" t="s">
         <v>962</v>
       </c>
-      <c r="I145" s="10" t="s">
+      <c r="I145" s="11" t="s">
         <v>963</v>
       </c>
       <c r="J145" s="1">
@@ -14336,21 +14477,21 @@
         <f t="shared" si="53"/>
         <v>4700</v>
       </c>
-      <c r="P145" s="4">
+      <c r="P145" s="5">
         <f t="shared" si="44"/>
         <v>84</v>
       </c>
-      <c r="Q145" s="4">
+      <c r="Q145" s="5">
         <f t="shared" si="45"/>
         <v>90</v>
       </c>
-      <c r="R145" s="4">
+      <c r="R145" s="5">
         <v>99.99</v>
       </c>
-      <c r="S145" s="15" t="s">
+      <c r="S145" s="19" t="s">
         <v>964</v>
       </c>
-      <c r="T145" s="15" t="s">
+      <c r="T145" s="19" t="s">
         <v>964</v>
       </c>
       <c r="V145" s="1" t="s">
@@ -14359,16 +14500,16 @@
       <c r="W145" s="1">
         <v>0</v>
       </c>
-      <c r="X145" s="4"/>
-      <c r="Y145" s="4"/>
+      <c r="X145" s="5"/>
+      <c r="Y145" s="5"/>
     </row>
     <row r="146" s="3" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A146" s="12"/>
-      <c r="B146" s="12"/>
-      <c r="C146" s="21" t="s">
+      <c r="A146" s="13"/>
+      <c r="B146" s="13"/>
+      <c r="C146" s="25" t="s">
         <v>965</v>
       </c>
-      <c r="D146" s="21" t="s">
+      <c r="D146" s="25" t="s">
         <v>966</v>
       </c>
       <c r="E146" s="3">
@@ -14377,13 +14518,13 @@
       <c r="F146" s="3" t="s">
         <v>967</v>
       </c>
-      <c r="G146" s="13" t="s">
+      <c r="G146" s="14" t="s">
         <v>968</v>
       </c>
       <c r="H146" s="3" t="s">
         <v>969</v>
       </c>
-      <c r="I146" s="14" t="s">
+      <c r="I146" s="17" t="s">
         <v>970</v>
       </c>
       <c r="J146" s="3">
@@ -14408,20 +14549,20 @@
         <f t="shared" si="53"/>
         <v>4950</v>
       </c>
-      <c r="P146" s="12">
+      <c r="P146" s="13">
         <f t="shared" ref="P146:P160" si="54">P145+3</f>
         <v>87</v>
       </c>
-      <c r="Q146" s="12">
+      <c r="Q146" s="13">
         <v>150</v>
       </c>
-      <c r="R146" s="12">
+      <c r="R146" s="13">
         <v>99.99</v>
       </c>
-      <c r="S146" s="21" t="s">
+      <c r="S146" s="25" t="s">
         <v>972</v>
       </c>
-      <c r="T146" s="21" t="s">
+      <c r="T146" s="25" t="s">
         <v>972</v>
       </c>
       <c r="V146" s="3" t="s">
@@ -14432,12 +14573,12 @@
       </c>
     </row>
     <row r="147" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A147" s="4"/>
-      <c r="B147" s="4"/>
-      <c r="C147" s="15" t="s">
+      <c r="A147" s="5"/>
+      <c r="B147" s="5"/>
+      <c r="C147" s="19" t="s">
         <v>973</v>
       </c>
-      <c r="D147" s="15" t="s">
+      <c r="D147" s="19" t="s">
         <v>974</v>
       </c>
       <c r="E147" s="1">
@@ -14446,13 +14587,13 @@
       <c r="F147" s="1" t="s">
         <v>975</v>
       </c>
-      <c r="G147" s="5" t="s">
+      <c r="G147" s="6" t="s">
         <v>976</v>
       </c>
-      <c r="H147" s="5" t="s">
+      <c r="H147" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="I147" s="10" t="s">
+      <c r="I147" s="11" t="s">
         <v>978</v>
       </c>
       <c r="J147" s="1">
@@ -14478,21 +14619,21 @@
         <f t="shared" si="53"/>
         <v>5200</v>
       </c>
-      <c r="P147" s="4">
+      <c r="P147" s="5">
         <f t="shared" si="54"/>
         <v>90</v>
       </c>
-      <c r="Q147" s="4">
+      <c r="Q147" s="5">
         <f t="shared" si="45"/>
         <v>154</v>
       </c>
-      <c r="R147" s="4">
+      <c r="R147" s="5">
         <v>99.99</v>
       </c>
-      <c r="S147" s="15" t="s">
+      <c r="S147" s="19" t="s">
         <v>980</v>
       </c>
-      <c r="T147" s="15" t="s">
+      <c r="T147" s="19" t="s">
         <v>980</v>
       </c>
       <c r="V147" s="1" t="s">
@@ -14503,12 +14644,12 @@
       </c>
     </row>
     <row r="148" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A148" s="4"/>
-      <c r="B148" s="4"/>
-      <c r="C148" s="15" t="s">
+      <c r="A148" s="5"/>
+      <c r="B148" s="5"/>
+      <c r="C148" s="19" t="s">
         <v>981</v>
       </c>
-      <c r="D148" s="15" t="s">
+      <c r="D148" s="19" t="s">
         <v>982</v>
       </c>
       <c r="E148" s="1">
@@ -14517,13 +14658,13 @@
       <c r="F148" s="1" t="s">
         <v>983</v>
       </c>
-      <c r="G148" s="5" t="s">
+      <c r="G148" s="6" t="s">
         <v>984</v>
       </c>
-      <c r="H148" s="5" t="s">
+      <c r="H148" s="6" t="s">
         <v>985</v>
       </c>
-      <c r="I148" s="10" t="s">
+      <c r="I148" s="11" t="s">
         <v>986</v>
       </c>
       <c r="J148" s="1">
@@ -14549,21 +14690,21 @@
         <f t="shared" si="53"/>
         <v>5450</v>
       </c>
-      <c r="P148" s="4">
+      <c r="P148" s="5">
         <f t="shared" si="54"/>
         <v>93</v>
       </c>
-      <c r="Q148" s="4">
+      <c r="Q148" s="5">
         <f t="shared" si="45"/>
         <v>158</v>
       </c>
-      <c r="R148" s="4">
+      <c r="R148" s="5">
         <v>99.99</v>
       </c>
-      <c r="S148" s="15" t="s">
+      <c r="S148" s="19" t="s">
         <v>988</v>
       </c>
-      <c r="T148" s="15" t="s">
+      <c r="T148" s="19" t="s">
         <v>988</v>
       </c>
       <c r="V148" s="1" t="s">
@@ -14574,12 +14715,12 @@
       </c>
     </row>
     <row r="149" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A149" s="4"/>
-      <c r="B149" s="4"/>
-      <c r="C149" s="15" t="s">
+      <c r="A149" s="5"/>
+      <c r="B149" s="5"/>
+      <c r="C149" s="19" t="s">
         <v>989</v>
       </c>
-      <c r="D149" s="15" t="s">
+      <c r="D149" s="19" t="s">
         <v>990</v>
       </c>
       <c r="E149" s="1">
@@ -14588,13 +14729,13 @@
       <c r="F149" s="1" t="s">
         <v>991</v>
       </c>
-      <c r="G149" s="5" t="s">
+      <c r="G149" s="6" t="s">
         <v>992</v>
       </c>
-      <c r="H149" s="5" t="s">
+      <c r="H149" s="6" t="s">
         <v>993</v>
       </c>
-      <c r="I149" s="10" t="s">
+      <c r="I149" s="11" t="s">
         <v>994</v>
       </c>
       <c r="J149" s="1">
@@ -14620,21 +14761,21 @@
         <f t="shared" si="53"/>
         <v>5700</v>
       </c>
-      <c r="P149" s="4">
+      <c r="P149" s="5">
         <f t="shared" si="54"/>
         <v>96</v>
       </c>
-      <c r="Q149" s="4">
+      <c r="Q149" s="5">
         <f t="shared" si="45"/>
         <v>162</v>
       </c>
-      <c r="R149" s="4">
+      <c r="R149" s="5">
         <v>99.99</v>
       </c>
-      <c r="S149" s="15" t="s">
+      <c r="S149" s="19" t="s">
         <v>996</v>
       </c>
-      <c r="T149" s="15" t="s">
+      <c r="T149" s="19" t="s">
         <v>996</v>
       </c>
       <c r="V149" s="1" t="s">
@@ -14645,12 +14786,12 @@
       </c>
     </row>
     <row r="150" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A150" s="4"/>
-      <c r="B150" s="4"/>
-      <c r="C150" s="15" t="s">
+      <c r="A150" s="5"/>
+      <c r="B150" s="5"/>
+      <c r="C150" s="19" t="s">
         <v>997</v>
       </c>
-      <c r="D150" s="15" t="s">
+      <c r="D150" s="19" t="s">
         <v>998</v>
       </c>
       <c r="E150" s="1">
@@ -14659,13 +14800,13 @@
       <c r="F150" s="1" t="s">
         <v>999</v>
       </c>
-      <c r="G150" s="5" t="s">
+      <c r="G150" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="H150" s="5" t="s">
+      <c r="H150" s="6" t="s">
         <v>1001</v>
       </c>
-      <c r="I150" s="10" t="s">
+      <c r="I150" s="11" t="s">
         <v>1002</v>
       </c>
       <c r="J150" s="1">
@@ -14691,21 +14832,21 @@
         <f t="shared" si="53"/>
         <v>5950</v>
       </c>
-      <c r="P150" s="4">
+      <c r="P150" s="5">
         <f t="shared" si="54"/>
         <v>99</v>
       </c>
-      <c r="Q150" s="4">
+      <c r="Q150" s="5">
         <f t="shared" si="45"/>
         <v>166</v>
       </c>
-      <c r="R150" s="4">
+      <c r="R150" s="5">
         <v>99.99</v>
       </c>
-      <c r="S150" s="15" t="s">
+      <c r="S150" s="19" t="s">
         <v>1004</v>
       </c>
-      <c r="T150" s="15" t="s">
+      <c r="T150" s="19" t="s">
         <v>1004</v>
       </c>
       <c r="V150" s="1" t="s">
@@ -14716,12 +14857,12 @@
       </c>
     </row>
     <row r="151" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A151" s="4"/>
-      <c r="B151" s="4"/>
-      <c r="C151" s="15" t="s">
+      <c r="A151" s="5"/>
+      <c r="B151" s="5"/>
+      <c r="C151" s="19" t="s">
         <v>1005</v>
       </c>
-      <c r="D151" s="15" t="s">
+      <c r="D151" s="19" t="s">
         <v>1006</v>
       </c>
       <c r="E151" s="1">
@@ -14733,7 +14874,7 @@
       <c r="G151" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="H151" s="5" t="s">
+      <c r="H151" s="6" t="s">
         <v>1009</v>
       </c>
       <c r="I151" s="1" t="s">
@@ -14761,21 +14902,21 @@
         <f t="shared" si="53"/>
         <v>6200</v>
       </c>
-      <c r="P151" s="4">
+      <c r="P151" s="5">
         <f t="shared" si="54"/>
         <v>102</v>
       </c>
-      <c r="Q151" s="4">
+      <c r="Q151" s="5">
         <f t="shared" si="45"/>
         <v>170</v>
       </c>
-      <c r="R151" s="4">
+      <c r="R151" s="5">
         <v>99.99</v>
       </c>
-      <c r="S151" s="15" t="s">
+      <c r="S151" s="19" t="s">
         <v>1013</v>
       </c>
-      <c r="T151" s="15" t="s">
+      <c r="T151" s="19" t="s">
         <v>1013</v>
       </c>
       <c r="V151" s="1" t="s">
@@ -14784,16 +14925,16 @@
       <c r="W151" s="1">
         <v>0</v>
       </c>
-      <c r="X151" s="4"/>
-      <c r="Y151" s="4"/>
+      <c r="X151" s="5"/>
+      <c r="Y151" s="5"/>
     </row>
     <row r="152" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A152" s="4"/>
-      <c r="B152" s="4"/>
-      <c r="C152" s="15" t="s">
+      <c r="A152" s="5"/>
+      <c r="B152" s="5"/>
+      <c r="C152" s="19" t="s">
         <v>1014</v>
       </c>
-      <c r="D152" s="15" t="s">
+      <c r="D152" s="19" t="s">
         <v>1015</v>
       </c>
       <c r="E152" s="1">
@@ -14805,7 +14946,7 @@
       <c r="G152" s="1" t="s">
         <v>1017</v>
       </c>
-      <c r="H152" s="5" t="s">
+      <c r="H152" s="6" t="s">
         <v>1018</v>
       </c>
       <c r="I152" s="1" t="s">
@@ -14833,21 +14974,21 @@
         <f t="shared" si="53"/>
         <v>6450</v>
       </c>
-      <c r="P152" s="4">
+      <c r="P152" s="5">
         <f t="shared" si="54"/>
         <v>105</v>
       </c>
-      <c r="Q152" s="4">
+      <c r="Q152" s="5">
         <f t="shared" si="45"/>
         <v>174</v>
       </c>
-      <c r="R152" s="4">
+      <c r="R152" s="5">
         <v>99.99</v>
       </c>
-      <c r="S152" s="15" t="s">
+      <c r="S152" s="19" t="s">
         <v>1022</v>
       </c>
-      <c r="T152" s="15" t="s">
+      <c r="T152" s="19" t="s">
         <v>1022</v>
       </c>
       <c r="V152" s="1" t="s">
@@ -14856,16 +14997,16 @@
       <c r="W152" s="1">
         <v>0</v>
       </c>
-      <c r="X152" s="4"/>
-      <c r="Y152" s="4"/>
+      <c r="X152" s="5"/>
+      <c r="Y152" s="5"/>
     </row>
     <row r="153" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A153" s="4"/>
-      <c r="B153" s="4"/>
-      <c r="C153" s="15" t="s">
+      <c r="A153" s="5"/>
+      <c r="B153" s="5"/>
+      <c r="C153" s="19" t="s">
         <v>1023</v>
       </c>
-      <c r="D153" s="15" t="s">
+      <c r="D153" s="19" t="s">
         <v>1024</v>
       </c>
       <c r="E153" s="1">
@@ -14877,7 +15018,7 @@
       <c r="G153" s="1" t="s">
         <v>1026</v>
       </c>
-      <c r="H153" s="5" t="s">
+      <c r="H153" s="6" t="s">
         <v>1027</v>
       </c>
       <c r="I153" s="1" t="s">
@@ -14905,21 +15046,21 @@
         <f t="shared" si="53"/>
         <v>6700</v>
       </c>
-      <c r="P153" s="4">
+      <c r="P153" s="5">
         <f t="shared" si="54"/>
         <v>108</v>
       </c>
-      <c r="Q153" s="4">
+      <c r="Q153" s="5">
         <f t="shared" si="45"/>
         <v>178</v>
       </c>
-      <c r="R153" s="4">
+      <c r="R153" s="5">
         <v>99.99</v>
       </c>
-      <c r="S153" s="15" t="s">
+      <c r="S153" s="19" t="s">
         <v>1031</v>
       </c>
-      <c r="T153" s="15" t="s">
+      <c r="T153" s="19" t="s">
         <v>1031</v>
       </c>
       <c r="V153" s="1" t="s">
@@ -14928,16 +15069,16 @@
       <c r="W153" s="1">
         <v>0</v>
       </c>
-      <c r="X153" s="4"/>
-      <c r="Y153" s="4"/>
+      <c r="X153" s="5"/>
+      <c r="Y153" s="5"/>
     </row>
     <row r="154" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A154" s="4"/>
-      <c r="B154" s="4"/>
-      <c r="C154" s="15" t="s">
+      <c r="A154" s="5"/>
+      <c r="B154" s="5"/>
+      <c r="C154" s="19" t="s">
         <v>1032</v>
       </c>
-      <c r="D154" s="15" t="s">
+      <c r="D154" s="19" t="s">
         <v>1033</v>
       </c>
       <c r="E154" s="1">
@@ -14949,7 +15090,7 @@
       <c r="G154" s="1" t="s">
         <v>1035</v>
       </c>
-      <c r="H154" s="5" t="s">
+      <c r="H154" s="6" t="s">
         <v>1036</v>
       </c>
       <c r="I154" s="1" t="s">
@@ -14977,21 +15118,21 @@
         <f t="shared" si="53"/>
         <v>6950</v>
       </c>
-      <c r="P154" s="4">
+      <c r="P154" s="5">
         <f t="shared" si="54"/>
         <v>111</v>
       </c>
-      <c r="Q154" s="4">
+      <c r="Q154" s="5">
         <f t="shared" si="45"/>
         <v>182</v>
       </c>
-      <c r="R154" s="4">
+      <c r="R154" s="5">
         <v>99.99</v>
       </c>
-      <c r="S154" s="15" t="s">
+      <c r="S154" s="19" t="s">
         <v>1040</v>
       </c>
-      <c r="T154" s="15" t="s">
+      <c r="T154" s="19" t="s">
         <v>1040</v>
       </c>
       <c r="V154" s="1" t="s">
@@ -15000,16 +15141,16 @@
       <c r="W154" s="1">
         <v>0</v>
       </c>
-      <c r="X154" s="4"/>
-      <c r="Y154" s="4"/>
+      <c r="X154" s="5"/>
+      <c r="Y154" s="5"/>
     </row>
     <row r="155" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A155" s="4"/>
-      <c r="B155" s="4"/>
-      <c r="C155" s="15" t="s">
+      <c r="A155" s="5"/>
+      <c r="B155" s="5"/>
+      <c r="C155" s="19" t="s">
         <v>1041</v>
       </c>
-      <c r="D155" s="15" t="s">
+      <c r="D155" s="19" t="s">
         <v>1042</v>
       </c>
       <c r="E155" s="1">
@@ -15021,7 +15162,7 @@
       <c r="G155" s="1" t="s">
         <v>1044</v>
       </c>
-      <c r="H155" s="5" t="s">
+      <c r="H155" s="6" t="s">
         <v>1045</v>
       </c>
       <c r="I155" s="1" t="s">
@@ -15049,21 +15190,21 @@
         <f t="shared" si="53"/>
         <v>7200</v>
       </c>
-      <c r="P155" s="4">
+      <c r="P155" s="5">
         <f t="shared" si="54"/>
         <v>114</v>
       </c>
-      <c r="Q155" s="4">
+      <c r="Q155" s="5">
         <f t="shared" si="45"/>
         <v>186</v>
       </c>
-      <c r="R155" s="4">
+      <c r="R155" s="5">
         <v>99.99</v>
       </c>
-      <c r="S155" s="15" t="s">
+      <c r="S155" s="19" t="s">
         <v>1049</v>
       </c>
-      <c r="T155" s="15" t="s">
+      <c r="T155" s="19" t="s">
         <v>1049</v>
       </c>
       <c r="V155" s="1" t="s">
@@ -15072,16 +15213,16 @@
       <c r="W155" s="1">
         <v>0</v>
       </c>
-      <c r="X155" s="4"/>
-      <c r="Y155" s="4"/>
+      <c r="X155" s="5"/>
+      <c r="Y155" s="5"/>
     </row>
     <row r="156" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A156" s="4"/>
-      <c r="B156" s="4"/>
-      <c r="C156" s="15" t="s">
+      <c r="A156" s="5"/>
+      <c r="B156" s="5"/>
+      <c r="C156" s="19" t="s">
         <v>1050</v>
       </c>
-      <c r="D156" s="15" t="s">
+      <c r="D156" s="19" t="s">
         <v>1051</v>
       </c>
       <c r="E156" s="1">
@@ -15093,7 +15234,7 @@
       <c r="G156" s="1" t="s">
         <v>1053</v>
       </c>
-      <c r="H156" s="5" t="s">
+      <c r="H156" s="6" t="s">
         <v>1054</v>
       </c>
       <c r="I156" s="1" t="s">
@@ -15121,21 +15262,21 @@
         <f t="shared" si="53"/>
         <v>7450</v>
       </c>
-      <c r="P156" s="4">
+      <c r="P156" s="5">
         <f t="shared" si="54"/>
         <v>117</v>
       </c>
-      <c r="Q156" s="4">
+      <c r="Q156" s="5">
         <f t="shared" si="45"/>
         <v>190</v>
       </c>
-      <c r="R156" s="4">
+      <c r="R156" s="5">
         <v>99.99</v>
       </c>
-      <c r="S156" s="15" t="s">
+      <c r="S156" s="19" t="s">
         <v>1058</v>
       </c>
-      <c r="T156" s="15" t="s">
+      <c r="T156" s="19" t="s">
         <v>1058</v>
       </c>
       <c r="V156" s="1" t="s">
@@ -15144,16 +15285,16 @@
       <c r="W156" s="1">
         <v>0</v>
       </c>
-      <c r="X156" s="4"/>
-      <c r="Y156" s="4"/>
+      <c r="X156" s="5"/>
+      <c r="Y156" s="5"/>
     </row>
     <row r="157" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A157" s="4"/>
-      <c r="B157" s="4"/>
-      <c r="C157" s="15" t="s">
+      <c r="A157" s="5"/>
+      <c r="B157" s="5"/>
+      <c r="C157" s="19" t="s">
         <v>1059</v>
       </c>
-      <c r="D157" s="15" t="s">
+      <c r="D157" s="19" t="s">
         <v>1060</v>
       </c>
       <c r="E157" s="1">
@@ -15165,7 +15306,7 @@
       <c r="G157" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="H157" s="5" t="s">
+      <c r="H157" s="6" t="s">
         <v>1063</v>
       </c>
       <c r="I157" s="1" t="s">
@@ -15193,21 +15334,21 @@
         <f t="shared" si="53"/>
         <v>7700</v>
       </c>
-      <c r="P157" s="4">
+      <c r="P157" s="5">
         <f t="shared" si="54"/>
         <v>120</v>
       </c>
-      <c r="Q157" s="4">
+      <c r="Q157" s="5">
         <f t="shared" si="45"/>
         <v>194</v>
       </c>
-      <c r="R157" s="4">
+      <c r="R157" s="5">
         <v>99.99</v>
       </c>
-      <c r="S157" s="15" t="s">
+      <c r="S157" s="19" t="s">
         <v>1067</v>
       </c>
-      <c r="T157" s="15" t="s">
+      <c r="T157" s="19" t="s">
         <v>1067</v>
       </c>
       <c r="V157" s="1" t="s">
@@ -15216,16 +15357,16 @@
       <c r="W157" s="1">
         <v>0</v>
       </c>
-      <c r="X157" s="4"/>
-      <c r="Y157" s="4"/>
+      <c r="X157" s="5"/>
+      <c r="Y157" s="5"/>
     </row>
     <row r="158" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A158" s="4"/>
-      <c r="B158" s="4"/>
-      <c r="C158" s="15" t="s">
+      <c r="A158" s="5"/>
+      <c r="B158" s="5"/>
+      <c r="C158" s="19" t="s">
         <v>1068</v>
       </c>
-      <c r="D158" s="15" t="s">
+      <c r="D158" s="19" t="s">
         <v>1069</v>
       </c>
       <c r="E158" s="1">
@@ -15237,7 +15378,7 @@
       <c r="G158" s="1" t="s">
         <v>1071</v>
       </c>
-      <c r="H158" s="5" t="s">
+      <c r="H158" s="6" t="s">
         <v>1072</v>
       </c>
       <c r="I158" s="1" t="s">
@@ -15265,21 +15406,21 @@
         <f t="shared" si="53"/>
         <v>7950</v>
       </c>
-      <c r="P158" s="4">
+      <c r="P158" s="5">
         <f t="shared" si="54"/>
         <v>123</v>
       </c>
-      <c r="Q158" s="4">
+      <c r="Q158" s="5">
         <f t="shared" si="45"/>
         <v>198</v>
       </c>
-      <c r="R158" s="4">
+      <c r="R158" s="5">
         <v>99.99</v>
       </c>
-      <c r="S158" s="15" t="s">
+      <c r="S158" s="19" t="s">
         <v>1076</v>
       </c>
-      <c r="T158" s="15" t="s">
+      <c r="T158" s="19" t="s">
         <v>1076</v>
       </c>
       <c r="V158" s="1" t="s">
@@ -15288,16 +15429,16 @@
       <c r="W158" s="1">
         <v>0</v>
       </c>
-      <c r="X158" s="4"/>
-      <c r="Y158" s="4"/>
+      <c r="X158" s="5"/>
+      <c r="Y158" s="5"/>
     </row>
     <row r="159" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A159" s="4"/>
-      <c r="B159" s="4"/>
-      <c r="C159" s="15" t="s">
+      <c r="A159" s="5"/>
+      <c r="B159" s="5"/>
+      <c r="C159" s="19" t="s">
         <v>1077</v>
       </c>
-      <c r="D159" s="15" t="s">
+      <c r="D159" s="19" t="s">
         <v>1078</v>
       </c>
       <c r="E159" s="1">
@@ -15309,7 +15450,7 @@
       <c r="G159" s="1" t="s">
         <v>1080</v>
       </c>
-      <c r="H159" s="5" t="s">
+      <c r="H159" s="6" t="s">
         <v>1081</v>
       </c>
       <c r="I159" s="1" t="s">
@@ -15337,21 +15478,21 @@
         <f t="shared" si="53"/>
         <v>8200</v>
       </c>
-      <c r="P159" s="4">
+      <c r="P159" s="5">
         <f t="shared" si="54"/>
         <v>126</v>
       </c>
-      <c r="Q159" s="4">
+      <c r="Q159" s="5">
         <f t="shared" si="45"/>
         <v>202</v>
       </c>
-      <c r="R159" s="4">
+      <c r="R159" s="5">
         <v>99.99</v>
       </c>
-      <c r="S159" s="15" t="s">
+      <c r="S159" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="T159" s="15" t="s">
+      <c r="T159" s="19" t="s">
         <v>1085</v>
       </c>
       <c r="V159" s="1" t="s">
@@ -15360,16 +15501,16 @@
       <c r="W159" s="1">
         <v>0</v>
       </c>
-      <c r="X159" s="4"/>
-      <c r="Y159" s="4"/>
+      <c r="X159" s="5"/>
+      <c r="Y159" s="5"/>
     </row>
     <row r="160" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A160" s="4"/>
-      <c r="B160" s="4"/>
-      <c r="C160" s="15" t="s">
+      <c r="A160" s="5"/>
+      <c r="B160" s="5"/>
+      <c r="C160" s="19" t="s">
         <v>1086</v>
       </c>
-      <c r="D160" s="15" t="s">
+      <c r="D160" s="19" t="s">
         <v>1087</v>
       </c>
       <c r="E160" s="1">
@@ -15381,7 +15522,7 @@
       <c r="G160" s="1" t="s">
         <v>1089</v>
       </c>
-      <c r="H160" s="5" t="s">
+      <c r="H160" s="6" t="s">
         <v>1090</v>
       </c>
       <c r="I160" s="1" t="s">
@@ -15409,21 +15550,21 @@
         <f t="shared" si="53"/>
         <v>8450</v>
       </c>
-      <c r="P160" s="4">
+      <c r="P160" s="5">
         <f t="shared" si="54"/>
         <v>129</v>
       </c>
-      <c r="Q160" s="4">
+      <c r="Q160" s="5">
         <f t="shared" si="45"/>
         <v>206</v>
       </c>
-      <c r="R160" s="4">
+      <c r="R160" s="5">
         <v>99.99</v>
       </c>
-      <c r="S160" s="15" t="s">
+      <c r="S160" s="19" t="s">
         <v>1094</v>
       </c>
-      <c r="T160" s="15" t="s">
+      <c r="T160" s="19" t="s">
         <v>1094</v>
       </c>
       <c r="V160" s="1" t="s">
@@ -15432,16 +15573,16 @@
       <c r="W160" s="1">
         <v>0</v>
       </c>
-      <c r="X160" s="4"/>
-      <c r="Y160" s="4"/>
+      <c r="X160" s="5"/>
+      <c r="Y160" s="5"/>
     </row>
     <row r="161" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A161" s="4"/>
-      <c r="B161" s="4"/>
-      <c r="C161" s="15" t="s">
+      <c r="A161" s="5"/>
+      <c r="B161" s="5"/>
+      <c r="C161" s="19" t="s">
         <v>1095</v>
       </c>
-      <c r="D161" s="15" t="s">
+      <c r="D161" s="19" t="s">
         <v>1096</v>
       </c>
       <c r="E161" s="1">
@@ -15453,7 +15594,7 @@
       <c r="G161" s="1" t="s">
         <v>1098</v>
       </c>
-      <c r="H161" s="5" t="s">
+      <c r="H161" s="6" t="s">
         <v>1099</v>
       </c>
       <c r="I161" s="1" t="s">
@@ -15481,21 +15622,21 @@
         <f t="shared" si="53"/>
         <v>8700</v>
       </c>
-      <c r="P161" s="4">
+      <c r="P161" s="5">
         <f>P160+4</f>
         <v>133</v>
       </c>
-      <c r="Q161" s="4">
+      <c r="Q161" s="5">
         <f>Q160+5</f>
         <v>211</v>
       </c>
-      <c r="R161" s="4">
+      <c r="R161" s="5">
         <v>99.99</v>
       </c>
-      <c r="S161" s="15" t="s">
+      <c r="S161" s="19" t="s">
         <v>1103</v>
       </c>
-      <c r="T161" s="15" t="s">
+      <c r="T161" s="19" t="s">
         <v>1103</v>
       </c>
       <c r="V161" s="1" t="s">
@@ -15504,16 +15645,16 @@
       <c r="W161" s="1">
         <v>0</v>
       </c>
-      <c r="X161" s="4"/>
-      <c r="Y161" s="4"/>
+      <c r="X161" s="5"/>
+      <c r="Y161" s="5"/>
     </row>
     <row r="162" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A162" s="4"/>
-      <c r="B162" s="4"/>
-      <c r="C162" s="15" t="s">
+      <c r="A162" s="5"/>
+      <c r="B162" s="5"/>
+      <c r="C162" s="19" t="s">
         <v>1104</v>
       </c>
-      <c r="D162" s="15" t="s">
+      <c r="D162" s="19" t="s">
         <v>1105</v>
       </c>
       <c r="E162" s="1">
@@ -15525,7 +15666,7 @@
       <c r="G162" s="1" t="s">
         <v>1107</v>
       </c>
-      <c r="H162" s="5" t="s">
+      <c r="H162" s="6" t="s">
         <v>1108</v>
       </c>
       <c r="I162" s="1" t="s">
@@ -15553,21 +15694,21 @@
         <f t="shared" si="53"/>
         <v>8950</v>
       </c>
-      <c r="P162" s="4">
+      <c r="P162" s="5">
         <f>P161+4</f>
         <v>137</v>
       </c>
-      <c r="Q162" s="4">
+      <c r="Q162" s="5">
         <f>Q161+5</f>
         <v>216</v>
       </c>
-      <c r="R162" s="4">
+      <c r="R162" s="5">
         <v>99.99</v>
       </c>
-      <c r="S162" s="15" t="s">
+      <c r="S162" s="19" t="s">
         <v>1112</v>
       </c>
-      <c r="T162" s="15" t="s">
+      <c r="T162" s="19" t="s">
         <v>1112</v>
       </c>
       <c r="V162" s="1" t="s">
@@ -15576,16 +15717,16 @@
       <c r="W162" s="1">
         <v>0</v>
       </c>
-      <c r="X162" s="4"/>
-      <c r="Y162" s="4"/>
+      <c r="X162" s="5"/>
+      <c r="Y162" s="5"/>
     </row>
     <row r="163" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A163" s="4"/>
-      <c r="B163" s="4"/>
-      <c r="C163" s="15" t="s">
+      <c r="A163" s="5"/>
+      <c r="B163" s="5"/>
+      <c r="C163" s="19" t="s">
         <v>1113</v>
       </c>
-      <c r="D163" s="15" t="s">
+      <c r="D163" s="19" t="s">
         <v>1114</v>
       </c>
       <c r="E163" s="1">
@@ -15600,7 +15741,7 @@
       <c r="H163" s="1" t="s">
         <v>1117</v>
       </c>
-      <c r="I163" s="1" t="s">
+      <c r="I163" s="26" t="s">
         <v>1118</v>
       </c>
       <c r="J163" s="1" t="s">
@@ -15625,21 +15766,21 @@
         <f t="shared" si="53"/>
         <v>9200</v>
       </c>
-      <c r="P163" s="4">
+      <c r="P163" s="5">
         <f>P162+4</f>
         <v>141</v>
       </c>
-      <c r="Q163" s="4">
+      <c r="Q163" s="5">
         <f>Q162+5</f>
         <v>221</v>
       </c>
-      <c r="R163" s="4">
+      <c r="R163" s="5">
         <v>99.99</v>
       </c>
-      <c r="S163" s="15" t="s">
+      <c r="S163" s="19" t="s">
         <v>1121</v>
       </c>
-      <c r="T163" s="15" t="s">
+      <c r="T163" s="19" t="s">
         <v>1121</v>
       </c>
       <c r="V163" s="1" t="s">
@@ -15648,88 +15789,88 @@
       <c r="W163" s="1">
         <v>0</v>
       </c>
-      <c r="X163" s="4"/>
-      <c r="Y163" s="4"/>
-    </row>
-    <row r="164" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A164" s="4"/>
-      <c r="B164" s="4"/>
-      <c r="C164" s="15" t="s">
+      <c r="X163" s="5"/>
+      <c r="Y163" s="5"/>
+    </row>
+    <row r="164" s="4" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A164" s="15"/>
+      <c r="B164" s="15"/>
+      <c r="C164" s="27" t="s">
         <v>1122</v>
       </c>
-      <c r="D164" s="15" t="s">
+      <c r="D164" s="27" t="s">
         <v>1123</v>
       </c>
-      <c r="E164" s="1">
+      <c r="E164" s="4">
         <v>5</v>
       </c>
-      <c r="F164" s="1" t="s">
+      <c r="F164" s="4" t="s">
         <v>1124</v>
       </c>
-      <c r="G164" s="1" t="s">
+      <c r="G164" s="4" t="s">
         <v>1125</v>
       </c>
-      <c r="H164" s="1" t="s">
+      <c r="H164" s="4" t="s">
         <v>1126</v>
       </c>
-      <c r="I164" s="1" t="s">
+      <c r="I164" s="28" t="s">
         <v>1127</v>
       </c>
-      <c r="J164" s="1" t="s">
+      <c r="J164" s="4" t="s">
         <v>1128</v>
       </c>
-      <c r="K164" s="1" t="s">
+      <c r="K164" s="4" t="s">
         <v>1129</v>
       </c>
-      <c r="L164" s="1">
+      <c r="L164" s="4">
         <f t="shared" si="50"/>
         <v>23500</v>
       </c>
-      <c r="M164" s="1">
+      <c r="M164" s="4">
         <f t="shared" si="51"/>
         <v>25100</v>
       </c>
-      <c r="N164" s="1">
+      <c r="N164" s="4">
         <f t="shared" si="52"/>
         <v>9450</v>
       </c>
-      <c r="O164" s="1">
+      <c r="O164" s="4">
         <f t="shared" si="53"/>
         <v>9450</v>
       </c>
-      <c r="P164" s="4">
+      <c r="P164" s="15">
         <f>P163+4</f>
         <v>145</v>
       </c>
-      <c r="Q164" s="4">
+      <c r="Q164" s="15">
         <f>Q163+5</f>
         <v>226</v>
       </c>
-      <c r="R164" s="4">
+      <c r="R164" s="15">
         <v>99.99</v>
       </c>
-      <c r="S164" s="15" t="s">
+      <c r="S164" s="27" t="s">
         <v>1130</v>
       </c>
-      <c r="T164" s="15" t="s">
+      <c r="T164" s="27" t="s">
         <v>1130</v>
       </c>
-      <c r="V164" s="1" t="s">
+      <c r="V164" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="W164" s="1">
-        <v>0</v>
-      </c>
-      <c r="X164" s="4"/>
-      <c r="Y164" s="4"/>
+      <c r="W164" s="4">
+        <v>0</v>
+      </c>
+      <c r="X164" s="15"/>
+      <c r="Y164" s="15"/>
     </row>
     <row r="165" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A165" s="4"/>
-      <c r="B165" s="4"/>
-      <c r="C165" s="15" t="s">
+      <c r="A165" s="5"/>
+      <c r="B165" s="5"/>
+      <c r="C165" s="19" t="s">
         <v>1131</v>
       </c>
-      <c r="D165" s="15" t="s">
+      <c r="D165" s="19" t="s">
         <v>1132</v>
       </c>
       <c r="E165" s="1">
@@ -15738,19 +15879,19 @@
       <c r="F165" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="G165" s="1" t="s">
+      <c r="G165" s="26" t="s">
         <v>1134</v>
       </c>
-      <c r="H165" s="1" t="s">
+      <c r="H165" s="26" t="s">
         <v>1135</v>
       </c>
-      <c r="I165" s="1" t="s">
+      <c r="I165" s="26" t="s">
         <v>1136</v>
       </c>
-      <c r="J165" s="1" t="s">
+      <c r="J165" s="26" t="s">
         <v>1137</v>
       </c>
-      <c r="K165" s="1" t="s">
+      <c r="K165" s="26" t="s">
         <v>1138</v>
       </c>
       <c r="L165" s="1">
@@ -15769,21 +15910,21 @@
         <f t="shared" si="53"/>
         <v>9700</v>
       </c>
-      <c r="P165" s="4">
+      <c r="P165" s="5">
         <f>P164+4</f>
         <v>149</v>
       </c>
-      <c r="Q165" s="4">
+      <c r="Q165" s="5">
         <f>Q164+5</f>
         <v>231</v>
       </c>
-      <c r="R165" s="4">
+      <c r="R165" s="5">
         <v>99.99</v>
       </c>
-      <c r="S165" s="15" t="s">
+      <c r="S165" s="19" t="s">
         <v>1139</v>
       </c>
-      <c r="T165" s="15" t="s">
+      <c r="T165" s="19" t="s">
         <v>1139</v>
       </c>
       <c r="V165" s="1" t="s">
@@ -15792,42 +15933,36 @@
       <c r="W165" s="1">
         <v>0</v>
       </c>
-      <c r="X165" s="4"/>
-      <c r="Y165" s="4"/>
-    </row>
-    <row r="166" customHeight="1" spans="1:23">
-      <c r="A166" s="4" t="s">
+      <c r="X165" s="5"/>
+      <c r="Y165" s="5"/>
+    </row>
+    <row r="166" customHeight="1" spans="3:23">
+      <c r="C166" s="19" t="s">
         <v>1140</v>
       </c>
-      <c r="B166" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C166" s="15" t="s">
+      <c r="D166" s="19" t="s">
         <v>1141</v>
-      </c>
-      <c r="D166" s="15" t="s">
-        <v>1142</v>
       </c>
       <c r="E166" s="1">
         <v>5</v>
       </c>
       <c r="F166" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G166" s="26" t="s">
         <v>1143</v>
       </c>
-      <c r="G166" s="1">
-        <v>0</v>
-      </c>
-      <c r="H166" s="1">
-        <v>0</v>
-      </c>
-      <c r="I166" s="1">
-        <v>0</v>
-      </c>
-      <c r="J166" s="1">
-        <v>0</v>
-      </c>
-      <c r="K166" s="1">
-        <v>0</v>
+      <c r="H166" s="26" t="s">
+        <v>1144</v>
+      </c>
+      <c r="I166" s="26" t="s">
+        <v>1145</v>
+      </c>
+      <c r="J166" s="26" t="s">
+        <v>1146</v>
+      </c>
+      <c r="K166" s="26" t="s">
+        <v>1147</v>
       </c>
       <c r="L166" s="1">
         <f t="shared" si="50"/>
@@ -15838,29 +15973,29 @@
         <v>26300</v>
       </c>
       <c r="N166" s="1">
-        <f t="shared" si="52"/>
-        <v>9950</v>
+        <f t="shared" ref="N166:N170" si="56">N165+300</f>
+        <v>10000</v>
       </c>
       <c r="O166" s="1">
-        <f t="shared" si="53"/>
-        <v>9950</v>
-      </c>
-      <c r="P166" s="4">
-        <f t="shared" ref="P166:P180" si="56">P165+5</f>
+        <f t="shared" ref="O166:O170" si="57">O165+300</f>
+        <v>10000</v>
+      </c>
+      <c r="P166" s="5">
+        <f t="shared" ref="P166:P180" si="58">P165+5</f>
         <v>154</v>
       </c>
-      <c r="Q166" s="4">
-        <f t="shared" ref="Q166:Q180" si="57">Q165+6</f>
+      <c r="Q166" s="5">
+        <f t="shared" ref="Q166:Q180" si="59">Q165+6</f>
         <v>237</v>
       </c>
-      <c r="R166" s="4">
+      <c r="R166" s="5">
         <v>99.99</v>
       </c>
-      <c r="S166" s="15" t="s">
-        <v>882</v>
-      </c>
-      <c r="T166" s="15" t="s">
-        <v>882</v>
+      <c r="S166" s="19" t="s">
+        <v>1148</v>
+      </c>
+      <c r="T166" s="19" t="s">
+        <v>1148</v>
       </c>
       <c r="V166" s="1" t="s">
         <v>156</v>
@@ -15869,39 +16004,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" customHeight="1" spans="1:23">
-      <c r="A167" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B167" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C167" s="15" t="s">
-        <v>1144</v>
-      </c>
-      <c r="D167" s="15" t="s">
-        <v>1145</v>
+    <row r="167" customHeight="1" spans="3:23">
+      <c r="C167" s="19" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D167" s="19" t="s">
+        <v>1150</v>
       </c>
       <c r="E167" s="1">
         <v>5</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="G167" s="1">
-        <v>0</v>
-      </c>
-      <c r="H167" s="1">
-        <v>0</v>
-      </c>
-      <c r="I167" s="1">
-        <v>0</v>
-      </c>
-      <c r="J167" s="1">
-        <v>0</v>
-      </c>
-      <c r="K167" s="1">
-        <v>0</v>
+        <v>1151</v>
+      </c>
+      <c r="G167" s="26" t="s">
+        <v>1152</v>
+      </c>
+      <c r="H167" s="26" t="s">
+        <v>1153</v>
+      </c>
+      <c r="I167" s="26" t="s">
+        <v>1154</v>
+      </c>
+      <c r="J167" s="26" t="s">
+        <v>1155</v>
+      </c>
+      <c r="K167" s="26" t="s">
+        <v>1156</v>
       </c>
       <c r="L167" s="1">
         <f t="shared" si="50"/>
@@ -15912,29 +16041,29 @@
         <v>26900</v>
       </c>
       <c r="N167" s="1">
-        <f t="shared" si="52"/>
-        <v>10200</v>
+        <f t="shared" si="56"/>
+        <v>10300</v>
       </c>
       <c r="O167" s="1">
-        <f t="shared" si="53"/>
-        <v>10200</v>
-      </c>
-      <c r="P167" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
+        <v>10300</v>
+      </c>
+      <c r="P167" s="5">
+        <f t="shared" si="58"/>
         <v>159</v>
       </c>
-      <c r="Q167" s="4">
-        <f t="shared" si="57"/>
+      <c r="Q167" s="5">
+        <f t="shared" si="59"/>
         <v>243</v>
       </c>
-      <c r="R167" s="4">
+      <c r="R167" s="5">
         <v>99.99</v>
       </c>
-      <c r="S167" s="15" t="s">
-        <v>888</v>
-      </c>
-      <c r="T167" s="15" t="s">
-        <v>888</v>
+      <c r="S167" s="19" t="s">
+        <v>1157</v>
+      </c>
+      <c r="T167" s="19" t="s">
+        <v>1157</v>
       </c>
       <c r="V167" s="1" t="s">
         <v>156</v>
@@ -15943,39 +16072,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" customHeight="1" spans="1:23">
-      <c r="A168" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C168" s="15" t="s">
-        <v>1147</v>
-      </c>
-      <c r="D168" s="15" t="s">
-        <v>1148</v>
+    <row r="168" customHeight="1" spans="3:23">
+      <c r="C168" s="19" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D168" s="19" t="s">
+        <v>1159</v>
       </c>
       <c r="E168" s="1">
         <v>5</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="G168" s="1">
-        <v>0</v>
-      </c>
-      <c r="H168" s="1">
-        <v>0</v>
-      </c>
-      <c r="I168" s="1">
-        <v>0</v>
-      </c>
-      <c r="J168" s="1">
-        <v>0</v>
-      </c>
-      <c r="K168" s="1">
-        <v>0</v>
+        <v>1160</v>
+      </c>
+      <c r="G168" s="26" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H168" s="26" t="s">
+        <v>1162</v>
+      </c>
+      <c r="I168" s="26" t="s">
+        <v>1163</v>
+      </c>
+      <c r="J168" s="26" t="s">
+        <v>1164</v>
+      </c>
+      <c r="K168" s="26" t="s">
+        <v>1165</v>
       </c>
       <c r="L168" s="1">
         <f t="shared" si="50"/>
@@ -15986,29 +16109,29 @@
         <v>27500</v>
       </c>
       <c r="N168" s="1">
-        <f t="shared" si="52"/>
-        <v>10450</v>
+        <f t="shared" si="56"/>
+        <v>10600</v>
       </c>
       <c r="O168" s="1">
-        <f t="shared" si="53"/>
-        <v>10450</v>
-      </c>
-      <c r="P168" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
+        <v>10600</v>
+      </c>
+      <c r="P168" s="5">
+        <f t="shared" si="58"/>
         <v>164</v>
       </c>
-      <c r="Q168" s="4">
-        <f t="shared" si="57"/>
+      <c r="Q168" s="5">
+        <f t="shared" si="59"/>
         <v>249</v>
       </c>
-      <c r="R168" s="4">
+      <c r="R168" s="5">
         <v>99.99</v>
       </c>
-      <c r="S168" s="15" t="s">
-        <v>894</v>
-      </c>
-      <c r="T168" s="15" t="s">
-        <v>894</v>
+      <c r="S168" s="19" t="s">
+        <v>1166</v>
+      </c>
+      <c r="T168" s="19" t="s">
+        <v>1166</v>
       </c>
       <c r="V168" s="1" t="s">
         <v>156</v>
@@ -16017,39 +16140,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" customHeight="1" spans="1:23">
-      <c r="A169" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B169" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C169" s="15" t="s">
-        <v>1150</v>
-      </c>
-      <c r="D169" s="15" t="s">
-        <v>1151</v>
+    <row r="169" customHeight="1" spans="3:23">
+      <c r="C169" s="19" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D169" s="19" t="s">
+        <v>1168</v>
       </c>
       <c r="E169" s="1">
         <v>5</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="G169" s="1">
-        <v>0</v>
-      </c>
-      <c r="H169" s="1">
-        <v>0</v>
-      </c>
-      <c r="I169" s="1">
-        <v>0</v>
-      </c>
-      <c r="J169" s="1">
-        <v>0</v>
-      </c>
-      <c r="K169" s="1">
-        <v>0</v>
+        <v>1169</v>
+      </c>
+      <c r="G169" s="26" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H169" s="26" t="s">
+        <v>1171</v>
+      </c>
+      <c r="I169" s="26" t="s">
+        <v>1172</v>
+      </c>
+      <c r="J169" s="26" t="s">
+        <v>1173</v>
+      </c>
+      <c r="K169" s="26" t="s">
+        <v>1174</v>
       </c>
       <c r="L169" s="1">
         <f t="shared" si="50"/>
@@ -16060,29 +16177,29 @@
         <v>28100</v>
       </c>
       <c r="N169" s="1">
-        <f t="shared" si="52"/>
-        <v>10700</v>
+        <f t="shared" si="56"/>
+        <v>10900</v>
       </c>
       <c r="O169" s="1">
-        <f t="shared" si="53"/>
-        <v>10700</v>
-      </c>
-      <c r="P169" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
+        <v>10900</v>
+      </c>
+      <c r="P169" s="5">
+        <f t="shared" si="58"/>
         <v>169</v>
       </c>
-      <c r="Q169" s="4">
-        <f t="shared" si="57"/>
+      <c r="Q169" s="5">
+        <f t="shared" si="59"/>
         <v>255</v>
       </c>
-      <c r="R169" s="4">
+      <c r="R169" s="5">
         <v>99.99</v>
       </c>
-      <c r="S169" s="15" t="s">
-        <v>900</v>
-      </c>
-      <c r="T169" s="15" t="s">
-        <v>900</v>
+      <c r="S169" s="19" t="s">
+        <v>1175</v>
+      </c>
+      <c r="T169" s="19" t="s">
+        <v>1175</v>
       </c>
       <c r="V169" s="1" t="s">
         <v>156</v>
@@ -16091,18 +16208,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" customHeight="1" spans="1:23">
-      <c r="A170" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B170" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C170" s="15" t="s">
-        <v>1153</v>
-      </c>
-      <c r="D170" s="15" t="s">
-        <v>1154</v>
+    <row r="170" customHeight="1" spans="3:23">
+      <c r="C170" s="19" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D170" s="19" t="s">
+        <v>1177</v>
       </c>
       <c r="E170" s="1">
         <v>5</v>
@@ -16110,20 +16221,20 @@
       <c r="F170" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="G170" s="1">
-        <v>0</v>
-      </c>
-      <c r="H170" s="1">
-        <v>0</v>
-      </c>
-      <c r="I170" s="1">
-        <v>0</v>
-      </c>
-      <c r="J170" s="1">
-        <v>0</v>
-      </c>
-      <c r="K170" s="1">
-        <v>0</v>
+      <c r="G170" s="26" t="s">
+        <v>1178</v>
+      </c>
+      <c r="H170" s="26" t="s">
+        <v>1179</v>
+      </c>
+      <c r="I170" s="26" t="s">
+        <v>1180</v>
+      </c>
+      <c r="J170" s="26" t="s">
+        <v>1181</v>
+      </c>
+      <c r="K170" s="26" t="s">
+        <v>1182</v>
       </c>
       <c r="L170" s="1">
         <f t="shared" si="50"/>
@@ -16134,29 +16245,29 @@
         <v>28700</v>
       </c>
       <c r="N170" s="1">
-        <f t="shared" si="52"/>
-        <v>10950</v>
+        <f t="shared" si="56"/>
+        <v>11200</v>
       </c>
       <c r="O170" s="1">
-        <f t="shared" si="53"/>
-        <v>10950</v>
-      </c>
-      <c r="P170" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
+        <v>11200</v>
+      </c>
+      <c r="P170" s="5">
+        <f t="shared" si="58"/>
         <v>174</v>
       </c>
-      <c r="Q170" s="4">
-        <f t="shared" si="57"/>
+      <c r="Q170" s="5">
+        <f t="shared" si="59"/>
         <v>261</v>
       </c>
-      <c r="R170" s="4">
+      <c r="R170" s="5">
         <v>99.99</v>
       </c>
-      <c r="S170" s="15" t="s">
-        <v>455</v>
-      </c>
-      <c r="T170" s="15" t="s">
-        <v>455</v>
+      <c r="S170" s="19" t="s">
+        <v>1183</v>
+      </c>
+      <c r="T170" s="19" t="s">
+        <v>1183</v>
       </c>
       <c r="V170" s="1" t="s">
         <v>156</v>
@@ -16166,23 +16277,23 @@
       </c>
     </row>
     <row r="171" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A171" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C171" s="15" t="s">
-        <v>1155</v>
-      </c>
-      <c r="D171" s="15" t="s">
-        <v>1156</v>
+      <c r="A171" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C171" s="19" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D171" s="19" t="s">
+        <v>1186</v>
       </c>
       <c r="E171" s="1">
         <v>5</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1157</v>
+        <v>1187</v>
       </c>
       <c r="G171" s="1">
         <v>0</v>
@@ -16208,29 +16319,29 @@
         <v>29300</v>
       </c>
       <c r="N171" s="1">
-        <f t="shared" si="52"/>
-        <v>11200</v>
+        <f t="shared" ref="N171:N175" si="60">N170+400</f>
+        <v>11600</v>
       </c>
       <c r="O171" s="1">
-        <f t="shared" si="53"/>
-        <v>11200</v>
-      </c>
-      <c r="P171" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" ref="O171:O175" si="61">O170+400</f>
+        <v>11600</v>
+      </c>
+      <c r="P171" s="5">
+        <f t="shared" si="58"/>
         <v>179</v>
       </c>
-      <c r="Q171" s="4">
-        <f t="shared" si="57"/>
+      <c r="Q171" s="5">
+        <f t="shared" si="59"/>
         <v>267</v>
       </c>
-      <c r="R171" s="4">
+      <c r="R171" s="5">
         <v>99.99</v>
       </c>
-      <c r="S171" s="15" t="s">
-        <v>910</v>
-      </c>
-      <c r="T171" s="15" t="s">
-        <v>910</v>
+      <c r="S171" s="19" t="s">
+        <v>1188</v>
+      </c>
+      <c r="T171" s="19" t="s">
+        <v>1188</v>
       </c>
       <c r="V171" s="1" t="s">
         <v>156</v>
@@ -16238,27 +16349,27 @@
       <c r="W171" s="1">
         <v>0</v>
       </c>
-      <c r="X171" s="4"/>
-      <c r="Y171" s="4"/>
+      <c r="X171" s="5"/>
+      <c r="Y171" s="5"/>
     </row>
     <row r="172" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A172" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B172" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C172" s="15" t="s">
-        <v>1158</v>
-      </c>
-      <c r="D172" s="15" t="s">
-        <v>1159</v>
+      <c r="A172" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C172" s="19" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D172" s="19" t="s">
+        <v>1190</v>
       </c>
       <c r="E172" s="1">
         <v>5</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1160</v>
+        <v>1191</v>
       </c>
       <c r="G172" s="1">
         <v>0</v>
@@ -16284,29 +16395,29 @@
         <v>29900</v>
       </c>
       <c r="N172" s="1">
-        <f t="shared" si="52"/>
-        <v>11450</v>
+        <f t="shared" si="60"/>
+        <v>12000</v>
       </c>
       <c r="O172" s="1">
-        <f t="shared" si="53"/>
-        <v>11450</v>
-      </c>
-      <c r="P172" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="61"/>
+        <v>12000</v>
+      </c>
+      <c r="P172" s="5">
+        <f t="shared" si="58"/>
         <v>184</v>
       </c>
-      <c r="Q172" s="4">
-        <f t="shared" si="57"/>
+      <c r="Q172" s="5">
+        <f t="shared" si="59"/>
         <v>273</v>
       </c>
-      <c r="R172" s="4">
+      <c r="R172" s="5">
         <v>99.99</v>
       </c>
-      <c r="S172" s="15" t="s">
-        <v>916</v>
-      </c>
-      <c r="T172" s="15" t="s">
-        <v>916</v>
+      <c r="S172" s="19" t="s">
+        <v>1192</v>
+      </c>
+      <c r="T172" s="19" t="s">
+        <v>1192</v>
       </c>
       <c r="V172" s="1" t="s">
         <v>156</v>
@@ -16314,27 +16425,27 @@
       <c r="W172" s="1">
         <v>0</v>
       </c>
-      <c r="X172" s="4"/>
-      <c r="Y172" s="4"/>
+      <c r="X172" s="5"/>
+      <c r="Y172" s="5"/>
     </row>
     <row r="173" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A173" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B173" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C173" s="15" t="s">
-        <v>1161</v>
-      </c>
-      <c r="D173" s="15" t="s">
-        <v>1162</v>
+      <c r="A173" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C173" s="19" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D173" s="19" t="s">
+        <v>1194</v>
       </c>
       <c r="E173" s="1">
         <v>5</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1163</v>
+        <v>1195</v>
       </c>
       <c r="G173" s="1">
         <v>0</v>
@@ -16360,29 +16471,29 @@
         <v>30500</v>
       </c>
       <c r="N173" s="1">
-        <f t="shared" si="52"/>
-        <v>11700</v>
+        <f t="shared" si="60"/>
+        <v>12400</v>
       </c>
       <c r="O173" s="1">
-        <f t="shared" si="53"/>
-        <v>11700</v>
-      </c>
-      <c r="P173" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="61"/>
+        <v>12400</v>
+      </c>
+      <c r="P173" s="5">
+        <f t="shared" si="58"/>
         <v>189</v>
       </c>
-      <c r="Q173" s="4">
-        <f t="shared" si="57"/>
+      <c r="Q173" s="5">
+        <f t="shared" si="59"/>
         <v>279</v>
       </c>
-      <c r="R173" s="4">
+      <c r="R173" s="5">
         <v>99.99</v>
       </c>
-      <c r="S173" s="15" t="s">
-        <v>922</v>
-      </c>
-      <c r="T173" s="15" t="s">
-        <v>922</v>
+      <c r="S173" s="19" t="s">
+        <v>1196</v>
+      </c>
+      <c r="T173" s="19" t="s">
+        <v>1196</v>
       </c>
       <c r="V173" s="1" t="s">
         <v>156</v>
@@ -16390,27 +16501,27 @@
       <c r="W173" s="1">
         <v>0</v>
       </c>
-      <c r="X173" s="4"/>
-      <c r="Y173" s="4"/>
+      <c r="X173" s="5"/>
+      <c r="Y173" s="5"/>
     </row>
     <row r="174" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A174" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B174" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C174" s="15" t="s">
-        <v>1164</v>
-      </c>
-      <c r="D174" s="15" t="s">
-        <v>1165</v>
+      <c r="A174" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C174" s="19" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D174" s="19" t="s">
+        <v>1198</v>
       </c>
       <c r="E174" s="1">
         <v>5</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1166</v>
+        <v>1199</v>
       </c>
       <c r="G174" s="1">
         <v>0</v>
@@ -16436,29 +16547,29 @@
         <v>31100</v>
       </c>
       <c r="N174" s="1">
-        <f t="shared" si="52"/>
-        <v>11950</v>
+        <f t="shared" si="60"/>
+        <v>12800</v>
       </c>
       <c r="O174" s="1">
-        <f t="shared" si="53"/>
-        <v>11950</v>
-      </c>
-      <c r="P174" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="61"/>
+        <v>12800</v>
+      </c>
+      <c r="P174" s="5">
+        <f t="shared" si="58"/>
         <v>194</v>
       </c>
-      <c r="Q174" s="4">
-        <f t="shared" si="57"/>
+      <c r="Q174" s="5">
+        <f t="shared" si="59"/>
         <v>285</v>
       </c>
-      <c r="R174" s="4">
+      <c r="R174" s="5">
         <v>99.99</v>
       </c>
-      <c r="S174" s="15" t="s">
-        <v>928</v>
-      </c>
-      <c r="T174" s="15" t="s">
-        <v>928</v>
+      <c r="S174" s="19" t="s">
+        <v>1200</v>
+      </c>
+      <c r="T174" s="19" t="s">
+        <v>1200</v>
       </c>
       <c r="V174" s="1" t="s">
         <v>156</v>
@@ -16466,27 +16577,27 @@
       <c r="W174" s="1">
         <v>0</v>
       </c>
-      <c r="X174" s="4"/>
-      <c r="Y174" s="4"/>
+      <c r="X174" s="5"/>
+      <c r="Y174" s="5"/>
     </row>
     <row r="175" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A175" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B175" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C175" s="15" t="s">
-        <v>1167</v>
-      </c>
-      <c r="D175" s="15" t="s">
-        <v>1168</v>
+      <c r="A175" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C175" s="19" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D175" s="19" t="s">
+        <v>1202</v>
       </c>
       <c r="E175" s="1">
         <v>5</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1169</v>
+        <v>1203</v>
       </c>
       <c r="G175" s="1">
         <v>0</v>
@@ -16512,29 +16623,29 @@
         <v>31700</v>
       </c>
       <c r="N175" s="1">
-        <f t="shared" si="52"/>
-        <v>12200</v>
+        <f t="shared" si="60"/>
+        <v>13200</v>
       </c>
       <c r="O175" s="1">
-        <f t="shared" si="53"/>
-        <v>12200</v>
-      </c>
-      <c r="P175" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="61"/>
+        <v>13200</v>
+      </c>
+      <c r="P175" s="5">
+        <f t="shared" si="58"/>
         <v>199</v>
       </c>
-      <c r="Q175" s="4">
-        <f t="shared" si="57"/>
+      <c r="Q175" s="5">
+        <f t="shared" si="59"/>
         <v>291</v>
       </c>
-      <c r="R175" s="4">
+      <c r="R175" s="5">
         <v>99.99</v>
       </c>
-      <c r="S175" s="15" t="s">
-        <v>934</v>
-      </c>
-      <c r="T175" s="15" t="s">
-        <v>934</v>
+      <c r="S175" s="19" t="s">
+        <v>1204</v>
+      </c>
+      <c r="T175" s="19" t="s">
+        <v>1204</v>
       </c>
       <c r="V175" s="1" t="s">
         <v>156</v>
@@ -16542,27 +16653,27 @@
       <c r="W175" s="1">
         <v>0</v>
       </c>
-      <c r="X175" s="4"/>
-      <c r="Y175" s="4"/>
+      <c r="X175" s="5"/>
+      <c r="Y175" s="5"/>
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A176" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B176" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C176" s="15" t="s">
-        <v>1170</v>
-      </c>
-      <c r="D176" s="15" t="s">
-        <v>1171</v>
+      <c r="A176" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C176" s="19" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D176" s="19" t="s">
+        <v>1206</v>
       </c>
       <c r="E176" s="1">
         <v>5</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1172</v>
+        <v>1207</v>
       </c>
       <c r="G176" s="1">
         <v>0</v>
@@ -16588,29 +16699,29 @@
         <v>32300</v>
       </c>
       <c r="N176" s="1">
-        <f t="shared" si="52"/>
-        <v>12450</v>
+        <f t="shared" ref="N176:N180" si="62">N175+500</f>
+        <v>13700</v>
       </c>
       <c r="O176" s="1">
-        <f t="shared" si="53"/>
-        <v>12450</v>
-      </c>
-      <c r="P176" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" ref="O176:O180" si="63">O175+500</f>
+        <v>13700</v>
+      </c>
+      <c r="P176" s="5">
+        <f t="shared" si="58"/>
         <v>204</v>
       </c>
-      <c r="Q176" s="4">
-        <f t="shared" si="57"/>
+      <c r="Q176" s="5">
+        <f t="shared" si="59"/>
         <v>297</v>
       </c>
-      <c r="R176" s="4">
+      <c r="R176" s="5">
         <v>99.99</v>
       </c>
-      <c r="S176" s="15" t="s">
-        <v>940</v>
-      </c>
-      <c r="T176" s="15" t="s">
-        <v>940</v>
+      <c r="S176" s="19" t="s">
+        <v>1208</v>
+      </c>
+      <c r="T176" s="19" t="s">
+        <v>1208</v>
       </c>
       <c r="V176" s="1" t="s">
         <v>156</v>
@@ -16618,27 +16729,27 @@
       <c r="W176" s="1">
         <v>0</v>
       </c>
-      <c r="X176" s="4"/>
-      <c r="Y176" s="4"/>
+      <c r="X176" s="5"/>
+      <c r="Y176" s="5"/>
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A177" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B177" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C177" s="15" t="s">
-        <v>1173</v>
-      </c>
-      <c r="D177" s="15" t="s">
-        <v>1174</v>
+      <c r="A177" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C177" s="19" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D177" s="19" t="s">
+        <v>1210</v>
       </c>
       <c r="E177" s="1">
         <v>5</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1175</v>
+        <v>1211</v>
       </c>
       <c r="G177" s="1">
         <v>0</v>
@@ -16664,29 +16775,29 @@
         <v>32900</v>
       </c>
       <c r="N177" s="1">
-        <f t="shared" si="52"/>
-        <v>12700</v>
+        <f t="shared" si="62"/>
+        <v>14200</v>
       </c>
       <c r="O177" s="1">
-        <f t="shared" si="53"/>
-        <v>12700</v>
-      </c>
-      <c r="P177" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="63"/>
+        <v>14200</v>
+      </c>
+      <c r="P177" s="5">
+        <f t="shared" si="58"/>
         <v>209</v>
       </c>
-      <c r="Q177" s="4">
-        <f t="shared" si="57"/>
+      <c r="Q177" s="5">
+        <f t="shared" si="59"/>
         <v>303</v>
       </c>
-      <c r="R177" s="4">
+      <c r="R177" s="5">
         <v>99.99</v>
       </c>
-      <c r="S177" s="15" t="s">
-        <v>946</v>
-      </c>
-      <c r="T177" s="15" t="s">
-        <v>946</v>
+      <c r="S177" s="19" t="s">
+        <v>1212</v>
+      </c>
+      <c r="T177" s="19" t="s">
+        <v>1212</v>
       </c>
       <c r="V177" s="1" t="s">
         <v>156</v>
@@ -16694,27 +16805,27 @@
       <c r="W177" s="1">
         <v>0</v>
       </c>
-      <c r="X177" s="4"/>
-      <c r="Y177" s="4"/>
+      <c r="X177" s="5"/>
+      <c r="Y177" s="5"/>
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A178" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B178" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C178" s="15" t="s">
-        <v>1176</v>
-      </c>
-      <c r="D178" s="15" t="s">
-        <v>1177</v>
+      <c r="A178" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C178" s="19" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D178" s="19" t="s">
+        <v>1214</v>
       </c>
       <c r="E178" s="1">
         <v>5</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1178</v>
+        <v>1215</v>
       </c>
       <c r="G178" s="1">
         <v>0</v>
@@ -16740,29 +16851,29 @@
         <v>33500</v>
       </c>
       <c r="N178" s="1">
-        <f t="shared" si="52"/>
-        <v>12950</v>
+        <f t="shared" si="62"/>
+        <v>14700</v>
       </c>
       <c r="O178" s="1">
-        <f t="shared" si="53"/>
-        <v>12950</v>
-      </c>
-      <c r="P178" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="63"/>
+        <v>14700</v>
+      </c>
+      <c r="P178" s="5">
+        <f t="shared" si="58"/>
         <v>214</v>
       </c>
-      <c r="Q178" s="4">
-        <f t="shared" si="57"/>
+      <c r="Q178" s="5">
+        <f t="shared" si="59"/>
         <v>309</v>
       </c>
-      <c r="R178" s="4">
+      <c r="R178" s="5">
         <v>99.99</v>
       </c>
-      <c r="S178" s="15" t="s">
-        <v>952</v>
-      </c>
-      <c r="T178" s="15" t="s">
-        <v>952</v>
+      <c r="S178" s="19" t="s">
+        <v>1216</v>
+      </c>
+      <c r="T178" s="19" t="s">
+        <v>1216</v>
       </c>
       <c r="V178" s="1" t="s">
         <v>156</v>
@@ -16770,27 +16881,27 @@
       <c r="W178" s="1">
         <v>0</v>
       </c>
-      <c r="X178" s="4"/>
-      <c r="Y178" s="4"/>
+      <c r="X178" s="5"/>
+      <c r="Y178" s="5"/>
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A179" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B179" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C179" s="15" t="s">
-        <v>1179</v>
-      </c>
-      <c r="D179" s="15" t="s">
-        <v>1180</v>
+      <c r="A179" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C179" s="19" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D179" s="19" t="s">
+        <v>1218</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1181</v>
+        <v>1219</v>
       </c>
       <c r="G179" s="1">
         <v>0</v>
@@ -16816,29 +16927,29 @@
         <v>34100</v>
       </c>
       <c r="N179" s="1">
-        <f t="shared" si="52"/>
-        <v>13200</v>
+        <f t="shared" si="62"/>
+        <v>15200</v>
       </c>
       <c r="O179" s="1">
-        <f t="shared" si="53"/>
-        <v>13200</v>
-      </c>
-      <c r="P179" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="63"/>
+        <v>15200</v>
+      </c>
+      <c r="P179" s="5">
+        <f t="shared" si="58"/>
         <v>219</v>
       </c>
-      <c r="Q179" s="4">
-        <f t="shared" si="57"/>
+      <c r="Q179" s="5">
+        <f t="shared" si="59"/>
         <v>315</v>
       </c>
-      <c r="R179" s="4">
+      <c r="R179" s="5">
         <v>99.99</v>
       </c>
-      <c r="S179" s="15" t="s">
-        <v>958</v>
-      </c>
-      <c r="T179" s="15" t="s">
-        <v>958</v>
+      <c r="S179" s="19" t="s">
+        <v>1220</v>
+      </c>
+      <c r="T179" s="19" t="s">
+        <v>1220</v>
       </c>
       <c r="V179" s="1" t="s">
         <v>156</v>
@@ -16846,27 +16957,27 @@
       <c r="W179" s="1">
         <v>0</v>
       </c>
-      <c r="X179" s="4"/>
-      <c r="Y179" s="4"/>
+      <c r="X179" s="5"/>
+      <c r="Y179" s="5"/>
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A180" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B180" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C180" s="15" t="s">
-        <v>1182</v>
-      </c>
-      <c r="D180" s="15" t="s">
-        <v>1183</v>
+      <c r="A180" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C180" s="19" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D180" s="19" t="s">
+        <v>1222</v>
       </c>
       <c r="E180" s="1">
         <v>5</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1184</v>
+        <v>1223</v>
       </c>
       <c r="G180" s="1">
         <v>0</v>
@@ -16892,29 +17003,29 @@
         <v>34700</v>
       </c>
       <c r="N180" s="1">
-        <f t="shared" si="52"/>
-        <v>13450</v>
+        <f t="shared" si="62"/>
+        <v>15700</v>
       </c>
       <c r="O180" s="1">
-        <f t="shared" si="53"/>
-        <v>13450</v>
-      </c>
-      <c r="P180" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="63"/>
+        <v>15700</v>
+      </c>
+      <c r="P180" s="5">
+        <f t="shared" si="58"/>
         <v>224</v>
       </c>
-      <c r="Q180" s="4">
-        <f t="shared" si="57"/>
+      <c r="Q180" s="5">
+        <f t="shared" si="59"/>
         <v>321</v>
       </c>
-      <c r="R180" s="4">
+      <c r="R180" s="5">
         <v>99.99</v>
       </c>
-      <c r="S180" s="15" t="s">
-        <v>964</v>
-      </c>
-      <c r="T180" s="15" t="s">
-        <v>964</v>
+      <c r="S180" s="19" t="s">
+        <v>1224</v>
+      </c>
+      <c r="T180" s="19" t="s">
+        <v>1224</v>
       </c>
       <c r="V180" s="1" t="s">
         <v>156</v>
@@ -16922,8 +17033,8 @@
       <c r="W180" s="1">
         <v>0</v>
       </c>
-      <c r="X180" s="4"/>
-      <c r="Y180" s="4"/>
+      <c r="X180" s="5"/>
+      <c r="Y180" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="1225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="1275">
   <si>
     <t>ID</t>
   </si>
@@ -3637,69 +3637,144 @@
     <t>10500000000000</t>
   </si>
   <si>
+    <t>10165</t>
+  </si>
+  <si>
+    <t>1165</t>
+  </si>
+  <si>
+    <t>深渊烈焰王</t>
+  </si>
+  <si>
+    <t>9E+72</t>
+  </si>
+  <si>
+    <t>9E+96</t>
+  </si>
+  <si>
+    <t>1E+126</t>
+  </si>
+  <si>
+    <t>128E+27</t>
+  </si>
+  <si>
+    <t>128E+55</t>
+  </si>
+  <si>
+    <t>10800000000000</t>
+  </si>
+  <si>
+    <t>10166</t>
+  </si>
+  <si>
+    <t>1166</t>
+  </si>
+  <si>
+    <t>深渊大邪王</t>
+  </si>
+  <si>
+    <t>9E+73</t>
+  </si>
+  <si>
+    <t>9E+97</t>
+  </si>
+  <si>
+    <t>2E+127</t>
+  </si>
+  <si>
+    <t>256E+28</t>
+  </si>
+  <si>
+    <t>256E+56</t>
+  </si>
+  <si>
+    <t>11100000000000</t>
+  </si>
+  <si>
+    <t>10167</t>
+  </si>
+  <si>
+    <t>1167</t>
+  </si>
+  <si>
+    <t>深渊尸魔王</t>
+  </si>
+  <si>
+    <t>9E+74</t>
+  </si>
+  <si>
+    <t>9E+98</t>
+  </si>
+  <si>
+    <t>4E+128</t>
+  </si>
+  <si>
+    <t>512E+29</t>
+  </si>
+  <si>
+    <t>512E+57</t>
+  </si>
+  <si>
+    <t>11400000000000</t>
+  </si>
+  <si>
+    <t>10168</t>
+  </si>
+  <si>
+    <t>1168</t>
+  </si>
+  <si>
+    <t>深渊骨魔王</t>
+  </si>
+  <si>
+    <t>9E+75</t>
+  </si>
+  <si>
+    <t>9E+99</t>
+  </si>
+  <si>
+    <t>8E+129</t>
+  </si>
+  <si>
+    <t>1E+33</t>
+  </si>
+  <si>
+    <t>1E+61</t>
+  </si>
+  <si>
+    <t>11700000000000</t>
+  </si>
+  <si>
+    <t>10169</t>
+  </si>
+  <si>
+    <t>1169</t>
+  </si>
+  <si>
+    <t>深渊牛魔王</t>
+  </si>
+  <si>
+    <t>9E+76</t>
+  </si>
+  <si>
+    <t>9E+100</t>
+  </si>
+  <si>
+    <t>16E+130</t>
+  </si>
+  <si>
+    <t>2E+34</t>
+  </si>
+  <si>
+    <t>2E+62</t>
+  </si>
+  <si>
+    <t>12000000000000</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
-    <t>10165</t>
-  </si>
-  <si>
-    <t>1165</t>
-  </si>
-  <si>
-    <t>深渊烈焰王</t>
-  </si>
-  <si>
-    <t>10800000000000</t>
-  </si>
-  <si>
-    <t>10166</t>
-  </si>
-  <si>
-    <t>1166</t>
-  </si>
-  <si>
-    <t>深渊大邪王</t>
-  </si>
-  <si>
-    <t>11100000000000</t>
-  </si>
-  <si>
-    <t>10167</t>
-  </si>
-  <si>
-    <t>1167</t>
-  </si>
-  <si>
-    <t>深渊尸魔王</t>
-  </si>
-  <si>
-    <t>11400000000000</t>
-  </si>
-  <si>
-    <t>10168</t>
-  </si>
-  <si>
-    <t>1168</t>
-  </si>
-  <si>
-    <t>深渊骨魔王</t>
-  </si>
-  <si>
-    <t>11700000000000</t>
-  </si>
-  <si>
-    <t>10169</t>
-  </si>
-  <si>
-    <t>1169</t>
-  </si>
-  <si>
-    <t>深渊牛魔王</t>
-  </si>
-  <si>
-    <t>12000000000000</t>
-  </si>
-  <si>
     <t>10170</t>
   </si>
   <si>
@@ -3709,6 +3784,21 @@
     <t>深渊水龙王</t>
   </si>
   <si>
+    <t>9E+77</t>
+  </si>
+  <si>
+    <t>9E+101</t>
+  </si>
+  <si>
+    <t>32E+131</t>
+  </si>
+  <si>
+    <t>4E+35</t>
+  </si>
+  <si>
+    <t>4E+63</t>
+  </si>
+  <si>
     <t>12300000000000</t>
   </si>
   <si>
@@ -3721,6 +3811,21 @@
     <t>深渊土龙王</t>
   </si>
   <si>
+    <t>9E+78</t>
+  </si>
+  <si>
+    <t>9E+102</t>
+  </si>
+  <si>
+    <t>64E+132</t>
+  </si>
+  <si>
+    <t>8E+36</t>
+  </si>
+  <si>
+    <t>8E+64</t>
+  </si>
+  <si>
     <t>12600000000000</t>
   </si>
   <si>
@@ -3733,6 +3838,21 @@
     <t>深渊毒龙王</t>
   </si>
   <si>
+    <t>9E+79</t>
+  </si>
+  <si>
+    <t>9E+103</t>
+  </si>
+  <si>
+    <t>128E+133</t>
+  </si>
+  <si>
+    <t>16E+37</t>
+  </si>
+  <si>
+    <t>16E+65</t>
+  </si>
+  <si>
     <t>12900000000000</t>
   </si>
   <si>
@@ -3745,6 +3865,21 @@
     <t>深渊火龙王</t>
   </si>
   <si>
+    <t>9E+80</t>
+  </si>
+  <si>
+    <t>9E+104</t>
+  </si>
+  <si>
+    <t>256E+134</t>
+  </si>
+  <si>
+    <t>32E+38</t>
+  </si>
+  <si>
+    <t>32E+66</t>
+  </si>
+  <si>
     <t>13200000000000</t>
   </si>
   <si>
@@ -3755,6 +3890,21 @@
   </si>
   <si>
     <t>深渊冰龙王</t>
+  </si>
+  <si>
+    <t>9E+81</t>
+  </si>
+  <si>
+    <t>9E+105</t>
+  </si>
+  <si>
+    <t>512E+135</t>
+  </si>
+  <si>
+    <t>64E+39</t>
+  </si>
+  <si>
+    <t>64E+67</t>
   </si>
   <si>
     <t>13500000000000</t>
@@ -15981,11 +16131,11 @@
         <v>10000</v>
       </c>
       <c r="P166" s="5">
-        <f t="shared" ref="P166:P180" si="58">P165+5</f>
+        <f>P165+5</f>
         <v>154</v>
       </c>
       <c r="Q166" s="5">
-        <f t="shared" ref="Q166:Q180" si="59">Q165+6</f>
+        <f>Q165+6</f>
         <v>237</v>
       </c>
       <c r="R166" s="5">
@@ -16049,11 +16199,11 @@
         <v>10300</v>
       </c>
       <c r="P167" s="5">
-        <f t="shared" si="58"/>
+        <f>P166+5</f>
         <v>159</v>
       </c>
       <c r="Q167" s="5">
-        <f t="shared" si="59"/>
+        <f>Q166+6</f>
         <v>243</v>
       </c>
       <c r="R167" s="5">
@@ -16117,11 +16267,11 @@
         <v>10600</v>
       </c>
       <c r="P168" s="5">
-        <f t="shared" si="58"/>
+        <f>P167+5</f>
         <v>164</v>
       </c>
       <c r="Q168" s="5">
-        <f t="shared" si="59"/>
+        <f>Q167+6</f>
         <v>249</v>
       </c>
       <c r="R168" s="5">
@@ -16185,11 +16335,11 @@
         <v>10900</v>
       </c>
       <c r="P169" s="5">
-        <f t="shared" si="58"/>
+        <f>P168+5</f>
         <v>169</v>
       </c>
       <c r="Q169" s="5">
-        <f t="shared" si="59"/>
+        <f>Q168+6</f>
         <v>255</v>
       </c>
       <c r="R169" s="5">
@@ -16253,11 +16403,11 @@
         <v>11200</v>
       </c>
       <c r="P170" s="5">
-        <f t="shared" si="58"/>
+        <f>P169+5</f>
         <v>174</v>
       </c>
       <c r="Q170" s="5">
-        <f t="shared" si="59"/>
+        <f>Q169+6</f>
         <v>261</v>
       </c>
       <c r="R170" s="5">
@@ -16277,38 +16427,34 @@
       </c>
     </row>
     <row r="171" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A171" s="5" t="s">
+      <c r="A171" s="5"/>
+      <c r="B171" s="5"/>
+      <c r="C171" s="19" t="s">
         <v>1184</v>
       </c>
-      <c r="B171" s="5" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C171" s="19" t="s">
+      <c r="D171" s="19" t="s">
         <v>1185</v>
-      </c>
-      <c r="D171" s="19" t="s">
-        <v>1186</v>
       </c>
       <c r="E171" s="1">
         <v>5</v>
       </c>
       <c r="F171" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="G171" s="26" t="s">
         <v>1187</v>
       </c>
-      <c r="G171" s="1">
-        <v>0</v>
-      </c>
-      <c r="H171" s="1">
-        <v>0</v>
-      </c>
-      <c r="I171" s="1">
-        <v>0</v>
-      </c>
-      <c r="J171" s="1">
-        <v>0</v>
-      </c>
-      <c r="K171" s="1">
-        <v>0</v>
+      <c r="H171" s="26" t="s">
+        <v>1188</v>
+      </c>
+      <c r="I171" s="26" t="s">
+        <v>1189</v>
+      </c>
+      <c r="J171" s="26" t="s">
+        <v>1190</v>
+      </c>
+      <c r="K171" s="26" t="s">
+        <v>1191</v>
       </c>
       <c r="L171" s="1">
         <f t="shared" si="50"/>
@@ -16319,29 +16465,29 @@
         <v>29300</v>
       </c>
       <c r="N171" s="1">
-        <f t="shared" ref="N171:N175" si="60">N170+400</f>
+        <f t="shared" ref="N171:N175" si="58">N170+400</f>
         <v>11600</v>
       </c>
       <c r="O171" s="1">
-        <f t="shared" ref="O171:O175" si="61">O170+400</f>
+        <f t="shared" ref="O171:O175" si="59">O170+400</f>
         <v>11600</v>
       </c>
       <c r="P171" s="5">
-        <f t="shared" si="58"/>
-        <v>179</v>
+        <f t="shared" ref="P171:P175" si="60">P170+6</f>
+        <v>180</v>
       </c>
       <c r="Q171" s="5">
-        <f t="shared" si="59"/>
-        <v>267</v>
+        <f t="shared" ref="Q171:Q175" si="61">Q170+7</f>
+        <v>268</v>
       </c>
       <c r="R171" s="5">
         <v>99.99</v>
       </c>
       <c r="S171" s="19" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="T171" s="19" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="V171" s="1" t="s">
         <v>156</v>
@@ -16353,38 +16499,34 @@
       <c r="Y171" s="5"/>
     </row>
     <row r="172" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A172" s="5" t="s">
-        <v>1184</v>
-      </c>
-      <c r="B172" s="5" t="s">
-        <v>1184</v>
-      </c>
+      <c r="A172" s="5"/>
+      <c r="B172" s="5"/>
       <c r="C172" s="19" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="D172" s="19" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="E172" s="1">
         <v>5</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1191</v>
-      </c>
-      <c r="G172" s="1">
-        <v>0</v>
-      </c>
-      <c r="H172" s="1">
-        <v>0</v>
-      </c>
-      <c r="I172" s="1">
-        <v>0</v>
-      </c>
-      <c r="J172" s="1">
-        <v>0</v>
-      </c>
-      <c r="K172" s="1">
-        <v>0</v>
+        <v>1195</v>
+      </c>
+      <c r="G172" s="26" t="s">
+        <v>1196</v>
+      </c>
+      <c r="H172" s="26" t="s">
+        <v>1197</v>
+      </c>
+      <c r="I172" s="26" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J172" s="26" t="s">
+        <v>1199</v>
+      </c>
+      <c r="K172" s="26" t="s">
+        <v>1200</v>
       </c>
       <c r="L172" s="1">
         <f t="shared" si="50"/>
@@ -16395,29 +16537,29 @@
         <v>29900</v>
       </c>
       <c r="N172" s="1">
+        <f t="shared" si="58"/>
+        <v>12000</v>
+      </c>
+      <c r="O172" s="1">
+        <f t="shared" si="59"/>
+        <v>12000</v>
+      </c>
+      <c r="P172" s="5">
         <f t="shared" si="60"/>
-        <v>12000</v>
-      </c>
-      <c r="O172" s="1">
+        <v>186</v>
+      </c>
+      <c r="Q172" s="5">
         <f t="shared" si="61"/>
-        <v>12000</v>
-      </c>
-      <c r="P172" s="5">
-        <f t="shared" si="58"/>
-        <v>184</v>
-      </c>
-      <c r="Q172" s="5">
-        <f t="shared" si="59"/>
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R172" s="5">
         <v>99.99</v>
       </c>
       <c r="S172" s="19" t="s">
-        <v>1192</v>
+        <v>1201</v>
       </c>
       <c r="T172" s="19" t="s">
-        <v>1192</v>
+        <v>1201</v>
       </c>
       <c r="V172" s="1" t="s">
         <v>156</v>
@@ -16429,38 +16571,34 @@
       <c r="Y172" s="5"/>
     </row>
     <row r="173" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A173" s="5" t="s">
-        <v>1184</v>
-      </c>
-      <c r="B173" s="5" t="s">
-        <v>1184</v>
-      </c>
+      <c r="A173" s="5"/>
+      <c r="B173" s="5"/>
       <c r="C173" s="19" t="s">
-        <v>1193</v>
+        <v>1202</v>
       </c>
       <c r="D173" s="19" t="s">
-        <v>1194</v>
+        <v>1203</v>
       </c>
       <c r="E173" s="1">
         <v>5</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1195</v>
-      </c>
-      <c r="G173" s="1">
-        <v>0</v>
-      </c>
-      <c r="H173" s="1">
-        <v>0</v>
-      </c>
-      <c r="I173" s="1">
-        <v>0</v>
-      </c>
-      <c r="J173" s="1">
-        <v>0</v>
-      </c>
-      <c r="K173" s="1">
-        <v>0</v>
+        <v>1204</v>
+      </c>
+      <c r="G173" s="26" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H173" s="26" t="s">
+        <v>1206</v>
+      </c>
+      <c r="I173" s="26" t="s">
+        <v>1207</v>
+      </c>
+      <c r="J173" s="26" t="s">
+        <v>1208</v>
+      </c>
+      <c r="K173" s="26" t="s">
+        <v>1209</v>
       </c>
       <c r="L173" s="1">
         <f t="shared" si="50"/>
@@ -16471,29 +16609,29 @@
         <v>30500</v>
       </c>
       <c r="N173" s="1">
+        <f t="shared" si="58"/>
+        <v>12400</v>
+      </c>
+      <c r="O173" s="1">
+        <f t="shared" si="59"/>
+        <v>12400</v>
+      </c>
+      <c r="P173" s="5">
         <f t="shared" si="60"/>
-        <v>12400</v>
-      </c>
-      <c r="O173" s="1">
+        <v>192</v>
+      </c>
+      <c r="Q173" s="5">
         <f t="shared" si="61"/>
-        <v>12400</v>
-      </c>
-      <c r="P173" s="5">
-        <f t="shared" si="58"/>
-        <v>189</v>
-      </c>
-      <c r="Q173" s="5">
-        <f t="shared" si="59"/>
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="R173" s="5">
         <v>99.99</v>
       </c>
       <c r="S173" s="19" t="s">
-        <v>1196</v>
+        <v>1210</v>
       </c>
       <c r="T173" s="19" t="s">
-        <v>1196</v>
+        <v>1210</v>
       </c>
       <c r="V173" s="1" t="s">
         <v>156</v>
@@ -16505,38 +16643,34 @@
       <c r="Y173" s="5"/>
     </row>
     <row r="174" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A174" s="5" t="s">
-        <v>1184</v>
-      </c>
-      <c r="B174" s="5" t="s">
-        <v>1184</v>
-      </c>
+      <c r="A174" s="5"/>
+      <c r="B174" s="5"/>
       <c r="C174" s="19" t="s">
-        <v>1197</v>
+        <v>1211</v>
       </c>
       <c r="D174" s="19" t="s">
-        <v>1198</v>
+        <v>1212</v>
       </c>
       <c r="E174" s="1">
         <v>5</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="G174" s="1">
-        <v>0</v>
-      </c>
-      <c r="H174" s="1">
-        <v>0</v>
-      </c>
-      <c r="I174" s="1">
-        <v>0</v>
-      </c>
-      <c r="J174" s="1">
-        <v>0</v>
-      </c>
-      <c r="K174" s="1">
-        <v>0</v>
+        <v>1213</v>
+      </c>
+      <c r="G174" s="26" t="s">
+        <v>1214</v>
+      </c>
+      <c r="H174" s="26" t="s">
+        <v>1215</v>
+      </c>
+      <c r="I174" s="26" t="s">
+        <v>1216</v>
+      </c>
+      <c r="J174" s="26" t="s">
+        <v>1217</v>
+      </c>
+      <c r="K174" s="26" t="s">
+        <v>1218</v>
       </c>
       <c r="L174" s="1">
         <f t="shared" si="50"/>
@@ -16547,29 +16681,29 @@
         <v>31100</v>
       </c>
       <c r="N174" s="1">
+        <f t="shared" si="58"/>
+        <v>12800</v>
+      </c>
+      <c r="O174" s="1">
+        <f t="shared" si="59"/>
+        <v>12800</v>
+      </c>
+      <c r="P174" s="5">
         <f t="shared" si="60"/>
-        <v>12800</v>
-      </c>
-      <c r="O174" s="1">
+        <v>198</v>
+      </c>
+      <c r="Q174" s="5">
         <f t="shared" si="61"/>
-        <v>12800</v>
-      </c>
-      <c r="P174" s="5">
-        <f t="shared" si="58"/>
-        <v>194</v>
-      </c>
-      <c r="Q174" s="5">
-        <f t="shared" si="59"/>
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="R174" s="5">
         <v>99.99</v>
       </c>
       <c r="S174" s="19" t="s">
-        <v>1200</v>
+        <v>1219</v>
       </c>
       <c r="T174" s="19" t="s">
-        <v>1200</v>
+        <v>1219</v>
       </c>
       <c r="V174" s="1" t="s">
         <v>156</v>
@@ -16581,38 +16715,34 @@
       <c r="Y174" s="5"/>
     </row>
     <row r="175" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A175" s="5" t="s">
-        <v>1184</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>1184</v>
-      </c>
+      <c r="A175" s="5"/>
+      <c r="B175" s="5"/>
       <c r="C175" s="19" t="s">
-        <v>1201</v>
+        <v>1220</v>
       </c>
       <c r="D175" s="19" t="s">
-        <v>1202</v>
+        <v>1221</v>
       </c>
       <c r="E175" s="1">
         <v>5</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1203</v>
-      </c>
-      <c r="G175" s="1">
-        <v>0</v>
-      </c>
-      <c r="H175" s="1">
-        <v>0</v>
-      </c>
-      <c r="I175" s="1">
-        <v>0</v>
-      </c>
-      <c r="J175" s="1">
-        <v>0</v>
-      </c>
-      <c r="K175" s="1">
-        <v>0</v>
+        <v>1222</v>
+      </c>
+      <c r="G175" s="26" t="s">
+        <v>1223</v>
+      </c>
+      <c r="H175" s="26" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I175" s="26" t="s">
+        <v>1225</v>
+      </c>
+      <c r="J175" s="26" t="s">
+        <v>1226</v>
+      </c>
+      <c r="K175" s="26" t="s">
+        <v>1227</v>
       </c>
       <c r="L175" s="1">
         <f t="shared" si="50"/>
@@ -16623,29 +16753,29 @@
         <v>31700</v>
       </c>
       <c r="N175" s="1">
+        <f t="shared" si="58"/>
+        <v>13200</v>
+      </c>
+      <c r="O175" s="1">
+        <f t="shared" si="59"/>
+        <v>13200</v>
+      </c>
+      <c r="P175" s="5">
         <f t="shared" si="60"/>
-        <v>13200</v>
-      </c>
-      <c r="O175" s="1">
+        <v>204</v>
+      </c>
+      <c r="Q175" s="5">
         <f t="shared" si="61"/>
-        <v>13200</v>
-      </c>
-      <c r="P175" s="5">
-        <f t="shared" si="58"/>
-        <v>199</v>
-      </c>
-      <c r="Q175" s="5">
-        <f t="shared" si="59"/>
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="R175" s="5">
         <v>99.99</v>
       </c>
       <c r="S175" s="19" t="s">
-        <v>1204</v>
+        <v>1228</v>
       </c>
       <c r="T175" s="19" t="s">
-        <v>1204</v>
+        <v>1228</v>
       </c>
       <c r="V175" s="1" t="s">
         <v>156</v>
@@ -16658,37 +16788,37 @@
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A176" s="5" t="s">
-        <v>1184</v>
+        <v>1229</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>1184</v>
+        <v>1229</v>
       </c>
       <c r="C176" s="19" t="s">
-        <v>1205</v>
+        <v>1230</v>
       </c>
       <c r="D176" s="19" t="s">
-        <v>1206</v>
+        <v>1231</v>
       </c>
       <c r="E176" s="1">
         <v>5</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1207</v>
-      </c>
-      <c r="G176" s="1">
-        <v>0</v>
-      </c>
-      <c r="H176" s="1">
-        <v>0</v>
-      </c>
-      <c r="I176" s="1">
-        <v>0</v>
-      </c>
-      <c r="J176" s="1">
-        <v>0</v>
-      </c>
-      <c r="K176" s="1">
-        <v>0</v>
+        <v>1232</v>
+      </c>
+      <c r="G176" s="26" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H176" s="26" t="s">
+        <v>1234</v>
+      </c>
+      <c r="I176" s="26" t="s">
+        <v>1235</v>
+      </c>
+      <c r="J176" s="26" t="s">
+        <v>1236</v>
+      </c>
+      <c r="K176" s="26" t="s">
+        <v>1237</v>
       </c>
       <c r="L176" s="1">
         <f t="shared" si="50"/>
@@ -16707,21 +16837,21 @@
         <v>13700</v>
       </c>
       <c r="P176" s="5">
-        <f t="shared" si="58"/>
-        <v>204</v>
+        <f t="shared" ref="P176:P180" si="64">P175+7</f>
+        <v>211</v>
       </c>
       <c r="Q176" s="5">
-        <f t="shared" si="59"/>
-        <v>297</v>
+        <f t="shared" ref="Q176:Q180" si="65">Q175+8</f>
+        <v>304</v>
       </c>
       <c r="R176" s="5">
         <v>99.99</v>
       </c>
       <c r="S176" s="19" t="s">
-        <v>1208</v>
+        <v>1238</v>
       </c>
       <c r="T176" s="19" t="s">
-        <v>1208</v>
+        <v>1238</v>
       </c>
       <c r="V176" s="1" t="s">
         <v>156</v>
@@ -16734,37 +16864,37 @@
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A177" s="5" t="s">
-        <v>1184</v>
+        <v>1229</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>1184</v>
+        <v>1229</v>
       </c>
       <c r="C177" s="19" t="s">
-        <v>1209</v>
+        <v>1239</v>
       </c>
       <c r="D177" s="19" t="s">
-        <v>1210</v>
+        <v>1240</v>
       </c>
       <c r="E177" s="1">
         <v>5</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1211</v>
-      </c>
-      <c r="G177" s="1">
-        <v>0</v>
-      </c>
-      <c r="H177" s="1">
-        <v>0</v>
-      </c>
-      <c r="I177" s="1">
-        <v>0</v>
-      </c>
-      <c r="J177" s="1">
-        <v>0</v>
-      </c>
-      <c r="K177" s="1">
-        <v>0</v>
+        <v>1241</v>
+      </c>
+      <c r="G177" s="26" t="s">
+        <v>1242</v>
+      </c>
+      <c r="H177" s="26" t="s">
+        <v>1243</v>
+      </c>
+      <c r="I177" s="26" t="s">
+        <v>1244</v>
+      </c>
+      <c r="J177" s="26" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K177" s="26" t="s">
+        <v>1246</v>
       </c>
       <c r="L177" s="1">
         <f t="shared" si="50"/>
@@ -16783,21 +16913,21 @@
         <v>14200</v>
       </c>
       <c r="P177" s="5">
-        <f t="shared" si="58"/>
-        <v>209</v>
+        <f t="shared" si="64"/>
+        <v>218</v>
       </c>
       <c r="Q177" s="5">
-        <f t="shared" si="59"/>
-        <v>303</v>
+        <f t="shared" si="65"/>
+        <v>312</v>
       </c>
       <c r="R177" s="5">
         <v>99.99</v>
       </c>
       <c r="S177" s="19" t="s">
-        <v>1212</v>
+        <v>1247</v>
       </c>
       <c r="T177" s="19" t="s">
-        <v>1212</v>
+        <v>1247</v>
       </c>
       <c r="V177" s="1" t="s">
         <v>156</v>
@@ -16810,37 +16940,37 @@
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A178" s="5" t="s">
-        <v>1184</v>
+        <v>1229</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>1184</v>
+        <v>1229</v>
       </c>
       <c r="C178" s="19" t="s">
-        <v>1213</v>
+        <v>1248</v>
       </c>
       <c r="D178" s="19" t="s">
-        <v>1214</v>
+        <v>1249</v>
       </c>
       <c r="E178" s="1">
         <v>5</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1215</v>
-      </c>
-      <c r="G178" s="1">
-        <v>0</v>
-      </c>
-      <c r="H178" s="1">
-        <v>0</v>
-      </c>
-      <c r="I178" s="1">
-        <v>0</v>
-      </c>
-      <c r="J178" s="1">
-        <v>0</v>
-      </c>
-      <c r="K178" s="1">
-        <v>0</v>
+        <v>1250</v>
+      </c>
+      <c r="G178" s="26" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H178" s="26" t="s">
+        <v>1252</v>
+      </c>
+      <c r="I178" s="26" t="s">
+        <v>1253</v>
+      </c>
+      <c r="J178" s="26" t="s">
+        <v>1254</v>
+      </c>
+      <c r="K178" s="26" t="s">
+        <v>1255</v>
       </c>
       <c r="L178" s="1">
         <f t="shared" si="50"/>
@@ -16859,21 +16989,21 @@
         <v>14700</v>
       </c>
       <c r="P178" s="5">
-        <f t="shared" si="58"/>
-        <v>214</v>
+        <f t="shared" si="64"/>
+        <v>225</v>
       </c>
       <c r="Q178" s="5">
-        <f t="shared" si="59"/>
-        <v>309</v>
+        <f t="shared" si="65"/>
+        <v>320</v>
       </c>
       <c r="R178" s="5">
         <v>99.99</v>
       </c>
       <c r="S178" s="19" t="s">
-        <v>1216</v>
+        <v>1256</v>
       </c>
       <c r="T178" s="19" t="s">
-        <v>1216</v>
+        <v>1256</v>
       </c>
       <c r="V178" s="1" t="s">
         <v>156</v>
@@ -16886,37 +17016,37 @@
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A179" s="5" t="s">
-        <v>1184</v>
+        <v>1229</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>1184</v>
+        <v>1229</v>
       </c>
       <c r="C179" s="19" t="s">
-        <v>1217</v>
+        <v>1257</v>
       </c>
       <c r="D179" s="19" t="s">
-        <v>1218</v>
+        <v>1258</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1219</v>
-      </c>
-      <c r="G179" s="1">
-        <v>0</v>
-      </c>
-      <c r="H179" s="1">
-        <v>0</v>
-      </c>
-      <c r="I179" s="1">
-        <v>0</v>
-      </c>
-      <c r="J179" s="1">
-        <v>0</v>
-      </c>
-      <c r="K179" s="1">
-        <v>0</v>
+        <v>1259</v>
+      </c>
+      <c r="G179" s="26" t="s">
+        <v>1260</v>
+      </c>
+      <c r="H179" s="26" t="s">
+        <v>1261</v>
+      </c>
+      <c r="I179" s="26" t="s">
+        <v>1262</v>
+      </c>
+      <c r="J179" s="26" t="s">
+        <v>1263</v>
+      </c>
+      <c r="K179" s="26" t="s">
+        <v>1264</v>
       </c>
       <c r="L179" s="1">
         <f t="shared" si="50"/>
@@ -16935,21 +17065,21 @@
         <v>15200</v>
       </c>
       <c r="P179" s="5">
-        <f t="shared" si="58"/>
-        <v>219</v>
+        <f t="shared" si="64"/>
+        <v>232</v>
       </c>
       <c r="Q179" s="5">
-        <f t="shared" si="59"/>
-        <v>315</v>
+        <f t="shared" si="65"/>
+        <v>328</v>
       </c>
       <c r="R179" s="5">
         <v>99.99</v>
       </c>
       <c r="S179" s="19" t="s">
-        <v>1220</v>
+        <v>1265</v>
       </c>
       <c r="T179" s="19" t="s">
-        <v>1220</v>
+        <v>1265</v>
       </c>
       <c r="V179" s="1" t="s">
         <v>156</v>
@@ -16962,37 +17092,37 @@
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A180" s="5" t="s">
-        <v>1184</v>
+        <v>1229</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>1184</v>
+        <v>1229</v>
       </c>
       <c r="C180" s="19" t="s">
-        <v>1221</v>
+        <v>1266</v>
       </c>
       <c r="D180" s="19" t="s">
-        <v>1222</v>
+        <v>1267</v>
       </c>
       <c r="E180" s="1">
         <v>5</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G180" s="1">
-        <v>0</v>
-      </c>
-      <c r="H180" s="1">
-        <v>0</v>
-      </c>
-      <c r="I180" s="1">
-        <v>0</v>
-      </c>
-      <c r="J180" s="1">
-        <v>0</v>
-      </c>
-      <c r="K180" s="1">
-        <v>0</v>
+        <v>1268</v>
+      </c>
+      <c r="G180" s="26" t="s">
+        <v>1269</v>
+      </c>
+      <c r="H180" s="26" t="s">
+        <v>1270</v>
+      </c>
+      <c r="I180" s="26" t="s">
+        <v>1271</v>
+      </c>
+      <c r="J180" s="26" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K180" s="26" t="s">
+        <v>1273</v>
       </c>
       <c r="L180" s="1">
         <f t="shared" si="50"/>
@@ -17011,21 +17141,21 @@
         <v>15700</v>
       </c>
       <c r="P180" s="5">
-        <f t="shared" si="58"/>
-        <v>224</v>
+        <f t="shared" si="64"/>
+        <v>239</v>
       </c>
       <c r="Q180" s="5">
-        <f t="shared" si="59"/>
-        <v>321</v>
+        <f t="shared" si="65"/>
+        <v>336</v>
       </c>
       <c r="R180" s="5">
         <v>99.99</v>
       </c>
       <c r="S180" s="19" t="s">
-        <v>1224</v>
+        <v>1274</v>
       </c>
       <c r="T180" s="19" t="s">
-        <v>1224</v>
+        <v>1274</v>
       </c>
       <c r="V180" s="1" t="s">
         <v>156</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="1275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="1274">
   <si>
     <t>ID</t>
   </si>
@@ -3770,9 +3770,6 @@
   </si>
   <si>
     <t>12000000000000</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
   <si>
     <t>10170</t>
@@ -4920,27 +4917,27 @@
   <dimension ref="A1:Y180"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.87610619469027" style="5" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="5" customWidth="1"/>
     <col min="2" max="2" width="9" style="5"/>
-    <col min="3" max="3" width="9.87610619469027" style="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6283185840708" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.87610619469027" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1238938053097" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.2477876106195" style="5" customWidth="1"/>
+    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.25" style="5" customWidth="1"/>
     <col min="8" max="8" width="23" style="5" customWidth="1"/>
-    <col min="9" max="9" width="22.6283185840708" style="5" customWidth="1"/>
+    <col min="9" max="9" width="22.625" style="5" customWidth="1"/>
     <col min="10" max="10" width="16" style="5" customWidth="1"/>
-    <col min="11" max="11" width="11.7522123893805" style="5" customWidth="1"/>
-    <col min="12" max="12" width="15.8761061946903" style="5" customWidth="1"/>
-    <col min="13" max="15" width="12.1238938053097" style="5" customWidth="1"/>
-    <col min="16" max="16" width="9.6283185840708" style="5" customWidth="1"/>
-    <col min="17" max="17" width="7.50442477876106" style="5" customWidth="1"/>
-    <col min="18" max="18" width="7.12389380530973" style="5" customWidth="1"/>
-    <col min="19" max="19" width="16.3716814159292" style="5" customWidth="1"/>
+    <col min="11" max="11" width="11.75" style="5" customWidth="1"/>
+    <col min="12" max="12" width="15.875" style="5" customWidth="1"/>
+    <col min="13" max="15" width="12.125" style="5" customWidth="1"/>
+    <col min="16" max="16" width="9.625" style="5" customWidth="1"/>
+    <col min="17" max="17" width="7.50833333333333" style="5" customWidth="1"/>
+    <col min="18" max="18" width="7.125" style="5" customWidth="1"/>
+    <col min="19" max="19" width="16.375" style="5" customWidth="1"/>
     <col min="20" max="20" width="13" style="5" customWidth="1"/>
-    <col min="21" max="21" width="13.7522123893805" style="1" customWidth="1"/>
-    <col min="22" max="22" width="15.5044247787611" style="1" customWidth="1"/>
-    <col min="23" max="23" width="13.3716814159292" style="1" customWidth="1"/>
+    <col min="21" max="21" width="13.75" style="1" customWidth="1"/>
+    <col min="22" max="22" width="15.5083333333333" style="1" customWidth="1"/>
+    <col min="23" max="23" width="13.375" style="1" customWidth="1"/>
     <col min="24" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -5180,7 +5177,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="11.6" spans="3:23">
+    <row r="6" s="1" customFormat="1" ht="11.5" spans="3:23">
       <c r="C6" s="1" t="s">
         <v>37</v>
       </c>
@@ -16787,38 +16784,34 @@
       <c r="Y175" s="5"/>
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A176" s="5" t="s">
+      <c r="A176" s="5"/>
+      <c r="B176" s="5"/>
+      <c r="C176" s="19" t="s">
         <v>1229</v>
       </c>
-      <c r="B176" s="5" t="s">
-        <v>1229</v>
-      </c>
-      <c r="C176" s="19" t="s">
+      <c r="D176" s="19" t="s">
         <v>1230</v>
-      </c>
-      <c r="D176" s="19" t="s">
-        <v>1231</v>
       </c>
       <c r="E176" s="1">
         <v>5</v>
       </c>
       <c r="F176" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G176" s="26" t="s">
         <v>1232</v>
       </c>
-      <c r="G176" s="26" t="s">
+      <c r="H176" s="26" t="s">
         <v>1233</v>
       </c>
-      <c r="H176" s="26" t="s">
+      <c r="I176" s="26" t="s">
         <v>1234</v>
       </c>
-      <c r="I176" s="26" t="s">
+      <c r="J176" s="26" t="s">
         <v>1235</v>
       </c>
-      <c r="J176" s="26" t="s">
+      <c r="K176" s="26" t="s">
         <v>1236</v>
-      </c>
-      <c r="K176" s="26" t="s">
-        <v>1237</v>
       </c>
       <c r="L176" s="1">
         <f t="shared" si="50"/>
@@ -16848,10 +16841,10 @@
         <v>99.99</v>
       </c>
       <c r="S176" s="19" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="T176" s="19" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="V176" s="1" t="s">
         <v>156</v>
@@ -16863,38 +16856,34 @@
       <c r="Y176" s="5"/>
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A177" s="5" t="s">
-        <v>1229</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>1229</v>
-      </c>
+      <c r="A177" s="5"/>
+      <c r="B177" s="5"/>
       <c r="C177" s="19" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D177" s="19" t="s">
         <v>1239</v>
-      </c>
-      <c r="D177" s="19" t="s">
-        <v>1240</v>
       </c>
       <c r="E177" s="1">
         <v>5</v>
       </c>
       <c r="F177" s="1" t="s">
+        <v>1240</v>
+      </c>
+      <c r="G177" s="26" t="s">
         <v>1241</v>
       </c>
-      <c r="G177" s="26" t="s">
+      <c r="H177" s="26" t="s">
         <v>1242</v>
       </c>
-      <c r="H177" s="26" t="s">
+      <c r="I177" s="26" t="s">
         <v>1243</v>
       </c>
-      <c r="I177" s="26" t="s">
+      <c r="J177" s="26" t="s">
         <v>1244</v>
       </c>
-      <c r="J177" s="26" t="s">
+      <c r="K177" s="26" t="s">
         <v>1245</v>
-      </c>
-      <c r="K177" s="26" t="s">
-        <v>1246</v>
       </c>
       <c r="L177" s="1">
         <f t="shared" si="50"/>
@@ -16924,10 +16913,10 @@
         <v>99.99</v>
       </c>
       <c r="S177" s="19" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="T177" s="19" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="V177" s="1" t="s">
         <v>156</v>
@@ -16939,38 +16928,34 @@
       <c r="Y177" s="5"/>
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A178" s="5" t="s">
-        <v>1229</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>1229</v>
-      </c>
+      <c r="A178" s="5"/>
+      <c r="B178" s="5"/>
       <c r="C178" s="19" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D178" s="19" t="s">
         <v>1248</v>
-      </c>
-      <c r="D178" s="19" t="s">
-        <v>1249</v>
       </c>
       <c r="E178" s="1">
         <v>5</v>
       </c>
       <c r="F178" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="G178" s="26" t="s">
         <v>1250</v>
       </c>
-      <c r="G178" s="26" t="s">
+      <c r="H178" s="26" t="s">
         <v>1251</v>
       </c>
-      <c r="H178" s="26" t="s">
+      <c r="I178" s="26" t="s">
         <v>1252</v>
       </c>
-      <c r="I178" s="26" t="s">
+      <c r="J178" s="26" t="s">
         <v>1253</v>
       </c>
-      <c r="J178" s="26" t="s">
+      <c r="K178" s="26" t="s">
         <v>1254</v>
-      </c>
-      <c r="K178" s="26" t="s">
-        <v>1255</v>
       </c>
       <c r="L178" s="1">
         <f t="shared" si="50"/>
@@ -17000,10 +16985,10 @@
         <v>99.99</v>
       </c>
       <c r="S178" s="19" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="T178" s="19" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="V178" s="1" t="s">
         <v>156</v>
@@ -17015,38 +17000,34 @@
       <c r="Y178" s="5"/>
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A179" s="5" t="s">
-        <v>1229</v>
-      </c>
-      <c r="B179" s="5" t="s">
-        <v>1229</v>
-      </c>
+      <c r="A179" s="5"/>
+      <c r="B179" s="5"/>
       <c r="C179" s="19" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D179" s="19" t="s">
         <v>1257</v>
-      </c>
-      <c r="D179" s="19" t="s">
-        <v>1258</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
       </c>
       <c r="F179" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="G179" s="26" t="s">
         <v>1259</v>
       </c>
-      <c r="G179" s="26" t="s">
+      <c r="H179" s="26" t="s">
         <v>1260</v>
       </c>
-      <c r="H179" s="26" t="s">
+      <c r="I179" s="26" t="s">
         <v>1261</v>
       </c>
-      <c r="I179" s="26" t="s">
+      <c r="J179" s="26" t="s">
         <v>1262</v>
       </c>
-      <c r="J179" s="26" t="s">
+      <c r="K179" s="26" t="s">
         <v>1263</v>
-      </c>
-      <c r="K179" s="26" t="s">
-        <v>1264</v>
       </c>
       <c r="L179" s="1">
         <f t="shared" si="50"/>
@@ -17076,10 +17057,10 @@
         <v>99.99</v>
       </c>
       <c r="S179" s="19" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="T179" s="19" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="V179" s="1" t="s">
         <v>156</v>
@@ -17091,38 +17072,34 @@
       <c r="Y179" s="5"/>
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A180" s="5" t="s">
-        <v>1229</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>1229</v>
-      </c>
+      <c r="A180" s="5"/>
+      <c r="B180" s="5"/>
       <c r="C180" s="19" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D180" s="19" t="s">
         <v>1266</v>
-      </c>
-      <c r="D180" s="19" t="s">
-        <v>1267</v>
       </c>
       <c r="E180" s="1">
         <v>5</v>
       </c>
       <c r="F180" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="G180" s="26" t="s">
         <v>1268</v>
       </c>
-      <c r="G180" s="26" t="s">
+      <c r="H180" s="26" t="s">
         <v>1269</v>
       </c>
-      <c r="H180" s="26" t="s">
+      <c r="I180" s="26" t="s">
         <v>1270</v>
       </c>
-      <c r="I180" s="26" t="s">
+      <c r="J180" s="26" t="s">
         <v>1271</v>
       </c>
-      <c r="J180" s="26" t="s">
+      <c r="K180" s="26" t="s">
         <v>1272</v>
-      </c>
-      <c r="K180" s="26" t="s">
-        <v>1273</v>
       </c>
       <c r="L180" s="1">
         <f t="shared" si="50"/>
@@ -17152,10 +17129,10 @@
         <v>99.99</v>
       </c>
       <c r="S180" s="19" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="T180" s="19" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="V180" s="1" t="s">
         <v>156</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="1274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2060" uniqueCount="1517">
   <si>
     <t>ID</t>
   </si>
@@ -3905,6 +3905,735 @@
   </si>
   <si>
     <t>13500000000000</t>
+  </si>
+  <si>
+    <t>10175</t>
+  </si>
+  <si>
+    <t>1175</t>
+  </si>
+  <si>
+    <t>混沌鸡王</t>
+  </si>
+  <si>
+    <t>9E+82</t>
+  </si>
+  <si>
+    <t>9E+106</t>
+  </si>
+  <si>
+    <t>512E+136</t>
+  </si>
+  <si>
+    <t>64E+40</t>
+  </si>
+  <si>
+    <t>64E+68</t>
+  </si>
+  <si>
+    <t>10176</t>
+  </si>
+  <si>
+    <t>1176</t>
+  </si>
+  <si>
+    <t>混沌鹿王</t>
+  </si>
+  <si>
+    <t>9E+83</t>
+  </si>
+  <si>
+    <t>9E+107</t>
+  </si>
+  <si>
+    <t>512E+137</t>
+  </si>
+  <si>
+    <t>64E+41</t>
+  </si>
+  <si>
+    <t>64E+69</t>
+  </si>
+  <si>
+    <t>10177</t>
+  </si>
+  <si>
+    <t>1177</t>
+  </si>
+  <si>
+    <t>混沌草王</t>
+  </si>
+  <si>
+    <t>9E+84</t>
+  </si>
+  <si>
+    <t>9E+108</t>
+  </si>
+  <si>
+    <t>512E+138</t>
+  </si>
+  <si>
+    <t>64E+42</t>
+  </si>
+  <si>
+    <t>64E+70</t>
+  </si>
+  <si>
+    <t>10178</t>
+  </si>
+  <si>
+    <t>1178</t>
+  </si>
+  <si>
+    <t>混沌猫王</t>
+  </si>
+  <si>
+    <t>9E+85</t>
+  </si>
+  <si>
+    <t>9E+109</t>
+  </si>
+  <si>
+    <t>512E+139</t>
+  </si>
+  <si>
+    <t>64E+43</t>
+  </si>
+  <si>
+    <t>64E+71</t>
+  </si>
+  <si>
+    <t>10179</t>
+  </si>
+  <si>
+    <t>1179</t>
+  </si>
+  <si>
+    <t>混沌花王</t>
+  </si>
+  <si>
+    <t>9E+86</t>
+  </si>
+  <si>
+    <t>9E+110</t>
+  </si>
+  <si>
+    <t>512E+140</t>
+  </si>
+  <si>
+    <t>64E+44</t>
+  </si>
+  <si>
+    <t>64E+72</t>
+  </si>
+  <si>
+    <t>10180</t>
+  </si>
+  <si>
+    <t>1180</t>
+  </si>
+  <si>
+    <t>混沌雪王</t>
+  </si>
+  <si>
+    <t>9E+87</t>
+  </si>
+  <si>
+    <t>9E+111</t>
+  </si>
+  <si>
+    <t>512E+141</t>
+  </si>
+  <si>
+    <t>64E+45</t>
+  </si>
+  <si>
+    <t>64E+73</t>
+  </si>
+  <si>
+    <t>10181</t>
+  </si>
+  <si>
+    <t>1181</t>
+  </si>
+  <si>
+    <t>混沌蝠王</t>
+  </si>
+  <si>
+    <t>9E+88</t>
+  </si>
+  <si>
+    <t>9E+112</t>
+  </si>
+  <si>
+    <t>512E+142</t>
+  </si>
+  <si>
+    <t>64E+46</t>
+  </si>
+  <si>
+    <t>64E+74</t>
+  </si>
+  <si>
+    <t>10182</t>
+  </si>
+  <si>
+    <t>1182</t>
+  </si>
+  <si>
+    <t>混沌骷髅王</t>
+  </si>
+  <si>
+    <t>9E+89</t>
+  </si>
+  <si>
+    <t>9E+113</t>
+  </si>
+  <si>
+    <t>512E+143</t>
+  </si>
+  <si>
+    <t>64E+47</t>
+  </si>
+  <si>
+    <t>64E+75</t>
+  </si>
+  <si>
+    <t>10183</t>
+  </si>
+  <si>
+    <t>1183</t>
+  </si>
+  <si>
+    <t>混沌尸王</t>
+  </si>
+  <si>
+    <t>9E+114</t>
+  </si>
+  <si>
+    <t>512E+144</t>
+  </si>
+  <si>
+    <t>64E+48</t>
+  </si>
+  <si>
+    <t>64E+76</t>
+  </si>
+  <si>
+    <t>10184</t>
+  </si>
+  <si>
+    <t>1184</t>
+  </si>
+  <si>
+    <t>混沌蛇王</t>
+  </si>
+  <si>
+    <t>9E+115</t>
+  </si>
+  <si>
+    <t>512E+145</t>
+  </si>
+  <si>
+    <t>64E+49</t>
+  </si>
+  <si>
+    <t>64E+77</t>
+  </si>
+  <si>
+    <t>10185</t>
+  </si>
+  <si>
+    <t>1185</t>
+  </si>
+  <si>
+    <t>混沌狼王</t>
+  </si>
+  <si>
+    <t>9E+116</t>
+  </si>
+  <si>
+    <t>512E+146</t>
+  </si>
+  <si>
+    <t>64E+50</t>
+  </si>
+  <si>
+    <t>64E+78</t>
+  </si>
+  <si>
+    <t>10186</t>
+  </si>
+  <si>
+    <t>1186</t>
+  </si>
+  <si>
+    <t>混沌沙虫王</t>
+  </si>
+  <si>
+    <t>9E+117</t>
+  </si>
+  <si>
+    <t>512E+147</t>
+  </si>
+  <si>
+    <t>64E+51</t>
+  </si>
+  <si>
+    <t>64E+79</t>
+  </si>
+  <si>
+    <t>10187</t>
+  </si>
+  <si>
+    <t>1187</t>
+  </si>
+  <si>
+    <t>混沌鹰王</t>
+  </si>
+  <si>
+    <t>9E+118</t>
+  </si>
+  <si>
+    <t>512E+148</t>
+  </si>
+  <si>
+    <t>64E+52</t>
+  </si>
+  <si>
+    <t>64E+80</t>
+  </si>
+  <si>
+    <t>10188</t>
+  </si>
+  <si>
+    <t>1188</t>
+  </si>
+  <si>
+    <t>混沌角虫王</t>
+  </si>
+  <si>
+    <t>9E+119</t>
+  </si>
+  <si>
+    <t>512E+149</t>
+  </si>
+  <si>
+    <t>64E+53</t>
+  </si>
+  <si>
+    <t>64E+81</t>
+  </si>
+  <si>
+    <t>10189</t>
+  </si>
+  <si>
+    <t>1189</t>
+  </si>
+  <si>
+    <t>混沌蜈蚣王</t>
+  </si>
+  <si>
+    <t>9E+120</t>
+  </si>
+  <si>
+    <t>512E+150</t>
+  </si>
+  <si>
+    <t>64E+82</t>
+  </si>
+  <si>
+    <t>10190</t>
+  </si>
+  <si>
+    <t>1190</t>
+  </si>
+  <si>
+    <t>混沌钳虫王</t>
+  </si>
+  <si>
+    <t>9E+121</t>
+  </si>
+  <si>
+    <t>512E+151</t>
+  </si>
+  <si>
+    <t>64E+55</t>
+  </si>
+  <si>
+    <t>64E+83</t>
+  </si>
+  <si>
+    <t>10191</t>
+  </si>
+  <si>
+    <t>1191</t>
+  </si>
+  <si>
+    <t>混沌蠕虫王</t>
+  </si>
+  <si>
+    <t>9E+122</t>
+  </si>
+  <si>
+    <t>512E+152</t>
+  </si>
+  <si>
+    <t>64E+56</t>
+  </si>
+  <si>
+    <t>64E+84</t>
+  </si>
+  <si>
+    <t>10192</t>
+  </si>
+  <si>
+    <t>1192</t>
+  </si>
+  <si>
+    <t>混沌猪王</t>
+  </si>
+  <si>
+    <t>9E+123</t>
+  </si>
+  <si>
+    <t>512E+153</t>
+  </si>
+  <si>
+    <t>64E+57</t>
+  </si>
+  <si>
+    <t>64E+85</t>
+  </si>
+  <si>
+    <t>10193</t>
+  </si>
+  <si>
+    <t>1193</t>
+  </si>
+  <si>
+    <t>混沌猪皇</t>
+  </si>
+  <si>
+    <t>9E+124</t>
+  </si>
+  <si>
+    <t>512E+154</t>
+  </si>
+  <si>
+    <t>64E+58</t>
+  </si>
+  <si>
+    <t>64E+86</t>
+  </si>
+  <si>
+    <t>10194</t>
+  </si>
+  <si>
+    <t>1194</t>
+  </si>
+  <si>
+    <t>混沌蝎王</t>
+  </si>
+  <si>
+    <t>9E+125</t>
+  </si>
+  <si>
+    <t>512E+155</t>
+  </si>
+  <si>
+    <t>64E+59</t>
+  </si>
+  <si>
+    <t>64E+87</t>
+  </si>
+  <si>
+    <t>10195</t>
+  </si>
+  <si>
+    <t>1195</t>
+  </si>
+  <si>
+    <t>混沌恶魔教主</t>
+  </si>
+  <si>
+    <t>9E+126</t>
+  </si>
+  <si>
+    <t>512E+156</t>
+  </si>
+  <si>
+    <t>64E+60</t>
+  </si>
+  <si>
+    <t>64E+88</t>
+  </si>
+  <si>
+    <t>10196</t>
+  </si>
+  <si>
+    <t>1196</t>
+  </si>
+  <si>
+    <t>混沌恶魔教皇</t>
+  </si>
+  <si>
+    <t>9E+127</t>
+  </si>
+  <si>
+    <t>512E+157</t>
+  </si>
+  <si>
+    <t>64E+61</t>
+  </si>
+  <si>
+    <t>64E+89</t>
+  </si>
+  <si>
+    <t>10197</t>
+  </si>
+  <si>
+    <t>1197</t>
+  </si>
+  <si>
+    <t>混沌邪魔教主</t>
+  </si>
+  <si>
+    <t>9E+128</t>
+  </si>
+  <si>
+    <t>512E+158</t>
+  </si>
+  <si>
+    <t>64E+62</t>
+  </si>
+  <si>
+    <t>64E+90</t>
+  </si>
+  <si>
+    <t>10198</t>
+  </si>
+  <si>
+    <t>1198</t>
+  </si>
+  <si>
+    <t>混沌邪魔教皇</t>
+  </si>
+  <si>
+    <t>9E+129</t>
+  </si>
+  <si>
+    <t>512E+159</t>
+  </si>
+  <si>
+    <t>64E+63</t>
+  </si>
+  <si>
+    <t>64E+91</t>
+  </si>
+  <si>
+    <t>10199</t>
+  </si>
+  <si>
+    <t>1199</t>
+  </si>
+  <si>
+    <t>9E+130</t>
+  </si>
+  <si>
+    <t>512E+160</t>
+  </si>
+  <si>
+    <t>64E+64</t>
+  </si>
+  <si>
+    <t>64E+92</t>
+  </si>
+  <si>
+    <t>10200</t>
+  </si>
+  <si>
+    <t>1200</t>
+  </si>
+  <si>
+    <t>混沌烈焰王</t>
+  </si>
+  <si>
+    <t>9E+131</t>
+  </si>
+  <si>
+    <t>512E+161</t>
+  </si>
+  <si>
+    <t>64E+65</t>
+  </si>
+  <si>
+    <t>64E+93</t>
+  </si>
+  <si>
+    <t>10201</t>
+  </si>
+  <si>
+    <t>1201</t>
+  </si>
+  <si>
+    <t>混沌大邪王</t>
+  </si>
+  <si>
+    <t>9E+132</t>
+  </si>
+  <si>
+    <t>512E+162</t>
+  </si>
+  <si>
+    <t>64E+66</t>
+  </si>
+  <si>
+    <t>64E+94</t>
+  </si>
+  <si>
+    <t>10202</t>
+  </si>
+  <si>
+    <t>1202</t>
+  </si>
+  <si>
+    <t>混沌尸魔王</t>
+  </si>
+  <si>
+    <t>9E+133</t>
+  </si>
+  <si>
+    <t>512E+163</t>
+  </si>
+  <si>
+    <t>64E+95</t>
+  </si>
+  <si>
+    <t>10203</t>
+  </si>
+  <si>
+    <t>1203</t>
+  </si>
+  <si>
+    <t>混沌骨魔王</t>
+  </si>
+  <si>
+    <t>9E+134</t>
+  </si>
+  <si>
+    <t>512E+164</t>
+  </si>
+  <si>
+    <t>64E+96</t>
+  </si>
+  <si>
+    <t>10204</t>
+  </si>
+  <si>
+    <t>1204</t>
+  </si>
+  <si>
+    <t>混沌牛魔王</t>
+  </si>
+  <si>
+    <t>9E+135</t>
+  </si>
+  <si>
+    <t>512E+165</t>
+  </si>
+  <si>
+    <t>64E+97</t>
+  </si>
+  <si>
+    <t>10205</t>
+  </si>
+  <si>
+    <t>1205</t>
+  </si>
+  <si>
+    <t>混沌水龙王</t>
+  </si>
+  <si>
+    <t>9E+136</t>
+  </si>
+  <si>
+    <t>512E+166</t>
+  </si>
+  <si>
+    <t>64E+98</t>
+  </si>
+  <si>
+    <t>10206</t>
+  </si>
+  <si>
+    <t>1206</t>
+  </si>
+  <si>
+    <t>混沌土龙王</t>
+  </si>
+  <si>
+    <t>9E+137</t>
+  </si>
+  <si>
+    <t>512E+167</t>
+  </si>
+  <si>
+    <t>64E+99</t>
+  </si>
+  <si>
+    <t>10207</t>
+  </si>
+  <si>
+    <t>1207</t>
+  </si>
+  <si>
+    <t>混沌毒龙王</t>
+  </si>
+  <si>
+    <t>9E+138</t>
+  </si>
+  <si>
+    <t>512E+168</t>
+  </si>
+  <si>
+    <t>64E+100</t>
+  </si>
+  <si>
+    <t>10208</t>
+  </si>
+  <si>
+    <t>1208</t>
+  </si>
+  <si>
+    <t>混沌火龙王</t>
+  </si>
+  <si>
+    <t>9E+139</t>
+  </si>
+  <si>
+    <t>512E+169</t>
+  </si>
+  <si>
+    <t>64E+101</t>
+  </si>
+  <si>
+    <t>10209</t>
+  </si>
+  <si>
+    <t>1209</t>
+  </si>
+  <si>
+    <t>混沌冰龙王</t>
+  </si>
+  <si>
+    <t>9E+140</t>
+  </si>
+  <si>
+    <t>512E+170</t>
+  </si>
+  <si>
+    <t>64E+102</t>
   </si>
 </sst>
 </file>
@@ -4914,7 +5643,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y180"/>
+  <dimension ref="A1:Y215"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="5" customWidth="1"/>
@@ -14321,11 +15050,11 @@
         <v>0</v>
       </c>
       <c r="L141" s="1">
-        <f t="shared" ref="L141:L180" si="50">L140+600</f>
+        <f t="shared" ref="L141:L204" si="50">L140+600</f>
         <v>9700</v>
       </c>
       <c r="M141" s="1">
-        <f t="shared" ref="M141:M180" si="51">M140+600</f>
+        <f t="shared" ref="M141:M204" si="51">M140+600</f>
         <v>11300</v>
       </c>
       <c r="N141" s="1">
@@ -17142,6 +17871,2495 @@
       </c>
       <c r="X180" s="5"/>
       <c r="Y180" s="5"/>
+    </row>
+    <row r="181" s="3" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A181" s="13"/>
+      <c r="B181" s="13"/>
+      <c r="C181" s="19" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D181" s="19" t="s">
+        <v>1275</v>
+      </c>
+      <c r="E181" s="3">
+        <v>6</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="G181" s="26" t="s">
+        <v>1277</v>
+      </c>
+      <c r="H181" s="26" t="s">
+        <v>1278</v>
+      </c>
+      <c r="I181" s="26" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J181" s="26" t="s">
+        <v>1280</v>
+      </c>
+      <c r="K181" s="26" t="s">
+        <v>1281</v>
+      </c>
+      <c r="L181" s="3">
+        <f t="shared" si="50"/>
+        <v>33700</v>
+      </c>
+      <c r="M181" s="3">
+        <f t="shared" si="51"/>
+        <v>35300</v>
+      </c>
+      <c r="N181" s="3">
+        <f t="shared" ref="N181:N200" si="66">N180+250</f>
+        <v>15950</v>
+      </c>
+      <c r="O181" s="3">
+        <f t="shared" ref="O181:O200" si="67">O180+250</f>
+        <v>15950</v>
+      </c>
+      <c r="P181" s="13">
+        <f t="shared" ref="P181:P195" si="68">P180+3</f>
+        <v>242</v>
+      </c>
+      <c r="Q181" s="13">
+        <v>150</v>
+      </c>
+      <c r="R181" s="13">
+        <v>99.99</v>
+      </c>
+      <c r="S181" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T181" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V181" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="W181" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A182" s="5"/>
+      <c r="B182" s="5"/>
+      <c r="C182" s="19" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D182" s="19" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E182" s="1">
+        <v>6</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="G182" s="26" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H182" s="26" t="s">
+        <v>1286</v>
+      </c>
+      <c r="I182" s="26" t="s">
+        <v>1287</v>
+      </c>
+      <c r="J182" s="26" t="s">
+        <v>1288</v>
+      </c>
+      <c r="K182" s="26" t="s">
+        <v>1289</v>
+      </c>
+      <c r="L182" s="1">
+        <f t="shared" si="50"/>
+        <v>34300</v>
+      </c>
+      <c r="M182" s="1">
+        <f t="shared" si="51"/>
+        <v>35900</v>
+      </c>
+      <c r="N182" s="1">
+        <f t="shared" si="66"/>
+        <v>16200</v>
+      </c>
+      <c r="O182" s="1">
+        <f t="shared" si="67"/>
+        <v>16200</v>
+      </c>
+      <c r="P182" s="5">
+        <f t="shared" si="68"/>
+        <v>245</v>
+      </c>
+      <c r="Q182" s="5">
+        <f t="shared" ref="Q182:Q195" si="69">Q181+4</f>
+        <v>154</v>
+      </c>
+      <c r="R182" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S182" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T182" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V182" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W182" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A183" s="5"/>
+      <c r="B183" s="5"/>
+      <c r="C183" s="19" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D183" s="19" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E183" s="1">
+        <v>6</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="G183" s="26" t="s">
+        <v>1293</v>
+      </c>
+      <c r="H183" s="26" t="s">
+        <v>1294</v>
+      </c>
+      <c r="I183" s="26" t="s">
+        <v>1295</v>
+      </c>
+      <c r="J183" s="26" t="s">
+        <v>1296</v>
+      </c>
+      <c r="K183" s="26" t="s">
+        <v>1297</v>
+      </c>
+      <c r="L183" s="1">
+        <f t="shared" si="50"/>
+        <v>34900</v>
+      </c>
+      <c r="M183" s="1">
+        <f t="shared" si="51"/>
+        <v>36500</v>
+      </c>
+      <c r="N183" s="1">
+        <f t="shared" si="66"/>
+        <v>16450</v>
+      </c>
+      <c r="O183" s="1">
+        <f t="shared" si="67"/>
+        <v>16450</v>
+      </c>
+      <c r="P183" s="5">
+        <f t="shared" si="68"/>
+        <v>248</v>
+      </c>
+      <c r="Q183" s="5">
+        <f t="shared" si="69"/>
+        <v>158</v>
+      </c>
+      <c r="R183" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S183" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T183" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V183" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W183" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A184" s="5"/>
+      <c r="B184" s="5"/>
+      <c r="C184" s="19" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D184" s="19" t="s">
+        <v>1299</v>
+      </c>
+      <c r="E184" s="1">
+        <v>6</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="G184" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H184" s="26" t="s">
+        <v>1302</v>
+      </c>
+      <c r="I184" s="26" t="s">
+        <v>1303</v>
+      </c>
+      <c r="J184" s="26" t="s">
+        <v>1304</v>
+      </c>
+      <c r="K184" s="26" t="s">
+        <v>1305</v>
+      </c>
+      <c r="L184" s="1">
+        <f t="shared" si="50"/>
+        <v>35500</v>
+      </c>
+      <c r="M184" s="1">
+        <f t="shared" si="51"/>
+        <v>37100</v>
+      </c>
+      <c r="N184" s="1">
+        <f t="shared" si="66"/>
+        <v>16700</v>
+      </c>
+      <c r="O184" s="1">
+        <f t="shared" si="67"/>
+        <v>16700</v>
+      </c>
+      <c r="P184" s="5">
+        <f t="shared" si="68"/>
+        <v>251</v>
+      </c>
+      <c r="Q184" s="5">
+        <f t="shared" si="69"/>
+        <v>162</v>
+      </c>
+      <c r="R184" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S184" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T184" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V184" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W184" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A185" s="5"/>
+      <c r="B185" s="5"/>
+      <c r="C185" s="19" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D185" s="19" t="s">
+        <v>1307</v>
+      </c>
+      <c r="E185" s="1">
+        <v>6</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="G185" s="26" t="s">
+        <v>1309</v>
+      </c>
+      <c r="H185" s="26" t="s">
+        <v>1310</v>
+      </c>
+      <c r="I185" s="26" t="s">
+        <v>1311</v>
+      </c>
+      <c r="J185" s="26" t="s">
+        <v>1312</v>
+      </c>
+      <c r="K185" s="26" t="s">
+        <v>1313</v>
+      </c>
+      <c r="L185" s="1">
+        <f t="shared" si="50"/>
+        <v>36100</v>
+      </c>
+      <c r="M185" s="1">
+        <f t="shared" si="51"/>
+        <v>37700</v>
+      </c>
+      <c r="N185" s="1">
+        <f t="shared" si="66"/>
+        <v>16950</v>
+      </c>
+      <c r="O185" s="1">
+        <f t="shared" si="67"/>
+        <v>16950</v>
+      </c>
+      <c r="P185" s="5">
+        <f t="shared" si="68"/>
+        <v>254</v>
+      </c>
+      <c r="Q185" s="5">
+        <f t="shared" si="69"/>
+        <v>166</v>
+      </c>
+      <c r="R185" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S185" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T185" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V185" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W185" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A186" s="5"/>
+      <c r="B186" s="5"/>
+      <c r="C186" s="19" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D186" s="19" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E186" s="1">
+        <v>6</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G186" s="26" t="s">
+        <v>1317</v>
+      </c>
+      <c r="H186" s="26" t="s">
+        <v>1318</v>
+      </c>
+      <c r="I186" s="26" t="s">
+        <v>1319</v>
+      </c>
+      <c r="J186" s="26" t="s">
+        <v>1320</v>
+      </c>
+      <c r="K186" s="26" t="s">
+        <v>1321</v>
+      </c>
+      <c r="L186" s="1">
+        <f t="shared" si="50"/>
+        <v>36700</v>
+      </c>
+      <c r="M186" s="1">
+        <f t="shared" si="51"/>
+        <v>38300</v>
+      </c>
+      <c r="N186" s="1">
+        <f t="shared" si="66"/>
+        <v>17200</v>
+      </c>
+      <c r="O186" s="1">
+        <f t="shared" si="67"/>
+        <v>17200</v>
+      </c>
+      <c r="P186" s="5">
+        <f t="shared" si="68"/>
+        <v>257</v>
+      </c>
+      <c r="Q186" s="5">
+        <f t="shared" si="69"/>
+        <v>170</v>
+      </c>
+      <c r="R186" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S186" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T186" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V186" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W186" s="1">
+        <v>0</v>
+      </c>
+      <c r="X186" s="5"/>
+      <c r="Y186" s="5"/>
+    </row>
+    <row r="187" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A187" s="5"/>
+      <c r="B187" s="5"/>
+      <c r="C187" s="19" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D187" s="19" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E187" s="1">
+        <v>6</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G187" s="26" t="s">
+        <v>1325</v>
+      </c>
+      <c r="H187" s="26" t="s">
+        <v>1326</v>
+      </c>
+      <c r="I187" s="26" t="s">
+        <v>1327</v>
+      </c>
+      <c r="J187" s="26" t="s">
+        <v>1328</v>
+      </c>
+      <c r="K187" s="26" t="s">
+        <v>1329</v>
+      </c>
+      <c r="L187" s="1">
+        <f t="shared" si="50"/>
+        <v>37300</v>
+      </c>
+      <c r="M187" s="1">
+        <f t="shared" si="51"/>
+        <v>38900</v>
+      </c>
+      <c r="N187" s="1">
+        <f t="shared" si="66"/>
+        <v>17450</v>
+      </c>
+      <c r="O187" s="1">
+        <f t="shared" si="67"/>
+        <v>17450</v>
+      </c>
+      <c r="P187" s="5">
+        <f t="shared" si="68"/>
+        <v>260</v>
+      </c>
+      <c r="Q187" s="5">
+        <f t="shared" si="69"/>
+        <v>174</v>
+      </c>
+      <c r="R187" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S187" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T187" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V187" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W187" s="1">
+        <v>0</v>
+      </c>
+      <c r="X187" s="5"/>
+      <c r="Y187" s="5"/>
+    </row>
+    <row r="188" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A188" s="5"/>
+      <c r="B188" s="5"/>
+      <c r="C188" s="19" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D188" s="19" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E188" s="1">
+        <v>6</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>1332</v>
+      </c>
+      <c r="G188" s="26" t="s">
+        <v>1333</v>
+      </c>
+      <c r="H188" s="26" t="s">
+        <v>1334</v>
+      </c>
+      <c r="I188" s="26" t="s">
+        <v>1335</v>
+      </c>
+      <c r="J188" s="26" t="s">
+        <v>1336</v>
+      </c>
+      <c r="K188" s="26" t="s">
+        <v>1337</v>
+      </c>
+      <c r="L188" s="1">
+        <f t="shared" si="50"/>
+        <v>37900</v>
+      </c>
+      <c r="M188" s="1">
+        <f t="shared" si="51"/>
+        <v>39500</v>
+      </c>
+      <c r="N188" s="1">
+        <f t="shared" si="66"/>
+        <v>17700</v>
+      </c>
+      <c r="O188" s="1">
+        <f t="shared" si="67"/>
+        <v>17700</v>
+      </c>
+      <c r="P188" s="5">
+        <f t="shared" si="68"/>
+        <v>263</v>
+      </c>
+      <c r="Q188" s="5">
+        <f t="shared" si="69"/>
+        <v>178</v>
+      </c>
+      <c r="R188" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S188" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T188" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V188" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W188" s="1">
+        <v>0</v>
+      </c>
+      <c r="X188" s="5"/>
+      <c r="Y188" s="5"/>
+    </row>
+    <row r="189" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A189" s="5"/>
+      <c r="B189" s="5"/>
+      <c r="C189" s="19" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D189" s="19" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E189" s="1">
+        <v>6</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G189" s="26" t="s">
+        <v>1135</v>
+      </c>
+      <c r="H189" s="26" t="s">
+        <v>1341</v>
+      </c>
+      <c r="I189" s="26" t="s">
+        <v>1342</v>
+      </c>
+      <c r="J189" s="26" t="s">
+        <v>1343</v>
+      </c>
+      <c r="K189" s="26" t="s">
+        <v>1344</v>
+      </c>
+      <c r="L189" s="1">
+        <f t="shared" si="50"/>
+        <v>38500</v>
+      </c>
+      <c r="M189" s="1">
+        <f t="shared" si="51"/>
+        <v>40100</v>
+      </c>
+      <c r="N189" s="1">
+        <f t="shared" si="66"/>
+        <v>17950</v>
+      </c>
+      <c r="O189" s="1">
+        <f t="shared" si="67"/>
+        <v>17950</v>
+      </c>
+      <c r="P189" s="5">
+        <f t="shared" si="68"/>
+        <v>266</v>
+      </c>
+      <c r="Q189" s="5">
+        <f t="shared" si="69"/>
+        <v>182</v>
+      </c>
+      <c r="R189" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S189" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T189" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V189" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W189" s="1">
+        <v>0</v>
+      </c>
+      <c r="X189" s="5"/>
+      <c r="Y189" s="5"/>
+    </row>
+    <row r="190" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A190" s="5"/>
+      <c r="B190" s="5"/>
+      <c r="C190" s="19" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D190" s="19" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E190" s="1">
+        <v>6</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G190" s="26" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H190" s="26" t="s">
+        <v>1348</v>
+      </c>
+      <c r="I190" s="26" t="s">
+        <v>1349</v>
+      </c>
+      <c r="J190" s="26" t="s">
+        <v>1350</v>
+      </c>
+      <c r="K190" s="26" t="s">
+        <v>1351</v>
+      </c>
+      <c r="L190" s="1">
+        <f t="shared" si="50"/>
+        <v>39100</v>
+      </c>
+      <c r="M190" s="1">
+        <f t="shared" si="51"/>
+        <v>40700</v>
+      </c>
+      <c r="N190" s="1">
+        <f t="shared" si="66"/>
+        <v>18200</v>
+      </c>
+      <c r="O190" s="1">
+        <f t="shared" si="67"/>
+        <v>18200</v>
+      </c>
+      <c r="P190" s="5">
+        <f t="shared" si="68"/>
+        <v>269</v>
+      </c>
+      <c r="Q190" s="5">
+        <f t="shared" si="69"/>
+        <v>186</v>
+      </c>
+      <c r="R190" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S190" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T190" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V190" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W190" s="1">
+        <v>0</v>
+      </c>
+      <c r="X190" s="5"/>
+      <c r="Y190" s="5"/>
+    </row>
+    <row r="191" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A191" s="5"/>
+      <c r="B191" s="5"/>
+      <c r="C191" s="19" t="s">
+        <v>1352</v>
+      </c>
+      <c r="D191" s="19" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E191" s="1">
+        <v>6</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="G191" s="26" t="s">
+        <v>1153</v>
+      </c>
+      <c r="H191" s="26" t="s">
+        <v>1355</v>
+      </c>
+      <c r="I191" s="26" t="s">
+        <v>1356</v>
+      </c>
+      <c r="J191" s="26" t="s">
+        <v>1357</v>
+      </c>
+      <c r="K191" s="26" t="s">
+        <v>1358</v>
+      </c>
+      <c r="L191" s="1">
+        <f t="shared" si="50"/>
+        <v>39700</v>
+      </c>
+      <c r="M191" s="1">
+        <f t="shared" si="51"/>
+        <v>41300</v>
+      </c>
+      <c r="N191" s="1">
+        <f t="shared" si="66"/>
+        <v>18450</v>
+      </c>
+      <c r="O191" s="1">
+        <f t="shared" si="67"/>
+        <v>18450</v>
+      </c>
+      <c r="P191" s="5">
+        <f t="shared" si="68"/>
+        <v>272</v>
+      </c>
+      <c r="Q191" s="5">
+        <f t="shared" si="69"/>
+        <v>190</v>
+      </c>
+      <c r="R191" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S191" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T191" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V191" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W191" s="1">
+        <v>0</v>
+      </c>
+      <c r="X191" s="5"/>
+      <c r="Y191" s="5"/>
+    </row>
+    <row r="192" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A192" s="5"/>
+      <c r="B192" s="5"/>
+      <c r="C192" s="19" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D192" s="19" t="s">
+        <v>1360</v>
+      </c>
+      <c r="E192" s="1">
+        <v>6</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="G192" s="26" t="s">
+        <v>1162</v>
+      </c>
+      <c r="H192" s="26" t="s">
+        <v>1362</v>
+      </c>
+      <c r="I192" s="26" t="s">
+        <v>1363</v>
+      </c>
+      <c r="J192" s="26" t="s">
+        <v>1364</v>
+      </c>
+      <c r="K192" s="26" t="s">
+        <v>1365</v>
+      </c>
+      <c r="L192" s="1">
+        <f t="shared" si="50"/>
+        <v>40300</v>
+      </c>
+      <c r="M192" s="1">
+        <f t="shared" si="51"/>
+        <v>41900</v>
+      </c>
+      <c r="N192" s="1">
+        <f t="shared" si="66"/>
+        <v>18700</v>
+      </c>
+      <c r="O192" s="1">
+        <f t="shared" si="67"/>
+        <v>18700</v>
+      </c>
+      <c r="P192" s="5">
+        <f t="shared" si="68"/>
+        <v>275</v>
+      </c>
+      <c r="Q192" s="5">
+        <f t="shared" si="69"/>
+        <v>194</v>
+      </c>
+      <c r="R192" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S192" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T192" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V192" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W192" s="1">
+        <v>0</v>
+      </c>
+      <c r="X192" s="5"/>
+      <c r="Y192" s="5"/>
+    </row>
+    <row r="193" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A193" s="5"/>
+      <c r="B193" s="5"/>
+      <c r="C193" s="19" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D193" s="19" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E193" s="1">
+        <v>6</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G193" s="26" t="s">
+        <v>1171</v>
+      </c>
+      <c r="H193" s="26" t="s">
+        <v>1369</v>
+      </c>
+      <c r="I193" s="26" t="s">
+        <v>1370</v>
+      </c>
+      <c r="J193" s="26" t="s">
+        <v>1371</v>
+      </c>
+      <c r="K193" s="26" t="s">
+        <v>1372</v>
+      </c>
+      <c r="L193" s="1">
+        <f t="shared" si="50"/>
+        <v>40900</v>
+      </c>
+      <c r="M193" s="1">
+        <f t="shared" si="51"/>
+        <v>42500</v>
+      </c>
+      <c r="N193" s="1">
+        <f t="shared" si="66"/>
+        <v>18950</v>
+      </c>
+      <c r="O193" s="1">
+        <f t="shared" si="67"/>
+        <v>18950</v>
+      </c>
+      <c r="P193" s="5">
+        <f t="shared" si="68"/>
+        <v>278</v>
+      </c>
+      <c r="Q193" s="5">
+        <f t="shared" si="69"/>
+        <v>198</v>
+      </c>
+      <c r="R193" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S193" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T193" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V193" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W193" s="1">
+        <v>0</v>
+      </c>
+      <c r="X193" s="5"/>
+      <c r="Y193" s="5"/>
+    </row>
+    <row r="194" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A194" s="5"/>
+      <c r="B194" s="5"/>
+      <c r="C194" s="19" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D194" s="19" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E194" s="1">
+        <v>6</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G194" s="26" t="s">
+        <v>1179</v>
+      </c>
+      <c r="H194" s="26" t="s">
+        <v>1376</v>
+      </c>
+      <c r="I194" s="26" t="s">
+        <v>1377</v>
+      </c>
+      <c r="J194" s="26" t="s">
+        <v>1378</v>
+      </c>
+      <c r="K194" s="26" t="s">
+        <v>1379</v>
+      </c>
+      <c r="L194" s="1">
+        <f t="shared" si="50"/>
+        <v>41500</v>
+      </c>
+      <c r="M194" s="1">
+        <f t="shared" si="51"/>
+        <v>43100</v>
+      </c>
+      <c r="N194" s="1">
+        <f t="shared" si="66"/>
+        <v>19200</v>
+      </c>
+      <c r="O194" s="1">
+        <f t="shared" si="67"/>
+        <v>19200</v>
+      </c>
+      <c r="P194" s="5">
+        <f t="shared" si="68"/>
+        <v>281</v>
+      </c>
+      <c r="Q194" s="5">
+        <f t="shared" si="69"/>
+        <v>202</v>
+      </c>
+      <c r="R194" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S194" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T194" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V194" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W194" s="1">
+        <v>0</v>
+      </c>
+      <c r="X194" s="5"/>
+      <c r="Y194" s="5"/>
+    </row>
+    <row r="195" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A195" s="5"/>
+      <c r="B195" s="5"/>
+      <c r="C195" s="19" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D195" s="19" t="s">
+        <v>1381</v>
+      </c>
+      <c r="E195" s="1">
+        <v>6</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G195" s="26" t="s">
+        <v>1188</v>
+      </c>
+      <c r="H195" s="26" t="s">
+        <v>1383</v>
+      </c>
+      <c r="I195" s="26" t="s">
+        <v>1384</v>
+      </c>
+      <c r="J195" s="26" t="s">
+        <v>1182</v>
+      </c>
+      <c r="K195" s="26" t="s">
+        <v>1385</v>
+      </c>
+      <c r="L195" s="1">
+        <f t="shared" si="50"/>
+        <v>42100</v>
+      </c>
+      <c r="M195" s="1">
+        <f t="shared" si="51"/>
+        <v>43700</v>
+      </c>
+      <c r="N195" s="1">
+        <f t="shared" si="66"/>
+        <v>19450</v>
+      </c>
+      <c r="O195" s="1">
+        <f t="shared" si="67"/>
+        <v>19450</v>
+      </c>
+      <c r="P195" s="5">
+        <f t="shared" si="68"/>
+        <v>284</v>
+      </c>
+      <c r="Q195" s="5">
+        <f t="shared" si="69"/>
+        <v>206</v>
+      </c>
+      <c r="R195" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S195" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T195" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V195" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W195" s="1">
+        <v>0</v>
+      </c>
+      <c r="X195" s="5"/>
+      <c r="Y195" s="5"/>
+    </row>
+    <row r="196" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A196" s="5"/>
+      <c r="B196" s="5"/>
+      <c r="C196" s="19" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D196" s="19" t="s">
+        <v>1387</v>
+      </c>
+      <c r="E196" s="1">
+        <v>6</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="G196" s="26" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H196" s="26" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I196" s="26" t="s">
+        <v>1390</v>
+      </c>
+      <c r="J196" s="26" t="s">
+        <v>1391</v>
+      </c>
+      <c r="K196" s="26" t="s">
+        <v>1392</v>
+      </c>
+      <c r="L196" s="1">
+        <f t="shared" si="50"/>
+        <v>42700</v>
+      </c>
+      <c r="M196" s="1">
+        <f t="shared" si="51"/>
+        <v>44300</v>
+      </c>
+      <c r="N196" s="1">
+        <f t="shared" si="66"/>
+        <v>19700</v>
+      </c>
+      <c r="O196" s="1">
+        <f t="shared" si="67"/>
+        <v>19700</v>
+      </c>
+      <c r="P196" s="5">
+        <f t="shared" ref="P196:P200" si="70">P195+4</f>
+        <v>288</v>
+      </c>
+      <c r="Q196" s="5">
+        <f t="shared" ref="Q196:Q200" si="71">Q195+5</f>
+        <v>211</v>
+      </c>
+      <c r="R196" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S196" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T196" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V196" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W196" s="1">
+        <v>0</v>
+      </c>
+      <c r="X196" s="5"/>
+      <c r="Y196" s="5"/>
+    </row>
+    <row r="197" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A197" s="5"/>
+      <c r="B197" s="5"/>
+      <c r="C197" s="19" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D197" s="19" t="s">
+        <v>1394</v>
+      </c>
+      <c r="E197" s="1">
+        <v>6</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G197" s="26" t="s">
+        <v>1206</v>
+      </c>
+      <c r="H197" s="26" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I197" s="26" t="s">
+        <v>1397</v>
+      </c>
+      <c r="J197" s="26" t="s">
+        <v>1398</v>
+      </c>
+      <c r="K197" s="26" t="s">
+        <v>1399</v>
+      </c>
+      <c r="L197" s="1">
+        <f t="shared" si="50"/>
+        <v>43300</v>
+      </c>
+      <c r="M197" s="1">
+        <f t="shared" si="51"/>
+        <v>44900</v>
+      </c>
+      <c r="N197" s="1">
+        <f t="shared" si="66"/>
+        <v>19950</v>
+      </c>
+      <c r="O197" s="1">
+        <f t="shared" si="67"/>
+        <v>19950</v>
+      </c>
+      <c r="P197" s="5">
+        <f t="shared" si="70"/>
+        <v>292</v>
+      </c>
+      <c r="Q197" s="5">
+        <f t="shared" si="71"/>
+        <v>216</v>
+      </c>
+      <c r="R197" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S197" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T197" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V197" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W197" s="1">
+        <v>0</v>
+      </c>
+      <c r="X197" s="5"/>
+      <c r="Y197" s="5"/>
+    </row>
+    <row r="198" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A198" s="5"/>
+      <c r="B198" s="5"/>
+      <c r="C198" s="19" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D198" s="19" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E198" s="1">
+        <v>6</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G198" s="26" t="s">
+        <v>1215</v>
+      </c>
+      <c r="H198" s="26" t="s">
+        <v>1403</v>
+      </c>
+      <c r="I198" s="26" t="s">
+        <v>1404</v>
+      </c>
+      <c r="J198" s="26" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K198" s="26" t="s">
+        <v>1406</v>
+      </c>
+      <c r="L198" s="1">
+        <f t="shared" si="50"/>
+        <v>43900</v>
+      </c>
+      <c r="M198" s="1">
+        <f t="shared" si="51"/>
+        <v>45500</v>
+      </c>
+      <c r="N198" s="1">
+        <f t="shared" si="66"/>
+        <v>20200</v>
+      </c>
+      <c r="O198" s="1">
+        <f t="shared" si="67"/>
+        <v>20200</v>
+      </c>
+      <c r="P198" s="5">
+        <f t="shared" si="70"/>
+        <v>296</v>
+      </c>
+      <c r="Q198" s="5">
+        <f t="shared" si="71"/>
+        <v>221</v>
+      </c>
+      <c r="R198" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S198" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T198" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V198" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W198" s="1">
+        <v>0</v>
+      </c>
+      <c r="X198" s="5"/>
+      <c r="Y198" s="5"/>
+    </row>
+    <row r="199" s="4" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A199" s="15"/>
+      <c r="B199" s="15"/>
+      <c r="C199" s="19" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D199" s="19" t="s">
+        <v>1408</v>
+      </c>
+      <c r="E199" s="1">
+        <v>6</v>
+      </c>
+      <c r="F199" s="4" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G199" s="26" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H199" s="26" t="s">
+        <v>1410</v>
+      </c>
+      <c r="I199" s="26" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J199" s="26" t="s">
+        <v>1412</v>
+      </c>
+      <c r="K199" s="26" t="s">
+        <v>1413</v>
+      </c>
+      <c r="L199" s="4">
+        <f t="shared" si="50"/>
+        <v>44500</v>
+      </c>
+      <c r="M199" s="4">
+        <f t="shared" si="51"/>
+        <v>46100</v>
+      </c>
+      <c r="N199" s="4">
+        <f t="shared" si="66"/>
+        <v>20450</v>
+      </c>
+      <c r="O199" s="4">
+        <f t="shared" si="67"/>
+        <v>20450</v>
+      </c>
+      <c r="P199" s="15">
+        <f t="shared" si="70"/>
+        <v>300</v>
+      </c>
+      <c r="Q199" s="15">
+        <f t="shared" si="71"/>
+        <v>226</v>
+      </c>
+      <c r="R199" s="15">
+        <v>99.99</v>
+      </c>
+      <c r="S199" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T199" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V199" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="W199" s="4">
+        <v>0</v>
+      </c>
+      <c r="X199" s="15"/>
+      <c r="Y199" s="15"/>
+    </row>
+    <row r="200" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A200" s="5"/>
+      <c r="B200" s="5"/>
+      <c r="C200" s="19" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D200" s="19" t="s">
+        <v>1415</v>
+      </c>
+      <c r="E200" s="1">
+        <v>6</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="G200" s="26" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H200" s="26" t="s">
+        <v>1417</v>
+      </c>
+      <c r="I200" s="26" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J200" s="26" t="s">
+        <v>1419</v>
+      </c>
+      <c r="K200" s="26" t="s">
+        <v>1420</v>
+      </c>
+      <c r="L200" s="1">
+        <f t="shared" si="50"/>
+        <v>45100</v>
+      </c>
+      <c r="M200" s="1">
+        <f t="shared" si="51"/>
+        <v>46700</v>
+      </c>
+      <c r="N200" s="1">
+        <f t="shared" si="66"/>
+        <v>20700</v>
+      </c>
+      <c r="O200" s="1">
+        <f t="shared" si="67"/>
+        <v>20700</v>
+      </c>
+      <c r="P200" s="5">
+        <f t="shared" si="70"/>
+        <v>304</v>
+      </c>
+      <c r="Q200" s="5">
+        <f t="shared" si="71"/>
+        <v>231</v>
+      </c>
+      <c r="R200" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S200" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T200" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V200" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W200" s="1">
+        <v>0</v>
+      </c>
+      <c r="X200" s="5"/>
+      <c r="Y200" s="5"/>
+    </row>
+    <row r="201" customHeight="1" spans="3:23">
+      <c r="C201" s="19" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D201" s="19" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E201" s="1">
+        <v>6</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G201" s="26" t="s">
+        <v>1242</v>
+      </c>
+      <c r="H201" s="26" t="s">
+        <v>1424</v>
+      </c>
+      <c r="I201" s="26" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J201" s="26" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K201" s="26" t="s">
+        <v>1427</v>
+      </c>
+      <c r="L201" s="1">
+        <f t="shared" si="50"/>
+        <v>45700</v>
+      </c>
+      <c r="M201" s="1">
+        <f t="shared" si="51"/>
+        <v>47300</v>
+      </c>
+      <c r="N201" s="1">
+        <f t="shared" ref="N201:N205" si="72">N200+300</f>
+        <v>21000</v>
+      </c>
+      <c r="O201" s="1">
+        <f t="shared" ref="O201:O205" si="73">O200+300</f>
+        <v>21000</v>
+      </c>
+      <c r="P201" s="5">
+        <f t="shared" ref="P201:P205" si="74">P200+5</f>
+        <v>309</v>
+      </c>
+      <c r="Q201" s="5">
+        <f t="shared" ref="Q201:Q205" si="75">Q200+6</f>
+        <v>237</v>
+      </c>
+      <c r="R201" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S201" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T201" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V201" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W201" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" spans="3:23">
+      <c r="C202" s="19" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D202" s="19" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E202" s="1">
+        <v>6</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>1430</v>
+      </c>
+      <c r="G202" s="26" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H202" s="26" t="s">
+        <v>1431</v>
+      </c>
+      <c r="I202" s="26" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J202" s="26" t="s">
+        <v>1433</v>
+      </c>
+      <c r="K202" s="26" t="s">
+        <v>1434</v>
+      </c>
+      <c r="L202" s="1">
+        <f t="shared" si="50"/>
+        <v>46300</v>
+      </c>
+      <c r="M202" s="1">
+        <f t="shared" si="51"/>
+        <v>47900</v>
+      </c>
+      <c r="N202" s="1">
+        <f t="shared" si="72"/>
+        <v>21300</v>
+      </c>
+      <c r="O202" s="1">
+        <f t="shared" si="73"/>
+        <v>21300</v>
+      </c>
+      <c r="P202" s="5">
+        <f t="shared" si="74"/>
+        <v>314</v>
+      </c>
+      <c r="Q202" s="5">
+        <f t="shared" si="75"/>
+        <v>243</v>
+      </c>
+      <c r="R202" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S202" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T202" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V202" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W202" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" spans="3:23">
+      <c r="C203" s="19" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D203" s="19" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E203" s="1">
+        <v>6</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="G203" s="26" t="s">
+        <v>1260</v>
+      </c>
+      <c r="H203" s="26" t="s">
+        <v>1438</v>
+      </c>
+      <c r="I203" s="26" t="s">
+        <v>1439</v>
+      </c>
+      <c r="J203" s="26" t="s">
+        <v>1440</v>
+      </c>
+      <c r="K203" s="26" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L203" s="1">
+        <f t="shared" si="50"/>
+        <v>46900</v>
+      </c>
+      <c r="M203" s="1">
+        <f t="shared" si="51"/>
+        <v>48500</v>
+      </c>
+      <c r="N203" s="1">
+        <f t="shared" si="72"/>
+        <v>21600</v>
+      </c>
+      <c r="O203" s="1">
+        <f t="shared" si="73"/>
+        <v>21600</v>
+      </c>
+      <c r="P203" s="5">
+        <f t="shared" si="74"/>
+        <v>319</v>
+      </c>
+      <c r="Q203" s="5">
+        <f t="shared" si="75"/>
+        <v>249</v>
+      </c>
+      <c r="R203" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S203" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T203" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V203" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W203" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" spans="3:23">
+      <c r="C204" s="19" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D204" s="19" t="s">
+        <v>1443</v>
+      </c>
+      <c r="E204" s="1">
+        <v>6</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="G204" s="26" t="s">
+        <v>1269</v>
+      </c>
+      <c r="H204" s="26" t="s">
+        <v>1445</v>
+      </c>
+      <c r="I204" s="26" t="s">
+        <v>1446</v>
+      </c>
+      <c r="J204" s="26" t="s">
+        <v>1447</v>
+      </c>
+      <c r="K204" s="26" t="s">
+        <v>1448</v>
+      </c>
+      <c r="L204" s="1">
+        <f t="shared" si="50"/>
+        <v>47500</v>
+      </c>
+      <c r="M204" s="1">
+        <f t="shared" si="51"/>
+        <v>49100</v>
+      </c>
+      <c r="N204" s="1">
+        <f t="shared" si="72"/>
+        <v>21900</v>
+      </c>
+      <c r="O204" s="1">
+        <f t="shared" si="73"/>
+        <v>21900</v>
+      </c>
+      <c r="P204" s="5">
+        <f t="shared" si="74"/>
+        <v>324</v>
+      </c>
+      <c r="Q204" s="5">
+        <f t="shared" si="75"/>
+        <v>255</v>
+      </c>
+      <c r="R204" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S204" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T204" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V204" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W204" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" spans="3:23">
+      <c r="C205" s="19" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D205" s="19" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E205" s="1">
+        <v>6</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="G205" s="26" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H205" s="26" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I205" s="26" t="s">
+        <v>1452</v>
+      </c>
+      <c r="J205" s="26" t="s">
+        <v>1453</v>
+      </c>
+      <c r="K205" s="26" t="s">
+        <v>1454</v>
+      </c>
+      <c r="L205" s="1">
+        <f t="shared" ref="L205:L215" si="76">L204+600</f>
+        <v>48100</v>
+      </c>
+      <c r="M205" s="1">
+        <f t="shared" ref="M205:M215" si="77">M204+600</f>
+        <v>49700</v>
+      </c>
+      <c r="N205" s="1">
+        <f t="shared" si="72"/>
+        <v>22200</v>
+      </c>
+      <c r="O205" s="1">
+        <f t="shared" si="73"/>
+        <v>22200</v>
+      </c>
+      <c r="P205" s="5">
+        <f t="shared" si="74"/>
+        <v>329</v>
+      </c>
+      <c r="Q205" s="5">
+        <f t="shared" si="75"/>
+        <v>261</v>
+      </c>
+      <c r="R205" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S205" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T205" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V205" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W205" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A206" s="5"/>
+      <c r="B206" s="5"/>
+      <c r="C206" s="19" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D206" s="19" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E206" s="1">
+        <v>6</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="G206" s="26" t="s">
+        <v>1286</v>
+      </c>
+      <c r="H206" s="26" t="s">
+        <v>1458</v>
+      </c>
+      <c r="I206" s="26" t="s">
+        <v>1459</v>
+      </c>
+      <c r="J206" s="26" t="s">
+        <v>1460</v>
+      </c>
+      <c r="K206" s="26" t="s">
+        <v>1461</v>
+      </c>
+      <c r="L206" s="1">
+        <f t="shared" si="76"/>
+        <v>48700</v>
+      </c>
+      <c r="M206" s="1">
+        <f t="shared" si="77"/>
+        <v>50300</v>
+      </c>
+      <c r="N206" s="1">
+        <f t="shared" ref="N206:N210" si="78">N205+400</f>
+        <v>22600</v>
+      </c>
+      <c r="O206" s="1">
+        <f t="shared" ref="O206:O210" si="79">O205+400</f>
+        <v>22600</v>
+      </c>
+      <c r="P206" s="5">
+        <f t="shared" ref="P206:P210" si="80">P205+6</f>
+        <v>335</v>
+      </c>
+      <c r="Q206" s="5">
+        <f t="shared" ref="Q206:Q210" si="81">Q205+7</f>
+        <v>268</v>
+      </c>
+      <c r="R206" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S206" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T206" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V206" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W206" s="1">
+        <v>0</v>
+      </c>
+      <c r="X206" s="5"/>
+      <c r="Y206" s="5"/>
+    </row>
+    <row r="207" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A207" s="5"/>
+      <c r="B207" s="5"/>
+      <c r="C207" s="19" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D207" s="19" t="s">
+        <v>1463</v>
+      </c>
+      <c r="E207" s="1">
+        <v>6</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G207" s="26" t="s">
+        <v>1294</v>
+      </c>
+      <c r="H207" s="26" t="s">
+        <v>1465</v>
+      </c>
+      <c r="I207" s="26" t="s">
+        <v>1466</v>
+      </c>
+      <c r="J207" s="26" t="s">
+        <v>1467</v>
+      </c>
+      <c r="K207" s="26" t="s">
+        <v>1468</v>
+      </c>
+      <c r="L207" s="1">
+        <f t="shared" si="76"/>
+        <v>49300</v>
+      </c>
+      <c r="M207" s="1">
+        <f t="shared" si="77"/>
+        <v>50900</v>
+      </c>
+      <c r="N207" s="1">
+        <f t="shared" si="78"/>
+        <v>23000</v>
+      </c>
+      <c r="O207" s="1">
+        <f t="shared" si="79"/>
+        <v>23000</v>
+      </c>
+      <c r="P207" s="5">
+        <f t="shared" si="80"/>
+        <v>341</v>
+      </c>
+      <c r="Q207" s="5">
+        <f t="shared" si="81"/>
+        <v>275</v>
+      </c>
+      <c r="R207" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S207" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T207" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V207" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W207" s="1">
+        <v>0</v>
+      </c>
+      <c r="X207" s="5"/>
+      <c r="Y207" s="5"/>
+    </row>
+    <row r="208" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A208" s="5"/>
+      <c r="B208" s="5"/>
+      <c r="C208" s="19" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D208" s="19" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E208" s="1">
+        <v>6</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>1471</v>
+      </c>
+      <c r="G208" s="26" t="s">
+        <v>1302</v>
+      </c>
+      <c r="H208" s="26" t="s">
+        <v>1472</v>
+      </c>
+      <c r="I208" s="26" t="s">
+        <v>1473</v>
+      </c>
+      <c r="J208" s="26" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K208" s="26" t="s">
+        <v>1474</v>
+      </c>
+      <c r="L208" s="1">
+        <f t="shared" si="76"/>
+        <v>49900</v>
+      </c>
+      <c r="M208" s="1">
+        <f t="shared" si="77"/>
+        <v>51500</v>
+      </c>
+      <c r="N208" s="1">
+        <f t="shared" si="78"/>
+        <v>23400</v>
+      </c>
+      <c r="O208" s="1">
+        <f t="shared" si="79"/>
+        <v>23400</v>
+      </c>
+      <c r="P208" s="5">
+        <f t="shared" si="80"/>
+        <v>347</v>
+      </c>
+      <c r="Q208" s="5">
+        <f t="shared" si="81"/>
+        <v>282</v>
+      </c>
+      <c r="R208" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S208" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T208" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V208" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W208" s="1">
+        <v>0</v>
+      </c>
+      <c r="X208" s="5"/>
+      <c r="Y208" s="5"/>
+    </row>
+    <row r="209" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A209" s="5"/>
+      <c r="B209" s="5"/>
+      <c r="C209" s="19" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D209" s="19" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E209" s="1">
+        <v>6</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G209" s="26" t="s">
+        <v>1310</v>
+      </c>
+      <c r="H209" s="26" t="s">
+        <v>1478</v>
+      </c>
+      <c r="I209" s="26" t="s">
+        <v>1479</v>
+      </c>
+      <c r="J209" s="26" t="s">
+        <v>1281</v>
+      </c>
+      <c r="K209" s="26" t="s">
+        <v>1480</v>
+      </c>
+      <c r="L209" s="1">
+        <f t="shared" si="76"/>
+        <v>50500</v>
+      </c>
+      <c r="M209" s="1">
+        <f t="shared" si="77"/>
+        <v>52100</v>
+      </c>
+      <c r="N209" s="1">
+        <f t="shared" si="78"/>
+        <v>23800</v>
+      </c>
+      <c r="O209" s="1">
+        <f t="shared" si="79"/>
+        <v>23800</v>
+      </c>
+      <c r="P209" s="5">
+        <f t="shared" si="80"/>
+        <v>353</v>
+      </c>
+      <c r="Q209" s="5">
+        <f t="shared" si="81"/>
+        <v>289</v>
+      </c>
+      <c r="R209" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S209" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T209" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V209" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W209" s="1">
+        <v>0</v>
+      </c>
+      <c r="X209" s="5"/>
+      <c r="Y209" s="5"/>
+    </row>
+    <row r="210" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A210" s="5"/>
+      <c r="B210" s="5"/>
+      <c r="C210" s="19" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D210" s="19" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E210" s="1">
+        <v>6</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="G210" s="26" t="s">
+        <v>1318</v>
+      </c>
+      <c r="H210" s="26" t="s">
+        <v>1484</v>
+      </c>
+      <c r="I210" s="26" t="s">
+        <v>1485</v>
+      </c>
+      <c r="J210" s="26" t="s">
+        <v>1289</v>
+      </c>
+      <c r="K210" s="26" t="s">
+        <v>1486</v>
+      </c>
+      <c r="L210" s="1">
+        <f t="shared" si="76"/>
+        <v>51100</v>
+      </c>
+      <c r="M210" s="1">
+        <f t="shared" si="77"/>
+        <v>52700</v>
+      </c>
+      <c r="N210" s="1">
+        <f t="shared" si="78"/>
+        <v>24200</v>
+      </c>
+      <c r="O210" s="1">
+        <f t="shared" si="79"/>
+        <v>24200</v>
+      </c>
+      <c r="P210" s="5">
+        <f t="shared" si="80"/>
+        <v>359</v>
+      </c>
+      <c r="Q210" s="5">
+        <f t="shared" si="81"/>
+        <v>296</v>
+      </c>
+      <c r="R210" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S210" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T210" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V210" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W210" s="1">
+        <v>0</v>
+      </c>
+      <c r="X210" s="5"/>
+      <c r="Y210" s="5"/>
+    </row>
+    <row r="211" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A211" s="5"/>
+      <c r="B211" s="5"/>
+      <c r="C211" s="19" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D211" s="19" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E211" s="1">
+        <v>6</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>1489</v>
+      </c>
+      <c r="G211" s="26" t="s">
+        <v>1326</v>
+      </c>
+      <c r="H211" s="26" t="s">
+        <v>1490</v>
+      </c>
+      <c r="I211" s="26" t="s">
+        <v>1491</v>
+      </c>
+      <c r="J211" s="26" t="s">
+        <v>1297</v>
+      </c>
+      <c r="K211" s="26" t="s">
+        <v>1492</v>
+      </c>
+      <c r="L211" s="1">
+        <f t="shared" si="76"/>
+        <v>51700</v>
+      </c>
+      <c r="M211" s="1">
+        <f t="shared" si="77"/>
+        <v>53300</v>
+      </c>
+      <c r="N211" s="1">
+        <f t="shared" ref="N211:N215" si="82">N210+500</f>
+        <v>24700</v>
+      </c>
+      <c r="O211" s="1">
+        <f t="shared" ref="O211:O215" si="83">O210+500</f>
+        <v>24700</v>
+      </c>
+      <c r="P211" s="5">
+        <f t="shared" ref="P211:P215" si="84">P210+7</f>
+        <v>366</v>
+      </c>
+      <c r="Q211" s="5">
+        <f t="shared" ref="Q211:Q215" si="85">Q210+8</f>
+        <v>304</v>
+      </c>
+      <c r="R211" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S211" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T211" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V211" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W211" s="1">
+        <v>0</v>
+      </c>
+      <c r="X211" s="5"/>
+      <c r="Y211" s="5"/>
+    </row>
+    <row r="212" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A212" s="5"/>
+      <c r="B212" s="5"/>
+      <c r="C212" s="19" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D212" s="19" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E212" s="1">
+        <v>6</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G212" s="26" t="s">
+        <v>1334</v>
+      </c>
+      <c r="H212" s="26" t="s">
+        <v>1496</v>
+      </c>
+      <c r="I212" s="26" t="s">
+        <v>1497</v>
+      </c>
+      <c r="J212" s="26" t="s">
+        <v>1305</v>
+      </c>
+      <c r="K212" s="26" t="s">
+        <v>1498</v>
+      </c>
+      <c r="L212" s="1">
+        <f t="shared" si="76"/>
+        <v>52300</v>
+      </c>
+      <c r="M212" s="1">
+        <f t="shared" si="77"/>
+        <v>53900</v>
+      </c>
+      <c r="N212" s="1">
+        <f t="shared" si="82"/>
+        <v>25200</v>
+      </c>
+      <c r="O212" s="1">
+        <f t="shared" si="83"/>
+        <v>25200</v>
+      </c>
+      <c r="P212" s="5">
+        <f t="shared" si="84"/>
+        <v>373</v>
+      </c>
+      <c r="Q212" s="5">
+        <f t="shared" si="85"/>
+        <v>312</v>
+      </c>
+      <c r="R212" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S212" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T212" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V212" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W212" s="1">
+        <v>0</v>
+      </c>
+      <c r="X212" s="5"/>
+      <c r="Y212" s="5"/>
+    </row>
+    <row r="213" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A213" s="5"/>
+      <c r="B213" s="5"/>
+      <c r="C213" s="19" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D213" s="19" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E213" s="1">
+        <v>6</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>1501</v>
+      </c>
+      <c r="G213" s="26" t="s">
+        <v>1341</v>
+      </c>
+      <c r="H213" s="26" t="s">
+        <v>1502</v>
+      </c>
+      <c r="I213" s="26" t="s">
+        <v>1503</v>
+      </c>
+      <c r="J213" s="26" t="s">
+        <v>1313</v>
+      </c>
+      <c r="K213" s="26" t="s">
+        <v>1504</v>
+      </c>
+      <c r="L213" s="1">
+        <f t="shared" si="76"/>
+        <v>52900</v>
+      </c>
+      <c r="M213" s="1">
+        <f t="shared" si="77"/>
+        <v>54500</v>
+      </c>
+      <c r="N213" s="1">
+        <f t="shared" si="82"/>
+        <v>25700</v>
+      </c>
+      <c r="O213" s="1">
+        <f t="shared" si="83"/>
+        <v>25700</v>
+      </c>
+      <c r="P213" s="5">
+        <f t="shared" si="84"/>
+        <v>380</v>
+      </c>
+      <c r="Q213" s="5">
+        <f t="shared" si="85"/>
+        <v>320</v>
+      </c>
+      <c r="R213" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S213" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T213" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V213" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W213" s="1">
+        <v>0</v>
+      </c>
+      <c r="X213" s="5"/>
+      <c r="Y213" s="5"/>
+    </row>
+    <row r="214" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A214" s="5"/>
+      <c r="B214" s="5"/>
+      <c r="C214" s="19" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D214" s="19" t="s">
+        <v>1506</v>
+      </c>
+      <c r="E214" s="1">
+        <v>6</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>1507</v>
+      </c>
+      <c r="G214" s="26" t="s">
+        <v>1348</v>
+      </c>
+      <c r="H214" s="26" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I214" s="26" t="s">
+        <v>1509</v>
+      </c>
+      <c r="J214" s="26" t="s">
+        <v>1321</v>
+      </c>
+      <c r="K214" s="26" t="s">
+        <v>1510</v>
+      </c>
+      <c r="L214" s="1">
+        <f t="shared" si="76"/>
+        <v>53500</v>
+      </c>
+      <c r="M214" s="1">
+        <f t="shared" si="77"/>
+        <v>55100</v>
+      </c>
+      <c r="N214" s="1">
+        <f t="shared" si="82"/>
+        <v>26200</v>
+      </c>
+      <c r="O214" s="1">
+        <f t="shared" si="83"/>
+        <v>26200</v>
+      </c>
+      <c r="P214" s="5">
+        <f t="shared" si="84"/>
+        <v>387</v>
+      </c>
+      <c r="Q214" s="5">
+        <f t="shared" si="85"/>
+        <v>328</v>
+      </c>
+      <c r="R214" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S214" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T214" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V214" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W214" s="1">
+        <v>0</v>
+      </c>
+      <c r="X214" s="5"/>
+      <c r="Y214" s="5"/>
+    </row>
+    <row r="215" s="1" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A215" s="5"/>
+      <c r="B215" s="5"/>
+      <c r="C215" s="19" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D215" s="19" t="s">
+        <v>1512</v>
+      </c>
+      <c r="E215" s="1">
+        <v>6</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="G215" s="26" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H215" s="26" t="s">
+        <v>1514</v>
+      </c>
+      <c r="I215" s="26" t="s">
+        <v>1515</v>
+      </c>
+      <c r="J215" s="26" t="s">
+        <v>1329</v>
+      </c>
+      <c r="K215" s="26" t="s">
+        <v>1516</v>
+      </c>
+      <c r="L215" s="1">
+        <f t="shared" si="76"/>
+        <v>54100</v>
+      </c>
+      <c r="M215" s="1">
+        <f t="shared" si="77"/>
+        <v>55700</v>
+      </c>
+      <c r="N215" s="1">
+        <f t="shared" si="82"/>
+        <v>26700</v>
+      </c>
+      <c r="O215" s="1">
+        <f t="shared" si="83"/>
+        <v>26700</v>
+      </c>
+      <c r="P215" s="5">
+        <f t="shared" si="84"/>
+        <v>394</v>
+      </c>
+      <c r="Q215" s="5">
+        <f t="shared" si="85"/>
+        <v>336</v>
+      </c>
+      <c r="R215" s="5">
+        <v>99.99</v>
+      </c>
+      <c r="S215" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="T215" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V215" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W215" s="1">
+        <v>0</v>
+      </c>
+      <c r="X215" s="5"/>
+      <c r="Y215" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2060" uniqueCount="1517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="1518">
   <si>
     <t>ID</t>
   </si>
@@ -3905,6 +3905,9 @@
   </si>
   <si>
     <t>13500000000000</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>10175</t>
@@ -17873,34 +17876,38 @@
       <c r="Y180" s="5"/>
     </row>
     <row r="181" s="3" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A181" s="13"/>
-      <c r="B181" s="13"/>
+      <c r="A181" s="13" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B181" s="13" t="s">
+        <v>1274</v>
+      </c>
       <c r="C181" s="19" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="D181" s="19" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="E181" s="3">
         <v>6</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="G181" s="26" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="H181" s="26" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="I181" s="26" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="J181" s="26" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="K181" s="26" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="L181" s="3">
         <f t="shared" si="50"/>
@@ -17942,34 +17949,38 @@
       </c>
     </row>
     <row r="182" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A182" s="5"/>
-      <c r="B182" s="5"/>
+      <c r="A182" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C182" s="19" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="D182" s="19" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="E182" s="1">
         <v>6</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="G182" s="26" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H182" s="26" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="I182" s="26" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="J182" s="26" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="K182" s="26" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="L182" s="1">
         <f t="shared" si="50"/>
@@ -18012,34 +18023,38 @@
       </c>
     </row>
     <row r="183" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A183" s="5"/>
-      <c r="B183" s="5"/>
+      <c r="A183" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C183" s="19" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="D183" s="19" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="E183" s="1">
         <v>6</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="G183" s="26" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H183" s="26" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="I183" s="26" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="J183" s="26" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="K183" s="26" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="L183" s="1">
         <f t="shared" si="50"/>
@@ -18082,34 +18097,38 @@
       </c>
     </row>
     <row r="184" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A184" s="5"/>
-      <c r="B184" s="5"/>
+      <c r="A184" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C184" s="19" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="D184" s="19" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="E184" s="1">
         <v>6</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="G184" s="26" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H184" s="26" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="I184" s="26" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="J184" s="26" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="K184" s="26" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="L184" s="1">
         <f t="shared" si="50"/>
@@ -18152,34 +18171,38 @@
       </c>
     </row>
     <row r="185" s="1" customFormat="1" customHeight="1" spans="1:23">
-      <c r="A185" s="5"/>
-      <c r="B185" s="5"/>
+      <c r="A185" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C185" s="19" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="D185" s="19" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="E185" s="1">
         <v>6</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="G185" s="26" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H185" s="26" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="I185" s="26" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="J185" s="26" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="K185" s="26" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="L185" s="1">
         <f t="shared" si="50"/>
@@ -18222,34 +18245,38 @@
       </c>
     </row>
     <row r="186" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A186" s="5"/>
-      <c r="B186" s="5"/>
+      <c r="A186" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C186" s="19" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="D186" s="19" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="E186" s="1">
         <v>6</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="G186" s="26" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H186" s="26" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="I186" s="26" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="J186" s="26" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="K186" s="26" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="L186" s="1">
         <f t="shared" si="50"/>
@@ -18294,34 +18321,38 @@
       <c r="Y186" s="5"/>
     </row>
     <row r="187" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A187" s="5"/>
-      <c r="B187" s="5"/>
+      <c r="A187" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C187" s="19" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="D187" s="19" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="E187" s="1">
         <v>6</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="G187" s="26" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H187" s="26" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="I187" s="26" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="J187" s="26" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="K187" s="26" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="L187" s="1">
         <f t="shared" si="50"/>
@@ -18366,34 +18397,38 @@
       <c r="Y187" s="5"/>
     </row>
     <row r="188" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A188" s="5"/>
-      <c r="B188" s="5"/>
+      <c r="A188" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C188" s="19" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="D188" s="19" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="E188" s="1">
         <v>6</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="G188" s="26" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H188" s="26" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="I188" s="26" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="J188" s="26" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="K188" s="26" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="L188" s="1">
         <f t="shared" si="50"/>
@@ -18438,34 +18473,38 @@
       <c r="Y188" s="5"/>
     </row>
     <row r="189" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A189" s="5"/>
-      <c r="B189" s="5"/>
+      <c r="A189" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C189" s="19" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="D189" s="19" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="E189" s="1">
         <v>6</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="G189" s="26" t="s">
         <v>1135</v>
       </c>
       <c r="H189" s="26" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="I189" s="26" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="J189" s="26" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="K189" s="26" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="L189" s="1">
         <f t="shared" si="50"/>
@@ -18510,34 +18549,38 @@
       <c r="Y189" s="5"/>
     </row>
     <row r="190" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A190" s="5"/>
-      <c r="B190" s="5"/>
+      <c r="A190" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C190" s="19" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="D190" s="19" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="E190" s="1">
         <v>6</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="G190" s="26" t="s">
         <v>1144</v>
       </c>
       <c r="H190" s="26" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="I190" s="26" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="J190" s="26" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="K190" s="26" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="L190" s="1">
         <f t="shared" si="50"/>
@@ -18582,34 +18625,38 @@
       <c r="Y190" s="5"/>
     </row>
     <row r="191" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A191" s="5"/>
-      <c r="B191" s="5"/>
+      <c r="A191" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C191" s="19" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="D191" s="19" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="E191" s="1">
         <v>6</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="G191" s="26" t="s">
         <v>1153</v>
       </c>
       <c r="H191" s="26" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="I191" s="26" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="J191" s="26" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="K191" s="26" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="L191" s="1">
         <f t="shared" si="50"/>
@@ -18654,34 +18701,38 @@
       <c r="Y191" s="5"/>
     </row>
     <row r="192" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A192" s="5"/>
-      <c r="B192" s="5"/>
+      <c r="A192" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C192" s="19" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="D192" s="19" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="E192" s="1">
         <v>6</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="G192" s="26" t="s">
         <v>1162</v>
       </c>
       <c r="H192" s="26" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="I192" s="26" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="J192" s="26" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="K192" s="26" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="L192" s="1">
         <f t="shared" si="50"/>
@@ -18726,34 +18777,38 @@
       <c r="Y192" s="5"/>
     </row>
     <row r="193" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A193" s="5"/>
-      <c r="B193" s="5"/>
+      <c r="A193" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C193" s="19" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="D193" s="19" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="E193" s="1">
         <v>6</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="G193" s="26" t="s">
         <v>1171</v>
       </c>
       <c r="H193" s="26" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="I193" s="26" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="J193" s="26" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="K193" s="26" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="L193" s="1">
         <f t="shared" si="50"/>
@@ -18798,34 +18853,38 @@
       <c r="Y193" s="5"/>
     </row>
     <row r="194" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A194" s="5"/>
-      <c r="B194" s="5"/>
+      <c r="A194" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C194" s="19" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="D194" s="19" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="E194" s="1">
         <v>6</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="G194" s="26" t="s">
         <v>1179</v>
       </c>
       <c r="H194" s="26" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="I194" s="26" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="J194" s="26" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="K194" s="26" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="L194" s="1">
         <f t="shared" si="50"/>
@@ -18870,34 +18929,38 @@
       <c r="Y194" s="5"/>
     </row>
     <row r="195" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A195" s="5"/>
-      <c r="B195" s="5"/>
+      <c r="A195" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C195" s="19" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="D195" s="19" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E195" s="1">
         <v>6</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="G195" s="26" t="s">
         <v>1188</v>
       </c>
       <c r="H195" s="26" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="I195" s="26" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="J195" s="26" t="s">
         <v>1182</v>
       </c>
       <c r="K195" s="26" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="L195" s="1">
         <f t="shared" si="50"/>
@@ -18942,34 +19005,38 @@
       <c r="Y195" s="5"/>
     </row>
     <row r="196" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A196" s="5"/>
-      <c r="B196" s="5"/>
+      <c r="A196" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C196" s="19" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="D196" s="19" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="E196" s="1">
         <v>6</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="G196" s="26" t="s">
         <v>1197</v>
       </c>
       <c r="H196" s="26" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="I196" s="26" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="J196" s="26" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="K196" s="26" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="L196" s="1">
         <f t="shared" si="50"/>
@@ -19014,34 +19081,38 @@
       <c r="Y196" s="5"/>
     </row>
     <row r="197" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A197" s="5"/>
-      <c r="B197" s="5"/>
+      <c r="A197" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C197" s="19" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="D197" s="19" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="E197" s="1">
         <v>6</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="G197" s="26" t="s">
         <v>1206</v>
       </c>
       <c r="H197" s="26" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="I197" s="26" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="J197" s="26" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="K197" s="26" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="L197" s="1">
         <f t="shared" si="50"/>
@@ -19086,34 +19157,38 @@
       <c r="Y197" s="5"/>
     </row>
     <row r="198" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A198" s="5"/>
-      <c r="B198" s="5"/>
+      <c r="A198" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C198" s="19" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="D198" s="19" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="E198" s="1">
         <v>6</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="G198" s="26" t="s">
         <v>1215</v>
       </c>
       <c r="H198" s="26" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="I198" s="26" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="J198" s="26" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="K198" s="26" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="L198" s="1">
         <f t="shared" si="50"/>
@@ -19158,34 +19233,38 @@
       <c r="Y198" s="5"/>
     </row>
     <row r="199" s="4" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A199" s="15"/>
-      <c r="B199" s="15"/>
+      <c r="A199" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C199" s="19" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="D199" s="19" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="E199" s="1">
         <v>6</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="G199" s="26" t="s">
         <v>1224</v>
       </c>
       <c r="H199" s="26" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="I199" s="26" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="J199" s="26" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="K199" s="26" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="L199" s="4">
         <f t="shared" si="50"/>
@@ -19230,34 +19309,38 @@
       <c r="Y199" s="15"/>
     </row>
     <row r="200" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A200" s="5"/>
-      <c r="B200" s="5"/>
+      <c r="A200" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C200" s="19" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="D200" s="19" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="E200" s="1">
         <v>6</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="G200" s="26" t="s">
         <v>1233</v>
       </c>
       <c r="H200" s="26" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="I200" s="26" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="J200" s="26" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="K200" s="26" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="L200" s="1">
         <f t="shared" si="50"/>
@@ -19301,33 +19384,39 @@
       <c r="X200" s="5"/>
       <c r="Y200" s="5"/>
     </row>
-    <row r="201" customHeight="1" spans="3:23">
+    <row r="201" customHeight="1" spans="1:23">
+      <c r="A201" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C201" s="19" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="D201" s="19" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="E201" s="1">
         <v>6</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="G201" s="26" t="s">
         <v>1242</v>
       </c>
       <c r="H201" s="26" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="I201" s="26" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="J201" s="26" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="K201" s="26" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="L201" s="1">
         <f t="shared" si="50"/>
@@ -19369,33 +19458,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" customHeight="1" spans="3:23">
+    <row r="202" customHeight="1" spans="1:23">
+      <c r="A202" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C202" s="19" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="D202" s="19" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="E202" s="1">
         <v>6</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="G202" s="26" t="s">
         <v>1251</v>
       </c>
       <c r="H202" s="26" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="I202" s="26" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="J202" s="26" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="K202" s="26" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="L202" s="1">
         <f t="shared" si="50"/>
@@ -19437,33 +19532,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" customHeight="1" spans="3:23">
+    <row r="203" customHeight="1" spans="1:23">
+      <c r="A203" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C203" s="19" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="D203" s="19" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="E203" s="1">
         <v>6</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="G203" s="26" t="s">
         <v>1260</v>
       </c>
       <c r="H203" s="26" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="I203" s="26" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="J203" s="26" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="K203" s="26" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="L203" s="1">
         <f t="shared" si="50"/>
@@ -19505,33 +19606,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" customHeight="1" spans="3:23">
+    <row r="204" customHeight="1" spans="1:23">
+      <c r="A204" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C204" s="19" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="D204" s="19" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="E204" s="1">
         <v>6</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="G204" s="26" t="s">
         <v>1269</v>
       </c>
       <c r="H204" s="26" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="I204" s="26" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="J204" s="26" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="K204" s="26" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="L204" s="1">
         <f t="shared" si="50"/>
@@ -19573,12 +19680,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" customHeight="1" spans="3:23">
+    <row r="205" customHeight="1" spans="1:23">
+      <c r="A205" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C205" s="19" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="D205" s="19" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="E205" s="1">
         <v>6</v>
@@ -19587,19 +19700,19 @@
         <v>460</v>
       </c>
       <c r="G205" s="26" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H205" s="26" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="I205" s="26" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="J205" s="26" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="K205" s="26" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="L205" s="1">
         <f t="shared" ref="L205:L215" si="76">L204+600</f>
@@ -19642,34 +19755,38 @@
       </c>
     </row>
     <row r="206" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A206" s="5"/>
-      <c r="B206" s="5"/>
+      <c r="A206" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C206" s="19" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="D206" s="19" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="E206" s="1">
         <v>6</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="G206" s="26" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H206" s="26" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="I206" s="26" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="J206" s="26" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="K206" s="26" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="L206" s="1">
         <f t="shared" si="76"/>
@@ -19714,34 +19831,38 @@
       <c r="Y206" s="5"/>
     </row>
     <row r="207" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A207" s="5"/>
-      <c r="B207" s="5"/>
+      <c r="A207" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C207" s="19" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="D207" s="19" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="E207" s="1">
         <v>6</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="G207" s="26" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="H207" s="26" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="I207" s="26" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="J207" s="26" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="K207" s="26" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="L207" s="1">
         <f t="shared" si="76"/>
@@ -19786,34 +19907,38 @@
       <c r="Y207" s="5"/>
     </row>
     <row r="208" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A208" s="5"/>
-      <c r="B208" s="5"/>
+      <c r="A208" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C208" s="19" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="D208" s="19" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="E208" s="1">
         <v>6</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="G208" s="26" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="H208" s="26" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="I208" s="26" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="J208" s="26" t="s">
         <v>1272</v>
       </c>
       <c r="K208" s="26" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="L208" s="1">
         <f t="shared" si="76"/>
@@ -19858,34 +19983,38 @@
       <c r="Y208" s="5"/>
     </row>
     <row r="209" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A209" s="5"/>
-      <c r="B209" s="5"/>
+      <c r="A209" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C209" s="19" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="D209" s="19" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="E209" s="1">
         <v>6</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="G209" s="26" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H209" s="26" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="I209" s="26" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="J209" s="26" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="K209" s="26" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="L209" s="1">
         <f t="shared" si="76"/>
@@ -19930,34 +20059,38 @@
       <c r="Y209" s="5"/>
     </row>
     <row r="210" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A210" s="5"/>
-      <c r="B210" s="5"/>
+      <c r="A210" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C210" s="19" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="D210" s="19" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="E210" s="1">
         <v>6</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="G210" s="26" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="H210" s="26" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="I210" s="26" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="J210" s="26" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="K210" s="26" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="L210" s="1">
         <f t="shared" si="76"/>
@@ -20002,34 +20135,38 @@
       <c r="Y210" s="5"/>
     </row>
     <row r="211" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A211" s="5"/>
-      <c r="B211" s="5"/>
+      <c r="A211" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C211" s="19" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="D211" s="19" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="E211" s="1">
         <v>6</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="G211" s="26" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="H211" s="26" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="I211" s="26" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="J211" s="26" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="K211" s="26" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="L211" s="1">
         <f t="shared" si="76"/>
@@ -20074,34 +20211,38 @@
       <c r="Y211" s="5"/>
     </row>
     <row r="212" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A212" s="5"/>
-      <c r="B212" s="5"/>
+      <c r="A212" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C212" s="19" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="D212" s="19" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="E212" s="1">
         <v>6</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="G212" s="26" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H212" s="26" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="I212" s="26" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="J212" s="26" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="K212" s="26" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="L212" s="1">
         <f t="shared" si="76"/>
@@ -20146,34 +20287,38 @@
       <c r="Y212" s="5"/>
     </row>
     <row r="213" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A213" s="5"/>
-      <c r="B213" s="5"/>
+      <c r="A213" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C213" s="19" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="D213" s="19" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="E213" s="1">
         <v>6</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="G213" s="26" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H213" s="26" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="I213" s="26" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="J213" s="26" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="K213" s="26" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="L213" s="1">
         <f t="shared" si="76"/>
@@ -20218,34 +20363,38 @@
       <c r="Y213" s="5"/>
     </row>
     <row r="214" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A214" s="5"/>
-      <c r="B214" s="5"/>
+      <c r="A214" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C214" s="19" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="D214" s="19" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="E214" s="1">
         <v>6</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="G214" s="26" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H214" s="26" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="I214" s="26" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="J214" s="26" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="K214" s="26" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="L214" s="1">
         <f t="shared" si="76"/>
@@ -20290,34 +20439,38 @@
       <c r="Y214" s="5"/>
     </row>
     <row r="215" s="1" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A215" s="5"/>
-      <c r="B215" s="5"/>
+      <c r="A215" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>1274</v>
+      </c>
       <c r="C215" s="19" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="D215" s="19" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="E215" s="1">
         <v>6</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="G215" s="26" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H215" s="26" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="I215" s="26" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="J215" s="26" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="K215" s="26" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="L215" s="1">
         <f t="shared" si="76"/>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="1532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="1531">
   <si>
     <t>ID</t>
   </si>
@@ -4037,9 +4037,6 @@
   </si>
   <si>
     <t>16000000000000</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
   <si>
     <t>10180</t>
@@ -4881,7 +4878,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4891,12 +4888,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5217,7 +5208,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5241,16 +5232,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -5259,89 +5250,89 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -5366,12 +5357,7 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5395,14 +5381,10 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="176" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
@@ -6013,13 +5995,13 @@
       <c r="F6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="G6" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="I6" s="27" t="s">
+      <c r="I6" s="24" t="s">
         <v>43</v>
       </c>
       <c r="J6" s="1">
@@ -8275,7 +8257,7 @@
       <c r="F40" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="G40" s="27" t="s">
+      <c r="G40" s="24" t="s">
         <v>287</v>
       </c>
       <c r="H40" s="1" t="s">
@@ -10027,7 +10009,7 @@
       <c r="H65" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="I65" s="27" t="s">
+      <c r="I65" s="24" t="s">
         <v>464</v>
       </c>
       <c r="J65" s="1">
@@ -10099,7 +10081,7 @@
       <c r="H66" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="I66" s="27" t="s">
+      <c r="I66" s="24" t="s">
         <v>471</v>
       </c>
       <c r="J66" s="1">
@@ -10171,7 +10153,7 @@
       <c r="H67" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="I67" s="27" t="s">
+      <c r="I67" s="24" t="s">
         <v>478</v>
       </c>
       <c r="J67" s="1">
@@ -10243,7 +10225,7 @@
       <c r="H68" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="I68" s="27" t="s">
+      <c r="I68" s="24" t="s">
         <v>485</v>
       </c>
       <c r="J68" s="1">
@@ -10315,7 +10297,7 @@
       <c r="H69" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="I69" s="27" t="s">
+      <c r="I69" s="24" t="s">
         <v>492</v>
       </c>
       <c r="J69" s="1">
@@ -10387,7 +10369,7 @@
       <c r="H70" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="I70" s="27" t="s">
+      <c r="I70" s="24" t="s">
         <v>499</v>
       </c>
       <c r="J70" s="1">
@@ -10452,13 +10434,13 @@
       <c r="F71" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="G71" s="28" t="s">
+      <c r="G71" s="25" t="s">
         <v>504</v>
       </c>
-      <c r="H71" s="27" t="s">
+      <c r="H71" s="24" t="s">
         <v>505</v>
       </c>
-      <c r="I71" s="28" t="s">
+      <c r="I71" s="25" t="s">
         <v>506</v>
       </c>
       <c r="J71" s="1">
@@ -10524,13 +10506,13 @@
       <c r="F72" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="G72" s="28" t="s">
+      <c r="G72" s="25" t="s">
         <v>511</v>
       </c>
-      <c r="H72" s="27" t="s">
+      <c r="H72" s="24" t="s">
         <v>512</v>
       </c>
-      <c r="I72" s="29" t="s">
+      <c r="I72" s="26" t="s">
         <v>513</v>
       </c>
       <c r="J72" s="1">
@@ -10596,13 +10578,13 @@
       <c r="F73" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="G73" s="28" t="s">
+      <c r="G73" s="25" t="s">
         <v>518</v>
       </c>
-      <c r="H73" s="27" t="s">
+      <c r="H73" s="24" t="s">
         <v>519</v>
       </c>
-      <c r="I73" s="29" t="s">
+      <c r="I73" s="26" t="s">
         <v>520</v>
       </c>
       <c r="J73" s="1">
@@ -10668,13 +10650,13 @@
       <c r="F74" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G74" s="28" t="s">
+      <c r="G74" s="25" t="s">
         <v>525</v>
       </c>
-      <c r="H74" s="27" t="s">
+      <c r="H74" s="24" t="s">
         <v>526</v>
       </c>
-      <c r="I74" s="29" t="s">
+      <c r="I74" s="26" t="s">
         <v>527</v>
       </c>
       <c r="J74" s="1">
@@ -10740,13 +10722,13 @@
       <c r="F75" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="G75" s="28" t="s">
+      <c r="G75" s="25" t="s">
         <v>532</v>
       </c>
-      <c r="H75" s="27" t="s">
+      <c r="H75" s="24" t="s">
         <v>533</v>
       </c>
-      <c r="I75" s="29" t="s">
+      <c r="I75" s="26" t="s">
         <v>534</v>
       </c>
       <c r="J75" s="1">
@@ -10786,7 +10768,7 @@
       <c r="T75" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="U75" s="27" t="s">
+      <c r="U75" s="24" t="s">
         <v>535</v>
       </c>
       <c r="W75" s="1" t="s">
@@ -10813,13 +10795,13 @@
       <c r="F76" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="G76" s="28" t="s">
+      <c r="G76" s="25" t="s">
         <v>539</v>
       </c>
-      <c r="H76" s="27" t="s">
+      <c r="H76" s="24" t="s">
         <v>540</v>
       </c>
-      <c r="I76" s="29" t="s">
+      <c r="I76" s="26" t="s">
         <v>541</v>
       </c>
       <c r="J76" s="1">
@@ -10884,13 +10866,13 @@
       <c r="F77" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="G77" s="28" t="s">
+      <c r="G77" s="25" t="s">
         <v>545</v>
       </c>
-      <c r="H77" s="27" t="s">
+      <c r="H77" s="24" t="s">
         <v>546</v>
       </c>
-      <c r="I77" s="29" t="s">
+      <c r="I77" s="26" t="s">
         <v>547</v>
       </c>
       <c r="J77" s="1">
@@ -10955,13 +10937,13 @@
       <c r="F78" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="G78" s="28" t="s">
+      <c r="G78" s="25" t="s">
         <v>551</v>
       </c>
-      <c r="H78" s="27" t="s">
+      <c r="H78" s="24" t="s">
         <v>552</v>
       </c>
-      <c r="I78" s="29" t="s">
+      <c r="I78" s="26" t="s">
         <v>553</v>
       </c>
       <c r="J78" s="1">
@@ -11026,13 +11008,13 @@
       <c r="F79" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="G79" s="28" t="s">
+      <c r="G79" s="25" t="s">
         <v>557</v>
       </c>
-      <c r="H79" s="27" t="s">
+      <c r="H79" s="24" t="s">
         <v>558</v>
       </c>
-      <c r="I79" s="29" t="s">
+      <c r="I79" s="26" t="s">
         <v>559</v>
       </c>
       <c r="J79" s="1">
@@ -11097,13 +11079,13 @@
       <c r="F80" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G80" s="28" t="s">
+      <c r="G80" s="25" t="s">
         <v>563</v>
       </c>
-      <c r="H80" s="27" t="s">
+      <c r="H80" s="24" t="s">
         <v>564</v>
       </c>
-      <c r="I80" s="29" t="s">
+      <c r="I80" s="26" t="s">
         <v>565</v>
       </c>
       <c r="J80" s="1">
@@ -11168,13 +11150,13 @@
       <c r="F81" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="G81" s="28" t="s">
+      <c r="G81" s="25" t="s">
         <v>569</v>
       </c>
-      <c r="H81" s="27" t="s">
+      <c r="H81" s="24" t="s">
         <v>570</v>
       </c>
-      <c r="I81" s="29" t="s">
+      <c r="I81" s="26" t="s">
         <v>571</v>
       </c>
       <c r="J81" s="1">
@@ -11241,13 +11223,13 @@
       <c r="F82" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="G82" s="28" t="s">
+      <c r="G82" s="25" t="s">
         <v>575</v>
       </c>
-      <c r="H82" s="27" t="s">
+      <c r="H82" s="24" t="s">
         <v>576</v>
       </c>
-      <c r="I82" s="29" t="s">
+      <c r="I82" s="26" t="s">
         <v>577</v>
       </c>
       <c r="J82" s="1">
@@ -11314,13 +11296,13 @@
       <c r="F83" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="G83" s="28" t="s">
+      <c r="G83" s="25" t="s">
         <v>581</v>
       </c>
-      <c r="H83" s="27" t="s">
+      <c r="H83" s="24" t="s">
         <v>532</v>
       </c>
-      <c r="I83" s="29" t="s">
+      <c r="I83" s="26" t="s">
         <v>582</v>
       </c>
       <c r="J83" s="1">
@@ -11387,13 +11369,13 @@
       <c r="F84" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="G84" s="28" t="s">
+      <c r="G84" s="25" t="s">
         <v>586</v>
       </c>
-      <c r="H84" s="27" t="s">
+      <c r="H84" s="24" t="s">
         <v>587</v>
       </c>
-      <c r="I84" s="29" t="s">
+      <c r="I84" s="26" t="s">
         <v>588</v>
       </c>
       <c r="J84" s="1">
@@ -11460,13 +11442,13 @@
       <c r="F85" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="G85" s="28" t="s">
+      <c r="G85" s="25" t="s">
         <v>464</v>
       </c>
-      <c r="H85" s="27" t="s">
+      <c r="H85" s="24" t="s">
         <v>592</v>
       </c>
-      <c r="I85" s="29" t="s">
+      <c r="I85" s="26" t="s">
         <v>593</v>
       </c>
       <c r="J85" s="1">
@@ -11533,13 +11515,13 @@
       <c r="F86" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="G86" s="28" t="s">
+      <c r="G86" s="25" t="s">
         <v>597</v>
       </c>
-      <c r="H86" s="27" t="s">
+      <c r="H86" s="24" t="s">
         <v>598</v>
       </c>
-      <c r="I86" s="29" t="s">
+      <c r="I86" s="26" t="s">
         <v>599</v>
       </c>
       <c r="J86" s="1">
@@ -11606,13 +11588,13 @@
       <c r="F87" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="G87" s="28" t="s">
+      <c r="G87" s="25" t="s">
         <v>603</v>
       </c>
-      <c r="H87" s="27" t="s">
+      <c r="H87" s="24" t="s">
         <v>604</v>
       </c>
-      <c r="I87" s="29" t="s">
+      <c r="I87" s="26" t="s">
         <v>605</v>
       </c>
       <c r="J87" s="1">
@@ -11679,13 +11661,13 @@
       <c r="F88" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="G88" s="28" t="s">
+      <c r="G88" s="25" t="s">
         <v>609</v>
       </c>
-      <c r="H88" s="27" t="s">
+      <c r="H88" s="24" t="s">
         <v>610</v>
       </c>
-      <c r="I88" s="29" t="s">
+      <c r="I88" s="26" t="s">
         <v>611</v>
       </c>
       <c r="J88" s="1">
@@ -11752,13 +11734,13 @@
       <c r="F89" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="G89" s="28" t="s">
+      <c r="G89" s="25" t="s">
         <v>615</v>
       </c>
-      <c r="H89" s="27" t="s">
+      <c r="H89" s="24" t="s">
         <v>464</v>
       </c>
-      <c r="I89" s="29" t="s">
+      <c r="I89" s="26" t="s">
         <v>616</v>
       </c>
       <c r="J89" s="1">
@@ -11825,13 +11807,13 @@
       <c r="F90" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="G90" s="28" t="s">
+      <c r="G90" s="25" t="s">
         <v>620</v>
       </c>
-      <c r="H90" s="27" t="s">
+      <c r="H90" s="24" t="s">
         <v>621</v>
       </c>
-      <c r="I90" s="29" t="s">
+      <c r="I90" s="26" t="s">
         <v>622</v>
       </c>
       <c r="J90" s="1">
@@ -11868,10 +11850,10 @@
       <c r="S90" s="12">
         <v>0</v>
       </c>
-      <c r="T90" s="27" t="s">
+      <c r="T90" s="24" t="s">
         <v>623</v>
       </c>
-      <c r="U90" s="27" t="s">
+      <c r="U90" s="24" t="s">
         <v>623</v>
       </c>
       <c r="W90" s="1" t="s">
@@ -11898,13 +11880,13 @@
       <c r="F91" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="G91" s="28" t="s">
+      <c r="G91" s="25" t="s">
         <v>513</v>
       </c>
-      <c r="H91" s="27" t="s">
+      <c r="H91" s="24" t="s">
         <v>627</v>
       </c>
-      <c r="I91" s="29" t="s">
+      <c r="I91" s="26" t="s">
         <v>628</v>
       </c>
       <c r="J91" s="1">
@@ -11941,10 +11923,10 @@
       <c r="S91" s="12">
         <v>0</v>
       </c>
-      <c r="T91" s="27" t="s">
+      <c r="T91" s="24" t="s">
         <v>629</v>
       </c>
-      <c r="U91" s="27" t="s">
+      <c r="U91" s="24" t="s">
         <v>629</v>
       </c>
       <c r="W91" s="1" t="s">
@@ -11971,13 +11953,13 @@
       <c r="F92" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="G92" s="28" t="s">
+      <c r="G92" s="25" t="s">
         <v>633</v>
       </c>
-      <c r="H92" s="27" t="s">
+      <c r="H92" s="24" t="s">
         <v>634</v>
       </c>
-      <c r="I92" s="29" t="s">
+      <c r="I92" s="26" t="s">
         <v>635</v>
       </c>
       <c r="J92" s="1">
@@ -12014,10 +11996,10 @@
       <c r="S92" s="12">
         <v>0</v>
       </c>
-      <c r="T92" s="27" t="s">
+      <c r="T92" s="24" t="s">
         <v>636</v>
       </c>
-      <c r="U92" s="27" t="s">
+      <c r="U92" s="24" t="s">
         <v>636</v>
       </c>
       <c r="W92" s="1" t="s">
@@ -12044,13 +12026,13 @@
       <c r="F93" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="G93" s="28" t="s">
+      <c r="G93" s="25" t="s">
         <v>640</v>
       </c>
-      <c r="H93" s="27" t="s">
+      <c r="H93" s="24" t="s">
         <v>641</v>
       </c>
-      <c r="I93" s="29" t="s">
+      <c r="I93" s="26" t="s">
         <v>642</v>
       </c>
       <c r="J93" s="1">
@@ -12087,10 +12069,10 @@
       <c r="S93" s="12">
         <v>0</v>
       </c>
-      <c r="T93" s="27" t="s">
+      <c r="T93" s="24" t="s">
         <v>643</v>
       </c>
-      <c r="U93" s="27" t="s">
+      <c r="U93" s="24" t="s">
         <v>643</v>
       </c>
       <c r="W93" s="1" t="s">
@@ -12117,13 +12099,13 @@
       <c r="F94" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="G94" s="28" t="s">
+      <c r="G94" s="25" t="s">
         <v>647</v>
       </c>
-      <c r="H94" s="27" t="s">
+      <c r="H94" s="24" t="s">
         <v>648</v>
       </c>
-      <c r="I94" s="29" t="s">
+      <c r="I94" s="26" t="s">
         <v>649</v>
       </c>
       <c r="J94" s="1">
@@ -12160,10 +12142,10 @@
       <c r="S94" s="12">
         <v>0</v>
       </c>
-      <c r="T94" s="27" t="s">
+      <c r="T94" s="24" t="s">
         <v>650</v>
       </c>
-      <c r="U94" s="27" t="s">
+      <c r="U94" s="24" t="s">
         <v>650</v>
       </c>
       <c r="W94" s="1" t="s">
@@ -12190,13 +12172,13 @@
       <c r="F95" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="G95" s="28" t="s">
+      <c r="G95" s="25" t="s">
         <v>654</v>
       </c>
-      <c r="H95" s="27" t="s">
+      <c r="H95" s="24" t="s">
         <v>655</v>
       </c>
-      <c r="I95" s="29" t="s">
+      <c r="I95" s="26" t="s">
         <v>656</v>
       </c>
       <c r="J95" s="1">
@@ -12233,10 +12215,10 @@
       <c r="S95" s="12">
         <v>0</v>
       </c>
-      <c r="T95" s="27" t="s">
+      <c r="T95" s="24" t="s">
         <v>657</v>
       </c>
-      <c r="U95" s="27" t="s">
+      <c r="U95" s="24" t="s">
         <v>657</v>
       </c>
       <c r="W95" s="1" t="s">
@@ -12261,13 +12243,13 @@
       <c r="F96" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="G96" s="28" t="s">
+      <c r="G96" s="25" t="s">
         <v>661</v>
       </c>
-      <c r="H96" s="27" t="s">
+      <c r="H96" s="24" t="s">
         <v>662</v>
       </c>
-      <c r="I96" s="29" t="s">
+      <c r="I96" s="26" t="s">
         <v>663</v>
       </c>
       <c r="J96" s="1">
@@ -12304,10 +12286,10 @@
       <c r="S96" s="12">
         <v>0</v>
       </c>
-      <c r="T96" s="27" t="s">
+      <c r="T96" s="24" t="s">
         <v>664</v>
       </c>
-      <c r="U96" s="27" t="s">
+      <c r="U96" s="24" t="s">
         <v>664</v>
       </c>
       <c r="W96" s="1" t="s">
@@ -12330,13 +12312,13 @@
       <c r="F97" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="G97" s="28" t="s">
+      <c r="G97" s="25" t="s">
         <v>668</v>
       </c>
-      <c r="H97" s="27" t="s">
+      <c r="H97" s="24" t="s">
         <v>669</v>
       </c>
-      <c r="I97" s="29" t="s">
+      <c r="I97" s="26" t="s">
         <v>670</v>
       </c>
       <c r="J97" s="1">
@@ -12373,10 +12355,10 @@
       <c r="S97" s="12">
         <v>0</v>
       </c>
-      <c r="T97" s="27" t="s">
+      <c r="T97" s="24" t="s">
         <v>671</v>
       </c>
-      <c r="U97" s="27" t="s">
+      <c r="U97" s="24" t="s">
         <v>671</v>
       </c>
       <c r="W97" s="1" t="s">
@@ -12399,13 +12381,13 @@
       <c r="F98" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="G98" s="28" t="s">
+      <c r="G98" s="25" t="s">
         <v>675</v>
       </c>
-      <c r="H98" s="27" t="s">
+      <c r="H98" s="24" t="s">
         <v>676</v>
       </c>
-      <c r="I98" s="29" t="s">
+      <c r="I98" s="26" t="s">
         <v>677</v>
       </c>
       <c r="J98" s="1">
@@ -12442,10 +12424,10 @@
       <c r="S98" s="12">
         <v>0</v>
       </c>
-      <c r="T98" s="27" t="s">
+      <c r="T98" s="24" t="s">
         <v>678</v>
       </c>
-      <c r="U98" s="27" t="s">
+      <c r="U98" s="24" t="s">
         <v>678</v>
       </c>
       <c r="W98" s="1" t="s">
@@ -12468,13 +12450,13 @@
       <c r="F99" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="G99" s="28" t="s">
+      <c r="G99" s="25" t="s">
         <v>682</v>
       </c>
-      <c r="H99" s="27" t="s">
+      <c r="H99" s="24" t="s">
         <v>683</v>
       </c>
-      <c r="I99" s="29" t="s">
+      <c r="I99" s="26" t="s">
         <v>684</v>
       </c>
       <c r="J99" s="1">
@@ -12511,10 +12493,10 @@
       <c r="S99" s="12">
         <v>0</v>
       </c>
-      <c r="T99" s="27" t="s">
+      <c r="T99" s="24" t="s">
         <v>685</v>
       </c>
-      <c r="U99" s="27" t="s">
+      <c r="U99" s="24" t="s">
         <v>685</v>
       </c>
       <c r="W99" s="1" t="s">
@@ -12537,13 +12519,13 @@
       <c r="F100" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="G100" s="28" t="s">
+      <c r="G100" s="25" t="s">
         <v>688</v>
       </c>
-      <c r="H100" s="27" t="s">
+      <c r="H100" s="24" t="s">
         <v>689</v>
       </c>
-      <c r="I100" s="29" t="s">
+      <c r="I100" s="26" t="s">
         <v>690</v>
       </c>
       <c r="J100" s="1">
@@ -12580,10 +12562,10 @@
       <c r="S100" s="12">
         <v>0</v>
       </c>
-      <c r="T100" s="27" t="s">
+      <c r="T100" s="24" t="s">
         <v>691</v>
       </c>
-      <c r="U100" s="27" t="s">
+      <c r="U100" s="24" t="s">
         <v>691</v>
       </c>
       <c r="W100" s="1" t="s">
@@ -12608,13 +12590,13 @@
       <c r="F101" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="G101" s="28" t="s">
+      <c r="G101" s="25" t="s">
         <v>695</v>
       </c>
-      <c r="H101" s="27" t="s">
+      <c r="H101" s="24" t="s">
         <v>696</v>
       </c>
-      <c r="I101" s="29" t="s">
+      <c r="I101" s="26" t="s">
         <v>697</v>
       </c>
       <c r="J101" s="1">
@@ -12651,10 +12633,10 @@
       <c r="S101" s="12">
         <v>0</v>
       </c>
-      <c r="T101" s="27" t="s">
+      <c r="T101" s="24" t="s">
         <v>698</v>
       </c>
-      <c r="U101" s="27" t="s">
+      <c r="U101" s="24" t="s">
         <v>698</v>
       </c>
       <c r="W101" s="1" t="s">
@@ -12681,13 +12663,13 @@
       <c r="F102" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="G102" s="28" t="s">
+      <c r="G102" s="25" t="s">
         <v>702</v>
       </c>
-      <c r="H102" s="27" t="s">
+      <c r="H102" s="24" t="s">
         <v>611</v>
       </c>
-      <c r="I102" s="29" t="s">
+      <c r="I102" s="26" t="s">
         <v>703</v>
       </c>
       <c r="J102" s="1">
@@ -12724,10 +12706,10 @@
       <c r="S102" s="12">
         <v>0</v>
       </c>
-      <c r="T102" s="27" t="s">
+      <c r="T102" s="24" t="s">
         <v>704</v>
       </c>
-      <c r="U102" s="27" t="s">
+      <c r="U102" s="24" t="s">
         <v>704</v>
       </c>
       <c r="W102" s="1" t="s">
@@ -12754,13 +12736,13 @@
       <c r="F103" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="G103" s="28" t="s">
+      <c r="G103" s="25" t="s">
         <v>708</v>
       </c>
-      <c r="H103" s="27" t="s">
+      <c r="H103" s="24" t="s">
         <v>616</v>
       </c>
-      <c r="I103" s="29" t="s">
+      <c r="I103" s="26" t="s">
         <v>709</v>
       </c>
       <c r="J103" s="1">
@@ -12797,10 +12779,10 @@
       <c r="S103" s="12">
         <v>0</v>
       </c>
-      <c r="T103" s="27" t="s">
+      <c r="T103" s="24" t="s">
         <v>710</v>
       </c>
-      <c r="U103" s="27" t="s">
+      <c r="U103" s="24" t="s">
         <v>710</v>
       </c>
       <c r="W103" s="1" t="s">
@@ -12827,13 +12809,13 @@
       <c r="F104" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="G104" s="28" t="s">
+      <c r="G104" s="25" t="s">
         <v>714</v>
       </c>
-      <c r="H104" s="27" t="s">
+      <c r="H104" s="24" t="s">
         <v>715</v>
       </c>
-      <c r="I104" s="29" t="s">
+      <c r="I104" s="26" t="s">
         <v>716</v>
       </c>
       <c r="J104" s="1">
@@ -12870,10 +12852,10 @@
       <c r="S104" s="12">
         <v>0</v>
       </c>
-      <c r="T104" s="27" t="s">
+      <c r="T104" s="24" t="s">
         <v>717</v>
       </c>
-      <c r="U104" s="27" t="s">
+      <c r="U104" s="24" t="s">
         <v>717</v>
       </c>
       <c r="W104" s="1" t="s">
@@ -12900,13 +12882,13 @@
       <c r="F105" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="G105" s="28" t="s">
+      <c r="G105" s="25" t="s">
         <v>721</v>
       </c>
-      <c r="H105" s="27" t="s">
+      <c r="H105" s="24" t="s">
         <v>722</v>
       </c>
-      <c r="I105" s="29" t="s">
+      <c r="I105" s="26" t="s">
         <v>723</v>
       </c>
       <c r="J105" s="1">
@@ -12943,10 +12925,10 @@
       <c r="S105" s="12">
         <v>0</v>
       </c>
-      <c r="T105" s="27" t="s">
+      <c r="T105" s="24" t="s">
         <v>724</v>
       </c>
-      <c r="U105" s="27" t="s">
+      <c r="U105" s="24" t="s">
         <v>724</v>
       </c>
       <c r="W105" s="1" t="s">
@@ -12973,13 +12955,13 @@
       <c r="F106" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="G106" s="28" t="s">
+      <c r="G106" s="25" t="s">
         <v>728</v>
       </c>
-      <c r="H106" s="27" t="s">
+      <c r="H106" s="24" t="s">
         <v>729</v>
       </c>
-      <c r="I106" s="29" t="s">
+      <c r="I106" s="26" t="s">
         <v>730</v>
       </c>
       <c r="J106" s="1">
@@ -13016,10 +12998,10 @@
       <c r="S106" s="12">
         <v>0</v>
       </c>
-      <c r="T106" s="27" t="s">
+      <c r="T106" s="24" t="s">
         <v>731</v>
       </c>
-      <c r="U106" s="27" t="s">
+      <c r="U106" s="24" t="s">
         <v>731</v>
       </c>
       <c r="W106" s="1" t="s">
@@ -13046,13 +13028,13 @@
       <c r="F107" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="G107" s="28" t="s">
+      <c r="G107" s="25" t="s">
         <v>735</v>
       </c>
-      <c r="H107" s="27" t="s">
+      <c r="H107" s="24" t="s">
         <v>736</v>
       </c>
-      <c r="I107" s="29" t="s">
+      <c r="I107" s="26" t="s">
         <v>737</v>
       </c>
       <c r="J107" s="1">
@@ -13089,10 +13071,10 @@
       <c r="S107" s="12">
         <v>0</v>
       </c>
-      <c r="T107" s="27" t="s">
+      <c r="T107" s="24" t="s">
         <v>738</v>
       </c>
-      <c r="U107" s="27" t="s">
+      <c r="U107" s="24" t="s">
         <v>738</v>
       </c>
       <c r="W107" s="1" t="s">
@@ -13119,13 +13101,13 @@
       <c r="F108" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="G108" s="28" t="s">
+      <c r="G108" s="25" t="s">
         <v>742</v>
       </c>
-      <c r="H108" s="27" t="s">
+      <c r="H108" s="24" t="s">
         <v>743</v>
       </c>
-      <c r="I108" s="29" t="s">
+      <c r="I108" s="26" t="s">
         <v>744</v>
       </c>
       <c r="J108" s="1">
@@ -13162,10 +13144,10 @@
       <c r="S108" s="12">
         <v>0</v>
       </c>
-      <c r="T108" s="27" t="s">
+      <c r="T108" s="24" t="s">
         <v>745</v>
       </c>
-      <c r="U108" s="27" t="s">
+      <c r="U108" s="24" t="s">
         <v>745</v>
       </c>
       <c r="W108" s="1" t="s">
@@ -13192,13 +13174,13 @@
       <c r="F109" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="G109" s="28" t="s">
+      <c r="G109" s="25" t="s">
         <v>749</v>
       </c>
-      <c r="H109" s="27" t="s">
+      <c r="H109" s="24" t="s">
         <v>750</v>
       </c>
-      <c r="I109" s="29" t="s">
+      <c r="I109" s="26" t="s">
         <v>751</v>
       </c>
       <c r="J109" s="1">
@@ -13235,10 +13217,10 @@
       <c r="S109" s="12">
         <v>0</v>
       </c>
-      <c r="T109" s="27" t="s">
+      <c r="T109" s="24" t="s">
         <v>752</v>
       </c>
-      <c r="U109" s="27" t="s">
+      <c r="U109" s="24" t="s">
         <v>752</v>
       </c>
       <c r="W109" s="1" t="s">
@@ -13265,13 +13247,13 @@
       <c r="F110" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="G110" s="28" t="s">
+      <c r="G110" s="25" t="s">
         <v>677</v>
       </c>
-      <c r="H110" s="27" t="s">
+      <c r="H110" s="24" t="s">
         <v>756</v>
       </c>
-      <c r="I110" s="29" t="s">
+      <c r="I110" s="26" t="s">
         <v>757</v>
       </c>
       <c r="J110" s="1">
@@ -13308,10 +13290,10 @@
       <c r="S110" s="12">
         <v>0</v>
       </c>
-      <c r="T110" s="27" t="s">
+      <c r="T110" s="24" t="s">
         <v>758</v>
       </c>
-      <c r="U110" s="27" t="s">
+      <c r="U110" s="24" t="s">
         <v>758</v>
       </c>
       <c r="W110" s="1" t="s">
@@ -13338,13 +13320,13 @@
       <c r="F111" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="G111" s="30" t="s">
+      <c r="G111" s="27" t="s">
         <v>762</v>
       </c>
-      <c r="H111" s="31" t="s">
+      <c r="H111" s="28" t="s">
         <v>762</v>
       </c>
-      <c r="I111" s="32" t="s">
+      <c r="I111" s="29" t="s">
         <v>763</v>
       </c>
       <c r="J111" s="1">
@@ -13377,10 +13359,10 @@
       <c r="S111" s="8">
         <v>90</v>
       </c>
-      <c r="T111" s="31" t="s">
+      <c r="T111" s="28" t="s">
         <v>764</v>
       </c>
-      <c r="U111" s="31" t="s">
+      <c r="U111" s="28" t="s">
         <v>764</v>
       </c>
       <c r="W111" s="2" t="s">
@@ -13405,13 +13387,13 @@
       <c r="F112" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="G112" s="28" t="s">
+      <c r="G112" s="25" t="s">
         <v>768</v>
       </c>
-      <c r="H112" s="27" t="s">
+      <c r="H112" s="24" t="s">
         <v>768</v>
       </c>
-      <c r="I112" s="29" t="s">
+      <c r="I112" s="26" t="s">
         <v>769</v>
       </c>
       <c r="J112" s="1">
@@ -13449,10 +13431,10 @@
       <c r="S112" s="8">
         <v>90</v>
       </c>
-      <c r="T112" s="27" t="s">
+      <c r="T112" s="24" t="s">
         <v>770</v>
       </c>
-      <c r="U112" s="27" t="s">
+      <c r="U112" s="24" t="s">
         <v>770</v>
       </c>
       <c r="W112" s="1" t="s">
@@ -13477,13 +13459,13 @@
       <c r="F113" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="G113" s="28" t="s">
+      <c r="G113" s="25" t="s">
         <v>774</v>
       </c>
-      <c r="H113" s="27" t="s">
+      <c r="H113" s="24" t="s">
         <v>774</v>
       </c>
-      <c r="I113" s="29" t="s">
+      <c r="I113" s="26" t="s">
         <v>775</v>
       </c>
       <c r="J113" s="1">
@@ -13521,10 +13503,10 @@
       <c r="S113" s="8">
         <v>90</v>
       </c>
-      <c r="T113" s="27" t="s">
+      <c r="T113" s="24" t="s">
         <v>776</v>
       </c>
-      <c r="U113" s="27" t="s">
+      <c r="U113" s="24" t="s">
         <v>776</v>
       </c>
       <c r="W113" s="1" t="s">
@@ -13549,13 +13531,13 @@
       <c r="F114" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="G114" s="28" t="s">
+      <c r="G114" s="25" t="s">
         <v>780</v>
       </c>
-      <c r="H114" s="27" t="s">
+      <c r="H114" s="24" t="s">
         <v>780</v>
       </c>
-      <c r="I114" s="29" t="s">
+      <c r="I114" s="26" t="s">
         <v>781</v>
       </c>
       <c r="J114" s="1">
@@ -13593,10 +13575,10 @@
       <c r="S114" s="8">
         <v>90</v>
       </c>
-      <c r="T114" s="27" t="s">
+      <c r="T114" s="24" t="s">
         <v>782</v>
       </c>
-      <c r="U114" s="27" t="s">
+      <c r="U114" s="24" t="s">
         <v>782</v>
       </c>
       <c r="W114" s="1" t="s">
@@ -13621,13 +13603,13 @@
       <c r="F115" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="G115" s="28" t="s">
+      <c r="G115" s="25" t="s">
         <v>786</v>
       </c>
-      <c r="H115" s="27" t="s">
+      <c r="H115" s="24" t="s">
         <v>786</v>
       </c>
-      <c r="I115" s="29" t="s">
+      <c r="I115" s="26" t="s">
         <v>787</v>
       </c>
       <c r="J115" s="1">
@@ -13665,10 +13647,10 @@
       <c r="S115" s="8">
         <v>90</v>
       </c>
-      <c r="T115" s="27" t="s">
+      <c r="T115" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="U115" s="27" t="s">
+      <c r="U115" s="24" t="s">
         <v>788</v>
       </c>
       <c r="W115" s="1" t="s">
@@ -13693,13 +13675,13 @@
       <c r="F116" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="G116" s="28" t="s">
+      <c r="G116" s="25" t="s">
         <v>792</v>
       </c>
-      <c r="H116" s="27" t="s">
+      <c r="H116" s="24" t="s">
         <v>792</v>
       </c>
-      <c r="I116" s="29" t="s">
+      <c r="I116" s="26" t="s">
         <v>793</v>
       </c>
       <c r="J116" s="1">
@@ -13737,10 +13719,10 @@
       <c r="S116" s="8">
         <v>90</v>
       </c>
-      <c r="T116" s="27" t="s">
+      <c r="T116" s="24" t="s">
         <v>794</v>
       </c>
-      <c r="U116" s="27" t="s">
+      <c r="U116" s="24" t="s">
         <v>794</v>
       </c>
       <c r="W116" s="1" t="s">
@@ -13767,13 +13749,13 @@
       <c r="F117" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="G117" s="28" t="s">
+      <c r="G117" s="25" t="s">
         <v>798</v>
       </c>
-      <c r="H117" s="27" t="s">
+      <c r="H117" s="24" t="s">
         <v>798</v>
       </c>
-      <c r="I117" s="29" t="s">
+      <c r="I117" s="26" t="s">
         <v>799</v>
       </c>
       <c r="J117" s="1">
@@ -13811,10 +13793,10 @@
       <c r="S117" s="8">
         <v>90</v>
       </c>
-      <c r="T117" s="27" t="s">
+      <c r="T117" s="24" t="s">
         <v>800</v>
       </c>
-      <c r="U117" s="27" t="s">
+      <c r="U117" s="24" t="s">
         <v>800</v>
       </c>
       <c r="W117" s="1" t="s">
@@ -13841,13 +13823,13 @@
       <c r="F118" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="G118" s="28" t="s">
+      <c r="G118" s="25" t="s">
         <v>804</v>
       </c>
-      <c r="H118" s="27" t="s">
+      <c r="H118" s="24" t="s">
         <v>804</v>
       </c>
-      <c r="I118" s="29" t="s">
+      <c r="I118" s="26" t="s">
         <v>805</v>
       </c>
       <c r="J118" s="1">
@@ -13885,10 +13867,10 @@
       <c r="S118" s="8">
         <v>90</v>
       </c>
-      <c r="T118" s="27" t="s">
+      <c r="T118" s="24" t="s">
         <v>806</v>
       </c>
-      <c r="U118" s="27" t="s">
+      <c r="U118" s="24" t="s">
         <v>806</v>
       </c>
       <c r="W118" s="1" t="s">
@@ -13915,13 +13897,13 @@
       <c r="F119" s="1" t="s">
         <v>809</v>
       </c>
-      <c r="G119" s="28" t="s">
+      <c r="G119" s="25" t="s">
         <v>810</v>
       </c>
-      <c r="H119" s="27" t="s">
+      <c r="H119" s="24" t="s">
         <v>810</v>
       </c>
-      <c r="I119" s="29" t="s">
+      <c r="I119" s="26" t="s">
         <v>811</v>
       </c>
       <c r="J119" s="1">
@@ -13959,10 +13941,10 @@
       <c r="S119" s="8">
         <v>90</v>
       </c>
-      <c r="T119" s="27" t="s">
+      <c r="T119" s="24" t="s">
         <v>812</v>
       </c>
-      <c r="U119" s="27" t="s">
+      <c r="U119" s="24" t="s">
         <v>812</v>
       </c>
       <c r="W119" s="1" t="s">
@@ -13989,13 +13971,13 @@
       <c r="F120" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="G120" s="28" t="s">
+      <c r="G120" s="25" t="s">
         <v>816</v>
       </c>
-      <c r="H120" s="27" t="s">
+      <c r="H120" s="24" t="s">
         <v>816</v>
       </c>
-      <c r="I120" s="29" t="s">
+      <c r="I120" s="26" t="s">
         <v>817</v>
       </c>
       <c r="J120" s="1">
@@ -14033,10 +14015,10 @@
       <c r="S120" s="8">
         <v>90</v>
       </c>
-      <c r="T120" s="27" t="s">
+      <c r="T120" s="24" t="s">
         <v>818</v>
       </c>
-      <c r="U120" s="27" t="s">
+      <c r="U120" s="24" t="s">
         <v>818</v>
       </c>
       <c r="W120" s="1" t="s">
@@ -14061,13 +14043,13 @@
       <c r="F121" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="G121" s="28" t="s">
+      <c r="G121" s="25" t="s">
         <v>763</v>
       </c>
-      <c r="H121" s="27" t="s">
+      <c r="H121" s="24" t="s">
         <v>763</v>
       </c>
-      <c r="I121" s="29" t="s">
+      <c r="I121" s="26" t="s">
         <v>822</v>
       </c>
       <c r="J121" s="1">
@@ -14106,10 +14088,10 @@
       <c r="S121" s="8">
         <v>90</v>
       </c>
-      <c r="T121" s="27" t="s">
+      <c r="T121" s="24" t="s">
         <v>823</v>
       </c>
-      <c r="U121" s="27" t="s">
+      <c r="U121" s="24" t="s">
         <v>823</v>
       </c>
       <c r="W121" s="1" t="s">
@@ -14134,13 +14116,13 @@
       <c r="F122" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="G122" s="28" t="s">
+      <c r="G122" s="25" t="s">
         <v>827</v>
       </c>
-      <c r="H122" s="27" t="s">
+      <c r="H122" s="24" t="s">
         <v>827</v>
       </c>
-      <c r="I122" s="29" t="s">
+      <c r="I122" s="26" t="s">
         <v>828</v>
       </c>
       <c r="J122" s="1">
@@ -14179,10 +14161,10 @@
       <c r="S122" s="8">
         <v>90</v>
       </c>
-      <c r="T122" s="27" t="s">
+      <c r="T122" s="24" t="s">
         <v>829</v>
       </c>
-      <c r="U122" s="27" t="s">
+      <c r="U122" s="24" t="s">
         <v>829</v>
       </c>
       <c r="W122" s="1" t="s">
@@ -14207,13 +14189,13 @@
       <c r="F123" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="G123" s="28" t="s">
+      <c r="G123" s="25" t="s">
         <v>833</v>
       </c>
-      <c r="H123" s="27" t="s">
+      <c r="H123" s="24" t="s">
         <v>833</v>
       </c>
-      <c r="I123" s="29" t="s">
+      <c r="I123" s="26" t="s">
         <v>834</v>
       </c>
       <c r="J123" s="1">
@@ -14252,10 +14234,10 @@
       <c r="S123" s="8">
         <v>90</v>
       </c>
-      <c r="T123" s="27" t="s">
+      <c r="T123" s="24" t="s">
         <v>835</v>
       </c>
-      <c r="U123" s="27" t="s">
+      <c r="U123" s="24" t="s">
         <v>835</v>
       </c>
       <c r="W123" s="1" t="s">
@@ -14280,13 +14262,13 @@
       <c r="F124" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="G124" s="28" t="s">
+      <c r="G124" s="25" t="s">
         <v>839</v>
       </c>
-      <c r="H124" s="27" t="s">
+      <c r="H124" s="24" t="s">
         <v>839</v>
       </c>
-      <c r="I124" s="29" t="s">
+      <c r="I124" s="26" t="s">
         <v>840</v>
       </c>
       <c r="J124" s="1">
@@ -14325,10 +14307,10 @@
       <c r="S124" s="8">
         <v>90</v>
       </c>
-      <c r="T124" s="27" t="s">
+      <c r="T124" s="24" t="s">
         <v>841</v>
       </c>
-      <c r="U124" s="27" t="s">
+      <c r="U124" s="24" t="s">
         <v>841</v>
       </c>
       <c r="W124" s="1" t="s">
@@ -14353,13 +14335,13 @@
       <c r="F125" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="G125" s="28" t="s">
+      <c r="G125" s="25" t="s">
         <v>845</v>
       </c>
-      <c r="H125" s="27" t="s">
+      <c r="H125" s="24" t="s">
         <v>845</v>
       </c>
-      <c r="I125" s="29" t="s">
+      <c r="I125" s="26" t="s">
         <v>846</v>
       </c>
       <c r="J125" s="1">
@@ -14398,10 +14380,10 @@
       <c r="S125" s="8">
         <v>90</v>
       </c>
-      <c r="T125" s="27" t="s">
+      <c r="T125" s="24" t="s">
         <v>847</v>
       </c>
-      <c r="U125" s="27" t="s">
+      <c r="U125" s="24" t="s">
         <v>847</v>
       </c>
       <c r="W125" s="1" t="s">
@@ -14428,13 +14410,13 @@
       <c r="F126" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="G126" s="28" t="s">
+      <c r="G126" s="25" t="s">
         <v>851</v>
       </c>
-      <c r="H126" s="27" t="s">
+      <c r="H126" s="24" t="s">
         <v>851</v>
       </c>
-      <c r="I126" s="29" t="s">
+      <c r="I126" s="26" t="s">
         <v>852</v>
       </c>
       <c r="J126" s="1">
@@ -14473,10 +14455,10 @@
       <c r="S126" s="8">
         <v>90</v>
       </c>
-      <c r="T126" s="27" t="s">
+      <c r="T126" s="24" t="s">
         <v>853</v>
       </c>
-      <c r="U126" s="27" t="s">
+      <c r="U126" s="24" t="s">
         <v>853</v>
       </c>
       <c r="W126" s="1" t="s">
@@ -14503,13 +14485,13 @@
       <c r="F127" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="G127" s="28" t="s">
+      <c r="G127" s="25" t="s">
         <v>857</v>
       </c>
-      <c r="H127" s="27" t="s">
+      <c r="H127" s="24" t="s">
         <v>857</v>
       </c>
-      <c r="I127" s="29" t="s">
+      <c r="I127" s="26" t="s">
         <v>858</v>
       </c>
       <c r="J127" s="1">
@@ -14548,10 +14530,10 @@
       <c r="S127" s="8">
         <v>90</v>
       </c>
-      <c r="T127" s="27" t="s">
+      <c r="T127" s="24" t="s">
         <v>859</v>
       </c>
-      <c r="U127" s="27" t="s">
+      <c r="U127" s="24" t="s">
         <v>859</v>
       </c>
       <c r="W127" s="1" t="s">
@@ -14578,13 +14560,13 @@
       <c r="F128" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="G128" s="28" t="s">
+      <c r="G128" s="25" t="s">
         <v>863</v>
       </c>
-      <c r="H128" s="27" t="s">
+      <c r="H128" s="24" t="s">
         <v>863</v>
       </c>
-      <c r="I128" s="29" t="s">
+      <c r="I128" s="26" t="s">
         <v>864</v>
       </c>
       <c r="J128" s="1">
@@ -14623,10 +14605,10 @@
       <c r="S128" s="8">
         <v>90</v>
       </c>
-      <c r="T128" s="27" t="s">
+      <c r="T128" s="24" t="s">
         <v>865</v>
       </c>
-      <c r="U128" s="27" t="s">
+      <c r="U128" s="24" t="s">
         <v>865</v>
       </c>
       <c r="W128" s="1" t="s">
@@ -14653,13 +14635,13 @@
       <c r="F129" s="1" t="s">
         <v>868</v>
       </c>
-      <c r="G129" s="28" t="s">
+      <c r="G129" s="25" t="s">
         <v>869</v>
       </c>
-      <c r="H129" s="27" t="s">
+      <c r="H129" s="24" t="s">
         <v>869</v>
       </c>
-      <c r="I129" s="29" t="s">
+      <c r="I129" s="26" t="s">
         <v>870</v>
       </c>
       <c r="J129" s="1">
@@ -14698,10 +14680,10 @@
       <c r="S129" s="8">
         <v>90</v>
       </c>
-      <c r="T129" s="27" t="s">
+      <c r="T129" s="24" t="s">
         <v>871</v>
       </c>
-      <c r="U129" s="27" t="s">
+      <c r="U129" s="24" t="s">
         <v>871</v>
       </c>
       <c r="W129" s="1" t="s">
@@ -14728,13 +14710,13 @@
       <c r="F130" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="G130" s="28" t="s">
+      <c r="G130" s="25" t="s">
         <v>875</v>
       </c>
-      <c r="H130" s="27" t="s">
+      <c r="H130" s="24" t="s">
         <v>875</v>
       </c>
-      <c r="I130" s="29" t="s">
+      <c r="I130" s="26" t="s">
         <v>876</v>
       </c>
       <c r="J130" s="1">
@@ -14773,10 +14755,10 @@
       <c r="S130" s="8">
         <v>90</v>
       </c>
-      <c r="T130" s="27" t="s">
+      <c r="T130" s="24" t="s">
         <v>877</v>
       </c>
-      <c r="U130" s="27" t="s">
+      <c r="U130" s="24" t="s">
         <v>877</v>
       </c>
       <c r="W130" s="1" t="s">
@@ -14801,13 +14783,13 @@
       <c r="F131" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="G131" s="28" t="s">
+      <c r="G131" s="25" t="s">
         <v>881</v>
       </c>
-      <c r="H131" s="27" t="s">
+      <c r="H131" s="24" t="s">
         <v>881</v>
       </c>
-      <c r="I131" s="29" t="s">
+      <c r="I131" s="26" t="s">
         <v>882</v>
       </c>
       <c r="J131" s="1">
@@ -14846,10 +14828,10 @@
       <c r="S131" s="8">
         <v>92</v>
       </c>
-      <c r="T131" s="27" t="s">
+      <c r="T131" s="24" t="s">
         <v>883</v>
       </c>
-      <c r="U131" s="27" t="s">
+      <c r="U131" s="24" t="s">
         <v>883</v>
       </c>
       <c r="W131" s="1" t="s">
@@ -14872,13 +14854,13 @@
       <c r="F132" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="G132" s="28" t="s">
+      <c r="G132" s="25" t="s">
         <v>887</v>
       </c>
-      <c r="H132" s="27" t="s">
+      <c r="H132" s="24" t="s">
         <v>887</v>
       </c>
-      <c r="I132" s="29" t="s">
+      <c r="I132" s="26" t="s">
         <v>888</v>
       </c>
       <c r="J132" s="1">
@@ -14917,10 +14899,10 @@
       <c r="S132" s="8">
         <v>94</v>
       </c>
-      <c r="T132" s="27" t="s">
+      <c r="T132" s="24" t="s">
         <v>889</v>
       </c>
-      <c r="U132" s="27" t="s">
+      <c r="U132" s="24" t="s">
         <v>889</v>
       </c>
       <c r="W132" s="1" t="s">
@@ -14943,13 +14925,13 @@
       <c r="F133" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="G133" s="28" t="s">
+      <c r="G133" s="25" t="s">
         <v>893</v>
       </c>
-      <c r="H133" s="27" t="s">
+      <c r="H133" s="24" t="s">
         <v>893</v>
       </c>
-      <c r="I133" s="29" t="s">
+      <c r="I133" s="26" t="s">
         <v>894</v>
       </c>
       <c r="J133" s="1">
@@ -14988,10 +14970,10 @@
       <c r="S133" s="8">
         <v>96</v>
       </c>
-      <c r="T133" s="27" t="s">
+      <c r="T133" s="24" t="s">
         <v>895</v>
       </c>
-      <c r="U133" s="27" t="s">
+      <c r="U133" s="24" t="s">
         <v>895</v>
       </c>
       <c r="W133" s="1" t="s">
@@ -15014,13 +14996,13 @@
       <c r="F134" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="G134" s="28" t="s">
+      <c r="G134" s="25" t="s">
         <v>899</v>
       </c>
-      <c r="H134" s="27" t="s">
+      <c r="H134" s="24" t="s">
         <v>899</v>
       </c>
-      <c r="I134" s="29" t="s">
+      <c r="I134" s="26" t="s">
         <v>900</v>
       </c>
       <c r="J134" s="1">
@@ -15059,10 +15041,10 @@
       <c r="S134" s="8">
         <v>98</v>
       </c>
-      <c r="T134" s="27" t="s">
+      <c r="T134" s="24" t="s">
         <v>901</v>
       </c>
-      <c r="U134" s="27" t="s">
+      <c r="U134" s="24" t="s">
         <v>901</v>
       </c>
       <c r="W134" s="1" t="s">
@@ -15085,13 +15067,13 @@
       <c r="F135" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="G135" s="28" t="s">
+      <c r="G135" s="25" t="s">
         <v>904</v>
       </c>
-      <c r="H135" s="27" t="s">
+      <c r="H135" s="24" t="s">
         <v>904</v>
       </c>
-      <c r="I135" s="29" t="s">
+      <c r="I135" s="26" t="s">
         <v>905</v>
       </c>
       <c r="J135" s="1">
@@ -15130,10 +15112,10 @@
       <c r="S135" s="8">
         <v>99</v>
       </c>
-      <c r="T135" s="27" t="s">
+      <c r="T135" s="24" t="s">
         <v>456</v>
       </c>
-      <c r="U135" s="27" t="s">
+      <c r="U135" s="24" t="s">
         <v>456</v>
       </c>
       <c r="W135" s="1" t="s">
@@ -15158,13 +15140,13 @@
       <c r="F136" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="G136" s="28" t="s">
+      <c r="G136" s="25" t="s">
         <v>909</v>
       </c>
-      <c r="H136" s="27" t="s">
+      <c r="H136" s="24" t="s">
         <v>909</v>
       </c>
-      <c r="I136" s="29" t="s">
+      <c r="I136" s="26" t="s">
         <v>910</v>
       </c>
       <c r="J136" s="1">
@@ -15203,10 +15185,10 @@
       <c r="S136" s="8">
         <v>99.2</v>
       </c>
-      <c r="T136" s="27" t="s">
+      <c r="T136" s="24" t="s">
         <v>911</v>
       </c>
-      <c r="U136" s="27" t="s">
+      <c r="U136" s="24" t="s">
         <v>911</v>
       </c>
       <c r="W136" s="1" t="s">
@@ -15233,13 +15215,13 @@
       <c r="F137" s="1" t="s">
         <v>914</v>
       </c>
-      <c r="G137" s="28" t="s">
+      <c r="G137" s="25" t="s">
         <v>915</v>
       </c>
-      <c r="H137" s="27" t="s">
+      <c r="H137" s="24" t="s">
         <v>915</v>
       </c>
-      <c r="I137" s="29" t="s">
+      <c r="I137" s="26" t="s">
         <v>916</v>
       </c>
       <c r="J137" s="1">
@@ -15278,10 +15260,10 @@
       <c r="S137" s="8">
         <v>99.4</v>
       </c>
-      <c r="T137" s="27" t="s">
+      <c r="T137" s="24" t="s">
         <v>917</v>
       </c>
-      <c r="U137" s="27" t="s">
+      <c r="U137" s="24" t="s">
         <v>917</v>
       </c>
       <c r="W137" s="1" t="s">
@@ -15308,13 +15290,13 @@
       <c r="F138" s="1" t="s">
         <v>920</v>
       </c>
-      <c r="G138" s="28" t="s">
+      <c r="G138" s="25" t="s">
         <v>921</v>
       </c>
-      <c r="H138" s="27" t="s">
+      <c r="H138" s="24" t="s">
         <v>921</v>
       </c>
-      <c r="I138" s="29" t="s">
+      <c r="I138" s="26" t="s">
         <v>922</v>
       </c>
       <c r="J138" s="1">
@@ -15353,10 +15335,10 @@
       <c r="S138" s="8">
         <v>99.6</v>
       </c>
-      <c r="T138" s="27" t="s">
+      <c r="T138" s="24" t="s">
         <v>923</v>
       </c>
-      <c r="U138" s="27" t="s">
+      <c r="U138" s="24" t="s">
         <v>923</v>
       </c>
       <c r="W138" s="1" t="s">
@@ -15383,13 +15365,13 @@
       <c r="F139" s="1" t="s">
         <v>926</v>
       </c>
-      <c r="G139" s="28" t="s">
+      <c r="G139" s="25" t="s">
         <v>927</v>
       </c>
-      <c r="H139" s="27" t="s">
+      <c r="H139" s="24" t="s">
         <v>927</v>
       </c>
-      <c r="I139" s="29" t="s">
+      <c r="I139" s="26" t="s">
         <v>928</v>
       </c>
       <c r="J139" s="1">
@@ -15428,10 +15410,10 @@
       <c r="S139" s="8">
         <v>99.8</v>
       </c>
-      <c r="T139" s="27" t="s">
+      <c r="T139" s="24" t="s">
         <v>929</v>
       </c>
-      <c r="U139" s="27" t="s">
+      <c r="U139" s="24" t="s">
         <v>929</v>
       </c>
       <c r="W139" s="1" t="s">
@@ -15458,13 +15440,13 @@
       <c r="F140" s="1" t="s">
         <v>932</v>
       </c>
-      <c r="G140" s="28" t="s">
+      <c r="G140" s="25" t="s">
         <v>933</v>
       </c>
-      <c r="H140" s="27" t="s">
+      <c r="H140" s="24" t="s">
         <v>933</v>
       </c>
-      <c r="I140" s="29" t="s">
+      <c r="I140" s="26" t="s">
         <v>934</v>
       </c>
       <c r="J140" s="1">
@@ -15503,10 +15485,10 @@
       <c r="S140" s="8">
         <v>99.9</v>
       </c>
-      <c r="T140" s="27" t="s">
+      <c r="T140" s="24" t="s">
         <v>935</v>
       </c>
-      <c r="U140" s="27" t="s">
+      <c r="U140" s="24" t="s">
         <v>935</v>
       </c>
       <c r="W140" s="1" t="s">
@@ -15533,13 +15515,13 @@
       <c r="F141" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="G141" s="28" t="s">
+      <c r="G141" s="25" t="s">
         <v>939</v>
       </c>
-      <c r="H141" s="27" t="s">
+      <c r="H141" s="24" t="s">
         <v>939</v>
       </c>
-      <c r="I141" s="29" t="s">
+      <c r="I141" s="26" t="s">
         <v>940</v>
       </c>
       <c r="J141" s="1">
@@ -15578,10 +15560,10 @@
       <c r="S141" s="8">
         <v>99.92</v>
       </c>
-      <c r="T141" s="27" t="s">
+      <c r="T141" s="24" t="s">
         <v>941</v>
       </c>
-      <c r="U141" s="27" t="s">
+      <c r="U141" s="24" t="s">
         <v>941</v>
       </c>
       <c r="W141" s="1" t="s">
@@ -15608,13 +15590,13 @@
       <c r="F142" s="1" t="s">
         <v>944</v>
       </c>
-      <c r="G142" s="28" t="s">
+      <c r="G142" s="25" t="s">
         <v>945</v>
       </c>
-      <c r="H142" s="27" t="s">
+      <c r="H142" s="24" t="s">
         <v>945</v>
       </c>
-      <c r="I142" s="29" t="s">
+      <c r="I142" s="26" t="s">
         <v>946</v>
       </c>
       <c r="J142" s="1">
@@ -15653,10 +15635,10 @@
       <c r="S142" s="8">
         <v>99.94</v>
       </c>
-      <c r="T142" s="27" t="s">
+      <c r="T142" s="24" t="s">
         <v>947</v>
       </c>
-      <c r="U142" s="27" t="s">
+      <c r="U142" s="24" t="s">
         <v>947</v>
       </c>
       <c r="W142" s="1" t="s">
@@ -15683,13 +15665,13 @@
       <c r="F143" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="G143" s="28" t="s">
+      <c r="G143" s="25" t="s">
         <v>951</v>
       </c>
-      <c r="H143" s="27" t="s">
+      <c r="H143" s="24" t="s">
         <v>951</v>
       </c>
-      <c r="I143" s="29" t="s">
+      <c r="I143" s="26" t="s">
         <v>952</v>
       </c>
       <c r="J143" s="1">
@@ -15728,10 +15710,10 @@
       <c r="S143" s="8">
         <v>99.96</v>
       </c>
-      <c r="T143" s="27" t="s">
+      <c r="T143" s="24" t="s">
         <v>953</v>
       </c>
-      <c r="U143" s="27" t="s">
+      <c r="U143" s="24" t="s">
         <v>953</v>
       </c>
       <c r="W143" s="1" t="s">
@@ -15758,13 +15740,13 @@
       <c r="F144" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="G144" s="28" t="s">
+      <c r="G144" s="25" t="s">
         <v>957</v>
       </c>
-      <c r="H144" s="27" t="s">
+      <c r="H144" s="24" t="s">
         <v>957</v>
       </c>
-      <c r="I144" s="29" t="s">
+      <c r="I144" s="26" t="s">
         <v>958</v>
       </c>
       <c r="J144" s="1">
@@ -15803,10 +15785,10 @@
       <c r="S144" s="8">
         <v>99.98</v>
       </c>
-      <c r="T144" s="27" t="s">
+      <c r="T144" s="24" t="s">
         <v>959</v>
       </c>
-      <c r="U144" s="27" t="s">
+      <c r="U144" s="24" t="s">
         <v>959</v>
       </c>
       <c r="W144" s="1" t="s">
@@ -15878,10 +15860,10 @@
       <c r="S145" s="8">
         <v>99.99</v>
       </c>
-      <c r="T145" s="27" t="s">
+      <c r="T145" s="24" t="s">
         <v>965</v>
       </c>
-      <c r="U145" s="27" t="s">
+      <c r="U145" s="24" t="s">
         <v>965</v>
       </c>
       <c r="W145" s="1" t="s">
@@ -15896,10 +15878,10 @@
     <row r="146" s="3" customFormat="1" hidden="1" customHeight="1" spans="1:24">
       <c r="A146" s="16"/>
       <c r="B146" s="16"/>
-      <c r="C146" s="33" t="s">
+      <c r="C146" s="30" t="s">
         <v>966</v>
       </c>
-      <c r="D146" s="33" t="s">
+      <c r="D146" s="30" t="s">
         <v>967</v>
       </c>
       <c r="E146" s="3">
@@ -15914,7 +15896,7 @@
       <c r="H146" s="3" t="s">
         <v>970</v>
       </c>
-      <c r="I146" s="25" t="s">
+      <c r="I146" s="22" t="s">
         <v>971</v>
       </c>
       <c r="J146" s="3">
@@ -15952,10 +15934,10 @@
       <c r="S146" s="16">
         <v>99.99</v>
       </c>
-      <c r="T146" s="33" t="s">
+      <c r="T146" s="30" t="s">
         <v>973</v>
       </c>
-      <c r="U146" s="33" t="s">
+      <c r="U146" s="30" t="s">
         <v>973</v>
       </c>
       <c r="W146" s="3" t="s">
@@ -15968,10 +15950,10 @@
     <row r="147" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:24">
       <c r="A147" s="8"/>
       <c r="B147" s="8"/>
-      <c r="C147" s="27" t="s">
+      <c r="C147" s="24" t="s">
         <v>974</v>
       </c>
-      <c r="D147" s="27" t="s">
+      <c r="D147" s="24" t="s">
         <v>975</v>
       </c>
       <c r="E147" s="1">
@@ -16026,10 +16008,10 @@
       <c r="S147" s="8">
         <v>99.99</v>
       </c>
-      <c r="T147" s="27" t="s">
+      <c r="T147" s="24" t="s">
         <v>981</v>
       </c>
-      <c r="U147" s="27" t="s">
+      <c r="U147" s="24" t="s">
         <v>981</v>
       </c>
       <c r="W147" s="1" t="s">
@@ -16042,10 +16024,10 @@
     <row r="148" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:24">
       <c r="A148" s="8"/>
       <c r="B148" s="8"/>
-      <c r="C148" s="27" t="s">
+      <c r="C148" s="24" t="s">
         <v>982</v>
       </c>
-      <c r="D148" s="27" t="s">
+      <c r="D148" s="24" t="s">
         <v>983</v>
       </c>
       <c r="E148" s="1">
@@ -16100,10 +16082,10 @@
       <c r="S148" s="8">
         <v>99.99</v>
       </c>
-      <c r="T148" s="27" t="s">
+      <c r="T148" s="24" t="s">
         <v>989</v>
       </c>
-      <c r="U148" s="27" t="s">
+      <c r="U148" s="24" t="s">
         <v>989</v>
       </c>
       <c r="W148" s="1" t="s">
@@ -16116,10 +16098,10 @@
     <row r="149" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:24">
       <c r="A149" s="8"/>
       <c r="B149" s="8"/>
-      <c r="C149" s="27" t="s">
+      <c r="C149" s="24" t="s">
         <v>990</v>
       </c>
-      <c r="D149" s="27" t="s">
+      <c r="D149" s="24" t="s">
         <v>991</v>
       </c>
       <c r="E149" s="1">
@@ -16174,10 +16156,10 @@
       <c r="S149" s="8">
         <v>99.99</v>
       </c>
-      <c r="T149" s="27" t="s">
+      <c r="T149" s="24" t="s">
         <v>997</v>
       </c>
-      <c r="U149" s="27" t="s">
+      <c r="U149" s="24" t="s">
         <v>997</v>
       </c>
       <c r="W149" s="1" t="s">
@@ -16190,10 +16172,10 @@
     <row r="150" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:24">
       <c r="A150" s="8"/>
       <c r="B150" s="8"/>
-      <c r="C150" s="27" t="s">
+      <c r="C150" s="24" t="s">
         <v>998</v>
       </c>
-      <c r="D150" s="27" t="s">
+      <c r="D150" s="24" t="s">
         <v>999</v>
       </c>
       <c r="E150" s="1">
@@ -16248,10 +16230,10 @@
       <c r="S150" s="8">
         <v>99.99</v>
       </c>
-      <c r="T150" s="27" t="s">
+      <c r="T150" s="24" t="s">
         <v>1005</v>
       </c>
-      <c r="U150" s="27" t="s">
+      <c r="U150" s="24" t="s">
         <v>1005</v>
       </c>
       <c r="W150" s="1" t="s">
@@ -16264,10 +16246,10 @@
     <row r="151" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A151" s="8"/>
       <c r="B151" s="8"/>
-      <c r="C151" s="27" t="s">
+      <c r="C151" s="24" t="s">
         <v>1006</v>
       </c>
-      <c r="D151" s="27" t="s">
+      <c r="D151" s="24" t="s">
         <v>1007</v>
       </c>
       <c r="E151" s="1">
@@ -16321,10 +16303,10 @@
       <c r="S151" s="8">
         <v>99.99</v>
       </c>
-      <c r="T151" s="27" t="s">
+      <c r="T151" s="24" t="s">
         <v>1014</v>
       </c>
-      <c r="U151" s="27" t="s">
+      <c r="U151" s="24" t="s">
         <v>1014</v>
       </c>
       <c r="W151" s="1" t="s">
@@ -16339,10 +16321,10 @@
     <row r="152" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A152" s="8"/>
       <c r="B152" s="8"/>
-      <c r="C152" s="27" t="s">
+      <c r="C152" s="24" t="s">
         <v>1015</v>
       </c>
-      <c r="D152" s="27" t="s">
+      <c r="D152" s="24" t="s">
         <v>1016</v>
       </c>
       <c r="E152" s="1">
@@ -16396,10 +16378,10 @@
       <c r="S152" s="8">
         <v>99.99</v>
       </c>
-      <c r="T152" s="27" t="s">
+      <c r="T152" s="24" t="s">
         <v>1023</v>
       </c>
-      <c r="U152" s="27" t="s">
+      <c r="U152" s="24" t="s">
         <v>1023</v>
       </c>
       <c r="W152" s="1" t="s">
@@ -16414,10 +16396,10 @@
     <row r="153" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A153" s="8"/>
       <c r="B153" s="8"/>
-      <c r="C153" s="27" t="s">
+      <c r="C153" s="24" t="s">
         <v>1024</v>
       </c>
-      <c r="D153" s="27" t="s">
+      <c r="D153" s="24" t="s">
         <v>1025</v>
       </c>
       <c r="E153" s="1">
@@ -16471,10 +16453,10 @@
       <c r="S153" s="8">
         <v>99.99</v>
       </c>
-      <c r="T153" s="27" t="s">
+      <c r="T153" s="24" t="s">
         <v>1032</v>
       </c>
-      <c r="U153" s="27" t="s">
+      <c r="U153" s="24" t="s">
         <v>1032</v>
       </c>
       <c r="W153" s="1" t="s">
@@ -16489,10 +16471,10 @@
     <row r="154" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A154" s="8"/>
       <c r="B154" s="8"/>
-      <c r="C154" s="27" t="s">
+      <c r="C154" s="24" t="s">
         <v>1033</v>
       </c>
-      <c r="D154" s="27" t="s">
+      <c r="D154" s="24" t="s">
         <v>1034</v>
       </c>
       <c r="E154" s="1">
@@ -16546,10 +16528,10 @@
       <c r="S154" s="8">
         <v>99.99</v>
       </c>
-      <c r="T154" s="27" t="s">
+      <c r="T154" s="24" t="s">
         <v>1041</v>
       </c>
-      <c r="U154" s="27" t="s">
+      <c r="U154" s="24" t="s">
         <v>1041</v>
       </c>
       <c r="W154" s="1" t="s">
@@ -16564,10 +16546,10 @@
     <row r="155" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A155" s="8"/>
       <c r="B155" s="8"/>
-      <c r="C155" s="27" t="s">
+      <c r="C155" s="24" t="s">
         <v>1042</v>
       </c>
-      <c r="D155" s="27" t="s">
+      <c r="D155" s="24" t="s">
         <v>1043</v>
       </c>
       <c r="E155" s="1">
@@ -16621,10 +16603,10 @@
       <c r="S155" s="8">
         <v>99.99</v>
       </c>
-      <c r="T155" s="27" t="s">
+      <c r="T155" s="24" t="s">
         <v>1050</v>
       </c>
-      <c r="U155" s="27" t="s">
+      <c r="U155" s="24" t="s">
         <v>1050</v>
       </c>
       <c r="W155" s="1" t="s">
@@ -16639,10 +16621,10 @@
     <row r="156" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A156" s="8"/>
       <c r="B156" s="8"/>
-      <c r="C156" s="27" t="s">
+      <c r="C156" s="24" t="s">
         <v>1051</v>
       </c>
-      <c r="D156" s="27" t="s">
+      <c r="D156" s="24" t="s">
         <v>1052</v>
       </c>
       <c r="E156" s="1">
@@ -16696,10 +16678,10 @@
       <c r="S156" s="8">
         <v>99.99</v>
       </c>
-      <c r="T156" s="27" t="s">
+      <c r="T156" s="24" t="s">
         <v>1059</v>
       </c>
-      <c r="U156" s="27" t="s">
+      <c r="U156" s="24" t="s">
         <v>1059</v>
       </c>
       <c r="W156" s="1" t="s">
@@ -16714,10 +16696,10 @@
     <row r="157" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A157" s="8"/>
       <c r="B157" s="8"/>
-      <c r="C157" s="27" t="s">
+      <c r="C157" s="24" t="s">
         <v>1060</v>
       </c>
-      <c r="D157" s="27" t="s">
+      <c r="D157" s="24" t="s">
         <v>1061</v>
       </c>
       <c r="E157" s="1">
@@ -16771,10 +16753,10 @@
       <c r="S157" s="8">
         <v>99.99</v>
       </c>
-      <c r="T157" s="27" t="s">
+      <c r="T157" s="24" t="s">
         <v>1068</v>
       </c>
-      <c r="U157" s="27" t="s">
+      <c r="U157" s="24" t="s">
         <v>1068</v>
       </c>
       <c r="W157" s="1" t="s">
@@ -16789,10 +16771,10 @@
     <row r="158" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A158" s="8"/>
       <c r="B158" s="8"/>
-      <c r="C158" s="27" t="s">
+      <c r="C158" s="24" t="s">
         <v>1069</v>
       </c>
-      <c r="D158" s="27" t="s">
+      <c r="D158" s="24" t="s">
         <v>1070</v>
       </c>
       <c r="E158" s="1">
@@ -16846,10 +16828,10 @@
       <c r="S158" s="8">
         <v>99.99</v>
       </c>
-      <c r="T158" s="27" t="s">
+      <c r="T158" s="24" t="s">
         <v>1077</v>
       </c>
-      <c r="U158" s="27" t="s">
+      <c r="U158" s="24" t="s">
         <v>1077</v>
       </c>
       <c r="W158" s="1" t="s">
@@ -16864,10 +16846,10 @@
     <row r="159" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A159" s="8"/>
       <c r="B159" s="8"/>
-      <c r="C159" s="27" t="s">
+      <c r="C159" s="24" t="s">
         <v>1078</v>
       </c>
-      <c r="D159" s="27" t="s">
+      <c r="D159" s="24" t="s">
         <v>1079</v>
       </c>
       <c r="E159" s="1">
@@ -16921,10 +16903,10 @@
       <c r="S159" s="8">
         <v>99.99</v>
       </c>
-      <c r="T159" s="27" t="s">
+      <c r="T159" s="24" t="s">
         <v>1086</v>
       </c>
-      <c r="U159" s="27" t="s">
+      <c r="U159" s="24" t="s">
         <v>1086</v>
       </c>
       <c r="W159" s="1" t="s">
@@ -16939,10 +16921,10 @@
     <row r="160" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A160" s="8"/>
       <c r="B160" s="8"/>
-      <c r="C160" s="27" t="s">
+      <c r="C160" s="24" t="s">
         <v>1087</v>
       </c>
-      <c r="D160" s="27" t="s">
+      <c r="D160" s="24" t="s">
         <v>1088</v>
       </c>
       <c r="E160" s="1">
@@ -16996,10 +16978,10 @@
       <c r="S160" s="8">
         <v>99.99</v>
       </c>
-      <c r="T160" s="27" t="s">
+      <c r="T160" s="24" t="s">
         <v>1095</v>
       </c>
-      <c r="U160" s="27" t="s">
+      <c r="U160" s="24" t="s">
         <v>1095</v>
       </c>
       <c r="W160" s="1" t="s">
@@ -17014,10 +16996,10 @@
     <row r="161" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A161" s="8"/>
       <c r="B161" s="8"/>
-      <c r="C161" s="27" t="s">
+      <c r="C161" s="24" t="s">
         <v>1096</v>
       </c>
-      <c r="D161" s="27" t="s">
+      <c r="D161" s="24" t="s">
         <v>1097</v>
       </c>
       <c r="E161" s="1">
@@ -17071,10 +17053,10 @@
       <c r="S161" s="8">
         <v>99.99</v>
       </c>
-      <c r="T161" s="27" t="s">
+      <c r="T161" s="24" t="s">
         <v>1104</v>
       </c>
-      <c r="U161" s="27" t="s">
+      <c r="U161" s="24" t="s">
         <v>1104</v>
       </c>
       <c r="W161" s="1" t="s">
@@ -17089,10 +17071,10 @@
     <row r="162" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A162" s="8"/>
       <c r="B162" s="8"/>
-      <c r="C162" s="27" t="s">
+      <c r="C162" s="24" t="s">
         <v>1105</v>
       </c>
-      <c r="D162" s="27" t="s">
+      <c r="D162" s="24" t="s">
         <v>1106</v>
       </c>
       <c r="E162" s="1">
@@ -17146,10 +17128,10 @@
       <c r="S162" s="8">
         <v>99.99</v>
       </c>
-      <c r="T162" s="27" t="s">
+      <c r="T162" s="24" t="s">
         <v>1113</v>
       </c>
-      <c r="U162" s="27" t="s">
+      <c r="U162" s="24" t="s">
         <v>1113</v>
       </c>
       <c r="W162" s="1" t="s">
@@ -17164,10 +17146,10 @@
     <row r="163" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A163" s="8"/>
       <c r="B163" s="8"/>
-      <c r="C163" s="27" t="s">
+      <c r="C163" s="24" t="s">
         <v>1114</v>
       </c>
-      <c r="D163" s="27" t="s">
+      <c r="D163" s="24" t="s">
         <v>1115</v>
       </c>
       <c r="E163" s="1">
@@ -17182,7 +17164,7 @@
       <c r="H163" s="1" t="s">
         <v>1118</v>
       </c>
-      <c r="I163" s="34" t="s">
+      <c r="I163" s="31" t="s">
         <v>1119</v>
       </c>
       <c r="J163" s="1" t="s">
@@ -17221,10 +17203,10 @@
       <c r="S163" s="8">
         <v>99.99</v>
       </c>
-      <c r="T163" s="27" t="s">
+      <c r="T163" s="24" t="s">
         <v>1122</v>
       </c>
-      <c r="U163" s="27" t="s">
+      <c r="U163" s="24" t="s">
         <v>1122</v>
       </c>
       <c r="W163" s="1" t="s">
@@ -17239,10 +17221,10 @@
     <row r="164" s="4" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A164" s="18"/>
       <c r="B164" s="18"/>
-      <c r="C164" s="35" t="s">
+      <c r="C164" s="32" t="s">
         <v>1123</v>
       </c>
-      <c r="D164" s="35" t="s">
+      <c r="D164" s="32" t="s">
         <v>1124</v>
       </c>
       <c r="E164" s="4">
@@ -17257,7 +17239,7 @@
       <c r="H164" s="4" t="s">
         <v>1127</v>
       </c>
-      <c r="I164" s="36" t="s">
+      <c r="I164" s="33" t="s">
         <v>1128</v>
       </c>
       <c r="J164" s="4" t="s">
@@ -17296,10 +17278,10 @@
       <c r="S164" s="18">
         <v>99.99</v>
       </c>
-      <c r="T164" s="35" t="s">
+      <c r="T164" s="32" t="s">
         <v>1131</v>
       </c>
-      <c r="U164" s="35" t="s">
+      <c r="U164" s="32" t="s">
         <v>1131</v>
       </c>
       <c r="W164" s="4" t="s">
@@ -17314,10 +17296,10 @@
     <row r="165" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A165" s="8"/>
       <c r="B165" s="8"/>
-      <c r="C165" s="27" t="s">
+      <c r="C165" s="24" t="s">
         <v>1132</v>
       </c>
-      <c r="D165" s="27" t="s">
+      <c r="D165" s="24" t="s">
         <v>1133</v>
       </c>
       <c r="E165" s="1">
@@ -17326,19 +17308,19 @@
       <c r="F165" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="G165" s="34" t="s">
+      <c r="G165" s="31" t="s">
         <v>1135</v>
       </c>
-      <c r="H165" s="34" t="s">
+      <c r="H165" s="31" t="s">
         <v>1136</v>
       </c>
-      <c r="I165" s="34" t="s">
+      <c r="I165" s="31" t="s">
         <v>1137</v>
       </c>
-      <c r="J165" s="34" t="s">
+      <c r="J165" s="31" t="s">
         <v>1138</v>
       </c>
-      <c r="K165" s="34" t="s">
+      <c r="K165" s="31" t="s">
         <v>1139</v>
       </c>
       <c r="L165" s="1">
@@ -17371,10 +17353,10 @@
       <c r="S165" s="8">
         <v>99.99</v>
       </c>
-      <c r="T165" s="27" t="s">
+      <c r="T165" s="24" t="s">
         <v>1140</v>
       </c>
-      <c r="U165" s="27" t="s">
+      <c r="U165" s="24" t="s">
         <v>1140</v>
       </c>
       <c r="W165" s="1" t="s">
@@ -17387,10 +17369,10 @@
       <c r="Z165" s="8"/>
     </row>
     <row r="166" hidden="1" customHeight="1" spans="3:24">
-      <c r="C166" s="27" t="s">
+      <c r="C166" s="24" t="s">
         <v>1141</v>
       </c>
-      <c r="D166" s="27" t="s">
+      <c r="D166" s="24" t="s">
         <v>1142</v>
       </c>
       <c r="E166" s="1">
@@ -17399,19 +17381,19 @@
       <c r="F166" s="1" t="s">
         <v>1143</v>
       </c>
-      <c r="G166" s="34" t="s">
+      <c r="G166" s="31" t="s">
         <v>1144</v>
       </c>
-      <c r="H166" s="34" t="s">
+      <c r="H166" s="31" t="s">
         <v>1145</v>
       </c>
-      <c r="I166" s="34" t="s">
+      <c r="I166" s="31" t="s">
         <v>1146</v>
       </c>
-      <c r="J166" s="34" t="s">
+      <c r="J166" s="31" t="s">
         <v>1147</v>
       </c>
-      <c r="K166" s="34" t="s">
+      <c r="K166" s="31" t="s">
         <v>1148</v>
       </c>
       <c r="L166" s="1">
@@ -17444,10 +17426,10 @@
       <c r="S166" s="8">
         <v>99.99</v>
       </c>
-      <c r="T166" s="27" t="s">
+      <c r="T166" s="24" t="s">
         <v>1149</v>
       </c>
-      <c r="U166" s="27" t="s">
+      <c r="U166" s="24" t="s">
         <v>1149</v>
       </c>
       <c r="W166" s="1" t="s">
@@ -17458,10 +17440,10 @@
       </c>
     </row>
     <row r="167" hidden="1" customHeight="1" spans="3:24">
-      <c r="C167" s="27" t="s">
+      <c r="C167" s="24" t="s">
         <v>1150</v>
       </c>
-      <c r="D167" s="27" t="s">
+      <c r="D167" s="24" t="s">
         <v>1151</v>
       </c>
       <c r="E167" s="1">
@@ -17470,19 +17452,19 @@
       <c r="F167" s="1" t="s">
         <v>1152</v>
       </c>
-      <c r="G167" s="34" t="s">
+      <c r="G167" s="31" t="s">
         <v>1153</v>
       </c>
-      <c r="H167" s="34" t="s">
+      <c r="H167" s="31" t="s">
         <v>1154</v>
       </c>
-      <c r="I167" s="34" t="s">
+      <c r="I167" s="31" t="s">
         <v>1155</v>
       </c>
-      <c r="J167" s="34" t="s">
+      <c r="J167" s="31" t="s">
         <v>1156</v>
       </c>
-      <c r="K167" s="34" t="s">
+      <c r="K167" s="31" t="s">
         <v>1157</v>
       </c>
       <c r="L167" s="1">
@@ -17515,10 +17497,10 @@
       <c r="S167" s="8">
         <v>99.99</v>
       </c>
-      <c r="T167" s="27" t="s">
+      <c r="T167" s="24" t="s">
         <v>1158</v>
       </c>
-      <c r="U167" s="27" t="s">
+      <c r="U167" s="24" t="s">
         <v>1158</v>
       </c>
       <c r="W167" s="1" t="s">
@@ -17529,10 +17511,10 @@
       </c>
     </row>
     <row r="168" hidden="1" customHeight="1" spans="3:24">
-      <c r="C168" s="27" t="s">
+      <c r="C168" s="24" t="s">
         <v>1159</v>
       </c>
-      <c r="D168" s="27" t="s">
+      <c r="D168" s="24" t="s">
         <v>1160</v>
       </c>
       <c r="E168" s="1">
@@ -17541,19 +17523,19 @@
       <c r="F168" s="1" t="s">
         <v>1161</v>
       </c>
-      <c r="G168" s="34" t="s">
+      <c r="G168" s="31" t="s">
         <v>1162</v>
       </c>
-      <c r="H168" s="34" t="s">
+      <c r="H168" s="31" t="s">
         <v>1163</v>
       </c>
-      <c r="I168" s="34" t="s">
+      <c r="I168" s="31" t="s">
         <v>1164</v>
       </c>
-      <c r="J168" s="34" t="s">
+      <c r="J168" s="31" t="s">
         <v>1165</v>
       </c>
-      <c r="K168" s="34" t="s">
+      <c r="K168" s="31" t="s">
         <v>1166</v>
       </c>
       <c r="L168" s="1">
@@ -17586,10 +17568,10 @@
       <c r="S168" s="8">
         <v>99.99</v>
       </c>
-      <c r="T168" s="27" t="s">
+      <c r="T168" s="24" t="s">
         <v>1167</v>
       </c>
-      <c r="U168" s="27" t="s">
+      <c r="U168" s="24" t="s">
         <v>1167</v>
       </c>
       <c r="W168" s="1" t="s">
@@ -17600,10 +17582,10 @@
       </c>
     </row>
     <row r="169" hidden="1" customHeight="1" spans="3:24">
-      <c r="C169" s="27" t="s">
+      <c r="C169" s="24" t="s">
         <v>1168</v>
       </c>
-      <c r="D169" s="27" t="s">
+      <c r="D169" s="24" t="s">
         <v>1169</v>
       </c>
       <c r="E169" s="1">
@@ -17612,19 +17594,19 @@
       <c r="F169" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="G169" s="34" t="s">
+      <c r="G169" s="31" t="s">
         <v>1171</v>
       </c>
-      <c r="H169" s="34" t="s">
+      <c r="H169" s="31" t="s">
         <v>1172</v>
       </c>
-      <c r="I169" s="34" t="s">
+      <c r="I169" s="31" t="s">
         <v>1173</v>
       </c>
-      <c r="J169" s="34" t="s">
+      <c r="J169" s="31" t="s">
         <v>1174</v>
       </c>
-      <c r="K169" s="34" t="s">
+      <c r="K169" s="31" t="s">
         <v>1175</v>
       </c>
       <c r="L169" s="1">
@@ -17657,10 +17639,10 @@
       <c r="S169" s="8">
         <v>99.99</v>
       </c>
-      <c r="T169" s="27" t="s">
+      <c r="T169" s="24" t="s">
         <v>1176</v>
       </c>
-      <c r="U169" s="27" t="s">
+      <c r="U169" s="24" t="s">
         <v>1176</v>
       </c>
       <c r="W169" s="1" t="s">
@@ -17671,10 +17653,10 @@
       </c>
     </row>
     <row r="170" hidden="1" customHeight="1" spans="3:24">
-      <c r="C170" s="27" t="s">
+      <c r="C170" s="24" t="s">
         <v>1177</v>
       </c>
-      <c r="D170" s="27" t="s">
+      <c r="D170" s="24" t="s">
         <v>1178</v>
       </c>
       <c r="E170" s="1">
@@ -17683,19 +17665,19 @@
       <c r="F170" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="G170" s="34" t="s">
+      <c r="G170" s="31" t="s">
         <v>1179</v>
       </c>
-      <c r="H170" s="34" t="s">
+      <c r="H170" s="31" t="s">
         <v>1180</v>
       </c>
-      <c r="I170" s="34" t="s">
+      <c r="I170" s="31" t="s">
         <v>1181</v>
       </c>
-      <c r="J170" s="34" t="s">
+      <c r="J170" s="31" t="s">
         <v>1182</v>
       </c>
-      <c r="K170" s="34" t="s">
+      <c r="K170" s="31" t="s">
         <v>1183</v>
       </c>
       <c r="L170" s="1">
@@ -17728,10 +17710,10 @@
       <c r="S170" s="8">
         <v>99.99</v>
       </c>
-      <c r="T170" s="27" t="s">
+      <c r="T170" s="24" t="s">
         <v>1184</v>
       </c>
-      <c r="U170" s="27" t="s">
+      <c r="U170" s="24" t="s">
         <v>1184</v>
       </c>
       <c r="W170" s="1" t="s">
@@ -17744,10 +17726,10 @@
     <row r="171" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A171" s="8"/>
       <c r="B171" s="8"/>
-      <c r="C171" s="27" t="s">
+      <c r="C171" s="24" t="s">
         <v>1185</v>
       </c>
-      <c r="D171" s="27" t="s">
+      <c r="D171" s="24" t="s">
         <v>1186</v>
       </c>
       <c r="E171" s="1">
@@ -17756,19 +17738,19 @@
       <c r="F171" s="1" t="s">
         <v>1187</v>
       </c>
-      <c r="G171" s="34" t="s">
+      <c r="G171" s="31" t="s">
         <v>1188</v>
       </c>
-      <c r="H171" s="34" t="s">
+      <c r="H171" s="31" t="s">
         <v>1189</v>
       </c>
-      <c r="I171" s="34" t="s">
+      <c r="I171" s="31" t="s">
         <v>1190</v>
       </c>
-      <c r="J171" s="34" t="s">
+      <c r="J171" s="31" t="s">
         <v>1191</v>
       </c>
-      <c r="K171" s="34" t="s">
+      <c r="K171" s="31" t="s">
         <v>1192</v>
       </c>
       <c r="L171" s="1">
@@ -17801,10 +17783,10 @@
       <c r="S171" s="8">
         <v>99.99</v>
       </c>
-      <c r="T171" s="27" t="s">
+      <c r="T171" s="24" t="s">
         <v>1193</v>
       </c>
-      <c r="U171" s="27" t="s">
+      <c r="U171" s="24" t="s">
         <v>1193</v>
       </c>
       <c r="W171" s="1" t="s">
@@ -17819,10 +17801,10 @@
     <row r="172" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A172" s="8"/>
       <c r="B172" s="8"/>
-      <c r="C172" s="27" t="s">
+      <c r="C172" s="24" t="s">
         <v>1194</v>
       </c>
-      <c r="D172" s="27" t="s">
+      <c r="D172" s="24" t="s">
         <v>1195</v>
       </c>
       <c r="E172" s="1">
@@ -17831,19 +17813,19 @@
       <c r="F172" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="G172" s="34" t="s">
+      <c r="G172" s="31" t="s">
         <v>1197</v>
       </c>
-      <c r="H172" s="34" t="s">
+      <c r="H172" s="31" t="s">
         <v>1198</v>
       </c>
-      <c r="I172" s="34" t="s">
+      <c r="I172" s="31" t="s">
         <v>1199</v>
       </c>
-      <c r="J172" s="34" t="s">
+      <c r="J172" s="31" t="s">
         <v>1200</v>
       </c>
-      <c r="K172" s="34" t="s">
+      <c r="K172" s="31" t="s">
         <v>1201</v>
       </c>
       <c r="L172" s="1">
@@ -17876,10 +17858,10 @@
       <c r="S172" s="8">
         <v>99.99</v>
       </c>
-      <c r="T172" s="27" t="s">
+      <c r="T172" s="24" t="s">
         <v>1202</v>
       </c>
-      <c r="U172" s="27" t="s">
+      <c r="U172" s="24" t="s">
         <v>1202</v>
       </c>
       <c r="W172" s="1" t="s">
@@ -17894,10 +17876,10 @@
     <row r="173" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A173" s="8"/>
       <c r="B173" s="8"/>
-      <c r="C173" s="27" t="s">
+      <c r="C173" s="24" t="s">
         <v>1203</v>
       </c>
-      <c r="D173" s="27" t="s">
+      <c r="D173" s="24" t="s">
         <v>1204</v>
       </c>
       <c r="E173" s="1">
@@ -17906,19 +17888,19 @@
       <c r="F173" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="G173" s="34" t="s">
+      <c r="G173" s="31" t="s">
         <v>1206</v>
       </c>
-      <c r="H173" s="34" t="s">
+      <c r="H173" s="31" t="s">
         <v>1207</v>
       </c>
-      <c r="I173" s="34" t="s">
+      <c r="I173" s="31" t="s">
         <v>1208</v>
       </c>
-      <c r="J173" s="34" t="s">
+      <c r="J173" s="31" t="s">
         <v>1209</v>
       </c>
-      <c r="K173" s="34" t="s">
+      <c r="K173" s="31" t="s">
         <v>1210</v>
       </c>
       <c r="L173" s="1">
@@ -17951,10 +17933,10 @@
       <c r="S173" s="8">
         <v>99.99</v>
       </c>
-      <c r="T173" s="27" t="s">
+      <c r="T173" s="24" t="s">
         <v>1211</v>
       </c>
-      <c r="U173" s="27" t="s">
+      <c r="U173" s="24" t="s">
         <v>1211</v>
       </c>
       <c r="W173" s="1" t="s">
@@ -17969,10 +17951,10 @@
     <row r="174" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A174" s="8"/>
       <c r="B174" s="8"/>
-      <c r="C174" s="27" t="s">
+      <c r="C174" s="24" t="s">
         <v>1212</v>
       </c>
-      <c r="D174" s="27" t="s">
+      <c r="D174" s="24" t="s">
         <v>1213</v>
       </c>
       <c r="E174" s="1">
@@ -17981,19 +17963,19 @@
       <c r="F174" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="G174" s="34" t="s">
+      <c r="G174" s="31" t="s">
         <v>1215</v>
       </c>
-      <c r="H174" s="34" t="s">
+      <c r="H174" s="31" t="s">
         <v>1216</v>
       </c>
-      <c r="I174" s="34" t="s">
+      <c r="I174" s="31" t="s">
         <v>1217</v>
       </c>
-      <c r="J174" s="34" t="s">
+      <c r="J174" s="31" t="s">
         <v>1218</v>
       </c>
-      <c r="K174" s="34" t="s">
+      <c r="K174" s="31" t="s">
         <v>1219</v>
       </c>
       <c r="L174" s="1">
@@ -18026,10 +18008,10 @@
       <c r="S174" s="8">
         <v>99.99</v>
       </c>
-      <c r="T174" s="27" t="s">
+      <c r="T174" s="24" t="s">
         <v>1220</v>
       </c>
-      <c r="U174" s="27" t="s">
+      <c r="U174" s="24" t="s">
         <v>1220</v>
       </c>
       <c r="W174" s="1" t="s">
@@ -18044,10 +18026,10 @@
     <row r="175" s="1" customFormat="1" customHeight="1" spans="1:26">
       <c r="A175" s="8"/>
       <c r="B175" s="8"/>
-      <c r="C175" s="27" t="s">
+      <c r="C175" s="24" t="s">
         <v>1221</v>
       </c>
-      <c r="D175" s="27" t="s">
+      <c r="D175" s="24" t="s">
         <v>1222</v>
       </c>
       <c r="E175" s="1">
@@ -18056,19 +18038,19 @@
       <c r="F175" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="G175" s="34" t="s">
+      <c r="G175" s="31" t="s">
         <v>1224</v>
       </c>
-      <c r="H175" s="34" t="s">
+      <c r="H175" s="31" t="s">
         <v>1225</v>
       </c>
-      <c r="I175" s="34" t="s">
+      <c r="I175" s="31" t="s">
         <v>1226</v>
       </c>
-      <c r="J175" s="34" t="s">
+      <c r="J175" s="31" t="s">
         <v>1227</v>
       </c>
-      <c r="K175" s="34" t="s">
+      <c r="K175" s="31" t="s">
         <v>1228</v>
       </c>
       <c r="L175" s="1">
@@ -18101,10 +18083,10 @@
       <c r="S175" s="8">
         <v>99.99</v>
       </c>
-      <c r="T175" s="27" t="s">
+      <c r="T175" s="24" t="s">
         <v>1229</v>
       </c>
-      <c r="U175" s="27" t="s">
+      <c r="U175" s="24" t="s">
         <v>1229</v>
       </c>
       <c r="W175" s="1" t="s">
@@ -18119,10 +18101,10 @@
     <row r="176" s="1" customFormat="1" customHeight="1" spans="1:26">
       <c r="A176" s="8"/>
       <c r="B176" s="8"/>
-      <c r="C176" s="27" t="s">
+      <c r="C176" s="24" t="s">
         <v>1230</v>
       </c>
-      <c r="D176" s="27" t="s">
+      <c r="D176" s="24" t="s">
         <v>1231</v>
       </c>
       <c r="E176" s="1">
@@ -18131,19 +18113,19 @@
       <c r="F176" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="G176" s="34" t="s">
+      <c r="G176" s="31" t="s">
         <v>1233</v>
       </c>
-      <c r="H176" s="34" t="s">
+      <c r="H176" s="31" t="s">
         <v>1234</v>
       </c>
-      <c r="I176" s="34" t="s">
+      <c r="I176" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="J176" s="34" t="s">
+      <c r="J176" s="31" t="s">
         <v>1236</v>
       </c>
-      <c r="K176" s="34" t="s">
+      <c r="K176" s="31" t="s">
         <v>1237</v>
       </c>
       <c r="L176" s="1">
@@ -18176,10 +18158,10 @@
       <c r="S176" s="8">
         <v>99.99</v>
       </c>
-      <c r="T176" s="27" t="s">
+      <c r="T176" s="24" t="s">
         <v>1238</v>
       </c>
-      <c r="U176" s="27" t="s">
+      <c r="U176" s="24" t="s">
         <v>1238</v>
       </c>
       <c r="W176" s="1" t="s">
@@ -18194,10 +18176,10 @@
     <row r="177" s="1" customFormat="1" customHeight="1" spans="1:26">
       <c r="A177" s="8"/>
       <c r="B177" s="8"/>
-      <c r="C177" s="27" t="s">
+      <c r="C177" s="24" t="s">
         <v>1239</v>
       </c>
-      <c r="D177" s="27" t="s">
+      <c r="D177" s="24" t="s">
         <v>1240</v>
       </c>
       <c r="E177" s="1">
@@ -18206,19 +18188,19 @@
       <c r="F177" s="1" t="s">
         <v>1241</v>
       </c>
-      <c r="G177" s="34" t="s">
+      <c r="G177" s="31" t="s">
         <v>1242</v>
       </c>
-      <c r="H177" s="34" t="s">
+      <c r="H177" s="31" t="s">
         <v>1243</v>
       </c>
-      <c r="I177" s="34" t="s">
+      <c r="I177" s="31" t="s">
         <v>1244</v>
       </c>
-      <c r="J177" s="34" t="s">
+      <c r="J177" s="31" t="s">
         <v>1245</v>
       </c>
-      <c r="K177" s="34" t="s">
+      <c r="K177" s="31" t="s">
         <v>1246</v>
       </c>
       <c r="L177" s="1">
@@ -18251,10 +18233,10 @@
       <c r="S177" s="8">
         <v>99.99</v>
       </c>
-      <c r="T177" s="27" t="s">
+      <c r="T177" s="24" t="s">
         <v>1247</v>
       </c>
-      <c r="U177" s="27" t="s">
+      <c r="U177" s="24" t="s">
         <v>1247</v>
       </c>
       <c r="W177" s="1" t="s">
@@ -18269,10 +18251,10 @@
     <row r="178" s="1" customFormat="1" customHeight="1" spans="1:26">
       <c r="A178" s="8"/>
       <c r="B178" s="8"/>
-      <c r="C178" s="27" t="s">
+      <c r="C178" s="24" t="s">
         <v>1248</v>
       </c>
-      <c r="D178" s="27" t="s">
+      <c r="D178" s="24" t="s">
         <v>1249</v>
       </c>
       <c r="E178" s="1">
@@ -18281,19 +18263,19 @@
       <c r="F178" s="1" t="s">
         <v>1250</v>
       </c>
-      <c r="G178" s="34" t="s">
+      <c r="G178" s="31" t="s">
         <v>1251</v>
       </c>
-      <c r="H178" s="34" t="s">
+      <c r="H178" s="31" t="s">
         <v>1252</v>
       </c>
-      <c r="I178" s="34" t="s">
+      <c r="I178" s="31" t="s">
         <v>1253</v>
       </c>
-      <c r="J178" s="34" t="s">
+      <c r="J178" s="31" t="s">
         <v>1254</v>
       </c>
-      <c r="K178" s="34" t="s">
+      <c r="K178" s="31" t="s">
         <v>1255</v>
       </c>
       <c r="L178" s="1">
@@ -18326,10 +18308,10 @@
       <c r="S178" s="8">
         <v>99.99</v>
       </c>
-      <c r="T178" s="27" t="s">
+      <c r="T178" s="24" t="s">
         <v>1256</v>
       </c>
-      <c r="U178" s="27" t="s">
+      <c r="U178" s="24" t="s">
         <v>1256</v>
       </c>
       <c r="W178" s="1" t="s">
@@ -18344,10 +18326,10 @@
     <row r="179" s="1" customFormat="1" customHeight="1" spans="1:26">
       <c r="A179" s="8"/>
       <c r="B179" s="8"/>
-      <c r="C179" s="27" t="s">
+      <c r="C179" s="24" t="s">
         <v>1257</v>
       </c>
-      <c r="D179" s="27" t="s">
+      <c r="D179" s="24" t="s">
         <v>1258</v>
       </c>
       <c r="E179" s="1">
@@ -18356,19 +18338,19 @@
       <c r="F179" s="1" t="s">
         <v>1259</v>
       </c>
-      <c r="G179" s="34" t="s">
+      <c r="G179" s="31" t="s">
         <v>1260</v>
       </c>
-      <c r="H179" s="34" t="s">
+      <c r="H179" s="31" t="s">
         <v>1261</v>
       </c>
-      <c r="I179" s="34" t="s">
+      <c r="I179" s="31" t="s">
         <v>1262</v>
       </c>
-      <c r="J179" s="34" t="s">
+      <c r="J179" s="31" t="s">
         <v>1263</v>
       </c>
-      <c r="K179" s="34" t="s">
+      <c r="K179" s="31" t="s">
         <v>1264</v>
       </c>
       <c r="L179" s="1">
@@ -18401,10 +18383,10 @@
       <c r="S179" s="8">
         <v>99.99</v>
       </c>
-      <c r="T179" s="27" t="s">
+      <c r="T179" s="24" t="s">
         <v>1265</v>
       </c>
-      <c r="U179" s="27" t="s">
+      <c r="U179" s="24" t="s">
         <v>1265</v>
       </c>
       <c r="W179" s="1" t="s">
@@ -18419,10 +18401,10 @@
     <row r="180" s="1" customFormat="1" customHeight="1" spans="1:26">
       <c r="A180" s="8"/>
       <c r="B180" s="8"/>
-      <c r="C180" s="27" t="s">
+      <c r="C180" s="24" t="s">
         <v>1266</v>
       </c>
-      <c r="D180" s="27" t="s">
+      <c r="D180" s="24" t="s">
         <v>1267</v>
       </c>
       <c r="E180" s="1">
@@ -18431,19 +18413,19 @@
       <c r="F180" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="G180" s="34" t="s">
+      <c r="G180" s="31" t="s">
         <v>1269</v>
       </c>
-      <c r="H180" s="34" t="s">
+      <c r="H180" s="31" t="s">
         <v>1270</v>
       </c>
-      <c r="I180" s="34" t="s">
+      <c r="I180" s="31" t="s">
         <v>1271</v>
       </c>
-      <c r="J180" s="34" t="s">
+      <c r="J180" s="31" t="s">
         <v>1272</v>
       </c>
-      <c r="K180" s="34" t="s">
+      <c r="K180" s="31" t="s">
         <v>1273</v>
       </c>
       <c r="L180" s="1">
@@ -18476,10 +18458,10 @@
       <c r="S180" s="8">
         <v>99.99</v>
       </c>
-      <c r="T180" s="27" t="s">
+      <c r="T180" s="24" t="s">
         <v>1274</v>
       </c>
-      <c r="U180" s="27" t="s">
+      <c r="U180" s="24" t="s">
         <v>1274</v>
       </c>
       <c r="W180" s="1" t="s">
@@ -18494,10 +18476,10 @@
     <row r="181" s="3" customFormat="1" customHeight="1" spans="1:24">
       <c r="A181" s="16"/>
       <c r="B181" s="16"/>
-      <c r="C181" s="37" t="s">
+      <c r="C181" s="30" t="s">
         <v>1275</v>
       </c>
-      <c r="D181" s="37" t="s">
+      <c r="D181" s="30" t="s">
         <v>1276</v>
       </c>
       <c r="E181" s="3">
@@ -18506,19 +18488,19 @@
       <c r="F181" s="3" t="s">
         <v>1277</v>
       </c>
-      <c r="G181" s="38" t="s">
+      <c r="G181" s="34" t="s">
         <v>1278</v>
       </c>
-      <c r="H181" s="38" t="s">
+      <c r="H181" s="34" t="s">
         <v>1279</v>
       </c>
-      <c r="I181" s="38" t="s">
+      <c r="I181" s="34" t="s">
         <v>1280</v>
       </c>
-      <c r="J181" s="38" t="s">
+      <c r="J181" s="34" t="s">
         <v>1281</v>
       </c>
-      <c r="K181" s="38" t="s">
+      <c r="K181" s="34" t="s">
         <v>1282</v>
       </c>
       <c r="L181" s="3">
@@ -18546,10 +18528,10 @@
       <c r="S181" s="16">
         <v>99.99</v>
       </c>
-      <c r="T181" s="33" t="s">
+      <c r="T181" s="30" t="s">
         <v>1283</v>
       </c>
-      <c r="U181" s="33" t="s">
+      <c r="U181" s="30" t="s">
         <v>1283</v>
       </c>
       <c r="W181" s="3" t="s">
@@ -18560,12 +18542,12 @@
       </c>
     </row>
     <row r="182" s="5" customFormat="1" customHeight="1" spans="1:24">
-      <c r="A182" s="22"/>
-      <c r="B182" s="22"/>
-      <c r="C182" s="39" t="s">
+      <c r="A182" s="12"/>
+      <c r="B182" s="12"/>
+      <c r="C182" s="35" t="s">
         <v>1284</v>
       </c>
-      <c r="D182" s="39" t="s">
+      <c r="D182" s="35" t="s">
         <v>1285</v>
       </c>
       <c r="E182" s="5">
@@ -18574,19 +18556,19 @@
       <c r="F182" s="5" t="s">
         <v>1286</v>
       </c>
-      <c r="G182" s="40" t="s">
+      <c r="G182" s="31" t="s">
         <v>1287</v>
       </c>
-      <c r="H182" s="40" t="s">
+      <c r="H182" s="31" t="s">
         <v>1288</v>
       </c>
-      <c r="I182" s="40" t="s">
+      <c r="I182" s="31" t="s">
         <v>1289</v>
       </c>
-      <c r="J182" s="40" t="s">
+      <c r="J182" s="31" t="s">
         <v>1290</v>
       </c>
-      <c r="K182" s="40" t="s">
+      <c r="K182" s="31" t="s">
         <v>1291</v>
       </c>
       <c r="L182" s="5">
@@ -18609,21 +18591,21 @@
         <f t="shared" ref="P182:P215" si="69">P181+5</f>
         <v>105</v>
       </c>
-      <c r="Q182" s="22">
+      <c r="Q182" s="12">
         <f t="shared" si="66"/>
         <v>245</v>
       </c>
-      <c r="R182" s="22">
+      <c r="R182" s="12">
         <f t="shared" ref="R182:R195" si="70">R181+4</f>
         <v>154</v>
       </c>
-      <c r="S182" s="22">
+      <c r="S182" s="12">
         <v>99.99</v>
       </c>
-      <c r="T182" s="39" t="s">
+      <c r="T182" s="35" t="s">
         <v>1292</v>
       </c>
-      <c r="U182" s="39" t="s">
+      <c r="U182" s="35" t="s">
         <v>1292</v>
       </c>
       <c r="W182" s="5" t="s">
@@ -18636,10 +18618,10 @@
     <row r="183" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A183" s="8"/>
       <c r="B183" s="8"/>
-      <c r="C183" s="27" t="s">
+      <c r="C183" s="24" t="s">
         <v>1293</v>
       </c>
-      <c r="D183" s="27" t="s">
+      <c r="D183" s="24" t="s">
         <v>1294</v>
       </c>
       <c r="E183" s="1">
@@ -18648,19 +18630,19 @@
       <c r="F183" s="1" t="s">
         <v>1295</v>
       </c>
-      <c r="G183" s="40" t="s">
+      <c r="G183" s="31" t="s">
         <v>1296</v>
       </c>
-      <c r="H183" s="40" t="s">
+      <c r="H183" s="31" t="s">
         <v>1297</v>
       </c>
-      <c r="I183" s="40" t="s">
+      <c r="I183" s="31" t="s">
         <v>1298</v>
       </c>
-      <c r="J183" s="40" t="s">
+      <c r="J183" s="31" t="s">
         <v>1299</v>
       </c>
-      <c r="K183" s="40" t="s">
+      <c r="K183" s="31" t="s">
         <v>1300</v>
       </c>
       <c r="L183" s="1">
@@ -18694,10 +18676,10 @@
       <c r="S183" s="8">
         <v>99.99</v>
       </c>
-      <c r="T183" s="39" t="s">
+      <c r="T183" s="35" t="s">
         <v>512</v>
       </c>
-      <c r="U183" s="39" t="s">
+      <c r="U183" s="35" t="s">
         <v>512</v>
       </c>
       <c r="W183" s="1" t="s">
@@ -18710,10 +18692,10 @@
     <row r="184" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A184" s="8"/>
       <c r="B184" s="8"/>
-      <c r="C184" s="27" t="s">
+      <c r="C184" s="24" t="s">
         <v>1301</v>
       </c>
-      <c r="D184" s="27" t="s">
+      <c r="D184" s="24" t="s">
         <v>1302</v>
       </c>
       <c r="E184" s="1">
@@ -18722,19 +18704,19 @@
       <c r="F184" s="1" t="s">
         <v>1303</v>
       </c>
-      <c r="G184" s="40" t="s">
+      <c r="G184" s="31" t="s">
         <v>1304</v>
       </c>
-      <c r="H184" s="40" t="s">
+      <c r="H184" s="31" t="s">
         <v>1305</v>
       </c>
-      <c r="I184" s="40" t="s">
+      <c r="I184" s="31" t="s">
         <v>1306</v>
       </c>
-      <c r="J184" s="40" t="s">
+      <c r="J184" s="31" t="s">
         <v>1307</v>
       </c>
-      <c r="K184" s="40" t="s">
+      <c r="K184" s="31" t="s">
         <v>1308</v>
       </c>
       <c r="L184" s="1">
@@ -18768,10 +18750,10 @@
       <c r="S184" s="8">
         <v>99.99</v>
       </c>
-      <c r="T184" s="39" t="s">
+      <c r="T184" s="35" t="s">
         <v>1309</v>
       </c>
-      <c r="U184" s="39" t="s">
+      <c r="U184" s="35" t="s">
         <v>1309</v>
       </c>
       <c r="W184" s="1" t="s">
@@ -18784,10 +18766,10 @@
     <row r="185" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A185" s="8"/>
       <c r="B185" s="8"/>
-      <c r="C185" s="27" t="s">
+      <c r="C185" s="24" t="s">
         <v>1310</v>
       </c>
-      <c r="D185" s="27" t="s">
+      <c r="D185" s="24" t="s">
         <v>1311</v>
       </c>
       <c r="E185" s="1">
@@ -18796,19 +18778,19 @@
       <c r="F185" s="1" t="s">
         <v>1312</v>
       </c>
-      <c r="G185" s="40" t="s">
+      <c r="G185" s="31" t="s">
         <v>1313</v>
       </c>
-      <c r="H185" s="40" t="s">
+      <c r="H185" s="31" t="s">
         <v>1314</v>
       </c>
-      <c r="I185" s="40" t="s">
+      <c r="I185" s="31" t="s">
         <v>1315</v>
       </c>
-      <c r="J185" s="40" t="s">
+      <c r="J185" s="31" t="s">
         <v>1316</v>
       </c>
-      <c r="K185" s="40" t="s">
+      <c r="K185" s="31" t="s">
         <v>1278</v>
       </c>
       <c r="L185" s="1">
@@ -18842,10 +18824,10 @@
       <c r="S185" s="8">
         <v>99.99</v>
       </c>
-      <c r="T185" s="39" t="s">
+      <c r="T185" s="35" t="s">
         <v>1317</v>
       </c>
-      <c r="U185" s="39" t="s">
+      <c r="U185" s="35" t="s">
         <v>1317</v>
       </c>
       <c r="W185" s="1" t="s">
@@ -18856,38 +18838,34 @@
       </c>
     </row>
     <row r="186" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A186" s="7" t="s">
+      <c r="A186" s="7"/>
+      <c r="B186" s="7"/>
+      <c r="C186" s="36" t="s">
         <v>1318</v>
       </c>
-      <c r="B186" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C186" s="41" t="s">
+      <c r="D186" s="36" t="s">
         <v>1319</v>
-      </c>
-      <c r="D186" s="41" t="s">
-        <v>1320</v>
       </c>
       <c r="E186" s="6">
         <v>6</v>
       </c>
       <c r="F186" s="6" t="s">
+        <v>1320</v>
+      </c>
+      <c r="G186" s="37" t="s">
         <v>1321</v>
       </c>
-      <c r="G186" s="42" t="s">
+      <c r="H186" s="37" t="s">
         <v>1322</v>
       </c>
-      <c r="H186" s="42" t="s">
+      <c r="I186" s="37" t="s">
         <v>1323</v>
       </c>
-      <c r="I186" s="42" t="s">
+      <c r="J186" s="37" t="s">
         <v>1324</v>
       </c>
-      <c r="J186" s="42" t="s">
+      <c r="K186" s="37" t="s">
         <v>1325</v>
-      </c>
-      <c r="K186" s="42" t="s">
-        <v>1326</v>
       </c>
       <c r="L186" s="6">
         <f t="shared" si="50"/>
@@ -18920,10 +18898,10 @@
       <c r="S186" s="7">
         <v>99.99</v>
       </c>
-      <c r="T186" s="41" t="s">
+      <c r="T186" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U186" s="41" t="s">
+      <c r="U186" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W186" s="6" t="s">
@@ -18936,38 +18914,34 @@
       <c r="Z186" s="7"/>
     </row>
     <row r="187" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A187" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B187" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C187" s="41" t="s">
+      <c r="A187" s="7"/>
+      <c r="B187" s="7"/>
+      <c r="C187" s="36" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D187" s="36" t="s">
         <v>1327</v>
-      </c>
-      <c r="D187" s="41" t="s">
-        <v>1328</v>
       </c>
       <c r="E187" s="6">
         <v>6</v>
       </c>
       <c r="F187" s="6" t="s">
+        <v>1328</v>
+      </c>
+      <c r="G187" s="37" t="s">
         <v>1329</v>
       </c>
-      <c r="G187" s="42" t="s">
+      <c r="H187" s="37" t="s">
         <v>1330</v>
       </c>
-      <c r="H187" s="42" t="s">
+      <c r="I187" s="37" t="s">
         <v>1331</v>
       </c>
-      <c r="I187" s="42" t="s">
+      <c r="J187" s="37" t="s">
         <v>1332</v>
       </c>
-      <c r="J187" s="42" t="s">
+      <c r="K187" s="37" t="s">
         <v>1333</v>
-      </c>
-      <c r="K187" s="42" t="s">
-        <v>1334</v>
       </c>
       <c r="L187" s="6">
         <f t="shared" si="50"/>
@@ -19000,10 +18974,10 @@
       <c r="S187" s="7">
         <v>99.99</v>
       </c>
-      <c r="T187" s="41" t="s">
+      <c r="T187" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U187" s="41" t="s">
+      <c r="U187" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W187" s="6" t="s">
@@ -19016,38 +18990,34 @@
       <c r="Z187" s="7"/>
     </row>
     <row r="188" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A188" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B188" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C188" s="41" t="s">
+      <c r="A188" s="7"/>
+      <c r="B188" s="7"/>
+      <c r="C188" s="36" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D188" s="36" t="s">
         <v>1335</v>
-      </c>
-      <c r="D188" s="41" t="s">
-        <v>1336</v>
       </c>
       <c r="E188" s="6">
         <v>6</v>
       </c>
       <c r="F188" s="6" t="s">
+        <v>1336</v>
+      </c>
+      <c r="G188" s="37" t="s">
         <v>1337</v>
       </c>
-      <c r="G188" s="42" t="s">
+      <c r="H188" s="37" t="s">
         <v>1338</v>
       </c>
-      <c r="H188" s="42" t="s">
+      <c r="I188" s="37" t="s">
         <v>1339</v>
       </c>
-      <c r="I188" s="42" t="s">
+      <c r="J188" s="37" t="s">
         <v>1340</v>
       </c>
-      <c r="J188" s="42" t="s">
+      <c r="K188" s="37" t="s">
         <v>1341</v>
-      </c>
-      <c r="K188" s="42" t="s">
-        <v>1342</v>
       </c>
       <c r="L188" s="6">
         <f t="shared" si="50"/>
@@ -19080,10 +19050,10 @@
       <c r="S188" s="7">
         <v>99.99</v>
       </c>
-      <c r="T188" s="41" t="s">
+      <c r="T188" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U188" s="41" t="s">
+      <c r="U188" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W188" s="6" t="s">
@@ -19096,38 +19066,34 @@
       <c r="Z188" s="7"/>
     </row>
     <row r="189" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A189" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B189" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C189" s="41" t="s">
+      <c r="A189" s="7"/>
+      <c r="B189" s="7"/>
+      <c r="C189" s="36" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D189" s="36" t="s">
         <v>1343</v>
-      </c>
-      <c r="D189" s="41" t="s">
-        <v>1344</v>
       </c>
       <c r="E189" s="6">
         <v>6</v>
       </c>
       <c r="F189" s="6" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G189" s="37" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H189" s="37" t="s">
         <v>1345</v>
       </c>
-      <c r="G189" s="42" t="s">
-        <v>1136</v>
-      </c>
-      <c r="H189" s="42" t="s">
+      <c r="I189" s="37" t="s">
         <v>1346</v>
       </c>
-      <c r="I189" s="42" t="s">
+      <c r="J189" s="37" t="s">
         <v>1347</v>
       </c>
-      <c r="J189" s="42" t="s">
+      <c r="K189" s="37" t="s">
         <v>1348</v>
-      </c>
-      <c r="K189" s="42" t="s">
-        <v>1349</v>
       </c>
       <c r="L189" s="6">
         <f t="shared" si="50"/>
@@ -19160,10 +19126,10 @@
       <c r="S189" s="7">
         <v>99.99</v>
       </c>
-      <c r="T189" s="41" t="s">
+      <c r="T189" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U189" s="41" t="s">
+      <c r="U189" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W189" s="6" t="s">
@@ -19176,38 +19142,34 @@
       <c r="Z189" s="7"/>
     </row>
     <row r="190" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A190" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B190" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C190" s="41" t="s">
+      <c r="A190" s="7"/>
+      <c r="B190" s="7"/>
+      <c r="C190" s="36" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D190" s="36" t="s">
         <v>1350</v>
-      </c>
-      <c r="D190" s="41" t="s">
-        <v>1351</v>
       </c>
       <c r="E190" s="6">
         <v>6</v>
       </c>
       <c r="F190" s="6" t="s">
+        <v>1351</v>
+      </c>
+      <c r="G190" s="37" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H190" s="37" t="s">
         <v>1352</v>
       </c>
-      <c r="G190" s="42" t="s">
-        <v>1145</v>
-      </c>
-      <c r="H190" s="42" t="s">
+      <c r="I190" s="37" t="s">
         <v>1353</v>
       </c>
-      <c r="I190" s="42" t="s">
+      <c r="J190" s="37" t="s">
         <v>1354</v>
       </c>
-      <c r="J190" s="42" t="s">
+      <c r="K190" s="37" t="s">
         <v>1355</v>
-      </c>
-      <c r="K190" s="42" t="s">
-        <v>1356</v>
       </c>
       <c r="L190" s="6">
         <f t="shared" si="50"/>
@@ -19240,10 +19202,10 @@
       <c r="S190" s="7">
         <v>99.99</v>
       </c>
-      <c r="T190" s="41" t="s">
+      <c r="T190" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U190" s="41" t="s">
+      <c r="U190" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W190" s="6" t="s">
@@ -19256,38 +19218,34 @@
       <c r="Z190" s="7"/>
     </row>
     <row r="191" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A191" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B191" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C191" s="41" t="s">
+      <c r="A191" s="7"/>
+      <c r="B191" s="7"/>
+      <c r="C191" s="36" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D191" s="36" t="s">
         <v>1357</v>
-      </c>
-      <c r="D191" s="41" t="s">
-        <v>1358</v>
       </c>
       <c r="E191" s="6">
         <v>6</v>
       </c>
       <c r="F191" s="6" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G191" s="37" t="s">
+        <v>1154</v>
+      </c>
+      <c r="H191" s="37" t="s">
         <v>1359</v>
       </c>
-      <c r="G191" s="42" t="s">
-        <v>1154</v>
-      </c>
-      <c r="H191" s="42" t="s">
+      <c r="I191" s="37" t="s">
         <v>1360</v>
       </c>
-      <c r="I191" s="42" t="s">
+      <c r="J191" s="37" t="s">
         <v>1361</v>
       </c>
-      <c r="J191" s="42" t="s">
+      <c r="K191" s="37" t="s">
         <v>1362</v>
-      </c>
-      <c r="K191" s="42" t="s">
-        <v>1363</v>
       </c>
       <c r="L191" s="6">
         <f t="shared" si="50"/>
@@ -19320,10 +19278,10 @@
       <c r="S191" s="7">
         <v>99.99</v>
       </c>
-      <c r="T191" s="41" t="s">
+      <c r="T191" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U191" s="41" t="s">
+      <c r="U191" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W191" s="6" t="s">
@@ -19336,38 +19294,34 @@
       <c r="Z191" s="7"/>
     </row>
     <row r="192" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A192" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B192" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C192" s="41" t="s">
+      <c r="A192" s="7"/>
+      <c r="B192" s="7"/>
+      <c r="C192" s="36" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D192" s="36" t="s">
         <v>1364</v>
-      </c>
-      <c r="D192" s="41" t="s">
-        <v>1365</v>
       </c>
       <c r="E192" s="6">
         <v>6</v>
       </c>
       <c r="F192" s="6" t="s">
+        <v>1365</v>
+      </c>
+      <c r="G192" s="37" t="s">
+        <v>1163</v>
+      </c>
+      <c r="H192" s="37" t="s">
         <v>1366</v>
       </c>
-      <c r="G192" s="42" t="s">
-        <v>1163</v>
-      </c>
-      <c r="H192" s="42" t="s">
+      <c r="I192" s="37" t="s">
         <v>1367</v>
       </c>
-      <c r="I192" s="42" t="s">
+      <c r="J192" s="37" t="s">
         <v>1368</v>
       </c>
-      <c r="J192" s="42" t="s">
+      <c r="K192" s="37" t="s">
         <v>1369</v>
-      </c>
-      <c r="K192" s="42" t="s">
-        <v>1370</v>
       </c>
       <c r="L192" s="6">
         <f t="shared" si="50"/>
@@ -19400,10 +19354,10 @@
       <c r="S192" s="7">
         <v>99.99</v>
       </c>
-      <c r="T192" s="41" t="s">
+      <c r="T192" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U192" s="41" t="s">
+      <c r="U192" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W192" s="6" t="s">
@@ -19416,38 +19370,34 @@
       <c r="Z192" s="7"/>
     </row>
     <row r="193" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A193" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B193" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C193" s="41" t="s">
+      <c r="A193" s="7"/>
+      <c r="B193" s="7"/>
+      <c r="C193" s="36" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D193" s="36" t="s">
         <v>1371</v>
-      </c>
-      <c r="D193" s="41" t="s">
-        <v>1372</v>
       </c>
       <c r="E193" s="6">
         <v>6</v>
       </c>
       <c r="F193" s="6" t="s">
+        <v>1372</v>
+      </c>
+      <c r="G193" s="37" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H193" s="37" t="s">
         <v>1373</v>
       </c>
-      <c r="G193" s="42" t="s">
-        <v>1172</v>
-      </c>
-      <c r="H193" s="42" t="s">
+      <c r="I193" s="37" t="s">
         <v>1374</v>
       </c>
-      <c r="I193" s="42" t="s">
+      <c r="J193" s="37" t="s">
         <v>1375</v>
       </c>
-      <c r="J193" s="42" t="s">
+      <c r="K193" s="37" t="s">
         <v>1376</v>
-      </c>
-      <c r="K193" s="42" t="s">
-        <v>1377</v>
       </c>
       <c r="L193" s="6">
         <f t="shared" si="50"/>
@@ -19480,10 +19430,10 @@
       <c r="S193" s="7">
         <v>99.99</v>
       </c>
-      <c r="T193" s="41" t="s">
+      <c r="T193" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U193" s="41" t="s">
+      <c r="U193" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W193" s="6" t="s">
@@ -19496,38 +19446,34 @@
       <c r="Z193" s="7"/>
     </row>
     <row r="194" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A194" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B194" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C194" s="41" t="s">
+      <c r="A194" s="7"/>
+      <c r="B194" s="7"/>
+      <c r="C194" s="36" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D194" s="36" t="s">
         <v>1378</v>
-      </c>
-      <c r="D194" s="41" t="s">
-        <v>1379</v>
       </c>
       <c r="E194" s="6">
         <v>6</v>
       </c>
       <c r="F194" s="6" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G194" s="37" t="s">
+        <v>1180</v>
+      </c>
+      <c r="H194" s="37" t="s">
         <v>1380</v>
       </c>
-      <c r="G194" s="42" t="s">
-        <v>1180</v>
-      </c>
-      <c r="H194" s="42" t="s">
+      <c r="I194" s="37" t="s">
         <v>1381</v>
       </c>
-      <c r="I194" s="42" t="s">
+      <c r="J194" s="37" t="s">
         <v>1382</v>
       </c>
-      <c r="J194" s="42" t="s">
+      <c r="K194" s="37" t="s">
         <v>1383</v>
-      </c>
-      <c r="K194" s="42" t="s">
-        <v>1384</v>
       </c>
       <c r="L194" s="6">
         <f t="shared" si="50"/>
@@ -19560,10 +19506,10 @@
       <c r="S194" s="7">
         <v>99.99</v>
       </c>
-      <c r="T194" s="41" t="s">
+      <c r="T194" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U194" s="41" t="s">
+      <c r="U194" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W194" s="6" t="s">
@@ -19576,38 +19522,34 @@
       <c r="Z194" s="7"/>
     </row>
     <row r="195" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A195" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B195" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C195" s="41" t="s">
+      <c r="A195" s="7"/>
+      <c r="B195" s="7"/>
+      <c r="C195" s="36" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D195" s="36" t="s">
         <v>1385</v>
-      </c>
-      <c r="D195" s="41" t="s">
-        <v>1386</v>
       </c>
       <c r="E195" s="6">
         <v>6</v>
       </c>
       <c r="F195" s="6" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G195" s="37" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H195" s="37" t="s">
         <v>1387</v>
       </c>
-      <c r="G195" s="42" t="s">
-        <v>1189</v>
-      </c>
-      <c r="H195" s="42" t="s">
+      <c r="I195" s="37" t="s">
         <v>1388</v>
       </c>
-      <c r="I195" s="42" t="s">
+      <c r="J195" s="37" t="s">
+        <v>1183</v>
+      </c>
+      <c r="K195" s="37" t="s">
         <v>1389</v>
-      </c>
-      <c r="J195" s="42" t="s">
-        <v>1183</v>
-      </c>
-      <c r="K195" s="42" t="s">
-        <v>1390</v>
       </c>
       <c r="L195" s="6">
         <f t="shared" si="50"/>
@@ -19640,10 +19582,10 @@
       <c r="S195" s="7">
         <v>99.99</v>
       </c>
-      <c r="T195" s="41" t="s">
+      <c r="T195" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U195" s="41" t="s">
+      <c r="U195" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W195" s="6" t="s">
@@ -19656,38 +19598,34 @@
       <c r="Z195" s="7"/>
     </row>
     <row r="196" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A196" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B196" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C196" s="41" t="s">
+      <c r="A196" s="7"/>
+      <c r="B196" s="7"/>
+      <c r="C196" s="36" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D196" s="36" t="s">
         <v>1391</v>
-      </c>
-      <c r="D196" s="41" t="s">
-        <v>1392</v>
       </c>
       <c r="E196" s="6">
         <v>6</v>
       </c>
       <c r="F196" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G196" s="37" t="s">
+        <v>1198</v>
+      </c>
+      <c r="H196" s="37" t="s">
         <v>1393</v>
       </c>
-      <c r="G196" s="42" t="s">
-        <v>1198</v>
-      </c>
-      <c r="H196" s="42" t="s">
+      <c r="I196" s="37" t="s">
         <v>1394</v>
       </c>
-      <c r="I196" s="42" t="s">
+      <c r="J196" s="37" t="s">
         <v>1395</v>
       </c>
-      <c r="J196" s="42" t="s">
+      <c r="K196" s="37" t="s">
         <v>1396</v>
-      </c>
-      <c r="K196" s="42" t="s">
-        <v>1397</v>
       </c>
       <c r="L196" s="6">
         <f t="shared" si="50"/>
@@ -19720,10 +19658,10 @@
       <c r="S196" s="7">
         <v>99.99</v>
       </c>
-      <c r="T196" s="41" t="s">
+      <c r="T196" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U196" s="41" t="s">
+      <c r="U196" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W196" s="6" t="s">
@@ -19736,38 +19674,34 @@
       <c r="Z196" s="7"/>
     </row>
     <row r="197" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A197" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B197" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C197" s="41" t="s">
+      <c r="A197" s="7"/>
+      <c r="B197" s="7"/>
+      <c r="C197" s="36" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D197" s="36" t="s">
         <v>1398</v>
-      </c>
-      <c r="D197" s="41" t="s">
-        <v>1399</v>
       </c>
       <c r="E197" s="6">
         <v>6</v>
       </c>
       <c r="F197" s="6" t="s">
+        <v>1399</v>
+      </c>
+      <c r="G197" s="37" t="s">
+        <v>1207</v>
+      </c>
+      <c r="H197" s="37" t="s">
         <v>1400</v>
       </c>
-      <c r="G197" s="42" t="s">
-        <v>1207</v>
-      </c>
-      <c r="H197" s="42" t="s">
+      <c r="I197" s="37" t="s">
         <v>1401</v>
       </c>
-      <c r="I197" s="42" t="s">
+      <c r="J197" s="37" t="s">
         <v>1402</v>
       </c>
-      <c r="J197" s="42" t="s">
+      <c r="K197" s="37" t="s">
         <v>1403</v>
-      </c>
-      <c r="K197" s="42" t="s">
-        <v>1404</v>
       </c>
       <c r="L197" s="6">
         <f t="shared" si="50"/>
@@ -19800,10 +19734,10 @@
       <c r="S197" s="7">
         <v>99.99</v>
       </c>
-      <c r="T197" s="41" t="s">
+      <c r="T197" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U197" s="41" t="s">
+      <c r="U197" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W197" s="6" t="s">
@@ -19816,38 +19750,34 @@
       <c r="Z197" s="7"/>
     </row>
     <row r="198" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A198" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B198" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C198" s="41" t="s">
+      <c r="A198" s="7"/>
+      <c r="B198" s="7"/>
+      <c r="C198" s="36" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D198" s="36" t="s">
         <v>1405</v>
-      </c>
-      <c r="D198" s="41" t="s">
-        <v>1406</v>
       </c>
       <c r="E198" s="6">
         <v>6</v>
       </c>
       <c r="F198" s="6" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G198" s="37" t="s">
+        <v>1216</v>
+      </c>
+      <c r="H198" s="37" t="s">
         <v>1407</v>
       </c>
-      <c r="G198" s="42" t="s">
-        <v>1216</v>
-      </c>
-      <c r="H198" s="42" t="s">
+      <c r="I198" s="37" t="s">
         <v>1408</v>
       </c>
-      <c r="I198" s="42" t="s">
+      <c r="J198" s="37" t="s">
         <v>1409</v>
       </c>
-      <c r="J198" s="42" t="s">
+      <c r="K198" s="37" t="s">
         <v>1410</v>
-      </c>
-      <c r="K198" s="42" t="s">
-        <v>1411</v>
       </c>
       <c r="L198" s="6">
         <f t="shared" si="50"/>
@@ -19880,10 +19810,10 @@
       <c r="S198" s="7">
         <v>99.99</v>
       </c>
-      <c r="T198" s="41" t="s">
+      <c r="T198" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U198" s="41" t="s">
+      <c r="U198" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W198" s="6" t="s">
@@ -19896,38 +19826,34 @@
       <c r="Z198" s="7"/>
     </row>
     <row r="199" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A199" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B199" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C199" s="41" t="s">
+      <c r="A199" s="7"/>
+      <c r="B199" s="7"/>
+      <c r="C199" s="36" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D199" s="36" t="s">
         <v>1412</v>
-      </c>
-      <c r="D199" s="41" t="s">
-        <v>1413</v>
       </c>
       <c r="E199" s="6">
         <v>6</v>
       </c>
       <c r="F199" s="6" t="s">
+        <v>1413</v>
+      </c>
+      <c r="G199" s="37" t="s">
+        <v>1225</v>
+      </c>
+      <c r="H199" s="37" t="s">
         <v>1414</v>
       </c>
-      <c r="G199" s="42" t="s">
-        <v>1225</v>
-      </c>
-      <c r="H199" s="42" t="s">
+      <c r="I199" s="37" t="s">
         <v>1415</v>
       </c>
-      <c r="I199" s="42" t="s">
+      <c r="J199" s="37" t="s">
         <v>1416</v>
       </c>
-      <c r="J199" s="42" t="s">
+      <c r="K199" s="37" t="s">
         <v>1417</v>
-      </c>
-      <c r="K199" s="42" t="s">
-        <v>1418</v>
       </c>
       <c r="L199" s="6">
         <f t="shared" si="50"/>
@@ -19960,10 +19886,10 @@
       <c r="S199" s="7">
         <v>99.99</v>
       </c>
-      <c r="T199" s="41" t="s">
+      <c r="T199" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U199" s="41" t="s">
+      <c r="U199" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W199" s="6" t="s">
@@ -19976,38 +19902,34 @@
       <c r="Z199" s="7"/>
     </row>
     <row r="200" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A200" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B200" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C200" s="41" t="s">
+      <c r="A200" s="7"/>
+      <c r="B200" s="7"/>
+      <c r="C200" s="36" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D200" s="36" t="s">
         <v>1419</v>
-      </c>
-      <c r="D200" s="41" t="s">
-        <v>1420</v>
       </c>
       <c r="E200" s="6">
         <v>6</v>
       </c>
       <c r="F200" s="6" t="s">
+        <v>1420</v>
+      </c>
+      <c r="G200" s="37" t="s">
+        <v>1234</v>
+      </c>
+      <c r="H200" s="37" t="s">
         <v>1421</v>
       </c>
-      <c r="G200" s="42" t="s">
-        <v>1234</v>
-      </c>
-      <c r="H200" s="42" t="s">
+      <c r="I200" s="37" t="s">
         <v>1422</v>
       </c>
-      <c r="I200" s="42" t="s">
+      <c r="J200" s="37" t="s">
         <v>1423</v>
       </c>
-      <c r="J200" s="42" t="s">
+      <c r="K200" s="37" t="s">
         <v>1424</v>
-      </c>
-      <c r="K200" s="42" t="s">
-        <v>1425</v>
       </c>
       <c r="L200" s="6">
         <f t="shared" si="50"/>
@@ -20040,10 +19962,10 @@
       <c r="S200" s="7">
         <v>99.99</v>
       </c>
-      <c r="T200" s="41" t="s">
+      <c r="T200" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U200" s="41" t="s">
+      <c r="U200" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W200" s="6" t="s">
@@ -20055,39 +19977,33 @@
       <c r="Y200" s="7"/>
       <c r="Z200" s="7"/>
     </row>
-    <row r="201" s="7" customFormat="1" customHeight="1" spans="1:24">
-      <c r="A201" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B201" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C201" s="41" t="s">
+    <row r="201" s="7" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C201" s="36" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D201" s="36" t="s">
         <v>1426</v>
-      </c>
-      <c r="D201" s="41" t="s">
-        <v>1427</v>
       </c>
       <c r="E201" s="6">
         <v>6</v>
       </c>
       <c r="F201" s="6" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G201" s="37" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H201" s="37" t="s">
         <v>1428</v>
       </c>
-      <c r="G201" s="42" t="s">
-        <v>1243</v>
-      </c>
-      <c r="H201" s="42" t="s">
+      <c r="I201" s="37" t="s">
         <v>1429</v>
       </c>
-      <c r="I201" s="42" t="s">
+      <c r="J201" s="37" t="s">
         <v>1430</v>
       </c>
-      <c r="J201" s="42" t="s">
+      <c r="K201" s="37" t="s">
         <v>1431</v>
-      </c>
-      <c r="K201" s="42" t="s">
-        <v>1432</v>
       </c>
       <c r="L201" s="6">
         <f t="shared" si="50"/>
@@ -20120,10 +20036,10 @@
       <c r="S201" s="7">
         <v>99.99</v>
       </c>
-      <c r="T201" s="41" t="s">
+      <c r="T201" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U201" s="41" t="s">
+      <c r="U201" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="V201" s="6"/>
@@ -20134,39 +20050,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" s="7" customFormat="1" customHeight="1" spans="1:24">
-      <c r="A202" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B202" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C202" s="41" t="s">
+    <row r="202" s="7" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C202" s="36" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D202" s="36" t="s">
         <v>1433</v>
-      </c>
-      <c r="D202" s="41" t="s">
-        <v>1434</v>
       </c>
       <c r="E202" s="6">
         <v>6</v>
       </c>
       <c r="F202" s="6" t="s">
+        <v>1434</v>
+      </c>
+      <c r="G202" s="37" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H202" s="37" t="s">
         <v>1435</v>
       </c>
-      <c r="G202" s="42" t="s">
-        <v>1252</v>
-      </c>
-      <c r="H202" s="42" t="s">
+      <c r="I202" s="37" t="s">
         <v>1436</v>
       </c>
-      <c r="I202" s="42" t="s">
+      <c r="J202" s="37" t="s">
         <v>1437</v>
       </c>
-      <c r="J202" s="42" t="s">
+      <c r="K202" s="37" t="s">
         <v>1438</v>
-      </c>
-      <c r="K202" s="42" t="s">
-        <v>1439</v>
       </c>
       <c r="L202" s="6">
         <f t="shared" si="50"/>
@@ -20199,10 +20109,10 @@
       <c r="S202" s="7">
         <v>99.99</v>
       </c>
-      <c r="T202" s="41" t="s">
+      <c r="T202" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U202" s="41" t="s">
+      <c r="U202" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="V202" s="6"/>
@@ -20213,39 +20123,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" s="7" customFormat="1" customHeight="1" spans="1:24">
-      <c r="A203" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B203" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C203" s="41" t="s">
+    <row r="203" s="7" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C203" s="36" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D203" s="36" t="s">
         <v>1440</v>
-      </c>
-      <c r="D203" s="41" t="s">
-        <v>1441</v>
       </c>
       <c r="E203" s="6">
         <v>6</v>
       </c>
       <c r="F203" s="6" t="s">
+        <v>1441</v>
+      </c>
+      <c r="G203" s="37" t="s">
+        <v>1261</v>
+      </c>
+      <c r="H203" s="37" t="s">
         <v>1442</v>
       </c>
-      <c r="G203" s="42" t="s">
-        <v>1261</v>
-      </c>
-      <c r="H203" s="42" t="s">
+      <c r="I203" s="37" t="s">
         <v>1443</v>
       </c>
-      <c r="I203" s="42" t="s">
+      <c r="J203" s="37" t="s">
         <v>1444</v>
       </c>
-      <c r="J203" s="42" t="s">
+      <c r="K203" s="37" t="s">
         <v>1445</v>
-      </c>
-      <c r="K203" s="42" t="s">
-        <v>1446</v>
       </c>
       <c r="L203" s="6">
         <f t="shared" si="50"/>
@@ -20278,10 +20182,10 @@
       <c r="S203" s="7">
         <v>99.99</v>
       </c>
-      <c r="T203" s="41" t="s">
+      <c r="T203" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U203" s="41" t="s">
+      <c r="U203" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="V203" s="6"/>
@@ -20292,39 +20196,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" s="7" customFormat="1" customHeight="1" spans="1:24">
-      <c r="A204" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B204" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C204" s="41" t="s">
+    <row r="204" s="7" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C204" s="36" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D204" s="36" t="s">
         <v>1447</v>
-      </c>
-      <c r="D204" s="41" t="s">
-        <v>1448</v>
       </c>
       <c r="E204" s="6">
         <v>6</v>
       </c>
       <c r="F204" s="6" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G204" s="37" t="s">
+        <v>1270</v>
+      </c>
+      <c r="H204" s="37" t="s">
         <v>1449</v>
       </c>
-      <c r="G204" s="42" t="s">
-        <v>1270</v>
-      </c>
-      <c r="H204" s="42" t="s">
+      <c r="I204" s="37" t="s">
         <v>1450</v>
       </c>
-      <c r="I204" s="42" t="s">
+      <c r="J204" s="37" t="s">
         <v>1451</v>
       </c>
-      <c r="J204" s="42" t="s">
+      <c r="K204" s="37" t="s">
         <v>1452</v>
-      </c>
-      <c r="K204" s="42" t="s">
-        <v>1453</v>
       </c>
       <c r="L204" s="6">
         <f t="shared" si="50"/>
@@ -20357,10 +20255,10 @@
       <c r="S204" s="7">
         <v>99.99</v>
       </c>
-      <c r="T204" s="41" t="s">
+      <c r="T204" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U204" s="41" t="s">
+      <c r="U204" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="V204" s="6"/>
@@ -20371,18 +20269,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" s="7" customFormat="1" customHeight="1" spans="1:24">
-      <c r="A205" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B205" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C205" s="41" t="s">
+    <row r="205" s="7" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C205" s="36" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D205" s="36" t="s">
         <v>1454</v>
-      </c>
-      <c r="D205" s="41" t="s">
-        <v>1455</v>
       </c>
       <c r="E205" s="6">
         <v>6</v>
@@ -20390,20 +20282,20 @@
       <c r="F205" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="G205" s="42" t="s">
+      <c r="G205" s="37" t="s">
+        <v>1455</v>
+      </c>
+      <c r="H205" s="37" t="s">
         <v>1456</v>
       </c>
-      <c r="H205" s="42" t="s">
+      <c r="I205" s="37" t="s">
         <v>1457</v>
       </c>
-      <c r="I205" s="42" t="s">
+      <c r="J205" s="37" t="s">
         <v>1458</v>
       </c>
-      <c r="J205" s="42" t="s">
+      <c r="K205" s="37" t="s">
         <v>1459</v>
-      </c>
-      <c r="K205" s="42" t="s">
-        <v>1460</v>
       </c>
       <c r="L205" s="6">
         <f t="shared" ref="L205:L215" si="77">L204+600</f>
@@ -20436,10 +20328,10 @@
       <c r="S205" s="7">
         <v>99.99</v>
       </c>
-      <c r="T205" s="41" t="s">
+      <c r="T205" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U205" s="41" t="s">
+      <c r="U205" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="V205" s="6"/>
@@ -20451,38 +20343,34 @@
       </c>
     </row>
     <row r="206" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A206" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B206" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C206" s="41" t="s">
+      <c r="A206" s="7"/>
+      <c r="B206" s="7"/>
+      <c r="C206" s="36" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D206" s="36" t="s">
         <v>1461</v>
-      </c>
-      <c r="D206" s="41" t="s">
-        <v>1462</v>
       </c>
       <c r="E206" s="6">
         <v>6</v>
       </c>
       <c r="F206" s="6" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G206" s="37" t="s">
         <v>1463</v>
       </c>
-      <c r="G206" s="42" t="s">
+      <c r="H206" s="37" t="s">
         <v>1464</v>
       </c>
-      <c r="H206" s="42" t="s">
+      <c r="I206" s="37" t="s">
         <v>1465</v>
       </c>
-      <c r="I206" s="42" t="s">
+      <c r="J206" s="37" t="s">
         <v>1466</v>
       </c>
-      <c r="J206" s="42" t="s">
+      <c r="K206" s="37" t="s">
         <v>1467</v>
-      </c>
-      <c r="K206" s="42" t="s">
-        <v>1468</v>
       </c>
       <c r="L206" s="6">
         <f t="shared" si="77"/>
@@ -20515,10 +20403,10 @@
       <c r="S206" s="7">
         <v>99.99</v>
       </c>
-      <c r="T206" s="41" t="s">
+      <c r="T206" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U206" s="41" t="s">
+      <c r="U206" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W206" s="6" t="s">
@@ -20531,38 +20419,34 @@
       <c r="Z206" s="7"/>
     </row>
     <row r="207" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A207" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B207" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C207" s="41" t="s">
+      <c r="A207" s="7"/>
+      <c r="B207" s="7"/>
+      <c r="C207" s="36" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D207" s="36" t="s">
         <v>1469</v>
-      </c>
-      <c r="D207" s="41" t="s">
-        <v>1470</v>
       </c>
       <c r="E207" s="6">
         <v>6</v>
       </c>
       <c r="F207" s="6" t="s">
+        <v>1470</v>
+      </c>
+      <c r="G207" s="37" t="s">
         <v>1471</v>
       </c>
-      <c r="G207" s="42" t="s">
+      <c r="H207" s="37" t="s">
         <v>1472</v>
       </c>
-      <c r="H207" s="42" t="s">
+      <c r="I207" s="37" t="s">
         <v>1473</v>
       </c>
-      <c r="I207" s="42" t="s">
+      <c r="J207" s="37" t="s">
         <v>1474</v>
       </c>
-      <c r="J207" s="42" t="s">
+      <c r="K207" s="37" t="s">
         <v>1475</v>
-      </c>
-      <c r="K207" s="42" t="s">
-        <v>1476</v>
       </c>
       <c r="L207" s="6">
         <f t="shared" si="77"/>
@@ -20595,10 +20479,10 @@
       <c r="S207" s="7">
         <v>99.99</v>
       </c>
-      <c r="T207" s="41" t="s">
+      <c r="T207" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U207" s="41" t="s">
+      <c r="U207" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W207" s="6" t="s">
@@ -20611,38 +20495,34 @@
       <c r="Z207" s="7"/>
     </row>
     <row r="208" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A208" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B208" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C208" s="41" t="s">
+      <c r="A208" s="7"/>
+      <c r="B208" s="7"/>
+      <c r="C208" s="36" t="s">
+        <v>1476</v>
+      </c>
+      <c r="D208" s="36" t="s">
         <v>1477</v>
-      </c>
-      <c r="D208" s="41" t="s">
-        <v>1478</v>
       </c>
       <c r="E208" s="6">
         <v>6</v>
       </c>
       <c r="F208" s="6" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G208" s="37" t="s">
         <v>1479</v>
       </c>
-      <c r="G208" s="42" t="s">
+      <c r="H208" s="37" t="s">
         <v>1480</v>
       </c>
-      <c r="H208" s="42" t="s">
+      <c r="I208" s="37" t="s">
         <v>1481</v>
       </c>
-      <c r="I208" s="42" t="s">
+      <c r="J208" s="37" t="s">
+        <v>1273</v>
+      </c>
+      <c r="K208" s="37" t="s">
         <v>1482</v>
-      </c>
-      <c r="J208" s="42" t="s">
-        <v>1273</v>
-      </c>
-      <c r="K208" s="42" t="s">
-        <v>1483</v>
       </c>
       <c r="L208" s="6">
         <f t="shared" si="77"/>
@@ -20675,10 +20555,10 @@
       <c r="S208" s="7">
         <v>99.99</v>
       </c>
-      <c r="T208" s="41" t="s">
+      <c r="T208" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U208" s="41" t="s">
+      <c r="U208" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W208" s="6" t="s">
@@ -20691,38 +20571,34 @@
       <c r="Z208" s="7"/>
     </row>
     <row r="209" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A209" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B209" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C209" s="41" t="s">
+      <c r="A209" s="7"/>
+      <c r="B209" s="7"/>
+      <c r="C209" s="36" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D209" s="36" t="s">
         <v>1484</v>
-      </c>
-      <c r="D209" s="41" t="s">
-        <v>1485</v>
       </c>
       <c r="E209" s="6">
         <v>6</v>
       </c>
       <c r="F209" s="6" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G209" s="37" t="s">
         <v>1486</v>
       </c>
-      <c r="G209" s="42" t="s">
+      <c r="H209" s="37" t="s">
         <v>1487</v>
       </c>
-      <c r="H209" s="42" t="s">
+      <c r="I209" s="37" t="s">
         <v>1488</v>
       </c>
-      <c r="I209" s="42" t="s">
+      <c r="J209" s="37" t="s">
         <v>1489</v>
       </c>
-      <c r="J209" s="42" t="s">
+      <c r="K209" s="37" t="s">
         <v>1490</v>
-      </c>
-      <c r="K209" s="42" t="s">
-        <v>1491</v>
       </c>
       <c r="L209" s="6">
         <f t="shared" si="77"/>
@@ -20755,10 +20631,10 @@
       <c r="S209" s="7">
         <v>99.99</v>
       </c>
-      <c r="T209" s="41" t="s">
+      <c r="T209" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U209" s="41" t="s">
+      <c r="U209" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W209" s="6" t="s">
@@ -20771,38 +20647,34 @@
       <c r="Z209" s="7"/>
     </row>
     <row r="210" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A210" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B210" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C210" s="41" t="s">
+      <c r="A210" s="7"/>
+      <c r="B210" s="7"/>
+      <c r="C210" s="36" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D210" s="36" t="s">
         <v>1492</v>
-      </c>
-      <c r="D210" s="41" t="s">
-        <v>1493</v>
       </c>
       <c r="E210" s="6">
         <v>6</v>
       </c>
       <c r="F210" s="6" t="s">
+        <v>1493</v>
+      </c>
+      <c r="G210" s="37" t="s">
+        <v>1322</v>
+      </c>
+      <c r="H210" s="37" t="s">
         <v>1494</v>
       </c>
-      <c r="G210" s="42" t="s">
-        <v>1323</v>
-      </c>
-      <c r="H210" s="42" t="s">
+      <c r="I210" s="37" t="s">
         <v>1495</v>
       </c>
-      <c r="I210" s="42" t="s">
+      <c r="J210" s="37" t="s">
         <v>1496</v>
       </c>
-      <c r="J210" s="42" t="s">
+      <c r="K210" s="37" t="s">
         <v>1497</v>
-      </c>
-      <c r="K210" s="42" t="s">
-        <v>1498</v>
       </c>
       <c r="L210" s="6">
         <f t="shared" si="77"/>
@@ -20835,10 +20707,10 @@
       <c r="S210" s="7">
         <v>99.99</v>
       </c>
-      <c r="T210" s="41" t="s">
+      <c r="T210" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U210" s="41" t="s">
+      <c r="U210" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W210" s="6" t="s">
@@ -20851,38 +20723,34 @@
       <c r="Z210" s="7"/>
     </row>
     <row r="211" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A211" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B211" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C211" s="41" t="s">
+      <c r="A211" s="7"/>
+      <c r="B211" s="7"/>
+      <c r="C211" s="36" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D211" s="36" t="s">
         <v>1499</v>
-      </c>
-      <c r="D211" s="41" t="s">
-        <v>1500</v>
       </c>
       <c r="E211" s="6">
         <v>6</v>
       </c>
       <c r="F211" s="6" t="s">
+        <v>1500</v>
+      </c>
+      <c r="G211" s="37" t="s">
+        <v>1330</v>
+      </c>
+      <c r="H211" s="37" t="s">
         <v>1501</v>
       </c>
-      <c r="G211" s="42" t="s">
-        <v>1331</v>
-      </c>
-      <c r="H211" s="42" t="s">
+      <c r="I211" s="37" t="s">
         <v>1502</v>
       </c>
-      <c r="I211" s="42" t="s">
+      <c r="J211" s="37" t="s">
         <v>1503</v>
       </c>
-      <c r="J211" s="42" t="s">
+      <c r="K211" s="37" t="s">
         <v>1504</v>
-      </c>
-      <c r="K211" s="42" t="s">
-        <v>1505</v>
       </c>
       <c r="L211" s="6">
         <f t="shared" si="77"/>
@@ -20915,10 +20783,10 @@
       <c r="S211" s="7">
         <v>99.99</v>
       </c>
-      <c r="T211" s="41" t="s">
+      <c r="T211" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U211" s="41" t="s">
+      <c r="U211" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W211" s="6" t="s">
@@ -20931,38 +20799,34 @@
       <c r="Z211" s="7"/>
     </row>
     <row r="212" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A212" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B212" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C212" s="41" t="s">
+      <c r="A212" s="7"/>
+      <c r="B212" s="7"/>
+      <c r="C212" s="36" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D212" s="36" t="s">
         <v>1506</v>
-      </c>
-      <c r="D212" s="41" t="s">
-        <v>1507</v>
       </c>
       <c r="E212" s="6">
         <v>6</v>
       </c>
       <c r="F212" s="6" t="s">
+        <v>1507</v>
+      </c>
+      <c r="G212" s="37" t="s">
+        <v>1338</v>
+      </c>
+      <c r="H212" s="37" t="s">
         <v>1508</v>
       </c>
-      <c r="G212" s="42" t="s">
-        <v>1339</v>
-      </c>
-      <c r="H212" s="42" t="s">
+      <c r="I212" s="37" t="s">
         <v>1509</v>
       </c>
-      <c r="I212" s="42" t="s">
+      <c r="J212" s="37" t="s">
         <v>1510</v>
       </c>
-      <c r="J212" s="42" t="s">
+      <c r="K212" s="37" t="s">
         <v>1511</v>
-      </c>
-      <c r="K212" s="42" t="s">
-        <v>1512</v>
       </c>
       <c r="L212" s="6">
         <f t="shared" si="77"/>
@@ -20995,10 +20859,10 @@
       <c r="S212" s="7">
         <v>99.99</v>
       </c>
-      <c r="T212" s="41" t="s">
+      <c r="T212" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U212" s="41" t="s">
+      <c r="U212" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W212" s="6" t="s">
@@ -21011,38 +20875,34 @@
       <c r="Z212" s="7"/>
     </row>
     <row r="213" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A213" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B213" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C213" s="41" t="s">
+      <c r="A213" s="7"/>
+      <c r="B213" s="7"/>
+      <c r="C213" s="36" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D213" s="36" t="s">
         <v>1513</v>
-      </c>
-      <c r="D213" s="41" t="s">
-        <v>1514</v>
       </c>
       <c r="E213" s="6">
         <v>6</v>
       </c>
       <c r="F213" s="6" t="s">
+        <v>1514</v>
+      </c>
+      <c r="G213" s="37" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H213" s="37" t="s">
         <v>1515</v>
       </c>
-      <c r="G213" s="42" t="s">
-        <v>1346</v>
-      </c>
-      <c r="H213" s="42" t="s">
+      <c r="I213" s="37" t="s">
         <v>1516</v>
       </c>
-      <c r="I213" s="42" t="s">
+      <c r="J213" s="37" t="s">
         <v>1517</v>
       </c>
-      <c r="J213" s="42" t="s">
+      <c r="K213" s="37" t="s">
         <v>1518</v>
-      </c>
-      <c r="K213" s="42" t="s">
-        <v>1519</v>
       </c>
       <c r="L213" s="6">
         <f t="shared" si="77"/>
@@ -21075,10 +20935,10 @@
       <c r="S213" s="7">
         <v>99.99</v>
       </c>
-      <c r="T213" s="41" t="s">
+      <c r="T213" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U213" s="41" t="s">
+      <c r="U213" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W213" s="6" t="s">
@@ -21091,38 +20951,34 @@
       <c r="Z213" s="7"/>
     </row>
     <row r="214" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A214" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B214" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C214" s="41" t="s">
+      <c r="A214" s="7"/>
+      <c r="B214" s="7"/>
+      <c r="C214" s="36" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D214" s="36" t="s">
         <v>1520</v>
-      </c>
-      <c r="D214" s="41" t="s">
-        <v>1521</v>
       </c>
       <c r="E214" s="6">
         <v>6</v>
       </c>
       <c r="F214" s="6" t="s">
+        <v>1521</v>
+      </c>
+      <c r="G214" s="37" t="s">
+        <v>1352</v>
+      </c>
+      <c r="H214" s="37" t="s">
         <v>1522</v>
       </c>
-      <c r="G214" s="42" t="s">
-        <v>1353</v>
-      </c>
-      <c r="H214" s="42" t="s">
+      <c r="I214" s="37" t="s">
         <v>1523</v>
       </c>
-      <c r="I214" s="42" t="s">
+      <c r="J214" s="37" t="s">
+        <v>1325</v>
+      </c>
+      <c r="K214" s="37" t="s">
         <v>1524</v>
-      </c>
-      <c r="J214" s="42" t="s">
-        <v>1326</v>
-      </c>
-      <c r="K214" s="42" t="s">
-        <v>1525</v>
       </c>
       <c r="L214" s="6">
         <f t="shared" si="77"/>
@@ -21155,10 +21011,10 @@
       <c r="S214" s="7">
         <v>99.99</v>
       </c>
-      <c r="T214" s="41" t="s">
+      <c r="T214" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U214" s="41" t="s">
+      <c r="U214" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W214" s="6" t="s">
@@ -21171,38 +21027,34 @@
       <c r="Z214" s="7"/>
     </row>
     <row r="215" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A215" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B215" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C215" s="41" t="s">
+      <c r="A215" s="7"/>
+      <c r="B215" s="7"/>
+      <c r="C215" s="36" t="s">
+        <v>1525</v>
+      </c>
+      <c r="D215" s="36" t="s">
         <v>1526</v>
-      </c>
-      <c r="D215" s="41" t="s">
-        <v>1527</v>
       </c>
       <c r="E215" s="6">
         <v>6</v>
       </c>
       <c r="F215" s="6" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G215" s="37" t="s">
+        <v>1359</v>
+      </c>
+      <c r="H215" s="37" t="s">
         <v>1528</v>
       </c>
-      <c r="G215" s="42" t="s">
-        <v>1360</v>
-      </c>
-      <c r="H215" s="42" t="s">
+      <c r="I215" s="37" t="s">
         <v>1529</v>
       </c>
-      <c r="I215" s="42" t="s">
+      <c r="J215" s="37" t="s">
+        <v>1333</v>
+      </c>
+      <c r="K215" s="37" t="s">
         <v>1530</v>
-      </c>
-      <c r="J215" s="42" t="s">
-        <v>1334</v>
-      </c>
-      <c r="K215" s="42" t="s">
-        <v>1531</v>
       </c>
       <c r="L215" s="6">
         <f t="shared" si="77"/>
@@ -21235,10 +21087,10 @@
       <c r="S215" s="7">
         <v>99.99</v>
       </c>
-      <c r="T215" s="41" t="s">
+      <c r="T215" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="U215" s="41" t="s">
+      <c r="U215" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="W215" s="6" t="s">
@@ -21252,7 +21104,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="P3 P4 P5 C3:O5 Q3:S5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:S5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="1531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="1532">
   <si>
     <t>ID</t>
   </si>
@@ -4037,6 +4037,9 @@
   </si>
   <si>
     <t>16000000000000</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>10180</t>
@@ -18838,34 +18841,38 @@
       </c>
     </row>
     <row r="186" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A186" s="7"/>
-      <c r="B186" s="7"/>
+      <c r="A186" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B186" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C186" s="36" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="D186" s="36" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="E186" s="6">
         <v>6</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="G186" s="37" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H186" s="37" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="I186" s="37" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="J186" s="37" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="K186" s="37" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="L186" s="6">
         <f t="shared" si="50"/>
@@ -18914,34 +18921,38 @@
       <c r="Z186" s="7"/>
     </row>
     <row r="187" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A187" s="7"/>
-      <c r="B187" s="7"/>
+      <c r="A187" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B187" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C187" s="36" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="D187" s="36" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="E187" s="6">
         <v>6</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="G187" s="37" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="H187" s="37" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="I187" s="37" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="J187" s="37" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="K187" s="37" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="L187" s="6">
         <f t="shared" si="50"/>
@@ -18990,34 +19001,38 @@
       <c r="Z187" s="7"/>
     </row>
     <row r="188" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A188" s="7"/>
-      <c r="B188" s="7"/>
+      <c r="A188" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B188" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C188" s="36" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="D188" s="36" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="E188" s="6">
         <v>6</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="G188" s="37" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H188" s="37" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="I188" s="37" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="J188" s="37" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="K188" s="37" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="L188" s="6">
         <f t="shared" si="50"/>
@@ -19066,34 +19081,38 @@
       <c r="Z188" s="7"/>
     </row>
     <row r="189" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A189" s="7"/>
-      <c r="B189" s="7"/>
+      <c r="A189" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B189" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C189" s="36" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="D189" s="36" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="E189" s="6">
         <v>6</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="G189" s="37" t="s">
         <v>1136</v>
       </c>
       <c r="H189" s="37" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="I189" s="37" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="J189" s="37" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="K189" s="37" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="L189" s="6">
         <f t="shared" si="50"/>
@@ -19142,34 +19161,38 @@
       <c r="Z189" s="7"/>
     </row>
     <row r="190" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A190" s="7"/>
-      <c r="B190" s="7"/>
+      <c r="A190" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B190" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C190" s="36" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="D190" s="36" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="E190" s="6">
         <v>6</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="G190" s="37" t="s">
         <v>1145</v>
       </c>
       <c r="H190" s="37" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="I190" s="37" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="J190" s="37" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="K190" s="37" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="L190" s="6">
         <f t="shared" si="50"/>
@@ -19218,34 +19241,38 @@
       <c r="Z190" s="7"/>
     </row>
     <row r="191" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A191" s="7"/>
-      <c r="B191" s="7"/>
+      <c r="A191" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C191" s="36" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="D191" s="36" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="E191" s="6">
         <v>6</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="G191" s="37" t="s">
         <v>1154</v>
       </c>
       <c r="H191" s="37" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="I191" s="37" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="J191" s="37" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="K191" s="37" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="L191" s="6">
         <f t="shared" si="50"/>
@@ -19294,34 +19321,38 @@
       <c r="Z191" s="7"/>
     </row>
     <row r="192" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A192" s="7"/>
-      <c r="B192" s="7"/>
+      <c r="A192" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C192" s="36" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="D192" s="36" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="E192" s="6">
         <v>6</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="G192" s="37" t="s">
         <v>1163</v>
       </c>
       <c r="H192" s="37" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="I192" s="37" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="J192" s="37" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="K192" s="37" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="L192" s="6">
         <f t="shared" si="50"/>
@@ -19370,34 +19401,38 @@
       <c r="Z192" s="7"/>
     </row>
     <row r="193" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A193" s="7"/>
-      <c r="B193" s="7"/>
+      <c r="A193" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B193" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C193" s="36" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="D193" s="36" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="E193" s="6">
         <v>6</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="G193" s="37" t="s">
         <v>1172</v>
       </c>
       <c r="H193" s="37" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="I193" s="37" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="J193" s="37" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="K193" s="37" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="L193" s="6">
         <f t="shared" si="50"/>
@@ -19446,34 +19481,38 @@
       <c r="Z193" s="7"/>
     </row>
     <row r="194" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A194" s="7"/>
-      <c r="B194" s="7"/>
+      <c r="A194" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B194" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C194" s="36" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="D194" s="36" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="E194" s="6">
         <v>6</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="G194" s="37" t="s">
         <v>1180</v>
       </c>
       <c r="H194" s="37" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="I194" s="37" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="J194" s="37" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="K194" s="37" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="L194" s="6">
         <f t="shared" si="50"/>
@@ -19522,34 +19561,38 @@
       <c r="Z194" s="7"/>
     </row>
     <row r="195" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A195" s="7"/>
-      <c r="B195" s="7"/>
+      <c r="A195" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B195" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C195" s="36" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="D195" s="36" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="E195" s="6">
         <v>6</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="G195" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="H195" s="37" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="I195" s="37" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="J195" s="37" t="s">
         <v>1183</v>
       </c>
       <c r="K195" s="37" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="L195" s="6">
         <f t="shared" si="50"/>
@@ -19598,34 +19641,38 @@
       <c r="Z195" s="7"/>
     </row>
     <row r="196" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A196" s="7"/>
-      <c r="B196" s="7"/>
+      <c r="A196" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B196" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C196" s="36" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="D196" s="36" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="E196" s="6">
         <v>6</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="G196" s="37" t="s">
         <v>1198</v>
       </c>
       <c r="H196" s="37" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="I196" s="37" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="J196" s="37" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="K196" s="37" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="L196" s="6">
         <f t="shared" si="50"/>
@@ -19674,34 +19721,38 @@
       <c r="Z196" s="7"/>
     </row>
     <row r="197" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A197" s="7"/>
-      <c r="B197" s="7"/>
+      <c r="A197" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B197" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C197" s="36" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="D197" s="36" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="E197" s="6">
         <v>6</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="G197" s="37" t="s">
         <v>1207</v>
       </c>
       <c r="H197" s="37" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="I197" s="37" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="J197" s="37" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="K197" s="37" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="L197" s="6">
         <f t="shared" si="50"/>
@@ -19750,34 +19801,38 @@
       <c r="Z197" s="7"/>
     </row>
     <row r="198" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A198" s="7"/>
-      <c r="B198" s="7"/>
+      <c r="A198" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B198" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C198" s="36" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="D198" s="36" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="E198" s="6">
         <v>6</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="G198" s="37" t="s">
         <v>1216</v>
       </c>
       <c r="H198" s="37" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="I198" s="37" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="J198" s="37" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="K198" s="37" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="L198" s="6">
         <f t="shared" si="50"/>
@@ -19826,34 +19881,38 @@
       <c r="Z198" s="7"/>
     </row>
     <row r="199" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A199" s="7"/>
-      <c r="B199" s="7"/>
+      <c r="A199" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B199" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C199" s="36" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="D199" s="36" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="E199" s="6">
         <v>6</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="G199" s="37" t="s">
         <v>1225</v>
       </c>
       <c r="H199" s="37" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="I199" s="37" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="J199" s="37" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="K199" s="37" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="L199" s="6">
         <f t="shared" si="50"/>
@@ -19902,34 +19961,38 @@
       <c r="Z199" s="7"/>
     </row>
     <row r="200" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A200" s="7"/>
-      <c r="B200" s="7"/>
+      <c r="A200" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B200" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C200" s="36" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="D200" s="36" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="E200" s="6">
         <v>6</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="G200" s="37" t="s">
         <v>1234</v>
       </c>
       <c r="H200" s="37" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="I200" s="37" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="J200" s="37" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="K200" s="37" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="L200" s="6">
         <f t="shared" si="50"/>
@@ -19977,33 +20040,39 @@
       <c r="Y200" s="7"/>
       <c r="Z200" s="7"/>
     </row>
-    <row r="201" s="7" customFormat="1" customHeight="1" spans="3:24">
+    <row r="201" s="7" customFormat="1" customHeight="1" spans="1:24">
+      <c r="A201" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B201" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C201" s="36" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="D201" s="36" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="E201" s="6">
         <v>6</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="G201" s="37" t="s">
         <v>1243</v>
       </c>
       <c r="H201" s="37" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="I201" s="37" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="J201" s="37" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="K201" s="37" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="L201" s="6">
         <f t="shared" si="50"/>
@@ -20050,33 +20119,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" s="7" customFormat="1" customHeight="1" spans="3:24">
+    <row r="202" s="7" customFormat="1" customHeight="1" spans="1:24">
+      <c r="A202" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B202" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C202" s="36" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="D202" s="36" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="E202" s="6">
         <v>6</v>
       </c>
       <c r="F202" s="6" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="G202" s="37" t="s">
         <v>1252</v>
       </c>
       <c r="H202" s="37" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="I202" s="37" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="J202" s="37" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="K202" s="37" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="L202" s="6">
         <f t="shared" si="50"/>
@@ -20123,33 +20198,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" s="7" customFormat="1" customHeight="1" spans="3:24">
+    <row r="203" s="7" customFormat="1" customHeight="1" spans="1:24">
+      <c r="A203" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B203" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C203" s="36" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="D203" s="36" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="E203" s="6">
         <v>6</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="G203" s="37" t="s">
         <v>1261</v>
       </c>
       <c r="H203" s="37" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="I203" s="37" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="J203" s="37" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="K203" s="37" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="L203" s="6">
         <f t="shared" si="50"/>
@@ -20196,33 +20277,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" s="7" customFormat="1" customHeight="1" spans="3:24">
+    <row r="204" s="7" customFormat="1" customHeight="1" spans="1:24">
+      <c r="A204" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B204" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C204" s="36" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="D204" s="36" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="E204" s="6">
         <v>6</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="G204" s="37" t="s">
         <v>1270</v>
       </c>
       <c r="H204" s="37" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="I204" s="37" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="J204" s="37" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="K204" s="37" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="L204" s="6">
         <f t="shared" si="50"/>
@@ -20269,12 +20356,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" s="7" customFormat="1" customHeight="1" spans="3:24">
+    <row r="205" s="7" customFormat="1" customHeight="1" spans="1:24">
+      <c r="A205" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B205" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C205" s="36" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D205" s="36" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="E205" s="6">
         <v>6</v>
@@ -20283,19 +20376,19 @@
         <v>461</v>
       </c>
       <c r="G205" s="37" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H205" s="37" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="I205" s="37" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="J205" s="37" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="K205" s="37" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="L205" s="6">
         <f t="shared" ref="L205:L215" si="77">L204+600</f>
@@ -20343,34 +20436,38 @@
       </c>
     </row>
     <row r="206" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A206" s="7"/>
-      <c r="B206" s="7"/>
+      <c r="A206" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B206" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C206" s="36" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="D206" s="36" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="E206" s="6">
         <v>6</v>
       </c>
       <c r="F206" s="6" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="G206" s="37" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="H206" s="37" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="I206" s="37" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="J206" s="37" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="K206" s="37" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="L206" s="6">
         <f t="shared" si="77"/>
@@ -20419,34 +20516,38 @@
       <c r="Z206" s="7"/>
     </row>
     <row r="207" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A207" s="7"/>
-      <c r="B207" s="7"/>
+      <c r="A207" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B207" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C207" s="36" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="D207" s="36" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="E207" s="6">
         <v>6</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="G207" s="37" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H207" s="37" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="I207" s="37" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="J207" s="37" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="K207" s="37" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="L207" s="6">
         <f t="shared" si="77"/>
@@ -20495,34 +20596,38 @@
       <c r="Z207" s="7"/>
     </row>
     <row r="208" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A208" s="7"/>
-      <c r="B208" s="7"/>
+      <c r="A208" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B208" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C208" s="36" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="D208" s="36" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="E208" s="6">
         <v>6</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="G208" s="37" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="H208" s="37" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="I208" s="37" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="J208" s="37" t="s">
         <v>1273</v>
       </c>
       <c r="K208" s="37" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="L208" s="6">
         <f t="shared" si="77"/>
@@ -20571,34 +20676,38 @@
       <c r="Z208" s="7"/>
     </row>
     <row r="209" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A209" s="7"/>
-      <c r="B209" s="7"/>
+      <c r="A209" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B209" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C209" s="36" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="D209" s="36" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="E209" s="6">
         <v>6</v>
       </c>
       <c r="F209" s="6" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="G209" s="37" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="H209" s="37" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="I209" s="37" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="J209" s="37" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="K209" s="37" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="L209" s="6">
         <f t="shared" si="77"/>
@@ -20647,34 +20756,38 @@
       <c r="Z209" s="7"/>
     </row>
     <row r="210" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A210" s="7"/>
-      <c r="B210" s="7"/>
+      <c r="A210" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B210" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C210" s="36" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="D210" s="36" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="E210" s="6">
         <v>6</v>
       </c>
       <c r="F210" s="6" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="G210" s="37" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="H210" s="37" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="I210" s="37" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="J210" s="37" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="K210" s="37" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="L210" s="6">
         <f t="shared" si="77"/>
@@ -20723,34 +20836,38 @@
       <c r="Z210" s="7"/>
     </row>
     <row r="211" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A211" s="7"/>
-      <c r="B211" s="7"/>
+      <c r="A211" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B211" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C211" s="36" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="D211" s="36" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="E211" s="6">
         <v>6</v>
       </c>
       <c r="F211" s="6" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="G211" s="37" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H211" s="37" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="I211" s="37" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="J211" s="37" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="K211" s="37" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="L211" s="6">
         <f t="shared" si="77"/>
@@ -20799,34 +20916,38 @@
       <c r="Z211" s="7"/>
     </row>
     <row r="212" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A212" s="7"/>
-      <c r="B212" s="7"/>
+      <c r="A212" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B212" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C212" s="36" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="D212" s="36" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="E212" s="6">
         <v>6</v>
       </c>
       <c r="F212" s="6" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="G212" s="37" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H212" s="37" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="I212" s="37" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="J212" s="37" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="K212" s="37" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="L212" s="6">
         <f t="shared" si="77"/>
@@ -20875,34 +20996,38 @@
       <c r="Z212" s="7"/>
     </row>
     <row r="213" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A213" s="7"/>
-      <c r="B213" s="7"/>
+      <c r="A213" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B213" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C213" s="36" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="D213" s="36" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="E213" s="6">
         <v>6</v>
       </c>
       <c r="F213" s="6" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="G213" s="37" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H213" s="37" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="I213" s="37" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="J213" s="37" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="K213" s="37" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="L213" s="6">
         <f t="shared" si="77"/>
@@ -20951,34 +21076,38 @@
       <c r="Z213" s="7"/>
     </row>
     <row r="214" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A214" s="7"/>
-      <c r="B214" s="7"/>
+      <c r="A214" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B214" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C214" s="36" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="D214" s="36" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="E214" s="6">
         <v>6</v>
       </c>
       <c r="F214" s="6" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="G214" s="37" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H214" s="37" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="I214" s="37" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="J214" s="37" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="K214" s="37" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="L214" s="6">
         <f t="shared" si="77"/>
@@ -21027,34 +21156,38 @@
       <c r="Z214" s="7"/>
     </row>
     <row r="215" s="6" customFormat="1" customHeight="1" spans="1:26">
-      <c r="A215" s="7"/>
-      <c r="B215" s="7"/>
+      <c r="A215" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B215" s="7" t="s">
+        <v>1318</v>
+      </c>
       <c r="C215" s="36" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="D215" s="36" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="E215" s="6">
         <v>6</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="G215" s="37" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H215" s="37" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="I215" s="37" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="J215" s="37" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="K215" s="37" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="L215" s="6">
         <f t="shared" si="77"/>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="1532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="1531">
   <si>
     <t>ID</t>
   </si>
@@ -3922,13 +3922,13 @@
     <t>1E+87</t>
   </si>
   <si>
-    <t>1E+110</t>
-  </si>
-  <si>
-    <t>1E+142</t>
-  </si>
-  <si>
-    <t>1E+46</t>
+    <t>1E+113</t>
+  </si>
+  <si>
+    <t>1E+143</t>
+  </si>
+  <si>
+    <t>1E+47</t>
   </si>
   <si>
     <t>1E+75</t>
@@ -3946,19 +3946,19 @@
     <t>混沌鹿王</t>
   </si>
   <si>
-    <t>1E+90</t>
-  </si>
-  <si>
-    <t>1E+113</t>
-  </si>
-  <si>
-    <t>1E+145</t>
-  </si>
-  <si>
-    <t>1E+49</t>
-  </si>
-  <si>
-    <t>1E+78</t>
+    <t>1E+91</t>
+  </si>
+  <si>
+    <t>1E+117</t>
+  </si>
+  <si>
+    <t>1E+147</t>
+  </si>
+  <si>
+    <t>1E+51</t>
+  </si>
+  <si>
+    <t>1E+79</t>
   </si>
   <si>
     <t>14500000000000</t>
@@ -3973,19 +3973,19 @@
     <t>混沌草王</t>
   </si>
   <si>
-    <t>1E+93</t>
-  </si>
-  <si>
-    <t>1E+116</t>
-  </si>
-  <si>
-    <t>1E+148</t>
-  </si>
-  <si>
-    <t>1E+52</t>
-  </si>
-  <si>
-    <t>1E+81</t>
+    <t>1E+95</t>
+  </si>
+  <si>
+    <t>1E+121</t>
+  </si>
+  <si>
+    <t>1E+151</t>
+  </si>
+  <si>
+    <t>1E+55</t>
+  </si>
+  <si>
+    <t>1E+83</t>
   </si>
   <si>
     <t>10178</t>
@@ -3997,19 +3997,16 @@
     <t>混沌猫王</t>
   </si>
   <si>
-    <t>1E+96</t>
-  </si>
-  <si>
-    <t>1E+119</t>
-  </si>
-  <si>
-    <t>1E+151</t>
-  </si>
-  <si>
-    <t>1E+55</t>
-  </si>
-  <si>
-    <t>1E+84</t>
+    <t>1E+99</t>
+  </si>
+  <si>
+    <t>1E+125</t>
+  </si>
+  <si>
+    <t>1E+155</t>
+  </si>
+  <si>
+    <t>1E+59</t>
   </si>
   <si>
     <t>15500000000000</t>
@@ -4024,16 +4021,16 @@
     <t>混沌花王</t>
   </si>
   <si>
-    <t>1E+99</t>
-  </si>
-  <si>
-    <t>1E+122</t>
-  </si>
-  <si>
-    <t>1E+154</t>
-  </si>
-  <si>
-    <t>1E+58</t>
+    <t>1E+103</t>
+  </si>
+  <si>
+    <t>1E+129</t>
+  </si>
+  <si>
+    <t>1E+159</t>
+  </si>
+  <si>
+    <t>1E+63</t>
   </si>
   <si>
     <t>16000000000000</t>
@@ -5335,7 +5332,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -5370,6 +5367,7 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
@@ -5998,13 +5996,13 @@
       <c r="F6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="I6" s="24" t="s">
+      <c r="I6" s="25" t="s">
         <v>43</v>
       </c>
       <c r="J6" s="1">
@@ -8260,7 +8258,7 @@
       <c r="F40" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="G40" s="24" t="s">
+      <c r="G40" s="25" t="s">
         <v>287</v>
       </c>
       <c r="H40" s="1" t="s">
@@ -10012,7 +10010,7 @@
       <c r="H65" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="I65" s="24" t="s">
+      <c r="I65" s="25" t="s">
         <v>464</v>
       </c>
       <c r="J65" s="1">
@@ -10084,7 +10082,7 @@
       <c r="H66" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="I66" s="24" t="s">
+      <c r="I66" s="25" t="s">
         <v>471</v>
       </c>
       <c r="J66" s="1">
@@ -10156,7 +10154,7 @@
       <c r="H67" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="I67" s="24" t="s">
+      <c r="I67" s="25" t="s">
         <v>478</v>
       </c>
       <c r="J67" s="1">
@@ -10228,7 +10226,7 @@
       <c r="H68" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="I68" s="24" t="s">
+      <c r="I68" s="25" t="s">
         <v>485</v>
       </c>
       <c r="J68" s="1">
@@ -10300,7 +10298,7 @@
       <c r="H69" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="I69" s="24" t="s">
+      <c r="I69" s="25" t="s">
         <v>492</v>
       </c>
       <c r="J69" s="1">
@@ -10372,7 +10370,7 @@
       <c r="H70" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="I70" s="24" t="s">
+      <c r="I70" s="25" t="s">
         <v>499</v>
       </c>
       <c r="J70" s="1">
@@ -10437,13 +10435,13 @@
       <c r="F71" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="G71" s="25" t="s">
+      <c r="G71" s="26" t="s">
         <v>504</v>
       </c>
-      <c r="H71" s="24" t="s">
+      <c r="H71" s="25" t="s">
         <v>505</v>
       </c>
-      <c r="I71" s="25" t="s">
+      <c r="I71" s="26" t="s">
         <v>506</v>
       </c>
       <c r="J71" s="1">
@@ -10509,13 +10507,13 @@
       <c r="F72" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="G72" s="25" t="s">
+      <c r="G72" s="26" t="s">
         <v>511</v>
       </c>
-      <c r="H72" s="24" t="s">
+      <c r="H72" s="25" t="s">
         <v>512</v>
       </c>
-      <c r="I72" s="26" t="s">
+      <c r="I72" s="27" t="s">
         <v>513</v>
       </c>
       <c r="J72" s="1">
@@ -10581,13 +10579,13 @@
       <c r="F73" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="G73" s="25" t="s">
+      <c r="G73" s="26" t="s">
         <v>518</v>
       </c>
-      <c r="H73" s="24" t="s">
+      <c r="H73" s="25" t="s">
         <v>519</v>
       </c>
-      <c r="I73" s="26" t="s">
+      <c r="I73" s="27" t="s">
         <v>520</v>
       </c>
       <c r="J73" s="1">
@@ -10653,13 +10651,13 @@
       <c r="F74" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G74" s="25" t="s">
+      <c r="G74" s="26" t="s">
         <v>525</v>
       </c>
-      <c r="H74" s="24" t="s">
+      <c r="H74" s="25" t="s">
         <v>526</v>
       </c>
-      <c r="I74" s="26" t="s">
+      <c r="I74" s="27" t="s">
         <v>527</v>
       </c>
       <c r="J74" s="1">
@@ -10725,13 +10723,13 @@
       <c r="F75" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="G75" s="25" t="s">
+      <c r="G75" s="26" t="s">
         <v>532</v>
       </c>
-      <c r="H75" s="24" t="s">
+      <c r="H75" s="25" t="s">
         <v>533</v>
       </c>
-      <c r="I75" s="26" t="s">
+      <c r="I75" s="27" t="s">
         <v>534</v>
       </c>
       <c r="J75" s="1">
@@ -10771,7 +10769,7 @@
       <c r="T75" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="U75" s="24" t="s">
+      <c r="U75" s="25" t="s">
         <v>535</v>
       </c>
       <c r="W75" s="1" t="s">
@@ -10798,13 +10796,13 @@
       <c r="F76" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="G76" s="25" t="s">
+      <c r="G76" s="26" t="s">
         <v>539</v>
       </c>
-      <c r="H76" s="24" t="s">
+      <c r="H76" s="25" t="s">
         <v>540</v>
       </c>
-      <c r="I76" s="26" t="s">
+      <c r="I76" s="27" t="s">
         <v>541</v>
       </c>
       <c r="J76" s="1">
@@ -10869,13 +10867,13 @@
       <c r="F77" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="G77" s="25" t="s">
+      <c r="G77" s="26" t="s">
         <v>545</v>
       </c>
-      <c r="H77" s="24" t="s">
+      <c r="H77" s="25" t="s">
         <v>546</v>
       </c>
-      <c r="I77" s="26" t="s">
+      <c r="I77" s="27" t="s">
         <v>547</v>
       </c>
       <c r="J77" s="1">
@@ -10940,13 +10938,13 @@
       <c r="F78" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="G78" s="25" t="s">
+      <c r="G78" s="26" t="s">
         <v>551</v>
       </c>
-      <c r="H78" s="24" t="s">
+      <c r="H78" s="25" t="s">
         <v>552</v>
       </c>
-      <c r="I78" s="26" t="s">
+      <c r="I78" s="27" t="s">
         <v>553</v>
       </c>
       <c r="J78" s="1">
@@ -11011,13 +11009,13 @@
       <c r="F79" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="G79" s="25" t="s">
+      <c r="G79" s="26" t="s">
         <v>557</v>
       </c>
-      <c r="H79" s="24" t="s">
+      <c r="H79" s="25" t="s">
         <v>558</v>
       </c>
-      <c r="I79" s="26" t="s">
+      <c r="I79" s="27" t="s">
         <v>559</v>
       </c>
       <c r="J79" s="1">
@@ -11082,13 +11080,13 @@
       <c r="F80" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G80" s="25" t="s">
+      <c r="G80" s="26" t="s">
         <v>563</v>
       </c>
-      <c r="H80" s="24" t="s">
+      <c r="H80" s="25" t="s">
         <v>564</v>
       </c>
-      <c r="I80" s="26" t="s">
+      <c r="I80" s="27" t="s">
         <v>565</v>
       </c>
       <c r="J80" s="1">
@@ -11153,13 +11151,13 @@
       <c r="F81" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="G81" s="25" t="s">
+      <c r="G81" s="26" t="s">
         <v>569</v>
       </c>
-      <c r="H81" s="24" t="s">
+      <c r="H81" s="25" t="s">
         <v>570</v>
       </c>
-      <c r="I81" s="26" t="s">
+      <c r="I81" s="27" t="s">
         <v>571</v>
       </c>
       <c r="J81" s="1">
@@ -11226,13 +11224,13 @@
       <c r="F82" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="G82" s="25" t="s">
+      <c r="G82" s="26" t="s">
         <v>575</v>
       </c>
-      <c r="H82" s="24" t="s">
+      <c r="H82" s="25" t="s">
         <v>576</v>
       </c>
-      <c r="I82" s="26" t="s">
+      <c r="I82" s="27" t="s">
         <v>577</v>
       </c>
       <c r="J82" s="1">
@@ -11299,13 +11297,13 @@
       <c r="F83" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="G83" s="25" t="s">
+      <c r="G83" s="26" t="s">
         <v>581</v>
       </c>
-      <c r="H83" s="24" t="s">
+      <c r="H83" s="25" t="s">
         <v>532</v>
       </c>
-      <c r="I83" s="26" t="s">
+      <c r="I83" s="27" t="s">
         <v>582</v>
       </c>
       <c r="J83" s="1">
@@ -11372,13 +11370,13 @@
       <c r="F84" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="G84" s="25" t="s">
+      <c r="G84" s="26" t="s">
         <v>586</v>
       </c>
-      <c r="H84" s="24" t="s">
+      <c r="H84" s="25" t="s">
         <v>587</v>
       </c>
-      <c r="I84" s="26" t="s">
+      <c r="I84" s="27" t="s">
         <v>588</v>
       </c>
       <c r="J84" s="1">
@@ -11445,13 +11443,13 @@
       <c r="F85" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="G85" s="25" t="s">
+      <c r="G85" s="26" t="s">
         <v>464</v>
       </c>
-      <c r="H85" s="24" t="s">
+      <c r="H85" s="25" t="s">
         <v>592</v>
       </c>
-      <c r="I85" s="26" t="s">
+      <c r="I85" s="27" t="s">
         <v>593</v>
       </c>
       <c r="J85" s="1">
@@ -11518,13 +11516,13 @@
       <c r="F86" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="G86" s="25" t="s">
+      <c r="G86" s="26" t="s">
         <v>597</v>
       </c>
-      <c r="H86" s="24" t="s">
+      <c r="H86" s="25" t="s">
         <v>598</v>
       </c>
-      <c r="I86" s="26" t="s">
+      <c r="I86" s="27" t="s">
         <v>599</v>
       </c>
       <c r="J86" s="1">
@@ -11591,13 +11589,13 @@
       <c r="F87" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="G87" s="25" t="s">
+      <c r="G87" s="26" t="s">
         <v>603</v>
       </c>
-      <c r="H87" s="24" t="s">
+      <c r="H87" s="25" t="s">
         <v>604</v>
       </c>
-      <c r="I87" s="26" t="s">
+      <c r="I87" s="27" t="s">
         <v>605</v>
       </c>
       <c r="J87" s="1">
@@ -11664,13 +11662,13 @@
       <c r="F88" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="G88" s="25" t="s">
+      <c r="G88" s="26" t="s">
         <v>609</v>
       </c>
-      <c r="H88" s="24" t="s">
+      <c r="H88" s="25" t="s">
         <v>610</v>
       </c>
-      <c r="I88" s="26" t="s">
+      <c r="I88" s="27" t="s">
         <v>611</v>
       </c>
       <c r="J88" s="1">
@@ -11737,13 +11735,13 @@
       <c r="F89" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="G89" s="25" t="s">
+      <c r="G89" s="26" t="s">
         <v>615</v>
       </c>
-      <c r="H89" s="24" t="s">
+      <c r="H89" s="25" t="s">
         <v>464</v>
       </c>
-      <c r="I89" s="26" t="s">
+      <c r="I89" s="27" t="s">
         <v>616</v>
       </c>
       <c r="J89" s="1">
@@ -11810,13 +11808,13 @@
       <c r="F90" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="G90" s="25" t="s">
+      <c r="G90" s="26" t="s">
         <v>620</v>
       </c>
-      <c r="H90" s="24" t="s">
+      <c r="H90" s="25" t="s">
         <v>621</v>
       </c>
-      <c r="I90" s="26" t="s">
+      <c r="I90" s="27" t="s">
         <v>622</v>
       </c>
       <c r="J90" s="1">
@@ -11853,10 +11851,10 @@
       <c r="S90" s="12">
         <v>0</v>
       </c>
-      <c r="T90" s="24" t="s">
+      <c r="T90" s="25" t="s">
         <v>623</v>
       </c>
-      <c r="U90" s="24" t="s">
+      <c r="U90" s="25" t="s">
         <v>623</v>
       </c>
       <c r="W90" s="1" t="s">
@@ -11883,13 +11881,13 @@
       <c r="F91" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="G91" s="25" t="s">
+      <c r="G91" s="26" t="s">
         <v>513</v>
       </c>
-      <c r="H91" s="24" t="s">
+      <c r="H91" s="25" t="s">
         <v>627</v>
       </c>
-      <c r="I91" s="26" t="s">
+      <c r="I91" s="27" t="s">
         <v>628</v>
       </c>
       <c r="J91" s="1">
@@ -11926,10 +11924,10 @@
       <c r="S91" s="12">
         <v>0</v>
       </c>
-      <c r="T91" s="24" t="s">
+      <c r="T91" s="25" t="s">
         <v>629</v>
       </c>
-      <c r="U91" s="24" t="s">
+      <c r="U91" s="25" t="s">
         <v>629</v>
       </c>
       <c r="W91" s="1" t="s">
@@ -11956,13 +11954,13 @@
       <c r="F92" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="G92" s="25" t="s">
+      <c r="G92" s="26" t="s">
         <v>633</v>
       </c>
-      <c r="H92" s="24" t="s">
+      <c r="H92" s="25" t="s">
         <v>634</v>
       </c>
-      <c r="I92" s="26" t="s">
+      <c r="I92" s="27" t="s">
         <v>635</v>
       </c>
       <c r="J92" s="1">
@@ -11999,10 +11997,10 @@
       <c r="S92" s="12">
         <v>0</v>
       </c>
-      <c r="T92" s="24" t="s">
+      <c r="T92" s="25" t="s">
         <v>636</v>
       </c>
-      <c r="U92" s="24" t="s">
+      <c r="U92" s="25" t="s">
         <v>636</v>
       </c>
       <c r="W92" s="1" t="s">
@@ -12029,13 +12027,13 @@
       <c r="F93" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="G93" s="25" t="s">
+      <c r="G93" s="26" t="s">
         <v>640</v>
       </c>
-      <c r="H93" s="24" t="s">
+      <c r="H93" s="25" t="s">
         <v>641</v>
       </c>
-      <c r="I93" s="26" t="s">
+      <c r="I93" s="27" t="s">
         <v>642</v>
       </c>
       <c r="J93" s="1">
@@ -12072,10 +12070,10 @@
       <c r="S93" s="12">
         <v>0</v>
       </c>
-      <c r="T93" s="24" t="s">
+      <c r="T93" s="25" t="s">
         <v>643</v>
       </c>
-      <c r="U93" s="24" t="s">
+      <c r="U93" s="25" t="s">
         <v>643</v>
       </c>
       <c r="W93" s="1" t="s">
@@ -12102,13 +12100,13 @@
       <c r="F94" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="G94" s="25" t="s">
+      <c r="G94" s="26" t="s">
         <v>647</v>
       </c>
-      <c r="H94" s="24" t="s">
+      <c r="H94" s="25" t="s">
         <v>648</v>
       </c>
-      <c r="I94" s="26" t="s">
+      <c r="I94" s="27" t="s">
         <v>649</v>
       </c>
       <c r="J94" s="1">
@@ -12145,10 +12143,10 @@
       <c r="S94" s="12">
         <v>0</v>
       </c>
-      <c r="T94" s="24" t="s">
+      <c r="T94" s="25" t="s">
         <v>650</v>
       </c>
-      <c r="U94" s="24" t="s">
+      <c r="U94" s="25" t="s">
         <v>650</v>
       </c>
       <c r="W94" s="1" t="s">
@@ -12175,13 +12173,13 @@
       <c r="F95" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="G95" s="25" t="s">
+      <c r="G95" s="26" t="s">
         <v>654</v>
       </c>
-      <c r="H95" s="24" t="s">
+      <c r="H95" s="25" t="s">
         <v>655</v>
       </c>
-      <c r="I95" s="26" t="s">
+      <c r="I95" s="27" t="s">
         <v>656</v>
       </c>
       <c r="J95" s="1">
@@ -12218,10 +12216,10 @@
       <c r="S95" s="12">
         <v>0</v>
       </c>
-      <c r="T95" s="24" t="s">
+      <c r="T95" s="25" t="s">
         <v>657</v>
       </c>
-      <c r="U95" s="24" t="s">
+      <c r="U95" s="25" t="s">
         <v>657</v>
       </c>
       <c r="W95" s="1" t="s">
@@ -12246,13 +12244,13 @@
       <c r="F96" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="G96" s="25" t="s">
+      <c r="G96" s="26" t="s">
         <v>661</v>
       </c>
-      <c r="H96" s="24" t="s">
+      <c r="H96" s="25" t="s">
         <v>662</v>
       </c>
-      <c r="I96" s="26" t="s">
+      <c r="I96" s="27" t="s">
         <v>663</v>
       </c>
       <c r="J96" s="1">
@@ -12289,10 +12287,10 @@
       <c r="S96" s="12">
         <v>0</v>
       </c>
-      <c r="T96" s="24" t="s">
+      <c r="T96" s="25" t="s">
         <v>664</v>
       </c>
-      <c r="U96" s="24" t="s">
+      <c r="U96" s="25" t="s">
         <v>664</v>
       </c>
       <c r="W96" s="1" t="s">
@@ -12315,13 +12313,13 @@
       <c r="F97" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="G97" s="25" t="s">
+      <c r="G97" s="26" t="s">
         <v>668</v>
       </c>
-      <c r="H97" s="24" t="s">
+      <c r="H97" s="25" t="s">
         <v>669</v>
       </c>
-      <c r="I97" s="26" t="s">
+      <c r="I97" s="27" t="s">
         <v>670</v>
       </c>
       <c r="J97" s="1">
@@ -12358,10 +12356,10 @@
       <c r="S97" s="12">
         <v>0</v>
       </c>
-      <c r="T97" s="24" t="s">
+      <c r="T97" s="25" t="s">
         <v>671</v>
       </c>
-      <c r="U97" s="24" t="s">
+      <c r="U97" s="25" t="s">
         <v>671</v>
       </c>
       <c r="W97" s="1" t="s">
@@ -12384,13 +12382,13 @@
       <c r="F98" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="G98" s="25" t="s">
+      <c r="G98" s="26" t="s">
         <v>675</v>
       </c>
-      <c r="H98" s="24" t="s">
+      <c r="H98" s="25" t="s">
         <v>676</v>
       </c>
-      <c r="I98" s="26" t="s">
+      <c r="I98" s="27" t="s">
         <v>677</v>
       </c>
       <c r="J98" s="1">
@@ -12427,10 +12425,10 @@
       <c r="S98" s="12">
         <v>0</v>
       </c>
-      <c r="T98" s="24" t="s">
+      <c r="T98" s="25" t="s">
         <v>678</v>
       </c>
-      <c r="U98" s="24" t="s">
+      <c r="U98" s="25" t="s">
         <v>678</v>
       </c>
       <c r="W98" s="1" t="s">
@@ -12453,13 +12451,13 @@
       <c r="F99" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="G99" s="25" t="s">
+      <c r="G99" s="26" t="s">
         <v>682</v>
       </c>
-      <c r="H99" s="24" t="s">
+      <c r="H99" s="25" t="s">
         <v>683</v>
       </c>
-      <c r="I99" s="26" t="s">
+      <c r="I99" s="27" t="s">
         <v>684</v>
       </c>
       <c r="J99" s="1">
@@ -12496,10 +12494,10 @@
       <c r="S99" s="12">
         <v>0</v>
       </c>
-      <c r="T99" s="24" t="s">
+      <c r="T99" s="25" t="s">
         <v>685</v>
       </c>
-      <c r="U99" s="24" t="s">
+      <c r="U99" s="25" t="s">
         <v>685</v>
       </c>
       <c r="W99" s="1" t="s">
@@ -12522,13 +12520,13 @@
       <c r="F100" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="G100" s="25" t="s">
+      <c r="G100" s="26" t="s">
         <v>688</v>
       </c>
-      <c r="H100" s="24" t="s">
+      <c r="H100" s="25" t="s">
         <v>689</v>
       </c>
-      <c r="I100" s="26" t="s">
+      <c r="I100" s="27" t="s">
         <v>690</v>
       </c>
       <c r="J100" s="1">
@@ -12565,10 +12563,10 @@
       <c r="S100" s="12">
         <v>0</v>
       </c>
-      <c r="T100" s="24" t="s">
+      <c r="T100" s="25" t="s">
         <v>691</v>
       </c>
-      <c r="U100" s="24" t="s">
+      <c r="U100" s="25" t="s">
         <v>691</v>
       </c>
       <c r="W100" s="1" t="s">
@@ -12593,13 +12591,13 @@
       <c r="F101" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="G101" s="25" t="s">
+      <c r="G101" s="26" t="s">
         <v>695</v>
       </c>
-      <c r="H101" s="24" t="s">
+      <c r="H101" s="25" t="s">
         <v>696</v>
       </c>
-      <c r="I101" s="26" t="s">
+      <c r="I101" s="27" t="s">
         <v>697</v>
       </c>
       <c r="J101" s="1">
@@ -12636,10 +12634,10 @@
       <c r="S101" s="12">
         <v>0</v>
       </c>
-      <c r="T101" s="24" t="s">
+      <c r="T101" s="25" t="s">
         <v>698</v>
       </c>
-      <c r="U101" s="24" t="s">
+      <c r="U101" s="25" t="s">
         <v>698</v>
       </c>
       <c r="W101" s="1" t="s">
@@ -12666,13 +12664,13 @@
       <c r="F102" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="G102" s="25" t="s">
+      <c r="G102" s="26" t="s">
         <v>702</v>
       </c>
-      <c r="H102" s="24" t="s">
+      <c r="H102" s="25" t="s">
         <v>611</v>
       </c>
-      <c r="I102" s="26" t="s">
+      <c r="I102" s="27" t="s">
         <v>703</v>
       </c>
       <c r="J102" s="1">
@@ -12709,10 +12707,10 @@
       <c r="S102" s="12">
         <v>0</v>
       </c>
-      <c r="T102" s="24" t="s">
+      <c r="T102" s="25" t="s">
         <v>704</v>
       </c>
-      <c r="U102" s="24" t="s">
+      <c r="U102" s="25" t="s">
         <v>704</v>
       </c>
       <c r="W102" s="1" t="s">
@@ -12739,13 +12737,13 @@
       <c r="F103" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="G103" s="25" t="s">
+      <c r="G103" s="26" t="s">
         <v>708</v>
       </c>
-      <c r="H103" s="24" t="s">
+      <c r="H103" s="25" t="s">
         <v>616</v>
       </c>
-      <c r="I103" s="26" t="s">
+      <c r="I103" s="27" t="s">
         <v>709</v>
       </c>
       <c r="J103" s="1">
@@ -12782,10 +12780,10 @@
       <c r="S103" s="12">
         <v>0</v>
       </c>
-      <c r="T103" s="24" t="s">
+      <c r="T103" s="25" t="s">
         <v>710</v>
       </c>
-      <c r="U103" s="24" t="s">
+      <c r="U103" s="25" t="s">
         <v>710</v>
       </c>
       <c r="W103" s="1" t="s">
@@ -12812,13 +12810,13 @@
       <c r="F104" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="G104" s="25" t="s">
+      <c r="G104" s="26" t="s">
         <v>714</v>
       </c>
-      <c r="H104" s="24" t="s">
+      <c r="H104" s="25" t="s">
         <v>715</v>
       </c>
-      <c r="I104" s="26" t="s">
+      <c r="I104" s="27" t="s">
         <v>716</v>
       </c>
       <c r="J104" s="1">
@@ -12855,10 +12853,10 @@
       <c r="S104" s="12">
         <v>0</v>
       </c>
-      <c r="T104" s="24" t="s">
+      <c r="T104" s="25" t="s">
         <v>717</v>
       </c>
-      <c r="U104" s="24" t="s">
+      <c r="U104" s="25" t="s">
         <v>717</v>
       </c>
       <c r="W104" s="1" t="s">
@@ -12885,13 +12883,13 @@
       <c r="F105" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="G105" s="25" t="s">
+      <c r="G105" s="26" t="s">
         <v>721</v>
       </c>
-      <c r="H105" s="24" t="s">
+      <c r="H105" s="25" t="s">
         <v>722</v>
       </c>
-      <c r="I105" s="26" t="s">
+      <c r="I105" s="27" t="s">
         <v>723</v>
       </c>
       <c r="J105" s="1">
@@ -12928,10 +12926,10 @@
       <c r="S105" s="12">
         <v>0</v>
       </c>
-      <c r="T105" s="24" t="s">
+      <c r="T105" s="25" t="s">
         <v>724</v>
       </c>
-      <c r="U105" s="24" t="s">
+      <c r="U105" s="25" t="s">
         <v>724</v>
       </c>
       <c r="W105" s="1" t="s">
@@ -12958,13 +12956,13 @@
       <c r="F106" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="G106" s="25" t="s">
+      <c r="G106" s="26" t="s">
         <v>728</v>
       </c>
-      <c r="H106" s="24" t="s">
+      <c r="H106" s="25" t="s">
         <v>729</v>
       </c>
-      <c r="I106" s="26" t="s">
+      <c r="I106" s="27" t="s">
         <v>730</v>
       </c>
       <c r="J106" s="1">
@@ -13001,10 +12999,10 @@
       <c r="S106" s="12">
         <v>0</v>
       </c>
-      <c r="T106" s="24" t="s">
+      <c r="T106" s="25" t="s">
         <v>731</v>
       </c>
-      <c r="U106" s="24" t="s">
+      <c r="U106" s="25" t="s">
         <v>731</v>
       </c>
       <c r="W106" s="1" t="s">
@@ -13031,13 +13029,13 @@
       <c r="F107" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="G107" s="25" t="s">
+      <c r="G107" s="26" t="s">
         <v>735</v>
       </c>
-      <c r="H107" s="24" t="s">
+      <c r="H107" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="I107" s="26" t="s">
+      <c r="I107" s="27" t="s">
         <v>737</v>
       </c>
       <c r="J107" s="1">
@@ -13074,10 +13072,10 @@
       <c r="S107" s="12">
         <v>0</v>
       </c>
-      <c r="T107" s="24" t="s">
+      <c r="T107" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="U107" s="24" t="s">
+      <c r="U107" s="25" t="s">
         <v>738</v>
       </c>
       <c r="W107" s="1" t="s">
@@ -13104,13 +13102,13 @@
       <c r="F108" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="G108" s="25" t="s">
+      <c r="G108" s="26" t="s">
         <v>742</v>
       </c>
-      <c r="H108" s="24" t="s">
+      <c r="H108" s="25" t="s">
         <v>743</v>
       </c>
-      <c r="I108" s="26" t="s">
+      <c r="I108" s="27" t="s">
         <v>744</v>
       </c>
       <c r="J108" s="1">
@@ -13147,10 +13145,10 @@
       <c r="S108" s="12">
         <v>0</v>
       </c>
-      <c r="T108" s="24" t="s">
+      <c r="T108" s="25" t="s">
         <v>745</v>
       </c>
-      <c r="U108" s="24" t="s">
+      <c r="U108" s="25" t="s">
         <v>745</v>
       </c>
       <c r="W108" s="1" t="s">
@@ -13177,13 +13175,13 @@
       <c r="F109" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="G109" s="25" t="s">
+      <c r="G109" s="26" t="s">
         <v>749</v>
       </c>
-      <c r="H109" s="24" t="s">
+      <c r="H109" s="25" t="s">
         <v>750</v>
       </c>
-      <c r="I109" s="26" t="s">
+      <c r="I109" s="27" t="s">
         <v>751</v>
       </c>
       <c r="J109" s="1">
@@ -13220,10 +13218,10 @@
       <c r="S109" s="12">
         <v>0</v>
       </c>
-      <c r="T109" s="24" t="s">
+      <c r="T109" s="25" t="s">
         <v>752</v>
       </c>
-      <c r="U109" s="24" t="s">
+      <c r="U109" s="25" t="s">
         <v>752</v>
       </c>
       <c r="W109" s="1" t="s">
@@ -13250,13 +13248,13 @@
       <c r="F110" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="G110" s="25" t="s">
+      <c r="G110" s="26" t="s">
         <v>677</v>
       </c>
-      <c r="H110" s="24" t="s">
+      <c r="H110" s="25" t="s">
         <v>756</v>
       </c>
-      <c r="I110" s="26" t="s">
+      <c r="I110" s="27" t="s">
         <v>757</v>
       </c>
       <c r="J110" s="1">
@@ -13293,10 +13291,10 @@
       <c r="S110" s="12">
         <v>0</v>
       </c>
-      <c r="T110" s="24" t="s">
+      <c r="T110" s="25" t="s">
         <v>758</v>
       </c>
-      <c r="U110" s="24" t="s">
+      <c r="U110" s="25" t="s">
         <v>758</v>
       </c>
       <c r="W110" s="1" t="s">
@@ -13323,13 +13321,13 @@
       <c r="F111" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="G111" s="27" t="s">
+      <c r="G111" s="28" t="s">
         <v>762</v>
       </c>
-      <c r="H111" s="28" t="s">
+      <c r="H111" s="29" t="s">
         <v>762</v>
       </c>
-      <c r="I111" s="29" t="s">
+      <c r="I111" s="30" t="s">
         <v>763</v>
       </c>
       <c r="J111" s="1">
@@ -13362,10 +13360,10 @@
       <c r="S111" s="8">
         <v>90</v>
       </c>
-      <c r="T111" s="28" t="s">
+      <c r="T111" s="29" t="s">
         <v>764</v>
       </c>
-      <c r="U111" s="28" t="s">
+      <c r="U111" s="29" t="s">
         <v>764</v>
       </c>
       <c r="W111" s="2" t="s">
@@ -13390,13 +13388,13 @@
       <c r="F112" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="G112" s="25" t="s">
+      <c r="G112" s="26" t="s">
         <v>768</v>
       </c>
-      <c r="H112" s="24" t="s">
+      <c r="H112" s="25" t="s">
         <v>768</v>
       </c>
-      <c r="I112" s="26" t="s">
+      <c r="I112" s="27" t="s">
         <v>769</v>
       </c>
       <c r="J112" s="1">
@@ -13434,10 +13432,10 @@
       <c r="S112" s="8">
         <v>90</v>
       </c>
-      <c r="T112" s="24" t="s">
+      <c r="T112" s="25" t="s">
         <v>770</v>
       </c>
-      <c r="U112" s="24" t="s">
+      <c r="U112" s="25" t="s">
         <v>770</v>
       </c>
       <c r="W112" s="1" t="s">
@@ -13462,13 +13460,13 @@
       <c r="F113" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="G113" s="25" t="s">
+      <c r="G113" s="26" t="s">
         <v>774</v>
       </c>
-      <c r="H113" s="24" t="s">
+      <c r="H113" s="25" t="s">
         <v>774</v>
       </c>
-      <c r="I113" s="26" t="s">
+      <c r="I113" s="27" t="s">
         <v>775</v>
       </c>
       <c r="J113" s="1">
@@ -13506,10 +13504,10 @@
       <c r="S113" s="8">
         <v>90</v>
       </c>
-      <c r="T113" s="24" t="s">
+      <c r="T113" s="25" t="s">
         <v>776</v>
       </c>
-      <c r="U113" s="24" t="s">
+      <c r="U113" s="25" t="s">
         <v>776</v>
       </c>
       <c r="W113" s="1" t="s">
@@ -13534,13 +13532,13 @@
       <c r="F114" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="G114" s="25" t="s">
+      <c r="G114" s="26" t="s">
         <v>780</v>
       </c>
-      <c r="H114" s="24" t="s">
+      <c r="H114" s="25" t="s">
         <v>780</v>
       </c>
-      <c r="I114" s="26" t="s">
+      <c r="I114" s="27" t="s">
         <v>781</v>
       </c>
       <c r="J114" s="1">
@@ -13578,10 +13576,10 @@
       <c r="S114" s="8">
         <v>90</v>
       </c>
-      <c r="T114" s="24" t="s">
+      <c r="T114" s="25" t="s">
         <v>782</v>
       </c>
-      <c r="U114" s="24" t="s">
+      <c r="U114" s="25" t="s">
         <v>782</v>
       </c>
       <c r="W114" s="1" t="s">
@@ -13606,13 +13604,13 @@
       <c r="F115" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="G115" s="25" t="s">
+      <c r="G115" s="26" t="s">
         <v>786</v>
       </c>
-      <c r="H115" s="24" t="s">
+      <c r="H115" s="25" t="s">
         <v>786</v>
       </c>
-      <c r="I115" s="26" t="s">
+      <c r="I115" s="27" t="s">
         <v>787</v>
       </c>
       <c r="J115" s="1">
@@ -13650,10 +13648,10 @@
       <c r="S115" s="8">
         <v>90</v>
       </c>
-      <c r="T115" s="24" t="s">
+      <c r="T115" s="25" t="s">
         <v>788</v>
       </c>
-      <c r="U115" s="24" t="s">
+      <c r="U115" s="25" t="s">
         <v>788</v>
       </c>
       <c r="W115" s="1" t="s">
@@ -13678,13 +13676,13 @@
       <c r="F116" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="G116" s="25" t="s">
+      <c r="G116" s="26" t="s">
         <v>792</v>
       </c>
-      <c r="H116" s="24" t="s">
+      <c r="H116" s="25" t="s">
         <v>792</v>
       </c>
-      <c r="I116" s="26" t="s">
+      <c r="I116" s="27" t="s">
         <v>793</v>
       </c>
       <c r="J116" s="1">
@@ -13722,10 +13720,10 @@
       <c r="S116" s="8">
         <v>90</v>
       </c>
-      <c r="T116" s="24" t="s">
+      <c r="T116" s="25" t="s">
         <v>794</v>
       </c>
-      <c r="U116" s="24" t="s">
+      <c r="U116" s="25" t="s">
         <v>794</v>
       </c>
       <c r="W116" s="1" t="s">
@@ -13752,13 +13750,13 @@
       <c r="F117" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="G117" s="25" t="s">
+      <c r="G117" s="26" t="s">
         <v>798</v>
       </c>
-      <c r="H117" s="24" t="s">
+      <c r="H117" s="25" t="s">
         <v>798</v>
       </c>
-      <c r="I117" s="26" t="s">
+      <c r="I117" s="27" t="s">
         <v>799</v>
       </c>
       <c r="J117" s="1">
@@ -13796,10 +13794,10 @@
       <c r="S117" s="8">
         <v>90</v>
       </c>
-      <c r="T117" s="24" t="s">
+      <c r="T117" s="25" t="s">
         <v>800</v>
       </c>
-      <c r="U117" s="24" t="s">
+      <c r="U117" s="25" t="s">
         <v>800</v>
       </c>
       <c r="W117" s="1" t="s">
@@ -13826,13 +13824,13 @@
       <c r="F118" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="G118" s="25" t="s">
+      <c r="G118" s="26" t="s">
         <v>804</v>
       </c>
-      <c r="H118" s="24" t="s">
+      <c r="H118" s="25" t="s">
         <v>804</v>
       </c>
-      <c r="I118" s="26" t="s">
+      <c r="I118" s="27" t="s">
         <v>805</v>
       </c>
       <c r="J118" s="1">
@@ -13870,10 +13868,10 @@
       <c r="S118" s="8">
         <v>90</v>
       </c>
-      <c r="T118" s="24" t="s">
+      <c r="T118" s="25" t="s">
         <v>806</v>
       </c>
-      <c r="U118" s="24" t="s">
+      <c r="U118" s="25" t="s">
         <v>806</v>
       </c>
       <c r="W118" s="1" t="s">
@@ -13900,13 +13898,13 @@
       <c r="F119" s="1" t="s">
         <v>809</v>
       </c>
-      <c r="G119" s="25" t="s">
+      <c r="G119" s="26" t="s">
         <v>810</v>
       </c>
-      <c r="H119" s="24" t="s">
+      <c r="H119" s="25" t="s">
         <v>810</v>
       </c>
-      <c r="I119" s="26" t="s">
+      <c r="I119" s="27" t="s">
         <v>811</v>
       </c>
       <c r="J119" s="1">
@@ -13944,10 +13942,10 @@
       <c r="S119" s="8">
         <v>90</v>
       </c>
-      <c r="T119" s="24" t="s">
+      <c r="T119" s="25" t="s">
         <v>812</v>
       </c>
-      <c r="U119" s="24" t="s">
+      <c r="U119" s="25" t="s">
         <v>812</v>
       </c>
       <c r="W119" s="1" t="s">
@@ -13974,13 +13972,13 @@
       <c r="F120" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="G120" s="25" t="s">
+      <c r="G120" s="26" t="s">
         <v>816</v>
       </c>
-      <c r="H120" s="24" t="s">
+      <c r="H120" s="25" t="s">
         <v>816</v>
       </c>
-      <c r="I120" s="26" t="s">
+      <c r="I120" s="27" t="s">
         <v>817</v>
       </c>
       <c r="J120" s="1">
@@ -14018,10 +14016,10 @@
       <c r="S120" s="8">
         <v>90</v>
       </c>
-      <c r="T120" s="24" t="s">
+      <c r="T120" s="25" t="s">
         <v>818</v>
       </c>
-      <c r="U120" s="24" t="s">
+      <c r="U120" s="25" t="s">
         <v>818</v>
       </c>
       <c r="W120" s="1" t="s">
@@ -14046,13 +14044,13 @@
       <c r="F121" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="G121" s="25" t="s">
+      <c r="G121" s="26" t="s">
         <v>763</v>
       </c>
-      <c r="H121" s="24" t="s">
+      <c r="H121" s="25" t="s">
         <v>763</v>
       </c>
-      <c r="I121" s="26" t="s">
+      <c r="I121" s="27" t="s">
         <v>822</v>
       </c>
       <c r="J121" s="1">
@@ -14091,10 +14089,10 @@
       <c r="S121" s="8">
         <v>90</v>
       </c>
-      <c r="T121" s="24" t="s">
+      <c r="T121" s="25" t="s">
         <v>823</v>
       </c>
-      <c r="U121" s="24" t="s">
+      <c r="U121" s="25" t="s">
         <v>823</v>
       </c>
       <c r="W121" s="1" t="s">
@@ -14119,13 +14117,13 @@
       <c r="F122" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="G122" s="25" t="s">
+      <c r="G122" s="26" t="s">
         <v>827</v>
       </c>
-      <c r="H122" s="24" t="s">
+      <c r="H122" s="25" t="s">
         <v>827</v>
       </c>
-      <c r="I122" s="26" t="s">
+      <c r="I122" s="27" t="s">
         <v>828</v>
       </c>
       <c r="J122" s="1">
@@ -14164,10 +14162,10 @@
       <c r="S122" s="8">
         <v>90</v>
       </c>
-      <c r="T122" s="24" t="s">
+      <c r="T122" s="25" t="s">
         <v>829</v>
       </c>
-      <c r="U122" s="24" t="s">
+      <c r="U122" s="25" t="s">
         <v>829</v>
       </c>
       <c r="W122" s="1" t="s">
@@ -14192,13 +14190,13 @@
       <c r="F123" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="G123" s="25" t="s">
+      <c r="G123" s="26" t="s">
         <v>833</v>
       </c>
-      <c r="H123" s="24" t="s">
+      <c r="H123" s="25" t="s">
         <v>833</v>
       </c>
-      <c r="I123" s="26" t="s">
+      <c r="I123" s="27" t="s">
         <v>834</v>
       </c>
       <c r="J123" s="1">
@@ -14237,10 +14235,10 @@
       <c r="S123" s="8">
         <v>90</v>
       </c>
-      <c r="T123" s="24" t="s">
+      <c r="T123" s="25" t="s">
         <v>835</v>
       </c>
-      <c r="U123" s="24" t="s">
+      <c r="U123" s="25" t="s">
         <v>835</v>
       </c>
       <c r="W123" s="1" t="s">
@@ -14265,13 +14263,13 @@
       <c r="F124" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="G124" s="25" t="s">
+      <c r="G124" s="26" t="s">
         <v>839</v>
       </c>
-      <c r="H124" s="24" t="s">
+      <c r="H124" s="25" t="s">
         <v>839</v>
       </c>
-      <c r="I124" s="26" t="s">
+      <c r="I124" s="27" t="s">
         <v>840</v>
       </c>
       <c r="J124" s="1">
@@ -14310,10 +14308,10 @@
       <c r="S124" s="8">
         <v>90</v>
       </c>
-      <c r="T124" s="24" t="s">
+      <c r="T124" s="25" t="s">
         <v>841</v>
       </c>
-      <c r="U124" s="24" t="s">
+      <c r="U124" s="25" t="s">
         <v>841</v>
       </c>
       <c r="W124" s="1" t="s">
@@ -14338,13 +14336,13 @@
       <c r="F125" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="G125" s="25" t="s">
+      <c r="G125" s="26" t="s">
         <v>845</v>
       </c>
-      <c r="H125" s="24" t="s">
+      <c r="H125" s="25" t="s">
         <v>845</v>
       </c>
-      <c r="I125" s="26" t="s">
+      <c r="I125" s="27" t="s">
         <v>846</v>
       </c>
       <c r="J125" s="1">
@@ -14383,10 +14381,10 @@
       <c r="S125" s="8">
         <v>90</v>
       </c>
-      <c r="T125" s="24" t="s">
+      <c r="T125" s="25" t="s">
         <v>847</v>
       </c>
-      <c r="U125" s="24" t="s">
+      <c r="U125" s="25" t="s">
         <v>847</v>
       </c>
       <c r="W125" s="1" t="s">
@@ -14413,13 +14411,13 @@
       <c r="F126" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="G126" s="25" t="s">
+      <c r="G126" s="26" t="s">
         <v>851</v>
       </c>
-      <c r="H126" s="24" t="s">
+      <c r="H126" s="25" t="s">
         <v>851</v>
       </c>
-      <c r="I126" s="26" t="s">
+      <c r="I126" s="27" t="s">
         <v>852</v>
       </c>
       <c r="J126" s="1">
@@ -14458,10 +14456,10 @@
       <c r="S126" s="8">
         <v>90</v>
       </c>
-      <c r="T126" s="24" t="s">
+      <c r="T126" s="25" t="s">
         <v>853</v>
       </c>
-      <c r="U126" s="24" t="s">
+      <c r="U126" s="25" t="s">
         <v>853</v>
       </c>
       <c r="W126" s="1" t="s">
@@ -14488,13 +14486,13 @@
       <c r="F127" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="G127" s="25" t="s">
+      <c r="G127" s="26" t="s">
         <v>857</v>
       </c>
-      <c r="H127" s="24" t="s">
+      <c r="H127" s="25" t="s">
         <v>857</v>
       </c>
-      <c r="I127" s="26" t="s">
+      <c r="I127" s="27" t="s">
         <v>858</v>
       </c>
       <c r="J127" s="1">
@@ -14533,10 +14531,10 @@
       <c r="S127" s="8">
         <v>90</v>
       </c>
-      <c r="T127" s="24" t="s">
+      <c r="T127" s="25" t="s">
         <v>859</v>
       </c>
-      <c r="U127" s="24" t="s">
+      <c r="U127" s="25" t="s">
         <v>859</v>
       </c>
       <c r="W127" s="1" t="s">
@@ -14563,13 +14561,13 @@
       <c r="F128" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="G128" s="25" t="s">
+      <c r="G128" s="26" t="s">
         <v>863</v>
       </c>
-      <c r="H128" s="24" t="s">
+      <c r="H128" s="25" t="s">
         <v>863</v>
       </c>
-      <c r="I128" s="26" t="s">
+      <c r="I128" s="27" t="s">
         <v>864</v>
       </c>
       <c r="J128" s="1">
@@ -14608,10 +14606,10 @@
       <c r="S128" s="8">
         <v>90</v>
       </c>
-      <c r="T128" s="24" t="s">
+      <c r="T128" s="25" t="s">
         <v>865</v>
       </c>
-      <c r="U128" s="24" t="s">
+      <c r="U128" s="25" t="s">
         <v>865</v>
       </c>
       <c r="W128" s="1" t="s">
@@ -14638,13 +14636,13 @@
       <c r="F129" s="1" t="s">
         <v>868</v>
       </c>
-      <c r="G129" s="25" t="s">
+      <c r="G129" s="26" t="s">
         <v>869</v>
       </c>
-      <c r="H129" s="24" t="s">
+      <c r="H129" s="25" t="s">
         <v>869</v>
       </c>
-      <c r="I129" s="26" t="s">
+      <c r="I129" s="27" t="s">
         <v>870</v>
       </c>
       <c r="J129" s="1">
@@ -14683,10 +14681,10 @@
       <c r="S129" s="8">
         <v>90</v>
       </c>
-      <c r="T129" s="24" t="s">
+      <c r="T129" s="25" t="s">
         <v>871</v>
       </c>
-      <c r="U129" s="24" t="s">
+      <c r="U129" s="25" t="s">
         <v>871</v>
       </c>
       <c r="W129" s="1" t="s">
@@ -14713,13 +14711,13 @@
       <c r="F130" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="G130" s="25" t="s">
+      <c r="G130" s="26" t="s">
         <v>875</v>
       </c>
-      <c r="H130" s="24" t="s">
+      <c r="H130" s="25" t="s">
         <v>875</v>
       </c>
-      <c r="I130" s="26" t="s">
+      <c r="I130" s="27" t="s">
         <v>876</v>
       </c>
       <c r="J130" s="1">
@@ -14758,10 +14756,10 @@
       <c r="S130" s="8">
         <v>90</v>
       </c>
-      <c r="T130" s="24" t="s">
+      <c r="T130" s="25" t="s">
         <v>877</v>
       </c>
-      <c r="U130" s="24" t="s">
+      <c r="U130" s="25" t="s">
         <v>877</v>
       </c>
       <c r="W130" s="1" t="s">
@@ -14786,13 +14784,13 @@
       <c r="F131" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="G131" s="25" t="s">
+      <c r="G131" s="26" t="s">
         <v>881</v>
       </c>
-      <c r="H131" s="24" t="s">
+      <c r="H131" s="25" t="s">
         <v>881</v>
       </c>
-      <c r="I131" s="26" t="s">
+      <c r="I131" s="27" t="s">
         <v>882</v>
       </c>
       <c r="J131" s="1">
@@ -14831,10 +14829,10 @@
       <c r="S131" s="8">
         <v>92</v>
       </c>
-      <c r="T131" s="24" t="s">
+      <c r="T131" s="25" t="s">
         <v>883</v>
       </c>
-      <c r="U131" s="24" t="s">
+      <c r="U131" s="25" t="s">
         <v>883</v>
       </c>
       <c r="W131" s="1" t="s">
@@ -14857,13 +14855,13 @@
       <c r="F132" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="G132" s="25" t="s">
+      <c r="G132" s="26" t="s">
         <v>887</v>
       </c>
-      <c r="H132" s="24" t="s">
+      <c r="H132" s="25" t="s">
         <v>887</v>
       </c>
-      <c r="I132" s="26" t="s">
+      <c r="I132" s="27" t="s">
         <v>888</v>
       </c>
       <c r="J132" s="1">
@@ -14902,10 +14900,10 @@
       <c r="S132" s="8">
         <v>94</v>
       </c>
-      <c r="T132" s="24" t="s">
+      <c r="T132" s="25" t="s">
         <v>889</v>
       </c>
-      <c r="U132" s="24" t="s">
+      <c r="U132" s="25" t="s">
         <v>889</v>
       </c>
       <c r="W132" s="1" t="s">
@@ -14928,13 +14926,13 @@
       <c r="F133" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="G133" s="25" t="s">
+      <c r="G133" s="26" t="s">
         <v>893</v>
       </c>
-      <c r="H133" s="24" t="s">
+      <c r="H133" s="25" t="s">
         <v>893</v>
       </c>
-      <c r="I133" s="26" t="s">
+      <c r="I133" s="27" t="s">
         <v>894</v>
       </c>
       <c r="J133" s="1">
@@ -14973,10 +14971,10 @@
       <c r="S133" s="8">
         <v>96</v>
       </c>
-      <c r="T133" s="24" t="s">
+      <c r="T133" s="25" t="s">
         <v>895</v>
       </c>
-      <c r="U133" s="24" t="s">
+      <c r="U133" s="25" t="s">
         <v>895</v>
       </c>
       <c r="W133" s="1" t="s">
@@ -14999,13 +14997,13 @@
       <c r="F134" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="G134" s="25" t="s">
+      <c r="G134" s="26" t="s">
         <v>899</v>
       </c>
-      <c r="H134" s="24" t="s">
+      <c r="H134" s="25" t="s">
         <v>899</v>
       </c>
-      <c r="I134" s="26" t="s">
+      <c r="I134" s="27" t="s">
         <v>900</v>
       </c>
       <c r="J134" s="1">
@@ -15044,10 +15042,10 @@
       <c r="S134" s="8">
         <v>98</v>
       </c>
-      <c r="T134" s="24" t="s">
+      <c r="T134" s="25" t="s">
         <v>901</v>
       </c>
-      <c r="U134" s="24" t="s">
+      <c r="U134" s="25" t="s">
         <v>901</v>
       </c>
       <c r="W134" s="1" t="s">
@@ -15070,13 +15068,13 @@
       <c r="F135" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="G135" s="25" t="s">
+      <c r="G135" s="26" t="s">
         <v>904</v>
       </c>
-      <c r="H135" s="24" t="s">
+      <c r="H135" s="25" t="s">
         <v>904</v>
       </c>
-      <c r="I135" s="26" t="s">
+      <c r="I135" s="27" t="s">
         <v>905</v>
       </c>
       <c r="J135" s="1">
@@ -15115,10 +15113,10 @@
       <c r="S135" s="8">
         <v>99</v>
       </c>
-      <c r="T135" s="24" t="s">
+      <c r="T135" s="25" t="s">
         <v>456</v>
       </c>
-      <c r="U135" s="24" t="s">
+      <c r="U135" s="25" t="s">
         <v>456</v>
       </c>
       <c r="W135" s="1" t="s">
@@ -15143,13 +15141,13 @@
       <c r="F136" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="G136" s="25" t="s">
+      <c r="G136" s="26" t="s">
         <v>909</v>
       </c>
-      <c r="H136" s="24" t="s">
+      <c r="H136" s="25" t="s">
         <v>909</v>
       </c>
-      <c r="I136" s="26" t="s">
+      <c r="I136" s="27" t="s">
         <v>910</v>
       </c>
       <c r="J136" s="1">
@@ -15188,10 +15186,10 @@
       <c r="S136" s="8">
         <v>99.2</v>
       </c>
-      <c r="T136" s="24" t="s">
+      <c r="T136" s="25" t="s">
         <v>911</v>
       </c>
-      <c r="U136" s="24" t="s">
+      <c r="U136" s="25" t="s">
         <v>911</v>
       </c>
       <c r="W136" s="1" t="s">
@@ -15218,13 +15216,13 @@
       <c r="F137" s="1" t="s">
         <v>914</v>
       </c>
-      <c r="G137" s="25" t="s">
+      <c r="G137" s="26" t="s">
         <v>915</v>
       </c>
-      <c r="H137" s="24" t="s">
+      <c r="H137" s="25" t="s">
         <v>915</v>
       </c>
-      <c r="I137" s="26" t="s">
+      <c r="I137" s="27" t="s">
         <v>916</v>
       </c>
       <c r="J137" s="1">
@@ -15263,10 +15261,10 @@
       <c r="S137" s="8">
         <v>99.4</v>
       </c>
-      <c r="T137" s="24" t="s">
+      <c r="T137" s="25" t="s">
         <v>917</v>
       </c>
-      <c r="U137" s="24" t="s">
+      <c r="U137" s="25" t="s">
         <v>917</v>
       </c>
       <c r="W137" s="1" t="s">
@@ -15293,13 +15291,13 @@
       <c r="F138" s="1" t="s">
         <v>920</v>
       </c>
-      <c r="G138" s="25" t="s">
+      <c r="G138" s="26" t="s">
         <v>921</v>
       </c>
-      <c r="H138" s="24" t="s">
+      <c r="H138" s="25" t="s">
         <v>921</v>
       </c>
-      <c r="I138" s="26" t="s">
+      <c r="I138" s="27" t="s">
         <v>922</v>
       </c>
       <c r="J138" s="1">
@@ -15338,10 +15336,10 @@
       <c r="S138" s="8">
         <v>99.6</v>
       </c>
-      <c r="T138" s="24" t="s">
+      <c r="T138" s="25" t="s">
         <v>923</v>
       </c>
-      <c r="U138" s="24" t="s">
+      <c r="U138" s="25" t="s">
         <v>923</v>
       </c>
       <c r="W138" s="1" t="s">
@@ -15368,13 +15366,13 @@
       <c r="F139" s="1" t="s">
         <v>926</v>
       </c>
-      <c r="G139" s="25" t="s">
+      <c r="G139" s="26" t="s">
         <v>927</v>
       </c>
-      <c r="H139" s="24" t="s">
+      <c r="H139" s="25" t="s">
         <v>927</v>
       </c>
-      <c r="I139" s="26" t="s">
+      <c r="I139" s="27" t="s">
         <v>928</v>
       </c>
       <c r="J139" s="1">
@@ -15413,10 +15411,10 @@
       <c r="S139" s="8">
         <v>99.8</v>
       </c>
-      <c r="T139" s="24" t="s">
+      <c r="T139" s="25" t="s">
         <v>929</v>
       </c>
-      <c r="U139" s="24" t="s">
+      <c r="U139" s="25" t="s">
         <v>929</v>
       </c>
       <c r="W139" s="1" t="s">
@@ -15443,13 +15441,13 @@
       <c r="F140" s="1" t="s">
         <v>932</v>
       </c>
-      <c r="G140" s="25" t="s">
+      <c r="G140" s="26" t="s">
         <v>933</v>
       </c>
-      <c r="H140" s="24" t="s">
+      <c r="H140" s="25" t="s">
         <v>933</v>
       </c>
-      <c r="I140" s="26" t="s">
+      <c r="I140" s="27" t="s">
         <v>934</v>
       </c>
       <c r="J140" s="1">
@@ -15488,10 +15486,10 @@
       <c r="S140" s="8">
         <v>99.9</v>
       </c>
-      <c r="T140" s="24" t="s">
+      <c r="T140" s="25" t="s">
         <v>935</v>
       </c>
-      <c r="U140" s="24" t="s">
+      <c r="U140" s="25" t="s">
         <v>935</v>
       </c>
       <c r="W140" s="1" t="s">
@@ -15518,13 +15516,13 @@
       <c r="F141" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="G141" s="25" t="s">
+      <c r="G141" s="26" t="s">
         <v>939</v>
       </c>
-      <c r="H141" s="24" t="s">
+      <c r="H141" s="25" t="s">
         <v>939</v>
       </c>
-      <c r="I141" s="26" t="s">
+      <c r="I141" s="27" t="s">
         <v>940</v>
       </c>
       <c r="J141" s="1">
@@ -15563,10 +15561,10 @@
       <c r="S141" s="8">
         <v>99.92</v>
       </c>
-      <c r="T141" s="24" t="s">
+      <c r="T141" s="25" t="s">
         <v>941</v>
       </c>
-      <c r="U141" s="24" t="s">
+      <c r="U141" s="25" t="s">
         <v>941</v>
       </c>
       <c r="W141" s="1" t="s">
@@ -15593,13 +15591,13 @@
       <c r="F142" s="1" t="s">
         <v>944</v>
       </c>
-      <c r="G142" s="25" t="s">
+      <c r="G142" s="26" t="s">
         <v>945</v>
       </c>
-      <c r="H142" s="24" t="s">
+      <c r="H142" s="25" t="s">
         <v>945</v>
       </c>
-      <c r="I142" s="26" t="s">
+      <c r="I142" s="27" t="s">
         <v>946</v>
       </c>
       <c r="J142" s="1">
@@ -15638,10 +15636,10 @@
       <c r="S142" s="8">
         <v>99.94</v>
       </c>
-      <c r="T142" s="24" t="s">
+      <c r="T142" s="25" t="s">
         <v>947</v>
       </c>
-      <c r="U142" s="24" t="s">
+      <c r="U142" s="25" t="s">
         <v>947</v>
       </c>
       <c r="W142" s="1" t="s">
@@ -15668,13 +15666,13 @@
       <c r="F143" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="G143" s="25" t="s">
+      <c r="G143" s="26" t="s">
         <v>951</v>
       </c>
-      <c r="H143" s="24" t="s">
+      <c r="H143" s="25" t="s">
         <v>951</v>
       </c>
-      <c r="I143" s="26" t="s">
+      <c r="I143" s="27" t="s">
         <v>952</v>
       </c>
       <c r="J143" s="1">
@@ -15713,10 +15711,10 @@
       <c r="S143" s="8">
         <v>99.96</v>
       </c>
-      <c r="T143" s="24" t="s">
+      <c r="T143" s="25" t="s">
         <v>953</v>
       </c>
-      <c r="U143" s="24" t="s">
+      <c r="U143" s="25" t="s">
         <v>953</v>
       </c>
       <c r="W143" s="1" t="s">
@@ -15743,13 +15741,13 @@
       <c r="F144" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="G144" s="25" t="s">
+      <c r="G144" s="26" t="s">
         <v>957</v>
       </c>
-      <c r="H144" s="24" t="s">
+      <c r="H144" s="25" t="s">
         <v>957</v>
       </c>
-      <c r="I144" s="26" t="s">
+      <c r="I144" s="27" t="s">
         <v>958</v>
       </c>
       <c r="J144" s="1">
@@ -15788,10 +15786,10 @@
       <c r="S144" s="8">
         <v>99.98</v>
       </c>
-      <c r="T144" s="24" t="s">
+      <c r="T144" s="25" t="s">
         <v>959</v>
       </c>
-      <c r="U144" s="24" t="s">
+      <c r="U144" s="25" t="s">
         <v>959</v>
       </c>
       <c r="W144" s="1" t="s">
@@ -15863,10 +15861,10 @@
       <c r="S145" s="8">
         <v>99.99</v>
       </c>
-      <c r="T145" s="24" t="s">
+      <c r="T145" s="25" t="s">
         <v>965</v>
       </c>
-      <c r="U145" s="24" t="s">
+      <c r="U145" s="25" t="s">
         <v>965</v>
       </c>
       <c r="W145" s="1" t="s">
@@ -15881,10 +15879,10 @@
     <row r="146" s="3" customFormat="1" hidden="1" customHeight="1" spans="1:24">
       <c r="A146" s="16"/>
       <c r="B146" s="16"/>
-      <c r="C146" s="30" t="s">
+      <c r="C146" s="31" t="s">
         <v>966</v>
       </c>
-      <c r="D146" s="30" t="s">
+      <c r="D146" s="31" t="s">
         <v>967</v>
       </c>
       <c r="E146" s="3">
@@ -15937,10 +15935,10 @@
       <c r="S146" s="16">
         <v>99.99</v>
       </c>
-      <c r="T146" s="30" t="s">
+      <c r="T146" s="31" t="s">
         <v>973</v>
       </c>
-      <c r="U146" s="30" t="s">
+      <c r="U146" s="31" t="s">
         <v>973</v>
       </c>
       <c r="W146" s="3" t="s">
@@ -15953,10 +15951,10 @@
     <row r="147" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:24">
       <c r="A147" s="8"/>
       <c r="B147" s="8"/>
-      <c r="C147" s="24" t="s">
+      <c r="C147" s="25" t="s">
         <v>974</v>
       </c>
-      <c r="D147" s="24" t="s">
+      <c r="D147" s="25" t="s">
         <v>975</v>
       </c>
       <c r="E147" s="1">
@@ -16011,10 +16009,10 @@
       <c r="S147" s="8">
         <v>99.99</v>
       </c>
-      <c r="T147" s="24" t="s">
+      <c r="T147" s="25" t="s">
         <v>981</v>
       </c>
-      <c r="U147" s="24" t="s">
+      <c r="U147" s="25" t="s">
         <v>981</v>
       </c>
       <c r="W147" s="1" t="s">
@@ -16027,10 +16025,10 @@
     <row r="148" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:24">
       <c r="A148" s="8"/>
       <c r="B148" s="8"/>
-      <c r="C148" s="24" t="s">
+      <c r="C148" s="25" t="s">
         <v>982</v>
       </c>
-      <c r="D148" s="24" t="s">
+      <c r="D148" s="25" t="s">
         <v>983</v>
       </c>
       <c r="E148" s="1">
@@ -16085,10 +16083,10 @@
       <c r="S148" s="8">
         <v>99.99</v>
       </c>
-      <c r="T148" s="24" t="s">
+      <c r="T148" s="25" t="s">
         <v>989</v>
       </c>
-      <c r="U148" s="24" t="s">
+      <c r="U148" s="25" t="s">
         <v>989</v>
       </c>
       <c r="W148" s="1" t="s">
@@ -16101,10 +16099,10 @@
     <row r="149" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:24">
       <c r="A149" s="8"/>
       <c r="B149" s="8"/>
-      <c r="C149" s="24" t="s">
+      <c r="C149" s="25" t="s">
         <v>990</v>
       </c>
-      <c r="D149" s="24" t="s">
+      <c r="D149" s="25" t="s">
         <v>991</v>
       </c>
       <c r="E149" s="1">
@@ -16159,10 +16157,10 @@
       <c r="S149" s="8">
         <v>99.99</v>
       </c>
-      <c r="T149" s="24" t="s">
+      <c r="T149" s="25" t="s">
         <v>997</v>
       </c>
-      <c r="U149" s="24" t="s">
+      <c r="U149" s="25" t="s">
         <v>997</v>
       </c>
       <c r="W149" s="1" t="s">
@@ -16175,10 +16173,10 @@
     <row r="150" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:24">
       <c r="A150" s="8"/>
       <c r="B150" s="8"/>
-      <c r="C150" s="24" t="s">
+      <c r="C150" s="25" t="s">
         <v>998</v>
       </c>
-      <c r="D150" s="24" t="s">
+      <c r="D150" s="25" t="s">
         <v>999</v>
       </c>
       <c r="E150" s="1">
@@ -16233,10 +16231,10 @@
       <c r="S150" s="8">
         <v>99.99</v>
       </c>
-      <c r="T150" s="24" t="s">
+      <c r="T150" s="25" t="s">
         <v>1005</v>
       </c>
-      <c r="U150" s="24" t="s">
+      <c r="U150" s="25" t="s">
         <v>1005</v>
       </c>
       <c r="W150" s="1" t="s">
@@ -16249,10 +16247,10 @@
     <row r="151" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A151" s="8"/>
       <c r="B151" s="8"/>
-      <c r="C151" s="24" t="s">
+      <c r="C151" s="25" t="s">
         <v>1006</v>
       </c>
-      <c r="D151" s="24" t="s">
+      <c r="D151" s="25" t="s">
         <v>1007</v>
       </c>
       <c r="E151" s="1">
@@ -16306,10 +16304,10 @@
       <c r="S151" s="8">
         <v>99.99</v>
       </c>
-      <c r="T151" s="24" t="s">
+      <c r="T151" s="25" t="s">
         <v>1014</v>
       </c>
-      <c r="U151" s="24" t="s">
+      <c r="U151" s="25" t="s">
         <v>1014</v>
       </c>
       <c r="W151" s="1" t="s">
@@ -16324,10 +16322,10 @@
     <row r="152" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A152" s="8"/>
       <c r="B152" s="8"/>
-      <c r="C152" s="24" t="s">
+      <c r="C152" s="25" t="s">
         <v>1015</v>
       </c>
-      <c r="D152" s="24" t="s">
+      <c r="D152" s="25" t="s">
         <v>1016</v>
       </c>
       <c r="E152" s="1">
@@ -16381,10 +16379,10 @@
       <c r="S152" s="8">
         <v>99.99</v>
       </c>
-      <c r="T152" s="24" t="s">
+      <c r="T152" s="25" t="s">
         <v>1023</v>
       </c>
-      <c r="U152" s="24" t="s">
+      <c r="U152" s="25" t="s">
         <v>1023</v>
       </c>
       <c r="W152" s="1" t="s">
@@ -16399,10 +16397,10 @@
     <row r="153" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A153" s="8"/>
       <c r="B153" s="8"/>
-      <c r="C153" s="24" t="s">
+      <c r="C153" s="25" t="s">
         <v>1024</v>
       </c>
-      <c r="D153" s="24" t="s">
+      <c r="D153" s="25" t="s">
         <v>1025</v>
       </c>
       <c r="E153" s="1">
@@ -16456,10 +16454,10 @@
       <c r="S153" s="8">
         <v>99.99</v>
       </c>
-      <c r="T153" s="24" t="s">
+      <c r="T153" s="25" t="s">
         <v>1032</v>
       </c>
-      <c r="U153" s="24" t="s">
+      <c r="U153" s="25" t="s">
         <v>1032</v>
       </c>
       <c r="W153" s="1" t="s">
@@ -16474,10 +16472,10 @@
     <row r="154" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A154" s="8"/>
       <c r="B154" s="8"/>
-      <c r="C154" s="24" t="s">
+      <c r="C154" s="25" t="s">
         <v>1033</v>
       </c>
-      <c r="D154" s="24" t="s">
+      <c r="D154" s="25" t="s">
         <v>1034</v>
       </c>
       <c r="E154" s="1">
@@ -16531,10 +16529,10 @@
       <c r="S154" s="8">
         <v>99.99</v>
       </c>
-      <c r="T154" s="24" t="s">
+      <c r="T154" s="25" t="s">
         <v>1041</v>
       </c>
-      <c r="U154" s="24" t="s">
+      <c r="U154" s="25" t="s">
         <v>1041</v>
       </c>
       <c r="W154" s="1" t="s">
@@ -16549,10 +16547,10 @@
     <row r="155" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A155" s="8"/>
       <c r="B155" s="8"/>
-      <c r="C155" s="24" t="s">
+      <c r="C155" s="25" t="s">
         <v>1042</v>
       </c>
-      <c r="D155" s="24" t="s">
+      <c r="D155" s="25" t="s">
         <v>1043</v>
       </c>
       <c r="E155" s="1">
@@ -16606,10 +16604,10 @@
       <c r="S155" s="8">
         <v>99.99</v>
       </c>
-      <c r="T155" s="24" t="s">
+      <c r="T155" s="25" t="s">
         <v>1050</v>
       </c>
-      <c r="U155" s="24" t="s">
+      <c r="U155" s="25" t="s">
         <v>1050</v>
       </c>
       <c r="W155" s="1" t="s">
@@ -16624,10 +16622,10 @@
     <row r="156" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A156" s="8"/>
       <c r="B156" s="8"/>
-      <c r="C156" s="24" t="s">
+      <c r="C156" s="25" t="s">
         <v>1051</v>
       </c>
-      <c r="D156" s="24" t="s">
+      <c r="D156" s="25" t="s">
         <v>1052</v>
       </c>
       <c r="E156" s="1">
@@ -16681,10 +16679,10 @@
       <c r="S156" s="8">
         <v>99.99</v>
       </c>
-      <c r="T156" s="24" t="s">
+      <c r="T156" s="25" t="s">
         <v>1059</v>
       </c>
-      <c r="U156" s="24" t="s">
+      <c r="U156" s="25" t="s">
         <v>1059</v>
       </c>
       <c r="W156" s="1" t="s">
@@ -16699,10 +16697,10 @@
     <row r="157" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A157" s="8"/>
       <c r="B157" s="8"/>
-      <c r="C157" s="24" t="s">
+      <c r="C157" s="25" t="s">
         <v>1060</v>
       </c>
-      <c r="D157" s="24" t="s">
+      <c r="D157" s="25" t="s">
         <v>1061</v>
       </c>
       <c r="E157" s="1">
@@ -16756,10 +16754,10 @@
       <c r="S157" s="8">
         <v>99.99</v>
       </c>
-      <c r="T157" s="24" t="s">
+      <c r="T157" s="25" t="s">
         <v>1068</v>
       </c>
-      <c r="U157" s="24" t="s">
+      <c r="U157" s="25" t="s">
         <v>1068</v>
       </c>
       <c r="W157" s="1" t="s">
@@ -16774,10 +16772,10 @@
     <row r="158" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A158" s="8"/>
       <c r="B158" s="8"/>
-      <c r="C158" s="24" t="s">
+      <c r="C158" s="25" t="s">
         <v>1069</v>
       </c>
-      <c r="D158" s="24" t="s">
+      <c r="D158" s="25" t="s">
         <v>1070</v>
       </c>
       <c r="E158" s="1">
@@ -16831,10 +16829,10 @@
       <c r="S158" s="8">
         <v>99.99</v>
       </c>
-      <c r="T158" s="24" t="s">
+      <c r="T158" s="25" t="s">
         <v>1077</v>
       </c>
-      <c r="U158" s="24" t="s">
+      <c r="U158" s="25" t="s">
         <v>1077</v>
       </c>
       <c r="W158" s="1" t="s">
@@ -16849,10 +16847,10 @@
     <row r="159" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A159" s="8"/>
       <c r="B159" s="8"/>
-      <c r="C159" s="24" t="s">
+      <c r="C159" s="25" t="s">
         <v>1078</v>
       </c>
-      <c r="D159" s="24" t="s">
+      <c r="D159" s="25" t="s">
         <v>1079</v>
       </c>
       <c r="E159" s="1">
@@ -16906,10 +16904,10 @@
       <c r="S159" s="8">
         <v>99.99</v>
       </c>
-      <c r="T159" s="24" t="s">
+      <c r="T159" s="25" t="s">
         <v>1086</v>
       </c>
-      <c r="U159" s="24" t="s">
+      <c r="U159" s="25" t="s">
         <v>1086</v>
       </c>
       <c r="W159" s="1" t="s">
@@ -16924,10 +16922,10 @@
     <row r="160" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A160" s="8"/>
       <c r="B160" s="8"/>
-      <c r="C160" s="24" t="s">
+      <c r="C160" s="25" t="s">
         <v>1087</v>
       </c>
-      <c r="D160" s="24" t="s">
+      <c r="D160" s="25" t="s">
         <v>1088</v>
       </c>
       <c r="E160" s="1">
@@ -16981,10 +16979,10 @@
       <c r="S160" s="8">
         <v>99.99</v>
       </c>
-      <c r="T160" s="24" t="s">
+      <c r="T160" s="25" t="s">
         <v>1095</v>
       </c>
-      <c r="U160" s="24" t="s">
+      <c r="U160" s="25" t="s">
         <v>1095</v>
       </c>
       <c r="W160" s="1" t="s">
@@ -16999,10 +16997,10 @@
     <row r="161" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A161" s="8"/>
       <c r="B161" s="8"/>
-      <c r="C161" s="24" t="s">
+      <c r="C161" s="25" t="s">
         <v>1096</v>
       </c>
-      <c r="D161" s="24" t="s">
+      <c r="D161" s="25" t="s">
         <v>1097</v>
       </c>
       <c r="E161" s="1">
@@ -17056,10 +17054,10 @@
       <c r="S161" s="8">
         <v>99.99</v>
       </c>
-      <c r="T161" s="24" t="s">
+      <c r="T161" s="25" t="s">
         <v>1104</v>
       </c>
-      <c r="U161" s="24" t="s">
+      <c r="U161" s="25" t="s">
         <v>1104</v>
       </c>
       <c r="W161" s="1" t="s">
@@ -17074,10 +17072,10 @@
     <row r="162" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A162" s="8"/>
       <c r="B162" s="8"/>
-      <c r="C162" s="24" t="s">
+      <c r="C162" s="25" t="s">
         <v>1105</v>
       </c>
-      <c r="D162" s="24" t="s">
+      <c r="D162" s="25" t="s">
         <v>1106</v>
       </c>
       <c r="E162" s="1">
@@ -17131,10 +17129,10 @@
       <c r="S162" s="8">
         <v>99.99</v>
       </c>
-      <c r="T162" s="24" t="s">
+      <c r="T162" s="25" t="s">
         <v>1113</v>
       </c>
-      <c r="U162" s="24" t="s">
+      <c r="U162" s="25" t="s">
         <v>1113</v>
       </c>
       <c r="W162" s="1" t="s">
@@ -17149,10 +17147,10 @@
     <row r="163" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A163" s="8"/>
       <c r="B163" s="8"/>
-      <c r="C163" s="24" t="s">
+      <c r="C163" s="25" t="s">
         <v>1114</v>
       </c>
-      <c r="D163" s="24" t="s">
+      <c r="D163" s="25" t="s">
         <v>1115</v>
       </c>
       <c r="E163" s="1">
@@ -17167,7 +17165,7 @@
       <c r="H163" s="1" t="s">
         <v>1118</v>
       </c>
-      <c r="I163" s="31" t="s">
+      <c r="I163" s="32" t="s">
         <v>1119</v>
       </c>
       <c r="J163" s="1" t="s">
@@ -17206,10 +17204,10 @@
       <c r="S163" s="8">
         <v>99.99</v>
       </c>
-      <c r="T163" s="24" t="s">
+      <c r="T163" s="25" t="s">
         <v>1122</v>
       </c>
-      <c r="U163" s="24" t="s">
+      <c r="U163" s="25" t="s">
         <v>1122</v>
       </c>
       <c r="W163" s="1" t="s">
@@ -17224,10 +17222,10 @@
     <row r="164" s="4" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A164" s="18"/>
       <c r="B164" s="18"/>
-      <c r="C164" s="32" t="s">
+      <c r="C164" s="33" t="s">
         <v>1123</v>
       </c>
-      <c r="D164" s="32" t="s">
+      <c r="D164" s="33" t="s">
         <v>1124</v>
       </c>
       <c r="E164" s="4">
@@ -17242,7 +17240,7 @@
       <c r="H164" s="4" t="s">
         <v>1127</v>
       </c>
-      <c r="I164" s="33" t="s">
+      <c r="I164" s="34" t="s">
         <v>1128</v>
       </c>
       <c r="J164" s="4" t="s">
@@ -17281,10 +17279,10 @@
       <c r="S164" s="18">
         <v>99.99</v>
       </c>
-      <c r="T164" s="32" t="s">
+      <c r="T164" s="33" t="s">
         <v>1131</v>
       </c>
-      <c r="U164" s="32" t="s">
+      <c r="U164" s="33" t="s">
         <v>1131</v>
       </c>
       <c r="W164" s="4" t="s">
@@ -17299,10 +17297,10 @@
     <row r="165" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A165" s="8"/>
       <c r="B165" s="8"/>
-      <c r="C165" s="24" t="s">
+      <c r="C165" s="25" t="s">
         <v>1132</v>
       </c>
-      <c r="D165" s="24" t="s">
+      <c r="D165" s="25" t="s">
         <v>1133</v>
       </c>
       <c r="E165" s="1">
@@ -17311,19 +17309,19 @@
       <c r="F165" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="G165" s="31" t="s">
+      <c r="G165" s="32" t="s">
         <v>1135</v>
       </c>
-      <c r="H165" s="31" t="s">
+      <c r="H165" s="32" t="s">
         <v>1136</v>
       </c>
-      <c r="I165" s="31" t="s">
+      <c r="I165" s="32" t="s">
         <v>1137</v>
       </c>
-      <c r="J165" s="31" t="s">
+      <c r="J165" s="32" t="s">
         <v>1138</v>
       </c>
-      <c r="K165" s="31" t="s">
+      <c r="K165" s="32" t="s">
         <v>1139</v>
       </c>
       <c r="L165" s="1">
@@ -17356,10 +17354,10 @@
       <c r="S165" s="8">
         <v>99.99</v>
       </c>
-      <c r="T165" s="24" t="s">
+      <c r="T165" s="25" t="s">
         <v>1140</v>
       </c>
-      <c r="U165" s="24" t="s">
+      <c r="U165" s="25" t="s">
         <v>1140</v>
       </c>
       <c r="W165" s="1" t="s">
@@ -17372,10 +17370,10 @@
       <c r="Z165" s="8"/>
     </row>
     <row r="166" hidden="1" customHeight="1" spans="3:24">
-      <c r="C166" s="24" t="s">
+      <c r="C166" s="25" t="s">
         <v>1141</v>
       </c>
-      <c r="D166" s="24" t="s">
+      <c r="D166" s="25" t="s">
         <v>1142</v>
       </c>
       <c r="E166" s="1">
@@ -17384,19 +17382,19 @@
       <c r="F166" s="1" t="s">
         <v>1143</v>
       </c>
-      <c r="G166" s="31" t="s">
+      <c r="G166" s="32" t="s">
         <v>1144</v>
       </c>
-      <c r="H166" s="31" t="s">
+      <c r="H166" s="32" t="s">
         <v>1145</v>
       </c>
-      <c r="I166" s="31" t="s">
+      <c r="I166" s="32" t="s">
         <v>1146</v>
       </c>
-      <c r="J166" s="31" t="s">
+      <c r="J166" s="32" t="s">
         <v>1147</v>
       </c>
-      <c r="K166" s="31" t="s">
+      <c r="K166" s="32" t="s">
         <v>1148</v>
       </c>
       <c r="L166" s="1">
@@ -17429,10 +17427,10 @@
       <c r="S166" s="8">
         <v>99.99</v>
       </c>
-      <c r="T166" s="24" t="s">
+      <c r="T166" s="25" t="s">
         <v>1149</v>
       </c>
-      <c r="U166" s="24" t="s">
+      <c r="U166" s="25" t="s">
         <v>1149</v>
       </c>
       <c r="W166" s="1" t="s">
@@ -17443,10 +17441,10 @@
       </c>
     </row>
     <row r="167" hidden="1" customHeight="1" spans="3:24">
-      <c r="C167" s="24" t="s">
+      <c r="C167" s="25" t="s">
         <v>1150</v>
       </c>
-      <c r="D167" s="24" t="s">
+      <c r="D167" s="25" t="s">
         <v>1151</v>
       </c>
       <c r="E167" s="1">
@@ -17455,19 +17453,19 @@
       <c r="F167" s="1" t="s">
         <v>1152</v>
       </c>
-      <c r="G167" s="31" t="s">
+      <c r="G167" s="32" t="s">
         <v>1153</v>
       </c>
-      <c r="H167" s="31" t="s">
+      <c r="H167" s="32" t="s">
         <v>1154</v>
       </c>
-      <c r="I167" s="31" t="s">
+      <c r="I167" s="32" t="s">
         <v>1155</v>
       </c>
-      <c r="J167" s="31" t="s">
+      <c r="J167" s="32" t="s">
         <v>1156</v>
       </c>
-      <c r="K167" s="31" t="s">
+      <c r="K167" s="32" t="s">
         <v>1157</v>
       </c>
       <c r="L167" s="1">
@@ -17500,10 +17498,10 @@
       <c r="S167" s="8">
         <v>99.99</v>
       </c>
-      <c r="T167" s="24" t="s">
+      <c r="T167" s="25" t="s">
         <v>1158</v>
       </c>
-      <c r="U167" s="24" t="s">
+      <c r="U167" s="25" t="s">
         <v>1158</v>
       </c>
       <c r="W167" s="1" t="s">
@@ -17514,10 +17512,10 @@
       </c>
     </row>
     <row r="168" hidden="1" customHeight="1" spans="3:24">
-      <c r="C168" s="24" t="s">
+      <c r="C168" s="25" t="s">
         <v>1159</v>
       </c>
-      <c r="D168" s="24" t="s">
+      <c r="D168" s="25" t="s">
         <v>1160</v>
       </c>
       <c r="E168" s="1">
@@ -17526,19 +17524,19 @@
       <c r="F168" s="1" t="s">
         <v>1161</v>
       </c>
-      <c r="G168" s="31" t="s">
+      <c r="G168" s="32" t="s">
         <v>1162</v>
       </c>
-      <c r="H168" s="31" t="s">
+      <c r="H168" s="32" t="s">
         <v>1163</v>
       </c>
-      <c r="I168" s="31" t="s">
+      <c r="I168" s="32" t="s">
         <v>1164</v>
       </c>
-      <c r="J168" s="31" t="s">
+      <c r="J168" s="32" t="s">
         <v>1165</v>
       </c>
-      <c r="K168" s="31" t="s">
+      <c r="K168" s="32" t="s">
         <v>1166</v>
       </c>
       <c r="L168" s="1">
@@ -17571,10 +17569,10 @@
       <c r="S168" s="8">
         <v>99.99</v>
       </c>
-      <c r="T168" s="24" t="s">
+      <c r="T168" s="25" t="s">
         <v>1167</v>
       </c>
-      <c r="U168" s="24" t="s">
+      <c r="U168" s="25" t="s">
         <v>1167</v>
       </c>
       <c r="W168" s="1" t="s">
@@ -17585,10 +17583,10 @@
       </c>
     </row>
     <row r="169" hidden="1" customHeight="1" spans="3:24">
-      <c r="C169" s="24" t="s">
+      <c r="C169" s="25" t="s">
         <v>1168</v>
       </c>
-      <c r="D169" s="24" t="s">
+      <c r="D169" s="25" t="s">
         <v>1169</v>
       </c>
       <c r="E169" s="1">
@@ -17597,19 +17595,19 @@
       <c r="F169" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="G169" s="31" t="s">
+      <c r="G169" s="32" t="s">
         <v>1171</v>
       </c>
-      <c r="H169" s="31" t="s">
+      <c r="H169" s="32" t="s">
         <v>1172</v>
       </c>
-      <c r="I169" s="31" t="s">
+      <c r="I169" s="32" t="s">
         <v>1173</v>
       </c>
-      <c r="J169" s="31" t="s">
+      <c r="J169" s="32" t="s">
         <v>1174</v>
       </c>
-      <c r="K169" s="31" t="s">
+      <c r="K169" s="32" t="s">
         <v>1175</v>
       </c>
       <c r="L169" s="1">
@@ -17642,10 +17640,10 @@
       <c r="S169" s="8">
         <v>99.99</v>
       </c>
-      <c r="T169" s="24" t="s">
+      <c r="T169" s="25" t="s">
         <v>1176</v>
       </c>
-      <c r="U169" s="24" t="s">
+      <c r="U169" s="25" t="s">
         <v>1176</v>
       </c>
       <c r="W169" s="1" t="s">
@@ -17656,10 +17654,10 @@
       </c>
     </row>
     <row r="170" hidden="1" customHeight="1" spans="3:24">
-      <c r="C170" s="24" t="s">
+      <c r="C170" s="25" t="s">
         <v>1177</v>
       </c>
-      <c r="D170" s="24" t="s">
+      <c r="D170" s="25" t="s">
         <v>1178</v>
       </c>
       <c r="E170" s="1">
@@ -17668,19 +17666,19 @@
       <c r="F170" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="G170" s="31" t="s">
+      <c r="G170" s="32" t="s">
         <v>1179</v>
       </c>
-      <c r="H170" s="31" t="s">
+      <c r="H170" s="32" t="s">
         <v>1180</v>
       </c>
-      <c r="I170" s="31" t="s">
+      <c r="I170" s="32" t="s">
         <v>1181</v>
       </c>
-      <c r="J170" s="31" t="s">
+      <c r="J170" s="32" t="s">
         <v>1182</v>
       </c>
-      <c r="K170" s="31" t="s">
+      <c r="K170" s="32" t="s">
         <v>1183</v>
       </c>
       <c r="L170" s="1">
@@ -17713,10 +17711,10 @@
       <c r="S170" s="8">
         <v>99.99</v>
       </c>
-      <c r="T170" s="24" t="s">
+      <c r="T170" s="25" t="s">
         <v>1184</v>
       </c>
-      <c r="U170" s="24" t="s">
+      <c r="U170" s="25" t="s">
         <v>1184</v>
       </c>
       <c r="W170" s="1" t="s">
@@ -17729,10 +17727,10 @@
     <row r="171" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A171" s="8"/>
       <c r="B171" s="8"/>
-      <c r="C171" s="24" t="s">
+      <c r="C171" s="25" t="s">
         <v>1185</v>
       </c>
-      <c r="D171" s="24" t="s">
+      <c r="D171" s="25" t="s">
         <v>1186</v>
       </c>
       <c r="E171" s="1">
@@ -17741,19 +17739,19 @@
       <c r="F171" s="1" t="s">
         <v>1187</v>
       </c>
-      <c r="G171" s="31" t="s">
+      <c r="G171" s="32" t="s">
         <v>1188</v>
       </c>
-      <c r="H171" s="31" t="s">
+      <c r="H171" s="32" t="s">
         <v>1189</v>
       </c>
-      <c r="I171" s="31" t="s">
+      <c r="I171" s="32" t="s">
         <v>1190</v>
       </c>
-      <c r="J171" s="31" t="s">
+      <c r="J171" s="32" t="s">
         <v>1191</v>
       </c>
-      <c r="K171" s="31" t="s">
+      <c r="K171" s="32" t="s">
         <v>1192</v>
       </c>
       <c r="L171" s="1">
@@ -17786,10 +17784,10 @@
       <c r="S171" s="8">
         <v>99.99</v>
       </c>
-      <c r="T171" s="24" t="s">
+      <c r="T171" s="25" t="s">
         <v>1193</v>
       </c>
-      <c r="U171" s="24" t="s">
+      <c r="U171" s="25" t="s">
         <v>1193</v>
       </c>
       <c r="W171" s="1" t="s">
@@ -17804,10 +17802,10 @@
     <row r="172" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A172" s="8"/>
       <c r="B172" s="8"/>
-      <c r="C172" s="24" t="s">
+      <c r="C172" s="25" t="s">
         <v>1194</v>
       </c>
-      <c r="D172" s="24" t="s">
+      <c r="D172" s="25" t="s">
         <v>1195</v>
       </c>
       <c r="E172" s="1">
@@ -17816,19 +17814,19 @@
       <c r="F172" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="G172" s="31" t="s">
+      <c r="G172" s="32" t="s">
         <v>1197</v>
       </c>
-      <c r="H172" s="31" t="s">
+      <c r="H172" s="32" t="s">
         <v>1198</v>
       </c>
-      <c r="I172" s="31" t="s">
+      <c r="I172" s="32" t="s">
         <v>1199</v>
       </c>
-      <c r="J172" s="31" t="s">
+      <c r="J172" s="32" t="s">
         <v>1200</v>
       </c>
-      <c r="K172" s="31" t="s">
+      <c r="K172" s="32" t="s">
         <v>1201</v>
       </c>
       <c r="L172" s="1">
@@ -17861,10 +17859,10 @@
       <c r="S172" s="8">
         <v>99.99</v>
       </c>
-      <c r="T172" s="24" t="s">
+      <c r="T172" s="25" t="s">
         <v>1202</v>
       </c>
-      <c r="U172" s="24" t="s">
+      <c r="U172" s="25" t="s">
         <v>1202</v>
       </c>
       <c r="W172" s="1" t="s">
@@ -17879,10 +17877,10 @@
     <row r="173" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A173" s="8"/>
       <c r="B173" s="8"/>
-      <c r="C173" s="24" t="s">
+      <c r="C173" s="25" t="s">
         <v>1203</v>
       </c>
-      <c r="D173" s="24" t="s">
+      <c r="D173" s="25" t="s">
         <v>1204</v>
       </c>
       <c r="E173" s="1">
@@ -17891,19 +17889,19 @@
       <c r="F173" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="G173" s="31" t="s">
+      <c r="G173" s="32" t="s">
         <v>1206</v>
       </c>
-      <c r="H173" s="31" t="s">
+      <c r="H173" s="32" t="s">
         <v>1207</v>
       </c>
-      <c r="I173" s="31" t="s">
+      <c r="I173" s="32" t="s">
         <v>1208</v>
       </c>
-      <c r="J173" s="31" t="s">
+      <c r="J173" s="32" t="s">
         <v>1209</v>
       </c>
-      <c r="K173" s="31" t="s">
+      <c r="K173" s="32" t="s">
         <v>1210</v>
       </c>
       <c r="L173" s="1">
@@ -17936,10 +17934,10 @@
       <c r="S173" s="8">
         <v>99.99</v>
       </c>
-      <c r="T173" s="24" t="s">
+      <c r="T173" s="25" t="s">
         <v>1211</v>
       </c>
-      <c r="U173" s="24" t="s">
+      <c r="U173" s="25" t="s">
         <v>1211</v>
       </c>
       <c r="W173" s="1" t="s">
@@ -17954,10 +17952,10 @@
     <row r="174" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:26">
       <c r="A174" s="8"/>
       <c r="B174" s="8"/>
-      <c r="C174" s="24" t="s">
+      <c r="C174" s="25" t="s">
         <v>1212</v>
       </c>
-      <c r="D174" s="24" t="s">
+      <c r="D174" s="25" t="s">
         <v>1213</v>
       </c>
       <c r="E174" s="1">
@@ -17966,19 +17964,19 @@
       <c r="F174" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="G174" s="31" t="s">
+      <c r="G174" s="32" t="s">
         <v>1215</v>
       </c>
-      <c r="H174" s="31" t="s">
+      <c r="H174" s="32" t="s">
         <v>1216</v>
       </c>
-      <c r="I174" s="31" t="s">
+      <c r="I174" s="32" t="s">
         <v>1217</v>
       </c>
-      <c r="J174" s="31" t="s">
+      <c r="J174" s="32" t="s">
         <v>1218</v>
       </c>
-      <c r="K174" s="31" t="s">
+      <c r="K174" s="32" t="s">
         <v>1219</v>
       </c>
       <c r="L174" s="1">
@@ -18011,10 +18009,10 @@
       <c r="S174" s="8">
         <v>99.99</v>
       </c>
-      <c r="T174" s="24" t="s">
+      <c r="T174" s="25" t="s">
         <v>1220</v>
       </c>
-      <c r="U174" s="24" t="s">
+      <c r="U174" s="25" t="s">
         <v>1220</v>
       </c>
       <c r="W174" s="1" t="s">
@@ -18029,10 +18027,10 @@
     <row r="175" s="1" customFormat="1" customHeight="1" spans="1:26">
       <c r="A175" s="8"/>
       <c r="B175" s="8"/>
-      <c r="C175" s="24" t="s">
+      <c r="C175" s="25" t="s">
         <v>1221</v>
       </c>
-      <c r="D175" s="24" t="s">
+      <c r="D175" s="25" t="s">
         <v>1222</v>
       </c>
       <c r="E175" s="1">
@@ -18041,19 +18039,19 @@
       <c r="F175" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="G175" s="31" t="s">
+      <c r="G175" s="32" t="s">
         <v>1224</v>
       </c>
-      <c r="H175" s="31" t="s">
+      <c r="H175" s="32" t="s">
         <v>1225</v>
       </c>
-      <c r="I175" s="31" t="s">
+      <c r="I175" s="32" t="s">
         <v>1226</v>
       </c>
-      <c r="J175" s="31" t="s">
+      <c r="J175" s="32" t="s">
         <v>1227</v>
       </c>
-      <c r="K175" s="31" t="s">
+      <c r="K175" s="32" t="s">
         <v>1228</v>
       </c>
       <c r="L175" s="1">
@@ -18086,10 +18084,10 @@
       <c r="S175" s="8">
         <v>99.99</v>
       </c>
-      <c r="T175" s="24" t="s">
+      <c r="T175" s="25" t="s">
         <v>1229</v>
       </c>
-      <c r="U175" s="24" t="s">
+      <c r="U175" s="25" t="s">
         <v>1229</v>
       </c>
       <c r="W175" s="1" t="s">
@@ -18104,10 +18102,10 @@
     <row r="176" s="1" customFormat="1" customHeight="1" spans="1:26">
       <c r="A176" s="8"/>
       <c r="B176" s="8"/>
-      <c r="C176" s="24" t="s">
+      <c r="C176" s="25" t="s">
         <v>1230</v>
       </c>
-      <c r="D176" s="24" t="s">
+      <c r="D176" s="25" t="s">
         <v>1231</v>
       </c>
       <c r="E176" s="1">
@@ -18116,19 +18114,19 @@
       <c r="F176" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="G176" s="31" t="s">
+      <c r="G176" s="32" t="s">
         <v>1233</v>
       </c>
-      <c r="H176" s="31" t="s">
+      <c r="H176" s="32" t="s">
         <v>1234</v>
       </c>
-      <c r="I176" s="31" t="s">
+      <c r="I176" s="32" t="s">
         <v>1235</v>
       </c>
-      <c r="J176" s="31" t="s">
+      <c r="J176" s="32" t="s">
         <v>1236</v>
       </c>
-      <c r="K176" s="31" t="s">
+      <c r="K176" s="32" t="s">
         <v>1237</v>
       </c>
       <c r="L176" s="1">
@@ -18155,16 +18153,16 @@
         <v>211</v>
       </c>
       <c r="R176" s="8">
-        <f t="shared" ref="R176:R180" si="65">R175+8</f>
+        <f t="shared" ref="R176:R185" si="65">R175+8</f>
         <v>304</v>
       </c>
       <c r="S176" s="8">
         <v>99.99</v>
       </c>
-      <c r="T176" s="24" t="s">
+      <c r="T176" s="25" t="s">
         <v>1238</v>
       </c>
-      <c r="U176" s="24" t="s">
+      <c r="U176" s="25" t="s">
         <v>1238</v>
       </c>
       <c r="W176" s="1" t="s">
@@ -18179,10 +18177,10 @@
     <row r="177" s="1" customFormat="1" customHeight="1" spans="1:26">
       <c r="A177" s="8"/>
       <c r="B177" s="8"/>
-      <c r="C177" s="24" t="s">
+      <c r="C177" s="25" t="s">
         <v>1239</v>
       </c>
-      <c r="D177" s="24" t="s">
+      <c r="D177" s="25" t="s">
         <v>1240</v>
       </c>
       <c r="E177" s="1">
@@ -18191,19 +18189,19 @@
       <c r="F177" s="1" t="s">
         <v>1241</v>
       </c>
-      <c r="G177" s="31" t="s">
+      <c r="G177" s="32" t="s">
         <v>1242</v>
       </c>
-      <c r="H177" s="31" t="s">
+      <c r="H177" s="32" t="s">
         <v>1243</v>
       </c>
-      <c r="I177" s="31" t="s">
+      <c r="I177" s="32" t="s">
         <v>1244</v>
       </c>
-      <c r="J177" s="31" t="s">
+      <c r="J177" s="32" t="s">
         <v>1245</v>
       </c>
-      <c r="K177" s="31" t="s">
+      <c r="K177" s="32" t="s">
         <v>1246</v>
       </c>
       <c r="L177" s="1">
@@ -18236,10 +18234,10 @@
       <c r="S177" s="8">
         <v>99.99</v>
       </c>
-      <c r="T177" s="24" t="s">
+      <c r="T177" s="25" t="s">
         <v>1247</v>
       </c>
-      <c r="U177" s="24" t="s">
+      <c r="U177" s="25" t="s">
         <v>1247</v>
       </c>
       <c r="W177" s="1" t="s">
@@ -18254,10 +18252,10 @@
     <row r="178" s="1" customFormat="1" customHeight="1" spans="1:26">
       <c r="A178" s="8"/>
       <c r="B178" s="8"/>
-      <c r="C178" s="24" t="s">
+      <c r="C178" s="25" t="s">
         <v>1248</v>
       </c>
-      <c r="D178" s="24" t="s">
+      <c r="D178" s="25" t="s">
         <v>1249</v>
       </c>
       <c r="E178" s="1">
@@ -18266,19 +18264,19 @@
       <c r="F178" s="1" t="s">
         <v>1250</v>
       </c>
-      <c r="G178" s="31" t="s">
+      <c r="G178" s="32" t="s">
         <v>1251</v>
       </c>
-      <c r="H178" s="31" t="s">
+      <c r="H178" s="32" t="s">
         <v>1252</v>
       </c>
-      <c r="I178" s="31" t="s">
+      <c r="I178" s="32" t="s">
         <v>1253</v>
       </c>
-      <c r="J178" s="31" t="s">
+      <c r="J178" s="32" t="s">
         <v>1254</v>
       </c>
-      <c r="K178" s="31" t="s">
+      <c r="K178" s="32" t="s">
         <v>1255</v>
       </c>
       <c r="L178" s="1">
@@ -18311,10 +18309,10 @@
       <c r="S178" s="8">
         <v>99.99</v>
       </c>
-      <c r="T178" s="24" t="s">
+      <c r="T178" s="25" t="s">
         <v>1256</v>
       </c>
-      <c r="U178" s="24" t="s">
+      <c r="U178" s="25" t="s">
         <v>1256</v>
       </c>
       <c r="W178" s="1" t="s">
@@ -18329,10 +18327,10 @@
     <row r="179" s="1" customFormat="1" customHeight="1" spans="1:26">
       <c r="A179" s="8"/>
       <c r="B179" s="8"/>
-      <c r="C179" s="24" t="s">
+      <c r="C179" s="25" t="s">
         <v>1257</v>
       </c>
-      <c r="D179" s="24" t="s">
+      <c r="D179" s="25" t="s">
         <v>1258</v>
       </c>
       <c r="E179" s="1">
@@ -18341,19 +18339,19 @@
       <c r="F179" s="1" t="s">
         <v>1259</v>
       </c>
-      <c r="G179" s="31" t="s">
+      <c r="G179" s="32" t="s">
         <v>1260</v>
       </c>
-      <c r="H179" s="31" t="s">
+      <c r="H179" s="32" t="s">
         <v>1261</v>
       </c>
-      <c r="I179" s="31" t="s">
+      <c r="I179" s="32" t="s">
         <v>1262</v>
       </c>
-      <c r="J179" s="31" t="s">
+      <c r="J179" s="32" t="s">
         <v>1263</v>
       </c>
-      <c r="K179" s="31" t="s">
+      <c r="K179" s="32" t="s">
         <v>1264</v>
       </c>
       <c r="L179" s="1">
@@ -18386,10 +18384,10 @@
       <c r="S179" s="8">
         <v>99.99</v>
       </c>
-      <c r="T179" s="24" t="s">
+      <c r="T179" s="25" t="s">
         <v>1265</v>
       </c>
-      <c r="U179" s="24" t="s">
+      <c r="U179" s="25" t="s">
         <v>1265</v>
       </c>
       <c r="W179" s="1" t="s">
@@ -18404,10 +18402,10 @@
     <row r="180" s="1" customFormat="1" customHeight="1" spans="1:26">
       <c r="A180" s="8"/>
       <c r="B180" s="8"/>
-      <c r="C180" s="24" t="s">
+      <c r="C180" s="25" t="s">
         <v>1266</v>
       </c>
-      <c r="D180" s="24" t="s">
+      <c r="D180" s="25" t="s">
         <v>1267</v>
       </c>
       <c r="E180" s="1">
@@ -18416,19 +18414,19 @@
       <c r="F180" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="G180" s="31" t="s">
+      <c r="G180" s="32" t="s">
         <v>1269</v>
       </c>
-      <c r="H180" s="31" t="s">
+      <c r="H180" s="32" t="s">
         <v>1270</v>
       </c>
-      <c r="I180" s="31" t="s">
+      <c r="I180" s="32" t="s">
         <v>1271</v>
       </c>
-      <c r="J180" s="31" t="s">
+      <c r="J180" s="32" t="s">
         <v>1272</v>
       </c>
-      <c r="K180" s="31" t="s">
+      <c r="K180" s="32" t="s">
         <v>1273</v>
       </c>
       <c r="L180" s="1">
@@ -18461,10 +18459,10 @@
       <c r="S180" s="8">
         <v>99.99</v>
       </c>
-      <c r="T180" s="24" t="s">
+      <c r="T180" s="25" t="s">
         <v>1274</v>
       </c>
-      <c r="U180" s="24" t="s">
+      <c r="U180" s="25" t="s">
         <v>1274</v>
       </c>
       <c r="W180" s="1" t="s">
@@ -18479,10 +18477,10 @@
     <row r="181" s="3" customFormat="1" customHeight="1" spans="1:24">
       <c r="A181" s="16"/>
       <c r="B181" s="16"/>
-      <c r="C181" s="30" t="s">
+      <c r="C181" s="31" t="s">
         <v>1275</v>
       </c>
-      <c r="D181" s="30" t="s">
+      <c r="D181" s="31" t="s">
         <v>1276</v>
       </c>
       <c r="E181" s="3">
@@ -18491,19 +18489,19 @@
       <c r="F181" s="3" t="s">
         <v>1277</v>
       </c>
-      <c r="G181" s="34" t="s">
+      <c r="G181" s="35" t="s">
         <v>1278</v>
       </c>
-      <c r="H181" s="34" t="s">
+      <c r="H181" s="35" t="s">
         <v>1279</v>
       </c>
-      <c r="I181" s="34" t="s">
+      <c r="I181" s="35" t="s">
         <v>1280</v>
       </c>
-      <c r="J181" s="34" t="s">
+      <c r="J181" s="35" t="s">
         <v>1281</v>
       </c>
-      <c r="K181" s="34" t="s">
+      <c r="K181" s="35" t="s">
         <v>1282</v>
       </c>
       <c r="L181" s="3">
@@ -18522,19 +18520,20 @@
         <v>100</v>
       </c>
       <c r="Q181" s="16">
-        <f t="shared" ref="Q181:Q195" si="66">Q180+3</f>
-        <v>242</v>
+        <f t="shared" ref="Q181:Q185" si="66">Q180+9</f>
+        <v>248</v>
       </c>
       <c r="R181" s="16">
-        <v>150</v>
+        <f t="shared" ref="R181:R185" si="67">R180+10</f>
+        <v>346</v>
       </c>
       <c r="S181" s="16">
         <v>99.99</v>
       </c>
-      <c r="T181" s="30" t="s">
+      <c r="T181" s="31" t="s">
         <v>1283</v>
       </c>
-      <c r="U181" s="30" t="s">
+      <c r="U181" s="31" t="s">
         <v>1283</v>
       </c>
       <c r="W181" s="3" t="s">
@@ -18547,10 +18546,10 @@
     <row r="182" s="5" customFormat="1" customHeight="1" spans="1:24">
       <c r="A182" s="12"/>
       <c r="B182" s="12"/>
-      <c r="C182" s="35" t="s">
+      <c r="C182" s="36" t="s">
         <v>1284</v>
       </c>
-      <c r="D182" s="35" t="s">
+      <c r="D182" s="36" t="s">
         <v>1285</v>
       </c>
       <c r="E182" s="5">
@@ -18559,56 +18558,56 @@
       <c r="F182" s="5" t="s">
         <v>1286</v>
       </c>
-      <c r="G182" s="31" t="s">
+      <c r="G182" s="32" t="s">
         <v>1287</v>
       </c>
-      <c r="H182" s="31" t="s">
+      <c r="H182" s="32" t="s">
         <v>1288</v>
       </c>
-      <c r="I182" s="31" t="s">
+      <c r="I182" s="32" t="s">
         <v>1289</v>
       </c>
-      <c r="J182" s="31" t="s">
+      <c r="J182" s="32" t="s">
         <v>1290</v>
       </c>
-      <c r="K182" s="31" t="s">
+      <c r="K182" s="32" t="s">
         <v>1291</v>
       </c>
       <c r="L182" s="5">
-        <f t="shared" si="50"/>
-        <v>43600</v>
+        <f t="shared" ref="L182:L185" si="68">L181+1000</f>
+        <v>44000</v>
       </c>
       <c r="M182" s="5">
-        <f t="shared" si="51"/>
-        <v>43600</v>
+        <f t="shared" ref="M182:M185" si="69">M181+1000</f>
+        <v>44000</v>
       </c>
       <c r="N182" s="5">
-        <f t="shared" ref="N181:N200" si="67">N181+250</f>
-        <v>22250</v>
+        <f t="shared" ref="N182:N185" si="70">N181+500</f>
+        <v>22500</v>
       </c>
       <c r="O182" s="5">
-        <f t="shared" ref="O181:O200" si="68">O181+250</f>
-        <v>22250</v>
+        <f t="shared" ref="O182:O185" si="71">O181+500</f>
+        <v>22500</v>
       </c>
       <c r="P182" s="5">
-        <f t="shared" ref="P182:P215" si="69">P181+5</f>
+        <f t="shared" ref="P182:P215" si="72">P181+5</f>
         <v>105</v>
       </c>
-      <c r="Q182" s="12">
+      <c r="Q182" s="24">
         <f t="shared" si="66"/>
-        <v>245</v>
-      </c>
-      <c r="R182" s="12">
-        <f t="shared" ref="R182:R195" si="70">R181+4</f>
-        <v>154</v>
+        <v>257</v>
+      </c>
+      <c r="R182" s="8">
+        <f t="shared" si="67"/>
+        <v>356</v>
       </c>
       <c r="S182" s="12">
         <v>99.99</v>
       </c>
-      <c r="T182" s="35" t="s">
+      <c r="T182" s="36" t="s">
         <v>1292</v>
       </c>
-      <c r="U182" s="35" t="s">
+      <c r="U182" s="36" t="s">
         <v>1292</v>
       </c>
       <c r="W182" s="5" t="s">
@@ -18621,10 +18620,10 @@
     <row r="183" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A183" s="8"/>
       <c r="B183" s="8"/>
-      <c r="C183" s="24" t="s">
+      <c r="C183" s="25" t="s">
         <v>1293</v>
       </c>
-      <c r="D183" s="24" t="s">
+      <c r="D183" s="25" t="s">
         <v>1294</v>
       </c>
       <c r="E183" s="1">
@@ -18633,56 +18632,56 @@
       <c r="F183" s="1" t="s">
         <v>1295</v>
       </c>
-      <c r="G183" s="31" t="s">
+      <c r="G183" s="32" t="s">
         <v>1296</v>
       </c>
-      <c r="H183" s="31" t="s">
+      <c r="H183" s="32" t="s">
         <v>1297</v>
       </c>
-      <c r="I183" s="31" t="s">
+      <c r="I183" s="32" t="s">
         <v>1298</v>
       </c>
-      <c r="J183" s="31" t="s">
+      <c r="J183" s="32" t="s">
         <v>1299</v>
       </c>
-      <c r="K183" s="31" t="s">
+      <c r="K183" s="32" t="s">
         <v>1300</v>
       </c>
-      <c r="L183" s="1">
-        <f t="shared" si="50"/>
-        <v>44200</v>
-      </c>
-      <c r="M183" s="1">
-        <f t="shared" si="51"/>
-        <v>44200</v>
-      </c>
-      <c r="N183" s="1">
+      <c r="L183" s="5">
+        <f t="shared" si="68"/>
+        <v>45000</v>
+      </c>
+      <c r="M183" s="5">
+        <f t="shared" si="69"/>
+        <v>45000</v>
+      </c>
+      <c r="N183" s="5">
+        <f t="shared" si="70"/>
+        <v>23000</v>
+      </c>
+      <c r="O183" s="5">
+        <f t="shared" si="71"/>
+        <v>23000</v>
+      </c>
+      <c r="P183" s="1">
+        <f t="shared" si="72"/>
+        <v>110</v>
+      </c>
+      <c r="Q183" s="24">
+        <f t="shared" si="66"/>
+        <v>266</v>
+      </c>
+      <c r="R183" s="8">
         <f t="shared" si="67"/>
-        <v>22500</v>
-      </c>
-      <c r="O183" s="1">
-        <f t="shared" si="68"/>
-        <v>22500</v>
-      </c>
-      <c r="P183" s="1">
-        <f t="shared" si="69"/>
-        <v>110</v>
-      </c>
-      <c r="Q183" s="8">
-        <f t="shared" si="66"/>
-        <v>248</v>
-      </c>
-      <c r="R183" s="8">
-        <f t="shared" si="70"/>
-        <v>158</v>
+        <v>366</v>
       </c>
       <c r="S183" s="8">
         <v>99.99</v>
       </c>
-      <c r="T183" s="35" t="s">
+      <c r="T183" s="36" t="s">
         <v>512</v>
       </c>
-      <c r="U183" s="35" t="s">
+      <c r="U183" s="36" t="s">
         <v>512</v>
       </c>
       <c r="W183" s="1" t="s">
@@ -18695,10 +18694,10 @@
     <row r="184" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A184" s="8"/>
       <c r="B184" s="8"/>
-      <c r="C184" s="24" t="s">
+      <c r="C184" s="25" t="s">
         <v>1301</v>
       </c>
-      <c r="D184" s="24" t="s">
+      <c r="D184" s="25" t="s">
         <v>1302</v>
       </c>
       <c r="E184" s="1">
@@ -18707,57 +18706,57 @@
       <c r="F184" s="1" t="s">
         <v>1303</v>
       </c>
-      <c r="G184" s="31" t="s">
+      <c r="G184" s="32" t="s">
         <v>1304</v>
       </c>
-      <c r="H184" s="31" t="s">
+      <c r="H184" s="32" t="s">
         <v>1305</v>
       </c>
-      <c r="I184" s="31" t="s">
+      <c r="I184" s="32" t="s">
         <v>1306</v>
       </c>
-      <c r="J184" s="31" t="s">
+      <c r="J184" s="32" t="s">
         <v>1307</v>
       </c>
-      <c r="K184" s="31" t="s">
-        <v>1308</v>
-      </c>
-      <c r="L184" s="1">
-        <f t="shared" si="50"/>
-        <v>44800</v>
-      </c>
-      <c r="M184" s="1">
-        <f t="shared" si="51"/>
-        <v>44800</v>
-      </c>
-      <c r="N184" s="1">
+      <c r="K184" s="32" t="s">
+        <v>1278</v>
+      </c>
+      <c r="L184" s="5">
+        <f t="shared" si="68"/>
+        <v>46000</v>
+      </c>
+      <c r="M184" s="5">
+        <f t="shared" si="69"/>
+        <v>46000</v>
+      </c>
+      <c r="N184" s="5">
+        <f t="shared" si="70"/>
+        <v>23500</v>
+      </c>
+      <c r="O184" s="5">
+        <f t="shared" si="71"/>
+        <v>23500</v>
+      </c>
+      <c r="P184" s="1">
+        <f t="shared" si="72"/>
+        <v>115</v>
+      </c>
+      <c r="Q184" s="24">
+        <f t="shared" si="66"/>
+        <v>275</v>
+      </c>
+      <c r="R184" s="8">
         <f t="shared" si="67"/>
-        <v>22750</v>
-      </c>
-      <c r="O184" s="1">
-        <f t="shared" si="68"/>
-        <v>22750</v>
-      </c>
-      <c r="P184" s="1">
-        <f t="shared" si="69"/>
-        <v>115</v>
-      </c>
-      <c r="Q184" s="8">
-        <f t="shared" si="66"/>
-        <v>251</v>
-      </c>
-      <c r="R184" s="8">
-        <f t="shared" si="70"/>
-        <v>162</v>
+        <v>376</v>
       </c>
       <c r="S184" s="8">
         <v>99.99</v>
       </c>
-      <c r="T184" s="35" t="s">
-        <v>1309</v>
-      </c>
-      <c r="U184" s="35" t="s">
-        <v>1309</v>
+      <c r="T184" s="36" t="s">
+        <v>1308</v>
+      </c>
+      <c r="U184" s="36" t="s">
+        <v>1308</v>
       </c>
       <c r="W184" s="1" t="s">
         <v>157</v>
@@ -18769,69 +18768,69 @@
     <row r="185" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A185" s="8"/>
       <c r="B185" s="8"/>
-      <c r="C185" s="24" t="s">
+      <c r="C185" s="25" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D185" s="25" t="s">
         <v>1310</v>
-      </c>
-      <c r="D185" s="24" t="s">
-        <v>1311</v>
       </c>
       <c r="E185" s="1">
         <v>6</v>
       </c>
       <c r="F185" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G185" s="32" t="s">
         <v>1312</v>
       </c>
-      <c r="G185" s="31" t="s">
+      <c r="H185" s="32" t="s">
         <v>1313</v>
       </c>
-      <c r="H185" s="31" t="s">
+      <c r="I185" s="32" t="s">
         <v>1314</v>
       </c>
-      <c r="I185" s="31" t="s">
+      <c r="J185" s="32" t="s">
         <v>1315</v>
       </c>
-      <c r="J185" s="31" t="s">
-        <v>1316</v>
-      </c>
-      <c r="K185" s="31" t="s">
-        <v>1278</v>
-      </c>
-      <c r="L185" s="1">
-        <f t="shared" si="50"/>
-        <v>45400</v>
-      </c>
-      <c r="M185" s="1">
-        <f t="shared" si="51"/>
-        <v>45400</v>
-      </c>
-      <c r="N185" s="1">
+      <c r="K185" s="32" t="s">
+        <v>1287</v>
+      </c>
+      <c r="L185" s="5">
+        <f t="shared" si="68"/>
+        <v>47000</v>
+      </c>
+      <c r="M185" s="5">
+        <f t="shared" si="69"/>
+        <v>47000</v>
+      </c>
+      <c r="N185" s="5">
+        <f t="shared" si="70"/>
+        <v>24000</v>
+      </c>
+      <c r="O185" s="5">
+        <f t="shared" si="71"/>
+        <v>24000</v>
+      </c>
+      <c r="P185" s="1">
+        <f t="shared" si="72"/>
+        <v>120</v>
+      </c>
+      <c r="Q185" s="24">
+        <f t="shared" si="66"/>
+        <v>284</v>
+      </c>
+      <c r="R185" s="8">
         <f t="shared" si="67"/>
-        <v>23000</v>
-      </c>
-      <c r="O185" s="1">
-        <f t="shared" si="68"/>
-        <v>23000</v>
-      </c>
-      <c r="P185" s="1">
-        <f t="shared" si="69"/>
-        <v>120</v>
-      </c>
-      <c r="Q185" s="8">
-        <f t="shared" si="66"/>
-        <v>254</v>
-      </c>
-      <c r="R185" s="8">
-        <f t="shared" si="70"/>
-        <v>166</v>
+        <v>386</v>
       </c>
       <c r="S185" s="8">
         <v>99.99</v>
       </c>
-      <c r="T185" s="35" t="s">
-        <v>1317</v>
-      </c>
-      <c r="U185" s="35" t="s">
-        <v>1317</v>
+      <c r="T185" s="36" t="s">
+        <v>1316</v>
+      </c>
+      <c r="U185" s="36" t="s">
+        <v>1316</v>
       </c>
       <c r="W185" s="1" t="s">
         <v>157</v>
@@ -18842,73 +18841,73 @@
     </row>
     <row r="186" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A186" s="7" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B186" s="7" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C186" s="37" t="s">
         <v>1318</v>
       </c>
-      <c r="B186" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C186" s="36" t="s">
+      <c r="D186" s="37" t="s">
         <v>1319</v>
-      </c>
-      <c r="D186" s="36" t="s">
-        <v>1320</v>
       </c>
       <c r="E186" s="6">
         <v>6</v>
       </c>
       <c r="F186" s="6" t="s">
+        <v>1320</v>
+      </c>
+      <c r="G186" s="38" t="s">
         <v>1321</v>
       </c>
-      <c r="G186" s="37" t="s">
+      <c r="H186" s="38" t="s">
         <v>1322</v>
       </c>
-      <c r="H186" s="37" t="s">
+      <c r="I186" s="38" t="s">
         <v>1323</v>
       </c>
-      <c r="I186" s="37" t="s">
+      <c r="J186" s="38" t="s">
         <v>1324</v>
       </c>
-      <c r="J186" s="37" t="s">
+      <c r="K186" s="38" t="s">
         <v>1325</v>
-      </c>
-      <c r="K186" s="37" t="s">
-        <v>1326</v>
       </c>
       <c r="L186" s="6">
         <f t="shared" si="50"/>
-        <v>46000</v>
+        <v>47600</v>
       </c>
       <c r="M186" s="6">
         <f t="shared" si="51"/>
-        <v>46000</v>
+        <v>47600</v>
       </c>
       <c r="N186" s="6">
-        <f t="shared" si="67"/>
-        <v>23250</v>
+        <f t="shared" ref="N181:N200" si="73">N185+250</f>
+        <v>24250</v>
       </c>
       <c r="O186" s="6">
-        <f t="shared" si="68"/>
-        <v>23250</v>
+        <f t="shared" ref="O181:O200" si="74">O185+250</f>
+        <v>24250</v>
       </c>
       <c r="P186" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>125</v>
       </c>
       <c r="Q186" s="7">
-        <f t="shared" si="66"/>
-        <v>257</v>
+        <f t="shared" ref="Q181:Q195" si="75">Q185+3</f>
+        <v>287</v>
       </c>
       <c r="R186" s="7">
-        <f t="shared" si="70"/>
-        <v>170</v>
+        <f t="shared" ref="R182:R195" si="76">R185+4</f>
+        <v>390</v>
       </c>
       <c r="S186" s="7">
         <v>99.99</v>
       </c>
-      <c r="T186" s="36" t="s">
+      <c r="T186" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U186" s="36" t="s">
+      <c r="U186" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W186" s="6" t="s">
@@ -18922,73 +18921,73 @@
     </row>
     <row r="187" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A187" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C187" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C187" s="37" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D187" s="37" t="s">
         <v>1327</v>
-      </c>
-      <c r="D187" s="36" t="s">
-        <v>1328</v>
       </c>
       <c r="E187" s="6">
         <v>6</v>
       </c>
       <c r="F187" s="6" t="s">
+        <v>1328</v>
+      </c>
+      <c r="G187" s="38" t="s">
         <v>1329</v>
       </c>
-      <c r="G187" s="37" t="s">
+      <c r="H187" s="38" t="s">
         <v>1330</v>
       </c>
-      <c r="H187" s="37" t="s">
+      <c r="I187" s="38" t="s">
         <v>1331</v>
       </c>
-      <c r="I187" s="37" t="s">
+      <c r="J187" s="38" t="s">
         <v>1332</v>
       </c>
-      <c r="J187" s="37" t="s">
+      <c r="K187" s="38" t="s">
         <v>1333</v>
-      </c>
-      <c r="K187" s="37" t="s">
-        <v>1334</v>
       </c>
       <c r="L187" s="6">
         <f t="shared" si="50"/>
-        <v>46600</v>
+        <v>48200</v>
       </c>
       <c r="M187" s="6">
         <f t="shared" si="51"/>
-        <v>46600</v>
+        <v>48200</v>
       </c>
       <c r="N187" s="6">
-        <f t="shared" si="67"/>
-        <v>23500</v>
+        <f t="shared" si="73"/>
+        <v>24500</v>
       </c>
       <c r="O187" s="6">
-        <f t="shared" si="68"/>
-        <v>23500</v>
+        <f t="shared" si="74"/>
+        <v>24500</v>
       </c>
       <c r="P187" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>130</v>
       </c>
       <c r="Q187" s="7">
-        <f t="shared" si="66"/>
-        <v>260</v>
+        <f t="shared" si="75"/>
+        <v>290</v>
       </c>
       <c r="R187" s="7">
-        <f t="shared" si="70"/>
-        <v>174</v>
+        <f t="shared" si="76"/>
+        <v>394</v>
       </c>
       <c r="S187" s="7">
         <v>99.99</v>
       </c>
-      <c r="T187" s="36" t="s">
+      <c r="T187" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U187" s="36" t="s">
+      <c r="U187" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W187" s="6" t="s">
@@ -19002,73 +19001,73 @@
     </row>
     <row r="188" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A188" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C188" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C188" s="37" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D188" s="37" t="s">
         <v>1335</v>
-      </c>
-      <c r="D188" s="36" t="s">
-        <v>1336</v>
       </c>
       <c r="E188" s="6">
         <v>6</v>
       </c>
       <c r="F188" s="6" t="s">
+        <v>1336</v>
+      </c>
+      <c r="G188" s="38" t="s">
         <v>1337</v>
       </c>
-      <c r="G188" s="37" t="s">
+      <c r="H188" s="38" t="s">
         <v>1338</v>
       </c>
-      <c r="H188" s="37" t="s">
+      <c r="I188" s="38" t="s">
         <v>1339</v>
       </c>
-      <c r="I188" s="37" t="s">
+      <c r="J188" s="38" t="s">
         <v>1340</v>
       </c>
-      <c r="J188" s="37" t="s">
+      <c r="K188" s="38" t="s">
         <v>1341</v>
-      </c>
-      <c r="K188" s="37" t="s">
-        <v>1342</v>
       </c>
       <c r="L188" s="6">
         <f t="shared" si="50"/>
-        <v>47200</v>
+        <v>48800</v>
       </c>
       <c r="M188" s="6">
         <f t="shared" si="51"/>
-        <v>47200</v>
+        <v>48800</v>
       </c>
       <c r="N188" s="6">
-        <f t="shared" si="67"/>
-        <v>23750</v>
+        <f t="shared" si="73"/>
+        <v>24750</v>
       </c>
       <c r="O188" s="6">
-        <f t="shared" si="68"/>
-        <v>23750</v>
+        <f t="shared" si="74"/>
+        <v>24750</v>
       </c>
       <c r="P188" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>135</v>
       </c>
       <c r="Q188" s="7">
-        <f t="shared" si="66"/>
-        <v>263</v>
+        <f t="shared" si="75"/>
+        <v>293</v>
       </c>
       <c r="R188" s="7">
-        <f t="shared" si="70"/>
-        <v>178</v>
+        <f t="shared" si="76"/>
+        <v>398</v>
       </c>
       <c r="S188" s="7">
         <v>99.99</v>
       </c>
-      <c r="T188" s="36" t="s">
+      <c r="T188" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U188" s="36" t="s">
+      <c r="U188" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W188" s="6" t="s">
@@ -19082,73 +19081,73 @@
     </row>
     <row r="189" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A189" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C189" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C189" s="37" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D189" s="37" t="s">
         <v>1343</v>
-      </c>
-      <c r="D189" s="36" t="s">
-        <v>1344</v>
       </c>
       <c r="E189" s="6">
         <v>6</v>
       </c>
       <c r="F189" s="6" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G189" s="38" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H189" s="38" t="s">
         <v>1345</v>
       </c>
-      <c r="G189" s="37" t="s">
-        <v>1136</v>
-      </c>
-      <c r="H189" s="37" t="s">
+      <c r="I189" s="38" t="s">
         <v>1346</v>
       </c>
-      <c r="I189" s="37" t="s">
+      <c r="J189" s="38" t="s">
         <v>1347</v>
       </c>
-      <c r="J189" s="37" t="s">
+      <c r="K189" s="38" t="s">
         <v>1348</v>
-      </c>
-      <c r="K189" s="37" t="s">
-        <v>1349</v>
       </c>
       <c r="L189" s="6">
         <f t="shared" si="50"/>
-        <v>47800</v>
+        <v>49400</v>
       </c>
       <c r="M189" s="6">
         <f t="shared" si="51"/>
-        <v>47800</v>
+        <v>49400</v>
       </c>
       <c r="N189" s="6">
-        <f t="shared" si="67"/>
-        <v>24000</v>
+        <f t="shared" si="73"/>
+        <v>25000</v>
       </c>
       <c r="O189" s="6">
-        <f t="shared" si="68"/>
-        <v>24000</v>
+        <f t="shared" si="74"/>
+        <v>25000</v>
       </c>
       <c r="P189" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>140</v>
       </c>
       <c r="Q189" s="7">
-        <f t="shared" si="66"/>
-        <v>266</v>
+        <f t="shared" si="75"/>
+        <v>296</v>
       </c>
       <c r="R189" s="7">
-        <f t="shared" si="70"/>
-        <v>182</v>
+        <f t="shared" si="76"/>
+        <v>402</v>
       </c>
       <c r="S189" s="7">
         <v>99.99</v>
       </c>
-      <c r="T189" s="36" t="s">
+      <c r="T189" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U189" s="36" t="s">
+      <c r="U189" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W189" s="6" t="s">
@@ -19162,73 +19161,73 @@
     </row>
     <row r="190" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A190" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C190" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C190" s="37" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D190" s="37" t="s">
         <v>1350</v>
-      </c>
-      <c r="D190" s="36" t="s">
-        <v>1351</v>
       </c>
       <c r="E190" s="6">
         <v>6</v>
       </c>
       <c r="F190" s="6" t="s">
+        <v>1351</v>
+      </c>
+      <c r="G190" s="38" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H190" s="38" t="s">
         <v>1352</v>
       </c>
-      <c r="G190" s="37" t="s">
-        <v>1145</v>
-      </c>
-      <c r="H190" s="37" t="s">
+      <c r="I190" s="38" t="s">
         <v>1353</v>
       </c>
-      <c r="I190" s="37" t="s">
+      <c r="J190" s="38" t="s">
         <v>1354</v>
       </c>
-      <c r="J190" s="37" t="s">
+      <c r="K190" s="38" t="s">
         <v>1355</v>
-      </c>
-      <c r="K190" s="37" t="s">
-        <v>1356</v>
       </c>
       <c r="L190" s="6">
         <f t="shared" si="50"/>
-        <v>48400</v>
+        <v>50000</v>
       </c>
       <c r="M190" s="6">
         <f t="shared" si="51"/>
-        <v>48400</v>
+        <v>50000</v>
       </c>
       <c r="N190" s="6">
-        <f t="shared" si="67"/>
-        <v>24250</v>
+        <f t="shared" si="73"/>
+        <v>25250</v>
       </c>
       <c r="O190" s="6">
-        <f t="shared" si="68"/>
-        <v>24250</v>
+        <f t="shared" si="74"/>
+        <v>25250</v>
       </c>
       <c r="P190" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>145</v>
       </c>
       <c r="Q190" s="7">
-        <f t="shared" si="66"/>
-        <v>269</v>
+        <f t="shared" si="75"/>
+        <v>299</v>
       </c>
       <c r="R190" s="7">
-        <f t="shared" si="70"/>
-        <v>186</v>
+        <f t="shared" si="76"/>
+        <v>406</v>
       </c>
       <c r="S190" s="7">
         <v>99.99</v>
       </c>
-      <c r="T190" s="36" t="s">
+      <c r="T190" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U190" s="36" t="s">
+      <c r="U190" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W190" s="6" t="s">
@@ -19242,73 +19241,73 @@
     </row>
     <row r="191" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A191" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C191" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C191" s="37" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D191" s="37" t="s">
         <v>1357</v>
-      </c>
-      <c r="D191" s="36" t="s">
-        <v>1358</v>
       </c>
       <c r="E191" s="6">
         <v>6</v>
       </c>
       <c r="F191" s="6" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G191" s="38" t="s">
+        <v>1154</v>
+      </c>
+      <c r="H191" s="38" t="s">
         <v>1359</v>
       </c>
-      <c r="G191" s="37" t="s">
-        <v>1154</v>
-      </c>
-      <c r="H191" s="37" t="s">
+      <c r="I191" s="38" t="s">
         <v>1360</v>
       </c>
-      <c r="I191" s="37" t="s">
+      <c r="J191" s="38" t="s">
         <v>1361</v>
       </c>
-      <c r="J191" s="37" t="s">
+      <c r="K191" s="38" t="s">
         <v>1362</v>
-      </c>
-      <c r="K191" s="37" t="s">
-        <v>1363</v>
       </c>
       <c r="L191" s="6">
         <f t="shared" si="50"/>
-        <v>49000</v>
+        <v>50600</v>
       </c>
       <c r="M191" s="6">
         <f t="shared" si="51"/>
-        <v>49000</v>
+        <v>50600</v>
       </c>
       <c r="N191" s="6">
-        <f t="shared" si="67"/>
-        <v>24500</v>
+        <f t="shared" si="73"/>
+        <v>25500</v>
       </c>
       <c r="O191" s="6">
-        <f t="shared" si="68"/>
-        <v>24500</v>
+        <f t="shared" si="74"/>
+        <v>25500</v>
       </c>
       <c r="P191" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>150</v>
       </c>
       <c r="Q191" s="7">
-        <f t="shared" si="66"/>
-        <v>272</v>
+        <f t="shared" si="75"/>
+        <v>302</v>
       </c>
       <c r="R191" s="7">
-        <f t="shared" si="70"/>
-        <v>190</v>
+        <f t="shared" si="76"/>
+        <v>410</v>
       </c>
       <c r="S191" s="7">
         <v>99.99</v>
       </c>
-      <c r="T191" s="36" t="s">
+      <c r="T191" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U191" s="36" t="s">
+      <c r="U191" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W191" s="6" t="s">
@@ -19322,73 +19321,73 @@
     </row>
     <row r="192" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A192" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C192" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C192" s="37" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D192" s="37" t="s">
         <v>1364</v>
-      </c>
-      <c r="D192" s="36" t="s">
-        <v>1365</v>
       </c>
       <c r="E192" s="6">
         <v>6</v>
       </c>
       <c r="F192" s="6" t="s">
+        <v>1365</v>
+      </c>
+      <c r="G192" s="38" t="s">
+        <v>1163</v>
+      </c>
+      <c r="H192" s="38" t="s">
         <v>1366</v>
       </c>
-      <c r="G192" s="37" t="s">
-        <v>1163</v>
-      </c>
-      <c r="H192" s="37" t="s">
+      <c r="I192" s="38" t="s">
         <v>1367</v>
       </c>
-      <c r="I192" s="37" t="s">
+      <c r="J192" s="38" t="s">
         <v>1368</v>
       </c>
-      <c r="J192" s="37" t="s">
+      <c r="K192" s="38" t="s">
         <v>1369</v>
-      </c>
-      <c r="K192" s="37" t="s">
-        <v>1370</v>
       </c>
       <c r="L192" s="6">
         <f t="shared" si="50"/>
-        <v>49600</v>
+        <v>51200</v>
       </c>
       <c r="M192" s="6">
         <f t="shared" si="51"/>
-        <v>49600</v>
+        <v>51200</v>
       </c>
       <c r="N192" s="6">
-        <f t="shared" si="67"/>
-        <v>24750</v>
+        <f t="shared" si="73"/>
+        <v>25750</v>
       </c>
       <c r="O192" s="6">
-        <f t="shared" si="68"/>
-        <v>24750</v>
+        <f t="shared" si="74"/>
+        <v>25750</v>
       </c>
       <c r="P192" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>155</v>
       </c>
       <c r="Q192" s="7">
-        <f t="shared" si="66"/>
-        <v>275</v>
+        <f t="shared" si="75"/>
+        <v>305</v>
       </c>
       <c r="R192" s="7">
-        <f t="shared" si="70"/>
-        <v>194</v>
+        <f t="shared" si="76"/>
+        <v>414</v>
       </c>
       <c r="S192" s="7">
         <v>99.99</v>
       </c>
-      <c r="T192" s="36" t="s">
+      <c r="T192" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U192" s="36" t="s">
+      <c r="U192" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W192" s="6" t="s">
@@ -19402,73 +19401,73 @@
     </row>
     <row r="193" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A193" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C193" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C193" s="37" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D193" s="37" t="s">
         <v>1371</v>
-      </c>
-      <c r="D193" s="36" t="s">
-        <v>1372</v>
       </c>
       <c r="E193" s="6">
         <v>6</v>
       </c>
       <c r="F193" s="6" t="s">
+        <v>1372</v>
+      </c>
+      <c r="G193" s="38" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H193" s="38" t="s">
         <v>1373</v>
       </c>
-      <c r="G193" s="37" t="s">
-        <v>1172</v>
-      </c>
-      <c r="H193" s="37" t="s">
+      <c r="I193" s="38" t="s">
         <v>1374</v>
       </c>
-      <c r="I193" s="37" t="s">
+      <c r="J193" s="38" t="s">
         <v>1375</v>
       </c>
-      <c r="J193" s="37" t="s">
+      <c r="K193" s="38" t="s">
         <v>1376</v>
-      </c>
-      <c r="K193" s="37" t="s">
-        <v>1377</v>
       </c>
       <c r="L193" s="6">
         <f t="shared" si="50"/>
-        <v>50200</v>
+        <v>51800</v>
       </c>
       <c r="M193" s="6">
         <f t="shared" si="51"/>
-        <v>50200</v>
+        <v>51800</v>
       </c>
       <c r="N193" s="6">
-        <f t="shared" si="67"/>
-        <v>25000</v>
+        <f t="shared" si="73"/>
+        <v>26000</v>
       </c>
       <c r="O193" s="6">
-        <f t="shared" si="68"/>
-        <v>25000</v>
+        <f t="shared" si="74"/>
+        <v>26000</v>
       </c>
       <c r="P193" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>160</v>
       </c>
       <c r="Q193" s="7">
-        <f t="shared" si="66"/>
-        <v>278</v>
+        <f t="shared" si="75"/>
+        <v>308</v>
       </c>
       <c r="R193" s="7">
-        <f t="shared" si="70"/>
-        <v>198</v>
+        <f t="shared" si="76"/>
+        <v>418</v>
       </c>
       <c r="S193" s="7">
         <v>99.99</v>
       </c>
-      <c r="T193" s="36" t="s">
+      <c r="T193" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U193" s="36" t="s">
+      <c r="U193" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W193" s="6" t="s">
@@ -19482,73 +19481,73 @@
     </row>
     <row r="194" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A194" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C194" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C194" s="37" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D194" s="37" t="s">
         <v>1378</v>
-      </c>
-      <c r="D194" s="36" t="s">
-        <v>1379</v>
       </c>
       <c r="E194" s="6">
         <v>6</v>
       </c>
       <c r="F194" s="6" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G194" s="38" t="s">
+        <v>1180</v>
+      </c>
+      <c r="H194" s="38" t="s">
         <v>1380</v>
       </c>
-      <c r="G194" s="37" t="s">
-        <v>1180</v>
-      </c>
-      <c r="H194" s="37" t="s">
+      <c r="I194" s="38" t="s">
         <v>1381</v>
       </c>
-      <c r="I194" s="37" t="s">
+      <c r="J194" s="38" t="s">
         <v>1382</v>
       </c>
-      <c r="J194" s="37" t="s">
+      <c r="K194" s="38" t="s">
         <v>1383</v>
-      </c>
-      <c r="K194" s="37" t="s">
-        <v>1384</v>
       </c>
       <c r="L194" s="6">
         <f t="shared" si="50"/>
-        <v>50800</v>
+        <v>52400</v>
       </c>
       <c r="M194" s="6">
         <f t="shared" si="51"/>
-        <v>50800</v>
+        <v>52400</v>
       </c>
       <c r="N194" s="6">
-        <f t="shared" si="67"/>
-        <v>25250</v>
+        <f t="shared" si="73"/>
+        <v>26250</v>
       </c>
       <c r="O194" s="6">
-        <f t="shared" si="68"/>
-        <v>25250</v>
+        <f t="shared" si="74"/>
+        <v>26250</v>
       </c>
       <c r="P194" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>165</v>
       </c>
       <c r="Q194" s="7">
-        <f t="shared" si="66"/>
-        <v>281</v>
+        <f t="shared" si="75"/>
+        <v>311</v>
       </c>
       <c r="R194" s="7">
-        <f t="shared" si="70"/>
-        <v>202</v>
+        <f t="shared" si="76"/>
+        <v>422</v>
       </c>
       <c r="S194" s="7">
         <v>99.99</v>
       </c>
-      <c r="T194" s="36" t="s">
+      <c r="T194" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U194" s="36" t="s">
+      <c r="U194" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W194" s="6" t="s">
@@ -19562,73 +19561,73 @@
     </row>
     <row r="195" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A195" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C195" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C195" s="37" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D195" s="37" t="s">
         <v>1385</v>
-      </c>
-      <c r="D195" s="36" t="s">
-        <v>1386</v>
       </c>
       <c r="E195" s="6">
         <v>6</v>
       </c>
       <c r="F195" s="6" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G195" s="38" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H195" s="38" t="s">
         <v>1387</v>
       </c>
-      <c r="G195" s="37" t="s">
-        <v>1189</v>
-      </c>
-      <c r="H195" s="37" t="s">
+      <c r="I195" s="38" t="s">
         <v>1388</v>
       </c>
-      <c r="I195" s="37" t="s">
+      <c r="J195" s="38" t="s">
+        <v>1183</v>
+      </c>
+      <c r="K195" s="38" t="s">
         <v>1389</v>
-      </c>
-      <c r="J195" s="37" t="s">
-        <v>1183</v>
-      </c>
-      <c r="K195" s="37" t="s">
-        <v>1390</v>
       </c>
       <c r="L195" s="6">
         <f t="shared" si="50"/>
-        <v>51400</v>
+        <v>53000</v>
       </c>
       <c r="M195" s="6">
         <f t="shared" si="51"/>
-        <v>51400</v>
+        <v>53000</v>
       </c>
       <c r="N195" s="6">
-        <f t="shared" si="67"/>
-        <v>25500</v>
+        <f t="shared" si="73"/>
+        <v>26500</v>
       </c>
       <c r="O195" s="6">
-        <f t="shared" si="68"/>
-        <v>25500</v>
+        <f t="shared" si="74"/>
+        <v>26500</v>
       </c>
       <c r="P195" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>170</v>
       </c>
       <c r="Q195" s="7">
-        <f t="shared" si="66"/>
-        <v>284</v>
+        <f t="shared" si="75"/>
+        <v>314</v>
       </c>
       <c r="R195" s="7">
-        <f t="shared" si="70"/>
-        <v>206</v>
+        <f t="shared" si="76"/>
+        <v>426</v>
       </c>
       <c r="S195" s="7">
         <v>99.99</v>
       </c>
-      <c r="T195" s="36" t="s">
+      <c r="T195" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U195" s="36" t="s">
+      <c r="U195" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W195" s="6" t="s">
@@ -19642,73 +19641,73 @@
     </row>
     <row r="196" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A196" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C196" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C196" s="37" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D196" s="37" t="s">
         <v>1391</v>
-      </c>
-      <c r="D196" s="36" t="s">
-        <v>1392</v>
       </c>
       <c r="E196" s="6">
         <v>6</v>
       </c>
       <c r="F196" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G196" s="38" t="s">
+        <v>1198</v>
+      </c>
+      <c r="H196" s="38" t="s">
         <v>1393</v>
       </c>
-      <c r="G196" s="37" t="s">
-        <v>1198</v>
-      </c>
-      <c r="H196" s="37" t="s">
+      <c r="I196" s="38" t="s">
         <v>1394</v>
       </c>
-      <c r="I196" s="37" t="s">
+      <c r="J196" s="38" t="s">
         <v>1395</v>
       </c>
-      <c r="J196" s="37" t="s">
+      <c r="K196" s="38" t="s">
         <v>1396</v>
-      </c>
-      <c r="K196" s="37" t="s">
-        <v>1397</v>
       </c>
       <c r="L196" s="6">
         <f t="shared" si="50"/>
-        <v>52000</v>
+        <v>53600</v>
       </c>
       <c r="M196" s="6">
         <f t="shared" si="51"/>
-        <v>52000</v>
+        <v>53600</v>
       </c>
       <c r="N196" s="6">
-        <f t="shared" si="67"/>
-        <v>25750</v>
+        <f t="shared" si="73"/>
+        <v>26750</v>
       </c>
       <c r="O196" s="6">
-        <f t="shared" si="68"/>
-        <v>25750</v>
+        <f t="shared" si="74"/>
+        <v>26750</v>
       </c>
       <c r="P196" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>175</v>
       </c>
       <c r="Q196" s="7">
-        <f t="shared" ref="Q196:Q200" si="71">Q195+4</f>
-        <v>288</v>
+        <f t="shared" ref="Q196:Q200" si="77">Q195+4</f>
+        <v>318</v>
       </c>
       <c r="R196" s="7">
-        <f t="shared" ref="R196:R200" si="72">R195+5</f>
-        <v>211</v>
+        <f t="shared" ref="R196:R200" si="78">R195+5</f>
+        <v>431</v>
       </c>
       <c r="S196" s="7">
         <v>99.99</v>
       </c>
-      <c r="T196" s="36" t="s">
+      <c r="T196" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U196" s="36" t="s">
+      <c r="U196" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W196" s="6" t="s">
@@ -19722,73 +19721,73 @@
     </row>
     <row r="197" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A197" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C197" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C197" s="37" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D197" s="37" t="s">
         <v>1398</v>
-      </c>
-      <c r="D197" s="36" t="s">
-        <v>1399</v>
       </c>
       <c r="E197" s="6">
         <v>6</v>
       </c>
       <c r="F197" s="6" t="s">
+        <v>1399</v>
+      </c>
+      <c r="G197" s="38" t="s">
+        <v>1207</v>
+      </c>
+      <c r="H197" s="38" t="s">
         <v>1400</v>
       </c>
-      <c r="G197" s="37" t="s">
-        <v>1207</v>
-      </c>
-      <c r="H197" s="37" t="s">
+      <c r="I197" s="38" t="s">
         <v>1401</v>
       </c>
-      <c r="I197" s="37" t="s">
+      <c r="J197" s="38" t="s">
         <v>1402</v>
       </c>
-      <c r="J197" s="37" t="s">
+      <c r="K197" s="38" t="s">
         <v>1403</v>
-      </c>
-      <c r="K197" s="37" t="s">
-        <v>1404</v>
       </c>
       <c r="L197" s="6">
         <f t="shared" si="50"/>
-        <v>52600</v>
+        <v>54200</v>
       </c>
       <c r="M197" s="6">
         <f t="shared" si="51"/>
-        <v>52600</v>
+        <v>54200</v>
       </c>
       <c r="N197" s="6">
-        <f t="shared" si="67"/>
-        <v>26000</v>
+        <f t="shared" si="73"/>
+        <v>27000</v>
       </c>
       <c r="O197" s="6">
-        <f t="shared" si="68"/>
-        <v>26000</v>
+        <f t="shared" si="74"/>
+        <v>27000</v>
       </c>
       <c r="P197" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>180</v>
       </c>
       <c r="Q197" s="7">
-        <f t="shared" si="71"/>
-        <v>292</v>
+        <f t="shared" si="77"/>
+        <v>322</v>
       </c>
       <c r="R197" s="7">
-        <f t="shared" si="72"/>
-        <v>216</v>
+        <f t="shared" si="78"/>
+        <v>436</v>
       </c>
       <c r="S197" s="7">
         <v>99.99</v>
       </c>
-      <c r="T197" s="36" t="s">
+      <c r="T197" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U197" s="36" t="s">
+      <c r="U197" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W197" s="6" t="s">
@@ -19802,73 +19801,73 @@
     </row>
     <row r="198" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A198" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C198" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C198" s="37" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D198" s="37" t="s">
         <v>1405</v>
-      </c>
-      <c r="D198" s="36" t="s">
-        <v>1406</v>
       </c>
       <c r="E198" s="6">
         <v>6</v>
       </c>
       <c r="F198" s="6" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G198" s="38" t="s">
+        <v>1216</v>
+      </c>
+      <c r="H198" s="38" t="s">
         <v>1407</v>
       </c>
-      <c r="G198" s="37" t="s">
-        <v>1216</v>
-      </c>
-      <c r="H198" s="37" t="s">
+      <c r="I198" s="38" t="s">
         <v>1408</v>
       </c>
-      <c r="I198" s="37" t="s">
+      <c r="J198" s="38" t="s">
         <v>1409</v>
       </c>
-      <c r="J198" s="37" t="s">
+      <c r="K198" s="38" t="s">
         <v>1410</v>
-      </c>
-      <c r="K198" s="37" t="s">
-        <v>1411</v>
       </c>
       <c r="L198" s="6">
         <f t="shared" si="50"/>
-        <v>53200</v>
+        <v>54800</v>
       </c>
       <c r="M198" s="6">
         <f t="shared" si="51"/>
-        <v>53200</v>
+        <v>54800</v>
       </c>
       <c r="N198" s="6">
-        <f t="shared" si="67"/>
-        <v>26250</v>
+        <f t="shared" si="73"/>
+        <v>27250</v>
       </c>
       <c r="O198" s="6">
-        <f t="shared" si="68"/>
-        <v>26250</v>
+        <f t="shared" si="74"/>
+        <v>27250</v>
       </c>
       <c r="P198" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>185</v>
       </c>
       <c r="Q198" s="7">
-        <f t="shared" si="71"/>
-        <v>296</v>
+        <f t="shared" si="77"/>
+        <v>326</v>
       </c>
       <c r="R198" s="7">
-        <f t="shared" si="72"/>
-        <v>221</v>
+        <f t="shared" si="78"/>
+        <v>441</v>
       </c>
       <c r="S198" s="7">
         <v>99.99</v>
       </c>
-      <c r="T198" s="36" t="s">
+      <c r="T198" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U198" s="36" t="s">
+      <c r="U198" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W198" s="6" t="s">
@@ -19882,73 +19881,73 @@
     </row>
     <row r="199" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A199" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C199" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C199" s="37" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D199" s="37" t="s">
         <v>1412</v>
-      </c>
-      <c r="D199" s="36" t="s">
-        <v>1413</v>
       </c>
       <c r="E199" s="6">
         <v>6</v>
       </c>
       <c r="F199" s="6" t="s">
+        <v>1413</v>
+      </c>
+      <c r="G199" s="38" t="s">
+        <v>1225</v>
+      </c>
+      <c r="H199" s="38" t="s">
         <v>1414</v>
       </c>
-      <c r="G199" s="37" t="s">
-        <v>1225</v>
-      </c>
-      <c r="H199" s="37" t="s">
+      <c r="I199" s="38" t="s">
         <v>1415</v>
       </c>
-      <c r="I199" s="37" t="s">
+      <c r="J199" s="38" t="s">
         <v>1416</v>
       </c>
-      <c r="J199" s="37" t="s">
+      <c r="K199" s="38" t="s">
         <v>1417</v>
-      </c>
-      <c r="K199" s="37" t="s">
-        <v>1418</v>
       </c>
       <c r="L199" s="6">
         <f t="shared" si="50"/>
-        <v>53800</v>
+        <v>55400</v>
       </c>
       <c r="M199" s="6">
         <f t="shared" si="51"/>
-        <v>53800</v>
+        <v>55400</v>
       </c>
       <c r="N199" s="6">
-        <f t="shared" si="67"/>
-        <v>26500</v>
+        <f t="shared" si="73"/>
+        <v>27500</v>
       </c>
       <c r="O199" s="6">
-        <f t="shared" si="68"/>
-        <v>26500</v>
+        <f t="shared" si="74"/>
+        <v>27500</v>
       </c>
       <c r="P199" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>190</v>
       </c>
       <c r="Q199" s="7">
-        <f t="shared" si="71"/>
-        <v>300</v>
+        <f t="shared" si="77"/>
+        <v>330</v>
       </c>
       <c r="R199" s="7">
-        <f t="shared" si="72"/>
-        <v>226</v>
+        <f t="shared" si="78"/>
+        <v>446</v>
       </c>
       <c r="S199" s="7">
         <v>99.99</v>
       </c>
-      <c r="T199" s="36" t="s">
+      <c r="T199" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U199" s="36" t="s">
+      <c r="U199" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W199" s="6" t="s">
@@ -19962,73 +19961,73 @@
     </row>
     <row r="200" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A200" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C200" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C200" s="37" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D200" s="37" t="s">
         <v>1419</v>
-      </c>
-      <c r="D200" s="36" t="s">
-        <v>1420</v>
       </c>
       <c r="E200" s="6">
         <v>6</v>
       </c>
       <c r="F200" s="6" t="s">
+        <v>1420</v>
+      </c>
+      <c r="G200" s="38" t="s">
+        <v>1234</v>
+      </c>
+      <c r="H200" s="38" t="s">
         <v>1421</v>
       </c>
-      <c r="G200" s="37" t="s">
-        <v>1234</v>
-      </c>
-      <c r="H200" s="37" t="s">
+      <c r="I200" s="38" t="s">
         <v>1422</v>
       </c>
-      <c r="I200" s="37" t="s">
+      <c r="J200" s="38" t="s">
         <v>1423</v>
       </c>
-      <c r="J200" s="37" t="s">
+      <c r="K200" s="38" t="s">
         <v>1424</v>
-      </c>
-      <c r="K200" s="37" t="s">
-        <v>1425</v>
       </c>
       <c r="L200" s="6">
         <f t="shared" si="50"/>
-        <v>54400</v>
+        <v>56000</v>
       </c>
       <c r="M200" s="6">
         <f t="shared" si="51"/>
-        <v>54400</v>
+        <v>56000</v>
       </c>
       <c r="N200" s="6">
-        <f t="shared" si="67"/>
-        <v>26750</v>
+        <f t="shared" si="73"/>
+        <v>27750</v>
       </c>
       <c r="O200" s="6">
-        <f t="shared" si="68"/>
-        <v>26750</v>
+        <f t="shared" si="74"/>
+        <v>27750</v>
       </c>
       <c r="P200" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>195</v>
       </c>
       <c r="Q200" s="7">
-        <f t="shared" si="71"/>
-        <v>304</v>
+        <f t="shared" si="77"/>
+        <v>334</v>
       </c>
       <c r="R200" s="7">
-        <f t="shared" si="72"/>
-        <v>231</v>
+        <f t="shared" si="78"/>
+        <v>451</v>
       </c>
       <c r="S200" s="7">
         <v>99.99</v>
       </c>
-      <c r="T200" s="36" t="s">
+      <c r="T200" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U200" s="36" t="s">
+      <c r="U200" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W200" s="6" t="s">
@@ -20042,73 +20041,73 @@
     </row>
     <row r="201" s="7" customFormat="1" customHeight="1" spans="1:24">
       <c r="A201" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C201" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C201" s="37" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D201" s="37" t="s">
         <v>1426</v>
-      </c>
-      <c r="D201" s="36" t="s">
-        <v>1427</v>
       </c>
       <c r="E201" s="6">
         <v>6</v>
       </c>
       <c r="F201" s="6" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G201" s="38" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H201" s="38" t="s">
         <v>1428</v>
       </c>
-      <c r="G201" s="37" t="s">
-        <v>1243</v>
-      </c>
-      <c r="H201" s="37" t="s">
+      <c r="I201" s="38" t="s">
         <v>1429</v>
       </c>
-      <c r="I201" s="37" t="s">
+      <c r="J201" s="38" t="s">
         <v>1430</v>
       </c>
-      <c r="J201" s="37" t="s">
+      <c r="K201" s="38" t="s">
         <v>1431</v>
-      </c>
-      <c r="K201" s="37" t="s">
-        <v>1432</v>
       </c>
       <c r="L201" s="6">
         <f t="shared" si="50"/>
-        <v>55000</v>
+        <v>56600</v>
       </c>
       <c r="M201" s="6">
         <f t="shared" si="51"/>
-        <v>55000</v>
+        <v>56600</v>
       </c>
       <c r="N201" s="6">
-        <f t="shared" ref="N201:N205" si="73">N200+300</f>
-        <v>27050</v>
+        <f t="shared" ref="N201:N205" si="79">N200+300</f>
+        <v>28050</v>
       </c>
       <c r="O201" s="6">
-        <f t="shared" ref="O201:O205" si="74">O200+300</f>
-        <v>27050</v>
+        <f t="shared" ref="O201:O205" si="80">O200+300</f>
+        <v>28050</v>
       </c>
       <c r="P201" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>200</v>
       </c>
       <c r="Q201" s="7">
-        <f t="shared" ref="Q201:Q205" si="75">Q200+5</f>
-        <v>309</v>
+        <f t="shared" ref="Q201:Q205" si="81">Q200+5</f>
+        <v>339</v>
       </c>
       <c r="R201" s="7">
-        <f t="shared" ref="R201:R205" si="76">R200+6</f>
-        <v>237</v>
+        <f t="shared" ref="R201:R205" si="82">R200+6</f>
+        <v>457</v>
       </c>
       <c r="S201" s="7">
         <v>99.99</v>
       </c>
-      <c r="T201" s="36" t="s">
+      <c r="T201" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U201" s="36" t="s">
+      <c r="U201" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="V201" s="6"/>
@@ -20121,73 +20120,73 @@
     </row>
     <row r="202" s="7" customFormat="1" customHeight="1" spans="1:24">
       <c r="A202" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C202" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C202" s="37" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D202" s="37" t="s">
         <v>1433</v>
-      </c>
-      <c r="D202" s="36" t="s">
-        <v>1434</v>
       </c>
       <c r="E202" s="6">
         <v>6</v>
       </c>
       <c r="F202" s="6" t="s">
+        <v>1434</v>
+      </c>
+      <c r="G202" s="38" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H202" s="38" t="s">
         <v>1435</v>
       </c>
-      <c r="G202" s="37" t="s">
-        <v>1252</v>
-      </c>
-      <c r="H202" s="37" t="s">
+      <c r="I202" s="38" t="s">
         <v>1436</v>
       </c>
-      <c r="I202" s="37" t="s">
+      <c r="J202" s="38" t="s">
         <v>1437</v>
       </c>
-      <c r="J202" s="37" t="s">
+      <c r="K202" s="38" t="s">
         <v>1438</v>
-      </c>
-      <c r="K202" s="37" t="s">
-        <v>1439</v>
       </c>
       <c r="L202" s="6">
         <f t="shared" si="50"/>
-        <v>55600</v>
+        <v>57200</v>
       </c>
       <c r="M202" s="6">
         <f t="shared" si="51"/>
-        <v>55600</v>
+        <v>57200</v>
       </c>
       <c r="N202" s="6">
-        <f t="shared" si="73"/>
-        <v>27350</v>
+        <f t="shared" si="79"/>
+        <v>28350</v>
       </c>
       <c r="O202" s="6">
-        <f t="shared" si="74"/>
-        <v>27350</v>
+        <f t="shared" si="80"/>
+        <v>28350</v>
       </c>
       <c r="P202" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>205</v>
       </c>
       <c r="Q202" s="7">
-        <f t="shared" si="75"/>
-        <v>314</v>
+        <f t="shared" si="81"/>
+        <v>344</v>
       </c>
       <c r="R202" s="7">
-        <f t="shared" si="76"/>
-        <v>243</v>
+        <f t="shared" si="82"/>
+        <v>463</v>
       </c>
       <c r="S202" s="7">
         <v>99.99</v>
       </c>
-      <c r="T202" s="36" t="s">
+      <c r="T202" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U202" s="36" t="s">
+      <c r="U202" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="V202" s="6"/>
@@ -20200,73 +20199,73 @@
     </row>
     <row r="203" s="7" customFormat="1" customHeight="1" spans="1:24">
       <c r="A203" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C203" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C203" s="37" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D203" s="37" t="s">
         <v>1440</v>
-      </c>
-      <c r="D203" s="36" t="s">
-        <v>1441</v>
       </c>
       <c r="E203" s="6">
         <v>6</v>
       </c>
       <c r="F203" s="6" t="s">
+        <v>1441</v>
+      </c>
+      <c r="G203" s="38" t="s">
+        <v>1261</v>
+      </c>
+      <c r="H203" s="38" t="s">
         <v>1442</v>
       </c>
-      <c r="G203" s="37" t="s">
-        <v>1261</v>
-      </c>
-      <c r="H203" s="37" t="s">
+      <c r="I203" s="38" t="s">
         <v>1443</v>
       </c>
-      <c r="I203" s="37" t="s">
+      <c r="J203" s="38" t="s">
         <v>1444</v>
       </c>
-      <c r="J203" s="37" t="s">
+      <c r="K203" s="38" t="s">
         <v>1445</v>
-      </c>
-      <c r="K203" s="37" t="s">
-        <v>1446</v>
       </c>
       <c r="L203" s="6">
         <f t="shared" si="50"/>
-        <v>56200</v>
+        <v>57800</v>
       </c>
       <c r="M203" s="6">
         <f t="shared" si="51"/>
-        <v>56200</v>
+        <v>57800</v>
       </c>
       <c r="N203" s="6">
-        <f t="shared" si="73"/>
-        <v>27650</v>
+        <f t="shared" si="79"/>
+        <v>28650</v>
       </c>
       <c r="O203" s="6">
-        <f t="shared" si="74"/>
-        <v>27650</v>
+        <f t="shared" si="80"/>
+        <v>28650</v>
       </c>
       <c r="P203" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>210</v>
       </c>
       <c r="Q203" s="7">
-        <f t="shared" si="75"/>
-        <v>319</v>
+        <f t="shared" si="81"/>
+        <v>349</v>
       </c>
       <c r="R203" s="7">
-        <f t="shared" si="76"/>
-        <v>249</v>
+        <f t="shared" si="82"/>
+        <v>469</v>
       </c>
       <c r="S203" s="7">
         <v>99.99</v>
       </c>
-      <c r="T203" s="36" t="s">
+      <c r="T203" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U203" s="36" t="s">
+      <c r="U203" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="V203" s="6"/>
@@ -20279,73 +20278,73 @@
     </row>
     <row r="204" s="7" customFormat="1" customHeight="1" spans="1:24">
       <c r="A204" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C204" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C204" s="37" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D204" s="37" t="s">
         <v>1447</v>
-      </c>
-      <c r="D204" s="36" t="s">
-        <v>1448</v>
       </c>
       <c r="E204" s="6">
         <v>6</v>
       </c>
       <c r="F204" s="6" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G204" s="38" t="s">
+        <v>1270</v>
+      </c>
+      <c r="H204" s="38" t="s">
         <v>1449</v>
       </c>
-      <c r="G204" s="37" t="s">
-        <v>1270</v>
-      </c>
-      <c r="H204" s="37" t="s">
+      <c r="I204" s="38" t="s">
         <v>1450</v>
       </c>
-      <c r="I204" s="37" t="s">
+      <c r="J204" s="38" t="s">
         <v>1451</v>
       </c>
-      <c r="J204" s="37" t="s">
+      <c r="K204" s="38" t="s">
         <v>1452</v>
-      </c>
-      <c r="K204" s="37" t="s">
-        <v>1453</v>
       </c>
       <c r="L204" s="6">
         <f t="shared" si="50"/>
-        <v>56800</v>
+        <v>58400</v>
       </c>
       <c r="M204" s="6">
         <f t="shared" si="51"/>
-        <v>56800</v>
+        <v>58400</v>
       </c>
       <c r="N204" s="6">
-        <f t="shared" si="73"/>
-        <v>27950</v>
+        <f t="shared" si="79"/>
+        <v>28950</v>
       </c>
       <c r="O204" s="6">
-        <f t="shared" si="74"/>
-        <v>27950</v>
+        <f t="shared" si="80"/>
+        <v>28950</v>
       </c>
       <c r="P204" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>215</v>
       </c>
       <c r="Q204" s="7">
-        <f t="shared" si="75"/>
-        <v>324</v>
+        <f t="shared" si="81"/>
+        <v>354</v>
       </c>
       <c r="R204" s="7">
-        <f t="shared" si="76"/>
-        <v>255</v>
+        <f t="shared" si="82"/>
+        <v>475</v>
       </c>
       <c r="S204" s="7">
         <v>99.99</v>
       </c>
-      <c r="T204" s="36" t="s">
+      <c r="T204" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U204" s="36" t="s">
+      <c r="U204" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="V204" s="6"/>
@@ -20358,16 +20357,16 @@
     </row>
     <row r="205" s="7" customFormat="1" customHeight="1" spans="1:24">
       <c r="A205" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C205" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C205" s="37" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D205" s="37" t="s">
         <v>1454</v>
-      </c>
-      <c r="D205" s="36" t="s">
-        <v>1455</v>
       </c>
       <c r="E205" s="6">
         <v>6</v>
@@ -20375,56 +20374,56 @@
       <c r="F205" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="G205" s="37" t="s">
+      <c r="G205" s="38" t="s">
+        <v>1455</v>
+      </c>
+      <c r="H205" s="38" t="s">
         <v>1456</v>
       </c>
-      <c r="H205" s="37" t="s">
+      <c r="I205" s="38" t="s">
         <v>1457</v>
       </c>
-      <c r="I205" s="37" t="s">
+      <c r="J205" s="38" t="s">
         <v>1458</v>
       </c>
-      <c r="J205" s="37" t="s">
+      <c r="K205" s="38" t="s">
         <v>1459</v>
       </c>
-      <c r="K205" s="37" t="s">
-        <v>1460</v>
-      </c>
       <c r="L205" s="6">
-        <f t="shared" ref="L205:L215" si="77">L204+600</f>
-        <v>57400</v>
+        <f t="shared" ref="L205:L215" si="83">L204+600</f>
+        <v>59000</v>
       </c>
       <c r="M205" s="6">
-        <f t="shared" ref="M205:M215" si="78">M204+600</f>
-        <v>57400</v>
+        <f t="shared" ref="M205:M215" si="84">M204+600</f>
+        <v>59000</v>
       </c>
       <c r="N205" s="6">
-        <f t="shared" si="73"/>
-        <v>28250</v>
+        <f t="shared" si="79"/>
+        <v>29250</v>
       </c>
       <c r="O205" s="6">
-        <f t="shared" si="74"/>
-        <v>28250</v>
+        <f t="shared" si="80"/>
+        <v>29250</v>
       </c>
       <c r="P205" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>220</v>
       </c>
       <c r="Q205" s="7">
-        <f t="shared" si="75"/>
-        <v>329</v>
+        <f t="shared" si="81"/>
+        <v>359</v>
       </c>
       <c r="R205" s="7">
-        <f t="shared" si="76"/>
-        <v>261</v>
+        <f t="shared" si="82"/>
+        <v>481</v>
       </c>
       <c r="S205" s="7">
         <v>99.99</v>
       </c>
-      <c r="T205" s="36" t="s">
+      <c r="T205" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U205" s="36" t="s">
+      <c r="U205" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="V205" s="6"/>
@@ -20437,73 +20436,73 @@
     </row>
     <row r="206" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A206" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C206" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C206" s="37" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D206" s="37" t="s">
         <v>1461</v>
-      </c>
-      <c r="D206" s="36" t="s">
-        <v>1462</v>
       </c>
       <c r="E206" s="6">
         <v>6</v>
       </c>
       <c r="F206" s="6" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G206" s="38" t="s">
         <v>1463</v>
       </c>
-      <c r="G206" s="37" t="s">
+      <c r="H206" s="38" t="s">
         <v>1464</v>
       </c>
-      <c r="H206" s="37" t="s">
+      <c r="I206" s="38" t="s">
         <v>1465</v>
       </c>
-      <c r="I206" s="37" t="s">
+      <c r="J206" s="38" t="s">
         <v>1466</v>
       </c>
-      <c r="J206" s="37" t="s">
+      <c r="K206" s="38" t="s">
         <v>1467</v>
       </c>
-      <c r="K206" s="37" t="s">
-        <v>1468</v>
-      </c>
       <c r="L206" s="6">
-        <f t="shared" si="77"/>
-        <v>58000</v>
+        <f t="shared" si="83"/>
+        <v>59600</v>
       </c>
       <c r="M206" s="6">
-        <f t="shared" si="78"/>
-        <v>58000</v>
+        <f t="shared" si="84"/>
+        <v>59600</v>
       </c>
       <c r="N206" s="6">
-        <f t="shared" ref="N206:N210" si="79">N205+400</f>
-        <v>28650</v>
+        <f t="shared" ref="N206:N210" si="85">N205+400</f>
+        <v>29650</v>
       </c>
       <c r="O206" s="6">
-        <f t="shared" ref="O206:O210" si="80">O205+400</f>
-        <v>28650</v>
+        <f t="shared" ref="O206:O210" si="86">O205+400</f>
+        <v>29650</v>
       </c>
       <c r="P206" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>225</v>
       </c>
       <c r="Q206" s="7">
-        <f t="shared" ref="Q206:Q210" si="81">Q205+6</f>
-        <v>335</v>
+        <f t="shared" ref="Q206:Q210" si="87">Q205+6</f>
+        <v>365</v>
       </c>
       <c r="R206" s="7">
-        <f t="shared" ref="R206:R210" si="82">R205+7</f>
-        <v>268</v>
+        <f t="shared" ref="R206:R210" si="88">R205+7</f>
+        <v>488</v>
       </c>
       <c r="S206" s="7">
         <v>99.99</v>
       </c>
-      <c r="T206" s="36" t="s">
+      <c r="T206" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U206" s="36" t="s">
+      <c r="U206" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W206" s="6" t="s">
@@ -20517,73 +20516,73 @@
     </row>
     <row r="207" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A207" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C207" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C207" s="37" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D207" s="37" t="s">
         <v>1469</v>
-      </c>
-      <c r="D207" s="36" t="s">
-        <v>1470</v>
       </c>
       <c r="E207" s="6">
         <v>6</v>
       </c>
       <c r="F207" s="6" t="s">
+        <v>1470</v>
+      </c>
+      <c r="G207" s="38" t="s">
         <v>1471</v>
       </c>
-      <c r="G207" s="37" t="s">
+      <c r="H207" s="38" t="s">
         <v>1472</v>
       </c>
-      <c r="H207" s="37" t="s">
+      <c r="I207" s="38" t="s">
         <v>1473</v>
       </c>
-      <c r="I207" s="37" t="s">
+      <c r="J207" s="38" t="s">
         <v>1474</v>
       </c>
-      <c r="J207" s="37" t="s">
+      <c r="K207" s="38" t="s">
         <v>1475</v>
       </c>
-      <c r="K207" s="37" t="s">
-        <v>1476</v>
-      </c>
       <c r="L207" s="6">
-        <f t="shared" si="77"/>
-        <v>58600</v>
+        <f t="shared" si="83"/>
+        <v>60200</v>
       </c>
       <c r="M207" s="6">
-        <f t="shared" si="78"/>
-        <v>58600</v>
+        <f t="shared" si="84"/>
+        <v>60200</v>
       </c>
       <c r="N207" s="6">
-        <f t="shared" si="79"/>
-        <v>29050</v>
+        <f t="shared" si="85"/>
+        <v>30050</v>
       </c>
       <c r="O207" s="6">
-        <f t="shared" si="80"/>
-        <v>29050</v>
+        <f t="shared" si="86"/>
+        <v>30050</v>
       </c>
       <c r="P207" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>230</v>
       </c>
       <c r="Q207" s="7">
-        <f t="shared" si="81"/>
-        <v>341</v>
+        <f t="shared" si="87"/>
+        <v>371</v>
       </c>
       <c r="R207" s="7">
-        <f t="shared" si="82"/>
-        <v>275</v>
+        <f t="shared" si="88"/>
+        <v>495</v>
       </c>
       <c r="S207" s="7">
         <v>99.99</v>
       </c>
-      <c r="T207" s="36" t="s">
+      <c r="T207" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U207" s="36" t="s">
+      <c r="U207" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W207" s="6" t="s">
@@ -20597,73 +20596,73 @@
     </row>
     <row r="208" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A208" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C208" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C208" s="37" t="s">
+        <v>1476</v>
+      </c>
+      <c r="D208" s="37" t="s">
         <v>1477</v>
-      </c>
-      <c r="D208" s="36" t="s">
-        <v>1478</v>
       </c>
       <c r="E208" s="6">
         <v>6</v>
       </c>
       <c r="F208" s="6" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G208" s="38" t="s">
         <v>1479</v>
       </c>
-      <c r="G208" s="37" t="s">
+      <c r="H208" s="38" t="s">
         <v>1480</v>
       </c>
-      <c r="H208" s="37" t="s">
+      <c r="I208" s="38" t="s">
         <v>1481</v>
       </c>
-      <c r="I208" s="37" t="s">
+      <c r="J208" s="38" t="s">
+        <v>1273</v>
+      </c>
+      <c r="K208" s="38" t="s">
         <v>1482</v>
       </c>
-      <c r="J208" s="37" t="s">
-        <v>1273</v>
-      </c>
-      <c r="K208" s="37" t="s">
-        <v>1483</v>
-      </c>
       <c r="L208" s="6">
-        <f t="shared" si="77"/>
-        <v>59200</v>
+        <f t="shared" si="83"/>
+        <v>60800</v>
       </c>
       <c r="M208" s="6">
-        <f t="shared" si="78"/>
-        <v>59200</v>
+        <f t="shared" si="84"/>
+        <v>60800</v>
       </c>
       <c r="N208" s="6">
-        <f t="shared" si="79"/>
-        <v>29450</v>
+        <f t="shared" si="85"/>
+        <v>30450</v>
       </c>
       <c r="O208" s="6">
-        <f t="shared" si="80"/>
-        <v>29450</v>
+        <f t="shared" si="86"/>
+        <v>30450</v>
       </c>
       <c r="P208" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>235</v>
       </c>
       <c r="Q208" s="7">
-        <f t="shared" si="81"/>
-        <v>347</v>
+        <f t="shared" si="87"/>
+        <v>377</v>
       </c>
       <c r="R208" s="7">
-        <f t="shared" si="82"/>
-        <v>282</v>
+        <f t="shared" si="88"/>
+        <v>502</v>
       </c>
       <c r="S208" s="7">
         <v>99.99</v>
       </c>
-      <c r="T208" s="36" t="s">
+      <c r="T208" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U208" s="36" t="s">
+      <c r="U208" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W208" s="6" t="s">
@@ -20677,73 +20676,73 @@
     </row>
     <row r="209" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A209" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C209" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C209" s="37" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D209" s="37" t="s">
         <v>1484</v>
-      </c>
-      <c r="D209" s="36" t="s">
-        <v>1485</v>
       </c>
       <c r="E209" s="6">
         <v>6</v>
       </c>
       <c r="F209" s="6" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G209" s="38" t="s">
         <v>1486</v>
       </c>
-      <c r="G209" s="37" t="s">
+      <c r="H209" s="38" t="s">
         <v>1487</v>
       </c>
-      <c r="H209" s="37" t="s">
+      <c r="I209" s="38" t="s">
         <v>1488</v>
       </c>
-      <c r="I209" s="37" t="s">
+      <c r="J209" s="38" t="s">
         <v>1489</v>
       </c>
-      <c r="J209" s="37" t="s">
+      <c r="K209" s="38" t="s">
         <v>1490</v>
       </c>
-      <c r="K209" s="37" t="s">
-        <v>1491</v>
-      </c>
       <c r="L209" s="6">
-        <f t="shared" si="77"/>
-        <v>59800</v>
+        <f t="shared" si="83"/>
+        <v>61400</v>
       </c>
       <c r="M209" s="6">
-        <f t="shared" si="78"/>
-        <v>59800</v>
+        <f t="shared" si="84"/>
+        <v>61400</v>
       </c>
       <c r="N209" s="6">
-        <f t="shared" si="79"/>
-        <v>29850</v>
+        <f t="shared" si="85"/>
+        <v>30850</v>
       </c>
       <c r="O209" s="6">
-        <f t="shared" si="80"/>
-        <v>29850</v>
+        <f t="shared" si="86"/>
+        <v>30850</v>
       </c>
       <c r="P209" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>240</v>
       </c>
       <c r="Q209" s="7">
-        <f t="shared" si="81"/>
-        <v>353</v>
+        <f t="shared" si="87"/>
+        <v>383</v>
       </c>
       <c r="R209" s="7">
-        <f t="shared" si="82"/>
-        <v>289</v>
+        <f t="shared" si="88"/>
+        <v>509</v>
       </c>
       <c r="S209" s="7">
         <v>99.99</v>
       </c>
-      <c r="T209" s="36" t="s">
+      <c r="T209" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U209" s="36" t="s">
+      <c r="U209" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W209" s="6" t="s">
@@ -20757,73 +20756,73 @@
     </row>
     <row r="210" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A210" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C210" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C210" s="37" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D210" s="37" t="s">
         <v>1492</v>
-      </c>
-      <c r="D210" s="36" t="s">
-        <v>1493</v>
       </c>
       <c r="E210" s="6">
         <v>6</v>
       </c>
       <c r="F210" s="6" t="s">
+        <v>1493</v>
+      </c>
+      <c r="G210" s="38" t="s">
+        <v>1322</v>
+      </c>
+      <c r="H210" s="38" t="s">
         <v>1494</v>
       </c>
-      <c r="G210" s="37" t="s">
-        <v>1323</v>
-      </c>
-      <c r="H210" s="37" t="s">
+      <c r="I210" s="38" t="s">
         <v>1495</v>
       </c>
-      <c r="I210" s="37" t="s">
+      <c r="J210" s="38" t="s">
         <v>1496</v>
       </c>
-      <c r="J210" s="37" t="s">
+      <c r="K210" s="38" t="s">
         <v>1497</v>
       </c>
-      <c r="K210" s="37" t="s">
-        <v>1498</v>
-      </c>
       <c r="L210" s="6">
-        <f t="shared" si="77"/>
-        <v>60400</v>
+        <f t="shared" si="83"/>
+        <v>62000</v>
       </c>
       <c r="M210" s="6">
-        <f t="shared" si="78"/>
-        <v>60400</v>
+        <f t="shared" si="84"/>
+        <v>62000</v>
       </c>
       <c r="N210" s="6">
-        <f t="shared" si="79"/>
-        <v>30250</v>
+        <f t="shared" si="85"/>
+        <v>31250</v>
       </c>
       <c r="O210" s="6">
-        <f t="shared" si="80"/>
-        <v>30250</v>
+        <f t="shared" si="86"/>
+        <v>31250</v>
       </c>
       <c r="P210" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>245</v>
       </c>
       <c r="Q210" s="7">
-        <f t="shared" si="81"/>
-        <v>359</v>
+        <f t="shared" si="87"/>
+        <v>389</v>
       </c>
       <c r="R210" s="7">
-        <f t="shared" si="82"/>
-        <v>296</v>
+        <f t="shared" si="88"/>
+        <v>516</v>
       </c>
       <c r="S210" s="7">
         <v>99.99</v>
       </c>
-      <c r="T210" s="36" t="s">
+      <c r="T210" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U210" s="36" t="s">
+      <c r="U210" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W210" s="6" t="s">
@@ -20837,73 +20836,73 @@
     </row>
     <row r="211" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A211" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C211" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C211" s="37" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D211" s="37" t="s">
         <v>1499</v>
-      </c>
-      <c r="D211" s="36" t="s">
-        <v>1500</v>
       </c>
       <c r="E211" s="6">
         <v>6</v>
       </c>
       <c r="F211" s="6" t="s">
+        <v>1500</v>
+      </c>
+      <c r="G211" s="38" t="s">
+        <v>1330</v>
+      </c>
+      <c r="H211" s="38" t="s">
         <v>1501</v>
       </c>
-      <c r="G211" s="37" t="s">
-        <v>1331</v>
-      </c>
-      <c r="H211" s="37" t="s">
+      <c r="I211" s="38" t="s">
         <v>1502</v>
       </c>
-      <c r="I211" s="37" t="s">
+      <c r="J211" s="38" t="s">
         <v>1503</v>
       </c>
-      <c r="J211" s="37" t="s">
+      <c r="K211" s="38" t="s">
         <v>1504</v>
       </c>
-      <c r="K211" s="37" t="s">
-        <v>1505</v>
-      </c>
       <c r="L211" s="6">
-        <f t="shared" si="77"/>
-        <v>61000</v>
+        <f t="shared" si="83"/>
+        <v>62600</v>
       </c>
       <c r="M211" s="6">
-        <f t="shared" si="78"/>
-        <v>61000</v>
+        <f t="shared" si="84"/>
+        <v>62600</v>
       </c>
       <c r="N211" s="6">
-        <f t="shared" ref="N211:N215" si="83">N210+500</f>
-        <v>30750</v>
+        <f t="shared" ref="N211:N215" si="89">N210+500</f>
+        <v>31750</v>
       </c>
       <c r="O211" s="6">
-        <f t="shared" ref="O211:O215" si="84">O210+500</f>
-        <v>30750</v>
+        <f t="shared" ref="O211:O215" si="90">O210+500</f>
+        <v>31750</v>
       </c>
       <c r="P211" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>250</v>
       </c>
       <c r="Q211" s="7">
-        <f t="shared" ref="Q211:Q215" si="85">Q210+7</f>
-        <v>366</v>
+        <f t="shared" ref="Q211:Q215" si="91">Q210+7</f>
+        <v>396</v>
       </c>
       <c r="R211" s="7">
-        <f t="shared" ref="R211:R215" si="86">R210+8</f>
-        <v>304</v>
+        <f t="shared" ref="R211:R215" si="92">R210+8</f>
+        <v>524</v>
       </c>
       <c r="S211" s="7">
         <v>99.99</v>
       </c>
-      <c r="T211" s="36" t="s">
+      <c r="T211" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U211" s="36" t="s">
+      <c r="U211" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W211" s="6" t="s">
@@ -20917,73 +20916,73 @@
     </row>
     <row r="212" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A212" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C212" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C212" s="37" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D212" s="37" t="s">
         <v>1506</v>
-      </c>
-      <c r="D212" s="36" t="s">
-        <v>1507</v>
       </c>
       <c r="E212" s="6">
         <v>6</v>
       </c>
       <c r="F212" s="6" t="s">
+        <v>1507</v>
+      </c>
+      <c r="G212" s="38" t="s">
+        <v>1338</v>
+      </c>
+      <c r="H212" s="38" t="s">
         <v>1508</v>
       </c>
-      <c r="G212" s="37" t="s">
-        <v>1339</v>
-      </c>
-      <c r="H212" s="37" t="s">
+      <c r="I212" s="38" t="s">
         <v>1509</v>
       </c>
-      <c r="I212" s="37" t="s">
+      <c r="J212" s="38" t="s">
         <v>1510</v>
       </c>
-      <c r="J212" s="37" t="s">
+      <c r="K212" s="38" t="s">
         <v>1511</v>
       </c>
-      <c r="K212" s="37" t="s">
-        <v>1512</v>
-      </c>
       <c r="L212" s="6">
-        <f t="shared" si="77"/>
-        <v>61600</v>
+        <f t="shared" si="83"/>
+        <v>63200</v>
       </c>
       <c r="M212" s="6">
-        <f t="shared" si="78"/>
-        <v>61600</v>
+        <f t="shared" si="84"/>
+        <v>63200</v>
       </c>
       <c r="N212" s="6">
-        <f t="shared" si="83"/>
-        <v>31250</v>
+        <f t="shared" si="89"/>
+        <v>32250</v>
       </c>
       <c r="O212" s="6">
-        <f t="shared" si="84"/>
-        <v>31250</v>
+        <f t="shared" si="90"/>
+        <v>32250</v>
       </c>
       <c r="P212" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>255</v>
       </c>
       <c r="Q212" s="7">
-        <f t="shared" si="85"/>
-        <v>373</v>
+        <f t="shared" si="91"/>
+        <v>403</v>
       </c>
       <c r="R212" s="7">
-        <f t="shared" si="86"/>
-        <v>312</v>
+        <f t="shared" si="92"/>
+        <v>532</v>
       </c>
       <c r="S212" s="7">
         <v>99.99</v>
       </c>
-      <c r="T212" s="36" t="s">
+      <c r="T212" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U212" s="36" t="s">
+      <c r="U212" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W212" s="6" t="s">
@@ -20997,73 +20996,73 @@
     </row>
     <row r="213" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A213" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C213" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C213" s="37" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D213" s="37" t="s">
         <v>1513</v>
-      </c>
-      <c r="D213" s="36" t="s">
-        <v>1514</v>
       </c>
       <c r="E213" s="6">
         <v>6</v>
       </c>
       <c r="F213" s="6" t="s">
+        <v>1514</v>
+      </c>
+      <c r="G213" s="38" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H213" s="38" t="s">
         <v>1515</v>
       </c>
-      <c r="G213" s="37" t="s">
-        <v>1346</v>
-      </c>
-      <c r="H213" s="37" t="s">
+      <c r="I213" s="38" t="s">
         <v>1516</v>
       </c>
-      <c r="I213" s="37" t="s">
+      <c r="J213" s="38" t="s">
         <v>1517</v>
       </c>
-      <c r="J213" s="37" t="s">
+      <c r="K213" s="38" t="s">
         <v>1518</v>
       </c>
-      <c r="K213" s="37" t="s">
-        <v>1519</v>
-      </c>
       <c r="L213" s="6">
-        <f t="shared" si="77"/>
-        <v>62200</v>
+        <f t="shared" si="83"/>
+        <v>63800</v>
       </c>
       <c r="M213" s="6">
-        <f t="shared" si="78"/>
-        <v>62200</v>
+        <f t="shared" si="84"/>
+        <v>63800</v>
       </c>
       <c r="N213" s="6">
-        <f t="shared" si="83"/>
-        <v>31750</v>
+        <f t="shared" si="89"/>
+        <v>32750</v>
       </c>
       <c r="O213" s="6">
-        <f t="shared" si="84"/>
-        <v>31750</v>
+        <f t="shared" si="90"/>
+        <v>32750</v>
       </c>
       <c r="P213" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>260</v>
       </c>
       <c r="Q213" s="7">
-        <f t="shared" si="85"/>
-        <v>380</v>
+        <f t="shared" si="91"/>
+        <v>410</v>
       </c>
       <c r="R213" s="7">
-        <f t="shared" si="86"/>
-        <v>320</v>
+        <f t="shared" si="92"/>
+        <v>540</v>
       </c>
       <c r="S213" s="7">
         <v>99.99</v>
       </c>
-      <c r="T213" s="36" t="s">
+      <c r="T213" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U213" s="36" t="s">
+      <c r="U213" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W213" s="6" t="s">
@@ -21077,73 +21076,73 @@
     </row>
     <row r="214" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A214" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C214" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C214" s="37" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D214" s="37" t="s">
         <v>1520</v>
-      </c>
-      <c r="D214" s="36" t="s">
-        <v>1521</v>
       </c>
       <c r="E214" s="6">
         <v>6</v>
       </c>
       <c r="F214" s="6" t="s">
+        <v>1521</v>
+      </c>
+      <c r="G214" s="38" t="s">
+        <v>1352</v>
+      </c>
+      <c r="H214" s="38" t="s">
         <v>1522</v>
       </c>
-      <c r="G214" s="37" t="s">
-        <v>1353</v>
-      </c>
-      <c r="H214" s="37" t="s">
+      <c r="I214" s="38" t="s">
         <v>1523</v>
       </c>
-      <c r="I214" s="37" t="s">
+      <c r="J214" s="38" t="s">
+        <v>1325</v>
+      </c>
+      <c r="K214" s="38" t="s">
         <v>1524</v>
       </c>
-      <c r="J214" s="37" t="s">
-        <v>1326</v>
-      </c>
-      <c r="K214" s="37" t="s">
-        <v>1525</v>
-      </c>
       <c r="L214" s="6">
-        <f t="shared" si="77"/>
-        <v>62800</v>
+        <f t="shared" si="83"/>
+        <v>64400</v>
       </c>
       <c r="M214" s="6">
-        <f t="shared" si="78"/>
-        <v>62800</v>
+        <f t="shared" si="84"/>
+        <v>64400</v>
       </c>
       <c r="N214" s="6">
-        <f t="shared" si="83"/>
-        <v>32250</v>
+        <f t="shared" si="89"/>
+        <v>33250</v>
       </c>
       <c r="O214" s="6">
-        <f t="shared" si="84"/>
-        <v>32250</v>
+        <f t="shared" si="90"/>
+        <v>33250</v>
       </c>
       <c r="P214" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>265</v>
       </c>
       <c r="Q214" s="7">
-        <f t="shared" si="85"/>
-        <v>387</v>
+        <f t="shared" si="91"/>
+        <v>417</v>
       </c>
       <c r="R214" s="7">
-        <f t="shared" si="86"/>
-        <v>328</v>
+        <f t="shared" si="92"/>
+        <v>548</v>
       </c>
       <c r="S214" s="7">
         <v>99.99</v>
       </c>
-      <c r="T214" s="36" t="s">
+      <c r="T214" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U214" s="36" t="s">
+      <c r="U214" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W214" s="6" t="s">
@@ -21157,73 +21156,73 @@
     </row>
     <row r="215" s="6" customFormat="1" customHeight="1" spans="1:26">
       <c r="A215" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C215" s="36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C215" s="37" t="s">
+        <v>1525</v>
+      </c>
+      <c r="D215" s="37" t="s">
         <v>1526</v>
-      </c>
-      <c r="D215" s="36" t="s">
-        <v>1527</v>
       </c>
       <c r="E215" s="6">
         <v>6</v>
       </c>
       <c r="F215" s="6" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G215" s="38" t="s">
+        <v>1359</v>
+      </c>
+      <c r="H215" s="38" t="s">
         <v>1528</v>
       </c>
-      <c r="G215" s="37" t="s">
-        <v>1360</v>
-      </c>
-      <c r="H215" s="37" t="s">
+      <c r="I215" s="38" t="s">
         <v>1529</v>
       </c>
-      <c r="I215" s="37" t="s">
+      <c r="J215" s="38" t="s">
+        <v>1333</v>
+      </c>
+      <c r="K215" s="38" t="s">
         <v>1530</v>
       </c>
-      <c r="J215" s="37" t="s">
-        <v>1334</v>
-      </c>
-      <c r="K215" s="37" t="s">
-        <v>1531</v>
-      </c>
       <c r="L215" s="6">
-        <f t="shared" si="77"/>
-        <v>63400</v>
+        <f t="shared" si="83"/>
+        <v>65000</v>
       </c>
       <c r="M215" s="6">
-        <f t="shared" si="78"/>
-        <v>63400</v>
+        <f t="shared" si="84"/>
+        <v>65000</v>
       </c>
       <c r="N215" s="6">
-        <f t="shared" si="83"/>
-        <v>32750</v>
+        <f t="shared" si="89"/>
+        <v>33750</v>
       </c>
       <c r="O215" s="6">
-        <f t="shared" si="84"/>
-        <v>32750</v>
+        <f t="shared" si="90"/>
+        <v>33750</v>
       </c>
       <c r="P215" s="6">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>270</v>
       </c>
       <c r="Q215" s="7">
-        <f t="shared" si="85"/>
-        <v>394</v>
+        <f t="shared" si="91"/>
+        <v>424</v>
       </c>
       <c r="R215" s="7">
-        <f t="shared" si="86"/>
-        <v>336</v>
+        <f t="shared" si="92"/>
+        <v>556</v>
       </c>
       <c r="S215" s="7">
         <v>99.99</v>
       </c>
-      <c r="T215" s="36" t="s">
+      <c r="T215" s="37" t="s">
         <v>1274</v>
       </c>
-      <c r="U215" s="36" t="s">
+      <c r="U215" s="37" t="s">
         <v>1274</v>
       </c>
       <c r="W215" s="6" t="s">

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -21337,7 +21337,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="K3:K5 C3:J5 L3:Q5 R3:T5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:T5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2111" uniqueCount="1556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2111" uniqueCount="1555">
   <si>
     <t>ID</t>
   </si>
@@ -3931,570 +3931,573 @@
     <t>1E+143</t>
   </si>
   <si>
+    <t>1E+41</t>
+  </si>
+  <si>
+    <t>1E+1</t>
+  </si>
+  <si>
+    <t>1E+75</t>
+  </si>
+  <si>
+    <t>14000000000000</t>
+  </si>
+  <si>
+    <t>10176</t>
+  </si>
+  <si>
+    <t>1176</t>
+  </si>
+  <si>
+    <t>混沌鹿王</t>
+  </si>
+  <si>
+    <t>1E+91</t>
+  </si>
+  <si>
+    <t>1E+117</t>
+  </si>
+  <si>
+    <t>1E+147</t>
+  </si>
+  <si>
+    <t>1E+43</t>
+  </si>
+  <si>
+    <t>1E+2</t>
+  </si>
+  <si>
+    <t>1E+79</t>
+  </si>
+  <si>
+    <t>14500000000000</t>
+  </si>
+  <si>
+    <t>10177</t>
+  </si>
+  <si>
+    <t>1177</t>
+  </si>
+  <si>
+    <t>混沌草王</t>
+  </si>
+  <si>
+    <t>1E+95</t>
+  </si>
+  <si>
+    <t>1E+121</t>
+  </si>
+  <si>
+    <t>1E+151</t>
+  </si>
+  <si>
+    <t>1E+45</t>
+  </si>
+  <si>
+    <t>1E+3</t>
+  </si>
+  <si>
+    <t>1E+83</t>
+  </si>
+  <si>
+    <t>10178</t>
+  </si>
+  <si>
+    <t>1178</t>
+  </si>
+  <si>
+    <t>混沌猫王</t>
+  </si>
+  <si>
+    <t>1E+99</t>
+  </si>
+  <si>
+    <t>1E+125</t>
+  </si>
+  <si>
+    <t>1E+155</t>
+  </si>
+  <si>
     <t>1E+47</t>
   </si>
   <si>
-    <t>1E+1</t>
-  </si>
-  <si>
-    <t>1E+75</t>
-  </si>
-  <si>
-    <t>14000000000000</t>
-  </si>
-  <si>
-    <t>10176</t>
-  </si>
-  <si>
-    <t>1176</t>
-  </si>
-  <si>
-    <t>混沌鹿王</t>
-  </si>
-  <si>
-    <t>1E+91</t>
-  </si>
-  <si>
-    <t>1E+117</t>
-  </si>
-  <si>
-    <t>1E+147</t>
-  </si>
-  <si>
-    <t>1E+50</t>
-  </si>
-  <si>
-    <t>1E+2</t>
-  </si>
-  <si>
-    <t>1E+79</t>
-  </si>
-  <si>
-    <t>14500000000000</t>
-  </si>
-  <si>
-    <t>10177</t>
-  </si>
-  <si>
-    <t>1177</t>
-  </si>
-  <si>
-    <t>混沌草王</t>
-  </si>
-  <si>
-    <t>1E+95</t>
-  </si>
-  <si>
-    <t>1E+121</t>
-  </si>
-  <si>
-    <t>1E+151</t>
+    <t>1E+4</t>
+  </si>
+  <si>
+    <t>15500000000000</t>
+  </si>
+  <si>
+    <t>10179</t>
+  </si>
+  <si>
+    <t>1179</t>
+  </si>
+  <si>
+    <t>混沌花王</t>
+  </si>
+  <si>
+    <t>1E+103</t>
+  </si>
+  <si>
+    <t>1E+129</t>
+  </si>
+  <si>
+    <t>1E+158</t>
+  </si>
+  <si>
+    <t>1E+49</t>
+  </si>
+  <si>
+    <t>1E+5</t>
+  </si>
+  <si>
+    <t>16000000000000</t>
+  </si>
+  <si>
+    <t>10180</t>
+  </si>
+  <si>
+    <t>1180</t>
+  </si>
+  <si>
+    <t>混沌雪王</t>
+  </si>
+  <si>
+    <t>1E+106</t>
+  </si>
+  <si>
+    <t>9E+131</t>
+  </si>
+  <si>
+    <t>1E+161</t>
+  </si>
+  <si>
+    <t>1E+51</t>
+  </si>
+  <si>
+    <t>1E+7</t>
+  </si>
+  <si>
+    <t>1E+94</t>
+  </si>
+  <si>
+    <t>16500000000000</t>
+  </si>
+  <si>
+    <t>10181</t>
+  </si>
+  <si>
+    <t>1181</t>
+  </si>
+  <si>
+    <t>混沌蝠王</t>
+  </si>
+  <si>
+    <t>1E+109</t>
+  </si>
+  <si>
+    <t>9E+134</t>
+  </si>
+  <si>
+    <t>1E+164</t>
   </si>
   <si>
     <t>1E+53</t>
   </si>
   <si>
-    <t>1E+3</t>
-  </si>
-  <si>
-    <t>1E+83</t>
-  </si>
-  <si>
-    <t>10178</t>
-  </si>
-  <si>
-    <t>1178</t>
-  </si>
-  <si>
-    <t>混沌猫王</t>
-  </si>
-  <si>
-    <t>1E+99</t>
-  </si>
-  <si>
-    <t>1E+125</t>
-  </si>
-  <si>
-    <t>1E+155</t>
-  </si>
-  <si>
-    <t>1E+56</t>
-  </si>
-  <si>
-    <t>1E+4</t>
-  </si>
-  <si>
-    <t>15500000000000</t>
-  </si>
-  <si>
-    <t>10179</t>
-  </si>
-  <si>
-    <t>1179</t>
-  </si>
-  <si>
-    <t>混沌花王</t>
-  </si>
-  <si>
-    <t>1E+103</t>
-  </si>
-  <si>
-    <t>1E+129</t>
-  </si>
-  <si>
-    <t>1E+158</t>
+    <t>1E+9</t>
+  </si>
+  <si>
+    <t>1E+97</t>
+  </si>
+  <si>
+    <t>17000000000000</t>
+  </si>
+  <si>
+    <t>10182</t>
+  </si>
+  <si>
+    <t>1182</t>
+  </si>
+  <si>
+    <t>混沌骷髅王</t>
+  </si>
+  <si>
+    <t>1E+112</t>
+  </si>
+  <si>
+    <t>9E+137</t>
+  </si>
+  <si>
+    <t>1E+167</t>
+  </si>
+  <si>
+    <t>1E+55</t>
+  </si>
+  <si>
+    <t>1E+11</t>
+  </si>
+  <si>
+    <t>1E+100</t>
+  </si>
+  <si>
+    <t>17500000000000</t>
+  </si>
+  <si>
+    <t>10183</t>
+  </si>
+  <si>
+    <t>1183</t>
+  </si>
+  <si>
+    <t>混沌尸王</t>
+  </si>
+  <si>
+    <t>1E+115</t>
+  </si>
+  <si>
+    <t>9E+140</t>
+  </si>
+  <si>
+    <t>1E+170</t>
+  </si>
+  <si>
+    <t>1E+57</t>
+  </si>
+  <si>
+    <t>1E+13</t>
+  </si>
+  <si>
+    <t>18000000000000</t>
+  </si>
+  <si>
+    <t>10184</t>
+  </si>
+  <si>
+    <t>1184</t>
+  </si>
+  <si>
+    <t>混沌蛇王</t>
+  </si>
+  <si>
+    <t>1E+118</t>
+  </si>
+  <si>
+    <t>9E+143</t>
+  </si>
+  <si>
+    <t>1E+173</t>
   </si>
   <si>
     <t>1E+59</t>
   </si>
   <si>
-    <t>1E+5</t>
-  </si>
-  <si>
-    <t>16000000000000</t>
-  </si>
-  <si>
-    <t>10180</t>
-  </si>
-  <si>
-    <t>1180</t>
-  </si>
-  <si>
-    <t>混沌雪王</t>
-  </si>
-  <si>
-    <t>1E+106</t>
-  </si>
-  <si>
-    <t>9E+131</t>
-  </si>
-  <si>
-    <t>1E+161</t>
-  </si>
-  <si>
-    <t>1E+7</t>
-  </si>
-  <si>
-    <t>1E+94</t>
-  </si>
-  <si>
-    <t>16500000000000</t>
-  </si>
-  <si>
-    <t>10181</t>
-  </si>
-  <si>
-    <t>1181</t>
-  </si>
-  <si>
-    <t>混沌蝠王</t>
-  </si>
-  <si>
-    <t>1E+109</t>
-  </si>
-  <si>
-    <t>9E+134</t>
-  </si>
-  <si>
-    <t>1E+164</t>
+    <t>1E+15</t>
+  </si>
+  <si>
+    <t>18500000000000</t>
+  </si>
+  <si>
+    <t>10185</t>
+  </si>
+  <si>
+    <t>1185</t>
+  </si>
+  <si>
+    <t>混沌狼王</t>
+  </si>
+  <si>
+    <t>1E+120</t>
+  </si>
+  <si>
+    <t>1E+176</t>
+  </si>
+  <si>
+    <t>1E+17</t>
+  </si>
+  <si>
+    <t>1E+108</t>
+  </si>
+  <si>
+    <t>19000000000000</t>
+  </si>
+  <si>
+    <t>10186</t>
+  </si>
+  <si>
+    <t>1186</t>
+  </si>
+  <si>
+    <t>混沌沙虫王</t>
+  </si>
+  <si>
+    <t>1E+122</t>
+  </si>
+  <si>
+    <t>1E+179</t>
   </si>
   <si>
     <t>1E+63</t>
   </si>
   <si>
-    <t>1E+9</t>
-  </si>
-  <si>
-    <t>1E+97</t>
-  </si>
-  <si>
-    <t>17000000000000</t>
-  </si>
-  <si>
-    <t>10182</t>
-  </si>
-  <si>
-    <t>1182</t>
-  </si>
-  <si>
-    <t>混沌骷髅王</t>
-  </si>
-  <si>
-    <t>1E+112</t>
-  </si>
-  <si>
-    <t>9E+137</t>
-  </si>
-  <si>
-    <t>1E+167</t>
+    <t>1E+19</t>
+  </si>
+  <si>
+    <t>1E+110</t>
+  </si>
+  <si>
+    <t>19500000000000</t>
+  </si>
+  <si>
+    <t>10187</t>
+  </si>
+  <si>
+    <t>1187</t>
+  </si>
+  <si>
+    <t>混沌鹰王</t>
+  </si>
+  <si>
+    <t>1E+124</t>
+  </si>
+  <si>
+    <t>1E+182</t>
   </si>
   <si>
     <t>1E+65</t>
   </si>
   <si>
-    <t>1E+11</t>
-  </si>
-  <si>
-    <t>1E+100</t>
-  </si>
-  <si>
-    <t>17500000000000</t>
-  </si>
-  <si>
-    <t>10183</t>
-  </si>
-  <si>
-    <t>1183</t>
-  </si>
-  <si>
-    <t>混沌尸王</t>
-  </si>
-  <si>
-    <t>1E+115</t>
-  </si>
-  <si>
-    <t>9E+140</t>
-  </si>
-  <si>
-    <t>1E+170</t>
+    <t>1E+21</t>
+  </si>
+  <si>
+    <t>20000000000000</t>
+  </si>
+  <si>
+    <t>10188</t>
+  </si>
+  <si>
+    <t>1188</t>
+  </si>
+  <si>
+    <t>混沌角虫王</t>
+  </si>
+  <si>
+    <t>1E+185</t>
   </si>
   <si>
     <t>1E+67</t>
   </si>
   <si>
-    <t>1E+13</t>
-  </si>
-  <si>
-    <t>18000000000000</t>
-  </si>
-  <si>
-    <t>10184</t>
-  </si>
-  <si>
-    <t>1184</t>
-  </si>
-  <si>
-    <t>混沌蛇王</t>
-  </si>
-  <si>
-    <t>1E+118</t>
-  </si>
-  <si>
-    <t>9E+143</t>
-  </si>
-  <si>
-    <t>1E+173</t>
+    <t>1E+23</t>
+  </si>
+  <si>
+    <t>1E+114</t>
+  </si>
+  <si>
+    <t>21000000000000</t>
+  </si>
+  <si>
+    <t>10189</t>
+  </si>
+  <si>
+    <t>1189</t>
+  </si>
+  <si>
+    <t>混沌蜈蚣王</t>
+  </si>
+  <si>
+    <t>1E+128</t>
+  </si>
+  <si>
+    <t>1E+188</t>
   </si>
   <si>
     <t>1E+69</t>
   </si>
   <si>
-    <t>1E+15</t>
-  </si>
-  <si>
-    <t>18500000000000</t>
-  </si>
-  <si>
-    <t>10185</t>
-  </si>
-  <si>
-    <t>1185</t>
-  </si>
-  <si>
-    <t>混沌狼王</t>
-  </si>
-  <si>
-    <t>1E+120</t>
-  </si>
-  <si>
-    <t>1E+176</t>
+    <t>1E+25</t>
+  </si>
+  <si>
+    <t>1E+116</t>
+  </si>
+  <si>
+    <t>10190</t>
+  </si>
+  <si>
+    <t>1190</t>
+  </si>
+  <si>
+    <t>混沌钳虫王</t>
+  </si>
+  <si>
+    <t>1E+130</t>
+  </si>
+  <si>
+    <t>1E+190</t>
+  </si>
+  <si>
+    <t>1E+70</t>
+  </si>
+  <si>
+    <t>1E+28</t>
+  </si>
+  <si>
+    <t>23000000000000</t>
+  </si>
+  <si>
+    <t>10191</t>
+  </si>
+  <si>
+    <t>1191</t>
+  </si>
+  <si>
+    <t>混沌蠕虫王</t>
+  </si>
+  <si>
+    <t>1E+132</t>
+  </si>
+  <si>
+    <t>1E+192</t>
   </si>
   <si>
     <t>1E+71</t>
   </si>
   <si>
-    <t>1E+17</t>
-  </si>
-  <si>
-    <t>1E+108</t>
-  </si>
-  <si>
-    <t>19000000000000</t>
-  </si>
-  <si>
-    <t>10186</t>
-  </si>
-  <si>
-    <t>1186</t>
-  </si>
-  <si>
-    <t>混沌沙虫王</t>
-  </si>
-  <si>
-    <t>1E+122</t>
-  </si>
-  <si>
-    <t>1E+179</t>
+    <t>1E+31</t>
+  </si>
+  <si>
+    <t>24000000000000</t>
+  </si>
+  <si>
+    <t>10192</t>
+  </si>
+  <si>
+    <t>1192</t>
+  </si>
+  <si>
+    <t>混沌猪王</t>
+  </si>
+  <si>
+    <t>1E+134</t>
+  </si>
+  <si>
+    <t>1E+194</t>
+  </si>
+  <si>
+    <t>1E+72</t>
+  </si>
+  <si>
+    <t>1E+34</t>
+  </si>
+  <si>
+    <t>25000000000000</t>
+  </si>
+  <si>
+    <t>10193</t>
+  </si>
+  <si>
+    <t>1193</t>
+  </si>
+  <si>
+    <t>混沌猪皇</t>
+  </si>
+  <si>
+    <t>1E+136</t>
+  </si>
+  <si>
+    <t>1E+196</t>
   </si>
   <si>
     <t>1E+73</t>
   </si>
   <si>
-    <t>1E+19</t>
-  </si>
-  <si>
-    <t>1E+110</t>
-  </si>
-  <si>
-    <t>19500000000000</t>
-  </si>
-  <si>
-    <t>10187</t>
-  </si>
-  <si>
-    <t>1187</t>
-  </si>
-  <si>
-    <t>混沌鹰王</t>
-  </si>
-  <si>
-    <t>1E+124</t>
-  </si>
-  <si>
-    <t>1E+182</t>
-  </si>
-  <si>
-    <t>1E+21</t>
-  </si>
-  <si>
-    <t>20000000000000</t>
-  </si>
-  <si>
-    <t>10188</t>
-  </si>
-  <si>
-    <t>1188</t>
-  </si>
-  <si>
-    <t>混沌角虫王</t>
-  </si>
-  <si>
-    <t>1E+185</t>
+    <t>1E+37</t>
+  </si>
+  <si>
+    <t>26000000000000</t>
+  </si>
+  <si>
+    <t>10194</t>
+  </si>
+  <si>
+    <t>1194</t>
+  </si>
+  <si>
+    <t>混沌蝎王</t>
+  </si>
+  <si>
+    <t>1E+138</t>
+  </si>
+  <si>
+    <t>1E+198</t>
+  </si>
+  <si>
+    <t>1E+74</t>
+  </si>
+  <si>
+    <t>1E+40</t>
+  </si>
+  <si>
+    <t>27000000000000</t>
+  </si>
+  <si>
+    <t>10195</t>
+  </si>
+  <si>
+    <t>1195</t>
+  </si>
+  <si>
+    <t>混沌恶魔教主</t>
+  </si>
+  <si>
+    <t>1E+200</t>
+  </si>
+  <si>
+    <t>28000000000000</t>
+  </si>
+  <si>
+    <t>10196</t>
+  </si>
+  <si>
+    <t>1196</t>
+  </si>
+  <si>
+    <t>混沌恶魔教皇</t>
+  </si>
+  <si>
+    <t>9E+142</t>
+  </si>
+  <si>
+    <t>1E+202</t>
+  </si>
+  <si>
+    <t>1E+76</t>
+  </si>
+  <si>
+    <t>1E+46</t>
+  </si>
+  <si>
+    <t>29000000000000</t>
+  </si>
+  <si>
+    <t>10197</t>
+  </si>
+  <si>
+    <t>1197</t>
+  </si>
+  <si>
+    <t>混沌邪魔教主</t>
+  </si>
+  <si>
+    <t>9E+144</t>
+  </si>
+  <si>
+    <t>1E+204</t>
   </si>
   <si>
     <t>1E+77</t>
   </si>
   <si>
-    <t>1E+23</t>
-  </si>
-  <si>
-    <t>1E+114</t>
-  </si>
-  <si>
-    <t>21000000000000</t>
-  </si>
-  <si>
-    <t>10189</t>
-  </si>
-  <si>
-    <t>1189</t>
-  </si>
-  <si>
-    <t>混沌蜈蚣王</t>
-  </si>
-  <si>
-    <t>1E+128</t>
-  </si>
-  <si>
-    <t>1E+188</t>
-  </si>
-  <si>
-    <t>1E+25</t>
-  </si>
-  <si>
-    <t>1E+116</t>
-  </si>
-  <si>
-    <t>10190</t>
-  </si>
-  <si>
-    <t>1190</t>
-  </si>
-  <si>
-    <t>混沌钳虫王</t>
-  </si>
-  <si>
-    <t>1E+130</t>
-  </si>
-  <si>
-    <t>1E+190</t>
-  </si>
-  <si>
-    <t>1E+80</t>
-  </si>
-  <si>
-    <t>1E+28</t>
-  </si>
-  <si>
-    <t>23000000000000</t>
-  </si>
-  <si>
-    <t>10191</t>
-  </si>
-  <si>
-    <t>1191</t>
-  </si>
-  <si>
-    <t>混沌蠕虫王</t>
-  </si>
-  <si>
-    <t>1E+132</t>
-  </si>
-  <si>
-    <t>1E+192</t>
-  </si>
-  <si>
-    <t>1E+81</t>
-  </si>
-  <si>
-    <t>1E+31</t>
-  </si>
-  <si>
-    <t>24000000000000</t>
-  </si>
-  <si>
-    <t>10192</t>
-  </si>
-  <si>
-    <t>1192</t>
-  </si>
-  <si>
-    <t>混沌猪王</t>
-  </si>
-  <si>
-    <t>1E+134</t>
-  </si>
-  <si>
-    <t>1E+194</t>
-  </si>
-  <si>
-    <t>1E+82</t>
-  </si>
-  <si>
-    <t>1E+34</t>
-  </si>
-  <si>
-    <t>25000000000000</t>
-  </si>
-  <si>
-    <t>10193</t>
-  </si>
-  <si>
-    <t>1193</t>
-  </si>
-  <si>
-    <t>混沌猪皇</t>
-  </si>
-  <si>
-    <t>1E+136</t>
-  </si>
-  <si>
-    <t>1E+196</t>
-  </si>
-  <si>
-    <t>1E+37</t>
-  </si>
-  <si>
-    <t>26000000000000</t>
-  </si>
-  <si>
-    <t>10194</t>
-  </si>
-  <si>
-    <t>1194</t>
-  </si>
-  <si>
-    <t>混沌蝎王</t>
-  </si>
-  <si>
-    <t>1E+138</t>
-  </si>
-  <si>
-    <t>1E+198</t>
-  </si>
-  <si>
-    <t>1E+84</t>
-  </si>
-  <si>
-    <t>1E+40</t>
-  </si>
-  <si>
-    <t>27000000000000</t>
-  </si>
-  <si>
-    <t>10195</t>
-  </si>
-  <si>
-    <t>1195</t>
-  </si>
-  <si>
-    <t>混沌恶魔教主</t>
-  </si>
-  <si>
-    <t>1E+200</t>
-  </si>
-  <si>
-    <t>1E+85</t>
-  </si>
-  <si>
-    <t>1E+43</t>
-  </si>
-  <si>
-    <t>28000000000000</t>
-  </si>
-  <si>
-    <t>10196</t>
-  </si>
-  <si>
-    <t>1196</t>
-  </si>
-  <si>
-    <t>混沌恶魔教皇</t>
-  </si>
-  <si>
-    <t>9E+142</t>
-  </si>
-  <si>
-    <t>1E+202</t>
-  </si>
-  <si>
-    <t>1E+86</t>
-  </si>
-  <si>
-    <t>1E+46</t>
-  </si>
-  <si>
-    <t>29000000000000</t>
-  </si>
-  <si>
-    <t>10197</t>
-  </si>
-  <si>
-    <t>1197</t>
-  </si>
-  <si>
-    <t>混沌邪魔教主</t>
-  </si>
-  <si>
-    <t>9E+144</t>
-  </si>
-  <si>
-    <t>1E+204</t>
-  </si>
-  <si>
-    <t>1E+49</t>
-  </si>
-  <si>
     <t>10198</t>
   </si>
   <si>
@@ -4510,7 +4513,7 @@
     <t>1E+206</t>
   </si>
   <si>
-    <t>1E+88</t>
+    <t>1E+78</t>
   </si>
   <si>
     <t>1E+52</t>
@@ -4532,12 +4535,6 @@
   </si>
   <si>
     <t>1E+208</t>
-  </si>
-  <si>
-    <t>1E+89</t>
-  </si>
-  <si>
-    <t>1E+55</t>
   </si>
   <si>
     <t>32000000000000</t>
@@ -19049,13 +19046,13 @@
         <v>1328</v>
       </c>
       <c r="J186" s="45" t="s">
-        <v>1220</v>
+        <v>1329</v>
       </c>
       <c r="K186" s="43" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="L186" s="45" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="M186" s="6">
         <f t="shared" si="50"/>
@@ -19089,10 +19086,10 @@
         <v>99.99</v>
       </c>
       <c r="U186" s="44" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="V186" s="44" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="X186" s="6" t="s">
         <v>158</v>
@@ -19107,34 +19104,34 @@
       <c r="A187" s="26"/>
       <c r="B187" s="26"/>
       <c r="C187" s="44" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="D187" s="44" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="E187" s="6">
         <v>6</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="G187" s="39" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H187" s="45" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="I187" s="45" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="J187" s="45" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="K187" s="43" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="L187" s="45" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="M187" s="6">
         <f t="shared" si="50"/>
@@ -19168,10 +19165,10 @@
         <v>99.99</v>
       </c>
       <c r="U187" s="44" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="V187" s="44" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="X187" s="6" t="s">
         <v>158</v>
@@ -19186,34 +19183,34 @@
       <c r="A188" s="26"/>
       <c r="B188" s="26"/>
       <c r="C188" s="44" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="D188" s="44" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="E188" s="6">
         <v>6</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="G188" s="39" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H188" s="45" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="I188" s="45" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="J188" s="45" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="K188" s="43" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="L188" s="45" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="M188" s="6">
         <f t="shared" si="50"/>
@@ -19247,10 +19244,10 @@
         <v>99.99</v>
       </c>
       <c r="U188" s="44" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="V188" s="44" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="X188" s="6" t="s">
         <v>158</v>
@@ -19265,31 +19262,31 @@
       <c r="A189" s="26"/>
       <c r="B189" s="26"/>
       <c r="C189" s="44" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="D189" s="44" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="E189" s="6">
         <v>6</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="G189" s="39" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H189" s="45" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="I189" s="45" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="J189" s="45" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="K189" s="43" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="L189" s="45" t="s">
         <v>1317</v>
@@ -19326,10 +19323,10 @@
         <v>99.99</v>
       </c>
       <c r="U189" s="44" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="V189" s="44" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="X189" s="6" t="s">
         <v>158</v>
@@ -19344,31 +19341,31 @@
       <c r="A190" s="26"/>
       <c r="B190" s="26"/>
       <c r="C190" s="44" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="D190" s="44" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="E190" s="6">
         <v>6</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="G190" s="39" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H190" s="45" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="I190" s="45" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="J190" s="45" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="K190" s="43" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="L190" s="45" t="s">
         <v>1326</v>
@@ -19405,10 +19402,10 @@
         <v>99.99</v>
       </c>
       <c r="U190" s="44" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="V190" s="44" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="X190" s="6" t="s">
         <v>158</v>
@@ -19423,28 +19420,28 @@
       <c r="A191" s="26"/>
       <c r="B191" s="26"/>
       <c r="C191" s="44" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="D191" s="44" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="E191" s="6">
         <v>6</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="G191" s="39" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="H191" s="45" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="I191" s="45" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="J191" s="45" t="s">
-        <v>1375</v>
+        <v>1220</v>
       </c>
       <c r="K191" s="43" t="s">
         <v>1376</v>
@@ -19517,7 +19514,7 @@
         <v>1382</v>
       </c>
       <c r="H192" s="45" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="I192" s="45" t="s">
         <v>1383</v>
@@ -19596,19 +19593,19 @@
         <v>1391</v>
       </c>
       <c r="H193" s="45" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="I193" s="45" t="s">
         <v>1392</v>
       </c>
       <c r="J193" s="45" t="s">
-        <v>1284</v>
+        <v>1393</v>
       </c>
       <c r="K193" s="43" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="L193" s="45" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="M193" s="6">
         <f t="shared" si="50"/>
@@ -19642,10 +19639,10 @@
         <v>99.99</v>
       </c>
       <c r="U193" s="44" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="V193" s="44" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="X193" s="6" t="s">
         <v>158</v>
@@ -19660,34 +19657,34 @@
       <c r="A194" s="26"/>
       <c r="B194" s="26"/>
       <c r="C194" s="44" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="D194" s="44" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="E194" s="6">
         <v>6</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="G194" s="39" t="s">
         <v>1191</v>
       </c>
       <c r="H194" s="45" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="I194" s="45" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="J194" s="45" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="K194" s="43" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="L194" s="45" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="M194" s="6">
         <f t="shared" si="50"/>
@@ -19721,10 +19718,10 @@
         <v>99.99</v>
       </c>
       <c r="U194" s="44" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="V194" s="44" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="X194" s="6" t="s">
         <v>158</v>
@@ -19739,34 +19736,34 @@
       <c r="A195" s="26"/>
       <c r="B195" s="26"/>
       <c r="C195" s="44" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="D195" s="44" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="E195" s="6">
         <v>6</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="G195" s="39" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H195" s="45" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="I195" s="45" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="J195" s="45" t="s">
-        <v>1294</v>
+        <v>1409</v>
       </c>
       <c r="K195" s="43" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="L195" s="45" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="M195" s="6">
         <f t="shared" si="50"/>
@@ -19818,34 +19815,34 @@
       <c r="A196" s="26"/>
       <c r="B196" s="26"/>
       <c r="C196" s="44" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="D196" s="44" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="E196" s="6">
         <v>6</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="G196" s="39" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="H196" s="45" t="s">
+        <v>1366</v>
+      </c>
+      <c r="I196" s="45" t="s">
+        <v>1416</v>
+      </c>
+      <c r="J196" s="45" t="s">
+        <v>1417</v>
+      </c>
+      <c r="K196" s="43" t="s">
+        <v>1418</v>
+      </c>
+      <c r="L196" s="45" t="s">
         <v>1365</v>
-      </c>
-      <c r="I196" s="45" t="s">
-        <v>1414</v>
-      </c>
-      <c r="J196" s="45" t="s">
-        <v>1415</v>
-      </c>
-      <c r="K196" s="43" t="s">
-        <v>1416</v>
-      </c>
-      <c r="L196" s="45" t="s">
-        <v>1364</v>
       </c>
       <c r="M196" s="6">
         <f t="shared" si="50"/>
@@ -19879,10 +19876,10 @@
         <v>99.99</v>
       </c>
       <c r="U196" s="44" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="V196" s="44" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="X196" s="6" t="s">
         <v>158</v>
@@ -19897,34 +19894,34 @@
       <c r="A197" s="9"/>
       <c r="B197" s="9"/>
       <c r="C197" s="46" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="D197" s="46" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="E197" s="7">
         <v>6</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="G197" s="39" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="H197" s="45" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="I197" s="45" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="J197" s="45" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="K197" s="43" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="L197" s="45" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="M197" s="7">
         <f t="shared" si="50"/>
@@ -19958,10 +19955,10 @@
         <v>99.99</v>
       </c>
       <c r="U197" s="46" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="V197" s="46" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="X197" s="7" t="s">
         <v>158</v>
@@ -19976,31 +19973,31 @@
       <c r="A198" s="9"/>
       <c r="B198" s="9"/>
       <c r="C198" s="46" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="D198" s="46" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="E198" s="7">
         <v>6</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="G198" s="39" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="H198" s="45" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="I198" s="45" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="J198" s="45" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="K198" s="43" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="L198" s="45" t="s">
         <v>1382</v>
@@ -20037,10 +20034,10 @@
         <v>99.99</v>
       </c>
       <c r="U198" s="46" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="V198" s="46" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="X198" s="7" t="s">
         <v>158</v>
@@ -20055,31 +20052,31 @@
       <c r="A199" s="9"/>
       <c r="B199" s="9"/>
       <c r="C199" s="46" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="D199" s="46" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="E199" s="7">
         <v>6</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="G199" s="39" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="H199" s="45" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="I199" s="45" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="J199" s="45" t="s">
-        <v>1304</v>
+        <v>1441</v>
       </c>
       <c r="K199" s="43" t="s">
-        <v>1439</v>
+        <v>1442</v>
       </c>
       <c r="L199" s="45" t="s">
         <v>1391</v>
@@ -20116,10 +20113,10 @@
         <v>99.99</v>
       </c>
       <c r="U199" s="46" t="s">
-        <v>1440</v>
+        <v>1443</v>
       </c>
       <c r="V199" s="46" t="s">
-        <v>1440</v>
+        <v>1443</v>
       </c>
       <c r="X199" s="7" t="s">
         <v>158</v>
@@ -20134,31 +20131,31 @@
       <c r="A200" s="9"/>
       <c r="B200" s="9"/>
       <c r="C200" s="46" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
       <c r="D200" s="46" t="s">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="E200" s="7">
         <v>6</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>1443</v>
+        <v>1446</v>
       </c>
       <c r="G200" s="39" t="s">
-        <v>1444</v>
+        <v>1447</v>
       </c>
       <c r="H200" s="45" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="I200" s="45" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="J200" s="45" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="K200" s="43" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="L200" s="45" t="s">
         <v>1191</v>
@@ -20195,10 +20192,10 @@
         <v>99.99</v>
       </c>
       <c r="U200" s="46" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="V200" s="46" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="X200" s="7" t="s">
         <v>158</v>
@@ -20211,34 +20208,34 @@
     </row>
     <row r="201" s="8" customFormat="1" customHeight="1" spans="1:27">
       <c r="C201" s="47" t="s">
-        <v>1449</v>
+        <v>1452</v>
       </c>
       <c r="D201" s="47" t="s">
-        <v>1450</v>
+        <v>1453</v>
       </c>
       <c r="E201" s="28">
         <v>6</v>
       </c>
       <c r="F201" s="28" t="s">
-        <v>1451</v>
+        <v>1454</v>
       </c>
       <c r="G201" s="48" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H201" s="45" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="I201" s="45" t="s">
-        <v>1452</v>
+        <v>1455</v>
       </c>
       <c r="J201" s="45" t="s">
-        <v>1453</v>
+        <v>1284</v>
       </c>
       <c r="K201" s="43" t="s">
-        <v>1454</v>
+        <v>1292</v>
       </c>
       <c r="L201" s="45" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="M201" s="7">
         <f t="shared" ref="M201:M205" si="77">M200+5000</f>
@@ -20272,10 +20269,10 @@
         <v>99.99</v>
       </c>
       <c r="U201" s="46" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="V201" s="46" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="W201" s="28"/>
       <c r="X201" s="28" t="s">
@@ -20287,34 +20284,34 @@
     </row>
     <row r="202" s="9" customFormat="1" customHeight="1" spans="1:27">
       <c r="C202" s="46" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="D202" s="46" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="E202" s="7">
         <v>6</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="G202" s="45" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H202" s="45" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="I202" s="45" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="J202" s="45" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="K202" s="43" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="L202" s="45" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="M202" s="7">
         <f t="shared" si="77"/>
@@ -20348,10 +20345,10 @@
         <v>99.99</v>
       </c>
       <c r="U202" s="46" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="V202" s="46" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="W202" s="7"/>
       <c r="X202" s="7" t="s">
@@ -20363,34 +20360,34 @@
     </row>
     <row r="203" s="9" customFormat="1" customHeight="1" spans="1:27">
       <c r="C203" s="46" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="D203" s="46" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="E203" s="7">
         <v>6</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="G203" s="45" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H203" s="45" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="I203" s="45" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="J203" s="45" t="s">
-        <v>1279</v>
+        <v>1470</v>
       </c>
       <c r="K203" s="43" t="s">
-        <v>1469</v>
+        <v>1320</v>
       </c>
       <c r="L203" s="45" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="M203" s="7">
         <f t="shared" si="77"/>
@@ -20439,34 +20436,34 @@
     </row>
     <row r="204" s="9" customFormat="1" customHeight="1" spans="1:27">
       <c r="C204" s="46" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="D204" s="46" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="E204" s="7">
         <v>6</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="G204" s="45" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H204" s="45" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="I204" s="45" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="J204" s="45" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="K204" s="43" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="L204" s="45" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="M204" s="7">
         <f t="shared" si="77"/>
@@ -20500,10 +20497,10 @@
         <v>99.99</v>
       </c>
       <c r="U204" s="46" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="V204" s="46" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="W204" s="7"/>
       <c r="X204" s="7" t="s">
@@ -20515,34 +20512,34 @@
     </row>
     <row r="205" s="9" customFormat="1" customHeight="1" spans="1:27">
       <c r="C205" s="46" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="D205" s="46" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="E205" s="7">
         <v>6</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="G205" s="45" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="H205" s="45" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="I205" s="45" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="J205" s="45" t="s">
-        <v>1483</v>
+        <v>1294</v>
       </c>
       <c r="K205" s="43" t="s">
-        <v>1484</v>
+        <v>1349</v>
       </c>
       <c r="L205" s="45" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="M205" s="7">
         <f t="shared" si="77"/>
@@ -20576,10 +20573,10 @@
         <v>99.99</v>
       </c>
       <c r="U205" s="46" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="V205" s="46" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="W205" s="7"/>
       <c r="X205" s="7" t="s">
@@ -20591,37 +20588,37 @@
     </row>
     <row r="206" s="10" customFormat="1" customHeight="1" spans="1:27">
       <c r="A206" s="30" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B206" s="30" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C206" s="49" t="s">
         <v>1486</v>
       </c>
-      <c r="B206" s="30" t="s">
-        <v>1486</v>
-      </c>
-      <c r="C206" s="49" t="s">
+      <c r="D206" s="49" t="s">
         <v>1487</v>
-      </c>
-      <c r="D206" s="49" t="s">
-        <v>1488</v>
       </c>
       <c r="E206" s="10">
         <v>6</v>
       </c>
       <c r="F206" s="10" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G206" s="50" t="s">
         <v>1489</v>
       </c>
-      <c r="G206" s="50" t="s">
+      <c r="H206" s="45" t="s">
+        <v>1366</v>
+      </c>
+      <c r="I206" s="50" t="s">
         <v>1490</v>
       </c>
-      <c r="H206" s="45" t="s">
-        <v>1365</v>
-      </c>
-      <c r="I206" s="50" t="s">
+      <c r="J206" s="50" t="s">
         <v>1491</v>
       </c>
-      <c r="J206" s="50" t="s">
+      <c r="L206" s="50" t="s">
         <v>1492</v>
-      </c>
-      <c r="L206" s="50" t="s">
-        <v>1493</v>
       </c>
       <c r="M206" s="10">
         <f t="shared" ref="M205:M215" si="84">M205+600</f>
@@ -20671,37 +20668,37 @@
     </row>
     <row r="207" s="10" customFormat="1" customHeight="1" spans="1:27">
       <c r="A207" s="30" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B207" s="30" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C207" s="49" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D207" s="49" t="s">
         <v>1494</v>
-      </c>
-      <c r="D207" s="49" t="s">
-        <v>1495</v>
       </c>
       <c r="E207" s="10">
         <v>6</v>
       </c>
       <c r="F207" s="10" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G207" s="50" t="s">
         <v>1496</v>
       </c>
-      <c r="G207" s="50" t="s">
+      <c r="H207" s="45" t="s">
+        <v>1366</v>
+      </c>
+      <c r="I207" s="50" t="s">
         <v>1497</v>
       </c>
-      <c r="H207" s="45" t="s">
-        <v>1365</v>
-      </c>
-      <c r="I207" s="50" t="s">
+      <c r="J207" s="50" t="s">
         <v>1498</v>
       </c>
-      <c r="J207" s="50" t="s">
+      <c r="L207" s="50" t="s">
         <v>1499</v>
-      </c>
-      <c r="L207" s="50" t="s">
-        <v>1500</v>
       </c>
       <c r="M207" s="10">
         <f t="shared" si="84"/>
@@ -20751,37 +20748,37 @@
     </row>
     <row r="208" s="10" customFormat="1" customHeight="1" spans="1:27">
       <c r="A208" s="30" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B208" s="30" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C208" s="49" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D208" s="49" t="s">
         <v>1501</v>
-      </c>
-      <c r="D208" s="49" t="s">
-        <v>1502</v>
       </c>
       <c r="E208" s="10">
         <v>6</v>
       </c>
       <c r="F208" s="10" t="s">
+        <v>1502</v>
+      </c>
+      <c r="G208" s="50" t="s">
         <v>1503</v>
       </c>
-      <c r="G208" s="50" t="s">
+      <c r="H208" s="45" t="s">
+        <v>1366</v>
+      </c>
+      <c r="I208" s="50" t="s">
         <v>1504</v>
-      </c>
-      <c r="H208" s="45" t="s">
-        <v>1365</v>
-      </c>
-      <c r="I208" s="50" t="s">
-        <v>1505</v>
       </c>
       <c r="J208" s="50" t="s">
         <v>1274</v>
       </c>
       <c r="L208" s="50" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="M208" s="10">
         <f t="shared" si="84"/>
@@ -20831,37 +20828,37 @@
     </row>
     <row r="209" s="10" customFormat="1" customHeight="1" spans="1:27">
       <c r="A209" s="30" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B209" s="30" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C209" s="49" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D209" s="49" t="s">
         <v>1507</v>
-      </c>
-      <c r="D209" s="49" t="s">
-        <v>1508</v>
       </c>
       <c r="E209" s="10">
         <v>6</v>
       </c>
       <c r="F209" s="10" t="s">
+        <v>1508</v>
+      </c>
+      <c r="G209" s="50" t="s">
         <v>1509</v>
       </c>
-      <c r="G209" s="50" t="s">
+      <c r="H209" s="45" t="s">
+        <v>1366</v>
+      </c>
+      <c r="I209" s="50" t="s">
         <v>1510</v>
       </c>
-      <c r="H209" s="45" t="s">
-        <v>1365</v>
-      </c>
-      <c r="I209" s="50" t="s">
+      <c r="J209" s="50" t="s">
         <v>1511</v>
       </c>
-      <c r="J209" s="50" t="s">
+      <c r="L209" s="50" t="s">
         <v>1512</v>
-      </c>
-      <c r="L209" s="50" t="s">
-        <v>1513</v>
       </c>
       <c r="M209" s="10">
         <f t="shared" si="84"/>
@@ -20911,37 +20908,37 @@
     </row>
     <row r="210" s="10" customFormat="1" customHeight="1" spans="1:27">
       <c r="A210" s="30" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B210" s="30" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C210" s="49" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D210" s="49" t="s">
         <v>1514</v>
-      </c>
-      <c r="D210" s="49" t="s">
-        <v>1515</v>
       </c>
       <c r="E210" s="10">
         <v>6</v>
       </c>
       <c r="F210" s="10" t="s">
+        <v>1515</v>
+      </c>
+      <c r="G210" s="50" t="s">
         <v>1516</v>
       </c>
-      <c r="G210" s="50" t="s">
+      <c r="H210" s="45" t="s">
+        <v>1366</v>
+      </c>
+      <c r="I210" s="50" t="s">
         <v>1517</v>
       </c>
-      <c r="H210" s="45" t="s">
-        <v>1365</v>
-      </c>
-      <c r="I210" s="50" t="s">
+      <c r="J210" s="50" t="s">
         <v>1518</v>
       </c>
-      <c r="J210" s="50" t="s">
+      <c r="L210" s="50" t="s">
         <v>1519</v>
-      </c>
-      <c r="L210" s="50" t="s">
-        <v>1520</v>
       </c>
       <c r="M210" s="10">
         <f t="shared" si="84"/>
@@ -20991,37 +20988,37 @@
     </row>
     <row r="211" s="10" customFormat="1" customHeight="1" spans="1:27">
       <c r="A211" s="30" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B211" s="30" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C211" s="49" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D211" s="49" t="s">
         <v>1521</v>
-      </c>
-      <c r="D211" s="49" t="s">
-        <v>1522</v>
       </c>
       <c r="E211" s="10">
         <v>6</v>
       </c>
       <c r="F211" s="10" t="s">
+        <v>1522</v>
+      </c>
+      <c r="G211" s="50" t="s">
         <v>1523</v>
       </c>
-      <c r="G211" s="50" t="s">
+      <c r="H211" s="45" t="s">
+        <v>1366</v>
+      </c>
+      <c r="I211" s="50" t="s">
         <v>1524</v>
       </c>
-      <c r="H211" s="45" t="s">
-        <v>1365</v>
-      </c>
-      <c r="I211" s="50" t="s">
+      <c r="J211" s="50" t="s">
         <v>1525</v>
       </c>
-      <c r="J211" s="50" t="s">
+      <c r="L211" s="50" t="s">
         <v>1526</v>
-      </c>
-      <c r="L211" s="50" t="s">
-        <v>1527</v>
       </c>
       <c r="M211" s="10">
         <f t="shared" si="84"/>
@@ -21071,37 +21068,37 @@
     </row>
     <row r="212" s="10" customFormat="1" customHeight="1" spans="1:27">
       <c r="A212" s="30" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B212" s="30" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C212" s="49" t="s">
+        <v>1527</v>
+      </c>
+      <c r="D212" s="49" t="s">
         <v>1528</v>
-      </c>
-      <c r="D212" s="49" t="s">
-        <v>1529</v>
       </c>
       <c r="E212" s="10">
         <v>6</v>
       </c>
       <c r="F212" s="10" t="s">
+        <v>1529</v>
+      </c>
+      <c r="G212" s="50" t="s">
         <v>1530</v>
       </c>
-      <c r="G212" s="50" t="s">
+      <c r="H212" s="45" t="s">
+        <v>1366</v>
+      </c>
+      <c r="I212" s="50" t="s">
         <v>1531</v>
       </c>
-      <c r="H212" s="45" t="s">
-        <v>1365</v>
-      </c>
-      <c r="I212" s="50" t="s">
+      <c r="J212" s="50" t="s">
         <v>1532</v>
       </c>
-      <c r="J212" s="50" t="s">
+      <c r="L212" s="50" t="s">
         <v>1533</v>
-      </c>
-      <c r="L212" s="50" t="s">
-        <v>1534</v>
       </c>
       <c r="M212" s="10">
         <f t="shared" si="84"/>
@@ -21151,37 +21148,37 @@
     </row>
     <row r="213" s="10" customFormat="1" customHeight="1" spans="1:27">
       <c r="A213" s="30" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B213" s="30" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C213" s="49" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D213" s="49" t="s">
         <v>1535</v>
-      </c>
-      <c r="D213" s="49" t="s">
-        <v>1536</v>
       </c>
       <c r="E213" s="10">
         <v>6</v>
       </c>
       <c r="F213" s="10" t="s">
+        <v>1536</v>
+      </c>
+      <c r="G213" s="50" t="s">
         <v>1537</v>
       </c>
-      <c r="G213" s="50" t="s">
+      <c r="H213" s="45" t="s">
+        <v>1366</v>
+      </c>
+      <c r="I213" s="50" t="s">
         <v>1538</v>
       </c>
-      <c r="H213" s="45" t="s">
-        <v>1365</v>
-      </c>
-      <c r="I213" s="50" t="s">
+      <c r="J213" s="50" t="s">
         <v>1539</v>
       </c>
-      <c r="J213" s="50" t="s">
+      <c r="L213" s="50" t="s">
         <v>1540</v>
-      </c>
-      <c r="L213" s="50" t="s">
-        <v>1541</v>
       </c>
       <c r="M213" s="10">
         <f t="shared" si="84"/>
@@ -21231,37 +21228,37 @@
     </row>
     <row r="214" s="10" customFormat="1" customHeight="1" spans="1:27">
       <c r="A214" s="30" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B214" s="30" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C214" s="49" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D214" s="49" t="s">
         <v>1542</v>
-      </c>
-      <c r="D214" s="49" t="s">
-        <v>1543</v>
       </c>
       <c r="E214" s="10">
         <v>6</v>
       </c>
       <c r="F214" s="10" t="s">
+        <v>1543</v>
+      </c>
+      <c r="G214" s="50" t="s">
         <v>1544</v>
       </c>
-      <c r="G214" s="50" t="s">
+      <c r="H214" s="45" t="s">
+        <v>1366</v>
+      </c>
+      <c r="I214" s="50" t="s">
         <v>1545</v>
       </c>
-      <c r="H214" s="45" t="s">
-        <v>1365</v>
-      </c>
-      <c r="I214" s="50" t="s">
+      <c r="J214" s="50" t="s">
         <v>1546</v>
       </c>
-      <c r="J214" s="50" t="s">
+      <c r="L214" s="50" t="s">
         <v>1547</v>
-      </c>
-      <c r="L214" s="50" t="s">
-        <v>1548</v>
       </c>
       <c r="M214" s="10">
         <f t="shared" si="84"/>
@@ -21311,37 +21308,37 @@
     </row>
     <row r="215" s="10" customFormat="1" customHeight="1" spans="1:27">
       <c r="A215" s="30" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B215" s="30" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C215" s="49" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D215" s="49" t="s">
         <v>1549</v>
-      </c>
-      <c r="D215" s="49" t="s">
-        <v>1550</v>
       </c>
       <c r="E215" s="10">
         <v>6</v>
       </c>
       <c r="F215" s="10" t="s">
+        <v>1550</v>
+      </c>
+      <c r="G215" s="50" t="s">
         <v>1551</v>
       </c>
-      <c r="G215" s="50" t="s">
+      <c r="H215" s="45" t="s">
+        <v>1366</v>
+      </c>
+      <c r="I215" s="50" t="s">
         <v>1552</v>
       </c>
-      <c r="H215" s="45" t="s">
-        <v>1365</v>
-      </c>
-      <c r="I215" s="50" t="s">
+      <c r="J215" s="50" t="s">
         <v>1553</v>
       </c>
-      <c r="J215" s="50" t="s">
+      <c r="L215" s="50" t="s">
         <v>1554</v>
-      </c>
-      <c r="L215" s="50" t="s">
-        <v>1555</v>
       </c>
       <c r="M215" s="10">
         <f t="shared" si="84"/>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2571" uniqueCount="1689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2561" uniqueCount="1708">
   <si>
     <t>ID</t>
   </si>
@@ -4744,7 +4744,7 @@
     <t>虚无鸡王</t>
   </si>
   <si>
-    <t>1E+233</t>
+    <t>1E+231</t>
   </si>
   <si>
     <t>1E+93</t>
@@ -4768,7 +4768,10 @@
     <t>1E+205</t>
   </si>
   <si>
-    <t>1E+238</t>
+    <t>1E+234</t>
+  </si>
+  <si>
+    <t>1E+96</t>
   </si>
   <si>
     <t>44000000000000</t>
@@ -4783,193 +4786,247 @@
     <t>虚无草王</t>
   </si>
   <si>
+    <t>1E+237</t>
+  </si>
+  <si>
+    <t>45000000000000</t>
+  </si>
+  <si>
+    <t>10213</t>
+  </si>
+  <si>
+    <t>1213</t>
+  </si>
+  <si>
+    <t>虚无猫王</t>
+  </si>
+  <si>
+    <t>1E+215</t>
+  </si>
+  <si>
+    <t>1E+240</t>
+  </si>
+  <si>
+    <t>1E+102</t>
+  </si>
+  <si>
+    <t>1E+101</t>
+  </si>
+  <si>
+    <t>1E+195</t>
+  </si>
+  <si>
+    <t>46000000000000</t>
+  </si>
+  <si>
+    <t>10214</t>
+  </si>
+  <si>
+    <t>1214</t>
+  </si>
+  <si>
+    <t>虚无花王</t>
+  </si>
+  <si>
     <t>1E+243</t>
   </si>
   <si>
-    <t>1E+101</t>
-  </si>
-  <si>
-    <t>45000000000000</t>
-  </si>
-  <si>
-    <t>10213</t>
-  </si>
-  <si>
-    <t>1213</t>
-  </si>
-  <si>
-    <t>虚无猫王</t>
-  </si>
-  <si>
-    <t>1E+215</t>
+    <t>1E+105</t>
+  </si>
+  <si>
+    <t>47000000000000</t>
+  </si>
+  <si>
+    <t>10215</t>
+  </si>
+  <si>
+    <t>1215</t>
+  </si>
+  <si>
+    <t>虚无雪王</t>
+  </si>
+  <si>
+    <t>1E+225</t>
+  </si>
+  <si>
+    <t>1E+246</t>
+  </si>
+  <si>
+    <t>48000000000000</t>
+  </si>
+  <si>
+    <t>10216</t>
+  </si>
+  <si>
+    <t>1216</t>
+  </si>
+  <si>
+    <t>虚无蝠王</t>
+  </si>
+  <si>
+    <t>1E+230</t>
+  </si>
+  <si>
+    <t>1E+249</t>
+  </si>
+  <si>
+    <t>1E+111</t>
+  </si>
+  <si>
+    <t>49000000000000</t>
+  </si>
+  <si>
+    <t>10217</t>
+  </si>
+  <si>
+    <t>1217</t>
+  </si>
+  <si>
+    <t>虚无骷髅王</t>
+  </si>
+  <si>
+    <t>1E+235</t>
+  </si>
+  <si>
+    <t>1E+252</t>
+  </si>
+  <si>
+    <t>50000000000000</t>
+  </si>
+  <si>
+    <t>10218</t>
+  </si>
+  <si>
+    <t>1218</t>
+  </si>
+  <si>
+    <t>虚无尸王</t>
+  </si>
+  <si>
+    <t>1E+255</t>
+  </si>
+  <si>
+    <t>51000000000000</t>
+  </si>
+  <si>
+    <t>10219</t>
+  </si>
+  <si>
+    <t>1219</t>
+  </si>
+  <si>
+    <t>虚无蛇王</t>
+  </si>
+  <si>
+    <t>1E+245</t>
+  </si>
+  <si>
+    <t>1E+258</t>
+  </si>
+  <si>
+    <t>52000000000000</t>
+  </si>
+  <si>
+    <t>10220</t>
+  </si>
+  <si>
+    <t>1220</t>
+  </si>
+  <si>
+    <t>虚无狼王</t>
   </si>
   <si>
     <t>1E+248</t>
   </si>
   <si>
-    <t>1E+105</t>
-  </si>
-  <si>
-    <t>1E+195</t>
-  </si>
-  <si>
-    <t>46000000000000</t>
-  </si>
-  <si>
-    <t>10214</t>
-  </si>
-  <si>
-    <t>1214</t>
-  </si>
-  <si>
-    <t>虚无花王</t>
-  </si>
-  <si>
-    <t>1E+253</t>
-  </si>
-  <si>
-    <t>47000000000000</t>
-  </si>
-  <si>
-    <t>10215</t>
-  </si>
-  <si>
-    <t>1215</t>
-  </si>
-  <si>
-    <t>虚无雪王</t>
-  </si>
-  <si>
-    <t>1E+225</t>
+    <t>1E+261</t>
+  </si>
+  <si>
+    <t>1E+123</t>
+  </si>
+  <si>
+    <t>53000000000000</t>
+  </si>
+  <si>
+    <t>10221</t>
+  </si>
+  <si>
+    <t>1221</t>
+  </si>
+  <si>
+    <t>虚无沙虫王</t>
+  </si>
+  <si>
+    <t>1E+251</t>
+  </si>
+  <si>
+    <t>1E+264</t>
+  </si>
+  <si>
+    <t>54000000000000</t>
+  </si>
+  <si>
+    <t>10222</t>
+  </si>
+  <si>
+    <t>1222</t>
+  </si>
+  <si>
+    <t>虚无鹰王</t>
+  </si>
+  <si>
+    <t>1E+254</t>
+  </si>
+  <si>
+    <t>1E+267</t>
+  </si>
+  <si>
+    <t>55000000000000</t>
+  </si>
+  <si>
+    <t>10223</t>
+  </si>
+  <si>
+    <t>1223</t>
+  </si>
+  <si>
+    <t>虚无角虫王</t>
   </si>
   <si>
     <t>1E+257</t>
   </si>
   <si>
-    <t>48000000000000</t>
-  </si>
-  <si>
-    <t>10216</t>
-  </si>
-  <si>
-    <t>1216</t>
-  </si>
-  <si>
-    <t>虚无蝠王</t>
-  </si>
-  <si>
-    <t>1E+230</t>
-  </si>
-  <si>
-    <t>1E+261</t>
-  </si>
-  <si>
-    <t>1E+111</t>
-  </si>
-  <si>
-    <t>49000000000000</t>
-  </si>
-  <si>
-    <t>10217</t>
-  </si>
-  <si>
-    <t>1217</t>
-  </si>
-  <si>
-    <t>虚无骷髅王</t>
-  </si>
-  <si>
-    <t>1E+235</t>
-  </si>
-  <si>
-    <t>1E+265</t>
-  </si>
-  <si>
-    <t>50000000000000</t>
-  </si>
-  <si>
-    <t>10218</t>
-  </si>
-  <si>
-    <t>1218</t>
-  </si>
-  <si>
-    <t>虚无尸王</t>
-  </si>
-  <si>
-    <t>1E+240</t>
-  </si>
-  <si>
-    <t>1E+269</t>
-  </si>
-  <si>
-    <t>51000000000000</t>
-  </si>
-  <si>
-    <t>10219</t>
-  </si>
-  <si>
-    <t>1219</t>
-  </si>
-  <si>
-    <t>虚无蛇王</t>
-  </si>
-  <si>
-    <t>1E+245</t>
+    <t>1E+270</t>
+  </si>
+  <si>
+    <t>56000000000000</t>
+  </si>
+  <si>
+    <t>10224</t>
+  </si>
+  <si>
+    <t>1224</t>
+  </si>
+  <si>
+    <t>虚无蜈蚣王</t>
+  </si>
+  <si>
+    <t>1E+260</t>
   </si>
   <si>
     <t>1E+273</t>
   </si>
   <si>
-    <t>52000000000000</t>
+    <t>1E+135</t>
+  </si>
+  <si>
+    <t>1E+250</t>
+  </si>
+  <si>
+    <t>57000000000000</t>
   </si>
   <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>10220</t>
-  </si>
-  <si>
-    <t>1220</t>
-  </si>
-  <si>
-    <t>虚无狼王</t>
-  </si>
-  <si>
-    <t>10221</t>
-  </si>
-  <si>
-    <t>1221</t>
-  </si>
-  <si>
-    <t>虚无沙虫王</t>
-  </si>
-  <si>
-    <t>10222</t>
-  </si>
-  <si>
-    <t>1222</t>
-  </si>
-  <si>
-    <t>虚无鹰王</t>
-  </si>
-  <si>
-    <t>10223</t>
-  </si>
-  <si>
-    <t>1223</t>
-  </si>
-  <si>
-    <t>虚无角虫王</t>
-  </si>
-  <si>
-    <t>10224</t>
-  </si>
-  <si>
-    <t>1224</t>
-  </si>
-  <si>
-    <t>虚无蜈蚣王</t>
   </si>
   <si>
     <t>10225</t>
@@ -5857,7 +5914,7 @@
     <xf numFmtId="176" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -5891,10 +5948,10 @@
     <xf numFmtId="176" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -21437,7 +21494,7 @@
         <v>261</v>
       </c>
       <c r="R211" s="9">
-        <f t="shared" ref="R211:R225" si="92">R210+20</f>
+        <f t="shared" ref="R211:R230" si="92">R210+20</f>
         <v>604</v>
       </c>
       <c r="S211" s="9">
@@ -21802,33 +21859,33 @@
       <c r="I216" s="49" t="s">
         <v>1553</v>
       </c>
-      <c r="J216" s="49" t="s">
+      <c r="J216" s="43" t="s">
         <v>1554</v>
       </c>
-      <c r="K216" s="51" t="s">
+      <c r="K216" s="39" t="s">
         <v>1549</v>
       </c>
-      <c r="L216" s="49" t="s">
+      <c r="L216" s="43" t="s">
         <v>1555</v>
       </c>
       <c r="M216" s="28">
-        <f t="shared" ref="M216:M225" si="94">M215+30000</f>
+        <f t="shared" ref="M216:M230" si="94">M215+30000</f>
         <v>261000</v>
       </c>
       <c r="N216" s="28">
-        <f t="shared" ref="N216:N225" si="95">N215+30000</f>
+        <f t="shared" ref="N216:N230" si="95">N215+30000</f>
         <v>261000</v>
       </c>
       <c r="O216" s="28">
-        <f t="shared" ref="O216:O225" si="96">O215+30000</f>
+        <f t="shared" ref="O216:O230" si="96">O215+30000</f>
         <v>232750</v>
       </c>
       <c r="P216" s="28">
-        <f t="shared" ref="P216:P225" si="97">P215+30000</f>
+        <f t="shared" ref="P216:P230" si="97">P215+30000</f>
         <v>232750</v>
       </c>
       <c r="Q216" s="28">
-        <f t="shared" ref="Q216:Q225" si="98">Q215+7</f>
+        <f t="shared" ref="Q216:Q230" si="98">Q215+7</f>
         <v>292</v>
       </c>
       <c r="R216" s="27">
@@ -21836,7 +21893,7 @@
         <v>704</v>
       </c>
       <c r="S216" s="27">
-        <f t="shared" ref="S216:S225" si="99">S215+30</f>
+        <f t="shared" ref="S216:S230" si="99">S215+30</f>
         <v>826</v>
       </c>
       <c r="T216" s="27">
@@ -21879,8 +21936,8 @@
       <c r="I217" s="40" t="s">
         <v>1561</v>
       </c>
-      <c r="J217" s="40" t="s">
-        <v>1341</v>
+      <c r="J217" s="44" t="s">
+        <v>1562</v>
       </c>
       <c r="K217" s="44" t="s">
         <v>1554</v>
@@ -21920,10 +21977,10 @@
         <v>99.99</v>
       </c>
       <c r="U217" s="47" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="V217" s="47" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="X217" s="5" t="s">
         <v>158</v>
@@ -21936,16 +21993,16 @@
       <c r="A218" s="8"/>
       <c r="B218" s="8"/>
       <c r="C218" s="45" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="D218" s="47" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="E218" s="6">
         <v>7</v>
       </c>
       <c r="F218" s="5" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="G218" s="40" t="s">
         <v>1487</v>
@@ -21954,10 +22011,10 @@
         <v>1281</v>
       </c>
       <c r="I218" s="40" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="J218" s="40" t="s">
-        <v>1567</v>
+        <v>1308</v>
       </c>
       <c r="K218" s="40" t="s">
         <v>1341</v>
@@ -22037,10 +22094,10 @@
         <v>1574</v>
       </c>
       <c r="K219" s="40" t="s">
-        <v>1567</v>
+        <v>1575</v>
       </c>
       <c r="L219" s="40" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="M219" s="7">
         <f t="shared" si="94"/>
@@ -22074,10 +22131,10 @@
         <v>99.99</v>
       </c>
       <c r="U219" s="47" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="V219" s="47" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="X219" s="5" t="s">
         <v>158</v>
@@ -22088,16 +22145,16 @@
     </row>
     <row r="220" s="5" customFormat="1" customHeight="1" spans="1:27">
       <c r="C220" s="45" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="D220" s="47" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="E220" s="6">
         <v>7</v>
       </c>
       <c r="F220" s="5" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="G220" s="40" t="s">
         <v>1522</v>
@@ -22106,13 +22163,13 @@
         <v>1281</v>
       </c>
       <c r="I220" s="40" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="J220" s="40" t="s">
-        <v>1336</v>
+        <v>1582</v>
       </c>
       <c r="K220" s="40" t="s">
-        <v>1574</v>
+        <v>1582</v>
       </c>
       <c r="L220" s="40" t="s">
         <v>1453</v>
@@ -22149,10 +22206,10 @@
         <v>99.99</v>
       </c>
       <c r="U220" s="47" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="V220" s="47" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="X220" s="5" t="s">
         <v>158</v>
@@ -22165,28 +22222,28 @@
       <c r="A221" s="8"/>
       <c r="B221" s="8"/>
       <c r="C221" s="47" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="D221" s="47" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="E221" s="7">
         <v>7</v>
       </c>
       <c r="F221" s="6" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="G221" s="40" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="H221" s="46" t="s">
         <v>1281</v>
       </c>
       <c r="I221" s="40" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="J221" s="40" t="s">
-        <v>1346</v>
+        <v>1376</v>
       </c>
       <c r="K221" s="40" t="s">
         <v>1376</v>
@@ -22226,10 +22283,10 @@
         <v>99.99</v>
       </c>
       <c r="U221" s="47" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="V221" s="47" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="X221" s="3" t="s">
         <v>158</v>
@@ -22242,31 +22299,31 @@
       <c r="A222" s="8"/>
       <c r="B222" s="8"/>
       <c r="C222" s="47" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="D222" s="47" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="E222" s="7">
         <v>7</v>
       </c>
       <c r="F222" s="6" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="G222" s="40" t="s">
-        <v>1591</v>
-      </c>
-      <c r="H222" s="52" t="s">
+        <v>1593</v>
+      </c>
+      <c r="H222" s="46" t="s">
         <v>1281</v>
       </c>
       <c r="I222" s="40" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="J222" s="40" t="s">
-        <v>1356</v>
+        <v>1595</v>
       </c>
       <c r="K222" s="40" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="L222" s="40" t="s">
         <v>1487</v>
@@ -22303,13 +22360,13 @@
         <v>99.99</v>
       </c>
       <c r="U222" s="47" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="V222" s="47" t="s">
-        <v>1594</v>
-      </c>
-      <c r="W222" s="32"/>
-      <c r="X222" s="32" t="s">
+        <v>1596</v>
+      </c>
+      <c r="W222" s="5"/>
+      <c r="X222" s="5" t="s">
         <v>158</v>
       </c>
       <c r="Y222" s="3">
@@ -22320,28 +22377,28 @@
       <c r="A223" s="8"/>
       <c r="B223" s="8"/>
       <c r="C223" s="47" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="D223" s="47" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="E223" s="7">
         <v>7</v>
       </c>
       <c r="F223" s="6" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="G223" s="40" t="s">
-        <v>1598</v>
-      </c>
-      <c r="H223" s="52" t="s">
+        <v>1600</v>
+      </c>
+      <c r="H223" s="46" t="s">
         <v>1281</v>
       </c>
       <c r="I223" s="40" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="J223" s="40" t="s">
-        <v>1365</v>
+        <v>1401</v>
       </c>
       <c r="K223" s="40" t="s">
         <v>1401</v>
@@ -22381,13 +22438,13 @@
         <v>99.99</v>
       </c>
       <c r="U223" s="47" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="V223" s="47" t="s">
-        <v>1600</v>
-      </c>
-      <c r="W223" s="32"/>
-      <c r="X223" s="32" t="s">
+        <v>1602</v>
+      </c>
+      <c r="W223" s="5"/>
+      <c r="X223" s="5" t="s">
         <v>158</v>
       </c>
       <c r="Y223" s="3">
@@ -22398,28 +22455,28 @@
       <c r="A224" s="8"/>
       <c r="B224" s="8"/>
       <c r="C224" s="47" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="D224" s="47" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="E224" s="7">
         <v>7</v>
       </c>
       <c r="F224" s="6" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="G224" s="40" t="s">
-        <v>1604</v>
-      </c>
-      <c r="H224" s="52" t="s">
+        <v>1573</v>
+      </c>
+      <c r="H224" s="46" t="s">
         <v>1281</v>
       </c>
       <c r="I224" s="40" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="J224" s="40" t="s">
-        <v>1300</v>
+        <v>1290</v>
       </c>
       <c r="K224" s="40" t="s">
         <v>1290</v>
@@ -22459,13 +22516,13 @@
         <v>99.99</v>
       </c>
       <c r="U224" s="47" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="V224" s="47" t="s">
-        <v>1606</v>
-      </c>
-      <c r="W224" s="32"/>
-      <c r="X224" s="32" t="s">
+        <v>1607</v>
+      </c>
+      <c r="W224" s="5"/>
+      <c r="X224" s="5" t="s">
         <v>158</v>
       </c>
       <c r="Y224" s="3">
@@ -22476,34 +22533,34 @@
       <c r="A225" s="8"/>
       <c r="B225" s="8"/>
       <c r="C225" s="47" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="D225" s="47" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="E225" s="7">
         <v>7</v>
       </c>
       <c r="F225" s="6" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="G225" s="40" t="s">
-        <v>1610</v>
-      </c>
-      <c r="H225" s="52" t="s">
+        <v>1611</v>
+      </c>
+      <c r="H225" s="46" t="s">
         <v>1281</v>
       </c>
       <c r="I225" s="40" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="J225" s="40" t="s">
-        <v>1390</v>
+        <v>1373</v>
       </c>
       <c r="K225" s="40" t="s">
         <v>1373</v>
       </c>
       <c r="L225" s="40" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="M225" s="7">
         <f t="shared" si="94"/>
@@ -22537,13 +22594,13 @@
         <v>99.99</v>
       </c>
       <c r="U225" s="47" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="V225" s="47" t="s">
-        <v>1612</v>
-      </c>
-      <c r="W225" s="32"/>
-      <c r="X225" s="32" t="s">
+        <v>1613</v>
+      </c>
+      <c r="W225" s="5"/>
+      <c r="X225" s="5" t="s">
         <v>158</v>
       </c>
       <c r="Y225" s="3">
@@ -22551,12 +22608,8 @@
       </c>
     </row>
     <row r="226" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A226" s="8" t="s">
-        <v>1613</v>
-      </c>
-      <c r="B226" s="8" t="s">
-        <v>1613</v>
-      </c>
+      <c r="A226" s="8"/>
+      <c r="B226" s="8"/>
       <c r="C226" s="47" t="s">
         <v>1614</v>
       </c>
@@ -22569,55 +22622,60 @@
       <c r="F226" s="6" t="s">
         <v>1616</v>
       </c>
-      <c r="G226" s="43" t="s">
-        <v>1279</v>
+      <c r="G226" s="51" t="s">
+        <v>1617</v>
       </c>
       <c r="H226" s="46" t="s">
         <v>1281</v>
       </c>
-      <c r="I226" s="43" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J226" s="43" t="s">
-        <v>1282</v>
-      </c>
-      <c r="K226" s="39" t="s">
-        <v>1283</v>
-      </c>
-      <c r="L226" s="43" t="s">
-        <v>1284</v>
-      </c>
-      <c r="M226" s="3">
-        <v>43000</v>
-      </c>
-      <c r="N226" s="3">
-        <v>43000</v>
-      </c>
-      <c r="O226" s="3">
-        <v>22000</v>
-      </c>
-      <c r="P226" s="3">
-        <v>22000</v>
-      </c>
-      <c r="Q226" s="3">
-        <v>100</v>
-      </c>
-      <c r="R226" s="19">
-        <f t="shared" ref="R216:R250" si="100">R225+9</f>
-        <v>893</v>
-      </c>
-      <c r="S226" s="19">
-        <f t="shared" ref="S216:S250" si="101">S225+10</f>
-        <v>1106</v>
-      </c>
-      <c r="T226" s="19">
+      <c r="I226" s="40" t="s">
+        <v>1618</v>
+      </c>
+      <c r="J226" s="52" t="s">
+        <v>1619</v>
+      </c>
+      <c r="K226" s="52" t="s">
+        <v>1619</v>
+      </c>
+      <c r="L226" s="51" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M226" s="7">
+        <f t="shared" si="94"/>
+        <v>561000</v>
+      </c>
+      <c r="N226" s="7">
+        <f t="shared" si="95"/>
+        <v>561000</v>
+      </c>
+      <c r="O226" s="7">
+        <f t="shared" si="96"/>
+        <v>532750</v>
+      </c>
+      <c r="P226" s="7">
+        <f t="shared" si="97"/>
+        <v>532750</v>
+      </c>
+      <c r="Q226" s="6">
+        <f t="shared" si="98"/>
+        <v>362</v>
+      </c>
+      <c r="R226" s="9">
+        <f t="shared" si="92"/>
+        <v>904</v>
+      </c>
+      <c r="S226" s="9">
+        <f t="shared" si="99"/>
+        <v>1126</v>
+      </c>
+      <c r="T226" s="9">
         <v>99.99</v>
       </c>
-      <c r="U226" s="39" t="s">
-        <v>1285</v>
-      </c>
-      <c r="V226" s="39" t="s">
-        <v>1285</v>
+      <c r="U226" s="47" t="s">
+        <v>1620</v>
+      </c>
+      <c r="V226" s="47" t="s">
+        <v>1620</v>
       </c>
       <c r="X226" s="3" t="s">
         <v>158</v>
@@ -22627,73 +22685,74 @@
       </c>
     </row>
     <row r="227" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A227" s="8" t="s">
-        <v>1613</v>
-      </c>
-      <c r="B227" s="8" t="s">
-        <v>1613</v>
-      </c>
+      <c r="A227" s="8"/>
+      <c r="B227" s="8"/>
       <c r="C227" s="47" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="D227" s="47" t="s">
-        <v>1618</v>
+        <v>1622</v>
       </c>
       <c r="E227" s="7">
         <v>7</v>
       </c>
       <c r="F227" s="6" t="s">
-        <v>1619</v>
-      </c>
-      <c r="G227" s="43" t="s">
-        <v>1279</v>
+        <v>1623</v>
+      </c>
+      <c r="G227" s="51" t="s">
+        <v>1624</v>
       </c>
       <c r="H227" s="46" t="s">
         <v>1281</v>
       </c>
-      <c r="I227" s="43" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J227" s="43" t="s">
-        <v>1282</v>
-      </c>
-      <c r="K227" s="39" t="s">
-        <v>1283</v>
-      </c>
-      <c r="L227" s="43" t="s">
-        <v>1284</v>
-      </c>
-      <c r="M227" s="3">
-        <v>43000</v>
-      </c>
-      <c r="N227" s="3">
-        <v>43000</v>
-      </c>
-      <c r="O227" s="3">
-        <v>22000</v>
-      </c>
-      <c r="P227" s="3">
-        <v>22000</v>
-      </c>
-      <c r="Q227" s="3">
-        <v>100</v>
-      </c>
-      <c r="R227" s="19">
-        <f t="shared" si="100"/>
-        <v>902</v>
-      </c>
-      <c r="S227" s="19">
-        <f t="shared" si="101"/>
-        <v>1116</v>
-      </c>
-      <c r="T227" s="19">
+      <c r="I227" s="40" t="s">
+        <v>1625</v>
+      </c>
+      <c r="J227" s="52" t="s">
+        <v>1191</v>
+      </c>
+      <c r="K227" s="52" t="s">
+        <v>1191</v>
+      </c>
+      <c r="L227" s="51" t="s">
+        <v>1600</v>
+      </c>
+      <c r="M227" s="7">
+        <f t="shared" si="94"/>
+        <v>591000</v>
+      </c>
+      <c r="N227" s="7">
+        <f t="shared" si="95"/>
+        <v>591000</v>
+      </c>
+      <c r="O227" s="7">
+        <f t="shared" si="96"/>
+        <v>562750</v>
+      </c>
+      <c r="P227" s="7">
+        <f t="shared" si="97"/>
+        <v>562750</v>
+      </c>
+      <c r="Q227" s="6">
+        <f t="shared" si="98"/>
+        <v>369</v>
+      </c>
+      <c r="R227" s="9">
+        <f t="shared" si="92"/>
+        <v>924</v>
+      </c>
+      <c r="S227" s="9">
+        <f t="shared" si="99"/>
+        <v>1156</v>
+      </c>
+      <c r="T227" s="9">
         <v>99.99</v>
       </c>
-      <c r="U227" s="39" t="s">
-        <v>1285</v>
-      </c>
-      <c r="V227" s="39" t="s">
-        <v>1285</v>
+      <c r="U227" s="47" t="s">
+        <v>1626</v>
+      </c>
+      <c r="V227" s="47" t="s">
+        <v>1626</v>
       </c>
       <c r="X227" s="3" t="s">
         <v>158</v>
@@ -22703,73 +22762,74 @@
       </c>
     </row>
     <row r="228" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A228" s="8" t="s">
-        <v>1613</v>
-      </c>
-      <c r="B228" s="8" t="s">
-        <v>1613</v>
-      </c>
+      <c r="A228" s="8"/>
+      <c r="B228" s="8"/>
       <c r="C228" s="47" t="s">
-        <v>1620</v>
+        <v>1627</v>
       </c>
       <c r="D228" s="47" t="s">
-        <v>1621</v>
+        <v>1628</v>
       </c>
       <c r="E228" s="7">
         <v>7</v>
       </c>
       <c r="F228" s="6" t="s">
-        <v>1622</v>
-      </c>
-      <c r="G228" s="43" t="s">
-        <v>1279</v>
+        <v>1629</v>
+      </c>
+      <c r="G228" s="51" t="s">
+        <v>1630</v>
       </c>
       <c r="H228" s="46" t="s">
         <v>1281</v>
       </c>
-      <c r="I228" s="43" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J228" s="43" t="s">
-        <v>1282</v>
-      </c>
-      <c r="K228" s="39" t="s">
-        <v>1283</v>
-      </c>
-      <c r="L228" s="43" t="s">
-        <v>1284</v>
-      </c>
-      <c r="M228" s="3">
-        <v>43000</v>
-      </c>
-      <c r="N228" s="3">
-        <v>43000</v>
-      </c>
-      <c r="O228" s="3">
-        <v>22000</v>
-      </c>
-      <c r="P228" s="3">
-        <v>22000</v>
-      </c>
-      <c r="Q228" s="3">
-        <v>100</v>
-      </c>
-      <c r="R228" s="19">
-        <f t="shared" si="100"/>
-        <v>911</v>
-      </c>
-      <c r="S228" s="19">
-        <f t="shared" si="101"/>
-        <v>1126</v>
-      </c>
-      <c r="T228" s="19">
+      <c r="I228" s="40" t="s">
+        <v>1631</v>
+      </c>
+      <c r="J228" s="52" t="s">
+        <v>1318</v>
+      </c>
+      <c r="K228" s="52" t="s">
+        <v>1318</v>
+      </c>
+      <c r="L228" s="51" t="s">
+        <v>1573</v>
+      </c>
+      <c r="M228" s="7">
+        <f t="shared" si="94"/>
+        <v>621000</v>
+      </c>
+      <c r="N228" s="7">
+        <f t="shared" si="95"/>
+        <v>621000</v>
+      </c>
+      <c r="O228" s="7">
+        <f t="shared" si="96"/>
+        <v>592750</v>
+      </c>
+      <c r="P228" s="7">
+        <f t="shared" si="97"/>
+        <v>592750</v>
+      </c>
+      <c r="Q228" s="6">
+        <f t="shared" si="98"/>
+        <v>376</v>
+      </c>
+      <c r="R228" s="9">
+        <f t="shared" si="92"/>
+        <v>944</v>
+      </c>
+      <c r="S228" s="9">
+        <f t="shared" si="99"/>
+        <v>1186</v>
+      </c>
+      <c r="T228" s="9">
         <v>99.99</v>
       </c>
-      <c r="U228" s="39" t="s">
-        <v>1285</v>
-      </c>
-      <c r="V228" s="39" t="s">
-        <v>1285</v>
+      <c r="U228" s="47" t="s">
+        <v>1632</v>
+      </c>
+      <c r="V228" s="47" t="s">
+        <v>1632</v>
       </c>
       <c r="X228" s="3" t="s">
         <v>158</v>
@@ -22779,73 +22839,74 @@
       </c>
     </row>
     <row r="229" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A229" s="8" t="s">
-        <v>1613</v>
-      </c>
-      <c r="B229" s="8" t="s">
-        <v>1613</v>
-      </c>
+      <c r="A229" s="8"/>
+      <c r="B229" s="8"/>
       <c r="C229" s="47" t="s">
-        <v>1623</v>
+        <v>1633</v>
       </c>
       <c r="D229" s="47" t="s">
-        <v>1624</v>
+        <v>1634</v>
       </c>
       <c r="E229" s="7">
         <v>7</v>
       </c>
       <c r="F229" s="6" t="s">
-        <v>1625</v>
-      </c>
-      <c r="G229" s="43" t="s">
-        <v>1279</v>
+        <v>1635</v>
+      </c>
+      <c r="G229" s="51" t="s">
+        <v>1636</v>
       </c>
       <c r="H229" s="46" t="s">
         <v>1281</v>
       </c>
-      <c r="I229" s="43" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J229" s="43" t="s">
-        <v>1282</v>
-      </c>
-      <c r="K229" s="39" t="s">
-        <v>1283</v>
-      </c>
-      <c r="L229" s="43" t="s">
-        <v>1284</v>
-      </c>
-      <c r="M229" s="3">
-        <v>43000</v>
-      </c>
-      <c r="N229" s="3">
-        <v>43000</v>
-      </c>
-      <c r="O229" s="3">
-        <v>22000</v>
-      </c>
-      <c r="P229" s="3">
-        <v>22000</v>
-      </c>
-      <c r="Q229" s="3">
-        <v>100</v>
-      </c>
-      <c r="R229" s="19">
-        <f t="shared" si="100"/>
-        <v>920</v>
-      </c>
-      <c r="S229" s="19">
-        <f t="shared" si="101"/>
-        <v>1136</v>
-      </c>
-      <c r="T229" s="19">
+      <c r="I229" s="40" t="s">
+        <v>1637</v>
+      </c>
+      <c r="J229" s="52" t="s">
+        <v>1422</v>
+      </c>
+      <c r="K229" s="52" t="s">
+        <v>1422</v>
+      </c>
+      <c r="L229" s="51" t="s">
+        <v>1611</v>
+      </c>
+      <c r="M229" s="7">
+        <f t="shared" si="94"/>
+        <v>651000</v>
+      </c>
+      <c r="N229" s="7">
+        <f t="shared" si="95"/>
+        <v>651000</v>
+      </c>
+      <c r="O229" s="7">
+        <f t="shared" si="96"/>
+        <v>622750</v>
+      </c>
+      <c r="P229" s="7">
+        <f t="shared" si="97"/>
+        <v>622750</v>
+      </c>
+      <c r="Q229" s="6">
+        <f t="shared" si="98"/>
+        <v>383</v>
+      </c>
+      <c r="R229" s="9">
+        <f t="shared" si="92"/>
+        <v>964</v>
+      </c>
+      <c r="S229" s="9">
+        <f t="shared" si="99"/>
+        <v>1216</v>
+      </c>
+      <c r="T229" s="9">
         <v>99.99</v>
       </c>
-      <c r="U229" s="39" t="s">
-        <v>1285</v>
-      </c>
-      <c r="V229" s="39" t="s">
-        <v>1285</v>
+      <c r="U229" s="47" t="s">
+        <v>1638</v>
+      </c>
+      <c r="V229" s="47" t="s">
+        <v>1638</v>
       </c>
       <c r="X229" s="3" t="s">
         <v>158</v>
@@ -22855,73 +22916,74 @@
       </c>
     </row>
     <row r="230" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A230" s="8" t="s">
-        <v>1613</v>
-      </c>
-      <c r="B230" s="8" t="s">
-        <v>1613</v>
-      </c>
+      <c r="A230" s="8"/>
+      <c r="B230" s="8"/>
       <c r="C230" s="47" t="s">
-        <v>1626</v>
+        <v>1639</v>
       </c>
       <c r="D230" s="47" t="s">
-        <v>1627</v>
+        <v>1640</v>
       </c>
       <c r="E230" s="7">
         <v>7</v>
       </c>
       <c r="F230" s="6" t="s">
-        <v>1628</v>
-      </c>
-      <c r="G230" s="43" t="s">
-        <v>1279</v>
+        <v>1641</v>
+      </c>
+      <c r="G230" s="51" t="s">
+        <v>1642</v>
       </c>
       <c r="H230" s="46" t="s">
         <v>1281</v>
       </c>
-      <c r="I230" s="43" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J230" s="43" t="s">
-        <v>1282</v>
-      </c>
-      <c r="K230" s="39" t="s">
-        <v>1283</v>
-      </c>
-      <c r="L230" s="43" t="s">
-        <v>1284</v>
-      </c>
-      <c r="M230" s="3">
-        <v>43000</v>
-      </c>
-      <c r="N230" s="3">
-        <v>43000</v>
-      </c>
-      <c r="O230" s="3">
-        <v>22000</v>
-      </c>
-      <c r="P230" s="3">
-        <v>22000</v>
-      </c>
-      <c r="Q230" s="3">
-        <v>100</v>
-      </c>
-      <c r="R230" s="19">
-        <f t="shared" si="100"/>
-        <v>929</v>
-      </c>
-      <c r="S230" s="19">
-        <f t="shared" si="101"/>
-        <v>1146</v>
-      </c>
-      <c r="T230" s="19">
+      <c r="I230" s="40" t="s">
+        <v>1643</v>
+      </c>
+      <c r="J230" s="52" t="s">
+        <v>1644</v>
+      </c>
+      <c r="K230" s="52" t="s">
+        <v>1644</v>
+      </c>
+      <c r="L230" s="51" t="s">
+        <v>1645</v>
+      </c>
+      <c r="M230" s="7">
+        <f t="shared" si="94"/>
+        <v>681000</v>
+      </c>
+      <c r="N230" s="7">
+        <f t="shared" si="95"/>
+        <v>681000</v>
+      </c>
+      <c r="O230" s="7">
+        <f t="shared" si="96"/>
+        <v>652750</v>
+      </c>
+      <c r="P230" s="7">
+        <f t="shared" si="97"/>
+        <v>652750</v>
+      </c>
+      <c r="Q230" s="6">
+        <f t="shared" si="98"/>
+        <v>390</v>
+      </c>
+      <c r="R230" s="9">
+        <f t="shared" si="92"/>
+        <v>984</v>
+      </c>
+      <c r="S230" s="9">
+        <f t="shared" si="99"/>
+        <v>1246</v>
+      </c>
+      <c r="T230" s="9">
         <v>99.99</v>
       </c>
-      <c r="U230" s="39" t="s">
-        <v>1285</v>
-      </c>
-      <c r="V230" s="39" t="s">
-        <v>1285</v>
+      <c r="U230" s="47" t="s">
+        <v>1646</v>
+      </c>
+      <c r="V230" s="47" t="s">
+        <v>1646</v>
       </c>
       <c r="X230" s="3" t="s">
         <v>158</v>
@@ -22932,22 +22994,22 @@
     </row>
     <row r="231" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A231" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B231" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C231" s="47" t="s">
-        <v>1629</v>
+        <v>1648</v>
       </c>
       <c r="D231" s="47" t="s">
-        <v>1630</v>
+        <v>1649</v>
       </c>
       <c r="E231" s="7">
         <v>7</v>
       </c>
       <c r="F231" s="6" t="s">
-        <v>1631</v>
+        <v>1650</v>
       </c>
       <c r="G231" s="43" t="s">
         <v>1279</v>
@@ -22983,12 +23045,12 @@
         <v>100</v>
       </c>
       <c r="R231" s="19">
-        <f t="shared" si="100"/>
-        <v>938</v>
+        <f t="shared" ref="R216:R250" si="100">R230+9</f>
+        <v>993</v>
       </c>
       <c r="S231" s="19">
-        <f t="shared" si="101"/>
-        <v>1156</v>
+        <f t="shared" ref="S216:S250" si="101">S230+10</f>
+        <v>1256</v>
       </c>
       <c r="T231" s="19">
         <v>99.99</v>
@@ -23008,22 +23070,22 @@
     </row>
     <row r="232" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A232" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B232" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C232" s="47" t="s">
-        <v>1632</v>
+        <v>1651</v>
       </c>
       <c r="D232" s="47" t="s">
-        <v>1633</v>
+        <v>1652</v>
       </c>
       <c r="E232" s="7">
         <v>7</v>
       </c>
       <c r="F232" s="7" t="s">
-        <v>1634</v>
+        <v>1653</v>
       </c>
       <c r="G232" s="43" t="s">
         <v>1279</v>
@@ -23060,11 +23122,11 @@
       </c>
       <c r="R232" s="19">
         <f t="shared" si="100"/>
-        <v>947</v>
+        <v>1002</v>
       </c>
       <c r="S232" s="19">
         <f t="shared" si="101"/>
-        <v>1166</v>
+        <v>1266</v>
       </c>
       <c r="T232" s="19">
         <v>99.99</v>
@@ -23084,22 +23146,22 @@
     </row>
     <row r="233" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A233" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B233" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C233" s="47" t="s">
-        <v>1635</v>
+        <v>1654</v>
       </c>
       <c r="D233" s="47" t="s">
-        <v>1636</v>
+        <v>1655</v>
       </c>
       <c r="E233" s="7">
         <v>7</v>
       </c>
       <c r="F233" s="7" t="s">
-        <v>1637</v>
+        <v>1656</v>
       </c>
       <c r="G233" s="43" t="s">
         <v>1279</v>
@@ -23136,11 +23198,11 @@
       </c>
       <c r="R233" s="19">
         <f t="shared" si="100"/>
-        <v>956</v>
+        <v>1011</v>
       </c>
       <c r="S233" s="19">
         <f t="shared" si="101"/>
-        <v>1176</v>
+        <v>1276</v>
       </c>
       <c r="T233" s="19">
         <v>99.99</v>
@@ -23160,22 +23222,22 @@
     </row>
     <row r="234" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A234" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B234" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C234" s="47" t="s">
-        <v>1638</v>
+        <v>1657</v>
       </c>
       <c r="D234" s="47" t="s">
-        <v>1639</v>
+        <v>1658</v>
       </c>
       <c r="E234" s="7">
         <v>7</v>
       </c>
       <c r="F234" s="7" t="s">
-        <v>1640</v>
+        <v>1659</v>
       </c>
       <c r="G234" s="43" t="s">
         <v>1279</v>
@@ -23212,11 +23274,11 @@
       </c>
       <c r="R234" s="19">
         <f t="shared" si="100"/>
-        <v>965</v>
+        <v>1020</v>
       </c>
       <c r="S234" s="19">
         <f t="shared" si="101"/>
-        <v>1186</v>
+        <v>1286</v>
       </c>
       <c r="T234" s="19">
         <v>99.99</v>
@@ -23236,22 +23298,22 @@
     </row>
     <row r="235" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A235" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B235" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C235" s="47" t="s">
-        <v>1641</v>
+        <v>1660</v>
       </c>
       <c r="D235" s="47" t="s">
-        <v>1642</v>
+        <v>1661</v>
       </c>
       <c r="E235" s="7">
         <v>7</v>
       </c>
       <c r="F235" s="7" t="s">
-        <v>1643</v>
+        <v>1662</v>
       </c>
       <c r="G235" s="43" t="s">
         <v>1279</v>
@@ -23288,11 +23350,11 @@
       </c>
       <c r="R235" s="19">
         <f t="shared" si="100"/>
-        <v>974</v>
+        <v>1029</v>
       </c>
       <c r="S235" s="19">
         <f t="shared" si="101"/>
-        <v>1196</v>
+        <v>1296</v>
       </c>
       <c r="T235" s="19">
         <v>99.99</v>
@@ -23312,22 +23374,22 @@
     </row>
     <row r="236" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A236" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B236" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C236" s="47" t="s">
-        <v>1644</v>
+        <v>1663</v>
       </c>
       <c r="D236" s="47" t="s">
-        <v>1645</v>
+        <v>1664</v>
       </c>
       <c r="E236" s="7">
         <v>7</v>
       </c>
       <c r="F236" s="6" t="s">
-        <v>1646</v>
+        <v>1665</v>
       </c>
       <c r="G236" s="43" t="s">
         <v>1279</v>
@@ -23364,11 +23426,11 @@
       </c>
       <c r="R236" s="19">
         <f t="shared" si="100"/>
-        <v>983</v>
+        <v>1038</v>
       </c>
       <c r="S236" s="19">
         <f t="shared" si="101"/>
-        <v>1206</v>
+        <v>1306</v>
       </c>
       <c r="T236" s="19">
         <v>99.99</v>
@@ -23388,22 +23450,22 @@
     </row>
     <row r="237" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A237" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B237" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C237" s="47" t="s">
-        <v>1647</v>
+        <v>1666</v>
       </c>
       <c r="D237" s="47" t="s">
-        <v>1648</v>
+        <v>1667</v>
       </c>
       <c r="E237" s="7">
         <v>7</v>
       </c>
       <c r="F237" s="7" t="s">
-        <v>1649</v>
+        <v>1668</v>
       </c>
       <c r="G237" s="43" t="s">
         <v>1279</v>
@@ -23440,11 +23502,11 @@
       </c>
       <c r="R237" s="19">
         <f t="shared" si="100"/>
-        <v>992</v>
+        <v>1047</v>
       </c>
       <c r="S237" s="19">
         <f t="shared" si="101"/>
-        <v>1216</v>
+        <v>1316</v>
       </c>
       <c r="T237" s="19">
         <v>99.99</v>
@@ -23464,22 +23526,22 @@
     </row>
     <row r="238" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A238" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B238" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C238" s="47" t="s">
-        <v>1650</v>
+        <v>1669</v>
       </c>
       <c r="D238" s="47" t="s">
-        <v>1651</v>
+        <v>1670</v>
       </c>
       <c r="E238" s="7">
         <v>7</v>
       </c>
       <c r="F238" s="7" t="s">
-        <v>1652</v>
+        <v>1671</v>
       </c>
       <c r="G238" s="43" t="s">
         <v>1279</v>
@@ -23516,11 +23578,11 @@
       </c>
       <c r="R238" s="19">
         <f t="shared" si="100"/>
-        <v>1001</v>
+        <v>1056</v>
       </c>
       <c r="S238" s="19">
         <f t="shared" si="101"/>
-        <v>1226</v>
+        <v>1326</v>
       </c>
       <c r="T238" s="19">
         <v>99.99</v>
@@ -23540,22 +23602,22 @@
     </row>
     <row r="239" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A239" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B239" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C239" s="47" t="s">
-        <v>1653</v>
+        <v>1672</v>
       </c>
       <c r="D239" s="47" t="s">
-        <v>1654</v>
+        <v>1673</v>
       </c>
       <c r="E239" s="7">
         <v>7</v>
       </c>
       <c r="F239" s="7" t="s">
-        <v>1655</v>
+        <v>1674</v>
       </c>
       <c r="G239" s="43" t="s">
         <v>1279</v>
@@ -23592,11 +23654,11 @@
       </c>
       <c r="R239" s="19">
         <f t="shared" si="100"/>
-        <v>1010</v>
+        <v>1065</v>
       </c>
       <c r="S239" s="19">
         <f t="shared" si="101"/>
-        <v>1236</v>
+        <v>1336</v>
       </c>
       <c r="T239" s="19">
         <v>99.99</v>
@@ -23616,22 +23678,22 @@
     </row>
     <row r="240" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A240" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B240" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C240" s="47" t="s">
-        <v>1656</v>
+        <v>1675</v>
       </c>
       <c r="D240" s="47" t="s">
-        <v>1657</v>
+        <v>1676</v>
       </c>
       <c r="E240" s="7">
         <v>7</v>
       </c>
       <c r="F240" s="7" t="s">
-        <v>1658</v>
+        <v>1677</v>
       </c>
       <c r="G240" s="43" t="s">
         <v>1279</v>
@@ -23668,11 +23730,11 @@
       </c>
       <c r="R240" s="19">
         <f t="shared" si="100"/>
-        <v>1019</v>
+        <v>1074</v>
       </c>
       <c r="S240" s="19">
         <f t="shared" si="101"/>
-        <v>1246</v>
+        <v>1346</v>
       </c>
       <c r="T240" s="19">
         <v>99.99</v>
@@ -23692,22 +23754,22 @@
     </row>
     <row r="241" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A241" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B241" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C241" s="47" t="s">
-        <v>1659</v>
+        <v>1678</v>
       </c>
       <c r="D241" s="47" t="s">
-        <v>1660</v>
+        <v>1679</v>
       </c>
       <c r="E241" s="7">
         <v>7</v>
       </c>
       <c r="F241" s="6" t="s">
-        <v>1661</v>
+        <v>1680</v>
       </c>
       <c r="G241" s="43" t="s">
         <v>1279</v>
@@ -23744,11 +23806,11 @@
       </c>
       <c r="R241" s="19">
         <f t="shared" si="100"/>
-        <v>1028</v>
+        <v>1083</v>
       </c>
       <c r="S241" s="19">
         <f t="shared" si="101"/>
-        <v>1256</v>
+        <v>1356</v>
       </c>
       <c r="T241" s="19">
         <v>99.99</v>
@@ -23768,22 +23830,22 @@
     </row>
     <row r="242" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A242" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B242" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C242" s="47" t="s">
-        <v>1662</v>
+        <v>1681</v>
       </c>
       <c r="D242" s="47" t="s">
-        <v>1663</v>
+        <v>1682</v>
       </c>
       <c r="E242" s="7">
         <v>7</v>
       </c>
       <c r="F242" s="7" t="s">
-        <v>1664</v>
+        <v>1683</v>
       </c>
       <c r="G242" s="43" t="s">
         <v>1279</v>
@@ -23820,11 +23882,11 @@
       </c>
       <c r="R242" s="19">
         <f t="shared" si="100"/>
-        <v>1037</v>
+        <v>1092</v>
       </c>
       <c r="S242" s="19">
         <f t="shared" si="101"/>
-        <v>1266</v>
+        <v>1366</v>
       </c>
       <c r="T242" s="19">
         <v>99.99</v>
@@ -23844,22 +23906,22 @@
     </row>
     <row r="243" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A243" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B243" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C243" s="47" t="s">
-        <v>1665</v>
+        <v>1684</v>
       </c>
       <c r="D243" s="47" t="s">
-        <v>1666</v>
+        <v>1685</v>
       </c>
       <c r="E243" s="7">
         <v>7</v>
       </c>
       <c r="F243" s="7" t="s">
-        <v>1667</v>
+        <v>1686</v>
       </c>
       <c r="G243" s="43" t="s">
         <v>1279</v>
@@ -23896,11 +23958,11 @@
       </c>
       <c r="R243" s="19">
         <f t="shared" si="100"/>
-        <v>1046</v>
+        <v>1101</v>
       </c>
       <c r="S243" s="19">
         <f t="shared" si="101"/>
-        <v>1276</v>
+        <v>1376</v>
       </c>
       <c r="T243" s="19">
         <v>99.99</v>
@@ -23920,22 +23982,22 @@
     </row>
     <row r="244" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A244" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B244" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C244" s="47" t="s">
-        <v>1668</v>
+        <v>1687</v>
       </c>
       <c r="D244" s="47" t="s">
-        <v>1669</v>
+        <v>1688</v>
       </c>
       <c r="E244" s="7">
         <v>7</v>
       </c>
       <c r="F244" s="7" t="s">
-        <v>1670</v>
+        <v>1689</v>
       </c>
       <c r="G244" s="43" t="s">
         <v>1279</v>
@@ -23972,11 +24034,11 @@
       </c>
       <c r="R244" s="19">
         <f t="shared" si="100"/>
-        <v>1055</v>
+        <v>1110</v>
       </c>
       <c r="S244" s="19">
         <f t="shared" si="101"/>
-        <v>1286</v>
+        <v>1386</v>
       </c>
       <c r="T244" s="19">
         <v>99.99</v>
@@ -23996,22 +24058,22 @@
     </row>
     <row r="245" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A245" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B245" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C245" s="47" t="s">
-        <v>1671</v>
+        <v>1690</v>
       </c>
       <c r="D245" s="47" t="s">
-        <v>1672</v>
+        <v>1691</v>
       </c>
       <c r="E245" s="7">
         <v>7</v>
       </c>
       <c r="F245" s="7" t="s">
-        <v>1673</v>
+        <v>1692</v>
       </c>
       <c r="G245" s="43" t="s">
         <v>1279</v>
@@ -24048,11 +24110,11 @@
       </c>
       <c r="R245" s="19">
         <f t="shared" si="100"/>
-        <v>1064</v>
+        <v>1119</v>
       </c>
       <c r="S245" s="19">
         <f t="shared" si="101"/>
-        <v>1296</v>
+        <v>1396</v>
       </c>
       <c r="T245" s="19">
         <v>99.99</v>
@@ -24072,22 +24134,22 @@
     </row>
     <row r="246" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A246" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B246" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C246" s="47" t="s">
-        <v>1674</v>
+        <v>1693</v>
       </c>
       <c r="D246" s="47" t="s">
-        <v>1675</v>
+        <v>1694</v>
       </c>
       <c r="E246" s="7">
         <v>7</v>
       </c>
       <c r="F246" s="7" t="s">
-        <v>1676</v>
+        <v>1695</v>
       </c>
       <c r="G246" s="43" t="s">
         <v>1279</v>
@@ -24124,11 +24186,11 @@
       </c>
       <c r="R246" s="19">
         <f t="shared" si="100"/>
-        <v>1073</v>
+        <v>1128</v>
       </c>
       <c r="S246" s="19">
         <f t="shared" si="101"/>
-        <v>1306</v>
+        <v>1406</v>
       </c>
       <c r="T246" s="19">
         <v>99.99</v>
@@ -24148,22 +24210,22 @@
     </row>
     <row r="247" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A247" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B247" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C247" s="47" t="s">
-        <v>1677</v>
+        <v>1696</v>
       </c>
       <c r="D247" s="47" t="s">
-        <v>1678</v>
+        <v>1697</v>
       </c>
       <c r="E247" s="7">
         <v>7</v>
       </c>
       <c r="F247" s="7" t="s">
-        <v>1679</v>
+        <v>1698</v>
       </c>
       <c r="G247" s="43" t="s">
         <v>1279</v>
@@ -24200,11 +24262,11 @@
       </c>
       <c r="R247" s="19">
         <f t="shared" si="100"/>
-        <v>1082</v>
+        <v>1137</v>
       </c>
       <c r="S247" s="19">
         <f t="shared" si="101"/>
-        <v>1316</v>
+        <v>1416</v>
       </c>
       <c r="T247" s="19">
         <v>99.99</v>
@@ -24224,22 +24286,22 @@
     </row>
     <row r="248" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A248" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B248" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C248" s="47" t="s">
-        <v>1680</v>
+        <v>1699</v>
       </c>
       <c r="D248" s="47" t="s">
-        <v>1681</v>
+        <v>1700</v>
       </c>
       <c r="E248" s="7">
         <v>7</v>
       </c>
       <c r="F248" s="7" t="s">
-        <v>1682</v>
+        <v>1701</v>
       </c>
       <c r="G248" s="43" t="s">
         <v>1279</v>
@@ -24276,11 +24338,11 @@
       </c>
       <c r="R248" s="19">
         <f t="shared" si="100"/>
-        <v>1091</v>
+        <v>1146</v>
       </c>
       <c r="S248" s="19">
         <f t="shared" si="101"/>
-        <v>1326</v>
+        <v>1426</v>
       </c>
       <c r="T248" s="19">
         <v>99.99</v>
@@ -24300,22 +24362,22 @@
     </row>
     <row r="249" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A249" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B249" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C249" s="47" t="s">
-        <v>1683</v>
+        <v>1702</v>
       </c>
       <c r="D249" s="47" t="s">
-        <v>1684</v>
+        <v>1703</v>
       </c>
       <c r="E249" s="7">
         <v>7</v>
       </c>
       <c r="F249" s="7" t="s">
-        <v>1685</v>
+        <v>1704</v>
       </c>
       <c r="G249" s="43" t="s">
         <v>1279</v>
@@ -24352,11 +24414,11 @@
       </c>
       <c r="R249" s="19">
         <f t="shared" si="100"/>
-        <v>1100</v>
+        <v>1155</v>
       </c>
       <c r="S249" s="19">
         <f t="shared" si="101"/>
-        <v>1336</v>
+        <v>1436</v>
       </c>
       <c r="T249" s="19">
         <v>99.99</v>
@@ -24376,22 +24438,22 @@
     </row>
     <row r="250" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A250" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="B250" s="8" t="s">
-        <v>1613</v>
+        <v>1647</v>
       </c>
       <c r="C250" s="47" t="s">
-        <v>1686</v>
+        <v>1705</v>
       </c>
       <c r="D250" s="47" t="s">
-        <v>1687</v>
+        <v>1706</v>
       </c>
       <c r="E250" s="7">
         <v>7</v>
       </c>
       <c r="F250" s="7" t="s">
-        <v>1688</v>
+        <v>1707</v>
       </c>
       <c r="G250" s="43" t="s">
         <v>1279</v>
@@ -24428,11 +24490,11 @@
       </c>
       <c r="R250" s="19">
         <f t="shared" si="100"/>
-        <v>1109</v>
+        <v>1164</v>
       </c>
       <c r="S250" s="19">
         <f t="shared" si="101"/>
-        <v>1346</v>
+        <v>1446</v>
       </c>
       <c r="T250" s="19">
         <v>99.99</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2561" uniqueCount="1708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2551" uniqueCount="1724">
   <si>
     <t>ID</t>
   </si>
@@ -5026,52 +5026,100 @@
     <t>57000000000000</t>
   </si>
   <si>
+    <t>10225</t>
+  </si>
+  <si>
+    <t>1225</t>
+  </si>
+  <si>
+    <t>虚无钳虫王</t>
+  </si>
+  <si>
+    <t>1E+263</t>
+  </si>
+  <si>
+    <t>1E+276</t>
+  </si>
+  <si>
+    <t>10226</t>
+  </si>
+  <si>
+    <t>1226</t>
+  </si>
+  <si>
+    <t>虚无蠕虫王</t>
+  </si>
+  <si>
+    <t>1E+266</t>
+  </si>
+  <si>
+    <t>1E+279</t>
+  </si>
+  <si>
+    <t>1E+141</t>
+  </si>
+  <si>
+    <t>59000000000000</t>
+  </si>
+  <si>
+    <t>10227</t>
+  </si>
+  <si>
+    <t>1227</t>
+  </si>
+  <si>
+    <t>虚无猪王</t>
+  </si>
+  <si>
+    <t>1E+269</t>
+  </si>
+  <si>
+    <t>1E+282</t>
+  </si>
+  <si>
+    <t>1E+256</t>
+  </si>
+  <si>
+    <t>60000000000000</t>
+  </si>
+  <si>
+    <t>10228</t>
+  </si>
+  <si>
+    <t>1228</t>
+  </si>
+  <si>
+    <t>虚无猪皇</t>
+  </si>
+  <si>
+    <t>1E+272</t>
+  </si>
+  <si>
+    <t>1E+285</t>
+  </si>
+  <si>
+    <t>61000000000000</t>
+  </si>
+  <si>
+    <t>10229</t>
+  </si>
+  <si>
+    <t>1229</t>
+  </si>
+  <si>
+    <t>虚无蝎王</t>
+  </si>
+  <si>
+    <t>1E+275</t>
+  </si>
+  <si>
+    <t>1E+288</t>
+  </si>
+  <si>
+    <t>62000000000000</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>10225</t>
-  </si>
-  <si>
-    <t>1225</t>
-  </si>
-  <si>
-    <t>虚无钳虫王</t>
-  </si>
-  <si>
-    <t>10226</t>
-  </si>
-  <si>
-    <t>1226</t>
-  </si>
-  <si>
-    <t>虚无蠕虫王</t>
-  </si>
-  <si>
-    <t>10227</t>
-  </si>
-  <si>
-    <t>1227</t>
-  </si>
-  <si>
-    <t>虚无猪王</t>
-  </si>
-  <si>
-    <t>10228</t>
-  </si>
-  <si>
-    <t>1228</t>
-  </si>
-  <si>
-    <t>虚无猪皇</t>
-  </si>
-  <si>
-    <t>10229</t>
-  </si>
-  <si>
-    <t>1229</t>
-  </si>
-  <si>
-    <t>虚无蝎王</t>
   </si>
   <si>
     <t>10230</t>
@@ -5397,12 +5445,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5868,7 +5916,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -5914,10 +5962,6 @@
     <xf numFmtId="176" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
@@ -5948,10 +5992,6 @@
     <xf numFmtId="176" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6570,13 +6610,13 @@
       <c r="F6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="33" t="s">
+      <c r="G6" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="33" t="s">
+      <c r="H6" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="I6" s="33" t="s">
+      <c r="I6" s="31" t="s">
         <v>44</v>
       </c>
       <c r="J6" s="1">
@@ -8865,7 +8905,7 @@
       <c r="F40" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G40" s="33" t="s">
+      <c r="G40" s="31" t="s">
         <v>288</v>
       </c>
       <c r="H40" s="1" t="s">
@@ -10618,7 +10658,7 @@
       <c r="H65" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="I65" s="33" t="s">
+      <c r="I65" s="31" t="s">
         <v>465</v>
       </c>
       <c r="J65" s="1">
@@ -10690,7 +10730,7 @@
       <c r="H66" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="I66" s="33" t="s">
+      <c r="I66" s="31" t="s">
         <v>472</v>
       </c>
       <c r="J66" s="1">
@@ -10762,7 +10802,7 @@
       <c r="H67" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="I67" s="33" t="s">
+      <c r="I67" s="31" t="s">
         <v>479</v>
       </c>
       <c r="J67" s="1">
@@ -10834,7 +10874,7 @@
       <c r="H68" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="I68" s="33" t="s">
+      <c r="I68" s="31" t="s">
         <v>486</v>
       </c>
       <c r="J68" s="1">
@@ -10906,7 +10946,7 @@
       <c r="H69" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="I69" s="33" t="s">
+      <c r="I69" s="31" t="s">
         <v>493</v>
       </c>
       <c r="J69" s="1">
@@ -10978,7 +11018,7 @@
       <c r="H70" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="I70" s="33" t="s">
+      <c r="I70" s="31" t="s">
         <v>500</v>
       </c>
       <c r="J70" s="1">
@@ -11043,13 +11083,13 @@
       <c r="F71" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="G71" s="34" t="s">
+      <c r="G71" s="32" t="s">
         <v>505</v>
       </c>
-      <c r="H71" s="33" t="s">
+      <c r="H71" s="31" t="s">
         <v>506</v>
       </c>
-      <c r="I71" s="34" t="s">
+      <c r="I71" s="32" t="s">
         <v>507</v>
       </c>
       <c r="J71" s="1">
@@ -11115,13 +11155,13 @@
       <c r="F72" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="G72" s="34" t="s">
+      <c r="G72" s="32" t="s">
         <v>512</v>
       </c>
-      <c r="H72" s="33" t="s">
+      <c r="H72" s="31" t="s">
         <v>513</v>
       </c>
-      <c r="I72" s="35" t="s">
+      <c r="I72" s="33" t="s">
         <v>514</v>
       </c>
       <c r="J72" s="1">
@@ -11187,13 +11227,13 @@
       <c r="F73" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="G73" s="34" t="s">
+      <c r="G73" s="32" t="s">
         <v>519</v>
       </c>
-      <c r="H73" s="33" t="s">
+      <c r="H73" s="31" t="s">
         <v>520</v>
       </c>
-      <c r="I73" s="35" t="s">
+      <c r="I73" s="33" t="s">
         <v>521</v>
       </c>
       <c r="J73" s="1">
@@ -11259,13 +11299,13 @@
       <c r="F74" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="G74" s="34" t="s">
+      <c r="G74" s="32" t="s">
         <v>526</v>
       </c>
-      <c r="H74" s="33" t="s">
+      <c r="H74" s="31" t="s">
         <v>527</v>
       </c>
-      <c r="I74" s="35" t="s">
+      <c r="I74" s="33" t="s">
         <v>528</v>
       </c>
       <c r="J74" s="1">
@@ -11331,13 +11371,13 @@
       <c r="F75" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G75" s="34" t="s">
+      <c r="G75" s="32" t="s">
         <v>533</v>
       </c>
-      <c r="H75" s="33" t="s">
+      <c r="H75" s="31" t="s">
         <v>534</v>
       </c>
-      <c r="I75" s="35" t="s">
+      <c r="I75" s="33" t="s">
         <v>535</v>
       </c>
       <c r="J75" s="1">
@@ -11377,7 +11417,7 @@
       <c r="U75" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="V75" s="33" t="s">
+      <c r="V75" s="31" t="s">
         <v>536</v>
       </c>
       <c r="X75" s="1" t="s">
@@ -11404,13 +11444,13 @@
       <c r="F76" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="G76" s="34" t="s">
+      <c r="G76" s="32" t="s">
         <v>540</v>
       </c>
-      <c r="H76" s="33" t="s">
+      <c r="H76" s="31" t="s">
         <v>541</v>
       </c>
-      <c r="I76" s="35" t="s">
+      <c r="I76" s="33" t="s">
         <v>542</v>
       </c>
       <c r="J76" s="1">
@@ -11475,13 +11515,13 @@
       <c r="F77" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="G77" s="34" t="s">
+      <c r="G77" s="32" t="s">
         <v>546</v>
       </c>
-      <c r="H77" s="33" t="s">
+      <c r="H77" s="31" t="s">
         <v>547</v>
       </c>
-      <c r="I77" s="35" t="s">
+      <c r="I77" s="33" t="s">
         <v>548</v>
       </c>
       <c r="J77" s="1">
@@ -11546,13 +11586,13 @@
       <c r="F78" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="G78" s="34" t="s">
+      <c r="G78" s="32" t="s">
         <v>552</v>
       </c>
-      <c r="H78" s="33" t="s">
+      <c r="H78" s="31" t="s">
         <v>553</v>
       </c>
-      <c r="I78" s="35" t="s">
+      <c r="I78" s="33" t="s">
         <v>554</v>
       </c>
       <c r="J78" s="1">
@@ -11617,13 +11657,13 @@
       <c r="F79" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="G79" s="34" t="s">
+      <c r="G79" s="32" t="s">
         <v>558</v>
       </c>
-      <c r="H79" s="33" t="s">
+      <c r="H79" s="31" t="s">
         <v>559</v>
       </c>
-      <c r="I79" s="35" t="s">
+      <c r="I79" s="33" t="s">
         <v>560</v>
       </c>
       <c r="J79" s="1">
@@ -11688,13 +11728,13 @@
       <c r="F80" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="G80" s="34" t="s">
+      <c r="G80" s="32" t="s">
         <v>564</v>
       </c>
-      <c r="H80" s="33" t="s">
+      <c r="H80" s="31" t="s">
         <v>565</v>
       </c>
-      <c r="I80" s="35" t="s">
+      <c r="I80" s="33" t="s">
         <v>566</v>
       </c>
       <c r="J80" s="1">
@@ -11759,13 +11799,13 @@
       <c r="F81" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="G81" s="34" t="s">
+      <c r="G81" s="32" t="s">
         <v>570</v>
       </c>
-      <c r="H81" s="33" t="s">
+      <c r="H81" s="31" t="s">
         <v>571</v>
       </c>
-      <c r="I81" s="35" t="s">
+      <c r="I81" s="33" t="s">
         <v>572</v>
       </c>
       <c r="J81" s="1">
@@ -11832,13 +11872,13 @@
       <c r="F82" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="G82" s="34" t="s">
+      <c r="G82" s="32" t="s">
         <v>576</v>
       </c>
-      <c r="H82" s="33" t="s">
+      <c r="H82" s="31" t="s">
         <v>577</v>
       </c>
-      <c r="I82" s="35" t="s">
+      <c r="I82" s="33" t="s">
         <v>578</v>
       </c>
       <c r="J82" s="1">
@@ -11905,13 +11945,13 @@
       <c r="F83" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="G83" s="34" t="s">
+      <c r="G83" s="32" t="s">
         <v>582</v>
       </c>
-      <c r="H83" s="33" t="s">
+      <c r="H83" s="31" t="s">
         <v>533</v>
       </c>
-      <c r="I83" s="35" t="s">
+      <c r="I83" s="33" t="s">
         <v>583</v>
       </c>
       <c r="J83" s="1">
@@ -11978,13 +12018,13 @@
       <c r="F84" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="G84" s="34" t="s">
+      <c r="G84" s="32" t="s">
         <v>587</v>
       </c>
-      <c r="H84" s="33" t="s">
+      <c r="H84" s="31" t="s">
         <v>588</v>
       </c>
-      <c r="I84" s="35" t="s">
+      <c r="I84" s="33" t="s">
         <v>589</v>
       </c>
       <c r="J84" s="1">
@@ -12051,13 +12091,13 @@
       <c r="F85" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="G85" s="34" t="s">
+      <c r="G85" s="32" t="s">
         <v>465</v>
       </c>
-      <c r="H85" s="33" t="s">
+      <c r="H85" s="31" t="s">
         <v>593</v>
       </c>
-      <c r="I85" s="35" t="s">
+      <c r="I85" s="33" t="s">
         <v>594</v>
       </c>
       <c r="J85" s="1">
@@ -12124,13 +12164,13 @@
       <c r="F86" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="G86" s="34" t="s">
+      <c r="G86" s="32" t="s">
         <v>598</v>
       </c>
-      <c r="H86" s="33" t="s">
+      <c r="H86" s="31" t="s">
         <v>599</v>
       </c>
-      <c r="I86" s="35" t="s">
+      <c r="I86" s="33" t="s">
         <v>600</v>
       </c>
       <c r="J86" s="1">
@@ -12197,13 +12237,13 @@
       <c r="F87" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="G87" s="34" t="s">
+      <c r="G87" s="32" t="s">
         <v>604</v>
       </c>
-      <c r="H87" s="33" t="s">
+      <c r="H87" s="31" t="s">
         <v>605</v>
       </c>
-      <c r="I87" s="35" t="s">
+      <c r="I87" s="33" t="s">
         <v>606</v>
       </c>
       <c r="J87" s="1">
@@ -12270,13 +12310,13 @@
       <c r="F88" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="G88" s="34" t="s">
+      <c r="G88" s="32" t="s">
         <v>610</v>
       </c>
-      <c r="H88" s="33" t="s">
+      <c r="H88" s="31" t="s">
         <v>611</v>
       </c>
-      <c r="I88" s="35" t="s">
+      <c r="I88" s="33" t="s">
         <v>612</v>
       </c>
       <c r="J88" s="1">
@@ -12343,13 +12383,13 @@
       <c r="F89" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="G89" s="34" t="s">
+      <c r="G89" s="32" t="s">
         <v>616</v>
       </c>
-      <c r="H89" s="33" t="s">
+      <c r="H89" s="31" t="s">
         <v>465</v>
       </c>
-      <c r="I89" s="35" t="s">
+      <c r="I89" s="33" t="s">
         <v>617</v>
       </c>
       <c r="J89" s="1">
@@ -12416,13 +12456,13 @@
       <c r="F90" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="G90" s="34" t="s">
+      <c r="G90" s="32" t="s">
         <v>621</v>
       </c>
-      <c r="H90" s="33" t="s">
+      <c r="H90" s="31" t="s">
         <v>622</v>
       </c>
-      <c r="I90" s="35" t="s">
+      <c r="I90" s="33" t="s">
         <v>623</v>
       </c>
       <c r="J90" s="1">
@@ -12459,10 +12499,10 @@
       <c r="T90" s="15">
         <v>0</v>
       </c>
-      <c r="U90" s="33" t="s">
+      <c r="U90" s="31" t="s">
         <v>624</v>
       </c>
-      <c r="V90" s="33" t="s">
+      <c r="V90" s="31" t="s">
         <v>624</v>
       </c>
       <c r="X90" s="1" t="s">
@@ -12489,13 +12529,13 @@
       <c r="F91" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="G91" s="34" t="s">
+      <c r="G91" s="32" t="s">
         <v>514</v>
       </c>
-      <c r="H91" s="33" t="s">
+      <c r="H91" s="31" t="s">
         <v>628</v>
       </c>
-      <c r="I91" s="35" t="s">
+      <c r="I91" s="33" t="s">
         <v>629</v>
       </c>
       <c r="J91" s="1">
@@ -12532,10 +12572,10 @@
       <c r="T91" s="15">
         <v>0</v>
       </c>
-      <c r="U91" s="33" t="s">
+      <c r="U91" s="31" t="s">
         <v>630</v>
       </c>
-      <c r="V91" s="33" t="s">
+      <c r="V91" s="31" t="s">
         <v>630</v>
       </c>
       <c r="X91" s="1" t="s">
@@ -12562,13 +12602,13 @@
       <c r="F92" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="G92" s="34" t="s">
+      <c r="G92" s="32" t="s">
         <v>634</v>
       </c>
-      <c r="H92" s="33" t="s">
+      <c r="H92" s="31" t="s">
         <v>635</v>
       </c>
-      <c r="I92" s="35" t="s">
+      <c r="I92" s="33" t="s">
         <v>636</v>
       </c>
       <c r="J92" s="1">
@@ -12605,10 +12645,10 @@
       <c r="T92" s="15">
         <v>0</v>
       </c>
-      <c r="U92" s="33" t="s">
+      <c r="U92" s="31" t="s">
         <v>637</v>
       </c>
-      <c r="V92" s="33" t="s">
+      <c r="V92" s="31" t="s">
         <v>637</v>
       </c>
       <c r="X92" s="1" t="s">
@@ -12635,13 +12675,13 @@
       <c r="F93" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="G93" s="34" t="s">
+      <c r="G93" s="32" t="s">
         <v>641</v>
       </c>
-      <c r="H93" s="33" t="s">
+      <c r="H93" s="31" t="s">
         <v>642</v>
       </c>
-      <c r="I93" s="35" t="s">
+      <c r="I93" s="33" t="s">
         <v>643</v>
       </c>
       <c r="J93" s="1">
@@ -12678,10 +12718,10 @@
       <c r="T93" s="15">
         <v>0</v>
       </c>
-      <c r="U93" s="33" t="s">
+      <c r="U93" s="31" t="s">
         <v>644</v>
       </c>
-      <c r="V93" s="33" t="s">
+      <c r="V93" s="31" t="s">
         <v>644</v>
       </c>
       <c r="X93" s="1" t="s">
@@ -12708,13 +12748,13 @@
       <c r="F94" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="G94" s="34" t="s">
+      <c r="G94" s="32" t="s">
         <v>648</v>
       </c>
-      <c r="H94" s="33" t="s">
+      <c r="H94" s="31" t="s">
         <v>649</v>
       </c>
-      <c r="I94" s="35" t="s">
+      <c r="I94" s="33" t="s">
         <v>650</v>
       </c>
       <c r="J94" s="1">
@@ -12751,10 +12791,10 @@
       <c r="T94" s="15">
         <v>0</v>
       </c>
-      <c r="U94" s="33" t="s">
+      <c r="U94" s="31" t="s">
         <v>651</v>
       </c>
-      <c r="V94" s="33" t="s">
+      <c r="V94" s="31" t="s">
         <v>651</v>
       </c>
       <c r="X94" s="1" t="s">
@@ -12781,13 +12821,13 @@
       <c r="F95" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="G95" s="34" t="s">
+      <c r="G95" s="32" t="s">
         <v>655</v>
       </c>
-      <c r="H95" s="33" t="s">
+      <c r="H95" s="31" t="s">
         <v>656</v>
       </c>
-      <c r="I95" s="35" t="s">
+      <c r="I95" s="33" t="s">
         <v>657</v>
       </c>
       <c r="J95" s="1">
@@ -12824,10 +12864,10 @@
       <c r="T95" s="15">
         <v>0</v>
       </c>
-      <c r="U95" s="33" t="s">
+      <c r="U95" s="31" t="s">
         <v>658</v>
       </c>
-      <c r="V95" s="33" t="s">
+      <c r="V95" s="31" t="s">
         <v>658</v>
       </c>
       <c r="X95" s="1" t="s">
@@ -12852,13 +12892,13 @@
       <c r="F96" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="G96" s="34" t="s">
+      <c r="G96" s="32" t="s">
         <v>662</v>
       </c>
-      <c r="H96" s="33" t="s">
+      <c r="H96" s="31" t="s">
         <v>663</v>
       </c>
-      <c r="I96" s="35" t="s">
+      <c r="I96" s="33" t="s">
         <v>664</v>
       </c>
       <c r="J96" s="1">
@@ -12896,10 +12936,10 @@
       <c r="T96" s="15">
         <v>0</v>
       </c>
-      <c r="U96" s="33" t="s">
+      <c r="U96" s="31" t="s">
         <v>665</v>
       </c>
-      <c r="V96" s="33" t="s">
+      <c r="V96" s="31" t="s">
         <v>665</v>
       </c>
       <c r="X96" s="1" t="s">
@@ -12922,13 +12962,13 @@
       <c r="F97" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="G97" s="34" t="s">
+      <c r="G97" s="32" t="s">
         <v>669</v>
       </c>
-      <c r="H97" s="33" t="s">
+      <c r="H97" s="31" t="s">
         <v>670</v>
       </c>
-      <c r="I97" s="35" t="s">
+      <c r="I97" s="33" t="s">
         <v>671</v>
       </c>
       <c r="J97" s="1">
@@ -12966,10 +13006,10 @@
       <c r="T97" s="15">
         <v>0</v>
       </c>
-      <c r="U97" s="33" t="s">
+      <c r="U97" s="31" t="s">
         <v>672</v>
       </c>
-      <c r="V97" s="33" t="s">
+      <c r="V97" s="31" t="s">
         <v>672</v>
       </c>
       <c r="X97" s="1" t="s">
@@ -12992,13 +13032,13 @@
       <c r="F98" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="G98" s="34" t="s">
+      <c r="G98" s="32" t="s">
         <v>676</v>
       </c>
-      <c r="H98" s="33" t="s">
+      <c r="H98" s="31" t="s">
         <v>677</v>
       </c>
-      <c r="I98" s="35" t="s">
+      <c r="I98" s="33" t="s">
         <v>678</v>
       </c>
       <c r="J98" s="1">
@@ -13036,10 +13076,10 @@
       <c r="T98" s="15">
         <v>0</v>
       </c>
-      <c r="U98" s="33" t="s">
+      <c r="U98" s="31" t="s">
         <v>679</v>
       </c>
-      <c r="V98" s="33" t="s">
+      <c r="V98" s="31" t="s">
         <v>679</v>
       </c>
       <c r="X98" s="1" t="s">
@@ -13062,13 +13102,13 @@
       <c r="F99" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="G99" s="34" t="s">
+      <c r="G99" s="32" t="s">
         <v>683</v>
       </c>
-      <c r="H99" s="33" t="s">
+      <c r="H99" s="31" t="s">
         <v>684</v>
       </c>
-      <c r="I99" s="35" t="s">
+      <c r="I99" s="33" t="s">
         <v>685</v>
       </c>
       <c r="J99" s="1">
@@ -13106,10 +13146,10 @@
       <c r="T99" s="15">
         <v>0</v>
       </c>
-      <c r="U99" s="33" t="s">
+      <c r="U99" s="31" t="s">
         <v>686</v>
       </c>
-      <c r="V99" s="33" t="s">
+      <c r="V99" s="31" t="s">
         <v>686</v>
       </c>
       <c r="X99" s="1" t="s">
@@ -13132,13 +13172,13 @@
       <c r="F100" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="G100" s="34" t="s">
+      <c r="G100" s="32" t="s">
         <v>689</v>
       </c>
-      <c r="H100" s="33" t="s">
+      <c r="H100" s="31" t="s">
         <v>690</v>
       </c>
-      <c r="I100" s="35" t="s">
+      <c r="I100" s="33" t="s">
         <v>691</v>
       </c>
       <c r="J100" s="1">
@@ -13176,10 +13216,10 @@
       <c r="T100" s="15">
         <v>0</v>
       </c>
-      <c r="U100" s="33" t="s">
+      <c r="U100" s="31" t="s">
         <v>692</v>
       </c>
-      <c r="V100" s="33" t="s">
+      <c r="V100" s="31" t="s">
         <v>692</v>
       </c>
       <c r="X100" s="1" t="s">
@@ -13204,13 +13244,13 @@
       <c r="F101" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="G101" s="34" t="s">
+      <c r="G101" s="32" t="s">
         <v>696</v>
       </c>
-      <c r="H101" s="33" t="s">
+      <c r="H101" s="31" t="s">
         <v>697</v>
       </c>
-      <c r="I101" s="35" t="s">
+      <c r="I101" s="33" t="s">
         <v>698</v>
       </c>
       <c r="J101" s="1">
@@ -13247,10 +13287,10 @@
       <c r="T101" s="15">
         <v>0</v>
       </c>
-      <c r="U101" s="33" t="s">
+      <c r="U101" s="31" t="s">
         <v>699</v>
       </c>
-      <c r="V101" s="33" t="s">
+      <c r="V101" s="31" t="s">
         <v>699</v>
       </c>
       <c r="X101" s="1" t="s">
@@ -13277,13 +13317,13 @@
       <c r="F102" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="G102" s="34" t="s">
+      <c r="G102" s="32" t="s">
         <v>703</v>
       </c>
-      <c r="H102" s="33" t="s">
+      <c r="H102" s="31" t="s">
         <v>612</v>
       </c>
-      <c r="I102" s="35" t="s">
+      <c r="I102" s="33" t="s">
         <v>704</v>
       </c>
       <c r="J102" s="1">
@@ -13320,10 +13360,10 @@
       <c r="T102" s="15">
         <v>0</v>
       </c>
-      <c r="U102" s="33" t="s">
+      <c r="U102" s="31" t="s">
         <v>705</v>
       </c>
-      <c r="V102" s="33" t="s">
+      <c r="V102" s="31" t="s">
         <v>705</v>
       </c>
       <c r="X102" s="1" t="s">
@@ -13350,13 +13390,13 @@
       <c r="F103" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="G103" s="34" t="s">
+      <c r="G103" s="32" t="s">
         <v>709</v>
       </c>
-      <c r="H103" s="33" t="s">
+      <c r="H103" s="31" t="s">
         <v>617</v>
       </c>
-      <c r="I103" s="35" t="s">
+      <c r="I103" s="33" t="s">
         <v>710</v>
       </c>
       <c r="J103" s="1">
@@ -13393,10 +13433,10 @@
       <c r="T103" s="15">
         <v>0</v>
       </c>
-      <c r="U103" s="33" t="s">
+      <c r="U103" s="31" t="s">
         <v>711</v>
       </c>
-      <c r="V103" s="33" t="s">
+      <c r="V103" s="31" t="s">
         <v>711</v>
       </c>
       <c r="X103" s="1" t="s">
@@ -13423,13 +13463,13 @@
       <c r="F104" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="G104" s="34" t="s">
+      <c r="G104" s="32" t="s">
         <v>715</v>
       </c>
-      <c r="H104" s="33" t="s">
+      <c r="H104" s="31" t="s">
         <v>716</v>
       </c>
-      <c r="I104" s="35" t="s">
+      <c r="I104" s="33" t="s">
         <v>717</v>
       </c>
       <c r="J104" s="1">
@@ -13466,10 +13506,10 @@
       <c r="T104" s="15">
         <v>0</v>
       </c>
-      <c r="U104" s="33" t="s">
+      <c r="U104" s="31" t="s">
         <v>718</v>
       </c>
-      <c r="V104" s="33" t="s">
+      <c r="V104" s="31" t="s">
         <v>718</v>
       </c>
       <c r="X104" s="1" t="s">
@@ -13496,13 +13536,13 @@
       <c r="F105" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="G105" s="34" t="s">
+      <c r="G105" s="32" t="s">
         <v>722</v>
       </c>
-      <c r="H105" s="33" t="s">
+      <c r="H105" s="31" t="s">
         <v>723</v>
       </c>
-      <c r="I105" s="35" t="s">
+      <c r="I105" s="33" t="s">
         <v>724</v>
       </c>
       <c r="J105" s="1">
@@ -13539,10 +13579,10 @@
       <c r="T105" s="15">
         <v>0</v>
       </c>
-      <c r="U105" s="33" t="s">
+      <c r="U105" s="31" t="s">
         <v>725</v>
       </c>
-      <c r="V105" s="33" t="s">
+      <c r="V105" s="31" t="s">
         <v>725</v>
       </c>
       <c r="X105" s="1" t="s">
@@ -13569,13 +13609,13 @@
       <c r="F106" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="G106" s="34" t="s">
+      <c r="G106" s="32" t="s">
         <v>729</v>
       </c>
-      <c r="H106" s="33" t="s">
+      <c r="H106" s="31" t="s">
         <v>730</v>
       </c>
-      <c r="I106" s="35" t="s">
+      <c r="I106" s="33" t="s">
         <v>731</v>
       </c>
       <c r="J106" s="1">
@@ -13612,10 +13652,10 @@
       <c r="T106" s="15">
         <v>0</v>
       </c>
-      <c r="U106" s="33" t="s">
+      <c r="U106" s="31" t="s">
         <v>732</v>
       </c>
-      <c r="V106" s="33" t="s">
+      <c r="V106" s="31" t="s">
         <v>732</v>
       </c>
       <c r="X106" s="1" t="s">
@@ -13642,13 +13682,13 @@
       <c r="F107" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="G107" s="34" t="s">
+      <c r="G107" s="32" t="s">
         <v>736</v>
       </c>
-      <c r="H107" s="33" t="s">
+      <c r="H107" s="31" t="s">
         <v>737</v>
       </c>
-      <c r="I107" s="35" t="s">
+      <c r="I107" s="33" t="s">
         <v>738</v>
       </c>
       <c r="J107" s="1">
@@ -13685,10 +13725,10 @@
       <c r="T107" s="15">
         <v>0</v>
       </c>
-      <c r="U107" s="33" t="s">
+      <c r="U107" s="31" t="s">
         <v>739</v>
       </c>
-      <c r="V107" s="33" t="s">
+      <c r="V107" s="31" t="s">
         <v>739</v>
       </c>
       <c r="X107" s="1" t="s">
@@ -13715,13 +13755,13 @@
       <c r="F108" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="G108" s="34" t="s">
+      <c r="G108" s="32" t="s">
         <v>743</v>
       </c>
-      <c r="H108" s="33" t="s">
+      <c r="H108" s="31" t="s">
         <v>744</v>
       </c>
-      <c r="I108" s="35" t="s">
+      <c r="I108" s="33" t="s">
         <v>745</v>
       </c>
       <c r="J108" s="1">
@@ -13758,10 +13798,10 @@
       <c r="T108" s="15">
         <v>0</v>
       </c>
-      <c r="U108" s="33" t="s">
+      <c r="U108" s="31" t="s">
         <v>746</v>
       </c>
-      <c r="V108" s="33" t="s">
+      <c r="V108" s="31" t="s">
         <v>746</v>
       </c>
       <c r="X108" s="1" t="s">
@@ -13788,13 +13828,13 @@
       <c r="F109" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="G109" s="34" t="s">
+      <c r="G109" s="32" t="s">
         <v>750</v>
       </c>
-      <c r="H109" s="33" t="s">
+      <c r="H109" s="31" t="s">
         <v>751</v>
       </c>
-      <c r="I109" s="35" t="s">
+      <c r="I109" s="33" t="s">
         <v>752</v>
       </c>
       <c r="J109" s="1">
@@ -13831,10 +13871,10 @@
       <c r="T109" s="15">
         <v>0</v>
       </c>
-      <c r="U109" s="33" t="s">
+      <c r="U109" s="31" t="s">
         <v>753</v>
       </c>
-      <c r="V109" s="33" t="s">
+      <c r="V109" s="31" t="s">
         <v>753</v>
       </c>
       <c r="X109" s="1" t="s">
@@ -13861,13 +13901,13 @@
       <c r="F110" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="G110" s="34" t="s">
+      <c r="G110" s="32" t="s">
         <v>678</v>
       </c>
-      <c r="H110" s="33" t="s">
+      <c r="H110" s="31" t="s">
         <v>757</v>
       </c>
-      <c r="I110" s="35" t="s">
+      <c r="I110" s="33" t="s">
         <v>758</v>
       </c>
       <c r="J110" s="1">
@@ -13904,10 +13944,10 @@
       <c r="T110" s="15">
         <v>0</v>
       </c>
-      <c r="U110" s="33" t="s">
+      <c r="U110" s="31" t="s">
         <v>759</v>
       </c>
-      <c r="V110" s="33" t="s">
+      <c r="V110" s="31" t="s">
         <v>759</v>
       </c>
       <c r="X110" s="1" t="s">
@@ -13934,13 +13974,13 @@
       <c r="F111" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="G111" s="36" t="s">
+      <c r="G111" s="34" t="s">
         <v>763</v>
       </c>
-      <c r="H111" s="37" t="s">
+      <c r="H111" s="35" t="s">
         <v>763</v>
       </c>
-      <c r="I111" s="38" t="s">
+      <c r="I111" s="36" t="s">
         <v>764</v>
       </c>
       <c r="J111" s="1">
@@ -13974,10 +14014,10 @@
       <c r="T111" s="11">
         <v>90</v>
       </c>
-      <c r="U111" s="37" t="s">
+      <c r="U111" s="35" t="s">
         <v>765</v>
       </c>
-      <c r="V111" s="37" t="s">
+      <c r="V111" s="35" t="s">
         <v>765</v>
       </c>
       <c r="X111" s="2" t="s">
@@ -14002,13 +14042,13 @@
       <c r="F112" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="G112" s="34" t="s">
+      <c r="G112" s="32" t="s">
         <v>769</v>
       </c>
-      <c r="H112" s="33" t="s">
+      <c r="H112" s="31" t="s">
         <v>769</v>
       </c>
-      <c r="I112" s="35" t="s">
+      <c r="I112" s="33" t="s">
         <v>770</v>
       </c>
       <c r="J112" s="1">
@@ -14046,10 +14086,10 @@
       <c r="T112" s="11">
         <v>90</v>
       </c>
-      <c r="U112" s="33" t="s">
+      <c r="U112" s="31" t="s">
         <v>771</v>
       </c>
-      <c r="V112" s="33" t="s">
+      <c r="V112" s="31" t="s">
         <v>771</v>
       </c>
       <c r="X112" s="1" t="s">
@@ -14074,13 +14114,13 @@
       <c r="F113" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="G113" s="34" t="s">
+      <c r="G113" s="32" t="s">
         <v>775</v>
       </c>
-      <c r="H113" s="33" t="s">
+      <c r="H113" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="I113" s="35" t="s">
+      <c r="I113" s="33" t="s">
         <v>776</v>
       </c>
       <c r="J113" s="1">
@@ -14118,10 +14158,10 @@
       <c r="T113" s="11">
         <v>90</v>
       </c>
-      <c r="U113" s="33" t="s">
+      <c r="U113" s="31" t="s">
         <v>777</v>
       </c>
-      <c r="V113" s="33" t="s">
+      <c r="V113" s="31" t="s">
         <v>777</v>
       </c>
       <c r="X113" s="1" t="s">
@@ -14146,13 +14186,13 @@
       <c r="F114" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="G114" s="34" t="s">
+      <c r="G114" s="32" t="s">
         <v>781</v>
       </c>
-      <c r="H114" s="33" t="s">
+      <c r="H114" s="31" t="s">
         <v>781</v>
       </c>
-      <c r="I114" s="35" t="s">
+      <c r="I114" s="33" t="s">
         <v>782</v>
       </c>
       <c r="J114" s="1">
@@ -14190,10 +14230,10 @@
       <c r="T114" s="11">
         <v>90</v>
       </c>
-      <c r="U114" s="33" t="s">
+      <c r="U114" s="31" t="s">
         <v>783</v>
       </c>
-      <c r="V114" s="33" t="s">
+      <c r="V114" s="31" t="s">
         <v>783</v>
       </c>
       <c r="X114" s="1" t="s">
@@ -14218,13 +14258,13 @@
       <c r="F115" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="G115" s="34" t="s">
+      <c r="G115" s="32" t="s">
         <v>787</v>
       </c>
-      <c r="H115" s="33" t="s">
+      <c r="H115" s="31" t="s">
         <v>787</v>
       </c>
-      <c r="I115" s="35" t="s">
+      <c r="I115" s="33" t="s">
         <v>788</v>
       </c>
       <c r="J115" s="1">
@@ -14262,10 +14302,10 @@
       <c r="T115" s="11">
         <v>90</v>
       </c>
-      <c r="U115" s="33" t="s">
+      <c r="U115" s="31" t="s">
         <v>789</v>
       </c>
-      <c r="V115" s="33" t="s">
+      <c r="V115" s="31" t="s">
         <v>789</v>
       </c>
       <c r="X115" s="1" t="s">
@@ -14290,13 +14330,13 @@
       <c r="F116" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="G116" s="34" t="s">
+      <c r="G116" s="32" t="s">
         <v>793</v>
       </c>
-      <c r="H116" s="33" t="s">
+      <c r="H116" s="31" t="s">
         <v>793</v>
       </c>
-      <c r="I116" s="35" t="s">
+      <c r="I116" s="33" t="s">
         <v>794</v>
       </c>
       <c r="J116" s="1">
@@ -14334,10 +14374,10 @@
       <c r="T116" s="11">
         <v>90</v>
       </c>
-      <c r="U116" s="33" t="s">
+      <c r="U116" s="31" t="s">
         <v>795</v>
       </c>
-      <c r="V116" s="33" t="s">
+      <c r="V116" s="31" t="s">
         <v>795</v>
       </c>
       <c r="X116" s="1" t="s">
@@ -14364,13 +14404,13 @@
       <c r="F117" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="G117" s="34" t="s">
+      <c r="G117" s="32" t="s">
         <v>799</v>
       </c>
-      <c r="H117" s="33" t="s">
+      <c r="H117" s="31" t="s">
         <v>799</v>
       </c>
-      <c r="I117" s="35" t="s">
+      <c r="I117" s="33" t="s">
         <v>800</v>
       </c>
       <c r="J117" s="1">
@@ -14408,10 +14448,10 @@
       <c r="T117" s="11">
         <v>90</v>
       </c>
-      <c r="U117" s="33" t="s">
+      <c r="U117" s="31" t="s">
         <v>801</v>
       </c>
-      <c r="V117" s="33" t="s">
+      <c r="V117" s="31" t="s">
         <v>801</v>
       </c>
       <c r="X117" s="1" t="s">
@@ -14438,13 +14478,13 @@
       <c r="F118" s="1" t="s">
         <v>804</v>
       </c>
-      <c r="G118" s="34" t="s">
+      <c r="G118" s="32" t="s">
         <v>805</v>
       </c>
-      <c r="H118" s="33" t="s">
+      <c r="H118" s="31" t="s">
         <v>805</v>
       </c>
-      <c r="I118" s="35" t="s">
+      <c r="I118" s="33" t="s">
         <v>806</v>
       </c>
       <c r="J118" s="1">
@@ -14482,10 +14522,10 @@
       <c r="T118" s="11">
         <v>90</v>
       </c>
-      <c r="U118" s="33" t="s">
+      <c r="U118" s="31" t="s">
         <v>807</v>
       </c>
-      <c r="V118" s="33" t="s">
+      <c r="V118" s="31" t="s">
         <v>807</v>
       </c>
       <c r="X118" s="1" t="s">
@@ -14512,13 +14552,13 @@
       <c r="F119" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="G119" s="34" t="s">
+      <c r="G119" s="32" t="s">
         <v>811</v>
       </c>
-      <c r="H119" s="33" t="s">
+      <c r="H119" s="31" t="s">
         <v>811</v>
       </c>
-      <c r="I119" s="35" t="s">
+      <c r="I119" s="33" t="s">
         <v>812</v>
       </c>
       <c r="J119" s="1">
@@ -14556,10 +14596,10 @@
       <c r="T119" s="11">
         <v>90</v>
       </c>
-      <c r="U119" s="33" t="s">
+      <c r="U119" s="31" t="s">
         <v>813</v>
       </c>
-      <c r="V119" s="33" t="s">
+      <c r="V119" s="31" t="s">
         <v>813</v>
       </c>
       <c r="X119" s="1" t="s">
@@ -14586,13 +14626,13 @@
       <c r="F120" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="G120" s="34" t="s">
+      <c r="G120" s="32" t="s">
         <v>817</v>
       </c>
-      <c r="H120" s="33" t="s">
+      <c r="H120" s="31" t="s">
         <v>817</v>
       </c>
-      <c r="I120" s="35" t="s">
+      <c r="I120" s="33" t="s">
         <v>818</v>
       </c>
       <c r="J120" s="1">
@@ -14630,10 +14670,10 @@
       <c r="T120" s="11">
         <v>90</v>
       </c>
-      <c r="U120" s="33" t="s">
+      <c r="U120" s="31" t="s">
         <v>819</v>
       </c>
-      <c r="V120" s="33" t="s">
+      <c r="V120" s="31" t="s">
         <v>819</v>
       </c>
       <c r="X120" s="1" t="s">
@@ -14658,13 +14698,13 @@
       <c r="F121" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="G121" s="34" t="s">
+      <c r="G121" s="32" t="s">
         <v>764</v>
       </c>
-      <c r="H121" s="33" t="s">
+      <c r="H121" s="31" t="s">
         <v>764</v>
       </c>
-      <c r="I121" s="35" t="s">
+      <c r="I121" s="33" t="s">
         <v>823</v>
       </c>
       <c r="J121" s="1">
@@ -14703,10 +14743,10 @@
       <c r="T121" s="11">
         <v>90</v>
       </c>
-      <c r="U121" s="33" t="s">
+      <c r="U121" s="31" t="s">
         <v>824</v>
       </c>
-      <c r="V121" s="33" t="s">
+      <c r="V121" s="31" t="s">
         <v>824</v>
       </c>
       <c r="X121" s="1" t="s">
@@ -14731,13 +14771,13 @@
       <c r="F122" s="1" t="s">
         <v>827</v>
       </c>
-      <c r="G122" s="34" t="s">
+      <c r="G122" s="32" t="s">
         <v>828</v>
       </c>
-      <c r="H122" s="33" t="s">
+      <c r="H122" s="31" t="s">
         <v>828</v>
       </c>
-      <c r="I122" s="35" t="s">
+      <c r="I122" s="33" t="s">
         <v>829</v>
       </c>
       <c r="J122" s="1">
@@ -14776,10 +14816,10 @@
       <c r="T122" s="11">
         <v>90</v>
       </c>
-      <c r="U122" s="33" t="s">
+      <c r="U122" s="31" t="s">
         <v>830</v>
       </c>
-      <c r="V122" s="33" t="s">
+      <c r="V122" s="31" t="s">
         <v>830</v>
       </c>
       <c r="X122" s="1" t="s">
@@ -14804,13 +14844,13 @@
       <c r="F123" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="G123" s="34" t="s">
+      <c r="G123" s="32" t="s">
         <v>834</v>
       </c>
-      <c r="H123" s="33" t="s">
+      <c r="H123" s="31" t="s">
         <v>834</v>
       </c>
-      <c r="I123" s="35" t="s">
+      <c r="I123" s="33" t="s">
         <v>835</v>
       </c>
       <c r="J123" s="1">
@@ -14849,10 +14889,10 @@
       <c r="T123" s="11">
         <v>90</v>
       </c>
-      <c r="U123" s="33" t="s">
+      <c r="U123" s="31" t="s">
         <v>836</v>
       </c>
-      <c r="V123" s="33" t="s">
+      <c r="V123" s="31" t="s">
         <v>836</v>
       </c>
       <c r="X123" s="1" t="s">
@@ -14877,13 +14917,13 @@
       <c r="F124" s="1" t="s">
         <v>839</v>
       </c>
-      <c r="G124" s="34" t="s">
+      <c r="G124" s="32" t="s">
         <v>840</v>
       </c>
-      <c r="H124" s="33" t="s">
+      <c r="H124" s="31" t="s">
         <v>840</v>
       </c>
-      <c r="I124" s="35" t="s">
+      <c r="I124" s="33" t="s">
         <v>841</v>
       </c>
       <c r="J124" s="1">
@@ -14922,10 +14962,10 @@
       <c r="T124" s="11">
         <v>90</v>
       </c>
-      <c r="U124" s="33" t="s">
+      <c r="U124" s="31" t="s">
         <v>842</v>
       </c>
-      <c r="V124" s="33" t="s">
+      <c r="V124" s="31" t="s">
         <v>842</v>
       </c>
       <c r="X124" s="1" t="s">
@@ -14950,13 +14990,13 @@
       <c r="F125" s="1" t="s">
         <v>845</v>
       </c>
-      <c r="G125" s="34" t="s">
+      <c r="G125" s="32" t="s">
         <v>846</v>
       </c>
-      <c r="H125" s="33" t="s">
+      <c r="H125" s="31" t="s">
         <v>846</v>
       </c>
-      <c r="I125" s="35" t="s">
+      <c r="I125" s="33" t="s">
         <v>847</v>
       </c>
       <c r="J125" s="1">
@@ -14995,10 +15035,10 @@
       <c r="T125" s="11">
         <v>90</v>
       </c>
-      <c r="U125" s="33" t="s">
+      <c r="U125" s="31" t="s">
         <v>848</v>
       </c>
-      <c r="V125" s="33" t="s">
+      <c r="V125" s="31" t="s">
         <v>848</v>
       </c>
       <c r="X125" s="1" t="s">
@@ -15025,13 +15065,13 @@
       <c r="F126" s="1" t="s">
         <v>851</v>
       </c>
-      <c r="G126" s="34" t="s">
+      <c r="G126" s="32" t="s">
         <v>852</v>
       </c>
-      <c r="H126" s="33" t="s">
+      <c r="H126" s="31" t="s">
         <v>852</v>
       </c>
-      <c r="I126" s="35" t="s">
+      <c r="I126" s="33" t="s">
         <v>853</v>
       </c>
       <c r="J126" s="1">
@@ -15070,10 +15110,10 @@
       <c r="T126" s="11">
         <v>90</v>
       </c>
-      <c r="U126" s="33" t="s">
+      <c r="U126" s="31" t="s">
         <v>854</v>
       </c>
-      <c r="V126" s="33" t="s">
+      <c r="V126" s="31" t="s">
         <v>854</v>
       </c>
       <c r="X126" s="1" t="s">
@@ -15100,13 +15140,13 @@
       <c r="F127" s="1" t="s">
         <v>857</v>
       </c>
-      <c r="G127" s="34" t="s">
+      <c r="G127" s="32" t="s">
         <v>858</v>
       </c>
-      <c r="H127" s="33" t="s">
+      <c r="H127" s="31" t="s">
         <v>858</v>
       </c>
-      <c r="I127" s="35" t="s">
+      <c r="I127" s="33" t="s">
         <v>859</v>
       </c>
       <c r="J127" s="1">
@@ -15145,10 +15185,10 @@
       <c r="T127" s="11">
         <v>90</v>
       </c>
-      <c r="U127" s="33" t="s">
+      <c r="U127" s="31" t="s">
         <v>860</v>
       </c>
-      <c r="V127" s="33" t="s">
+      <c r="V127" s="31" t="s">
         <v>860</v>
       </c>
       <c r="X127" s="1" t="s">
@@ -15175,13 +15215,13 @@
       <c r="F128" s="1" t="s">
         <v>863</v>
       </c>
-      <c r="G128" s="34" t="s">
+      <c r="G128" s="32" t="s">
         <v>864</v>
       </c>
-      <c r="H128" s="33" t="s">
+      <c r="H128" s="31" t="s">
         <v>864</v>
       </c>
-      <c r="I128" s="35" t="s">
+      <c r="I128" s="33" t="s">
         <v>865</v>
       </c>
       <c r="J128" s="1">
@@ -15220,10 +15260,10 @@
       <c r="T128" s="11">
         <v>90</v>
       </c>
-      <c r="U128" s="33" t="s">
+      <c r="U128" s="31" t="s">
         <v>866</v>
       </c>
-      <c r="V128" s="33" t="s">
+      <c r="V128" s="31" t="s">
         <v>866</v>
       </c>
       <c r="X128" s="1" t="s">
@@ -15250,13 +15290,13 @@
       <c r="F129" s="1" t="s">
         <v>869</v>
       </c>
-      <c r="G129" s="34" t="s">
+      <c r="G129" s="32" t="s">
         <v>870</v>
       </c>
-      <c r="H129" s="33" t="s">
+      <c r="H129" s="31" t="s">
         <v>870</v>
       </c>
-      <c r="I129" s="35" t="s">
+      <c r="I129" s="33" t="s">
         <v>871</v>
       </c>
       <c r="J129" s="1">
@@ -15295,10 +15335,10 @@
       <c r="T129" s="11">
         <v>90</v>
       </c>
-      <c r="U129" s="33" t="s">
+      <c r="U129" s="31" t="s">
         <v>872</v>
       </c>
-      <c r="V129" s="33" t="s">
+      <c r="V129" s="31" t="s">
         <v>872</v>
       </c>
       <c r="X129" s="1" t="s">
@@ -15325,13 +15365,13 @@
       <c r="F130" s="1" t="s">
         <v>875</v>
       </c>
-      <c r="G130" s="34" t="s">
+      <c r="G130" s="32" t="s">
         <v>876</v>
       </c>
-      <c r="H130" s="33" t="s">
+      <c r="H130" s="31" t="s">
         <v>876</v>
       </c>
-      <c r="I130" s="35" t="s">
+      <c r="I130" s="33" t="s">
         <v>877</v>
       </c>
       <c r="J130" s="1">
@@ -15370,10 +15410,10 @@
       <c r="T130" s="11">
         <v>90</v>
       </c>
-      <c r="U130" s="33" t="s">
+      <c r="U130" s="31" t="s">
         <v>878</v>
       </c>
-      <c r="V130" s="33" t="s">
+      <c r="V130" s="31" t="s">
         <v>878</v>
       </c>
       <c r="X130" s="1" t="s">
@@ -15398,13 +15438,13 @@
       <c r="F131" s="1" t="s">
         <v>881</v>
       </c>
-      <c r="G131" s="34" t="s">
+      <c r="G131" s="32" t="s">
         <v>882</v>
       </c>
-      <c r="H131" s="33" t="s">
+      <c r="H131" s="31" t="s">
         <v>882</v>
       </c>
-      <c r="I131" s="35" t="s">
+      <c r="I131" s="33" t="s">
         <v>883</v>
       </c>
       <c r="J131" s="1">
@@ -15444,10 +15484,10 @@
       <c r="T131" s="11">
         <v>92</v>
       </c>
-      <c r="U131" s="33" t="s">
+      <c r="U131" s="31" t="s">
         <v>884</v>
       </c>
-      <c r="V131" s="33" t="s">
+      <c r="V131" s="31" t="s">
         <v>884</v>
       </c>
       <c r="X131" s="1" t="s">
@@ -15470,13 +15510,13 @@
       <c r="F132" s="1" t="s">
         <v>887</v>
       </c>
-      <c r="G132" s="34" t="s">
+      <c r="G132" s="32" t="s">
         <v>888</v>
       </c>
-      <c r="H132" s="33" t="s">
+      <c r="H132" s="31" t="s">
         <v>888</v>
       </c>
-      <c r="I132" s="35" t="s">
+      <c r="I132" s="33" t="s">
         <v>889</v>
       </c>
       <c r="J132" s="1">
@@ -15516,10 +15556,10 @@
       <c r="T132" s="11">
         <v>94</v>
       </c>
-      <c r="U132" s="33" t="s">
+      <c r="U132" s="31" t="s">
         <v>890</v>
       </c>
-      <c r="V132" s="33" t="s">
+      <c r="V132" s="31" t="s">
         <v>890</v>
       </c>
       <c r="X132" s="1" t="s">
@@ -15542,13 +15582,13 @@
       <c r="F133" s="1" t="s">
         <v>893</v>
       </c>
-      <c r="G133" s="34" t="s">
+      <c r="G133" s="32" t="s">
         <v>894</v>
       </c>
-      <c r="H133" s="33" t="s">
+      <c r="H133" s="31" t="s">
         <v>894</v>
       </c>
-      <c r="I133" s="35" t="s">
+      <c r="I133" s="33" t="s">
         <v>895</v>
       </c>
       <c r="J133" s="1">
@@ -15588,10 +15628,10 @@
       <c r="T133" s="11">
         <v>96</v>
       </c>
-      <c r="U133" s="33" t="s">
+      <c r="U133" s="31" t="s">
         <v>896</v>
       </c>
-      <c r="V133" s="33" t="s">
+      <c r="V133" s="31" t="s">
         <v>896</v>
       </c>
       <c r="X133" s="1" t="s">
@@ -15614,13 +15654,13 @@
       <c r="F134" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="G134" s="34" t="s">
+      <c r="G134" s="32" t="s">
         <v>900</v>
       </c>
-      <c r="H134" s="33" t="s">
+      <c r="H134" s="31" t="s">
         <v>900</v>
       </c>
-      <c r="I134" s="35" t="s">
+      <c r="I134" s="33" t="s">
         <v>901</v>
       </c>
       <c r="J134" s="1">
@@ -15660,10 +15700,10 @@
       <c r="T134" s="11">
         <v>98</v>
       </c>
-      <c r="U134" s="33" t="s">
+      <c r="U134" s="31" t="s">
         <v>902</v>
       </c>
-      <c r="V134" s="33" t="s">
+      <c r="V134" s="31" t="s">
         <v>902</v>
       </c>
       <c r="X134" s="1" t="s">
@@ -15686,13 +15726,13 @@
       <c r="F135" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="G135" s="34" t="s">
+      <c r="G135" s="32" t="s">
         <v>905</v>
       </c>
-      <c r="H135" s="33" t="s">
+      <c r="H135" s="31" t="s">
         <v>905</v>
       </c>
-      <c r="I135" s="35" t="s">
+      <c r="I135" s="33" t="s">
         <v>906</v>
       </c>
       <c r="J135" s="1">
@@ -15732,10 +15772,10 @@
       <c r="T135" s="11">
         <v>99</v>
       </c>
-      <c r="U135" s="33" t="s">
+      <c r="U135" s="31" t="s">
         <v>457</v>
       </c>
-      <c r="V135" s="33" t="s">
+      <c r="V135" s="31" t="s">
         <v>457</v>
       </c>
       <c r="X135" s="1" t="s">
@@ -15760,13 +15800,13 @@
       <c r="F136" s="1" t="s">
         <v>909</v>
       </c>
-      <c r="G136" s="34" t="s">
+      <c r="G136" s="32" t="s">
         <v>910</v>
       </c>
-      <c r="H136" s="33" t="s">
+      <c r="H136" s="31" t="s">
         <v>910</v>
       </c>
-      <c r="I136" s="35" t="s">
+      <c r="I136" s="33" t="s">
         <v>911</v>
       </c>
       <c r="J136" s="1">
@@ -15805,10 +15845,10 @@
       <c r="T136" s="11">
         <v>99.2</v>
       </c>
-      <c r="U136" s="33" t="s">
+      <c r="U136" s="31" t="s">
         <v>912</v>
       </c>
-      <c r="V136" s="33" t="s">
+      <c r="V136" s="31" t="s">
         <v>912</v>
       </c>
       <c r="X136" s="1" t="s">
@@ -15835,13 +15875,13 @@
       <c r="F137" s="1" t="s">
         <v>915</v>
       </c>
-      <c r="G137" s="34" t="s">
+      <c r="G137" s="32" t="s">
         <v>916</v>
       </c>
-      <c r="H137" s="33" t="s">
+      <c r="H137" s="31" t="s">
         <v>916</v>
       </c>
-      <c r="I137" s="35" t="s">
+      <c r="I137" s="33" t="s">
         <v>917</v>
       </c>
       <c r="J137" s="1">
@@ -15880,10 +15920,10 @@
       <c r="T137" s="11">
         <v>99.4</v>
       </c>
-      <c r="U137" s="33" t="s">
+      <c r="U137" s="31" t="s">
         <v>918</v>
       </c>
-      <c r="V137" s="33" t="s">
+      <c r="V137" s="31" t="s">
         <v>918</v>
       </c>
       <c r="X137" s="1" t="s">
@@ -15910,13 +15950,13 @@
       <c r="F138" s="1" t="s">
         <v>921</v>
       </c>
-      <c r="G138" s="34" t="s">
+      <c r="G138" s="32" t="s">
         <v>922</v>
       </c>
-      <c r="H138" s="33" t="s">
+      <c r="H138" s="31" t="s">
         <v>922</v>
       </c>
-      <c r="I138" s="35" t="s">
+      <c r="I138" s="33" t="s">
         <v>923</v>
       </c>
       <c r="J138" s="1">
@@ -15955,10 +15995,10 @@
       <c r="T138" s="11">
         <v>99.6</v>
       </c>
-      <c r="U138" s="33" t="s">
+      <c r="U138" s="31" t="s">
         <v>924</v>
       </c>
-      <c r="V138" s="33" t="s">
+      <c r="V138" s="31" t="s">
         <v>924</v>
       </c>
       <c r="X138" s="1" t="s">
@@ -15985,13 +16025,13 @@
       <c r="F139" s="1" t="s">
         <v>927</v>
       </c>
-      <c r="G139" s="34" t="s">
+      <c r="G139" s="32" t="s">
         <v>928</v>
       </c>
-      <c r="H139" s="33" t="s">
+      <c r="H139" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="I139" s="35" t="s">
+      <c r="I139" s="33" t="s">
         <v>929</v>
       </c>
       <c r="J139" s="1">
@@ -16030,10 +16070,10 @@
       <c r="T139" s="11">
         <v>99.8</v>
       </c>
-      <c r="U139" s="33" t="s">
+      <c r="U139" s="31" t="s">
         <v>930</v>
       </c>
-      <c r="V139" s="33" t="s">
+      <c r="V139" s="31" t="s">
         <v>930</v>
       </c>
       <c r="X139" s="1" t="s">
@@ -16060,13 +16100,13 @@
       <c r="F140" s="1" t="s">
         <v>933</v>
       </c>
-      <c r="G140" s="34" t="s">
+      <c r="G140" s="32" t="s">
         <v>934</v>
       </c>
-      <c r="H140" s="33" t="s">
+      <c r="H140" s="31" t="s">
         <v>934</v>
       </c>
-      <c r="I140" s="35" t="s">
+      <c r="I140" s="33" t="s">
         <v>935</v>
       </c>
       <c r="J140" s="1">
@@ -16105,10 +16145,10 @@
       <c r="T140" s="11">
         <v>99.9</v>
       </c>
-      <c r="U140" s="33" t="s">
+      <c r="U140" s="31" t="s">
         <v>936</v>
       </c>
-      <c r="V140" s="33" t="s">
+      <c r="V140" s="31" t="s">
         <v>936</v>
       </c>
       <c r="X140" s="1" t="s">
@@ -16135,13 +16175,13 @@
       <c r="F141" s="1" t="s">
         <v>939</v>
       </c>
-      <c r="G141" s="34" t="s">
+      <c r="G141" s="32" t="s">
         <v>940</v>
       </c>
-      <c r="H141" s="33" t="s">
+      <c r="H141" s="31" t="s">
         <v>940</v>
       </c>
-      <c r="I141" s="35" t="s">
+      <c r="I141" s="33" t="s">
         <v>941</v>
       </c>
       <c r="J141" s="1">
@@ -16180,10 +16220,10 @@
       <c r="T141" s="11">
         <v>99.92</v>
       </c>
-      <c r="U141" s="33" t="s">
+      <c r="U141" s="31" t="s">
         <v>942</v>
       </c>
-      <c r="V141" s="33" t="s">
+      <c r="V141" s="31" t="s">
         <v>942</v>
       </c>
       <c r="X141" s="1" t="s">
@@ -16210,13 +16250,13 @@
       <c r="F142" s="1" t="s">
         <v>945</v>
       </c>
-      <c r="G142" s="34" t="s">
+      <c r="G142" s="32" t="s">
         <v>946</v>
       </c>
-      <c r="H142" s="33" t="s">
+      <c r="H142" s="31" t="s">
         <v>946</v>
       </c>
-      <c r="I142" s="35" t="s">
+      <c r="I142" s="33" t="s">
         <v>947</v>
       </c>
       <c r="J142" s="1">
@@ -16255,10 +16295,10 @@
       <c r="T142" s="11">
         <v>99.94</v>
       </c>
-      <c r="U142" s="33" t="s">
+      <c r="U142" s="31" t="s">
         <v>948</v>
       </c>
-      <c r="V142" s="33" t="s">
+      <c r="V142" s="31" t="s">
         <v>948</v>
       </c>
       <c r="X142" s="1" t="s">
@@ -16285,13 +16325,13 @@
       <c r="F143" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="G143" s="34" t="s">
+      <c r="G143" s="32" t="s">
         <v>952</v>
       </c>
-      <c r="H143" s="33" t="s">
+      <c r="H143" s="31" t="s">
         <v>952</v>
       </c>
-      <c r="I143" s="35" t="s">
+      <c r="I143" s="33" t="s">
         <v>953</v>
       </c>
       <c r="J143" s="1">
@@ -16330,10 +16370,10 @@
       <c r="T143" s="11">
         <v>99.96</v>
       </c>
-      <c r="U143" s="33" t="s">
+      <c r="U143" s="31" t="s">
         <v>954</v>
       </c>
-      <c r="V143" s="33" t="s">
+      <c r="V143" s="31" t="s">
         <v>954</v>
       </c>
       <c r="X143" s="1" t="s">
@@ -16360,13 +16400,13 @@
       <c r="F144" s="1" t="s">
         <v>957</v>
       </c>
-      <c r="G144" s="34" t="s">
+      <c r="G144" s="32" t="s">
         <v>958</v>
       </c>
-      <c r="H144" s="33" t="s">
+      <c r="H144" s="31" t="s">
         <v>958</v>
       </c>
-      <c r="I144" s="35" t="s">
+      <c r="I144" s="33" t="s">
         <v>959</v>
       </c>
       <c r="J144" s="1">
@@ -16405,10 +16445,10 @@
       <c r="T144" s="11">
         <v>99.98</v>
       </c>
-      <c r="U144" s="33" t="s">
+      <c r="U144" s="31" t="s">
         <v>960</v>
       </c>
-      <c r="V144" s="33" t="s">
+      <c r="V144" s="31" t="s">
         <v>960</v>
       </c>
       <c r="X144" s="1" t="s">
@@ -16480,10 +16520,10 @@
       <c r="T145" s="11">
         <v>99.99</v>
       </c>
-      <c r="U145" s="33" t="s">
+      <c r="U145" s="31" t="s">
         <v>966</v>
       </c>
-      <c r="V145" s="33" t="s">
+      <c r="V145" s="31" t="s">
         <v>966</v>
       </c>
       <c r="X145" s="1" t="s">
@@ -16498,10 +16538,10 @@
     <row r="146" s="3" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A146" s="19"/>
       <c r="B146" s="19"/>
-      <c r="C146" s="39" t="s">
+      <c r="C146" s="37" t="s">
         <v>967</v>
       </c>
-      <c r="D146" s="39" t="s">
+      <c r="D146" s="37" t="s">
         <v>968</v>
       </c>
       <c r="E146" s="3">
@@ -16555,10 +16595,10 @@
       <c r="T146" s="19">
         <v>99.99</v>
       </c>
-      <c r="U146" s="39" t="s">
+      <c r="U146" s="37" t="s">
         <v>974</v>
       </c>
-      <c r="V146" s="39" t="s">
+      <c r="V146" s="37" t="s">
         <v>974</v>
       </c>
       <c r="X146" s="3" t="s">
@@ -16571,10 +16611,10 @@
     <row r="147" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A147" s="11"/>
       <c r="B147" s="11"/>
-      <c r="C147" s="33" t="s">
+      <c r="C147" s="31" t="s">
         <v>975</v>
       </c>
-      <c r="D147" s="33" t="s">
+      <c r="D147" s="31" t="s">
         <v>976</v>
       </c>
       <c r="E147" s="1">
@@ -16629,10 +16669,10 @@
       <c r="T147" s="11">
         <v>99.99</v>
       </c>
-      <c r="U147" s="33" t="s">
+      <c r="U147" s="31" t="s">
         <v>982</v>
       </c>
-      <c r="V147" s="33" t="s">
+      <c r="V147" s="31" t="s">
         <v>982</v>
       </c>
       <c r="X147" s="1" t="s">
@@ -16645,10 +16685,10 @@
     <row r="148" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A148" s="11"/>
       <c r="B148" s="11"/>
-      <c r="C148" s="33" t="s">
+      <c r="C148" s="31" t="s">
         <v>983</v>
       </c>
-      <c r="D148" s="33" t="s">
+      <c r="D148" s="31" t="s">
         <v>984</v>
       </c>
       <c r="E148" s="1">
@@ -16703,10 +16743,10 @@
       <c r="T148" s="11">
         <v>99.99</v>
       </c>
-      <c r="U148" s="33" t="s">
+      <c r="U148" s="31" t="s">
         <v>990</v>
       </c>
-      <c r="V148" s="33" t="s">
+      <c r="V148" s="31" t="s">
         <v>990</v>
       </c>
       <c r="X148" s="1" t="s">
@@ -16719,10 +16759,10 @@
     <row r="149" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A149" s="11"/>
       <c r="B149" s="11"/>
-      <c r="C149" s="33" t="s">
+      <c r="C149" s="31" t="s">
         <v>991</v>
       </c>
-      <c r="D149" s="33" t="s">
+      <c r="D149" s="31" t="s">
         <v>992</v>
       </c>
       <c r="E149" s="1">
@@ -16777,10 +16817,10 @@
       <c r="T149" s="11">
         <v>99.99</v>
       </c>
-      <c r="U149" s="33" t="s">
+      <c r="U149" s="31" t="s">
         <v>998</v>
       </c>
-      <c r="V149" s="33" t="s">
+      <c r="V149" s="31" t="s">
         <v>998</v>
       </c>
       <c r="X149" s="1" t="s">
@@ -16793,10 +16833,10 @@
     <row r="150" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A150" s="11"/>
       <c r="B150" s="11"/>
-      <c r="C150" s="33" t="s">
+      <c r="C150" s="31" t="s">
         <v>999</v>
       </c>
-      <c r="D150" s="33" t="s">
+      <c r="D150" s="31" t="s">
         <v>1000</v>
       </c>
       <c r="E150" s="1">
@@ -16851,10 +16891,10 @@
       <c r="T150" s="11">
         <v>99.99</v>
       </c>
-      <c r="U150" s="33" t="s">
+      <c r="U150" s="31" t="s">
         <v>1006</v>
       </c>
-      <c r="V150" s="33" t="s">
+      <c r="V150" s="31" t="s">
         <v>1006</v>
       </c>
       <c r="X150" s="1" t="s">
@@ -16867,10 +16907,10 @@
     <row r="151" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A151" s="11"/>
       <c r="B151" s="11"/>
-      <c r="C151" s="33" t="s">
+      <c r="C151" s="31" t="s">
         <v>1007</v>
       </c>
-      <c r="D151" s="33" t="s">
+      <c r="D151" s="31" t="s">
         <v>1008</v>
       </c>
       <c r="E151" s="1">
@@ -16924,10 +16964,10 @@
       <c r="T151" s="11">
         <v>99.99</v>
       </c>
-      <c r="U151" s="33" t="s">
+      <c r="U151" s="31" t="s">
         <v>1015</v>
       </c>
-      <c r="V151" s="33" t="s">
+      <c r="V151" s="31" t="s">
         <v>1015</v>
       </c>
       <c r="X151" s="1" t="s">
@@ -16942,10 +16982,10 @@
     <row r="152" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A152" s="11"/>
       <c r="B152" s="11"/>
-      <c r="C152" s="33" t="s">
+      <c r="C152" s="31" t="s">
         <v>1016</v>
       </c>
-      <c r="D152" s="33" t="s">
+      <c r="D152" s="31" t="s">
         <v>1017</v>
       </c>
       <c r="E152" s="1">
@@ -16999,10 +17039,10 @@
       <c r="T152" s="11">
         <v>99.99</v>
       </c>
-      <c r="U152" s="33" t="s">
+      <c r="U152" s="31" t="s">
         <v>1024</v>
       </c>
-      <c r="V152" s="33" t="s">
+      <c r="V152" s="31" t="s">
         <v>1024</v>
       </c>
       <c r="X152" s="1" t="s">
@@ -17017,10 +17057,10 @@
     <row r="153" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A153" s="11"/>
       <c r="B153" s="11"/>
-      <c r="C153" s="33" t="s">
+      <c r="C153" s="31" t="s">
         <v>1025</v>
       </c>
-      <c r="D153" s="33" t="s">
+      <c r="D153" s="31" t="s">
         <v>1026</v>
       </c>
       <c r="E153" s="1">
@@ -17074,10 +17114,10 @@
       <c r="T153" s="11">
         <v>99.99</v>
       </c>
-      <c r="U153" s="33" t="s">
+      <c r="U153" s="31" t="s">
         <v>1033</v>
       </c>
-      <c r="V153" s="33" t="s">
+      <c r="V153" s="31" t="s">
         <v>1033</v>
       </c>
       <c r="X153" s="1" t="s">
@@ -17092,10 +17132,10 @@
     <row r="154" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A154" s="11"/>
       <c r="B154" s="11"/>
-      <c r="C154" s="33" t="s">
+      <c r="C154" s="31" t="s">
         <v>1034</v>
       </c>
-      <c r="D154" s="33" t="s">
+      <c r="D154" s="31" t="s">
         <v>1035</v>
       </c>
       <c r="E154" s="1">
@@ -17149,10 +17189,10 @@
       <c r="T154" s="11">
         <v>99.99</v>
       </c>
-      <c r="U154" s="33" t="s">
+      <c r="U154" s="31" t="s">
         <v>1042</v>
       </c>
-      <c r="V154" s="33" t="s">
+      <c r="V154" s="31" t="s">
         <v>1042</v>
       </c>
       <c r="X154" s="1" t="s">
@@ -17167,10 +17207,10 @@
     <row r="155" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A155" s="11"/>
       <c r="B155" s="11"/>
-      <c r="C155" s="33" t="s">
+      <c r="C155" s="31" t="s">
         <v>1043</v>
       </c>
-      <c r="D155" s="33" t="s">
+      <c r="D155" s="31" t="s">
         <v>1044</v>
       </c>
       <c r="E155" s="1">
@@ -17224,10 +17264,10 @@
       <c r="T155" s="11">
         <v>99.99</v>
       </c>
-      <c r="U155" s="33" t="s">
+      <c r="U155" s="31" t="s">
         <v>1051</v>
       </c>
-      <c r="V155" s="33" t="s">
+      <c r="V155" s="31" t="s">
         <v>1051</v>
       </c>
       <c r="X155" s="1" t="s">
@@ -17242,10 +17282,10 @@
     <row r="156" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A156" s="11"/>
       <c r="B156" s="11"/>
-      <c r="C156" s="33" t="s">
+      <c r="C156" s="31" t="s">
         <v>1052</v>
       </c>
-      <c r="D156" s="33" t="s">
+      <c r="D156" s="31" t="s">
         <v>1053</v>
       </c>
       <c r="E156" s="1">
@@ -17299,10 +17339,10 @@
       <c r="T156" s="11">
         <v>99.99</v>
       </c>
-      <c r="U156" s="33" t="s">
+      <c r="U156" s="31" t="s">
         <v>1060</v>
       </c>
-      <c r="V156" s="33" t="s">
+      <c r="V156" s="31" t="s">
         <v>1060</v>
       </c>
       <c r="X156" s="1" t="s">
@@ -17317,10 +17357,10 @@
     <row r="157" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A157" s="11"/>
       <c r="B157" s="11"/>
-      <c r="C157" s="33" t="s">
+      <c r="C157" s="31" t="s">
         <v>1061</v>
       </c>
-      <c r="D157" s="33" t="s">
+      <c r="D157" s="31" t="s">
         <v>1062</v>
       </c>
       <c r="E157" s="1">
@@ -17374,10 +17414,10 @@
       <c r="T157" s="11">
         <v>99.99</v>
       </c>
-      <c r="U157" s="33" t="s">
+      <c r="U157" s="31" t="s">
         <v>1069</v>
       </c>
-      <c r="V157" s="33" t="s">
+      <c r="V157" s="31" t="s">
         <v>1069</v>
       </c>
       <c r="X157" s="1" t="s">
@@ -17392,10 +17432,10 @@
     <row r="158" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A158" s="11"/>
       <c r="B158" s="11"/>
-      <c r="C158" s="33" t="s">
+      <c r="C158" s="31" t="s">
         <v>1070</v>
       </c>
-      <c r="D158" s="33" t="s">
+      <c r="D158" s="31" t="s">
         <v>1071</v>
       </c>
       <c r="E158" s="1">
@@ -17449,10 +17489,10 @@
       <c r="T158" s="11">
         <v>99.99</v>
       </c>
-      <c r="U158" s="33" t="s">
+      <c r="U158" s="31" t="s">
         <v>1078</v>
       </c>
-      <c r="V158" s="33" t="s">
+      <c r="V158" s="31" t="s">
         <v>1078</v>
       </c>
       <c r="X158" s="1" t="s">
@@ -17467,10 +17507,10 @@
     <row r="159" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A159" s="11"/>
       <c r="B159" s="11"/>
-      <c r="C159" s="33" t="s">
+      <c r="C159" s="31" t="s">
         <v>1079</v>
       </c>
-      <c r="D159" s="33" t="s">
+      <c r="D159" s="31" t="s">
         <v>1080</v>
       </c>
       <c r="E159" s="1">
@@ -17524,10 +17564,10 @@
       <c r="T159" s="11">
         <v>99.99</v>
       </c>
-      <c r="U159" s="33" t="s">
+      <c r="U159" s="31" t="s">
         <v>1087</v>
       </c>
-      <c r="V159" s="33" t="s">
+      <c r="V159" s="31" t="s">
         <v>1087</v>
       </c>
       <c r="X159" s="1" t="s">
@@ -17542,10 +17582,10 @@
     <row r="160" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A160" s="11"/>
       <c r="B160" s="11"/>
-      <c r="C160" s="33" t="s">
+      <c r="C160" s="31" t="s">
         <v>1088</v>
       </c>
-      <c r="D160" s="33" t="s">
+      <c r="D160" s="31" t="s">
         <v>1089</v>
       </c>
       <c r="E160" s="1">
@@ -17599,10 +17639,10 @@
       <c r="T160" s="11">
         <v>99.99</v>
       </c>
-      <c r="U160" s="33" t="s">
+      <c r="U160" s="31" t="s">
         <v>1096</v>
       </c>
-      <c r="V160" s="33" t="s">
+      <c r="V160" s="31" t="s">
         <v>1096</v>
       </c>
       <c r="X160" s="1" t="s">
@@ -17617,10 +17657,10 @@
     <row r="161" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A161" s="11"/>
       <c r="B161" s="11"/>
-      <c r="C161" s="33" t="s">
+      <c r="C161" s="31" t="s">
         <v>1097</v>
       </c>
-      <c r="D161" s="33" t="s">
+      <c r="D161" s="31" t="s">
         <v>1098</v>
       </c>
       <c r="E161" s="1">
@@ -17674,10 +17714,10 @@
       <c r="T161" s="11">
         <v>99.99</v>
       </c>
-      <c r="U161" s="33" t="s">
+      <c r="U161" s="31" t="s">
         <v>1105</v>
       </c>
-      <c r="V161" s="33" t="s">
+      <c r="V161" s="31" t="s">
         <v>1105</v>
       </c>
       <c r="X161" s="1" t="s">
@@ -17692,10 +17732,10 @@
     <row r="162" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A162" s="11"/>
       <c r="B162" s="11"/>
-      <c r="C162" s="33" t="s">
+      <c r="C162" s="31" t="s">
         <v>1106</v>
       </c>
-      <c r="D162" s="33" t="s">
+      <c r="D162" s="31" t="s">
         <v>1107</v>
       </c>
       <c r="E162" s="1">
@@ -17749,10 +17789,10 @@
       <c r="T162" s="11">
         <v>99.99</v>
       </c>
-      <c r="U162" s="33" t="s">
+      <c r="U162" s="31" t="s">
         <v>1114</v>
       </c>
-      <c r="V162" s="33" t="s">
+      <c r="V162" s="31" t="s">
         <v>1114</v>
       </c>
       <c r="X162" s="1" t="s">
@@ -17767,10 +17807,10 @@
     <row r="163" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A163" s="11"/>
       <c r="B163" s="11"/>
-      <c r="C163" s="33" t="s">
+      <c r="C163" s="31" t="s">
         <v>1115</v>
       </c>
-      <c r="D163" s="33" t="s">
+      <c r="D163" s="31" t="s">
         <v>1116</v>
       </c>
       <c r="E163" s="1">
@@ -17785,7 +17825,7 @@
       <c r="H163" s="1" t="s">
         <v>1119</v>
       </c>
-      <c r="I163" s="40" t="s">
+      <c r="I163" s="38" t="s">
         <v>1120</v>
       </c>
       <c r="J163" s="1" t="s">
@@ -17824,10 +17864,10 @@
       <c r="T163" s="11">
         <v>99.99</v>
       </c>
-      <c r="U163" s="33" t="s">
+      <c r="U163" s="31" t="s">
         <v>1123</v>
       </c>
-      <c r="V163" s="33" t="s">
+      <c r="V163" s="31" t="s">
         <v>1123</v>
       </c>
       <c r="X163" s="1" t="s">
@@ -17842,10 +17882,10 @@
     <row r="164" s="4" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A164" s="23"/>
       <c r="B164" s="23"/>
-      <c r="C164" s="41" t="s">
+      <c r="C164" s="39" t="s">
         <v>1124</v>
       </c>
-      <c r="D164" s="41" t="s">
+      <c r="D164" s="39" t="s">
         <v>1125</v>
       </c>
       <c r="E164" s="4">
@@ -17860,7 +17900,7 @@
       <c r="H164" s="4" t="s">
         <v>1128</v>
       </c>
-      <c r="I164" s="42" t="s">
+      <c r="I164" s="40" t="s">
         <v>1129</v>
       </c>
       <c r="J164" s="4" t="s">
@@ -17900,10 +17940,10 @@
       <c r="T164" s="23">
         <v>99.99</v>
       </c>
-      <c r="U164" s="41" t="s">
+      <c r="U164" s="39" t="s">
         <v>1132</v>
       </c>
-      <c r="V164" s="41" t="s">
+      <c r="V164" s="39" t="s">
         <v>1132</v>
       </c>
       <c r="X164" s="4" t="s">
@@ -17918,10 +17958,10 @@
     <row r="165" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A165" s="11"/>
       <c r="B165" s="11"/>
-      <c r="C165" s="33" t="s">
+      <c r="C165" s="31" t="s">
         <v>1133</v>
       </c>
-      <c r="D165" s="33" t="s">
+      <c r="D165" s="31" t="s">
         <v>1134</v>
       </c>
       <c r="E165" s="1">
@@ -17930,19 +17970,19 @@
       <c r="F165" s="1" t="s">
         <v>1135</v>
       </c>
-      <c r="G165" s="40" t="s">
+      <c r="G165" s="38" t="s">
         <v>1136</v>
       </c>
-      <c r="H165" s="40" t="s">
+      <c r="H165" s="38" t="s">
         <v>1137</v>
       </c>
-      <c r="I165" s="40" t="s">
+      <c r="I165" s="38" t="s">
         <v>1138</v>
       </c>
-      <c r="J165" s="40" t="s">
+      <c r="J165" s="38" t="s">
         <v>1139</v>
       </c>
-      <c r="L165" s="40" t="s">
+      <c r="L165" s="38" t="s">
         <v>1140</v>
       </c>
       <c r="M165" s="1">
@@ -17975,10 +18015,10 @@
       <c r="T165" s="11">
         <v>99.99</v>
       </c>
-      <c r="U165" s="33" t="s">
+      <c r="U165" s="31" t="s">
         <v>1141</v>
       </c>
-      <c r="V165" s="33" t="s">
+      <c r="V165" s="31" t="s">
         <v>1141</v>
       </c>
       <c r="X165" s="1" t="s">
@@ -17991,10 +18031,10 @@
       <c r="AA165" s="11"/>
     </row>
     <row r="166" hidden="1" customHeight="1" spans="1:27">
-      <c r="C166" s="33" t="s">
+      <c r="C166" s="31" t="s">
         <v>1142</v>
       </c>
-      <c r="D166" s="33" t="s">
+      <c r="D166" s="31" t="s">
         <v>1143</v>
       </c>
       <c r="E166" s="1">
@@ -18003,20 +18043,20 @@
       <c r="F166" s="1" t="s">
         <v>1144</v>
       </c>
-      <c r="G166" s="40" t="s">
+      <c r="G166" s="38" t="s">
         <v>1145</v>
       </c>
-      <c r="H166" s="40" t="s">
+      <c r="H166" s="38" t="s">
         <v>1146</v>
       </c>
-      <c r="I166" s="40" t="s">
+      <c r="I166" s="38" t="s">
         <v>1147</v>
       </c>
-      <c r="J166" s="40" t="s">
+      <c r="J166" s="38" t="s">
         <v>1148</v>
       </c>
       <c r="K166" s="1"/>
-      <c r="L166" s="40" t="s">
+      <c r="L166" s="38" t="s">
         <v>1149</v>
       </c>
       <c r="M166" s="1">
@@ -18049,10 +18089,10 @@
       <c r="T166" s="11">
         <v>99.99</v>
       </c>
-      <c r="U166" s="33" t="s">
+      <c r="U166" s="31" t="s">
         <v>1150</v>
       </c>
-      <c r="V166" s="33" t="s">
+      <c r="V166" s="31" t="s">
         <v>1150</v>
       </c>
       <c r="X166" s="1" t="s">
@@ -18063,10 +18103,10 @@
       </c>
     </row>
     <row r="167" hidden="1" customHeight="1" spans="1:27">
-      <c r="C167" s="33" t="s">
+      <c r="C167" s="31" t="s">
         <v>1151</v>
       </c>
-      <c r="D167" s="33" t="s">
+      <c r="D167" s="31" t="s">
         <v>1152</v>
       </c>
       <c r="E167" s="1">
@@ -18075,20 +18115,20 @@
       <c r="F167" s="1" t="s">
         <v>1153</v>
       </c>
-      <c r="G167" s="40" t="s">
+      <c r="G167" s="38" t="s">
         <v>1154</v>
       </c>
-      <c r="H167" s="40" t="s">
+      <c r="H167" s="38" t="s">
         <v>1155</v>
       </c>
-      <c r="I167" s="40" t="s">
+      <c r="I167" s="38" t="s">
         <v>1156</v>
       </c>
-      <c r="J167" s="40" t="s">
+      <c r="J167" s="38" t="s">
         <v>1157</v>
       </c>
       <c r="K167" s="1"/>
-      <c r="L167" s="40" t="s">
+      <c r="L167" s="38" t="s">
         <v>1158</v>
       </c>
       <c r="M167" s="1">
@@ -18121,10 +18161,10 @@
       <c r="T167" s="11">
         <v>99.99</v>
       </c>
-      <c r="U167" s="33" t="s">
+      <c r="U167" s="31" t="s">
         <v>1159</v>
       </c>
-      <c r="V167" s="33" t="s">
+      <c r="V167" s="31" t="s">
         <v>1159</v>
       </c>
       <c r="X167" s="1" t="s">
@@ -18135,10 +18175,10 @@
       </c>
     </row>
     <row r="168" hidden="1" customHeight="1" spans="1:27">
-      <c r="C168" s="33" t="s">
+      <c r="C168" s="31" t="s">
         <v>1160</v>
       </c>
-      <c r="D168" s="33" t="s">
+      <c r="D168" s="31" t="s">
         <v>1161</v>
       </c>
       <c r="E168" s="1">
@@ -18147,20 +18187,20 @@
       <c r="F168" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="G168" s="40" t="s">
+      <c r="G168" s="38" t="s">
         <v>1163</v>
       </c>
-      <c r="H168" s="40" t="s">
+      <c r="H168" s="38" t="s">
         <v>1164</v>
       </c>
-      <c r="I168" s="40" t="s">
+      <c r="I168" s="38" t="s">
         <v>1165</v>
       </c>
-      <c r="J168" s="40" t="s">
+      <c r="J168" s="38" t="s">
         <v>1166</v>
       </c>
       <c r="K168" s="1"/>
-      <c r="L168" s="40" t="s">
+      <c r="L168" s="38" t="s">
         <v>1167</v>
       </c>
       <c r="M168" s="1">
@@ -18193,10 +18233,10 @@
       <c r="T168" s="11">
         <v>99.99</v>
       </c>
-      <c r="U168" s="33" t="s">
+      <c r="U168" s="31" t="s">
         <v>1168</v>
       </c>
-      <c r="V168" s="33" t="s">
+      <c r="V168" s="31" t="s">
         <v>1168</v>
       </c>
       <c r="X168" s="1" t="s">
@@ -18207,10 +18247,10 @@
       </c>
     </row>
     <row r="169" hidden="1" customHeight="1" spans="1:27">
-      <c r="C169" s="33" t="s">
+      <c r="C169" s="31" t="s">
         <v>1169</v>
       </c>
-      <c r="D169" s="33" t="s">
+      <c r="D169" s="31" t="s">
         <v>1170</v>
       </c>
       <c r="E169" s="1">
@@ -18219,20 +18259,20 @@
       <c r="F169" s="1" t="s">
         <v>1171</v>
       </c>
-      <c r="G169" s="40" t="s">
+      <c r="G169" s="38" t="s">
         <v>1172</v>
       </c>
-      <c r="H169" s="40" t="s">
+      <c r="H169" s="38" t="s">
         <v>1173</v>
       </c>
-      <c r="I169" s="40" t="s">
+      <c r="I169" s="38" t="s">
         <v>1174</v>
       </c>
-      <c r="J169" s="40" t="s">
+      <c r="J169" s="38" t="s">
         <v>1175</v>
       </c>
       <c r="K169" s="1"/>
-      <c r="L169" s="40" t="s">
+      <c r="L169" s="38" t="s">
         <v>1176</v>
       </c>
       <c r="M169" s="1">
@@ -18265,10 +18305,10 @@
       <c r="T169" s="11">
         <v>99.99</v>
       </c>
-      <c r="U169" s="33" t="s">
+      <c r="U169" s="31" t="s">
         <v>1177</v>
       </c>
-      <c r="V169" s="33" t="s">
+      <c r="V169" s="31" t="s">
         <v>1177</v>
       </c>
       <c r="X169" s="1" t="s">
@@ -18279,10 +18319,10 @@
       </c>
     </row>
     <row r="170" hidden="1" customHeight="1" spans="1:27">
-      <c r="C170" s="33" t="s">
+      <c r="C170" s="31" t="s">
         <v>1178</v>
       </c>
-      <c r="D170" s="33" t="s">
+      <c r="D170" s="31" t="s">
         <v>1179</v>
       </c>
       <c r="E170" s="1">
@@ -18291,20 +18331,20 @@
       <c r="F170" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="G170" s="40" t="s">
+      <c r="G170" s="38" t="s">
         <v>1180</v>
       </c>
-      <c r="H170" s="40" t="s">
+      <c r="H170" s="38" t="s">
         <v>1181</v>
       </c>
-      <c r="I170" s="40" t="s">
+      <c r="I170" s="38" t="s">
         <v>1182</v>
       </c>
-      <c r="J170" s="40" t="s">
+      <c r="J170" s="38" t="s">
         <v>1183</v>
       </c>
       <c r="K170" s="1"/>
-      <c r="L170" s="40" t="s">
+      <c r="L170" s="38" t="s">
         <v>1184</v>
       </c>
       <c r="M170" s="1">
@@ -18337,10 +18377,10 @@
       <c r="T170" s="11">
         <v>99.99</v>
       </c>
-      <c r="U170" s="33" t="s">
+      <c r="U170" s="31" t="s">
         <v>1185</v>
       </c>
-      <c r="V170" s="33" t="s">
+      <c r="V170" s="31" t="s">
         <v>1185</v>
       </c>
       <c r="X170" s="1" t="s">
@@ -18353,10 +18393,10 @@
     <row r="171" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A171" s="11"/>
       <c r="B171" s="11"/>
-      <c r="C171" s="33" t="s">
+      <c r="C171" s="31" t="s">
         <v>1186</v>
       </c>
-      <c r="D171" s="33" t="s">
+      <c r="D171" s="31" t="s">
         <v>1187</v>
       </c>
       <c r="E171" s="1">
@@ -18365,19 +18405,19 @@
       <c r="F171" s="1" t="s">
         <v>1188</v>
       </c>
-      <c r="G171" s="40" t="s">
+      <c r="G171" s="38" t="s">
         <v>1189</v>
       </c>
-      <c r="H171" s="40" t="s">
+      <c r="H171" s="38" t="s">
         <v>1190</v>
       </c>
-      <c r="I171" s="40" t="s">
+      <c r="I171" s="38" t="s">
         <v>1191</v>
       </c>
-      <c r="J171" s="40" t="s">
+      <c r="J171" s="38" t="s">
         <v>1192</v>
       </c>
-      <c r="L171" s="40" t="s">
+      <c r="L171" s="38" t="s">
         <v>1193</v>
       </c>
       <c r="M171" s="1">
@@ -18410,10 +18450,10 @@
       <c r="T171" s="11">
         <v>99.99</v>
       </c>
-      <c r="U171" s="33" t="s">
+      <c r="U171" s="31" t="s">
         <v>1194</v>
       </c>
-      <c r="V171" s="33" t="s">
+      <c r="V171" s="31" t="s">
         <v>1194</v>
       </c>
       <c r="X171" s="1" t="s">
@@ -18428,10 +18468,10 @@
     <row r="172" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A172" s="11"/>
       <c r="B172" s="11"/>
-      <c r="C172" s="33" t="s">
+      <c r="C172" s="31" t="s">
         <v>1195</v>
       </c>
-      <c r="D172" s="33" t="s">
+      <c r="D172" s="31" t="s">
         <v>1196</v>
       </c>
       <c r="E172" s="1">
@@ -18440,19 +18480,19 @@
       <c r="F172" s="1" t="s">
         <v>1197</v>
       </c>
-      <c r="G172" s="40" t="s">
+      <c r="G172" s="38" t="s">
         <v>1198</v>
       </c>
-      <c r="H172" s="40" t="s">
+      <c r="H172" s="38" t="s">
         <v>1199</v>
       </c>
-      <c r="I172" s="40" t="s">
+      <c r="I172" s="38" t="s">
         <v>1200</v>
       </c>
-      <c r="J172" s="40" t="s">
+      <c r="J172" s="38" t="s">
         <v>1201</v>
       </c>
-      <c r="L172" s="40" t="s">
+      <c r="L172" s="38" t="s">
         <v>1202</v>
       </c>
       <c r="M172" s="1">
@@ -18485,10 +18525,10 @@
       <c r="T172" s="11">
         <v>99.99</v>
       </c>
-      <c r="U172" s="33" t="s">
+      <c r="U172" s="31" t="s">
         <v>1203</v>
       </c>
-      <c r="V172" s="33" t="s">
+      <c r="V172" s="31" t="s">
         <v>1203</v>
       </c>
       <c r="X172" s="1" t="s">
@@ -18503,10 +18543,10 @@
     <row r="173" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A173" s="11"/>
       <c r="B173" s="11"/>
-      <c r="C173" s="33" t="s">
+      <c r="C173" s="31" t="s">
         <v>1204</v>
       </c>
-      <c r="D173" s="33" t="s">
+      <c r="D173" s="31" t="s">
         <v>1205</v>
       </c>
       <c r="E173" s="1">
@@ -18515,19 +18555,19 @@
       <c r="F173" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="G173" s="40" t="s">
+      <c r="G173" s="38" t="s">
         <v>1207</v>
       </c>
-      <c r="H173" s="40" t="s">
+      <c r="H173" s="38" t="s">
         <v>1208</v>
       </c>
-      <c r="I173" s="40" t="s">
+      <c r="I173" s="38" t="s">
         <v>1209</v>
       </c>
-      <c r="J173" s="40" t="s">
+      <c r="J173" s="38" t="s">
         <v>1210</v>
       </c>
-      <c r="L173" s="40" t="s">
+      <c r="L173" s="38" t="s">
         <v>1211</v>
       </c>
       <c r="M173" s="1">
@@ -18560,10 +18600,10 @@
       <c r="T173" s="11">
         <v>99.99</v>
       </c>
-      <c r="U173" s="33" t="s">
+      <c r="U173" s="31" t="s">
         <v>1212</v>
       </c>
-      <c r="V173" s="33" t="s">
+      <c r="V173" s="31" t="s">
         <v>1212</v>
       </c>
       <c r="X173" s="1" t="s">
@@ -18578,10 +18618,10 @@
     <row r="174" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A174" s="11"/>
       <c r="B174" s="11"/>
-      <c r="C174" s="33" t="s">
+      <c r="C174" s="31" t="s">
         <v>1213</v>
       </c>
-      <c r="D174" s="33" t="s">
+      <c r="D174" s="31" t="s">
         <v>1214</v>
       </c>
       <c r="E174" s="1">
@@ -18590,19 +18630,19 @@
       <c r="F174" s="1" t="s">
         <v>1215</v>
       </c>
-      <c r="G174" s="40" t="s">
+      <c r="G174" s="38" t="s">
         <v>1216</v>
       </c>
-      <c r="H174" s="40" t="s">
+      <c r="H174" s="38" t="s">
         <v>1217</v>
       </c>
-      <c r="I174" s="40" t="s">
+      <c r="I174" s="38" t="s">
         <v>1218</v>
       </c>
-      <c r="J174" s="40" t="s">
+      <c r="J174" s="38" t="s">
         <v>1219</v>
       </c>
-      <c r="L174" s="40" t="s">
+      <c r="L174" s="38" t="s">
         <v>1220</v>
       </c>
       <c r="M174" s="1">
@@ -18635,10 +18675,10 @@
       <c r="T174" s="11">
         <v>99.99</v>
       </c>
-      <c r="U174" s="33" t="s">
+      <c r="U174" s="31" t="s">
         <v>1221</v>
       </c>
-      <c r="V174" s="33" t="s">
+      <c r="V174" s="31" t="s">
         <v>1221</v>
       </c>
       <c r="X174" s="1" t="s">
@@ -18653,10 +18693,10 @@
     <row r="175" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A175" s="11"/>
       <c r="B175" s="11"/>
-      <c r="C175" s="33" t="s">
+      <c r="C175" s="31" t="s">
         <v>1222</v>
       </c>
-      <c r="D175" s="33" t="s">
+      <c r="D175" s="31" t="s">
         <v>1223</v>
       </c>
       <c r="E175" s="1">
@@ -18665,19 +18705,19 @@
       <c r="F175" s="1" t="s">
         <v>1224</v>
       </c>
-      <c r="G175" s="40" t="s">
+      <c r="G175" s="38" t="s">
         <v>1225</v>
       </c>
-      <c r="H175" s="40" t="s">
+      <c r="H175" s="38" t="s">
         <v>1226</v>
       </c>
-      <c r="I175" s="40" t="s">
+      <c r="I175" s="38" t="s">
         <v>1227</v>
       </c>
-      <c r="J175" s="40" t="s">
+      <c r="J175" s="38" t="s">
         <v>1228</v>
       </c>
-      <c r="L175" s="40" t="s">
+      <c r="L175" s="38" t="s">
         <v>1229</v>
       </c>
       <c r="M175" s="1">
@@ -18710,10 +18750,10 @@
       <c r="T175" s="11">
         <v>99.99</v>
       </c>
-      <c r="U175" s="33" t="s">
+      <c r="U175" s="31" t="s">
         <v>1230</v>
       </c>
-      <c r="V175" s="33" t="s">
+      <c r="V175" s="31" t="s">
         <v>1230</v>
       </c>
       <c r="X175" s="1" t="s">
@@ -18728,10 +18768,10 @@
     <row r="176" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A176" s="11"/>
       <c r="B176" s="11"/>
-      <c r="C176" s="33" t="s">
+      <c r="C176" s="31" t="s">
         <v>1231</v>
       </c>
-      <c r="D176" s="33" t="s">
+      <c r="D176" s="31" t="s">
         <v>1232</v>
       </c>
       <c r="E176" s="1">
@@ -18740,19 +18780,19 @@
       <c r="F176" s="1" t="s">
         <v>1233</v>
       </c>
-      <c r="G176" s="40" t="s">
+      <c r="G176" s="38" t="s">
         <v>1234</v>
       </c>
-      <c r="H176" s="40" t="s">
+      <c r="H176" s="38" t="s">
         <v>1235</v>
       </c>
-      <c r="I176" s="40" t="s">
+      <c r="I176" s="38" t="s">
         <v>1236</v>
       </c>
-      <c r="J176" s="40" t="s">
+      <c r="J176" s="38" t="s">
         <v>1237</v>
       </c>
-      <c r="L176" s="40" t="s">
+      <c r="L176" s="38" t="s">
         <v>1238</v>
       </c>
       <c r="M176" s="1">
@@ -18785,10 +18825,10 @@
       <c r="T176" s="11">
         <v>99.99</v>
       </c>
-      <c r="U176" s="33" t="s">
+      <c r="U176" s="31" t="s">
         <v>1239</v>
       </c>
-      <c r="V176" s="33" t="s">
+      <c r="V176" s="31" t="s">
         <v>1239</v>
       </c>
       <c r="X176" s="1" t="s">
@@ -18803,10 +18843,10 @@
     <row r="177" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A177" s="11"/>
       <c r="B177" s="11"/>
-      <c r="C177" s="33" t="s">
+      <c r="C177" s="31" t="s">
         <v>1240</v>
       </c>
-      <c r="D177" s="33" t="s">
+      <c r="D177" s="31" t="s">
         <v>1241</v>
       </c>
       <c r="E177" s="1">
@@ -18815,19 +18855,19 @@
       <c r="F177" s="1" t="s">
         <v>1242</v>
       </c>
-      <c r="G177" s="40" t="s">
+      <c r="G177" s="38" t="s">
         <v>1243</v>
       </c>
-      <c r="H177" s="40" t="s">
+      <c r="H177" s="38" t="s">
         <v>1244</v>
       </c>
-      <c r="I177" s="40" t="s">
+      <c r="I177" s="38" t="s">
         <v>1245</v>
       </c>
-      <c r="J177" s="40" t="s">
+      <c r="J177" s="38" t="s">
         <v>1246</v>
       </c>
-      <c r="L177" s="40" t="s">
+      <c r="L177" s="38" t="s">
         <v>1247</v>
       </c>
       <c r="M177" s="1">
@@ -18860,10 +18900,10 @@
       <c r="T177" s="11">
         <v>99.99</v>
       </c>
-      <c r="U177" s="33" t="s">
+      <c r="U177" s="31" t="s">
         <v>1248</v>
       </c>
-      <c r="V177" s="33" t="s">
+      <c r="V177" s="31" t="s">
         <v>1248</v>
       </c>
       <c r="X177" s="1" t="s">
@@ -18878,10 +18918,10 @@
     <row r="178" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A178" s="11"/>
       <c r="B178" s="11"/>
-      <c r="C178" s="33" t="s">
+      <c r="C178" s="31" t="s">
         <v>1249</v>
       </c>
-      <c r="D178" s="33" t="s">
+      <c r="D178" s="31" t="s">
         <v>1250</v>
       </c>
       <c r="E178" s="1">
@@ -18890,19 +18930,19 @@
       <c r="F178" s="1" t="s">
         <v>1251</v>
       </c>
-      <c r="G178" s="40" t="s">
+      <c r="G178" s="38" t="s">
         <v>1252</v>
       </c>
-      <c r="H178" s="40" t="s">
+      <c r="H178" s="38" t="s">
         <v>1253</v>
       </c>
-      <c r="I178" s="40" t="s">
+      <c r="I178" s="38" t="s">
         <v>1254</v>
       </c>
-      <c r="J178" s="40" t="s">
+      <c r="J178" s="38" t="s">
         <v>1255</v>
       </c>
-      <c r="L178" s="40" t="s">
+      <c r="L178" s="38" t="s">
         <v>1256</v>
       </c>
       <c r="M178" s="1">
@@ -18935,10 +18975,10 @@
       <c r="T178" s="11">
         <v>99.99</v>
       </c>
-      <c r="U178" s="33" t="s">
+      <c r="U178" s="31" t="s">
         <v>1257</v>
       </c>
-      <c r="V178" s="33" t="s">
+      <c r="V178" s="31" t="s">
         <v>1257</v>
       </c>
       <c r="X178" s="1" t="s">
@@ -18953,10 +18993,10 @@
     <row r="179" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A179" s="11"/>
       <c r="B179" s="11"/>
-      <c r="C179" s="33" t="s">
+      <c r="C179" s="31" t="s">
         <v>1258</v>
       </c>
-      <c r="D179" s="33" t="s">
+      <c r="D179" s="31" t="s">
         <v>1259</v>
       </c>
       <c r="E179" s="1">
@@ -18965,19 +19005,19 @@
       <c r="F179" s="1" t="s">
         <v>1260</v>
       </c>
-      <c r="G179" s="40" t="s">
+      <c r="G179" s="38" t="s">
         <v>1261</v>
       </c>
-      <c r="H179" s="40" t="s">
+      <c r="H179" s="38" t="s">
         <v>1262</v>
       </c>
-      <c r="I179" s="40" t="s">
+      <c r="I179" s="38" t="s">
         <v>1263</v>
       </c>
-      <c r="J179" s="40" t="s">
+      <c r="J179" s="38" t="s">
         <v>1264</v>
       </c>
-      <c r="L179" s="40" t="s">
+      <c r="L179" s="38" t="s">
         <v>1265</v>
       </c>
       <c r="M179" s="1">
@@ -19010,10 +19050,10 @@
       <c r="T179" s="11">
         <v>99.99</v>
       </c>
-      <c r="U179" s="33" t="s">
+      <c r="U179" s="31" t="s">
         <v>1266</v>
       </c>
-      <c r="V179" s="33" t="s">
+      <c r="V179" s="31" t="s">
         <v>1266</v>
       </c>
       <c r="X179" s="1" t="s">
@@ -19028,10 +19068,10 @@
     <row r="180" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:27">
       <c r="A180" s="11"/>
       <c r="B180" s="11"/>
-      <c r="C180" s="33" t="s">
+      <c r="C180" s="31" t="s">
         <v>1267</v>
       </c>
-      <c r="D180" s="33" t="s">
+      <c r="D180" s="31" t="s">
         <v>1268</v>
       </c>
       <c r="E180" s="1">
@@ -19040,19 +19080,19 @@
       <c r="F180" s="1" t="s">
         <v>1269</v>
       </c>
-      <c r="G180" s="40" t="s">
+      <c r="G180" s="38" t="s">
         <v>1270</v>
       </c>
-      <c r="H180" s="40" t="s">
+      <c r="H180" s="38" t="s">
         <v>1271</v>
       </c>
-      <c r="I180" s="40" t="s">
+      <c r="I180" s="38" t="s">
         <v>1272</v>
       </c>
-      <c r="J180" s="40" t="s">
+      <c r="J180" s="38" t="s">
         <v>1273</v>
       </c>
-      <c r="L180" s="40" t="s">
+      <c r="L180" s="38" t="s">
         <v>1274</v>
       </c>
       <c r="M180" s="1">
@@ -19085,10 +19125,10 @@
       <c r="T180" s="11">
         <v>99.99</v>
       </c>
-      <c r="U180" s="33" t="s">
+      <c r="U180" s="31" t="s">
         <v>1275</v>
       </c>
-      <c r="V180" s="33" t="s">
+      <c r="V180" s="31" t="s">
         <v>1275</v>
       </c>
       <c r="X180" s="1" t="s">
@@ -19103,10 +19143,10 @@
     <row r="181" s="3" customFormat="1" customHeight="1" spans="1:27">
       <c r="A181" s="19"/>
       <c r="B181" s="19"/>
-      <c r="C181" s="39" t="s">
+      <c r="C181" s="37" t="s">
         <v>1276</v>
       </c>
-      <c r="D181" s="39" t="s">
+      <c r="D181" s="37" t="s">
         <v>1277</v>
       </c>
       <c r="E181" s="3">
@@ -19115,22 +19155,22 @@
       <c r="F181" s="3" t="s">
         <v>1278</v>
       </c>
-      <c r="G181" s="43" t="s">
+      <c r="G181" s="41" t="s">
         <v>1279</v>
       </c>
-      <c r="H181" s="43" t="s">
+      <c r="H181" s="41" t="s">
         <v>1280</v>
       </c>
-      <c r="I181" s="43" t="s">
+      <c r="I181" s="41" t="s">
         <v>1281</v>
       </c>
-      <c r="J181" s="43" t="s">
+      <c r="J181" s="41" t="s">
         <v>1282</v>
       </c>
-      <c r="K181" s="39" t="s">
+      <c r="K181" s="37" t="s">
         <v>1283</v>
       </c>
-      <c r="L181" s="43" t="s">
+      <c r="L181" s="41" t="s">
         <v>1284</v>
       </c>
       <c r="M181" s="3">
@@ -19159,10 +19199,10 @@
       <c r="T181" s="19">
         <v>99.99</v>
       </c>
-      <c r="U181" s="39" t="s">
+      <c r="U181" s="37" t="s">
         <v>1285</v>
       </c>
-      <c r="V181" s="39" t="s">
+      <c r="V181" s="37" t="s">
         <v>1285</v>
       </c>
       <c r="X181" s="3" t="s">
@@ -19175,10 +19215,10 @@
     <row r="182" s="5" customFormat="1" customHeight="1" spans="1:27">
       <c r="A182" s="15"/>
       <c r="B182" s="15"/>
-      <c r="C182" s="44" t="s">
+      <c r="C182" s="42" t="s">
         <v>1286</v>
       </c>
-      <c r="D182" s="44" t="s">
+      <c r="D182" s="42" t="s">
         <v>1287</v>
       </c>
       <c r="E182" s="5">
@@ -19187,22 +19227,22 @@
       <c r="F182" s="5" t="s">
         <v>1288</v>
       </c>
-      <c r="G182" s="40" t="s">
+      <c r="G182" s="38" t="s">
         <v>1289</v>
       </c>
-      <c r="H182" s="40" t="s">
+      <c r="H182" s="38" t="s">
         <v>1290</v>
       </c>
-      <c r="I182" s="40" t="s">
+      <c r="I182" s="38" t="s">
         <v>1291</v>
       </c>
-      <c r="J182" s="40" t="s">
+      <c r="J182" s="38" t="s">
         <v>1292</v>
       </c>
-      <c r="K182" s="44" t="s">
+      <c r="K182" s="42" t="s">
         <v>1293</v>
       </c>
-      <c r="L182" s="40" t="s">
+      <c r="L182" s="38" t="s">
         <v>1294</v>
       </c>
       <c r="M182" s="5">
@@ -19236,10 +19276,10 @@
       <c r="T182" s="15">
         <v>99.99</v>
       </c>
-      <c r="U182" s="44" t="s">
+      <c r="U182" s="42" t="s">
         <v>1295</v>
       </c>
-      <c r="V182" s="44" t="s">
+      <c r="V182" s="42" t="s">
         <v>1295</v>
       </c>
       <c r="X182" s="5" t="s">
@@ -19252,10 +19292,10 @@
     <row r="183" s="1" customFormat="1" customHeight="1" spans="1:27">
       <c r="A183" s="11"/>
       <c r="B183" s="11"/>
-      <c r="C183" s="33" t="s">
+      <c r="C183" s="31" t="s">
         <v>1296</v>
       </c>
-      <c r="D183" s="33" t="s">
+      <c r="D183" s="31" t="s">
         <v>1297</v>
       </c>
       <c r="E183" s="1">
@@ -19264,22 +19304,22 @@
       <c r="F183" s="1" t="s">
         <v>1298</v>
       </c>
-      <c r="G183" s="40" t="s">
+      <c r="G183" s="38" t="s">
         <v>1299</v>
       </c>
-      <c r="H183" s="40" t="s">
+      <c r="H183" s="38" t="s">
         <v>1300</v>
       </c>
-      <c r="I183" s="40" t="s">
+      <c r="I183" s="38" t="s">
         <v>1301</v>
       </c>
-      <c r="J183" s="40" t="s">
+      <c r="J183" s="38" t="s">
         <v>1302</v>
       </c>
-      <c r="K183" s="44" t="s">
+      <c r="K183" s="42" t="s">
         <v>1303</v>
       </c>
-      <c r="L183" s="40" t="s">
+      <c r="L183" s="38" t="s">
         <v>1304</v>
       </c>
       <c r="M183" s="5">
@@ -19313,10 +19353,10 @@
       <c r="T183" s="11">
         <v>99.99</v>
       </c>
-      <c r="U183" s="44" t="s">
+      <c r="U183" s="42" t="s">
         <v>513</v>
       </c>
-      <c r="V183" s="44" t="s">
+      <c r="V183" s="42" t="s">
         <v>513</v>
       </c>
       <c r="X183" s="1" t="s">
@@ -19329,10 +19369,10 @@
     <row r="184" s="1" customFormat="1" customHeight="1" spans="1:27">
       <c r="A184" s="11"/>
       <c r="B184" s="11"/>
-      <c r="C184" s="33" t="s">
+      <c r="C184" s="31" t="s">
         <v>1305</v>
       </c>
-      <c r="D184" s="33" t="s">
+      <c r="D184" s="31" t="s">
         <v>1306</v>
       </c>
       <c r="E184" s="1">
@@ -19341,22 +19381,22 @@
       <c r="F184" s="1" t="s">
         <v>1307</v>
       </c>
-      <c r="G184" s="40" t="s">
+      <c r="G184" s="38" t="s">
         <v>1308</v>
       </c>
-      <c r="H184" s="40" t="s">
+      <c r="H184" s="38" t="s">
         <v>1309</v>
       </c>
-      <c r="I184" s="40" t="s">
+      <c r="I184" s="38" t="s">
         <v>1310</v>
       </c>
-      <c r="J184" s="40" t="s">
+      <c r="J184" s="38" t="s">
         <v>1311</v>
       </c>
-      <c r="K184" s="44" t="s">
+      <c r="K184" s="42" t="s">
         <v>1312</v>
       </c>
-      <c r="L184" s="40" t="s">
+      <c r="L184" s="38" t="s">
         <v>1279</v>
       </c>
       <c r="M184" s="5">
@@ -19390,10 +19430,10 @@
       <c r="T184" s="11">
         <v>99.99</v>
       </c>
-      <c r="U184" s="44" t="s">
+      <c r="U184" s="42" t="s">
         <v>1313</v>
       </c>
-      <c r="V184" s="44" t="s">
+      <c r="V184" s="42" t="s">
         <v>1313</v>
       </c>
       <c r="X184" s="1" t="s">
@@ -19406,10 +19446,10 @@
     <row r="185" s="1" customFormat="1" customHeight="1" spans="1:27">
       <c r="A185" s="11"/>
       <c r="B185" s="11"/>
-      <c r="C185" s="33" t="s">
+      <c r="C185" s="31" t="s">
         <v>1314</v>
       </c>
-      <c r="D185" s="33" t="s">
+      <c r="D185" s="31" t="s">
         <v>1315</v>
       </c>
       <c r="E185" s="1">
@@ -19418,22 +19458,22 @@
       <c r="F185" s="1" t="s">
         <v>1316</v>
       </c>
-      <c r="G185" s="40" t="s">
+      <c r="G185" s="38" t="s">
         <v>1317</v>
       </c>
-      <c r="H185" s="40" t="s">
+      <c r="H185" s="38" t="s">
         <v>1318</v>
       </c>
-      <c r="I185" s="40" t="s">
+      <c r="I185" s="38" t="s">
         <v>1319</v>
       </c>
-      <c r="J185" s="40" t="s">
+      <c r="J185" s="38" t="s">
         <v>1320</v>
       </c>
-      <c r="K185" s="44" t="s">
+      <c r="K185" s="42" t="s">
         <v>1321</v>
       </c>
-      <c r="L185" s="40" t="s">
+      <c r="L185" s="38" t="s">
         <v>1289</v>
       </c>
       <c r="M185" s="5">
@@ -19467,10 +19507,10 @@
       <c r="T185" s="11">
         <v>99.99</v>
       </c>
-      <c r="U185" s="44" t="s">
+      <c r="U185" s="42" t="s">
         <v>1322</v>
       </c>
-      <c r="V185" s="44" t="s">
+      <c r="V185" s="42" t="s">
         <v>1322</v>
       </c>
       <c r="X185" s="1" t="s">
@@ -19483,10 +19523,10 @@
     <row r="186" s="6" customFormat="1" customHeight="1" spans="1:27">
       <c r="A186" s="8"/>
       <c r="B186" s="8"/>
-      <c r="C186" s="45" t="s">
+      <c r="C186" s="43" t="s">
         <v>1323</v>
       </c>
-      <c r="D186" s="45" t="s">
+      <c r="D186" s="43" t="s">
         <v>1324</v>
       </c>
       <c r="E186" s="6">
@@ -19495,22 +19535,22 @@
       <c r="F186" s="6" t="s">
         <v>1325</v>
       </c>
-      <c r="G186" s="40" t="s">
+      <c r="G186" s="38" t="s">
         <v>1326</v>
       </c>
-      <c r="H186" s="46" t="s">
+      <c r="H186" s="44" t="s">
         <v>1327</v>
       </c>
-      <c r="I186" s="46" t="s">
+      <c r="I186" s="44" t="s">
         <v>1328</v>
       </c>
-      <c r="J186" s="46" t="s">
+      <c r="J186" s="44" t="s">
         <v>1329</v>
       </c>
-      <c r="K186" s="44" t="s">
+      <c r="K186" s="42" t="s">
         <v>1330</v>
       </c>
-      <c r="L186" s="46" t="s">
+      <c r="L186" s="44" t="s">
         <v>1331</v>
       </c>
       <c r="M186" s="6">
@@ -19544,10 +19584,10 @@
       <c r="T186" s="8">
         <v>99.99</v>
       </c>
-      <c r="U186" s="45" t="s">
+      <c r="U186" s="43" t="s">
         <v>1332</v>
       </c>
-      <c r="V186" s="45" t="s">
+      <c r="V186" s="43" t="s">
         <v>1332</v>
       </c>
       <c r="X186" s="6" t="s">
@@ -19562,10 +19602,10 @@
     <row r="187" s="6" customFormat="1" customHeight="1" spans="1:27">
       <c r="A187" s="8"/>
       <c r="B187" s="8"/>
-      <c r="C187" s="45" t="s">
+      <c r="C187" s="43" t="s">
         <v>1333</v>
       </c>
-      <c r="D187" s="45" t="s">
+      <c r="D187" s="43" t="s">
         <v>1334</v>
       </c>
       <c r="E187" s="6">
@@ -19574,22 +19614,22 @@
       <c r="F187" s="6" t="s">
         <v>1335</v>
       </c>
-      <c r="G187" s="40" t="s">
+      <c r="G187" s="38" t="s">
         <v>1336</v>
       </c>
-      <c r="H187" s="46" t="s">
+      <c r="H187" s="44" t="s">
         <v>1337</v>
       </c>
-      <c r="I187" s="46" t="s">
+      <c r="I187" s="44" t="s">
         <v>1338</v>
       </c>
-      <c r="J187" s="46" t="s">
+      <c r="J187" s="44" t="s">
         <v>1339</v>
       </c>
-      <c r="K187" s="44" t="s">
+      <c r="K187" s="42" t="s">
         <v>1340</v>
       </c>
-      <c r="L187" s="46" t="s">
+      <c r="L187" s="44" t="s">
         <v>1341</v>
       </c>
       <c r="M187" s="6">
@@ -19623,10 +19663,10 @@
       <c r="T187" s="8">
         <v>99.99</v>
       </c>
-      <c r="U187" s="45" t="s">
+      <c r="U187" s="43" t="s">
         <v>1342</v>
       </c>
-      <c r="V187" s="45" t="s">
+      <c r="V187" s="43" t="s">
         <v>1342</v>
       </c>
       <c r="X187" s="6" t="s">
@@ -19641,10 +19681,10 @@
     <row r="188" s="6" customFormat="1" customHeight="1" spans="1:27">
       <c r="A188" s="8"/>
       <c r="B188" s="8"/>
-      <c r="C188" s="45" t="s">
+      <c r="C188" s="43" t="s">
         <v>1343</v>
       </c>
-      <c r="D188" s="45" t="s">
+      <c r="D188" s="43" t="s">
         <v>1344</v>
       </c>
       <c r="E188" s="6">
@@ -19653,22 +19693,22 @@
       <c r="F188" s="6" t="s">
         <v>1345</v>
       </c>
-      <c r="G188" s="40" t="s">
+      <c r="G188" s="38" t="s">
         <v>1346</v>
       </c>
-      <c r="H188" s="46" t="s">
+      <c r="H188" s="44" t="s">
         <v>1347</v>
       </c>
-      <c r="I188" s="46" t="s">
+      <c r="I188" s="44" t="s">
         <v>1348</v>
       </c>
-      <c r="J188" s="46" t="s">
+      <c r="J188" s="44" t="s">
         <v>1349</v>
       </c>
-      <c r="K188" s="44" t="s">
+      <c r="K188" s="42" t="s">
         <v>1350</v>
       </c>
-      <c r="L188" s="46" t="s">
+      <c r="L188" s="44" t="s">
         <v>1351</v>
       </c>
       <c r="M188" s="6">
@@ -19702,10 +19742,10 @@
       <c r="T188" s="8">
         <v>99.99</v>
       </c>
-      <c r="U188" s="45" t="s">
+      <c r="U188" s="43" t="s">
         <v>1352</v>
       </c>
-      <c r="V188" s="45" t="s">
+      <c r="V188" s="43" t="s">
         <v>1352</v>
       </c>
       <c r="X188" s="6" t="s">
@@ -19720,10 +19760,10 @@
     <row r="189" s="6" customFormat="1" customHeight="1" spans="1:27">
       <c r="A189" s="8"/>
       <c r="B189" s="8"/>
-      <c r="C189" s="45" t="s">
+      <c r="C189" s="43" t="s">
         <v>1353</v>
       </c>
-      <c r="D189" s="45" t="s">
+      <c r="D189" s="43" t="s">
         <v>1354</v>
       </c>
       <c r="E189" s="6">
@@ -19732,22 +19772,22 @@
       <c r="F189" s="6" t="s">
         <v>1355</v>
       </c>
-      <c r="G189" s="40" t="s">
+      <c r="G189" s="38" t="s">
         <v>1356</v>
       </c>
-      <c r="H189" s="46" t="s">
+      <c r="H189" s="44" t="s">
         <v>1357</v>
       </c>
-      <c r="I189" s="46" t="s">
+      <c r="I189" s="44" t="s">
         <v>1358</v>
       </c>
-      <c r="J189" s="46" t="s">
+      <c r="J189" s="44" t="s">
         <v>1359</v>
       </c>
-      <c r="K189" s="44" t="s">
+      <c r="K189" s="42" t="s">
         <v>1360</v>
       </c>
-      <c r="L189" s="46" t="s">
+      <c r="L189" s="44" t="s">
         <v>1317</v>
       </c>
       <c r="M189" s="6">
@@ -19781,10 +19821,10 @@
       <c r="T189" s="8">
         <v>99.99</v>
       </c>
-      <c r="U189" s="45" t="s">
+      <c r="U189" s="43" t="s">
         <v>1361</v>
       </c>
-      <c r="V189" s="45" t="s">
+      <c r="V189" s="43" t="s">
         <v>1361</v>
       </c>
       <c r="X189" s="6" t="s">
@@ -19799,10 +19839,10 @@
     <row r="190" s="6" customFormat="1" customHeight="1" spans="1:27">
       <c r="A190" s="8"/>
       <c r="B190" s="8"/>
-      <c r="C190" s="45" t="s">
+      <c r="C190" s="43" t="s">
         <v>1362</v>
       </c>
-      <c r="D190" s="45" t="s">
+      <c r="D190" s="43" t="s">
         <v>1363</v>
       </c>
       <c r="E190" s="6">
@@ -19811,22 +19851,22 @@
       <c r="F190" s="6" t="s">
         <v>1364</v>
       </c>
-      <c r="G190" s="40" t="s">
+      <c r="G190" s="38" t="s">
         <v>1365</v>
       </c>
-      <c r="H190" s="46" t="s">
+      <c r="H190" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I190" s="46" t="s">
+      <c r="I190" s="44" t="s">
         <v>1366</v>
       </c>
-      <c r="J190" s="46" t="s">
+      <c r="J190" s="44" t="s">
         <v>1367</v>
       </c>
-      <c r="K190" s="44" t="s">
+      <c r="K190" s="42" t="s">
         <v>1368</v>
       </c>
-      <c r="L190" s="46" t="s">
+      <c r="L190" s="44" t="s">
         <v>1326</v>
       </c>
       <c r="M190" s="6">
@@ -19860,10 +19900,10 @@
       <c r="T190" s="8">
         <v>99.99</v>
       </c>
-      <c r="U190" s="45" t="s">
+      <c r="U190" s="43" t="s">
         <v>1369</v>
       </c>
-      <c r="V190" s="45" t="s">
+      <c r="V190" s="43" t="s">
         <v>1369</v>
       </c>
       <c r="X190" s="6" t="s">
@@ -19878,10 +19918,10 @@
     <row r="191" s="6" customFormat="1" customHeight="1" spans="1:27">
       <c r="A191" s="8"/>
       <c r="B191" s="8"/>
-      <c r="C191" s="45" t="s">
+      <c r="C191" s="43" t="s">
         <v>1370</v>
       </c>
-      <c r="D191" s="45" t="s">
+      <c r="D191" s="43" t="s">
         <v>1371</v>
       </c>
       <c r="E191" s="6">
@@ -19890,22 +19930,22 @@
       <c r="F191" s="6" t="s">
         <v>1372</v>
       </c>
-      <c r="G191" s="40" t="s">
+      <c r="G191" s="38" t="s">
         <v>1373</v>
       </c>
-      <c r="H191" s="46" t="s">
+      <c r="H191" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I191" s="46" t="s">
+      <c r="I191" s="44" t="s">
         <v>1374</v>
       </c>
-      <c r="J191" s="46" t="s">
+      <c r="J191" s="44" t="s">
         <v>1220</v>
       </c>
-      <c r="K191" s="44" t="s">
+      <c r="K191" s="42" t="s">
         <v>1375</v>
       </c>
-      <c r="L191" s="46" t="s">
+      <c r="L191" s="44" t="s">
         <v>1376</v>
       </c>
       <c r="M191" s="6">
@@ -19939,10 +19979,10 @@
       <c r="T191" s="8">
         <v>99.99</v>
       </c>
-      <c r="U191" s="45" t="s">
+      <c r="U191" s="43" t="s">
         <v>1377</v>
       </c>
-      <c r="V191" s="45" t="s">
+      <c r="V191" s="43" t="s">
         <v>1377</v>
       </c>
       <c r="X191" s="6" t="s">
@@ -19957,10 +19997,10 @@
     <row r="192" s="6" customFormat="1" customHeight="1" spans="1:27">
       <c r="A192" s="8"/>
       <c r="B192" s="8"/>
-      <c r="C192" s="45" t="s">
+      <c r="C192" s="43" t="s">
         <v>1378</v>
       </c>
-      <c r="D192" s="45" t="s">
+      <c r="D192" s="43" t="s">
         <v>1379</v>
       </c>
       <c r="E192" s="6">
@@ -19969,22 +20009,22 @@
       <c r="F192" s="6" t="s">
         <v>1380</v>
       </c>
-      <c r="G192" s="40" t="s">
+      <c r="G192" s="38" t="s">
         <v>1381</v>
       </c>
-      <c r="H192" s="46" t="s">
+      <c r="H192" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I192" s="46" t="s">
+      <c r="I192" s="44" t="s">
         <v>1382</v>
       </c>
-      <c r="J192" s="46" t="s">
+      <c r="J192" s="44" t="s">
         <v>1383</v>
       </c>
-      <c r="K192" s="44" t="s">
+      <c r="K192" s="42" t="s">
         <v>1384</v>
       </c>
-      <c r="L192" s="46" t="s">
+      <c r="L192" s="44" t="s">
         <v>1385</v>
       </c>
       <c r="M192" s="6">
@@ -20018,10 +20058,10 @@
       <c r="T192" s="8">
         <v>99.99</v>
       </c>
-      <c r="U192" s="45" t="s">
+      <c r="U192" s="43" t="s">
         <v>1386</v>
       </c>
-      <c r="V192" s="45" t="s">
+      <c r="V192" s="43" t="s">
         <v>1386</v>
       </c>
       <c r="X192" s="6" t="s">
@@ -20036,10 +20076,10 @@
     <row r="193" s="6" customFormat="1" customHeight="1" spans="1:27">
       <c r="A193" s="8"/>
       <c r="B193" s="8"/>
-      <c r="C193" s="45" t="s">
+      <c r="C193" s="43" t="s">
         <v>1387</v>
       </c>
-      <c r="D193" s="45" t="s">
+      <c r="D193" s="43" t="s">
         <v>1388</v>
       </c>
       <c r="E193" s="6">
@@ -20048,22 +20088,22 @@
       <c r="F193" s="6" t="s">
         <v>1389</v>
       </c>
-      <c r="G193" s="40" t="s">
+      <c r="G193" s="38" t="s">
         <v>1390</v>
       </c>
-      <c r="H193" s="46" t="s">
+      <c r="H193" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I193" s="46" t="s">
+      <c r="I193" s="44" t="s">
         <v>1391</v>
       </c>
-      <c r="J193" s="46" t="s">
+      <c r="J193" s="44" t="s">
         <v>1392</v>
       </c>
-      <c r="K193" s="44" t="s">
+      <c r="K193" s="42" t="s">
         <v>1393</v>
       </c>
-      <c r="L193" s="46" t="s">
+      <c r="L193" s="44" t="s">
         <v>1346</v>
       </c>
       <c r="M193" s="6">
@@ -20097,10 +20137,10 @@
       <c r="T193" s="8">
         <v>99.99</v>
       </c>
-      <c r="U193" s="45" t="s">
+      <c r="U193" s="43" t="s">
         <v>1394</v>
       </c>
-      <c r="V193" s="45" t="s">
+      <c r="V193" s="43" t="s">
         <v>1394</v>
       </c>
       <c r="X193" s="6" t="s">
@@ -20115,10 +20155,10 @@
     <row r="194" s="6" customFormat="1" customHeight="1" spans="1:27">
       <c r="A194" s="8"/>
       <c r="B194" s="8"/>
-      <c r="C194" s="45" t="s">
+      <c r="C194" s="43" t="s">
         <v>1395</v>
       </c>
-      <c r="D194" s="45" t="s">
+      <c r="D194" s="43" t="s">
         <v>1396</v>
       </c>
       <c r="E194" s="6">
@@ -20127,22 +20167,22 @@
       <c r="F194" s="6" t="s">
         <v>1397</v>
       </c>
-      <c r="G194" s="40" t="s">
+      <c r="G194" s="38" t="s">
         <v>1191</v>
       </c>
-      <c r="H194" s="46" t="s">
+      <c r="H194" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I194" s="46" t="s">
+      <c r="I194" s="44" t="s">
         <v>1398</v>
       </c>
-      <c r="J194" s="46" t="s">
+      <c r="J194" s="44" t="s">
         <v>1399</v>
       </c>
-      <c r="K194" s="44" t="s">
+      <c r="K194" s="42" t="s">
         <v>1400</v>
       </c>
-      <c r="L194" s="46" t="s">
+      <c r="L194" s="44" t="s">
         <v>1401</v>
       </c>
       <c r="M194" s="6">
@@ -20176,10 +20216,10 @@
       <c r="T194" s="8">
         <v>99.99</v>
       </c>
-      <c r="U194" s="45" t="s">
+      <c r="U194" s="43" t="s">
         <v>1402</v>
       </c>
-      <c r="V194" s="45" t="s">
+      <c r="V194" s="43" t="s">
         <v>1402</v>
       </c>
       <c r="X194" s="6" t="s">
@@ -20194,10 +20234,10 @@
     <row r="195" s="6" customFormat="1" customHeight="1" spans="1:27">
       <c r="A195" s="8"/>
       <c r="B195" s="8"/>
-      <c r="C195" s="45" t="s">
+      <c r="C195" s="43" t="s">
         <v>1403</v>
       </c>
-      <c r="D195" s="45" t="s">
+      <c r="D195" s="43" t="s">
         <v>1404</v>
       </c>
       <c r="E195" s="6">
@@ -20206,22 +20246,22 @@
       <c r="F195" s="6" t="s">
         <v>1405</v>
       </c>
-      <c r="G195" s="40" t="s">
+      <c r="G195" s="38" t="s">
         <v>1406</v>
       </c>
-      <c r="H195" s="46" t="s">
+      <c r="H195" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I195" s="46" t="s">
+      <c r="I195" s="44" t="s">
         <v>1407</v>
       </c>
-      <c r="J195" s="46" t="s">
+      <c r="J195" s="44" t="s">
         <v>1408</v>
       </c>
-      <c r="K195" s="44" t="s">
+      <c r="K195" s="42" t="s">
         <v>1409</v>
       </c>
-      <c r="L195" s="46" t="s">
+      <c r="L195" s="44" t="s">
         <v>1410</v>
       </c>
       <c r="M195" s="6">
@@ -20255,10 +20295,10 @@
       <c r="T195" s="8">
         <v>99.99</v>
       </c>
-      <c r="U195" s="45" t="s">
+      <c r="U195" s="43" t="s">
         <v>520</v>
       </c>
-      <c r="V195" s="45" t="s">
+      <c r="V195" s="43" t="s">
         <v>520</v>
       </c>
       <c r="X195" s="6" t="s">
@@ -20273,10 +20313,10 @@
     <row r="196" s="6" customFormat="1" customHeight="1" spans="1:27">
       <c r="A196" s="8"/>
       <c r="B196" s="8"/>
-      <c r="C196" s="45" t="s">
+      <c r="C196" s="43" t="s">
         <v>1411</v>
       </c>
-      <c r="D196" s="45" t="s">
+      <c r="D196" s="43" t="s">
         <v>1412</v>
       </c>
       <c r="E196" s="6">
@@ -20285,22 +20325,22 @@
       <c r="F196" s="6" t="s">
         <v>1413</v>
       </c>
-      <c r="G196" s="40" t="s">
+      <c r="G196" s="38" t="s">
         <v>1414</v>
       </c>
-      <c r="H196" s="46" t="s">
+      <c r="H196" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I196" s="46" t="s">
+      <c r="I196" s="44" t="s">
         <v>1415</v>
       </c>
-      <c r="J196" s="46" t="s">
+      <c r="J196" s="44" t="s">
         <v>1416</v>
       </c>
-      <c r="K196" s="44" t="s">
+      <c r="K196" s="42" t="s">
         <v>1417</v>
       </c>
-      <c r="L196" s="46" t="s">
+      <c r="L196" s="44" t="s">
         <v>1365</v>
       </c>
       <c r="M196" s="6">
@@ -20334,10 +20374,10 @@
       <c r="T196" s="8">
         <v>99.99</v>
       </c>
-      <c r="U196" s="45" t="s">
+      <c r="U196" s="43" t="s">
         <v>1418</v>
       </c>
-      <c r="V196" s="45" t="s">
+      <c r="V196" s="43" t="s">
         <v>1418</v>
       </c>
       <c r="X196" s="6" t="s">
@@ -20352,10 +20392,10 @@
     <row r="197" s="7" customFormat="1" customHeight="1" spans="1:27">
       <c r="A197" s="9"/>
       <c r="B197" s="9"/>
-      <c r="C197" s="47" t="s">
+      <c r="C197" s="45" t="s">
         <v>1419</v>
       </c>
-      <c r="D197" s="47" t="s">
+      <c r="D197" s="45" t="s">
         <v>1420</v>
       </c>
       <c r="E197" s="7">
@@ -20364,22 +20404,22 @@
       <c r="F197" s="7" t="s">
         <v>1421</v>
       </c>
-      <c r="G197" s="40" t="s">
+      <c r="G197" s="38" t="s">
         <v>1422</v>
       </c>
-      <c r="H197" s="46" t="s">
+      <c r="H197" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I197" s="46" t="s">
+      <c r="I197" s="44" t="s">
         <v>1423</v>
       </c>
-      <c r="J197" s="46" t="s">
+      <c r="J197" s="44" t="s">
         <v>1424</v>
       </c>
-      <c r="K197" s="44" t="s">
+      <c r="K197" s="42" t="s">
         <v>1425</v>
       </c>
-      <c r="L197" s="46" t="s">
+      <c r="L197" s="44" t="s">
         <v>1373</v>
       </c>
       <c r="M197" s="7">
@@ -20413,10 +20453,10 @@
       <c r="T197" s="9">
         <v>99.99</v>
       </c>
-      <c r="U197" s="47" t="s">
+      <c r="U197" s="45" t="s">
         <v>1426</v>
       </c>
-      <c r="V197" s="47" t="s">
+      <c r="V197" s="45" t="s">
         <v>1426</v>
       </c>
       <c r="X197" s="7" t="s">
@@ -20431,10 +20471,10 @@
     <row r="198" s="7" customFormat="1" customHeight="1" spans="1:27">
       <c r="A198" s="9"/>
       <c r="B198" s="9"/>
-      <c r="C198" s="47" t="s">
+      <c r="C198" s="45" t="s">
         <v>1427</v>
       </c>
-      <c r="D198" s="47" t="s">
+      <c r="D198" s="45" t="s">
         <v>1428</v>
       </c>
       <c r="E198" s="7">
@@ -20443,22 +20483,22 @@
       <c r="F198" s="7" t="s">
         <v>1429</v>
       </c>
-      <c r="G198" s="40" t="s">
+      <c r="G198" s="38" t="s">
         <v>1337</v>
       </c>
-      <c r="H198" s="46" t="s">
+      <c r="H198" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I198" s="46" t="s">
+      <c r="I198" s="44" t="s">
         <v>1430</v>
       </c>
-      <c r="J198" s="46" t="s">
+      <c r="J198" s="44" t="s">
         <v>1431</v>
       </c>
-      <c r="K198" s="44" t="s">
+      <c r="K198" s="42" t="s">
         <v>1432</v>
       </c>
-      <c r="L198" s="46" t="s">
+      <c r="L198" s="44" t="s">
         <v>1381</v>
       </c>
       <c r="M198" s="7">
@@ -20492,10 +20532,10 @@
       <c r="T198" s="9">
         <v>99.99</v>
       </c>
-      <c r="U198" s="47" t="s">
+      <c r="U198" s="45" t="s">
         <v>1433</v>
       </c>
-      <c r="V198" s="47" t="s">
+      <c r="V198" s="45" t="s">
         <v>1433</v>
       </c>
       <c r="X198" s="7" t="s">
@@ -20510,10 +20550,10 @@
     <row r="199" s="7" customFormat="1" customHeight="1" spans="1:27">
       <c r="A199" s="9"/>
       <c r="B199" s="9"/>
-      <c r="C199" s="47" t="s">
+      <c r="C199" s="45" t="s">
         <v>1434</v>
       </c>
-      <c r="D199" s="47" t="s">
+      <c r="D199" s="45" t="s">
         <v>1435</v>
       </c>
       <c r="E199" s="7">
@@ -20522,22 +20562,22 @@
       <c r="F199" s="7" t="s">
         <v>1436</v>
       </c>
-      <c r="G199" s="40" t="s">
+      <c r="G199" s="38" t="s">
         <v>1437</v>
       </c>
-      <c r="H199" s="46" t="s">
+      <c r="H199" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I199" s="46" t="s">
+      <c r="I199" s="44" t="s">
         <v>1438</v>
       </c>
-      <c r="J199" s="46" t="s">
+      <c r="J199" s="44" t="s">
         <v>1439</v>
       </c>
-      <c r="K199" s="44" t="s">
+      <c r="K199" s="42" t="s">
         <v>1440</v>
       </c>
-      <c r="L199" s="46" t="s">
+      <c r="L199" s="44" t="s">
         <v>1390</v>
       </c>
       <c r="M199" s="7">
@@ -20571,10 +20611,10 @@
       <c r="T199" s="9">
         <v>99.99</v>
       </c>
-      <c r="U199" s="47" t="s">
+      <c r="U199" s="45" t="s">
         <v>1441</v>
       </c>
-      <c r="V199" s="47" t="s">
+      <c r="V199" s="45" t="s">
         <v>1441</v>
       </c>
       <c r="X199" s="7" t="s">
@@ -20589,10 +20629,10 @@
     <row r="200" s="7" customFormat="1" customHeight="1" spans="1:27">
       <c r="A200" s="9"/>
       <c r="B200" s="9"/>
-      <c r="C200" s="47" t="s">
+      <c r="C200" s="45" t="s">
         <v>1442</v>
       </c>
-      <c r="D200" s="47" t="s">
+      <c r="D200" s="45" t="s">
         <v>1443</v>
       </c>
       <c r="E200" s="7">
@@ -20601,22 +20641,22 @@
       <c r="F200" s="7" t="s">
         <v>1444</v>
       </c>
-      <c r="G200" s="40" t="s">
+      <c r="G200" s="38" t="s">
         <v>1445</v>
       </c>
-      <c r="H200" s="46" t="s">
+      <c r="H200" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I200" s="46" t="s">
+      <c r="I200" s="44" t="s">
         <v>1446</v>
       </c>
-      <c r="J200" s="46" t="s">
+      <c r="J200" s="44" t="s">
         <v>1447</v>
       </c>
-      <c r="K200" s="44" t="s">
+      <c r="K200" s="42" t="s">
         <v>1448</v>
       </c>
-      <c r="L200" s="46" t="s">
+      <c r="L200" s="44" t="s">
         <v>1191</v>
       </c>
       <c r="M200" s="7">
@@ -20650,10 +20690,10 @@
       <c r="T200" s="9">
         <v>99.99</v>
       </c>
-      <c r="U200" s="47" t="s">
+      <c r="U200" s="45" t="s">
         <v>1449</v>
       </c>
-      <c r="V200" s="47" t="s">
+      <c r="V200" s="45" t="s">
         <v>1449</v>
       </c>
       <c r="X200" s="7" t="s">
@@ -20666,10 +20706,10 @@
       <c r="AA200" s="9"/>
     </row>
     <row r="201" s="8" customFormat="1" customHeight="1" spans="1:27">
-      <c r="C201" s="45" t="s">
+      <c r="C201" s="43" t="s">
         <v>1450</v>
       </c>
-      <c r="D201" s="45" t="s">
+      <c r="D201" s="43" t="s">
         <v>1451</v>
       </c>
       <c r="E201" s="6">
@@ -20678,22 +20718,22 @@
       <c r="F201" s="6" t="s">
         <v>1452</v>
       </c>
-      <c r="G201" s="46" t="s">
+      <c r="G201" s="44" t="s">
         <v>1357</v>
       </c>
-      <c r="H201" s="46" t="s">
+      <c r="H201" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I201" s="46" t="s">
+      <c r="I201" s="44" t="s">
         <v>1453</v>
       </c>
-      <c r="J201" s="46" t="s">
+      <c r="J201" s="44" t="s">
         <v>1284</v>
       </c>
-      <c r="K201" s="44" t="s">
+      <c r="K201" s="42" t="s">
         <v>1292</v>
       </c>
-      <c r="L201" s="46" t="s">
+      <c r="L201" s="44" t="s">
         <v>1406</v>
       </c>
       <c r="M201" s="6">
@@ -20727,10 +20767,10 @@
       <c r="T201" s="8">
         <v>99.99</v>
       </c>
-      <c r="U201" s="45" t="s">
+      <c r="U201" s="43" t="s">
         <v>1454</v>
       </c>
-      <c r="V201" s="45" t="s">
+      <c r="V201" s="43" t="s">
         <v>1454</v>
       </c>
       <c r="W201" s="6"/>
@@ -20742,10 +20782,10 @@
       </c>
     </row>
     <row r="202" s="9" customFormat="1" customHeight="1" spans="1:27">
-      <c r="C202" s="47" t="s">
+      <c r="C202" s="45" t="s">
         <v>1455</v>
       </c>
-      <c r="D202" s="47" t="s">
+      <c r="D202" s="45" t="s">
         <v>1456</v>
       </c>
       <c r="E202" s="7">
@@ -20754,22 +20794,22 @@
       <c r="F202" s="7" t="s">
         <v>1457</v>
       </c>
-      <c r="G202" s="46" t="s">
+      <c r="G202" s="44" t="s">
         <v>1458</v>
       </c>
-      <c r="H202" s="46" t="s">
+      <c r="H202" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I202" s="46" t="s">
+      <c r="I202" s="44" t="s">
         <v>1459</v>
       </c>
-      <c r="J202" s="46" t="s">
+      <c r="J202" s="44" t="s">
         <v>1460</v>
       </c>
-      <c r="K202" s="44" t="s">
+      <c r="K202" s="42" t="s">
         <v>1461</v>
       </c>
-      <c r="L202" s="46" t="s">
+      <c r="L202" s="44" t="s">
         <v>1414</v>
       </c>
       <c r="M202" s="7">
@@ -20803,10 +20843,10 @@
       <c r="T202" s="9">
         <v>99.99</v>
       </c>
-      <c r="U202" s="47" t="s">
+      <c r="U202" s="45" t="s">
         <v>1462</v>
       </c>
-      <c r="V202" s="47" t="s">
+      <c r="V202" s="45" t="s">
         <v>1462</v>
       </c>
       <c r="W202" s="7"/>
@@ -20818,10 +20858,10 @@
       </c>
     </row>
     <row r="203" s="9" customFormat="1" customHeight="1" spans="1:27">
-      <c r="C203" s="47" t="s">
+      <c r="C203" s="45" t="s">
         <v>1463</v>
       </c>
-      <c r="D203" s="47" t="s">
+      <c r="D203" s="45" t="s">
         <v>1464</v>
       </c>
       <c r="E203" s="7">
@@ -20830,22 +20870,22 @@
       <c r="F203" s="7" t="s">
         <v>1465</v>
       </c>
-      <c r="G203" s="46" t="s">
+      <c r="G203" s="44" t="s">
         <v>1466</v>
       </c>
-      <c r="H203" s="46" t="s">
+      <c r="H203" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I203" s="46" t="s">
+      <c r="I203" s="44" t="s">
         <v>1467</v>
       </c>
-      <c r="J203" s="46" t="s">
+      <c r="J203" s="44" t="s">
         <v>1468</v>
       </c>
-      <c r="K203" s="44" t="s">
+      <c r="K203" s="42" t="s">
         <v>1320</v>
       </c>
-      <c r="L203" s="46" t="s">
+      <c r="L203" s="44" t="s">
         <v>1422</v>
       </c>
       <c r="M203" s="7">
@@ -20879,10 +20919,10 @@
       <c r="T203" s="9">
         <v>99.99</v>
       </c>
-      <c r="U203" s="47" t="s">
+      <c r="U203" s="45" t="s">
         <v>527</v>
       </c>
-      <c r="V203" s="47" t="s">
+      <c r="V203" s="45" t="s">
         <v>527</v>
       </c>
       <c r="W203" s="7"/>
@@ -20894,10 +20934,10 @@
       </c>
     </row>
     <row r="204" s="9" customFormat="1" customHeight="1" spans="1:27">
-      <c r="C204" s="47" t="s">
+      <c r="C204" s="45" t="s">
         <v>1469</v>
       </c>
-      <c r="D204" s="47" t="s">
+      <c r="D204" s="45" t="s">
         <v>1470</v>
       </c>
       <c r="E204" s="7">
@@ -20906,22 +20946,22 @@
       <c r="F204" s="7" t="s">
         <v>1471</v>
       </c>
-      <c r="G204" s="46" t="s">
+      <c r="G204" s="44" t="s">
         <v>1472</v>
       </c>
-      <c r="H204" s="46" t="s">
+      <c r="H204" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I204" s="46" t="s">
+      <c r="I204" s="44" t="s">
         <v>1473</v>
       </c>
-      <c r="J204" s="46" t="s">
+      <c r="J204" s="44" t="s">
         <v>1474</v>
       </c>
-      <c r="K204" s="44" t="s">
+      <c r="K204" s="42" t="s">
         <v>1475</v>
       </c>
-      <c r="L204" s="46" t="s">
+      <c r="L204" s="44" t="s">
         <v>1337</v>
       </c>
       <c r="M204" s="7">
@@ -20955,10 +20995,10 @@
       <c r="T204" s="9">
         <v>99.99</v>
       </c>
-      <c r="U204" s="47" t="s">
+      <c r="U204" s="45" t="s">
         <v>1476</v>
       </c>
-      <c r="V204" s="47" t="s">
+      <c r="V204" s="45" t="s">
         <v>1476</v>
       </c>
       <c r="W204" s="7"/>
@@ -20970,10 +21010,10 @@
       </c>
     </row>
     <row r="205" s="9" customFormat="1" customHeight="1" spans="1:27">
-      <c r="C205" s="47" t="s">
+      <c r="C205" s="45" t="s">
         <v>1477</v>
       </c>
-      <c r="D205" s="47" t="s">
+      <c r="D205" s="45" t="s">
         <v>1478</v>
       </c>
       <c r="E205" s="7">
@@ -20982,22 +21022,22 @@
       <c r="F205" s="7" t="s">
         <v>1479</v>
       </c>
-      <c r="G205" s="46" t="s">
+      <c r="G205" s="44" t="s">
         <v>1480</v>
       </c>
-      <c r="H205" s="46" t="s">
+      <c r="H205" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I205" s="46" t="s">
+      <c r="I205" s="44" t="s">
         <v>1481</v>
       </c>
-      <c r="J205" s="46" t="s">
+      <c r="J205" s="44" t="s">
         <v>1294</v>
       </c>
-      <c r="K205" s="44" t="s">
+      <c r="K205" s="42" t="s">
         <v>1349</v>
       </c>
-      <c r="L205" s="46" t="s">
+      <c r="L205" s="44" t="s">
         <v>1437</v>
       </c>
       <c r="M205" s="7">
@@ -21031,10 +21071,10 @@
       <c r="T205" s="9">
         <v>99.99</v>
       </c>
-      <c r="U205" s="47" t="s">
+      <c r="U205" s="45" t="s">
         <v>1482</v>
       </c>
-      <c r="V205" s="47" t="s">
+      <c r="V205" s="45" t="s">
         <v>1482</v>
       </c>
       <c r="W205" s="7"/>
@@ -21048,10 +21088,10 @@
     <row r="206" s="6" customFormat="1" customHeight="1" spans="1:27">
       <c r="A206" s="8"/>
       <c r="B206" s="8"/>
-      <c r="C206" s="45" t="s">
+      <c r="C206" s="43" t="s">
         <v>1483</v>
       </c>
-      <c r="D206" s="45" t="s">
+      <c r="D206" s="43" t="s">
         <v>1484</v>
       </c>
       <c r="E206" s="6">
@@ -21060,22 +21100,22 @@
       <c r="F206" s="6" t="s">
         <v>1485</v>
       </c>
-      <c r="G206" s="46" t="s">
+      <c r="G206" s="44" t="s">
         <v>1486</v>
       </c>
-      <c r="H206" s="46" t="s">
+      <c r="H206" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I206" s="46" t="s">
+      <c r="I206" s="44" t="s">
         <v>1487</v>
       </c>
-      <c r="J206" s="46" t="s">
+      <c r="J206" s="44" t="s">
         <v>1488</v>
       </c>
-      <c r="K206" s="44" t="s">
+      <c r="K206" s="42" t="s">
         <v>1489</v>
       </c>
-      <c r="L206" s="46" t="s">
+      <c r="L206" s="44" t="s">
         <v>1445</v>
       </c>
       <c r="M206" s="6">
@@ -21109,10 +21149,10 @@
       <c r="T206" s="8">
         <v>99.99</v>
       </c>
-      <c r="U206" s="45" t="s">
+      <c r="U206" s="43" t="s">
         <v>1490</v>
       </c>
-      <c r="V206" s="45" t="s">
+      <c r="V206" s="43" t="s">
         <v>1490</v>
       </c>
       <c r="X206" s="6" t="s">
@@ -21127,10 +21167,10 @@
     <row r="207" s="7" customFormat="1" customHeight="1" spans="1:27">
       <c r="A207" s="9"/>
       <c r="B207" s="9"/>
-      <c r="C207" s="47" t="s">
+      <c r="C207" s="45" t="s">
         <v>1491</v>
       </c>
-      <c r="D207" s="47" t="s">
+      <c r="D207" s="45" t="s">
         <v>1492</v>
       </c>
       <c r="E207" s="7">
@@ -21139,22 +21179,22 @@
       <c r="F207" s="7" t="s">
         <v>1493</v>
       </c>
-      <c r="G207" s="46" t="s">
+      <c r="G207" s="44" t="s">
         <v>1494</v>
       </c>
-      <c r="H207" s="46" t="s">
+      <c r="H207" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I207" s="46" t="s">
+      <c r="I207" s="44" t="s">
         <v>1495</v>
       </c>
-      <c r="J207" s="46" t="s">
+      <c r="J207" s="44" t="s">
         <v>1496</v>
       </c>
-      <c r="K207" s="44" t="s">
+      <c r="K207" s="42" t="s">
         <v>1220</v>
       </c>
-      <c r="L207" s="46" t="s">
+      <c r="L207" s="44" t="s">
         <v>1357</v>
       </c>
       <c r="M207" s="7">
@@ -21188,10 +21228,10 @@
       <c r="T207" s="9">
         <v>99.99</v>
       </c>
-      <c r="U207" s="47" t="s">
+      <c r="U207" s="45" t="s">
         <v>1497</v>
       </c>
-      <c r="V207" s="47" t="s">
+      <c r="V207" s="45" t="s">
         <v>1497</v>
       </c>
       <c r="X207" s="7" t="s">
@@ -21206,10 +21246,10 @@
     <row r="208" s="7" customFormat="1" customHeight="1" spans="1:27">
       <c r="A208" s="9"/>
       <c r="B208" s="9"/>
-      <c r="C208" s="47" t="s">
+      <c r="C208" s="45" t="s">
         <v>1498</v>
       </c>
-      <c r="D208" s="47" t="s">
+      <c r="D208" s="45" t="s">
         <v>1499</v>
       </c>
       <c r="E208" s="7">
@@ -21218,22 +21258,22 @@
       <c r="F208" s="7" t="s">
         <v>1500</v>
       </c>
-      <c r="G208" s="46" t="s">
+      <c r="G208" s="44" t="s">
         <v>1501</v>
       </c>
-      <c r="H208" s="46" t="s">
+      <c r="H208" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I208" s="46" t="s">
+      <c r="I208" s="44" t="s">
         <v>1502</v>
       </c>
-      <c r="J208" s="46" t="s">
+      <c r="J208" s="44" t="s">
         <v>1503</v>
       </c>
-      <c r="K208" s="44" t="s">
+      <c r="K208" s="42" t="s">
         <v>1504</v>
       </c>
-      <c r="L208" s="46" t="s">
+      <c r="L208" s="44" t="s">
         <v>1458</v>
       </c>
       <c r="M208" s="7">
@@ -21267,10 +21307,10 @@
       <c r="T208" s="9">
         <v>99.99</v>
       </c>
-      <c r="U208" s="47" t="s">
+      <c r="U208" s="45" t="s">
         <v>1505</v>
       </c>
-      <c r="V208" s="47" t="s">
+      <c r="V208" s="45" t="s">
         <v>1505</v>
       </c>
       <c r="X208" s="7" t="s">
@@ -21285,10 +21325,10 @@
     <row r="209" s="7" customFormat="1" customHeight="1" spans="1:27">
       <c r="A209" s="9"/>
       <c r="B209" s="9"/>
-      <c r="C209" s="47" t="s">
+      <c r="C209" s="45" t="s">
         <v>1506</v>
       </c>
-      <c r="D209" s="47" t="s">
+      <c r="D209" s="45" t="s">
         <v>1507</v>
       </c>
       <c r="E209" s="7">
@@ -21297,22 +21337,22 @@
       <c r="F209" s="7" t="s">
         <v>1508</v>
       </c>
-      <c r="G209" s="46" t="s">
+      <c r="G209" s="44" t="s">
         <v>1509</v>
       </c>
-      <c r="H209" s="46" t="s">
+      <c r="H209" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I209" s="46" t="s">
+      <c r="I209" s="44" t="s">
         <v>1510</v>
       </c>
-      <c r="J209" s="46" t="s">
+      <c r="J209" s="44" t="s">
         <v>1304</v>
       </c>
-      <c r="K209" s="44" t="s">
+      <c r="K209" s="42" t="s">
         <v>1399</v>
       </c>
-      <c r="L209" s="46" t="s">
+      <c r="L209" s="44" t="s">
         <v>1466</v>
       </c>
       <c r="M209" s="7">
@@ -21346,10 +21386,10 @@
       <c r="T209" s="9">
         <v>99.99</v>
       </c>
-      <c r="U209" s="47" t="s">
+      <c r="U209" s="45" t="s">
         <v>1511</v>
       </c>
-      <c r="V209" s="47" t="s">
+      <c r="V209" s="45" t="s">
         <v>1511</v>
       </c>
       <c r="X209" s="7" t="s">
@@ -21364,10 +21404,10 @@
     <row r="210" s="7" customFormat="1" customHeight="1" spans="1:27">
       <c r="A210" s="9"/>
       <c r="B210" s="9"/>
-      <c r="C210" s="47" t="s">
+      <c r="C210" s="45" t="s">
         <v>1512</v>
       </c>
-      <c r="D210" s="47" t="s">
+      <c r="D210" s="45" t="s">
         <v>1513</v>
       </c>
       <c r="E210" s="7">
@@ -21376,22 +21416,22 @@
       <c r="F210" s="7" t="s">
         <v>1514</v>
       </c>
-      <c r="G210" s="46" t="s">
+      <c r="G210" s="44" t="s">
         <v>1319</v>
       </c>
-      <c r="H210" s="46" t="s">
+      <c r="H210" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I210" s="46" t="s">
+      <c r="I210" s="44" t="s">
         <v>1515</v>
       </c>
-      <c r="J210" s="46" t="s">
+      <c r="J210" s="44" t="s">
         <v>1516</v>
       </c>
-      <c r="K210" s="44" t="s">
+      <c r="K210" s="42" t="s">
         <v>1416</v>
       </c>
-      <c r="L210" s="46" t="s">
+      <c r="L210" s="44" t="s">
         <v>1472</v>
       </c>
       <c r="M210" s="7">
@@ -21425,10 +21465,10 @@
       <c r="T210" s="9">
         <v>99.99</v>
       </c>
-      <c r="U210" s="47" t="s">
+      <c r="U210" s="45" t="s">
         <v>1517</v>
       </c>
-      <c r="V210" s="47" t="s">
+      <c r="V210" s="45" t="s">
         <v>1517</v>
       </c>
       <c r="X210" s="7" t="s">
@@ -21443,10 +21483,10 @@
     <row r="211" s="7" customFormat="1" customHeight="1" spans="1:27">
       <c r="A211" s="9"/>
       <c r="B211" s="9"/>
-      <c r="C211" s="47" t="s">
+      <c r="C211" s="45" t="s">
         <v>1518</v>
       </c>
-      <c r="D211" s="47" t="s">
+      <c r="D211" s="45" t="s">
         <v>1519</v>
       </c>
       <c r="E211" s="7">
@@ -21455,22 +21495,22 @@
       <c r="F211" s="7" t="s">
         <v>1520</v>
       </c>
-      <c r="G211" s="46" t="s">
+      <c r="G211" s="44" t="s">
         <v>1521</v>
       </c>
-      <c r="H211" s="46" t="s">
+      <c r="H211" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I211" s="46" t="s">
+      <c r="I211" s="44" t="s">
         <v>1522</v>
       </c>
-      <c r="J211" s="46" t="s">
+      <c r="J211" s="44" t="s">
         <v>1523</v>
       </c>
-      <c r="K211" s="44" t="s">
+      <c r="K211" s="42" t="s">
         <v>1439</v>
       </c>
-      <c r="L211" s="46" t="s">
+      <c r="L211" s="44" t="s">
         <v>1480</v>
       </c>
       <c r="M211" s="7">
@@ -21494,7 +21534,7 @@
         <v>261</v>
       </c>
       <c r="R211" s="9">
-        <f t="shared" ref="R211:R230" si="92">R210+20</f>
+        <f t="shared" ref="R211:R235" si="92">R210+20</f>
         <v>604</v>
       </c>
       <c r="S211" s="9">
@@ -21504,10 +21544,10 @@
       <c r="T211" s="9">
         <v>99.99</v>
       </c>
-      <c r="U211" s="47" t="s">
+      <c r="U211" s="45" t="s">
         <v>1524</v>
       </c>
-      <c r="V211" s="47" t="s">
+      <c r="V211" s="45" t="s">
         <v>1524</v>
       </c>
       <c r="X211" s="7" t="s">
@@ -21522,10 +21562,10 @@
     <row r="212" s="7" customFormat="1" customHeight="1" spans="1:27">
       <c r="A212" s="9"/>
       <c r="B212" s="9"/>
-      <c r="C212" s="47" t="s">
+      <c r="C212" s="45" t="s">
         <v>1525</v>
       </c>
-      <c r="D212" s="47" t="s">
+      <c r="D212" s="45" t="s">
         <v>1526</v>
       </c>
       <c r="E212" s="7">
@@ -21534,22 +21574,22 @@
       <c r="F212" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="G212" s="46" t="s">
+      <c r="G212" s="44" t="s">
         <v>1528</v>
       </c>
-      <c r="H212" s="46" t="s">
+      <c r="H212" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I212" s="46" t="s">
+      <c r="I212" s="44" t="s">
         <v>1529</v>
       </c>
-      <c r="J212" s="46" t="s">
+      <c r="J212" s="44" t="s">
         <v>1530</v>
       </c>
-      <c r="K212" s="44" t="s">
+      <c r="K212" s="42" t="s">
         <v>1460</v>
       </c>
-      <c r="L212" s="46" t="s">
+      <c r="L212" s="44" t="s">
         <v>1486</v>
       </c>
       <c r="M212" s="7">
@@ -21583,10 +21623,10 @@
       <c r="T212" s="9">
         <v>99.99</v>
       </c>
-      <c r="U212" s="47" t="s">
+      <c r="U212" s="45" t="s">
         <v>1531</v>
       </c>
-      <c r="V212" s="47" t="s">
+      <c r="V212" s="45" t="s">
         <v>1531</v>
       </c>
       <c r="X212" s="7" t="s">
@@ -21601,10 +21641,10 @@
     <row r="213" s="7" customFormat="1" customHeight="1" spans="1:27">
       <c r="A213" s="9"/>
       <c r="B213" s="9"/>
-      <c r="C213" s="47" t="s">
+      <c r="C213" s="45" t="s">
         <v>1532</v>
       </c>
-      <c r="D213" s="47" t="s">
+      <c r="D213" s="45" t="s">
         <v>1533</v>
       </c>
       <c r="E213" s="7">
@@ -21613,22 +21653,22 @@
       <c r="F213" s="7" t="s">
         <v>1534</v>
       </c>
-      <c r="G213" s="46" t="s">
+      <c r="G213" s="44" t="s">
         <v>1338</v>
       </c>
-      <c r="H213" s="46" t="s">
+      <c r="H213" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I213" s="46" t="s">
+      <c r="I213" s="44" t="s">
         <v>1535</v>
       </c>
-      <c r="J213" s="46" t="s">
+      <c r="J213" s="44" t="s">
         <v>1279</v>
       </c>
-      <c r="K213" s="44" t="s">
+      <c r="K213" s="42" t="s">
         <v>1294</v>
       </c>
-      <c r="L213" s="46" t="s">
+      <c r="L213" s="44" t="s">
         <v>1494</v>
       </c>
       <c r="M213" s="7">
@@ -21662,10 +21702,10 @@
       <c r="T213" s="9">
         <v>99.99</v>
       </c>
-      <c r="U213" s="47" t="s">
+      <c r="U213" s="45" t="s">
         <v>1536</v>
       </c>
-      <c r="V213" s="47" t="s">
+      <c r="V213" s="45" t="s">
         <v>1536</v>
       </c>
       <c r="X213" s="7" t="s">
@@ -21680,10 +21720,10 @@
     <row r="214" s="7" customFormat="1" customHeight="1" spans="1:27">
       <c r="A214" s="9"/>
       <c r="B214" s="9"/>
-      <c r="C214" s="47" t="s">
+      <c r="C214" s="45" t="s">
         <v>1537</v>
       </c>
-      <c r="D214" s="47" t="s">
+      <c r="D214" s="45" t="s">
         <v>1538</v>
       </c>
       <c r="E214" s="7">
@@ -21692,22 +21732,22 @@
       <c r="F214" s="7" t="s">
         <v>1539</v>
       </c>
-      <c r="G214" s="46" t="s">
+      <c r="G214" s="44" t="s">
         <v>1540</v>
       </c>
-      <c r="H214" s="46" t="s">
+      <c r="H214" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I214" s="46" t="s">
+      <c r="I214" s="44" t="s">
         <v>1541</v>
       </c>
-      <c r="J214" s="46" t="s">
+      <c r="J214" s="44" t="s">
         <v>1542</v>
       </c>
-      <c r="K214" s="44" t="s">
+      <c r="K214" s="42" t="s">
         <v>1503</v>
       </c>
-      <c r="L214" s="46" t="s">
+      <c r="L214" s="44" t="s">
         <v>1501</v>
       </c>
       <c r="M214" s="7">
@@ -21741,10 +21781,10 @@
       <c r="T214" s="9">
         <v>99.99</v>
       </c>
-      <c r="U214" s="47" t="s">
+      <c r="U214" s="45" t="s">
         <v>1543</v>
       </c>
-      <c r="V214" s="47" t="s">
+      <c r="V214" s="45" t="s">
         <v>1543</v>
       </c>
       <c r="X214" s="7" t="s">
@@ -21759,10 +21799,10 @@
     <row r="215" s="7" customFormat="1" customHeight="1" spans="1:27">
       <c r="A215" s="9"/>
       <c r="B215" s="9"/>
-      <c r="C215" s="47" t="s">
+      <c r="C215" s="45" t="s">
         <v>1544</v>
       </c>
-      <c r="D215" s="47" t="s">
+      <c r="D215" s="45" t="s">
         <v>1545</v>
       </c>
       <c r="E215" s="7">
@@ -21771,22 +21811,22 @@
       <c r="F215" s="7" t="s">
         <v>1546</v>
       </c>
-      <c r="G215" s="46" t="s">
+      <c r="G215" s="44" t="s">
         <v>1547</v>
       </c>
-      <c r="H215" s="46" t="s">
+      <c r="H215" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I215" s="46" t="s">
+      <c r="I215" s="44" t="s">
         <v>1548</v>
       </c>
-      <c r="J215" s="46" t="s">
+      <c r="J215" s="44" t="s">
         <v>1549</v>
       </c>
-      <c r="K215" s="44" t="s">
+      <c r="K215" s="42" t="s">
         <v>1523</v>
       </c>
-      <c r="L215" s="46" t="s">
+      <c r="L215" s="44" t="s">
         <v>1509</v>
       </c>
       <c r="M215" s="7">
@@ -21820,10 +21860,10 @@
       <c r="T215" s="9">
         <v>99.99</v>
       </c>
-      <c r="U215" s="47" t="s">
+      <c r="U215" s="45" t="s">
         <v>534</v>
       </c>
-      <c r="V215" s="47" t="s">
+      <c r="V215" s="45" t="s">
         <v>534</v>
       </c>
       <c r="X215" s="7" t="s">
@@ -21838,10 +21878,10 @@
     <row r="216" s="10" customFormat="1" customHeight="1" spans="1:27">
       <c r="A216" s="27"/>
       <c r="B216" s="27"/>
-      <c r="C216" s="48" t="s">
+      <c r="C216" s="46" t="s">
         <v>1550</v>
       </c>
-      <c r="D216" s="48" t="s">
+      <c r="D216" s="46" t="s">
         <v>1551</v>
       </c>
       <c r="E216" s="28">
@@ -21850,42 +21890,42 @@
       <c r="F216" s="10" t="s">
         <v>1552</v>
       </c>
-      <c r="G216" s="49" t="s">
+      <c r="G216" s="47" t="s">
         <v>1453</v>
       </c>
-      <c r="H216" s="50" t="s">
+      <c r="H216" s="48" t="s">
         <v>1281</v>
       </c>
-      <c r="I216" s="49" t="s">
+      <c r="I216" s="47" t="s">
         <v>1553</v>
       </c>
-      <c r="J216" s="43" t="s">
+      <c r="J216" s="41" t="s">
         <v>1554</v>
       </c>
-      <c r="K216" s="39" t="s">
+      <c r="K216" s="37" t="s">
         <v>1549</v>
       </c>
-      <c r="L216" s="43" t="s">
+      <c r="L216" s="41" t="s">
         <v>1555</v>
       </c>
       <c r="M216" s="28">
-        <f t="shared" ref="M216:M230" si="94">M215+30000</f>
+        <f t="shared" ref="M216:M235" si="94">M215+30000</f>
         <v>261000</v>
       </c>
       <c r="N216" s="28">
-        <f t="shared" ref="N216:N230" si="95">N215+30000</f>
+        <f t="shared" ref="N216:N235" si="95">N215+30000</f>
         <v>261000</v>
       </c>
       <c r="O216" s="28">
-        <f t="shared" ref="O216:O230" si="96">O215+30000</f>
+        <f t="shared" ref="O216:O235" si="96">O215+30000</f>
         <v>232750</v>
       </c>
       <c r="P216" s="28">
-        <f t="shared" ref="P216:P230" si="97">P215+30000</f>
+        <f t="shared" ref="P216:P235" si="97">P215+30000</f>
         <v>232750</v>
       </c>
       <c r="Q216" s="28">
-        <f t="shared" ref="Q216:Q230" si="98">Q215+7</f>
+        <f t="shared" ref="Q216:Q235" si="98">Q215+7</f>
         <v>292</v>
       </c>
       <c r="R216" s="27">
@@ -21893,16 +21933,16 @@
         <v>704</v>
       </c>
       <c r="S216" s="27">
-        <f t="shared" ref="S216:S230" si="99">S215+30</f>
+        <f t="shared" ref="S216:S235" si="99">S215+30</f>
         <v>826</v>
       </c>
       <c r="T216" s="27">
         <v>99.99</v>
       </c>
-      <c r="U216" s="48" t="s">
+      <c r="U216" s="46" t="s">
         <v>1556</v>
       </c>
-      <c r="V216" s="48" t="s">
+      <c r="V216" s="46" t="s">
         <v>1556</v>
       </c>
       <c r="X216" s="10" t="s">
@@ -21915,10 +21955,10 @@
     <row r="217" s="5" customFormat="1" customHeight="1" spans="1:27">
       <c r="A217" s="8"/>
       <c r="B217" s="8"/>
-      <c r="C217" s="45" t="s">
+      <c r="C217" s="43" t="s">
         <v>1557</v>
       </c>
-      <c r="D217" s="47" t="s">
+      <c r="D217" s="45" t="s">
         <v>1558</v>
       </c>
       <c r="E217" s="6">
@@ -21927,22 +21967,22 @@
       <c r="F217" s="5" t="s">
         <v>1559</v>
       </c>
-      <c r="G217" s="40" t="s">
+      <c r="G217" s="38" t="s">
         <v>1560</v>
       </c>
-      <c r="H217" s="46" t="s">
+      <c r="H217" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I217" s="40" t="s">
+      <c r="I217" s="38" t="s">
         <v>1561</v>
       </c>
-      <c r="J217" s="44" t="s">
+      <c r="J217" s="42" t="s">
         <v>1562</v>
       </c>
-      <c r="K217" s="44" t="s">
+      <c r="K217" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="L217" s="40" t="s">
+      <c r="L217" s="38" t="s">
         <v>1398</v>
       </c>
       <c r="M217" s="7">
@@ -21976,10 +22016,10 @@
       <c r="T217" s="9">
         <v>99.99</v>
       </c>
-      <c r="U217" s="47" t="s">
+      <c r="U217" s="45" t="s">
         <v>1563</v>
       </c>
-      <c r="V217" s="47" t="s">
+      <c r="V217" s="45" t="s">
         <v>1563</v>
       </c>
       <c r="X217" s="5" t="s">
@@ -21992,10 +22032,10 @@
     <row r="218" s="5" customFormat="1" customHeight="1" spans="1:27">
       <c r="A218" s="8"/>
       <c r="B218" s="8"/>
-      <c r="C218" s="45" t="s">
+      <c r="C218" s="43" t="s">
         <v>1564</v>
       </c>
-      <c r="D218" s="47" t="s">
+      <c r="D218" s="45" t="s">
         <v>1565</v>
       </c>
       <c r="E218" s="6">
@@ -22004,22 +22044,22 @@
       <c r="F218" s="5" t="s">
         <v>1566</v>
       </c>
-      <c r="G218" s="40" t="s">
+      <c r="G218" s="38" t="s">
         <v>1487</v>
       </c>
-      <c r="H218" s="46" t="s">
+      <c r="H218" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I218" s="40" t="s">
+      <c r="I218" s="38" t="s">
         <v>1567</v>
       </c>
-      <c r="J218" s="40" t="s">
+      <c r="J218" s="38" t="s">
         <v>1308</v>
       </c>
-      <c r="K218" s="40" t="s">
+      <c r="K218" s="38" t="s">
         <v>1341</v>
       </c>
-      <c r="L218" s="40" t="s">
+      <c r="L218" s="38" t="s">
         <v>1415</v>
       </c>
       <c r="M218" s="7">
@@ -22053,10 +22093,10 @@
       <c r="T218" s="9">
         <v>99.99</v>
       </c>
-      <c r="U218" s="47" t="s">
+      <c r="U218" s="45" t="s">
         <v>1568</v>
       </c>
-      <c r="V218" s="47" t="s">
+      <c r="V218" s="45" t="s">
         <v>1568</v>
       </c>
       <c r="X218" s="5" t="s">
@@ -22069,10 +22109,10 @@
     <row r="219" s="5" customFormat="1" customHeight="1" spans="1:27">
       <c r="A219" s="8"/>
       <c r="B219" s="8"/>
-      <c r="C219" s="45" t="s">
+      <c r="C219" s="43" t="s">
         <v>1569</v>
       </c>
-      <c r="D219" s="47" t="s">
+      <c r="D219" s="45" t="s">
         <v>1570</v>
       </c>
       <c r="E219" s="6">
@@ -22081,22 +22121,22 @@
       <c r="F219" s="5" t="s">
         <v>1571</v>
       </c>
-      <c r="G219" s="40" t="s">
+      <c r="G219" s="38" t="s">
         <v>1572</v>
       </c>
-      <c r="H219" s="46" t="s">
+      <c r="H219" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I219" s="40" t="s">
+      <c r="I219" s="38" t="s">
         <v>1573</v>
       </c>
-      <c r="J219" s="40" t="s">
+      <c r="J219" s="38" t="s">
         <v>1574</v>
       </c>
-      <c r="K219" s="40" t="s">
+      <c r="K219" s="38" t="s">
         <v>1575</v>
       </c>
-      <c r="L219" s="40" t="s">
+      <c r="L219" s="38" t="s">
         <v>1576</v>
       </c>
       <c r="M219" s="7">
@@ -22130,10 +22170,10 @@
       <c r="T219" s="9">
         <v>99.99</v>
       </c>
-      <c r="U219" s="47" t="s">
+      <c r="U219" s="45" t="s">
         <v>1577</v>
       </c>
-      <c r="V219" s="47" t="s">
+      <c r="V219" s="45" t="s">
         <v>1577</v>
       </c>
       <c r="X219" s="5" t="s">
@@ -22144,10 +22184,10 @@
       </c>
     </row>
     <row r="220" s="5" customFormat="1" customHeight="1" spans="1:27">
-      <c r="C220" s="45" t="s">
+      <c r="C220" s="43" t="s">
         <v>1578</v>
       </c>
-      <c r="D220" s="47" t="s">
+      <c r="D220" s="45" t="s">
         <v>1579</v>
       </c>
       <c r="E220" s="6">
@@ -22156,22 +22196,22 @@
       <c r="F220" s="5" t="s">
         <v>1580</v>
       </c>
-      <c r="G220" s="40" t="s">
+      <c r="G220" s="38" t="s">
         <v>1522</v>
       </c>
-      <c r="H220" s="46" t="s">
+      <c r="H220" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I220" s="40" t="s">
+      <c r="I220" s="38" t="s">
         <v>1581</v>
       </c>
-      <c r="J220" s="40" t="s">
+      <c r="J220" s="38" t="s">
         <v>1582</v>
       </c>
-      <c r="K220" s="40" t="s">
+      <c r="K220" s="38" t="s">
         <v>1582</v>
       </c>
-      <c r="L220" s="40" t="s">
+      <c r="L220" s="38" t="s">
         <v>1453</v>
       </c>
       <c r="M220" s="7">
@@ -22205,10 +22245,10 @@
       <c r="T220" s="9">
         <v>99.99</v>
       </c>
-      <c r="U220" s="47" t="s">
+      <c r="U220" s="45" t="s">
         <v>1583</v>
       </c>
-      <c r="V220" s="47" t="s">
+      <c r="V220" s="45" t="s">
         <v>1583</v>
       </c>
       <c r="X220" s="5" t="s">
@@ -22221,10 +22261,10 @@
     <row r="221" s="3" customFormat="1" customHeight="1" spans="1:27">
       <c r="A221" s="8"/>
       <c r="B221" s="8"/>
-      <c r="C221" s="47" t="s">
+      <c r="C221" s="45" t="s">
         <v>1584</v>
       </c>
-      <c r="D221" s="47" t="s">
+      <c r="D221" s="45" t="s">
         <v>1585</v>
       </c>
       <c r="E221" s="7">
@@ -22233,22 +22273,22 @@
       <c r="F221" s="6" t="s">
         <v>1586</v>
       </c>
-      <c r="G221" s="40" t="s">
+      <c r="G221" s="38" t="s">
         <v>1587</v>
       </c>
-      <c r="H221" s="46" t="s">
+      <c r="H221" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I221" s="40" t="s">
+      <c r="I221" s="38" t="s">
         <v>1588</v>
       </c>
-      <c r="J221" s="40" t="s">
+      <c r="J221" s="38" t="s">
         <v>1376</v>
       </c>
-      <c r="K221" s="40" t="s">
+      <c r="K221" s="38" t="s">
         <v>1376</v>
       </c>
-      <c r="L221" s="40" t="s">
+      <c r="L221" s="38" t="s">
         <v>1560</v>
       </c>
       <c r="M221" s="7">
@@ -22282,10 +22322,10 @@
       <c r="T221" s="9">
         <v>99.99</v>
       </c>
-      <c r="U221" s="47" t="s">
+      <c r="U221" s="45" t="s">
         <v>1589</v>
       </c>
-      <c r="V221" s="47" t="s">
+      <c r="V221" s="45" t="s">
         <v>1589</v>
       </c>
       <c r="X221" s="3" t="s">
@@ -22298,10 +22338,10 @@
     <row r="222" s="3" customFormat="1" customHeight="1" spans="1:27">
       <c r="A222" s="8"/>
       <c r="B222" s="8"/>
-      <c r="C222" s="47" t="s">
+      <c r="C222" s="45" t="s">
         <v>1590</v>
       </c>
-      <c r="D222" s="47" t="s">
+      <c r="D222" s="45" t="s">
         <v>1591</v>
       </c>
       <c r="E222" s="7">
@@ -22310,22 +22350,22 @@
       <c r="F222" s="6" t="s">
         <v>1592</v>
       </c>
-      <c r="G222" s="40" t="s">
+      <c r="G222" s="38" t="s">
         <v>1593</v>
       </c>
-      <c r="H222" s="46" t="s">
+      <c r="H222" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I222" s="40" t="s">
+      <c r="I222" s="38" t="s">
         <v>1594</v>
       </c>
-      <c r="J222" s="40" t="s">
+      <c r="J222" s="38" t="s">
         <v>1595</v>
       </c>
-      <c r="K222" s="40" t="s">
+      <c r="K222" s="38" t="s">
         <v>1595</v>
       </c>
-      <c r="L222" s="40" t="s">
+      <c r="L222" s="38" t="s">
         <v>1487</v>
       </c>
       <c r="M222" s="7">
@@ -22359,10 +22399,10 @@
       <c r="T222" s="9">
         <v>99.99</v>
       </c>
-      <c r="U222" s="47" t="s">
+      <c r="U222" s="45" t="s">
         <v>1596</v>
       </c>
-      <c r="V222" s="47" t="s">
+      <c r="V222" s="45" t="s">
         <v>1596</v>
       </c>
       <c r="W222" s="5"/>
@@ -22376,10 +22416,10 @@
     <row r="223" s="3" customFormat="1" customHeight="1" spans="1:27">
       <c r="A223" s="8"/>
       <c r="B223" s="8"/>
-      <c r="C223" s="47" t="s">
+      <c r="C223" s="45" t="s">
         <v>1597</v>
       </c>
-      <c r="D223" s="47" t="s">
+      <c r="D223" s="45" t="s">
         <v>1598</v>
       </c>
       <c r="E223" s="7">
@@ -22388,22 +22428,22 @@
       <c r="F223" s="6" t="s">
         <v>1599</v>
       </c>
-      <c r="G223" s="40" t="s">
+      <c r="G223" s="38" t="s">
         <v>1600</v>
       </c>
-      <c r="H223" s="46" t="s">
+      <c r="H223" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I223" s="40" t="s">
+      <c r="I223" s="38" t="s">
         <v>1601</v>
       </c>
-      <c r="J223" s="40" t="s">
+      <c r="J223" s="38" t="s">
         <v>1401</v>
       </c>
-      <c r="K223" s="40" t="s">
+      <c r="K223" s="38" t="s">
         <v>1401</v>
       </c>
-      <c r="L223" s="40" t="s">
+      <c r="L223" s="38" t="s">
         <v>1572</v>
       </c>
       <c r="M223" s="7">
@@ -22437,10 +22477,10 @@
       <c r="T223" s="9">
         <v>99.99</v>
       </c>
-      <c r="U223" s="47" t="s">
+      <c r="U223" s="45" t="s">
         <v>1602</v>
       </c>
-      <c r="V223" s="47" t="s">
+      <c r="V223" s="45" t="s">
         <v>1602</v>
       </c>
       <c r="W223" s="5"/>
@@ -22454,10 +22494,10 @@
     <row r="224" s="3" customFormat="1" customHeight="1" spans="1:27">
       <c r="A224" s="8"/>
       <c r="B224" s="8"/>
-      <c r="C224" s="47" t="s">
+      <c r="C224" s="45" t="s">
         <v>1603</v>
       </c>
-      <c r="D224" s="47" t="s">
+      <c r="D224" s="45" t="s">
         <v>1604</v>
       </c>
       <c r="E224" s="7">
@@ -22466,22 +22506,22 @@
       <c r="F224" s="6" t="s">
         <v>1605</v>
       </c>
-      <c r="G224" s="40" t="s">
+      <c r="G224" s="38" t="s">
         <v>1573</v>
       </c>
-      <c r="H224" s="46" t="s">
+      <c r="H224" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I224" s="40" t="s">
+      <c r="I224" s="38" t="s">
         <v>1606</v>
       </c>
-      <c r="J224" s="40" t="s">
+      <c r="J224" s="38" t="s">
         <v>1290</v>
       </c>
-      <c r="K224" s="40" t="s">
+      <c r="K224" s="38" t="s">
         <v>1290</v>
       </c>
-      <c r="L224" s="40" t="s">
+      <c r="L224" s="38" t="s">
         <v>1522</v>
       </c>
       <c r="M224" s="7">
@@ -22515,10 +22555,10 @@
       <c r="T224" s="9">
         <v>99.99</v>
       </c>
-      <c r="U224" s="47" t="s">
+      <c r="U224" s="45" t="s">
         <v>1607</v>
       </c>
-      <c r="V224" s="47" t="s">
+      <c r="V224" s="45" t="s">
         <v>1607</v>
       </c>
       <c r="W224" s="5"/>
@@ -22532,10 +22572,10 @@
     <row r="225" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A225" s="8"/>
       <c r="B225" s="8"/>
-      <c r="C225" s="47" t="s">
+      <c r="C225" s="45" t="s">
         <v>1608</v>
       </c>
-      <c r="D225" s="47" t="s">
+      <c r="D225" s="45" t="s">
         <v>1609</v>
       </c>
       <c r="E225" s="7">
@@ -22544,22 +22584,22 @@
       <c r="F225" s="6" t="s">
         <v>1610</v>
       </c>
-      <c r="G225" s="40" t="s">
+      <c r="G225" s="38" t="s">
         <v>1611</v>
       </c>
-      <c r="H225" s="46" t="s">
+      <c r="H225" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I225" s="40" t="s">
+      <c r="I225" s="38" t="s">
         <v>1612</v>
       </c>
-      <c r="J225" s="40" t="s">
+      <c r="J225" s="38" t="s">
         <v>1373</v>
       </c>
-      <c r="K225" s="40" t="s">
+      <c r="K225" s="38" t="s">
         <v>1373</v>
       </c>
-      <c r="L225" s="40" t="s">
+      <c r="L225" s="38" t="s">
         <v>1587</v>
       </c>
       <c r="M225" s="7">
@@ -22593,10 +22633,10 @@
       <c r="T225" s="9">
         <v>99.99</v>
       </c>
-      <c r="U225" s="47" t="s">
+      <c r="U225" s="45" t="s">
         <v>1613</v>
       </c>
-      <c r="V225" s="47" t="s">
+      <c r="V225" s="45" t="s">
         <v>1613</v>
       </c>
       <c r="W225" s="5"/>
@@ -22610,10 +22650,10 @@
     <row r="226" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A226" s="8"/>
       <c r="B226" s="8"/>
-      <c r="C226" s="47" t="s">
+      <c r="C226" s="45" t="s">
         <v>1614</v>
       </c>
-      <c r="D226" s="47" t="s">
+      <c r="D226" s="45" t="s">
         <v>1615</v>
       </c>
       <c r="E226" s="7">
@@ -22622,22 +22662,22 @@
       <c r="F226" s="6" t="s">
         <v>1616</v>
       </c>
-      <c r="G226" s="51" t="s">
+      <c r="G226" s="38" t="s">
         <v>1617</v>
       </c>
-      <c r="H226" s="46" t="s">
+      <c r="H226" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I226" s="40" t="s">
+      <c r="I226" s="38" t="s">
         <v>1618</v>
       </c>
-      <c r="J226" s="52" t="s">
+      <c r="J226" s="42" t="s">
         <v>1619</v>
       </c>
-      <c r="K226" s="52" t="s">
+      <c r="K226" s="42" t="s">
         <v>1619</v>
       </c>
-      <c r="L226" s="51" t="s">
+      <c r="L226" s="38" t="s">
         <v>1593</v>
       </c>
       <c r="M226" s="7">
@@ -22671,10 +22711,10 @@
       <c r="T226" s="9">
         <v>99.99</v>
       </c>
-      <c r="U226" s="47" t="s">
+      <c r="U226" s="45" t="s">
         <v>1620</v>
       </c>
-      <c r="V226" s="47" t="s">
+      <c r="V226" s="45" t="s">
         <v>1620</v>
       </c>
       <c r="X226" s="3" t="s">
@@ -22687,10 +22727,10 @@
     <row r="227" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A227" s="8"/>
       <c r="B227" s="8"/>
-      <c r="C227" s="47" t="s">
+      <c r="C227" s="45" t="s">
         <v>1621</v>
       </c>
-      <c r="D227" s="47" t="s">
+      <c r="D227" s="45" t="s">
         <v>1622</v>
       </c>
       <c r="E227" s="7">
@@ -22699,22 +22739,22 @@
       <c r="F227" s="6" t="s">
         <v>1623</v>
       </c>
-      <c r="G227" s="51" t="s">
+      <c r="G227" s="38" t="s">
         <v>1624</v>
       </c>
-      <c r="H227" s="46" t="s">
+      <c r="H227" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I227" s="40" t="s">
+      <c r="I227" s="38" t="s">
         <v>1625</v>
       </c>
-      <c r="J227" s="52" t="s">
+      <c r="J227" s="42" t="s">
         <v>1191</v>
       </c>
-      <c r="K227" s="52" t="s">
+      <c r="K227" s="42" t="s">
         <v>1191</v>
       </c>
-      <c r="L227" s="51" t="s">
+      <c r="L227" s="38" t="s">
         <v>1600</v>
       </c>
       <c r="M227" s="7">
@@ -22748,10 +22788,10 @@
       <c r="T227" s="9">
         <v>99.99</v>
       </c>
-      <c r="U227" s="47" t="s">
+      <c r="U227" s="45" t="s">
         <v>1626</v>
       </c>
-      <c r="V227" s="47" t="s">
+      <c r="V227" s="45" t="s">
         <v>1626</v>
       </c>
       <c r="X227" s="3" t="s">
@@ -22764,10 +22804,10 @@
     <row r="228" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A228" s="8"/>
       <c r="B228" s="8"/>
-      <c r="C228" s="47" t="s">
+      <c r="C228" s="45" t="s">
         <v>1627</v>
       </c>
-      <c r="D228" s="47" t="s">
+      <c r="D228" s="45" t="s">
         <v>1628</v>
       </c>
       <c r="E228" s="7">
@@ -22776,22 +22816,22 @@
       <c r="F228" s="6" t="s">
         <v>1629</v>
       </c>
-      <c r="G228" s="51" t="s">
+      <c r="G228" s="38" t="s">
         <v>1630</v>
       </c>
-      <c r="H228" s="46" t="s">
+      <c r="H228" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I228" s="40" t="s">
+      <c r="I228" s="38" t="s">
         <v>1631</v>
       </c>
-      <c r="J228" s="52" t="s">
+      <c r="J228" s="42" t="s">
         <v>1318</v>
       </c>
-      <c r="K228" s="52" t="s">
+      <c r="K228" s="42" t="s">
         <v>1318</v>
       </c>
-      <c r="L228" s="51" t="s">
+      <c r="L228" s="38" t="s">
         <v>1573</v>
       </c>
       <c r="M228" s="7">
@@ -22825,10 +22865,10 @@
       <c r="T228" s="9">
         <v>99.99</v>
       </c>
-      <c r="U228" s="47" t="s">
+      <c r="U228" s="45" t="s">
         <v>1632</v>
       </c>
-      <c r="V228" s="47" t="s">
+      <c r="V228" s="45" t="s">
         <v>1632</v>
       </c>
       <c r="X228" s="3" t="s">
@@ -22841,10 +22881,10 @@
     <row r="229" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A229" s="8"/>
       <c r="B229" s="8"/>
-      <c r="C229" s="47" t="s">
+      <c r="C229" s="45" t="s">
         <v>1633</v>
       </c>
-      <c r="D229" s="47" t="s">
+      <c r="D229" s="45" t="s">
         <v>1634</v>
       </c>
       <c r="E229" s="7">
@@ -22853,22 +22893,22 @@
       <c r="F229" s="6" t="s">
         <v>1635</v>
       </c>
-      <c r="G229" s="51" t="s">
+      <c r="G229" s="38" t="s">
         <v>1636</v>
       </c>
-      <c r="H229" s="46" t="s">
+      <c r="H229" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I229" s="40" t="s">
+      <c r="I229" s="38" t="s">
         <v>1637</v>
       </c>
-      <c r="J229" s="52" t="s">
+      <c r="J229" s="42" t="s">
         <v>1422</v>
       </c>
-      <c r="K229" s="52" t="s">
+      <c r="K229" s="42" t="s">
         <v>1422</v>
       </c>
-      <c r="L229" s="51" t="s">
+      <c r="L229" s="38" t="s">
         <v>1611</v>
       </c>
       <c r="M229" s="7">
@@ -22902,10 +22942,10 @@
       <c r="T229" s="9">
         <v>99.99</v>
       </c>
-      <c r="U229" s="47" t="s">
+      <c r="U229" s="45" t="s">
         <v>1638</v>
       </c>
-      <c r="V229" s="47" t="s">
+      <c r="V229" s="45" t="s">
         <v>1638</v>
       </c>
       <c r="X229" s="3" t="s">
@@ -22918,10 +22958,10 @@
     <row r="230" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A230" s="8"/>
       <c r="B230" s="8"/>
-      <c r="C230" s="47" t="s">
+      <c r="C230" s="45" t="s">
         <v>1639</v>
       </c>
-      <c r="D230" s="47" t="s">
+      <c r="D230" s="45" t="s">
         <v>1640</v>
       </c>
       <c r="E230" s="7">
@@ -22930,22 +22970,22 @@
       <c r="F230" s="6" t="s">
         <v>1641</v>
       </c>
-      <c r="G230" s="51" t="s">
+      <c r="G230" s="38" t="s">
         <v>1642</v>
       </c>
-      <c r="H230" s="46" t="s">
+      <c r="H230" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I230" s="40" t="s">
+      <c r="I230" s="38" t="s">
         <v>1643</v>
       </c>
-      <c r="J230" s="52" t="s">
+      <c r="J230" s="42" t="s">
         <v>1644</v>
       </c>
-      <c r="K230" s="52" t="s">
+      <c r="K230" s="42" t="s">
         <v>1644</v>
       </c>
-      <c r="L230" s="51" t="s">
+      <c r="L230" s="38" t="s">
         <v>1645</v>
       </c>
       <c r="M230" s="7">
@@ -22979,10 +23019,10 @@
       <c r="T230" s="9">
         <v>99.99</v>
       </c>
-      <c r="U230" s="47" t="s">
+      <c r="U230" s="45" t="s">
         <v>1646</v>
       </c>
-      <c r="V230" s="47" t="s">
+      <c r="V230" s="45" t="s">
         <v>1646</v>
       </c>
       <c r="X230" s="3" t="s">
@@ -22993,73 +23033,74 @@
       </c>
     </row>
     <row r="231" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A231" s="8" t="s">
+      <c r="A231" s="8"/>
+      <c r="B231" s="8"/>
+      <c r="C231" s="45" t="s">
         <v>1647</v>
       </c>
-      <c r="B231" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C231" s="47" t="s">
+      <c r="D231" s="45" t="s">
         <v>1648</v>
-      </c>
-      <c r="D231" s="47" t="s">
-        <v>1649</v>
       </c>
       <c r="E231" s="7">
         <v>7</v>
       </c>
       <c r="F231" s="6" t="s">
+        <v>1649</v>
+      </c>
+      <c r="G231" s="38" t="s">
         <v>1650</v>
       </c>
-      <c r="G231" s="43" t="s">
-        <v>1279</v>
-      </c>
-      <c r="H231" s="46" t="s">
+      <c r="H231" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I231" s="43" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J231" s="43" t="s">
-        <v>1282</v>
-      </c>
-      <c r="K231" s="39" t="s">
-        <v>1283</v>
-      </c>
-      <c r="L231" s="43" t="s">
-        <v>1284</v>
-      </c>
-      <c r="M231" s="3">
-        <v>43000</v>
-      </c>
-      <c r="N231" s="3">
-        <v>43000</v>
-      </c>
-      <c r="O231" s="3">
-        <v>22000</v>
-      </c>
-      <c r="P231" s="3">
-        <v>22000</v>
-      </c>
-      <c r="Q231" s="3">
-        <v>100</v>
-      </c>
-      <c r="R231" s="19">
-        <f t="shared" ref="R216:R250" si="100">R230+9</f>
-        <v>993</v>
-      </c>
-      <c r="S231" s="19">
-        <f t="shared" ref="S216:S250" si="101">S230+10</f>
-        <v>1256</v>
-      </c>
-      <c r="T231" s="19">
+      <c r="I231" s="38" t="s">
+        <v>1651</v>
+      </c>
+      <c r="J231" s="42" t="s">
+        <v>1445</v>
+      </c>
+      <c r="K231" s="42" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L231" s="38" t="s">
+        <v>1601</v>
+      </c>
+      <c r="M231" s="7">
+        <f t="shared" si="94"/>
+        <v>711000</v>
+      </c>
+      <c r="N231" s="7">
+        <f t="shared" si="95"/>
+        <v>711000</v>
+      </c>
+      <c r="O231" s="7">
+        <f t="shared" si="96"/>
+        <v>682750</v>
+      </c>
+      <c r="P231" s="7">
+        <f t="shared" si="97"/>
+        <v>682750</v>
+      </c>
+      <c r="Q231" s="6">
+        <f t="shared" si="98"/>
+        <v>397</v>
+      </c>
+      <c r="R231" s="9">
+        <f t="shared" si="92"/>
+        <v>1004</v>
+      </c>
+      <c r="S231" s="9">
+        <f t="shared" si="99"/>
+        <v>1276</v>
+      </c>
+      <c r="T231" s="9">
         <v>99.99</v>
       </c>
-      <c r="U231" s="39" t="s">
-        <v>1285</v>
-      </c>
-      <c r="V231" s="39" t="s">
-        <v>1285</v>
+      <c r="U231" s="45" t="s">
+        <v>541</v>
+      </c>
+      <c r="V231" s="45" t="s">
+        <v>541</v>
       </c>
       <c r="X231" s="3" t="s">
         <v>158</v>
@@ -23069,73 +23110,74 @@
       </c>
     </row>
     <row r="232" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A232" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="B232" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C232" s="47" t="s">
-        <v>1651</v>
-      </c>
-      <c r="D232" s="47" t="s">
+      <c r="A232" s="8"/>
+      <c r="B232" s="8"/>
+      <c r="C232" s="45" t="s">
         <v>1652</v>
+      </c>
+      <c r="D232" s="45" t="s">
+        <v>1653</v>
       </c>
       <c r="E232" s="7">
         <v>7</v>
       </c>
       <c r="F232" s="7" t="s">
-        <v>1653</v>
-      </c>
-      <c r="G232" s="43" t="s">
-        <v>1279</v>
-      </c>
-      <c r="H232" s="46" t="s">
+        <v>1654</v>
+      </c>
+      <c r="G232" s="38" t="s">
+        <v>1655</v>
+      </c>
+      <c r="H232" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I232" s="43" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J232" s="43" t="s">
-        <v>1282</v>
-      </c>
-      <c r="K232" s="39" t="s">
-        <v>1283</v>
-      </c>
-      <c r="L232" s="43" t="s">
-        <v>1284</v>
-      </c>
-      <c r="M232" s="3">
-        <v>43000</v>
-      </c>
-      <c r="N232" s="3">
-        <v>43000</v>
-      </c>
-      <c r="O232" s="3">
-        <v>22000</v>
-      </c>
-      <c r="P232" s="3">
-        <v>22000</v>
-      </c>
-      <c r="Q232" s="3">
-        <v>100</v>
-      </c>
-      <c r="R232" s="19">
-        <f t="shared" si="100"/>
-        <v>1002</v>
-      </c>
-      <c r="S232" s="19">
-        <f t="shared" si="101"/>
-        <v>1266</v>
-      </c>
-      <c r="T232" s="19">
+      <c r="I232" s="38" t="s">
+        <v>1656</v>
+      </c>
+      <c r="J232" s="42" t="s">
+        <v>1657</v>
+      </c>
+      <c r="K232" s="42" t="s">
+        <v>1657</v>
+      </c>
+      <c r="L232" s="38" t="s">
+        <v>1630</v>
+      </c>
+      <c r="M232" s="7">
+        <f t="shared" si="94"/>
+        <v>741000</v>
+      </c>
+      <c r="N232" s="7">
+        <f t="shared" si="95"/>
+        <v>741000</v>
+      </c>
+      <c r="O232" s="7">
+        <f t="shared" si="96"/>
+        <v>712750</v>
+      </c>
+      <c r="P232" s="7">
+        <f t="shared" si="97"/>
+        <v>712750</v>
+      </c>
+      <c r="Q232" s="6">
+        <f t="shared" si="98"/>
+        <v>404</v>
+      </c>
+      <c r="R232" s="9">
+        <f t="shared" si="92"/>
+        <v>1024</v>
+      </c>
+      <c r="S232" s="9">
+        <f t="shared" si="99"/>
+        <v>1306</v>
+      </c>
+      <c r="T232" s="9">
         <v>99.99</v>
       </c>
-      <c r="U232" s="39" t="s">
-        <v>1285</v>
-      </c>
-      <c r="V232" s="39" t="s">
-        <v>1285</v>
+      <c r="U232" s="45" t="s">
+        <v>1658</v>
+      </c>
+      <c r="V232" s="45" t="s">
+        <v>1658</v>
       </c>
       <c r="X232" s="3" t="s">
         <v>158</v>
@@ -23145,73 +23187,74 @@
       </c>
     </row>
     <row r="233" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A233" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="B233" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C233" s="47" t="s">
-        <v>1654</v>
-      </c>
-      <c r="D233" s="47" t="s">
-        <v>1655</v>
+      <c r="A233" s="8"/>
+      <c r="B233" s="8"/>
+      <c r="C233" s="45" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D233" s="45" t="s">
+        <v>1660</v>
       </c>
       <c r="E233" s="7">
         <v>7</v>
       </c>
       <c r="F233" s="7" t="s">
-        <v>1656</v>
-      </c>
-      <c r="G233" s="43" t="s">
-        <v>1279</v>
-      </c>
-      <c r="H233" s="46" t="s">
+        <v>1661</v>
+      </c>
+      <c r="G233" s="38" t="s">
+        <v>1662</v>
+      </c>
+      <c r="H233" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I233" s="43" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J233" s="43" t="s">
-        <v>1282</v>
-      </c>
-      <c r="K233" s="39" t="s">
-        <v>1283</v>
-      </c>
-      <c r="L233" s="43" t="s">
-        <v>1284</v>
-      </c>
-      <c r="M233" s="3">
-        <v>43000</v>
-      </c>
-      <c r="N233" s="3">
-        <v>43000</v>
-      </c>
-      <c r="O233" s="3">
-        <v>22000</v>
-      </c>
-      <c r="P233" s="3">
-        <v>22000</v>
-      </c>
-      <c r="Q233" s="3">
-        <v>100</v>
-      </c>
-      <c r="R233" s="19">
-        <f t="shared" si="100"/>
-        <v>1011</v>
-      </c>
-      <c r="S233" s="19">
-        <f t="shared" si="101"/>
-        <v>1276</v>
-      </c>
-      <c r="T233" s="19">
+      <c r="I233" s="38" t="s">
+        <v>1663</v>
+      </c>
+      <c r="J233" s="42" t="s">
+        <v>1466</v>
+      </c>
+      <c r="K233" s="42" t="s">
+        <v>1466</v>
+      </c>
+      <c r="L233" s="38" t="s">
+        <v>1664</v>
+      </c>
+      <c r="M233" s="7">
+        <f t="shared" si="94"/>
+        <v>771000</v>
+      </c>
+      <c r="N233" s="7">
+        <f t="shared" si="95"/>
+        <v>771000</v>
+      </c>
+      <c r="O233" s="7">
+        <f t="shared" si="96"/>
+        <v>742750</v>
+      </c>
+      <c r="P233" s="7">
+        <f t="shared" si="97"/>
+        <v>742750</v>
+      </c>
+      <c r="Q233" s="6">
+        <f t="shared" si="98"/>
+        <v>411</v>
+      </c>
+      <c r="R233" s="9">
+        <f t="shared" si="92"/>
+        <v>1044</v>
+      </c>
+      <c r="S233" s="9">
+        <f t="shared" si="99"/>
+        <v>1336</v>
+      </c>
+      <c r="T233" s="9">
         <v>99.99</v>
       </c>
-      <c r="U233" s="39" t="s">
-        <v>1285</v>
-      </c>
-      <c r="V233" s="39" t="s">
-        <v>1285</v>
+      <c r="U233" s="45" t="s">
+        <v>1665</v>
+      </c>
+      <c r="V233" s="45" t="s">
+        <v>1665</v>
       </c>
       <c r="X233" s="3" t="s">
         <v>158</v>
@@ -23221,73 +23264,74 @@
       </c>
     </row>
     <row r="234" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A234" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="B234" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C234" s="47" t="s">
-        <v>1657</v>
-      </c>
-      <c r="D234" s="47" t="s">
-        <v>1658</v>
+      <c r="A234" s="8"/>
+      <c r="B234" s="8"/>
+      <c r="C234" s="45" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D234" s="45" t="s">
+        <v>1667</v>
       </c>
       <c r="E234" s="7">
         <v>7</v>
       </c>
       <c r="F234" s="7" t="s">
-        <v>1659</v>
-      </c>
-      <c r="G234" s="43" t="s">
-        <v>1279</v>
-      </c>
-      <c r="H234" s="46" t="s">
+        <v>1668</v>
+      </c>
+      <c r="G234" s="38" t="s">
+        <v>1669</v>
+      </c>
+      <c r="H234" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I234" s="43" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J234" s="43" t="s">
-        <v>1282</v>
-      </c>
-      <c r="K234" s="39" t="s">
-        <v>1283</v>
-      </c>
-      <c r="L234" s="43" t="s">
-        <v>1284</v>
-      </c>
-      <c r="M234" s="3">
-        <v>43000</v>
-      </c>
-      <c r="N234" s="3">
-        <v>43000</v>
-      </c>
-      <c r="O234" s="3">
-        <v>22000</v>
-      </c>
-      <c r="P234" s="3">
-        <v>22000</v>
-      </c>
-      <c r="Q234" s="3">
-        <v>100</v>
-      </c>
-      <c r="R234" s="19">
-        <f t="shared" si="100"/>
-        <v>1020</v>
-      </c>
-      <c r="S234" s="19">
-        <f t="shared" si="101"/>
-        <v>1286</v>
-      </c>
-      <c r="T234" s="19">
+      <c r="I234" s="38" t="s">
+        <v>1670</v>
+      </c>
+      <c r="J234" s="42" t="s">
+        <v>1291</v>
+      </c>
+      <c r="K234" s="42" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L234" s="38" t="s">
+        <v>1612</v>
+      </c>
+      <c r="M234" s="7">
+        <f t="shared" si="94"/>
+        <v>801000</v>
+      </c>
+      <c r="N234" s="7">
+        <f t="shared" si="95"/>
+        <v>801000</v>
+      </c>
+      <c r="O234" s="7">
+        <f t="shared" si="96"/>
+        <v>772750</v>
+      </c>
+      <c r="P234" s="7">
+        <f t="shared" si="97"/>
+        <v>772750</v>
+      </c>
+      <c r="Q234" s="6">
+        <f t="shared" si="98"/>
+        <v>418</v>
+      </c>
+      <c r="R234" s="9">
+        <f t="shared" si="92"/>
+        <v>1064</v>
+      </c>
+      <c r="S234" s="9">
+        <f t="shared" si="99"/>
+        <v>1366</v>
+      </c>
+      <c r="T234" s="9">
         <v>99.99</v>
       </c>
-      <c r="U234" s="39" t="s">
-        <v>1285</v>
-      </c>
-      <c r="V234" s="39" t="s">
-        <v>1285</v>
+      <c r="U234" s="45" t="s">
+        <v>1671</v>
+      </c>
+      <c r="V234" s="45" t="s">
+        <v>1671</v>
       </c>
       <c r="X234" s="3" t="s">
         <v>158</v>
@@ -23296,117 +23340,118 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A235" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="B235" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C235" s="47" t="s">
-        <v>1660</v>
-      </c>
-      <c r="D235" s="47" t="s">
-        <v>1661</v>
-      </c>
-      <c r="E235" s="7">
+    <row r="235" s="10" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A235" s="27"/>
+      <c r="B235" s="27"/>
+      <c r="C235" s="46" t="s">
+        <v>1672</v>
+      </c>
+      <c r="D235" s="46" t="s">
+        <v>1673</v>
+      </c>
+      <c r="E235" s="28">
         <v>7</v>
       </c>
-      <c r="F235" s="7" t="s">
-        <v>1662</v>
-      </c>
-      <c r="G235" s="43" t="s">
-        <v>1279</v>
-      </c>
-      <c r="H235" s="46" t="s">
+      <c r="F235" s="28" t="s">
+        <v>1674</v>
+      </c>
+      <c r="G235" s="38" t="s">
+        <v>1675</v>
+      </c>
+      <c r="H235" s="48" t="s">
         <v>1281</v>
       </c>
-      <c r="I235" s="43" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J235" s="43" t="s">
-        <v>1282</v>
-      </c>
-      <c r="K235" s="39" t="s">
-        <v>1283</v>
-      </c>
-      <c r="L235" s="43" t="s">
-        <v>1284</v>
-      </c>
-      <c r="M235" s="3">
-        <v>43000</v>
-      </c>
-      <c r="N235" s="3">
-        <v>43000</v>
-      </c>
-      <c r="O235" s="3">
-        <v>22000</v>
-      </c>
-      <c r="P235" s="3">
-        <v>22000</v>
-      </c>
-      <c r="Q235" s="3">
-        <v>100</v>
-      </c>
-      <c r="R235" s="19">
-        <f t="shared" si="100"/>
-        <v>1029</v>
-      </c>
-      <c r="S235" s="19">
-        <f t="shared" si="101"/>
-        <v>1296</v>
-      </c>
-      <c r="T235" s="19">
+      <c r="I235" s="38" t="s">
+        <v>1676</v>
+      </c>
+      <c r="J235" s="42" t="s">
+        <v>1486</v>
+      </c>
+      <c r="K235" s="42" t="s">
+        <v>1486</v>
+      </c>
+      <c r="L235" s="38" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M235" s="7">
+        <f t="shared" si="94"/>
+        <v>831000</v>
+      </c>
+      <c r="N235" s="7">
+        <f t="shared" si="95"/>
+        <v>831000</v>
+      </c>
+      <c r="O235" s="7">
+        <f t="shared" si="96"/>
+        <v>802750</v>
+      </c>
+      <c r="P235" s="7">
+        <f t="shared" si="97"/>
+        <v>802750</v>
+      </c>
+      <c r="Q235" s="6">
+        <f t="shared" si="98"/>
+        <v>425</v>
+      </c>
+      <c r="R235" s="9">
+        <f t="shared" si="92"/>
+        <v>1084</v>
+      </c>
+      <c r="S235" s="9">
+        <f t="shared" si="99"/>
+        <v>1396</v>
+      </c>
+      <c r="T235" s="9">
         <v>99.99</v>
       </c>
-      <c r="U235" s="39" t="s">
-        <v>1285</v>
-      </c>
-      <c r="V235" s="39" t="s">
-        <v>1285</v>
-      </c>
-      <c r="X235" s="3" t="s">
+      <c r="U235" s="45" t="s">
+        <v>1677</v>
+      </c>
+      <c r="V235" s="45" t="s">
+        <v>1677</v>
+      </c>
+      <c r="X235" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="Y235" s="3">
+      <c r="Y235" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="236" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A236" s="8" t="s">
-        <v>1647</v>
+        <v>1678</v>
       </c>
       <c r="B236" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C236" s="47" t="s">
-        <v>1663</v>
-      </c>
-      <c r="D236" s="47" t="s">
-        <v>1664</v>
+        <v>1678</v>
+      </c>
+      <c r="C236" s="45" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D236" s="45" t="s">
+        <v>1680</v>
       </c>
       <c r="E236" s="7">
         <v>7</v>
       </c>
       <c r="F236" s="6" t="s">
-        <v>1665</v>
-      </c>
-      <c r="G236" s="43" t="s">
+        <v>1681</v>
+      </c>
+      <c r="G236" s="41" t="s">
         <v>1279</v>
       </c>
-      <c r="H236" s="46" t="s">
+      <c r="H236" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I236" s="43" t="s">
+      <c r="I236" s="41" t="s">
         <v>1281</v>
       </c>
-      <c r="J236" s="43" t="s">
+      <c r="J236" s="41" t="s">
         <v>1282</v>
       </c>
-      <c r="K236" s="39" t="s">
+      <c r="K236" s="37" t="s">
         <v>1283</v>
       </c>
-      <c r="L236" s="43" t="s">
+      <c r="L236" s="41" t="s">
         <v>1284</v>
       </c>
       <c r="M236" s="3">
@@ -23425,20 +23470,20 @@
         <v>100</v>
       </c>
       <c r="R236" s="19">
-        <f t="shared" si="100"/>
-        <v>1038</v>
+        <f>R235+9</f>
+        <v>1093</v>
       </c>
       <c r="S236" s="19">
-        <f t="shared" si="101"/>
-        <v>1306</v>
+        <f>S235+10</f>
+        <v>1406</v>
       </c>
       <c r="T236" s="19">
         <v>99.99</v>
       </c>
-      <c r="U236" s="39" t="s">
+      <c r="U236" s="37" t="s">
         <v>1285</v>
       </c>
-      <c r="V236" s="39" t="s">
+      <c r="V236" s="37" t="s">
         <v>1285</v>
       </c>
       <c r="X236" s="3" t="s">
@@ -23450,39 +23495,39 @@
     </row>
     <row r="237" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A237" s="8" t="s">
-        <v>1647</v>
+        <v>1678</v>
       </c>
       <c r="B237" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C237" s="47" t="s">
-        <v>1666</v>
-      </c>
-      <c r="D237" s="47" t="s">
-        <v>1667</v>
+        <v>1678</v>
+      </c>
+      <c r="C237" s="45" t="s">
+        <v>1682</v>
+      </c>
+      <c r="D237" s="45" t="s">
+        <v>1683</v>
       </c>
       <c r="E237" s="7">
         <v>7</v>
       </c>
       <c r="F237" s="7" t="s">
-        <v>1668</v>
-      </c>
-      <c r="G237" s="43" t="s">
+        <v>1684</v>
+      </c>
+      <c r="G237" s="41" t="s">
         <v>1279</v>
       </c>
-      <c r="H237" s="46" t="s">
+      <c r="H237" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I237" s="43" t="s">
+      <c r="I237" s="41" t="s">
         <v>1281</v>
       </c>
-      <c r="J237" s="43" t="s">
+      <c r="J237" s="41" t="s">
         <v>1282</v>
       </c>
-      <c r="K237" s="39" t="s">
+      <c r="K237" s="37" t="s">
         <v>1283</v>
       </c>
-      <c r="L237" s="43" t="s">
+      <c r="L237" s="41" t="s">
         <v>1284</v>
       </c>
       <c r="M237" s="3">
@@ -23501,20 +23546,20 @@
         <v>100</v>
       </c>
       <c r="R237" s="19">
-        <f t="shared" si="100"/>
-        <v>1047</v>
+        <f>R236+9</f>
+        <v>1102</v>
       </c>
       <c r="S237" s="19">
-        <f t="shared" si="101"/>
-        <v>1316</v>
+        <f>S236+10</f>
+        <v>1416</v>
       </c>
       <c r="T237" s="19">
         <v>99.99</v>
       </c>
-      <c r="U237" s="39" t="s">
+      <c r="U237" s="37" t="s">
         <v>1285</v>
       </c>
-      <c r="V237" s="39" t="s">
+      <c r="V237" s="37" t="s">
         <v>1285</v>
       </c>
       <c r="X237" s="3" t="s">
@@ -23526,39 +23571,39 @@
     </row>
     <row r="238" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A238" s="8" t="s">
-        <v>1647</v>
+        <v>1678</v>
       </c>
       <c r="B238" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C238" s="47" t="s">
-        <v>1669</v>
-      </c>
-      <c r="D238" s="47" t="s">
-        <v>1670</v>
+        <v>1678</v>
+      </c>
+      <c r="C238" s="45" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D238" s="45" t="s">
+        <v>1686</v>
       </c>
       <c r="E238" s="7">
         <v>7</v>
       </c>
       <c r="F238" s="7" t="s">
-        <v>1671</v>
-      </c>
-      <c r="G238" s="43" t="s">
+        <v>1687</v>
+      </c>
+      <c r="G238" s="41" t="s">
         <v>1279</v>
       </c>
-      <c r="H238" s="46" t="s">
+      <c r="H238" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I238" s="43" t="s">
+      <c r="I238" s="41" t="s">
         <v>1281</v>
       </c>
-      <c r="J238" s="43" t="s">
+      <c r="J238" s="41" t="s">
         <v>1282</v>
       </c>
-      <c r="K238" s="39" t="s">
+      <c r="K238" s="37" t="s">
         <v>1283</v>
       </c>
-      <c r="L238" s="43" t="s">
+      <c r="L238" s="41" t="s">
         <v>1284</v>
       </c>
       <c r="M238" s="3">
@@ -23577,20 +23622,20 @@
         <v>100</v>
       </c>
       <c r="R238" s="19">
-        <f t="shared" si="100"/>
-        <v>1056</v>
+        <f>R237+9</f>
+        <v>1111</v>
       </c>
       <c r="S238" s="19">
-        <f t="shared" si="101"/>
-        <v>1326</v>
+        <f>S237+10</f>
+        <v>1426</v>
       </c>
       <c r="T238" s="19">
         <v>99.99</v>
       </c>
-      <c r="U238" s="39" t="s">
+      <c r="U238" s="37" t="s">
         <v>1285</v>
       </c>
-      <c r="V238" s="39" t="s">
+      <c r="V238" s="37" t="s">
         <v>1285</v>
       </c>
       <c r="X238" s="3" t="s">
@@ -23602,39 +23647,39 @@
     </row>
     <row r="239" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A239" s="8" t="s">
-        <v>1647</v>
+        <v>1678</v>
       </c>
       <c r="B239" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C239" s="47" t="s">
-        <v>1672</v>
-      </c>
-      <c r="D239" s="47" t="s">
-        <v>1673</v>
+        <v>1678</v>
+      </c>
+      <c r="C239" s="45" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D239" s="45" t="s">
+        <v>1689</v>
       </c>
       <c r="E239" s="7">
         <v>7</v>
       </c>
       <c r="F239" s="7" t="s">
-        <v>1674</v>
-      </c>
-      <c r="G239" s="43" t="s">
+        <v>1690</v>
+      </c>
+      <c r="G239" s="41" t="s">
         <v>1279</v>
       </c>
-      <c r="H239" s="46" t="s">
+      <c r="H239" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I239" s="43" t="s">
+      <c r="I239" s="41" t="s">
         <v>1281</v>
       </c>
-      <c r="J239" s="43" t="s">
+      <c r="J239" s="41" t="s">
         <v>1282</v>
       </c>
-      <c r="K239" s="39" t="s">
+      <c r="K239" s="37" t="s">
         <v>1283</v>
       </c>
-      <c r="L239" s="43" t="s">
+      <c r="L239" s="41" t="s">
         <v>1284</v>
       </c>
       <c r="M239" s="3">
@@ -23653,20 +23698,20 @@
         <v>100</v>
       </c>
       <c r="R239" s="19">
-        <f t="shared" si="100"/>
-        <v>1065</v>
+        <f>R238+9</f>
+        <v>1120</v>
       </c>
       <c r="S239" s="19">
-        <f t="shared" si="101"/>
-        <v>1336</v>
+        <f>S238+10</f>
+        <v>1436</v>
       </c>
       <c r="T239" s="19">
         <v>99.99</v>
       </c>
-      <c r="U239" s="39" t="s">
+      <c r="U239" s="37" t="s">
         <v>1285</v>
       </c>
-      <c r="V239" s="39" t="s">
+      <c r="V239" s="37" t="s">
         <v>1285</v>
       </c>
       <c r="X239" s="3" t="s">
@@ -23678,39 +23723,39 @@
     </row>
     <row r="240" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A240" s="8" t="s">
-        <v>1647</v>
+        <v>1678</v>
       </c>
       <c r="B240" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C240" s="47" t="s">
-        <v>1675</v>
-      </c>
-      <c r="D240" s="47" t="s">
-        <v>1676</v>
+        <v>1678</v>
+      </c>
+      <c r="C240" s="45" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D240" s="45" t="s">
+        <v>1692</v>
       </c>
       <c r="E240" s="7">
         <v>7</v>
       </c>
       <c r="F240" s="7" t="s">
-        <v>1677</v>
-      </c>
-      <c r="G240" s="43" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G240" s="41" t="s">
         <v>1279</v>
       </c>
-      <c r="H240" s="46" t="s">
+      <c r="H240" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I240" s="43" t="s">
+      <c r="I240" s="41" t="s">
         <v>1281</v>
       </c>
-      <c r="J240" s="43" t="s">
+      <c r="J240" s="41" t="s">
         <v>1282</v>
       </c>
-      <c r="K240" s="39" t="s">
+      <c r="K240" s="37" t="s">
         <v>1283</v>
       </c>
-      <c r="L240" s="43" t="s">
+      <c r="L240" s="41" t="s">
         <v>1284</v>
       </c>
       <c r="M240" s="3">
@@ -23729,20 +23774,20 @@
         <v>100</v>
       </c>
       <c r="R240" s="19">
-        <f t="shared" si="100"/>
-        <v>1074</v>
+        <f>R239+9</f>
+        <v>1129</v>
       </c>
       <c r="S240" s="19">
-        <f t="shared" si="101"/>
-        <v>1346</v>
+        <f>S239+10</f>
+        <v>1446</v>
       </c>
       <c r="T240" s="19">
         <v>99.99</v>
       </c>
-      <c r="U240" s="39" t="s">
+      <c r="U240" s="37" t="s">
         <v>1285</v>
       </c>
-      <c r="V240" s="39" t="s">
+      <c r="V240" s="37" t="s">
         <v>1285</v>
       </c>
       <c r="X240" s="3" t="s">
@@ -23754,39 +23799,39 @@
     </row>
     <row r="241" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A241" s="8" t="s">
-        <v>1647</v>
+        <v>1678</v>
       </c>
       <c r="B241" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C241" s="47" t="s">
         <v>1678</v>
       </c>
-      <c r="D241" s="47" t="s">
-        <v>1679</v>
+      <c r="C241" s="45" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D241" s="45" t="s">
+        <v>1695</v>
       </c>
       <c r="E241" s="7">
         <v>7</v>
       </c>
       <c r="F241" s="6" t="s">
-        <v>1680</v>
-      </c>
-      <c r="G241" s="43" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G241" s="41" t="s">
         <v>1279</v>
       </c>
-      <c r="H241" s="46" t="s">
+      <c r="H241" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I241" s="43" t="s">
+      <c r="I241" s="41" t="s">
         <v>1281</v>
       </c>
-      <c r="J241" s="43" t="s">
+      <c r="J241" s="41" t="s">
         <v>1282</v>
       </c>
-      <c r="K241" s="39" t="s">
+      <c r="K241" s="37" t="s">
         <v>1283</v>
       </c>
-      <c r="L241" s="43" t="s">
+      <c r="L241" s="41" t="s">
         <v>1284</v>
       </c>
       <c r="M241" s="3">
@@ -23805,20 +23850,20 @@
         <v>100</v>
       </c>
       <c r="R241" s="19">
-        <f t="shared" si="100"/>
-        <v>1083</v>
+        <f>R240+9</f>
+        <v>1138</v>
       </c>
       <c r="S241" s="19">
-        <f t="shared" si="101"/>
-        <v>1356</v>
+        <f>S240+10</f>
+        <v>1456</v>
       </c>
       <c r="T241" s="19">
         <v>99.99</v>
       </c>
-      <c r="U241" s="39" t="s">
+      <c r="U241" s="37" t="s">
         <v>1285</v>
       </c>
-      <c r="V241" s="39" t="s">
+      <c r="V241" s="37" t="s">
         <v>1285</v>
       </c>
       <c r="X241" s="3" t="s">
@@ -23830,39 +23875,39 @@
     </row>
     <row r="242" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A242" s="8" t="s">
-        <v>1647</v>
+        <v>1678</v>
       </c>
       <c r="B242" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C242" s="47" t="s">
-        <v>1681</v>
-      </c>
-      <c r="D242" s="47" t="s">
-        <v>1682</v>
+        <v>1678</v>
+      </c>
+      <c r="C242" s="45" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D242" s="45" t="s">
+        <v>1698</v>
       </c>
       <c r="E242" s="7">
         <v>7</v>
       </c>
       <c r="F242" s="7" t="s">
-        <v>1683</v>
-      </c>
-      <c r="G242" s="43" t="s">
+        <v>1699</v>
+      </c>
+      <c r="G242" s="41" t="s">
         <v>1279</v>
       </c>
-      <c r="H242" s="46" t="s">
+      <c r="H242" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I242" s="43" t="s">
+      <c r="I242" s="41" t="s">
         <v>1281</v>
       </c>
-      <c r="J242" s="43" t="s">
+      <c r="J242" s="41" t="s">
         <v>1282</v>
       </c>
-      <c r="K242" s="39" t="s">
+      <c r="K242" s="37" t="s">
         <v>1283</v>
       </c>
-      <c r="L242" s="43" t="s">
+      <c r="L242" s="41" t="s">
         <v>1284</v>
       </c>
       <c r="M242" s="3">
@@ -23881,20 +23926,20 @@
         <v>100</v>
       </c>
       <c r="R242" s="19">
-        <f t="shared" si="100"/>
-        <v>1092</v>
+        <f>R241+9</f>
+        <v>1147</v>
       </c>
       <c r="S242" s="19">
-        <f t="shared" si="101"/>
-        <v>1366</v>
+        <f>S241+10</f>
+        <v>1466</v>
       </c>
       <c r="T242" s="19">
         <v>99.99</v>
       </c>
-      <c r="U242" s="39" t="s">
+      <c r="U242" s="37" t="s">
         <v>1285</v>
       </c>
-      <c r="V242" s="39" t="s">
+      <c r="V242" s="37" t="s">
         <v>1285</v>
       </c>
       <c r="X242" s="3" t="s">
@@ -23906,39 +23951,39 @@
     </row>
     <row r="243" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A243" s="8" t="s">
-        <v>1647</v>
+        <v>1678</v>
       </c>
       <c r="B243" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C243" s="47" t="s">
-        <v>1684</v>
-      </c>
-      <c r="D243" s="47" t="s">
-        <v>1685</v>
+        <v>1678</v>
+      </c>
+      <c r="C243" s="45" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D243" s="45" t="s">
+        <v>1701</v>
       </c>
       <c r="E243" s="7">
         <v>7</v>
       </c>
       <c r="F243" s="7" t="s">
-        <v>1686</v>
-      </c>
-      <c r="G243" s="43" t="s">
+        <v>1702</v>
+      </c>
+      <c r="G243" s="41" t="s">
         <v>1279</v>
       </c>
-      <c r="H243" s="46" t="s">
+      <c r="H243" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I243" s="43" t="s">
+      <c r="I243" s="41" t="s">
         <v>1281</v>
       </c>
-      <c r="J243" s="43" t="s">
+      <c r="J243" s="41" t="s">
         <v>1282</v>
       </c>
-      <c r="K243" s="39" t="s">
+      <c r="K243" s="37" t="s">
         <v>1283</v>
       </c>
-      <c r="L243" s="43" t="s">
+      <c r="L243" s="41" t="s">
         <v>1284</v>
       </c>
       <c r="M243" s="3">
@@ -23957,20 +24002,20 @@
         <v>100</v>
       </c>
       <c r="R243" s="19">
-        <f t="shared" si="100"/>
-        <v>1101</v>
+        <f>R242+9</f>
+        <v>1156</v>
       </c>
       <c r="S243" s="19">
-        <f t="shared" si="101"/>
-        <v>1376</v>
+        <f>S242+10</f>
+        <v>1476</v>
       </c>
       <c r="T243" s="19">
         <v>99.99</v>
       </c>
-      <c r="U243" s="39" t="s">
+      <c r="U243" s="37" t="s">
         <v>1285</v>
       </c>
-      <c r="V243" s="39" t="s">
+      <c r="V243" s="37" t="s">
         <v>1285</v>
       </c>
       <c r="X243" s="3" t="s">
@@ -23982,39 +24027,39 @@
     </row>
     <row r="244" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A244" s="8" t="s">
-        <v>1647</v>
+        <v>1678</v>
       </c>
       <c r="B244" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C244" s="47" t="s">
-        <v>1687</v>
-      </c>
-      <c r="D244" s="47" t="s">
-        <v>1688</v>
+        <v>1678</v>
+      </c>
+      <c r="C244" s="45" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D244" s="45" t="s">
+        <v>1704</v>
       </c>
       <c r="E244" s="7">
         <v>7</v>
       </c>
       <c r="F244" s="7" t="s">
-        <v>1689</v>
-      </c>
-      <c r="G244" s="43" t="s">
+        <v>1705</v>
+      </c>
+      <c r="G244" s="41" t="s">
         <v>1279</v>
       </c>
-      <c r="H244" s="46" t="s">
+      <c r="H244" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I244" s="43" t="s">
+      <c r="I244" s="41" t="s">
         <v>1281</v>
       </c>
-      <c r="J244" s="43" t="s">
+      <c r="J244" s="41" t="s">
         <v>1282</v>
       </c>
-      <c r="K244" s="39" t="s">
+      <c r="K244" s="37" t="s">
         <v>1283</v>
       </c>
-      <c r="L244" s="43" t="s">
+      <c r="L244" s="41" t="s">
         <v>1284</v>
       </c>
       <c r="M244" s="3">
@@ -24033,20 +24078,20 @@
         <v>100</v>
       </c>
       <c r="R244" s="19">
-        <f t="shared" si="100"/>
-        <v>1110</v>
+        <f>R243+9</f>
+        <v>1165</v>
       </c>
       <c r="S244" s="19">
-        <f t="shared" si="101"/>
-        <v>1386</v>
+        <f>S243+10</f>
+        <v>1486</v>
       </c>
       <c r="T244" s="19">
         <v>99.99</v>
       </c>
-      <c r="U244" s="39" t="s">
+      <c r="U244" s="37" t="s">
         <v>1285</v>
       </c>
-      <c r="V244" s="39" t="s">
+      <c r="V244" s="37" t="s">
         <v>1285</v>
       </c>
       <c r="X244" s="3" t="s">
@@ -24058,39 +24103,39 @@
     </row>
     <row r="245" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A245" s="8" t="s">
-        <v>1647</v>
+        <v>1678</v>
       </c>
       <c r="B245" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C245" s="47" t="s">
-        <v>1690</v>
-      </c>
-      <c r="D245" s="47" t="s">
-        <v>1691</v>
+        <v>1678</v>
+      </c>
+      <c r="C245" s="45" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D245" s="45" t="s">
+        <v>1707</v>
       </c>
       <c r="E245" s="7">
         <v>7</v>
       </c>
       <c r="F245" s="7" t="s">
-        <v>1692</v>
-      </c>
-      <c r="G245" s="43" t="s">
+        <v>1708</v>
+      </c>
+      <c r="G245" s="41" t="s">
         <v>1279</v>
       </c>
-      <c r="H245" s="46" t="s">
+      <c r="H245" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I245" s="43" t="s">
+      <c r="I245" s="41" t="s">
         <v>1281</v>
       </c>
-      <c r="J245" s="43" t="s">
+      <c r="J245" s="41" t="s">
         <v>1282</v>
       </c>
-      <c r="K245" s="39" t="s">
+      <c r="K245" s="37" t="s">
         <v>1283</v>
       </c>
-      <c r="L245" s="43" t="s">
+      <c r="L245" s="41" t="s">
         <v>1284</v>
       </c>
       <c r="M245" s="3">
@@ -24109,20 +24154,20 @@
         <v>100</v>
       </c>
       <c r="R245" s="19">
-        <f t="shared" si="100"/>
-        <v>1119</v>
+        <f>R244+9</f>
+        <v>1174</v>
       </c>
       <c r="S245" s="19">
-        <f t="shared" si="101"/>
-        <v>1396</v>
+        <f>S244+10</f>
+        <v>1496</v>
       </c>
       <c r="T245" s="19">
         <v>99.99</v>
       </c>
-      <c r="U245" s="39" t="s">
+      <c r="U245" s="37" t="s">
         <v>1285</v>
       </c>
-      <c r="V245" s="39" t="s">
+      <c r="V245" s="37" t="s">
         <v>1285</v>
       </c>
       <c r="X245" s="3" t="s">
@@ -24134,39 +24179,39 @@
     </row>
     <row r="246" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A246" s="8" t="s">
-        <v>1647</v>
+        <v>1678</v>
       </c>
       <c r="B246" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C246" s="47" t="s">
-        <v>1693</v>
-      </c>
-      <c r="D246" s="47" t="s">
-        <v>1694</v>
+        <v>1678</v>
+      </c>
+      <c r="C246" s="45" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D246" s="45" t="s">
+        <v>1710</v>
       </c>
       <c r="E246" s="7">
         <v>7</v>
       </c>
       <c r="F246" s="7" t="s">
-        <v>1695</v>
-      </c>
-      <c r="G246" s="43" t="s">
+        <v>1711</v>
+      </c>
+      <c r="G246" s="41" t="s">
         <v>1279</v>
       </c>
-      <c r="H246" s="46" t="s">
+      <c r="H246" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I246" s="43" t="s">
+      <c r="I246" s="41" t="s">
         <v>1281</v>
       </c>
-      <c r="J246" s="43" t="s">
+      <c r="J246" s="41" t="s">
         <v>1282</v>
       </c>
-      <c r="K246" s="39" t="s">
+      <c r="K246" s="37" t="s">
         <v>1283</v>
       </c>
-      <c r="L246" s="43" t="s">
+      <c r="L246" s="41" t="s">
         <v>1284</v>
       </c>
       <c r="M246" s="3">
@@ -24185,20 +24230,20 @@
         <v>100</v>
       </c>
       <c r="R246" s="19">
-        <f t="shared" si="100"/>
-        <v>1128</v>
+        <f>R245+9</f>
+        <v>1183</v>
       </c>
       <c r="S246" s="19">
-        <f t="shared" si="101"/>
-        <v>1406</v>
+        <f>S245+10</f>
+        <v>1506</v>
       </c>
       <c r="T246" s="19">
         <v>99.99</v>
       </c>
-      <c r="U246" s="39" t="s">
+      <c r="U246" s="37" t="s">
         <v>1285</v>
       </c>
-      <c r="V246" s="39" t="s">
+      <c r="V246" s="37" t="s">
         <v>1285</v>
       </c>
       <c r="X246" s="3" t="s">
@@ -24210,39 +24255,39 @@
     </row>
     <row r="247" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A247" s="8" t="s">
-        <v>1647</v>
+        <v>1678</v>
       </c>
       <c r="B247" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C247" s="47" t="s">
-        <v>1696</v>
-      </c>
-      <c r="D247" s="47" t="s">
-        <v>1697</v>
+        <v>1678</v>
+      </c>
+      <c r="C247" s="45" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D247" s="45" t="s">
+        <v>1713</v>
       </c>
       <c r="E247" s="7">
         <v>7</v>
       </c>
       <c r="F247" s="7" t="s">
-        <v>1698</v>
-      </c>
-      <c r="G247" s="43" t="s">
+        <v>1714</v>
+      </c>
+      <c r="G247" s="41" t="s">
         <v>1279</v>
       </c>
-      <c r="H247" s="46" t="s">
+      <c r="H247" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I247" s="43" t="s">
+      <c r="I247" s="41" t="s">
         <v>1281</v>
       </c>
-      <c r="J247" s="43" t="s">
+      <c r="J247" s="41" t="s">
         <v>1282</v>
       </c>
-      <c r="K247" s="39" t="s">
+      <c r="K247" s="37" t="s">
         <v>1283</v>
       </c>
-      <c r="L247" s="43" t="s">
+      <c r="L247" s="41" t="s">
         <v>1284</v>
       </c>
       <c r="M247" s="3">
@@ -24261,20 +24306,20 @@
         <v>100</v>
       </c>
       <c r="R247" s="19">
-        <f t="shared" si="100"/>
-        <v>1137</v>
+        <f>R246+9</f>
+        <v>1192</v>
       </c>
       <c r="S247" s="19">
-        <f t="shared" si="101"/>
-        <v>1416</v>
+        <f>S246+10</f>
+        <v>1516</v>
       </c>
       <c r="T247" s="19">
         <v>99.99</v>
       </c>
-      <c r="U247" s="39" t="s">
+      <c r="U247" s="37" t="s">
         <v>1285</v>
       </c>
-      <c r="V247" s="39" t="s">
+      <c r="V247" s="37" t="s">
         <v>1285</v>
       </c>
       <c r="X247" s="3" t="s">
@@ -24286,39 +24331,39 @@
     </row>
     <row r="248" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A248" s="8" t="s">
-        <v>1647</v>
+        <v>1678</v>
       </c>
       <c r="B248" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C248" s="47" t="s">
-        <v>1699</v>
-      </c>
-      <c r="D248" s="47" t="s">
-        <v>1700</v>
+        <v>1678</v>
+      </c>
+      <c r="C248" s="45" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D248" s="45" t="s">
+        <v>1716</v>
       </c>
       <c r="E248" s="7">
         <v>7</v>
       </c>
       <c r="F248" s="7" t="s">
-        <v>1701</v>
-      </c>
-      <c r="G248" s="43" t="s">
+        <v>1717</v>
+      </c>
+      <c r="G248" s="41" t="s">
         <v>1279</v>
       </c>
-      <c r="H248" s="46" t="s">
+      <c r="H248" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I248" s="43" t="s">
+      <c r="I248" s="41" t="s">
         <v>1281</v>
       </c>
-      <c r="J248" s="43" t="s">
+      <c r="J248" s="41" t="s">
         <v>1282</v>
       </c>
-      <c r="K248" s="39" t="s">
+      <c r="K248" s="37" t="s">
         <v>1283</v>
       </c>
-      <c r="L248" s="43" t="s">
+      <c r="L248" s="41" t="s">
         <v>1284</v>
       </c>
       <c r="M248" s="3">
@@ -24337,20 +24382,20 @@
         <v>100</v>
       </c>
       <c r="R248" s="19">
-        <f t="shared" si="100"/>
-        <v>1146</v>
+        <f>R247+9</f>
+        <v>1201</v>
       </c>
       <c r="S248" s="19">
-        <f t="shared" si="101"/>
-        <v>1426</v>
+        <f>S247+10</f>
+        <v>1526</v>
       </c>
       <c r="T248" s="19">
         <v>99.99</v>
       </c>
-      <c r="U248" s="39" t="s">
+      <c r="U248" s="37" t="s">
         <v>1285</v>
       </c>
-      <c r="V248" s="39" t="s">
+      <c r="V248" s="37" t="s">
         <v>1285</v>
       </c>
       <c r="X248" s="3" t="s">
@@ -24362,39 +24407,39 @@
     </row>
     <row r="249" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A249" s="8" t="s">
-        <v>1647</v>
+        <v>1678</v>
       </c>
       <c r="B249" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C249" s="47" t="s">
-        <v>1702</v>
-      </c>
-      <c r="D249" s="47" t="s">
-        <v>1703</v>
+        <v>1678</v>
+      </c>
+      <c r="C249" s="45" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D249" s="45" t="s">
+        <v>1719</v>
       </c>
       <c r="E249" s="7">
         <v>7</v>
       </c>
       <c r="F249" s="7" t="s">
-        <v>1704</v>
-      </c>
-      <c r="G249" s="43" t="s">
+        <v>1720</v>
+      </c>
+      <c r="G249" s="41" t="s">
         <v>1279</v>
       </c>
-      <c r="H249" s="46" t="s">
+      <c r="H249" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I249" s="43" t="s">
+      <c r="I249" s="41" t="s">
         <v>1281</v>
       </c>
-      <c r="J249" s="43" t="s">
+      <c r="J249" s="41" t="s">
         <v>1282</v>
       </c>
-      <c r="K249" s="39" t="s">
+      <c r="K249" s="37" t="s">
         <v>1283</v>
       </c>
-      <c r="L249" s="43" t="s">
+      <c r="L249" s="41" t="s">
         <v>1284</v>
       </c>
       <c r="M249" s="3">
@@ -24413,20 +24458,20 @@
         <v>100</v>
       </c>
       <c r="R249" s="19">
-        <f t="shared" si="100"/>
-        <v>1155</v>
+        <f>R248+9</f>
+        <v>1210</v>
       </c>
       <c r="S249" s="19">
-        <f t="shared" si="101"/>
-        <v>1436</v>
+        <f>S248+10</f>
+        <v>1536</v>
       </c>
       <c r="T249" s="19">
         <v>99.99</v>
       </c>
-      <c r="U249" s="39" t="s">
+      <c r="U249" s="37" t="s">
         <v>1285</v>
       </c>
-      <c r="V249" s="39" t="s">
+      <c r="V249" s="37" t="s">
         <v>1285</v>
       </c>
       <c r="X249" s="3" t="s">
@@ -24438,39 +24483,39 @@
     </row>
     <row r="250" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A250" s="8" t="s">
-        <v>1647</v>
+        <v>1678</v>
       </c>
       <c r="B250" s="8" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C250" s="47" t="s">
-        <v>1705</v>
-      </c>
-      <c r="D250" s="47" t="s">
-        <v>1706</v>
+        <v>1678</v>
+      </c>
+      <c r="C250" s="45" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D250" s="45" t="s">
+        <v>1722</v>
       </c>
       <c r="E250" s="7">
         <v>7</v>
       </c>
       <c r="F250" s="7" t="s">
-        <v>1707</v>
-      </c>
-      <c r="G250" s="43" t="s">
+        <v>1723</v>
+      </c>
+      <c r="G250" s="41" t="s">
         <v>1279</v>
       </c>
-      <c r="H250" s="46" t="s">
+      <c r="H250" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I250" s="43" t="s">
+      <c r="I250" s="41" t="s">
         <v>1281</v>
       </c>
-      <c r="J250" s="43" t="s">
+      <c r="J250" s="41" t="s">
         <v>1282</v>
       </c>
-      <c r="K250" s="39" t="s">
+      <c r="K250" s="37" t="s">
         <v>1283</v>
       </c>
-      <c r="L250" s="43" t="s">
+      <c r="L250" s="41" t="s">
         <v>1284</v>
       </c>
       <c r="M250" s="3">
@@ -24489,20 +24534,20 @@
         <v>100</v>
       </c>
       <c r="R250" s="19">
-        <f t="shared" si="100"/>
-        <v>1164</v>
+        <f>R249+9</f>
+        <v>1219</v>
       </c>
       <c r="S250" s="19">
-        <f t="shared" si="101"/>
-        <v>1446</v>
+        <f>S249+10</f>
+        <v>1546</v>
       </c>
       <c r="T250" s="19">
         <v>99.99</v>
       </c>
-      <c r="U250" s="39" t="s">
+      <c r="U250" s="37" t="s">
         <v>1285</v>
       </c>
-      <c r="V250" s="39" t="s">
+      <c r="V250" s="37" t="s">
         <v>1285</v>
       </c>
       <c r="X250" s="3" t="s">

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -83,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2551" uniqueCount="1724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2541" uniqueCount="1742">
   <si>
     <t>ID</t>
   </si>
@@ -5119,52 +5124,106 @@
     <t>62000000000000</t>
   </si>
   <si>
+    <t>10230</t>
+  </si>
+  <si>
+    <t>1230</t>
+  </si>
+  <si>
+    <t>虚无恶魔教主</t>
+  </si>
+  <si>
+    <t>1E+291</t>
+  </si>
+  <si>
+    <t>1E+153</t>
+  </si>
+  <si>
+    <t>1E+262</t>
+  </si>
+  <si>
+    <t>63000000000000</t>
+  </si>
+  <si>
+    <t>10231</t>
+  </si>
+  <si>
+    <t>1231</t>
+  </si>
+  <si>
+    <t>虚无恶魔教皇</t>
+  </si>
+  <si>
+    <t>1E+277</t>
+  </si>
+  <si>
+    <t>1E+294</t>
+  </si>
+  <si>
+    <t>64000000000000</t>
+  </si>
+  <si>
+    <t>10232</t>
+  </si>
+  <si>
+    <t>1232</t>
+  </si>
+  <si>
+    <t>虚无邪魔教主</t>
+  </si>
+  <si>
+    <t>1E+278</t>
+  </si>
+  <si>
+    <t>1E+297</t>
+  </si>
+  <si>
+    <t>1E+159</t>
+  </si>
+  <si>
+    <t>65000000000000</t>
+  </si>
+  <si>
+    <t>10233</t>
+  </si>
+  <si>
+    <t>1233</t>
+  </si>
+  <si>
+    <t>虚无邪魔教皇</t>
+  </si>
+  <si>
+    <t>1E+300</t>
+  </si>
+  <si>
+    <t>1E+268</t>
+  </si>
+  <si>
+    <t>66000000000000</t>
+  </si>
+  <si>
+    <t>10234</t>
+  </si>
+  <si>
+    <t>1234</t>
+  </si>
+  <si>
+    <t>虚无虹魔猪王</t>
+  </si>
+  <si>
+    <t>1E+280</t>
+  </si>
+  <si>
+    <t>1E+303</t>
+  </si>
+  <si>
+    <t>1E+165</t>
+  </si>
+  <si>
+    <t>67000000000000</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>10230</t>
-  </si>
-  <si>
-    <t>1230</t>
-  </si>
-  <si>
-    <t>虚无恶魔教主</t>
-  </si>
-  <si>
-    <t>10231</t>
-  </si>
-  <si>
-    <t>1231</t>
-  </si>
-  <si>
-    <t>虚无恶魔教皇</t>
-  </si>
-  <si>
-    <t>10232</t>
-  </si>
-  <si>
-    <t>1232</t>
-  </si>
-  <si>
-    <t>虚无邪魔教主</t>
-  </si>
-  <si>
-    <t>10233</t>
-  </si>
-  <si>
-    <t>1233</t>
-  </si>
-  <si>
-    <t>虚无邪魔教皇</t>
-  </si>
-  <si>
-    <t>10234</t>
-  </si>
-  <si>
-    <t>1234</t>
-  </si>
-  <si>
-    <t>虚无虹魔猪王</t>
   </si>
   <si>
     <t>10235</t>
@@ -20757,7 +20816,7 @@
         <v>201</v>
       </c>
       <c r="R201" s="8">
-        <f t="shared" ref="R201:R215" si="82">R200+15</f>
+        <f>R200+15</f>
         <v>449</v>
       </c>
       <c r="S201" s="8">
@@ -20833,11 +20892,11 @@
         <v>207</v>
       </c>
       <c r="R202" s="9">
-        <f t="shared" si="82"/>
+        <f>R201+15</f>
         <v>464</v>
       </c>
       <c r="S202" s="9">
-        <f t="shared" ref="S201:S215" si="83">S201+15</f>
+        <f t="shared" ref="S201:S215" si="82">S201+15</f>
         <v>576</v>
       </c>
       <c r="T202" s="9">
@@ -20909,11 +20968,11 @@
         <v>213</v>
       </c>
       <c r="R203" s="9">
+        <f>R202+15</f>
+        <v>479</v>
+      </c>
+      <c r="S203" s="9">
         <f t="shared" si="82"/>
-        <v>479</v>
-      </c>
-      <c r="S203" s="9">
-        <f t="shared" si="83"/>
         <v>591</v>
       </c>
       <c r="T203" s="9">
@@ -20985,11 +21044,11 @@
         <v>219</v>
       </c>
       <c r="R204" s="9">
+        <f>R203+15</f>
+        <v>494</v>
+      </c>
+      <c r="S204" s="9">
         <f t="shared" si="82"/>
-        <v>494</v>
-      </c>
-      <c r="S204" s="9">
-        <f t="shared" si="83"/>
         <v>606</v>
       </c>
       <c r="T204" s="9">
@@ -21061,11 +21120,11 @@
         <v>225</v>
       </c>
       <c r="R205" s="9">
+        <f>R204+15</f>
+        <v>509</v>
+      </c>
+      <c r="S205" s="9">
         <f t="shared" si="82"/>
-        <v>509</v>
-      </c>
-      <c r="S205" s="9">
-        <f t="shared" si="83"/>
         <v>621</v>
       </c>
       <c r="T205" s="9">
@@ -21119,31 +21178,31 @@
         <v>1445</v>
       </c>
       <c r="M206" s="6">
-        <f t="shared" ref="M206:M215" si="84">M205+10000</f>
+        <f t="shared" ref="M206:M215" si="83">M205+10000</f>
         <v>91000</v>
       </c>
       <c r="N206" s="6">
-        <f t="shared" ref="N206:N215" si="85">N205+10000</f>
+        <f t="shared" ref="N206:N215" si="84">N205+10000</f>
         <v>91000</v>
       </c>
       <c r="O206" s="6">
-        <f t="shared" ref="O206:O215" si="86">O205+10000</f>
+        <f t="shared" ref="O206:O215" si="85">O205+10000</f>
         <v>62750</v>
       </c>
       <c r="P206" s="6">
-        <f t="shared" ref="P206:P215" si="87">P205+10000</f>
+        <f t="shared" ref="P206:P215" si="86">P205+10000</f>
         <v>62750</v>
       </c>
       <c r="Q206" s="6">
         <f t="shared" si="81"/>
         <v>231</v>
       </c>
-      <c r="R206" s="8">
+      <c r="R206" s="9">
+        <f>R205+15</f>
+        <v>524</v>
+      </c>
+      <c r="S206" s="8">
         <f t="shared" si="82"/>
-        <v>524</v>
-      </c>
-      <c r="S206" s="8">
-        <f t="shared" si="83"/>
         <v>636</v>
       </c>
       <c r="T206" s="8">
@@ -21198,19 +21257,19 @@
         <v>1357</v>
       </c>
       <c r="M207" s="7">
+        <f t="shared" si="83"/>
+        <v>101000</v>
+      </c>
+      <c r="N207" s="7">
         <f t="shared" si="84"/>
         <v>101000</v>
       </c>
-      <c r="N207" s="7">
+      <c r="O207" s="7">
         <f t="shared" si="85"/>
-        <v>101000</v>
-      </c>
-      <c r="O207" s="7">
+        <v>72750</v>
+      </c>
+      <c r="P207" s="7">
         <f t="shared" si="86"/>
-        <v>72750</v>
-      </c>
-      <c r="P207" s="7">
-        <f t="shared" si="87"/>
         <v>72750</v>
       </c>
       <c r="Q207" s="6">
@@ -21218,11 +21277,11 @@
         <v>237</v>
       </c>
       <c r="R207" s="9">
+        <f>R206+15</f>
+        <v>539</v>
+      </c>
+      <c r="S207" s="9">
         <f t="shared" si="82"/>
-        <v>539</v>
-      </c>
-      <c r="S207" s="9">
-        <f t="shared" si="83"/>
         <v>651</v>
       </c>
       <c r="T207" s="9">
@@ -21277,19 +21336,19 @@
         <v>1458</v>
       </c>
       <c r="M208" s="7">
+        <f t="shared" si="83"/>
+        <v>111000</v>
+      </c>
+      <c r="N208" s="7">
         <f t="shared" si="84"/>
         <v>111000</v>
       </c>
-      <c r="N208" s="7">
+      <c r="O208" s="7">
         <f t="shared" si="85"/>
-        <v>111000</v>
-      </c>
-      <c r="O208" s="7">
+        <v>82750</v>
+      </c>
+      <c r="P208" s="7">
         <f t="shared" si="86"/>
-        <v>82750</v>
-      </c>
-      <c r="P208" s="7">
-        <f t="shared" si="87"/>
         <v>82750</v>
       </c>
       <c r="Q208" s="6">
@@ -21297,11 +21356,11 @@
         <v>243</v>
       </c>
       <c r="R208" s="9">
+        <f>R207+15</f>
+        <v>554</v>
+      </c>
+      <c r="S208" s="9">
         <f t="shared" si="82"/>
-        <v>554</v>
-      </c>
-      <c r="S208" s="9">
-        <f t="shared" si="83"/>
         <v>666</v>
       </c>
       <c r="T208" s="9">
@@ -21356,19 +21415,19 @@
         <v>1466</v>
       </c>
       <c r="M209" s="7">
+        <f t="shared" si="83"/>
+        <v>121000</v>
+      </c>
+      <c r="N209" s="7">
         <f t="shared" si="84"/>
         <v>121000</v>
       </c>
-      <c r="N209" s="7">
+      <c r="O209" s="7">
         <f t="shared" si="85"/>
-        <v>121000</v>
-      </c>
-      <c r="O209" s="7">
+        <v>92750</v>
+      </c>
+      <c r="P209" s="7">
         <f t="shared" si="86"/>
-        <v>92750</v>
-      </c>
-      <c r="P209" s="7">
-        <f t="shared" si="87"/>
         <v>92750</v>
       </c>
       <c r="Q209" s="6">
@@ -21376,11 +21435,11 @@
         <v>249</v>
       </c>
       <c r="R209" s="9">
+        <f>R208+15</f>
+        <v>569</v>
+      </c>
+      <c r="S209" s="9">
         <f t="shared" si="82"/>
-        <v>569</v>
-      </c>
-      <c r="S209" s="9">
-        <f t="shared" si="83"/>
         <v>681</v>
       </c>
       <c r="T209" s="9">
@@ -21435,19 +21494,19 @@
         <v>1472</v>
       </c>
       <c r="M210" s="7">
+        <f t="shared" si="83"/>
+        <v>131000</v>
+      </c>
+      <c r="N210" s="7">
         <f t="shared" si="84"/>
         <v>131000</v>
       </c>
-      <c r="N210" s="7">
+      <c r="O210" s="7">
         <f t="shared" si="85"/>
-        <v>131000</v>
-      </c>
-      <c r="O210" s="7">
+        <v>102750</v>
+      </c>
+      <c r="P210" s="7">
         <f t="shared" si="86"/>
-        <v>102750</v>
-      </c>
-      <c r="P210" s="7">
-        <f t="shared" si="87"/>
         <v>102750</v>
       </c>
       <c r="Q210" s="6">
@@ -21455,11 +21514,11 @@
         <v>255</v>
       </c>
       <c r="R210" s="9">
+        <f>R209+15</f>
+        <v>584</v>
+      </c>
+      <c r="S210" s="9">
         <f t="shared" si="82"/>
-        <v>584</v>
-      </c>
-      <c r="S210" s="9">
-        <f t="shared" si="83"/>
         <v>696</v>
       </c>
       <c r="T210" s="9">
@@ -21514,19 +21573,19 @@
         <v>1480</v>
       </c>
       <c r="M211" s="7">
-        <f t="shared" ref="M211:M220" si="88">M210+20000</f>
+        <f t="shared" ref="M211:M220" si="87">M210+20000</f>
         <v>151000</v>
       </c>
       <c r="N211" s="7">
-        <f t="shared" ref="N211:N220" si="89">N210+20000</f>
+        <f t="shared" ref="N211:N220" si="88">N210+20000</f>
         <v>151000</v>
       </c>
       <c r="O211" s="7">
-        <f t="shared" ref="O211:O220" si="90">O210+20000</f>
+        <f t="shared" ref="O211:O220" si="89">O210+20000</f>
         <v>122750</v>
       </c>
       <c r="P211" s="7">
-        <f t="shared" ref="P211:P220" si="91">P210+20000</f>
+        <f t="shared" ref="P211:P220" si="90">P210+20000</f>
         <v>122750</v>
       </c>
       <c r="Q211" s="6">
@@ -21534,11 +21593,11 @@
         <v>261</v>
       </c>
       <c r="R211" s="9">
-        <f t="shared" ref="R211:R235" si="92">R210+20</f>
-        <v>604</v>
+        <f>R210+15</f>
+        <v>599</v>
       </c>
       <c r="S211" s="9">
-        <f t="shared" ref="S211:S220" si="93">S210+20</f>
+        <f t="shared" ref="S211:S220" si="91">S210+20</f>
         <v>716</v>
       </c>
       <c r="T211" s="9">
@@ -21593,19 +21652,19 @@
         <v>1486</v>
       </c>
       <c r="M212" s="7">
+        <f t="shared" si="87"/>
+        <v>171000</v>
+      </c>
+      <c r="N212" s="7">
         <f t="shared" si="88"/>
         <v>171000</v>
       </c>
-      <c r="N212" s="7">
+      <c r="O212" s="7">
         <f t="shared" si="89"/>
-        <v>171000</v>
-      </c>
-      <c r="O212" s="7">
+        <v>142750</v>
+      </c>
+      <c r="P212" s="7">
         <f t="shared" si="90"/>
-        <v>142750</v>
-      </c>
-      <c r="P212" s="7">
-        <f t="shared" si="91"/>
         <v>142750</v>
       </c>
       <c r="Q212" s="6">
@@ -21613,11 +21672,11 @@
         <v>267</v>
       </c>
       <c r="R212" s="9">
-        <f t="shared" si="92"/>
-        <v>624</v>
+        <f>R211+15</f>
+        <v>614</v>
       </c>
       <c r="S212" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="91"/>
         <v>736</v>
       </c>
       <c r="T212" s="9">
@@ -21672,19 +21731,19 @@
         <v>1494</v>
       </c>
       <c r="M213" s="7">
+        <f t="shared" si="87"/>
+        <v>191000</v>
+      </c>
+      <c r="N213" s="7">
         <f t="shared" si="88"/>
         <v>191000</v>
       </c>
-      <c r="N213" s="7">
+      <c r="O213" s="7">
         <f t="shared" si="89"/>
-        <v>191000</v>
-      </c>
-      <c r="O213" s="7">
+        <v>162750</v>
+      </c>
+      <c r="P213" s="7">
         <f t="shared" si="90"/>
-        <v>162750</v>
-      </c>
-      <c r="P213" s="7">
-        <f t="shared" si="91"/>
         <v>162750</v>
       </c>
       <c r="Q213" s="6">
@@ -21692,11 +21751,11 @@
         <v>273</v>
       </c>
       <c r="R213" s="9">
-        <f t="shared" si="92"/>
-        <v>644</v>
+        <f>R212+15</f>
+        <v>629</v>
       </c>
       <c r="S213" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="91"/>
         <v>756</v>
       </c>
       <c r="T213" s="9">
@@ -21751,19 +21810,19 @@
         <v>1501</v>
       </c>
       <c r="M214" s="7">
+        <f t="shared" si="87"/>
+        <v>211000</v>
+      </c>
+      <c r="N214" s="7">
         <f t="shared" si="88"/>
         <v>211000</v>
       </c>
-      <c r="N214" s="7">
+      <c r="O214" s="7">
         <f t="shared" si="89"/>
-        <v>211000</v>
-      </c>
-      <c r="O214" s="7">
+        <v>182750</v>
+      </c>
+      <c r="P214" s="7">
         <f t="shared" si="90"/>
-        <v>182750</v>
-      </c>
-      <c r="P214" s="7">
-        <f t="shared" si="91"/>
         <v>182750</v>
       </c>
       <c r="Q214" s="6">
@@ -21771,11 +21830,11 @@
         <v>279</v>
       </c>
       <c r="R214" s="9">
-        <f t="shared" si="92"/>
-        <v>664</v>
+        <f>R213+15</f>
+        <v>644</v>
       </c>
       <c r="S214" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="91"/>
         <v>776</v>
       </c>
       <c r="T214" s="9">
@@ -21830,19 +21889,19 @@
         <v>1509</v>
       </c>
       <c r="M215" s="7">
+        <f t="shared" si="87"/>
+        <v>231000</v>
+      </c>
+      <c r="N215" s="7">
         <f t="shared" si="88"/>
         <v>231000</v>
       </c>
-      <c r="N215" s="7">
+      <c r="O215" s="7">
         <f t="shared" si="89"/>
-        <v>231000</v>
-      </c>
-      <c r="O215" s="7">
+        <v>202750</v>
+      </c>
+      <c r="P215" s="7">
         <f t="shared" si="90"/>
-        <v>202750</v>
-      </c>
-      <c r="P215" s="7">
-        <f t="shared" si="91"/>
         <v>202750</v>
       </c>
       <c r="Q215" s="6">
@@ -21850,11 +21909,11 @@
         <v>285</v>
       </c>
       <c r="R215" s="9">
-        <f t="shared" si="92"/>
-        <v>684</v>
+        <f>R214+15</f>
+        <v>659</v>
       </c>
       <c r="S215" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="91"/>
         <v>796</v>
       </c>
       <c r="T215" s="9">
@@ -21909,31 +21968,31 @@
         <v>1555</v>
       </c>
       <c r="M216" s="28">
-        <f t="shared" ref="M216:M235" si="94">M215+30000</f>
+        <f t="shared" ref="M216:M240" si="92">M215+30000</f>
         <v>261000</v>
       </c>
       <c r="N216" s="28">
-        <f t="shared" ref="N216:N235" si="95">N215+30000</f>
+        <f t="shared" ref="N216:N240" si="93">N215+30000</f>
         <v>261000</v>
       </c>
       <c r="O216" s="28">
-        <f t="shared" ref="O216:O235" si="96">O215+30000</f>
+        <f t="shared" ref="O216:O240" si="94">O215+30000</f>
         <v>232750</v>
       </c>
       <c r="P216" s="28">
-        <f t="shared" ref="P216:P235" si="97">P215+30000</f>
+        <f t="shared" ref="P216:P240" si="95">P215+30000</f>
         <v>232750</v>
       </c>
       <c r="Q216" s="28">
-        <f t="shared" ref="Q216:Q235" si="98">Q215+7</f>
+        <f t="shared" ref="Q216:Q240" si="96">Q215+7</f>
         <v>292</v>
       </c>
-      <c r="R216" s="27">
-        <f t="shared" si="92"/>
-        <v>704</v>
+      <c r="R216" s="9">
+        <f t="shared" ref="R216:R250" si="97">R215+18</f>
+        <v>677</v>
       </c>
       <c r="S216" s="27">
-        <f t="shared" ref="S216:S235" si="99">S215+30</f>
+        <f t="shared" ref="S216:S240" si="98">S215+30</f>
         <v>826</v>
       </c>
       <c r="T216" s="27">
@@ -21986,31 +22045,31 @@
         <v>1398</v>
       </c>
       <c r="M217" s="7">
+        <f t="shared" si="92"/>
+        <v>291000</v>
+      </c>
+      <c r="N217" s="7">
+        <f t="shared" si="93"/>
+        <v>291000</v>
+      </c>
+      <c r="O217" s="7">
         <f t="shared" si="94"/>
-        <v>291000</v>
-      </c>
-      <c r="N217" s="7">
+        <v>262750</v>
+      </c>
+      <c r="P217" s="7">
         <f t="shared" si="95"/>
-        <v>291000</v>
-      </c>
-      <c r="O217" s="7">
+        <v>262750</v>
+      </c>
+      <c r="Q217" s="6">
         <f t="shared" si="96"/>
-        <v>262750</v>
-      </c>
-      <c r="P217" s="7">
+        <v>299</v>
+      </c>
+      <c r="R217" s="9">
         <f t="shared" si="97"/>
-        <v>262750</v>
-      </c>
-      <c r="Q217" s="6">
+        <v>695</v>
+      </c>
+      <c r="S217" s="9">
         <f t="shared" si="98"/>
-        <v>299</v>
-      </c>
-      <c r="R217" s="9">
-        <f t="shared" si="92"/>
-        <v>724</v>
-      </c>
-      <c r="S217" s="9">
-        <f t="shared" si="99"/>
         <v>856</v>
       </c>
       <c r="T217" s="9">
@@ -22063,31 +22122,31 @@
         <v>1415</v>
       </c>
       <c r="M218" s="7">
+        <f t="shared" si="92"/>
+        <v>321000</v>
+      </c>
+      <c r="N218" s="7">
+        <f t="shared" si="93"/>
+        <v>321000</v>
+      </c>
+      <c r="O218" s="7">
         <f t="shared" si="94"/>
-        <v>321000</v>
-      </c>
-      <c r="N218" s="7">
+        <v>292750</v>
+      </c>
+      <c r="P218" s="7">
         <f t="shared" si="95"/>
-        <v>321000</v>
-      </c>
-      <c r="O218" s="7">
+        <v>292750</v>
+      </c>
+      <c r="Q218" s="6">
         <f t="shared" si="96"/>
-        <v>292750</v>
-      </c>
-      <c r="P218" s="7">
+        <v>306</v>
+      </c>
+      <c r="R218" s="9">
         <f t="shared" si="97"/>
-        <v>292750</v>
-      </c>
-      <c r="Q218" s="6">
+        <v>713</v>
+      </c>
+      <c r="S218" s="9">
         <f t="shared" si="98"/>
-        <v>306</v>
-      </c>
-      <c r="R218" s="9">
-        <f t="shared" si="92"/>
-        <v>744</v>
-      </c>
-      <c r="S218" s="9">
-        <f t="shared" si="99"/>
         <v>886</v>
       </c>
       <c r="T218" s="9">
@@ -22140,31 +22199,31 @@
         <v>1576</v>
       </c>
       <c r="M219" s="7">
+        <f t="shared" si="92"/>
+        <v>351000</v>
+      </c>
+      <c r="N219" s="7">
+        <f t="shared" si="93"/>
+        <v>351000</v>
+      </c>
+      <c r="O219" s="7">
         <f t="shared" si="94"/>
-        <v>351000</v>
-      </c>
-      <c r="N219" s="7">
+        <v>322750</v>
+      </c>
+      <c r="P219" s="7">
         <f t="shared" si="95"/>
-        <v>351000</v>
-      </c>
-      <c r="O219" s="7">
+        <v>322750</v>
+      </c>
+      <c r="Q219" s="6">
         <f t="shared" si="96"/>
-        <v>322750</v>
-      </c>
-      <c r="P219" s="7">
+        <v>313</v>
+      </c>
+      <c r="R219" s="9">
         <f t="shared" si="97"/>
-        <v>322750</v>
-      </c>
-      <c r="Q219" s="6">
+        <v>731</v>
+      </c>
+      <c r="S219" s="9">
         <f t="shared" si="98"/>
-        <v>313</v>
-      </c>
-      <c r="R219" s="9">
-        <f t="shared" si="92"/>
-        <v>764</v>
-      </c>
-      <c r="S219" s="9">
-        <f t="shared" si="99"/>
         <v>916</v>
       </c>
       <c r="T219" s="9">
@@ -22215,31 +22274,31 @@
         <v>1453</v>
       </c>
       <c r="M220" s="7">
+        <f t="shared" si="92"/>
+        <v>381000</v>
+      </c>
+      <c r="N220" s="7">
+        <f t="shared" si="93"/>
+        <v>381000</v>
+      </c>
+      <c r="O220" s="7">
         <f t="shared" si="94"/>
-        <v>381000</v>
-      </c>
-      <c r="N220" s="7">
+        <v>352750</v>
+      </c>
+      <c r="P220" s="7">
         <f t="shared" si="95"/>
-        <v>381000</v>
-      </c>
-      <c r="O220" s="7">
+        <v>352750</v>
+      </c>
+      <c r="Q220" s="6">
         <f t="shared" si="96"/>
-        <v>352750</v>
-      </c>
-      <c r="P220" s="7">
+        <v>320</v>
+      </c>
+      <c r="R220" s="9">
         <f t="shared" si="97"/>
-        <v>352750</v>
-      </c>
-      <c r="Q220" s="6">
+        <v>749</v>
+      </c>
+      <c r="S220" s="9">
         <f t="shared" si="98"/>
-        <v>320</v>
-      </c>
-      <c r="R220" s="9">
-        <f t="shared" si="92"/>
-        <v>784</v>
-      </c>
-      <c r="S220" s="9">
-        <f t="shared" si="99"/>
         <v>946</v>
       </c>
       <c r="T220" s="9">
@@ -22292,31 +22351,31 @@
         <v>1560</v>
       </c>
       <c r="M221" s="7">
+        <f t="shared" si="92"/>
+        <v>411000</v>
+      </c>
+      <c r="N221" s="7">
+        <f t="shared" si="93"/>
+        <v>411000</v>
+      </c>
+      <c r="O221" s="7">
         <f t="shared" si="94"/>
-        <v>411000</v>
-      </c>
-      <c r="N221" s="7">
+        <v>382750</v>
+      </c>
+      <c r="P221" s="7">
         <f t="shared" si="95"/>
-        <v>411000</v>
-      </c>
-      <c r="O221" s="7">
+        <v>382750</v>
+      </c>
+      <c r="Q221" s="6">
         <f t="shared" si="96"/>
-        <v>382750</v>
-      </c>
-      <c r="P221" s="7">
+        <v>327</v>
+      </c>
+      <c r="R221" s="9">
         <f t="shared" si="97"/>
-        <v>382750</v>
-      </c>
-      <c r="Q221" s="6">
+        <v>767</v>
+      </c>
+      <c r="S221" s="9">
         <f t="shared" si="98"/>
-        <v>327</v>
-      </c>
-      <c r="R221" s="9">
-        <f t="shared" si="92"/>
-        <v>804</v>
-      </c>
-      <c r="S221" s="9">
-        <f t="shared" si="99"/>
         <v>976</v>
       </c>
       <c r="T221" s="9">
@@ -22369,31 +22428,31 @@
         <v>1487</v>
       </c>
       <c r="M222" s="7">
+        <f t="shared" si="92"/>
+        <v>441000</v>
+      </c>
+      <c r="N222" s="7">
+        <f t="shared" si="93"/>
+        <v>441000</v>
+      </c>
+      <c r="O222" s="7">
         <f t="shared" si="94"/>
-        <v>441000</v>
-      </c>
-      <c r="N222" s="7">
+        <v>412750</v>
+      </c>
+      <c r="P222" s="7">
         <f t="shared" si="95"/>
-        <v>441000</v>
-      </c>
-      <c r="O222" s="7">
+        <v>412750</v>
+      </c>
+      <c r="Q222" s="6">
         <f t="shared" si="96"/>
-        <v>412750</v>
-      </c>
-      <c r="P222" s="7">
+        <v>334</v>
+      </c>
+      <c r="R222" s="9">
         <f t="shared" si="97"/>
-        <v>412750</v>
-      </c>
-      <c r="Q222" s="6">
+        <v>785</v>
+      </c>
+      <c r="S222" s="9">
         <f t="shared" si="98"/>
-        <v>334</v>
-      </c>
-      <c r="R222" s="9">
-        <f t="shared" si="92"/>
-        <v>824</v>
-      </c>
-      <c r="S222" s="9">
-        <f t="shared" si="99"/>
         <v>1006</v>
       </c>
       <c r="T222" s="9">
@@ -22447,31 +22506,31 @@
         <v>1572</v>
       </c>
       <c r="M223" s="7">
+        <f t="shared" si="92"/>
+        <v>471000</v>
+      </c>
+      <c r="N223" s="7">
+        <f t="shared" si="93"/>
+        <v>471000</v>
+      </c>
+      <c r="O223" s="7">
         <f t="shared" si="94"/>
-        <v>471000</v>
-      </c>
-      <c r="N223" s="7">
+        <v>442750</v>
+      </c>
+      <c r="P223" s="7">
         <f t="shared" si="95"/>
-        <v>471000</v>
-      </c>
-      <c r="O223" s="7">
+        <v>442750</v>
+      </c>
+      <c r="Q223" s="6">
         <f t="shared" si="96"/>
-        <v>442750</v>
-      </c>
-      <c r="P223" s="7">
+        <v>341</v>
+      </c>
+      <c r="R223" s="9">
         <f t="shared" si="97"/>
-        <v>442750</v>
-      </c>
-      <c r="Q223" s="6">
+        <v>803</v>
+      </c>
+      <c r="S223" s="9">
         <f t="shared" si="98"/>
-        <v>341</v>
-      </c>
-      <c r="R223" s="9">
-        <f t="shared" si="92"/>
-        <v>844</v>
-      </c>
-      <c r="S223" s="9">
-        <f t="shared" si="99"/>
         <v>1036</v>
       </c>
       <c r="T223" s="9">
@@ -22525,31 +22584,31 @@
         <v>1522</v>
       </c>
       <c r="M224" s="7">
+        <f t="shared" si="92"/>
+        <v>501000</v>
+      </c>
+      <c r="N224" s="7">
+        <f t="shared" si="93"/>
+        <v>501000</v>
+      </c>
+      <c r="O224" s="7">
         <f t="shared" si="94"/>
-        <v>501000</v>
-      </c>
-      <c r="N224" s="7">
+        <v>472750</v>
+      </c>
+      <c r="P224" s="7">
         <f t="shared" si="95"/>
-        <v>501000</v>
-      </c>
-      <c r="O224" s="7">
+        <v>472750</v>
+      </c>
+      <c r="Q224" s="6">
         <f t="shared" si="96"/>
-        <v>472750</v>
-      </c>
-      <c r="P224" s="7">
+        <v>348</v>
+      </c>
+      <c r="R224" s="9">
         <f t="shared" si="97"/>
-        <v>472750</v>
-      </c>
-      <c r="Q224" s="6">
+        <v>821</v>
+      </c>
+      <c r="S224" s="9">
         <f t="shared" si="98"/>
-        <v>348</v>
-      </c>
-      <c r="R224" s="9">
-        <f t="shared" si="92"/>
-        <v>864</v>
-      </c>
-      <c r="S224" s="9">
-        <f t="shared" si="99"/>
         <v>1066</v>
       </c>
       <c r="T224" s="9">
@@ -22603,31 +22662,31 @@
         <v>1587</v>
       </c>
       <c r="M225" s="7">
+        <f t="shared" si="92"/>
+        <v>531000</v>
+      </c>
+      <c r="N225" s="7">
+        <f t="shared" si="93"/>
+        <v>531000</v>
+      </c>
+      <c r="O225" s="7">
         <f t="shared" si="94"/>
-        <v>531000</v>
-      </c>
-      <c r="N225" s="7">
+        <v>502750</v>
+      </c>
+      <c r="P225" s="7">
         <f t="shared" si="95"/>
-        <v>531000</v>
-      </c>
-      <c r="O225" s="7">
+        <v>502750</v>
+      </c>
+      <c r="Q225" s="6">
         <f t="shared" si="96"/>
-        <v>502750</v>
-      </c>
-      <c r="P225" s="7">
+        <v>355</v>
+      </c>
+      <c r="R225" s="9">
         <f t="shared" si="97"/>
-        <v>502750</v>
-      </c>
-      <c r="Q225" s="6">
+        <v>839</v>
+      </c>
+      <c r="S225" s="9">
         <f t="shared" si="98"/>
-        <v>355</v>
-      </c>
-      <c r="R225" s="9">
-        <f t="shared" si="92"/>
-        <v>884</v>
-      </c>
-      <c r="S225" s="9">
-        <f t="shared" si="99"/>
         <v>1096</v>
       </c>
       <c r="T225" s="9">
@@ -22681,31 +22740,31 @@
         <v>1593</v>
       </c>
       <c r="M226" s="7">
+        <f t="shared" si="92"/>
+        <v>561000</v>
+      </c>
+      <c r="N226" s="7">
+        <f t="shared" si="93"/>
+        <v>561000</v>
+      </c>
+      <c r="O226" s="7">
         <f t="shared" si="94"/>
-        <v>561000</v>
-      </c>
-      <c r="N226" s="7">
+        <v>532750</v>
+      </c>
+      <c r="P226" s="7">
         <f t="shared" si="95"/>
-        <v>561000</v>
-      </c>
-      <c r="O226" s="7">
+        <v>532750</v>
+      </c>
+      <c r="Q226" s="6">
         <f t="shared" si="96"/>
-        <v>532750</v>
-      </c>
-      <c r="P226" s="7">
+        <v>362</v>
+      </c>
+      <c r="R226" s="9">
         <f t="shared" si="97"/>
-        <v>532750</v>
-      </c>
-      <c r="Q226" s="6">
+        <v>857</v>
+      </c>
+      <c r="S226" s="9">
         <f t="shared" si="98"/>
-        <v>362</v>
-      </c>
-      <c r="R226" s="9">
-        <f t="shared" si="92"/>
-        <v>904</v>
-      </c>
-      <c r="S226" s="9">
-        <f t="shared" si="99"/>
         <v>1126</v>
       </c>
       <c r="T226" s="9">
@@ -22758,31 +22817,31 @@
         <v>1600</v>
       </c>
       <c r="M227" s="7">
+        <f t="shared" si="92"/>
+        <v>591000</v>
+      </c>
+      <c r="N227" s="7">
+        <f t="shared" si="93"/>
+        <v>591000</v>
+      </c>
+      <c r="O227" s="7">
         <f t="shared" si="94"/>
-        <v>591000</v>
-      </c>
-      <c r="N227" s="7">
+        <v>562750</v>
+      </c>
+      <c r="P227" s="7">
         <f t="shared" si="95"/>
-        <v>591000</v>
-      </c>
-      <c r="O227" s="7">
+        <v>562750</v>
+      </c>
+      <c r="Q227" s="6">
         <f t="shared" si="96"/>
-        <v>562750</v>
-      </c>
-      <c r="P227" s="7">
+        <v>369</v>
+      </c>
+      <c r="R227" s="9">
         <f t="shared" si="97"/>
-        <v>562750</v>
-      </c>
-      <c r="Q227" s="6">
+        <v>875</v>
+      </c>
+      <c r="S227" s="9">
         <f t="shared" si="98"/>
-        <v>369</v>
-      </c>
-      <c r="R227" s="9">
-        <f t="shared" si="92"/>
-        <v>924</v>
-      </c>
-      <c r="S227" s="9">
-        <f t="shared" si="99"/>
         <v>1156</v>
       </c>
       <c r="T227" s="9">
@@ -22835,31 +22894,31 @@
         <v>1573</v>
       </c>
       <c r="M228" s="7">
+        <f t="shared" si="92"/>
+        <v>621000</v>
+      </c>
+      <c r="N228" s="7">
+        <f t="shared" si="93"/>
+        <v>621000</v>
+      </c>
+      <c r="O228" s="7">
         <f t="shared" si="94"/>
-        <v>621000</v>
-      </c>
-      <c r="N228" s="7">
+        <v>592750</v>
+      </c>
+      <c r="P228" s="7">
         <f t="shared" si="95"/>
-        <v>621000</v>
-      </c>
-      <c r="O228" s="7">
+        <v>592750</v>
+      </c>
+      <c r="Q228" s="6">
         <f t="shared" si="96"/>
-        <v>592750</v>
-      </c>
-      <c r="P228" s="7">
+        <v>376</v>
+      </c>
+      <c r="R228" s="9">
         <f t="shared" si="97"/>
-        <v>592750</v>
-      </c>
-      <c r="Q228" s="6">
+        <v>893</v>
+      </c>
+      <c r="S228" s="9">
         <f t="shared" si="98"/>
-        <v>376</v>
-      </c>
-      <c r="R228" s="9">
-        <f t="shared" si="92"/>
-        <v>944</v>
-      </c>
-      <c r="S228" s="9">
-        <f t="shared" si="99"/>
         <v>1186</v>
       </c>
       <c r="T228" s="9">
@@ -22912,31 +22971,31 @@
         <v>1611</v>
       </c>
       <c r="M229" s="7">
+        <f t="shared" si="92"/>
+        <v>651000</v>
+      </c>
+      <c r="N229" s="7">
+        <f t="shared" si="93"/>
+        <v>651000</v>
+      </c>
+      <c r="O229" s="7">
         <f t="shared" si="94"/>
-        <v>651000</v>
-      </c>
-      <c r="N229" s="7">
+        <v>622750</v>
+      </c>
+      <c r="P229" s="7">
         <f t="shared" si="95"/>
-        <v>651000</v>
-      </c>
-      <c r="O229" s="7">
+        <v>622750</v>
+      </c>
+      <c r="Q229" s="6">
         <f t="shared" si="96"/>
-        <v>622750</v>
-      </c>
-      <c r="P229" s="7">
+        <v>383</v>
+      </c>
+      <c r="R229" s="9">
         <f t="shared" si="97"/>
-        <v>622750</v>
-      </c>
-      <c r="Q229" s="6">
+        <v>911</v>
+      </c>
+      <c r="S229" s="9">
         <f t="shared" si="98"/>
-        <v>383</v>
-      </c>
-      <c r="R229" s="9">
-        <f t="shared" si="92"/>
-        <v>964</v>
-      </c>
-      <c r="S229" s="9">
-        <f t="shared" si="99"/>
         <v>1216</v>
       </c>
       <c r="T229" s="9">
@@ -22989,31 +23048,31 @@
         <v>1645</v>
       </c>
       <c r="M230" s="7">
+        <f t="shared" si="92"/>
+        <v>681000</v>
+      </c>
+      <c r="N230" s="7">
+        <f t="shared" si="93"/>
+        <v>681000</v>
+      </c>
+      <c r="O230" s="7">
         <f t="shared" si="94"/>
-        <v>681000</v>
-      </c>
-      <c r="N230" s="7">
+        <v>652750</v>
+      </c>
+      <c r="P230" s="7">
         <f t="shared" si="95"/>
-        <v>681000</v>
-      </c>
-      <c r="O230" s="7">
+        <v>652750</v>
+      </c>
+      <c r="Q230" s="6">
         <f t="shared" si="96"/>
-        <v>652750</v>
-      </c>
-      <c r="P230" s="7">
+        <v>390</v>
+      </c>
+      <c r="R230" s="9">
         <f t="shared" si="97"/>
-        <v>652750</v>
-      </c>
-      <c r="Q230" s="6">
+        <v>929</v>
+      </c>
+      <c r="S230" s="9">
         <f t="shared" si="98"/>
-        <v>390</v>
-      </c>
-      <c r="R230" s="9">
-        <f t="shared" si="92"/>
-        <v>984</v>
-      </c>
-      <c r="S230" s="9">
-        <f t="shared" si="99"/>
         <v>1246</v>
       </c>
       <c r="T230" s="9">
@@ -23066,31 +23125,31 @@
         <v>1601</v>
       </c>
       <c r="M231" s="7">
+        <f t="shared" si="92"/>
+        <v>711000</v>
+      </c>
+      <c r="N231" s="7">
+        <f t="shared" si="93"/>
+        <v>711000</v>
+      </c>
+      <c r="O231" s="7">
         <f t="shared" si="94"/>
-        <v>711000</v>
-      </c>
-      <c r="N231" s="7">
+        <v>682750</v>
+      </c>
+      <c r="P231" s="7">
         <f t="shared" si="95"/>
-        <v>711000</v>
-      </c>
-      <c r="O231" s="7">
+        <v>682750</v>
+      </c>
+      <c r="Q231" s="6">
         <f t="shared" si="96"/>
-        <v>682750</v>
-      </c>
-      <c r="P231" s="7">
+        <v>397</v>
+      </c>
+      <c r="R231" s="9">
         <f t="shared" si="97"/>
-        <v>682750</v>
-      </c>
-      <c r="Q231" s="6">
+        <v>947</v>
+      </c>
+      <c r="S231" s="9">
         <f t="shared" si="98"/>
-        <v>397</v>
-      </c>
-      <c r="R231" s="9">
-        <f t="shared" si="92"/>
-        <v>1004</v>
-      </c>
-      <c r="S231" s="9">
-        <f t="shared" si="99"/>
         <v>1276</v>
       </c>
       <c r="T231" s="9">
@@ -23143,31 +23202,31 @@
         <v>1630</v>
       </c>
       <c r="M232" s="7">
+        <f t="shared" si="92"/>
+        <v>741000</v>
+      </c>
+      <c r="N232" s="7">
+        <f t="shared" si="93"/>
+        <v>741000</v>
+      </c>
+      <c r="O232" s="7">
         <f t="shared" si="94"/>
-        <v>741000</v>
-      </c>
-      <c r="N232" s="7">
+        <v>712750</v>
+      </c>
+      <c r="P232" s="7">
         <f t="shared" si="95"/>
-        <v>741000</v>
-      </c>
-      <c r="O232" s="7">
+        <v>712750</v>
+      </c>
+      <c r="Q232" s="6">
         <f t="shared" si="96"/>
-        <v>712750</v>
-      </c>
-      <c r="P232" s="7">
+        <v>404</v>
+      </c>
+      <c r="R232" s="9">
         <f t="shared" si="97"/>
-        <v>712750</v>
-      </c>
-      <c r="Q232" s="6">
+        <v>965</v>
+      </c>
+      <c r="S232" s="9">
         <f t="shared" si="98"/>
-        <v>404</v>
-      </c>
-      <c r="R232" s="9">
-        <f t="shared" si="92"/>
-        <v>1024</v>
-      </c>
-      <c r="S232" s="9">
-        <f t="shared" si="99"/>
         <v>1306</v>
       </c>
       <c r="T232" s="9">
@@ -23220,31 +23279,31 @@
         <v>1664</v>
       </c>
       <c r="M233" s="7">
+        <f t="shared" si="92"/>
+        <v>771000</v>
+      </c>
+      <c r="N233" s="7">
+        <f t="shared" si="93"/>
+        <v>771000</v>
+      </c>
+      <c r="O233" s="7">
         <f t="shared" si="94"/>
-        <v>771000</v>
-      </c>
-      <c r="N233" s="7">
+        <v>742750</v>
+      </c>
+      <c r="P233" s="7">
         <f t="shared" si="95"/>
-        <v>771000</v>
-      </c>
-      <c r="O233" s="7">
+        <v>742750</v>
+      </c>
+      <c r="Q233" s="6">
         <f t="shared" si="96"/>
-        <v>742750</v>
-      </c>
-      <c r="P233" s="7">
+        <v>411</v>
+      </c>
+      <c r="R233" s="9">
         <f t="shared" si="97"/>
-        <v>742750</v>
-      </c>
-      <c r="Q233" s="6">
+        <v>983</v>
+      </c>
+      <c r="S233" s="9">
         <f t="shared" si="98"/>
-        <v>411</v>
-      </c>
-      <c r="R233" s="9">
-        <f t="shared" si="92"/>
-        <v>1044</v>
-      </c>
-      <c r="S233" s="9">
-        <f t="shared" si="99"/>
         <v>1336</v>
       </c>
       <c r="T233" s="9">
@@ -23297,31 +23356,31 @@
         <v>1612</v>
       </c>
       <c r="M234" s="7">
+        <f t="shared" si="92"/>
+        <v>801000</v>
+      </c>
+      <c r="N234" s="7">
+        <f t="shared" si="93"/>
+        <v>801000</v>
+      </c>
+      <c r="O234" s="7">
         <f t="shared" si="94"/>
-        <v>801000</v>
-      </c>
-      <c r="N234" s="7">
+        <v>772750</v>
+      </c>
+      <c r="P234" s="7">
         <f t="shared" si="95"/>
-        <v>801000</v>
-      </c>
-      <c r="O234" s="7">
+        <v>772750</v>
+      </c>
+      <c r="Q234" s="6">
         <f t="shared" si="96"/>
-        <v>772750</v>
-      </c>
-      <c r="P234" s="7">
+        <v>418</v>
+      </c>
+      <c r="R234" s="9">
         <f t="shared" si="97"/>
-        <v>772750</v>
-      </c>
-      <c r="Q234" s="6">
+        <v>1001</v>
+      </c>
+      <c r="S234" s="9">
         <f t="shared" si="98"/>
-        <v>418</v>
-      </c>
-      <c r="R234" s="9">
-        <f t="shared" si="92"/>
-        <v>1064</v>
-      </c>
-      <c r="S234" s="9">
-        <f t="shared" si="99"/>
         <v>1366</v>
       </c>
       <c r="T234" s="9">
@@ -23340,25 +23399,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" s="10" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A235" s="27"/>
-      <c r="B235" s="27"/>
-      <c r="C235" s="46" t="s">
+    <row r="235" s="5" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A235" s="8"/>
+      <c r="B235" s="8"/>
+      <c r="C235" s="43" t="s">
         <v>1672</v>
       </c>
-      <c r="D235" s="46" t="s">
+      <c r="D235" s="43" t="s">
         <v>1673</v>
       </c>
-      <c r="E235" s="28">
+      <c r="E235" s="6">
         <v>7</v>
       </c>
-      <c r="F235" s="28" t="s">
+      <c r="F235" s="6" t="s">
         <v>1674</v>
       </c>
       <c r="G235" s="38" t="s">
         <v>1675</v>
       </c>
-      <c r="H235" s="48" t="s">
+      <c r="H235" s="44" t="s">
         <v>1281</v>
       </c>
       <c r="I235" s="38" t="s">
@@ -23373,118 +23432,119 @@
       <c r="L235" s="38" t="s">
         <v>1642</v>
       </c>
-      <c r="M235" s="7">
+      <c r="M235" s="6">
+        <f t="shared" si="92"/>
+        <v>831000</v>
+      </c>
+      <c r="N235" s="6">
+        <f t="shared" si="93"/>
+        <v>831000</v>
+      </c>
+      <c r="O235" s="6">
         <f t="shared" si="94"/>
-        <v>831000</v>
-      </c>
-      <c r="N235" s="7">
+        <v>802750</v>
+      </c>
+      <c r="P235" s="6">
         <f t="shared" si="95"/>
-        <v>831000</v>
-      </c>
-      <c r="O235" s="7">
+        <v>802750</v>
+      </c>
+      <c r="Q235" s="6">
         <f t="shared" si="96"/>
-        <v>802750</v>
-      </c>
-      <c r="P235" s="7">
+        <v>425</v>
+      </c>
+      <c r="R235" s="9">
         <f t="shared" si="97"/>
-        <v>802750</v>
-      </c>
-      <c r="Q235" s="6">
+        <v>1019</v>
+      </c>
+      <c r="S235" s="8">
         <f t="shared" si="98"/>
-        <v>425</v>
-      </c>
-      <c r="R235" s="9">
-        <f t="shared" si="92"/>
-        <v>1084</v>
-      </c>
-      <c r="S235" s="9">
-        <f t="shared" si="99"/>
         <v>1396</v>
       </c>
-      <c r="T235" s="9">
+      <c r="T235" s="8">
         <v>99.99</v>
       </c>
-      <c r="U235" s="45" t="s">
+      <c r="U235" s="43" t="s">
         <v>1677</v>
       </c>
-      <c r="V235" s="45" t="s">
+      <c r="V235" s="43" t="s">
         <v>1677</v>
       </c>
-      <c r="X235" s="10" t="s">
+      <c r="X235" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="Y235" s="10">
+      <c r="Y235" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="236" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A236" s="8" t="s">
+      <c r="A236" s="8"/>
+      <c r="B236" s="8"/>
+      <c r="C236" s="45" t="s">
         <v>1678</v>
       </c>
-      <c r="B236" s="8" t="s">
-        <v>1678</v>
-      </c>
-      <c r="C236" s="45" t="s">
+      <c r="D236" s="45" t="s">
         <v>1679</v>
-      </c>
-      <c r="D236" s="45" t="s">
-        <v>1680</v>
       </c>
       <c r="E236" s="7">
         <v>7</v>
       </c>
       <c r="F236" s="6" t="s">
-        <v>1681</v>
-      </c>
-      <c r="G236" s="41" t="s">
-        <v>1279</v>
+        <v>1680</v>
+      </c>
+      <c r="G236" s="38" t="s">
+        <v>1651</v>
       </c>
       <c r="H236" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I236" s="41" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J236" s="41" t="s">
-        <v>1282</v>
-      </c>
-      <c r="K236" s="37" t="s">
-        <v>1283</v>
-      </c>
-      <c r="L236" s="41" t="s">
-        <v>1284</v>
-      </c>
-      <c r="M236" s="3">
-        <v>43000</v>
-      </c>
-      <c r="N236" s="3">
-        <v>43000</v>
-      </c>
-      <c r="O236" s="3">
-        <v>22000</v>
-      </c>
-      <c r="P236" s="3">
-        <v>22000</v>
-      </c>
-      <c r="Q236" s="3">
-        <v>100</v>
-      </c>
-      <c r="R236" s="19">
-        <f>R235+9</f>
-        <v>1093</v>
-      </c>
-      <c r="S236" s="19">
-        <f>S235+10</f>
-        <v>1406</v>
-      </c>
-      <c r="T236" s="19">
+      <c r="I236" s="38" t="s">
+        <v>1681</v>
+      </c>
+      <c r="J236" s="42" t="s">
+        <v>1682</v>
+      </c>
+      <c r="K236" s="42" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L236" s="38" t="s">
+        <v>1683</v>
+      </c>
+      <c r="M236" s="6">
+        <f t="shared" si="92"/>
+        <v>861000</v>
+      </c>
+      <c r="N236" s="6">
+        <f t="shared" si="93"/>
+        <v>861000</v>
+      </c>
+      <c r="O236" s="6">
+        <f t="shared" si="94"/>
+        <v>832750</v>
+      </c>
+      <c r="P236" s="6">
+        <f t="shared" si="95"/>
+        <v>832750</v>
+      </c>
+      <c r="Q236" s="6">
+        <f t="shared" si="96"/>
+        <v>432</v>
+      </c>
+      <c r="R236" s="9">
+        <f t="shared" si="97"/>
+        <v>1037</v>
+      </c>
+      <c r="S236" s="8">
+        <f t="shared" si="98"/>
+        <v>1426</v>
+      </c>
+      <c r="T236" s="8">
         <v>99.99</v>
       </c>
-      <c r="U236" s="37" t="s">
-        <v>1285</v>
-      </c>
-      <c r="V236" s="37" t="s">
-        <v>1285</v>
+      <c r="U236" s="43" t="s">
+        <v>1684</v>
+      </c>
+      <c r="V236" s="43" t="s">
+        <v>1684</v>
       </c>
       <c r="X236" s="3" t="s">
         <v>158</v>
@@ -23494,73 +23554,74 @@
       </c>
     </row>
     <row r="237" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A237" s="8" t="s">
-        <v>1678</v>
-      </c>
-      <c r="B237" s="8" t="s">
-        <v>1678</v>
-      </c>
+      <c r="A237" s="8"/>
+      <c r="B237" s="8"/>
       <c r="C237" s="45" t="s">
-        <v>1682</v>
+        <v>1685</v>
       </c>
       <c r="D237" s="45" t="s">
-        <v>1683</v>
+        <v>1686</v>
       </c>
       <c r="E237" s="7">
         <v>7</v>
       </c>
       <c r="F237" s="7" t="s">
-        <v>1684</v>
-      </c>
-      <c r="G237" s="41" t="s">
-        <v>1279</v>
+        <v>1687</v>
+      </c>
+      <c r="G237" s="38" t="s">
+        <v>1688</v>
       </c>
       <c r="H237" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I237" s="41" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J237" s="41" t="s">
-        <v>1282</v>
-      </c>
-      <c r="K237" s="37" t="s">
-        <v>1283</v>
-      </c>
-      <c r="L237" s="41" t="s">
-        <v>1284</v>
-      </c>
-      <c r="M237" s="3">
-        <v>43000</v>
-      </c>
-      <c r="N237" s="3">
-        <v>43000</v>
-      </c>
-      <c r="O237" s="3">
-        <v>22000</v>
-      </c>
-      <c r="P237" s="3">
-        <v>22000</v>
-      </c>
-      <c r="Q237" s="3">
-        <v>100</v>
-      </c>
-      <c r="R237" s="19">
-        <f>R236+9</f>
-        <v>1102</v>
-      </c>
-      <c r="S237" s="19">
-        <f>S236+10</f>
-        <v>1416</v>
-      </c>
-      <c r="T237" s="19">
+      <c r="I237" s="38" t="s">
+        <v>1689</v>
+      </c>
+      <c r="J237" s="42" t="s">
+        <v>1509</v>
+      </c>
+      <c r="K237" s="42" t="s">
+        <v>1509</v>
+      </c>
+      <c r="L237" s="38" t="s">
+        <v>1625</v>
+      </c>
+      <c r="M237" s="6">
+        <f t="shared" si="92"/>
+        <v>891000</v>
+      </c>
+      <c r="N237" s="6">
+        <f t="shared" si="93"/>
+        <v>891000</v>
+      </c>
+      <c r="O237" s="6">
+        <f t="shared" si="94"/>
+        <v>862750</v>
+      </c>
+      <c r="P237" s="6">
+        <f t="shared" si="95"/>
+        <v>862750</v>
+      </c>
+      <c r="Q237" s="6">
+        <f t="shared" si="96"/>
+        <v>439</v>
+      </c>
+      <c r="R237" s="9">
+        <f t="shared" si="97"/>
+        <v>1055</v>
+      </c>
+      <c r="S237" s="8">
+        <f t="shared" si="98"/>
+        <v>1456</v>
+      </c>
+      <c r="T237" s="8">
         <v>99.99</v>
       </c>
-      <c r="U237" s="37" t="s">
-        <v>1285</v>
-      </c>
-      <c r="V237" s="37" t="s">
-        <v>1285</v>
+      <c r="U237" s="43" t="s">
+        <v>1690</v>
+      </c>
+      <c r="V237" s="43" t="s">
+        <v>1690</v>
       </c>
       <c r="X237" s="3" t="s">
         <v>158</v>
@@ -23570,73 +23631,74 @@
       </c>
     </row>
     <row r="238" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A238" s="8" t="s">
-        <v>1678</v>
-      </c>
-      <c r="B238" s="8" t="s">
-        <v>1678</v>
-      </c>
+      <c r="A238" s="8"/>
+      <c r="B238" s="8"/>
       <c r="C238" s="45" t="s">
-        <v>1685</v>
+        <v>1691</v>
       </c>
       <c r="D238" s="45" t="s">
-        <v>1686</v>
+        <v>1692</v>
       </c>
       <c r="E238" s="7">
         <v>7</v>
       </c>
       <c r="F238" s="7" t="s">
-        <v>1687</v>
-      </c>
-      <c r="G238" s="41" t="s">
-        <v>1279</v>
+        <v>1693</v>
+      </c>
+      <c r="G238" s="38" t="s">
+        <v>1694</v>
       </c>
       <c r="H238" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I238" s="41" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J238" s="41" t="s">
-        <v>1282</v>
-      </c>
-      <c r="K238" s="37" t="s">
-        <v>1283</v>
-      </c>
-      <c r="L238" s="41" t="s">
-        <v>1284</v>
-      </c>
-      <c r="M238" s="3">
-        <v>43000</v>
-      </c>
-      <c r="N238" s="3">
-        <v>43000</v>
-      </c>
-      <c r="O238" s="3">
-        <v>22000</v>
-      </c>
-      <c r="P238" s="3">
-        <v>22000</v>
-      </c>
-      <c r="Q238" s="3">
-        <v>100</v>
-      </c>
-      <c r="R238" s="19">
-        <f>R237+9</f>
-        <v>1111</v>
-      </c>
-      <c r="S238" s="19">
-        <f>S237+10</f>
-        <v>1426</v>
-      </c>
-      <c r="T238" s="19">
+      <c r="I238" s="38" t="s">
+        <v>1695</v>
+      </c>
+      <c r="J238" s="42" t="s">
+        <v>1696</v>
+      </c>
+      <c r="K238" s="42" t="s">
+        <v>1696</v>
+      </c>
+      <c r="L238" s="38" t="s">
+        <v>1655</v>
+      </c>
+      <c r="M238" s="6">
+        <f t="shared" si="92"/>
+        <v>921000</v>
+      </c>
+      <c r="N238" s="6">
+        <f t="shared" si="93"/>
+        <v>921000</v>
+      </c>
+      <c r="O238" s="6">
+        <f t="shared" si="94"/>
+        <v>892750</v>
+      </c>
+      <c r="P238" s="6">
+        <f t="shared" si="95"/>
+        <v>892750</v>
+      </c>
+      <c r="Q238" s="6">
+        <f t="shared" si="96"/>
+        <v>446</v>
+      </c>
+      <c r="R238" s="9">
+        <f t="shared" si="97"/>
+        <v>1073</v>
+      </c>
+      <c r="S238" s="8">
+        <f t="shared" si="98"/>
+        <v>1486</v>
+      </c>
+      <c r="T238" s="8">
         <v>99.99</v>
       </c>
-      <c r="U238" s="37" t="s">
-        <v>1285</v>
-      </c>
-      <c r="V238" s="37" t="s">
-        <v>1285</v>
+      <c r="U238" s="43" t="s">
+        <v>1697</v>
+      </c>
+      <c r="V238" s="43" t="s">
+        <v>1697</v>
       </c>
       <c r="X238" s="3" t="s">
         <v>158</v>
@@ -23646,73 +23708,74 @@
       </c>
     </row>
     <row r="239" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A239" s="8" t="s">
-        <v>1678</v>
-      </c>
-      <c r="B239" s="8" t="s">
-        <v>1678</v>
-      </c>
+      <c r="A239" s="8"/>
+      <c r="B239" s="8"/>
       <c r="C239" s="45" t="s">
-        <v>1688</v>
+        <v>1698</v>
       </c>
       <c r="D239" s="45" t="s">
-        <v>1689</v>
+        <v>1699</v>
       </c>
       <c r="E239" s="7">
         <v>7</v>
       </c>
       <c r="F239" s="7" t="s">
-        <v>1690</v>
-      </c>
-      <c r="G239" s="41" t="s">
-        <v>1279</v>
+        <v>1700</v>
+      </c>
+      <c r="G239" s="38" t="s">
+        <v>1656</v>
       </c>
       <c r="H239" s="44" t="s">
         <v>1281</v>
       </c>
-      <c r="I239" s="41" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J239" s="41" t="s">
-        <v>1282</v>
-      </c>
-      <c r="K239" s="37" t="s">
-        <v>1283</v>
-      </c>
-      <c r="L239" s="41" t="s">
-        <v>1284</v>
-      </c>
-      <c r="M239" s="3">
-        <v>43000</v>
-      </c>
-      <c r="N239" s="3">
-        <v>43000</v>
-      </c>
-      <c r="O239" s="3">
-        <v>22000</v>
-      </c>
-      <c r="P239" s="3">
-        <v>22000</v>
-      </c>
-      <c r="Q239" s="3">
-        <v>100</v>
-      </c>
-      <c r="R239" s="19">
-        <f>R238+9</f>
-        <v>1120</v>
-      </c>
-      <c r="S239" s="19">
-        <f>S238+10</f>
-        <v>1436</v>
-      </c>
-      <c r="T239" s="19">
+      <c r="I239" s="38" t="s">
+        <v>1701</v>
+      </c>
+      <c r="J239" s="42" t="s">
+        <v>1528</v>
+      </c>
+      <c r="K239" s="42" t="s">
+        <v>1528</v>
+      </c>
+      <c r="L239" s="38" t="s">
+        <v>1702</v>
+      </c>
+      <c r="M239" s="6">
+        <f t="shared" si="92"/>
+        <v>951000</v>
+      </c>
+      <c r="N239" s="6">
+        <f t="shared" si="93"/>
+        <v>951000</v>
+      </c>
+      <c r="O239" s="6">
+        <f t="shared" si="94"/>
+        <v>922750</v>
+      </c>
+      <c r="P239" s="6">
+        <f t="shared" si="95"/>
+        <v>922750</v>
+      </c>
+      <c r="Q239" s="6">
+        <f t="shared" si="96"/>
+        <v>453</v>
+      </c>
+      <c r="R239" s="9">
+        <f t="shared" si="97"/>
+        <v>1091</v>
+      </c>
+      <c r="S239" s="8">
+        <f t="shared" si="98"/>
+        <v>1516</v>
+      </c>
+      <c r="T239" s="8">
         <v>99.99</v>
       </c>
-      <c r="U239" s="37" t="s">
-        <v>1285</v>
-      </c>
-      <c r="V239" s="37" t="s">
-        <v>1285</v>
+      <c r="U239" s="43" t="s">
+        <v>1703</v>
+      </c>
+      <c r="V239" s="43" t="s">
+        <v>1703</v>
       </c>
       <c r="X239" s="3" t="s">
         <v>158</v>
@@ -23721,100 +23784,101 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A240" s="8" t="s">
-        <v>1678</v>
-      </c>
-      <c r="B240" s="8" t="s">
-        <v>1678</v>
-      </c>
-      <c r="C240" s="45" t="s">
-        <v>1691</v>
-      </c>
-      <c r="D240" s="45" t="s">
-        <v>1692</v>
-      </c>
-      <c r="E240" s="7">
+    <row r="240" s="10" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A240" s="27"/>
+      <c r="B240" s="27"/>
+      <c r="C240" s="46" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D240" s="46" t="s">
+        <v>1705</v>
+      </c>
+      <c r="E240" s="28">
         <v>7</v>
       </c>
-      <c r="F240" s="7" t="s">
-        <v>1693</v>
-      </c>
-      <c r="G240" s="41" t="s">
-        <v>1279</v>
-      </c>
-      <c r="H240" s="44" t="s">
+      <c r="F240" s="28" t="s">
+        <v>1706</v>
+      </c>
+      <c r="G240" s="38" t="s">
+        <v>1707</v>
+      </c>
+      <c r="H240" s="48" t="s">
         <v>1281</v>
       </c>
-      <c r="I240" s="41" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J240" s="41" t="s">
-        <v>1282</v>
-      </c>
-      <c r="K240" s="37" t="s">
-        <v>1283</v>
-      </c>
-      <c r="L240" s="41" t="s">
-        <v>1284</v>
-      </c>
-      <c r="M240" s="3">
-        <v>43000</v>
-      </c>
-      <c r="N240" s="3">
-        <v>43000</v>
-      </c>
-      <c r="O240" s="3">
-        <v>22000</v>
-      </c>
-      <c r="P240" s="3">
-        <v>22000</v>
-      </c>
-      <c r="Q240" s="3">
-        <v>100</v>
-      </c>
-      <c r="R240" s="19">
-        <f>R239+9</f>
-        <v>1129</v>
-      </c>
-      <c r="S240" s="19">
-        <f>S239+10</f>
-        <v>1446</v>
-      </c>
-      <c r="T240" s="19">
+      <c r="I240" s="38" t="s">
+        <v>1708</v>
+      </c>
+      <c r="J240" s="42" t="s">
+        <v>1709</v>
+      </c>
+      <c r="K240" s="42" t="s">
+        <v>1709</v>
+      </c>
+      <c r="L240" s="38" t="s">
+        <v>1637</v>
+      </c>
+      <c r="M240" s="6">
+        <f t="shared" si="92"/>
+        <v>981000</v>
+      </c>
+      <c r="N240" s="6">
+        <f t="shared" si="93"/>
+        <v>981000</v>
+      </c>
+      <c r="O240" s="6">
+        <f t="shared" si="94"/>
+        <v>952750</v>
+      </c>
+      <c r="P240" s="6">
+        <f t="shared" si="95"/>
+        <v>952750</v>
+      </c>
+      <c r="Q240" s="6">
+        <f t="shared" si="96"/>
+        <v>460</v>
+      </c>
+      <c r="R240" s="9">
+        <f t="shared" si="97"/>
+        <v>1109</v>
+      </c>
+      <c r="S240" s="8">
+        <f t="shared" si="98"/>
+        <v>1546</v>
+      </c>
+      <c r="T240" s="8">
         <v>99.99</v>
       </c>
-      <c r="U240" s="37" t="s">
-        <v>1285</v>
-      </c>
-      <c r="V240" s="37" t="s">
-        <v>1285</v>
-      </c>
-      <c r="X240" s="3" t="s">
+      <c r="U240" s="43" t="s">
+        <v>1710</v>
+      </c>
+      <c r="V240" s="43" t="s">
+        <v>1710</v>
+      </c>
+      <c r="X240" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="Y240" s="3">
+      <c r="Y240" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="241" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A241" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="B241" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="C241" s="45" t="s">
-        <v>1694</v>
+        <v>1712</v>
       </c>
       <c r="D241" s="45" t="s">
-        <v>1695</v>
+        <v>1713</v>
       </c>
       <c r="E241" s="7">
         <v>7</v>
       </c>
       <c r="F241" s="6" t="s">
-        <v>1696</v>
+        <v>1714</v>
       </c>
       <c r="G241" s="41" t="s">
         <v>1279</v>
@@ -23849,13 +23913,13 @@
       <c r="Q241" s="3">
         <v>100</v>
       </c>
-      <c r="R241" s="19">
-        <f>R240+9</f>
-        <v>1138</v>
+      <c r="R241" s="9">
+        <f t="shared" si="97"/>
+        <v>1127</v>
       </c>
       <c r="S241" s="19">
-        <f>S240+10</f>
-        <v>1456</v>
+        <f t="shared" ref="S236:S250" si="99">S240+10</f>
+        <v>1556</v>
       </c>
       <c r="T241" s="19">
         <v>99.99</v>
@@ -23875,22 +23939,22 @@
     </row>
     <row r="242" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A242" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="B242" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="C242" s="45" t="s">
-        <v>1697</v>
+        <v>1715</v>
       </c>
       <c r="D242" s="45" t="s">
-        <v>1698</v>
+        <v>1716</v>
       </c>
       <c r="E242" s="7">
         <v>7</v>
       </c>
       <c r="F242" s="7" t="s">
-        <v>1699</v>
+        <v>1717</v>
       </c>
       <c r="G242" s="41" t="s">
         <v>1279</v>
@@ -23925,13 +23989,13 @@
       <c r="Q242" s="3">
         <v>100</v>
       </c>
-      <c r="R242" s="19">
-        <f>R241+9</f>
-        <v>1147</v>
+      <c r="R242" s="9">
+        <f t="shared" si="97"/>
+        <v>1145</v>
       </c>
       <c r="S242" s="19">
-        <f>S241+10</f>
-        <v>1466</v>
+        <f t="shared" si="99"/>
+        <v>1566</v>
       </c>
       <c r="T242" s="19">
         <v>99.99</v>
@@ -23951,22 +24015,22 @@
     </row>
     <row r="243" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A243" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="B243" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="C243" s="45" t="s">
-        <v>1700</v>
+        <v>1718</v>
       </c>
       <c r="D243" s="45" t="s">
-        <v>1701</v>
+        <v>1719</v>
       </c>
       <c r="E243" s="7">
         <v>7</v>
       </c>
       <c r="F243" s="7" t="s">
-        <v>1702</v>
+        <v>1720</v>
       </c>
       <c r="G243" s="41" t="s">
         <v>1279</v>
@@ -24001,13 +24065,13 @@
       <c r="Q243" s="3">
         <v>100</v>
       </c>
-      <c r="R243" s="19">
-        <f>R242+9</f>
-        <v>1156</v>
+      <c r="R243" s="9">
+        <f t="shared" si="97"/>
+        <v>1163</v>
       </c>
       <c r="S243" s="19">
-        <f>S242+10</f>
-        <v>1476</v>
+        <f t="shared" si="99"/>
+        <v>1576</v>
       </c>
       <c r="T243" s="19">
         <v>99.99</v>
@@ -24027,22 +24091,22 @@
     </row>
     <row r="244" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A244" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="B244" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="C244" s="45" t="s">
-        <v>1703</v>
+        <v>1721</v>
       </c>
       <c r="D244" s="45" t="s">
-        <v>1704</v>
+        <v>1722</v>
       </c>
       <c r="E244" s="7">
         <v>7</v>
       </c>
       <c r="F244" s="7" t="s">
-        <v>1705</v>
+        <v>1723</v>
       </c>
       <c r="G244" s="41" t="s">
         <v>1279</v>
@@ -24077,13 +24141,13 @@
       <c r="Q244" s="3">
         <v>100</v>
       </c>
-      <c r="R244" s="19">
-        <f>R243+9</f>
-        <v>1165</v>
+      <c r="R244" s="9">
+        <f t="shared" si="97"/>
+        <v>1181</v>
       </c>
       <c r="S244" s="19">
-        <f>S243+10</f>
-        <v>1486</v>
+        <f t="shared" si="99"/>
+        <v>1586</v>
       </c>
       <c r="T244" s="19">
         <v>99.99</v>
@@ -24103,22 +24167,22 @@
     </row>
     <row r="245" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A245" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="B245" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="C245" s="45" t="s">
-        <v>1706</v>
+        <v>1724</v>
       </c>
       <c r="D245" s="45" t="s">
-        <v>1707</v>
+        <v>1725</v>
       </c>
       <c r="E245" s="7">
         <v>7</v>
       </c>
       <c r="F245" s="7" t="s">
-        <v>1708</v>
+        <v>1726</v>
       </c>
       <c r="G245" s="41" t="s">
         <v>1279</v>
@@ -24153,13 +24217,13 @@
       <c r="Q245" s="3">
         <v>100</v>
       </c>
-      <c r="R245" s="19">
-        <f>R244+9</f>
-        <v>1174</v>
+      <c r="R245" s="9">
+        <f t="shared" si="97"/>
+        <v>1199</v>
       </c>
       <c r="S245" s="19">
-        <f>S244+10</f>
-        <v>1496</v>
+        <f t="shared" si="99"/>
+        <v>1596</v>
       </c>
       <c r="T245" s="19">
         <v>99.99</v>
@@ -24179,22 +24243,22 @@
     </row>
     <row r="246" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A246" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="B246" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="C246" s="45" t="s">
-        <v>1709</v>
+        <v>1727</v>
       </c>
       <c r="D246" s="45" t="s">
-        <v>1710</v>
+        <v>1728</v>
       </c>
       <c r="E246" s="7">
         <v>7</v>
       </c>
       <c r="F246" s="7" t="s">
-        <v>1711</v>
+        <v>1729</v>
       </c>
       <c r="G246" s="41" t="s">
         <v>1279</v>
@@ -24229,13 +24293,13 @@
       <c r="Q246" s="3">
         <v>100</v>
       </c>
-      <c r="R246" s="19">
-        <f>R245+9</f>
-        <v>1183</v>
+      <c r="R246" s="9">
+        <f t="shared" si="97"/>
+        <v>1217</v>
       </c>
       <c r="S246" s="19">
-        <f>S245+10</f>
-        <v>1506</v>
+        <f t="shared" si="99"/>
+        <v>1606</v>
       </c>
       <c r="T246" s="19">
         <v>99.99</v>
@@ -24255,22 +24319,22 @@
     </row>
     <row r="247" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A247" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="B247" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="C247" s="45" t="s">
-        <v>1712</v>
+        <v>1730</v>
       </c>
       <c r="D247" s="45" t="s">
-        <v>1713</v>
+        <v>1731</v>
       </c>
       <c r="E247" s="7">
         <v>7</v>
       </c>
       <c r="F247" s="7" t="s">
-        <v>1714</v>
+        <v>1732</v>
       </c>
       <c r="G247" s="41" t="s">
         <v>1279</v>
@@ -24305,13 +24369,13 @@
       <c r="Q247" s="3">
         <v>100</v>
       </c>
-      <c r="R247" s="19">
-        <f>R246+9</f>
-        <v>1192</v>
+      <c r="R247" s="9">
+        <f t="shared" si="97"/>
+        <v>1235</v>
       </c>
       <c r="S247" s="19">
-        <f>S246+10</f>
-        <v>1516</v>
+        <f t="shared" si="99"/>
+        <v>1616</v>
       </c>
       <c r="T247" s="19">
         <v>99.99</v>
@@ -24331,22 +24395,22 @@
     </row>
     <row r="248" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A248" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="B248" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="C248" s="45" t="s">
-        <v>1715</v>
+        <v>1733</v>
       </c>
       <c r="D248" s="45" t="s">
-        <v>1716</v>
+        <v>1734</v>
       </c>
       <c r="E248" s="7">
         <v>7</v>
       </c>
       <c r="F248" s="7" t="s">
-        <v>1717</v>
+        <v>1735</v>
       </c>
       <c r="G248" s="41" t="s">
         <v>1279</v>
@@ -24381,13 +24445,13 @@
       <c r="Q248" s="3">
         <v>100</v>
       </c>
-      <c r="R248" s="19">
-        <f>R247+9</f>
-        <v>1201</v>
+      <c r="R248" s="9">
+        <f t="shared" si="97"/>
+        <v>1253</v>
       </c>
       <c r="S248" s="19">
-        <f>S247+10</f>
-        <v>1526</v>
+        <f t="shared" si="99"/>
+        <v>1626</v>
       </c>
       <c r="T248" s="19">
         <v>99.99</v>
@@ -24407,22 +24471,22 @@
     </row>
     <row r="249" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A249" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="B249" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="C249" s="45" t="s">
-        <v>1718</v>
+        <v>1736</v>
       </c>
       <c r="D249" s="45" t="s">
-        <v>1719</v>
+        <v>1737</v>
       </c>
       <c r="E249" s="7">
         <v>7</v>
       </c>
       <c r="F249" s="7" t="s">
-        <v>1720</v>
+        <v>1738</v>
       </c>
       <c r="G249" s="41" t="s">
         <v>1279</v>
@@ -24457,13 +24521,13 @@
       <c r="Q249" s="3">
         <v>100</v>
       </c>
-      <c r="R249" s="19">
-        <f>R248+9</f>
-        <v>1210</v>
+      <c r="R249" s="9">
+        <f t="shared" si="97"/>
+        <v>1271</v>
       </c>
       <c r="S249" s="19">
-        <f>S248+10</f>
-        <v>1536</v>
+        <f t="shared" si="99"/>
+        <v>1636</v>
       </c>
       <c r="T249" s="19">
         <v>99.99</v>
@@ -24483,22 +24547,22 @@
     </row>
     <row r="250" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A250" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="B250" s="8" t="s">
-        <v>1678</v>
+        <v>1711</v>
       </c>
       <c r="C250" s="45" t="s">
-        <v>1721</v>
+        <v>1739</v>
       </c>
       <c r="D250" s="45" t="s">
-        <v>1722</v>
+        <v>1740</v>
       </c>
       <c r="E250" s="7">
         <v>7</v>
       </c>
       <c r="F250" s="7" t="s">
-        <v>1723</v>
+        <v>1741</v>
       </c>
       <c r="G250" s="41" t="s">
         <v>1279</v>
@@ -24533,13 +24597,13 @@
       <c r="Q250" s="3">
         <v>100</v>
       </c>
-      <c r="R250" s="19">
-        <f>R249+9</f>
-        <v>1219</v>
+      <c r="R250" s="9">
+        <f t="shared" si="97"/>
+        <v>1289</v>
       </c>
       <c r="S250" s="19">
-        <f>S249+10</f>
-        <v>1546</v>
+        <f t="shared" si="99"/>
+        <v>1646</v>
       </c>
       <c r="T250" s="19">
         <v>99.99</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2541" uniqueCount="1742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2531" uniqueCount="1774">
   <si>
     <t>ID</t>
   </si>
@@ -5223,54 +5223,105 @@
     <t>67000000000000</t>
   </si>
   <si>
+    <t>10235</t>
+  </si>
+  <si>
+    <t>1235</t>
+  </si>
+  <si>
+    <t>虚无烈焰王</t>
+  </si>
+  <si>
+    <t>1E+281</t>
+  </si>
+  <si>
+    <t>1E+306</t>
+  </si>
+  <si>
+    <t>68000000000000</t>
+  </si>
+  <si>
+    <t>10236</t>
+  </si>
+  <si>
+    <t>1236</t>
+  </si>
+  <si>
+    <t>虚无大邪王</t>
+  </si>
+  <si>
+    <t>1E+309</t>
+  </si>
+  <si>
+    <t>1E+171</t>
+  </si>
+  <si>
+    <t>1E+274</t>
+  </si>
+  <si>
+    <t>69000000000000</t>
+  </si>
+  <si>
+    <t>10237</t>
+  </si>
+  <si>
+    <t>1237</t>
+  </si>
+  <si>
+    <t>虚无尸魔王</t>
+  </si>
+  <si>
+    <t>1E+283</t>
+  </si>
+  <si>
+    <t>1E+312</t>
+  </si>
+  <si>
+    <t>1E+174</t>
+  </si>
+  <si>
+    <t>70000000000000</t>
+  </si>
+  <si>
+    <t>10238</t>
+  </si>
+  <si>
+    <t>1238</t>
+  </si>
+  <si>
+    <t>虚无骨魔王</t>
+  </si>
+  <si>
+    <t>1E+284</t>
+  </si>
+  <si>
+    <t>1E+315</t>
+  </si>
+  <si>
+    <t>1E+177</t>
+  </si>
+  <si>
+    <t>72000000000000</t>
+  </si>
+  <si>
+    <t>10239</t>
+  </si>
+  <si>
+    <t>1239</t>
+  </si>
+  <si>
+    <t>虚无牛魔王</t>
+  </si>
+  <si>
+    <t>1E+318</t>
+  </si>
+  <si>
+    <t>74000000000000</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
-    <t>10235</t>
-  </si>
-  <si>
-    <t>1235</t>
-  </si>
-  <si>
-    <t>虚无烈焰王</t>
-  </si>
-  <si>
-    <t>10236</t>
-  </si>
-  <si>
-    <t>1236</t>
-  </si>
-  <si>
-    <t>虚无大邪王</t>
-  </si>
-  <si>
-    <t>10237</t>
-  </si>
-  <si>
-    <t>1237</t>
-  </si>
-  <si>
-    <t>虚无尸魔王</t>
-  </si>
-  <si>
-    <t>10238</t>
-  </si>
-  <si>
-    <t>1238</t>
-  </si>
-  <si>
-    <t>虚无骨魔王</t>
-  </si>
-  <si>
-    <t>10239</t>
-  </si>
-  <si>
-    <t>1239</t>
-  </si>
-  <si>
-    <t>虚无牛魔王</t>
-  </si>
-  <si>
     <t>10240</t>
   </si>
   <si>
@@ -5280,6 +5331,18 @@
     <t>虚无水龙王</t>
   </si>
   <si>
+    <t>1E+286</t>
+  </si>
+  <si>
+    <t>1E+321</t>
+  </si>
+  <si>
+    <t>1E+183</t>
+  </si>
+  <si>
+    <t>76000000000000</t>
+  </si>
+  <si>
     <t>10241</t>
   </si>
   <si>
@@ -5289,6 +5352,18 @@
     <t>虚无土龙王</t>
   </si>
   <si>
+    <t>1E+287</t>
+  </si>
+  <si>
+    <t>1E+324</t>
+  </si>
+  <si>
+    <t>1E+186</t>
+  </si>
+  <si>
+    <t>78000000000000</t>
+  </si>
+  <si>
     <t>10242</t>
   </si>
   <si>
@@ -5298,6 +5373,12 @@
     <t>虚无毒龙王</t>
   </si>
   <si>
+    <t>1E+327</t>
+  </si>
+  <si>
+    <t>1E+189</t>
+  </si>
+  <si>
     <t>10243</t>
   </si>
   <si>
@@ -5307,6 +5388,12 @@
     <t>虚无火龙王</t>
   </si>
   <si>
+    <t>1E+289</t>
+  </si>
+  <si>
+    <t>1E+330</t>
+  </si>
+  <si>
     <t>10244</t>
   </si>
   <si>
@@ -5314,6 +5401,15 @@
   </si>
   <si>
     <t>虚无冰龙王</t>
+  </si>
+  <si>
+    <t>1E+290</t>
+  </si>
+  <si>
+    <t>1E+333</t>
+  </si>
+  <si>
+    <t>84000000000000</t>
   </si>
 </sst>
 </file>
@@ -5504,12 +5600,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -20816,7 +20912,7 @@
         <v>201</v>
       </c>
       <c r="R201" s="8">
-        <f>R200+15</f>
+        <f t="shared" ref="R201:R215" si="82">R200+15</f>
         <v>449</v>
       </c>
       <c r="S201" s="8">
@@ -20892,11 +20988,11 @@
         <v>207</v>
       </c>
       <c r="R202" s="9">
-        <f>R201+15</f>
+        <f t="shared" si="82"/>
         <v>464</v>
       </c>
       <c r="S202" s="9">
-        <f t="shared" ref="S201:S215" si="82">S201+15</f>
+        <f t="shared" ref="S201:S215" si="83">S201+15</f>
         <v>576</v>
       </c>
       <c r="T202" s="9">
@@ -20968,11 +21064,11 @@
         <v>213</v>
       </c>
       <c r="R203" s="9">
-        <f>R202+15</f>
+        <f t="shared" si="82"/>
         <v>479</v>
       </c>
       <c r="S203" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>591</v>
       </c>
       <c r="T203" s="9">
@@ -21044,11 +21140,11 @@
         <v>219</v>
       </c>
       <c r="R204" s="9">
-        <f>R203+15</f>
+        <f t="shared" si="82"/>
         <v>494</v>
       </c>
       <c r="S204" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>606</v>
       </c>
       <c r="T204" s="9">
@@ -21120,11 +21216,11 @@
         <v>225</v>
       </c>
       <c r="R205" s="9">
-        <f>R204+15</f>
+        <f t="shared" si="82"/>
         <v>509</v>
       </c>
       <c r="S205" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>621</v>
       </c>
       <c r="T205" s="9">
@@ -21178,19 +21274,19 @@
         <v>1445</v>
       </c>
       <c r="M206" s="6">
-        <f t="shared" ref="M206:M215" si="83">M205+10000</f>
+        <f t="shared" ref="M206:M215" si="84">M205+10000</f>
         <v>91000</v>
       </c>
       <c r="N206" s="6">
-        <f t="shared" ref="N206:N215" si="84">N205+10000</f>
+        <f t="shared" ref="N206:N215" si="85">N205+10000</f>
         <v>91000</v>
       </c>
       <c r="O206" s="6">
-        <f t="shared" ref="O206:O215" si="85">O205+10000</f>
+        <f t="shared" ref="O206:O215" si="86">O205+10000</f>
         <v>62750</v>
       </c>
       <c r="P206" s="6">
-        <f t="shared" ref="P206:P215" si="86">P205+10000</f>
+        <f t="shared" ref="P206:P215" si="87">P205+10000</f>
         <v>62750</v>
       </c>
       <c r="Q206" s="6">
@@ -21198,11 +21294,11 @@
         <v>231</v>
       </c>
       <c r="R206" s="9">
-        <f>R205+15</f>
+        <f t="shared" si="82"/>
         <v>524</v>
       </c>
       <c r="S206" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>636</v>
       </c>
       <c r="T206" s="8">
@@ -21257,19 +21353,19 @@
         <v>1357</v>
       </c>
       <c r="M207" s="7">
-        <f t="shared" si="83"/>
-        <v>101000</v>
-      </c>
-      <c r="N207" s="7">
         <f t="shared" si="84"/>
         <v>101000</v>
       </c>
+      <c r="N207" s="7">
+        <f t="shared" si="85"/>
+        <v>101000</v>
+      </c>
       <c r="O207" s="7">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>72750</v>
       </c>
       <c r="P207" s="7">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>72750</v>
       </c>
       <c r="Q207" s="6">
@@ -21277,11 +21373,11 @@
         <v>237</v>
       </c>
       <c r="R207" s="9">
-        <f>R206+15</f>
+        <f t="shared" si="82"/>
         <v>539</v>
       </c>
       <c r="S207" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>651</v>
       </c>
       <c r="T207" s="9">
@@ -21336,19 +21432,19 @@
         <v>1458</v>
       </c>
       <c r="M208" s="7">
-        <f t="shared" si="83"/>
-        <v>111000</v>
-      </c>
-      <c r="N208" s="7">
         <f t="shared" si="84"/>
         <v>111000</v>
       </c>
+      <c r="N208" s="7">
+        <f t="shared" si="85"/>
+        <v>111000</v>
+      </c>
       <c r="O208" s="7">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>82750</v>
       </c>
       <c r="P208" s="7">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>82750</v>
       </c>
       <c r="Q208" s="6">
@@ -21356,11 +21452,11 @@
         <v>243</v>
       </c>
       <c r="R208" s="9">
-        <f>R207+15</f>
+        <f t="shared" si="82"/>
         <v>554</v>
       </c>
       <c r="S208" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>666</v>
       </c>
       <c r="T208" s="9">
@@ -21415,19 +21511,19 @@
         <v>1466</v>
       </c>
       <c r="M209" s="7">
-        <f t="shared" si="83"/>
-        <v>121000</v>
-      </c>
-      <c r="N209" s="7">
         <f t="shared" si="84"/>
         <v>121000</v>
       </c>
+      <c r="N209" s="7">
+        <f t="shared" si="85"/>
+        <v>121000</v>
+      </c>
       <c r="O209" s="7">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>92750</v>
       </c>
       <c r="P209" s="7">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>92750</v>
       </c>
       <c r="Q209" s="6">
@@ -21435,11 +21531,11 @@
         <v>249</v>
       </c>
       <c r="R209" s="9">
-        <f>R208+15</f>
+        <f t="shared" si="82"/>
         <v>569</v>
       </c>
       <c r="S209" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>681</v>
       </c>
       <c r="T209" s="9">
@@ -21494,19 +21590,19 @@
         <v>1472</v>
       </c>
       <c r="M210" s="7">
-        <f t="shared" si="83"/>
-        <v>131000</v>
-      </c>
-      <c r="N210" s="7">
         <f t="shared" si="84"/>
         <v>131000</v>
       </c>
+      <c r="N210" s="7">
+        <f t="shared" si="85"/>
+        <v>131000</v>
+      </c>
       <c r="O210" s="7">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>102750</v>
       </c>
       <c r="P210" s="7">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>102750</v>
       </c>
       <c r="Q210" s="6">
@@ -21514,11 +21610,11 @@
         <v>255</v>
       </c>
       <c r="R210" s="9">
-        <f>R209+15</f>
+        <f t="shared" si="82"/>
         <v>584</v>
       </c>
       <c r="S210" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>696</v>
       </c>
       <c r="T210" s="9">
@@ -21573,19 +21669,19 @@
         <v>1480</v>
       </c>
       <c r="M211" s="7">
-        <f t="shared" ref="M211:M220" si="87">M210+20000</f>
+        <f t="shared" ref="M211:M220" si="88">M210+20000</f>
         <v>151000</v>
       </c>
       <c r="N211" s="7">
-        <f t="shared" ref="N211:N220" si="88">N210+20000</f>
+        <f t="shared" ref="N211:N220" si="89">N210+20000</f>
         <v>151000</v>
       </c>
       <c r="O211" s="7">
-        <f t="shared" ref="O211:O220" si="89">O210+20000</f>
+        <f t="shared" ref="O211:O220" si="90">O210+20000</f>
         <v>122750</v>
       </c>
       <c r="P211" s="7">
-        <f t="shared" ref="P211:P220" si="90">P210+20000</f>
+        <f t="shared" ref="P211:P220" si="91">P210+20000</f>
         <v>122750</v>
       </c>
       <c r="Q211" s="6">
@@ -21593,11 +21689,11 @@
         <v>261</v>
       </c>
       <c r="R211" s="9">
-        <f>R210+15</f>
+        <f t="shared" si="82"/>
         <v>599</v>
       </c>
       <c r="S211" s="9">
-        <f t="shared" ref="S211:S220" si="91">S210+20</f>
+        <f t="shared" ref="S211:S220" si="92">S210+20</f>
         <v>716</v>
       </c>
       <c r="T211" s="9">
@@ -21652,19 +21748,19 @@
         <v>1486</v>
       </c>
       <c r="M212" s="7">
-        <f t="shared" si="87"/>
-        <v>171000</v>
-      </c>
-      <c r="N212" s="7">
         <f t="shared" si="88"/>
         <v>171000</v>
       </c>
+      <c r="N212" s="7">
+        <f t="shared" si="89"/>
+        <v>171000</v>
+      </c>
       <c r="O212" s="7">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>142750</v>
       </c>
       <c r="P212" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>142750</v>
       </c>
       <c r="Q212" s="6">
@@ -21672,11 +21768,11 @@
         <v>267</v>
       </c>
       <c r="R212" s="9">
-        <f>R211+15</f>
+        <f t="shared" si="82"/>
         <v>614</v>
       </c>
       <c r="S212" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>736</v>
       </c>
       <c r="T212" s="9">
@@ -21731,19 +21827,19 @@
         <v>1494</v>
       </c>
       <c r="M213" s="7">
-        <f t="shared" si="87"/>
-        <v>191000</v>
-      </c>
-      <c r="N213" s="7">
         <f t="shared" si="88"/>
         <v>191000</v>
       </c>
+      <c r="N213" s="7">
+        <f t="shared" si="89"/>
+        <v>191000</v>
+      </c>
       <c r="O213" s="7">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>162750</v>
       </c>
       <c r="P213" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>162750</v>
       </c>
       <c r="Q213" s="6">
@@ -21751,11 +21847,11 @@
         <v>273</v>
       </c>
       <c r="R213" s="9">
-        <f>R212+15</f>
+        <f t="shared" si="82"/>
         <v>629</v>
       </c>
       <c r="S213" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>756</v>
       </c>
       <c r="T213" s="9">
@@ -21810,19 +21906,19 @@
         <v>1501</v>
       </c>
       <c r="M214" s="7">
-        <f t="shared" si="87"/>
-        <v>211000</v>
-      </c>
-      <c r="N214" s="7">
         <f t="shared" si="88"/>
         <v>211000</v>
       </c>
+      <c r="N214" s="7">
+        <f t="shared" si="89"/>
+        <v>211000</v>
+      </c>
       <c r="O214" s="7">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>182750</v>
       </c>
       <c r="P214" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>182750</v>
       </c>
       <c r="Q214" s="6">
@@ -21830,11 +21926,11 @@
         <v>279</v>
       </c>
       <c r="R214" s="9">
-        <f>R213+15</f>
+        <f t="shared" si="82"/>
         <v>644</v>
       </c>
       <c r="S214" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>776</v>
       </c>
       <c r="T214" s="9">
@@ -21889,19 +21985,19 @@
         <v>1509</v>
       </c>
       <c r="M215" s="7">
-        <f t="shared" si="87"/>
-        <v>231000</v>
-      </c>
-      <c r="N215" s="7">
         <f t="shared" si="88"/>
         <v>231000</v>
       </c>
+      <c r="N215" s="7">
+        <f t="shared" si="89"/>
+        <v>231000</v>
+      </c>
       <c r="O215" s="7">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>202750</v>
       </c>
       <c r="P215" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>202750</v>
       </c>
       <c r="Q215" s="6">
@@ -21909,11 +22005,11 @@
         <v>285</v>
       </c>
       <c r="R215" s="9">
-        <f>R214+15</f>
+        <f t="shared" si="82"/>
         <v>659</v>
       </c>
       <c r="S215" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>796</v>
       </c>
       <c r="T215" s="9">
@@ -21968,31 +22064,31 @@
         <v>1555</v>
       </c>
       <c r="M216" s="28">
-        <f t="shared" ref="M216:M240" si="92">M215+30000</f>
+        <f t="shared" ref="M216:M250" si="93">M215+30000</f>
         <v>261000</v>
       </c>
       <c r="N216" s="28">
-        <f t="shared" ref="N216:N240" si="93">N215+30000</f>
+        <f t="shared" ref="N216:N250" si="94">N215+30000</f>
         <v>261000</v>
       </c>
       <c r="O216" s="28">
-        <f t="shared" ref="O216:O240" si="94">O215+30000</f>
+        <f t="shared" ref="O216:O250" si="95">O215+30000</f>
         <v>232750</v>
       </c>
       <c r="P216" s="28">
-        <f t="shared" ref="P216:P240" si="95">P215+30000</f>
+        <f t="shared" ref="P216:P250" si="96">P215+30000</f>
         <v>232750</v>
       </c>
       <c r="Q216" s="28">
-        <f t="shared" ref="Q216:Q240" si="96">Q215+7</f>
+        <f t="shared" ref="Q216:Q250" si="97">Q215+7</f>
         <v>292</v>
       </c>
       <c r="R216" s="9">
-        <f t="shared" ref="R216:R250" si="97">R215+18</f>
+        <f t="shared" ref="R216:R250" si="98">R215+18</f>
         <v>677</v>
       </c>
       <c r="S216" s="27">
-        <f t="shared" ref="S216:S240" si="98">S215+30</f>
+        <f t="shared" ref="S216:S250" si="99">S215+30</f>
         <v>826</v>
       </c>
       <c r="T216" s="27">
@@ -22045,31 +22141,31 @@
         <v>1398</v>
       </c>
       <c r="M217" s="7">
-        <f t="shared" si="92"/>
-        <v>291000</v>
-      </c>
-      <c r="N217" s="7">
         <f t="shared" si="93"/>
         <v>291000</v>
       </c>
+      <c r="N217" s="7">
+        <f t="shared" si="94"/>
+        <v>291000</v>
+      </c>
       <c r="O217" s="7">
-        <f t="shared" si="94"/>
-        <v>262750</v>
-      </c>
-      <c r="P217" s="7">
         <f t="shared" si="95"/>
         <v>262750</v>
       </c>
+      <c r="P217" s="7">
+        <f t="shared" si="96"/>
+        <v>262750</v>
+      </c>
       <c r="Q217" s="6">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>299</v>
       </c>
       <c r="R217" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>695</v>
       </c>
       <c r="S217" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>856</v>
       </c>
       <c r="T217" s="9">
@@ -22122,31 +22218,31 @@
         <v>1415</v>
       </c>
       <c r="M218" s="7">
-        <f t="shared" si="92"/>
-        <v>321000</v>
-      </c>
-      <c r="N218" s="7">
         <f t="shared" si="93"/>
         <v>321000</v>
       </c>
+      <c r="N218" s="7">
+        <f t="shared" si="94"/>
+        <v>321000</v>
+      </c>
       <c r="O218" s="7">
-        <f t="shared" si="94"/>
-        <v>292750</v>
-      </c>
-      <c r="P218" s="7">
         <f t="shared" si="95"/>
         <v>292750</v>
       </c>
+      <c r="P218" s="7">
+        <f t="shared" si="96"/>
+        <v>292750</v>
+      </c>
       <c r="Q218" s="6">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>306</v>
       </c>
       <c r="R218" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>713</v>
       </c>
       <c r="S218" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>886</v>
       </c>
       <c r="T218" s="9">
@@ -22199,31 +22295,31 @@
         <v>1576</v>
       </c>
       <c r="M219" s="7">
-        <f t="shared" si="92"/>
-        <v>351000</v>
-      </c>
-      <c r="N219" s="7">
         <f t="shared" si="93"/>
         <v>351000</v>
       </c>
+      <c r="N219" s="7">
+        <f t="shared" si="94"/>
+        <v>351000</v>
+      </c>
       <c r="O219" s="7">
-        <f t="shared" si="94"/>
-        <v>322750</v>
-      </c>
-      <c r="P219" s="7">
         <f t="shared" si="95"/>
         <v>322750</v>
       </c>
+      <c r="P219" s="7">
+        <f t="shared" si="96"/>
+        <v>322750</v>
+      </c>
       <c r="Q219" s="6">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>313</v>
       </c>
       <c r="R219" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>731</v>
       </c>
       <c r="S219" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>916</v>
       </c>
       <c r="T219" s="9">
@@ -22274,31 +22370,31 @@
         <v>1453</v>
       </c>
       <c r="M220" s="7">
-        <f t="shared" si="92"/>
-        <v>381000</v>
-      </c>
-      <c r="N220" s="7">
         <f t="shared" si="93"/>
         <v>381000</v>
       </c>
+      <c r="N220" s="7">
+        <f t="shared" si="94"/>
+        <v>381000</v>
+      </c>
       <c r="O220" s="7">
-        <f t="shared" si="94"/>
-        <v>352750</v>
-      </c>
-      <c r="P220" s="7">
         <f t="shared" si="95"/>
         <v>352750</v>
       </c>
+      <c r="P220" s="7">
+        <f t="shared" si="96"/>
+        <v>352750</v>
+      </c>
       <c r="Q220" s="6">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>320</v>
       </c>
       <c r="R220" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>749</v>
       </c>
       <c r="S220" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>946</v>
       </c>
       <c r="T220" s="9">
@@ -22351,31 +22447,31 @@
         <v>1560</v>
       </c>
       <c r="M221" s="7">
-        <f t="shared" si="92"/>
-        <v>411000</v>
-      </c>
-      <c r="N221" s="7">
         <f t="shared" si="93"/>
         <v>411000</v>
       </c>
+      <c r="N221" s="7">
+        <f t="shared" si="94"/>
+        <v>411000</v>
+      </c>
       <c r="O221" s="7">
-        <f t="shared" si="94"/>
-        <v>382750</v>
-      </c>
-      <c r="P221" s="7">
         <f t="shared" si="95"/>
         <v>382750</v>
       </c>
+      <c r="P221" s="7">
+        <f t="shared" si="96"/>
+        <v>382750</v>
+      </c>
       <c r="Q221" s="6">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>327</v>
       </c>
       <c r="R221" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>767</v>
       </c>
       <c r="S221" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>976</v>
       </c>
       <c r="T221" s="9">
@@ -22428,31 +22524,31 @@
         <v>1487</v>
       </c>
       <c r="M222" s="7">
-        <f t="shared" si="92"/>
-        <v>441000</v>
-      </c>
-      <c r="N222" s="7">
         <f t="shared" si="93"/>
         <v>441000</v>
       </c>
+      <c r="N222" s="7">
+        <f t="shared" si="94"/>
+        <v>441000</v>
+      </c>
       <c r="O222" s="7">
-        <f t="shared" si="94"/>
-        <v>412750</v>
-      </c>
-      <c r="P222" s="7">
         <f t="shared" si="95"/>
         <v>412750</v>
       </c>
+      <c r="P222" s="7">
+        <f t="shared" si="96"/>
+        <v>412750</v>
+      </c>
       <c r="Q222" s="6">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>334</v>
       </c>
       <c r="R222" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>785</v>
       </c>
       <c r="S222" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>1006</v>
       </c>
       <c r="T222" s="9">
@@ -22506,31 +22602,31 @@
         <v>1572</v>
       </c>
       <c r="M223" s="7">
-        <f t="shared" si="92"/>
-        <v>471000</v>
-      </c>
-      <c r="N223" s="7">
         <f t="shared" si="93"/>
         <v>471000</v>
       </c>
+      <c r="N223" s="7">
+        <f t="shared" si="94"/>
+        <v>471000</v>
+      </c>
       <c r="O223" s="7">
-        <f t="shared" si="94"/>
-        <v>442750</v>
-      </c>
-      <c r="P223" s="7">
         <f t="shared" si="95"/>
         <v>442750</v>
       </c>
+      <c r="P223" s="7">
+        <f t="shared" si="96"/>
+        <v>442750</v>
+      </c>
       <c r="Q223" s="6">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>341</v>
       </c>
       <c r="R223" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>803</v>
       </c>
       <c r="S223" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>1036</v>
       </c>
       <c r="T223" s="9">
@@ -22584,31 +22680,31 @@
         <v>1522</v>
       </c>
       <c r="M224" s="7">
-        <f t="shared" si="92"/>
-        <v>501000</v>
-      </c>
-      <c r="N224" s="7">
         <f t="shared" si="93"/>
         <v>501000</v>
       </c>
+      <c r="N224" s="7">
+        <f t="shared" si="94"/>
+        <v>501000</v>
+      </c>
       <c r="O224" s="7">
-        <f t="shared" si="94"/>
-        <v>472750</v>
-      </c>
-      <c r="P224" s="7">
         <f t="shared" si="95"/>
         <v>472750</v>
       </c>
+      <c r="P224" s="7">
+        <f t="shared" si="96"/>
+        <v>472750</v>
+      </c>
       <c r="Q224" s="6">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>348</v>
       </c>
       <c r="R224" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>821</v>
       </c>
       <c r="S224" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>1066</v>
       </c>
       <c r="T224" s="9">
@@ -22662,31 +22758,31 @@
         <v>1587</v>
       </c>
       <c r="M225" s="7">
-        <f t="shared" si="92"/>
-        <v>531000</v>
-      </c>
-      <c r="N225" s="7">
         <f t="shared" si="93"/>
         <v>531000</v>
       </c>
+      <c r="N225" s="7">
+        <f t="shared" si="94"/>
+        <v>531000</v>
+      </c>
       <c r="O225" s="7">
-        <f t="shared" si="94"/>
-        <v>502750</v>
-      </c>
-      <c r="P225" s="7">
         <f t="shared" si="95"/>
         <v>502750</v>
       </c>
+      <c r="P225" s="7">
+        <f t="shared" si="96"/>
+        <v>502750</v>
+      </c>
       <c r="Q225" s="6">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>355</v>
       </c>
       <c r="R225" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>839</v>
       </c>
       <c r="S225" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>1096</v>
       </c>
       <c r="T225" s="9">
@@ -22740,31 +22836,31 @@
         <v>1593</v>
       </c>
       <c r="M226" s="7">
-        <f t="shared" si="92"/>
-        <v>561000</v>
-      </c>
-      <c r="N226" s="7">
         <f t="shared" si="93"/>
         <v>561000</v>
       </c>
+      <c r="N226" s="7">
+        <f t="shared" si="94"/>
+        <v>561000</v>
+      </c>
       <c r="O226" s="7">
-        <f t="shared" si="94"/>
-        <v>532750</v>
-      </c>
-      <c r="P226" s="7">
         <f t="shared" si="95"/>
         <v>532750</v>
       </c>
+      <c r="P226" s="7">
+        <f t="shared" si="96"/>
+        <v>532750</v>
+      </c>
       <c r="Q226" s="6">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>362</v>
       </c>
       <c r="R226" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>857</v>
       </c>
       <c r="S226" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>1126</v>
       </c>
       <c r="T226" s="